--- a/plan-des-livres.xlsx
+++ b/plan-des-livres.xlsx
@@ -13,7 +13,7 @@
     <sheet name="Plan par livre" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Chapitres'!$A$1:$M$221</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Chapitres'!$A$1:$M$223</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -951,7 +951,7 @@
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>exploratoire</t>
+          <t>en-cours</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -960,7 +960,7 @@
         </is>
       </c>
       <c r="F12" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G12" s="5" t="inlineStr"/>
       <c r="H12" s="5" t="inlineStr">
@@ -1354,7 +1354,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M221"/>
+  <dimension ref="A1:M223"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -11414,17 +11414,17 @@
     <row r="162">
       <c r="A162" s="2" t="inlineStr">
         <is>
-          <t>L11.C01</t>
+          <t>L10.C02</t>
         </is>
       </c>
       <c r="B162" s="3" t="inlineStr">
         <is>
-          <t>L11</t>
+          <t>L10</t>
         </is>
       </c>
       <c r="C162" s="3" t="inlineStr">
         <is>
-          <t>Reflux ou destruction — la bifurcation</t>
+          <t>La dérogation existe, et elle referme une tenaille</t>
         </is>
       </c>
       <c r="D162" s="3" t="inlineStr">
@@ -11444,50 +11444,50 @@
       </c>
       <c r="G162" s="3" t="inlineStr">
         <is>
-          <t>conception</t>
+          <t>hybride</t>
         </is>
       </c>
       <c r="H162" s="3" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="I162" s="3" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="J162" s="3" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="K162" s="3" t="inlineStr">
         <is>
-          <t>contrepartie_comptable, reflux_monetaire, creation_monetaire, reflux_transactionnel, monnaie_comme_registre</t>
+          <t>contrepartie_comptable, creation_monetaire, monnaie_comme_registre, architecture_invisible, reflux_collectif</t>
         </is>
       </c>
       <c r="L162" s="3" t="inlineStr">
         <is>
-          <t>L1.C17, L1.C19, L1.C20, L1.C21, L1.C27, L1.C29</t>
+          <t>L1.C20, L1.C29, L5.C02, L10.C01, L18.C01, L18.C06, L18.C07, L20.C02</t>
         </is>
       </c>
       <c r="M162" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-11/c01-reflux-ou-destruction.md</t>
+          <t>corpus/livre-10/c02-la-derogation-existe-et-elle-referme-une-tenaille.md</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" s="2" t="inlineStr">
         <is>
-          <t>L11.C02</t>
+          <t>L10.C03</t>
         </is>
       </c>
       <c r="B163" s="3" t="inlineStr">
         <is>
-          <t>L11</t>
+          <t>L10</t>
         </is>
       </c>
       <c r="C163" s="3" t="inlineStr">
         <is>
-          <t>Le trajet complet de la valeur</t>
+          <t>La certitude qui fait marcher le dispositif est celle que la Cour interdit</t>
         </is>
       </c>
       <c r="D163" s="3" t="inlineStr">
@@ -11507,40 +11507,40 @@
       </c>
       <c r="G163" s="3" t="inlineStr">
         <is>
-          <t>conception</t>
+          <t>hybride</t>
         </is>
       </c>
       <c r="H163" s="3" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="I163" s="3" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J163" s="3" t="n">
         <v>4</v>
       </c>
       <c r="K163" s="3" t="inlineStr">
         <is>
-          <t>contrepartie_comptable, reflux_collectif, reflux_transactionnel, demurrage, creation_monetaire</t>
+          <t>contrepartie_comptable, creation_monetaire, reflux_collectif, qualification_regenerative, regle_contre_discretion, seuil_d_activation</t>
         </is>
       </c>
       <c r="L163" s="3" t="inlineStr">
         <is>
-          <t>L1.C18, L1.C20, L1.C21, L1.C29, L11.C01</t>
+          <t>L1.C20, L1.C27, L1.C29, L10.C01, L10.C02, L11.C13, L18.C06, L20.C02</t>
         </is>
       </c>
       <c r="M163" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-11/c02-le-trajet-complet-de-la-valeur.md</t>
+          <t>corpus/livre-10/c03-la-certitude-qui-fait-marcher-le-dispositif-est-celle-que-la-cour-interdit.md</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" s="2" t="inlineStr">
         <is>
-          <t>L11.C03</t>
+          <t>L11.C01</t>
         </is>
       </c>
       <c r="B164" s="3" t="inlineStr">
@@ -11550,7 +11550,7 @@
       </c>
       <c r="C164" s="3" t="inlineStr">
         <is>
-          <t>Le compte des objectifs et des instruments</t>
+          <t>Reflux ou destruction — la bifurcation</t>
         </is>
       </c>
       <c r="D164" s="3" t="inlineStr">
@@ -11575,35 +11575,35 @@
       </c>
       <c r="H164" s="3" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="I164" s="3" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="J164" s="3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K164" s="3" t="inlineStr">
         <is>
-          <t>affectation_des_instruments, bareme, effet_veblen, reflux_collectif, reflux_transactionnel, demurrage, degeneratif, qualification_regenerative</t>
+          <t>contrepartie_comptable, reflux_monetaire, creation_monetaire, reflux_transactionnel, monnaie_comme_registre</t>
         </is>
       </c>
       <c r="L164" s="3" t="inlineStr">
         <is>
-          <t>L1.C18, L1.C20, L1.C21, L1.C26, L1.C28, L11.C01, L11.C02, L11.C04, L11.C05, L11.C06, L11.C07, L11.C09, L11.C10, L11.C11</t>
+          <t>L1.C17, L1.C19, L1.C20, L1.C21, L1.C27, L1.C29</t>
         </is>
       </c>
       <c r="M164" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-11/c03-le-compte-des-objectifs-et-des-instruments.md</t>
+          <t>corpus/livre-11/c01-reflux-ou-destruction.md</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" s="2" t="inlineStr">
         <is>
-          <t>L11.C04</t>
+          <t>L11.C02</t>
         </is>
       </c>
       <c r="B165" s="3" t="inlineStr">
@@ -11613,7 +11613,7 @@
       </c>
       <c r="C165" s="3" t="inlineStr">
         <is>
-          <t>Les instruments du reflux sous parité fixe</t>
+          <t>Le trajet complet de la valeur</t>
         </is>
       </c>
       <c r="D165" s="3" t="inlineStr">
@@ -11638,35 +11638,35 @@
       </c>
       <c r="H165" s="3" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="I165" s="3" t="n">
         <v>5</v>
       </c>
       <c r="J165" s="3" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K165" s="3" t="inlineStr">
         <is>
-          <t>referentiel_de_change, demurrage, reflux_transactionnel, reflux_collectif, bareme, affectation_des_instruments, creation_monetaire</t>
+          <t>contrepartie_comptable, reflux_collectif, reflux_transactionnel, demurrage, creation_monetaire</t>
         </is>
       </c>
       <c r="L165" s="3" t="inlineStr">
         <is>
-          <t>L1.C19, L1.C21, L1.C24, L1.C26, L1.C27, L11.C01, L11.C02, L11.C03</t>
+          <t>L1.C18, L1.C20, L1.C21, L1.C29, L11.C01</t>
         </is>
       </c>
       <c r="M165" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-11/c04-les-instruments-du-reflux-sous-parite-fixe.md</t>
+          <t>corpus/livre-11/c02-le-trajet-complet-de-la-valeur.md</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" s="2" t="inlineStr">
         <is>
-          <t>L11.C05</t>
+          <t>L11.C03</t>
         </is>
       </c>
       <c r="B166" s="3" t="inlineStr">
@@ -11676,7 +11676,7 @@
       </c>
       <c r="C166" s="3" t="inlineStr">
         <is>
-          <t>L'assiette du reflux transactionnel</t>
+          <t>Le compte des objectifs et des instruments</t>
         </is>
       </c>
       <c r="D166" s="3" t="inlineStr">
@@ -11701,35 +11701,35 @@
       </c>
       <c r="H166" s="3" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="I166" s="3" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J166" s="3" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="K166" s="3" t="inlineStr">
         <is>
-          <t>reflux_transactionnel, bareme, degeneratif, reflux_collectif, robustesse, affectation_des_instruments</t>
+          <t>affectation_des_instruments, bareme, effet_veblen, reflux_collectif, reflux_transactionnel, demurrage, degeneratif, qualification_regenerative</t>
         </is>
       </c>
       <c r="L166" s="3" t="inlineStr">
         <is>
-          <t>L1.C18, L1.C21, L1.C23, L11.C02, L11.C03, L11.C04</t>
+          <t>L1.C18, L1.C20, L1.C21, L1.C26, L1.C28, L11.C01, L11.C02, L11.C04, L11.C05, L11.C06, L11.C07, L11.C09, L11.C10, L11.C11</t>
         </is>
       </c>
       <c r="M166" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-11/c05-l-assiette-du-reflux-transactionnel.md</t>
+          <t>corpus/livre-11/c03-le-compte-des-objectifs-et-des-instruments.md</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" s="2" t="inlineStr">
         <is>
-          <t>L11.C06</t>
+          <t>L11.C04</t>
         </is>
       </c>
       <c r="B167" s="3" t="inlineStr">
@@ -11739,7 +11739,7 @@
       </c>
       <c r="C167" s="3" t="inlineStr">
         <is>
-          <t>Le barème par défaut</t>
+          <t>Les instruments du reflux sous parité fixe</t>
         </is>
       </c>
       <c r="D167" s="3" t="inlineStr">
@@ -11764,7 +11764,7 @@
       </c>
       <c r="H167" s="3" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="I167" s="3" t="n">
@@ -11775,24 +11775,24 @@
       </c>
       <c r="K167" s="3" t="inlineStr">
         <is>
-          <t>bareme, qualification_regenerative, degeneratif, reflux_transactionnel, regle_contre_discretion, affectation_des_instruments</t>
+          <t>referentiel_de_change, demurrage, reflux_transactionnel, reflux_collectif, bareme, affectation_des_instruments, creation_monetaire</t>
         </is>
       </c>
       <c r="L167" s="3" t="inlineStr">
         <is>
-          <t>L1.C18, L1.C21, L1.C22, L1.C27, L1.C28, L11.C03, L11.C05</t>
+          <t>L1.C19, L1.C21, L1.C24, L1.C26, L1.C27, L11.C01, L11.C02, L11.C03</t>
         </is>
       </c>
       <c r="M167" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-11/c06-le-bareme-par-defaut.md</t>
+          <t>corpus/livre-11/c04-les-instruments-du-reflux-sous-parite-fixe.md</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" s="2" t="inlineStr">
         <is>
-          <t>L11.C07</t>
+          <t>L11.C05</t>
         </is>
       </c>
       <c r="B168" s="3" t="inlineStr">
@@ -11802,7 +11802,7 @@
       </c>
       <c r="C168" s="3" t="inlineStr">
         <is>
-          <t>Le demurrage et son nœud de prélèvement</t>
+          <t>L'assiette du reflux transactionnel</t>
         </is>
       </c>
       <c r="D168" s="3" t="inlineStr">
@@ -11831,31 +11831,31 @@
         </is>
       </c>
       <c r="I168" s="3" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="J168" s="3" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="K168" s="3" t="inlineStr">
         <is>
-          <t>demurrage, reflux_collectif, reflux_transactionnel, bareme, affectation_des_instruments, referentiel_de_change</t>
+          <t>reflux_transactionnel, bareme, degeneratif, reflux_collectif, robustesse, affectation_des_instruments</t>
         </is>
       </c>
       <c r="L168" s="3" t="inlineStr">
         <is>
-          <t>L1.C21, L1.C26, L11.C02, L11.C03, L11.C04, L11.C05, L11.C06</t>
+          <t>L1.C18, L1.C21, L1.C23, L11.C02, L11.C03, L11.C04</t>
         </is>
       </c>
       <c r="M168" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-11/c07-le-demurrage-et-son-noeud.md</t>
+          <t>corpus/livre-11/c05-l-assiette-du-reflux-transactionnel.md</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" s="2" t="inlineStr">
         <is>
-          <t>L11.C08</t>
+          <t>L11.C06</t>
         </is>
       </c>
       <c r="B169" s="3" t="inlineStr">
@@ -11865,7 +11865,7 @@
       </c>
       <c r="C169" s="3" t="inlineStr">
         <is>
-          <t>Les dérogations</t>
+          <t>Le barème par défaut</t>
         </is>
       </c>
       <c r="D169" s="3" t="inlineStr">
@@ -11901,24 +11901,24 @@
       </c>
       <c r="K169" s="3" t="inlineStr">
         <is>
-          <t>demurrage, reflux_transactionnel, bareme, qualification_regenerative, reflux_collectif, degeneratif</t>
+          <t>bareme, qualification_regenerative, degeneratif, reflux_transactionnel, regle_contre_discretion, affectation_des_instruments</t>
         </is>
       </c>
       <c r="L169" s="3" t="inlineStr">
         <is>
-          <t>L1.C18, L1.C20, L1.C21, L1.C22, L11.C03, L11.C05, L11.C06, L11.C07</t>
+          <t>L1.C18, L1.C21, L1.C22, L1.C27, L1.C28, L11.C03, L11.C05</t>
         </is>
       </c>
       <c r="M169" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-11/c08-les-derogations.md</t>
+          <t>corpus/livre-11/c06-le-bareme-par-defaut.md</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" s="2" t="inlineStr">
         <is>
-          <t>L11.C09</t>
+          <t>L11.C07</t>
         </is>
       </c>
       <c r="B170" s="3" t="inlineStr">
@@ -11928,7 +11928,7 @@
       </c>
       <c r="C170" s="3" t="inlineStr">
         <is>
-          <t>L'incidence — qui paie le reflux</t>
+          <t>Le demurrage et son nœud de prélèvement</t>
         </is>
       </c>
       <c r="D170" s="3" t="inlineStr">
@@ -11964,24 +11964,24 @@
       </c>
       <c r="K170" s="3" t="inlineStr">
         <is>
-          <t>reflux_collectif, reflux_transactionnel, demurrage, bareme, degeneratif, qualification_regenerative</t>
+          <t>demurrage, reflux_collectif, reflux_transactionnel, bareme, affectation_des_instruments, referentiel_de_change</t>
         </is>
       </c>
       <c r="L170" s="3" t="inlineStr">
         <is>
-          <t>L1.C21, L1.C22, L11.C03, L11.C05, L11.C06, L11.C07, L11.C08</t>
+          <t>L1.C21, L1.C26, L11.C02, L11.C03, L11.C04, L11.C05, L11.C06</t>
         </is>
       </c>
       <c r="M170" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-11/c09-l-incidence-qui-paie-le-reflux.md</t>
+          <t>corpus/livre-11/c07-le-demurrage-et-son-noeud.md</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" s="2" t="inlineStr">
         <is>
-          <t>L11.C10</t>
+          <t>L11.C08</t>
         </is>
       </c>
       <c r="B171" s="3" t="inlineStr">
@@ -11991,7 +11991,7 @@
       </c>
       <c r="C171" s="3" t="inlineStr">
         <is>
-          <t>La trajectoire de mise en place</t>
+          <t>Les dérogations</t>
         </is>
       </c>
       <c r="D171" s="3" t="inlineStr">
@@ -12016,35 +12016,35 @@
       </c>
       <c r="H171" s="3" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="I171" s="3" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="J171" s="3" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="K171" s="3" t="inlineStr">
         <is>
-          <t>bareme, regle_contre_discretion, degeneratif, reflux_transactionnel, qualification_regenerative, affectation_des_instruments</t>
+          <t>demurrage, reflux_transactionnel, bareme, qualification_regenerative, reflux_collectif, degeneratif</t>
         </is>
       </c>
       <c r="L171" s="3" t="inlineStr">
         <is>
-          <t>L1.C21, L1.C23, L1.C27, L11.C03, L11.C05, L11.C06, L11.C09</t>
+          <t>L1.C18, L1.C20, L1.C21, L1.C22, L11.C03, L11.C05, L11.C06, L11.C07</t>
         </is>
       </c>
       <c r="M171" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-11/c10-la-trajectoire-de-mise-en-place.md</t>
+          <t>corpus/livre-11/c08-les-derogations.md</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" s="2" t="inlineStr">
         <is>
-          <t>L11.C11</t>
+          <t>L11.C09</t>
         </is>
       </c>
       <c r="B172" s="3" t="inlineStr">
@@ -12054,7 +12054,7 @@
       </c>
       <c r="C172" s="3" t="inlineStr">
         <is>
-          <t>Qui arrête le barème</t>
+          <t>L'incidence — qui paie le reflux</t>
         </is>
       </c>
       <c r="D172" s="3" t="inlineStr">
@@ -12079,35 +12079,35 @@
       </c>
       <c r="H172" s="3" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="I172" s="3" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J172" s="3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K172" s="3" t="inlineStr">
         <is>
-          <t>bareme, affectation_des_instruments, referentiel_de_change, qualification_regenerative, regle_contre_discretion, reflux_collectif</t>
+          <t>reflux_collectif, reflux_transactionnel, demurrage, bareme, degeneratif, qualification_regenerative</t>
         </is>
       </c>
       <c r="L172" s="3" t="inlineStr">
         <is>
-          <t>L1.C18, L1.C22, L1.C26, L1.C27, L11.C04, L11.C06, L11.C08, L11.C10</t>
+          <t>L1.C21, L1.C22, L11.C03, L11.C05, L11.C06, L11.C07, L11.C08</t>
         </is>
       </c>
       <c r="M172" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-11/c11-qui-arrete-le-bareme.md</t>
+          <t>corpus/livre-11/c09-l-incidence-qui-paie-le-reflux.md</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" s="2" t="inlineStr">
         <is>
-          <t>L11.C12</t>
+          <t>L11.C10</t>
         </is>
       </c>
       <c r="B173" s="3" t="inlineStr">
@@ -12117,7 +12117,7 @@
       </c>
       <c r="C173" s="3" t="inlineStr">
         <is>
-          <t>La directive</t>
+          <t>La trajectoire de mise en place</t>
         </is>
       </c>
       <c r="D173" s="3" t="inlineStr">
@@ -12142,35 +12142,35 @@
       </c>
       <c r="H173" s="3" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="I173" s="3" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="J173" s="3" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="K173" s="3" t="inlineStr">
         <is>
-          <t>bareme, regle_contre_discretion, affectation_des_instruments, reflux_collectif, qualification_regenerative</t>
+          <t>bareme, regle_contre_discretion, degeneratif, reflux_transactionnel, qualification_regenerative, affectation_des_instruments</t>
         </is>
       </c>
       <c r="L173" s="3" t="inlineStr">
         <is>
-          <t>L1.C21, L11.C03, L11.C05, L11.C06, L11.C09, L11.C10, L11.C11</t>
+          <t>L1.C21, L1.C23, L1.C27, L11.C03, L11.C05, L11.C06, L11.C09</t>
         </is>
       </c>
       <c r="M173" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-11/c12-la-directive.md</t>
+          <t>corpus/livre-11/c10-la-trajectoire-de-mise-en-place.md</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" s="2" t="inlineStr">
         <is>
-          <t>L11.C13</t>
+          <t>L11.C11</t>
         </is>
       </c>
       <c r="B174" s="3" t="inlineStr">
@@ -12180,7 +12180,7 @@
       </c>
       <c r="C174" s="3" t="inlineStr">
         <is>
-          <t>Le barème de qualification</t>
+          <t>Qui arrête le barème</t>
         </is>
       </c>
       <c r="D174" s="3" t="inlineStr">
@@ -12205,35 +12205,35 @@
       </c>
       <c r="H174" s="3" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="I174" s="3" t="n">
         <v>6</v>
       </c>
       <c r="J174" s="3" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K174" s="3" t="inlineStr">
         <is>
-          <t>qualification_regenerative, bareme, creation_monetaire, additionnalite, degeneratif, essentiel_insolvable</t>
+          <t>bareme, affectation_des_instruments, referentiel_de_change, qualification_regenerative, regle_contre_discretion, reflux_collectif</t>
         </is>
       </c>
       <c r="L174" s="3" t="inlineStr">
         <is>
-          <t>L1.C18, L1.C20, L1.C22, L1.C27, L11.C03, L11.C05, L11.C06, L11.C08, L11.C09, L11.C10, L11.C11, L11.C12</t>
+          <t>L1.C18, L1.C22, L1.C26, L1.C27, L11.C04, L11.C06, L11.C08, L11.C10</t>
         </is>
       </c>
       <c r="M174" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-11/c13-le-bareme-de-qualification.md</t>
+          <t>corpus/livre-11/c11-qui-arrete-le-bareme.md</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" s="2" t="inlineStr">
         <is>
-          <t>L11.C14</t>
+          <t>L11.C12</t>
         </is>
       </c>
       <c r="B175" s="3" t="inlineStr">
@@ -12243,7 +12243,7 @@
       </c>
       <c r="C175" s="3" t="inlineStr">
         <is>
-          <t>Le tableau de bord, ou les données de la directive</t>
+          <t>La directive</t>
         </is>
       </c>
       <c r="D175" s="3" t="inlineStr">
@@ -12279,24 +12279,24 @@
       </c>
       <c r="K175" s="3" t="inlineStr">
         <is>
-          <t>indicateur_de_progres, bareme, regle_contre_discretion, affectation_des_instruments, degeneratif, qualification_regenerative</t>
+          <t>bareme, regle_contre_discretion, affectation_des_instruments, reflux_collectif, qualification_regenerative</t>
         </is>
       </c>
       <c r="L175" s="3" t="inlineStr">
         <is>
-          <t>L1.C21, L1.C28, L11.C03, L11.C05, L11.C11, L11.C12, L11.C13</t>
+          <t>L1.C21, L11.C03, L11.C05, L11.C06, L11.C09, L11.C10, L11.C11</t>
         </is>
       </c>
       <c r="M175" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-11/c14-le-tableau-de-bord.md</t>
+          <t>corpus/livre-11/c12-la-directive.md</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" s="2" t="inlineStr">
         <is>
-          <t>L11.C15</t>
+          <t>L11.C13</t>
         </is>
       </c>
       <c r="B176" s="3" t="inlineStr">
@@ -12306,7 +12306,7 @@
       </c>
       <c r="C176" s="3" t="inlineStr">
         <is>
-          <t>Les parités du référentiel de change</t>
+          <t>Le barème de qualification</t>
         </is>
       </c>
       <c r="D176" s="3" t="inlineStr">
@@ -12331,35 +12331,35 @@
       </c>
       <c r="H176" s="3" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="I176" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="J176" s="3" t="n">
         <v>5</v>
       </c>
-      <c r="J176" s="3" t="n">
-        <v>4</v>
-      </c>
       <c r="K176" s="3" t="inlineStr">
         <is>
-          <t>referentiel_de_change, bareme, indicateur_de_progres, regle_contre_discretion, affectation_des_instruments</t>
+          <t>qualification_regenerative, bareme, creation_monetaire, additionnalite, degeneratif, essentiel_insolvable</t>
         </is>
       </c>
       <c r="L176" s="3" t="inlineStr">
         <is>
-          <t>L1.C24, L1.C25, L1.C26, L1.C28, L11.C01, L11.C04, L11.C10, L11.C12, L11.C14</t>
+          <t>L1.C18, L1.C20, L1.C22, L1.C27, L11.C03, L11.C05, L11.C06, L11.C08, L11.C09, L11.C10, L11.C11, L11.C12</t>
         </is>
       </c>
       <c r="M176" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-11/c15-les-parites-du-referentiel.md</t>
+          <t>corpus/livre-11/c13-le-bareme-de-qualification.md</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" s="2" t="inlineStr">
         <is>
-          <t>L11.C16</t>
+          <t>L11.C14</t>
         </is>
       </c>
       <c r="B177" s="3" t="inlineStr">
@@ -12369,7 +12369,7 @@
       </c>
       <c r="C177" s="3" t="inlineStr">
         <is>
-          <t>La valorisation des communs</t>
+          <t>Le tableau de bord, ou les données de la directive</t>
         </is>
       </c>
       <c r="D177" s="3" t="inlineStr">
@@ -12394,35 +12394,35 @@
       </c>
       <c r="H177" s="3" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="I177" s="3" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J177" s="3" t="n">
         <v>4</v>
       </c>
       <c r="K177" s="3" t="inlineStr">
         <is>
-          <t>valorisation_des_communs, bareme, essentiel_insolvable, polycentricite, affectation_des_instruments, indicateur_de_progres</t>
+          <t>indicateur_de_progres, bareme, regle_contre_discretion, affectation_des_instruments, degeneratif, qualification_regenerative</t>
         </is>
       </c>
       <c r="L177" s="3" t="inlineStr">
         <is>
-          <t>L1.C15, L1.C18, L1.C21, L1.C22, L1.C24, L1.C26, L1.C27, L11.C02, L11.C03, L11.C04, L11.C06, L11.C09, L11.C11, L11.C12, L11.C13, L11.C15</t>
+          <t>L1.C21, L1.C28, L11.C03, L11.C05, L11.C11, L11.C12, L11.C13</t>
         </is>
       </c>
       <c r="M177" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-11/c16-la-valorisation-des-communs.md</t>
+          <t>corpus/livre-11/c14-le-tableau-de-bord.md</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" s="2" t="inlineStr">
         <is>
-          <t>L11.C17</t>
+          <t>L11.C15</t>
         </is>
       </c>
       <c r="B178" s="3" t="inlineStr">
@@ -12432,7 +12432,7 @@
       </c>
       <c r="C178" s="3" t="inlineStr">
         <is>
-          <t>La cohérence des cinq barèmes</t>
+          <t>Les parités du référentiel de change</t>
         </is>
       </c>
       <c r="D178" s="3" t="inlineStr">
@@ -12461,31 +12461,31 @@
         </is>
       </c>
       <c r="I178" s="3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J178" s="3" t="n">
         <v>4</v>
       </c>
       <c r="K178" s="3" t="inlineStr">
         <is>
-          <t>bareme, affectation_des_instruments, regle_contre_discretion, qualification_regenerative, valorisation_des_communs, reflux_transactionnel, referentiel_de_change, indicateur_de_progres, polycentricite</t>
+          <t>referentiel_de_change, bareme, indicateur_de_progres, regle_contre_discretion, affectation_des_instruments</t>
         </is>
       </c>
       <c r="L178" s="3" t="inlineStr">
         <is>
-          <t>L1.C18, L1.C20, L1.C21, L1.C26, L1.C27, L1.C28, L11.C03, L11.C05, L11.C06, L11.C07, L11.C09, L11.C10, L11.C11, L11.C12, L11.C13, L11.C14, L11.C15, L11.C16</t>
+          <t>L1.C24, L1.C25, L1.C26, L1.C28, L11.C01, L11.C04, L11.C10, L11.C12, L11.C14</t>
         </is>
       </c>
       <c r="M178" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-11/c17-la-coherence-des-cinq-baremes.md</t>
+          <t>corpus/livre-11/c15-les-parites-du-referentiel.md</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" s="2" t="inlineStr">
         <is>
-          <t>L11.C18</t>
+          <t>L11.C16</t>
         </is>
       </c>
       <c r="B179" s="3" t="inlineStr">
@@ -12495,7 +12495,7 @@
       </c>
       <c r="C179" s="3" t="inlineStr">
         <is>
-          <t>Le seuil d'exemption</t>
+          <t>La valorisation des communs</t>
         </is>
       </c>
       <c r="D179" s="3" t="inlineStr">
@@ -12520,35 +12520,35 @@
       </c>
       <c r="H179" s="3" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="I179" s="3" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="J179" s="3" t="n">
         <v>4</v>
       </c>
       <c r="K179" s="3" t="inlineStr">
         <is>
-          <t>demurrage, reflux_transactionnel, bareme, regle_contre_discretion, affectation_des_instruments, valorisation_des_communs</t>
+          <t>valorisation_des_communs, bareme, essentiel_insolvable, polycentricite, affectation_des_instruments, indicateur_de_progres</t>
         </is>
       </c>
       <c r="L179" s="3" t="inlineStr">
         <is>
-          <t>L1.C21, L11.C03, L11.C05, L11.C06, L11.C07, L11.C08, L11.C09, L11.C12, L11.C13, L11.C16, L11.C17</t>
+          <t>L1.C15, L1.C18, L1.C21, L1.C22, L1.C24, L1.C26, L1.C27, L11.C02, L11.C03, L11.C04, L11.C06, L11.C09, L11.C11, L11.C12, L11.C13, L11.C15</t>
         </is>
       </c>
       <c r="M179" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-11/c18-le-seuil-d-exemption.md</t>
+          <t>corpus/livre-11/c16-la-valorisation-des-communs.md</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" s="2" t="inlineStr">
         <is>
-          <t>L11.C19</t>
+          <t>L11.C17</t>
         </is>
       </c>
       <c r="B180" s="3" t="inlineStr">
@@ -12558,7 +12558,7 @@
       </c>
       <c r="C180" s="3" t="inlineStr">
         <is>
-          <t>Le recours</t>
+          <t>La cohérence des cinq barèmes</t>
         </is>
       </c>
       <c r="D180" s="3" t="inlineStr">
@@ -12587,31 +12587,31 @@
         </is>
       </c>
       <c r="I180" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J180" s="3" t="n">
         <v>4</v>
       </c>
       <c r="K180" s="3" t="inlineStr">
         <is>
-          <t>bareme, qualification_regenerative, valorisation_des_communs, demurrage, regle_contre_discretion, essentiel_insolvable, affectation_des_instruments</t>
+          <t>bareme, affectation_des_instruments, regle_contre_discretion, qualification_regenerative, valorisation_des_communs, reflux_transactionnel, referentiel_de_change, indicateur_de_progres, polycentricite</t>
         </is>
       </c>
       <c r="L180" s="3" t="inlineStr">
         <is>
-          <t>L1.C18, L11.C03, L11.C06, L11.C08, L11.C09, L11.C11, L11.C12, L11.C13, L11.C16, L11.C17, L11.C18</t>
+          <t>L1.C18, L1.C20, L1.C21, L1.C26, L1.C27, L1.C28, L11.C03, L11.C05, L11.C06, L11.C07, L11.C09, L11.C10, L11.C11, L11.C12, L11.C13, L11.C14, L11.C15, L11.C16</t>
         </is>
       </c>
       <c r="M180" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-11/c19-le-recours.md</t>
+          <t>corpus/livre-11/c17-la-coherence-des-cinq-baremes.md</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" s="2" t="inlineStr">
         <is>
-          <t>L11.C20</t>
+          <t>L11.C18</t>
         </is>
       </c>
       <c r="B181" s="3" t="inlineStr">
@@ -12621,7 +12621,7 @@
       </c>
       <c r="C181" s="3" t="inlineStr">
         <is>
-          <t>L'amendement de la directive</t>
+          <t>Le seuil d'exemption</t>
         </is>
       </c>
       <c r="D181" s="3" t="inlineStr">
@@ -12657,24 +12657,24 @@
       </c>
       <c r="K181" s="3" t="inlineStr">
         <is>
-          <t>bareme, regle_contre_discretion, qualification_regenerative, valorisation_des_communs, referentiel_de_change, affectation_des_instruments</t>
+          <t>demurrage, reflux_transactionnel, bareme, regle_contre_discretion, affectation_des_instruments, valorisation_des_communs</t>
         </is>
       </c>
       <c r="L181" s="3" t="inlineStr">
         <is>
-          <t>L1.C21, L1.C26, L1.C28, L11.C03, L11.C06, L11.C10, L11.C12, L11.C13, L11.C15, L11.C16, L11.C17, L11.C18, L11.C19</t>
+          <t>L1.C21, L11.C03, L11.C05, L11.C06, L11.C07, L11.C08, L11.C09, L11.C12, L11.C13, L11.C16, L11.C17</t>
         </is>
       </c>
       <c r="M181" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-11/c20-l-amendement-de-la-directive.md</t>
+          <t>corpus/livre-11/c18-le-seuil-d-exemption.md</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" s="2" t="inlineStr">
         <is>
-          <t>L11.C21</t>
+          <t>L11.C19</t>
         </is>
       </c>
       <c r="B182" s="3" t="inlineStr">
@@ -12684,7 +12684,7 @@
       </c>
       <c r="C182" s="3" t="inlineStr">
         <is>
-          <t>La perception</t>
+          <t>Le recours</t>
         </is>
       </c>
       <c r="D182" s="3" t="inlineStr">
@@ -12713,31 +12713,31 @@
         </is>
       </c>
       <c r="I182" s="3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J182" s="3" t="n">
         <v>4</v>
       </c>
       <c r="K182" s="3" t="inlineStr">
         <is>
-          <t>reflux_transactionnel, reflux_collectif, bareme, demurrage, affectation_des_instruments, contrepartie_comptable</t>
+          <t>bareme, qualification_regenerative, valorisation_des_communs, demurrage, regle_contre_discretion, essentiel_insolvable, affectation_des_instruments</t>
         </is>
       </c>
       <c r="L182" s="3" t="inlineStr">
         <is>
-          <t>L1.C21, L11.C01, L11.C02, L11.C03, L11.C05, L11.C09, L11.C10, L11.C16, L11.C17, L11.C19, L11.C20</t>
+          <t>L1.C18, L11.C03, L11.C06, L11.C08, L11.C09, L11.C11, L11.C12, L11.C13, L11.C16, L11.C17, L11.C18</t>
         </is>
       </c>
       <c r="M182" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-11/c21-la-perception.md</t>
+          <t>corpus/livre-11/c19-le-recours.md</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" s="2" t="inlineStr">
         <is>
-          <t>L11.C22</t>
+          <t>L11.C20</t>
         </is>
       </c>
       <c r="B183" s="3" t="inlineStr">
@@ -12747,7 +12747,7 @@
       </c>
       <c r="C183" s="3" t="inlineStr">
         <is>
-          <t>Les délais</t>
+          <t>L'amendement de la directive</t>
         </is>
       </c>
       <c r="D183" s="3" t="inlineStr">
@@ -12783,24 +12783,24 @@
       </c>
       <c r="K183" s="3" t="inlineStr">
         <is>
-          <t>reflux_collectif, reflux_transactionnel, bareme, regle_contre_discretion, qualification_regenerative, affectation_des_instruments, robustesse</t>
+          <t>bareme, regle_contre_discretion, qualification_regenerative, valorisation_des_communs, referentiel_de_change, affectation_des_instruments</t>
         </is>
       </c>
       <c r="L183" s="3" t="inlineStr">
         <is>
-          <t>L1.C21, L11.C03, L11.C07, L11.C10, L11.C12, L11.C13, L11.C16, L11.C17, L11.C19, L11.C20, L11.C21</t>
+          <t>L1.C21, L1.C26, L1.C28, L11.C03, L11.C06, L11.C10, L11.C12, L11.C13, L11.C15, L11.C16, L11.C17, L11.C18, L11.C19</t>
         </is>
       </c>
       <c r="M183" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-11/c22-les-delais.md</t>
+          <t>corpus/livre-11/c20-l-amendement-de-la-directive.md</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" s="2" t="inlineStr">
         <is>
-          <t>L11.C23</t>
+          <t>L11.C21</t>
         </is>
       </c>
       <c r="B184" s="3" t="inlineStr">
@@ -12810,7 +12810,7 @@
       </c>
       <c r="C184" s="3" t="inlineStr">
         <is>
-          <t>La contracyclicité</t>
+          <t>La perception</t>
         </is>
       </c>
       <c r="D184" s="3" t="inlineStr">
@@ -12846,24 +12846,24 @@
       </c>
       <c r="K184" s="3" t="inlineStr">
         <is>
-          <t>reflux_transactionnel, reflux_collectif, essentiel_insolvable, degeneratif, bareme, robustesse, affectation_des_instruments, contrepartie_comptable</t>
+          <t>reflux_transactionnel, reflux_collectif, bareme, demurrage, affectation_des_instruments, contrepartie_comptable</t>
         </is>
       </c>
       <c r="L184" s="3" t="inlineStr">
         <is>
-          <t>L1.C15, L1.C21, L1.C29, L11.C01, L11.C02, L11.C03, L11.C07, L11.C10, L11.C12, L11.C14, L11.C16, L11.C17, L11.C21, L11.C22</t>
+          <t>L1.C21, L11.C01, L11.C02, L11.C03, L11.C05, L11.C09, L11.C10, L11.C16, L11.C17, L11.C19, L11.C20</t>
         </is>
       </c>
       <c r="M184" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-11/c23-la-contracyclicite.md</t>
+          <t>corpus/livre-11/c21-la-perception.md</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" s="2" t="inlineStr">
         <is>
-          <t>L11.C24</t>
+          <t>L11.C22</t>
         </is>
       </c>
       <c r="B185" s="3" t="inlineStr">
@@ -12873,7 +12873,7 @@
       </c>
       <c r="C185" s="3" t="inlineStr">
         <is>
-          <t>Le barème aux frontières</t>
+          <t>Les délais</t>
         </is>
       </c>
       <c r="D185" s="3" t="inlineStr">
@@ -12898,7 +12898,7 @@
       </c>
       <c r="H185" s="3" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="I185" s="3" t="n">
@@ -12909,24 +12909,24 @@
       </c>
       <c r="K185" s="3" t="inlineStr">
         <is>
-          <t>seuil_d_activation, bareme, degeneratif, reflux_transactionnel, referentiel_de_change, essentiel_insolvable, affectation_des_instruments</t>
+          <t>reflux_collectif, reflux_transactionnel, bareme, regle_contre_discretion, qualification_regenerative, affectation_des_instruments, robustesse</t>
         </is>
       </c>
       <c r="L185" s="3" t="inlineStr">
         <is>
-          <t>L1.C26, L1.C27, L11.C04, L11.C05, L11.C06, L11.C09, L11.C13, L11.C16, L11.C17, L11.C19, L11.C21</t>
+          <t>L1.C21, L11.C03, L11.C07, L11.C10, L11.C12, L11.C13, L11.C16, L11.C17, L11.C19, L11.C20, L11.C21</t>
         </is>
       </c>
       <c r="M185" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-11/c24-le-bareme-aux-frontieres.md</t>
+          <t>corpus/livre-11/c22-les-delais.md</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" s="2" t="inlineStr">
         <is>
-          <t>L11.C25</t>
+          <t>L11.C23</t>
         </is>
       </c>
       <c r="B186" s="3" t="inlineStr">
@@ -12936,7 +12936,7 @@
       </c>
       <c r="C186" s="3" t="inlineStr">
         <is>
-          <t>Le contrôle</t>
+          <t>La contracyclicité</t>
         </is>
       </c>
       <c r="D186" s="3" t="inlineStr">
@@ -12961,35 +12961,35 @@
       </c>
       <c r="H186" s="3" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="I186" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J186" s="3" t="n">
         <v>4</v>
       </c>
       <c r="K186" s="3" t="inlineStr">
         <is>
-          <t>bareme, reflux_transactionnel, qualification_regenerative, regle_contre_discretion, affectation_des_instruments, essentiel_insolvable</t>
+          <t>reflux_transactionnel, reflux_collectif, essentiel_insolvable, degeneratif, bareme, robustesse, affectation_des_instruments, contrepartie_comptable</t>
         </is>
       </c>
       <c r="L186" s="3" t="inlineStr">
         <is>
-          <t>L1.C18, L1.C21, L1.C22, L11.C05, L11.C06, L11.C09, L11.C11, L11.C13, L11.C17, L11.C19, L11.C20, L11.C21, L11.C23, L11.C24</t>
+          <t>L1.C15, L1.C21, L1.C29, L11.C01, L11.C02, L11.C03, L11.C07, L11.C10, L11.C12, L11.C14, L11.C16, L11.C17, L11.C21, L11.C22</t>
         </is>
       </c>
       <c r="M186" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-11/c25-le-controle.md</t>
+          <t>corpus/livre-11/c23-la-contracyclicite.md</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" s="2" t="inlineStr">
         <is>
-          <t>L11.C26</t>
+          <t>L11.C24</t>
         </is>
       </c>
       <c r="B187" s="3" t="inlineStr">
@@ -12999,7 +12999,7 @@
       </c>
       <c r="C187" s="3" t="inlineStr">
         <is>
-          <t>La portée du Livre 11</t>
+          <t>Le barème aux frontières</t>
         </is>
       </c>
       <c r="D187" s="3" t="inlineStr">
@@ -13024,35 +13024,35 @@
       </c>
       <c r="H187" s="3" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="I187" s="3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J187" s="3" t="n">
         <v>4</v>
       </c>
       <c r="K187" s="3" t="inlineStr">
         <is>
-          <t>bareme, reflux_collectif, reflux_transactionnel, demurrage, qualification_regenerative, valorisation_des_communs, referentiel_de_change, regle_contre_discretion, affectation_des_instruments, polycentricite</t>
+          <t>seuil_d_activation, bareme, degeneratif, reflux_transactionnel, referentiel_de_change, essentiel_insolvable, affectation_des_instruments</t>
         </is>
       </c>
       <c r="L187" s="3" t="inlineStr">
         <is>
-          <t>L1.C15, L1.C18, L1.C21, L1.C22, L1.C26, L1.C27, L1.C28, L1.C29, L11.C01, L11.C03, L11.C06, L11.C07, L11.C09, L11.C11, L11.C12, L11.C13, L11.C16, L11.C17, L11.C19, L11.C21, L11.C22, L11.C23, L11.C24, L11.C25</t>
+          <t>L1.C26, L1.C27, L11.C04, L11.C05, L11.C06, L11.C09, L11.C13, L11.C16, L11.C17, L11.C19, L11.C21</t>
         </is>
       </c>
       <c r="M187" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-11/c26-la-portee-du-livre.md</t>
+          <t>corpus/livre-11/c24-le-bareme-aux-frontieres.md</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" s="2" t="inlineStr">
         <is>
-          <t>L11.C27</t>
+          <t>L11.C25</t>
         </is>
       </c>
       <c r="B188" s="3" t="inlineStr">
@@ -13062,7 +13062,7 @@
       </c>
       <c r="C188" s="3" t="inlineStr">
         <is>
-          <t>L'assiette de la fonte est celle de la TVA</t>
+          <t>Le contrôle</t>
         </is>
       </c>
       <c r="D188" s="3" t="inlineStr">
@@ -13091,31 +13091,31 @@
         </is>
       </c>
       <c r="I188" s="3" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J188" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K188" s="3" t="inlineStr">
         <is>
-          <t>reflux_transactionnel, demurrage, bareme, degeneratif, qualification_regenerative, externalisation, additionnalite</t>
+          <t>bareme, reflux_transactionnel, qualification_regenerative, regle_contre_discretion, affectation_des_instruments, essentiel_insolvable</t>
         </is>
       </c>
       <c r="L188" s="3" t="inlineStr">
         <is>
-          <t>L1.C21, L1.C27, L2.C16, L11.C02, L11.C05, L11.C09, L11.C21, L11.C24, L11.C25, L20.C02, L20.C19</t>
+          <t>L1.C18, L1.C21, L1.C22, L11.C05, L11.C06, L11.C09, L11.C11, L11.C13, L11.C17, L11.C19, L11.C20, L11.C21, L11.C23, L11.C24</t>
         </is>
       </c>
       <c r="M188" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-11/c27-l-assiette-de-la-fonte-est-celle-de-la-tva.md</t>
+          <t>corpus/livre-11/c25-le-controle.md</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" s="2" t="inlineStr">
         <is>
-          <t>L11.C28</t>
+          <t>L11.C26</t>
         </is>
       </c>
       <c r="B189" s="3" t="inlineStr">
@@ -13125,7 +13125,7 @@
       </c>
       <c r="C189" s="3" t="inlineStr">
         <is>
-          <t>La fonte sur les acquisitions d'actifs, éprouvée</t>
+          <t>La portée du Livre 11</t>
         </is>
       </c>
       <c r="D189" s="3" t="inlineStr">
@@ -13150,35 +13150,35 @@
       </c>
       <c r="H189" s="3" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="I189" s="3" t="n">
         <v>4</v>
       </c>
       <c r="J189" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K189" s="3" t="inlineStr">
         <is>
-          <t>reflux_transactionnel, demurrage, bareme, referentiel_de_change, degeneratif, robustesse</t>
+          <t>bareme, reflux_collectif, reflux_transactionnel, demurrage, qualification_regenerative, valorisation_des_communs, referentiel_de_change, regle_contre_discretion, affectation_des_instruments, polycentricite</t>
         </is>
       </c>
       <c r="L189" s="3" t="inlineStr">
         <is>
-          <t>L1.C19, L1.C21, L2.C13, L2.C16, L6.C02, L11.C02, L11.C05, L11.C09, L11.C23, L11.C27, L20.C13</t>
+          <t>L1.C15, L1.C18, L1.C21, L1.C22, L1.C26, L1.C27, L1.C28, L1.C29, L11.C01, L11.C03, L11.C06, L11.C07, L11.C09, L11.C11, L11.C12, L11.C13, L11.C16, L11.C17, L11.C19, L11.C21, L11.C22, L11.C23, L11.C24, L11.C25</t>
         </is>
       </c>
       <c r="M189" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-11/c28-la-fonte-sur-les-acquisitions-d-actifs-eprouvee.md</t>
+          <t>corpus/livre-11/c26-la-portee-du-livre.md</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" s="2" t="inlineStr">
         <is>
-          <t>L11.C29</t>
+          <t>L11.C27</t>
         </is>
       </c>
       <c r="B190" s="3" t="inlineStr">
@@ -13188,7 +13188,7 @@
       </c>
       <c r="C190" s="3" t="inlineStr">
         <is>
-          <t>La structure des sanctions</t>
+          <t>L'assiette de la fonte est celle de la TVA</t>
         </is>
       </c>
       <c r="D190" s="3" t="inlineStr">
@@ -13224,34 +13224,34 @@
       </c>
       <c r="K190" s="3" t="inlineStr">
         <is>
-          <t>bareme, seuil_d_activation, regle_contre_discretion, robustesse, qualification_regenerative, degeneratif</t>
+          <t>reflux_transactionnel, demurrage, bareme, degeneratif, qualification_regenerative, externalisation, additionnalite</t>
         </is>
       </c>
       <c r="L190" s="3" t="inlineStr">
         <is>
-          <t>L2.C08, L2.C14, L2.C21, L2.C22, L7.C19, L8.C31, L11.C18, L11.C19, L11.C20, L11.C23, L11.C25, L20.C17, L20.C18</t>
+          <t>L1.C21, L1.C27, L2.C16, L11.C02, L11.C05, L11.C09, L11.C21, L11.C24, L11.C25, L20.C02, L20.C19</t>
         </is>
       </c>
       <c r="M190" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-11/c29-la-structure-des-sanctions.md</t>
+          <t>corpus/livre-11/c27-l-assiette-de-la-fonte-est-celle-de-la-tva.md</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" s="2" t="inlineStr">
         <is>
-          <t>L18.C01</t>
+          <t>L11.C28</t>
         </is>
       </c>
       <c r="B191" s="3" t="inlineStr">
         <is>
-          <t>L18</t>
+          <t>L11</t>
         </is>
       </c>
       <c r="C191" s="3" t="inlineStr">
         <is>
-          <t>Ce que ce livre doit établir, et le repli n'est pas l'annexe</t>
+          <t>La fonte sur les acquisitions d'actifs, éprouvée</t>
         </is>
       </c>
       <c r="D191" s="3" t="inlineStr">
@@ -13271,7 +13271,7 @@
       </c>
       <c r="G191" s="3" t="inlineStr">
         <is>
-          <t>hybride</t>
+          <t>conception</t>
         </is>
       </c>
       <c r="H191" s="3" t="inlineStr">
@@ -13283,38 +13283,38 @@
         <v>4</v>
       </c>
       <c r="J191" s="3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K191" s="3" t="inlineStr">
         <is>
-          <t>contrepartie_comptable, valorisation_des_communs, communs, essentiel_insolvable, qualification_regenerative, architecture_invisible</t>
+          <t>reflux_transactionnel, demurrage, bareme, referentiel_de_change, degeneratif, robustesse</t>
         </is>
       </c>
       <c r="L191" s="3" t="inlineStr">
         <is>
-          <t>L1.C09, L1.C29, L5.C02, L5.C09, L5.C10, L6.C08, L6.C09, L6.C13, L11.C13, L11.C16, L20.C02</t>
+          <t>L1.C19, L1.C21, L2.C13, L2.C16, L6.C02, L11.C02, L11.C05, L11.C09, L11.C23, L11.C27, L20.C13</t>
         </is>
       </c>
       <c r="M191" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-18/c01-ce-que-ce-livre-doit-etablir.md</t>
+          <t>corpus/livre-11/c28-la-fonte-sur-les-acquisitions-d-actifs-eprouvee.md</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" s="2" t="inlineStr">
         <is>
-          <t>L18.C02</t>
+          <t>L11.C29</t>
         </is>
       </c>
       <c r="B192" s="3" t="inlineStr">
         <is>
-          <t>L18</t>
+          <t>L11</t>
         </is>
       </c>
       <c r="C192" s="3" t="inlineStr">
         <is>
-          <t>La métrologie existe, et ce qu'elle enregistre est l'ordre en place</t>
+          <t>La structure des sanctions</t>
         </is>
       </c>
       <c r="D192" s="3" t="inlineStr">
@@ -13334,7 +13334,7 @@
       </c>
       <c r="G192" s="3" t="inlineStr">
         <is>
-          <t>hybride</t>
+          <t>conception</t>
         </is>
       </c>
       <c r="H192" s="3" t="inlineStr">
@@ -13343,31 +13343,31 @@
         </is>
       </c>
       <c r="I192" s="3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J192" s="3" t="n">
         <v>3</v>
       </c>
       <c r="K192" s="3" t="inlineStr">
         <is>
-          <t>valorisation_des_communs, contrepartie_comptable, bareme, essentiel_insolvable, indicateur_de_progres, fausse_richesse</t>
+          <t>bareme, seuil_d_activation, regle_contre_discretion, robustesse, qualification_regenerative, degeneratif</t>
         </is>
       </c>
       <c r="L192" s="3" t="inlineStr">
         <is>
-          <t>L1.C09, L1.C15, L1.C18, L6.C06, L11.C03, L11.C07, L11.C13, L11.C16, L18.C01</t>
+          <t>L2.C08, L2.C14, L2.C21, L2.C22, L7.C19, L8.C31, L11.C18, L11.C19, L11.C20, L11.C23, L11.C25, L20.C17, L20.C18</t>
         </is>
       </c>
       <c r="M192" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-18/c02-la-metrologie-existe-et-ce-qu-elle-enregistre.md</t>
+          <t>corpus/livre-11/c29-la-structure-des-sanctions.md</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" s="2" t="inlineStr">
         <is>
-          <t>L18.C03</t>
+          <t>L18.C01</t>
         </is>
       </c>
       <c r="B193" s="3" t="inlineStr">
@@ -13377,7 +13377,7 @@
       </c>
       <c r="C193" s="3" t="inlineStr">
         <is>
-          <t>L'échelle de repli, et qui l'a arrêtée</t>
+          <t>Ce que ce livre doit établir, et le repli n'est pas l'annexe</t>
         </is>
       </c>
       <c r="D193" s="3" t="inlineStr">
@@ -13406,31 +13406,31 @@
         </is>
       </c>
       <c r="I193" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J193" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K193" s="3" t="inlineStr">
         <is>
-          <t>contrepartie_comptable, architecture_invisible, valorisation_des_communs, essentiel_insolvable, regle_contre_discretion</t>
+          <t>contrepartie_comptable, valorisation_des_communs, communs, essentiel_insolvable, qualification_regenerative, architecture_invisible</t>
         </is>
       </c>
       <c r="L193" s="3" t="inlineStr">
         <is>
-          <t>L1.C09, L1.C15, L1.C29, L6.C09, L11.C29, L18.C01, L18.C02, L20.C02</t>
+          <t>L1.C09, L1.C29, L5.C02, L5.C09, L5.C10, L6.C08, L6.C09, L6.C13, L11.C13, L11.C16, L20.C02</t>
         </is>
       </c>
       <c r="M193" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-18/c03-l-echelle-de-repli-et-qui-l-a-arretee.md</t>
+          <t>corpus/livre-18/c01-ce-que-ce-livre-doit-etablir.md</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" s="2" t="inlineStr">
         <is>
-          <t>L18.C04</t>
+          <t>L18.C02</t>
         </is>
       </c>
       <c r="B194" s="3" t="inlineStr">
@@ -13440,7 +13440,7 @@
       </c>
       <c r="C194" s="3" t="inlineStr">
         <is>
-          <t>Les grandeurs physiques, et l'endroit où elles frappent le dispositif</t>
+          <t>La métrologie existe, et ce qu'elle enregistre est l'ordre en place</t>
         </is>
       </c>
       <c r="D194" s="3" t="inlineStr">
@@ -13476,24 +13476,24 @@
       </c>
       <c r="K194" s="3" t="inlineStr">
         <is>
-          <t>decouplage, effet_rebond, externalisation, limites_planetaires, sobriete, fausse_richesse</t>
+          <t>valorisation_des_communs, contrepartie_comptable, bareme, essentiel_insolvable, indicateur_de_progres, fausse_richesse</t>
         </is>
       </c>
       <c r="L194" s="3" t="inlineStr">
         <is>
-          <t>L1.C02, L1.C03, L1.C04, L5.C08, L6.C08, L11.C10, L11.C24, L18.C01, L18.C02</t>
+          <t>L1.C09, L1.C15, L1.C18, L6.C06, L11.C03, L11.C07, L11.C13, L11.C16, L18.C01</t>
         </is>
       </c>
       <c r="M194" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-18/c04-les-grandeurs-physiques-et-ou-elles-frappent.md</t>
+          <t>corpus/livre-18/c02-la-metrologie-existe-et-ce-qu-elle-enregistre.md</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" s="2" t="inlineStr">
         <is>
-          <t>L18.C05</t>
+          <t>L18.C03</t>
         </is>
       </c>
       <c r="B195" s="3" t="inlineStr">
@@ -13503,7 +13503,7 @@
       </c>
       <c r="C195" s="3" t="inlineStr">
         <is>
-          <t>Le commun est ce que la norme exclut, et la symétrie de l'écriture</t>
+          <t>L'échelle de repli, et qui l'a arrêtée</t>
         </is>
       </c>
       <c r="D195" s="3" t="inlineStr">
@@ -13539,24 +13539,24 @@
       </c>
       <c r="K195" s="3" t="inlineStr">
         <is>
-          <t>communs, contrepartie_comptable, valorisation_des_communs, architecture_invisible, monnaie_comme_registre, creation_monetaire</t>
+          <t>contrepartie_comptable, architecture_invisible, valorisation_des_communs, essentiel_insolvable, regle_contre_discretion</t>
         </is>
       </c>
       <c r="L195" s="3" t="inlineStr">
         <is>
-          <t>L1.C09, L1.C20, L1.C29, L6.C06, L6.C08, L11.C13, L11.C16, L18.C01, L18.C02, L18.C03, L20.C02</t>
+          <t>L1.C09, L1.C15, L1.C29, L6.C09, L11.C29, L18.C01, L18.C02, L20.C02</t>
         </is>
       </c>
       <c r="M195" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-18/c05-le-commun-est-ce-que-la-norme-exclut.md</t>
+          <t>corpus/livre-18/c03-l-echelle-de-repli-et-qui-l-a-arretee.md</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" s="2" t="inlineStr">
         <is>
-          <t>L18.C06</t>
+          <t>L18.C04</t>
         </is>
       </c>
       <c r="B196" s="3" t="inlineStr">
@@ -13566,7 +13566,7 @@
       </c>
       <c r="C196" s="3" t="inlineStr">
         <is>
-          <t>Portée de la tranche, et une neuvième condition proposée</t>
+          <t>Les grandeurs physiques, et l'endroit où elles frappent le dispositif</t>
         </is>
       </c>
       <c r="D196" s="3" t="inlineStr">
@@ -13586,7 +13586,7 @@
       </c>
       <c r="G196" s="3" t="inlineStr">
         <is>
-          <t>conception</t>
+          <t>hybride</t>
         </is>
       </c>
       <c r="H196" s="3" t="inlineStr">
@@ -13595,31 +13595,31 @@
         </is>
       </c>
       <c r="I196" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J196" s="3" t="n">
         <v>3</v>
       </c>
       <c r="K196" s="3" t="inlineStr">
         <is>
-          <t>contrepartie_comptable, communs, valorisation_des_communs, architecture_invisible, essentiel_insolvable</t>
+          <t>decouplage, effet_rebond, externalisation, limites_planetaires, sobriete, fausse_richesse</t>
         </is>
       </c>
       <c r="L196" s="3" t="inlineStr">
         <is>
-          <t>L1.C09, L1.C18, L1.C20, L1.C29, L5.C02, L5.C08, L6.C06, L6.C08, L11.C13, L11.C16, L18.C01, L18.C02, L18.C03, L18.C04, L18.C05, L20.C02</t>
+          <t>L1.C02, L1.C03, L1.C04, L5.C08, L6.C08, L11.C10, L11.C24, L18.C01, L18.C02</t>
         </is>
       </c>
       <c r="M196" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-18/c06-portee-de-la-tranche-et-une-neuvieme-condition.md</t>
+          <t>corpus/livre-18/c04-les-grandeurs-physiques-et-ou-elles-frappent.md</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" s="2" t="inlineStr">
         <is>
-          <t>L18.C07</t>
+          <t>L18.C05</t>
         </is>
       </c>
       <c r="B197" s="3" t="inlineStr">
@@ -13629,7 +13629,7 @@
       </c>
       <c r="C197" s="3" t="inlineStr">
         <is>
-          <t>CARE/TDL répare deux objections, et en crée une plus grave</t>
+          <t>Le commun est ce que la norme exclut, et la symétrie de l'écriture</t>
         </is>
       </c>
       <c r="D197" s="3" t="inlineStr">
@@ -13658,31 +13658,31 @@
         </is>
       </c>
       <c r="I197" s="3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J197" s="3" t="n">
         <v>3</v>
       </c>
       <c r="K197" s="3" t="inlineStr">
         <is>
-          <t>contrepartie_comptable, bareme, valorisation_des_communs, communs, architecture_invisible, fausse_richesse</t>
+          <t>communs, contrepartie_comptable, valorisation_des_communs, architecture_invisible, monnaie_comme_registre, creation_monetaire</t>
         </is>
       </c>
       <c r="L197" s="3" t="inlineStr">
         <is>
-          <t>L1.C09, L1.C18, L1.C20, L6.C06, L11.C03, L11.C13, L11.C16, L18.C01, L18.C02, L18.C05, L18.C06</t>
+          <t>L1.C09, L1.C20, L1.C29, L6.C06, L6.C08, L11.C13, L11.C16, L18.C01, L18.C02, L18.C03, L20.C02</t>
         </is>
       </c>
       <c r="M197" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-18/c07-care-tdl-repare-une-objection-et-en-cree-une-autre.md</t>
+          <t>corpus/livre-18/c05-le-commun-est-ce-que-la-norme-exclut.md</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" s="2" t="inlineStr">
         <is>
-          <t>L18.C08</t>
+          <t>L18.C06</t>
         </is>
       </c>
       <c r="B198" s="3" t="inlineStr">
@@ -13692,7 +13692,7 @@
       </c>
       <c r="C198" s="3" t="inlineStr">
         <is>
-          <t>Le modèle au périmètre du dispositif, et F9 révisée</t>
+          <t>Portée de la tranche, et une neuvième condition proposée</t>
         </is>
       </c>
       <c r="D198" s="3" t="inlineStr">
@@ -13721,41 +13721,41 @@
         </is>
       </c>
       <c r="I198" s="3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J198" s="3" t="n">
         <v>3</v>
       </c>
       <c r="K198" s="3" t="inlineStr">
         <is>
-          <t>contrepartie_comptable, communs, valorisation_des_communs, polycentricite, essentiel_insolvable, indicateur_de_progres</t>
+          <t>contrepartie_comptable, communs, valorisation_des_communs, architecture_invisible, essentiel_insolvable</t>
         </is>
       </c>
       <c r="L198" s="3" t="inlineStr">
         <is>
-          <t>L1.C09, L1.C18, L6.C06, L7.C05, L11.C13, L11.C16, L11.C25, L18.C01, L18.C02, L18.C05, L18.C06, L18.C07</t>
+          <t>L1.C09, L1.C18, L1.C20, L1.C29, L5.C02, L5.C08, L6.C06, L6.C08, L11.C13, L11.C16, L18.C01, L18.C02, L18.C03, L18.C04, L18.C05, L20.C02</t>
         </is>
       </c>
       <c r="M198" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-18/c08-le-modele-au-perimetre-du-dispositif-et-f9-revisee.md</t>
+          <t>corpus/livre-18/c06-portee-de-la-tranche-et-une-neuvieme-condition.md</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" s="2" t="inlineStr">
         <is>
-          <t>L20.C01</t>
+          <t>L18.C07</t>
         </is>
       </c>
       <c r="B199" s="3" t="inlineStr">
         <is>
-          <t>L20</t>
+          <t>L18</t>
         </is>
       </c>
       <c r="C199" s="3" t="inlineStr">
         <is>
-          <t>Ce que ce livre doit établir</t>
+          <t>CARE/TDL répare deux objections, et en crée une plus grave</t>
         </is>
       </c>
       <c r="D199" s="3" t="inlineStr">
@@ -13775,50 +13775,50 @@
       </c>
       <c r="G199" s="3" t="inlineStr">
         <is>
-          <t>conception</t>
+          <t>hybride</t>
         </is>
       </c>
       <c r="H199" s="3" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="I199" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J199" s="3" t="n">
         <v>3</v>
       </c>
       <c r="K199" s="3" t="inlineStr">
         <is>
-          <t>fenetre_de_reforme, referentiel_de_change, communs, limites_planetaires, creation_monetaire</t>
+          <t>contrepartie_comptable, bareme, valorisation_des_communs, communs, architecture_invisible, fausse_richesse</t>
         </is>
       </c>
       <c r="L199" s="3" t="inlineStr">
         <is>
-          <t>L1.C18, L1.C25, L1.C27, L7.C01, L7.C03, L7.C13, L7.C17, L7.C21, L11.C24</t>
+          <t>L1.C09, L1.C18, L1.C20, L6.C06, L11.C03, L11.C13, L11.C16, L18.C01, L18.C02, L18.C05, L18.C06</t>
         </is>
       </c>
       <c r="M199" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-20/c01-ce-que-ce-livre-doit-etablir.md</t>
+          <t>corpus/livre-18/c07-care-tdl-repare-une-objection-et-en-cree-une-autre.md</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" s="2" t="inlineStr">
         <is>
-          <t>L20.C02</t>
+          <t>L18.C08</t>
         </is>
       </c>
       <c r="B200" s="3" t="inlineStr">
         <is>
-          <t>L20</t>
+          <t>L18</t>
         </is>
       </c>
       <c r="C200" s="3" t="inlineStr">
         <is>
-          <t>L'interdiction du financement monétaire</t>
+          <t>Le modèle au périmètre du dispositif, et F9 révisée</t>
         </is>
       </c>
       <c r="D200" s="3" t="inlineStr">
@@ -13847,31 +13847,31 @@
         </is>
       </c>
       <c r="I200" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J200" s="3" t="n">
         <v>3</v>
       </c>
       <c r="K200" s="3" t="inlineStr">
         <is>
-          <t>creation_monetaire, contrepartie_comptable, reflux_collectif, fenetre_de_reforme</t>
+          <t>contrepartie_comptable, communs, valorisation_des_communs, polycentricite, essentiel_insolvable, indicateur_de_progres</t>
         </is>
       </c>
       <c r="L200" s="3" t="inlineStr">
         <is>
-          <t>L1.C05, L1.C18, L1.C20, L1.C22, L7.C11, L7.C13, L11.C10, L20.C01</t>
+          <t>L1.C09, L1.C18, L6.C06, L7.C05, L11.C13, L11.C16, L11.C25, L18.C01, L18.C02, L18.C05, L18.C06, L18.C07</t>
         </is>
       </c>
       <c r="M200" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-20/c02-l-interdiction-du-financement-monetaire.md</t>
+          <t>corpus/livre-18/c08-le-modele-au-perimetre-du-dispositif-et-f9-revisee.md</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" s="2" t="inlineStr">
         <is>
-          <t>L20.C03</t>
+          <t>L20.C01</t>
         </is>
       </c>
       <c r="B201" s="3" t="inlineStr">
@@ -13881,7 +13881,7 @@
       </c>
       <c r="C201" s="3" t="inlineStr">
         <is>
-          <t>L'objectif principal et ce qu'il exclut</t>
+          <t>Ce que ce livre doit établir</t>
         </is>
       </c>
       <c r="D201" s="3" t="inlineStr">
@@ -13906,7 +13906,7 @@
       </c>
       <c r="H201" s="3" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="I201" s="3" t="n">
@@ -13917,24 +13917,24 @@
       </c>
       <c r="K201" s="3" t="inlineStr">
         <is>
-          <t>regle_contre_discretion, limites_planetaires, creation_monetaire, plafond_ecologique</t>
+          <t>fenetre_de_reforme, referentiel_de_change, communs, limites_planetaires, creation_monetaire</t>
         </is>
       </c>
       <c r="L201" s="3" t="inlineStr">
         <is>
-          <t>L1.C01, L1.C18, L1.C20, L7.C03, L8.C12, L8.C34, L11.C16, L20.C01, L20.C02</t>
+          <t>L1.C18, L1.C25, L1.C27, L7.C01, L7.C03, L7.C13, L7.C17, L7.C21, L11.C24</t>
         </is>
       </c>
       <c r="M201" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-20/c03-l-objectif-principal-et-ce-qu-il-exclut.md</t>
+          <t>corpus/livre-20/c01-ce-que-ce-livre-doit-etablir.md</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" s="2" t="inlineStr">
         <is>
-          <t>L20.C04</t>
+          <t>L20.C02</t>
         </is>
       </c>
       <c r="B202" s="3" t="inlineStr">
@@ -13944,7 +13944,7 @@
       </c>
       <c r="C202" s="3" t="inlineStr">
         <is>
-          <t>L'indépendance, et à l'égard de qui</t>
+          <t>L'interdiction du financement monétaire</t>
         </is>
       </c>
       <c r="D202" s="3" t="inlineStr">
@@ -13969,7 +13969,7 @@
       </c>
       <c r="H202" s="3" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="I202" s="3" t="n">
@@ -13980,24 +13980,24 @@
       </c>
       <c r="K202" s="3" t="inlineStr">
         <is>
-          <t>regle_contre_discretion, creation_monetaire, fenetre_de_reforme</t>
+          <t>creation_monetaire, contrepartie_comptable, reflux_collectif, fenetre_de_reforme</t>
         </is>
       </c>
       <c r="L202" s="3" t="inlineStr">
         <is>
-          <t>L1.C18, L7.C04, L7.C07, L7.C10, L8.C31, L11.C17, L20.C01, L20.C03, L20.C11</t>
+          <t>L1.C05, L1.C18, L1.C20, L1.C22, L7.C11, L7.C13, L11.C10, L20.C01</t>
         </is>
       </c>
       <c r="M202" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-20/c04-l-independance-et-a-l-egard-de-qui.md</t>
+          <t>corpus/livre-20/c02-l-interdiction-du-financement-monetaire.md</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" s="2" t="inlineStr">
         <is>
-          <t>L20.C05</t>
+          <t>L20.C03</t>
         </is>
       </c>
       <c r="B203" s="3" t="inlineStr">
@@ -14007,7 +14007,7 @@
       </c>
       <c r="C203" s="3" t="inlineStr">
         <is>
-          <t>Le monopole d'émission et le cours légal</t>
+          <t>L'objectif principal et ce qu'il exclut</t>
         </is>
       </c>
       <c r="D203" s="3" t="inlineStr">
@@ -14032,7 +14032,7 @@
       </c>
       <c r="H203" s="3" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="I203" s="3" t="n">
@@ -14043,24 +14043,24 @@
       </c>
       <c r="K203" s="3" t="inlineStr">
         <is>
-          <t>monnaie_comme_registre, creation_monetaire, referentiel_de_change, hierarchie_monetaire</t>
+          <t>regle_contre_discretion, limites_planetaires, creation_monetaire, plafond_ecologique</t>
         </is>
       </c>
       <c r="L203" s="3" t="inlineStr">
         <is>
-          <t>L1.C05, L1.C07, L1.C26, L7.C15, L11.C15, L20.C01, L20.C02, L20.C03</t>
+          <t>L1.C01, L1.C18, L1.C20, L7.C03, L8.C12, L8.C34, L11.C16, L20.C01, L20.C02</t>
         </is>
       </c>
       <c r="M203" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-20/c05-le-monopole-d-emission-et-le-cours-legal.md</t>
+          <t>corpus/livre-20/c03-l-objectif-principal-et-ce-qu-il-exclut.md</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" s="2" t="inlineStr">
         <is>
-          <t>L20.C06</t>
+          <t>L20.C04</t>
         </is>
       </c>
       <c r="B204" s="3" t="inlineStr">
@@ -14070,7 +14070,7 @@
       </c>
       <c r="C204" s="3" t="inlineStr">
         <is>
-          <t>Les voies de révision et leur coût</t>
+          <t>L'indépendance, et à l'égard de qui</t>
         </is>
       </c>
       <c r="D204" s="3" t="inlineStr">
@@ -14099,31 +14099,31 @@
         </is>
       </c>
       <c r="I204" s="3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J204" s="3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K204" s="3" t="inlineStr">
         <is>
-          <t>fenetre_de_reforme, regle_contre_discretion, creation_monetaire</t>
+          <t>regle_contre_discretion, creation_monetaire, fenetre_de_reforme</t>
         </is>
       </c>
       <c r="L204" s="3" t="inlineStr">
         <is>
-          <t>L1.C18, L7.C12, L7.C20, L7.C21, L11.C15, L20.C01, L20.C02, L20.C03, L20.C07, L20.C09, L20.C18</t>
+          <t>L1.C18, L7.C04, L7.C07, L7.C10, L8.C31, L11.C17, L20.C01, L20.C03, L20.C11</t>
         </is>
       </c>
       <c r="M204" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-20/c06-les-voies-de-revision-et-leur-cout.md</t>
+          <t>corpus/livre-20/c04-l-independance-et-a-l-egard-de-qui.md</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" s="2" t="inlineStr">
         <is>
-          <t>L20.C07</t>
+          <t>L20.C05</t>
         </is>
       </c>
       <c r="B205" s="3" t="inlineStr">
@@ -14133,7 +14133,7 @@
       </c>
       <c r="C205" s="3" t="inlineStr">
         <is>
-          <t>L'accord monétaire international</t>
+          <t>Le monopole d'émission et le cours légal</t>
         </is>
       </c>
       <c r="D205" s="3" t="inlineStr">
@@ -14169,24 +14169,24 @@
       </c>
       <c r="K205" s="3" t="inlineStr">
         <is>
-          <t>referentiel_de_change, fenetre_de_reforme, etalon_de_change_or, hierarchie_monetaire</t>
+          <t>monnaie_comme_registre, creation_monetaire, referentiel_de_change, hierarchie_monetaire</t>
         </is>
       </c>
       <c r="L205" s="3" t="inlineStr">
         <is>
-          <t>L1.C18, L1.C26, L7.C02, L7.C05, L7.C12, L7.C13, L11.C15, L20.C01, L20.C03, L20.C06, L20.C10</t>
+          <t>L1.C05, L1.C07, L1.C26, L7.C15, L11.C15, L20.C01, L20.C02, L20.C03</t>
         </is>
       </c>
       <c r="M205" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-20/c07-l-accord-monetaire-international.md</t>
+          <t>corpus/livre-20/c05-le-monopole-d-emission-et-le-cours-legal.md</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" s="2" t="inlineStr">
         <is>
-          <t>L20.C08</t>
+          <t>L20.C06</t>
         </is>
       </c>
       <c r="B206" s="3" t="inlineStr">
@@ -14196,7 +14196,7 @@
       </c>
       <c r="C206" s="3" t="inlineStr">
         <is>
-          <t>La parité inscrite dans le traité</t>
+          <t>Les voies de révision et leur coût</t>
         </is>
       </c>
       <c r="D206" s="3" t="inlineStr">
@@ -14221,35 +14221,35 @@
       </c>
       <c r="H206" s="3" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="I206" s="3" t="n">
         <v>4</v>
       </c>
       <c r="J206" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K206" s="3" t="inlineStr">
         <is>
-          <t>referentiel_de_change, etalon_de_change_or, hierarchie_monetaire, bareme, devise_cle</t>
+          <t>fenetre_de_reforme, regle_contre_discretion, creation_monetaire</t>
         </is>
       </c>
       <c r="L206" s="3" t="inlineStr">
         <is>
-          <t>L1.C25, L1.C26, L1.C28, L7.C02, L7.C20, L11.C15, L11.C17, L20.C01, L20.C09, L20.C13</t>
+          <t>L1.C18, L7.C12, L7.C20, L7.C21, L11.C15, L20.C01, L20.C02, L20.C03, L20.C07, L20.C09, L20.C18</t>
         </is>
       </c>
       <c r="M206" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-20/c08-la-parite-inscrite-dans-le-traite.md</t>
+          <t>corpus/livre-20/c06-les-voies-de-revision-et-leur-cout.md</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" s="2" t="inlineStr">
         <is>
-          <t>L20.C09</t>
+          <t>L20.C07</t>
         </is>
       </c>
       <c r="B207" s="3" t="inlineStr">
@@ -14259,7 +14259,7 @@
       </c>
       <c r="C207" s="3" t="inlineStr">
         <is>
-          <t>L'amendement des statuts du Fonds</t>
+          <t>L'accord monétaire international</t>
         </is>
       </c>
       <c r="D207" s="3" t="inlineStr">
@@ -14295,24 +14295,24 @@
       </c>
       <c r="K207" s="3" t="inlineStr">
         <is>
-          <t>fenetre_de_reforme, referentiel_de_change, bareme, regle_contre_discretion</t>
+          <t>referentiel_de_change, fenetre_de_reforme, etalon_de_change_or, hierarchie_monetaire</t>
         </is>
       </c>
       <c r="L207" s="3" t="inlineStr">
         <is>
-          <t>L7.C06, L7.C09, L7.C16, L7.C20, L11.C15, L11.C20, L20.C01, L20.C06, L20.C08, L20.C10, L20.C13</t>
+          <t>L1.C18, L1.C26, L7.C02, L7.C05, L7.C12, L7.C13, L11.C15, L20.C01, L20.C03, L20.C06, L20.C10</t>
         </is>
       </c>
       <c r="M207" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-20/c09-l-amendement-des-statuts-du-fonds.md</t>
+          <t>corpus/livre-20/c07-l-accord-monetaire-international.md</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" s="2" t="inlineStr">
         <is>
-          <t>L20.C10</t>
+          <t>L20.C08</t>
         </is>
       </c>
       <c r="B208" s="3" t="inlineStr">
@@ -14322,7 +14322,7 @@
       </c>
       <c r="C208" s="3" t="inlineStr">
         <is>
-          <t>Le vote pondéré et les voix de base</t>
+          <t>La parité inscrite dans le traité</t>
         </is>
       </c>
       <c r="D208" s="3" t="inlineStr">
@@ -14347,35 +14347,35 @@
       </c>
       <c r="H208" s="3" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="I208" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J208" s="3" t="n">
         <v>3</v>
       </c>
       <c r="K208" s="3" t="inlineStr">
         <is>
-          <t>bareme, devise_cle, hierarchie_monetaire, referentiel_de_change</t>
+          <t>referentiel_de_change, etalon_de_change_or, hierarchie_monetaire, bareme, devise_cle</t>
         </is>
       </c>
       <c r="L208" s="3" t="inlineStr">
         <is>
-          <t>L1.C25, L7.C02, L7.C05, L7.C06, L7.C09, L7.C10, L11.C16, L20.C01, L20.C07, L20.C09, L20.C12</t>
+          <t>L1.C25, L1.C26, L1.C28, L7.C02, L7.C20, L11.C15, L11.C17, L20.C01, L20.C09, L20.C13</t>
         </is>
       </c>
       <c r="M208" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-20/c10-le-vote-pondere-et-les-voix-de-base.md</t>
+          <t>corpus/livre-20/c08-la-parite-inscrite-dans-le-traite.md</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" s="2" t="inlineStr">
         <is>
-          <t>L20.C11</t>
+          <t>L20.C09</t>
         </is>
       </c>
       <c r="B209" s="3" t="inlineStr">
@@ -14385,7 +14385,7 @@
       </c>
       <c r="C209" s="3" t="inlineStr">
         <is>
-          <t>La personnalité juridique et les immunités</t>
+          <t>L'amendement des statuts du Fonds</t>
         </is>
       </c>
       <c r="D209" s="3" t="inlineStr">
@@ -14414,31 +14414,31 @@
         </is>
       </c>
       <c r="I209" s="3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J209" s="3" t="n">
         <v>3</v>
       </c>
       <c r="K209" s="3" t="inlineStr">
         <is>
-          <t>communs, creation_monetaire, fenetre_de_reforme, robustesse</t>
+          <t>fenetre_de_reforme, referentiel_de_change, bareme, regle_contre_discretion</t>
         </is>
       </c>
       <c r="L209" s="3" t="inlineStr">
         <is>
-          <t>L7.C01, L7.C03, L7.C07, L7.C10, L7.C13, L11.C25, L20.C01, L20.C04, L20.C12, L20.C14</t>
+          <t>L7.C06, L7.C09, L7.C16, L7.C20, L11.C15, L11.C20, L20.C01, L20.C06, L20.C08, L20.C10, L20.C13</t>
         </is>
       </c>
       <c r="M209" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-20/c11-la-personnalite-juridique-et-les-immunites.md</t>
+          <t>corpus/livre-20/c09-l-amendement-des-statuts-du-fonds.md</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" s="2" t="inlineStr">
         <is>
-          <t>L20.C12</t>
+          <t>L20.C10</t>
         </is>
       </c>
       <c r="B210" s="3" t="inlineStr">
@@ -14448,7 +14448,7 @@
       </c>
       <c r="C210" s="3" t="inlineStr">
         <is>
-          <t>Les pouvoirs non délégables</t>
+          <t>Le vote pondéré et les voix de base</t>
         </is>
       </c>
       <c r="D210" s="3" t="inlineStr">
@@ -14473,7 +14473,7 @@
       </c>
       <c r="H210" s="3" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="I210" s="3" t="n">
@@ -14484,24 +14484,24 @@
       </c>
       <c r="K210" s="3" t="inlineStr">
         <is>
-          <t>bareme, valorisation_des_communs, polycentricite, robustesse</t>
+          <t>bareme, devise_cle, hierarchie_monetaire, referentiel_de_change</t>
         </is>
       </c>
       <c r="L210" s="3" t="inlineStr">
         <is>
-          <t>L7.C05, L7.C06, L7.C07, L7.C11, L7.C14, L11.C16, L11.C20, L20.C01, L20.C09, L20.C10, L20.C14</t>
+          <t>L1.C25, L7.C02, L7.C05, L7.C06, L7.C09, L7.C10, L11.C16, L20.C01, L20.C07, L20.C09, L20.C12</t>
         </is>
       </c>
       <c r="M210" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-20/c12-les-pouvoirs-non-delegables.md</t>
+          <t>corpus/livre-20/c10-le-vote-pondere-et-les-voix-de-base.md</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" s="2" t="inlineStr">
         <is>
-          <t>L20.C13</t>
+          <t>L20.C11</t>
         </is>
       </c>
       <c r="B211" s="3" t="inlineStr">
@@ -14511,7 +14511,7 @@
       </c>
       <c r="C211" s="3" t="inlineStr">
         <is>
-          <t>L'entrée en vigueur, l'adhésion et le retrait</t>
+          <t>La personnalité juridique et les immunités</t>
         </is>
       </c>
       <c r="D211" s="3" t="inlineStr">
@@ -14536,7 +14536,7 @@
       </c>
       <c r="H211" s="3" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="I211" s="3" t="n">
@@ -14547,24 +14547,24 @@
       </c>
       <c r="K211" s="3" t="inlineStr">
         <is>
-          <t>seuil_d_activation, reflux_collectif, fenetre_de_reforme, additionnalite</t>
+          <t>communs, creation_monetaire, fenetre_de_reforme, robustesse</t>
         </is>
       </c>
       <c r="L211" s="3" t="inlineStr">
         <is>
-          <t>L7.C11, L7.C12, L7.C16, L7.C17, L7.C19, L11.C18, L20.C01, L20.C06, L20.C09, L20.C12</t>
+          <t>L7.C01, L7.C03, L7.C07, L7.C10, L7.C13, L11.C25, L20.C01, L20.C04, L20.C12, L20.C14</t>
         </is>
       </c>
       <c r="M211" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-20/c13-l-entree-en-vigueur-l-adhesion-et-le-retrait.md</t>
+          <t>corpus/livre-20/c11-la-personnalite-juridique-et-les-immunites.md</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" s="2" t="inlineStr">
         <is>
-          <t>L20.C14</t>
+          <t>L20.C12</t>
         </is>
       </c>
       <c r="B212" s="3" t="inlineStr">
@@ -14574,7 +14574,7 @@
       </c>
       <c r="C212" s="3" t="inlineStr">
         <is>
-          <t>Qui interprète le traité</t>
+          <t>Les pouvoirs non délégables</t>
         </is>
       </c>
       <c r="D212" s="3" t="inlineStr">
@@ -14610,24 +14610,24 @@
       </c>
       <c r="K212" s="3" t="inlineStr">
         <is>
-          <t>robustesse, regle_contre_discretion, communs</t>
+          <t>bareme, valorisation_des_communs, polycentricite, robustesse</t>
         </is>
       </c>
       <c r="L212" s="3" t="inlineStr">
         <is>
-          <t>L7.C07, L7.C13, L7.C14, L7.C19, L11.C19, L11.C25, L20.C01, L20.C03, L20.C11, L20.C12, L20.C21</t>
+          <t>L7.C05, L7.C06, L7.C07, L7.C11, L7.C14, L11.C16, L11.C20, L20.C01, L20.C09, L20.C10, L20.C14</t>
         </is>
       </c>
       <c r="M212" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-20/c14-qui-interprete-le-traite.md</t>
+          <t>corpus/livre-20/c12-les-pouvoirs-non-delegables.md</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" s="2" t="inlineStr">
         <is>
-          <t>L20.C15</t>
+          <t>L20.C13</t>
         </is>
       </c>
       <c r="B213" s="3" t="inlineStr">
@@ -14637,7 +14637,7 @@
       </c>
       <c r="C213" s="3" t="inlineStr">
         <is>
-          <t>Le devoir international des agents</t>
+          <t>L'entrée en vigueur, l'adhésion et le retrait</t>
         </is>
       </c>
       <c r="D213" s="3" t="inlineStr">
@@ -14662,35 +14662,35 @@
       </c>
       <c r="H213" s="3" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="I213" s="3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J213" s="3" t="n">
         <v>3</v>
       </c>
       <c r="K213" s="3" t="inlineStr">
         <is>
-          <t>robustesse, regle_contre_discretion, indicateur_de_progres</t>
+          <t>seuil_d_activation, reflux_collectif, fenetre_de_reforme, additionnalite</t>
         </is>
       </c>
       <c r="L213" s="3" t="inlineStr">
         <is>
-          <t>L7.C04, L7.C07, L7.C10, L11.C21, L11.C25, L20.C01, L20.C04, L20.C11, L20.C14</t>
+          <t>L7.C11, L7.C12, L7.C16, L7.C17, L7.C19, L11.C18, L20.C01, L20.C06, L20.C09, L20.C12</t>
         </is>
       </c>
       <c r="M213" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-20/c15-le-devoir-international-des-agents.md</t>
+          <t>corpus/livre-20/c13-l-entree-en-vigueur-l-adhesion-et-le-retrait.md</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" s="2" t="inlineStr">
         <is>
-          <t>L20.C16</t>
+          <t>L20.C14</t>
         </is>
       </c>
       <c r="B214" s="3" t="inlineStr">
@@ -14700,7 +14700,7 @@
       </c>
       <c r="C214" s="3" t="inlineStr">
         <is>
-          <t>Le patrimoine commun de l'humanité</t>
+          <t>Qui interprète le traité</t>
         </is>
       </c>
       <c r="D214" s="3" t="inlineStr">
@@ -14736,24 +14736,24 @@
       </c>
       <c r="K214" s="3" t="inlineStr">
         <is>
-          <t>communs, valorisation_des_communs, limites_planetaires, additionnalite, plafond_ecologique</t>
+          <t>robustesse, regle_contre_discretion, communs</t>
         </is>
       </c>
       <c r="L214" s="3" t="inlineStr">
         <is>
-          <t>L1.C17, L1.C22, L7.C05, L7.C13, L11.C16, L20.C01, L20.C11, L20.C17, L20.C22</t>
+          <t>L7.C07, L7.C13, L7.C14, L7.C19, L11.C19, L11.C25, L20.C01, L20.C03, L20.C11, L20.C12, L20.C21</t>
         </is>
       </c>
       <c r="M214" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-20/c16-le-patrimoine-commun-de-l-humanite.md</t>
+          <t>corpus/livre-20/c14-qui-interprete-le-traite.md</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" s="2" t="inlineStr">
         <is>
-          <t>L20.C17</t>
+          <t>L20.C15</t>
         </is>
       </c>
       <c r="B215" s="3" t="inlineStr">
@@ -14763,7 +14763,7 @@
       </c>
       <c r="C215" s="3" t="inlineStr">
         <is>
-          <t>La sanctuarisation, et elle existe</t>
+          <t>Le devoir international des agents</t>
         </is>
       </c>
       <c r="D215" s="3" t="inlineStr">
@@ -14788,35 +14788,35 @@
       </c>
       <c r="H215" s="3" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="I215" s="3" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J215" s="3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K215" s="3" t="inlineStr">
         <is>
-          <t>communs, limites_planetaires, fenetre_de_reforme, robustesse, plafond_ecologique</t>
+          <t>robustesse, regle_contre_discretion, indicateur_de_progres</t>
         </is>
       </c>
       <c r="L215" s="3" t="inlineStr">
         <is>
-          <t>L1.C17, L1.C18, L7.C13, L7.C19, L7.C20, L11.C20, L20.C01, L20.C06, L20.C09, L20.C16, L20.C22</t>
+          <t>L7.C04, L7.C07, L7.C10, L11.C21, L11.C25, L20.C01, L20.C04, L20.C11, L20.C14</t>
         </is>
       </c>
       <c r="M215" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-20/c17-la-sanctuarisation-et-elle-existe.md</t>
+          <t>corpus/livre-20/c15-le-devoir-international-des-agents.md</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" s="2" t="inlineStr">
         <is>
-          <t>L20.C18</t>
+          <t>L20.C16</t>
         </is>
       </c>
       <c r="B216" s="3" t="inlineStr">
@@ -14826,7 +14826,7 @@
       </c>
       <c r="C216" s="3" t="inlineStr">
         <is>
-          <t>L'amendement et la dérogation dans l'ordre commercial</t>
+          <t>Le patrimoine commun de l'humanité</t>
         </is>
       </c>
       <c r="D216" s="3" t="inlineStr">
@@ -14851,7 +14851,7 @@
       </c>
       <c r="H216" s="3" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="I216" s="3" t="n">
@@ -14862,24 +14862,24 @@
       </c>
       <c r="K216" s="3" t="inlineStr">
         <is>
-          <t>bareme, seuil_d_activation, additionnalite, fenetre_de_reforme</t>
+          <t>communs, valorisation_des_communs, limites_planetaires, additionnalite, plafond_ecologique</t>
         </is>
       </c>
       <c r="L216" s="3" t="inlineStr">
         <is>
-          <t>L1.C27, L7.C17, L7.C20, L11.C24, L20.C01, L20.C06, L20.C09, L20.C13, L20.C19, L20.C20</t>
+          <t>L1.C17, L1.C22, L7.C05, L7.C13, L11.C16, L20.C01, L20.C11, L20.C17, L20.C22</t>
         </is>
       </c>
       <c r="M216" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-20/c18-l-amendement-et-la-derogation-dans-l-ordre-commercial.md</t>
+          <t>corpus/livre-20/c16-le-patrimoine-commun-de-l-humanite.md</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" s="2" t="inlineStr">
         <is>
-          <t>L20.C19</t>
+          <t>L20.C17</t>
         </is>
       </c>
       <c r="B217" s="3" t="inlineStr">
@@ -14889,7 +14889,7 @@
       </c>
       <c r="C217" s="3" t="inlineStr">
         <is>
-          <t>Le texte que la conformité invoque</t>
+          <t>La sanctuarisation, et elle existe</t>
         </is>
       </c>
       <c r="D217" s="3" t="inlineStr">
@@ -14921,28 +14921,28 @@
         <v>4</v>
       </c>
       <c r="J217" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K217" s="3" t="inlineStr">
         <is>
-          <t>bareme, additionnalite, limites_planetaires, seuil_d_activation, externalisation</t>
+          <t>communs, limites_planetaires, fenetre_de_reforme, robustesse, plafond_ecologique</t>
         </is>
       </c>
       <c r="L217" s="3" t="inlineStr">
         <is>
-          <t>L1.C27, L7.C17, L11.C24, L20.C01, L20.C18, L20.C20, L20.C22</t>
+          <t>L1.C17, L1.C18, L7.C13, L7.C19, L7.C20, L11.C20, L20.C01, L20.C06, L20.C09, L20.C16, L20.C22</t>
         </is>
       </c>
       <c r="M217" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-20/c19-le-texte-que-la-conformite-invoque.md</t>
+          <t>corpus/livre-20/c17-la-sanctuarisation-et-elle-existe.md</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" s="2" t="inlineStr">
         <is>
-          <t>L20.C20</t>
+          <t>L20.C18</t>
         </is>
       </c>
       <c r="B218" s="3" t="inlineStr">
@@ -14952,7 +14952,7 @@
       </c>
       <c r="C218" s="3" t="inlineStr">
         <is>
-          <t>L'ajustement aux frontières comme précédent</t>
+          <t>L'amendement et la dérogation dans l'ordre commercial</t>
         </is>
       </c>
       <c r="D218" s="3" t="inlineStr">
@@ -14981,31 +14981,31 @@
         </is>
       </c>
       <c r="I218" s="3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J218" s="3" t="n">
         <v>3</v>
       </c>
       <c r="K218" s="3" t="inlineStr">
         <is>
-          <t>bareme, seuil_d_activation, externalisation, additionnalite, contrepartie_comptable</t>
+          <t>bareme, seuil_d_activation, additionnalite, fenetre_de_reforme</t>
         </is>
       </c>
       <c r="L218" s="3" t="inlineStr">
         <is>
-          <t>L1.C27, L7.C17, L11.C21, L11.C24, L11.C25, L20.C01, L20.C18, L20.C19, L20.C22</t>
+          <t>L1.C27, L7.C17, L7.C20, L11.C24, L20.C01, L20.C06, L20.C09, L20.C13, L20.C19, L20.C20</t>
         </is>
       </c>
       <c r="M218" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-20/c20-l-ajustement-aux-frontieres-comme-precedent.md</t>
+          <t>corpus/livre-20/c18-l-amendement-et-la-derogation-dans-l-ordre-commercial.md</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" s="2" t="inlineStr">
         <is>
-          <t>L20.C21</t>
+          <t>L20.C19</t>
         </is>
       </c>
       <c r="B219" s="3" t="inlineStr">
@@ -15015,7 +15015,7 @@
       </c>
       <c r="C219" s="3" t="inlineStr">
         <is>
-          <t>La transparence et sa limite juridictionnelle</t>
+          <t>Le texte que la conformité invoque</t>
         </is>
       </c>
       <c r="D219" s="3" t="inlineStr">
@@ -15040,35 +15040,35 @@
       </c>
       <c r="H219" s="3" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="I219" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J219" s="3" t="n">
         <v>3</v>
       </c>
       <c r="K219" s="3" t="inlineStr">
         <is>
-          <t>robustesse, contrepartie_comptable, bareme, monnaie_comme_registre</t>
+          <t>bareme, additionnalite, limites_planetaires, seuil_d_activation, externalisation</t>
         </is>
       </c>
       <c r="L219" s="3" t="inlineStr">
         <is>
-          <t>L7.C18, L11.C21, L11.C24, L11.C25, L20.C01, L20.C11, L20.C14, L20.C20, L20.C22</t>
+          <t>L1.C27, L7.C17, L11.C24, L20.C01, L20.C18, L20.C20, L20.C22</t>
         </is>
       </c>
       <c r="M219" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-20/c21-la-transparence-et-sa-limite-juridictionnelle.md</t>
+          <t>corpus/livre-20/c19-le-texte-que-la-conformite-invoque.md</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" s="2" t="inlineStr">
         <is>
-          <t>L20.C22</t>
+          <t>L20.C20</t>
         </is>
       </c>
       <c r="B220" s="3" t="inlineStr">
@@ -15078,7 +15078,7 @@
       </c>
       <c r="C220" s="3" t="inlineStr">
         <is>
-          <t>Ce que le droit devrait devenir</t>
+          <t>L'ajustement aux frontières comme précédent</t>
         </is>
       </c>
       <c r="D220" s="3" t="inlineStr">
@@ -15107,92 +15107,218 @@
         </is>
       </c>
       <c r="I220" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J220" s="3" t="n">
         <v>3</v>
       </c>
       <c r="K220" s="3" t="inlineStr">
         <is>
-          <t>fenetre_de_reforme, communs, limites_planetaires, regle_contre_discretion, bareme, referentiel_de_change</t>
+          <t>bareme, seuil_d_activation, externalisation, additionnalite, contrepartie_comptable</t>
         </is>
       </c>
       <c r="L220" s="3" t="inlineStr">
         <is>
-          <t>L1.C18, L7.C12, L7.C13, L11.C15, L11.C25, L20.C01, L20.C03, L20.C06, L20.C07, L20.C08, L20.C12, L20.C13, L20.C16, L20.C17, L20.C19, L20.C20, L20.C21, L20.C23</t>
+          <t>L1.C27, L7.C17, L11.C21, L11.C24, L11.C25, L20.C01, L20.C18, L20.C19, L20.C22</t>
         </is>
       </c>
       <c r="M220" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-20/c22-ce-que-le-droit-devrait-devenir.md</t>
+          <t>corpus/livre-20/c20-l-ajustement-aux-frontieres-comme-precedent.md</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" s="2" t="inlineStr">
         <is>
+          <t>L20.C21</t>
+        </is>
+      </c>
+      <c r="B221" s="3" t="inlineStr">
+        <is>
+          <t>L20</t>
+        </is>
+      </c>
+      <c r="C221" s="3" t="inlineStr">
+        <is>
+          <t>La transparence et sa limite juridictionnelle</t>
+        </is>
+      </c>
+      <c r="D221" s="3" t="inlineStr">
+        <is>
+          <t>brouillon</t>
+        </is>
+      </c>
+      <c r="E221" s="3" t="inlineStr">
+        <is>
+          <t>preparatoire</t>
+        </is>
+      </c>
+      <c r="F221" s="3" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="G221" s="3" t="inlineStr">
+        <is>
+          <t>conception</t>
+        </is>
+      </c>
+      <c r="H221" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="I221" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="J221" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="K221" s="3" t="inlineStr">
+        <is>
+          <t>robustesse, contrepartie_comptable, bareme, monnaie_comme_registre</t>
+        </is>
+      </c>
+      <c r="L221" s="3" t="inlineStr">
+        <is>
+          <t>L7.C18, L11.C21, L11.C24, L11.C25, L20.C01, L20.C11, L20.C14, L20.C20, L20.C22</t>
+        </is>
+      </c>
+      <c r="M221" s="3" t="inlineStr">
+        <is>
+          <t>corpus/livre-20/c21-la-transparence-et-sa-limite-juridictionnelle.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" s="2" t="inlineStr">
+        <is>
+          <t>L20.C22</t>
+        </is>
+      </c>
+      <c r="B222" s="3" t="inlineStr">
+        <is>
+          <t>L20</t>
+        </is>
+      </c>
+      <c r="C222" s="3" t="inlineStr">
+        <is>
+          <t>Ce que le droit devrait devenir</t>
+        </is>
+      </c>
+      <c r="D222" s="3" t="inlineStr">
+        <is>
+          <t>brouillon</t>
+        </is>
+      </c>
+      <c r="E222" s="3" t="inlineStr">
+        <is>
+          <t>preparatoire</t>
+        </is>
+      </c>
+      <c r="F222" s="3" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="G222" s="3" t="inlineStr">
+        <is>
+          <t>conception</t>
+        </is>
+      </c>
+      <c r="H222" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="I222" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="J222" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="K222" s="3" t="inlineStr">
+        <is>
+          <t>fenetre_de_reforme, communs, limites_planetaires, regle_contre_discretion, bareme, referentiel_de_change</t>
+        </is>
+      </c>
+      <c r="L222" s="3" t="inlineStr">
+        <is>
+          <t>L1.C18, L7.C12, L7.C13, L11.C15, L11.C25, L20.C01, L20.C03, L20.C06, L20.C07, L20.C08, L20.C12, L20.C13, L20.C16, L20.C17, L20.C19, L20.C20, L20.C21, L20.C23</t>
+        </is>
+      </c>
+      <c r="M222" s="3" t="inlineStr">
+        <is>
+          <t>corpus/livre-20/c22-ce-que-le-droit-devrait-devenir.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" s="2" t="inlineStr">
+        <is>
           <t>L20.C23</t>
         </is>
       </c>
-      <c r="B221" s="3" t="inlineStr">
+      <c r="B223" s="3" t="inlineStr">
         <is>
           <t>L20</t>
         </is>
       </c>
-      <c r="C221" s="3" t="inlineStr">
+      <c r="C223" s="3" t="inlineStr">
         <is>
           <t>La portée du livre</t>
         </is>
       </c>
-      <c r="D221" s="3" t="inlineStr">
-        <is>
-          <t>brouillon</t>
-        </is>
-      </c>
-      <c r="E221" s="3" t="inlineStr">
-        <is>
-          <t>preparatoire</t>
-        </is>
-      </c>
-      <c r="F221" s="3" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="G221" s="3" t="inlineStr">
+      <c r="D223" s="3" t="inlineStr">
+        <is>
+          <t>brouillon</t>
+        </is>
+      </c>
+      <c r="E223" s="3" t="inlineStr">
+        <is>
+          <t>preparatoire</t>
+        </is>
+      </c>
+      <c r="F223" s="3" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="G223" s="3" t="inlineStr">
         <is>
           <t>conception</t>
         </is>
       </c>
-      <c r="H221" s="3" t="inlineStr">
+      <c r="H223" s="3" t="inlineStr">
         <is>
           <t>2026-09-06</t>
         </is>
       </c>
-      <c r="I221" s="3" t="n">
+      <c r="I223" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="J221" s="3" t="n">
+      <c r="J223" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="K221" s="3" t="inlineStr">
+      <c r="K223" s="3" t="inlineStr">
         <is>
           <t>fenetre_de_reforme, communs, limites_planetaires, creation_monetaire, robustesse</t>
         </is>
       </c>
-      <c r="L221" s="3" t="inlineStr">
+      <c r="L223" s="3" t="inlineStr">
         <is>
           <t>L1.C18, L1.C27, L7.C05, L7.C10, L7.C12, L7.C13, L11.C15, L11.C24, L11.C25, L20.C01, L20.C02, L20.C03, L20.C06, L20.C07, L20.C08, L20.C11, L20.C12, L20.C13, L20.C16, L20.C17, L20.C19, L20.C20, L20.C21, L20.C22</t>
         </is>
       </c>
-      <c r="M221" s="3" t="inlineStr">
+      <c r="M223" s="3" t="inlineStr">
         <is>
           <t>corpus/livre-20/c23-la-portee-du-livre.md</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:M221"/>
+  <autoFilter ref="A1:M223"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -15271,7 +15397,7 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>220</v>
+        <v>222</v>
       </c>
     </row>
     <row r="7">
@@ -15281,7 +15407,7 @@
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>211</v>
+        <v>213</v>
       </c>
     </row>
     <row r="8">
@@ -15301,7 +15427,7 @@
         </is>
       </c>
       <c r="B9" s="3" t="n">
-        <v>1120</v>
+        <v>1127</v>
       </c>
     </row>
     <row r="10">
@@ -15311,7 +15437,7 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>930</v>
+        <v>936</v>
       </c>
     </row>
     <row r="11">
@@ -15393,7 +15519,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C249"/>
+  <dimension ref="A1:C251"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -18322,7 +18448,7 @@
       </c>
       <c r="C173" s="6" t="inlineStr">
         <is>
-          <t>exploratoire — 1 chapitre(s)</t>
+          <t>en-cours — 3 chapitre(s)</t>
         </is>
       </c>
     </row>
@@ -18344,31 +18470,31 @@
       </c>
     </row>
     <row r="175">
-      <c r="A175" s="6" t="inlineStr">
-        <is>
-          <t>L11</t>
-        </is>
-      </c>
-      <c r="B175" s="6" t="inlineStr">
-        <is>
-          <t>Ingénierie des barèmes : reflux, qualification, périmètre et pondérations</t>
-        </is>
-      </c>
-      <c r="C175" s="6" t="inlineStr">
-        <is>
-          <t>defrichage — 29 chapitre(s)</t>
+      <c r="A175" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    L10.C02</t>
+        </is>
+      </c>
+      <c r="B175" s="3" t="inlineStr">
+        <is>
+          <t>La dérogation existe, et elle referme une tenaille</t>
+        </is>
+      </c>
+      <c r="C175" s="3" t="inlineStr">
+        <is>
+          <t>brouillon</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L11.C01</t>
+          <t xml:space="preserve">    L10.C03</t>
         </is>
       </c>
       <c r="B176" s="3" t="inlineStr">
         <is>
-          <t>Reflux ou destruction — la bifurcation</t>
+          <t>La certitude qui fait marcher le dispositif est celle que la Cour interdit</t>
         </is>
       </c>
       <c r="C176" s="3" t="inlineStr">
@@ -18378,31 +18504,31 @@
       </c>
     </row>
     <row r="177">
-      <c r="A177" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    L11.C02</t>
-        </is>
-      </c>
-      <c r="B177" s="3" t="inlineStr">
-        <is>
-          <t>Le trajet complet de la valeur</t>
-        </is>
-      </c>
-      <c r="C177" s="3" t="inlineStr">
-        <is>
-          <t>brouillon</t>
+      <c r="A177" s="6" t="inlineStr">
+        <is>
+          <t>L11</t>
+        </is>
+      </c>
+      <c r="B177" s="6" t="inlineStr">
+        <is>
+          <t>Ingénierie des barèmes : reflux, qualification, périmètre et pondérations</t>
+        </is>
+      </c>
+      <c r="C177" s="6" t="inlineStr">
+        <is>
+          <t>defrichage — 29 chapitre(s)</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L11.C03</t>
+          <t xml:space="preserve">    L11.C01</t>
         </is>
       </c>
       <c r="B178" s="3" t="inlineStr">
         <is>
-          <t>Le compte des objectifs et des instruments</t>
+          <t>Reflux ou destruction — la bifurcation</t>
         </is>
       </c>
       <c r="C178" s="3" t="inlineStr">
@@ -18414,12 +18540,12 @@
     <row r="179">
       <c r="A179" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L11.C04</t>
+          <t xml:space="preserve">    L11.C02</t>
         </is>
       </c>
       <c r="B179" s="3" t="inlineStr">
         <is>
-          <t>Les instruments du reflux sous parité fixe</t>
+          <t>Le trajet complet de la valeur</t>
         </is>
       </c>
       <c r="C179" s="3" t="inlineStr">
@@ -18431,12 +18557,12 @@
     <row r="180">
       <c r="A180" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L11.C05</t>
+          <t xml:space="preserve">    L11.C03</t>
         </is>
       </c>
       <c r="B180" s="3" t="inlineStr">
         <is>
-          <t>L'assiette du reflux transactionnel</t>
+          <t>Le compte des objectifs et des instruments</t>
         </is>
       </c>
       <c r="C180" s="3" t="inlineStr">
@@ -18448,12 +18574,12 @@
     <row r="181">
       <c r="A181" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L11.C06</t>
+          <t xml:space="preserve">    L11.C04</t>
         </is>
       </c>
       <c r="B181" s="3" t="inlineStr">
         <is>
-          <t>Le barème par défaut</t>
+          <t>Les instruments du reflux sous parité fixe</t>
         </is>
       </c>
       <c r="C181" s="3" t="inlineStr">
@@ -18465,12 +18591,12 @@
     <row r="182">
       <c r="A182" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L11.C07</t>
+          <t xml:space="preserve">    L11.C05</t>
         </is>
       </c>
       <c r="B182" s="3" t="inlineStr">
         <is>
-          <t>Le demurrage et son nœud de prélèvement</t>
+          <t>L'assiette du reflux transactionnel</t>
         </is>
       </c>
       <c r="C182" s="3" t="inlineStr">
@@ -18482,12 +18608,12 @@
     <row r="183">
       <c r="A183" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L11.C08</t>
+          <t xml:space="preserve">    L11.C06</t>
         </is>
       </c>
       <c r="B183" s="3" t="inlineStr">
         <is>
-          <t>Les dérogations</t>
+          <t>Le barème par défaut</t>
         </is>
       </c>
       <c r="C183" s="3" t="inlineStr">
@@ -18499,12 +18625,12 @@
     <row r="184">
       <c r="A184" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L11.C09</t>
+          <t xml:space="preserve">    L11.C07</t>
         </is>
       </c>
       <c r="B184" s="3" t="inlineStr">
         <is>
-          <t>L'incidence — qui paie le reflux</t>
+          <t>Le demurrage et son nœud de prélèvement</t>
         </is>
       </c>
       <c r="C184" s="3" t="inlineStr">
@@ -18516,12 +18642,12 @@
     <row r="185">
       <c r="A185" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L11.C10</t>
+          <t xml:space="preserve">    L11.C08</t>
         </is>
       </c>
       <c r="B185" s="3" t="inlineStr">
         <is>
-          <t>La trajectoire de mise en place</t>
+          <t>Les dérogations</t>
         </is>
       </c>
       <c r="C185" s="3" t="inlineStr">
@@ -18533,12 +18659,12 @@
     <row r="186">
       <c r="A186" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L11.C11</t>
+          <t xml:space="preserve">    L11.C09</t>
         </is>
       </c>
       <c r="B186" s="3" t="inlineStr">
         <is>
-          <t>Qui arrête le barème</t>
+          <t>L'incidence — qui paie le reflux</t>
         </is>
       </c>
       <c r="C186" s="3" t="inlineStr">
@@ -18550,12 +18676,12 @@
     <row r="187">
       <c r="A187" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L11.C12</t>
+          <t xml:space="preserve">    L11.C10</t>
         </is>
       </c>
       <c r="B187" s="3" t="inlineStr">
         <is>
-          <t>La directive</t>
+          <t>La trajectoire de mise en place</t>
         </is>
       </c>
       <c r="C187" s="3" t="inlineStr">
@@ -18567,12 +18693,12 @@
     <row r="188">
       <c r="A188" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L11.C13</t>
+          <t xml:space="preserve">    L11.C11</t>
         </is>
       </c>
       <c r="B188" s="3" t="inlineStr">
         <is>
-          <t>Le barème de qualification</t>
+          <t>Qui arrête le barème</t>
         </is>
       </c>
       <c r="C188" s="3" t="inlineStr">
@@ -18584,12 +18710,12 @@
     <row r="189">
       <c r="A189" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L11.C14</t>
+          <t xml:space="preserve">    L11.C12</t>
         </is>
       </c>
       <c r="B189" s="3" t="inlineStr">
         <is>
-          <t>Le tableau de bord, ou les données de la directive</t>
+          <t>La directive</t>
         </is>
       </c>
       <c r="C189" s="3" t="inlineStr">
@@ -18601,12 +18727,12 @@
     <row r="190">
       <c r="A190" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L11.C15</t>
+          <t xml:space="preserve">    L11.C13</t>
         </is>
       </c>
       <c r="B190" s="3" t="inlineStr">
         <is>
-          <t>Les parités du référentiel de change</t>
+          <t>Le barème de qualification</t>
         </is>
       </c>
       <c r="C190" s="3" t="inlineStr">
@@ -18618,12 +18744,12 @@
     <row r="191">
       <c r="A191" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L11.C16</t>
+          <t xml:space="preserve">    L11.C14</t>
         </is>
       </c>
       <c r="B191" s="3" t="inlineStr">
         <is>
-          <t>La valorisation des communs</t>
+          <t>Le tableau de bord, ou les données de la directive</t>
         </is>
       </c>
       <c r="C191" s="3" t="inlineStr">
@@ -18635,12 +18761,12 @@
     <row r="192">
       <c r="A192" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L11.C17</t>
+          <t xml:space="preserve">    L11.C15</t>
         </is>
       </c>
       <c r="B192" s="3" t="inlineStr">
         <is>
-          <t>La cohérence des cinq barèmes</t>
+          <t>Les parités du référentiel de change</t>
         </is>
       </c>
       <c r="C192" s="3" t="inlineStr">
@@ -18652,12 +18778,12 @@
     <row r="193">
       <c r="A193" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L11.C18</t>
+          <t xml:space="preserve">    L11.C16</t>
         </is>
       </c>
       <c r="B193" s="3" t="inlineStr">
         <is>
-          <t>Le seuil d'exemption</t>
+          <t>La valorisation des communs</t>
         </is>
       </c>
       <c r="C193" s="3" t="inlineStr">
@@ -18669,12 +18795,12 @@
     <row r="194">
       <c r="A194" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L11.C19</t>
+          <t xml:space="preserve">    L11.C17</t>
         </is>
       </c>
       <c r="B194" s="3" t="inlineStr">
         <is>
-          <t>Le recours</t>
+          <t>La cohérence des cinq barèmes</t>
         </is>
       </c>
       <c r="C194" s="3" t="inlineStr">
@@ -18686,12 +18812,12 @@
     <row r="195">
       <c r="A195" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L11.C20</t>
+          <t xml:space="preserve">    L11.C18</t>
         </is>
       </c>
       <c r="B195" s="3" t="inlineStr">
         <is>
-          <t>L'amendement de la directive</t>
+          <t>Le seuil d'exemption</t>
         </is>
       </c>
       <c r="C195" s="3" t="inlineStr">
@@ -18703,12 +18829,12 @@
     <row r="196">
       <c r="A196" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L11.C21</t>
+          <t xml:space="preserve">    L11.C19</t>
         </is>
       </c>
       <c r="B196" s="3" t="inlineStr">
         <is>
-          <t>La perception</t>
+          <t>Le recours</t>
         </is>
       </c>
       <c r="C196" s="3" t="inlineStr">
@@ -18720,12 +18846,12 @@
     <row r="197">
       <c r="A197" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L11.C22</t>
+          <t xml:space="preserve">    L11.C20</t>
         </is>
       </c>
       <c r="B197" s="3" t="inlineStr">
         <is>
-          <t>Les délais</t>
+          <t>L'amendement de la directive</t>
         </is>
       </c>
       <c r="C197" s="3" t="inlineStr">
@@ -18737,12 +18863,12 @@
     <row r="198">
       <c r="A198" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L11.C23</t>
+          <t xml:space="preserve">    L11.C21</t>
         </is>
       </c>
       <c r="B198" s="3" t="inlineStr">
         <is>
-          <t>La contracyclicité</t>
+          <t>La perception</t>
         </is>
       </c>
       <c r="C198" s="3" t="inlineStr">
@@ -18754,12 +18880,12 @@
     <row r="199">
       <c r="A199" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L11.C24</t>
+          <t xml:space="preserve">    L11.C22</t>
         </is>
       </c>
       <c r="B199" s="3" t="inlineStr">
         <is>
-          <t>Le barème aux frontières</t>
+          <t>Les délais</t>
         </is>
       </c>
       <c r="C199" s="3" t="inlineStr">
@@ -18771,12 +18897,12 @@
     <row r="200">
       <c r="A200" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L11.C25</t>
+          <t xml:space="preserve">    L11.C23</t>
         </is>
       </c>
       <c r="B200" s="3" t="inlineStr">
         <is>
-          <t>Le contrôle</t>
+          <t>La contracyclicité</t>
         </is>
       </c>
       <c r="C200" s="3" t="inlineStr">
@@ -18788,12 +18914,12 @@
     <row r="201">
       <c r="A201" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L11.C26</t>
+          <t xml:space="preserve">    L11.C24</t>
         </is>
       </c>
       <c r="B201" s="3" t="inlineStr">
         <is>
-          <t>La portée du Livre 11</t>
+          <t>Le barème aux frontières</t>
         </is>
       </c>
       <c r="C201" s="3" t="inlineStr">
@@ -18805,12 +18931,12 @@
     <row r="202">
       <c r="A202" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L11.C27</t>
+          <t xml:space="preserve">    L11.C25</t>
         </is>
       </c>
       <c r="B202" s="3" t="inlineStr">
         <is>
-          <t>L'assiette de la fonte est celle de la TVA</t>
+          <t>Le contrôle</t>
         </is>
       </c>
       <c r="C202" s="3" t="inlineStr">
@@ -18822,12 +18948,12 @@
     <row r="203">
       <c r="A203" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L11.C28</t>
+          <t xml:space="preserve">    L11.C26</t>
         </is>
       </c>
       <c r="B203" s="3" t="inlineStr">
         <is>
-          <t>La fonte sur les acquisitions d'actifs, éprouvée</t>
+          <t>La portée du Livre 11</t>
         </is>
       </c>
       <c r="C203" s="3" t="inlineStr">
@@ -18839,55 +18965,63 @@
     <row r="204">
       <c r="A204" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">    L11.C27</t>
+        </is>
+      </c>
+      <c r="B204" s="3" t="inlineStr">
+        <is>
+          <t>L'assiette de la fonte est celle de la TVA</t>
+        </is>
+      </c>
+      <c r="C204" s="3" t="inlineStr">
+        <is>
+          <t>brouillon</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    L11.C28</t>
+        </is>
+      </c>
+      <c r="B205" s="3" t="inlineStr">
+        <is>
+          <t>La fonte sur les acquisitions d'actifs, éprouvée</t>
+        </is>
+      </c>
+      <c r="C205" s="3" t="inlineStr">
+        <is>
+          <t>brouillon</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">    L11.C29</t>
         </is>
       </c>
-      <c r="B204" s="3" t="inlineStr">
+      <c r="B206" s="3" t="inlineStr">
         <is>
           <t>La structure des sanctions</t>
         </is>
       </c>
-      <c r="C204" s="3" t="inlineStr">
-        <is>
-          <t>brouillon</t>
-        </is>
-      </c>
-    </row>
-    <row r="205">
-      <c r="A205" s="6" t="inlineStr">
-        <is>
-          <t>L12</t>
-        </is>
-      </c>
-      <c r="B205" s="6" t="inlineStr">
-        <is>
-          <t>Comment réaliser les ODD avec NEMO IMS ?</t>
-        </is>
-      </c>
-      <c r="C205" s="6" t="inlineStr">
-        <is>
-          <t>candidat — 0 chapitre(s)</t>
-        </is>
-      </c>
-    </row>
-    <row r="206">
-      <c r="A206" s="7" t="inlineStr"/>
-      <c r="B206" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    (aucun chapitre écrit)</t>
-        </is>
-      </c>
-      <c r="C206" s="7" t="inlineStr"/>
+      <c r="C206" s="3" t="inlineStr">
+        <is>
+          <t>brouillon</t>
+        </is>
+      </c>
     </row>
     <row r="207">
       <c r="A207" s="6" t="inlineStr">
         <is>
-          <t>L13</t>
+          <t>L12</t>
         </is>
       </c>
       <c r="B207" s="6" t="inlineStr">
         <is>
-          <t>Méthodes, données, scénarios et simulateur NEMO IMS</t>
+          <t>Comment réaliser les ODD avec NEMO IMS ?</t>
         </is>
       </c>
       <c r="C207" s="6" t="inlineStr">
@@ -18908,12 +19042,12 @@
     <row r="209">
       <c r="A209" s="6" t="inlineStr">
         <is>
-          <t>L14</t>
+          <t>L13</t>
         </is>
       </c>
       <c r="B209" s="6" t="inlineStr">
         <is>
-          <t>Gouverner la preuve : méthodes, vérification et traçabilité</t>
+          <t>Méthodes, données, scénarios et simulateur NEMO IMS</t>
         </is>
       </c>
       <c r="C209" s="6" t="inlineStr">
@@ -18934,17 +19068,17 @@
     <row r="211">
       <c r="A211" s="6" t="inlineStr">
         <is>
-          <t>L15</t>
+          <t>L14</t>
         </is>
       </c>
       <c r="B211" s="6" t="inlineStr">
         <is>
-          <t>Fraudes, corruptions et architectures de la triche</t>
+          <t>Gouverner la preuve : méthodes, vérification et traçabilité</t>
         </is>
       </c>
       <c r="C211" s="6" t="inlineStr">
         <is>
-          <t>exploratoire — 0 chapitre(s)</t>
+          <t>candidat — 0 chapitre(s)</t>
         </is>
       </c>
     </row>
@@ -18960,17 +19094,17 @@
     <row r="213">
       <c r="A213" s="6" t="inlineStr">
         <is>
-          <t>L16</t>
+          <t>L15</t>
         </is>
       </c>
       <c r="B213" s="6" t="inlineStr">
         <is>
-          <t>Typologie comparée des systèmes et alternatives monétaires</t>
+          <t>Fraudes, corruptions et architectures de la triche</t>
         </is>
       </c>
       <c r="C213" s="6" t="inlineStr">
         <is>
-          <t>candidat — 0 chapitre(s)</t>
+          <t>exploratoire — 0 chapitre(s)</t>
         </is>
       </c>
     </row>
@@ -18986,12 +19120,12 @@
     <row r="215">
       <c r="A215" s="6" t="inlineStr">
         <is>
-          <t>L17</t>
+          <t>L16</t>
         </is>
       </c>
       <c r="B215" s="6" t="inlineStr">
         <is>
-          <t>Après la croissance : décroissance, post-croissance et prospérité sans croissance</t>
+          <t>Typologie comparée des systèmes et alternatives monétaires</t>
         </is>
       </c>
       <c r="C215" s="6" t="inlineStr">
@@ -19012,63 +19146,55 @@
     <row r="217">
       <c r="A217" s="6" t="inlineStr">
         <is>
+          <t>L17</t>
+        </is>
+      </c>
+      <c r="B217" s="6" t="inlineStr">
+        <is>
+          <t>Après la croissance : décroissance, post-croissance et prospérité sans croissance</t>
+        </is>
+      </c>
+      <c r="C217" s="6" t="inlineStr">
+        <is>
+          <t>candidat — 0 chapitre(s)</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" s="7" t="inlineStr"/>
+      <c r="B218" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    (aucun chapitre écrit)</t>
+        </is>
+      </c>
+      <c r="C218" s="7" t="inlineStr"/>
+    </row>
+    <row r="219">
+      <c r="A219" s="6" t="inlineStr">
+        <is>
           <t>L18</t>
         </is>
       </c>
-      <c r="B217" s="6" t="inlineStr">
+      <c r="B219" s="6" t="inlineStr">
         <is>
           <t>Comptabilités écologiques, sociales et biophysiques</t>
         </is>
       </c>
-      <c r="C217" s="6" t="inlineStr">
+      <c r="C219" s="6" t="inlineStr">
         <is>
           <t>en-cours — 8 chapitre(s)</t>
-        </is>
-      </c>
-    </row>
-    <row r="218">
-      <c r="A218" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    L18.C01</t>
-        </is>
-      </c>
-      <c r="B218" s="3" t="inlineStr">
-        <is>
-          <t>Ce que ce livre doit établir, et le repli n'est pas l'annexe</t>
-        </is>
-      </c>
-      <c r="C218" s="3" t="inlineStr">
-        <is>
-          <t>brouillon</t>
-        </is>
-      </c>
-    </row>
-    <row r="219">
-      <c r="A219" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    L18.C02</t>
-        </is>
-      </c>
-      <c r="B219" s="3" t="inlineStr">
-        <is>
-          <t>La métrologie existe, et ce qu'elle enregistre est l'ordre en place</t>
-        </is>
-      </c>
-      <c r="C219" s="3" t="inlineStr">
-        <is>
-          <t>brouillon</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L18.C03</t>
+          <t xml:space="preserve">    L18.C01</t>
         </is>
       </c>
       <c r="B220" s="3" t="inlineStr">
         <is>
-          <t>L'échelle de repli, et qui l'a arrêtée</t>
+          <t>Ce que ce livre doit établir, et le repli n'est pas l'annexe</t>
         </is>
       </c>
       <c r="C220" s="3" t="inlineStr">
@@ -19080,12 +19206,12 @@
     <row r="221">
       <c r="A221" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L18.C04</t>
+          <t xml:space="preserve">    L18.C02</t>
         </is>
       </c>
       <c r="B221" s="3" t="inlineStr">
         <is>
-          <t>Les grandeurs physiques, et l'endroit où elles frappent le dispositif</t>
+          <t>La métrologie existe, et ce qu'elle enregistre est l'ordre en place</t>
         </is>
       </c>
       <c r="C221" s="3" t="inlineStr">
@@ -19097,12 +19223,12 @@
     <row r="222">
       <c r="A222" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L18.C05</t>
+          <t xml:space="preserve">    L18.C03</t>
         </is>
       </c>
       <c r="B222" s="3" t="inlineStr">
         <is>
-          <t>Le commun est ce que la norme exclut, et la symétrie de l'écriture</t>
+          <t>L'échelle de repli, et qui l'a arrêtée</t>
         </is>
       </c>
       <c r="C222" s="3" t="inlineStr">
@@ -19114,12 +19240,12 @@
     <row r="223">
       <c r="A223" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L18.C06</t>
+          <t xml:space="preserve">    L18.C04</t>
         </is>
       </c>
       <c r="B223" s="3" t="inlineStr">
         <is>
-          <t>Portée de la tranche, et une neuvième condition proposée</t>
+          <t>Les grandeurs physiques, et l'endroit où elles frappent le dispositif</t>
         </is>
       </c>
       <c r="C223" s="3" t="inlineStr">
@@ -19131,12 +19257,12 @@
     <row r="224">
       <c r="A224" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L18.C07</t>
+          <t xml:space="preserve">    L18.C05</t>
         </is>
       </c>
       <c r="B224" s="3" t="inlineStr">
         <is>
-          <t>CARE/TDL répare deux objections, et en crée une plus grave</t>
+          <t>Le commun est ce que la norme exclut, et la symétrie de l'écriture</t>
         </is>
       </c>
       <c r="C224" s="3" t="inlineStr">
@@ -19148,12 +19274,12 @@
     <row r="225">
       <c r="A225" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L18.C08</t>
+          <t xml:space="preserve">    L18.C06</t>
         </is>
       </c>
       <c r="B225" s="3" t="inlineStr">
         <is>
-          <t>Le modèle au périmètre du dispositif, et F9 révisée</t>
+          <t>Portée de la tranche, et une neuvième condition proposée</t>
         </is>
       </c>
       <c r="C225" s="3" t="inlineStr">
@@ -19163,31 +19289,31 @@
       </c>
     </row>
     <row r="226">
-      <c r="A226" s="6" t="inlineStr">
-        <is>
-          <t>L20</t>
-        </is>
-      </c>
-      <c r="B226" s="6" t="inlineStr">
-        <is>
-          <t>Droit international public, droit monétaire et commercial de la réforme</t>
-        </is>
-      </c>
-      <c r="C226" s="6" t="inlineStr">
-        <is>
-          <t>en-cours — 23 chapitre(s)</t>
+      <c r="A226" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    L18.C07</t>
+        </is>
+      </c>
+      <c r="B226" s="3" t="inlineStr">
+        <is>
+          <t>CARE/TDL répare deux objections, et en crée une plus grave</t>
+        </is>
+      </c>
+      <c r="C226" s="3" t="inlineStr">
+        <is>
+          <t>brouillon</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L20.C01</t>
+          <t xml:space="preserve">    L18.C08</t>
         </is>
       </c>
       <c r="B227" s="3" t="inlineStr">
         <is>
-          <t>Ce que ce livre doit établir</t>
+          <t>Le modèle au périmètre du dispositif, et F9 révisée</t>
         </is>
       </c>
       <c r="C227" s="3" t="inlineStr">
@@ -19197,31 +19323,31 @@
       </c>
     </row>
     <row r="228">
-      <c r="A228" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    L20.C02</t>
-        </is>
-      </c>
-      <c r="B228" s="3" t="inlineStr">
-        <is>
-          <t>L'interdiction du financement monétaire</t>
-        </is>
-      </c>
-      <c r="C228" s="3" t="inlineStr">
-        <is>
-          <t>brouillon</t>
+      <c r="A228" s="6" t="inlineStr">
+        <is>
+          <t>L20</t>
+        </is>
+      </c>
+      <c r="B228" s="6" t="inlineStr">
+        <is>
+          <t>Droit international public, droit monétaire et commercial de la réforme</t>
+        </is>
+      </c>
+      <c r="C228" s="6" t="inlineStr">
+        <is>
+          <t>en-cours — 23 chapitre(s)</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L20.C03</t>
+          <t xml:space="preserve">    L20.C01</t>
         </is>
       </c>
       <c r="B229" s="3" t="inlineStr">
         <is>
-          <t>L'objectif principal et ce qu'il exclut</t>
+          <t>Ce que ce livre doit établir</t>
         </is>
       </c>
       <c r="C229" s="3" t="inlineStr">
@@ -19233,12 +19359,12 @@
     <row r="230">
       <c r="A230" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L20.C04</t>
+          <t xml:space="preserve">    L20.C02</t>
         </is>
       </c>
       <c r="B230" s="3" t="inlineStr">
         <is>
-          <t>L'indépendance, et à l'égard de qui</t>
+          <t>L'interdiction du financement monétaire</t>
         </is>
       </c>
       <c r="C230" s="3" t="inlineStr">
@@ -19250,12 +19376,12 @@
     <row r="231">
       <c r="A231" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L20.C05</t>
+          <t xml:space="preserve">    L20.C03</t>
         </is>
       </c>
       <c r="B231" s="3" t="inlineStr">
         <is>
-          <t>Le monopole d'émission et le cours légal</t>
+          <t>L'objectif principal et ce qu'il exclut</t>
         </is>
       </c>
       <c r="C231" s="3" t="inlineStr">
@@ -19267,12 +19393,12 @@
     <row r="232">
       <c r="A232" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L20.C06</t>
+          <t xml:space="preserve">    L20.C04</t>
         </is>
       </c>
       <c r="B232" s="3" t="inlineStr">
         <is>
-          <t>Les voies de révision et leur coût</t>
+          <t>L'indépendance, et à l'égard de qui</t>
         </is>
       </c>
       <c r="C232" s="3" t="inlineStr">
@@ -19284,12 +19410,12 @@
     <row r="233">
       <c r="A233" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L20.C07</t>
+          <t xml:space="preserve">    L20.C05</t>
         </is>
       </c>
       <c r="B233" s="3" t="inlineStr">
         <is>
-          <t>L'accord monétaire international</t>
+          <t>Le monopole d'émission et le cours légal</t>
         </is>
       </c>
       <c r="C233" s="3" t="inlineStr">
@@ -19301,12 +19427,12 @@
     <row r="234">
       <c r="A234" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L20.C08</t>
+          <t xml:space="preserve">    L20.C06</t>
         </is>
       </c>
       <c r="B234" s="3" t="inlineStr">
         <is>
-          <t>La parité inscrite dans le traité</t>
+          <t>Les voies de révision et leur coût</t>
         </is>
       </c>
       <c r="C234" s="3" t="inlineStr">
@@ -19318,12 +19444,12 @@
     <row r="235">
       <c r="A235" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L20.C09</t>
+          <t xml:space="preserve">    L20.C07</t>
         </is>
       </c>
       <c r="B235" s="3" t="inlineStr">
         <is>
-          <t>L'amendement des statuts du Fonds</t>
+          <t>L'accord monétaire international</t>
         </is>
       </c>
       <c r="C235" s="3" t="inlineStr">
@@ -19335,12 +19461,12 @@
     <row r="236">
       <c r="A236" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L20.C10</t>
+          <t xml:space="preserve">    L20.C08</t>
         </is>
       </c>
       <c r="B236" s="3" t="inlineStr">
         <is>
-          <t>Le vote pondéré et les voix de base</t>
+          <t>La parité inscrite dans le traité</t>
         </is>
       </c>
       <c r="C236" s="3" t="inlineStr">
@@ -19352,12 +19478,12 @@
     <row r="237">
       <c r="A237" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L20.C11</t>
+          <t xml:space="preserve">    L20.C09</t>
         </is>
       </c>
       <c r="B237" s="3" t="inlineStr">
         <is>
-          <t>La personnalité juridique et les immunités</t>
+          <t>L'amendement des statuts du Fonds</t>
         </is>
       </c>
       <c r="C237" s="3" t="inlineStr">
@@ -19369,12 +19495,12 @@
     <row r="238">
       <c r="A238" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L20.C12</t>
+          <t xml:space="preserve">    L20.C10</t>
         </is>
       </c>
       <c r="B238" s="3" t="inlineStr">
         <is>
-          <t>Les pouvoirs non délégables</t>
+          <t>Le vote pondéré et les voix de base</t>
         </is>
       </c>
       <c r="C238" s="3" t="inlineStr">
@@ -19386,12 +19512,12 @@
     <row r="239">
       <c r="A239" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L20.C13</t>
+          <t xml:space="preserve">    L20.C11</t>
         </is>
       </c>
       <c r="B239" s="3" t="inlineStr">
         <is>
-          <t>L'entrée en vigueur, l'adhésion et le retrait</t>
+          <t>La personnalité juridique et les immunités</t>
         </is>
       </c>
       <c r="C239" s="3" t="inlineStr">
@@ -19403,12 +19529,12 @@
     <row r="240">
       <c r="A240" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L20.C14</t>
+          <t xml:space="preserve">    L20.C12</t>
         </is>
       </c>
       <c r="B240" s="3" t="inlineStr">
         <is>
-          <t>Qui interprète le traité</t>
+          <t>Les pouvoirs non délégables</t>
         </is>
       </c>
       <c r="C240" s="3" t="inlineStr">
@@ -19420,12 +19546,12 @@
     <row r="241">
       <c r="A241" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L20.C15</t>
+          <t xml:space="preserve">    L20.C13</t>
         </is>
       </c>
       <c r="B241" s="3" t="inlineStr">
         <is>
-          <t>Le devoir international des agents</t>
+          <t>L'entrée en vigueur, l'adhésion et le retrait</t>
         </is>
       </c>
       <c r="C241" s="3" t="inlineStr">
@@ -19437,12 +19563,12 @@
     <row r="242">
       <c r="A242" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L20.C16</t>
+          <t xml:space="preserve">    L20.C14</t>
         </is>
       </c>
       <c r="B242" s="3" t="inlineStr">
         <is>
-          <t>Le patrimoine commun de l'humanité</t>
+          <t>Qui interprète le traité</t>
         </is>
       </c>
       <c r="C242" s="3" t="inlineStr">
@@ -19454,12 +19580,12 @@
     <row r="243">
       <c r="A243" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L20.C17</t>
+          <t xml:space="preserve">    L20.C15</t>
         </is>
       </c>
       <c r="B243" s="3" t="inlineStr">
         <is>
-          <t>La sanctuarisation, et elle existe</t>
+          <t>Le devoir international des agents</t>
         </is>
       </c>
       <c r="C243" s="3" t="inlineStr">
@@ -19471,12 +19597,12 @@
     <row r="244">
       <c r="A244" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L20.C18</t>
+          <t xml:space="preserve">    L20.C16</t>
         </is>
       </c>
       <c r="B244" s="3" t="inlineStr">
         <is>
-          <t>L'amendement et la dérogation dans l'ordre commercial</t>
+          <t>Le patrimoine commun de l'humanité</t>
         </is>
       </c>
       <c r="C244" s="3" t="inlineStr">
@@ -19488,12 +19614,12 @@
     <row r="245">
       <c r="A245" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L20.C19</t>
+          <t xml:space="preserve">    L20.C17</t>
         </is>
       </c>
       <c r="B245" s="3" t="inlineStr">
         <is>
-          <t>Le texte que la conformité invoque</t>
+          <t>La sanctuarisation, et elle existe</t>
         </is>
       </c>
       <c r="C245" s="3" t="inlineStr">
@@ -19505,12 +19631,12 @@
     <row r="246">
       <c r="A246" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L20.C20</t>
+          <t xml:space="preserve">    L20.C18</t>
         </is>
       </c>
       <c r="B246" s="3" t="inlineStr">
         <is>
-          <t>L'ajustement aux frontières comme précédent</t>
+          <t>L'amendement et la dérogation dans l'ordre commercial</t>
         </is>
       </c>
       <c r="C246" s="3" t="inlineStr">
@@ -19522,12 +19648,12 @@
     <row r="247">
       <c r="A247" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L20.C21</t>
+          <t xml:space="preserve">    L20.C19</t>
         </is>
       </c>
       <c r="B247" s="3" t="inlineStr">
         <is>
-          <t>La transparence et sa limite juridictionnelle</t>
+          <t>Le texte que la conformité invoque</t>
         </is>
       </c>
       <c r="C247" s="3" t="inlineStr">
@@ -19539,12 +19665,12 @@
     <row r="248">
       <c r="A248" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L20.C22</t>
+          <t xml:space="preserve">    L20.C20</t>
         </is>
       </c>
       <c r="B248" s="3" t="inlineStr">
         <is>
-          <t>Ce que le droit devrait devenir</t>
+          <t>L'ajustement aux frontières comme précédent</t>
         </is>
       </c>
       <c r="C248" s="3" t="inlineStr">
@@ -19556,15 +19682,49 @@
     <row r="249">
       <c r="A249" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">    L20.C21</t>
+        </is>
+      </c>
+      <c r="B249" s="3" t="inlineStr">
+        <is>
+          <t>La transparence et sa limite juridictionnelle</t>
+        </is>
+      </c>
+      <c r="C249" s="3" t="inlineStr">
+        <is>
+          <t>brouillon</t>
+        </is>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    L20.C22</t>
+        </is>
+      </c>
+      <c r="B250" s="3" t="inlineStr">
+        <is>
+          <t>Ce que le droit devrait devenir</t>
+        </is>
+      </c>
+      <c r="C250" s="3" t="inlineStr">
+        <is>
+          <t>brouillon</t>
+        </is>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">    L20.C23</t>
         </is>
       </c>
-      <c r="B249" s="3" t="inlineStr">
+      <c r="B251" s="3" t="inlineStr">
         <is>
           <t>La portée du livre</t>
         </is>
       </c>
-      <c r="C249" s="3" t="inlineStr">
+      <c r="C251" s="3" t="inlineStr">
         <is>
           <t>brouillon</t>
         </is>

--- a/plan-des-livres.xlsx
+++ b/plan-des-livres.xlsx
@@ -13,7 +13,7 @@
     <sheet name="Plan par livre" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Chapitres'!$A$1:$M$223</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Chapitres'!$A$1:$M$225</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -960,7 +960,7 @@
         </is>
       </c>
       <c r="F12" s="5" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G12" s="5" t="inlineStr"/>
       <c r="H12" s="5" t="inlineStr">
@@ -1354,7 +1354,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M223"/>
+  <dimension ref="A1:M225"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -11540,17 +11540,17 @@
     <row r="164">
       <c r="A164" s="2" t="inlineStr">
         <is>
-          <t>L11.C01</t>
+          <t>L10.C04</t>
         </is>
       </c>
       <c r="B164" s="3" t="inlineStr">
         <is>
-          <t>L11</t>
+          <t>L10</t>
         </is>
       </c>
       <c r="C164" s="3" t="inlineStr">
         <is>
-          <t>Reflux ou destruction — la bifurcation</t>
+          <t>Qui la prohibition vise, et où le chapitre précédent avait trop dit</t>
         </is>
       </c>
       <c r="D164" s="3" t="inlineStr">
@@ -11570,50 +11570,50 @@
       </c>
       <c r="G164" s="3" t="inlineStr">
         <is>
-          <t>conception</t>
+          <t>hybride</t>
         </is>
       </c>
       <c r="H164" s="3" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="I164" s="3" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="J164" s="3" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="K164" s="3" t="inlineStr">
         <is>
-          <t>contrepartie_comptable, reflux_monetaire, creation_monetaire, reflux_transactionnel, monnaie_comme_registre</t>
+          <t>contrepartie_comptable, creation_monetaire, reflux_collectif, qualification_regenerative, regle_contre_discretion</t>
         </is>
       </c>
       <c r="L164" s="3" t="inlineStr">
         <is>
-          <t>L1.C17, L1.C19, L1.C20, L1.C21, L1.C27, L1.C29</t>
+          <t>L1.C20, L1.C27, L1.C29, L10.C01, L10.C02, L10.C03, L11.C13, L20.C02</t>
         </is>
       </c>
       <c r="M164" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-11/c01-reflux-ou-destruction.md</t>
+          <t>corpus/livre-10/c04-qui-la-prohibition-vise-et-ou-le-corpus-avait-trop-dit.md</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" s="2" t="inlineStr">
         <is>
-          <t>L11.C02</t>
+          <t>L10.C05</t>
         </is>
       </c>
       <c r="B165" s="3" t="inlineStr">
         <is>
-          <t>L11</t>
+          <t>L10</t>
         </is>
       </c>
       <c r="C165" s="3" t="inlineStr">
         <is>
-          <t>Le trajet complet de la valeur</t>
+          <t>La définition-balai, et ce qu'elle emporte</t>
         </is>
       </c>
       <c r="D165" s="3" t="inlineStr">
@@ -11633,40 +11633,40 @@
       </c>
       <c r="G165" s="3" t="inlineStr">
         <is>
-          <t>conception</t>
+          <t>hybride</t>
         </is>
       </c>
       <c r="H165" s="3" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="I165" s="3" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J165" s="3" t="n">
         <v>4</v>
       </c>
       <c r="K165" s="3" t="inlineStr">
         <is>
-          <t>contrepartie_comptable, reflux_collectif, reflux_transactionnel, demurrage, creation_monetaire</t>
+          <t>contrepartie_comptable, creation_monetaire, reflux_collectif, architecture_invisible, regle_contre_discretion</t>
         </is>
       </c>
       <c r="L165" s="3" t="inlineStr">
         <is>
-          <t>L1.C18, L1.C20, L1.C21, L1.C29, L11.C01</t>
+          <t>L1.C20, L1.C29, L6.C09, L10.C01, L10.C02, L10.C03, L10.C04, L11.C13, L20.C02</t>
         </is>
       </c>
       <c r="M165" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-11/c02-le-trajet-complet-de-la-valeur.md</t>
+          <t>corpus/livre-10/c05-la-definition-balai-et-ce-qu-elle-emporte.md</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" s="2" t="inlineStr">
         <is>
-          <t>L11.C03</t>
+          <t>L11.C01</t>
         </is>
       </c>
       <c r="B166" s="3" t="inlineStr">
@@ -11676,7 +11676,7 @@
       </c>
       <c r="C166" s="3" t="inlineStr">
         <is>
-          <t>Le compte des objectifs et des instruments</t>
+          <t>Reflux ou destruction — la bifurcation</t>
         </is>
       </c>
       <c r="D166" s="3" t="inlineStr">
@@ -11701,35 +11701,35 @@
       </c>
       <c r="H166" s="3" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="I166" s="3" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="J166" s="3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K166" s="3" t="inlineStr">
         <is>
-          <t>affectation_des_instruments, bareme, effet_veblen, reflux_collectif, reflux_transactionnel, demurrage, degeneratif, qualification_regenerative</t>
+          <t>contrepartie_comptable, reflux_monetaire, creation_monetaire, reflux_transactionnel, monnaie_comme_registre</t>
         </is>
       </c>
       <c r="L166" s="3" t="inlineStr">
         <is>
-          <t>L1.C18, L1.C20, L1.C21, L1.C26, L1.C28, L11.C01, L11.C02, L11.C04, L11.C05, L11.C06, L11.C07, L11.C09, L11.C10, L11.C11</t>
+          <t>L1.C17, L1.C19, L1.C20, L1.C21, L1.C27, L1.C29</t>
         </is>
       </c>
       <c r="M166" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-11/c03-le-compte-des-objectifs-et-des-instruments.md</t>
+          <t>corpus/livre-11/c01-reflux-ou-destruction.md</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" s="2" t="inlineStr">
         <is>
-          <t>L11.C04</t>
+          <t>L11.C02</t>
         </is>
       </c>
       <c r="B167" s="3" t="inlineStr">
@@ -11739,7 +11739,7 @@
       </c>
       <c r="C167" s="3" t="inlineStr">
         <is>
-          <t>Les instruments du reflux sous parité fixe</t>
+          <t>Le trajet complet de la valeur</t>
         </is>
       </c>
       <c r="D167" s="3" t="inlineStr">
@@ -11764,35 +11764,35 @@
       </c>
       <c r="H167" s="3" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="I167" s="3" t="n">
         <v>5</v>
       </c>
       <c r="J167" s="3" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K167" s="3" t="inlineStr">
         <is>
-          <t>referentiel_de_change, demurrage, reflux_transactionnel, reflux_collectif, bareme, affectation_des_instruments, creation_monetaire</t>
+          <t>contrepartie_comptable, reflux_collectif, reflux_transactionnel, demurrage, creation_monetaire</t>
         </is>
       </c>
       <c r="L167" s="3" t="inlineStr">
         <is>
-          <t>L1.C19, L1.C21, L1.C24, L1.C26, L1.C27, L11.C01, L11.C02, L11.C03</t>
+          <t>L1.C18, L1.C20, L1.C21, L1.C29, L11.C01</t>
         </is>
       </c>
       <c r="M167" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-11/c04-les-instruments-du-reflux-sous-parite-fixe.md</t>
+          <t>corpus/livre-11/c02-le-trajet-complet-de-la-valeur.md</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" s="2" t="inlineStr">
         <is>
-          <t>L11.C05</t>
+          <t>L11.C03</t>
         </is>
       </c>
       <c r="B168" s="3" t="inlineStr">
@@ -11802,7 +11802,7 @@
       </c>
       <c r="C168" s="3" t="inlineStr">
         <is>
-          <t>L'assiette du reflux transactionnel</t>
+          <t>Le compte des objectifs et des instruments</t>
         </is>
       </c>
       <c r="D168" s="3" t="inlineStr">
@@ -11827,35 +11827,35 @@
       </c>
       <c r="H168" s="3" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="I168" s="3" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J168" s="3" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="K168" s="3" t="inlineStr">
         <is>
-          <t>reflux_transactionnel, bareme, degeneratif, reflux_collectif, robustesse, affectation_des_instruments</t>
+          <t>affectation_des_instruments, bareme, effet_veblen, reflux_collectif, reflux_transactionnel, demurrage, degeneratif, qualification_regenerative</t>
         </is>
       </c>
       <c r="L168" s="3" t="inlineStr">
         <is>
-          <t>L1.C18, L1.C21, L1.C23, L11.C02, L11.C03, L11.C04</t>
+          <t>L1.C18, L1.C20, L1.C21, L1.C26, L1.C28, L11.C01, L11.C02, L11.C04, L11.C05, L11.C06, L11.C07, L11.C09, L11.C10, L11.C11</t>
         </is>
       </c>
       <c r="M168" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-11/c05-l-assiette-du-reflux-transactionnel.md</t>
+          <t>corpus/livre-11/c03-le-compte-des-objectifs-et-des-instruments.md</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" s="2" t="inlineStr">
         <is>
-          <t>L11.C06</t>
+          <t>L11.C04</t>
         </is>
       </c>
       <c r="B169" s="3" t="inlineStr">
@@ -11865,7 +11865,7 @@
       </c>
       <c r="C169" s="3" t="inlineStr">
         <is>
-          <t>Le barème par défaut</t>
+          <t>Les instruments du reflux sous parité fixe</t>
         </is>
       </c>
       <c r="D169" s="3" t="inlineStr">
@@ -11890,7 +11890,7 @@
       </c>
       <c r="H169" s="3" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="I169" s="3" t="n">
@@ -11901,24 +11901,24 @@
       </c>
       <c r="K169" s="3" t="inlineStr">
         <is>
-          <t>bareme, qualification_regenerative, degeneratif, reflux_transactionnel, regle_contre_discretion, affectation_des_instruments</t>
+          <t>referentiel_de_change, demurrage, reflux_transactionnel, reflux_collectif, bareme, affectation_des_instruments, creation_monetaire</t>
         </is>
       </c>
       <c r="L169" s="3" t="inlineStr">
         <is>
-          <t>L1.C18, L1.C21, L1.C22, L1.C27, L1.C28, L11.C03, L11.C05</t>
+          <t>L1.C19, L1.C21, L1.C24, L1.C26, L1.C27, L11.C01, L11.C02, L11.C03</t>
         </is>
       </c>
       <c r="M169" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-11/c06-le-bareme-par-defaut.md</t>
+          <t>corpus/livre-11/c04-les-instruments-du-reflux-sous-parite-fixe.md</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" s="2" t="inlineStr">
         <is>
-          <t>L11.C07</t>
+          <t>L11.C05</t>
         </is>
       </c>
       <c r="B170" s="3" t="inlineStr">
@@ -11928,7 +11928,7 @@
       </c>
       <c r="C170" s="3" t="inlineStr">
         <is>
-          <t>Le demurrage et son nœud de prélèvement</t>
+          <t>L'assiette du reflux transactionnel</t>
         </is>
       </c>
       <c r="D170" s="3" t="inlineStr">
@@ -11957,31 +11957,31 @@
         </is>
       </c>
       <c r="I170" s="3" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="J170" s="3" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="K170" s="3" t="inlineStr">
         <is>
-          <t>demurrage, reflux_collectif, reflux_transactionnel, bareme, affectation_des_instruments, referentiel_de_change</t>
+          <t>reflux_transactionnel, bareme, degeneratif, reflux_collectif, robustesse, affectation_des_instruments</t>
         </is>
       </c>
       <c r="L170" s="3" t="inlineStr">
         <is>
-          <t>L1.C21, L1.C26, L11.C02, L11.C03, L11.C04, L11.C05, L11.C06</t>
+          <t>L1.C18, L1.C21, L1.C23, L11.C02, L11.C03, L11.C04</t>
         </is>
       </c>
       <c r="M170" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-11/c07-le-demurrage-et-son-noeud.md</t>
+          <t>corpus/livre-11/c05-l-assiette-du-reflux-transactionnel.md</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" s="2" t="inlineStr">
         <is>
-          <t>L11.C08</t>
+          <t>L11.C06</t>
         </is>
       </c>
       <c r="B171" s="3" t="inlineStr">
@@ -11991,7 +11991,7 @@
       </c>
       <c r="C171" s="3" t="inlineStr">
         <is>
-          <t>Les dérogations</t>
+          <t>Le barème par défaut</t>
         </is>
       </c>
       <c r="D171" s="3" t="inlineStr">
@@ -12027,24 +12027,24 @@
       </c>
       <c r="K171" s="3" t="inlineStr">
         <is>
-          <t>demurrage, reflux_transactionnel, bareme, qualification_regenerative, reflux_collectif, degeneratif</t>
+          <t>bareme, qualification_regenerative, degeneratif, reflux_transactionnel, regle_contre_discretion, affectation_des_instruments</t>
         </is>
       </c>
       <c r="L171" s="3" t="inlineStr">
         <is>
-          <t>L1.C18, L1.C20, L1.C21, L1.C22, L11.C03, L11.C05, L11.C06, L11.C07</t>
+          <t>L1.C18, L1.C21, L1.C22, L1.C27, L1.C28, L11.C03, L11.C05</t>
         </is>
       </c>
       <c r="M171" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-11/c08-les-derogations.md</t>
+          <t>corpus/livre-11/c06-le-bareme-par-defaut.md</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" s="2" t="inlineStr">
         <is>
-          <t>L11.C09</t>
+          <t>L11.C07</t>
         </is>
       </c>
       <c r="B172" s="3" t="inlineStr">
@@ -12054,7 +12054,7 @@
       </c>
       <c r="C172" s="3" t="inlineStr">
         <is>
-          <t>L'incidence — qui paie le reflux</t>
+          <t>Le demurrage et son nœud de prélèvement</t>
         </is>
       </c>
       <c r="D172" s="3" t="inlineStr">
@@ -12090,24 +12090,24 @@
       </c>
       <c r="K172" s="3" t="inlineStr">
         <is>
-          <t>reflux_collectif, reflux_transactionnel, demurrage, bareme, degeneratif, qualification_regenerative</t>
+          <t>demurrage, reflux_collectif, reflux_transactionnel, bareme, affectation_des_instruments, referentiel_de_change</t>
         </is>
       </c>
       <c r="L172" s="3" t="inlineStr">
         <is>
-          <t>L1.C21, L1.C22, L11.C03, L11.C05, L11.C06, L11.C07, L11.C08</t>
+          <t>L1.C21, L1.C26, L11.C02, L11.C03, L11.C04, L11.C05, L11.C06</t>
         </is>
       </c>
       <c r="M172" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-11/c09-l-incidence-qui-paie-le-reflux.md</t>
+          <t>corpus/livre-11/c07-le-demurrage-et-son-noeud.md</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" s="2" t="inlineStr">
         <is>
-          <t>L11.C10</t>
+          <t>L11.C08</t>
         </is>
       </c>
       <c r="B173" s="3" t="inlineStr">
@@ -12117,7 +12117,7 @@
       </c>
       <c r="C173" s="3" t="inlineStr">
         <is>
-          <t>La trajectoire de mise en place</t>
+          <t>Les dérogations</t>
         </is>
       </c>
       <c r="D173" s="3" t="inlineStr">
@@ -12142,35 +12142,35 @@
       </c>
       <c r="H173" s="3" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="I173" s="3" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="J173" s="3" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="K173" s="3" t="inlineStr">
         <is>
-          <t>bareme, regle_contre_discretion, degeneratif, reflux_transactionnel, qualification_regenerative, affectation_des_instruments</t>
+          <t>demurrage, reflux_transactionnel, bareme, qualification_regenerative, reflux_collectif, degeneratif</t>
         </is>
       </c>
       <c r="L173" s="3" t="inlineStr">
         <is>
-          <t>L1.C21, L1.C23, L1.C27, L11.C03, L11.C05, L11.C06, L11.C09</t>
+          <t>L1.C18, L1.C20, L1.C21, L1.C22, L11.C03, L11.C05, L11.C06, L11.C07</t>
         </is>
       </c>
       <c r="M173" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-11/c10-la-trajectoire-de-mise-en-place.md</t>
+          <t>corpus/livre-11/c08-les-derogations.md</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" s="2" t="inlineStr">
         <is>
-          <t>L11.C11</t>
+          <t>L11.C09</t>
         </is>
       </c>
       <c r="B174" s="3" t="inlineStr">
@@ -12180,7 +12180,7 @@
       </c>
       <c r="C174" s="3" t="inlineStr">
         <is>
-          <t>Qui arrête le barème</t>
+          <t>L'incidence — qui paie le reflux</t>
         </is>
       </c>
       <c r="D174" s="3" t="inlineStr">
@@ -12205,35 +12205,35 @@
       </c>
       <c r="H174" s="3" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="I174" s="3" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J174" s="3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K174" s="3" t="inlineStr">
         <is>
-          <t>bareme, affectation_des_instruments, referentiel_de_change, qualification_regenerative, regle_contre_discretion, reflux_collectif</t>
+          <t>reflux_collectif, reflux_transactionnel, demurrage, bareme, degeneratif, qualification_regenerative</t>
         </is>
       </c>
       <c r="L174" s="3" t="inlineStr">
         <is>
-          <t>L1.C18, L1.C22, L1.C26, L1.C27, L11.C04, L11.C06, L11.C08, L11.C10</t>
+          <t>L1.C21, L1.C22, L11.C03, L11.C05, L11.C06, L11.C07, L11.C08</t>
         </is>
       </c>
       <c r="M174" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-11/c11-qui-arrete-le-bareme.md</t>
+          <t>corpus/livre-11/c09-l-incidence-qui-paie-le-reflux.md</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" s="2" t="inlineStr">
         <is>
-          <t>L11.C12</t>
+          <t>L11.C10</t>
         </is>
       </c>
       <c r="B175" s="3" t="inlineStr">
@@ -12243,7 +12243,7 @@
       </c>
       <c r="C175" s="3" t="inlineStr">
         <is>
-          <t>La directive</t>
+          <t>La trajectoire de mise en place</t>
         </is>
       </c>
       <c r="D175" s="3" t="inlineStr">
@@ -12268,35 +12268,35 @@
       </c>
       <c r="H175" s="3" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="I175" s="3" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="J175" s="3" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="K175" s="3" t="inlineStr">
         <is>
-          <t>bareme, regle_contre_discretion, affectation_des_instruments, reflux_collectif, qualification_regenerative</t>
+          <t>bareme, regle_contre_discretion, degeneratif, reflux_transactionnel, qualification_regenerative, affectation_des_instruments</t>
         </is>
       </c>
       <c r="L175" s="3" t="inlineStr">
         <is>
-          <t>L1.C21, L11.C03, L11.C05, L11.C06, L11.C09, L11.C10, L11.C11</t>
+          <t>L1.C21, L1.C23, L1.C27, L11.C03, L11.C05, L11.C06, L11.C09</t>
         </is>
       </c>
       <c r="M175" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-11/c12-la-directive.md</t>
+          <t>corpus/livre-11/c10-la-trajectoire-de-mise-en-place.md</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" s="2" t="inlineStr">
         <is>
-          <t>L11.C13</t>
+          <t>L11.C11</t>
         </is>
       </c>
       <c r="B176" s="3" t="inlineStr">
@@ -12306,7 +12306,7 @@
       </c>
       <c r="C176" s="3" t="inlineStr">
         <is>
-          <t>Le barème de qualification</t>
+          <t>Qui arrête le barème</t>
         </is>
       </c>
       <c r="D176" s="3" t="inlineStr">
@@ -12331,35 +12331,35 @@
       </c>
       <c r="H176" s="3" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="I176" s="3" t="n">
         <v>6</v>
       </c>
       <c r="J176" s="3" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K176" s="3" t="inlineStr">
         <is>
-          <t>qualification_regenerative, bareme, creation_monetaire, additionnalite, degeneratif, essentiel_insolvable</t>
+          <t>bareme, affectation_des_instruments, referentiel_de_change, qualification_regenerative, regle_contre_discretion, reflux_collectif</t>
         </is>
       </c>
       <c r="L176" s="3" t="inlineStr">
         <is>
-          <t>L1.C18, L1.C20, L1.C22, L1.C27, L11.C03, L11.C05, L11.C06, L11.C08, L11.C09, L11.C10, L11.C11, L11.C12</t>
+          <t>L1.C18, L1.C22, L1.C26, L1.C27, L11.C04, L11.C06, L11.C08, L11.C10</t>
         </is>
       </c>
       <c r="M176" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-11/c13-le-bareme-de-qualification.md</t>
+          <t>corpus/livre-11/c11-qui-arrete-le-bareme.md</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" s="2" t="inlineStr">
         <is>
-          <t>L11.C14</t>
+          <t>L11.C12</t>
         </is>
       </c>
       <c r="B177" s="3" t="inlineStr">
@@ -12369,7 +12369,7 @@
       </c>
       <c r="C177" s="3" t="inlineStr">
         <is>
-          <t>Le tableau de bord, ou les données de la directive</t>
+          <t>La directive</t>
         </is>
       </c>
       <c r="D177" s="3" t="inlineStr">
@@ -12405,24 +12405,24 @@
       </c>
       <c r="K177" s="3" t="inlineStr">
         <is>
-          <t>indicateur_de_progres, bareme, regle_contre_discretion, affectation_des_instruments, degeneratif, qualification_regenerative</t>
+          <t>bareme, regle_contre_discretion, affectation_des_instruments, reflux_collectif, qualification_regenerative</t>
         </is>
       </c>
       <c r="L177" s="3" t="inlineStr">
         <is>
-          <t>L1.C21, L1.C28, L11.C03, L11.C05, L11.C11, L11.C12, L11.C13</t>
+          <t>L1.C21, L11.C03, L11.C05, L11.C06, L11.C09, L11.C10, L11.C11</t>
         </is>
       </c>
       <c r="M177" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-11/c14-le-tableau-de-bord.md</t>
+          <t>corpus/livre-11/c12-la-directive.md</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" s="2" t="inlineStr">
         <is>
-          <t>L11.C15</t>
+          <t>L11.C13</t>
         </is>
       </c>
       <c r="B178" s="3" t="inlineStr">
@@ -12432,7 +12432,7 @@
       </c>
       <c r="C178" s="3" t="inlineStr">
         <is>
-          <t>Les parités du référentiel de change</t>
+          <t>Le barème de qualification</t>
         </is>
       </c>
       <c r="D178" s="3" t="inlineStr">
@@ -12457,35 +12457,35 @@
       </c>
       <c r="H178" s="3" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="I178" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="J178" s="3" t="n">
         <v>5</v>
       </c>
-      <c r="J178" s="3" t="n">
-        <v>4</v>
-      </c>
       <c r="K178" s="3" t="inlineStr">
         <is>
-          <t>referentiel_de_change, bareme, indicateur_de_progres, regle_contre_discretion, affectation_des_instruments</t>
+          <t>qualification_regenerative, bareme, creation_monetaire, additionnalite, degeneratif, essentiel_insolvable</t>
         </is>
       </c>
       <c r="L178" s="3" t="inlineStr">
         <is>
-          <t>L1.C24, L1.C25, L1.C26, L1.C28, L11.C01, L11.C04, L11.C10, L11.C12, L11.C14</t>
+          <t>L1.C18, L1.C20, L1.C22, L1.C27, L11.C03, L11.C05, L11.C06, L11.C08, L11.C09, L11.C10, L11.C11, L11.C12</t>
         </is>
       </c>
       <c r="M178" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-11/c15-les-parites-du-referentiel.md</t>
+          <t>corpus/livre-11/c13-le-bareme-de-qualification.md</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" s="2" t="inlineStr">
         <is>
-          <t>L11.C16</t>
+          <t>L11.C14</t>
         </is>
       </c>
       <c r="B179" s="3" t="inlineStr">
@@ -12495,7 +12495,7 @@
       </c>
       <c r="C179" s="3" t="inlineStr">
         <is>
-          <t>La valorisation des communs</t>
+          <t>Le tableau de bord, ou les données de la directive</t>
         </is>
       </c>
       <c r="D179" s="3" t="inlineStr">
@@ -12520,35 +12520,35 @@
       </c>
       <c r="H179" s="3" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="I179" s="3" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J179" s="3" t="n">
         <v>4</v>
       </c>
       <c r="K179" s="3" t="inlineStr">
         <is>
-          <t>valorisation_des_communs, bareme, essentiel_insolvable, polycentricite, affectation_des_instruments, indicateur_de_progres</t>
+          <t>indicateur_de_progres, bareme, regle_contre_discretion, affectation_des_instruments, degeneratif, qualification_regenerative</t>
         </is>
       </c>
       <c r="L179" s="3" t="inlineStr">
         <is>
-          <t>L1.C15, L1.C18, L1.C21, L1.C22, L1.C24, L1.C26, L1.C27, L11.C02, L11.C03, L11.C04, L11.C06, L11.C09, L11.C11, L11.C12, L11.C13, L11.C15</t>
+          <t>L1.C21, L1.C28, L11.C03, L11.C05, L11.C11, L11.C12, L11.C13</t>
         </is>
       </c>
       <c r="M179" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-11/c16-la-valorisation-des-communs.md</t>
+          <t>corpus/livre-11/c14-le-tableau-de-bord.md</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" s="2" t="inlineStr">
         <is>
-          <t>L11.C17</t>
+          <t>L11.C15</t>
         </is>
       </c>
       <c r="B180" s="3" t="inlineStr">
@@ -12558,7 +12558,7 @@
       </c>
       <c r="C180" s="3" t="inlineStr">
         <is>
-          <t>La cohérence des cinq barèmes</t>
+          <t>Les parités du référentiel de change</t>
         </is>
       </c>
       <c r="D180" s="3" t="inlineStr">
@@ -12587,31 +12587,31 @@
         </is>
       </c>
       <c r="I180" s="3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J180" s="3" t="n">
         <v>4</v>
       </c>
       <c r="K180" s="3" t="inlineStr">
         <is>
-          <t>bareme, affectation_des_instruments, regle_contre_discretion, qualification_regenerative, valorisation_des_communs, reflux_transactionnel, referentiel_de_change, indicateur_de_progres, polycentricite</t>
+          <t>referentiel_de_change, bareme, indicateur_de_progres, regle_contre_discretion, affectation_des_instruments</t>
         </is>
       </c>
       <c r="L180" s="3" t="inlineStr">
         <is>
-          <t>L1.C18, L1.C20, L1.C21, L1.C26, L1.C27, L1.C28, L11.C03, L11.C05, L11.C06, L11.C07, L11.C09, L11.C10, L11.C11, L11.C12, L11.C13, L11.C14, L11.C15, L11.C16</t>
+          <t>L1.C24, L1.C25, L1.C26, L1.C28, L11.C01, L11.C04, L11.C10, L11.C12, L11.C14</t>
         </is>
       </c>
       <c r="M180" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-11/c17-la-coherence-des-cinq-baremes.md</t>
+          <t>corpus/livre-11/c15-les-parites-du-referentiel.md</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" s="2" t="inlineStr">
         <is>
-          <t>L11.C18</t>
+          <t>L11.C16</t>
         </is>
       </c>
       <c r="B181" s="3" t="inlineStr">
@@ -12621,7 +12621,7 @@
       </c>
       <c r="C181" s="3" t="inlineStr">
         <is>
-          <t>Le seuil d'exemption</t>
+          <t>La valorisation des communs</t>
         </is>
       </c>
       <c r="D181" s="3" t="inlineStr">
@@ -12646,35 +12646,35 @@
       </c>
       <c r="H181" s="3" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="I181" s="3" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="J181" s="3" t="n">
         <v>4</v>
       </c>
       <c r="K181" s="3" t="inlineStr">
         <is>
-          <t>demurrage, reflux_transactionnel, bareme, regle_contre_discretion, affectation_des_instruments, valorisation_des_communs</t>
+          <t>valorisation_des_communs, bareme, essentiel_insolvable, polycentricite, affectation_des_instruments, indicateur_de_progres</t>
         </is>
       </c>
       <c r="L181" s="3" t="inlineStr">
         <is>
-          <t>L1.C21, L11.C03, L11.C05, L11.C06, L11.C07, L11.C08, L11.C09, L11.C12, L11.C13, L11.C16, L11.C17</t>
+          <t>L1.C15, L1.C18, L1.C21, L1.C22, L1.C24, L1.C26, L1.C27, L11.C02, L11.C03, L11.C04, L11.C06, L11.C09, L11.C11, L11.C12, L11.C13, L11.C15</t>
         </is>
       </c>
       <c r="M181" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-11/c18-le-seuil-d-exemption.md</t>
+          <t>corpus/livre-11/c16-la-valorisation-des-communs.md</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" s="2" t="inlineStr">
         <is>
-          <t>L11.C19</t>
+          <t>L11.C17</t>
         </is>
       </c>
       <c r="B182" s="3" t="inlineStr">
@@ -12684,7 +12684,7 @@
       </c>
       <c r="C182" s="3" t="inlineStr">
         <is>
-          <t>Le recours</t>
+          <t>La cohérence des cinq barèmes</t>
         </is>
       </c>
       <c r="D182" s="3" t="inlineStr">
@@ -12713,31 +12713,31 @@
         </is>
       </c>
       <c r="I182" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J182" s="3" t="n">
         <v>4</v>
       </c>
       <c r="K182" s="3" t="inlineStr">
         <is>
-          <t>bareme, qualification_regenerative, valorisation_des_communs, demurrage, regle_contre_discretion, essentiel_insolvable, affectation_des_instruments</t>
+          <t>bareme, affectation_des_instruments, regle_contre_discretion, qualification_regenerative, valorisation_des_communs, reflux_transactionnel, referentiel_de_change, indicateur_de_progres, polycentricite</t>
         </is>
       </c>
       <c r="L182" s="3" t="inlineStr">
         <is>
-          <t>L1.C18, L11.C03, L11.C06, L11.C08, L11.C09, L11.C11, L11.C12, L11.C13, L11.C16, L11.C17, L11.C18</t>
+          <t>L1.C18, L1.C20, L1.C21, L1.C26, L1.C27, L1.C28, L11.C03, L11.C05, L11.C06, L11.C07, L11.C09, L11.C10, L11.C11, L11.C12, L11.C13, L11.C14, L11.C15, L11.C16</t>
         </is>
       </c>
       <c r="M182" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-11/c19-le-recours.md</t>
+          <t>corpus/livre-11/c17-la-coherence-des-cinq-baremes.md</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" s="2" t="inlineStr">
         <is>
-          <t>L11.C20</t>
+          <t>L11.C18</t>
         </is>
       </c>
       <c r="B183" s="3" t="inlineStr">
@@ -12747,7 +12747,7 @@
       </c>
       <c r="C183" s="3" t="inlineStr">
         <is>
-          <t>L'amendement de la directive</t>
+          <t>Le seuil d'exemption</t>
         </is>
       </c>
       <c r="D183" s="3" t="inlineStr">
@@ -12783,24 +12783,24 @@
       </c>
       <c r="K183" s="3" t="inlineStr">
         <is>
-          <t>bareme, regle_contre_discretion, qualification_regenerative, valorisation_des_communs, referentiel_de_change, affectation_des_instruments</t>
+          <t>demurrage, reflux_transactionnel, bareme, regle_contre_discretion, affectation_des_instruments, valorisation_des_communs</t>
         </is>
       </c>
       <c r="L183" s="3" t="inlineStr">
         <is>
-          <t>L1.C21, L1.C26, L1.C28, L11.C03, L11.C06, L11.C10, L11.C12, L11.C13, L11.C15, L11.C16, L11.C17, L11.C18, L11.C19</t>
+          <t>L1.C21, L11.C03, L11.C05, L11.C06, L11.C07, L11.C08, L11.C09, L11.C12, L11.C13, L11.C16, L11.C17</t>
         </is>
       </c>
       <c r="M183" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-11/c20-l-amendement-de-la-directive.md</t>
+          <t>corpus/livre-11/c18-le-seuil-d-exemption.md</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" s="2" t="inlineStr">
         <is>
-          <t>L11.C21</t>
+          <t>L11.C19</t>
         </is>
       </c>
       <c r="B184" s="3" t="inlineStr">
@@ -12810,7 +12810,7 @@
       </c>
       <c r="C184" s="3" t="inlineStr">
         <is>
-          <t>La perception</t>
+          <t>Le recours</t>
         </is>
       </c>
       <c r="D184" s="3" t="inlineStr">
@@ -12839,31 +12839,31 @@
         </is>
       </c>
       <c r="I184" s="3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J184" s="3" t="n">
         <v>4</v>
       </c>
       <c r="K184" s="3" t="inlineStr">
         <is>
-          <t>reflux_transactionnel, reflux_collectif, bareme, demurrage, affectation_des_instruments, contrepartie_comptable</t>
+          <t>bareme, qualification_regenerative, valorisation_des_communs, demurrage, regle_contre_discretion, essentiel_insolvable, affectation_des_instruments</t>
         </is>
       </c>
       <c r="L184" s="3" t="inlineStr">
         <is>
-          <t>L1.C21, L11.C01, L11.C02, L11.C03, L11.C05, L11.C09, L11.C10, L11.C16, L11.C17, L11.C19, L11.C20</t>
+          <t>L1.C18, L11.C03, L11.C06, L11.C08, L11.C09, L11.C11, L11.C12, L11.C13, L11.C16, L11.C17, L11.C18</t>
         </is>
       </c>
       <c r="M184" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-11/c21-la-perception.md</t>
+          <t>corpus/livre-11/c19-le-recours.md</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" s="2" t="inlineStr">
         <is>
-          <t>L11.C22</t>
+          <t>L11.C20</t>
         </is>
       </c>
       <c r="B185" s="3" t="inlineStr">
@@ -12873,7 +12873,7 @@
       </c>
       <c r="C185" s="3" t="inlineStr">
         <is>
-          <t>Les délais</t>
+          <t>L'amendement de la directive</t>
         </is>
       </c>
       <c r="D185" s="3" t="inlineStr">
@@ -12909,24 +12909,24 @@
       </c>
       <c r="K185" s="3" t="inlineStr">
         <is>
-          <t>reflux_collectif, reflux_transactionnel, bareme, regle_contre_discretion, qualification_regenerative, affectation_des_instruments, robustesse</t>
+          <t>bareme, regle_contre_discretion, qualification_regenerative, valorisation_des_communs, referentiel_de_change, affectation_des_instruments</t>
         </is>
       </c>
       <c r="L185" s="3" t="inlineStr">
         <is>
-          <t>L1.C21, L11.C03, L11.C07, L11.C10, L11.C12, L11.C13, L11.C16, L11.C17, L11.C19, L11.C20, L11.C21</t>
+          <t>L1.C21, L1.C26, L1.C28, L11.C03, L11.C06, L11.C10, L11.C12, L11.C13, L11.C15, L11.C16, L11.C17, L11.C18, L11.C19</t>
         </is>
       </c>
       <c r="M185" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-11/c22-les-delais.md</t>
+          <t>corpus/livre-11/c20-l-amendement-de-la-directive.md</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" s="2" t="inlineStr">
         <is>
-          <t>L11.C23</t>
+          <t>L11.C21</t>
         </is>
       </c>
       <c r="B186" s="3" t="inlineStr">
@@ -12936,7 +12936,7 @@
       </c>
       <c r="C186" s="3" t="inlineStr">
         <is>
-          <t>La contracyclicité</t>
+          <t>La perception</t>
         </is>
       </c>
       <c r="D186" s="3" t="inlineStr">
@@ -12972,24 +12972,24 @@
       </c>
       <c r="K186" s="3" t="inlineStr">
         <is>
-          <t>reflux_transactionnel, reflux_collectif, essentiel_insolvable, degeneratif, bareme, robustesse, affectation_des_instruments, contrepartie_comptable</t>
+          <t>reflux_transactionnel, reflux_collectif, bareme, demurrage, affectation_des_instruments, contrepartie_comptable</t>
         </is>
       </c>
       <c r="L186" s="3" t="inlineStr">
         <is>
-          <t>L1.C15, L1.C21, L1.C29, L11.C01, L11.C02, L11.C03, L11.C07, L11.C10, L11.C12, L11.C14, L11.C16, L11.C17, L11.C21, L11.C22</t>
+          <t>L1.C21, L11.C01, L11.C02, L11.C03, L11.C05, L11.C09, L11.C10, L11.C16, L11.C17, L11.C19, L11.C20</t>
         </is>
       </c>
       <c r="M186" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-11/c23-la-contracyclicite.md</t>
+          <t>corpus/livre-11/c21-la-perception.md</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" s="2" t="inlineStr">
         <is>
-          <t>L11.C24</t>
+          <t>L11.C22</t>
         </is>
       </c>
       <c r="B187" s="3" t="inlineStr">
@@ -12999,7 +12999,7 @@
       </c>
       <c r="C187" s="3" t="inlineStr">
         <is>
-          <t>Le barème aux frontières</t>
+          <t>Les délais</t>
         </is>
       </c>
       <c r="D187" s="3" t="inlineStr">
@@ -13024,7 +13024,7 @@
       </c>
       <c r="H187" s="3" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="I187" s="3" t="n">
@@ -13035,24 +13035,24 @@
       </c>
       <c r="K187" s="3" t="inlineStr">
         <is>
-          <t>seuil_d_activation, bareme, degeneratif, reflux_transactionnel, referentiel_de_change, essentiel_insolvable, affectation_des_instruments</t>
+          <t>reflux_collectif, reflux_transactionnel, bareme, regle_contre_discretion, qualification_regenerative, affectation_des_instruments, robustesse</t>
         </is>
       </c>
       <c r="L187" s="3" t="inlineStr">
         <is>
-          <t>L1.C26, L1.C27, L11.C04, L11.C05, L11.C06, L11.C09, L11.C13, L11.C16, L11.C17, L11.C19, L11.C21</t>
+          <t>L1.C21, L11.C03, L11.C07, L11.C10, L11.C12, L11.C13, L11.C16, L11.C17, L11.C19, L11.C20, L11.C21</t>
         </is>
       </c>
       <c r="M187" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-11/c24-le-bareme-aux-frontieres.md</t>
+          <t>corpus/livre-11/c22-les-delais.md</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" s="2" t="inlineStr">
         <is>
-          <t>L11.C25</t>
+          <t>L11.C23</t>
         </is>
       </c>
       <c r="B188" s="3" t="inlineStr">
@@ -13062,7 +13062,7 @@
       </c>
       <c r="C188" s="3" t="inlineStr">
         <is>
-          <t>Le contrôle</t>
+          <t>La contracyclicité</t>
         </is>
       </c>
       <c r="D188" s="3" t="inlineStr">
@@ -13087,35 +13087,35 @@
       </c>
       <c r="H188" s="3" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="I188" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J188" s="3" t="n">
         <v>4</v>
       </c>
       <c r="K188" s="3" t="inlineStr">
         <is>
-          <t>bareme, reflux_transactionnel, qualification_regenerative, regle_contre_discretion, affectation_des_instruments, essentiel_insolvable</t>
+          <t>reflux_transactionnel, reflux_collectif, essentiel_insolvable, degeneratif, bareme, robustesse, affectation_des_instruments, contrepartie_comptable</t>
         </is>
       </c>
       <c r="L188" s="3" t="inlineStr">
         <is>
-          <t>L1.C18, L1.C21, L1.C22, L11.C05, L11.C06, L11.C09, L11.C11, L11.C13, L11.C17, L11.C19, L11.C20, L11.C21, L11.C23, L11.C24</t>
+          <t>L1.C15, L1.C21, L1.C29, L11.C01, L11.C02, L11.C03, L11.C07, L11.C10, L11.C12, L11.C14, L11.C16, L11.C17, L11.C21, L11.C22</t>
         </is>
       </c>
       <c r="M188" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-11/c25-le-controle.md</t>
+          <t>corpus/livre-11/c23-la-contracyclicite.md</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" s="2" t="inlineStr">
         <is>
-          <t>L11.C26</t>
+          <t>L11.C24</t>
         </is>
       </c>
       <c r="B189" s="3" t="inlineStr">
@@ -13125,7 +13125,7 @@
       </c>
       <c r="C189" s="3" t="inlineStr">
         <is>
-          <t>La portée du Livre 11</t>
+          <t>Le barème aux frontières</t>
         </is>
       </c>
       <c r="D189" s="3" t="inlineStr">
@@ -13150,35 +13150,35 @@
       </c>
       <c r="H189" s="3" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="I189" s="3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J189" s="3" t="n">
         <v>4</v>
       </c>
       <c r="K189" s="3" t="inlineStr">
         <is>
-          <t>bareme, reflux_collectif, reflux_transactionnel, demurrage, qualification_regenerative, valorisation_des_communs, referentiel_de_change, regle_contre_discretion, affectation_des_instruments, polycentricite</t>
+          <t>seuil_d_activation, bareme, degeneratif, reflux_transactionnel, referentiel_de_change, essentiel_insolvable, affectation_des_instruments</t>
         </is>
       </c>
       <c r="L189" s="3" t="inlineStr">
         <is>
-          <t>L1.C15, L1.C18, L1.C21, L1.C22, L1.C26, L1.C27, L1.C28, L1.C29, L11.C01, L11.C03, L11.C06, L11.C07, L11.C09, L11.C11, L11.C12, L11.C13, L11.C16, L11.C17, L11.C19, L11.C21, L11.C22, L11.C23, L11.C24, L11.C25</t>
+          <t>L1.C26, L1.C27, L11.C04, L11.C05, L11.C06, L11.C09, L11.C13, L11.C16, L11.C17, L11.C19, L11.C21</t>
         </is>
       </c>
       <c r="M189" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-11/c26-la-portee-du-livre.md</t>
+          <t>corpus/livre-11/c24-le-bareme-aux-frontieres.md</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" s="2" t="inlineStr">
         <is>
-          <t>L11.C27</t>
+          <t>L11.C25</t>
         </is>
       </c>
       <c r="B190" s="3" t="inlineStr">
@@ -13188,7 +13188,7 @@
       </c>
       <c r="C190" s="3" t="inlineStr">
         <is>
-          <t>L'assiette de la fonte est celle de la TVA</t>
+          <t>Le contrôle</t>
         </is>
       </c>
       <c r="D190" s="3" t="inlineStr">
@@ -13217,31 +13217,31 @@
         </is>
       </c>
       <c r="I190" s="3" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J190" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K190" s="3" t="inlineStr">
         <is>
-          <t>reflux_transactionnel, demurrage, bareme, degeneratif, qualification_regenerative, externalisation, additionnalite</t>
+          <t>bareme, reflux_transactionnel, qualification_regenerative, regle_contre_discretion, affectation_des_instruments, essentiel_insolvable</t>
         </is>
       </c>
       <c r="L190" s="3" t="inlineStr">
         <is>
-          <t>L1.C21, L1.C27, L2.C16, L11.C02, L11.C05, L11.C09, L11.C21, L11.C24, L11.C25, L20.C02, L20.C19</t>
+          <t>L1.C18, L1.C21, L1.C22, L11.C05, L11.C06, L11.C09, L11.C11, L11.C13, L11.C17, L11.C19, L11.C20, L11.C21, L11.C23, L11.C24</t>
         </is>
       </c>
       <c r="M190" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-11/c27-l-assiette-de-la-fonte-est-celle-de-la-tva.md</t>
+          <t>corpus/livre-11/c25-le-controle.md</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" s="2" t="inlineStr">
         <is>
-          <t>L11.C28</t>
+          <t>L11.C26</t>
         </is>
       </c>
       <c r="B191" s="3" t="inlineStr">
@@ -13251,7 +13251,7 @@
       </c>
       <c r="C191" s="3" t="inlineStr">
         <is>
-          <t>La fonte sur les acquisitions d'actifs, éprouvée</t>
+          <t>La portée du Livre 11</t>
         </is>
       </c>
       <c r="D191" s="3" t="inlineStr">
@@ -13276,35 +13276,35 @@
       </c>
       <c r="H191" s="3" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="I191" s="3" t="n">
         <v>4</v>
       </c>
       <c r="J191" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K191" s="3" t="inlineStr">
         <is>
-          <t>reflux_transactionnel, demurrage, bareme, referentiel_de_change, degeneratif, robustesse</t>
+          <t>bareme, reflux_collectif, reflux_transactionnel, demurrage, qualification_regenerative, valorisation_des_communs, referentiel_de_change, regle_contre_discretion, affectation_des_instruments, polycentricite</t>
         </is>
       </c>
       <c r="L191" s="3" t="inlineStr">
         <is>
-          <t>L1.C19, L1.C21, L2.C13, L2.C16, L6.C02, L11.C02, L11.C05, L11.C09, L11.C23, L11.C27, L20.C13</t>
+          <t>L1.C15, L1.C18, L1.C21, L1.C22, L1.C26, L1.C27, L1.C28, L1.C29, L11.C01, L11.C03, L11.C06, L11.C07, L11.C09, L11.C11, L11.C12, L11.C13, L11.C16, L11.C17, L11.C19, L11.C21, L11.C22, L11.C23, L11.C24, L11.C25</t>
         </is>
       </c>
       <c r="M191" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-11/c28-la-fonte-sur-les-acquisitions-d-actifs-eprouvee.md</t>
+          <t>corpus/livre-11/c26-la-portee-du-livre.md</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" s="2" t="inlineStr">
         <is>
-          <t>L11.C29</t>
+          <t>L11.C27</t>
         </is>
       </c>
       <c r="B192" s="3" t="inlineStr">
@@ -13314,7 +13314,7 @@
       </c>
       <c r="C192" s="3" t="inlineStr">
         <is>
-          <t>La structure des sanctions</t>
+          <t>L'assiette de la fonte est celle de la TVA</t>
         </is>
       </c>
       <c r="D192" s="3" t="inlineStr">
@@ -13350,34 +13350,34 @@
       </c>
       <c r="K192" s="3" t="inlineStr">
         <is>
-          <t>bareme, seuil_d_activation, regle_contre_discretion, robustesse, qualification_regenerative, degeneratif</t>
+          <t>reflux_transactionnel, demurrage, bareme, degeneratif, qualification_regenerative, externalisation, additionnalite</t>
         </is>
       </c>
       <c r="L192" s="3" t="inlineStr">
         <is>
-          <t>L2.C08, L2.C14, L2.C21, L2.C22, L7.C19, L8.C31, L11.C18, L11.C19, L11.C20, L11.C23, L11.C25, L20.C17, L20.C18</t>
+          <t>L1.C21, L1.C27, L2.C16, L11.C02, L11.C05, L11.C09, L11.C21, L11.C24, L11.C25, L20.C02, L20.C19</t>
         </is>
       </c>
       <c r="M192" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-11/c29-la-structure-des-sanctions.md</t>
+          <t>corpus/livre-11/c27-l-assiette-de-la-fonte-est-celle-de-la-tva.md</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" s="2" t="inlineStr">
         <is>
-          <t>L18.C01</t>
+          <t>L11.C28</t>
         </is>
       </c>
       <c r="B193" s="3" t="inlineStr">
         <is>
-          <t>L18</t>
+          <t>L11</t>
         </is>
       </c>
       <c r="C193" s="3" t="inlineStr">
         <is>
-          <t>Ce que ce livre doit établir, et le repli n'est pas l'annexe</t>
+          <t>La fonte sur les acquisitions d'actifs, éprouvée</t>
         </is>
       </c>
       <c r="D193" s="3" t="inlineStr">
@@ -13397,7 +13397,7 @@
       </c>
       <c r="G193" s="3" t="inlineStr">
         <is>
-          <t>hybride</t>
+          <t>conception</t>
         </is>
       </c>
       <c r="H193" s="3" t="inlineStr">
@@ -13409,38 +13409,38 @@
         <v>4</v>
       </c>
       <c r="J193" s="3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K193" s="3" t="inlineStr">
         <is>
-          <t>contrepartie_comptable, valorisation_des_communs, communs, essentiel_insolvable, qualification_regenerative, architecture_invisible</t>
+          <t>reflux_transactionnel, demurrage, bareme, referentiel_de_change, degeneratif, robustesse</t>
         </is>
       </c>
       <c r="L193" s="3" t="inlineStr">
         <is>
-          <t>L1.C09, L1.C29, L5.C02, L5.C09, L5.C10, L6.C08, L6.C09, L6.C13, L11.C13, L11.C16, L20.C02</t>
+          <t>L1.C19, L1.C21, L2.C13, L2.C16, L6.C02, L11.C02, L11.C05, L11.C09, L11.C23, L11.C27, L20.C13</t>
         </is>
       </c>
       <c r="M193" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-18/c01-ce-que-ce-livre-doit-etablir.md</t>
+          <t>corpus/livre-11/c28-la-fonte-sur-les-acquisitions-d-actifs-eprouvee.md</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" s="2" t="inlineStr">
         <is>
-          <t>L18.C02</t>
+          <t>L11.C29</t>
         </is>
       </c>
       <c r="B194" s="3" t="inlineStr">
         <is>
-          <t>L18</t>
+          <t>L11</t>
         </is>
       </c>
       <c r="C194" s="3" t="inlineStr">
         <is>
-          <t>La métrologie existe, et ce qu'elle enregistre est l'ordre en place</t>
+          <t>La structure des sanctions</t>
         </is>
       </c>
       <c r="D194" s="3" t="inlineStr">
@@ -13460,7 +13460,7 @@
       </c>
       <c r="G194" s="3" t="inlineStr">
         <is>
-          <t>hybride</t>
+          <t>conception</t>
         </is>
       </c>
       <c r="H194" s="3" t="inlineStr">
@@ -13469,31 +13469,31 @@
         </is>
       </c>
       <c r="I194" s="3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J194" s="3" t="n">
         <v>3</v>
       </c>
       <c r="K194" s="3" t="inlineStr">
         <is>
-          <t>valorisation_des_communs, contrepartie_comptable, bareme, essentiel_insolvable, indicateur_de_progres, fausse_richesse</t>
+          <t>bareme, seuil_d_activation, regle_contre_discretion, robustesse, qualification_regenerative, degeneratif</t>
         </is>
       </c>
       <c r="L194" s="3" t="inlineStr">
         <is>
-          <t>L1.C09, L1.C15, L1.C18, L6.C06, L11.C03, L11.C07, L11.C13, L11.C16, L18.C01</t>
+          <t>L2.C08, L2.C14, L2.C21, L2.C22, L7.C19, L8.C31, L11.C18, L11.C19, L11.C20, L11.C23, L11.C25, L20.C17, L20.C18</t>
         </is>
       </c>
       <c r="M194" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-18/c02-la-metrologie-existe-et-ce-qu-elle-enregistre.md</t>
+          <t>corpus/livre-11/c29-la-structure-des-sanctions.md</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" s="2" t="inlineStr">
         <is>
-          <t>L18.C03</t>
+          <t>L18.C01</t>
         </is>
       </c>
       <c r="B195" s="3" t="inlineStr">
@@ -13503,7 +13503,7 @@
       </c>
       <c r="C195" s="3" t="inlineStr">
         <is>
-          <t>L'échelle de repli, et qui l'a arrêtée</t>
+          <t>Ce que ce livre doit établir, et le repli n'est pas l'annexe</t>
         </is>
       </c>
       <c r="D195" s="3" t="inlineStr">
@@ -13532,31 +13532,31 @@
         </is>
       </c>
       <c r="I195" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J195" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K195" s="3" t="inlineStr">
         <is>
-          <t>contrepartie_comptable, architecture_invisible, valorisation_des_communs, essentiel_insolvable, regle_contre_discretion</t>
+          <t>contrepartie_comptable, valorisation_des_communs, communs, essentiel_insolvable, qualification_regenerative, architecture_invisible</t>
         </is>
       </c>
       <c r="L195" s="3" t="inlineStr">
         <is>
-          <t>L1.C09, L1.C15, L1.C29, L6.C09, L11.C29, L18.C01, L18.C02, L20.C02</t>
+          <t>L1.C09, L1.C29, L5.C02, L5.C09, L5.C10, L6.C08, L6.C09, L6.C13, L11.C13, L11.C16, L20.C02</t>
         </is>
       </c>
       <c r="M195" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-18/c03-l-echelle-de-repli-et-qui-l-a-arretee.md</t>
+          <t>corpus/livre-18/c01-ce-que-ce-livre-doit-etablir.md</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" s="2" t="inlineStr">
         <is>
-          <t>L18.C04</t>
+          <t>L18.C02</t>
         </is>
       </c>
       <c r="B196" s="3" t="inlineStr">
@@ -13566,7 +13566,7 @@
       </c>
       <c r="C196" s="3" t="inlineStr">
         <is>
-          <t>Les grandeurs physiques, et l'endroit où elles frappent le dispositif</t>
+          <t>La métrologie existe, et ce qu'elle enregistre est l'ordre en place</t>
         </is>
       </c>
       <c r="D196" s="3" t="inlineStr">
@@ -13602,24 +13602,24 @@
       </c>
       <c r="K196" s="3" t="inlineStr">
         <is>
-          <t>decouplage, effet_rebond, externalisation, limites_planetaires, sobriete, fausse_richesse</t>
+          <t>valorisation_des_communs, contrepartie_comptable, bareme, essentiel_insolvable, indicateur_de_progres, fausse_richesse</t>
         </is>
       </c>
       <c r="L196" s="3" t="inlineStr">
         <is>
-          <t>L1.C02, L1.C03, L1.C04, L5.C08, L6.C08, L11.C10, L11.C24, L18.C01, L18.C02</t>
+          <t>L1.C09, L1.C15, L1.C18, L6.C06, L11.C03, L11.C07, L11.C13, L11.C16, L18.C01</t>
         </is>
       </c>
       <c r="M196" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-18/c04-les-grandeurs-physiques-et-ou-elles-frappent.md</t>
+          <t>corpus/livre-18/c02-la-metrologie-existe-et-ce-qu-elle-enregistre.md</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" s="2" t="inlineStr">
         <is>
-          <t>L18.C05</t>
+          <t>L18.C03</t>
         </is>
       </c>
       <c r="B197" s="3" t="inlineStr">
@@ -13629,7 +13629,7 @@
       </c>
       <c r="C197" s="3" t="inlineStr">
         <is>
-          <t>Le commun est ce que la norme exclut, et la symétrie de l'écriture</t>
+          <t>L'échelle de repli, et qui l'a arrêtée</t>
         </is>
       </c>
       <c r="D197" s="3" t="inlineStr">
@@ -13665,24 +13665,24 @@
       </c>
       <c r="K197" s="3" t="inlineStr">
         <is>
-          <t>communs, contrepartie_comptable, valorisation_des_communs, architecture_invisible, monnaie_comme_registre, creation_monetaire</t>
+          <t>contrepartie_comptable, architecture_invisible, valorisation_des_communs, essentiel_insolvable, regle_contre_discretion</t>
         </is>
       </c>
       <c r="L197" s="3" t="inlineStr">
         <is>
-          <t>L1.C09, L1.C20, L1.C29, L6.C06, L6.C08, L11.C13, L11.C16, L18.C01, L18.C02, L18.C03, L20.C02</t>
+          <t>L1.C09, L1.C15, L1.C29, L6.C09, L11.C29, L18.C01, L18.C02, L20.C02</t>
         </is>
       </c>
       <c r="M197" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-18/c05-le-commun-est-ce-que-la-norme-exclut.md</t>
+          <t>corpus/livre-18/c03-l-echelle-de-repli-et-qui-l-a-arretee.md</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" s="2" t="inlineStr">
         <is>
-          <t>L18.C06</t>
+          <t>L18.C04</t>
         </is>
       </c>
       <c r="B198" s="3" t="inlineStr">
@@ -13692,7 +13692,7 @@
       </c>
       <c r="C198" s="3" t="inlineStr">
         <is>
-          <t>Portée de la tranche, et une neuvième condition proposée</t>
+          <t>Les grandeurs physiques, et l'endroit où elles frappent le dispositif</t>
         </is>
       </c>
       <c r="D198" s="3" t="inlineStr">
@@ -13712,7 +13712,7 @@
       </c>
       <c r="G198" s="3" t="inlineStr">
         <is>
-          <t>conception</t>
+          <t>hybride</t>
         </is>
       </c>
       <c r="H198" s="3" t="inlineStr">
@@ -13721,31 +13721,31 @@
         </is>
       </c>
       <c r="I198" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J198" s="3" t="n">
         <v>3</v>
       </c>
       <c r="K198" s="3" t="inlineStr">
         <is>
-          <t>contrepartie_comptable, communs, valorisation_des_communs, architecture_invisible, essentiel_insolvable</t>
+          <t>decouplage, effet_rebond, externalisation, limites_planetaires, sobriete, fausse_richesse</t>
         </is>
       </c>
       <c r="L198" s="3" t="inlineStr">
         <is>
-          <t>L1.C09, L1.C18, L1.C20, L1.C29, L5.C02, L5.C08, L6.C06, L6.C08, L11.C13, L11.C16, L18.C01, L18.C02, L18.C03, L18.C04, L18.C05, L20.C02</t>
+          <t>L1.C02, L1.C03, L1.C04, L5.C08, L6.C08, L11.C10, L11.C24, L18.C01, L18.C02</t>
         </is>
       </c>
       <c r="M198" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-18/c06-portee-de-la-tranche-et-une-neuvieme-condition.md</t>
+          <t>corpus/livre-18/c04-les-grandeurs-physiques-et-ou-elles-frappent.md</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" s="2" t="inlineStr">
         <is>
-          <t>L18.C07</t>
+          <t>L18.C05</t>
         </is>
       </c>
       <c r="B199" s="3" t="inlineStr">
@@ -13755,7 +13755,7 @@
       </c>
       <c r="C199" s="3" t="inlineStr">
         <is>
-          <t>CARE/TDL répare deux objections, et en crée une plus grave</t>
+          <t>Le commun est ce que la norme exclut, et la symétrie de l'écriture</t>
         </is>
       </c>
       <c r="D199" s="3" t="inlineStr">
@@ -13784,31 +13784,31 @@
         </is>
       </c>
       <c r="I199" s="3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J199" s="3" t="n">
         <v>3</v>
       </c>
       <c r="K199" s="3" t="inlineStr">
         <is>
-          <t>contrepartie_comptable, bareme, valorisation_des_communs, communs, architecture_invisible, fausse_richesse</t>
+          <t>communs, contrepartie_comptable, valorisation_des_communs, architecture_invisible, monnaie_comme_registre, creation_monetaire</t>
         </is>
       </c>
       <c r="L199" s="3" t="inlineStr">
         <is>
-          <t>L1.C09, L1.C18, L1.C20, L6.C06, L11.C03, L11.C13, L11.C16, L18.C01, L18.C02, L18.C05, L18.C06</t>
+          <t>L1.C09, L1.C20, L1.C29, L6.C06, L6.C08, L11.C13, L11.C16, L18.C01, L18.C02, L18.C03, L20.C02</t>
         </is>
       </c>
       <c r="M199" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-18/c07-care-tdl-repare-une-objection-et-en-cree-une-autre.md</t>
+          <t>corpus/livre-18/c05-le-commun-est-ce-que-la-norme-exclut.md</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" s="2" t="inlineStr">
         <is>
-          <t>L18.C08</t>
+          <t>L18.C06</t>
         </is>
       </c>
       <c r="B200" s="3" t="inlineStr">
@@ -13818,7 +13818,7 @@
       </c>
       <c r="C200" s="3" t="inlineStr">
         <is>
-          <t>Le modèle au périmètre du dispositif, et F9 révisée</t>
+          <t>Portée de la tranche, et une neuvième condition proposée</t>
         </is>
       </c>
       <c r="D200" s="3" t="inlineStr">
@@ -13847,41 +13847,41 @@
         </is>
       </c>
       <c r="I200" s="3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J200" s="3" t="n">
         <v>3</v>
       </c>
       <c r="K200" s="3" t="inlineStr">
         <is>
-          <t>contrepartie_comptable, communs, valorisation_des_communs, polycentricite, essentiel_insolvable, indicateur_de_progres</t>
+          <t>contrepartie_comptable, communs, valorisation_des_communs, architecture_invisible, essentiel_insolvable</t>
         </is>
       </c>
       <c r="L200" s="3" t="inlineStr">
         <is>
-          <t>L1.C09, L1.C18, L6.C06, L7.C05, L11.C13, L11.C16, L11.C25, L18.C01, L18.C02, L18.C05, L18.C06, L18.C07</t>
+          <t>L1.C09, L1.C18, L1.C20, L1.C29, L5.C02, L5.C08, L6.C06, L6.C08, L11.C13, L11.C16, L18.C01, L18.C02, L18.C03, L18.C04, L18.C05, L20.C02</t>
         </is>
       </c>
       <c r="M200" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-18/c08-le-modele-au-perimetre-du-dispositif-et-f9-revisee.md</t>
+          <t>corpus/livre-18/c06-portee-de-la-tranche-et-une-neuvieme-condition.md</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" s="2" t="inlineStr">
         <is>
-          <t>L20.C01</t>
+          <t>L18.C07</t>
         </is>
       </c>
       <c r="B201" s="3" t="inlineStr">
         <is>
-          <t>L20</t>
+          <t>L18</t>
         </is>
       </c>
       <c r="C201" s="3" t="inlineStr">
         <is>
-          <t>Ce que ce livre doit établir</t>
+          <t>CARE/TDL répare deux objections, et en crée une plus grave</t>
         </is>
       </c>
       <c r="D201" s="3" t="inlineStr">
@@ -13901,50 +13901,50 @@
       </c>
       <c r="G201" s="3" t="inlineStr">
         <is>
-          <t>conception</t>
+          <t>hybride</t>
         </is>
       </c>
       <c r="H201" s="3" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="I201" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J201" s="3" t="n">
         <v>3</v>
       </c>
       <c r="K201" s="3" t="inlineStr">
         <is>
-          <t>fenetre_de_reforme, referentiel_de_change, communs, limites_planetaires, creation_monetaire</t>
+          <t>contrepartie_comptable, bareme, valorisation_des_communs, communs, architecture_invisible, fausse_richesse</t>
         </is>
       </c>
       <c r="L201" s="3" t="inlineStr">
         <is>
-          <t>L1.C18, L1.C25, L1.C27, L7.C01, L7.C03, L7.C13, L7.C17, L7.C21, L11.C24</t>
+          <t>L1.C09, L1.C18, L1.C20, L6.C06, L11.C03, L11.C13, L11.C16, L18.C01, L18.C02, L18.C05, L18.C06</t>
         </is>
       </c>
       <c r="M201" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-20/c01-ce-que-ce-livre-doit-etablir.md</t>
+          <t>corpus/livre-18/c07-care-tdl-repare-une-objection-et-en-cree-une-autre.md</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" s="2" t="inlineStr">
         <is>
-          <t>L20.C02</t>
+          <t>L18.C08</t>
         </is>
       </c>
       <c r="B202" s="3" t="inlineStr">
         <is>
-          <t>L20</t>
+          <t>L18</t>
         </is>
       </c>
       <c r="C202" s="3" t="inlineStr">
         <is>
-          <t>L'interdiction du financement monétaire</t>
+          <t>Le modèle au périmètre du dispositif, et F9 révisée</t>
         </is>
       </c>
       <c r="D202" s="3" t="inlineStr">
@@ -13973,31 +13973,31 @@
         </is>
       </c>
       <c r="I202" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J202" s="3" t="n">
         <v>3</v>
       </c>
       <c r="K202" s="3" t="inlineStr">
         <is>
-          <t>creation_monetaire, contrepartie_comptable, reflux_collectif, fenetre_de_reforme</t>
+          <t>contrepartie_comptable, communs, valorisation_des_communs, polycentricite, essentiel_insolvable, indicateur_de_progres</t>
         </is>
       </c>
       <c r="L202" s="3" t="inlineStr">
         <is>
-          <t>L1.C05, L1.C18, L1.C20, L1.C22, L7.C11, L7.C13, L11.C10, L20.C01</t>
+          <t>L1.C09, L1.C18, L6.C06, L7.C05, L11.C13, L11.C16, L11.C25, L18.C01, L18.C02, L18.C05, L18.C06, L18.C07</t>
         </is>
       </c>
       <c r="M202" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-20/c02-l-interdiction-du-financement-monetaire.md</t>
+          <t>corpus/livre-18/c08-le-modele-au-perimetre-du-dispositif-et-f9-revisee.md</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" s="2" t="inlineStr">
         <is>
-          <t>L20.C03</t>
+          <t>L20.C01</t>
         </is>
       </c>
       <c r="B203" s="3" t="inlineStr">
@@ -14007,7 +14007,7 @@
       </c>
       <c r="C203" s="3" t="inlineStr">
         <is>
-          <t>L'objectif principal et ce qu'il exclut</t>
+          <t>Ce que ce livre doit établir</t>
         </is>
       </c>
       <c r="D203" s="3" t="inlineStr">
@@ -14032,7 +14032,7 @@
       </c>
       <c r="H203" s="3" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="I203" s="3" t="n">
@@ -14043,24 +14043,24 @@
       </c>
       <c r="K203" s="3" t="inlineStr">
         <is>
-          <t>regle_contre_discretion, limites_planetaires, creation_monetaire, plafond_ecologique</t>
+          <t>fenetre_de_reforme, referentiel_de_change, communs, limites_planetaires, creation_monetaire</t>
         </is>
       </c>
       <c r="L203" s="3" t="inlineStr">
         <is>
-          <t>L1.C01, L1.C18, L1.C20, L7.C03, L8.C12, L8.C34, L11.C16, L20.C01, L20.C02</t>
+          <t>L1.C18, L1.C25, L1.C27, L7.C01, L7.C03, L7.C13, L7.C17, L7.C21, L11.C24</t>
         </is>
       </c>
       <c r="M203" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-20/c03-l-objectif-principal-et-ce-qu-il-exclut.md</t>
+          <t>corpus/livre-20/c01-ce-que-ce-livre-doit-etablir.md</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" s="2" t="inlineStr">
         <is>
-          <t>L20.C04</t>
+          <t>L20.C02</t>
         </is>
       </c>
       <c r="B204" s="3" t="inlineStr">
@@ -14070,7 +14070,7 @@
       </c>
       <c r="C204" s="3" t="inlineStr">
         <is>
-          <t>L'indépendance, et à l'égard de qui</t>
+          <t>L'interdiction du financement monétaire</t>
         </is>
       </c>
       <c r="D204" s="3" t="inlineStr">
@@ -14095,7 +14095,7 @@
       </c>
       <c r="H204" s="3" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="I204" s="3" t="n">
@@ -14106,24 +14106,24 @@
       </c>
       <c r="K204" s="3" t="inlineStr">
         <is>
-          <t>regle_contre_discretion, creation_monetaire, fenetre_de_reforme</t>
+          <t>creation_monetaire, contrepartie_comptable, reflux_collectif, fenetre_de_reforme</t>
         </is>
       </c>
       <c r="L204" s="3" t="inlineStr">
         <is>
-          <t>L1.C18, L7.C04, L7.C07, L7.C10, L8.C31, L11.C17, L20.C01, L20.C03, L20.C11</t>
+          <t>L1.C05, L1.C18, L1.C20, L1.C22, L7.C11, L7.C13, L11.C10, L20.C01</t>
         </is>
       </c>
       <c r="M204" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-20/c04-l-independance-et-a-l-egard-de-qui.md</t>
+          <t>corpus/livre-20/c02-l-interdiction-du-financement-monetaire.md</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" s="2" t="inlineStr">
         <is>
-          <t>L20.C05</t>
+          <t>L20.C03</t>
         </is>
       </c>
       <c r="B205" s="3" t="inlineStr">
@@ -14133,7 +14133,7 @@
       </c>
       <c r="C205" s="3" t="inlineStr">
         <is>
-          <t>Le monopole d'émission et le cours légal</t>
+          <t>L'objectif principal et ce qu'il exclut</t>
         </is>
       </c>
       <c r="D205" s="3" t="inlineStr">
@@ -14158,7 +14158,7 @@
       </c>
       <c r="H205" s="3" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="I205" s="3" t="n">
@@ -14169,24 +14169,24 @@
       </c>
       <c r="K205" s="3" t="inlineStr">
         <is>
-          <t>monnaie_comme_registre, creation_monetaire, referentiel_de_change, hierarchie_monetaire</t>
+          <t>regle_contre_discretion, limites_planetaires, creation_monetaire, plafond_ecologique</t>
         </is>
       </c>
       <c r="L205" s="3" t="inlineStr">
         <is>
-          <t>L1.C05, L1.C07, L1.C26, L7.C15, L11.C15, L20.C01, L20.C02, L20.C03</t>
+          <t>L1.C01, L1.C18, L1.C20, L7.C03, L8.C12, L8.C34, L11.C16, L20.C01, L20.C02</t>
         </is>
       </c>
       <c r="M205" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-20/c05-le-monopole-d-emission-et-le-cours-legal.md</t>
+          <t>corpus/livre-20/c03-l-objectif-principal-et-ce-qu-il-exclut.md</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" s="2" t="inlineStr">
         <is>
-          <t>L20.C06</t>
+          <t>L20.C04</t>
         </is>
       </c>
       <c r="B206" s="3" t="inlineStr">
@@ -14196,7 +14196,7 @@
       </c>
       <c r="C206" s="3" t="inlineStr">
         <is>
-          <t>Les voies de révision et leur coût</t>
+          <t>L'indépendance, et à l'égard de qui</t>
         </is>
       </c>
       <c r="D206" s="3" t="inlineStr">
@@ -14225,31 +14225,31 @@
         </is>
       </c>
       <c r="I206" s="3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J206" s="3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K206" s="3" t="inlineStr">
         <is>
-          <t>fenetre_de_reforme, regle_contre_discretion, creation_monetaire</t>
+          <t>regle_contre_discretion, creation_monetaire, fenetre_de_reforme</t>
         </is>
       </c>
       <c r="L206" s="3" t="inlineStr">
         <is>
-          <t>L1.C18, L7.C12, L7.C20, L7.C21, L11.C15, L20.C01, L20.C02, L20.C03, L20.C07, L20.C09, L20.C18</t>
+          <t>L1.C18, L7.C04, L7.C07, L7.C10, L8.C31, L11.C17, L20.C01, L20.C03, L20.C11</t>
         </is>
       </c>
       <c r="M206" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-20/c06-les-voies-de-revision-et-leur-cout.md</t>
+          <t>corpus/livre-20/c04-l-independance-et-a-l-egard-de-qui.md</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" s="2" t="inlineStr">
         <is>
-          <t>L20.C07</t>
+          <t>L20.C05</t>
         </is>
       </c>
       <c r="B207" s="3" t="inlineStr">
@@ -14259,7 +14259,7 @@
       </c>
       <c r="C207" s="3" t="inlineStr">
         <is>
-          <t>L'accord monétaire international</t>
+          <t>Le monopole d'émission et le cours légal</t>
         </is>
       </c>
       <c r="D207" s="3" t="inlineStr">
@@ -14295,24 +14295,24 @@
       </c>
       <c r="K207" s="3" t="inlineStr">
         <is>
-          <t>referentiel_de_change, fenetre_de_reforme, etalon_de_change_or, hierarchie_monetaire</t>
+          <t>monnaie_comme_registre, creation_monetaire, referentiel_de_change, hierarchie_monetaire</t>
         </is>
       </c>
       <c r="L207" s="3" t="inlineStr">
         <is>
-          <t>L1.C18, L1.C26, L7.C02, L7.C05, L7.C12, L7.C13, L11.C15, L20.C01, L20.C03, L20.C06, L20.C10</t>
+          <t>L1.C05, L1.C07, L1.C26, L7.C15, L11.C15, L20.C01, L20.C02, L20.C03</t>
         </is>
       </c>
       <c r="M207" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-20/c07-l-accord-monetaire-international.md</t>
+          <t>corpus/livre-20/c05-le-monopole-d-emission-et-le-cours-legal.md</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" s="2" t="inlineStr">
         <is>
-          <t>L20.C08</t>
+          <t>L20.C06</t>
         </is>
       </c>
       <c r="B208" s="3" t="inlineStr">
@@ -14322,7 +14322,7 @@
       </c>
       <c r="C208" s="3" t="inlineStr">
         <is>
-          <t>La parité inscrite dans le traité</t>
+          <t>Les voies de révision et leur coût</t>
         </is>
       </c>
       <c r="D208" s="3" t="inlineStr">
@@ -14347,35 +14347,35 @@
       </c>
       <c r="H208" s="3" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="I208" s="3" t="n">
         <v>4</v>
       </c>
       <c r="J208" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K208" s="3" t="inlineStr">
         <is>
-          <t>referentiel_de_change, etalon_de_change_or, hierarchie_monetaire, bareme, devise_cle</t>
+          <t>fenetre_de_reforme, regle_contre_discretion, creation_monetaire</t>
         </is>
       </c>
       <c r="L208" s="3" t="inlineStr">
         <is>
-          <t>L1.C25, L1.C26, L1.C28, L7.C02, L7.C20, L11.C15, L11.C17, L20.C01, L20.C09, L20.C13</t>
+          <t>L1.C18, L7.C12, L7.C20, L7.C21, L11.C15, L20.C01, L20.C02, L20.C03, L20.C07, L20.C09, L20.C18</t>
         </is>
       </c>
       <c r="M208" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-20/c08-la-parite-inscrite-dans-le-traite.md</t>
+          <t>corpus/livre-20/c06-les-voies-de-revision-et-leur-cout.md</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" s="2" t="inlineStr">
         <is>
-          <t>L20.C09</t>
+          <t>L20.C07</t>
         </is>
       </c>
       <c r="B209" s="3" t="inlineStr">
@@ -14385,7 +14385,7 @@
       </c>
       <c r="C209" s="3" t="inlineStr">
         <is>
-          <t>L'amendement des statuts du Fonds</t>
+          <t>L'accord monétaire international</t>
         </is>
       </c>
       <c r="D209" s="3" t="inlineStr">
@@ -14421,24 +14421,24 @@
       </c>
       <c r="K209" s="3" t="inlineStr">
         <is>
-          <t>fenetre_de_reforme, referentiel_de_change, bareme, regle_contre_discretion</t>
+          <t>referentiel_de_change, fenetre_de_reforme, etalon_de_change_or, hierarchie_monetaire</t>
         </is>
       </c>
       <c r="L209" s="3" t="inlineStr">
         <is>
-          <t>L7.C06, L7.C09, L7.C16, L7.C20, L11.C15, L11.C20, L20.C01, L20.C06, L20.C08, L20.C10, L20.C13</t>
+          <t>L1.C18, L1.C26, L7.C02, L7.C05, L7.C12, L7.C13, L11.C15, L20.C01, L20.C03, L20.C06, L20.C10</t>
         </is>
       </c>
       <c r="M209" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-20/c09-l-amendement-des-statuts-du-fonds.md</t>
+          <t>corpus/livre-20/c07-l-accord-monetaire-international.md</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" s="2" t="inlineStr">
         <is>
-          <t>L20.C10</t>
+          <t>L20.C08</t>
         </is>
       </c>
       <c r="B210" s="3" t="inlineStr">
@@ -14448,7 +14448,7 @@
       </c>
       <c r="C210" s="3" t="inlineStr">
         <is>
-          <t>Le vote pondéré et les voix de base</t>
+          <t>La parité inscrite dans le traité</t>
         </is>
       </c>
       <c r="D210" s="3" t="inlineStr">
@@ -14473,35 +14473,35 @@
       </c>
       <c r="H210" s="3" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="I210" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J210" s="3" t="n">
         <v>3</v>
       </c>
       <c r="K210" s="3" t="inlineStr">
         <is>
-          <t>bareme, devise_cle, hierarchie_monetaire, referentiel_de_change</t>
+          <t>referentiel_de_change, etalon_de_change_or, hierarchie_monetaire, bareme, devise_cle</t>
         </is>
       </c>
       <c r="L210" s="3" t="inlineStr">
         <is>
-          <t>L1.C25, L7.C02, L7.C05, L7.C06, L7.C09, L7.C10, L11.C16, L20.C01, L20.C07, L20.C09, L20.C12</t>
+          <t>L1.C25, L1.C26, L1.C28, L7.C02, L7.C20, L11.C15, L11.C17, L20.C01, L20.C09, L20.C13</t>
         </is>
       </c>
       <c r="M210" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-20/c10-le-vote-pondere-et-les-voix-de-base.md</t>
+          <t>corpus/livre-20/c08-la-parite-inscrite-dans-le-traite.md</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" s="2" t="inlineStr">
         <is>
-          <t>L20.C11</t>
+          <t>L20.C09</t>
         </is>
       </c>
       <c r="B211" s="3" t="inlineStr">
@@ -14511,7 +14511,7 @@
       </c>
       <c r="C211" s="3" t="inlineStr">
         <is>
-          <t>La personnalité juridique et les immunités</t>
+          <t>L'amendement des statuts du Fonds</t>
         </is>
       </c>
       <c r="D211" s="3" t="inlineStr">
@@ -14540,31 +14540,31 @@
         </is>
       </c>
       <c r="I211" s="3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J211" s="3" t="n">
         <v>3</v>
       </c>
       <c r="K211" s="3" t="inlineStr">
         <is>
-          <t>communs, creation_monetaire, fenetre_de_reforme, robustesse</t>
+          <t>fenetre_de_reforme, referentiel_de_change, bareme, regle_contre_discretion</t>
         </is>
       </c>
       <c r="L211" s="3" t="inlineStr">
         <is>
-          <t>L7.C01, L7.C03, L7.C07, L7.C10, L7.C13, L11.C25, L20.C01, L20.C04, L20.C12, L20.C14</t>
+          <t>L7.C06, L7.C09, L7.C16, L7.C20, L11.C15, L11.C20, L20.C01, L20.C06, L20.C08, L20.C10, L20.C13</t>
         </is>
       </c>
       <c r="M211" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-20/c11-la-personnalite-juridique-et-les-immunites.md</t>
+          <t>corpus/livre-20/c09-l-amendement-des-statuts-du-fonds.md</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" s="2" t="inlineStr">
         <is>
-          <t>L20.C12</t>
+          <t>L20.C10</t>
         </is>
       </c>
       <c r="B212" s="3" t="inlineStr">
@@ -14574,7 +14574,7 @@
       </c>
       <c r="C212" s="3" t="inlineStr">
         <is>
-          <t>Les pouvoirs non délégables</t>
+          <t>Le vote pondéré et les voix de base</t>
         </is>
       </c>
       <c r="D212" s="3" t="inlineStr">
@@ -14599,7 +14599,7 @@
       </c>
       <c r="H212" s="3" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="I212" s="3" t="n">
@@ -14610,24 +14610,24 @@
       </c>
       <c r="K212" s="3" t="inlineStr">
         <is>
-          <t>bareme, valorisation_des_communs, polycentricite, robustesse</t>
+          <t>bareme, devise_cle, hierarchie_monetaire, referentiel_de_change</t>
         </is>
       </c>
       <c r="L212" s="3" t="inlineStr">
         <is>
-          <t>L7.C05, L7.C06, L7.C07, L7.C11, L7.C14, L11.C16, L11.C20, L20.C01, L20.C09, L20.C10, L20.C14</t>
+          <t>L1.C25, L7.C02, L7.C05, L7.C06, L7.C09, L7.C10, L11.C16, L20.C01, L20.C07, L20.C09, L20.C12</t>
         </is>
       </c>
       <c r="M212" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-20/c12-les-pouvoirs-non-delegables.md</t>
+          <t>corpus/livre-20/c10-le-vote-pondere-et-les-voix-de-base.md</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" s="2" t="inlineStr">
         <is>
-          <t>L20.C13</t>
+          <t>L20.C11</t>
         </is>
       </c>
       <c r="B213" s="3" t="inlineStr">
@@ -14637,7 +14637,7 @@
       </c>
       <c r="C213" s="3" t="inlineStr">
         <is>
-          <t>L'entrée en vigueur, l'adhésion et le retrait</t>
+          <t>La personnalité juridique et les immunités</t>
         </is>
       </c>
       <c r="D213" s="3" t="inlineStr">
@@ -14662,7 +14662,7 @@
       </c>
       <c r="H213" s="3" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="I213" s="3" t="n">
@@ -14673,24 +14673,24 @@
       </c>
       <c r="K213" s="3" t="inlineStr">
         <is>
-          <t>seuil_d_activation, reflux_collectif, fenetre_de_reforme, additionnalite</t>
+          <t>communs, creation_monetaire, fenetre_de_reforme, robustesse</t>
         </is>
       </c>
       <c r="L213" s="3" t="inlineStr">
         <is>
-          <t>L7.C11, L7.C12, L7.C16, L7.C17, L7.C19, L11.C18, L20.C01, L20.C06, L20.C09, L20.C12</t>
+          <t>L7.C01, L7.C03, L7.C07, L7.C10, L7.C13, L11.C25, L20.C01, L20.C04, L20.C12, L20.C14</t>
         </is>
       </c>
       <c r="M213" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-20/c13-l-entree-en-vigueur-l-adhesion-et-le-retrait.md</t>
+          <t>corpus/livre-20/c11-la-personnalite-juridique-et-les-immunites.md</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" s="2" t="inlineStr">
         <is>
-          <t>L20.C14</t>
+          <t>L20.C12</t>
         </is>
       </c>
       <c r="B214" s="3" t="inlineStr">
@@ -14700,7 +14700,7 @@
       </c>
       <c r="C214" s="3" t="inlineStr">
         <is>
-          <t>Qui interprète le traité</t>
+          <t>Les pouvoirs non délégables</t>
         </is>
       </c>
       <c r="D214" s="3" t="inlineStr">
@@ -14736,24 +14736,24 @@
       </c>
       <c r="K214" s="3" t="inlineStr">
         <is>
-          <t>robustesse, regle_contre_discretion, communs</t>
+          <t>bareme, valorisation_des_communs, polycentricite, robustesse</t>
         </is>
       </c>
       <c r="L214" s="3" t="inlineStr">
         <is>
-          <t>L7.C07, L7.C13, L7.C14, L7.C19, L11.C19, L11.C25, L20.C01, L20.C03, L20.C11, L20.C12, L20.C21</t>
+          <t>L7.C05, L7.C06, L7.C07, L7.C11, L7.C14, L11.C16, L11.C20, L20.C01, L20.C09, L20.C10, L20.C14</t>
         </is>
       </c>
       <c r="M214" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-20/c14-qui-interprete-le-traite.md</t>
+          <t>corpus/livre-20/c12-les-pouvoirs-non-delegables.md</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" s="2" t="inlineStr">
         <is>
-          <t>L20.C15</t>
+          <t>L20.C13</t>
         </is>
       </c>
       <c r="B215" s="3" t="inlineStr">
@@ -14763,7 +14763,7 @@
       </c>
       <c r="C215" s="3" t="inlineStr">
         <is>
-          <t>Le devoir international des agents</t>
+          <t>L'entrée en vigueur, l'adhésion et le retrait</t>
         </is>
       </c>
       <c r="D215" s="3" t="inlineStr">
@@ -14788,35 +14788,35 @@
       </c>
       <c r="H215" s="3" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="I215" s="3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J215" s="3" t="n">
         <v>3</v>
       </c>
       <c r="K215" s="3" t="inlineStr">
         <is>
-          <t>robustesse, regle_contre_discretion, indicateur_de_progres</t>
+          <t>seuil_d_activation, reflux_collectif, fenetre_de_reforme, additionnalite</t>
         </is>
       </c>
       <c r="L215" s="3" t="inlineStr">
         <is>
-          <t>L7.C04, L7.C07, L7.C10, L11.C21, L11.C25, L20.C01, L20.C04, L20.C11, L20.C14</t>
+          <t>L7.C11, L7.C12, L7.C16, L7.C17, L7.C19, L11.C18, L20.C01, L20.C06, L20.C09, L20.C12</t>
         </is>
       </c>
       <c r="M215" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-20/c15-le-devoir-international-des-agents.md</t>
+          <t>corpus/livre-20/c13-l-entree-en-vigueur-l-adhesion-et-le-retrait.md</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" s="2" t="inlineStr">
         <is>
-          <t>L20.C16</t>
+          <t>L20.C14</t>
         </is>
       </c>
       <c r="B216" s="3" t="inlineStr">
@@ -14826,7 +14826,7 @@
       </c>
       <c r="C216" s="3" t="inlineStr">
         <is>
-          <t>Le patrimoine commun de l'humanité</t>
+          <t>Qui interprète le traité</t>
         </is>
       </c>
       <c r="D216" s="3" t="inlineStr">
@@ -14862,24 +14862,24 @@
       </c>
       <c r="K216" s="3" t="inlineStr">
         <is>
-          <t>communs, valorisation_des_communs, limites_planetaires, additionnalite, plafond_ecologique</t>
+          <t>robustesse, regle_contre_discretion, communs</t>
         </is>
       </c>
       <c r="L216" s="3" t="inlineStr">
         <is>
-          <t>L1.C17, L1.C22, L7.C05, L7.C13, L11.C16, L20.C01, L20.C11, L20.C17, L20.C22</t>
+          <t>L7.C07, L7.C13, L7.C14, L7.C19, L11.C19, L11.C25, L20.C01, L20.C03, L20.C11, L20.C12, L20.C21</t>
         </is>
       </c>
       <c r="M216" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-20/c16-le-patrimoine-commun-de-l-humanite.md</t>
+          <t>corpus/livre-20/c14-qui-interprete-le-traite.md</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" s="2" t="inlineStr">
         <is>
-          <t>L20.C17</t>
+          <t>L20.C15</t>
         </is>
       </c>
       <c r="B217" s="3" t="inlineStr">
@@ -14889,7 +14889,7 @@
       </c>
       <c r="C217" s="3" t="inlineStr">
         <is>
-          <t>La sanctuarisation, et elle existe</t>
+          <t>Le devoir international des agents</t>
         </is>
       </c>
       <c r="D217" s="3" t="inlineStr">
@@ -14914,35 +14914,35 @@
       </c>
       <c r="H217" s="3" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="I217" s="3" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J217" s="3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K217" s="3" t="inlineStr">
         <is>
-          <t>communs, limites_planetaires, fenetre_de_reforme, robustesse, plafond_ecologique</t>
+          <t>robustesse, regle_contre_discretion, indicateur_de_progres</t>
         </is>
       </c>
       <c r="L217" s="3" t="inlineStr">
         <is>
-          <t>L1.C17, L1.C18, L7.C13, L7.C19, L7.C20, L11.C20, L20.C01, L20.C06, L20.C09, L20.C16, L20.C22</t>
+          <t>L7.C04, L7.C07, L7.C10, L11.C21, L11.C25, L20.C01, L20.C04, L20.C11, L20.C14</t>
         </is>
       </c>
       <c r="M217" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-20/c17-la-sanctuarisation-et-elle-existe.md</t>
+          <t>corpus/livre-20/c15-le-devoir-international-des-agents.md</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" s="2" t="inlineStr">
         <is>
-          <t>L20.C18</t>
+          <t>L20.C16</t>
         </is>
       </c>
       <c r="B218" s="3" t="inlineStr">
@@ -14952,7 +14952,7 @@
       </c>
       <c r="C218" s="3" t="inlineStr">
         <is>
-          <t>L'amendement et la dérogation dans l'ordre commercial</t>
+          <t>Le patrimoine commun de l'humanité</t>
         </is>
       </c>
       <c r="D218" s="3" t="inlineStr">
@@ -14977,7 +14977,7 @@
       </c>
       <c r="H218" s="3" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="I218" s="3" t="n">
@@ -14988,24 +14988,24 @@
       </c>
       <c r="K218" s="3" t="inlineStr">
         <is>
-          <t>bareme, seuil_d_activation, additionnalite, fenetre_de_reforme</t>
+          <t>communs, valorisation_des_communs, limites_planetaires, additionnalite, plafond_ecologique</t>
         </is>
       </c>
       <c r="L218" s="3" t="inlineStr">
         <is>
-          <t>L1.C27, L7.C17, L7.C20, L11.C24, L20.C01, L20.C06, L20.C09, L20.C13, L20.C19, L20.C20</t>
+          <t>L1.C17, L1.C22, L7.C05, L7.C13, L11.C16, L20.C01, L20.C11, L20.C17, L20.C22</t>
         </is>
       </c>
       <c r="M218" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-20/c18-l-amendement-et-la-derogation-dans-l-ordre-commercial.md</t>
+          <t>corpus/livre-20/c16-le-patrimoine-commun-de-l-humanite.md</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" s="2" t="inlineStr">
         <is>
-          <t>L20.C19</t>
+          <t>L20.C17</t>
         </is>
       </c>
       <c r="B219" s="3" t="inlineStr">
@@ -15015,7 +15015,7 @@
       </c>
       <c r="C219" s="3" t="inlineStr">
         <is>
-          <t>Le texte que la conformité invoque</t>
+          <t>La sanctuarisation, et elle existe</t>
         </is>
       </c>
       <c r="D219" s="3" t="inlineStr">
@@ -15047,28 +15047,28 @@
         <v>4</v>
       </c>
       <c r="J219" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K219" s="3" t="inlineStr">
         <is>
-          <t>bareme, additionnalite, limites_planetaires, seuil_d_activation, externalisation</t>
+          <t>communs, limites_planetaires, fenetre_de_reforme, robustesse, plafond_ecologique</t>
         </is>
       </c>
       <c r="L219" s="3" t="inlineStr">
         <is>
-          <t>L1.C27, L7.C17, L11.C24, L20.C01, L20.C18, L20.C20, L20.C22</t>
+          <t>L1.C17, L1.C18, L7.C13, L7.C19, L7.C20, L11.C20, L20.C01, L20.C06, L20.C09, L20.C16, L20.C22</t>
         </is>
       </c>
       <c r="M219" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-20/c19-le-texte-que-la-conformite-invoque.md</t>
+          <t>corpus/livre-20/c17-la-sanctuarisation-et-elle-existe.md</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" s="2" t="inlineStr">
         <is>
-          <t>L20.C20</t>
+          <t>L20.C18</t>
         </is>
       </c>
       <c r="B220" s="3" t="inlineStr">
@@ -15078,7 +15078,7 @@
       </c>
       <c r="C220" s="3" t="inlineStr">
         <is>
-          <t>L'ajustement aux frontières comme précédent</t>
+          <t>L'amendement et la dérogation dans l'ordre commercial</t>
         </is>
       </c>
       <c r="D220" s="3" t="inlineStr">
@@ -15107,31 +15107,31 @@
         </is>
       </c>
       <c r="I220" s="3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J220" s="3" t="n">
         <v>3</v>
       </c>
       <c r="K220" s="3" t="inlineStr">
         <is>
-          <t>bareme, seuil_d_activation, externalisation, additionnalite, contrepartie_comptable</t>
+          <t>bareme, seuil_d_activation, additionnalite, fenetre_de_reforme</t>
         </is>
       </c>
       <c r="L220" s="3" t="inlineStr">
         <is>
-          <t>L1.C27, L7.C17, L11.C21, L11.C24, L11.C25, L20.C01, L20.C18, L20.C19, L20.C22</t>
+          <t>L1.C27, L7.C17, L7.C20, L11.C24, L20.C01, L20.C06, L20.C09, L20.C13, L20.C19, L20.C20</t>
         </is>
       </c>
       <c r="M220" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-20/c20-l-ajustement-aux-frontieres-comme-precedent.md</t>
+          <t>corpus/livre-20/c18-l-amendement-et-la-derogation-dans-l-ordre-commercial.md</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" s="2" t="inlineStr">
         <is>
-          <t>L20.C21</t>
+          <t>L20.C19</t>
         </is>
       </c>
       <c r="B221" s="3" t="inlineStr">
@@ -15141,7 +15141,7 @@
       </c>
       <c r="C221" s="3" t="inlineStr">
         <is>
-          <t>La transparence et sa limite juridictionnelle</t>
+          <t>Le texte que la conformité invoque</t>
         </is>
       </c>
       <c r="D221" s="3" t="inlineStr">
@@ -15166,35 +15166,35 @@
       </c>
       <c r="H221" s="3" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="I221" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J221" s="3" t="n">
         <v>3</v>
       </c>
       <c r="K221" s="3" t="inlineStr">
         <is>
-          <t>robustesse, contrepartie_comptable, bareme, monnaie_comme_registre</t>
+          <t>bareme, additionnalite, limites_planetaires, seuil_d_activation, externalisation</t>
         </is>
       </c>
       <c r="L221" s="3" t="inlineStr">
         <is>
-          <t>L7.C18, L11.C21, L11.C24, L11.C25, L20.C01, L20.C11, L20.C14, L20.C20, L20.C22</t>
+          <t>L1.C27, L7.C17, L11.C24, L20.C01, L20.C18, L20.C20, L20.C22</t>
         </is>
       </c>
       <c r="M221" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-20/c21-la-transparence-et-sa-limite-juridictionnelle.md</t>
+          <t>corpus/livre-20/c19-le-texte-que-la-conformite-invoque.md</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" s="2" t="inlineStr">
         <is>
-          <t>L20.C22</t>
+          <t>L20.C20</t>
         </is>
       </c>
       <c r="B222" s="3" t="inlineStr">
@@ -15204,7 +15204,7 @@
       </c>
       <c r="C222" s="3" t="inlineStr">
         <is>
-          <t>Ce que le droit devrait devenir</t>
+          <t>L'ajustement aux frontières comme précédent</t>
         </is>
       </c>
       <c r="D222" s="3" t="inlineStr">
@@ -15233,92 +15233,218 @@
         </is>
       </c>
       <c r="I222" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J222" s="3" t="n">
         <v>3</v>
       </c>
       <c r="K222" s="3" t="inlineStr">
         <is>
-          <t>fenetre_de_reforme, communs, limites_planetaires, regle_contre_discretion, bareme, referentiel_de_change</t>
+          <t>bareme, seuil_d_activation, externalisation, additionnalite, contrepartie_comptable</t>
         </is>
       </c>
       <c r="L222" s="3" t="inlineStr">
         <is>
-          <t>L1.C18, L7.C12, L7.C13, L11.C15, L11.C25, L20.C01, L20.C03, L20.C06, L20.C07, L20.C08, L20.C12, L20.C13, L20.C16, L20.C17, L20.C19, L20.C20, L20.C21, L20.C23</t>
+          <t>L1.C27, L7.C17, L11.C21, L11.C24, L11.C25, L20.C01, L20.C18, L20.C19, L20.C22</t>
         </is>
       </c>
       <c r="M222" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-20/c22-ce-que-le-droit-devrait-devenir.md</t>
+          <t>corpus/livre-20/c20-l-ajustement-aux-frontieres-comme-precedent.md</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" s="2" t="inlineStr">
         <is>
+          <t>L20.C21</t>
+        </is>
+      </c>
+      <c r="B223" s="3" t="inlineStr">
+        <is>
+          <t>L20</t>
+        </is>
+      </c>
+      <c r="C223" s="3" t="inlineStr">
+        <is>
+          <t>La transparence et sa limite juridictionnelle</t>
+        </is>
+      </c>
+      <c r="D223" s="3" t="inlineStr">
+        <is>
+          <t>brouillon</t>
+        </is>
+      </c>
+      <c r="E223" s="3" t="inlineStr">
+        <is>
+          <t>preparatoire</t>
+        </is>
+      </c>
+      <c r="F223" s="3" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="G223" s="3" t="inlineStr">
+        <is>
+          <t>conception</t>
+        </is>
+      </c>
+      <c r="H223" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="I223" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="J223" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="K223" s="3" t="inlineStr">
+        <is>
+          <t>robustesse, contrepartie_comptable, bareme, monnaie_comme_registre</t>
+        </is>
+      </c>
+      <c r="L223" s="3" t="inlineStr">
+        <is>
+          <t>L7.C18, L11.C21, L11.C24, L11.C25, L20.C01, L20.C11, L20.C14, L20.C20, L20.C22</t>
+        </is>
+      </c>
+      <c r="M223" s="3" t="inlineStr">
+        <is>
+          <t>corpus/livre-20/c21-la-transparence-et-sa-limite-juridictionnelle.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" s="2" t="inlineStr">
+        <is>
+          <t>L20.C22</t>
+        </is>
+      </c>
+      <c r="B224" s="3" t="inlineStr">
+        <is>
+          <t>L20</t>
+        </is>
+      </c>
+      <c r="C224" s="3" t="inlineStr">
+        <is>
+          <t>Ce que le droit devrait devenir</t>
+        </is>
+      </c>
+      <c r="D224" s="3" t="inlineStr">
+        <is>
+          <t>brouillon</t>
+        </is>
+      </c>
+      <c r="E224" s="3" t="inlineStr">
+        <is>
+          <t>preparatoire</t>
+        </is>
+      </c>
+      <c r="F224" s="3" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="G224" s="3" t="inlineStr">
+        <is>
+          <t>conception</t>
+        </is>
+      </c>
+      <c r="H224" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="I224" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="J224" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="K224" s="3" t="inlineStr">
+        <is>
+          <t>fenetre_de_reforme, communs, limites_planetaires, regle_contre_discretion, bareme, referentiel_de_change</t>
+        </is>
+      </c>
+      <c r="L224" s="3" t="inlineStr">
+        <is>
+          <t>L1.C18, L7.C12, L7.C13, L11.C15, L11.C25, L20.C01, L20.C03, L20.C06, L20.C07, L20.C08, L20.C12, L20.C13, L20.C16, L20.C17, L20.C19, L20.C20, L20.C21, L20.C23</t>
+        </is>
+      </c>
+      <c r="M224" s="3" t="inlineStr">
+        <is>
+          <t>corpus/livre-20/c22-ce-que-le-droit-devrait-devenir.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" s="2" t="inlineStr">
+        <is>
           <t>L20.C23</t>
         </is>
       </c>
-      <c r="B223" s="3" t="inlineStr">
+      <c r="B225" s="3" t="inlineStr">
         <is>
           <t>L20</t>
         </is>
       </c>
-      <c r="C223" s="3" t="inlineStr">
+      <c r="C225" s="3" t="inlineStr">
         <is>
           <t>La portée du livre</t>
         </is>
       </c>
-      <c r="D223" s="3" t="inlineStr">
-        <is>
-          <t>brouillon</t>
-        </is>
-      </c>
-      <c r="E223" s="3" t="inlineStr">
-        <is>
-          <t>preparatoire</t>
-        </is>
-      </c>
-      <c r="F223" s="3" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="G223" s="3" t="inlineStr">
+      <c r="D225" s="3" t="inlineStr">
+        <is>
+          <t>brouillon</t>
+        </is>
+      </c>
+      <c r="E225" s="3" t="inlineStr">
+        <is>
+          <t>preparatoire</t>
+        </is>
+      </c>
+      <c r="F225" s="3" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="G225" s="3" t="inlineStr">
         <is>
           <t>conception</t>
         </is>
       </c>
-      <c r="H223" s="3" t="inlineStr">
+      <c r="H225" s="3" t="inlineStr">
         <is>
           <t>2026-09-06</t>
         </is>
       </c>
-      <c r="I223" s="3" t="n">
+      <c r="I225" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="J223" s="3" t="n">
+      <c r="J225" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="K223" s="3" t="inlineStr">
+      <c r="K225" s="3" t="inlineStr">
         <is>
           <t>fenetre_de_reforme, communs, limites_planetaires, creation_monetaire, robustesse</t>
         </is>
       </c>
-      <c r="L223" s="3" t="inlineStr">
+      <c r="L225" s="3" t="inlineStr">
         <is>
           <t>L1.C18, L1.C27, L7.C05, L7.C10, L7.C12, L7.C13, L11.C15, L11.C24, L11.C25, L20.C01, L20.C02, L20.C03, L20.C06, L20.C07, L20.C08, L20.C11, L20.C12, L20.C13, L20.C16, L20.C17, L20.C19, L20.C20, L20.C21, L20.C22</t>
         </is>
       </c>
-      <c r="M223" s="3" t="inlineStr">
+      <c r="M225" s="3" t="inlineStr">
         <is>
           <t>corpus/livre-20/c23-la-portee-du-livre.md</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:M223"/>
+  <autoFilter ref="A1:M225"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -15397,7 +15523,7 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>222</v>
+        <v>224</v>
       </c>
     </row>
     <row r="7">
@@ -15407,7 +15533,7 @@
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>213</v>
+        <v>215</v>
       </c>
     </row>
     <row r="8">
@@ -15427,7 +15553,7 @@
         </is>
       </c>
       <c r="B9" s="3" t="n">
-        <v>1127</v>
+        <v>1134</v>
       </c>
     </row>
     <row r="10">
@@ -15437,7 +15563,7 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>936</v>
+        <v>942</v>
       </c>
     </row>
     <row r="11">
@@ -15519,7 +15645,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C251"/>
+  <dimension ref="A1:C253"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -18448,7 +18574,7 @@
       </c>
       <c r="C173" s="6" t="inlineStr">
         <is>
-          <t>en-cours — 3 chapitre(s)</t>
+          <t>en-cours — 5 chapitre(s)</t>
         </is>
       </c>
     </row>
@@ -18504,31 +18630,31 @@
       </c>
     </row>
     <row r="177">
-      <c r="A177" s="6" t="inlineStr">
-        <is>
-          <t>L11</t>
-        </is>
-      </c>
-      <c r="B177" s="6" t="inlineStr">
-        <is>
-          <t>Ingénierie des barèmes : reflux, qualification, périmètre et pondérations</t>
-        </is>
-      </c>
-      <c r="C177" s="6" t="inlineStr">
-        <is>
-          <t>defrichage — 29 chapitre(s)</t>
+      <c r="A177" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    L10.C04</t>
+        </is>
+      </c>
+      <c r="B177" s="3" t="inlineStr">
+        <is>
+          <t>Qui la prohibition vise, et où le chapitre précédent avait trop dit</t>
+        </is>
+      </c>
+      <c r="C177" s="3" t="inlineStr">
+        <is>
+          <t>brouillon</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L11.C01</t>
+          <t xml:space="preserve">    L10.C05</t>
         </is>
       </c>
       <c r="B178" s="3" t="inlineStr">
         <is>
-          <t>Reflux ou destruction — la bifurcation</t>
+          <t>La définition-balai, et ce qu'elle emporte</t>
         </is>
       </c>
       <c r="C178" s="3" t="inlineStr">
@@ -18538,31 +18664,31 @@
       </c>
     </row>
     <row r="179">
-      <c r="A179" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    L11.C02</t>
-        </is>
-      </c>
-      <c r="B179" s="3" t="inlineStr">
-        <is>
-          <t>Le trajet complet de la valeur</t>
-        </is>
-      </c>
-      <c r="C179" s="3" t="inlineStr">
-        <is>
-          <t>brouillon</t>
+      <c r="A179" s="6" t="inlineStr">
+        <is>
+          <t>L11</t>
+        </is>
+      </c>
+      <c r="B179" s="6" t="inlineStr">
+        <is>
+          <t>Ingénierie des barèmes : reflux, qualification, périmètre et pondérations</t>
+        </is>
+      </c>
+      <c r="C179" s="6" t="inlineStr">
+        <is>
+          <t>defrichage — 29 chapitre(s)</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L11.C03</t>
+          <t xml:space="preserve">    L11.C01</t>
         </is>
       </c>
       <c r="B180" s="3" t="inlineStr">
         <is>
-          <t>Le compte des objectifs et des instruments</t>
+          <t>Reflux ou destruction — la bifurcation</t>
         </is>
       </c>
       <c r="C180" s="3" t="inlineStr">
@@ -18574,12 +18700,12 @@
     <row r="181">
       <c r="A181" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L11.C04</t>
+          <t xml:space="preserve">    L11.C02</t>
         </is>
       </c>
       <c r="B181" s="3" t="inlineStr">
         <is>
-          <t>Les instruments du reflux sous parité fixe</t>
+          <t>Le trajet complet de la valeur</t>
         </is>
       </c>
       <c r="C181" s="3" t="inlineStr">
@@ -18591,12 +18717,12 @@
     <row r="182">
       <c r="A182" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L11.C05</t>
+          <t xml:space="preserve">    L11.C03</t>
         </is>
       </c>
       <c r="B182" s="3" t="inlineStr">
         <is>
-          <t>L'assiette du reflux transactionnel</t>
+          <t>Le compte des objectifs et des instruments</t>
         </is>
       </c>
       <c r="C182" s="3" t="inlineStr">
@@ -18608,12 +18734,12 @@
     <row r="183">
       <c r="A183" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L11.C06</t>
+          <t xml:space="preserve">    L11.C04</t>
         </is>
       </c>
       <c r="B183" s="3" t="inlineStr">
         <is>
-          <t>Le barème par défaut</t>
+          <t>Les instruments du reflux sous parité fixe</t>
         </is>
       </c>
       <c r="C183" s="3" t="inlineStr">
@@ -18625,12 +18751,12 @@
     <row r="184">
       <c r="A184" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L11.C07</t>
+          <t xml:space="preserve">    L11.C05</t>
         </is>
       </c>
       <c r="B184" s="3" t="inlineStr">
         <is>
-          <t>Le demurrage et son nœud de prélèvement</t>
+          <t>L'assiette du reflux transactionnel</t>
         </is>
       </c>
       <c r="C184" s="3" t="inlineStr">
@@ -18642,12 +18768,12 @@
     <row r="185">
       <c r="A185" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L11.C08</t>
+          <t xml:space="preserve">    L11.C06</t>
         </is>
       </c>
       <c r="B185" s="3" t="inlineStr">
         <is>
-          <t>Les dérogations</t>
+          <t>Le barème par défaut</t>
         </is>
       </c>
       <c r="C185" s="3" t="inlineStr">
@@ -18659,12 +18785,12 @@
     <row r="186">
       <c r="A186" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L11.C09</t>
+          <t xml:space="preserve">    L11.C07</t>
         </is>
       </c>
       <c r="B186" s="3" t="inlineStr">
         <is>
-          <t>L'incidence — qui paie le reflux</t>
+          <t>Le demurrage et son nœud de prélèvement</t>
         </is>
       </c>
       <c r="C186" s="3" t="inlineStr">
@@ -18676,12 +18802,12 @@
     <row r="187">
       <c r="A187" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L11.C10</t>
+          <t xml:space="preserve">    L11.C08</t>
         </is>
       </c>
       <c r="B187" s="3" t="inlineStr">
         <is>
-          <t>La trajectoire de mise en place</t>
+          <t>Les dérogations</t>
         </is>
       </c>
       <c r="C187" s="3" t="inlineStr">
@@ -18693,12 +18819,12 @@
     <row r="188">
       <c r="A188" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L11.C11</t>
+          <t xml:space="preserve">    L11.C09</t>
         </is>
       </c>
       <c r="B188" s="3" t="inlineStr">
         <is>
-          <t>Qui arrête le barème</t>
+          <t>L'incidence — qui paie le reflux</t>
         </is>
       </c>
       <c r="C188" s="3" t="inlineStr">
@@ -18710,12 +18836,12 @@
     <row r="189">
       <c r="A189" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L11.C12</t>
+          <t xml:space="preserve">    L11.C10</t>
         </is>
       </c>
       <c r="B189" s="3" t="inlineStr">
         <is>
-          <t>La directive</t>
+          <t>La trajectoire de mise en place</t>
         </is>
       </c>
       <c r="C189" s="3" t="inlineStr">
@@ -18727,12 +18853,12 @@
     <row r="190">
       <c r="A190" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L11.C13</t>
+          <t xml:space="preserve">    L11.C11</t>
         </is>
       </c>
       <c r="B190" s="3" t="inlineStr">
         <is>
-          <t>Le barème de qualification</t>
+          <t>Qui arrête le barème</t>
         </is>
       </c>
       <c r="C190" s="3" t="inlineStr">
@@ -18744,12 +18870,12 @@
     <row r="191">
       <c r="A191" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L11.C14</t>
+          <t xml:space="preserve">    L11.C12</t>
         </is>
       </c>
       <c r="B191" s="3" t="inlineStr">
         <is>
-          <t>Le tableau de bord, ou les données de la directive</t>
+          <t>La directive</t>
         </is>
       </c>
       <c r="C191" s="3" t="inlineStr">
@@ -18761,12 +18887,12 @@
     <row r="192">
       <c r="A192" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L11.C15</t>
+          <t xml:space="preserve">    L11.C13</t>
         </is>
       </c>
       <c r="B192" s="3" t="inlineStr">
         <is>
-          <t>Les parités du référentiel de change</t>
+          <t>Le barème de qualification</t>
         </is>
       </c>
       <c r="C192" s="3" t="inlineStr">
@@ -18778,12 +18904,12 @@
     <row r="193">
       <c r="A193" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L11.C16</t>
+          <t xml:space="preserve">    L11.C14</t>
         </is>
       </c>
       <c r="B193" s="3" t="inlineStr">
         <is>
-          <t>La valorisation des communs</t>
+          <t>Le tableau de bord, ou les données de la directive</t>
         </is>
       </c>
       <c r="C193" s="3" t="inlineStr">
@@ -18795,12 +18921,12 @@
     <row r="194">
       <c r="A194" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L11.C17</t>
+          <t xml:space="preserve">    L11.C15</t>
         </is>
       </c>
       <c r="B194" s="3" t="inlineStr">
         <is>
-          <t>La cohérence des cinq barèmes</t>
+          <t>Les parités du référentiel de change</t>
         </is>
       </c>
       <c r="C194" s="3" t="inlineStr">
@@ -18812,12 +18938,12 @@
     <row r="195">
       <c r="A195" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L11.C18</t>
+          <t xml:space="preserve">    L11.C16</t>
         </is>
       </c>
       <c r="B195" s="3" t="inlineStr">
         <is>
-          <t>Le seuil d'exemption</t>
+          <t>La valorisation des communs</t>
         </is>
       </c>
       <c r="C195" s="3" t="inlineStr">
@@ -18829,12 +18955,12 @@
     <row r="196">
       <c r="A196" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L11.C19</t>
+          <t xml:space="preserve">    L11.C17</t>
         </is>
       </c>
       <c r="B196" s="3" t="inlineStr">
         <is>
-          <t>Le recours</t>
+          <t>La cohérence des cinq barèmes</t>
         </is>
       </c>
       <c r="C196" s="3" t="inlineStr">
@@ -18846,12 +18972,12 @@
     <row r="197">
       <c r="A197" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L11.C20</t>
+          <t xml:space="preserve">    L11.C18</t>
         </is>
       </c>
       <c r="B197" s="3" t="inlineStr">
         <is>
-          <t>L'amendement de la directive</t>
+          <t>Le seuil d'exemption</t>
         </is>
       </c>
       <c r="C197" s="3" t="inlineStr">
@@ -18863,12 +18989,12 @@
     <row r="198">
       <c r="A198" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L11.C21</t>
+          <t xml:space="preserve">    L11.C19</t>
         </is>
       </c>
       <c r="B198" s="3" t="inlineStr">
         <is>
-          <t>La perception</t>
+          <t>Le recours</t>
         </is>
       </c>
       <c r="C198" s="3" t="inlineStr">
@@ -18880,12 +19006,12 @@
     <row r="199">
       <c r="A199" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L11.C22</t>
+          <t xml:space="preserve">    L11.C20</t>
         </is>
       </c>
       <c r="B199" s="3" t="inlineStr">
         <is>
-          <t>Les délais</t>
+          <t>L'amendement de la directive</t>
         </is>
       </c>
       <c r="C199" s="3" t="inlineStr">
@@ -18897,12 +19023,12 @@
     <row r="200">
       <c r="A200" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L11.C23</t>
+          <t xml:space="preserve">    L11.C21</t>
         </is>
       </c>
       <c r="B200" s="3" t="inlineStr">
         <is>
-          <t>La contracyclicité</t>
+          <t>La perception</t>
         </is>
       </c>
       <c r="C200" s="3" t="inlineStr">
@@ -18914,12 +19040,12 @@
     <row r="201">
       <c r="A201" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L11.C24</t>
+          <t xml:space="preserve">    L11.C22</t>
         </is>
       </c>
       <c r="B201" s="3" t="inlineStr">
         <is>
-          <t>Le barème aux frontières</t>
+          <t>Les délais</t>
         </is>
       </c>
       <c r="C201" s="3" t="inlineStr">
@@ -18931,12 +19057,12 @@
     <row r="202">
       <c r="A202" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L11.C25</t>
+          <t xml:space="preserve">    L11.C23</t>
         </is>
       </c>
       <c r="B202" s="3" t="inlineStr">
         <is>
-          <t>Le contrôle</t>
+          <t>La contracyclicité</t>
         </is>
       </c>
       <c r="C202" s="3" t="inlineStr">
@@ -18948,12 +19074,12 @@
     <row r="203">
       <c r="A203" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L11.C26</t>
+          <t xml:space="preserve">    L11.C24</t>
         </is>
       </c>
       <c r="B203" s="3" t="inlineStr">
         <is>
-          <t>La portée du Livre 11</t>
+          <t>Le barème aux frontières</t>
         </is>
       </c>
       <c r="C203" s="3" t="inlineStr">
@@ -18965,12 +19091,12 @@
     <row r="204">
       <c r="A204" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L11.C27</t>
+          <t xml:space="preserve">    L11.C25</t>
         </is>
       </c>
       <c r="B204" s="3" t="inlineStr">
         <is>
-          <t>L'assiette de la fonte est celle de la TVA</t>
+          <t>Le contrôle</t>
         </is>
       </c>
       <c r="C204" s="3" t="inlineStr">
@@ -18982,12 +19108,12 @@
     <row r="205">
       <c r="A205" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L11.C28</t>
+          <t xml:space="preserve">    L11.C26</t>
         </is>
       </c>
       <c r="B205" s="3" t="inlineStr">
         <is>
-          <t>La fonte sur les acquisitions d'actifs, éprouvée</t>
+          <t>La portée du Livre 11</t>
         </is>
       </c>
       <c r="C205" s="3" t="inlineStr">
@@ -18999,55 +19125,63 @@
     <row r="206">
       <c r="A206" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">    L11.C27</t>
+        </is>
+      </c>
+      <c r="B206" s="3" t="inlineStr">
+        <is>
+          <t>L'assiette de la fonte est celle de la TVA</t>
+        </is>
+      </c>
+      <c r="C206" s="3" t="inlineStr">
+        <is>
+          <t>brouillon</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    L11.C28</t>
+        </is>
+      </c>
+      <c r="B207" s="3" t="inlineStr">
+        <is>
+          <t>La fonte sur les acquisitions d'actifs, éprouvée</t>
+        </is>
+      </c>
+      <c r="C207" s="3" t="inlineStr">
+        <is>
+          <t>brouillon</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">    L11.C29</t>
         </is>
       </c>
-      <c r="B206" s="3" t="inlineStr">
+      <c r="B208" s="3" t="inlineStr">
         <is>
           <t>La structure des sanctions</t>
         </is>
       </c>
-      <c r="C206" s="3" t="inlineStr">
-        <is>
-          <t>brouillon</t>
-        </is>
-      </c>
-    </row>
-    <row r="207">
-      <c r="A207" s="6" t="inlineStr">
-        <is>
-          <t>L12</t>
-        </is>
-      </c>
-      <c r="B207" s="6" t="inlineStr">
-        <is>
-          <t>Comment réaliser les ODD avec NEMO IMS ?</t>
-        </is>
-      </c>
-      <c r="C207" s="6" t="inlineStr">
-        <is>
-          <t>candidat — 0 chapitre(s)</t>
-        </is>
-      </c>
-    </row>
-    <row r="208">
-      <c r="A208" s="7" t="inlineStr"/>
-      <c r="B208" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    (aucun chapitre écrit)</t>
-        </is>
-      </c>
-      <c r="C208" s="7" t="inlineStr"/>
+      <c r="C208" s="3" t="inlineStr">
+        <is>
+          <t>brouillon</t>
+        </is>
+      </c>
     </row>
     <row r="209">
       <c r="A209" s="6" t="inlineStr">
         <is>
-          <t>L13</t>
+          <t>L12</t>
         </is>
       </c>
       <c r="B209" s="6" t="inlineStr">
         <is>
-          <t>Méthodes, données, scénarios et simulateur NEMO IMS</t>
+          <t>Comment réaliser les ODD avec NEMO IMS ?</t>
         </is>
       </c>
       <c r="C209" s="6" t="inlineStr">
@@ -19068,12 +19202,12 @@
     <row r="211">
       <c r="A211" s="6" t="inlineStr">
         <is>
-          <t>L14</t>
+          <t>L13</t>
         </is>
       </c>
       <c r="B211" s="6" t="inlineStr">
         <is>
-          <t>Gouverner la preuve : méthodes, vérification et traçabilité</t>
+          <t>Méthodes, données, scénarios et simulateur NEMO IMS</t>
         </is>
       </c>
       <c r="C211" s="6" t="inlineStr">
@@ -19094,17 +19228,17 @@
     <row r="213">
       <c r="A213" s="6" t="inlineStr">
         <is>
-          <t>L15</t>
+          <t>L14</t>
         </is>
       </c>
       <c r="B213" s="6" t="inlineStr">
         <is>
-          <t>Fraudes, corruptions et architectures de la triche</t>
+          <t>Gouverner la preuve : méthodes, vérification et traçabilité</t>
         </is>
       </c>
       <c r="C213" s="6" t="inlineStr">
         <is>
-          <t>exploratoire — 0 chapitre(s)</t>
+          <t>candidat — 0 chapitre(s)</t>
         </is>
       </c>
     </row>
@@ -19120,17 +19254,17 @@
     <row r="215">
       <c r="A215" s="6" t="inlineStr">
         <is>
-          <t>L16</t>
+          <t>L15</t>
         </is>
       </c>
       <c r="B215" s="6" t="inlineStr">
         <is>
-          <t>Typologie comparée des systèmes et alternatives monétaires</t>
+          <t>Fraudes, corruptions et architectures de la triche</t>
         </is>
       </c>
       <c r="C215" s="6" t="inlineStr">
         <is>
-          <t>candidat — 0 chapitre(s)</t>
+          <t>exploratoire — 0 chapitre(s)</t>
         </is>
       </c>
     </row>
@@ -19146,12 +19280,12 @@
     <row r="217">
       <c r="A217" s="6" t="inlineStr">
         <is>
-          <t>L17</t>
+          <t>L16</t>
         </is>
       </c>
       <c r="B217" s="6" t="inlineStr">
         <is>
-          <t>Après la croissance : décroissance, post-croissance et prospérité sans croissance</t>
+          <t>Typologie comparée des systèmes et alternatives monétaires</t>
         </is>
       </c>
       <c r="C217" s="6" t="inlineStr">
@@ -19172,63 +19306,55 @@
     <row r="219">
       <c r="A219" s="6" t="inlineStr">
         <is>
+          <t>L17</t>
+        </is>
+      </c>
+      <c r="B219" s="6" t="inlineStr">
+        <is>
+          <t>Après la croissance : décroissance, post-croissance et prospérité sans croissance</t>
+        </is>
+      </c>
+      <c r="C219" s="6" t="inlineStr">
+        <is>
+          <t>candidat — 0 chapitre(s)</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" s="7" t="inlineStr"/>
+      <c r="B220" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    (aucun chapitre écrit)</t>
+        </is>
+      </c>
+      <c r="C220" s="7" t="inlineStr"/>
+    </row>
+    <row r="221">
+      <c r="A221" s="6" t="inlineStr">
+        <is>
           <t>L18</t>
         </is>
       </c>
-      <c r="B219" s="6" t="inlineStr">
+      <c r="B221" s="6" t="inlineStr">
         <is>
           <t>Comptabilités écologiques, sociales et biophysiques</t>
         </is>
       </c>
-      <c r="C219" s="6" t="inlineStr">
+      <c r="C221" s="6" t="inlineStr">
         <is>
           <t>en-cours — 8 chapitre(s)</t>
-        </is>
-      </c>
-    </row>
-    <row r="220">
-      <c r="A220" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    L18.C01</t>
-        </is>
-      </c>
-      <c r="B220" s="3" t="inlineStr">
-        <is>
-          <t>Ce que ce livre doit établir, et le repli n'est pas l'annexe</t>
-        </is>
-      </c>
-      <c r="C220" s="3" t="inlineStr">
-        <is>
-          <t>brouillon</t>
-        </is>
-      </c>
-    </row>
-    <row r="221">
-      <c r="A221" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    L18.C02</t>
-        </is>
-      </c>
-      <c r="B221" s="3" t="inlineStr">
-        <is>
-          <t>La métrologie existe, et ce qu'elle enregistre est l'ordre en place</t>
-        </is>
-      </c>
-      <c r="C221" s="3" t="inlineStr">
-        <is>
-          <t>brouillon</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L18.C03</t>
+          <t xml:space="preserve">    L18.C01</t>
         </is>
       </c>
       <c r="B222" s="3" t="inlineStr">
         <is>
-          <t>L'échelle de repli, et qui l'a arrêtée</t>
+          <t>Ce que ce livre doit établir, et le repli n'est pas l'annexe</t>
         </is>
       </c>
       <c r="C222" s="3" t="inlineStr">
@@ -19240,12 +19366,12 @@
     <row r="223">
       <c r="A223" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L18.C04</t>
+          <t xml:space="preserve">    L18.C02</t>
         </is>
       </c>
       <c r="B223" s="3" t="inlineStr">
         <is>
-          <t>Les grandeurs physiques, et l'endroit où elles frappent le dispositif</t>
+          <t>La métrologie existe, et ce qu'elle enregistre est l'ordre en place</t>
         </is>
       </c>
       <c r="C223" s="3" t="inlineStr">
@@ -19257,12 +19383,12 @@
     <row r="224">
       <c r="A224" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L18.C05</t>
+          <t xml:space="preserve">    L18.C03</t>
         </is>
       </c>
       <c r="B224" s="3" t="inlineStr">
         <is>
-          <t>Le commun est ce que la norme exclut, et la symétrie de l'écriture</t>
+          <t>L'échelle de repli, et qui l'a arrêtée</t>
         </is>
       </c>
       <c r="C224" s="3" t="inlineStr">
@@ -19274,12 +19400,12 @@
     <row r="225">
       <c r="A225" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L18.C06</t>
+          <t xml:space="preserve">    L18.C04</t>
         </is>
       </c>
       <c r="B225" s="3" t="inlineStr">
         <is>
-          <t>Portée de la tranche, et une neuvième condition proposée</t>
+          <t>Les grandeurs physiques, et l'endroit où elles frappent le dispositif</t>
         </is>
       </c>
       <c r="C225" s="3" t="inlineStr">
@@ -19291,12 +19417,12 @@
     <row r="226">
       <c r="A226" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L18.C07</t>
+          <t xml:space="preserve">    L18.C05</t>
         </is>
       </c>
       <c r="B226" s="3" t="inlineStr">
         <is>
-          <t>CARE/TDL répare deux objections, et en crée une plus grave</t>
+          <t>Le commun est ce que la norme exclut, et la symétrie de l'écriture</t>
         </is>
       </c>
       <c r="C226" s="3" t="inlineStr">
@@ -19308,12 +19434,12 @@
     <row r="227">
       <c r="A227" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L18.C08</t>
+          <t xml:space="preserve">    L18.C06</t>
         </is>
       </c>
       <c r="B227" s="3" t="inlineStr">
         <is>
-          <t>Le modèle au périmètre du dispositif, et F9 révisée</t>
+          <t>Portée de la tranche, et une neuvième condition proposée</t>
         </is>
       </c>
       <c r="C227" s="3" t="inlineStr">
@@ -19323,31 +19449,31 @@
       </c>
     </row>
     <row r="228">
-      <c r="A228" s="6" t="inlineStr">
-        <is>
-          <t>L20</t>
-        </is>
-      </c>
-      <c r="B228" s="6" t="inlineStr">
-        <is>
-          <t>Droit international public, droit monétaire et commercial de la réforme</t>
-        </is>
-      </c>
-      <c r="C228" s="6" t="inlineStr">
-        <is>
-          <t>en-cours — 23 chapitre(s)</t>
+      <c r="A228" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    L18.C07</t>
+        </is>
+      </c>
+      <c r="B228" s="3" t="inlineStr">
+        <is>
+          <t>CARE/TDL répare deux objections, et en crée une plus grave</t>
+        </is>
+      </c>
+      <c r="C228" s="3" t="inlineStr">
+        <is>
+          <t>brouillon</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L20.C01</t>
+          <t xml:space="preserve">    L18.C08</t>
         </is>
       </c>
       <c r="B229" s="3" t="inlineStr">
         <is>
-          <t>Ce que ce livre doit établir</t>
+          <t>Le modèle au périmètre du dispositif, et F9 révisée</t>
         </is>
       </c>
       <c r="C229" s="3" t="inlineStr">
@@ -19357,31 +19483,31 @@
       </c>
     </row>
     <row r="230">
-      <c r="A230" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    L20.C02</t>
-        </is>
-      </c>
-      <c r="B230" s="3" t="inlineStr">
-        <is>
-          <t>L'interdiction du financement monétaire</t>
-        </is>
-      </c>
-      <c r="C230" s="3" t="inlineStr">
-        <is>
-          <t>brouillon</t>
+      <c r="A230" s="6" t="inlineStr">
+        <is>
+          <t>L20</t>
+        </is>
+      </c>
+      <c r="B230" s="6" t="inlineStr">
+        <is>
+          <t>Droit international public, droit monétaire et commercial de la réforme</t>
+        </is>
+      </c>
+      <c r="C230" s="6" t="inlineStr">
+        <is>
+          <t>en-cours — 23 chapitre(s)</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L20.C03</t>
+          <t xml:space="preserve">    L20.C01</t>
         </is>
       </c>
       <c r="B231" s="3" t="inlineStr">
         <is>
-          <t>L'objectif principal et ce qu'il exclut</t>
+          <t>Ce que ce livre doit établir</t>
         </is>
       </c>
       <c r="C231" s="3" t="inlineStr">
@@ -19393,12 +19519,12 @@
     <row r="232">
       <c r="A232" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L20.C04</t>
+          <t xml:space="preserve">    L20.C02</t>
         </is>
       </c>
       <c r="B232" s="3" t="inlineStr">
         <is>
-          <t>L'indépendance, et à l'égard de qui</t>
+          <t>L'interdiction du financement monétaire</t>
         </is>
       </c>
       <c r="C232" s="3" t="inlineStr">
@@ -19410,12 +19536,12 @@
     <row r="233">
       <c r="A233" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L20.C05</t>
+          <t xml:space="preserve">    L20.C03</t>
         </is>
       </c>
       <c r="B233" s="3" t="inlineStr">
         <is>
-          <t>Le monopole d'émission et le cours légal</t>
+          <t>L'objectif principal et ce qu'il exclut</t>
         </is>
       </c>
       <c r="C233" s="3" t="inlineStr">
@@ -19427,12 +19553,12 @@
     <row r="234">
       <c r="A234" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L20.C06</t>
+          <t xml:space="preserve">    L20.C04</t>
         </is>
       </c>
       <c r="B234" s="3" t="inlineStr">
         <is>
-          <t>Les voies de révision et leur coût</t>
+          <t>L'indépendance, et à l'égard de qui</t>
         </is>
       </c>
       <c r="C234" s="3" t="inlineStr">
@@ -19444,12 +19570,12 @@
     <row r="235">
       <c r="A235" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L20.C07</t>
+          <t xml:space="preserve">    L20.C05</t>
         </is>
       </c>
       <c r="B235" s="3" t="inlineStr">
         <is>
-          <t>L'accord monétaire international</t>
+          <t>Le monopole d'émission et le cours légal</t>
         </is>
       </c>
       <c r="C235" s="3" t="inlineStr">
@@ -19461,12 +19587,12 @@
     <row r="236">
       <c r="A236" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L20.C08</t>
+          <t xml:space="preserve">    L20.C06</t>
         </is>
       </c>
       <c r="B236" s="3" t="inlineStr">
         <is>
-          <t>La parité inscrite dans le traité</t>
+          <t>Les voies de révision et leur coût</t>
         </is>
       </c>
       <c r="C236" s="3" t="inlineStr">
@@ -19478,12 +19604,12 @@
     <row r="237">
       <c r="A237" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L20.C09</t>
+          <t xml:space="preserve">    L20.C07</t>
         </is>
       </c>
       <c r="B237" s="3" t="inlineStr">
         <is>
-          <t>L'amendement des statuts du Fonds</t>
+          <t>L'accord monétaire international</t>
         </is>
       </c>
       <c r="C237" s="3" t="inlineStr">
@@ -19495,12 +19621,12 @@
     <row r="238">
       <c r="A238" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L20.C10</t>
+          <t xml:space="preserve">    L20.C08</t>
         </is>
       </c>
       <c r="B238" s="3" t="inlineStr">
         <is>
-          <t>Le vote pondéré et les voix de base</t>
+          <t>La parité inscrite dans le traité</t>
         </is>
       </c>
       <c r="C238" s="3" t="inlineStr">
@@ -19512,12 +19638,12 @@
     <row r="239">
       <c r="A239" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L20.C11</t>
+          <t xml:space="preserve">    L20.C09</t>
         </is>
       </c>
       <c r="B239" s="3" t="inlineStr">
         <is>
-          <t>La personnalité juridique et les immunités</t>
+          <t>L'amendement des statuts du Fonds</t>
         </is>
       </c>
       <c r="C239" s="3" t="inlineStr">
@@ -19529,12 +19655,12 @@
     <row r="240">
       <c r="A240" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L20.C12</t>
+          <t xml:space="preserve">    L20.C10</t>
         </is>
       </c>
       <c r="B240" s="3" t="inlineStr">
         <is>
-          <t>Les pouvoirs non délégables</t>
+          <t>Le vote pondéré et les voix de base</t>
         </is>
       </c>
       <c r="C240" s="3" t="inlineStr">
@@ -19546,12 +19672,12 @@
     <row r="241">
       <c r="A241" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L20.C13</t>
+          <t xml:space="preserve">    L20.C11</t>
         </is>
       </c>
       <c r="B241" s="3" t="inlineStr">
         <is>
-          <t>L'entrée en vigueur, l'adhésion et le retrait</t>
+          <t>La personnalité juridique et les immunités</t>
         </is>
       </c>
       <c r="C241" s="3" t="inlineStr">
@@ -19563,12 +19689,12 @@
     <row r="242">
       <c r="A242" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L20.C14</t>
+          <t xml:space="preserve">    L20.C12</t>
         </is>
       </c>
       <c r="B242" s="3" t="inlineStr">
         <is>
-          <t>Qui interprète le traité</t>
+          <t>Les pouvoirs non délégables</t>
         </is>
       </c>
       <c r="C242" s="3" t="inlineStr">
@@ -19580,12 +19706,12 @@
     <row r="243">
       <c r="A243" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L20.C15</t>
+          <t xml:space="preserve">    L20.C13</t>
         </is>
       </c>
       <c r="B243" s="3" t="inlineStr">
         <is>
-          <t>Le devoir international des agents</t>
+          <t>L'entrée en vigueur, l'adhésion et le retrait</t>
         </is>
       </c>
       <c r="C243" s="3" t="inlineStr">
@@ -19597,12 +19723,12 @@
     <row r="244">
       <c r="A244" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L20.C16</t>
+          <t xml:space="preserve">    L20.C14</t>
         </is>
       </c>
       <c r="B244" s="3" t="inlineStr">
         <is>
-          <t>Le patrimoine commun de l'humanité</t>
+          <t>Qui interprète le traité</t>
         </is>
       </c>
       <c r="C244" s="3" t="inlineStr">
@@ -19614,12 +19740,12 @@
     <row r="245">
       <c r="A245" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L20.C17</t>
+          <t xml:space="preserve">    L20.C15</t>
         </is>
       </c>
       <c r="B245" s="3" t="inlineStr">
         <is>
-          <t>La sanctuarisation, et elle existe</t>
+          <t>Le devoir international des agents</t>
         </is>
       </c>
       <c r="C245" s="3" t="inlineStr">
@@ -19631,12 +19757,12 @@
     <row r="246">
       <c r="A246" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L20.C18</t>
+          <t xml:space="preserve">    L20.C16</t>
         </is>
       </c>
       <c r="B246" s="3" t="inlineStr">
         <is>
-          <t>L'amendement et la dérogation dans l'ordre commercial</t>
+          <t>Le patrimoine commun de l'humanité</t>
         </is>
       </c>
       <c r="C246" s="3" t="inlineStr">
@@ -19648,12 +19774,12 @@
     <row r="247">
       <c r="A247" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L20.C19</t>
+          <t xml:space="preserve">    L20.C17</t>
         </is>
       </c>
       <c r="B247" s="3" t="inlineStr">
         <is>
-          <t>Le texte que la conformité invoque</t>
+          <t>La sanctuarisation, et elle existe</t>
         </is>
       </c>
       <c r="C247" s="3" t="inlineStr">
@@ -19665,12 +19791,12 @@
     <row r="248">
       <c r="A248" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L20.C20</t>
+          <t xml:space="preserve">    L20.C18</t>
         </is>
       </c>
       <c r="B248" s="3" t="inlineStr">
         <is>
-          <t>L'ajustement aux frontières comme précédent</t>
+          <t>L'amendement et la dérogation dans l'ordre commercial</t>
         </is>
       </c>
       <c r="C248" s="3" t="inlineStr">
@@ -19682,12 +19808,12 @@
     <row r="249">
       <c r="A249" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L20.C21</t>
+          <t xml:space="preserve">    L20.C19</t>
         </is>
       </c>
       <c r="B249" s="3" t="inlineStr">
         <is>
-          <t>La transparence et sa limite juridictionnelle</t>
+          <t>Le texte que la conformité invoque</t>
         </is>
       </c>
       <c r="C249" s="3" t="inlineStr">
@@ -19699,12 +19825,12 @@
     <row r="250">
       <c r="A250" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L20.C22</t>
+          <t xml:space="preserve">    L20.C20</t>
         </is>
       </c>
       <c r="B250" s="3" t="inlineStr">
         <is>
-          <t>Ce que le droit devrait devenir</t>
+          <t>L'ajustement aux frontières comme précédent</t>
         </is>
       </c>
       <c r="C250" s="3" t="inlineStr">
@@ -19716,15 +19842,49 @@
     <row r="251">
       <c r="A251" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">    L20.C21</t>
+        </is>
+      </c>
+      <c r="B251" s="3" t="inlineStr">
+        <is>
+          <t>La transparence et sa limite juridictionnelle</t>
+        </is>
+      </c>
+      <c r="C251" s="3" t="inlineStr">
+        <is>
+          <t>brouillon</t>
+        </is>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    L20.C22</t>
+        </is>
+      </c>
+      <c r="B252" s="3" t="inlineStr">
+        <is>
+          <t>Ce que le droit devrait devenir</t>
+        </is>
+      </c>
+      <c r="C252" s="3" t="inlineStr">
+        <is>
+          <t>brouillon</t>
+        </is>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">    L20.C23</t>
         </is>
       </c>
-      <c r="B251" s="3" t="inlineStr">
+      <c r="B253" s="3" t="inlineStr">
         <is>
           <t>La portée du livre</t>
         </is>
       </c>
-      <c r="C251" s="3" t="inlineStr">
+      <c r="C253" s="3" t="inlineStr">
         <is>
           <t>brouillon</t>
         </is>

--- a/plan-des-livres.xlsx
+++ b/plan-des-livres.xlsx
@@ -13,7 +13,7 @@
     <sheet name="Plan par livre" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Chapitres'!$A$1:$M$225</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Chapitres'!$A$1:$M$226</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -960,7 +960,7 @@
         </is>
       </c>
       <c r="F12" s="5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G12" s="5" t="inlineStr"/>
       <c r="H12" s="5" t="inlineStr">
@@ -1354,7 +1354,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M225"/>
+  <dimension ref="A1:M226"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -11666,17 +11666,17 @@
     <row r="166">
       <c r="A166" s="2" t="inlineStr">
         <is>
-          <t>L11.C01</t>
+          <t>L10.C06</t>
         </is>
       </c>
       <c r="B166" s="3" t="inlineStr">
         <is>
-          <t>L11</t>
+          <t>L10</t>
         </is>
       </c>
       <c r="C166" s="3" t="inlineStr">
         <is>
-          <t>Reflux ou destruction — la bifurcation</t>
+          <t>L'arbitrage A35, et ce qu'il déplace</t>
         </is>
       </c>
       <c r="D166" s="3" t="inlineStr">
@@ -11701,35 +11701,35 @@
       </c>
       <c r="H166" s="3" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="I166" s="3" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="J166" s="3" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="K166" s="3" t="inlineStr">
         <is>
-          <t>contrepartie_comptable, reflux_monetaire, creation_monetaire, reflux_transactionnel, monnaie_comme_registre</t>
+          <t>reflux_collectif, contrepartie_comptable, essentiel_insolvable, monnaie_fondante, demurrage, reflux_transactionnel, degeneratif</t>
         </is>
       </c>
       <c r="L166" s="3" t="inlineStr">
         <is>
-          <t>L1.C17, L1.C19, L1.C20, L1.C21, L1.C27, L1.C29</t>
+          <t>L1.C15, L1.C20, L1.C29, L10.C01, L10.C02, L10.C04, L10.C05, L11.C05, L11.C07, L11.C09, L18.C01, L18.C05, L20.C02</t>
         </is>
       </c>
       <c r="M166" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-11/c01-reflux-ou-destruction.md</t>
+          <t>corpus/livre-10/c06-l-arbitrage-a35-et-ce-qu-il-deplace.md</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" s="2" t="inlineStr">
         <is>
-          <t>L11.C02</t>
+          <t>L11.C01</t>
         </is>
       </c>
       <c r="B167" s="3" t="inlineStr">
@@ -11739,7 +11739,7 @@
       </c>
       <c r="C167" s="3" t="inlineStr">
         <is>
-          <t>Le trajet complet de la valeur</t>
+          <t>Reflux ou destruction — la bifurcation</t>
         </is>
       </c>
       <c r="D167" s="3" t="inlineStr">
@@ -11768,31 +11768,31 @@
         </is>
       </c>
       <c r="I167" s="3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J167" s="3" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K167" s="3" t="inlineStr">
         <is>
-          <t>contrepartie_comptable, reflux_collectif, reflux_transactionnel, demurrage, creation_monetaire</t>
+          <t>contrepartie_comptable, reflux_monetaire, creation_monetaire, reflux_transactionnel, monnaie_comme_registre</t>
         </is>
       </c>
       <c r="L167" s="3" t="inlineStr">
         <is>
-          <t>L1.C18, L1.C20, L1.C21, L1.C29, L11.C01</t>
+          <t>L1.C17, L1.C19, L1.C20, L1.C21, L1.C27, L1.C29</t>
         </is>
       </c>
       <c r="M167" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-11/c02-le-trajet-complet-de-la-valeur.md</t>
+          <t>corpus/livre-11/c01-reflux-ou-destruction.md</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" s="2" t="inlineStr">
         <is>
-          <t>L11.C03</t>
+          <t>L11.C02</t>
         </is>
       </c>
       <c r="B168" s="3" t="inlineStr">
@@ -11802,7 +11802,7 @@
       </c>
       <c r="C168" s="3" t="inlineStr">
         <is>
-          <t>Le compte des objectifs et des instruments</t>
+          <t>Le trajet complet de la valeur</t>
         </is>
       </c>
       <c r="D168" s="3" t="inlineStr">
@@ -11827,35 +11827,35 @@
       </c>
       <c r="H168" s="3" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="I168" s="3" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="J168" s="3" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K168" s="3" t="inlineStr">
         <is>
-          <t>affectation_des_instruments, bareme, effet_veblen, reflux_collectif, reflux_transactionnel, demurrage, degeneratif, qualification_regenerative</t>
+          <t>contrepartie_comptable, reflux_collectif, reflux_transactionnel, demurrage, creation_monetaire</t>
         </is>
       </c>
       <c r="L168" s="3" t="inlineStr">
         <is>
-          <t>L1.C18, L1.C20, L1.C21, L1.C26, L1.C28, L11.C01, L11.C02, L11.C04, L11.C05, L11.C06, L11.C07, L11.C09, L11.C10, L11.C11</t>
+          <t>L1.C18, L1.C20, L1.C21, L1.C29, L11.C01</t>
         </is>
       </c>
       <c r="M168" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-11/c03-le-compte-des-objectifs-et-des-instruments.md</t>
+          <t>corpus/livre-11/c02-le-trajet-complet-de-la-valeur.md</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" s="2" t="inlineStr">
         <is>
-          <t>L11.C04</t>
+          <t>L11.C03</t>
         </is>
       </c>
       <c r="B169" s="3" t="inlineStr">
@@ -11865,7 +11865,7 @@
       </c>
       <c r="C169" s="3" t="inlineStr">
         <is>
-          <t>Les instruments du reflux sous parité fixe</t>
+          <t>Le compte des objectifs et des instruments</t>
         </is>
       </c>
       <c r="D169" s="3" t="inlineStr">
@@ -11894,31 +11894,31 @@
         </is>
       </c>
       <c r="I169" s="3" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="J169" s="3" t="n">
         <v>5</v>
       </c>
       <c r="K169" s="3" t="inlineStr">
         <is>
-          <t>referentiel_de_change, demurrage, reflux_transactionnel, reflux_collectif, bareme, affectation_des_instruments, creation_monetaire</t>
+          <t>affectation_des_instruments, bareme, effet_veblen, reflux_collectif, reflux_transactionnel, demurrage, degeneratif, qualification_regenerative</t>
         </is>
       </c>
       <c r="L169" s="3" t="inlineStr">
         <is>
-          <t>L1.C19, L1.C21, L1.C24, L1.C26, L1.C27, L11.C01, L11.C02, L11.C03</t>
+          <t>L1.C18, L1.C20, L1.C21, L1.C26, L1.C28, L11.C01, L11.C02, L11.C04, L11.C05, L11.C06, L11.C07, L11.C09, L11.C10, L11.C11</t>
         </is>
       </c>
       <c r="M169" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-11/c04-les-instruments-du-reflux-sous-parite-fixe.md</t>
+          <t>corpus/livre-11/c03-le-compte-des-objectifs-et-des-instruments.md</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" s="2" t="inlineStr">
         <is>
-          <t>L11.C05</t>
+          <t>L11.C04</t>
         </is>
       </c>
       <c r="B170" s="3" t="inlineStr">
@@ -11928,7 +11928,7 @@
       </c>
       <c r="C170" s="3" t="inlineStr">
         <is>
-          <t>L'assiette du reflux transactionnel</t>
+          <t>Les instruments du reflux sous parité fixe</t>
         </is>
       </c>
       <c r="D170" s="3" t="inlineStr">
@@ -11953,35 +11953,35 @@
       </c>
       <c r="H170" s="3" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="I170" s="3" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="J170" s="3" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="K170" s="3" t="inlineStr">
         <is>
-          <t>reflux_transactionnel, bareme, degeneratif, reflux_collectif, robustesse, affectation_des_instruments</t>
+          <t>referentiel_de_change, demurrage, reflux_transactionnel, reflux_collectif, bareme, affectation_des_instruments, creation_monetaire</t>
         </is>
       </c>
       <c r="L170" s="3" t="inlineStr">
         <is>
-          <t>L1.C18, L1.C21, L1.C23, L11.C02, L11.C03, L11.C04</t>
+          <t>L1.C19, L1.C21, L1.C24, L1.C26, L1.C27, L11.C01, L11.C02, L11.C03</t>
         </is>
       </c>
       <c r="M170" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-11/c05-l-assiette-du-reflux-transactionnel.md</t>
+          <t>corpus/livre-11/c04-les-instruments-du-reflux-sous-parite-fixe.md</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" s="2" t="inlineStr">
         <is>
-          <t>L11.C06</t>
+          <t>L11.C05</t>
         </is>
       </c>
       <c r="B171" s="3" t="inlineStr">
@@ -11991,7 +11991,7 @@
       </c>
       <c r="C171" s="3" t="inlineStr">
         <is>
-          <t>Le barème par défaut</t>
+          <t>L'assiette du reflux transactionnel</t>
         </is>
       </c>
       <c r="D171" s="3" t="inlineStr">
@@ -12020,31 +12020,31 @@
         </is>
       </c>
       <c r="I171" s="3" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="J171" s="3" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="K171" s="3" t="inlineStr">
         <is>
-          <t>bareme, qualification_regenerative, degeneratif, reflux_transactionnel, regle_contre_discretion, affectation_des_instruments</t>
+          <t>reflux_transactionnel, bareme, degeneratif, reflux_collectif, robustesse, affectation_des_instruments</t>
         </is>
       </c>
       <c r="L171" s="3" t="inlineStr">
         <is>
-          <t>L1.C18, L1.C21, L1.C22, L1.C27, L1.C28, L11.C03, L11.C05</t>
+          <t>L1.C18, L1.C21, L1.C23, L11.C02, L11.C03, L11.C04</t>
         </is>
       </c>
       <c r="M171" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-11/c06-le-bareme-par-defaut.md</t>
+          <t>corpus/livre-11/c05-l-assiette-du-reflux-transactionnel.md</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" s="2" t="inlineStr">
         <is>
-          <t>L11.C07</t>
+          <t>L11.C06</t>
         </is>
       </c>
       <c r="B172" s="3" t="inlineStr">
@@ -12054,7 +12054,7 @@
       </c>
       <c r="C172" s="3" t="inlineStr">
         <is>
-          <t>Le demurrage et son nœud de prélèvement</t>
+          <t>Le barème par défaut</t>
         </is>
       </c>
       <c r="D172" s="3" t="inlineStr">
@@ -12090,24 +12090,24 @@
       </c>
       <c r="K172" s="3" t="inlineStr">
         <is>
-          <t>demurrage, reflux_collectif, reflux_transactionnel, bareme, affectation_des_instruments, referentiel_de_change</t>
+          <t>bareme, qualification_regenerative, degeneratif, reflux_transactionnel, regle_contre_discretion, affectation_des_instruments</t>
         </is>
       </c>
       <c r="L172" s="3" t="inlineStr">
         <is>
-          <t>L1.C21, L1.C26, L11.C02, L11.C03, L11.C04, L11.C05, L11.C06</t>
+          <t>L1.C18, L1.C21, L1.C22, L1.C27, L1.C28, L11.C03, L11.C05</t>
         </is>
       </c>
       <c r="M172" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-11/c07-le-demurrage-et-son-noeud.md</t>
+          <t>corpus/livre-11/c06-le-bareme-par-defaut.md</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" s="2" t="inlineStr">
         <is>
-          <t>L11.C08</t>
+          <t>L11.C07</t>
         </is>
       </c>
       <c r="B173" s="3" t="inlineStr">
@@ -12117,7 +12117,7 @@
       </c>
       <c r="C173" s="3" t="inlineStr">
         <is>
-          <t>Les dérogations</t>
+          <t>Le demurrage et son nœud de prélèvement</t>
         </is>
       </c>
       <c r="D173" s="3" t="inlineStr">
@@ -12153,24 +12153,24 @@
       </c>
       <c r="K173" s="3" t="inlineStr">
         <is>
-          <t>demurrage, reflux_transactionnel, bareme, qualification_regenerative, reflux_collectif, degeneratif</t>
+          <t>demurrage, reflux_collectif, reflux_transactionnel, bareme, affectation_des_instruments, referentiel_de_change</t>
         </is>
       </c>
       <c r="L173" s="3" t="inlineStr">
         <is>
-          <t>L1.C18, L1.C20, L1.C21, L1.C22, L11.C03, L11.C05, L11.C06, L11.C07</t>
+          <t>L1.C21, L1.C26, L11.C02, L11.C03, L11.C04, L11.C05, L11.C06</t>
         </is>
       </c>
       <c r="M173" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-11/c08-les-derogations.md</t>
+          <t>corpus/livre-11/c07-le-demurrage-et-son-noeud.md</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" s="2" t="inlineStr">
         <is>
-          <t>L11.C09</t>
+          <t>L11.C08</t>
         </is>
       </c>
       <c r="B174" s="3" t="inlineStr">
@@ -12180,7 +12180,7 @@
       </c>
       <c r="C174" s="3" t="inlineStr">
         <is>
-          <t>L'incidence — qui paie le reflux</t>
+          <t>Les dérogations</t>
         </is>
       </c>
       <c r="D174" s="3" t="inlineStr">
@@ -12216,24 +12216,24 @@
       </c>
       <c r="K174" s="3" t="inlineStr">
         <is>
-          <t>reflux_collectif, reflux_transactionnel, demurrage, bareme, degeneratif, qualification_regenerative</t>
+          <t>demurrage, reflux_transactionnel, bareme, qualification_regenerative, reflux_collectif, degeneratif</t>
         </is>
       </c>
       <c r="L174" s="3" t="inlineStr">
         <is>
-          <t>L1.C21, L1.C22, L11.C03, L11.C05, L11.C06, L11.C07, L11.C08</t>
+          <t>L1.C18, L1.C20, L1.C21, L1.C22, L11.C03, L11.C05, L11.C06, L11.C07</t>
         </is>
       </c>
       <c r="M174" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-11/c09-l-incidence-qui-paie-le-reflux.md</t>
+          <t>corpus/livre-11/c08-les-derogations.md</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" s="2" t="inlineStr">
         <is>
-          <t>L11.C10</t>
+          <t>L11.C09</t>
         </is>
       </c>
       <c r="B175" s="3" t="inlineStr">
@@ -12243,7 +12243,7 @@
       </c>
       <c r="C175" s="3" t="inlineStr">
         <is>
-          <t>La trajectoire de mise en place</t>
+          <t>L'incidence — qui paie le reflux</t>
         </is>
       </c>
       <c r="D175" s="3" t="inlineStr">
@@ -12272,31 +12272,31 @@
         </is>
       </c>
       <c r="I175" s="3" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="J175" s="3" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="K175" s="3" t="inlineStr">
         <is>
-          <t>bareme, regle_contre_discretion, degeneratif, reflux_transactionnel, qualification_regenerative, affectation_des_instruments</t>
+          <t>reflux_collectif, reflux_transactionnel, demurrage, bareme, degeneratif, qualification_regenerative</t>
         </is>
       </c>
       <c r="L175" s="3" t="inlineStr">
         <is>
-          <t>L1.C21, L1.C23, L1.C27, L11.C03, L11.C05, L11.C06, L11.C09</t>
+          <t>L1.C21, L1.C22, L11.C03, L11.C05, L11.C06, L11.C07, L11.C08</t>
         </is>
       </c>
       <c r="M175" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-11/c10-la-trajectoire-de-mise-en-place.md</t>
+          <t>corpus/livre-11/c09-l-incidence-qui-paie-le-reflux.md</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" s="2" t="inlineStr">
         <is>
-          <t>L11.C11</t>
+          <t>L11.C10</t>
         </is>
       </c>
       <c r="B176" s="3" t="inlineStr">
@@ -12306,7 +12306,7 @@
       </c>
       <c r="C176" s="3" t="inlineStr">
         <is>
-          <t>Qui arrête le barème</t>
+          <t>La trajectoire de mise en place</t>
         </is>
       </c>
       <c r="D176" s="3" t="inlineStr">
@@ -12331,35 +12331,35 @@
       </c>
       <c r="H176" s="3" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="I176" s="3" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="J176" s="3" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="K176" s="3" t="inlineStr">
         <is>
-          <t>bareme, affectation_des_instruments, referentiel_de_change, qualification_regenerative, regle_contre_discretion, reflux_collectif</t>
+          <t>bareme, regle_contre_discretion, degeneratif, reflux_transactionnel, qualification_regenerative, affectation_des_instruments</t>
         </is>
       </c>
       <c r="L176" s="3" t="inlineStr">
         <is>
-          <t>L1.C18, L1.C22, L1.C26, L1.C27, L11.C04, L11.C06, L11.C08, L11.C10</t>
+          <t>L1.C21, L1.C23, L1.C27, L11.C03, L11.C05, L11.C06, L11.C09</t>
         </is>
       </c>
       <c r="M176" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-11/c11-qui-arrete-le-bareme.md</t>
+          <t>corpus/livre-11/c10-la-trajectoire-de-mise-en-place.md</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" s="2" t="inlineStr">
         <is>
-          <t>L11.C12</t>
+          <t>L11.C11</t>
         </is>
       </c>
       <c r="B177" s="3" t="inlineStr">
@@ -12369,7 +12369,7 @@
       </c>
       <c r="C177" s="3" t="inlineStr">
         <is>
-          <t>La directive</t>
+          <t>Qui arrête le barème</t>
         </is>
       </c>
       <c r="D177" s="3" t="inlineStr">
@@ -12398,31 +12398,31 @@
         </is>
       </c>
       <c r="I177" s="3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J177" s="3" t="n">
         <v>4</v>
       </c>
       <c r="K177" s="3" t="inlineStr">
         <is>
-          <t>bareme, regle_contre_discretion, affectation_des_instruments, reflux_collectif, qualification_regenerative</t>
+          <t>bareme, affectation_des_instruments, referentiel_de_change, qualification_regenerative, regle_contre_discretion, reflux_collectif</t>
         </is>
       </c>
       <c r="L177" s="3" t="inlineStr">
         <is>
-          <t>L1.C21, L11.C03, L11.C05, L11.C06, L11.C09, L11.C10, L11.C11</t>
+          <t>L1.C18, L1.C22, L1.C26, L1.C27, L11.C04, L11.C06, L11.C08, L11.C10</t>
         </is>
       </c>
       <c r="M177" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-11/c12-la-directive.md</t>
+          <t>corpus/livre-11/c11-qui-arrete-le-bareme.md</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" s="2" t="inlineStr">
         <is>
-          <t>L11.C13</t>
+          <t>L11.C12</t>
         </is>
       </c>
       <c r="B178" s="3" t="inlineStr">
@@ -12432,7 +12432,7 @@
       </c>
       <c r="C178" s="3" t="inlineStr">
         <is>
-          <t>Le barème de qualification</t>
+          <t>La directive</t>
         </is>
       </c>
       <c r="D178" s="3" t="inlineStr">
@@ -12457,35 +12457,35 @@
       </c>
       <c r="H178" s="3" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="I178" s="3" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J178" s="3" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K178" s="3" t="inlineStr">
         <is>
-          <t>qualification_regenerative, bareme, creation_monetaire, additionnalite, degeneratif, essentiel_insolvable</t>
+          <t>bareme, regle_contre_discretion, affectation_des_instruments, reflux_collectif, qualification_regenerative</t>
         </is>
       </c>
       <c r="L178" s="3" t="inlineStr">
         <is>
-          <t>L1.C18, L1.C20, L1.C22, L1.C27, L11.C03, L11.C05, L11.C06, L11.C08, L11.C09, L11.C10, L11.C11, L11.C12</t>
+          <t>L1.C21, L11.C03, L11.C05, L11.C06, L11.C09, L11.C10, L11.C11</t>
         </is>
       </c>
       <c r="M178" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-11/c13-le-bareme-de-qualification.md</t>
+          <t>corpus/livre-11/c12-la-directive.md</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" s="2" t="inlineStr">
         <is>
-          <t>L11.C14</t>
+          <t>L11.C13</t>
         </is>
       </c>
       <c r="B179" s="3" t="inlineStr">
@@ -12495,7 +12495,7 @@
       </c>
       <c r="C179" s="3" t="inlineStr">
         <is>
-          <t>Le tableau de bord, ou les données de la directive</t>
+          <t>Le barème de qualification</t>
         </is>
       </c>
       <c r="D179" s="3" t="inlineStr">
@@ -12520,35 +12520,35 @@
       </c>
       <c r="H179" s="3" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="I179" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="J179" s="3" t="n">
         <v>5</v>
       </c>
-      <c r="J179" s="3" t="n">
-        <v>4</v>
-      </c>
       <c r="K179" s="3" t="inlineStr">
         <is>
-          <t>indicateur_de_progres, bareme, regle_contre_discretion, affectation_des_instruments, degeneratif, qualification_regenerative</t>
+          <t>qualification_regenerative, bareme, creation_monetaire, additionnalite, degeneratif, essentiel_insolvable</t>
         </is>
       </c>
       <c r="L179" s="3" t="inlineStr">
         <is>
-          <t>L1.C21, L1.C28, L11.C03, L11.C05, L11.C11, L11.C12, L11.C13</t>
+          <t>L1.C18, L1.C20, L1.C22, L1.C27, L11.C03, L11.C05, L11.C06, L11.C08, L11.C09, L11.C10, L11.C11, L11.C12</t>
         </is>
       </c>
       <c r="M179" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-11/c14-le-tableau-de-bord.md</t>
+          <t>corpus/livre-11/c13-le-bareme-de-qualification.md</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" s="2" t="inlineStr">
         <is>
-          <t>L11.C15</t>
+          <t>L11.C14</t>
         </is>
       </c>
       <c r="B180" s="3" t="inlineStr">
@@ -12558,7 +12558,7 @@
       </c>
       <c r="C180" s="3" t="inlineStr">
         <is>
-          <t>Les parités du référentiel de change</t>
+          <t>Le tableau de bord, ou les données de la directive</t>
         </is>
       </c>
       <c r="D180" s="3" t="inlineStr">
@@ -12594,24 +12594,24 @@
       </c>
       <c r="K180" s="3" t="inlineStr">
         <is>
-          <t>referentiel_de_change, bareme, indicateur_de_progres, regle_contre_discretion, affectation_des_instruments</t>
+          <t>indicateur_de_progres, bareme, regle_contre_discretion, affectation_des_instruments, degeneratif, qualification_regenerative</t>
         </is>
       </c>
       <c r="L180" s="3" t="inlineStr">
         <is>
-          <t>L1.C24, L1.C25, L1.C26, L1.C28, L11.C01, L11.C04, L11.C10, L11.C12, L11.C14</t>
+          <t>L1.C21, L1.C28, L11.C03, L11.C05, L11.C11, L11.C12, L11.C13</t>
         </is>
       </c>
       <c r="M180" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-11/c15-les-parites-du-referentiel.md</t>
+          <t>corpus/livre-11/c14-le-tableau-de-bord.md</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" s="2" t="inlineStr">
         <is>
-          <t>L11.C16</t>
+          <t>L11.C15</t>
         </is>
       </c>
       <c r="B181" s="3" t="inlineStr">
@@ -12621,7 +12621,7 @@
       </c>
       <c r="C181" s="3" t="inlineStr">
         <is>
-          <t>La valorisation des communs</t>
+          <t>Les parités du référentiel de change</t>
         </is>
       </c>
       <c r="D181" s="3" t="inlineStr">
@@ -12646,35 +12646,35 @@
       </c>
       <c r="H181" s="3" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="I181" s="3" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J181" s="3" t="n">
         <v>4</v>
       </c>
       <c r="K181" s="3" t="inlineStr">
         <is>
-          <t>valorisation_des_communs, bareme, essentiel_insolvable, polycentricite, affectation_des_instruments, indicateur_de_progres</t>
+          <t>referentiel_de_change, bareme, indicateur_de_progres, regle_contre_discretion, affectation_des_instruments</t>
         </is>
       </c>
       <c r="L181" s="3" t="inlineStr">
         <is>
-          <t>L1.C15, L1.C18, L1.C21, L1.C22, L1.C24, L1.C26, L1.C27, L11.C02, L11.C03, L11.C04, L11.C06, L11.C09, L11.C11, L11.C12, L11.C13, L11.C15</t>
+          <t>L1.C24, L1.C25, L1.C26, L1.C28, L11.C01, L11.C04, L11.C10, L11.C12, L11.C14</t>
         </is>
       </c>
       <c r="M181" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-11/c16-la-valorisation-des-communs.md</t>
+          <t>corpus/livre-11/c15-les-parites-du-referentiel.md</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" s="2" t="inlineStr">
         <is>
-          <t>L11.C17</t>
+          <t>L11.C16</t>
         </is>
       </c>
       <c r="B182" s="3" t="inlineStr">
@@ -12684,7 +12684,7 @@
       </c>
       <c r="C182" s="3" t="inlineStr">
         <is>
-          <t>La cohérence des cinq barèmes</t>
+          <t>La valorisation des communs</t>
         </is>
       </c>
       <c r="D182" s="3" t="inlineStr">
@@ -12709,35 +12709,35 @@
       </c>
       <c r="H182" s="3" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="I182" s="3" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="J182" s="3" t="n">
         <v>4</v>
       </c>
       <c r="K182" s="3" t="inlineStr">
         <is>
-          <t>bareme, affectation_des_instruments, regle_contre_discretion, qualification_regenerative, valorisation_des_communs, reflux_transactionnel, referentiel_de_change, indicateur_de_progres, polycentricite</t>
+          <t>valorisation_des_communs, bareme, essentiel_insolvable, polycentricite, affectation_des_instruments, indicateur_de_progres</t>
         </is>
       </c>
       <c r="L182" s="3" t="inlineStr">
         <is>
-          <t>L1.C18, L1.C20, L1.C21, L1.C26, L1.C27, L1.C28, L11.C03, L11.C05, L11.C06, L11.C07, L11.C09, L11.C10, L11.C11, L11.C12, L11.C13, L11.C14, L11.C15, L11.C16</t>
+          <t>L1.C15, L1.C18, L1.C21, L1.C22, L1.C24, L1.C26, L1.C27, L11.C02, L11.C03, L11.C04, L11.C06, L11.C09, L11.C11, L11.C12, L11.C13, L11.C15</t>
         </is>
       </c>
       <c r="M182" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-11/c17-la-coherence-des-cinq-baremes.md</t>
+          <t>corpus/livre-11/c16-la-valorisation-des-communs.md</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" s="2" t="inlineStr">
         <is>
-          <t>L11.C18</t>
+          <t>L11.C17</t>
         </is>
       </c>
       <c r="B183" s="3" t="inlineStr">
@@ -12747,7 +12747,7 @@
       </c>
       <c r="C183" s="3" t="inlineStr">
         <is>
-          <t>Le seuil d'exemption</t>
+          <t>La cohérence des cinq barèmes</t>
         </is>
       </c>
       <c r="D183" s="3" t="inlineStr">
@@ -12776,31 +12776,31 @@
         </is>
       </c>
       <c r="I183" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J183" s="3" t="n">
         <v>4</v>
       </c>
       <c r="K183" s="3" t="inlineStr">
         <is>
-          <t>demurrage, reflux_transactionnel, bareme, regle_contre_discretion, affectation_des_instruments, valorisation_des_communs</t>
+          <t>bareme, affectation_des_instruments, regle_contre_discretion, qualification_regenerative, valorisation_des_communs, reflux_transactionnel, referentiel_de_change, indicateur_de_progres, polycentricite</t>
         </is>
       </c>
       <c r="L183" s="3" t="inlineStr">
         <is>
-          <t>L1.C21, L11.C03, L11.C05, L11.C06, L11.C07, L11.C08, L11.C09, L11.C12, L11.C13, L11.C16, L11.C17</t>
+          <t>L1.C18, L1.C20, L1.C21, L1.C26, L1.C27, L1.C28, L11.C03, L11.C05, L11.C06, L11.C07, L11.C09, L11.C10, L11.C11, L11.C12, L11.C13, L11.C14, L11.C15, L11.C16</t>
         </is>
       </c>
       <c r="M183" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-11/c18-le-seuil-d-exemption.md</t>
+          <t>corpus/livre-11/c17-la-coherence-des-cinq-baremes.md</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" s="2" t="inlineStr">
         <is>
-          <t>L11.C19</t>
+          <t>L11.C18</t>
         </is>
       </c>
       <c r="B184" s="3" t="inlineStr">
@@ -12810,7 +12810,7 @@
       </c>
       <c r="C184" s="3" t="inlineStr">
         <is>
-          <t>Le recours</t>
+          <t>Le seuil d'exemption</t>
         </is>
       </c>
       <c r="D184" s="3" t="inlineStr">
@@ -12846,24 +12846,24 @@
       </c>
       <c r="K184" s="3" t="inlineStr">
         <is>
-          <t>bareme, qualification_regenerative, valorisation_des_communs, demurrage, regle_contre_discretion, essentiel_insolvable, affectation_des_instruments</t>
+          <t>demurrage, reflux_transactionnel, bareme, regle_contre_discretion, affectation_des_instruments, valorisation_des_communs</t>
         </is>
       </c>
       <c r="L184" s="3" t="inlineStr">
         <is>
-          <t>L1.C18, L11.C03, L11.C06, L11.C08, L11.C09, L11.C11, L11.C12, L11.C13, L11.C16, L11.C17, L11.C18</t>
+          <t>L1.C21, L11.C03, L11.C05, L11.C06, L11.C07, L11.C08, L11.C09, L11.C12, L11.C13, L11.C16, L11.C17</t>
         </is>
       </c>
       <c r="M184" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-11/c19-le-recours.md</t>
+          <t>corpus/livre-11/c18-le-seuil-d-exemption.md</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" s="2" t="inlineStr">
         <is>
-          <t>L11.C20</t>
+          <t>L11.C19</t>
         </is>
       </c>
       <c r="B185" s="3" t="inlineStr">
@@ -12873,7 +12873,7 @@
       </c>
       <c r="C185" s="3" t="inlineStr">
         <is>
-          <t>L'amendement de la directive</t>
+          <t>Le recours</t>
         </is>
       </c>
       <c r="D185" s="3" t="inlineStr">
@@ -12909,24 +12909,24 @@
       </c>
       <c r="K185" s="3" t="inlineStr">
         <is>
-          <t>bareme, regle_contre_discretion, qualification_regenerative, valorisation_des_communs, referentiel_de_change, affectation_des_instruments</t>
+          <t>bareme, qualification_regenerative, valorisation_des_communs, demurrage, regle_contre_discretion, essentiel_insolvable, affectation_des_instruments</t>
         </is>
       </c>
       <c r="L185" s="3" t="inlineStr">
         <is>
-          <t>L1.C21, L1.C26, L1.C28, L11.C03, L11.C06, L11.C10, L11.C12, L11.C13, L11.C15, L11.C16, L11.C17, L11.C18, L11.C19</t>
+          <t>L1.C18, L11.C03, L11.C06, L11.C08, L11.C09, L11.C11, L11.C12, L11.C13, L11.C16, L11.C17, L11.C18</t>
         </is>
       </c>
       <c r="M185" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-11/c20-l-amendement-de-la-directive.md</t>
+          <t>corpus/livre-11/c19-le-recours.md</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" s="2" t="inlineStr">
         <is>
-          <t>L11.C21</t>
+          <t>L11.C20</t>
         </is>
       </c>
       <c r="B186" s="3" t="inlineStr">
@@ -12936,7 +12936,7 @@
       </c>
       <c r="C186" s="3" t="inlineStr">
         <is>
-          <t>La perception</t>
+          <t>L'amendement de la directive</t>
         </is>
       </c>
       <c r="D186" s="3" t="inlineStr">
@@ -12965,31 +12965,31 @@
         </is>
       </c>
       <c r="I186" s="3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J186" s="3" t="n">
         <v>4</v>
       </c>
       <c r="K186" s="3" t="inlineStr">
         <is>
-          <t>reflux_transactionnel, reflux_collectif, bareme, demurrage, affectation_des_instruments, contrepartie_comptable</t>
+          <t>bareme, regle_contre_discretion, qualification_regenerative, valorisation_des_communs, referentiel_de_change, affectation_des_instruments</t>
         </is>
       </c>
       <c r="L186" s="3" t="inlineStr">
         <is>
-          <t>L1.C21, L11.C01, L11.C02, L11.C03, L11.C05, L11.C09, L11.C10, L11.C16, L11.C17, L11.C19, L11.C20</t>
+          <t>L1.C21, L1.C26, L1.C28, L11.C03, L11.C06, L11.C10, L11.C12, L11.C13, L11.C15, L11.C16, L11.C17, L11.C18, L11.C19</t>
         </is>
       </c>
       <c r="M186" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-11/c21-la-perception.md</t>
+          <t>corpus/livre-11/c20-l-amendement-de-la-directive.md</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" s="2" t="inlineStr">
         <is>
-          <t>L11.C22</t>
+          <t>L11.C21</t>
         </is>
       </c>
       <c r="B187" s="3" t="inlineStr">
@@ -12999,7 +12999,7 @@
       </c>
       <c r="C187" s="3" t="inlineStr">
         <is>
-          <t>Les délais</t>
+          <t>La perception</t>
         </is>
       </c>
       <c r="D187" s="3" t="inlineStr">
@@ -13028,31 +13028,31 @@
         </is>
       </c>
       <c r="I187" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J187" s="3" t="n">
         <v>4</v>
       </c>
       <c r="K187" s="3" t="inlineStr">
         <is>
-          <t>reflux_collectif, reflux_transactionnel, bareme, regle_contre_discretion, qualification_regenerative, affectation_des_instruments, robustesse</t>
+          <t>reflux_transactionnel, reflux_collectif, bareme, demurrage, affectation_des_instruments, contrepartie_comptable</t>
         </is>
       </c>
       <c r="L187" s="3" t="inlineStr">
         <is>
-          <t>L1.C21, L11.C03, L11.C07, L11.C10, L11.C12, L11.C13, L11.C16, L11.C17, L11.C19, L11.C20, L11.C21</t>
+          <t>L1.C21, L11.C01, L11.C02, L11.C03, L11.C05, L11.C09, L11.C10, L11.C16, L11.C17, L11.C19, L11.C20</t>
         </is>
       </c>
       <c r="M187" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-11/c22-les-delais.md</t>
+          <t>corpus/livre-11/c21-la-perception.md</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" s="2" t="inlineStr">
         <is>
-          <t>L11.C23</t>
+          <t>L11.C22</t>
         </is>
       </c>
       <c r="B188" s="3" t="inlineStr">
@@ -13062,7 +13062,7 @@
       </c>
       <c r="C188" s="3" t="inlineStr">
         <is>
-          <t>La contracyclicité</t>
+          <t>Les délais</t>
         </is>
       </c>
       <c r="D188" s="3" t="inlineStr">
@@ -13091,31 +13091,31 @@
         </is>
       </c>
       <c r="I188" s="3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J188" s="3" t="n">
         <v>4</v>
       </c>
       <c r="K188" s="3" t="inlineStr">
         <is>
-          <t>reflux_transactionnel, reflux_collectif, essentiel_insolvable, degeneratif, bareme, robustesse, affectation_des_instruments, contrepartie_comptable</t>
+          <t>reflux_collectif, reflux_transactionnel, bareme, regle_contre_discretion, qualification_regenerative, affectation_des_instruments, robustesse</t>
         </is>
       </c>
       <c r="L188" s="3" t="inlineStr">
         <is>
-          <t>L1.C15, L1.C21, L1.C29, L11.C01, L11.C02, L11.C03, L11.C07, L11.C10, L11.C12, L11.C14, L11.C16, L11.C17, L11.C21, L11.C22</t>
+          <t>L1.C21, L11.C03, L11.C07, L11.C10, L11.C12, L11.C13, L11.C16, L11.C17, L11.C19, L11.C20, L11.C21</t>
         </is>
       </c>
       <c r="M188" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-11/c23-la-contracyclicite.md</t>
+          <t>corpus/livre-11/c22-les-delais.md</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" s="2" t="inlineStr">
         <is>
-          <t>L11.C24</t>
+          <t>L11.C23</t>
         </is>
       </c>
       <c r="B189" s="3" t="inlineStr">
@@ -13125,7 +13125,7 @@
       </c>
       <c r="C189" s="3" t="inlineStr">
         <is>
-          <t>Le barème aux frontières</t>
+          <t>La contracyclicité</t>
         </is>
       </c>
       <c r="D189" s="3" t="inlineStr">
@@ -13150,35 +13150,35 @@
       </c>
       <c r="H189" s="3" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="I189" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J189" s="3" t="n">
         <v>4</v>
       </c>
       <c r="K189" s="3" t="inlineStr">
         <is>
-          <t>seuil_d_activation, bareme, degeneratif, reflux_transactionnel, referentiel_de_change, essentiel_insolvable, affectation_des_instruments</t>
+          <t>reflux_transactionnel, reflux_collectif, essentiel_insolvable, degeneratif, bareme, robustesse, affectation_des_instruments, contrepartie_comptable</t>
         </is>
       </c>
       <c r="L189" s="3" t="inlineStr">
         <is>
-          <t>L1.C26, L1.C27, L11.C04, L11.C05, L11.C06, L11.C09, L11.C13, L11.C16, L11.C17, L11.C19, L11.C21</t>
+          <t>L1.C15, L1.C21, L1.C29, L11.C01, L11.C02, L11.C03, L11.C07, L11.C10, L11.C12, L11.C14, L11.C16, L11.C17, L11.C21, L11.C22</t>
         </is>
       </c>
       <c r="M189" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-11/c24-le-bareme-aux-frontieres.md</t>
+          <t>corpus/livre-11/c23-la-contracyclicite.md</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" s="2" t="inlineStr">
         <is>
-          <t>L11.C25</t>
+          <t>L11.C24</t>
         </is>
       </c>
       <c r="B190" s="3" t="inlineStr">
@@ -13188,7 +13188,7 @@
       </c>
       <c r="C190" s="3" t="inlineStr">
         <is>
-          <t>Le contrôle</t>
+          <t>Le barème aux frontières</t>
         </is>
       </c>
       <c r="D190" s="3" t="inlineStr">
@@ -13224,24 +13224,24 @@
       </c>
       <c r="K190" s="3" t="inlineStr">
         <is>
-          <t>bareme, reflux_transactionnel, qualification_regenerative, regle_contre_discretion, affectation_des_instruments, essentiel_insolvable</t>
+          <t>seuil_d_activation, bareme, degeneratif, reflux_transactionnel, referentiel_de_change, essentiel_insolvable, affectation_des_instruments</t>
         </is>
       </c>
       <c r="L190" s="3" t="inlineStr">
         <is>
-          <t>L1.C18, L1.C21, L1.C22, L11.C05, L11.C06, L11.C09, L11.C11, L11.C13, L11.C17, L11.C19, L11.C20, L11.C21, L11.C23, L11.C24</t>
+          <t>L1.C26, L1.C27, L11.C04, L11.C05, L11.C06, L11.C09, L11.C13, L11.C16, L11.C17, L11.C19, L11.C21</t>
         </is>
       </c>
       <c r="M190" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-11/c25-le-controle.md</t>
+          <t>corpus/livre-11/c24-le-bareme-aux-frontieres.md</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" s="2" t="inlineStr">
         <is>
-          <t>L11.C26</t>
+          <t>L11.C25</t>
         </is>
       </c>
       <c r="B191" s="3" t="inlineStr">
@@ -13251,7 +13251,7 @@
       </c>
       <c r="C191" s="3" t="inlineStr">
         <is>
-          <t>La portée du Livre 11</t>
+          <t>Le contrôle</t>
         </is>
       </c>
       <c r="D191" s="3" t="inlineStr">
@@ -13276,35 +13276,35 @@
       </c>
       <c r="H191" s="3" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="I191" s="3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J191" s="3" t="n">
         <v>4</v>
       </c>
       <c r="K191" s="3" t="inlineStr">
         <is>
-          <t>bareme, reflux_collectif, reflux_transactionnel, demurrage, qualification_regenerative, valorisation_des_communs, referentiel_de_change, regle_contre_discretion, affectation_des_instruments, polycentricite</t>
+          <t>bareme, reflux_transactionnel, qualification_regenerative, regle_contre_discretion, affectation_des_instruments, essentiel_insolvable</t>
         </is>
       </c>
       <c r="L191" s="3" t="inlineStr">
         <is>
-          <t>L1.C15, L1.C18, L1.C21, L1.C22, L1.C26, L1.C27, L1.C28, L1.C29, L11.C01, L11.C03, L11.C06, L11.C07, L11.C09, L11.C11, L11.C12, L11.C13, L11.C16, L11.C17, L11.C19, L11.C21, L11.C22, L11.C23, L11.C24, L11.C25</t>
+          <t>L1.C18, L1.C21, L1.C22, L11.C05, L11.C06, L11.C09, L11.C11, L11.C13, L11.C17, L11.C19, L11.C20, L11.C21, L11.C23, L11.C24</t>
         </is>
       </c>
       <c r="M191" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-11/c26-la-portee-du-livre.md</t>
+          <t>corpus/livre-11/c25-le-controle.md</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" s="2" t="inlineStr">
         <is>
-          <t>L11.C27</t>
+          <t>L11.C26</t>
         </is>
       </c>
       <c r="B192" s="3" t="inlineStr">
@@ -13314,7 +13314,7 @@
       </c>
       <c r="C192" s="3" t="inlineStr">
         <is>
-          <t>L'assiette de la fonte est celle de la TVA</t>
+          <t>La portée du Livre 11</t>
         </is>
       </c>
       <c r="D192" s="3" t="inlineStr">
@@ -13339,35 +13339,35 @@
       </c>
       <c r="H192" s="3" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="I192" s="3" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J192" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K192" s="3" t="inlineStr">
         <is>
-          <t>reflux_transactionnel, demurrage, bareme, degeneratif, qualification_regenerative, externalisation, additionnalite</t>
+          <t>bareme, reflux_collectif, reflux_transactionnel, demurrage, qualification_regenerative, valorisation_des_communs, referentiel_de_change, regle_contre_discretion, affectation_des_instruments, polycentricite</t>
         </is>
       </c>
       <c r="L192" s="3" t="inlineStr">
         <is>
-          <t>L1.C21, L1.C27, L2.C16, L11.C02, L11.C05, L11.C09, L11.C21, L11.C24, L11.C25, L20.C02, L20.C19</t>
+          <t>L1.C15, L1.C18, L1.C21, L1.C22, L1.C26, L1.C27, L1.C28, L1.C29, L11.C01, L11.C03, L11.C06, L11.C07, L11.C09, L11.C11, L11.C12, L11.C13, L11.C16, L11.C17, L11.C19, L11.C21, L11.C22, L11.C23, L11.C24, L11.C25</t>
         </is>
       </c>
       <c r="M192" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-11/c27-l-assiette-de-la-fonte-est-celle-de-la-tva.md</t>
+          <t>corpus/livre-11/c26-la-portee-du-livre.md</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" s="2" t="inlineStr">
         <is>
-          <t>L11.C28</t>
+          <t>L11.C27</t>
         </is>
       </c>
       <c r="B193" s="3" t="inlineStr">
@@ -13377,7 +13377,7 @@
       </c>
       <c r="C193" s="3" t="inlineStr">
         <is>
-          <t>La fonte sur les acquisitions d'actifs, éprouvée</t>
+          <t>L'assiette de la fonte est celle de la TVA</t>
         </is>
       </c>
       <c r="D193" s="3" t="inlineStr">
@@ -13406,31 +13406,31 @@
         </is>
       </c>
       <c r="I193" s="3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J193" s="3" t="n">
         <v>3</v>
       </c>
       <c r="K193" s="3" t="inlineStr">
         <is>
-          <t>reflux_transactionnel, demurrage, bareme, referentiel_de_change, degeneratif, robustesse</t>
+          <t>reflux_transactionnel, demurrage, bareme, degeneratif, qualification_regenerative, externalisation, additionnalite</t>
         </is>
       </c>
       <c r="L193" s="3" t="inlineStr">
         <is>
-          <t>L1.C19, L1.C21, L2.C13, L2.C16, L6.C02, L11.C02, L11.C05, L11.C09, L11.C23, L11.C27, L20.C13</t>
+          <t>L1.C21, L1.C27, L2.C16, L11.C02, L11.C05, L11.C09, L11.C21, L11.C24, L11.C25, L20.C02, L20.C19</t>
         </is>
       </c>
       <c r="M193" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-11/c28-la-fonte-sur-les-acquisitions-d-actifs-eprouvee.md</t>
+          <t>corpus/livre-11/c27-l-assiette-de-la-fonte-est-celle-de-la-tva.md</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" s="2" t="inlineStr">
         <is>
-          <t>L11.C29</t>
+          <t>L11.C28</t>
         </is>
       </c>
       <c r="B194" s="3" t="inlineStr">
@@ -13440,7 +13440,7 @@
       </c>
       <c r="C194" s="3" t="inlineStr">
         <is>
-          <t>La structure des sanctions</t>
+          <t>La fonte sur les acquisitions d'actifs, éprouvée</t>
         </is>
       </c>
       <c r="D194" s="3" t="inlineStr">
@@ -13469,41 +13469,41 @@
         </is>
       </c>
       <c r="I194" s="3" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J194" s="3" t="n">
         <v>3</v>
       </c>
       <c r="K194" s="3" t="inlineStr">
         <is>
-          <t>bareme, seuil_d_activation, regle_contre_discretion, robustesse, qualification_regenerative, degeneratif</t>
+          <t>reflux_transactionnel, demurrage, bareme, referentiel_de_change, degeneratif, robustesse</t>
         </is>
       </c>
       <c r="L194" s="3" t="inlineStr">
         <is>
-          <t>L2.C08, L2.C14, L2.C21, L2.C22, L7.C19, L8.C31, L11.C18, L11.C19, L11.C20, L11.C23, L11.C25, L20.C17, L20.C18</t>
+          <t>L1.C19, L1.C21, L2.C13, L2.C16, L6.C02, L11.C02, L11.C05, L11.C09, L11.C23, L11.C27, L20.C13</t>
         </is>
       </c>
       <c r="M194" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-11/c29-la-structure-des-sanctions.md</t>
+          <t>corpus/livre-11/c28-la-fonte-sur-les-acquisitions-d-actifs-eprouvee.md</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" s="2" t="inlineStr">
         <is>
-          <t>L18.C01</t>
+          <t>L11.C29</t>
         </is>
       </c>
       <c r="B195" s="3" t="inlineStr">
         <is>
-          <t>L18</t>
+          <t>L11</t>
         </is>
       </c>
       <c r="C195" s="3" t="inlineStr">
         <is>
-          <t>Ce que ce livre doit établir, et le repli n'est pas l'annexe</t>
+          <t>La structure des sanctions</t>
         </is>
       </c>
       <c r="D195" s="3" t="inlineStr">
@@ -13523,7 +13523,7 @@
       </c>
       <c r="G195" s="3" t="inlineStr">
         <is>
-          <t>hybride</t>
+          <t>conception</t>
         </is>
       </c>
       <c r="H195" s="3" t="inlineStr">
@@ -13532,31 +13532,31 @@
         </is>
       </c>
       <c r="I195" s="3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J195" s="3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K195" s="3" t="inlineStr">
         <is>
-          <t>contrepartie_comptable, valorisation_des_communs, communs, essentiel_insolvable, qualification_regenerative, architecture_invisible</t>
+          <t>bareme, seuil_d_activation, regle_contre_discretion, robustesse, qualification_regenerative, degeneratif</t>
         </is>
       </c>
       <c r="L195" s="3" t="inlineStr">
         <is>
-          <t>L1.C09, L1.C29, L5.C02, L5.C09, L5.C10, L6.C08, L6.C09, L6.C13, L11.C13, L11.C16, L20.C02</t>
+          <t>L2.C08, L2.C14, L2.C21, L2.C22, L7.C19, L8.C31, L11.C18, L11.C19, L11.C20, L11.C23, L11.C25, L20.C17, L20.C18</t>
         </is>
       </c>
       <c r="M195" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-18/c01-ce-que-ce-livre-doit-etablir.md</t>
+          <t>corpus/livre-11/c29-la-structure-des-sanctions.md</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" s="2" t="inlineStr">
         <is>
-          <t>L18.C02</t>
+          <t>L18.C01</t>
         </is>
       </c>
       <c r="B196" s="3" t="inlineStr">
@@ -13566,7 +13566,7 @@
       </c>
       <c r="C196" s="3" t="inlineStr">
         <is>
-          <t>La métrologie existe, et ce qu'elle enregistre est l'ordre en place</t>
+          <t>Ce que ce livre doit établir, et le repli n'est pas l'annexe</t>
         </is>
       </c>
       <c r="D196" s="3" t="inlineStr">
@@ -13598,28 +13598,28 @@
         <v>4</v>
       </c>
       <c r="J196" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K196" s="3" t="inlineStr">
         <is>
-          <t>valorisation_des_communs, contrepartie_comptable, bareme, essentiel_insolvable, indicateur_de_progres, fausse_richesse</t>
+          <t>contrepartie_comptable, valorisation_des_communs, communs, essentiel_insolvable, qualification_regenerative, architecture_invisible</t>
         </is>
       </c>
       <c r="L196" s="3" t="inlineStr">
         <is>
-          <t>L1.C09, L1.C15, L1.C18, L6.C06, L11.C03, L11.C07, L11.C13, L11.C16, L18.C01</t>
+          <t>L1.C09, L1.C29, L5.C02, L5.C09, L5.C10, L6.C08, L6.C09, L6.C13, L11.C13, L11.C16, L20.C02</t>
         </is>
       </c>
       <c r="M196" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-18/c02-la-metrologie-existe-et-ce-qu-elle-enregistre.md</t>
+          <t>corpus/livre-18/c01-ce-que-ce-livre-doit-etablir.md</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" s="2" t="inlineStr">
         <is>
-          <t>L18.C03</t>
+          <t>L18.C02</t>
         </is>
       </c>
       <c r="B197" s="3" t="inlineStr">
@@ -13629,7 +13629,7 @@
       </c>
       <c r="C197" s="3" t="inlineStr">
         <is>
-          <t>L'échelle de repli, et qui l'a arrêtée</t>
+          <t>La métrologie existe, et ce qu'elle enregistre est l'ordre en place</t>
         </is>
       </c>
       <c r="D197" s="3" t="inlineStr">
@@ -13658,31 +13658,31 @@
         </is>
       </c>
       <c r="I197" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J197" s="3" t="n">
         <v>3</v>
       </c>
       <c r="K197" s="3" t="inlineStr">
         <is>
-          <t>contrepartie_comptable, architecture_invisible, valorisation_des_communs, essentiel_insolvable, regle_contre_discretion</t>
+          <t>valorisation_des_communs, contrepartie_comptable, bareme, essentiel_insolvable, indicateur_de_progres, fausse_richesse</t>
         </is>
       </c>
       <c r="L197" s="3" t="inlineStr">
         <is>
-          <t>L1.C09, L1.C15, L1.C29, L6.C09, L11.C29, L18.C01, L18.C02, L20.C02</t>
+          <t>L1.C09, L1.C15, L1.C18, L6.C06, L11.C03, L11.C07, L11.C13, L11.C16, L18.C01</t>
         </is>
       </c>
       <c r="M197" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-18/c03-l-echelle-de-repli-et-qui-l-a-arretee.md</t>
+          <t>corpus/livre-18/c02-la-metrologie-existe-et-ce-qu-elle-enregistre.md</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" s="2" t="inlineStr">
         <is>
-          <t>L18.C04</t>
+          <t>L18.C03</t>
         </is>
       </c>
       <c r="B198" s="3" t="inlineStr">
@@ -13692,7 +13692,7 @@
       </c>
       <c r="C198" s="3" t="inlineStr">
         <is>
-          <t>Les grandeurs physiques, et l'endroit où elles frappent le dispositif</t>
+          <t>L'échelle de repli, et qui l'a arrêtée</t>
         </is>
       </c>
       <c r="D198" s="3" t="inlineStr">
@@ -13721,31 +13721,31 @@
         </is>
       </c>
       <c r="I198" s="3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J198" s="3" t="n">
         <v>3</v>
       </c>
       <c r="K198" s="3" t="inlineStr">
         <is>
-          <t>decouplage, effet_rebond, externalisation, limites_planetaires, sobriete, fausse_richesse</t>
+          <t>contrepartie_comptable, architecture_invisible, valorisation_des_communs, essentiel_insolvable, regle_contre_discretion</t>
         </is>
       </c>
       <c r="L198" s="3" t="inlineStr">
         <is>
-          <t>L1.C02, L1.C03, L1.C04, L5.C08, L6.C08, L11.C10, L11.C24, L18.C01, L18.C02</t>
+          <t>L1.C09, L1.C15, L1.C29, L6.C09, L11.C29, L18.C01, L18.C02, L20.C02</t>
         </is>
       </c>
       <c r="M198" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-18/c04-les-grandeurs-physiques-et-ou-elles-frappent.md</t>
+          <t>corpus/livre-18/c03-l-echelle-de-repli-et-qui-l-a-arretee.md</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" s="2" t="inlineStr">
         <is>
-          <t>L18.C05</t>
+          <t>L18.C04</t>
         </is>
       </c>
       <c r="B199" s="3" t="inlineStr">
@@ -13755,7 +13755,7 @@
       </c>
       <c r="C199" s="3" t="inlineStr">
         <is>
-          <t>Le commun est ce que la norme exclut, et la symétrie de l'écriture</t>
+          <t>Les grandeurs physiques, et l'endroit où elles frappent le dispositif</t>
         </is>
       </c>
       <c r="D199" s="3" t="inlineStr">
@@ -13784,31 +13784,31 @@
         </is>
       </c>
       <c r="I199" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J199" s="3" t="n">
         <v>3</v>
       </c>
       <c r="K199" s="3" t="inlineStr">
         <is>
-          <t>communs, contrepartie_comptable, valorisation_des_communs, architecture_invisible, monnaie_comme_registre, creation_monetaire</t>
+          <t>decouplage, effet_rebond, externalisation, limites_planetaires, sobriete, fausse_richesse</t>
         </is>
       </c>
       <c r="L199" s="3" t="inlineStr">
         <is>
-          <t>L1.C09, L1.C20, L1.C29, L6.C06, L6.C08, L11.C13, L11.C16, L18.C01, L18.C02, L18.C03, L20.C02</t>
+          <t>L1.C02, L1.C03, L1.C04, L5.C08, L6.C08, L11.C10, L11.C24, L18.C01, L18.C02</t>
         </is>
       </c>
       <c r="M199" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-18/c05-le-commun-est-ce-que-la-norme-exclut.md</t>
+          <t>corpus/livre-18/c04-les-grandeurs-physiques-et-ou-elles-frappent.md</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" s="2" t="inlineStr">
         <is>
-          <t>L18.C06</t>
+          <t>L18.C05</t>
         </is>
       </c>
       <c r="B200" s="3" t="inlineStr">
@@ -13818,7 +13818,7 @@
       </c>
       <c r="C200" s="3" t="inlineStr">
         <is>
-          <t>Portée de la tranche, et une neuvième condition proposée</t>
+          <t>Le commun est ce que la norme exclut, et la symétrie de l'écriture</t>
         </is>
       </c>
       <c r="D200" s="3" t="inlineStr">
@@ -13838,7 +13838,7 @@
       </c>
       <c r="G200" s="3" t="inlineStr">
         <is>
-          <t>conception</t>
+          <t>hybride</t>
         </is>
       </c>
       <c r="H200" s="3" t="inlineStr">
@@ -13854,24 +13854,24 @@
       </c>
       <c r="K200" s="3" t="inlineStr">
         <is>
-          <t>contrepartie_comptable, communs, valorisation_des_communs, architecture_invisible, essentiel_insolvable</t>
+          <t>communs, contrepartie_comptable, valorisation_des_communs, architecture_invisible, monnaie_comme_registre, creation_monetaire</t>
         </is>
       </c>
       <c r="L200" s="3" t="inlineStr">
         <is>
-          <t>L1.C09, L1.C18, L1.C20, L1.C29, L5.C02, L5.C08, L6.C06, L6.C08, L11.C13, L11.C16, L18.C01, L18.C02, L18.C03, L18.C04, L18.C05, L20.C02</t>
+          <t>L1.C09, L1.C20, L1.C29, L6.C06, L6.C08, L11.C13, L11.C16, L18.C01, L18.C02, L18.C03, L20.C02</t>
         </is>
       </c>
       <c r="M200" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-18/c06-portee-de-la-tranche-et-une-neuvieme-condition.md</t>
+          <t>corpus/livre-18/c05-le-commun-est-ce-que-la-norme-exclut.md</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" s="2" t="inlineStr">
         <is>
-          <t>L18.C07</t>
+          <t>L18.C06</t>
         </is>
       </c>
       <c r="B201" s="3" t="inlineStr">
@@ -13881,7 +13881,7 @@
       </c>
       <c r="C201" s="3" t="inlineStr">
         <is>
-          <t>CARE/TDL répare deux objections, et en crée une plus grave</t>
+          <t>Portée de la tranche, et une neuvième condition proposée</t>
         </is>
       </c>
       <c r="D201" s="3" t="inlineStr">
@@ -13901,7 +13901,7 @@
       </c>
       <c r="G201" s="3" t="inlineStr">
         <is>
-          <t>hybride</t>
+          <t>conception</t>
         </is>
       </c>
       <c r="H201" s="3" t="inlineStr">
@@ -13910,31 +13910,31 @@
         </is>
       </c>
       <c r="I201" s="3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J201" s="3" t="n">
         <v>3</v>
       </c>
       <c r="K201" s="3" t="inlineStr">
         <is>
-          <t>contrepartie_comptable, bareme, valorisation_des_communs, communs, architecture_invisible, fausse_richesse</t>
+          <t>contrepartie_comptable, communs, valorisation_des_communs, architecture_invisible, essentiel_insolvable</t>
         </is>
       </c>
       <c r="L201" s="3" t="inlineStr">
         <is>
-          <t>L1.C09, L1.C18, L1.C20, L6.C06, L11.C03, L11.C13, L11.C16, L18.C01, L18.C02, L18.C05, L18.C06</t>
+          <t>L1.C09, L1.C18, L1.C20, L1.C29, L5.C02, L5.C08, L6.C06, L6.C08, L11.C13, L11.C16, L18.C01, L18.C02, L18.C03, L18.C04, L18.C05, L20.C02</t>
         </is>
       </c>
       <c r="M201" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-18/c07-care-tdl-repare-une-objection-et-en-cree-une-autre.md</t>
+          <t>corpus/livre-18/c06-portee-de-la-tranche-et-une-neuvieme-condition.md</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" s="2" t="inlineStr">
         <is>
-          <t>L18.C08</t>
+          <t>L18.C07</t>
         </is>
       </c>
       <c r="B202" s="3" t="inlineStr">
@@ -13944,7 +13944,7 @@
       </c>
       <c r="C202" s="3" t="inlineStr">
         <is>
-          <t>Le modèle au périmètre du dispositif, et F9 révisée</t>
+          <t>CARE/TDL répare deux objections, et en crée une plus grave</t>
         </is>
       </c>
       <c r="D202" s="3" t="inlineStr">
@@ -13964,7 +13964,7 @@
       </c>
       <c r="G202" s="3" t="inlineStr">
         <is>
-          <t>conception</t>
+          <t>hybride</t>
         </is>
       </c>
       <c r="H202" s="3" t="inlineStr">
@@ -13980,34 +13980,34 @@
       </c>
       <c r="K202" s="3" t="inlineStr">
         <is>
-          <t>contrepartie_comptable, communs, valorisation_des_communs, polycentricite, essentiel_insolvable, indicateur_de_progres</t>
+          <t>contrepartie_comptable, bareme, valorisation_des_communs, communs, architecture_invisible, fausse_richesse</t>
         </is>
       </c>
       <c r="L202" s="3" t="inlineStr">
         <is>
-          <t>L1.C09, L1.C18, L6.C06, L7.C05, L11.C13, L11.C16, L11.C25, L18.C01, L18.C02, L18.C05, L18.C06, L18.C07</t>
+          <t>L1.C09, L1.C18, L1.C20, L6.C06, L11.C03, L11.C13, L11.C16, L18.C01, L18.C02, L18.C05, L18.C06</t>
         </is>
       </c>
       <c r="M202" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-18/c08-le-modele-au-perimetre-du-dispositif-et-f9-revisee.md</t>
+          <t>corpus/livre-18/c07-care-tdl-repare-une-objection-et-en-cree-une-autre.md</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" s="2" t="inlineStr">
         <is>
-          <t>L20.C01</t>
+          <t>L18.C08</t>
         </is>
       </c>
       <c r="B203" s="3" t="inlineStr">
         <is>
-          <t>L20</t>
+          <t>L18</t>
         </is>
       </c>
       <c r="C203" s="3" t="inlineStr">
         <is>
-          <t>Ce que ce livre doit établir</t>
+          <t>Le modèle au périmètre du dispositif, et F9 révisée</t>
         </is>
       </c>
       <c r="D203" s="3" t="inlineStr">
@@ -14032,35 +14032,35 @@
       </c>
       <c r="H203" s="3" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="I203" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J203" s="3" t="n">
         <v>3</v>
       </c>
       <c r="K203" s="3" t="inlineStr">
         <is>
-          <t>fenetre_de_reforme, referentiel_de_change, communs, limites_planetaires, creation_monetaire</t>
+          <t>contrepartie_comptable, communs, valorisation_des_communs, polycentricite, essentiel_insolvable, indicateur_de_progres</t>
         </is>
       </c>
       <c r="L203" s="3" t="inlineStr">
         <is>
-          <t>L1.C18, L1.C25, L1.C27, L7.C01, L7.C03, L7.C13, L7.C17, L7.C21, L11.C24</t>
+          <t>L1.C09, L1.C18, L6.C06, L7.C05, L11.C13, L11.C16, L11.C25, L18.C01, L18.C02, L18.C05, L18.C06, L18.C07</t>
         </is>
       </c>
       <c r="M203" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-20/c01-ce-que-ce-livre-doit-etablir.md</t>
+          <t>corpus/livre-18/c08-le-modele-au-perimetre-du-dispositif-et-f9-revisee.md</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" s="2" t="inlineStr">
         <is>
-          <t>L20.C02</t>
+          <t>L20.C01</t>
         </is>
       </c>
       <c r="B204" s="3" t="inlineStr">
@@ -14070,7 +14070,7 @@
       </c>
       <c r="C204" s="3" t="inlineStr">
         <is>
-          <t>L'interdiction du financement monétaire</t>
+          <t>Ce que ce livre doit établir</t>
         </is>
       </c>
       <c r="D204" s="3" t="inlineStr">
@@ -14095,7 +14095,7 @@
       </c>
       <c r="H204" s="3" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="I204" s="3" t="n">
@@ -14106,24 +14106,24 @@
       </c>
       <c r="K204" s="3" t="inlineStr">
         <is>
-          <t>creation_monetaire, contrepartie_comptable, reflux_collectif, fenetre_de_reforme</t>
+          <t>fenetre_de_reforme, referentiel_de_change, communs, limites_planetaires, creation_monetaire</t>
         </is>
       </c>
       <c r="L204" s="3" t="inlineStr">
         <is>
-          <t>L1.C05, L1.C18, L1.C20, L1.C22, L7.C11, L7.C13, L11.C10, L20.C01</t>
+          <t>L1.C18, L1.C25, L1.C27, L7.C01, L7.C03, L7.C13, L7.C17, L7.C21, L11.C24</t>
         </is>
       </c>
       <c r="M204" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-20/c02-l-interdiction-du-financement-monetaire.md</t>
+          <t>corpus/livre-20/c01-ce-que-ce-livre-doit-etablir.md</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" s="2" t="inlineStr">
         <is>
-          <t>L20.C03</t>
+          <t>L20.C02</t>
         </is>
       </c>
       <c r="B205" s="3" t="inlineStr">
@@ -14133,7 +14133,7 @@
       </c>
       <c r="C205" s="3" t="inlineStr">
         <is>
-          <t>L'objectif principal et ce qu'il exclut</t>
+          <t>L'interdiction du financement monétaire</t>
         </is>
       </c>
       <c r="D205" s="3" t="inlineStr">
@@ -14169,24 +14169,24 @@
       </c>
       <c r="K205" s="3" t="inlineStr">
         <is>
-          <t>regle_contre_discretion, limites_planetaires, creation_monetaire, plafond_ecologique</t>
+          <t>creation_monetaire, contrepartie_comptable, reflux_collectif, fenetre_de_reforme</t>
         </is>
       </c>
       <c r="L205" s="3" t="inlineStr">
         <is>
-          <t>L1.C01, L1.C18, L1.C20, L7.C03, L8.C12, L8.C34, L11.C16, L20.C01, L20.C02</t>
+          <t>L1.C05, L1.C18, L1.C20, L1.C22, L7.C11, L7.C13, L11.C10, L20.C01</t>
         </is>
       </c>
       <c r="M205" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-20/c03-l-objectif-principal-et-ce-qu-il-exclut.md</t>
+          <t>corpus/livre-20/c02-l-interdiction-du-financement-monetaire.md</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" s="2" t="inlineStr">
         <is>
-          <t>L20.C04</t>
+          <t>L20.C03</t>
         </is>
       </c>
       <c r="B206" s="3" t="inlineStr">
@@ -14196,7 +14196,7 @@
       </c>
       <c r="C206" s="3" t="inlineStr">
         <is>
-          <t>L'indépendance, et à l'égard de qui</t>
+          <t>L'objectif principal et ce qu'il exclut</t>
         </is>
       </c>
       <c r="D206" s="3" t="inlineStr">
@@ -14221,7 +14221,7 @@
       </c>
       <c r="H206" s="3" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="I206" s="3" t="n">
@@ -14232,24 +14232,24 @@
       </c>
       <c r="K206" s="3" t="inlineStr">
         <is>
-          <t>regle_contre_discretion, creation_monetaire, fenetre_de_reforme</t>
+          <t>regle_contre_discretion, limites_planetaires, creation_monetaire, plafond_ecologique</t>
         </is>
       </c>
       <c r="L206" s="3" t="inlineStr">
         <is>
-          <t>L1.C18, L7.C04, L7.C07, L7.C10, L8.C31, L11.C17, L20.C01, L20.C03, L20.C11</t>
+          <t>L1.C01, L1.C18, L1.C20, L7.C03, L8.C12, L8.C34, L11.C16, L20.C01, L20.C02</t>
         </is>
       </c>
       <c r="M206" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-20/c04-l-independance-et-a-l-egard-de-qui.md</t>
+          <t>corpus/livre-20/c03-l-objectif-principal-et-ce-qu-il-exclut.md</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" s="2" t="inlineStr">
         <is>
-          <t>L20.C05</t>
+          <t>L20.C04</t>
         </is>
       </c>
       <c r="B207" s="3" t="inlineStr">
@@ -14259,7 +14259,7 @@
       </c>
       <c r="C207" s="3" t="inlineStr">
         <is>
-          <t>Le monopole d'émission et le cours légal</t>
+          <t>L'indépendance, et à l'égard de qui</t>
         </is>
       </c>
       <c r="D207" s="3" t="inlineStr">
@@ -14295,24 +14295,24 @@
       </c>
       <c r="K207" s="3" t="inlineStr">
         <is>
-          <t>monnaie_comme_registre, creation_monetaire, referentiel_de_change, hierarchie_monetaire</t>
+          <t>regle_contre_discretion, creation_monetaire, fenetre_de_reforme</t>
         </is>
       </c>
       <c r="L207" s="3" t="inlineStr">
         <is>
-          <t>L1.C05, L1.C07, L1.C26, L7.C15, L11.C15, L20.C01, L20.C02, L20.C03</t>
+          <t>L1.C18, L7.C04, L7.C07, L7.C10, L8.C31, L11.C17, L20.C01, L20.C03, L20.C11</t>
         </is>
       </c>
       <c r="M207" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-20/c05-le-monopole-d-emission-et-le-cours-legal.md</t>
+          <t>corpus/livre-20/c04-l-independance-et-a-l-egard-de-qui.md</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" s="2" t="inlineStr">
         <is>
-          <t>L20.C06</t>
+          <t>L20.C05</t>
         </is>
       </c>
       <c r="B208" s="3" t="inlineStr">
@@ -14322,7 +14322,7 @@
       </c>
       <c r="C208" s="3" t="inlineStr">
         <is>
-          <t>Les voies de révision et leur coût</t>
+          <t>Le monopole d'émission et le cours légal</t>
         </is>
       </c>
       <c r="D208" s="3" t="inlineStr">
@@ -14351,31 +14351,31 @@
         </is>
       </c>
       <c r="I208" s="3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J208" s="3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K208" s="3" t="inlineStr">
         <is>
-          <t>fenetre_de_reforme, regle_contre_discretion, creation_monetaire</t>
+          <t>monnaie_comme_registre, creation_monetaire, referentiel_de_change, hierarchie_monetaire</t>
         </is>
       </c>
       <c r="L208" s="3" t="inlineStr">
         <is>
-          <t>L1.C18, L7.C12, L7.C20, L7.C21, L11.C15, L20.C01, L20.C02, L20.C03, L20.C07, L20.C09, L20.C18</t>
+          <t>L1.C05, L1.C07, L1.C26, L7.C15, L11.C15, L20.C01, L20.C02, L20.C03</t>
         </is>
       </c>
       <c r="M208" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-20/c06-les-voies-de-revision-et-leur-cout.md</t>
+          <t>corpus/livre-20/c05-le-monopole-d-emission-et-le-cours-legal.md</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" s="2" t="inlineStr">
         <is>
-          <t>L20.C07</t>
+          <t>L20.C06</t>
         </is>
       </c>
       <c r="B209" s="3" t="inlineStr">
@@ -14385,7 +14385,7 @@
       </c>
       <c r="C209" s="3" t="inlineStr">
         <is>
-          <t>L'accord monétaire international</t>
+          <t>Les voies de révision et leur coût</t>
         </is>
       </c>
       <c r="D209" s="3" t="inlineStr">
@@ -14414,31 +14414,31 @@
         </is>
       </c>
       <c r="I209" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J209" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K209" s="3" t="inlineStr">
         <is>
-          <t>referentiel_de_change, fenetre_de_reforme, etalon_de_change_or, hierarchie_monetaire</t>
+          <t>fenetre_de_reforme, regle_contre_discretion, creation_monetaire</t>
         </is>
       </c>
       <c r="L209" s="3" t="inlineStr">
         <is>
-          <t>L1.C18, L1.C26, L7.C02, L7.C05, L7.C12, L7.C13, L11.C15, L20.C01, L20.C03, L20.C06, L20.C10</t>
+          <t>L1.C18, L7.C12, L7.C20, L7.C21, L11.C15, L20.C01, L20.C02, L20.C03, L20.C07, L20.C09, L20.C18</t>
         </is>
       </c>
       <c r="M209" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-20/c07-l-accord-monetaire-international.md</t>
+          <t>corpus/livre-20/c06-les-voies-de-revision-et-leur-cout.md</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" s="2" t="inlineStr">
         <is>
-          <t>L20.C08</t>
+          <t>L20.C07</t>
         </is>
       </c>
       <c r="B210" s="3" t="inlineStr">
@@ -14448,7 +14448,7 @@
       </c>
       <c r="C210" s="3" t="inlineStr">
         <is>
-          <t>La parité inscrite dans le traité</t>
+          <t>L'accord monétaire international</t>
         </is>
       </c>
       <c r="D210" s="3" t="inlineStr">
@@ -14473,35 +14473,35 @@
       </c>
       <c r="H210" s="3" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="I210" s="3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J210" s="3" t="n">
         <v>3</v>
       </c>
       <c r="K210" s="3" t="inlineStr">
         <is>
-          <t>referentiel_de_change, etalon_de_change_or, hierarchie_monetaire, bareme, devise_cle</t>
+          <t>referentiel_de_change, fenetre_de_reforme, etalon_de_change_or, hierarchie_monetaire</t>
         </is>
       </c>
       <c r="L210" s="3" t="inlineStr">
         <is>
-          <t>L1.C25, L1.C26, L1.C28, L7.C02, L7.C20, L11.C15, L11.C17, L20.C01, L20.C09, L20.C13</t>
+          <t>L1.C18, L1.C26, L7.C02, L7.C05, L7.C12, L7.C13, L11.C15, L20.C01, L20.C03, L20.C06, L20.C10</t>
         </is>
       </c>
       <c r="M210" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-20/c08-la-parite-inscrite-dans-le-traite.md</t>
+          <t>corpus/livre-20/c07-l-accord-monetaire-international.md</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" s="2" t="inlineStr">
         <is>
-          <t>L20.C09</t>
+          <t>L20.C08</t>
         </is>
       </c>
       <c r="B211" s="3" t="inlineStr">
@@ -14511,7 +14511,7 @@
       </c>
       <c r="C211" s="3" t="inlineStr">
         <is>
-          <t>L'amendement des statuts du Fonds</t>
+          <t>La parité inscrite dans le traité</t>
         </is>
       </c>
       <c r="D211" s="3" t="inlineStr">
@@ -14536,35 +14536,35 @@
       </c>
       <c r="H211" s="3" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="I211" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J211" s="3" t="n">
         <v>3</v>
       </c>
       <c r="K211" s="3" t="inlineStr">
         <is>
-          <t>fenetre_de_reforme, referentiel_de_change, bareme, regle_contre_discretion</t>
+          <t>referentiel_de_change, etalon_de_change_or, hierarchie_monetaire, bareme, devise_cle</t>
         </is>
       </c>
       <c r="L211" s="3" t="inlineStr">
         <is>
-          <t>L7.C06, L7.C09, L7.C16, L7.C20, L11.C15, L11.C20, L20.C01, L20.C06, L20.C08, L20.C10, L20.C13</t>
+          <t>L1.C25, L1.C26, L1.C28, L7.C02, L7.C20, L11.C15, L11.C17, L20.C01, L20.C09, L20.C13</t>
         </is>
       </c>
       <c r="M211" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-20/c09-l-amendement-des-statuts-du-fonds.md</t>
+          <t>corpus/livre-20/c08-la-parite-inscrite-dans-le-traite.md</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" s="2" t="inlineStr">
         <is>
-          <t>L20.C10</t>
+          <t>L20.C09</t>
         </is>
       </c>
       <c r="B212" s="3" t="inlineStr">
@@ -14574,7 +14574,7 @@
       </c>
       <c r="C212" s="3" t="inlineStr">
         <is>
-          <t>Le vote pondéré et les voix de base</t>
+          <t>L'amendement des statuts du Fonds</t>
         </is>
       </c>
       <c r="D212" s="3" t="inlineStr">
@@ -14610,24 +14610,24 @@
       </c>
       <c r="K212" s="3" t="inlineStr">
         <is>
-          <t>bareme, devise_cle, hierarchie_monetaire, referentiel_de_change</t>
+          <t>fenetre_de_reforme, referentiel_de_change, bareme, regle_contre_discretion</t>
         </is>
       </c>
       <c r="L212" s="3" t="inlineStr">
         <is>
-          <t>L1.C25, L7.C02, L7.C05, L7.C06, L7.C09, L7.C10, L11.C16, L20.C01, L20.C07, L20.C09, L20.C12</t>
+          <t>L7.C06, L7.C09, L7.C16, L7.C20, L11.C15, L11.C20, L20.C01, L20.C06, L20.C08, L20.C10, L20.C13</t>
         </is>
       </c>
       <c r="M212" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-20/c10-le-vote-pondere-et-les-voix-de-base.md</t>
+          <t>corpus/livre-20/c09-l-amendement-des-statuts-du-fonds.md</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" s="2" t="inlineStr">
         <is>
-          <t>L20.C11</t>
+          <t>L20.C10</t>
         </is>
       </c>
       <c r="B213" s="3" t="inlineStr">
@@ -14637,7 +14637,7 @@
       </c>
       <c r="C213" s="3" t="inlineStr">
         <is>
-          <t>La personnalité juridique et les immunités</t>
+          <t>Le vote pondéré et les voix de base</t>
         </is>
       </c>
       <c r="D213" s="3" t="inlineStr">
@@ -14666,31 +14666,31 @@
         </is>
       </c>
       <c r="I213" s="3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J213" s="3" t="n">
         <v>3</v>
       </c>
       <c r="K213" s="3" t="inlineStr">
         <is>
-          <t>communs, creation_monetaire, fenetre_de_reforme, robustesse</t>
+          <t>bareme, devise_cle, hierarchie_monetaire, referentiel_de_change</t>
         </is>
       </c>
       <c r="L213" s="3" t="inlineStr">
         <is>
-          <t>L7.C01, L7.C03, L7.C07, L7.C10, L7.C13, L11.C25, L20.C01, L20.C04, L20.C12, L20.C14</t>
+          <t>L1.C25, L7.C02, L7.C05, L7.C06, L7.C09, L7.C10, L11.C16, L20.C01, L20.C07, L20.C09, L20.C12</t>
         </is>
       </c>
       <c r="M213" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-20/c11-la-personnalite-juridique-et-les-immunites.md</t>
+          <t>corpus/livre-20/c10-le-vote-pondere-et-les-voix-de-base.md</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" s="2" t="inlineStr">
         <is>
-          <t>L20.C12</t>
+          <t>L20.C11</t>
         </is>
       </c>
       <c r="B214" s="3" t="inlineStr">
@@ -14700,7 +14700,7 @@
       </c>
       <c r="C214" s="3" t="inlineStr">
         <is>
-          <t>Les pouvoirs non délégables</t>
+          <t>La personnalité juridique et les immunités</t>
         </is>
       </c>
       <c r="D214" s="3" t="inlineStr">
@@ -14725,35 +14725,35 @@
       </c>
       <c r="H214" s="3" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="I214" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J214" s="3" t="n">
         <v>3</v>
       </c>
       <c r="K214" s="3" t="inlineStr">
         <is>
-          <t>bareme, valorisation_des_communs, polycentricite, robustesse</t>
+          <t>communs, creation_monetaire, fenetre_de_reforme, robustesse</t>
         </is>
       </c>
       <c r="L214" s="3" t="inlineStr">
         <is>
-          <t>L7.C05, L7.C06, L7.C07, L7.C11, L7.C14, L11.C16, L11.C20, L20.C01, L20.C09, L20.C10, L20.C14</t>
+          <t>L7.C01, L7.C03, L7.C07, L7.C10, L7.C13, L11.C25, L20.C01, L20.C04, L20.C12, L20.C14</t>
         </is>
       </c>
       <c r="M214" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-20/c12-les-pouvoirs-non-delegables.md</t>
+          <t>corpus/livre-20/c11-la-personnalite-juridique-et-les-immunites.md</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" s="2" t="inlineStr">
         <is>
-          <t>L20.C13</t>
+          <t>L20.C12</t>
         </is>
       </c>
       <c r="B215" s="3" t="inlineStr">
@@ -14763,7 +14763,7 @@
       </c>
       <c r="C215" s="3" t="inlineStr">
         <is>
-          <t>L'entrée en vigueur, l'adhésion et le retrait</t>
+          <t>Les pouvoirs non délégables</t>
         </is>
       </c>
       <c r="D215" s="3" t="inlineStr">
@@ -14792,31 +14792,31 @@
         </is>
       </c>
       <c r="I215" s="3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J215" s="3" t="n">
         <v>3</v>
       </c>
       <c r="K215" s="3" t="inlineStr">
         <is>
-          <t>seuil_d_activation, reflux_collectif, fenetre_de_reforme, additionnalite</t>
+          <t>bareme, valorisation_des_communs, polycentricite, robustesse</t>
         </is>
       </c>
       <c r="L215" s="3" t="inlineStr">
         <is>
-          <t>L7.C11, L7.C12, L7.C16, L7.C17, L7.C19, L11.C18, L20.C01, L20.C06, L20.C09, L20.C12</t>
+          <t>L7.C05, L7.C06, L7.C07, L7.C11, L7.C14, L11.C16, L11.C20, L20.C01, L20.C09, L20.C10, L20.C14</t>
         </is>
       </c>
       <c r="M215" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-20/c13-l-entree-en-vigueur-l-adhesion-et-le-retrait.md</t>
+          <t>corpus/livre-20/c12-les-pouvoirs-non-delegables.md</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" s="2" t="inlineStr">
         <is>
-          <t>L20.C14</t>
+          <t>L20.C13</t>
         </is>
       </c>
       <c r="B216" s="3" t="inlineStr">
@@ -14826,7 +14826,7 @@
       </c>
       <c r="C216" s="3" t="inlineStr">
         <is>
-          <t>Qui interprète le traité</t>
+          <t>L'entrée en vigueur, l'adhésion et le retrait</t>
         </is>
       </c>
       <c r="D216" s="3" t="inlineStr">
@@ -14855,31 +14855,31 @@
         </is>
       </c>
       <c r="I216" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J216" s="3" t="n">
         <v>3</v>
       </c>
       <c r="K216" s="3" t="inlineStr">
         <is>
-          <t>robustesse, regle_contre_discretion, communs</t>
+          <t>seuil_d_activation, reflux_collectif, fenetre_de_reforme, additionnalite</t>
         </is>
       </c>
       <c r="L216" s="3" t="inlineStr">
         <is>
-          <t>L7.C07, L7.C13, L7.C14, L7.C19, L11.C19, L11.C25, L20.C01, L20.C03, L20.C11, L20.C12, L20.C21</t>
+          <t>L7.C11, L7.C12, L7.C16, L7.C17, L7.C19, L11.C18, L20.C01, L20.C06, L20.C09, L20.C12</t>
         </is>
       </c>
       <c r="M216" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-20/c14-qui-interprete-le-traite.md</t>
+          <t>corpus/livre-20/c13-l-entree-en-vigueur-l-adhesion-et-le-retrait.md</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" s="2" t="inlineStr">
         <is>
-          <t>L20.C15</t>
+          <t>L20.C14</t>
         </is>
       </c>
       <c r="B217" s="3" t="inlineStr">
@@ -14889,7 +14889,7 @@
       </c>
       <c r="C217" s="3" t="inlineStr">
         <is>
-          <t>Le devoir international des agents</t>
+          <t>Qui interprète le traité</t>
         </is>
       </c>
       <c r="D217" s="3" t="inlineStr">
@@ -14914,35 +14914,35 @@
       </c>
       <c r="H217" s="3" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="I217" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J217" s="3" t="n">
         <v>3</v>
       </c>
       <c r="K217" s="3" t="inlineStr">
         <is>
-          <t>robustesse, regle_contre_discretion, indicateur_de_progres</t>
+          <t>robustesse, regle_contre_discretion, communs</t>
         </is>
       </c>
       <c r="L217" s="3" t="inlineStr">
         <is>
-          <t>L7.C04, L7.C07, L7.C10, L11.C21, L11.C25, L20.C01, L20.C04, L20.C11, L20.C14</t>
+          <t>L7.C07, L7.C13, L7.C14, L7.C19, L11.C19, L11.C25, L20.C01, L20.C03, L20.C11, L20.C12, L20.C21</t>
         </is>
       </c>
       <c r="M217" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-20/c15-le-devoir-international-des-agents.md</t>
+          <t>corpus/livre-20/c14-qui-interprete-le-traite.md</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" s="2" t="inlineStr">
         <is>
-          <t>L20.C16</t>
+          <t>L20.C15</t>
         </is>
       </c>
       <c r="B218" s="3" t="inlineStr">
@@ -14952,7 +14952,7 @@
       </c>
       <c r="C218" s="3" t="inlineStr">
         <is>
-          <t>Le patrimoine commun de l'humanité</t>
+          <t>Le devoir international des agents</t>
         </is>
       </c>
       <c r="D218" s="3" t="inlineStr">
@@ -14977,35 +14977,35 @@
       </c>
       <c r="H218" s="3" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="I218" s="3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J218" s="3" t="n">
         <v>3</v>
       </c>
       <c r="K218" s="3" t="inlineStr">
         <is>
-          <t>communs, valorisation_des_communs, limites_planetaires, additionnalite, plafond_ecologique</t>
+          <t>robustesse, regle_contre_discretion, indicateur_de_progres</t>
         </is>
       </c>
       <c r="L218" s="3" t="inlineStr">
         <is>
-          <t>L1.C17, L1.C22, L7.C05, L7.C13, L11.C16, L20.C01, L20.C11, L20.C17, L20.C22</t>
+          <t>L7.C04, L7.C07, L7.C10, L11.C21, L11.C25, L20.C01, L20.C04, L20.C11, L20.C14</t>
         </is>
       </c>
       <c r="M218" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-20/c16-le-patrimoine-commun-de-l-humanite.md</t>
+          <t>corpus/livre-20/c15-le-devoir-international-des-agents.md</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" s="2" t="inlineStr">
         <is>
-          <t>L20.C17</t>
+          <t>L20.C16</t>
         </is>
       </c>
       <c r="B219" s="3" t="inlineStr">
@@ -15015,7 +15015,7 @@
       </c>
       <c r="C219" s="3" t="inlineStr">
         <is>
-          <t>La sanctuarisation, et elle existe</t>
+          <t>Le patrimoine commun de l'humanité</t>
         </is>
       </c>
       <c r="D219" s="3" t="inlineStr">
@@ -15044,31 +15044,31 @@
         </is>
       </c>
       <c r="I219" s="3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J219" s="3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K219" s="3" t="inlineStr">
         <is>
-          <t>communs, limites_planetaires, fenetre_de_reforme, robustesse, plafond_ecologique</t>
+          <t>communs, valorisation_des_communs, limites_planetaires, additionnalite, plafond_ecologique</t>
         </is>
       </c>
       <c r="L219" s="3" t="inlineStr">
         <is>
-          <t>L1.C17, L1.C18, L7.C13, L7.C19, L7.C20, L11.C20, L20.C01, L20.C06, L20.C09, L20.C16, L20.C22</t>
+          <t>L1.C17, L1.C22, L7.C05, L7.C13, L11.C16, L20.C01, L20.C11, L20.C17, L20.C22</t>
         </is>
       </c>
       <c r="M219" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-20/c17-la-sanctuarisation-et-elle-existe.md</t>
+          <t>corpus/livre-20/c16-le-patrimoine-commun-de-l-humanite.md</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" s="2" t="inlineStr">
         <is>
-          <t>L20.C18</t>
+          <t>L20.C17</t>
         </is>
       </c>
       <c r="B220" s="3" t="inlineStr">
@@ -15078,7 +15078,7 @@
       </c>
       <c r="C220" s="3" t="inlineStr">
         <is>
-          <t>L'amendement et la dérogation dans l'ordre commercial</t>
+          <t>La sanctuarisation, et elle existe</t>
         </is>
       </c>
       <c r="D220" s="3" t="inlineStr">
@@ -15103,35 +15103,35 @@
       </c>
       <c r="H220" s="3" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="I220" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J220" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K220" s="3" t="inlineStr">
         <is>
-          <t>bareme, seuil_d_activation, additionnalite, fenetre_de_reforme</t>
+          <t>communs, limites_planetaires, fenetre_de_reforme, robustesse, plafond_ecologique</t>
         </is>
       </c>
       <c r="L220" s="3" t="inlineStr">
         <is>
-          <t>L1.C27, L7.C17, L7.C20, L11.C24, L20.C01, L20.C06, L20.C09, L20.C13, L20.C19, L20.C20</t>
+          <t>L1.C17, L1.C18, L7.C13, L7.C19, L7.C20, L11.C20, L20.C01, L20.C06, L20.C09, L20.C16, L20.C22</t>
         </is>
       </c>
       <c r="M220" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-20/c18-l-amendement-et-la-derogation-dans-l-ordre-commercial.md</t>
+          <t>corpus/livre-20/c17-la-sanctuarisation-et-elle-existe.md</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" s="2" t="inlineStr">
         <is>
-          <t>L20.C19</t>
+          <t>L20.C18</t>
         </is>
       </c>
       <c r="B221" s="3" t="inlineStr">
@@ -15141,7 +15141,7 @@
       </c>
       <c r="C221" s="3" t="inlineStr">
         <is>
-          <t>Le texte que la conformité invoque</t>
+          <t>L'amendement et la dérogation dans l'ordre commercial</t>
         </is>
       </c>
       <c r="D221" s="3" t="inlineStr">
@@ -15166,35 +15166,35 @@
       </c>
       <c r="H221" s="3" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="I221" s="3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J221" s="3" t="n">
         <v>3</v>
       </c>
       <c r="K221" s="3" t="inlineStr">
         <is>
-          <t>bareme, additionnalite, limites_planetaires, seuil_d_activation, externalisation</t>
+          <t>bareme, seuil_d_activation, additionnalite, fenetre_de_reforme</t>
         </is>
       </c>
       <c r="L221" s="3" t="inlineStr">
         <is>
-          <t>L1.C27, L7.C17, L11.C24, L20.C01, L20.C18, L20.C20, L20.C22</t>
+          <t>L1.C27, L7.C17, L7.C20, L11.C24, L20.C01, L20.C06, L20.C09, L20.C13, L20.C19, L20.C20</t>
         </is>
       </c>
       <c r="M221" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-20/c19-le-texte-que-la-conformite-invoque.md</t>
+          <t>corpus/livre-20/c18-l-amendement-et-la-derogation-dans-l-ordre-commercial.md</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" s="2" t="inlineStr">
         <is>
-          <t>L20.C20</t>
+          <t>L20.C19</t>
         </is>
       </c>
       <c r="B222" s="3" t="inlineStr">
@@ -15204,7 +15204,7 @@
       </c>
       <c r="C222" s="3" t="inlineStr">
         <is>
-          <t>L'ajustement aux frontières comme précédent</t>
+          <t>Le texte que la conformité invoque</t>
         </is>
       </c>
       <c r="D222" s="3" t="inlineStr">
@@ -15229,7 +15229,7 @@
       </c>
       <c r="H222" s="3" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="I222" s="3" t="n">
@@ -15240,24 +15240,24 @@
       </c>
       <c r="K222" s="3" t="inlineStr">
         <is>
-          <t>bareme, seuil_d_activation, externalisation, additionnalite, contrepartie_comptable</t>
+          <t>bareme, additionnalite, limites_planetaires, seuil_d_activation, externalisation</t>
         </is>
       </c>
       <c r="L222" s="3" t="inlineStr">
         <is>
-          <t>L1.C27, L7.C17, L11.C21, L11.C24, L11.C25, L20.C01, L20.C18, L20.C19, L20.C22</t>
+          <t>L1.C27, L7.C17, L11.C24, L20.C01, L20.C18, L20.C20, L20.C22</t>
         </is>
       </c>
       <c r="M222" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-20/c20-l-ajustement-aux-frontieres-comme-precedent.md</t>
+          <t>corpus/livre-20/c19-le-texte-que-la-conformite-invoque.md</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" s="2" t="inlineStr">
         <is>
-          <t>L20.C21</t>
+          <t>L20.C20</t>
         </is>
       </c>
       <c r="B223" s="3" t="inlineStr">
@@ -15267,7 +15267,7 @@
       </c>
       <c r="C223" s="3" t="inlineStr">
         <is>
-          <t>La transparence et sa limite juridictionnelle</t>
+          <t>L'ajustement aux frontières comme précédent</t>
         </is>
       </c>
       <c r="D223" s="3" t="inlineStr">
@@ -15296,31 +15296,31 @@
         </is>
       </c>
       <c r="I223" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J223" s="3" t="n">
         <v>3</v>
       </c>
       <c r="K223" s="3" t="inlineStr">
         <is>
-          <t>robustesse, contrepartie_comptable, bareme, monnaie_comme_registre</t>
+          <t>bareme, seuil_d_activation, externalisation, additionnalite, contrepartie_comptable</t>
         </is>
       </c>
       <c r="L223" s="3" t="inlineStr">
         <is>
-          <t>L7.C18, L11.C21, L11.C24, L11.C25, L20.C01, L20.C11, L20.C14, L20.C20, L20.C22</t>
+          <t>L1.C27, L7.C17, L11.C21, L11.C24, L11.C25, L20.C01, L20.C18, L20.C19, L20.C22</t>
         </is>
       </c>
       <c r="M223" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-20/c21-la-transparence-et-sa-limite-juridictionnelle.md</t>
+          <t>corpus/livre-20/c20-l-ajustement-aux-frontieres-comme-precedent.md</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" s="2" t="inlineStr">
         <is>
-          <t>L20.C22</t>
+          <t>L20.C21</t>
         </is>
       </c>
       <c r="B224" s="3" t="inlineStr">
@@ -15330,7 +15330,7 @@
       </c>
       <c r="C224" s="3" t="inlineStr">
         <is>
-          <t>Ce que le droit devrait devenir</t>
+          <t>La transparence et sa limite juridictionnelle</t>
         </is>
       </c>
       <c r="D224" s="3" t="inlineStr">
@@ -15366,85 +15366,148 @@
       </c>
       <c r="K224" s="3" t="inlineStr">
         <is>
-          <t>fenetre_de_reforme, communs, limites_planetaires, regle_contre_discretion, bareme, referentiel_de_change</t>
+          <t>robustesse, contrepartie_comptable, bareme, monnaie_comme_registre</t>
         </is>
       </c>
       <c r="L224" s="3" t="inlineStr">
         <is>
-          <t>L1.C18, L7.C12, L7.C13, L11.C15, L11.C25, L20.C01, L20.C03, L20.C06, L20.C07, L20.C08, L20.C12, L20.C13, L20.C16, L20.C17, L20.C19, L20.C20, L20.C21, L20.C23</t>
+          <t>L7.C18, L11.C21, L11.C24, L11.C25, L20.C01, L20.C11, L20.C14, L20.C20, L20.C22</t>
         </is>
       </c>
       <c r="M224" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-20/c22-ce-que-le-droit-devrait-devenir.md</t>
+          <t>corpus/livre-20/c21-la-transparence-et-sa-limite-juridictionnelle.md</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" s="2" t="inlineStr">
         <is>
+          <t>L20.C22</t>
+        </is>
+      </c>
+      <c r="B225" s="3" t="inlineStr">
+        <is>
+          <t>L20</t>
+        </is>
+      </c>
+      <c r="C225" s="3" t="inlineStr">
+        <is>
+          <t>Ce que le droit devrait devenir</t>
+        </is>
+      </c>
+      <c r="D225" s="3" t="inlineStr">
+        <is>
+          <t>brouillon</t>
+        </is>
+      </c>
+      <c r="E225" s="3" t="inlineStr">
+        <is>
+          <t>preparatoire</t>
+        </is>
+      </c>
+      <c r="F225" s="3" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="G225" s="3" t="inlineStr">
+        <is>
+          <t>conception</t>
+        </is>
+      </c>
+      <c r="H225" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="I225" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="J225" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="K225" s="3" t="inlineStr">
+        <is>
+          <t>fenetre_de_reforme, communs, limites_planetaires, regle_contre_discretion, bareme, referentiel_de_change</t>
+        </is>
+      </c>
+      <c r="L225" s="3" t="inlineStr">
+        <is>
+          <t>L1.C18, L7.C12, L7.C13, L11.C15, L11.C25, L20.C01, L20.C03, L20.C06, L20.C07, L20.C08, L20.C12, L20.C13, L20.C16, L20.C17, L20.C19, L20.C20, L20.C21, L20.C23</t>
+        </is>
+      </c>
+      <c r="M225" s="3" t="inlineStr">
+        <is>
+          <t>corpus/livre-20/c22-ce-que-le-droit-devrait-devenir.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" s="2" t="inlineStr">
+        <is>
           <t>L20.C23</t>
         </is>
       </c>
-      <c r="B225" s="3" t="inlineStr">
+      <c r="B226" s="3" t="inlineStr">
         <is>
           <t>L20</t>
         </is>
       </c>
-      <c r="C225" s="3" t="inlineStr">
+      <c r="C226" s="3" t="inlineStr">
         <is>
           <t>La portée du livre</t>
         </is>
       </c>
-      <c r="D225" s="3" t="inlineStr">
-        <is>
-          <t>brouillon</t>
-        </is>
-      </c>
-      <c r="E225" s="3" t="inlineStr">
-        <is>
-          <t>preparatoire</t>
-        </is>
-      </c>
-      <c r="F225" s="3" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="G225" s="3" t="inlineStr">
+      <c r="D226" s="3" t="inlineStr">
+        <is>
+          <t>brouillon</t>
+        </is>
+      </c>
+      <c r="E226" s="3" t="inlineStr">
+        <is>
+          <t>preparatoire</t>
+        </is>
+      </c>
+      <c r="F226" s="3" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="G226" s="3" t="inlineStr">
         <is>
           <t>conception</t>
         </is>
       </c>
-      <c r="H225" s="3" t="inlineStr">
+      <c r="H226" s="3" t="inlineStr">
         <is>
           <t>2026-09-06</t>
         </is>
       </c>
-      <c r="I225" s="3" t="n">
+      <c r="I226" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="J225" s="3" t="n">
+      <c r="J226" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="K225" s="3" t="inlineStr">
+      <c r="K226" s="3" t="inlineStr">
         <is>
           <t>fenetre_de_reforme, communs, limites_planetaires, creation_monetaire, robustesse</t>
         </is>
       </c>
-      <c r="L225" s="3" t="inlineStr">
+      <c r="L226" s="3" t="inlineStr">
         <is>
           <t>L1.C18, L1.C27, L7.C05, L7.C10, L7.C12, L7.C13, L11.C15, L11.C24, L11.C25, L20.C01, L20.C02, L20.C03, L20.C06, L20.C07, L20.C08, L20.C11, L20.C12, L20.C13, L20.C16, L20.C17, L20.C19, L20.C20, L20.C21, L20.C22</t>
         </is>
       </c>
-      <c r="M225" s="3" t="inlineStr">
+      <c r="M226" s="3" t="inlineStr">
         <is>
           <t>corpus/livre-20/c23-la-portee-du-livre.md</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:M225"/>
+  <autoFilter ref="A1:M226"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -15523,7 +15586,7 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>224</v>
+        <v>225</v>
       </c>
     </row>
     <row r="7">
@@ -15533,7 +15596,7 @@
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>215</v>
+        <v>216</v>
       </c>
     </row>
     <row r="8">
@@ -15553,7 +15616,7 @@
         </is>
       </c>
       <c r="B9" s="3" t="n">
-        <v>1134</v>
+        <v>1137</v>
       </c>
     </row>
     <row r="10">
@@ -15563,7 +15626,7 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>942</v>
+        <v>945</v>
       </c>
     </row>
     <row r="11">
@@ -15645,7 +15708,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C253"/>
+  <dimension ref="A1:C254"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -18574,7 +18637,7 @@
       </c>
       <c r="C173" s="6" t="inlineStr">
         <is>
-          <t>en-cours — 5 chapitre(s)</t>
+          <t>en-cours — 6 chapitre(s)</t>
         </is>
       </c>
     </row>
@@ -18664,48 +18727,48 @@
       </c>
     </row>
     <row r="179">
-      <c r="A179" s="6" t="inlineStr">
+      <c r="A179" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    L10.C06</t>
+        </is>
+      </c>
+      <c r="B179" s="3" t="inlineStr">
+        <is>
+          <t>L'arbitrage A35, et ce qu'il déplace</t>
+        </is>
+      </c>
+      <c r="C179" s="3" t="inlineStr">
+        <is>
+          <t>brouillon</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" s="6" t="inlineStr">
         <is>
           <t>L11</t>
         </is>
       </c>
-      <c r="B179" s="6" t="inlineStr">
+      <c r="B180" s="6" t="inlineStr">
         <is>
           <t>Ingénierie des barèmes : reflux, qualification, périmètre et pondérations</t>
         </is>
       </c>
-      <c r="C179" s="6" t="inlineStr">
+      <c r="C180" s="6" t="inlineStr">
         <is>
           <t>defrichage — 29 chapitre(s)</t>
-        </is>
-      </c>
-    </row>
-    <row r="180">
-      <c r="A180" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    L11.C01</t>
-        </is>
-      </c>
-      <c r="B180" s="3" t="inlineStr">
-        <is>
-          <t>Reflux ou destruction — la bifurcation</t>
-        </is>
-      </c>
-      <c r="C180" s="3" t="inlineStr">
-        <is>
-          <t>brouillon</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L11.C02</t>
+          <t xml:space="preserve">    L11.C01</t>
         </is>
       </c>
       <c r="B181" s="3" t="inlineStr">
         <is>
-          <t>Le trajet complet de la valeur</t>
+          <t>Reflux ou destruction — la bifurcation</t>
         </is>
       </c>
       <c r="C181" s="3" t="inlineStr">
@@ -18717,12 +18780,12 @@
     <row r="182">
       <c r="A182" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L11.C03</t>
+          <t xml:space="preserve">    L11.C02</t>
         </is>
       </c>
       <c r="B182" s="3" t="inlineStr">
         <is>
-          <t>Le compte des objectifs et des instruments</t>
+          <t>Le trajet complet de la valeur</t>
         </is>
       </c>
       <c r="C182" s="3" t="inlineStr">
@@ -18734,12 +18797,12 @@
     <row r="183">
       <c r="A183" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L11.C04</t>
+          <t xml:space="preserve">    L11.C03</t>
         </is>
       </c>
       <c r="B183" s="3" t="inlineStr">
         <is>
-          <t>Les instruments du reflux sous parité fixe</t>
+          <t>Le compte des objectifs et des instruments</t>
         </is>
       </c>
       <c r="C183" s="3" t="inlineStr">
@@ -18751,12 +18814,12 @@
     <row r="184">
       <c r="A184" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L11.C05</t>
+          <t xml:space="preserve">    L11.C04</t>
         </is>
       </c>
       <c r="B184" s="3" t="inlineStr">
         <is>
-          <t>L'assiette du reflux transactionnel</t>
+          <t>Les instruments du reflux sous parité fixe</t>
         </is>
       </c>
       <c r="C184" s="3" t="inlineStr">
@@ -18768,12 +18831,12 @@
     <row r="185">
       <c r="A185" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L11.C06</t>
+          <t xml:space="preserve">    L11.C05</t>
         </is>
       </c>
       <c r="B185" s="3" t="inlineStr">
         <is>
-          <t>Le barème par défaut</t>
+          <t>L'assiette du reflux transactionnel</t>
         </is>
       </c>
       <c r="C185" s="3" t="inlineStr">
@@ -18785,12 +18848,12 @@
     <row r="186">
       <c r="A186" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L11.C07</t>
+          <t xml:space="preserve">    L11.C06</t>
         </is>
       </c>
       <c r="B186" s="3" t="inlineStr">
         <is>
-          <t>Le demurrage et son nœud de prélèvement</t>
+          <t>Le barème par défaut</t>
         </is>
       </c>
       <c r="C186" s="3" t="inlineStr">
@@ -18802,12 +18865,12 @@
     <row r="187">
       <c r="A187" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L11.C08</t>
+          <t xml:space="preserve">    L11.C07</t>
         </is>
       </c>
       <c r="B187" s="3" t="inlineStr">
         <is>
-          <t>Les dérogations</t>
+          <t>Le demurrage et son nœud de prélèvement</t>
         </is>
       </c>
       <c r="C187" s="3" t="inlineStr">
@@ -18819,12 +18882,12 @@
     <row r="188">
       <c r="A188" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L11.C09</t>
+          <t xml:space="preserve">    L11.C08</t>
         </is>
       </c>
       <c r="B188" s="3" t="inlineStr">
         <is>
-          <t>L'incidence — qui paie le reflux</t>
+          <t>Les dérogations</t>
         </is>
       </c>
       <c r="C188" s="3" t="inlineStr">
@@ -18836,12 +18899,12 @@
     <row r="189">
       <c r="A189" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L11.C10</t>
+          <t xml:space="preserve">    L11.C09</t>
         </is>
       </c>
       <c r="B189" s="3" t="inlineStr">
         <is>
-          <t>La trajectoire de mise en place</t>
+          <t>L'incidence — qui paie le reflux</t>
         </is>
       </c>
       <c r="C189" s="3" t="inlineStr">
@@ -18853,12 +18916,12 @@
     <row r="190">
       <c r="A190" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L11.C11</t>
+          <t xml:space="preserve">    L11.C10</t>
         </is>
       </c>
       <c r="B190" s="3" t="inlineStr">
         <is>
-          <t>Qui arrête le barème</t>
+          <t>La trajectoire de mise en place</t>
         </is>
       </c>
       <c r="C190" s="3" t="inlineStr">
@@ -18870,12 +18933,12 @@
     <row r="191">
       <c r="A191" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L11.C12</t>
+          <t xml:space="preserve">    L11.C11</t>
         </is>
       </c>
       <c r="B191" s="3" t="inlineStr">
         <is>
-          <t>La directive</t>
+          <t>Qui arrête le barème</t>
         </is>
       </c>
       <c r="C191" s="3" t="inlineStr">
@@ -18887,12 +18950,12 @@
     <row r="192">
       <c r="A192" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L11.C13</t>
+          <t xml:space="preserve">    L11.C12</t>
         </is>
       </c>
       <c r="B192" s="3" t="inlineStr">
         <is>
-          <t>Le barème de qualification</t>
+          <t>La directive</t>
         </is>
       </c>
       <c r="C192" s="3" t="inlineStr">
@@ -18904,12 +18967,12 @@
     <row r="193">
       <c r="A193" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L11.C14</t>
+          <t xml:space="preserve">    L11.C13</t>
         </is>
       </c>
       <c r="B193" s="3" t="inlineStr">
         <is>
-          <t>Le tableau de bord, ou les données de la directive</t>
+          <t>Le barème de qualification</t>
         </is>
       </c>
       <c r="C193" s="3" t="inlineStr">
@@ -18921,12 +18984,12 @@
     <row r="194">
       <c r="A194" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L11.C15</t>
+          <t xml:space="preserve">    L11.C14</t>
         </is>
       </c>
       <c r="B194" s="3" t="inlineStr">
         <is>
-          <t>Les parités du référentiel de change</t>
+          <t>Le tableau de bord, ou les données de la directive</t>
         </is>
       </c>
       <c r="C194" s="3" t="inlineStr">
@@ -18938,12 +19001,12 @@
     <row r="195">
       <c r="A195" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L11.C16</t>
+          <t xml:space="preserve">    L11.C15</t>
         </is>
       </c>
       <c r="B195" s="3" t="inlineStr">
         <is>
-          <t>La valorisation des communs</t>
+          <t>Les parités du référentiel de change</t>
         </is>
       </c>
       <c r="C195" s="3" t="inlineStr">
@@ -18955,12 +19018,12 @@
     <row r="196">
       <c r="A196" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L11.C17</t>
+          <t xml:space="preserve">    L11.C16</t>
         </is>
       </c>
       <c r="B196" s="3" t="inlineStr">
         <is>
-          <t>La cohérence des cinq barèmes</t>
+          <t>La valorisation des communs</t>
         </is>
       </c>
       <c r="C196" s="3" t="inlineStr">
@@ -18972,12 +19035,12 @@
     <row r="197">
       <c r="A197" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L11.C18</t>
+          <t xml:space="preserve">    L11.C17</t>
         </is>
       </c>
       <c r="B197" s="3" t="inlineStr">
         <is>
-          <t>Le seuil d'exemption</t>
+          <t>La cohérence des cinq barèmes</t>
         </is>
       </c>
       <c r="C197" s="3" t="inlineStr">
@@ -18989,12 +19052,12 @@
     <row r="198">
       <c r="A198" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L11.C19</t>
+          <t xml:space="preserve">    L11.C18</t>
         </is>
       </c>
       <c r="B198" s="3" t="inlineStr">
         <is>
-          <t>Le recours</t>
+          <t>Le seuil d'exemption</t>
         </is>
       </c>
       <c r="C198" s="3" t="inlineStr">
@@ -19006,12 +19069,12 @@
     <row r="199">
       <c r="A199" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L11.C20</t>
+          <t xml:space="preserve">    L11.C19</t>
         </is>
       </c>
       <c r="B199" s="3" t="inlineStr">
         <is>
-          <t>L'amendement de la directive</t>
+          <t>Le recours</t>
         </is>
       </c>
       <c r="C199" s="3" t="inlineStr">
@@ -19023,12 +19086,12 @@
     <row r="200">
       <c r="A200" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L11.C21</t>
+          <t xml:space="preserve">    L11.C20</t>
         </is>
       </c>
       <c r="B200" s="3" t="inlineStr">
         <is>
-          <t>La perception</t>
+          <t>L'amendement de la directive</t>
         </is>
       </c>
       <c r="C200" s="3" t="inlineStr">
@@ -19040,12 +19103,12 @@
     <row r="201">
       <c r="A201" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L11.C22</t>
+          <t xml:space="preserve">    L11.C21</t>
         </is>
       </c>
       <c r="B201" s="3" t="inlineStr">
         <is>
-          <t>Les délais</t>
+          <t>La perception</t>
         </is>
       </c>
       <c r="C201" s="3" t="inlineStr">
@@ -19057,12 +19120,12 @@
     <row r="202">
       <c r="A202" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L11.C23</t>
+          <t xml:space="preserve">    L11.C22</t>
         </is>
       </c>
       <c r="B202" s="3" t="inlineStr">
         <is>
-          <t>La contracyclicité</t>
+          <t>Les délais</t>
         </is>
       </c>
       <c r="C202" s="3" t="inlineStr">
@@ -19074,12 +19137,12 @@
     <row r="203">
       <c r="A203" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L11.C24</t>
+          <t xml:space="preserve">    L11.C23</t>
         </is>
       </c>
       <c r="B203" s="3" t="inlineStr">
         <is>
-          <t>Le barème aux frontières</t>
+          <t>La contracyclicité</t>
         </is>
       </c>
       <c r="C203" s="3" t="inlineStr">
@@ -19091,12 +19154,12 @@
     <row r="204">
       <c r="A204" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L11.C25</t>
+          <t xml:space="preserve">    L11.C24</t>
         </is>
       </c>
       <c r="B204" s="3" t="inlineStr">
         <is>
-          <t>Le contrôle</t>
+          <t>Le barème aux frontières</t>
         </is>
       </c>
       <c r="C204" s="3" t="inlineStr">
@@ -19108,12 +19171,12 @@
     <row r="205">
       <c r="A205" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L11.C26</t>
+          <t xml:space="preserve">    L11.C25</t>
         </is>
       </c>
       <c r="B205" s="3" t="inlineStr">
         <is>
-          <t>La portée du Livre 11</t>
+          <t>Le contrôle</t>
         </is>
       </c>
       <c r="C205" s="3" t="inlineStr">
@@ -19125,12 +19188,12 @@
     <row r="206">
       <c r="A206" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L11.C27</t>
+          <t xml:space="preserve">    L11.C26</t>
         </is>
       </c>
       <c r="B206" s="3" t="inlineStr">
         <is>
-          <t>L'assiette de la fonte est celle de la TVA</t>
+          <t>La portée du Livre 11</t>
         </is>
       </c>
       <c r="C206" s="3" t="inlineStr">
@@ -19142,12 +19205,12 @@
     <row r="207">
       <c r="A207" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L11.C28</t>
+          <t xml:space="preserve">    L11.C27</t>
         </is>
       </c>
       <c r="B207" s="3" t="inlineStr">
         <is>
-          <t>La fonte sur les acquisitions d'actifs, éprouvée</t>
+          <t>L'assiette de la fonte est celle de la TVA</t>
         </is>
       </c>
       <c r="C207" s="3" t="inlineStr">
@@ -19159,219 +19222,219 @@
     <row r="208">
       <c r="A208" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">    L11.C28</t>
+        </is>
+      </c>
+      <c r="B208" s="3" t="inlineStr">
+        <is>
+          <t>La fonte sur les acquisitions d'actifs, éprouvée</t>
+        </is>
+      </c>
+      <c r="C208" s="3" t="inlineStr">
+        <is>
+          <t>brouillon</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">    L11.C29</t>
         </is>
       </c>
-      <c r="B208" s="3" t="inlineStr">
+      <c r="B209" s="3" t="inlineStr">
         <is>
           <t>La structure des sanctions</t>
         </is>
       </c>
-      <c r="C208" s="3" t="inlineStr">
-        <is>
-          <t>brouillon</t>
-        </is>
-      </c>
-    </row>
-    <row r="209">
-      <c r="A209" s="6" t="inlineStr">
+      <c r="C209" s="3" t="inlineStr">
+        <is>
+          <t>brouillon</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" s="6" t="inlineStr">
         <is>
           <t>L12</t>
         </is>
       </c>
-      <c r="B209" s="6" t="inlineStr">
+      <c r="B210" s="6" t="inlineStr">
         <is>
           <t>Comment réaliser les ODD avec NEMO IMS ?</t>
         </is>
       </c>
-      <c r="C209" s="6" t="inlineStr">
+      <c r="C210" s="6" t="inlineStr">
         <is>
           <t>candidat — 0 chapitre(s)</t>
         </is>
       </c>
     </row>
-    <row r="210">
-      <c r="A210" s="7" t="inlineStr"/>
-      <c r="B210" s="7" t="inlineStr">
+    <row r="211">
+      <c r="A211" s="7" t="inlineStr"/>
+      <c r="B211" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">    (aucun chapitre écrit)</t>
         </is>
       </c>
-      <c r="C210" s="7" t="inlineStr"/>
-    </row>
-    <row r="211">
-      <c r="A211" s="6" t="inlineStr">
+      <c r="C211" s="7" t="inlineStr"/>
+    </row>
+    <row r="212">
+      <c r="A212" s="6" t="inlineStr">
         <is>
           <t>L13</t>
         </is>
       </c>
-      <c r="B211" s="6" t="inlineStr">
+      <c r="B212" s="6" t="inlineStr">
         <is>
           <t>Méthodes, données, scénarios et simulateur NEMO IMS</t>
         </is>
       </c>
-      <c r="C211" s="6" t="inlineStr">
+      <c r="C212" s="6" t="inlineStr">
         <is>
           <t>candidat — 0 chapitre(s)</t>
         </is>
       </c>
     </row>
-    <row r="212">
-      <c r="A212" s="7" t="inlineStr"/>
-      <c r="B212" s="7" t="inlineStr">
+    <row r="213">
+      <c r="A213" s="7" t="inlineStr"/>
+      <c r="B213" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">    (aucun chapitre écrit)</t>
         </is>
       </c>
-      <c r="C212" s="7" t="inlineStr"/>
-    </row>
-    <row r="213">
-      <c r="A213" s="6" t="inlineStr">
+      <c r="C213" s="7" t="inlineStr"/>
+    </row>
+    <row r="214">
+      <c r="A214" s="6" t="inlineStr">
         <is>
           <t>L14</t>
         </is>
       </c>
-      <c r="B213" s="6" t="inlineStr">
+      <c r="B214" s="6" t="inlineStr">
         <is>
           <t>Gouverner la preuve : méthodes, vérification et traçabilité</t>
         </is>
       </c>
-      <c r="C213" s="6" t="inlineStr">
+      <c r="C214" s="6" t="inlineStr">
         <is>
           <t>candidat — 0 chapitre(s)</t>
         </is>
       </c>
     </row>
-    <row r="214">
-      <c r="A214" s="7" t="inlineStr"/>
-      <c r="B214" s="7" t="inlineStr">
+    <row r="215">
+      <c r="A215" s="7" t="inlineStr"/>
+      <c r="B215" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">    (aucun chapitre écrit)</t>
         </is>
       </c>
-      <c r="C214" s="7" t="inlineStr"/>
-    </row>
-    <row r="215">
-      <c r="A215" s="6" t="inlineStr">
+      <c r="C215" s="7" t="inlineStr"/>
+    </row>
+    <row r="216">
+      <c r="A216" s="6" t="inlineStr">
         <is>
           <t>L15</t>
         </is>
       </c>
-      <c r="B215" s="6" t="inlineStr">
+      <c r="B216" s="6" t="inlineStr">
         <is>
           <t>Fraudes, corruptions et architectures de la triche</t>
         </is>
       </c>
-      <c r="C215" s="6" t="inlineStr">
+      <c r="C216" s="6" t="inlineStr">
         <is>
           <t>exploratoire — 0 chapitre(s)</t>
         </is>
       </c>
     </row>
-    <row r="216">
-      <c r="A216" s="7" t="inlineStr"/>
-      <c r="B216" s="7" t="inlineStr">
+    <row r="217">
+      <c r="A217" s="7" t="inlineStr"/>
+      <c r="B217" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">    (aucun chapitre écrit)</t>
         </is>
       </c>
-      <c r="C216" s="7" t="inlineStr"/>
-    </row>
-    <row r="217">
-      <c r="A217" s="6" t="inlineStr">
+      <c r="C217" s="7" t="inlineStr"/>
+    </row>
+    <row r="218">
+      <c r="A218" s="6" t="inlineStr">
         <is>
           <t>L16</t>
         </is>
       </c>
-      <c r="B217" s="6" t="inlineStr">
+      <c r="B218" s="6" t="inlineStr">
         <is>
           <t>Typologie comparée des systèmes et alternatives monétaires</t>
         </is>
       </c>
-      <c r="C217" s="6" t="inlineStr">
+      <c r="C218" s="6" t="inlineStr">
         <is>
           <t>candidat — 0 chapitre(s)</t>
         </is>
       </c>
     </row>
-    <row r="218">
-      <c r="A218" s="7" t="inlineStr"/>
-      <c r="B218" s="7" t="inlineStr">
+    <row r="219">
+      <c r="A219" s="7" t="inlineStr"/>
+      <c r="B219" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">    (aucun chapitre écrit)</t>
         </is>
       </c>
-      <c r="C218" s="7" t="inlineStr"/>
-    </row>
-    <row r="219">
-      <c r="A219" s="6" t="inlineStr">
+      <c r="C219" s="7" t="inlineStr"/>
+    </row>
+    <row r="220">
+      <c r="A220" s="6" t="inlineStr">
         <is>
           <t>L17</t>
         </is>
       </c>
-      <c r="B219" s="6" t="inlineStr">
+      <c r="B220" s="6" t="inlineStr">
         <is>
           <t>Après la croissance : décroissance, post-croissance et prospérité sans croissance</t>
         </is>
       </c>
-      <c r="C219" s="6" t="inlineStr">
+      <c r="C220" s="6" t="inlineStr">
         <is>
           <t>candidat — 0 chapitre(s)</t>
         </is>
       </c>
     </row>
-    <row r="220">
-      <c r="A220" s="7" t="inlineStr"/>
-      <c r="B220" s="7" t="inlineStr">
+    <row r="221">
+      <c r="A221" s="7" t="inlineStr"/>
+      <c r="B221" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">    (aucun chapitre écrit)</t>
         </is>
       </c>
-      <c r="C220" s="7" t="inlineStr"/>
-    </row>
-    <row r="221">
-      <c r="A221" s="6" t="inlineStr">
+      <c r="C221" s="7" t="inlineStr"/>
+    </row>
+    <row r="222">
+      <c r="A222" s="6" t="inlineStr">
         <is>
           <t>L18</t>
         </is>
       </c>
-      <c r="B221" s="6" t="inlineStr">
+      <c r="B222" s="6" t="inlineStr">
         <is>
           <t>Comptabilités écologiques, sociales et biophysiques</t>
         </is>
       </c>
-      <c r="C221" s="6" t="inlineStr">
+      <c r="C222" s="6" t="inlineStr">
         <is>
           <t>en-cours — 8 chapitre(s)</t>
-        </is>
-      </c>
-    </row>
-    <row r="222">
-      <c r="A222" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    L18.C01</t>
-        </is>
-      </c>
-      <c r="B222" s="3" t="inlineStr">
-        <is>
-          <t>Ce que ce livre doit établir, et le repli n'est pas l'annexe</t>
-        </is>
-      </c>
-      <c r="C222" s="3" t="inlineStr">
-        <is>
-          <t>brouillon</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L18.C02</t>
+          <t xml:space="preserve">    L18.C01</t>
         </is>
       </c>
       <c r="B223" s="3" t="inlineStr">
         <is>
-          <t>La métrologie existe, et ce qu'elle enregistre est l'ordre en place</t>
+          <t>Ce que ce livre doit établir, et le repli n'est pas l'annexe</t>
         </is>
       </c>
       <c r="C223" s="3" t="inlineStr">
@@ -19383,12 +19446,12 @@
     <row r="224">
       <c r="A224" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L18.C03</t>
+          <t xml:space="preserve">    L18.C02</t>
         </is>
       </c>
       <c r="B224" s="3" t="inlineStr">
         <is>
-          <t>L'échelle de repli, et qui l'a arrêtée</t>
+          <t>La métrologie existe, et ce qu'elle enregistre est l'ordre en place</t>
         </is>
       </c>
       <c r="C224" s="3" t="inlineStr">
@@ -19400,12 +19463,12 @@
     <row r="225">
       <c r="A225" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L18.C04</t>
+          <t xml:space="preserve">    L18.C03</t>
         </is>
       </c>
       <c r="B225" s="3" t="inlineStr">
         <is>
-          <t>Les grandeurs physiques, et l'endroit où elles frappent le dispositif</t>
+          <t>L'échelle de repli, et qui l'a arrêtée</t>
         </is>
       </c>
       <c r="C225" s="3" t="inlineStr">
@@ -19417,12 +19480,12 @@
     <row r="226">
       <c r="A226" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L18.C05</t>
+          <t xml:space="preserve">    L18.C04</t>
         </is>
       </c>
       <c r="B226" s="3" t="inlineStr">
         <is>
-          <t>Le commun est ce que la norme exclut, et la symétrie de l'écriture</t>
+          <t>Les grandeurs physiques, et l'endroit où elles frappent le dispositif</t>
         </is>
       </c>
       <c r="C226" s="3" t="inlineStr">
@@ -19434,12 +19497,12 @@
     <row r="227">
       <c r="A227" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L18.C06</t>
+          <t xml:space="preserve">    L18.C05</t>
         </is>
       </c>
       <c r="B227" s="3" t="inlineStr">
         <is>
-          <t>Portée de la tranche, et une neuvième condition proposée</t>
+          <t>Le commun est ce que la norme exclut, et la symétrie de l'écriture</t>
         </is>
       </c>
       <c r="C227" s="3" t="inlineStr">
@@ -19451,12 +19514,12 @@
     <row r="228">
       <c r="A228" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L18.C07</t>
+          <t xml:space="preserve">    L18.C06</t>
         </is>
       </c>
       <c r="B228" s="3" t="inlineStr">
         <is>
-          <t>CARE/TDL répare deux objections, et en crée une plus grave</t>
+          <t>Portée de la tranche, et une neuvième condition proposée</t>
         </is>
       </c>
       <c r="C228" s="3" t="inlineStr">
@@ -19468,63 +19531,63 @@
     <row r="229">
       <c r="A229" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">    L18.C07</t>
+        </is>
+      </c>
+      <c r="B229" s="3" t="inlineStr">
+        <is>
+          <t>CARE/TDL répare deux objections, et en crée une plus grave</t>
+        </is>
+      </c>
+      <c r="C229" s="3" t="inlineStr">
+        <is>
+          <t>brouillon</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">    L18.C08</t>
         </is>
       </c>
-      <c r="B229" s="3" t="inlineStr">
+      <c r="B230" s="3" t="inlineStr">
         <is>
           <t>Le modèle au périmètre du dispositif, et F9 révisée</t>
         </is>
       </c>
-      <c r="C229" s="3" t="inlineStr">
-        <is>
-          <t>brouillon</t>
-        </is>
-      </c>
-    </row>
-    <row r="230">
-      <c r="A230" s="6" t="inlineStr">
+      <c r="C230" s="3" t="inlineStr">
+        <is>
+          <t>brouillon</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" s="6" t="inlineStr">
         <is>
           <t>L20</t>
         </is>
       </c>
-      <c r="B230" s="6" t="inlineStr">
+      <c r="B231" s="6" t="inlineStr">
         <is>
           <t>Droit international public, droit monétaire et commercial de la réforme</t>
         </is>
       </c>
-      <c r="C230" s="6" t="inlineStr">
+      <c r="C231" s="6" t="inlineStr">
         <is>
           <t>en-cours — 23 chapitre(s)</t>
-        </is>
-      </c>
-    </row>
-    <row r="231">
-      <c r="A231" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    L20.C01</t>
-        </is>
-      </c>
-      <c r="B231" s="3" t="inlineStr">
-        <is>
-          <t>Ce que ce livre doit établir</t>
-        </is>
-      </c>
-      <c r="C231" s="3" t="inlineStr">
-        <is>
-          <t>brouillon</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="A232" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L20.C02</t>
+          <t xml:space="preserve">    L20.C01</t>
         </is>
       </c>
       <c r="B232" s="3" t="inlineStr">
         <is>
-          <t>L'interdiction du financement monétaire</t>
+          <t>Ce que ce livre doit établir</t>
         </is>
       </c>
       <c r="C232" s="3" t="inlineStr">
@@ -19536,12 +19599,12 @@
     <row r="233">
       <c r="A233" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L20.C03</t>
+          <t xml:space="preserve">    L20.C02</t>
         </is>
       </c>
       <c r="B233" s="3" t="inlineStr">
         <is>
-          <t>L'objectif principal et ce qu'il exclut</t>
+          <t>L'interdiction du financement monétaire</t>
         </is>
       </c>
       <c r="C233" s="3" t="inlineStr">
@@ -19553,12 +19616,12 @@
     <row r="234">
       <c r="A234" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L20.C04</t>
+          <t xml:space="preserve">    L20.C03</t>
         </is>
       </c>
       <c r="B234" s="3" t="inlineStr">
         <is>
-          <t>L'indépendance, et à l'égard de qui</t>
+          <t>L'objectif principal et ce qu'il exclut</t>
         </is>
       </c>
       <c r="C234" s="3" t="inlineStr">
@@ -19570,12 +19633,12 @@
     <row r="235">
       <c r="A235" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L20.C05</t>
+          <t xml:space="preserve">    L20.C04</t>
         </is>
       </c>
       <c r="B235" s="3" t="inlineStr">
         <is>
-          <t>Le monopole d'émission et le cours légal</t>
+          <t>L'indépendance, et à l'égard de qui</t>
         </is>
       </c>
       <c r="C235" s="3" t="inlineStr">
@@ -19587,12 +19650,12 @@
     <row r="236">
       <c r="A236" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L20.C06</t>
+          <t xml:space="preserve">    L20.C05</t>
         </is>
       </c>
       <c r="B236" s="3" t="inlineStr">
         <is>
-          <t>Les voies de révision et leur coût</t>
+          <t>Le monopole d'émission et le cours légal</t>
         </is>
       </c>
       <c r="C236" s="3" t="inlineStr">
@@ -19604,12 +19667,12 @@
     <row r="237">
       <c r="A237" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L20.C07</t>
+          <t xml:space="preserve">    L20.C06</t>
         </is>
       </c>
       <c r="B237" s="3" t="inlineStr">
         <is>
-          <t>L'accord monétaire international</t>
+          <t>Les voies de révision et leur coût</t>
         </is>
       </c>
       <c r="C237" s="3" t="inlineStr">
@@ -19621,12 +19684,12 @@
     <row r="238">
       <c r="A238" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L20.C08</t>
+          <t xml:space="preserve">    L20.C07</t>
         </is>
       </c>
       <c r="B238" s="3" t="inlineStr">
         <is>
-          <t>La parité inscrite dans le traité</t>
+          <t>L'accord monétaire international</t>
         </is>
       </c>
       <c r="C238" s="3" t="inlineStr">
@@ -19638,12 +19701,12 @@
     <row r="239">
       <c r="A239" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L20.C09</t>
+          <t xml:space="preserve">    L20.C08</t>
         </is>
       </c>
       <c r="B239" s="3" t="inlineStr">
         <is>
-          <t>L'amendement des statuts du Fonds</t>
+          <t>La parité inscrite dans le traité</t>
         </is>
       </c>
       <c r="C239" s="3" t="inlineStr">
@@ -19655,12 +19718,12 @@
     <row r="240">
       <c r="A240" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L20.C10</t>
+          <t xml:space="preserve">    L20.C09</t>
         </is>
       </c>
       <c r="B240" s="3" t="inlineStr">
         <is>
-          <t>Le vote pondéré et les voix de base</t>
+          <t>L'amendement des statuts du Fonds</t>
         </is>
       </c>
       <c r="C240" s="3" t="inlineStr">
@@ -19672,12 +19735,12 @@
     <row r="241">
       <c r="A241" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L20.C11</t>
+          <t xml:space="preserve">    L20.C10</t>
         </is>
       </c>
       <c r="B241" s="3" t="inlineStr">
         <is>
-          <t>La personnalité juridique et les immunités</t>
+          <t>Le vote pondéré et les voix de base</t>
         </is>
       </c>
       <c r="C241" s="3" t="inlineStr">
@@ -19689,12 +19752,12 @@
     <row r="242">
       <c r="A242" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L20.C12</t>
+          <t xml:space="preserve">    L20.C11</t>
         </is>
       </c>
       <c r="B242" s="3" t="inlineStr">
         <is>
-          <t>Les pouvoirs non délégables</t>
+          <t>La personnalité juridique et les immunités</t>
         </is>
       </c>
       <c r="C242" s="3" t="inlineStr">
@@ -19706,12 +19769,12 @@
     <row r="243">
       <c r="A243" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L20.C13</t>
+          <t xml:space="preserve">    L20.C12</t>
         </is>
       </c>
       <c r="B243" s="3" t="inlineStr">
         <is>
-          <t>L'entrée en vigueur, l'adhésion et le retrait</t>
+          <t>Les pouvoirs non délégables</t>
         </is>
       </c>
       <c r="C243" s="3" t="inlineStr">
@@ -19723,12 +19786,12 @@
     <row r="244">
       <c r="A244" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L20.C14</t>
+          <t xml:space="preserve">    L20.C13</t>
         </is>
       </c>
       <c r="B244" s="3" t="inlineStr">
         <is>
-          <t>Qui interprète le traité</t>
+          <t>L'entrée en vigueur, l'adhésion et le retrait</t>
         </is>
       </c>
       <c r="C244" s="3" t="inlineStr">
@@ -19740,12 +19803,12 @@
     <row r="245">
       <c r="A245" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L20.C15</t>
+          <t xml:space="preserve">    L20.C14</t>
         </is>
       </c>
       <c r="B245" s="3" t="inlineStr">
         <is>
-          <t>Le devoir international des agents</t>
+          <t>Qui interprète le traité</t>
         </is>
       </c>
       <c r="C245" s="3" t="inlineStr">
@@ -19757,12 +19820,12 @@
     <row r="246">
       <c r="A246" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L20.C16</t>
+          <t xml:space="preserve">    L20.C15</t>
         </is>
       </c>
       <c r="B246" s="3" t="inlineStr">
         <is>
-          <t>Le patrimoine commun de l'humanité</t>
+          <t>Le devoir international des agents</t>
         </is>
       </c>
       <c r="C246" s="3" t="inlineStr">
@@ -19774,12 +19837,12 @@
     <row r="247">
       <c r="A247" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L20.C17</t>
+          <t xml:space="preserve">    L20.C16</t>
         </is>
       </c>
       <c r="B247" s="3" t="inlineStr">
         <is>
-          <t>La sanctuarisation, et elle existe</t>
+          <t>Le patrimoine commun de l'humanité</t>
         </is>
       </c>
       <c r="C247" s="3" t="inlineStr">
@@ -19791,12 +19854,12 @@
     <row r="248">
       <c r="A248" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L20.C18</t>
+          <t xml:space="preserve">    L20.C17</t>
         </is>
       </c>
       <c r="B248" s="3" t="inlineStr">
         <is>
-          <t>L'amendement et la dérogation dans l'ordre commercial</t>
+          <t>La sanctuarisation, et elle existe</t>
         </is>
       </c>
       <c r="C248" s="3" t="inlineStr">
@@ -19808,12 +19871,12 @@
     <row r="249">
       <c r="A249" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L20.C19</t>
+          <t xml:space="preserve">    L20.C18</t>
         </is>
       </c>
       <c r="B249" s="3" t="inlineStr">
         <is>
-          <t>Le texte que la conformité invoque</t>
+          <t>L'amendement et la dérogation dans l'ordre commercial</t>
         </is>
       </c>
       <c r="C249" s="3" t="inlineStr">
@@ -19825,12 +19888,12 @@
     <row r="250">
       <c r="A250" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L20.C20</t>
+          <t xml:space="preserve">    L20.C19</t>
         </is>
       </c>
       <c r="B250" s="3" t="inlineStr">
         <is>
-          <t>L'ajustement aux frontières comme précédent</t>
+          <t>Le texte que la conformité invoque</t>
         </is>
       </c>
       <c r="C250" s="3" t="inlineStr">
@@ -19842,12 +19905,12 @@
     <row r="251">
       <c r="A251" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L20.C21</t>
+          <t xml:space="preserve">    L20.C20</t>
         </is>
       </c>
       <c r="B251" s="3" t="inlineStr">
         <is>
-          <t>La transparence et sa limite juridictionnelle</t>
+          <t>L'ajustement aux frontières comme précédent</t>
         </is>
       </c>
       <c r="C251" s="3" t="inlineStr">
@@ -19859,12 +19922,12 @@
     <row r="252">
       <c r="A252" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L20.C22</t>
+          <t xml:space="preserve">    L20.C21</t>
         </is>
       </c>
       <c r="B252" s="3" t="inlineStr">
         <is>
-          <t>Ce que le droit devrait devenir</t>
+          <t>La transparence et sa limite juridictionnelle</t>
         </is>
       </c>
       <c r="C252" s="3" t="inlineStr">
@@ -19876,15 +19939,32 @@
     <row r="253">
       <c r="A253" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">    L20.C22</t>
+        </is>
+      </c>
+      <c r="B253" s="3" t="inlineStr">
+        <is>
+          <t>Ce que le droit devrait devenir</t>
+        </is>
+      </c>
+      <c r="C253" s="3" t="inlineStr">
+        <is>
+          <t>brouillon</t>
+        </is>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">    L20.C23</t>
         </is>
       </c>
-      <c r="B253" s="3" t="inlineStr">
+      <c r="B254" s="3" t="inlineStr">
         <is>
           <t>La portée du livre</t>
         </is>
       </c>
-      <c r="C253" s="3" t="inlineStr">
+      <c r="C254" s="3" t="inlineStr">
         <is>
           <t>brouillon</t>
         </is>

--- a/plan-des-livres.xlsx
+++ b/plan-des-livres.xlsx
@@ -1494,7 +1494,7 @@
       <c r="L2" s="3" t="inlineStr"/>
       <c r="M2" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-01/c01-nouveau-paradigme-economique.md</t>
+          <t>corpus/livre-01-monnaie-finance-limites-planetaires/c01-nouveau-paradigme-economique.md</t>
         </is>
       </c>
     </row>
@@ -1553,7 +1553,7 @@
       <c r="L3" s="3" t="inlineStr"/>
       <c r="M3" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-01/c02-la-grande-contradiction.md</t>
+          <t>corpus/livre-01-monnaie-finance-limites-planetaires/c02-la-grande-contradiction.md</t>
         </is>
       </c>
     </row>
@@ -1612,7 +1612,7 @@
       <c r="L4" s="3" t="inlineStr"/>
       <c r="M4" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-01/c03-croissance-infinie-planete-finie.md</t>
+          <t>corpus/livre-01-monnaie-finance-limites-planetaires/c03-croissance-infinie-planete-finie.md</t>
         </is>
       </c>
     </row>
@@ -1671,7 +1671,7 @@
       <c r="L5" s="3" t="inlineStr"/>
       <c r="M5" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-01/c04-economie-interieur-nature.md</t>
+          <t>corpus/livre-01-monnaie-finance-limites-planetaires/c04-economie-interieur-nature.md</t>
         </is>
       </c>
     </row>
@@ -1730,7 +1730,7 @@
       <c r="L6" s="3" t="inlineStr"/>
       <c r="M6" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-01/c05-quest-ce-que-la-monnaie.md</t>
+          <t>corpus/livre-01-monnaie-finance-limites-planetaires/c05-quest-ce-que-la-monnaie.md</t>
         </is>
       </c>
     </row>
@@ -1793,7 +1793,7 @@
       </c>
       <c r="M7" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-01/c06-monnaie-angle-mort.md</t>
+          <t>corpus/livre-01-monnaie-finance-limites-planetaires/c06-monnaie-angle-mort.md</t>
         </is>
       </c>
     </row>
@@ -1856,7 +1856,7 @@
       </c>
       <c r="M8" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-01/c07-comment-les-banques-creent-la-monnaie.md</t>
+          <t>corpus/livre-01-monnaie-finance-limites-planetaires/c07-comment-les-banques-creent-la-monnaie.md</t>
         </is>
       </c>
     </row>
@@ -1919,7 +1919,7 @@
       </c>
       <c r="M9" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-01/c08-pourquoi-la-dette-change-tout.md</t>
+          <t>corpus/livre-01-monnaie-finance-limites-planetaires/c08-pourquoi-la-dette-change-tout.md</t>
         </is>
       </c>
     </row>
@@ -1982,7 +1982,7 @@
       </c>
       <c r="M10" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-01/c09-l-architecture-invisible.md</t>
+          <t>corpus/livre-01-monnaie-finance-limites-planetaires/c09-l-architecture-invisible.md</t>
         </is>
       </c>
     </row>
@@ -2045,7 +2045,7 @@
       </c>
       <c r="M11" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-01/c10-une-monnaie-peut-elle-etre-concue-autrement.md</t>
+          <t>corpus/livre-01-monnaie-finance-limites-planetaires/c10-une-monnaie-peut-elle-etre-concue-autrement.md</t>
         </is>
       </c>
     </row>
@@ -2108,7 +2108,7 @@
       </c>
       <c r="M12" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-01/c11-la-premiere-malediction-monetaire.md</t>
+          <t>corpus/livre-01-monnaie-finance-limites-planetaires/c11-la-premiere-malediction-monetaire.md</t>
         </is>
       </c>
     </row>
@@ -2171,7 +2171,7 @@
       </c>
       <c r="M13" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-01/c12-la-deuxieme-malediction-monetaire.md</t>
+          <t>corpus/livre-01-monnaie-finance-limites-planetaires/c12-la-deuxieme-malediction-monetaire.md</t>
         </is>
       </c>
     </row>
@@ -2234,7 +2234,7 @@
       </c>
       <c r="M14" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-01/c13-la-troisieme-malediction-monetaire.md</t>
+          <t>corpus/livre-01-monnaie-finance-limites-planetaires/c13-la-troisieme-malediction-monetaire.md</t>
         </is>
       </c>
     </row>
@@ -2297,7 +2297,7 @@
       </c>
       <c r="M15" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-01/c14-la-dette-un-mythe-de-sisyphe-economique.md</t>
+          <t>corpus/livre-01-monnaie-finance-limites-planetaires/c14-la-dette-un-mythe-de-sisyphe-economique.md</t>
         </is>
       </c>
     </row>
@@ -2360,7 +2360,7 @@
       </c>
       <c r="M16" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-01/c15-l-essentiel-insolvable.md</t>
+          <t>corpus/livre-01-monnaie-finance-limites-planetaires/c15-l-essentiel-insolvable.md</t>
         </is>
       </c>
     </row>
@@ -2423,7 +2423,7 @@
       </c>
       <c r="M17" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-01/c16-l-ere-de-la-bullshitnovation.md</t>
+          <t>corpus/livre-01-monnaie-finance-limites-planetaires/c16-l-ere-de-la-bullshitnovation.md</t>
         </is>
       </c>
     </row>
@@ -2486,7 +2486,7 @@
       </c>
       <c r="M18" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-01/c17-et-si-la-planete-avait-sa-propre-banque.md</t>
+          <t>corpus/livre-01-monnaie-finance-limites-planetaires/c17-et-si-la-planete-avait-sa-propre-banque.md</t>
         </is>
       </c>
     </row>
@@ -2549,7 +2549,7 @@
       </c>
       <c r="M19" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-01/c18-le-gaia-economic-symposium.md</t>
+          <t>corpus/livre-01-monnaie-finance-limites-planetaires/c18-le-gaia-economic-symposium.md</t>
         </is>
       </c>
     </row>
@@ -2612,7 +2612,7 @@
       </c>
       <c r="M20" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-01/c19-le-yin-et-le-yang-de-la-finance.md</t>
+          <t>corpus/livre-01-monnaie-finance-limites-planetaires/c19-le-yin-et-le-yang-de-la-finance.md</t>
         </is>
       </c>
     </row>
@@ -2675,7 +2675,7 @@
       </c>
       <c r="M21" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-01/c20-de-l-argent-sans-dette.md</t>
+          <t>corpus/livre-01-monnaie-finance-limites-planetaires/c20-de-l-argent-sans-dette.md</t>
         </is>
       </c>
     </row>
@@ -2738,7 +2738,7 @@
       </c>
       <c r="M22" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-01/c21-le-reflux-collectif.md</t>
+          <t>corpus/livre-01-monnaie-finance-limites-planetaires/c21-le-reflux-collectif.md</t>
         </is>
       </c>
     </row>
@@ -2801,7 +2801,7 @@
       </c>
       <c r="M23" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-01/c22-financer-les-communs.md</t>
+          <t>corpus/livre-01-monnaie-finance-limites-planetaires/c22-financer-les-communs.md</t>
         </is>
       </c>
     </row>
@@ -2864,7 +2864,7 @@
       </c>
       <c r="M24" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-01/c23-l-economie-de-la-robustesse.md</t>
+          <t>corpus/livre-01-monnaie-finance-limites-planetaires/c23-l-economie-de-la-robustesse.md</t>
         </is>
       </c>
     </row>
@@ -2927,7 +2927,7 @@
       </c>
       <c r="M25" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-01/c24-pourquoi-le-dollar-ne-peut-pas-durer.md</t>
+          <t>corpus/livre-01-monnaie-finance-limites-planetaires/c24-pourquoi-le-dollar-ne-peut-pas-durer.md</t>
         </is>
       </c>
     </row>
@@ -2990,7 +2990,7 @@
       </c>
       <c r="M26" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-01/c25-histoire-des-systemes-monetaires-internationaux.md</t>
+          <t>corpus/livre-01-monnaie-finance-limites-planetaires/c25-histoire-des-systemes-monetaires-internationaux.md</t>
         </is>
       </c>
     </row>
@@ -3053,7 +3053,7 @@
       </c>
       <c r="M27" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-01/c26-le-nemo-exchange-standard.md</t>
+          <t>corpus/livre-01-monnaie-finance-limites-planetaires/c26-le-nemo-exchange-standard.md</t>
         </is>
       </c>
     </row>
@@ -3116,7 +3116,7 @@
       </c>
       <c r="M28" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-01/c27-une-economie-mondiale-cooperative-nemo-swift.md</t>
+          <t>corpus/livre-01-monnaie-finance-limites-planetaires/c27-une-economie-mondiale-cooperative-nemo-swift.md</t>
         </is>
       </c>
     </row>
@@ -3179,7 +3179,7 @@
       </c>
       <c r="M29" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-01/c28-au-dela-du-pib.md</t>
+          <t>corpus/livre-01-monnaie-finance-limites-planetaires/c28-au-dela-du-pib.md</t>
         </is>
       </c>
     </row>
@@ -3242,7 +3242,7 @@
       </c>
       <c r="M30" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-01/c29-vision-globale-et-chantiers-ouverts.md</t>
+          <t>corpus/livre-01-monnaie-finance-limites-planetaires/c29-vision-globale-et-chantiers-ouverts.md</t>
         </is>
       </c>
     </row>
@@ -3305,7 +3305,7 @@
       </c>
       <c r="M31" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-01/c30-imagine-l-annee-2100.md</t>
+          <t>corpus/livre-01-monnaie-finance-limites-planetaires/c30-imagine-l-annee-2100.md</t>
         </is>
       </c>
     </row>
@@ -3368,7 +3368,7 @@
       </c>
       <c r="M32" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-02/c01-ce-que-ce-livre-doit-etablir.md</t>
+          <t>corpus/livre-02-recommandations-macro-prudentielles/c01-ce-que-ce-livre-doit-etablir.md</t>
         </is>
       </c>
     </row>
@@ -3431,7 +3431,7 @@
       </c>
       <c r="M33" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-02/c02-ce-que-macroprudentiel-veut-dire.md</t>
+          <t>corpus/livre-02-recommandations-macro-prudentielles/c02-ce-que-macroprudentiel-veut-dire.md</t>
         </is>
       </c>
     </row>
@@ -3494,7 +3494,7 @@
       </c>
       <c r="M34" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-02/c03-l-objectif-ultime-est-une-perte-de-produit.md</t>
+          <t>corpus/livre-02-recommandations-macro-prudentielles/c03-l-objectif-ultime-est-une-perte-de-produit.md</t>
         </is>
       </c>
     </row>
@@ -3557,7 +3557,7 @@
       </c>
       <c r="M35" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-02/c04-rupture-ou-extension.md</t>
+          <t>corpus/livre-02-recommandations-macro-prudentielles/c04-rupture-ou-extension.md</t>
         </is>
       </c>
     </row>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="M36" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-02/c05-aglietta-la-fragilite-climatique.md</t>
+          <t>corpus/livre-02-recommandations-macro-prudentielles/c05-aglietta-la-fragilite-climatique.md</t>
         </is>
       </c>
     </row>
@@ -3683,7 +3683,7 @@
       </c>
       <c r="M37" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-02/c06-plihon-le-pilier-structurel.md</t>
+          <t>corpus/livre-02-recommandations-macro-prudentielles/c06-plihon-le-pilier-structurel.md</t>
         </is>
       </c>
     </row>
@@ -3746,7 +3746,7 @@
       </c>
       <c r="M38" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-02/c07-l-affectation-des-instruments.md</t>
+          <t>corpus/livre-02-recommandations-macro-prudentielles/c07-l-affectation-des-instruments.md</t>
         </is>
       </c>
     </row>
@@ -3809,7 +3809,7 @@
       </c>
       <c r="M39" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-02/c08-les-mecanismes-bancaires-du-controle-monetaire.md</t>
+          <t>corpus/livre-02-recommandations-macro-prudentielles/c08-les-mecanismes-bancaires-du-controle-monetaire.md</t>
         </is>
       </c>
     </row>
@@ -3872,7 +3872,7 @@
       </c>
       <c r="M40" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-02/c09-l-emboitement-systemique.md</t>
+          <t>corpus/livre-02-recommandations-macro-prudentielles/c09-l-emboitement-systemique.md</t>
         </is>
       </c>
     </row>
@@ -3935,7 +3935,7 @@
       </c>
       <c r="M41" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-02/c10-de-la-stabilite-a-la-robustesse.md</t>
+          <t>corpus/livre-02-recommandations-macro-prudentielles/c10-de-la-stabilite-a-la-robustesse.md</t>
         </is>
       </c>
     </row>
@@ -3998,7 +3998,7 @@
       </c>
       <c r="M42" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-02/c11-des-risques-financiers-aux-risques-planetaires.md</t>
+          <t>corpus/livre-02-recommandations-macro-prudentielles/c11-des-risques-financiers-aux-risques-planetaires.md</t>
         </is>
       </c>
     </row>
@@ -4061,7 +4061,7 @@
       </c>
       <c r="M43" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-02/c12-du-controle-quantitatif-au-controle-qualitatif.md</t>
+          <t>corpus/livre-02-recommandations-macro-prudentielles/c12-du-controle-quantitatif-au-controle-qualitatif.md</t>
         </is>
       </c>
     </row>
@@ -4124,7 +4124,7 @@
       </c>
       <c r="M44" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-02/c13-de-la-neutralite-a-l-allocation-strategique.md</t>
+          <t>corpus/livre-02-recommandations-macro-prudentielles/c13-de-la-neutralite-a-l-allocation-strategique.md</t>
         </is>
       </c>
     </row>
@@ -4187,7 +4187,7 @@
       </c>
       <c r="M45" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-02/c14-des-bulles-financieres-aux-bulles-ecologiques.md</t>
+          <t>corpus/livre-02-recommandations-macro-prudentielles/c14-des-bulles-financieres-aux-bulles-ecologiques.md</t>
         </is>
       </c>
     </row>
@@ -4250,7 +4250,7 @@
       </c>
       <c r="M46" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-02/c15-de-la-resilience-bancaire-a-la-resilience-territoriale.md</t>
+          <t>corpus/livre-02-recommandations-macro-prudentielles/c15-de-la-resilience-bancaire-a-la-resilience-territoriale.md</t>
         </is>
       </c>
     </row>
@@ -4313,7 +4313,7 @@
       </c>
       <c r="M47" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-02/c16-de-la-gestion-de-la-dette-au-reflux-monetaire-actif.md</t>
+          <t>corpus/livre-02-recommandations-macro-prudentielles/c16-de-la-gestion-de-la-dette-au-reflux-monetaire-actif.md</t>
         </is>
       </c>
     </row>
@@ -4376,7 +4376,7 @@
       </c>
       <c r="M48" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-02/c17-de-la-surveillance-bancaire-a-la-gouvernance-des-communs.md</t>
+          <t>corpus/livre-02-recommandations-macro-prudentielles/c17-de-la-surveillance-bancaire-a-la-gouvernance-des-communs.md</t>
         </is>
       </c>
     </row>
@@ -4439,7 +4439,7 @@
       </c>
       <c r="M49" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-02/c18-la-gouvernance-monetaire-mondiale.md</t>
+          <t>corpus/livre-02-recommandations-macro-prudentielles/c18-la-gouvernance-monetaire-mondiale.md</t>
         </is>
       </c>
     </row>
@@ -4502,7 +4502,7 @@
       </c>
       <c r="M50" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-02/c19-la-macroprudence-regenerative.md</t>
+          <t>corpus/livre-02-recommandations-macro-prudentielles/c19-la-macroprudence-regenerative.md</t>
         </is>
       </c>
     </row>
@@ -4565,7 +4565,7 @@
       </c>
       <c r="M51" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-02/c20-la-portee-du-livre.md</t>
+          <t>corpus/livre-02-recommandations-macro-prudentielles/c20-la-portee-du-livre.md</t>
         </is>
       </c>
     </row>
@@ -4628,7 +4628,7 @@
       </c>
       <c r="M52" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-02/c21-aglietta-la-renovation-des-politiques-monetaires.md</t>
+          <t>corpus/livre-02-recommandations-macro-prudentielles/c21-aglietta-la-renovation-des-politiques-monetaires.md</t>
         </is>
       </c>
     </row>
@@ -4691,7 +4691,7 @@
       </c>
       <c r="M53" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-02/c22-goodhart-l-inventaire-des-instruments.md</t>
+          <t>corpus/livre-02-recommandations-macro-prudentielles/c22-goodhart-l-inventaire-des-instruments.md</t>
         </is>
       </c>
     </row>
@@ -4754,7 +4754,7 @@
       </c>
       <c r="M54" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-03/c01-ce-que-ce-livre-doit-etablir.md</t>
+          <t>corpus/livre-03-dilemmes-du-systeme-monetaire-international/c01-ce-que-ce-livre-doit-etablir.md</t>
         </is>
       </c>
     </row>
@@ -4817,7 +4817,7 @@
       </c>
       <c r="M55" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-03/c02-le-trilemme-et-le-coin-que-le-dispositif-occupe.md</t>
+          <t>corpus/livre-03-dilemmes-du-systeme-monetaire-international/c02-le-trilemme-et-le-coin-que-le-dispositif-occupe.md</t>
         </is>
       </c>
     </row>
@@ -4880,7 +4880,7 @@
       </c>
       <c r="M56" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-03/c03-la-sortie-du-coin-et-dans-quel-ordre.md</t>
+          <t>corpus/livre-03-dilemmes-du-systeme-monetaire-international/c03-la-sortie-du-coin-et-dans-quel-ordre.md</t>
         </is>
       </c>
     </row>
@@ -4943,7 +4943,7 @@
       </c>
       <c r="M57" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-03/c04-le-privilege-le-devoir-et-la-fenetre-qui-n-est-pas-la-notre.md</t>
+          <t>corpus/livre-03-dilemmes-du-systeme-monetaire-international/c04-le-privilege-le-devoir-et-la-fenetre-qui-n-est-pas-la-notre.md</t>
         </is>
       </c>
     </row>
@@ -5006,7 +5006,7 @@
       </c>
       <c r="M58" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-03/c05-ce-que-les-concurrents-choisissent-si-les-descriptions-sont-exactes.md</t>
+          <t>corpus/livre-03-dilemmes-du-systeme-monetaire-international/c05-ce-que-les-concurrents-choisissent-si-les-descriptions-sont-exactes.md</t>
         </is>
       </c>
     </row>
@@ -5069,7 +5069,7 @@
       </c>
       <c r="M59" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-03/c06-le-filet-de-securite-et-la-jambe-oubliee.md</t>
+          <t>corpus/livre-03-dilemmes-du-systeme-monetaire-international/c06-le-filet-de-securite-et-la-jambe-oubliee.md</t>
         </is>
       </c>
     </row>
@@ -5132,7 +5132,7 @@
       </c>
       <c r="M60" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-03/c07-comment-le-filet-etait-ecrit.md</t>
+          <t>corpus/livre-03-dilemmes-du-systeme-monetaire-international/c07-comment-le-filet-etait-ecrit.md</t>
         </is>
       </c>
     </row>
@@ -5195,7 +5195,7 @@
       </c>
       <c r="M61" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-03/c08-le-filtre-et-ou-il-se-redeplace.md</t>
+          <t>corpus/livre-03-dilemmes-du-systeme-monetaire-international/c08-le-filtre-et-ou-il-se-redeplace.md</t>
         </is>
       </c>
     </row>
@@ -5258,7 +5258,7 @@
       </c>
       <c r="M62" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-03/c09-un-bretton-woods-sans-pivot.md</t>
+          <t>corpus/livre-03-dilemmes-du-systeme-monetaire-international/c09-un-bretton-woods-sans-pivot.md</t>
         </is>
       </c>
     </row>
@@ -5321,7 +5321,7 @@
       </c>
       <c r="M63" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-03/c10-la-portee-du-livre.md</t>
+          <t>corpus/livre-03-dilemmes-du-systeme-monetaire-international/c10-la-portee-du-livre.md</t>
         </is>
       </c>
     </row>
@@ -5376,7 +5376,7 @@
       <c r="L64" s="3" t="inlineStr"/>
       <c r="M64" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-04/c01-weber-le-protestantisme-et-le-travail-vocation.md</t>
+          <t>corpus/livre-04-les-cahiers-humanistes/c01-weber-le-protestantisme-et-le-travail-vocation.md</t>
         </is>
       </c>
     </row>
@@ -5431,7 +5431,7 @@
       <c r="L65" s="3" t="inlineStr"/>
       <c r="M65" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-04/c02-lafargue-russell-et-le-droit-a-la-paresse.md</t>
+          <t>corpus/livre-04-les-cahiers-humanistes/c02-lafargue-russell-et-le-droit-a-la-paresse.md</t>
         </is>
       </c>
     </row>
@@ -5486,7 +5486,7 @@
       <c r="L66" s="3" t="inlineStr"/>
       <c r="M66" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-04/c03-hannah-arendt-et-la-triple-distinction.md</t>
+          <t>corpus/livre-04-les-cahiers-humanistes/c03-hannah-arendt-et-la-triple-distinction.md</t>
         </is>
       </c>
     </row>
@@ -5541,7 +5541,7 @@
       <c r="L67" s="3" t="inlineStr"/>
       <c r="M67" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-04/c04-simone-weil-et-l-experience-de-l-usine.md</t>
+          <t>corpus/livre-04-les-cahiers-humanistes/c04-simone-weil-et-l-experience-de-l-usine.md</t>
         </is>
       </c>
     </row>
@@ -5596,7 +5596,7 @@
       <c r="L68" s="3" t="inlineStr"/>
       <c r="M68" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-04/c05-robert-castel-et-les-metamorphoses-de-la-question-sociale.md</t>
+          <t>corpus/livre-04-les-cahiers-humanistes/c05-robert-castel-et-les-metamorphoses-de-la-question-sociale.md</t>
         </is>
       </c>
     </row>
@@ -5651,7 +5651,7 @@
       <c r="L69" s="3" t="inlineStr"/>
       <c r="M69" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-04/c06-andre-gorz-et-la-sortie-de-la-societe-salariale.md</t>
+          <t>corpus/livre-04-les-cahiers-humanistes/c06-andre-gorz-et-la-sortie-de-la-societe-salariale.md</t>
         </is>
       </c>
     </row>
@@ -5706,7 +5706,7 @@
       <c r="L70" s="3" t="inlineStr"/>
       <c r="M70" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-04/c07-ellul-illich-et-la-contreproductivite.md</t>
+          <t>corpus/livre-04-les-cahiers-humanistes/c07-ellul-illich-et-la-contreproductivite.md</t>
         </is>
       </c>
     </row>
@@ -5761,7 +5761,7 @@
       <c r="L71" s="3" t="inlineStr"/>
       <c r="M71" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-04/c08-bob-black-graeber-bullshit-jobs-et-bullshitnovation.md</t>
+          <t>corpus/livre-04-les-cahiers-humanistes/c08-bob-black-graeber-bullshit-jobs-et-bullshitnovation.md</t>
         </is>
       </c>
     </row>
@@ -5816,7 +5816,7 @@
       <c r="L72" s="3" t="inlineStr"/>
       <c r="M72" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-04/c09-federici-fraser-et-le-travail-reproductif.md</t>
+          <t>corpus/livre-04-les-cahiers-humanistes/c09-federici-fraser-et-le-travail-reproductif.md</t>
         </is>
       </c>
     </row>
@@ -5871,7 +5871,7 @@
       <c r="L73" s="3" t="inlineStr"/>
       <c r="M73" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-04/c10-foucault-ehrenberg-byung-chul-han-et-l-auto-exploitation-contemporaine.md</t>
+          <t>corpus/livre-04-les-cahiers-humanistes/c10-foucault-ehrenberg-byung-chul-han-et-l-auto-exploitation-contemporaine.md</t>
         </is>
       </c>
     </row>
@@ -5926,7 +5926,7 @@
       <c r="L74" s="3" t="inlineStr"/>
       <c r="M74" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-04/c11-tainter-tort-suzman-effondrement-effet-reversif-autres-cosmologies.md</t>
+          <t>corpus/livre-04-les-cahiers-humanistes/c11-tainter-tort-suzman-effondrement-effet-reversif-autres-cosmologies.md</t>
         </is>
       </c>
     </row>
@@ -5989,7 +5989,7 @@
       </c>
       <c r="M75" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-05/c01-ce-que-ce-livre-doit-etablir.md</t>
+          <t>corpus/livre-05-trajectoires-et-transitions/c01-ce-que-ce-livre-doit-etablir.md</t>
         </is>
       </c>
     </row>
@@ -6052,7 +6052,7 @@
       </c>
       <c r="M76" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-05/c02-la-voie-de-l-infrastructure-et-ce-qu-elle-exige.md</t>
+          <t>corpus/livre-05-trajectoires-et-transitions/c02-la-voie-de-l-infrastructure-et-ce-qu-elle-exige.md</t>
         </is>
       </c>
     </row>
@@ -6115,7 +6115,7 @@
       </c>
       <c r="M77" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-05/c03-la-coalition-pilote-et-ce-qu-elle-reserve.md</t>
+          <t>corpus/livre-05-trajectoires-et-transitions/c03-la-coalition-pilote-et-ce-qu-elle-reserve.md</t>
         </is>
       </c>
     </row>
@@ -6178,7 +6178,7 @@
       </c>
       <c r="M78" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-05/c04-la-voie-multilaterale-et-son-mode-d-echec.md</t>
+          <t>corpus/livre-05-trajectoires-et-transitions/c04-la-voie-multilaterale-et-son-mode-d-echec.md</t>
         </is>
       </c>
     </row>
@@ -6241,7 +6241,7 @@
       </c>
       <c r="M79" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-05/c05-la-voie-regionale-et-le-precedent-qu-elle-invoque.md</t>
+          <t>corpus/livre-05-trajectoires-et-transitions/c05-la-voie-regionale-et-le-precedent-qu-elle-invoque.md</t>
         </is>
       </c>
     </row>
@@ -6304,7 +6304,7 @@
       </c>
       <c r="M80" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-05/c06-la-fenetre-de-crise-n-est-pas-une-voie.md</t>
+          <t>corpus/livre-05-trajectoires-et-transitions/c06-la-fenetre-de-crise-n-est-pas-une-voie.md</t>
         </is>
       </c>
     </row>
@@ -6367,7 +6367,7 @@
       </c>
       <c r="M81" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-05/c07-la-concurrence-des-alternatives.md</t>
+          <t>corpus/livre-05-trajectoires-et-transitions/c07-la-concurrence-des-alternatives.md</t>
         </is>
       </c>
     </row>
@@ -6430,7 +6430,7 @@
       </c>
       <c r="M82" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-05/c08-la-transition-sectorielle-et-ce-qu-elle-suppose.md</t>
+          <t>corpus/livre-05-trajectoires-et-transitions/c08-la-transition-sectorielle-et-ce-qu-elle-suppose.md</t>
         </is>
       </c>
     </row>
@@ -6493,7 +6493,7 @@
       </c>
       <c r="M83" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-05/c09-la-comparaison-des-voies.md</t>
+          <t>corpus/livre-05-trajectoires-et-transitions/c09-la-comparaison-des-voies.md</t>
         </is>
       </c>
     </row>
@@ -6556,7 +6556,7 @@
       </c>
       <c r="M84" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-05/c10-portee-du-livre-et-ou-il-laisse-f6.md</t>
+          <t>corpus/livre-05-trajectoires-et-transitions/c10-portee-du-livre-et-ou-il-laisse-f6.md</t>
         </is>
       </c>
     </row>
@@ -6619,7 +6619,7 @@
       </c>
       <c r="M85" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-06/c01-ce-que-ce-livre-doit-etablir.md</t>
+          <t>corpus/livre-06-droits-de-la-nature-et-des-ecosystemes/c01-ce-que-ce-livre-doit-etablir.md</t>
         </is>
       </c>
     </row>
@@ -6682,7 +6682,7 @@
       </c>
       <c r="M86" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-06/c02-la-discipline-des-cinq-donnees.md</t>
+          <t>corpus/livre-06-droits-de-la-nature-et-des-ecosystemes/c02-la-discipline-des-cinq-donnees.md</t>
         </is>
       </c>
     </row>
@@ -6745,7 +6745,7 @@
       </c>
       <c r="M87" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-06/c03-le-sixieme-etat-et-l-exhaustivite-negative.md</t>
+          <t>corpus/livre-06-droits-de-la-nature-et-des-ecosystemes/c03-le-sixieme-etat-et-l-exhaustivite-negative.md</t>
         </is>
       </c>
     </row>
@@ -6808,7 +6808,7 @@
       </c>
       <c r="M88" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-06/c04-ce-que-les-rapports-de-defrichage-ont-produit-de-faux.md</t>
+          <t>corpus/livre-06-droits-de-la-nature-et-des-ecosystemes/c04-ce-que-les-rapports-de-defrichage-ont-produit-de-faux.md</t>
         </is>
       </c>
     </row>
@@ -6871,7 +6871,7 @@
       </c>
       <c r="M89" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-06/c05-qui-agit-quand-le-representant-est-le-defendeur.md</t>
+          <t>corpus/livre-06-droits-de-la-nature-et-des-ecosystemes/c05-qui-agit-quand-le-representant-est-le-defendeur.md</t>
         </is>
       </c>
     </row>
@@ -6934,7 +6934,7 @@
       </c>
       <c r="M90" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-06/c06-trois-regimes-de-commun-et-ce-qui-les-fait-tenir.md</t>
+          <t>corpus/livre-06-droits-de-la-nature-et-des-ecosystemes/c06-trois-regimes-de-commun-et-ce-qui-les-fait-tenir.md</t>
         </is>
       </c>
     </row>
@@ -6997,7 +6997,7 @@
       </c>
       <c r="M91" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-06/c07-la-charge-attachee-au-sol-et-qui-peut-la-refuser.md</t>
+          <t>corpus/livre-06-droits-de-la-nature-et-des-ecosystemes/c07-la-charge-attachee-au-sol-et-qui-peut-la-refuser.md</t>
         </is>
       </c>
     </row>
@@ -7060,7 +7060,7 @@
       </c>
       <c r="M92" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-06/c08-le-sous-sol-et-qui-a-competence-pour-dire-non.md</t>
+          <t>corpus/livre-06-droits-de-la-nature-et-des-ecosystemes/c08-le-sous-sol-et-qui-a-competence-pour-dire-non.md</t>
         </is>
       </c>
     </row>
@@ -7123,7 +7123,7 @@
       </c>
       <c r="M93" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-06/c09-l-obligation-desarmee-et-le-seuil-defini-par-sa-consequence.md</t>
+          <t>corpus/livre-06-droits-de-la-nature-et-des-ecosystemes/c09-l-obligation-desarmee-et-le-seuil-defini-par-sa-consequence.md</t>
         </is>
       </c>
     </row>
@@ -7186,7 +7186,7 @@
       </c>
       <c r="M94" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-06/c10-l-egalite-de-rang-et-le-prix-qu-on-empeche-de-signaler.md</t>
+          <t>corpus/livre-06-droits-de-la-nature-et-des-ecosystemes/c10-l-egalite-de-rang-et-le-prix-qu-on-empeche-de-signaler.md</t>
         </is>
       </c>
     </row>
@@ -7249,7 +7249,7 @@
       </c>
       <c r="M95" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-06/c11-trois-modeles-de-representation-et-aucun-qui-se-retourne.md</t>
+          <t>corpus/livre-06-droits-de-la-nature-et-des-ecosystemes/c11-trois-modeles-de-representation-et-aucun-qui-se-retourne.md</t>
         </is>
       </c>
     </row>
@@ -7312,7 +7312,7 @@
       </c>
       <c r="M96" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-06/c12-la-technique-qui-resiste-et-elle-protege-l-investisseur.md</t>
+          <t>corpus/livre-06-droits-de-la-nature-et-des-ecosystemes/c12-la-technique-qui-resiste-et-elle-protege-l-investisseur.md</t>
         </is>
       </c>
     </row>
@@ -7375,7 +7375,7 @@
       </c>
       <c r="M97" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-06/c13-un-regime-de-responsabilite-cree-puis-retire.md</t>
+          <t>corpus/livre-06-droits-de-la-nature-et-des-ecosystemes/c13-un-regime-de-responsabilite-cree-puis-retire.md</t>
         </is>
       </c>
     </row>
@@ -7438,7 +7438,7 @@
       </c>
       <c r="M98" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-07/c01-ce-que-ce-livre-doit-etablir.md</t>
+          <t>corpus/livre-07-organisation-du-gaia-economic-symposium/c01-ce-que-ce-livre-doit-etablir.md</t>
         </is>
       </c>
     </row>
@@ -7501,7 +7501,7 @@
       </c>
       <c r="M99" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-07/c02-les-trois-precedents-de-cle.md</t>
+          <t>corpus/livre-07-organisation-du-gaia-economic-symposium/c02-les-trois-precedents-de-cle.md</t>
         </is>
       </c>
     </row>
@@ -7564,7 +7564,7 @@
       </c>
       <c r="M100" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-07/c03-le-mandat-et-son-autorisation.md</t>
+          <t>corpus/livre-07-organisation-du-gaia-economic-symposium/c03-le-mandat-et-son-autorisation.md</t>
         </is>
       </c>
     </row>
@@ -7627,7 +7627,7 @@
       </c>
       <c r="M101" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-07/c04-le-conflit-d-interets-structurel.md</t>
+          <t>corpus/livre-07-organisation-du-gaia-economic-symposium/c04-le-conflit-d-interets-structurel.md</t>
         </is>
       </c>
     </row>
@@ -7690,7 +7690,7 @@
       </c>
       <c r="M102" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-07/c05-les-quatre-chambres.md</t>
+          <t>corpus/livre-07-organisation-du-gaia-economic-symposium/c05-les-quatre-chambres.md</t>
         </is>
       </c>
     </row>
@@ -7753,7 +7753,7 @@
       </c>
       <c r="M103" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-07/c06-la-reconnaissance-collective.md</t>
+          <t>corpus/livre-07-organisation-du-gaia-economic-symposium/c06-la-reconnaissance-collective.md</t>
         </is>
       </c>
     </row>
@@ -7816,7 +7816,7 @@
       </c>
       <c r="M104" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-07/c07-qui-audite-l-auditeur.md</t>
+          <t>corpus/livre-07-organisation-du-gaia-economic-symposium/c07-qui-audite-l-auditeur.md</t>
         </is>
       </c>
     </row>
@@ -7879,7 +7879,7 @@
       </c>
       <c r="M105" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-07/c08-le-frein-conservateur.md</t>
+          <t>corpus/livre-07-organisation-du-gaia-economic-symposium/c08-le-frein-conservateur.md</t>
         </is>
       </c>
     </row>
@@ -7942,7 +7942,7 @@
       </c>
       <c r="M106" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-07/c09-la-regle-de-vote-et-la-loi-de-penrose.md</t>
+          <t>corpus/livre-07-organisation-du-gaia-economic-symposium/c09-la-regle-de-vote-et-la-loi-de-penrose.md</t>
         </is>
       </c>
     </row>
@@ -8005,7 +8005,7 @@
       </c>
       <c r="M107" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-07/c10-les-garanties-et-la-capture-par-le-budget.md</t>
+          <t>corpus/livre-07-organisation-du-gaia-economic-symposium/c10-les-garanties-et-la-capture-par-le-budget.md</t>
         </is>
       </c>
     </row>
@@ -8068,7 +8068,7 @@
       </c>
       <c r="M108" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-07/c11-le-financement-du-symposium.md</t>
+          <t>corpus/livre-07-organisation-du-gaia-economic-symposium/c11-le-financement-du-symposium.md</t>
         </is>
       </c>
     </row>
@@ -8131,7 +8131,7 @@
       </c>
       <c r="M109" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-07/c12-le-point-de-demarrage.md</t>
+          <t>corpus/livre-07-organisation-du-gaia-economic-symposium/c12-le-point-de-demarrage.md</t>
         </is>
       </c>
     </row>
@@ -8194,7 +8194,7 @@
       </c>
       <c r="M110" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-07/c13-la-sanctuarisation-juridique.md</t>
+          <t>corpus/livre-07-organisation-du-gaia-economic-symposium/c13-la-sanctuarisation-juridique.md</t>
         </is>
       </c>
     </row>
@@ -8257,7 +8257,7 @@
       </c>
       <c r="M111" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-07/c14-la-chambre-de-recours.md</t>
+          <t>corpus/livre-07-organisation-du-gaia-economic-symposium/c14-la-chambre-de-recours.md</t>
         </is>
       </c>
     </row>
@@ -8320,7 +8320,7 @@
       </c>
       <c r="M112" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-07/c15-le-perimetre-finance.md</t>
+          <t>corpus/livre-07-organisation-du-gaia-economic-symposium/c15-le-perimetre-finance.md</t>
         </is>
       </c>
     </row>
@@ -8383,7 +8383,7 @@
       </c>
       <c r="M113" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-07/c16-l-adhesion-et-la-sortie.md</t>
+          <t>corpus/livre-07-organisation-du-gaia-economic-symposium/c16-l-adhesion-et-la-sortie.md</t>
         </is>
       </c>
     </row>
@@ -8446,7 +8446,7 @@
       </c>
       <c r="M114" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-07/c17-le-club-et-son-seuil.md</t>
+          <t>corpus/livre-07-organisation-du-gaia-economic-symposium/c17-le-club-et-son-seuil.md</t>
         </is>
       </c>
     </row>
@@ -8509,7 +8509,7 @@
       </c>
       <c r="M115" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-07/c18-la-fraude-et-le-scenario-de-reference.md</t>
+          <t>corpus/livre-07-organisation-du-gaia-economic-symposium/c18-la-fraude-et-le-scenario-de-reference.md</t>
         </is>
       </c>
     </row>
@@ -8572,7 +8572,7 @@
       </c>
       <c r="M116" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-07/c19-la-sanction-et-l-execution.md</t>
+          <t>corpus/livre-07-organisation-du-gaia-economic-symposium/c19-la-sanction-et-l-execution.md</t>
         </is>
       </c>
     </row>
@@ -8635,7 +8635,7 @@
       </c>
       <c r="M117" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-07/c20-l-amendement-et-la-revision.md</t>
+          <t>corpus/livre-07-organisation-du-gaia-economic-symposium/c20-l-amendement-et-la-revision.md</t>
         </is>
       </c>
     </row>
@@ -8698,7 +8698,7 @@
       </c>
       <c r="M118" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-07/c21-l-articulation-avec-l-existant.md</t>
+          <t>corpus/livre-07-organisation-du-gaia-economic-symposium/c21-l-articulation-avec-l-existant.md</t>
         </is>
       </c>
     </row>
@@ -8761,7 +8761,7 @@
       </c>
       <c r="M119" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-07/c22-la-portee-du-livre.md</t>
+          <t>corpus/livre-07-organisation-du-gaia-economic-symposium/c22-la-portee-du-livre.md</t>
         </is>
       </c>
     </row>
@@ -8824,7 +8824,7 @@
       </c>
       <c r="M120" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-08/c01-il-n-y-a-pas-une-theorie-standard.md</t>
+          <t>corpus/livre-08-theories-economiques-ecoles-et-angles-morts/c01-il-n-y-a-pas-une-theorie-standard.md</t>
         </is>
       </c>
     </row>
@@ -8887,7 +8887,7 @@
       </c>
       <c r="M121" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-08/c02-copernic-et-l-alteration-des-monnaies.md</t>
+          <t>corpus/livre-08-theories-economiques-ecoles-et-angles-morts/c02-copernic-et-l-alteration-des-monnaies.md</t>
         </is>
       </c>
     </row>
@@ -8950,7 +8950,7 @@
       </c>
       <c r="M122" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-08/c03-l-ecole-de-salamanque.md</t>
+          <t>corpus/livre-08-theories-economiques-ecoles-et-angles-morts/c03-l-ecole-de-salamanque.md</t>
         </is>
       </c>
     </row>
@@ -9013,7 +9013,7 @@
       </c>
       <c r="M123" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-08/c04-bodin-gresham-mun.md</t>
+          <t>corpus/livre-08-theories-economiques-ecoles-et-angles-morts/c04-bodin-gresham-mun.md</t>
         </is>
       </c>
     </row>
@@ -9076,7 +9076,7 @@
       </c>
       <c r="M124" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-08/c05-petty-et-l-arithmetique-politique.md</t>
+          <t>corpus/livre-08-theories-economiques-ecoles-et-angles-morts/c05-petty-et-l-arithmetique-politique.md</t>
         </is>
       </c>
     </row>
@@ -9139,7 +9139,7 @@
       </c>
       <c r="M125" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-08/c06-locke-et-law.md</t>
+          <t>corpus/livre-08-theories-economiques-ecoles-et-angles-morts/c06-locke-et-law.md</t>
         </is>
       </c>
     </row>
@@ -9202,7 +9202,7 @@
       </c>
       <c r="M126" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-08/c07-cantillon-et-l-effet-de-premier-receveur.md</t>
+          <t>corpus/livre-08-theories-economiques-ecoles-et-angles-morts/c07-cantillon-et-l-effet-de-premier-receveur.md</t>
         </is>
       </c>
     </row>
@@ -9265,7 +9265,7 @@
       </c>
       <c r="M127" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-08/c08-quesnay-et-les-physiocrates.md</t>
+          <t>corpus/livre-08-theories-economiques-ecoles-et-angles-morts/c08-quesnay-et-les-physiocrates.md</t>
         </is>
       </c>
     </row>
@@ -9328,7 +9328,7 @@
       </c>
       <c r="M128" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-08/c09-turgot-et-le-taux-fixe-par-decret.md</t>
+          <t>corpus/livre-08-theories-economiques-ecoles-et-angles-morts/c09-turgot-et-le-taux-fixe-par-decret.md</t>
         </is>
       </c>
     </row>
@@ -9391,7 +9391,7 @@
       </c>
       <c r="M129" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-08/c10-hume-et-le-mecanisme-des-flux-d-especes.md</t>
+          <t>corpus/livre-08-theories-economiques-ecoles-et-angles-morts/c10-hume-et-le-mecanisme-des-flux-d-especes.md</t>
         </is>
       </c>
     </row>
@@ -9454,7 +9454,7 @@
       </c>
       <c r="M130" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-08/c11-smith-et-l-ordre-non-intentionnel.md</t>
+          <t>corpus/livre-08-theories-economiques-ecoles-et-angles-morts/c11-smith-et-l-ordre-non-intentionnel.md</t>
         </is>
       </c>
     </row>
@@ -9517,7 +9517,7 @@
       </c>
       <c r="M131" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-08/c12-ricardo-rente-et-avantage-comparatif.md</t>
+          <t>corpus/livre-08-theories-economiques-ecoles-et-angles-morts/c12-ricardo-rente-et-avantage-comparatif.md</t>
         </is>
       </c>
     </row>
@@ -9580,7 +9580,7 @@
       </c>
       <c r="M132" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-08/c13-malthus-et-la-limite-physique.md</t>
+          <t>corpus/livre-08-theories-economiques-ecoles-et-angles-morts/c13-malthus-et-la-limite-physique.md</t>
         </is>
       </c>
     </row>
@@ -9643,7 +9643,7 @@
       </c>
       <c r="M133" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-08/c14-la-loi-des-debouches.md</t>
+          <t>corpus/livre-08-theories-economiques-ecoles-et-angles-morts/c14-la-loi-des-debouches.md</t>
         </is>
       </c>
     </row>
@@ -9706,7 +9706,7 @@
       </c>
       <c r="M134" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-08/c15-mill-et-l-etat-stationnaire.md</t>
+          <t>corpus/livre-08-theories-economiques-ecoles-et-angles-morts/c15-mill-et-l-etat-stationnaire.md</t>
         </is>
       </c>
     </row>
@@ -9769,7 +9769,7 @@
       </c>
       <c r="M135" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-08/c16-currency-school-contre-banking-school.md</t>
+          <t>corpus/livre-08-theories-economiques-ecoles-et-angles-morts/c16-currency-school-contre-banking-school.md</t>
         </is>
       </c>
     </row>
@@ -9832,7 +9832,7 @@
       </c>
       <c r="M136" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-08/c17-marx-et-la-neutralite-de-la-monnaie.md</t>
+          <t>corpus/livre-08-theories-economiques-ecoles-et-angles-morts/c17-marx-et-la-neutralite-de-la-monnaie.md</t>
         </is>
       </c>
     </row>
@@ -9895,7 +9895,7 @@
       </c>
       <c r="M137" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-08/c18-l-ecole-historique-et-veblen.md</t>
+          <t>corpus/livre-08-theories-economiques-ecoles-et-angles-morts/c18-l-ecole-historique-et-veblen.md</t>
         </is>
       </c>
     </row>
@@ -9958,7 +9958,7 @@
       </c>
       <c r="M138" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-08/c19-proudhon-et-le-credit-gratuit.md</t>
+          <t>corpus/livre-08-theories-economiques-ecoles-et-angles-morts/c19-proudhon-et-le-credit-gratuit.md</t>
         </is>
       </c>
     </row>
@@ -10021,7 +10021,7 @@
       </c>
       <c r="M139" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-08/c20-gesell-et-la-monnaie-franche.md</t>
+          <t>corpus/livre-08-theories-economiques-ecoles-et-angles-morts/c20-gesell-et-la-monnaie-franche.md</t>
         </is>
       </c>
     </row>
@@ -10084,7 +10084,7 @@
       </c>
       <c r="M140" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-08/c21-la-revolution-marginaliste.md</t>
+          <t>corpus/livre-08-theories-economiques-ecoles-et-angles-morts/c21-la-revolution-marginaliste.md</t>
         </is>
       </c>
     </row>
@@ -10147,7 +10147,7 @@
       </c>
       <c r="M141" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-08/c22-marshall-et-le-ceteris-paribus.md</t>
+          <t>corpus/livre-08-theories-economiques-ecoles-et-angles-morts/c22-marshall-et-le-ceteris-paribus.md</t>
         </is>
       </c>
     </row>
@@ -10210,7 +10210,7 @@
       </c>
       <c r="M142" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-08/c23-wicksell-et-la-monnaie-endogene.md</t>
+          <t>corpus/livre-08-theories-economiques-ecoles-et-angles-morts/c23-wicksell-et-la-monnaie-endogene.md</t>
         </is>
       </c>
     </row>
@@ -10273,7 +10273,7 @@
       </c>
       <c r="M143" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-08/c24-fisher-et-la-separation-monnaie-credit.md</t>
+          <t>corpus/livre-08-theories-economiques-ecoles-et-angles-morts/c24-fisher-et-la-separation-monnaie-credit.md</t>
         </is>
       </c>
     </row>
@@ -10336,7 +10336,7 @@
       </c>
       <c r="M144" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-08/c25-pigou-et-le-prix-administre.md</t>
+          <t>corpus/livre-08-theories-economiques-ecoles-et-angles-morts/c25-pigou-et-le-prix-administre.md</t>
         </is>
       </c>
     </row>
@@ -10399,7 +10399,7 @@
       </c>
       <c r="M145" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-08/c26-keynes-et-la-demande-effective.md</t>
+          <t>corpus/livre-08-theories-economiques-ecoles-et-angles-morts/c26-keynes-et-la-demande-effective.md</t>
         </is>
       </c>
     </row>
@@ -10462,7 +10462,7 @@
       </c>
       <c r="M146" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-08/c27-keynes-a-bretton-woods.md</t>
+          <t>corpus/livre-08-theories-economiques-ecoles-et-angles-morts/c27-keynes-a-bretton-woods.md</t>
         </is>
       </c>
     </row>
@@ -10525,7 +10525,7 @@
       </c>
       <c r="M147" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-08/c28-tinbergen-mundell-et-l-affectation.md</t>
+          <t>corpus/livre-08-theories-economiques-ecoles-et-angles-morts/c28-tinbergen-mundell-et-l-affectation.md</t>
         </is>
       </c>
     </row>
@@ -10588,7 +10588,7 @@
       </c>
       <c r="M148" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-08/c29-hayek-et-le-debat-du-calcul.md</t>
+          <t>corpus/livre-08-theories-economiques-ecoles-et-angles-morts/c29-hayek-et-le-debat-du-calcul.md</t>
         </is>
       </c>
     </row>
@@ -10651,7 +10651,7 @@
       </c>
       <c r="M149" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-08/c30-friedman-et-le-monetarisme.md</t>
+          <t>corpus/livre-08-theories-economiques-ecoles-et-angles-morts/c30-friedman-et-le-monetarisme.md</t>
         </is>
       </c>
     </row>
@@ -10714,7 +10714,7 @@
       </c>
       <c r="M150" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-08/c31-lucas-kydland-prescott-et-les-anticipations.md</t>
+          <t>corpus/livre-08-theories-economiques-ecoles-et-angles-morts/c31-lucas-kydland-prescott-et-les-anticipations.md</t>
         </is>
       </c>
     </row>
@@ -10777,7 +10777,7 @@
       </c>
       <c r="M151" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-08/c32-les-nouveaux-keynesiens.md</t>
+          <t>corpus/livre-08-theories-economiques-ecoles-et-angles-morts/c32-les-nouveaux-keynesiens.md</t>
         </is>
       </c>
     </row>
@@ -10840,7 +10840,7 @@
       </c>
       <c r="M152" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-08/c33-ostrom-et-la-gouvernance-des-communs.md</t>
+          <t>corpus/livre-08-theories-economiques-ecoles-et-angles-morts/c33-ostrom-et-la-gouvernance-des-communs.md</t>
         </is>
       </c>
     </row>
@@ -10903,7 +10903,7 @@
       </c>
       <c r="M153" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-08/c34-l-economie-ecologique.md</t>
+          <t>corpus/livre-08-theories-economiques-ecoles-et-angles-morts/c34-l-economie-ecologique.md</t>
         </is>
       </c>
     </row>
@@ -10966,7 +10966,7 @@
       </c>
       <c r="M154" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-08/c35-l-economie-comportementale.md</t>
+          <t>corpus/livre-08-theories-economiques-ecoles-et-angles-morts/c35-l-economie-comportementale.md</t>
         </is>
       </c>
     </row>
@@ -11029,7 +11029,7 @@
       </c>
       <c r="M155" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-08/c36-la-revolution-de-la-credibilite.md</t>
+          <t>corpus/livre-08-theories-economiques-ecoles-et-angles-morts/c36-la-revolution-de-la-credibilite.md</t>
         </is>
       </c>
     </row>
@@ -11092,7 +11092,7 @@
       </c>
       <c r="M156" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-08/c37-la-macroeconomie-apres-2008.md</t>
+          <t>corpus/livre-08-theories-economiques-ecoles-et-angles-morts/c37-la-macroeconomie-apres-2008.md</t>
         </is>
       </c>
     </row>
@@ -11155,7 +11155,7 @@
       </c>
       <c r="M157" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-08/c38-monnaie-endogene-contemporaine-et-mmt.md</t>
+          <t>corpus/livre-08-theories-economiques-ecoles-et-angles-morts/c38-monnaie-endogene-contemporaine-et-mmt.md</t>
         </is>
       </c>
     </row>
@@ -11218,7 +11218,7 @@
       </c>
       <c r="M158" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-08/c39-post-croissance-et-inegalite.md</t>
+          <t>corpus/livre-08-theories-economiques-ecoles-et-angles-morts/c39-post-croissance-et-inegalite.md</t>
         </is>
       </c>
     </row>
@@ -11281,7 +11281,7 @@
       </c>
       <c r="M159" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-08/c40-ce-qui-n-est-pas-encore-une-ecole.md</t>
+          <t>corpus/livre-08-theories-economiques-ecoles-et-angles-morts/c40-ce-qui-n-est-pas-encore-une-ecole.md</t>
         </is>
       </c>
     </row>
@@ -11344,7 +11344,7 @@
       </c>
       <c r="M160" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-08/c41-la-portee-du-livre.md</t>
+          <t>corpus/livre-08-theories-economiques-ecoles-et-angles-morts/c41-la-portee-du-livre.md</t>
         </is>
       </c>
     </row>
@@ -11407,7 +11407,7 @@
       </c>
       <c r="M161" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-10/c01-le-referentiel-qui-s-applique-vraiment.md</t>
+          <t>corpus/livre-10-monnaies-banques-et-banques-centrales/c01-le-referentiel-qui-s-applique-vraiment.md</t>
         </is>
       </c>
     </row>
@@ -11470,7 +11470,7 @@
       </c>
       <c r="M162" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-10/c02-la-derogation-existe-et-elle-referme-une-tenaille.md</t>
+          <t>corpus/livre-10-monnaies-banques-et-banques-centrales/c02-la-derogation-existe-et-elle-referme-une-tenaille.md</t>
         </is>
       </c>
     </row>
@@ -11533,7 +11533,7 @@
       </c>
       <c r="M163" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-10/c03-la-certitude-qui-fait-marcher-le-dispositif-est-celle-que-la-cour-interdit.md</t>
+          <t>corpus/livre-10-monnaies-banques-et-banques-centrales/c03-la-certitude-qui-fait-marcher-le-dispositif-est-celle-que-la-cour-interdit.md</t>
         </is>
       </c>
     </row>
@@ -11596,7 +11596,7 @@
       </c>
       <c r="M164" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-10/c04-qui-la-prohibition-vise-et-ou-le-corpus-avait-trop-dit.md</t>
+          <t>corpus/livre-10-monnaies-banques-et-banques-centrales/c04-qui-la-prohibition-vise-et-ou-le-corpus-avait-trop-dit.md</t>
         </is>
       </c>
     </row>
@@ -11659,7 +11659,7 @@
       </c>
       <c r="M165" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-10/c05-la-definition-balai-et-ce-qu-elle-emporte.md</t>
+          <t>corpus/livre-10-monnaies-banques-et-banques-centrales/c05-la-definition-balai-et-ce-qu-elle-emporte.md</t>
         </is>
       </c>
     </row>
@@ -11722,7 +11722,7 @@
       </c>
       <c r="M166" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-10/c06-l-arbitrage-a35-et-ce-qu-il-deplace.md</t>
+          <t>corpus/livre-10-monnaies-banques-et-banques-centrales/c06-l-arbitrage-a35-et-ce-qu-il-deplace.md</t>
         </is>
       </c>
     </row>
@@ -11785,7 +11785,7 @@
       </c>
       <c r="M167" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-11/c01-reflux-ou-destruction.md</t>
+          <t>corpus/livre-11-ingenierie-des-baremes/c01-reflux-ou-destruction.md</t>
         </is>
       </c>
     </row>
@@ -11848,7 +11848,7 @@
       </c>
       <c r="M168" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-11/c02-le-trajet-complet-de-la-valeur.md</t>
+          <t>corpus/livre-11-ingenierie-des-baremes/c02-le-trajet-complet-de-la-valeur.md</t>
         </is>
       </c>
     </row>
@@ -11911,7 +11911,7 @@
       </c>
       <c r="M169" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-11/c03-le-compte-des-objectifs-et-des-instruments.md</t>
+          <t>corpus/livre-11-ingenierie-des-baremes/c03-le-compte-des-objectifs-et-des-instruments.md</t>
         </is>
       </c>
     </row>
@@ -11974,7 +11974,7 @@
       </c>
       <c r="M170" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-11/c04-les-instruments-du-reflux-sous-parite-fixe.md</t>
+          <t>corpus/livre-11-ingenierie-des-baremes/c04-les-instruments-du-reflux-sous-parite-fixe.md</t>
         </is>
       </c>
     </row>
@@ -12037,7 +12037,7 @@
       </c>
       <c r="M171" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-11/c05-l-assiette-du-reflux-transactionnel.md</t>
+          <t>corpus/livre-11-ingenierie-des-baremes/c05-l-assiette-du-reflux-transactionnel.md</t>
         </is>
       </c>
     </row>
@@ -12100,7 +12100,7 @@
       </c>
       <c r="M172" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-11/c06-le-bareme-par-defaut.md</t>
+          <t>corpus/livre-11-ingenierie-des-baremes/c06-le-bareme-par-defaut.md</t>
         </is>
       </c>
     </row>
@@ -12163,7 +12163,7 @@
       </c>
       <c r="M173" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-11/c07-le-demurrage-et-son-noeud.md</t>
+          <t>corpus/livre-11-ingenierie-des-baremes/c07-le-demurrage-et-son-noeud.md</t>
         </is>
       </c>
     </row>
@@ -12226,7 +12226,7 @@
       </c>
       <c r="M174" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-11/c08-les-derogations.md</t>
+          <t>corpus/livre-11-ingenierie-des-baremes/c08-les-derogations.md</t>
         </is>
       </c>
     </row>
@@ -12289,7 +12289,7 @@
       </c>
       <c r="M175" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-11/c09-l-incidence-qui-paie-le-reflux.md</t>
+          <t>corpus/livre-11-ingenierie-des-baremes/c09-l-incidence-qui-paie-le-reflux.md</t>
         </is>
       </c>
     </row>
@@ -12352,7 +12352,7 @@
       </c>
       <c r="M176" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-11/c10-la-trajectoire-de-mise-en-place.md</t>
+          <t>corpus/livre-11-ingenierie-des-baremes/c10-la-trajectoire-de-mise-en-place.md</t>
         </is>
       </c>
     </row>
@@ -12415,7 +12415,7 @@
       </c>
       <c r="M177" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-11/c11-qui-arrete-le-bareme.md</t>
+          <t>corpus/livre-11-ingenierie-des-baremes/c11-qui-arrete-le-bareme.md</t>
         </is>
       </c>
     </row>
@@ -12478,7 +12478,7 @@
       </c>
       <c r="M178" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-11/c12-la-directive.md</t>
+          <t>corpus/livre-11-ingenierie-des-baremes/c12-la-directive.md</t>
         </is>
       </c>
     </row>
@@ -12541,7 +12541,7 @@
       </c>
       <c r="M179" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-11/c13-le-bareme-de-qualification.md</t>
+          <t>corpus/livre-11-ingenierie-des-baremes/c13-le-bareme-de-qualification.md</t>
         </is>
       </c>
     </row>
@@ -12604,7 +12604,7 @@
       </c>
       <c r="M180" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-11/c14-le-tableau-de-bord.md</t>
+          <t>corpus/livre-11-ingenierie-des-baremes/c14-le-tableau-de-bord.md</t>
         </is>
       </c>
     </row>
@@ -12667,7 +12667,7 @@
       </c>
       <c r="M181" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-11/c15-les-parites-du-referentiel.md</t>
+          <t>corpus/livre-11-ingenierie-des-baremes/c15-les-parites-du-referentiel.md</t>
         </is>
       </c>
     </row>
@@ -12730,7 +12730,7 @@
       </c>
       <c r="M182" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-11/c16-la-valorisation-des-communs.md</t>
+          <t>corpus/livre-11-ingenierie-des-baremes/c16-la-valorisation-des-communs.md</t>
         </is>
       </c>
     </row>
@@ -12793,7 +12793,7 @@
       </c>
       <c r="M183" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-11/c17-la-coherence-des-cinq-baremes.md</t>
+          <t>corpus/livre-11-ingenierie-des-baremes/c17-la-coherence-des-cinq-baremes.md</t>
         </is>
       </c>
     </row>
@@ -12856,7 +12856,7 @@
       </c>
       <c r="M184" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-11/c18-le-seuil-d-exemption.md</t>
+          <t>corpus/livre-11-ingenierie-des-baremes/c18-le-seuil-d-exemption.md</t>
         </is>
       </c>
     </row>
@@ -12919,7 +12919,7 @@
       </c>
       <c r="M185" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-11/c19-le-recours.md</t>
+          <t>corpus/livre-11-ingenierie-des-baremes/c19-le-recours.md</t>
         </is>
       </c>
     </row>
@@ -12982,7 +12982,7 @@
       </c>
       <c r="M186" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-11/c20-l-amendement-de-la-directive.md</t>
+          <t>corpus/livre-11-ingenierie-des-baremes/c20-l-amendement-de-la-directive.md</t>
         </is>
       </c>
     </row>
@@ -13045,7 +13045,7 @@
       </c>
       <c r="M187" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-11/c21-la-perception.md</t>
+          <t>corpus/livre-11-ingenierie-des-baremes/c21-la-perception.md</t>
         </is>
       </c>
     </row>
@@ -13108,7 +13108,7 @@
       </c>
       <c r="M188" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-11/c22-les-delais.md</t>
+          <t>corpus/livre-11-ingenierie-des-baremes/c22-les-delais.md</t>
         </is>
       </c>
     </row>
@@ -13171,7 +13171,7 @@
       </c>
       <c r="M189" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-11/c23-la-contracyclicite.md</t>
+          <t>corpus/livre-11-ingenierie-des-baremes/c23-la-contracyclicite.md</t>
         </is>
       </c>
     </row>
@@ -13234,7 +13234,7 @@
       </c>
       <c r="M190" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-11/c24-le-bareme-aux-frontieres.md</t>
+          <t>corpus/livre-11-ingenierie-des-baremes/c24-le-bareme-aux-frontieres.md</t>
         </is>
       </c>
     </row>
@@ -13297,7 +13297,7 @@
       </c>
       <c r="M191" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-11/c25-le-controle.md</t>
+          <t>corpus/livre-11-ingenierie-des-baremes/c25-le-controle.md</t>
         </is>
       </c>
     </row>
@@ -13360,7 +13360,7 @@
       </c>
       <c r="M192" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-11/c26-la-portee-du-livre.md</t>
+          <t>corpus/livre-11-ingenierie-des-baremes/c26-la-portee-du-livre.md</t>
         </is>
       </c>
     </row>
@@ -13423,7 +13423,7 @@
       </c>
       <c r="M193" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-11/c27-l-assiette-de-la-fonte-est-celle-de-la-tva.md</t>
+          <t>corpus/livre-11-ingenierie-des-baremes/c27-l-assiette-de-la-fonte-est-celle-de-la-tva.md</t>
         </is>
       </c>
     </row>
@@ -13486,7 +13486,7 @@
       </c>
       <c r="M194" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-11/c28-la-fonte-sur-les-acquisitions-d-actifs-eprouvee.md</t>
+          <t>corpus/livre-11-ingenierie-des-baremes/c28-la-fonte-sur-les-acquisitions-d-actifs-eprouvee.md</t>
         </is>
       </c>
     </row>
@@ -13549,7 +13549,7 @@
       </c>
       <c r="M195" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-11/c29-la-structure-des-sanctions.md</t>
+          <t>corpus/livre-11-ingenierie-des-baremes/c29-la-structure-des-sanctions.md</t>
         </is>
       </c>
     </row>
@@ -13612,7 +13612,7 @@
       </c>
       <c r="M196" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-18/c01-ce-que-ce-livre-doit-etablir.md</t>
+          <t>corpus/livre-18-comptabilites-ecologiques-et-biophysiques/c01-ce-que-ce-livre-doit-etablir.md</t>
         </is>
       </c>
     </row>
@@ -13675,7 +13675,7 @@
       </c>
       <c r="M197" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-18/c02-la-metrologie-existe-et-ce-qu-elle-enregistre.md</t>
+          <t>corpus/livre-18-comptabilites-ecologiques-et-biophysiques/c02-la-metrologie-existe-et-ce-qu-elle-enregistre.md</t>
         </is>
       </c>
     </row>
@@ -13738,7 +13738,7 @@
       </c>
       <c r="M198" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-18/c03-l-echelle-de-repli-et-qui-l-a-arretee.md</t>
+          <t>corpus/livre-18-comptabilites-ecologiques-et-biophysiques/c03-l-echelle-de-repli-et-qui-l-a-arretee.md</t>
         </is>
       </c>
     </row>
@@ -13801,7 +13801,7 @@
       </c>
       <c r="M199" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-18/c04-les-grandeurs-physiques-et-ou-elles-frappent.md</t>
+          <t>corpus/livre-18-comptabilites-ecologiques-et-biophysiques/c04-les-grandeurs-physiques-et-ou-elles-frappent.md</t>
         </is>
       </c>
     </row>
@@ -13818,7 +13818,7 @@
       </c>
       <c r="C200" s="3" t="inlineStr">
         <is>
-          <t>Le commun est ce que la norme exclut, et la symétrie de l'écriture</t>
+          <t>Ce que la norme exclut, et ce n'est pas le commun</t>
         </is>
       </c>
       <c r="D200" s="3" t="inlineStr">
@@ -13864,7 +13864,7 @@
       </c>
       <c r="M200" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-18/c05-le-commun-est-ce-que-la-norme-exclut.md</t>
+          <t>corpus/livre-18-comptabilites-ecologiques-et-biophysiques/c05-ce-que-la-norme-exclut-et-ce-n-est-pas-le-commun.md</t>
         </is>
       </c>
     </row>
@@ -13927,7 +13927,7 @@
       </c>
       <c r="M201" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-18/c06-portee-de-la-tranche-et-une-neuvieme-condition.md</t>
+          <t>corpus/livre-18-comptabilites-ecologiques-et-biophysiques/c06-portee-de-la-tranche-et-une-neuvieme-condition.md</t>
         </is>
       </c>
     </row>
@@ -13990,7 +13990,7 @@
       </c>
       <c r="M202" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-18/c07-care-tdl-repare-une-objection-et-en-cree-une-autre.md</t>
+          <t>corpus/livre-18-comptabilites-ecologiques-et-biophysiques/c07-care-tdl-repare-une-objection-et-en-cree-une-autre.md</t>
         </is>
       </c>
     </row>
@@ -14053,7 +14053,7 @@
       </c>
       <c r="M203" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-18/c08-le-modele-au-perimetre-du-dispositif-et-f9-revisee.md</t>
+          <t>corpus/livre-18-comptabilites-ecologiques-et-biophysiques/c08-le-modele-au-perimetre-du-dispositif-et-f9-revisee.md</t>
         </is>
       </c>
     </row>
@@ -14116,7 +14116,7 @@
       </c>
       <c r="M204" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-20/c01-ce-que-ce-livre-doit-etablir.md</t>
+          <t>corpus/livre-20-droit-international-monetaire-et-commercial/c01-ce-que-ce-livre-doit-etablir.md</t>
         </is>
       </c>
     </row>
@@ -14179,7 +14179,7 @@
       </c>
       <c r="M205" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-20/c02-l-interdiction-du-financement-monetaire.md</t>
+          <t>corpus/livre-20-droit-international-monetaire-et-commercial/c02-l-interdiction-du-financement-monetaire.md</t>
         </is>
       </c>
     </row>
@@ -14242,7 +14242,7 @@
       </c>
       <c r="M206" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-20/c03-l-objectif-principal-et-ce-qu-il-exclut.md</t>
+          <t>corpus/livre-20-droit-international-monetaire-et-commercial/c03-l-objectif-principal-et-ce-qu-il-exclut.md</t>
         </is>
       </c>
     </row>
@@ -14305,7 +14305,7 @@
       </c>
       <c r="M207" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-20/c04-l-independance-et-a-l-egard-de-qui.md</t>
+          <t>corpus/livre-20-droit-international-monetaire-et-commercial/c04-l-independance-et-a-l-egard-de-qui.md</t>
         </is>
       </c>
     </row>
@@ -14368,7 +14368,7 @@
       </c>
       <c r="M208" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-20/c05-le-monopole-d-emission-et-le-cours-legal.md</t>
+          <t>corpus/livre-20-droit-international-monetaire-et-commercial/c05-le-monopole-d-emission-et-le-cours-legal.md</t>
         </is>
       </c>
     </row>
@@ -14431,7 +14431,7 @@
       </c>
       <c r="M209" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-20/c06-les-voies-de-revision-et-leur-cout.md</t>
+          <t>corpus/livre-20-droit-international-monetaire-et-commercial/c06-les-voies-de-revision-et-leur-cout.md</t>
         </is>
       </c>
     </row>
@@ -14494,7 +14494,7 @@
       </c>
       <c r="M210" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-20/c07-l-accord-monetaire-international.md</t>
+          <t>corpus/livre-20-droit-international-monetaire-et-commercial/c07-l-accord-monetaire-international.md</t>
         </is>
       </c>
     </row>
@@ -14557,7 +14557,7 @@
       </c>
       <c r="M211" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-20/c08-la-parite-inscrite-dans-le-traite.md</t>
+          <t>corpus/livre-20-droit-international-monetaire-et-commercial/c08-la-parite-inscrite-dans-le-traite.md</t>
         </is>
       </c>
     </row>
@@ -14620,7 +14620,7 @@
       </c>
       <c r="M212" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-20/c09-l-amendement-des-statuts-du-fonds.md</t>
+          <t>corpus/livre-20-droit-international-monetaire-et-commercial/c09-l-amendement-des-statuts-du-fonds.md</t>
         </is>
       </c>
     </row>
@@ -14683,7 +14683,7 @@
       </c>
       <c r="M213" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-20/c10-le-vote-pondere-et-les-voix-de-base.md</t>
+          <t>corpus/livre-20-droit-international-monetaire-et-commercial/c10-le-vote-pondere-et-les-voix-de-base.md</t>
         </is>
       </c>
     </row>
@@ -14746,7 +14746,7 @@
       </c>
       <c r="M214" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-20/c11-la-personnalite-juridique-et-les-immunites.md</t>
+          <t>corpus/livre-20-droit-international-monetaire-et-commercial/c11-la-personnalite-juridique-et-les-immunites.md</t>
         </is>
       </c>
     </row>
@@ -14809,7 +14809,7 @@
       </c>
       <c r="M215" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-20/c12-les-pouvoirs-non-delegables.md</t>
+          <t>corpus/livre-20-droit-international-monetaire-et-commercial/c12-les-pouvoirs-non-delegables.md</t>
         </is>
       </c>
     </row>
@@ -14872,7 +14872,7 @@
       </c>
       <c r="M216" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-20/c13-l-entree-en-vigueur-l-adhesion-et-le-retrait.md</t>
+          <t>corpus/livre-20-droit-international-monetaire-et-commercial/c13-l-entree-en-vigueur-l-adhesion-et-le-retrait.md</t>
         </is>
       </c>
     </row>
@@ -14935,7 +14935,7 @@
       </c>
       <c r="M217" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-20/c14-qui-interprete-le-traite.md</t>
+          <t>corpus/livre-20-droit-international-monetaire-et-commercial/c14-qui-interprete-le-traite.md</t>
         </is>
       </c>
     </row>
@@ -14998,7 +14998,7 @@
       </c>
       <c r="M218" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-20/c15-le-devoir-international-des-agents.md</t>
+          <t>corpus/livre-20-droit-international-monetaire-et-commercial/c15-le-devoir-international-des-agents.md</t>
         </is>
       </c>
     </row>
@@ -15061,7 +15061,7 @@
       </c>
       <c r="M219" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-20/c16-le-patrimoine-commun-de-l-humanite.md</t>
+          <t>corpus/livre-20-droit-international-monetaire-et-commercial/c16-le-patrimoine-commun-de-l-humanite.md</t>
         </is>
       </c>
     </row>
@@ -15124,7 +15124,7 @@
       </c>
       <c r="M220" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-20/c17-la-sanctuarisation-et-elle-existe.md</t>
+          <t>corpus/livre-20-droit-international-monetaire-et-commercial/c17-la-sanctuarisation-et-elle-existe.md</t>
         </is>
       </c>
     </row>
@@ -15187,7 +15187,7 @@
       </c>
       <c r="M221" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-20/c18-l-amendement-et-la-derogation-dans-l-ordre-commercial.md</t>
+          <t>corpus/livre-20-droit-international-monetaire-et-commercial/c18-l-amendement-et-la-derogation-dans-l-ordre-commercial.md</t>
         </is>
       </c>
     </row>
@@ -15250,7 +15250,7 @@
       </c>
       <c r="M222" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-20/c19-le-texte-que-la-conformite-invoque.md</t>
+          <t>corpus/livre-20-droit-international-monetaire-et-commercial/c19-le-texte-que-la-conformite-invoque.md</t>
         </is>
       </c>
     </row>
@@ -15313,7 +15313,7 @@
       </c>
       <c r="M223" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-20/c20-l-ajustement-aux-frontieres-comme-precedent.md</t>
+          <t>corpus/livre-20-droit-international-monetaire-et-commercial/c20-l-ajustement-aux-frontieres-comme-precedent.md</t>
         </is>
       </c>
     </row>
@@ -15376,7 +15376,7 @@
       </c>
       <c r="M224" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-20/c21-la-transparence-et-sa-limite-juridictionnelle.md</t>
+          <t>corpus/livre-20-droit-international-monetaire-et-commercial/c21-la-transparence-et-sa-limite-juridictionnelle.md</t>
         </is>
       </c>
     </row>
@@ -15439,7 +15439,7 @@
       </c>
       <c r="M225" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-20/c22-ce-que-le-droit-devrait-devenir.md</t>
+          <t>corpus/livre-20-droit-international-monetaire-et-commercial/c22-ce-que-le-droit-devrait-devenir.md</t>
         </is>
       </c>
     </row>
@@ -15502,7 +15502,7 @@
       </c>
       <c r="M226" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-20/c23-la-portee-du-livre.md</t>
+          <t>corpus/livre-20-droit-international-monetaire-et-commercial/c23-la-portee-du-livre.md</t>
         </is>
       </c>
     </row>
@@ -19502,7 +19502,7 @@
       </c>
       <c r="B227" s="3" t="inlineStr">
         <is>
-          <t>Le commun est ce que la norme exclut, et la symétrie de l'écriture</t>
+          <t>Ce que la norme exclut, et ce n'est pas le commun</t>
         </is>
       </c>
       <c r="C227" s="3" t="inlineStr">

--- a/plan-des-livres.xlsx
+++ b/plan-des-livres.xlsx
@@ -13,7 +13,7 @@
     <sheet name="Plan par livre" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Chapitres'!$A$1:$M$226</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Chapitres'!$A$1:$M$227</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -1288,7 +1288,7 @@
         </is>
       </c>
       <c r="F20" s="5" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G20" s="5" t="inlineStr"/>
       <c r="H20" s="5" t="inlineStr">
@@ -1354,7 +1354,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M226"/>
+  <dimension ref="A1:M227"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -14060,17 +14060,17 @@
     <row r="204">
       <c r="A204" s="2" t="inlineStr">
         <is>
-          <t>L20.C01</t>
+          <t>L18.C09</t>
         </is>
       </c>
       <c r="B204" s="3" t="inlineStr">
         <is>
-          <t>L20</t>
+          <t>L18</t>
         </is>
       </c>
       <c r="C204" s="3" t="inlineStr">
         <is>
-          <t>Ce que ce livre doit établir</t>
+          <t>L'ordre de grandeur, et le concurrent qu'il désigne</t>
         </is>
       </c>
       <c r="D204" s="3" t="inlineStr">
@@ -14090,12 +14090,12 @@
       </c>
       <c r="G204" s="3" t="inlineStr">
         <is>
-          <t>conception</t>
+          <t>hybride</t>
         </is>
       </c>
       <c r="H204" s="3" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="I204" s="3" t="n">
@@ -14106,24 +14106,24 @@
       </c>
       <c r="K204" s="3" t="inlineStr">
         <is>
-          <t>fenetre_de_reforme, referentiel_de_change, communs, limites_planetaires, creation_monetaire</t>
+          <t>essentiel_insolvable, valorisation_des_communs, externalisation, additionnalite, fausse_richesse, degeneratif</t>
         </is>
       </c>
       <c r="L204" s="3" t="inlineStr">
         <is>
-          <t>L1.C18, L1.C25, L1.C27, L7.C01, L7.C03, L7.C13, L7.C17, L7.C21, L11.C24</t>
+          <t>L1.C15, L1.C18, L5.C07, L10.C04, L10.C06, L11.C03, L11.C13, L18.C01, L18.C04, L18.C06</t>
         </is>
       </c>
       <c r="M204" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-20-droit-international-monetaire-et-commercial/c01-ce-que-ce-livre-doit-etablir.md</t>
+          <t>corpus/livre-18-comptabilites-ecologiques-et-biophysiques/c09-l-ordre-de-grandeur-et-le-concurrent-qu-il-designe.md</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" s="2" t="inlineStr">
         <is>
-          <t>L20.C02</t>
+          <t>L20.C01</t>
         </is>
       </c>
       <c r="B205" s="3" t="inlineStr">
@@ -14133,7 +14133,7 @@
       </c>
       <c r="C205" s="3" t="inlineStr">
         <is>
-          <t>L'interdiction du financement monétaire</t>
+          <t>Ce que ce livre doit établir</t>
         </is>
       </c>
       <c r="D205" s="3" t="inlineStr">
@@ -14158,7 +14158,7 @@
       </c>
       <c r="H205" s="3" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="I205" s="3" t="n">
@@ -14169,24 +14169,24 @@
       </c>
       <c r="K205" s="3" t="inlineStr">
         <is>
-          <t>creation_monetaire, contrepartie_comptable, reflux_collectif, fenetre_de_reforme</t>
+          <t>fenetre_de_reforme, referentiel_de_change, communs, limites_planetaires, creation_monetaire</t>
         </is>
       </c>
       <c r="L205" s="3" t="inlineStr">
         <is>
-          <t>L1.C05, L1.C18, L1.C20, L1.C22, L7.C11, L7.C13, L11.C10, L20.C01</t>
+          <t>L1.C18, L1.C25, L1.C27, L7.C01, L7.C03, L7.C13, L7.C17, L7.C21, L11.C24</t>
         </is>
       </c>
       <c r="M205" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-20-droit-international-monetaire-et-commercial/c02-l-interdiction-du-financement-monetaire.md</t>
+          <t>corpus/livre-20-droit-international-monetaire-et-commercial/c01-ce-que-ce-livre-doit-etablir.md</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" s="2" t="inlineStr">
         <is>
-          <t>L20.C03</t>
+          <t>L20.C02</t>
         </is>
       </c>
       <c r="B206" s="3" t="inlineStr">
@@ -14196,7 +14196,7 @@
       </c>
       <c r="C206" s="3" t="inlineStr">
         <is>
-          <t>L'objectif principal et ce qu'il exclut</t>
+          <t>L'interdiction du financement monétaire</t>
         </is>
       </c>
       <c r="D206" s="3" t="inlineStr">
@@ -14232,24 +14232,24 @@
       </c>
       <c r="K206" s="3" t="inlineStr">
         <is>
-          <t>regle_contre_discretion, limites_planetaires, creation_monetaire, plafond_ecologique</t>
+          <t>creation_monetaire, contrepartie_comptable, reflux_collectif, fenetre_de_reforme</t>
         </is>
       </c>
       <c r="L206" s="3" t="inlineStr">
         <is>
-          <t>L1.C01, L1.C18, L1.C20, L7.C03, L8.C12, L8.C34, L11.C16, L20.C01, L20.C02</t>
+          <t>L1.C05, L1.C18, L1.C20, L1.C22, L7.C11, L7.C13, L11.C10, L20.C01</t>
         </is>
       </c>
       <c r="M206" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-20-droit-international-monetaire-et-commercial/c03-l-objectif-principal-et-ce-qu-il-exclut.md</t>
+          <t>corpus/livre-20-droit-international-monetaire-et-commercial/c02-l-interdiction-du-financement-monetaire.md</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" s="2" t="inlineStr">
         <is>
-          <t>L20.C04</t>
+          <t>L20.C03</t>
         </is>
       </c>
       <c r="B207" s="3" t="inlineStr">
@@ -14259,7 +14259,7 @@
       </c>
       <c r="C207" s="3" t="inlineStr">
         <is>
-          <t>L'indépendance, et à l'égard de qui</t>
+          <t>L'objectif principal et ce qu'il exclut</t>
         </is>
       </c>
       <c r="D207" s="3" t="inlineStr">
@@ -14284,7 +14284,7 @@
       </c>
       <c r="H207" s="3" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="I207" s="3" t="n">
@@ -14295,24 +14295,24 @@
       </c>
       <c r="K207" s="3" t="inlineStr">
         <is>
-          <t>regle_contre_discretion, creation_monetaire, fenetre_de_reforme</t>
+          <t>regle_contre_discretion, limites_planetaires, creation_monetaire, plafond_ecologique</t>
         </is>
       </c>
       <c r="L207" s="3" t="inlineStr">
         <is>
-          <t>L1.C18, L7.C04, L7.C07, L7.C10, L8.C31, L11.C17, L20.C01, L20.C03, L20.C11</t>
+          <t>L1.C01, L1.C18, L1.C20, L7.C03, L8.C12, L8.C34, L11.C16, L20.C01, L20.C02</t>
         </is>
       </c>
       <c r="M207" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-20-droit-international-monetaire-et-commercial/c04-l-independance-et-a-l-egard-de-qui.md</t>
+          <t>corpus/livre-20-droit-international-monetaire-et-commercial/c03-l-objectif-principal-et-ce-qu-il-exclut.md</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" s="2" t="inlineStr">
         <is>
-          <t>L20.C05</t>
+          <t>L20.C04</t>
         </is>
       </c>
       <c r="B208" s="3" t="inlineStr">
@@ -14322,7 +14322,7 @@
       </c>
       <c r="C208" s="3" t="inlineStr">
         <is>
-          <t>Le monopole d'émission et le cours légal</t>
+          <t>L'indépendance, et à l'égard de qui</t>
         </is>
       </c>
       <c r="D208" s="3" t="inlineStr">
@@ -14358,24 +14358,24 @@
       </c>
       <c r="K208" s="3" t="inlineStr">
         <is>
-          <t>monnaie_comme_registre, creation_monetaire, referentiel_de_change, hierarchie_monetaire</t>
+          <t>regle_contre_discretion, creation_monetaire, fenetre_de_reforme</t>
         </is>
       </c>
       <c r="L208" s="3" t="inlineStr">
         <is>
-          <t>L1.C05, L1.C07, L1.C26, L7.C15, L11.C15, L20.C01, L20.C02, L20.C03</t>
+          <t>L1.C18, L7.C04, L7.C07, L7.C10, L8.C31, L11.C17, L20.C01, L20.C03, L20.C11</t>
         </is>
       </c>
       <c r="M208" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-20-droit-international-monetaire-et-commercial/c05-le-monopole-d-emission-et-le-cours-legal.md</t>
+          <t>corpus/livre-20-droit-international-monetaire-et-commercial/c04-l-independance-et-a-l-egard-de-qui.md</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" s="2" t="inlineStr">
         <is>
-          <t>L20.C06</t>
+          <t>L20.C05</t>
         </is>
       </c>
       <c r="B209" s="3" t="inlineStr">
@@ -14385,7 +14385,7 @@
       </c>
       <c r="C209" s="3" t="inlineStr">
         <is>
-          <t>Les voies de révision et leur coût</t>
+          <t>Le monopole d'émission et le cours légal</t>
         </is>
       </c>
       <c r="D209" s="3" t="inlineStr">
@@ -14414,31 +14414,31 @@
         </is>
       </c>
       <c r="I209" s="3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J209" s="3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K209" s="3" t="inlineStr">
         <is>
-          <t>fenetre_de_reforme, regle_contre_discretion, creation_monetaire</t>
+          <t>monnaie_comme_registre, creation_monetaire, referentiel_de_change, hierarchie_monetaire</t>
         </is>
       </c>
       <c r="L209" s="3" t="inlineStr">
         <is>
-          <t>L1.C18, L7.C12, L7.C20, L7.C21, L11.C15, L20.C01, L20.C02, L20.C03, L20.C07, L20.C09, L20.C18</t>
+          <t>L1.C05, L1.C07, L1.C26, L7.C15, L11.C15, L20.C01, L20.C02, L20.C03</t>
         </is>
       </c>
       <c r="M209" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-20-droit-international-monetaire-et-commercial/c06-les-voies-de-revision-et-leur-cout.md</t>
+          <t>corpus/livre-20-droit-international-monetaire-et-commercial/c05-le-monopole-d-emission-et-le-cours-legal.md</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" s="2" t="inlineStr">
         <is>
-          <t>L20.C07</t>
+          <t>L20.C06</t>
         </is>
       </c>
       <c r="B210" s="3" t="inlineStr">
@@ -14448,7 +14448,7 @@
       </c>
       <c r="C210" s="3" t="inlineStr">
         <is>
-          <t>L'accord monétaire international</t>
+          <t>Les voies de révision et leur coût</t>
         </is>
       </c>
       <c r="D210" s="3" t="inlineStr">
@@ -14477,31 +14477,31 @@
         </is>
       </c>
       <c r="I210" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J210" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K210" s="3" t="inlineStr">
         <is>
-          <t>referentiel_de_change, fenetre_de_reforme, etalon_de_change_or, hierarchie_monetaire</t>
+          <t>fenetre_de_reforme, regle_contre_discretion, creation_monetaire</t>
         </is>
       </c>
       <c r="L210" s="3" t="inlineStr">
         <is>
-          <t>L1.C18, L1.C26, L7.C02, L7.C05, L7.C12, L7.C13, L11.C15, L20.C01, L20.C03, L20.C06, L20.C10</t>
+          <t>L1.C18, L7.C12, L7.C20, L7.C21, L11.C15, L20.C01, L20.C02, L20.C03, L20.C07, L20.C09, L20.C18</t>
         </is>
       </c>
       <c r="M210" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-20-droit-international-monetaire-et-commercial/c07-l-accord-monetaire-international.md</t>
+          <t>corpus/livre-20-droit-international-monetaire-et-commercial/c06-les-voies-de-revision-et-leur-cout.md</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" s="2" t="inlineStr">
         <is>
-          <t>L20.C08</t>
+          <t>L20.C07</t>
         </is>
       </c>
       <c r="B211" s="3" t="inlineStr">
@@ -14511,7 +14511,7 @@
       </c>
       <c r="C211" s="3" t="inlineStr">
         <is>
-          <t>La parité inscrite dans le traité</t>
+          <t>L'accord monétaire international</t>
         </is>
       </c>
       <c r="D211" s="3" t="inlineStr">
@@ -14536,35 +14536,35 @@
       </c>
       <c r="H211" s="3" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="I211" s="3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J211" s="3" t="n">
         <v>3</v>
       </c>
       <c r="K211" s="3" t="inlineStr">
         <is>
-          <t>referentiel_de_change, etalon_de_change_or, hierarchie_monetaire, bareme, devise_cle</t>
+          <t>referentiel_de_change, fenetre_de_reforme, etalon_de_change_or, hierarchie_monetaire</t>
         </is>
       </c>
       <c r="L211" s="3" t="inlineStr">
         <is>
-          <t>L1.C25, L1.C26, L1.C28, L7.C02, L7.C20, L11.C15, L11.C17, L20.C01, L20.C09, L20.C13</t>
+          <t>L1.C18, L1.C26, L7.C02, L7.C05, L7.C12, L7.C13, L11.C15, L20.C01, L20.C03, L20.C06, L20.C10</t>
         </is>
       </c>
       <c r="M211" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-20-droit-international-monetaire-et-commercial/c08-la-parite-inscrite-dans-le-traite.md</t>
+          <t>corpus/livre-20-droit-international-monetaire-et-commercial/c07-l-accord-monetaire-international.md</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" s="2" t="inlineStr">
         <is>
-          <t>L20.C09</t>
+          <t>L20.C08</t>
         </is>
       </c>
       <c r="B212" s="3" t="inlineStr">
@@ -14574,7 +14574,7 @@
       </c>
       <c r="C212" s="3" t="inlineStr">
         <is>
-          <t>L'amendement des statuts du Fonds</t>
+          <t>La parité inscrite dans le traité</t>
         </is>
       </c>
       <c r="D212" s="3" t="inlineStr">
@@ -14599,35 +14599,35 @@
       </c>
       <c r="H212" s="3" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="I212" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J212" s="3" t="n">
         <v>3</v>
       </c>
       <c r="K212" s="3" t="inlineStr">
         <is>
-          <t>fenetre_de_reforme, referentiel_de_change, bareme, regle_contre_discretion</t>
+          <t>referentiel_de_change, etalon_de_change_or, hierarchie_monetaire, bareme, devise_cle</t>
         </is>
       </c>
       <c r="L212" s="3" t="inlineStr">
         <is>
-          <t>L7.C06, L7.C09, L7.C16, L7.C20, L11.C15, L11.C20, L20.C01, L20.C06, L20.C08, L20.C10, L20.C13</t>
+          <t>L1.C25, L1.C26, L1.C28, L7.C02, L7.C20, L11.C15, L11.C17, L20.C01, L20.C09, L20.C13</t>
         </is>
       </c>
       <c r="M212" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-20-droit-international-monetaire-et-commercial/c09-l-amendement-des-statuts-du-fonds.md</t>
+          <t>corpus/livre-20-droit-international-monetaire-et-commercial/c08-la-parite-inscrite-dans-le-traite.md</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" s="2" t="inlineStr">
         <is>
-          <t>L20.C10</t>
+          <t>L20.C09</t>
         </is>
       </c>
       <c r="B213" s="3" t="inlineStr">
@@ -14637,7 +14637,7 @@
       </c>
       <c r="C213" s="3" t="inlineStr">
         <is>
-          <t>Le vote pondéré et les voix de base</t>
+          <t>L'amendement des statuts du Fonds</t>
         </is>
       </c>
       <c r="D213" s="3" t="inlineStr">
@@ -14673,24 +14673,24 @@
       </c>
       <c r="K213" s="3" t="inlineStr">
         <is>
-          <t>bareme, devise_cle, hierarchie_monetaire, referentiel_de_change</t>
+          <t>fenetre_de_reforme, referentiel_de_change, bareme, regle_contre_discretion</t>
         </is>
       </c>
       <c r="L213" s="3" t="inlineStr">
         <is>
-          <t>L1.C25, L7.C02, L7.C05, L7.C06, L7.C09, L7.C10, L11.C16, L20.C01, L20.C07, L20.C09, L20.C12</t>
+          <t>L7.C06, L7.C09, L7.C16, L7.C20, L11.C15, L11.C20, L20.C01, L20.C06, L20.C08, L20.C10, L20.C13</t>
         </is>
       </c>
       <c r="M213" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-20-droit-international-monetaire-et-commercial/c10-le-vote-pondere-et-les-voix-de-base.md</t>
+          <t>corpus/livre-20-droit-international-monetaire-et-commercial/c09-l-amendement-des-statuts-du-fonds.md</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" s="2" t="inlineStr">
         <is>
-          <t>L20.C11</t>
+          <t>L20.C10</t>
         </is>
       </c>
       <c r="B214" s="3" t="inlineStr">
@@ -14700,7 +14700,7 @@
       </c>
       <c r="C214" s="3" t="inlineStr">
         <is>
-          <t>La personnalité juridique et les immunités</t>
+          <t>Le vote pondéré et les voix de base</t>
         </is>
       </c>
       <c r="D214" s="3" t="inlineStr">
@@ -14729,31 +14729,31 @@
         </is>
       </c>
       <c r="I214" s="3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J214" s="3" t="n">
         <v>3</v>
       </c>
       <c r="K214" s="3" t="inlineStr">
         <is>
-          <t>communs, creation_monetaire, fenetre_de_reforme, robustesse</t>
+          <t>bareme, devise_cle, hierarchie_monetaire, referentiel_de_change</t>
         </is>
       </c>
       <c r="L214" s="3" t="inlineStr">
         <is>
-          <t>L7.C01, L7.C03, L7.C07, L7.C10, L7.C13, L11.C25, L20.C01, L20.C04, L20.C12, L20.C14</t>
+          <t>L1.C25, L7.C02, L7.C05, L7.C06, L7.C09, L7.C10, L11.C16, L20.C01, L20.C07, L20.C09, L20.C12</t>
         </is>
       </c>
       <c r="M214" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-20-droit-international-monetaire-et-commercial/c11-la-personnalite-juridique-et-les-immunites.md</t>
+          <t>corpus/livre-20-droit-international-monetaire-et-commercial/c10-le-vote-pondere-et-les-voix-de-base.md</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" s="2" t="inlineStr">
         <is>
-          <t>L20.C12</t>
+          <t>L20.C11</t>
         </is>
       </c>
       <c r="B215" s="3" t="inlineStr">
@@ -14763,7 +14763,7 @@
       </c>
       <c r="C215" s="3" t="inlineStr">
         <is>
-          <t>Les pouvoirs non délégables</t>
+          <t>La personnalité juridique et les immunités</t>
         </is>
       </c>
       <c r="D215" s="3" t="inlineStr">
@@ -14788,35 +14788,35 @@
       </c>
       <c r="H215" s="3" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="I215" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J215" s="3" t="n">
         <v>3</v>
       </c>
       <c r="K215" s="3" t="inlineStr">
         <is>
-          <t>bareme, valorisation_des_communs, polycentricite, robustesse</t>
+          <t>communs, creation_monetaire, fenetre_de_reforme, robustesse</t>
         </is>
       </c>
       <c r="L215" s="3" t="inlineStr">
         <is>
-          <t>L7.C05, L7.C06, L7.C07, L7.C11, L7.C14, L11.C16, L11.C20, L20.C01, L20.C09, L20.C10, L20.C14</t>
+          <t>L7.C01, L7.C03, L7.C07, L7.C10, L7.C13, L11.C25, L20.C01, L20.C04, L20.C12, L20.C14</t>
         </is>
       </c>
       <c r="M215" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-20-droit-international-monetaire-et-commercial/c12-les-pouvoirs-non-delegables.md</t>
+          <t>corpus/livre-20-droit-international-monetaire-et-commercial/c11-la-personnalite-juridique-et-les-immunites.md</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" s="2" t="inlineStr">
         <is>
-          <t>L20.C13</t>
+          <t>L20.C12</t>
         </is>
       </c>
       <c r="B216" s="3" t="inlineStr">
@@ -14826,7 +14826,7 @@
       </c>
       <c r="C216" s="3" t="inlineStr">
         <is>
-          <t>L'entrée en vigueur, l'adhésion et le retrait</t>
+          <t>Les pouvoirs non délégables</t>
         </is>
       </c>
       <c r="D216" s="3" t="inlineStr">
@@ -14855,31 +14855,31 @@
         </is>
       </c>
       <c r="I216" s="3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J216" s="3" t="n">
         <v>3</v>
       </c>
       <c r="K216" s="3" t="inlineStr">
         <is>
-          <t>seuil_d_activation, reflux_collectif, fenetre_de_reforme, additionnalite</t>
+          <t>bareme, valorisation_des_communs, polycentricite, robustesse</t>
         </is>
       </c>
       <c r="L216" s="3" t="inlineStr">
         <is>
-          <t>L7.C11, L7.C12, L7.C16, L7.C17, L7.C19, L11.C18, L20.C01, L20.C06, L20.C09, L20.C12</t>
+          <t>L7.C05, L7.C06, L7.C07, L7.C11, L7.C14, L11.C16, L11.C20, L20.C01, L20.C09, L20.C10, L20.C14</t>
         </is>
       </c>
       <c r="M216" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-20-droit-international-monetaire-et-commercial/c13-l-entree-en-vigueur-l-adhesion-et-le-retrait.md</t>
+          <t>corpus/livre-20-droit-international-monetaire-et-commercial/c12-les-pouvoirs-non-delegables.md</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" s="2" t="inlineStr">
         <is>
-          <t>L20.C14</t>
+          <t>L20.C13</t>
         </is>
       </c>
       <c r="B217" s="3" t="inlineStr">
@@ -14889,7 +14889,7 @@
       </c>
       <c r="C217" s="3" t="inlineStr">
         <is>
-          <t>Qui interprète le traité</t>
+          <t>L'entrée en vigueur, l'adhésion et le retrait</t>
         </is>
       </c>
       <c r="D217" s="3" t="inlineStr">
@@ -14918,31 +14918,31 @@
         </is>
       </c>
       <c r="I217" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J217" s="3" t="n">
         <v>3</v>
       </c>
       <c r="K217" s="3" t="inlineStr">
         <is>
-          <t>robustesse, regle_contre_discretion, communs</t>
+          <t>seuil_d_activation, reflux_collectif, fenetre_de_reforme, additionnalite</t>
         </is>
       </c>
       <c r="L217" s="3" t="inlineStr">
         <is>
-          <t>L7.C07, L7.C13, L7.C14, L7.C19, L11.C19, L11.C25, L20.C01, L20.C03, L20.C11, L20.C12, L20.C21</t>
+          <t>L7.C11, L7.C12, L7.C16, L7.C17, L7.C19, L11.C18, L20.C01, L20.C06, L20.C09, L20.C12</t>
         </is>
       </c>
       <c r="M217" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-20-droit-international-monetaire-et-commercial/c14-qui-interprete-le-traite.md</t>
+          <t>corpus/livre-20-droit-international-monetaire-et-commercial/c13-l-entree-en-vigueur-l-adhesion-et-le-retrait.md</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" s="2" t="inlineStr">
         <is>
-          <t>L20.C15</t>
+          <t>L20.C14</t>
         </is>
       </c>
       <c r="B218" s="3" t="inlineStr">
@@ -14952,7 +14952,7 @@
       </c>
       <c r="C218" s="3" t="inlineStr">
         <is>
-          <t>Le devoir international des agents</t>
+          <t>Qui interprète le traité</t>
         </is>
       </c>
       <c r="D218" s="3" t="inlineStr">
@@ -14977,35 +14977,35 @@
       </c>
       <c r="H218" s="3" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="I218" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J218" s="3" t="n">
         <v>3</v>
       </c>
       <c r="K218" s="3" t="inlineStr">
         <is>
-          <t>robustesse, regle_contre_discretion, indicateur_de_progres</t>
+          <t>robustesse, regle_contre_discretion, communs</t>
         </is>
       </c>
       <c r="L218" s="3" t="inlineStr">
         <is>
-          <t>L7.C04, L7.C07, L7.C10, L11.C21, L11.C25, L20.C01, L20.C04, L20.C11, L20.C14</t>
+          <t>L7.C07, L7.C13, L7.C14, L7.C19, L11.C19, L11.C25, L20.C01, L20.C03, L20.C11, L20.C12, L20.C21</t>
         </is>
       </c>
       <c r="M218" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-20-droit-international-monetaire-et-commercial/c15-le-devoir-international-des-agents.md</t>
+          <t>corpus/livre-20-droit-international-monetaire-et-commercial/c14-qui-interprete-le-traite.md</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" s="2" t="inlineStr">
         <is>
-          <t>L20.C16</t>
+          <t>L20.C15</t>
         </is>
       </c>
       <c r="B219" s="3" t="inlineStr">
@@ -15015,7 +15015,7 @@
       </c>
       <c r="C219" s="3" t="inlineStr">
         <is>
-          <t>Le patrimoine commun de l'humanité</t>
+          <t>Le devoir international des agents</t>
         </is>
       </c>
       <c r="D219" s="3" t="inlineStr">
@@ -15040,35 +15040,35 @@
       </c>
       <c r="H219" s="3" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="I219" s="3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J219" s="3" t="n">
         <v>3</v>
       </c>
       <c r="K219" s="3" t="inlineStr">
         <is>
-          <t>communs, valorisation_des_communs, limites_planetaires, additionnalite, plafond_ecologique</t>
+          <t>robustesse, regle_contre_discretion, indicateur_de_progres</t>
         </is>
       </c>
       <c r="L219" s="3" t="inlineStr">
         <is>
-          <t>L1.C17, L1.C22, L7.C05, L7.C13, L11.C16, L20.C01, L20.C11, L20.C17, L20.C22</t>
+          <t>L7.C04, L7.C07, L7.C10, L11.C21, L11.C25, L20.C01, L20.C04, L20.C11, L20.C14</t>
         </is>
       </c>
       <c r="M219" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-20-droit-international-monetaire-et-commercial/c16-le-patrimoine-commun-de-l-humanite.md</t>
+          <t>corpus/livre-20-droit-international-monetaire-et-commercial/c15-le-devoir-international-des-agents.md</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" s="2" t="inlineStr">
         <is>
-          <t>L20.C17</t>
+          <t>L20.C16</t>
         </is>
       </c>
       <c r="B220" s="3" t="inlineStr">
@@ -15078,7 +15078,7 @@
       </c>
       <c r="C220" s="3" t="inlineStr">
         <is>
-          <t>La sanctuarisation, et elle existe</t>
+          <t>Le patrimoine commun de l'humanité</t>
         </is>
       </c>
       <c r="D220" s="3" t="inlineStr">
@@ -15107,31 +15107,31 @@
         </is>
       </c>
       <c r="I220" s="3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J220" s="3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K220" s="3" t="inlineStr">
         <is>
-          <t>communs, limites_planetaires, fenetre_de_reforme, robustesse, plafond_ecologique</t>
+          <t>communs, valorisation_des_communs, limites_planetaires, additionnalite, plafond_ecologique</t>
         </is>
       </c>
       <c r="L220" s="3" t="inlineStr">
         <is>
-          <t>L1.C17, L1.C18, L7.C13, L7.C19, L7.C20, L11.C20, L20.C01, L20.C06, L20.C09, L20.C16, L20.C22</t>
+          <t>L1.C17, L1.C22, L7.C05, L7.C13, L11.C16, L20.C01, L20.C11, L20.C17, L20.C22</t>
         </is>
       </c>
       <c r="M220" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-20-droit-international-monetaire-et-commercial/c17-la-sanctuarisation-et-elle-existe.md</t>
+          <t>corpus/livre-20-droit-international-monetaire-et-commercial/c16-le-patrimoine-commun-de-l-humanite.md</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" s="2" t="inlineStr">
         <is>
-          <t>L20.C18</t>
+          <t>L20.C17</t>
         </is>
       </c>
       <c r="B221" s="3" t="inlineStr">
@@ -15141,7 +15141,7 @@
       </c>
       <c r="C221" s="3" t="inlineStr">
         <is>
-          <t>L'amendement et la dérogation dans l'ordre commercial</t>
+          <t>La sanctuarisation, et elle existe</t>
         </is>
       </c>
       <c r="D221" s="3" t="inlineStr">
@@ -15166,35 +15166,35 @@
       </c>
       <c r="H221" s="3" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="I221" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J221" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K221" s="3" t="inlineStr">
         <is>
-          <t>bareme, seuil_d_activation, additionnalite, fenetre_de_reforme</t>
+          <t>communs, limites_planetaires, fenetre_de_reforme, robustesse, plafond_ecologique</t>
         </is>
       </c>
       <c r="L221" s="3" t="inlineStr">
         <is>
-          <t>L1.C27, L7.C17, L7.C20, L11.C24, L20.C01, L20.C06, L20.C09, L20.C13, L20.C19, L20.C20</t>
+          <t>L1.C17, L1.C18, L7.C13, L7.C19, L7.C20, L11.C20, L20.C01, L20.C06, L20.C09, L20.C16, L20.C22</t>
         </is>
       </c>
       <c r="M221" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-20-droit-international-monetaire-et-commercial/c18-l-amendement-et-la-derogation-dans-l-ordre-commercial.md</t>
+          <t>corpus/livre-20-droit-international-monetaire-et-commercial/c17-la-sanctuarisation-et-elle-existe.md</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" s="2" t="inlineStr">
         <is>
-          <t>L20.C19</t>
+          <t>L20.C18</t>
         </is>
       </c>
       <c r="B222" s="3" t="inlineStr">
@@ -15204,7 +15204,7 @@
       </c>
       <c r="C222" s="3" t="inlineStr">
         <is>
-          <t>Le texte que la conformité invoque</t>
+          <t>L'amendement et la dérogation dans l'ordre commercial</t>
         </is>
       </c>
       <c r="D222" s="3" t="inlineStr">
@@ -15229,35 +15229,35 @@
       </c>
       <c r="H222" s="3" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="I222" s="3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J222" s="3" t="n">
         <v>3</v>
       </c>
       <c r="K222" s="3" t="inlineStr">
         <is>
-          <t>bareme, additionnalite, limites_planetaires, seuil_d_activation, externalisation</t>
+          <t>bareme, seuil_d_activation, additionnalite, fenetre_de_reforme</t>
         </is>
       </c>
       <c r="L222" s="3" t="inlineStr">
         <is>
-          <t>L1.C27, L7.C17, L11.C24, L20.C01, L20.C18, L20.C20, L20.C22</t>
+          <t>L1.C27, L7.C17, L7.C20, L11.C24, L20.C01, L20.C06, L20.C09, L20.C13, L20.C19, L20.C20</t>
         </is>
       </c>
       <c r="M222" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-20-droit-international-monetaire-et-commercial/c19-le-texte-que-la-conformite-invoque.md</t>
+          <t>corpus/livre-20-droit-international-monetaire-et-commercial/c18-l-amendement-et-la-derogation-dans-l-ordre-commercial.md</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" s="2" t="inlineStr">
         <is>
-          <t>L20.C20</t>
+          <t>L20.C19</t>
         </is>
       </c>
       <c r="B223" s="3" t="inlineStr">
@@ -15267,7 +15267,7 @@
       </c>
       <c r="C223" s="3" t="inlineStr">
         <is>
-          <t>L'ajustement aux frontières comme précédent</t>
+          <t>Le texte que la conformité invoque</t>
         </is>
       </c>
       <c r="D223" s="3" t="inlineStr">
@@ -15292,7 +15292,7 @@
       </c>
       <c r="H223" s="3" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="I223" s="3" t="n">
@@ -15303,24 +15303,24 @@
       </c>
       <c r="K223" s="3" t="inlineStr">
         <is>
-          <t>bareme, seuil_d_activation, externalisation, additionnalite, contrepartie_comptable</t>
+          <t>bareme, additionnalite, limites_planetaires, seuil_d_activation, externalisation</t>
         </is>
       </c>
       <c r="L223" s="3" t="inlineStr">
         <is>
-          <t>L1.C27, L7.C17, L11.C21, L11.C24, L11.C25, L20.C01, L20.C18, L20.C19, L20.C22</t>
+          <t>L1.C27, L7.C17, L11.C24, L20.C01, L20.C18, L20.C20, L20.C22</t>
         </is>
       </c>
       <c r="M223" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-20-droit-international-monetaire-et-commercial/c20-l-ajustement-aux-frontieres-comme-precedent.md</t>
+          <t>corpus/livre-20-droit-international-monetaire-et-commercial/c19-le-texte-que-la-conformite-invoque.md</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" s="2" t="inlineStr">
         <is>
-          <t>L20.C21</t>
+          <t>L20.C20</t>
         </is>
       </c>
       <c r="B224" s="3" t="inlineStr">
@@ -15330,7 +15330,7 @@
       </c>
       <c r="C224" s="3" t="inlineStr">
         <is>
-          <t>La transparence et sa limite juridictionnelle</t>
+          <t>L'ajustement aux frontières comme précédent</t>
         </is>
       </c>
       <c r="D224" s="3" t="inlineStr">
@@ -15359,31 +15359,31 @@
         </is>
       </c>
       <c r="I224" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J224" s="3" t="n">
         <v>3</v>
       </c>
       <c r="K224" s="3" t="inlineStr">
         <is>
-          <t>robustesse, contrepartie_comptable, bareme, monnaie_comme_registre</t>
+          <t>bareme, seuil_d_activation, externalisation, additionnalite, contrepartie_comptable</t>
         </is>
       </c>
       <c r="L224" s="3" t="inlineStr">
         <is>
-          <t>L7.C18, L11.C21, L11.C24, L11.C25, L20.C01, L20.C11, L20.C14, L20.C20, L20.C22</t>
+          <t>L1.C27, L7.C17, L11.C21, L11.C24, L11.C25, L20.C01, L20.C18, L20.C19, L20.C22</t>
         </is>
       </c>
       <c r="M224" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-20-droit-international-monetaire-et-commercial/c21-la-transparence-et-sa-limite-juridictionnelle.md</t>
+          <t>corpus/livre-20-droit-international-monetaire-et-commercial/c20-l-ajustement-aux-frontieres-comme-precedent.md</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" s="2" t="inlineStr">
         <is>
-          <t>L20.C22</t>
+          <t>L20.C21</t>
         </is>
       </c>
       <c r="B225" s="3" t="inlineStr">
@@ -15393,7 +15393,7 @@
       </c>
       <c r="C225" s="3" t="inlineStr">
         <is>
-          <t>Ce que le droit devrait devenir</t>
+          <t>La transparence et sa limite juridictionnelle</t>
         </is>
       </c>
       <c r="D225" s="3" t="inlineStr">
@@ -15429,85 +15429,148 @@
       </c>
       <c r="K225" s="3" t="inlineStr">
         <is>
-          <t>fenetre_de_reforme, communs, limites_planetaires, regle_contre_discretion, bareme, referentiel_de_change</t>
+          <t>robustesse, contrepartie_comptable, bareme, monnaie_comme_registre</t>
         </is>
       </c>
       <c r="L225" s="3" t="inlineStr">
         <is>
-          <t>L1.C18, L7.C12, L7.C13, L11.C15, L11.C25, L20.C01, L20.C03, L20.C06, L20.C07, L20.C08, L20.C12, L20.C13, L20.C16, L20.C17, L20.C19, L20.C20, L20.C21, L20.C23</t>
+          <t>L7.C18, L11.C21, L11.C24, L11.C25, L20.C01, L20.C11, L20.C14, L20.C20, L20.C22</t>
         </is>
       </c>
       <c r="M225" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-20-droit-international-monetaire-et-commercial/c22-ce-que-le-droit-devrait-devenir.md</t>
+          <t>corpus/livre-20-droit-international-monetaire-et-commercial/c21-la-transparence-et-sa-limite-juridictionnelle.md</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" s="2" t="inlineStr">
         <is>
+          <t>L20.C22</t>
+        </is>
+      </c>
+      <c r="B226" s="3" t="inlineStr">
+        <is>
+          <t>L20</t>
+        </is>
+      </c>
+      <c r="C226" s="3" t="inlineStr">
+        <is>
+          <t>Ce que le droit devrait devenir</t>
+        </is>
+      </c>
+      <c r="D226" s="3" t="inlineStr">
+        <is>
+          <t>brouillon</t>
+        </is>
+      </c>
+      <c r="E226" s="3" t="inlineStr">
+        <is>
+          <t>preparatoire</t>
+        </is>
+      </c>
+      <c r="F226" s="3" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="G226" s="3" t="inlineStr">
+        <is>
+          <t>conception</t>
+        </is>
+      </c>
+      <c r="H226" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="I226" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="J226" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="K226" s="3" t="inlineStr">
+        <is>
+          <t>fenetre_de_reforme, communs, limites_planetaires, regle_contre_discretion, bareme, referentiel_de_change</t>
+        </is>
+      </c>
+      <c r="L226" s="3" t="inlineStr">
+        <is>
+          <t>L1.C18, L7.C12, L7.C13, L11.C15, L11.C25, L20.C01, L20.C03, L20.C06, L20.C07, L20.C08, L20.C12, L20.C13, L20.C16, L20.C17, L20.C19, L20.C20, L20.C21, L20.C23</t>
+        </is>
+      </c>
+      <c r="M226" s="3" t="inlineStr">
+        <is>
+          <t>corpus/livre-20-droit-international-monetaire-et-commercial/c22-ce-que-le-droit-devrait-devenir.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" s="2" t="inlineStr">
+        <is>
           <t>L20.C23</t>
         </is>
       </c>
-      <c r="B226" s="3" t="inlineStr">
+      <c r="B227" s="3" t="inlineStr">
         <is>
           <t>L20</t>
         </is>
       </c>
-      <c r="C226" s="3" t="inlineStr">
+      <c r="C227" s="3" t="inlineStr">
         <is>
           <t>La portée du livre</t>
         </is>
       </c>
-      <c r="D226" s="3" t="inlineStr">
-        <is>
-          <t>brouillon</t>
-        </is>
-      </c>
-      <c r="E226" s="3" t="inlineStr">
-        <is>
-          <t>preparatoire</t>
-        </is>
-      </c>
-      <c r="F226" s="3" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="G226" s="3" t="inlineStr">
+      <c r="D227" s="3" t="inlineStr">
+        <is>
+          <t>brouillon</t>
+        </is>
+      </c>
+      <c r="E227" s="3" t="inlineStr">
+        <is>
+          <t>preparatoire</t>
+        </is>
+      </c>
+      <c r="F227" s="3" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="G227" s="3" t="inlineStr">
         <is>
           <t>conception</t>
         </is>
       </c>
-      <c r="H226" s="3" t="inlineStr">
+      <c r="H227" s="3" t="inlineStr">
         <is>
           <t>2026-09-06</t>
         </is>
       </c>
-      <c r="I226" s="3" t="n">
+      <c r="I227" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="J226" s="3" t="n">
+      <c r="J227" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="K226" s="3" t="inlineStr">
+      <c r="K227" s="3" t="inlineStr">
         <is>
           <t>fenetre_de_reforme, communs, limites_planetaires, creation_monetaire, robustesse</t>
         </is>
       </c>
-      <c r="L226" s="3" t="inlineStr">
+      <c r="L227" s="3" t="inlineStr">
         <is>
           <t>L1.C18, L1.C27, L7.C05, L7.C10, L7.C12, L7.C13, L11.C15, L11.C24, L11.C25, L20.C01, L20.C02, L20.C03, L20.C06, L20.C07, L20.C08, L20.C11, L20.C12, L20.C13, L20.C16, L20.C17, L20.C19, L20.C20, L20.C21, L20.C22</t>
         </is>
       </c>
-      <c r="M226" s="3" t="inlineStr">
+      <c r="M227" s="3" t="inlineStr">
         <is>
           <t>corpus/livre-20-droit-international-monetaire-et-commercial/c23-la-portee-du-livre.md</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:M226"/>
+  <autoFilter ref="A1:M227"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -15586,7 +15649,7 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>225</v>
+        <v>226</v>
       </c>
     </row>
     <row r="7">
@@ -15596,7 +15659,7 @@
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="8">
@@ -15616,7 +15679,7 @@
         </is>
       </c>
       <c r="B9" s="3" t="n">
-        <v>1137</v>
+        <v>1140</v>
       </c>
     </row>
     <row r="10">
@@ -15626,7 +15689,7 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>945</v>
+        <v>948</v>
       </c>
     </row>
     <row r="11">
@@ -15708,7 +15771,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C254"/>
+  <dimension ref="A1:C255"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -19422,7 +19485,7 @@
       </c>
       <c r="C222" s="6" t="inlineStr">
         <is>
-          <t>en-cours — 8 chapitre(s)</t>
+          <t>en-cours — 9 chapitre(s)</t>
         </is>
       </c>
     </row>
@@ -19563,48 +19626,48 @@
       </c>
     </row>
     <row r="231">
-      <c r="A231" s="6" t="inlineStr">
+      <c r="A231" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    L18.C09</t>
+        </is>
+      </c>
+      <c r="B231" s="3" t="inlineStr">
+        <is>
+          <t>L'ordre de grandeur, et le concurrent qu'il désigne</t>
+        </is>
+      </c>
+      <c r="C231" s="3" t="inlineStr">
+        <is>
+          <t>brouillon</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" s="6" t="inlineStr">
         <is>
           <t>L20</t>
         </is>
       </c>
-      <c r="B231" s="6" t="inlineStr">
+      <c r="B232" s="6" t="inlineStr">
         <is>
           <t>Droit international public, droit monétaire et commercial de la réforme</t>
         </is>
       </c>
-      <c r="C231" s="6" t="inlineStr">
+      <c r="C232" s="6" t="inlineStr">
         <is>
           <t>en-cours — 23 chapitre(s)</t>
-        </is>
-      </c>
-    </row>
-    <row r="232">
-      <c r="A232" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    L20.C01</t>
-        </is>
-      </c>
-      <c r="B232" s="3" t="inlineStr">
-        <is>
-          <t>Ce que ce livre doit établir</t>
-        </is>
-      </c>
-      <c r="C232" s="3" t="inlineStr">
-        <is>
-          <t>brouillon</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L20.C02</t>
+          <t xml:space="preserve">    L20.C01</t>
         </is>
       </c>
       <c r="B233" s="3" t="inlineStr">
         <is>
-          <t>L'interdiction du financement monétaire</t>
+          <t>Ce que ce livre doit établir</t>
         </is>
       </c>
       <c r="C233" s="3" t="inlineStr">
@@ -19616,12 +19679,12 @@
     <row r="234">
       <c r="A234" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L20.C03</t>
+          <t xml:space="preserve">    L20.C02</t>
         </is>
       </c>
       <c r="B234" s="3" t="inlineStr">
         <is>
-          <t>L'objectif principal et ce qu'il exclut</t>
+          <t>L'interdiction du financement monétaire</t>
         </is>
       </c>
       <c r="C234" s="3" t="inlineStr">
@@ -19633,12 +19696,12 @@
     <row r="235">
       <c r="A235" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L20.C04</t>
+          <t xml:space="preserve">    L20.C03</t>
         </is>
       </c>
       <c r="B235" s="3" t="inlineStr">
         <is>
-          <t>L'indépendance, et à l'égard de qui</t>
+          <t>L'objectif principal et ce qu'il exclut</t>
         </is>
       </c>
       <c r="C235" s="3" t="inlineStr">
@@ -19650,12 +19713,12 @@
     <row r="236">
       <c r="A236" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L20.C05</t>
+          <t xml:space="preserve">    L20.C04</t>
         </is>
       </c>
       <c r="B236" s="3" t="inlineStr">
         <is>
-          <t>Le monopole d'émission et le cours légal</t>
+          <t>L'indépendance, et à l'égard de qui</t>
         </is>
       </c>
       <c r="C236" s="3" t="inlineStr">
@@ -19667,12 +19730,12 @@
     <row r="237">
       <c r="A237" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L20.C06</t>
+          <t xml:space="preserve">    L20.C05</t>
         </is>
       </c>
       <c r="B237" s="3" t="inlineStr">
         <is>
-          <t>Les voies de révision et leur coût</t>
+          <t>Le monopole d'émission et le cours légal</t>
         </is>
       </c>
       <c r="C237" s="3" t="inlineStr">
@@ -19684,12 +19747,12 @@
     <row r="238">
       <c r="A238" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L20.C07</t>
+          <t xml:space="preserve">    L20.C06</t>
         </is>
       </c>
       <c r="B238" s="3" t="inlineStr">
         <is>
-          <t>L'accord monétaire international</t>
+          <t>Les voies de révision et leur coût</t>
         </is>
       </c>
       <c r="C238" s="3" t="inlineStr">
@@ -19701,12 +19764,12 @@
     <row r="239">
       <c r="A239" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L20.C08</t>
+          <t xml:space="preserve">    L20.C07</t>
         </is>
       </c>
       <c r="B239" s="3" t="inlineStr">
         <is>
-          <t>La parité inscrite dans le traité</t>
+          <t>L'accord monétaire international</t>
         </is>
       </c>
       <c r="C239" s="3" t="inlineStr">
@@ -19718,12 +19781,12 @@
     <row r="240">
       <c r="A240" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L20.C09</t>
+          <t xml:space="preserve">    L20.C08</t>
         </is>
       </c>
       <c r="B240" s="3" t="inlineStr">
         <is>
-          <t>L'amendement des statuts du Fonds</t>
+          <t>La parité inscrite dans le traité</t>
         </is>
       </c>
       <c r="C240" s="3" t="inlineStr">
@@ -19735,12 +19798,12 @@
     <row r="241">
       <c r="A241" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L20.C10</t>
+          <t xml:space="preserve">    L20.C09</t>
         </is>
       </c>
       <c r="B241" s="3" t="inlineStr">
         <is>
-          <t>Le vote pondéré et les voix de base</t>
+          <t>L'amendement des statuts du Fonds</t>
         </is>
       </c>
       <c r="C241" s="3" t="inlineStr">
@@ -19752,12 +19815,12 @@
     <row r="242">
       <c r="A242" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L20.C11</t>
+          <t xml:space="preserve">    L20.C10</t>
         </is>
       </c>
       <c r="B242" s="3" t="inlineStr">
         <is>
-          <t>La personnalité juridique et les immunités</t>
+          <t>Le vote pondéré et les voix de base</t>
         </is>
       </c>
       <c r="C242" s="3" t="inlineStr">
@@ -19769,12 +19832,12 @@
     <row r="243">
       <c r="A243" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L20.C12</t>
+          <t xml:space="preserve">    L20.C11</t>
         </is>
       </c>
       <c r="B243" s="3" t="inlineStr">
         <is>
-          <t>Les pouvoirs non délégables</t>
+          <t>La personnalité juridique et les immunités</t>
         </is>
       </c>
       <c r="C243" s="3" t="inlineStr">
@@ -19786,12 +19849,12 @@
     <row r="244">
       <c r="A244" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L20.C13</t>
+          <t xml:space="preserve">    L20.C12</t>
         </is>
       </c>
       <c r="B244" s="3" t="inlineStr">
         <is>
-          <t>L'entrée en vigueur, l'adhésion et le retrait</t>
+          <t>Les pouvoirs non délégables</t>
         </is>
       </c>
       <c r="C244" s="3" t="inlineStr">
@@ -19803,12 +19866,12 @@
     <row r="245">
       <c r="A245" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L20.C14</t>
+          <t xml:space="preserve">    L20.C13</t>
         </is>
       </c>
       <c r="B245" s="3" t="inlineStr">
         <is>
-          <t>Qui interprète le traité</t>
+          <t>L'entrée en vigueur, l'adhésion et le retrait</t>
         </is>
       </c>
       <c r="C245" s="3" t="inlineStr">
@@ -19820,12 +19883,12 @@
     <row r="246">
       <c r="A246" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L20.C15</t>
+          <t xml:space="preserve">    L20.C14</t>
         </is>
       </c>
       <c r="B246" s="3" t="inlineStr">
         <is>
-          <t>Le devoir international des agents</t>
+          <t>Qui interprète le traité</t>
         </is>
       </c>
       <c r="C246" s="3" t="inlineStr">
@@ -19837,12 +19900,12 @@
     <row r="247">
       <c r="A247" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L20.C16</t>
+          <t xml:space="preserve">    L20.C15</t>
         </is>
       </c>
       <c r="B247" s="3" t="inlineStr">
         <is>
-          <t>Le patrimoine commun de l'humanité</t>
+          <t>Le devoir international des agents</t>
         </is>
       </c>
       <c r="C247" s="3" t="inlineStr">
@@ -19854,12 +19917,12 @@
     <row r="248">
       <c r="A248" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L20.C17</t>
+          <t xml:space="preserve">    L20.C16</t>
         </is>
       </c>
       <c r="B248" s="3" t="inlineStr">
         <is>
-          <t>La sanctuarisation, et elle existe</t>
+          <t>Le patrimoine commun de l'humanité</t>
         </is>
       </c>
       <c r="C248" s="3" t="inlineStr">
@@ -19871,12 +19934,12 @@
     <row r="249">
       <c r="A249" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L20.C18</t>
+          <t xml:space="preserve">    L20.C17</t>
         </is>
       </c>
       <c r="B249" s="3" t="inlineStr">
         <is>
-          <t>L'amendement et la dérogation dans l'ordre commercial</t>
+          <t>La sanctuarisation, et elle existe</t>
         </is>
       </c>
       <c r="C249" s="3" t="inlineStr">
@@ -19888,12 +19951,12 @@
     <row r="250">
       <c r="A250" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L20.C19</t>
+          <t xml:space="preserve">    L20.C18</t>
         </is>
       </c>
       <c r="B250" s="3" t="inlineStr">
         <is>
-          <t>Le texte que la conformité invoque</t>
+          <t>L'amendement et la dérogation dans l'ordre commercial</t>
         </is>
       </c>
       <c r="C250" s="3" t="inlineStr">
@@ -19905,12 +19968,12 @@
     <row r="251">
       <c r="A251" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L20.C20</t>
+          <t xml:space="preserve">    L20.C19</t>
         </is>
       </c>
       <c r="B251" s="3" t="inlineStr">
         <is>
-          <t>L'ajustement aux frontières comme précédent</t>
+          <t>Le texte que la conformité invoque</t>
         </is>
       </c>
       <c r="C251" s="3" t="inlineStr">
@@ -19922,12 +19985,12 @@
     <row r="252">
       <c r="A252" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L20.C21</t>
+          <t xml:space="preserve">    L20.C20</t>
         </is>
       </c>
       <c r="B252" s="3" t="inlineStr">
         <is>
-          <t>La transparence et sa limite juridictionnelle</t>
+          <t>L'ajustement aux frontières comme précédent</t>
         </is>
       </c>
       <c r="C252" s="3" t="inlineStr">
@@ -19939,12 +20002,12 @@
     <row r="253">
       <c r="A253" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L20.C22</t>
+          <t xml:space="preserve">    L20.C21</t>
         </is>
       </c>
       <c r="B253" s="3" t="inlineStr">
         <is>
-          <t>Ce que le droit devrait devenir</t>
+          <t>La transparence et sa limite juridictionnelle</t>
         </is>
       </c>
       <c r="C253" s="3" t="inlineStr">
@@ -19956,15 +20019,32 @@
     <row r="254">
       <c r="A254" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">    L20.C22</t>
+        </is>
+      </c>
+      <c r="B254" s="3" t="inlineStr">
+        <is>
+          <t>Ce que le droit devrait devenir</t>
+        </is>
+      </c>
+      <c r="C254" s="3" t="inlineStr">
+        <is>
+          <t>brouillon</t>
+        </is>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">    L20.C23</t>
         </is>
       </c>
-      <c r="B254" s="3" t="inlineStr">
+      <c r="B255" s="3" t="inlineStr">
         <is>
           <t>La portée du livre</t>
         </is>
       </c>
-      <c r="C254" s="3" t="inlineStr">
+      <c r="C255" s="3" t="inlineStr">
         <is>
           <t>brouillon</t>
         </is>

--- a/plan-des-livres.xlsx
+++ b/plan-des-livres.xlsx
@@ -13,7 +13,7 @@
     <sheet name="Plan par livre" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Chapitres'!$A$1:$M$227</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Chapitres'!$A$1:$M$228</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -960,7 +960,7 @@
         </is>
       </c>
       <c r="F12" s="5" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G12" s="5" t="inlineStr"/>
       <c r="H12" s="5" t="inlineStr">
@@ -1354,7 +1354,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M227"/>
+  <dimension ref="A1:M228"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -2780,7 +2780,7 @@
       </c>
       <c r="H23" s="3" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="I23" s="3" t="n">
@@ -11729,17 +11729,17 @@
     <row r="167">
       <c r="A167" s="2" t="inlineStr">
         <is>
-          <t>L11.C01</t>
+          <t>L10.C07</t>
         </is>
       </c>
       <c r="B167" s="3" t="inlineStr">
         <is>
-          <t>L11</t>
+          <t>L10</t>
         </is>
       </c>
       <c r="C167" s="3" t="inlineStr">
         <is>
-          <t>Reflux ou destruction — la bifurcation</t>
+          <t>Ce qu'une banque centrale a le droit d'acheter, et le corpus généralisait depuis le cadre le plus permissif</t>
         </is>
       </c>
       <c r="D167" s="3" t="inlineStr">
@@ -11759,40 +11759,40 @@
       </c>
       <c r="G167" s="3" t="inlineStr">
         <is>
-          <t>conception</t>
+          <t>hybride</t>
         </is>
       </c>
       <c r="H167" s="3" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="I167" s="3" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="J167" s="3" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="K167" s="3" t="inlineStr">
         <is>
-          <t>contrepartie_comptable, reflux_monetaire, creation_monetaire, reflux_transactionnel, monnaie_comme_registre</t>
+          <t>contrepartie_comptable, creation_monetaire, hierarchie_monetaire, regle_contre_discretion, reflux_collectif, devise_cle</t>
         </is>
       </c>
       <c r="L167" s="3" t="inlineStr">
         <is>
-          <t>L1.C17, L1.C19, L1.C20, L1.C21, L1.C27, L1.C29</t>
+          <t>L1.C20, L1.C22, L1.C29, L10.C01, L10.C02, L10.C04, L10.C05, L10.C06, L11.C13, L20.C02</t>
         </is>
       </c>
       <c r="M167" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-11-ingenierie-des-baremes/c01-reflux-ou-destruction.md</t>
+          <t>corpus/livre-10-monnaies-banques-et-banques-centrales/c07-ce-qu-une-banque-centrale-a-le-droit-d-acheter.md</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" s="2" t="inlineStr">
         <is>
-          <t>L11.C02</t>
+          <t>L11.C01</t>
         </is>
       </c>
       <c r="B168" s="3" t="inlineStr">
@@ -11802,7 +11802,7 @@
       </c>
       <c r="C168" s="3" t="inlineStr">
         <is>
-          <t>Le trajet complet de la valeur</t>
+          <t>Reflux ou destruction — la bifurcation</t>
         </is>
       </c>
       <c r="D168" s="3" t="inlineStr">
@@ -11831,31 +11831,31 @@
         </is>
       </c>
       <c r="I168" s="3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J168" s="3" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K168" s="3" t="inlineStr">
         <is>
-          <t>contrepartie_comptable, reflux_collectif, reflux_transactionnel, demurrage, creation_monetaire</t>
+          <t>contrepartie_comptable, reflux_monetaire, creation_monetaire, reflux_transactionnel, monnaie_comme_registre</t>
         </is>
       </c>
       <c r="L168" s="3" t="inlineStr">
         <is>
-          <t>L1.C18, L1.C20, L1.C21, L1.C29, L11.C01</t>
+          <t>L1.C17, L1.C19, L1.C20, L1.C21, L1.C27, L1.C29</t>
         </is>
       </c>
       <c r="M168" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-11-ingenierie-des-baremes/c02-le-trajet-complet-de-la-valeur.md</t>
+          <t>corpus/livre-11-ingenierie-des-baremes/c01-reflux-ou-destruction.md</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" s="2" t="inlineStr">
         <is>
-          <t>L11.C03</t>
+          <t>L11.C02</t>
         </is>
       </c>
       <c r="B169" s="3" t="inlineStr">
@@ -11865,7 +11865,7 @@
       </c>
       <c r="C169" s="3" t="inlineStr">
         <is>
-          <t>Le compte des objectifs et des instruments</t>
+          <t>Le trajet complet de la valeur</t>
         </is>
       </c>
       <c r="D169" s="3" t="inlineStr">
@@ -11890,35 +11890,35 @@
       </c>
       <c r="H169" s="3" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="I169" s="3" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="J169" s="3" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K169" s="3" t="inlineStr">
         <is>
-          <t>affectation_des_instruments, bareme, effet_veblen, reflux_collectif, reflux_transactionnel, demurrage, degeneratif, qualification_regenerative</t>
+          <t>contrepartie_comptable, reflux_collectif, reflux_transactionnel, demurrage, creation_monetaire</t>
         </is>
       </c>
       <c r="L169" s="3" t="inlineStr">
         <is>
-          <t>L1.C18, L1.C20, L1.C21, L1.C26, L1.C28, L11.C01, L11.C02, L11.C04, L11.C05, L11.C06, L11.C07, L11.C09, L11.C10, L11.C11</t>
+          <t>L1.C18, L1.C20, L1.C21, L1.C29, L11.C01</t>
         </is>
       </c>
       <c r="M169" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-11-ingenierie-des-baremes/c03-le-compte-des-objectifs-et-des-instruments.md</t>
+          <t>corpus/livre-11-ingenierie-des-baremes/c02-le-trajet-complet-de-la-valeur.md</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" s="2" t="inlineStr">
         <is>
-          <t>L11.C04</t>
+          <t>L11.C03</t>
         </is>
       </c>
       <c r="B170" s="3" t="inlineStr">
@@ -11928,7 +11928,7 @@
       </c>
       <c r="C170" s="3" t="inlineStr">
         <is>
-          <t>Les instruments du reflux sous parité fixe</t>
+          <t>Le compte des objectifs et des instruments</t>
         </is>
       </c>
       <c r="D170" s="3" t="inlineStr">
@@ -11957,31 +11957,31 @@
         </is>
       </c>
       <c r="I170" s="3" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="J170" s="3" t="n">
         <v>5</v>
       </c>
       <c r="K170" s="3" t="inlineStr">
         <is>
-          <t>referentiel_de_change, demurrage, reflux_transactionnel, reflux_collectif, bareme, affectation_des_instruments, creation_monetaire</t>
+          <t>affectation_des_instruments, bareme, effet_veblen, reflux_collectif, reflux_transactionnel, demurrage, degeneratif, qualification_regenerative</t>
         </is>
       </c>
       <c r="L170" s="3" t="inlineStr">
         <is>
-          <t>L1.C19, L1.C21, L1.C24, L1.C26, L1.C27, L11.C01, L11.C02, L11.C03</t>
+          <t>L1.C18, L1.C20, L1.C21, L1.C26, L1.C28, L11.C01, L11.C02, L11.C04, L11.C05, L11.C06, L11.C07, L11.C09, L11.C10, L11.C11</t>
         </is>
       </c>
       <c r="M170" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-11-ingenierie-des-baremes/c04-les-instruments-du-reflux-sous-parite-fixe.md</t>
+          <t>corpus/livre-11-ingenierie-des-baremes/c03-le-compte-des-objectifs-et-des-instruments.md</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" s="2" t="inlineStr">
         <is>
-          <t>L11.C05</t>
+          <t>L11.C04</t>
         </is>
       </c>
       <c r="B171" s="3" t="inlineStr">
@@ -11991,7 +11991,7 @@
       </c>
       <c r="C171" s="3" t="inlineStr">
         <is>
-          <t>L'assiette du reflux transactionnel</t>
+          <t>Les instruments du reflux sous parité fixe</t>
         </is>
       </c>
       <c r="D171" s="3" t="inlineStr">
@@ -12016,35 +12016,35 @@
       </c>
       <c r="H171" s="3" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="I171" s="3" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="J171" s="3" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="K171" s="3" t="inlineStr">
         <is>
-          <t>reflux_transactionnel, bareme, degeneratif, reflux_collectif, robustesse, affectation_des_instruments</t>
+          <t>referentiel_de_change, demurrage, reflux_transactionnel, reflux_collectif, bareme, affectation_des_instruments, creation_monetaire</t>
         </is>
       </c>
       <c r="L171" s="3" t="inlineStr">
         <is>
-          <t>L1.C18, L1.C21, L1.C23, L11.C02, L11.C03, L11.C04</t>
+          <t>L1.C19, L1.C21, L1.C24, L1.C26, L1.C27, L11.C01, L11.C02, L11.C03</t>
         </is>
       </c>
       <c r="M171" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-11-ingenierie-des-baremes/c05-l-assiette-du-reflux-transactionnel.md</t>
+          <t>corpus/livre-11-ingenierie-des-baremes/c04-les-instruments-du-reflux-sous-parite-fixe.md</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" s="2" t="inlineStr">
         <is>
-          <t>L11.C06</t>
+          <t>L11.C05</t>
         </is>
       </c>
       <c r="B172" s="3" t="inlineStr">
@@ -12054,7 +12054,7 @@
       </c>
       <c r="C172" s="3" t="inlineStr">
         <is>
-          <t>Le barème par défaut</t>
+          <t>L'assiette du reflux transactionnel</t>
         </is>
       </c>
       <c r="D172" s="3" t="inlineStr">
@@ -12083,31 +12083,31 @@
         </is>
       </c>
       <c r="I172" s="3" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="J172" s="3" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="K172" s="3" t="inlineStr">
         <is>
-          <t>bareme, qualification_regenerative, degeneratif, reflux_transactionnel, regle_contre_discretion, affectation_des_instruments</t>
+          <t>reflux_transactionnel, bareme, degeneratif, reflux_collectif, robustesse, affectation_des_instruments</t>
         </is>
       </c>
       <c r="L172" s="3" t="inlineStr">
         <is>
-          <t>L1.C18, L1.C21, L1.C22, L1.C27, L1.C28, L11.C03, L11.C05</t>
+          <t>L1.C18, L1.C21, L1.C23, L11.C02, L11.C03, L11.C04</t>
         </is>
       </c>
       <c r="M172" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-11-ingenierie-des-baremes/c06-le-bareme-par-defaut.md</t>
+          <t>corpus/livre-11-ingenierie-des-baremes/c05-l-assiette-du-reflux-transactionnel.md</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" s="2" t="inlineStr">
         <is>
-          <t>L11.C07</t>
+          <t>L11.C06</t>
         </is>
       </c>
       <c r="B173" s="3" t="inlineStr">
@@ -12117,7 +12117,7 @@
       </c>
       <c r="C173" s="3" t="inlineStr">
         <is>
-          <t>Le demurrage et son nœud de prélèvement</t>
+          <t>Le barème par défaut</t>
         </is>
       </c>
       <c r="D173" s="3" t="inlineStr">
@@ -12153,24 +12153,24 @@
       </c>
       <c r="K173" s="3" t="inlineStr">
         <is>
-          <t>demurrage, reflux_collectif, reflux_transactionnel, bareme, affectation_des_instruments, referentiel_de_change</t>
+          <t>bareme, qualification_regenerative, degeneratif, reflux_transactionnel, regle_contre_discretion, affectation_des_instruments</t>
         </is>
       </c>
       <c r="L173" s="3" t="inlineStr">
         <is>
-          <t>L1.C21, L1.C26, L11.C02, L11.C03, L11.C04, L11.C05, L11.C06</t>
+          <t>L1.C18, L1.C21, L1.C22, L1.C27, L1.C28, L11.C03, L11.C05</t>
         </is>
       </c>
       <c r="M173" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-11-ingenierie-des-baremes/c07-le-demurrage-et-son-noeud.md</t>
+          <t>corpus/livre-11-ingenierie-des-baremes/c06-le-bareme-par-defaut.md</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" s="2" t="inlineStr">
         <is>
-          <t>L11.C08</t>
+          <t>L11.C07</t>
         </is>
       </c>
       <c r="B174" s="3" t="inlineStr">
@@ -12180,7 +12180,7 @@
       </c>
       <c r="C174" s="3" t="inlineStr">
         <is>
-          <t>Les dérogations</t>
+          <t>Le demurrage et son nœud de prélèvement</t>
         </is>
       </c>
       <c r="D174" s="3" t="inlineStr">
@@ -12216,24 +12216,24 @@
       </c>
       <c r="K174" s="3" t="inlineStr">
         <is>
-          <t>demurrage, reflux_transactionnel, bareme, qualification_regenerative, reflux_collectif, degeneratif</t>
+          <t>demurrage, reflux_collectif, reflux_transactionnel, bareme, affectation_des_instruments, referentiel_de_change</t>
         </is>
       </c>
       <c r="L174" s="3" t="inlineStr">
         <is>
-          <t>L1.C18, L1.C20, L1.C21, L1.C22, L11.C03, L11.C05, L11.C06, L11.C07</t>
+          <t>L1.C21, L1.C26, L11.C02, L11.C03, L11.C04, L11.C05, L11.C06</t>
         </is>
       </c>
       <c r="M174" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-11-ingenierie-des-baremes/c08-les-derogations.md</t>
+          <t>corpus/livre-11-ingenierie-des-baremes/c07-le-demurrage-et-son-noeud.md</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" s="2" t="inlineStr">
         <is>
-          <t>L11.C09</t>
+          <t>L11.C08</t>
         </is>
       </c>
       <c r="B175" s="3" t="inlineStr">
@@ -12243,7 +12243,7 @@
       </c>
       <c r="C175" s="3" t="inlineStr">
         <is>
-          <t>L'incidence — qui paie le reflux</t>
+          <t>Les dérogations</t>
         </is>
       </c>
       <c r="D175" s="3" t="inlineStr">
@@ -12268,7 +12268,7 @@
       </c>
       <c r="H175" s="3" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="I175" s="3" t="n">
@@ -12279,24 +12279,24 @@
       </c>
       <c r="K175" s="3" t="inlineStr">
         <is>
-          <t>reflux_collectif, reflux_transactionnel, demurrage, bareme, degeneratif, qualification_regenerative</t>
+          <t>demurrage, reflux_transactionnel, bareme, qualification_regenerative, reflux_collectif, degeneratif</t>
         </is>
       </c>
       <c r="L175" s="3" t="inlineStr">
         <is>
-          <t>L1.C21, L1.C22, L11.C03, L11.C05, L11.C06, L11.C07, L11.C08</t>
+          <t>L1.C18, L1.C20, L1.C21, L1.C22, L11.C03, L11.C05, L11.C06, L11.C07</t>
         </is>
       </c>
       <c r="M175" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-11-ingenierie-des-baremes/c09-l-incidence-qui-paie-le-reflux.md</t>
+          <t>corpus/livre-11-ingenierie-des-baremes/c08-les-derogations.md</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" s="2" t="inlineStr">
         <is>
-          <t>L11.C10</t>
+          <t>L11.C09</t>
         </is>
       </c>
       <c r="B176" s="3" t="inlineStr">
@@ -12306,7 +12306,7 @@
       </c>
       <c r="C176" s="3" t="inlineStr">
         <is>
-          <t>La trajectoire de mise en place</t>
+          <t>L'incidence — qui paie le reflux</t>
         </is>
       </c>
       <c r="D176" s="3" t="inlineStr">
@@ -12335,31 +12335,31 @@
         </is>
       </c>
       <c r="I176" s="3" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="J176" s="3" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="K176" s="3" t="inlineStr">
         <is>
-          <t>bareme, regle_contre_discretion, degeneratif, reflux_transactionnel, qualification_regenerative, affectation_des_instruments</t>
+          <t>reflux_collectif, reflux_transactionnel, demurrage, bareme, degeneratif, qualification_regenerative</t>
         </is>
       </c>
       <c r="L176" s="3" t="inlineStr">
         <is>
-          <t>L1.C21, L1.C23, L1.C27, L11.C03, L11.C05, L11.C06, L11.C09</t>
+          <t>L1.C21, L1.C22, L11.C03, L11.C05, L11.C06, L11.C07, L11.C08</t>
         </is>
       </c>
       <c r="M176" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-11-ingenierie-des-baremes/c10-la-trajectoire-de-mise-en-place.md</t>
+          <t>corpus/livre-11-ingenierie-des-baremes/c09-l-incidence-qui-paie-le-reflux.md</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" s="2" t="inlineStr">
         <is>
-          <t>L11.C11</t>
+          <t>L11.C10</t>
         </is>
       </c>
       <c r="B177" s="3" t="inlineStr">
@@ -12369,7 +12369,7 @@
       </c>
       <c r="C177" s="3" t="inlineStr">
         <is>
-          <t>Qui arrête le barème</t>
+          <t>La trajectoire de mise en place</t>
         </is>
       </c>
       <c r="D177" s="3" t="inlineStr">
@@ -12394,35 +12394,35 @@
       </c>
       <c r="H177" s="3" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="I177" s="3" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="J177" s="3" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="K177" s="3" t="inlineStr">
         <is>
-          <t>bareme, affectation_des_instruments, referentiel_de_change, qualification_regenerative, regle_contre_discretion, reflux_collectif</t>
+          <t>bareme, regle_contre_discretion, degeneratif, reflux_transactionnel, qualification_regenerative, affectation_des_instruments</t>
         </is>
       </c>
       <c r="L177" s="3" t="inlineStr">
         <is>
-          <t>L1.C18, L1.C22, L1.C26, L1.C27, L11.C04, L11.C06, L11.C08, L11.C10</t>
+          <t>L1.C21, L1.C23, L1.C27, L11.C03, L11.C05, L11.C06, L11.C09</t>
         </is>
       </c>
       <c r="M177" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-11-ingenierie-des-baremes/c11-qui-arrete-le-bareme.md</t>
+          <t>corpus/livre-11-ingenierie-des-baremes/c10-la-trajectoire-de-mise-en-place.md</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" s="2" t="inlineStr">
         <is>
-          <t>L11.C12</t>
+          <t>L11.C11</t>
         </is>
       </c>
       <c r="B178" s="3" t="inlineStr">
@@ -12432,7 +12432,7 @@
       </c>
       <c r="C178" s="3" t="inlineStr">
         <is>
-          <t>La directive</t>
+          <t>Qui arrête le barème</t>
         </is>
       </c>
       <c r="D178" s="3" t="inlineStr">
@@ -12461,31 +12461,31 @@
         </is>
       </c>
       <c r="I178" s="3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J178" s="3" t="n">
         <v>4</v>
       </c>
       <c r="K178" s="3" t="inlineStr">
         <is>
-          <t>bareme, regle_contre_discretion, affectation_des_instruments, reflux_collectif, qualification_regenerative</t>
+          <t>bareme, affectation_des_instruments, referentiel_de_change, qualification_regenerative, regle_contre_discretion, reflux_collectif</t>
         </is>
       </c>
       <c r="L178" s="3" t="inlineStr">
         <is>
-          <t>L1.C21, L11.C03, L11.C05, L11.C06, L11.C09, L11.C10, L11.C11</t>
+          <t>L1.C18, L1.C22, L1.C26, L1.C27, L11.C04, L11.C06, L11.C08, L11.C10</t>
         </is>
       </c>
       <c r="M178" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-11-ingenierie-des-baremes/c12-la-directive.md</t>
+          <t>corpus/livre-11-ingenierie-des-baremes/c11-qui-arrete-le-bareme.md</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" s="2" t="inlineStr">
         <is>
-          <t>L11.C13</t>
+          <t>L11.C12</t>
         </is>
       </c>
       <c r="B179" s="3" t="inlineStr">
@@ -12495,7 +12495,7 @@
       </c>
       <c r="C179" s="3" t="inlineStr">
         <is>
-          <t>Le barème de qualification</t>
+          <t>La directive</t>
         </is>
       </c>
       <c r="D179" s="3" t="inlineStr">
@@ -12520,35 +12520,35 @@
       </c>
       <c r="H179" s="3" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="I179" s="3" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J179" s="3" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K179" s="3" t="inlineStr">
         <is>
-          <t>qualification_regenerative, bareme, creation_monetaire, additionnalite, degeneratif, essentiel_insolvable</t>
+          <t>bareme, regle_contre_discretion, affectation_des_instruments, reflux_collectif, qualification_regenerative</t>
         </is>
       </c>
       <c r="L179" s="3" t="inlineStr">
         <is>
-          <t>L1.C18, L1.C20, L1.C22, L1.C27, L11.C03, L11.C05, L11.C06, L11.C08, L11.C09, L11.C10, L11.C11, L11.C12</t>
+          <t>L1.C21, L11.C03, L11.C05, L11.C06, L11.C09, L11.C10, L11.C11</t>
         </is>
       </c>
       <c r="M179" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-11-ingenierie-des-baremes/c13-le-bareme-de-qualification.md</t>
+          <t>corpus/livre-11-ingenierie-des-baremes/c12-la-directive.md</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" s="2" t="inlineStr">
         <is>
-          <t>L11.C14</t>
+          <t>L11.C13</t>
         </is>
       </c>
       <c r="B180" s="3" t="inlineStr">
@@ -12558,7 +12558,7 @@
       </c>
       <c r="C180" s="3" t="inlineStr">
         <is>
-          <t>Le tableau de bord, ou les données de la directive</t>
+          <t>Le barème de qualification</t>
         </is>
       </c>
       <c r="D180" s="3" t="inlineStr">
@@ -12583,35 +12583,35 @@
       </c>
       <c r="H180" s="3" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="I180" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="J180" s="3" t="n">
         <v>5</v>
       </c>
-      <c r="J180" s="3" t="n">
-        <v>4</v>
-      </c>
       <c r="K180" s="3" t="inlineStr">
         <is>
-          <t>indicateur_de_progres, bareme, regle_contre_discretion, affectation_des_instruments, degeneratif, qualification_regenerative</t>
+          <t>qualification_regenerative, bareme, creation_monetaire, additionnalite, degeneratif, essentiel_insolvable</t>
         </is>
       </c>
       <c r="L180" s="3" t="inlineStr">
         <is>
-          <t>L1.C21, L1.C28, L11.C03, L11.C05, L11.C11, L11.C12, L11.C13</t>
+          <t>L1.C18, L1.C20, L1.C22, L1.C27, L11.C03, L11.C05, L11.C06, L11.C08, L11.C09, L11.C10, L11.C11, L11.C12</t>
         </is>
       </c>
       <c r="M180" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-11-ingenierie-des-baremes/c14-le-tableau-de-bord.md</t>
+          <t>corpus/livre-11-ingenierie-des-baremes/c13-le-bareme-de-qualification.md</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" s="2" t="inlineStr">
         <is>
-          <t>L11.C15</t>
+          <t>L11.C14</t>
         </is>
       </c>
       <c r="B181" s="3" t="inlineStr">
@@ -12621,7 +12621,7 @@
       </c>
       <c r="C181" s="3" t="inlineStr">
         <is>
-          <t>Les parités du référentiel de change</t>
+          <t>Le tableau de bord, ou les données de la directive</t>
         </is>
       </c>
       <c r="D181" s="3" t="inlineStr">
@@ -12657,24 +12657,24 @@
       </c>
       <c r="K181" s="3" t="inlineStr">
         <is>
-          <t>referentiel_de_change, bareme, indicateur_de_progres, regle_contre_discretion, affectation_des_instruments</t>
+          <t>indicateur_de_progres, bareme, regle_contre_discretion, affectation_des_instruments, degeneratif, qualification_regenerative</t>
         </is>
       </c>
       <c r="L181" s="3" t="inlineStr">
         <is>
-          <t>L1.C24, L1.C25, L1.C26, L1.C28, L11.C01, L11.C04, L11.C10, L11.C12, L11.C14</t>
+          <t>L1.C21, L1.C28, L11.C03, L11.C05, L11.C11, L11.C12, L11.C13</t>
         </is>
       </c>
       <c r="M181" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-11-ingenierie-des-baremes/c15-les-parites-du-referentiel.md</t>
+          <t>corpus/livre-11-ingenierie-des-baremes/c14-le-tableau-de-bord.md</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" s="2" t="inlineStr">
         <is>
-          <t>L11.C16</t>
+          <t>L11.C15</t>
         </is>
       </c>
       <c r="B182" s="3" t="inlineStr">
@@ -12684,7 +12684,7 @@
       </c>
       <c r="C182" s="3" t="inlineStr">
         <is>
-          <t>La valorisation des communs</t>
+          <t>Les parités du référentiel de change</t>
         </is>
       </c>
       <c r="D182" s="3" t="inlineStr">
@@ -12709,35 +12709,35 @@
       </c>
       <c r="H182" s="3" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="I182" s="3" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J182" s="3" t="n">
         <v>4</v>
       </c>
       <c r="K182" s="3" t="inlineStr">
         <is>
-          <t>valorisation_des_communs, bareme, essentiel_insolvable, polycentricite, affectation_des_instruments, indicateur_de_progres</t>
+          <t>referentiel_de_change, bareme, indicateur_de_progres, regle_contre_discretion, affectation_des_instruments</t>
         </is>
       </c>
       <c r="L182" s="3" t="inlineStr">
         <is>
-          <t>L1.C15, L1.C18, L1.C21, L1.C22, L1.C24, L1.C26, L1.C27, L11.C02, L11.C03, L11.C04, L11.C06, L11.C09, L11.C11, L11.C12, L11.C13, L11.C15</t>
+          <t>L1.C24, L1.C25, L1.C26, L1.C28, L11.C01, L11.C04, L11.C10, L11.C12, L11.C14</t>
         </is>
       </c>
       <c r="M182" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-11-ingenierie-des-baremes/c16-la-valorisation-des-communs.md</t>
+          <t>corpus/livre-11-ingenierie-des-baremes/c15-les-parites-du-referentiel.md</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" s="2" t="inlineStr">
         <is>
-          <t>L11.C17</t>
+          <t>L11.C16</t>
         </is>
       </c>
       <c r="B183" s="3" t="inlineStr">
@@ -12747,7 +12747,7 @@
       </c>
       <c r="C183" s="3" t="inlineStr">
         <is>
-          <t>La cohérence des cinq barèmes</t>
+          <t>La valorisation des communs</t>
         </is>
       </c>
       <c r="D183" s="3" t="inlineStr">
@@ -12772,35 +12772,35 @@
       </c>
       <c r="H183" s="3" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="I183" s="3" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="J183" s="3" t="n">
         <v>4</v>
       </c>
       <c r="K183" s="3" t="inlineStr">
         <is>
-          <t>bareme, affectation_des_instruments, regle_contre_discretion, qualification_regenerative, valorisation_des_communs, reflux_transactionnel, referentiel_de_change, indicateur_de_progres, polycentricite</t>
+          <t>valorisation_des_communs, bareme, essentiel_insolvable, polycentricite, affectation_des_instruments, indicateur_de_progres</t>
         </is>
       </c>
       <c r="L183" s="3" t="inlineStr">
         <is>
-          <t>L1.C18, L1.C20, L1.C21, L1.C26, L1.C27, L1.C28, L11.C03, L11.C05, L11.C06, L11.C07, L11.C09, L11.C10, L11.C11, L11.C12, L11.C13, L11.C14, L11.C15, L11.C16</t>
+          <t>L1.C15, L1.C18, L1.C21, L1.C22, L1.C24, L1.C26, L1.C27, L11.C02, L11.C03, L11.C04, L11.C06, L11.C09, L11.C11, L11.C12, L11.C13, L11.C15</t>
         </is>
       </c>
       <c r="M183" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-11-ingenierie-des-baremes/c17-la-coherence-des-cinq-baremes.md</t>
+          <t>corpus/livre-11-ingenierie-des-baremes/c16-la-valorisation-des-communs.md</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" s="2" t="inlineStr">
         <is>
-          <t>L11.C18</t>
+          <t>L11.C17</t>
         </is>
       </c>
       <c r="B184" s="3" t="inlineStr">
@@ -12810,7 +12810,7 @@
       </c>
       <c r="C184" s="3" t="inlineStr">
         <is>
-          <t>Le seuil d'exemption</t>
+          <t>La cohérence des cinq barèmes</t>
         </is>
       </c>
       <c r="D184" s="3" t="inlineStr">
@@ -12839,31 +12839,31 @@
         </is>
       </c>
       <c r="I184" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J184" s="3" t="n">
         <v>4</v>
       </c>
       <c r="K184" s="3" t="inlineStr">
         <is>
-          <t>demurrage, reflux_transactionnel, bareme, regle_contre_discretion, affectation_des_instruments, valorisation_des_communs</t>
+          <t>bareme, affectation_des_instruments, regle_contre_discretion, qualification_regenerative, valorisation_des_communs, reflux_transactionnel, referentiel_de_change, indicateur_de_progres, polycentricite</t>
         </is>
       </c>
       <c r="L184" s="3" t="inlineStr">
         <is>
-          <t>L1.C21, L11.C03, L11.C05, L11.C06, L11.C07, L11.C08, L11.C09, L11.C12, L11.C13, L11.C16, L11.C17</t>
+          <t>L1.C18, L1.C20, L1.C21, L1.C26, L1.C27, L1.C28, L11.C03, L11.C05, L11.C06, L11.C07, L11.C09, L11.C10, L11.C11, L11.C12, L11.C13, L11.C14, L11.C15, L11.C16</t>
         </is>
       </c>
       <c r="M184" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-11-ingenierie-des-baremes/c18-le-seuil-d-exemption.md</t>
+          <t>corpus/livre-11-ingenierie-des-baremes/c17-la-coherence-des-cinq-baremes.md</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" s="2" t="inlineStr">
         <is>
-          <t>L11.C19</t>
+          <t>L11.C18</t>
         </is>
       </c>
       <c r="B185" s="3" t="inlineStr">
@@ -12873,7 +12873,7 @@
       </c>
       <c r="C185" s="3" t="inlineStr">
         <is>
-          <t>Le recours</t>
+          <t>Le seuil d'exemption</t>
         </is>
       </c>
       <c r="D185" s="3" t="inlineStr">
@@ -12909,24 +12909,24 @@
       </c>
       <c r="K185" s="3" t="inlineStr">
         <is>
-          <t>bareme, qualification_regenerative, valorisation_des_communs, demurrage, regle_contre_discretion, essentiel_insolvable, affectation_des_instruments</t>
+          <t>demurrage, reflux_transactionnel, bareme, regle_contre_discretion, affectation_des_instruments, valorisation_des_communs</t>
         </is>
       </c>
       <c r="L185" s="3" t="inlineStr">
         <is>
-          <t>L1.C18, L11.C03, L11.C06, L11.C08, L11.C09, L11.C11, L11.C12, L11.C13, L11.C16, L11.C17, L11.C18</t>
+          <t>L1.C21, L11.C03, L11.C05, L11.C06, L11.C07, L11.C08, L11.C09, L11.C12, L11.C13, L11.C16, L11.C17</t>
         </is>
       </c>
       <c r="M185" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-11-ingenierie-des-baremes/c19-le-recours.md</t>
+          <t>corpus/livre-11-ingenierie-des-baremes/c18-le-seuil-d-exemption.md</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" s="2" t="inlineStr">
         <is>
-          <t>L11.C20</t>
+          <t>L11.C19</t>
         </is>
       </c>
       <c r="B186" s="3" t="inlineStr">
@@ -12936,7 +12936,7 @@
       </c>
       <c r="C186" s="3" t="inlineStr">
         <is>
-          <t>L'amendement de la directive</t>
+          <t>Le recours</t>
         </is>
       </c>
       <c r="D186" s="3" t="inlineStr">
@@ -12972,24 +12972,24 @@
       </c>
       <c r="K186" s="3" t="inlineStr">
         <is>
-          <t>bareme, regle_contre_discretion, qualification_regenerative, valorisation_des_communs, referentiel_de_change, affectation_des_instruments</t>
+          <t>bareme, qualification_regenerative, valorisation_des_communs, demurrage, regle_contre_discretion, essentiel_insolvable, affectation_des_instruments</t>
         </is>
       </c>
       <c r="L186" s="3" t="inlineStr">
         <is>
-          <t>L1.C21, L1.C26, L1.C28, L11.C03, L11.C06, L11.C10, L11.C12, L11.C13, L11.C15, L11.C16, L11.C17, L11.C18, L11.C19</t>
+          <t>L1.C18, L11.C03, L11.C06, L11.C08, L11.C09, L11.C11, L11.C12, L11.C13, L11.C16, L11.C17, L11.C18</t>
         </is>
       </c>
       <c r="M186" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-11-ingenierie-des-baremes/c20-l-amendement-de-la-directive.md</t>
+          <t>corpus/livre-11-ingenierie-des-baremes/c19-le-recours.md</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" s="2" t="inlineStr">
         <is>
-          <t>L11.C21</t>
+          <t>L11.C20</t>
         </is>
       </c>
       <c r="B187" s="3" t="inlineStr">
@@ -12999,7 +12999,7 @@
       </c>
       <c r="C187" s="3" t="inlineStr">
         <is>
-          <t>La perception</t>
+          <t>L'amendement de la directive</t>
         </is>
       </c>
       <c r="D187" s="3" t="inlineStr">
@@ -13028,31 +13028,31 @@
         </is>
       </c>
       <c r="I187" s="3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J187" s="3" t="n">
         <v>4</v>
       </c>
       <c r="K187" s="3" t="inlineStr">
         <is>
-          <t>reflux_transactionnel, reflux_collectif, bareme, demurrage, affectation_des_instruments, contrepartie_comptable</t>
+          <t>bareme, regle_contre_discretion, qualification_regenerative, valorisation_des_communs, referentiel_de_change, affectation_des_instruments</t>
         </is>
       </c>
       <c r="L187" s="3" t="inlineStr">
         <is>
-          <t>L1.C21, L11.C01, L11.C02, L11.C03, L11.C05, L11.C09, L11.C10, L11.C16, L11.C17, L11.C19, L11.C20</t>
+          <t>L1.C21, L1.C26, L1.C28, L11.C03, L11.C06, L11.C10, L11.C12, L11.C13, L11.C15, L11.C16, L11.C17, L11.C18, L11.C19</t>
         </is>
       </c>
       <c r="M187" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-11-ingenierie-des-baremes/c21-la-perception.md</t>
+          <t>corpus/livre-11-ingenierie-des-baremes/c20-l-amendement-de-la-directive.md</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" s="2" t="inlineStr">
         <is>
-          <t>L11.C22</t>
+          <t>L11.C21</t>
         </is>
       </c>
       <c r="B188" s="3" t="inlineStr">
@@ -13062,7 +13062,7 @@
       </c>
       <c r="C188" s="3" t="inlineStr">
         <is>
-          <t>Les délais</t>
+          <t>La perception</t>
         </is>
       </c>
       <c r="D188" s="3" t="inlineStr">
@@ -13091,31 +13091,31 @@
         </is>
       </c>
       <c r="I188" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J188" s="3" t="n">
         <v>4</v>
       </c>
       <c r="K188" s="3" t="inlineStr">
         <is>
-          <t>reflux_collectif, reflux_transactionnel, bareme, regle_contre_discretion, qualification_regenerative, affectation_des_instruments, robustesse</t>
+          <t>reflux_transactionnel, reflux_collectif, bareme, demurrage, affectation_des_instruments, contrepartie_comptable</t>
         </is>
       </c>
       <c r="L188" s="3" t="inlineStr">
         <is>
-          <t>L1.C21, L11.C03, L11.C07, L11.C10, L11.C12, L11.C13, L11.C16, L11.C17, L11.C19, L11.C20, L11.C21</t>
+          <t>L1.C21, L11.C01, L11.C02, L11.C03, L11.C05, L11.C09, L11.C10, L11.C16, L11.C17, L11.C19, L11.C20</t>
         </is>
       </c>
       <c r="M188" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-11-ingenierie-des-baremes/c22-les-delais.md</t>
+          <t>corpus/livre-11-ingenierie-des-baremes/c21-la-perception.md</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" s="2" t="inlineStr">
         <is>
-          <t>L11.C23</t>
+          <t>L11.C22</t>
         </is>
       </c>
       <c r="B189" s="3" t="inlineStr">
@@ -13125,7 +13125,7 @@
       </c>
       <c r="C189" s="3" t="inlineStr">
         <is>
-          <t>La contracyclicité</t>
+          <t>Les délais</t>
         </is>
       </c>
       <c r="D189" s="3" t="inlineStr">
@@ -13154,31 +13154,31 @@
         </is>
       </c>
       <c r="I189" s="3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J189" s="3" t="n">
         <v>4</v>
       </c>
       <c r="K189" s="3" t="inlineStr">
         <is>
-          <t>reflux_transactionnel, reflux_collectif, essentiel_insolvable, degeneratif, bareme, robustesse, affectation_des_instruments, contrepartie_comptable</t>
+          <t>reflux_collectif, reflux_transactionnel, bareme, regle_contre_discretion, qualification_regenerative, affectation_des_instruments, robustesse</t>
         </is>
       </c>
       <c r="L189" s="3" t="inlineStr">
         <is>
-          <t>L1.C15, L1.C21, L1.C29, L11.C01, L11.C02, L11.C03, L11.C07, L11.C10, L11.C12, L11.C14, L11.C16, L11.C17, L11.C21, L11.C22</t>
+          <t>L1.C21, L11.C03, L11.C07, L11.C10, L11.C12, L11.C13, L11.C16, L11.C17, L11.C19, L11.C20, L11.C21</t>
         </is>
       </c>
       <c r="M189" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-11-ingenierie-des-baremes/c23-la-contracyclicite.md</t>
+          <t>corpus/livre-11-ingenierie-des-baremes/c22-les-delais.md</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" s="2" t="inlineStr">
         <is>
-          <t>L11.C24</t>
+          <t>L11.C23</t>
         </is>
       </c>
       <c r="B190" s="3" t="inlineStr">
@@ -13188,7 +13188,7 @@
       </c>
       <c r="C190" s="3" t="inlineStr">
         <is>
-          <t>Le barème aux frontières</t>
+          <t>La contracyclicité</t>
         </is>
       </c>
       <c r="D190" s="3" t="inlineStr">
@@ -13213,35 +13213,35 @@
       </c>
       <c r="H190" s="3" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="I190" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J190" s="3" t="n">
         <v>4</v>
       </c>
       <c r="K190" s="3" t="inlineStr">
         <is>
-          <t>seuil_d_activation, bareme, degeneratif, reflux_transactionnel, referentiel_de_change, essentiel_insolvable, affectation_des_instruments</t>
+          <t>reflux_transactionnel, reflux_collectif, essentiel_insolvable, degeneratif, bareme, robustesse, affectation_des_instruments, contrepartie_comptable</t>
         </is>
       </c>
       <c r="L190" s="3" t="inlineStr">
         <is>
-          <t>L1.C26, L1.C27, L11.C04, L11.C05, L11.C06, L11.C09, L11.C13, L11.C16, L11.C17, L11.C19, L11.C21</t>
+          <t>L1.C15, L1.C21, L1.C29, L11.C01, L11.C02, L11.C03, L11.C07, L11.C10, L11.C12, L11.C14, L11.C16, L11.C17, L11.C21, L11.C22</t>
         </is>
       </c>
       <c r="M190" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-11-ingenierie-des-baremes/c24-le-bareme-aux-frontieres.md</t>
+          <t>corpus/livre-11-ingenierie-des-baremes/c23-la-contracyclicite.md</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" s="2" t="inlineStr">
         <is>
-          <t>L11.C25</t>
+          <t>L11.C24</t>
         </is>
       </c>
       <c r="B191" s="3" t="inlineStr">
@@ -13251,7 +13251,7 @@
       </c>
       <c r="C191" s="3" t="inlineStr">
         <is>
-          <t>Le contrôle</t>
+          <t>Le barème aux frontières</t>
         </is>
       </c>
       <c r="D191" s="3" t="inlineStr">
@@ -13287,24 +13287,24 @@
       </c>
       <c r="K191" s="3" t="inlineStr">
         <is>
-          <t>bareme, reflux_transactionnel, qualification_regenerative, regle_contre_discretion, affectation_des_instruments, essentiel_insolvable</t>
+          <t>seuil_d_activation, bareme, degeneratif, reflux_transactionnel, referentiel_de_change, essentiel_insolvable, affectation_des_instruments</t>
         </is>
       </c>
       <c r="L191" s="3" t="inlineStr">
         <is>
-          <t>L1.C18, L1.C21, L1.C22, L11.C05, L11.C06, L11.C09, L11.C11, L11.C13, L11.C17, L11.C19, L11.C20, L11.C21, L11.C23, L11.C24</t>
+          <t>L1.C26, L1.C27, L11.C04, L11.C05, L11.C06, L11.C09, L11.C13, L11.C16, L11.C17, L11.C19, L11.C21</t>
         </is>
       </c>
       <c r="M191" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-11-ingenierie-des-baremes/c25-le-controle.md</t>
+          <t>corpus/livre-11-ingenierie-des-baremes/c24-le-bareme-aux-frontieres.md</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" s="2" t="inlineStr">
         <is>
-          <t>L11.C26</t>
+          <t>L11.C25</t>
         </is>
       </c>
       <c r="B192" s="3" t="inlineStr">
@@ -13314,7 +13314,7 @@
       </c>
       <c r="C192" s="3" t="inlineStr">
         <is>
-          <t>La portée du Livre 11</t>
+          <t>Le contrôle</t>
         </is>
       </c>
       <c r="D192" s="3" t="inlineStr">
@@ -13339,35 +13339,35 @@
       </c>
       <c r="H192" s="3" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="I192" s="3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J192" s="3" t="n">
         <v>4</v>
       </c>
       <c r="K192" s="3" t="inlineStr">
         <is>
-          <t>bareme, reflux_collectif, reflux_transactionnel, demurrage, qualification_regenerative, valorisation_des_communs, referentiel_de_change, regle_contre_discretion, affectation_des_instruments, polycentricite</t>
+          <t>bareme, reflux_transactionnel, qualification_regenerative, regle_contre_discretion, affectation_des_instruments, essentiel_insolvable</t>
         </is>
       </c>
       <c r="L192" s="3" t="inlineStr">
         <is>
-          <t>L1.C15, L1.C18, L1.C21, L1.C22, L1.C26, L1.C27, L1.C28, L1.C29, L11.C01, L11.C03, L11.C06, L11.C07, L11.C09, L11.C11, L11.C12, L11.C13, L11.C16, L11.C17, L11.C19, L11.C21, L11.C22, L11.C23, L11.C24, L11.C25</t>
+          <t>L1.C18, L1.C21, L1.C22, L11.C05, L11.C06, L11.C09, L11.C11, L11.C13, L11.C17, L11.C19, L11.C20, L11.C21, L11.C23, L11.C24</t>
         </is>
       </c>
       <c r="M192" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-11-ingenierie-des-baremes/c26-la-portee-du-livre.md</t>
+          <t>corpus/livre-11-ingenierie-des-baremes/c25-le-controle.md</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" s="2" t="inlineStr">
         <is>
-          <t>L11.C27</t>
+          <t>L11.C26</t>
         </is>
       </c>
       <c r="B193" s="3" t="inlineStr">
@@ -13377,7 +13377,7 @@
       </c>
       <c r="C193" s="3" t="inlineStr">
         <is>
-          <t>L'assiette de la fonte est celle de la TVA</t>
+          <t>La portée du Livre 11</t>
         </is>
       </c>
       <c r="D193" s="3" t="inlineStr">
@@ -13402,35 +13402,35 @@
       </c>
       <c r="H193" s="3" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="I193" s="3" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J193" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K193" s="3" t="inlineStr">
         <is>
-          <t>reflux_transactionnel, demurrage, bareme, degeneratif, qualification_regenerative, externalisation, additionnalite</t>
+          <t>bareme, reflux_collectif, reflux_transactionnel, demurrage, qualification_regenerative, valorisation_des_communs, referentiel_de_change, regle_contre_discretion, affectation_des_instruments, polycentricite</t>
         </is>
       </c>
       <c r="L193" s="3" t="inlineStr">
         <is>
-          <t>L1.C21, L1.C27, L2.C16, L11.C02, L11.C05, L11.C09, L11.C21, L11.C24, L11.C25, L20.C02, L20.C19</t>
+          <t>L1.C15, L1.C18, L1.C21, L1.C22, L1.C26, L1.C27, L1.C28, L1.C29, L11.C01, L11.C03, L11.C06, L11.C07, L11.C09, L11.C11, L11.C12, L11.C13, L11.C16, L11.C17, L11.C19, L11.C21, L11.C22, L11.C23, L11.C24, L11.C25</t>
         </is>
       </c>
       <c r="M193" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-11-ingenierie-des-baremes/c27-l-assiette-de-la-fonte-est-celle-de-la-tva.md</t>
+          <t>corpus/livre-11-ingenierie-des-baremes/c26-la-portee-du-livre.md</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" s="2" t="inlineStr">
         <is>
-          <t>L11.C28</t>
+          <t>L11.C27</t>
         </is>
       </c>
       <c r="B194" s="3" t="inlineStr">
@@ -13440,7 +13440,7 @@
       </c>
       <c r="C194" s="3" t="inlineStr">
         <is>
-          <t>La fonte sur les acquisitions d'actifs, éprouvée</t>
+          <t>L'assiette de la fonte est celle de la TVA</t>
         </is>
       </c>
       <c r="D194" s="3" t="inlineStr">
@@ -13469,31 +13469,31 @@
         </is>
       </c>
       <c r="I194" s="3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J194" s="3" t="n">
         <v>3</v>
       </c>
       <c r="K194" s="3" t="inlineStr">
         <is>
-          <t>reflux_transactionnel, demurrage, bareme, referentiel_de_change, degeneratif, robustesse</t>
+          <t>reflux_transactionnel, demurrage, bareme, degeneratif, qualification_regenerative, externalisation, additionnalite</t>
         </is>
       </c>
       <c r="L194" s="3" t="inlineStr">
         <is>
-          <t>L1.C19, L1.C21, L2.C13, L2.C16, L6.C02, L11.C02, L11.C05, L11.C09, L11.C23, L11.C27, L20.C13</t>
+          <t>L1.C21, L1.C27, L2.C16, L11.C02, L11.C05, L11.C09, L11.C21, L11.C24, L11.C25, L20.C02, L20.C19</t>
         </is>
       </c>
       <c r="M194" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-11-ingenierie-des-baremes/c28-la-fonte-sur-les-acquisitions-d-actifs-eprouvee.md</t>
+          <t>corpus/livre-11-ingenierie-des-baremes/c27-l-assiette-de-la-fonte-est-celle-de-la-tva.md</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" s="2" t="inlineStr">
         <is>
-          <t>L11.C29</t>
+          <t>L11.C28</t>
         </is>
       </c>
       <c r="B195" s="3" t="inlineStr">
@@ -13503,7 +13503,7 @@
       </c>
       <c r="C195" s="3" t="inlineStr">
         <is>
-          <t>La structure des sanctions</t>
+          <t>La fonte sur les acquisitions d'actifs, éprouvée</t>
         </is>
       </c>
       <c r="D195" s="3" t="inlineStr">
@@ -13532,41 +13532,41 @@
         </is>
       </c>
       <c r="I195" s="3" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J195" s="3" t="n">
         <v>3</v>
       </c>
       <c r="K195" s="3" t="inlineStr">
         <is>
-          <t>bareme, seuil_d_activation, regle_contre_discretion, robustesse, qualification_regenerative, degeneratif</t>
+          <t>reflux_transactionnel, demurrage, bareme, referentiel_de_change, degeneratif, robustesse</t>
         </is>
       </c>
       <c r="L195" s="3" t="inlineStr">
         <is>
-          <t>L2.C08, L2.C14, L2.C21, L2.C22, L7.C19, L8.C31, L11.C18, L11.C19, L11.C20, L11.C23, L11.C25, L20.C17, L20.C18</t>
+          <t>L1.C19, L1.C21, L2.C13, L2.C16, L6.C02, L11.C02, L11.C05, L11.C09, L11.C23, L11.C27, L20.C13</t>
         </is>
       </c>
       <c r="M195" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-11-ingenierie-des-baremes/c29-la-structure-des-sanctions.md</t>
+          <t>corpus/livre-11-ingenierie-des-baremes/c28-la-fonte-sur-les-acquisitions-d-actifs-eprouvee.md</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" s="2" t="inlineStr">
         <is>
-          <t>L18.C01</t>
+          <t>L11.C29</t>
         </is>
       </c>
       <c r="B196" s="3" t="inlineStr">
         <is>
-          <t>L18</t>
+          <t>L11</t>
         </is>
       </c>
       <c r="C196" s="3" t="inlineStr">
         <is>
-          <t>Ce que ce livre doit établir, et le repli n'est pas l'annexe</t>
+          <t>La structure des sanctions</t>
         </is>
       </c>
       <c r="D196" s="3" t="inlineStr">
@@ -13586,7 +13586,7 @@
       </c>
       <c r="G196" s="3" t="inlineStr">
         <is>
-          <t>hybride</t>
+          <t>conception</t>
         </is>
       </c>
       <c r="H196" s="3" t="inlineStr">
@@ -13595,31 +13595,31 @@
         </is>
       </c>
       <c r="I196" s="3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J196" s="3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K196" s="3" t="inlineStr">
         <is>
-          <t>contrepartie_comptable, valorisation_des_communs, communs, essentiel_insolvable, qualification_regenerative, architecture_invisible</t>
+          <t>bareme, seuil_d_activation, regle_contre_discretion, robustesse, qualification_regenerative, degeneratif</t>
         </is>
       </c>
       <c r="L196" s="3" t="inlineStr">
         <is>
-          <t>L1.C09, L1.C29, L5.C02, L5.C09, L5.C10, L6.C08, L6.C09, L6.C13, L11.C13, L11.C16, L20.C02</t>
+          <t>L2.C08, L2.C14, L2.C21, L2.C22, L7.C19, L8.C31, L11.C18, L11.C19, L11.C20, L11.C23, L11.C25, L20.C17, L20.C18</t>
         </is>
       </c>
       <c r="M196" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-18-comptabilites-ecologiques-et-biophysiques/c01-ce-que-ce-livre-doit-etablir.md</t>
+          <t>corpus/livre-11-ingenierie-des-baremes/c29-la-structure-des-sanctions.md</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" s="2" t="inlineStr">
         <is>
-          <t>L18.C02</t>
+          <t>L18.C01</t>
         </is>
       </c>
       <c r="B197" s="3" t="inlineStr">
@@ -13629,7 +13629,7 @@
       </c>
       <c r="C197" s="3" t="inlineStr">
         <is>
-          <t>La métrologie existe, et ce qu'elle enregistre est l'ordre en place</t>
+          <t>Ce que ce livre doit établir, et le repli n'est pas l'annexe</t>
         </is>
       </c>
       <c r="D197" s="3" t="inlineStr">
@@ -13661,28 +13661,28 @@
         <v>4</v>
       </c>
       <c r="J197" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K197" s="3" t="inlineStr">
         <is>
-          <t>valorisation_des_communs, contrepartie_comptable, bareme, essentiel_insolvable, indicateur_de_progres, fausse_richesse</t>
+          <t>contrepartie_comptable, valorisation_des_communs, communs, essentiel_insolvable, qualification_regenerative, architecture_invisible</t>
         </is>
       </c>
       <c r="L197" s="3" t="inlineStr">
         <is>
-          <t>L1.C09, L1.C15, L1.C18, L6.C06, L11.C03, L11.C07, L11.C13, L11.C16, L18.C01</t>
+          <t>L1.C09, L1.C29, L5.C02, L5.C09, L5.C10, L6.C08, L6.C09, L6.C13, L11.C13, L11.C16, L20.C02</t>
         </is>
       </c>
       <c r="M197" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-18-comptabilites-ecologiques-et-biophysiques/c02-la-metrologie-existe-et-ce-qu-elle-enregistre.md</t>
+          <t>corpus/livre-18-comptabilites-ecologiques-et-biophysiques/c01-ce-que-ce-livre-doit-etablir.md</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" s="2" t="inlineStr">
         <is>
-          <t>L18.C03</t>
+          <t>L18.C02</t>
         </is>
       </c>
       <c r="B198" s="3" t="inlineStr">
@@ -13692,7 +13692,7 @@
       </c>
       <c r="C198" s="3" t="inlineStr">
         <is>
-          <t>L'échelle de repli, et qui l'a arrêtée</t>
+          <t>La métrologie existe, et ce qu'elle enregistre est l'ordre en place</t>
         </is>
       </c>
       <c r="D198" s="3" t="inlineStr">
@@ -13721,31 +13721,31 @@
         </is>
       </c>
       <c r="I198" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J198" s="3" t="n">
         <v>3</v>
       </c>
       <c r="K198" s="3" t="inlineStr">
         <is>
-          <t>contrepartie_comptable, architecture_invisible, valorisation_des_communs, essentiel_insolvable, regle_contre_discretion</t>
+          <t>valorisation_des_communs, contrepartie_comptable, bareme, essentiel_insolvable, indicateur_de_progres, fausse_richesse</t>
         </is>
       </c>
       <c r="L198" s="3" t="inlineStr">
         <is>
-          <t>L1.C09, L1.C15, L1.C29, L6.C09, L11.C29, L18.C01, L18.C02, L20.C02</t>
+          <t>L1.C09, L1.C15, L1.C18, L6.C06, L11.C03, L11.C07, L11.C13, L11.C16, L18.C01</t>
         </is>
       </c>
       <c r="M198" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-18-comptabilites-ecologiques-et-biophysiques/c03-l-echelle-de-repli-et-qui-l-a-arretee.md</t>
+          <t>corpus/livre-18-comptabilites-ecologiques-et-biophysiques/c02-la-metrologie-existe-et-ce-qu-elle-enregistre.md</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" s="2" t="inlineStr">
         <is>
-          <t>L18.C04</t>
+          <t>L18.C03</t>
         </is>
       </c>
       <c r="B199" s="3" t="inlineStr">
@@ -13755,7 +13755,7 @@
       </c>
       <c r="C199" s="3" t="inlineStr">
         <is>
-          <t>Les grandeurs physiques, et l'endroit où elles frappent le dispositif</t>
+          <t>L'échelle de repli, et qui l'a arrêtée</t>
         </is>
       </c>
       <c r="D199" s="3" t="inlineStr">
@@ -13784,31 +13784,31 @@
         </is>
       </c>
       <c r="I199" s="3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J199" s="3" t="n">
         <v>3</v>
       </c>
       <c r="K199" s="3" t="inlineStr">
         <is>
-          <t>decouplage, effet_rebond, externalisation, limites_planetaires, sobriete, fausse_richesse</t>
+          <t>contrepartie_comptable, architecture_invisible, valorisation_des_communs, essentiel_insolvable, regle_contre_discretion</t>
         </is>
       </c>
       <c r="L199" s="3" t="inlineStr">
         <is>
-          <t>L1.C02, L1.C03, L1.C04, L5.C08, L6.C08, L11.C10, L11.C24, L18.C01, L18.C02</t>
+          <t>L1.C09, L1.C15, L1.C29, L6.C09, L11.C29, L18.C01, L18.C02, L20.C02</t>
         </is>
       </c>
       <c r="M199" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-18-comptabilites-ecologiques-et-biophysiques/c04-les-grandeurs-physiques-et-ou-elles-frappent.md</t>
+          <t>corpus/livre-18-comptabilites-ecologiques-et-biophysiques/c03-l-echelle-de-repli-et-qui-l-a-arretee.md</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" s="2" t="inlineStr">
         <is>
-          <t>L18.C05</t>
+          <t>L18.C04</t>
         </is>
       </c>
       <c r="B200" s="3" t="inlineStr">
@@ -13818,7 +13818,7 @@
       </c>
       <c r="C200" s="3" t="inlineStr">
         <is>
-          <t>Ce que la norme exclut, et ce n'est pas le commun</t>
+          <t>Les grandeurs physiques, et l'endroit où elles frappent le dispositif</t>
         </is>
       </c>
       <c r="D200" s="3" t="inlineStr">
@@ -13847,31 +13847,31 @@
         </is>
       </c>
       <c r="I200" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J200" s="3" t="n">
         <v>3</v>
       </c>
       <c r="K200" s="3" t="inlineStr">
         <is>
-          <t>communs, contrepartie_comptable, valorisation_des_communs, architecture_invisible, monnaie_comme_registre, creation_monetaire</t>
+          <t>decouplage, effet_rebond, externalisation, limites_planetaires, sobriete, fausse_richesse</t>
         </is>
       </c>
       <c r="L200" s="3" t="inlineStr">
         <is>
-          <t>L1.C09, L1.C20, L1.C29, L6.C06, L6.C08, L11.C13, L11.C16, L18.C01, L18.C02, L18.C03, L20.C02</t>
+          <t>L1.C02, L1.C03, L1.C04, L5.C08, L6.C08, L11.C10, L11.C24, L18.C01, L18.C02</t>
         </is>
       </c>
       <c r="M200" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-18-comptabilites-ecologiques-et-biophysiques/c05-ce-que-la-norme-exclut-et-ce-n-est-pas-le-commun.md</t>
+          <t>corpus/livre-18-comptabilites-ecologiques-et-biophysiques/c04-les-grandeurs-physiques-et-ou-elles-frappent.md</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" s="2" t="inlineStr">
         <is>
-          <t>L18.C06</t>
+          <t>L18.C05</t>
         </is>
       </c>
       <c r="B201" s="3" t="inlineStr">
@@ -13881,7 +13881,7 @@
       </c>
       <c r="C201" s="3" t="inlineStr">
         <is>
-          <t>Portée de la tranche, et une neuvième condition proposée</t>
+          <t>Ce que la norme exclut, et ce n'est pas le commun</t>
         </is>
       </c>
       <c r="D201" s="3" t="inlineStr">
@@ -13901,7 +13901,7 @@
       </c>
       <c r="G201" s="3" t="inlineStr">
         <is>
-          <t>conception</t>
+          <t>hybride</t>
         </is>
       </c>
       <c r="H201" s="3" t="inlineStr">
@@ -13917,24 +13917,24 @@
       </c>
       <c r="K201" s="3" t="inlineStr">
         <is>
-          <t>contrepartie_comptable, communs, valorisation_des_communs, architecture_invisible, essentiel_insolvable</t>
+          <t>communs, contrepartie_comptable, valorisation_des_communs, architecture_invisible, monnaie_comme_registre, creation_monetaire</t>
         </is>
       </c>
       <c r="L201" s="3" t="inlineStr">
         <is>
-          <t>L1.C09, L1.C18, L1.C20, L1.C29, L5.C02, L5.C08, L6.C06, L6.C08, L11.C13, L11.C16, L18.C01, L18.C02, L18.C03, L18.C04, L18.C05, L20.C02</t>
+          <t>L1.C09, L1.C20, L1.C29, L6.C06, L6.C08, L11.C13, L11.C16, L18.C01, L18.C02, L18.C03, L20.C02</t>
         </is>
       </c>
       <c r="M201" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-18-comptabilites-ecologiques-et-biophysiques/c06-portee-de-la-tranche-et-une-neuvieme-condition.md</t>
+          <t>corpus/livre-18-comptabilites-ecologiques-et-biophysiques/c05-ce-que-la-norme-exclut-et-ce-n-est-pas-le-commun.md</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" s="2" t="inlineStr">
         <is>
-          <t>L18.C07</t>
+          <t>L18.C06</t>
         </is>
       </c>
       <c r="B202" s="3" t="inlineStr">
@@ -13944,7 +13944,7 @@
       </c>
       <c r="C202" s="3" t="inlineStr">
         <is>
-          <t>CARE/TDL répare deux objections, et en crée une plus grave</t>
+          <t>Portée de la tranche, et une neuvième condition proposée</t>
         </is>
       </c>
       <c r="D202" s="3" t="inlineStr">
@@ -13964,7 +13964,7 @@
       </c>
       <c r="G202" s="3" t="inlineStr">
         <is>
-          <t>hybride</t>
+          <t>conception</t>
         </is>
       </c>
       <c r="H202" s="3" t="inlineStr">
@@ -13973,31 +13973,31 @@
         </is>
       </c>
       <c r="I202" s="3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J202" s="3" t="n">
         <v>3</v>
       </c>
       <c r="K202" s="3" t="inlineStr">
         <is>
-          <t>contrepartie_comptable, bareme, valorisation_des_communs, communs, architecture_invisible, fausse_richesse</t>
+          <t>contrepartie_comptable, communs, valorisation_des_communs, architecture_invisible, essentiel_insolvable</t>
         </is>
       </c>
       <c r="L202" s="3" t="inlineStr">
         <is>
-          <t>L1.C09, L1.C18, L1.C20, L6.C06, L11.C03, L11.C13, L11.C16, L18.C01, L18.C02, L18.C05, L18.C06</t>
+          <t>L1.C09, L1.C18, L1.C20, L1.C29, L5.C02, L5.C08, L6.C06, L6.C08, L11.C13, L11.C16, L18.C01, L18.C02, L18.C03, L18.C04, L18.C05, L20.C02</t>
         </is>
       </c>
       <c r="M202" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-18-comptabilites-ecologiques-et-biophysiques/c07-care-tdl-repare-une-objection-et-en-cree-une-autre.md</t>
+          <t>corpus/livre-18-comptabilites-ecologiques-et-biophysiques/c06-portee-de-la-tranche-et-une-neuvieme-condition.md</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" s="2" t="inlineStr">
         <is>
-          <t>L18.C08</t>
+          <t>L18.C07</t>
         </is>
       </c>
       <c r="B203" s="3" t="inlineStr">
@@ -14007,7 +14007,7 @@
       </c>
       <c r="C203" s="3" t="inlineStr">
         <is>
-          <t>Le modèle au périmètre du dispositif, et F9 révisée</t>
+          <t>CARE/TDL répare deux objections, et en crée une plus grave</t>
         </is>
       </c>
       <c r="D203" s="3" t="inlineStr">
@@ -14027,7 +14027,7 @@
       </c>
       <c r="G203" s="3" t="inlineStr">
         <is>
-          <t>conception</t>
+          <t>hybride</t>
         </is>
       </c>
       <c r="H203" s="3" t="inlineStr">
@@ -14043,24 +14043,24 @@
       </c>
       <c r="K203" s="3" t="inlineStr">
         <is>
-          <t>contrepartie_comptable, communs, valorisation_des_communs, polycentricite, essentiel_insolvable, indicateur_de_progres</t>
+          <t>contrepartie_comptable, bareme, valorisation_des_communs, communs, architecture_invisible, fausse_richesse</t>
         </is>
       </c>
       <c r="L203" s="3" t="inlineStr">
         <is>
-          <t>L1.C09, L1.C18, L6.C06, L7.C05, L11.C13, L11.C16, L11.C25, L18.C01, L18.C02, L18.C05, L18.C06, L18.C07</t>
+          <t>L1.C09, L1.C18, L1.C20, L6.C06, L11.C03, L11.C13, L11.C16, L18.C01, L18.C02, L18.C05, L18.C06</t>
         </is>
       </c>
       <c r="M203" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-18-comptabilites-ecologiques-et-biophysiques/c08-le-modele-au-perimetre-du-dispositif-et-f9-revisee.md</t>
+          <t>corpus/livre-18-comptabilites-ecologiques-et-biophysiques/c07-care-tdl-repare-une-objection-et-en-cree-une-autre.md</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" s="2" t="inlineStr">
         <is>
-          <t>L18.C09</t>
+          <t>L18.C08</t>
         </is>
       </c>
       <c r="B204" s="3" t="inlineStr">
@@ -14070,7 +14070,7 @@
       </c>
       <c r="C204" s="3" t="inlineStr">
         <is>
-          <t>L'ordre de grandeur, et le concurrent qu'il désigne</t>
+          <t>Le modèle au périmètre du dispositif, et F9 révisée</t>
         </is>
       </c>
       <c r="D204" s="3" t="inlineStr">
@@ -14090,7 +14090,7 @@
       </c>
       <c r="G204" s="3" t="inlineStr">
         <is>
-          <t>hybride</t>
+          <t>conception</t>
         </is>
       </c>
       <c r="H204" s="3" t="inlineStr">
@@ -14099,41 +14099,41 @@
         </is>
       </c>
       <c r="I204" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J204" s="3" t="n">
         <v>3</v>
       </c>
       <c r="K204" s="3" t="inlineStr">
         <is>
-          <t>essentiel_insolvable, valorisation_des_communs, externalisation, additionnalite, fausse_richesse, degeneratif</t>
+          <t>contrepartie_comptable, communs, valorisation_des_communs, polycentricite, essentiel_insolvable, indicateur_de_progres</t>
         </is>
       </c>
       <c r="L204" s="3" t="inlineStr">
         <is>
-          <t>L1.C15, L1.C18, L5.C07, L10.C04, L10.C06, L11.C03, L11.C13, L18.C01, L18.C04, L18.C06</t>
+          <t>L1.C09, L1.C18, L6.C06, L7.C05, L11.C13, L11.C16, L11.C25, L18.C01, L18.C02, L18.C05, L18.C06, L18.C07</t>
         </is>
       </c>
       <c r="M204" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-18-comptabilites-ecologiques-et-biophysiques/c09-l-ordre-de-grandeur-et-le-concurrent-qu-il-designe.md</t>
+          <t>corpus/livre-18-comptabilites-ecologiques-et-biophysiques/c08-le-modele-au-perimetre-du-dispositif-et-f9-revisee.md</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" s="2" t="inlineStr">
         <is>
-          <t>L20.C01</t>
+          <t>L18.C09</t>
         </is>
       </c>
       <c r="B205" s="3" t="inlineStr">
         <is>
-          <t>L20</t>
+          <t>L18</t>
         </is>
       </c>
       <c r="C205" s="3" t="inlineStr">
         <is>
-          <t>Ce que ce livre doit établir</t>
+          <t>L'ordre de grandeur, et le concurrent qu'il désigne</t>
         </is>
       </c>
       <c r="D205" s="3" t="inlineStr">
@@ -14153,12 +14153,12 @@
       </c>
       <c r="G205" s="3" t="inlineStr">
         <is>
-          <t>conception</t>
+          <t>hybride</t>
         </is>
       </c>
       <c r="H205" s="3" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="I205" s="3" t="n">
@@ -14169,24 +14169,24 @@
       </c>
       <c r="K205" s="3" t="inlineStr">
         <is>
-          <t>fenetre_de_reforme, referentiel_de_change, communs, limites_planetaires, creation_monetaire</t>
+          <t>essentiel_insolvable, valorisation_des_communs, externalisation, additionnalite, fausse_richesse, degeneratif</t>
         </is>
       </c>
       <c r="L205" s="3" t="inlineStr">
         <is>
-          <t>L1.C18, L1.C25, L1.C27, L7.C01, L7.C03, L7.C13, L7.C17, L7.C21, L11.C24</t>
+          <t>L1.C15, L1.C18, L5.C07, L10.C04, L10.C06, L11.C03, L11.C13, L18.C01, L18.C04, L18.C06</t>
         </is>
       </c>
       <c r="M205" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-20-droit-international-monetaire-et-commercial/c01-ce-que-ce-livre-doit-etablir.md</t>
+          <t>corpus/livre-18-comptabilites-ecologiques-et-biophysiques/c09-l-ordre-de-grandeur-et-le-concurrent-qu-il-designe.md</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" s="2" t="inlineStr">
         <is>
-          <t>L20.C02</t>
+          <t>L20.C01</t>
         </is>
       </c>
       <c r="B206" s="3" t="inlineStr">
@@ -14196,7 +14196,7 @@
       </c>
       <c r="C206" s="3" t="inlineStr">
         <is>
-          <t>L'interdiction du financement monétaire</t>
+          <t>Ce que ce livre doit établir</t>
         </is>
       </c>
       <c r="D206" s="3" t="inlineStr">
@@ -14221,7 +14221,7 @@
       </c>
       <c r="H206" s="3" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="I206" s="3" t="n">
@@ -14232,24 +14232,24 @@
       </c>
       <c r="K206" s="3" t="inlineStr">
         <is>
-          <t>creation_monetaire, contrepartie_comptable, reflux_collectif, fenetre_de_reforme</t>
+          <t>fenetre_de_reforme, referentiel_de_change, communs, limites_planetaires, creation_monetaire</t>
         </is>
       </c>
       <c r="L206" s="3" t="inlineStr">
         <is>
-          <t>L1.C05, L1.C18, L1.C20, L1.C22, L7.C11, L7.C13, L11.C10, L20.C01</t>
+          <t>L1.C18, L1.C25, L1.C27, L7.C01, L7.C03, L7.C13, L7.C17, L7.C21, L11.C24</t>
         </is>
       </c>
       <c r="M206" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-20-droit-international-monetaire-et-commercial/c02-l-interdiction-du-financement-monetaire.md</t>
+          <t>corpus/livre-20-droit-international-monetaire-et-commercial/c01-ce-que-ce-livre-doit-etablir.md</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" s="2" t="inlineStr">
         <is>
-          <t>L20.C03</t>
+          <t>L20.C02</t>
         </is>
       </c>
       <c r="B207" s="3" t="inlineStr">
@@ -14259,7 +14259,7 @@
       </c>
       <c r="C207" s="3" t="inlineStr">
         <is>
-          <t>L'objectif principal et ce qu'il exclut</t>
+          <t>L'interdiction du financement monétaire</t>
         </is>
       </c>
       <c r="D207" s="3" t="inlineStr">
@@ -14295,24 +14295,24 @@
       </c>
       <c r="K207" s="3" t="inlineStr">
         <is>
-          <t>regle_contre_discretion, limites_planetaires, creation_monetaire, plafond_ecologique</t>
+          <t>creation_monetaire, contrepartie_comptable, reflux_collectif, fenetre_de_reforme</t>
         </is>
       </c>
       <c r="L207" s="3" t="inlineStr">
         <is>
-          <t>L1.C01, L1.C18, L1.C20, L7.C03, L8.C12, L8.C34, L11.C16, L20.C01, L20.C02</t>
+          <t>L1.C05, L1.C18, L1.C20, L1.C22, L7.C11, L7.C13, L11.C10, L20.C01</t>
         </is>
       </c>
       <c r="M207" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-20-droit-international-monetaire-et-commercial/c03-l-objectif-principal-et-ce-qu-il-exclut.md</t>
+          <t>corpus/livre-20-droit-international-monetaire-et-commercial/c02-l-interdiction-du-financement-monetaire.md</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" s="2" t="inlineStr">
         <is>
-          <t>L20.C04</t>
+          <t>L20.C03</t>
         </is>
       </c>
       <c r="B208" s="3" t="inlineStr">
@@ -14322,7 +14322,7 @@
       </c>
       <c r="C208" s="3" t="inlineStr">
         <is>
-          <t>L'indépendance, et à l'égard de qui</t>
+          <t>L'objectif principal et ce qu'il exclut</t>
         </is>
       </c>
       <c r="D208" s="3" t="inlineStr">
@@ -14347,7 +14347,7 @@
       </c>
       <c r="H208" s="3" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="I208" s="3" t="n">
@@ -14358,24 +14358,24 @@
       </c>
       <c r="K208" s="3" t="inlineStr">
         <is>
-          <t>regle_contre_discretion, creation_monetaire, fenetre_de_reforme</t>
+          <t>regle_contre_discretion, limites_planetaires, creation_monetaire, plafond_ecologique</t>
         </is>
       </c>
       <c r="L208" s="3" t="inlineStr">
         <is>
-          <t>L1.C18, L7.C04, L7.C07, L7.C10, L8.C31, L11.C17, L20.C01, L20.C03, L20.C11</t>
+          <t>L1.C01, L1.C18, L1.C20, L7.C03, L8.C12, L8.C34, L11.C16, L20.C01, L20.C02</t>
         </is>
       </c>
       <c r="M208" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-20-droit-international-monetaire-et-commercial/c04-l-independance-et-a-l-egard-de-qui.md</t>
+          <t>corpus/livre-20-droit-international-monetaire-et-commercial/c03-l-objectif-principal-et-ce-qu-il-exclut.md</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" s="2" t="inlineStr">
         <is>
-          <t>L20.C05</t>
+          <t>L20.C04</t>
         </is>
       </c>
       <c r="B209" s="3" t="inlineStr">
@@ -14385,7 +14385,7 @@
       </c>
       <c r="C209" s="3" t="inlineStr">
         <is>
-          <t>Le monopole d'émission et le cours légal</t>
+          <t>L'indépendance, et à l'égard de qui</t>
         </is>
       </c>
       <c r="D209" s="3" t="inlineStr">
@@ -14421,24 +14421,24 @@
       </c>
       <c r="K209" s="3" t="inlineStr">
         <is>
-          <t>monnaie_comme_registre, creation_monetaire, referentiel_de_change, hierarchie_monetaire</t>
+          <t>regle_contre_discretion, creation_monetaire, fenetre_de_reforme</t>
         </is>
       </c>
       <c r="L209" s="3" t="inlineStr">
         <is>
-          <t>L1.C05, L1.C07, L1.C26, L7.C15, L11.C15, L20.C01, L20.C02, L20.C03</t>
+          <t>L1.C18, L7.C04, L7.C07, L7.C10, L8.C31, L11.C17, L20.C01, L20.C03, L20.C11</t>
         </is>
       </c>
       <c r="M209" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-20-droit-international-monetaire-et-commercial/c05-le-monopole-d-emission-et-le-cours-legal.md</t>
+          <t>corpus/livre-20-droit-international-monetaire-et-commercial/c04-l-independance-et-a-l-egard-de-qui.md</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" s="2" t="inlineStr">
         <is>
-          <t>L20.C06</t>
+          <t>L20.C05</t>
         </is>
       </c>
       <c r="B210" s="3" t="inlineStr">
@@ -14448,7 +14448,7 @@
       </c>
       <c r="C210" s="3" t="inlineStr">
         <is>
-          <t>Les voies de révision et leur coût</t>
+          <t>Le monopole d'émission et le cours légal</t>
         </is>
       </c>
       <c r="D210" s="3" t="inlineStr">
@@ -14477,31 +14477,31 @@
         </is>
       </c>
       <c r="I210" s="3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J210" s="3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K210" s="3" t="inlineStr">
         <is>
-          <t>fenetre_de_reforme, regle_contre_discretion, creation_monetaire</t>
+          <t>monnaie_comme_registre, creation_monetaire, referentiel_de_change, hierarchie_monetaire</t>
         </is>
       </c>
       <c r="L210" s="3" t="inlineStr">
         <is>
-          <t>L1.C18, L7.C12, L7.C20, L7.C21, L11.C15, L20.C01, L20.C02, L20.C03, L20.C07, L20.C09, L20.C18</t>
+          <t>L1.C05, L1.C07, L1.C26, L7.C15, L11.C15, L20.C01, L20.C02, L20.C03</t>
         </is>
       </c>
       <c r="M210" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-20-droit-international-monetaire-et-commercial/c06-les-voies-de-revision-et-leur-cout.md</t>
+          <t>corpus/livre-20-droit-international-monetaire-et-commercial/c05-le-monopole-d-emission-et-le-cours-legal.md</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" s="2" t="inlineStr">
         <is>
-          <t>L20.C07</t>
+          <t>L20.C06</t>
         </is>
       </c>
       <c r="B211" s="3" t="inlineStr">
@@ -14511,7 +14511,7 @@
       </c>
       <c r="C211" s="3" t="inlineStr">
         <is>
-          <t>L'accord monétaire international</t>
+          <t>Les voies de révision et leur coût</t>
         </is>
       </c>
       <c r="D211" s="3" t="inlineStr">
@@ -14540,31 +14540,31 @@
         </is>
       </c>
       <c r="I211" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J211" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K211" s="3" t="inlineStr">
         <is>
-          <t>referentiel_de_change, fenetre_de_reforme, etalon_de_change_or, hierarchie_monetaire</t>
+          <t>fenetre_de_reforme, regle_contre_discretion, creation_monetaire</t>
         </is>
       </c>
       <c r="L211" s="3" t="inlineStr">
         <is>
-          <t>L1.C18, L1.C26, L7.C02, L7.C05, L7.C12, L7.C13, L11.C15, L20.C01, L20.C03, L20.C06, L20.C10</t>
+          <t>L1.C18, L7.C12, L7.C20, L7.C21, L11.C15, L20.C01, L20.C02, L20.C03, L20.C07, L20.C09, L20.C18</t>
         </is>
       </c>
       <c r="M211" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-20-droit-international-monetaire-et-commercial/c07-l-accord-monetaire-international.md</t>
+          <t>corpus/livre-20-droit-international-monetaire-et-commercial/c06-les-voies-de-revision-et-leur-cout.md</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" s="2" t="inlineStr">
         <is>
-          <t>L20.C08</t>
+          <t>L20.C07</t>
         </is>
       </c>
       <c r="B212" s="3" t="inlineStr">
@@ -14574,7 +14574,7 @@
       </c>
       <c r="C212" s="3" t="inlineStr">
         <is>
-          <t>La parité inscrite dans le traité</t>
+          <t>L'accord monétaire international</t>
         </is>
       </c>
       <c r="D212" s="3" t="inlineStr">
@@ -14599,35 +14599,35 @@
       </c>
       <c r="H212" s="3" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="I212" s="3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J212" s="3" t="n">
         <v>3</v>
       </c>
       <c r="K212" s="3" t="inlineStr">
         <is>
-          <t>referentiel_de_change, etalon_de_change_or, hierarchie_monetaire, bareme, devise_cle</t>
+          <t>referentiel_de_change, fenetre_de_reforme, etalon_de_change_or, hierarchie_monetaire</t>
         </is>
       </c>
       <c r="L212" s="3" t="inlineStr">
         <is>
-          <t>L1.C25, L1.C26, L1.C28, L7.C02, L7.C20, L11.C15, L11.C17, L20.C01, L20.C09, L20.C13</t>
+          <t>L1.C18, L1.C26, L7.C02, L7.C05, L7.C12, L7.C13, L11.C15, L20.C01, L20.C03, L20.C06, L20.C10</t>
         </is>
       </c>
       <c r="M212" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-20-droit-international-monetaire-et-commercial/c08-la-parite-inscrite-dans-le-traite.md</t>
+          <t>corpus/livre-20-droit-international-monetaire-et-commercial/c07-l-accord-monetaire-international.md</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" s="2" t="inlineStr">
         <is>
-          <t>L20.C09</t>
+          <t>L20.C08</t>
         </is>
       </c>
       <c r="B213" s="3" t="inlineStr">
@@ -14637,7 +14637,7 @@
       </c>
       <c r="C213" s="3" t="inlineStr">
         <is>
-          <t>L'amendement des statuts du Fonds</t>
+          <t>La parité inscrite dans le traité</t>
         </is>
       </c>
       <c r="D213" s="3" t="inlineStr">
@@ -14662,35 +14662,35 @@
       </c>
       <c r="H213" s="3" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="I213" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J213" s="3" t="n">
         <v>3</v>
       </c>
       <c r="K213" s="3" t="inlineStr">
         <is>
-          <t>fenetre_de_reforme, referentiel_de_change, bareme, regle_contre_discretion</t>
+          <t>referentiel_de_change, etalon_de_change_or, hierarchie_monetaire, bareme, devise_cle</t>
         </is>
       </c>
       <c r="L213" s="3" t="inlineStr">
         <is>
-          <t>L7.C06, L7.C09, L7.C16, L7.C20, L11.C15, L11.C20, L20.C01, L20.C06, L20.C08, L20.C10, L20.C13</t>
+          <t>L1.C25, L1.C26, L1.C28, L7.C02, L7.C20, L11.C15, L11.C17, L20.C01, L20.C09, L20.C13</t>
         </is>
       </c>
       <c r="M213" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-20-droit-international-monetaire-et-commercial/c09-l-amendement-des-statuts-du-fonds.md</t>
+          <t>corpus/livre-20-droit-international-monetaire-et-commercial/c08-la-parite-inscrite-dans-le-traite.md</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" s="2" t="inlineStr">
         <is>
-          <t>L20.C10</t>
+          <t>L20.C09</t>
         </is>
       </c>
       <c r="B214" s="3" t="inlineStr">
@@ -14700,7 +14700,7 @@
       </c>
       <c r="C214" s="3" t="inlineStr">
         <is>
-          <t>Le vote pondéré et les voix de base</t>
+          <t>L'amendement des statuts du Fonds</t>
         </is>
       </c>
       <c r="D214" s="3" t="inlineStr">
@@ -14736,24 +14736,24 @@
       </c>
       <c r="K214" s="3" t="inlineStr">
         <is>
-          <t>bareme, devise_cle, hierarchie_monetaire, referentiel_de_change</t>
+          <t>fenetre_de_reforme, referentiel_de_change, bareme, regle_contre_discretion</t>
         </is>
       </c>
       <c r="L214" s="3" t="inlineStr">
         <is>
-          <t>L1.C25, L7.C02, L7.C05, L7.C06, L7.C09, L7.C10, L11.C16, L20.C01, L20.C07, L20.C09, L20.C12</t>
+          <t>L7.C06, L7.C09, L7.C16, L7.C20, L11.C15, L11.C20, L20.C01, L20.C06, L20.C08, L20.C10, L20.C13</t>
         </is>
       </c>
       <c r="M214" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-20-droit-international-monetaire-et-commercial/c10-le-vote-pondere-et-les-voix-de-base.md</t>
+          <t>corpus/livre-20-droit-international-monetaire-et-commercial/c09-l-amendement-des-statuts-du-fonds.md</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" s="2" t="inlineStr">
         <is>
-          <t>L20.C11</t>
+          <t>L20.C10</t>
         </is>
       </c>
       <c r="B215" s="3" t="inlineStr">
@@ -14763,7 +14763,7 @@
       </c>
       <c r="C215" s="3" t="inlineStr">
         <is>
-          <t>La personnalité juridique et les immunités</t>
+          <t>Le vote pondéré et les voix de base</t>
         </is>
       </c>
       <c r="D215" s="3" t="inlineStr">
@@ -14792,31 +14792,31 @@
         </is>
       </c>
       <c r="I215" s="3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J215" s="3" t="n">
         <v>3</v>
       </c>
       <c r="K215" s="3" t="inlineStr">
         <is>
-          <t>communs, creation_monetaire, fenetre_de_reforme, robustesse</t>
+          <t>bareme, devise_cle, hierarchie_monetaire, referentiel_de_change</t>
         </is>
       </c>
       <c r="L215" s="3" t="inlineStr">
         <is>
-          <t>L7.C01, L7.C03, L7.C07, L7.C10, L7.C13, L11.C25, L20.C01, L20.C04, L20.C12, L20.C14</t>
+          <t>L1.C25, L7.C02, L7.C05, L7.C06, L7.C09, L7.C10, L11.C16, L20.C01, L20.C07, L20.C09, L20.C12</t>
         </is>
       </c>
       <c r="M215" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-20-droit-international-monetaire-et-commercial/c11-la-personnalite-juridique-et-les-immunites.md</t>
+          <t>corpus/livre-20-droit-international-monetaire-et-commercial/c10-le-vote-pondere-et-les-voix-de-base.md</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" s="2" t="inlineStr">
         <is>
-          <t>L20.C12</t>
+          <t>L20.C11</t>
         </is>
       </c>
       <c r="B216" s="3" t="inlineStr">
@@ -14826,7 +14826,7 @@
       </c>
       <c r="C216" s="3" t="inlineStr">
         <is>
-          <t>Les pouvoirs non délégables</t>
+          <t>La personnalité juridique et les immunités</t>
         </is>
       </c>
       <c r="D216" s="3" t="inlineStr">
@@ -14851,35 +14851,35 @@
       </c>
       <c r="H216" s="3" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="I216" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J216" s="3" t="n">
         <v>3</v>
       </c>
       <c r="K216" s="3" t="inlineStr">
         <is>
-          <t>bareme, valorisation_des_communs, polycentricite, robustesse</t>
+          <t>communs, creation_monetaire, fenetre_de_reforme, robustesse</t>
         </is>
       </c>
       <c r="L216" s="3" t="inlineStr">
         <is>
-          <t>L7.C05, L7.C06, L7.C07, L7.C11, L7.C14, L11.C16, L11.C20, L20.C01, L20.C09, L20.C10, L20.C14</t>
+          <t>L7.C01, L7.C03, L7.C07, L7.C10, L7.C13, L11.C25, L20.C01, L20.C04, L20.C12, L20.C14</t>
         </is>
       </c>
       <c r="M216" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-20-droit-international-monetaire-et-commercial/c12-les-pouvoirs-non-delegables.md</t>
+          <t>corpus/livre-20-droit-international-monetaire-et-commercial/c11-la-personnalite-juridique-et-les-immunites.md</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" s="2" t="inlineStr">
         <is>
-          <t>L20.C13</t>
+          <t>L20.C12</t>
         </is>
       </c>
       <c r="B217" s="3" t="inlineStr">
@@ -14889,7 +14889,7 @@
       </c>
       <c r="C217" s="3" t="inlineStr">
         <is>
-          <t>L'entrée en vigueur, l'adhésion et le retrait</t>
+          <t>Les pouvoirs non délégables</t>
         </is>
       </c>
       <c r="D217" s="3" t="inlineStr">
@@ -14918,31 +14918,31 @@
         </is>
       </c>
       <c r="I217" s="3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J217" s="3" t="n">
         <v>3</v>
       </c>
       <c r="K217" s="3" t="inlineStr">
         <is>
-          <t>seuil_d_activation, reflux_collectif, fenetre_de_reforme, additionnalite</t>
+          <t>bareme, valorisation_des_communs, polycentricite, robustesse</t>
         </is>
       </c>
       <c r="L217" s="3" t="inlineStr">
         <is>
-          <t>L7.C11, L7.C12, L7.C16, L7.C17, L7.C19, L11.C18, L20.C01, L20.C06, L20.C09, L20.C12</t>
+          <t>L7.C05, L7.C06, L7.C07, L7.C11, L7.C14, L11.C16, L11.C20, L20.C01, L20.C09, L20.C10, L20.C14</t>
         </is>
       </c>
       <c r="M217" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-20-droit-international-monetaire-et-commercial/c13-l-entree-en-vigueur-l-adhesion-et-le-retrait.md</t>
+          <t>corpus/livre-20-droit-international-monetaire-et-commercial/c12-les-pouvoirs-non-delegables.md</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" s="2" t="inlineStr">
         <is>
-          <t>L20.C14</t>
+          <t>L20.C13</t>
         </is>
       </c>
       <c r="B218" s="3" t="inlineStr">
@@ -14952,7 +14952,7 @@
       </c>
       <c r="C218" s="3" t="inlineStr">
         <is>
-          <t>Qui interprète le traité</t>
+          <t>L'entrée en vigueur, l'adhésion et le retrait</t>
         </is>
       </c>
       <c r="D218" s="3" t="inlineStr">
@@ -14981,31 +14981,31 @@
         </is>
       </c>
       <c r="I218" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J218" s="3" t="n">
         <v>3</v>
       </c>
       <c r="K218" s="3" t="inlineStr">
         <is>
-          <t>robustesse, regle_contre_discretion, communs</t>
+          <t>seuil_d_activation, reflux_collectif, fenetre_de_reforme, additionnalite</t>
         </is>
       </c>
       <c r="L218" s="3" t="inlineStr">
         <is>
-          <t>L7.C07, L7.C13, L7.C14, L7.C19, L11.C19, L11.C25, L20.C01, L20.C03, L20.C11, L20.C12, L20.C21</t>
+          <t>L7.C11, L7.C12, L7.C16, L7.C17, L7.C19, L11.C18, L20.C01, L20.C06, L20.C09, L20.C12</t>
         </is>
       </c>
       <c r="M218" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-20-droit-international-monetaire-et-commercial/c14-qui-interprete-le-traite.md</t>
+          <t>corpus/livre-20-droit-international-monetaire-et-commercial/c13-l-entree-en-vigueur-l-adhesion-et-le-retrait.md</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" s="2" t="inlineStr">
         <is>
-          <t>L20.C15</t>
+          <t>L20.C14</t>
         </is>
       </c>
       <c r="B219" s="3" t="inlineStr">
@@ -15015,7 +15015,7 @@
       </c>
       <c r="C219" s="3" t="inlineStr">
         <is>
-          <t>Le devoir international des agents</t>
+          <t>Qui interprète le traité</t>
         </is>
       </c>
       <c r="D219" s="3" t="inlineStr">
@@ -15040,35 +15040,35 @@
       </c>
       <c r="H219" s="3" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="I219" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J219" s="3" t="n">
         <v>3</v>
       </c>
       <c r="K219" s="3" t="inlineStr">
         <is>
-          <t>robustesse, regle_contre_discretion, indicateur_de_progres</t>
+          <t>robustesse, regle_contre_discretion, communs</t>
         </is>
       </c>
       <c r="L219" s="3" t="inlineStr">
         <is>
-          <t>L7.C04, L7.C07, L7.C10, L11.C21, L11.C25, L20.C01, L20.C04, L20.C11, L20.C14</t>
+          <t>L7.C07, L7.C13, L7.C14, L7.C19, L11.C19, L11.C25, L20.C01, L20.C03, L20.C11, L20.C12, L20.C21</t>
         </is>
       </c>
       <c r="M219" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-20-droit-international-monetaire-et-commercial/c15-le-devoir-international-des-agents.md</t>
+          <t>corpus/livre-20-droit-international-monetaire-et-commercial/c14-qui-interprete-le-traite.md</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" s="2" t="inlineStr">
         <is>
-          <t>L20.C16</t>
+          <t>L20.C15</t>
         </is>
       </c>
       <c r="B220" s="3" t="inlineStr">
@@ -15078,7 +15078,7 @@
       </c>
       <c r="C220" s="3" t="inlineStr">
         <is>
-          <t>Le patrimoine commun de l'humanité</t>
+          <t>Le devoir international des agents</t>
         </is>
       </c>
       <c r="D220" s="3" t="inlineStr">
@@ -15103,35 +15103,35 @@
       </c>
       <c r="H220" s="3" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="I220" s="3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J220" s="3" t="n">
         <v>3</v>
       </c>
       <c r="K220" s="3" t="inlineStr">
         <is>
-          <t>communs, valorisation_des_communs, limites_planetaires, additionnalite, plafond_ecologique</t>
+          <t>robustesse, regle_contre_discretion, indicateur_de_progres</t>
         </is>
       </c>
       <c r="L220" s="3" t="inlineStr">
         <is>
-          <t>L1.C17, L1.C22, L7.C05, L7.C13, L11.C16, L20.C01, L20.C11, L20.C17, L20.C22</t>
+          <t>L7.C04, L7.C07, L7.C10, L11.C21, L11.C25, L20.C01, L20.C04, L20.C11, L20.C14</t>
         </is>
       </c>
       <c r="M220" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-20-droit-international-monetaire-et-commercial/c16-le-patrimoine-commun-de-l-humanite.md</t>
+          <t>corpus/livre-20-droit-international-monetaire-et-commercial/c15-le-devoir-international-des-agents.md</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" s="2" t="inlineStr">
         <is>
-          <t>L20.C17</t>
+          <t>L20.C16</t>
         </is>
       </c>
       <c r="B221" s="3" t="inlineStr">
@@ -15141,7 +15141,7 @@
       </c>
       <c r="C221" s="3" t="inlineStr">
         <is>
-          <t>La sanctuarisation, et elle existe</t>
+          <t>Le patrimoine commun de l'humanité</t>
         </is>
       </c>
       <c r="D221" s="3" t="inlineStr">
@@ -15170,31 +15170,31 @@
         </is>
       </c>
       <c r="I221" s="3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J221" s="3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K221" s="3" t="inlineStr">
         <is>
-          <t>communs, limites_planetaires, fenetre_de_reforme, robustesse, plafond_ecologique</t>
+          <t>communs, valorisation_des_communs, limites_planetaires, additionnalite, plafond_ecologique</t>
         </is>
       </c>
       <c r="L221" s="3" t="inlineStr">
         <is>
-          <t>L1.C17, L1.C18, L7.C13, L7.C19, L7.C20, L11.C20, L20.C01, L20.C06, L20.C09, L20.C16, L20.C22</t>
+          <t>L1.C17, L1.C22, L7.C05, L7.C13, L11.C16, L20.C01, L20.C11, L20.C17, L20.C22</t>
         </is>
       </c>
       <c r="M221" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-20-droit-international-monetaire-et-commercial/c17-la-sanctuarisation-et-elle-existe.md</t>
+          <t>corpus/livre-20-droit-international-monetaire-et-commercial/c16-le-patrimoine-commun-de-l-humanite.md</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" s="2" t="inlineStr">
         <is>
-          <t>L20.C18</t>
+          <t>L20.C17</t>
         </is>
       </c>
       <c r="B222" s="3" t="inlineStr">
@@ -15204,7 +15204,7 @@
       </c>
       <c r="C222" s="3" t="inlineStr">
         <is>
-          <t>L'amendement et la dérogation dans l'ordre commercial</t>
+          <t>La sanctuarisation, et elle existe</t>
         </is>
       </c>
       <c r="D222" s="3" t="inlineStr">
@@ -15229,35 +15229,35 @@
       </c>
       <c r="H222" s="3" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="I222" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J222" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K222" s="3" t="inlineStr">
         <is>
-          <t>bareme, seuil_d_activation, additionnalite, fenetre_de_reforme</t>
+          <t>communs, limites_planetaires, fenetre_de_reforme, robustesse, plafond_ecologique</t>
         </is>
       </c>
       <c r="L222" s="3" t="inlineStr">
         <is>
-          <t>L1.C27, L7.C17, L7.C20, L11.C24, L20.C01, L20.C06, L20.C09, L20.C13, L20.C19, L20.C20</t>
+          <t>L1.C17, L1.C18, L7.C13, L7.C19, L7.C20, L11.C20, L20.C01, L20.C06, L20.C09, L20.C16, L20.C22</t>
         </is>
       </c>
       <c r="M222" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-20-droit-international-monetaire-et-commercial/c18-l-amendement-et-la-derogation-dans-l-ordre-commercial.md</t>
+          <t>corpus/livre-20-droit-international-monetaire-et-commercial/c17-la-sanctuarisation-et-elle-existe.md</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" s="2" t="inlineStr">
         <is>
-          <t>L20.C19</t>
+          <t>L20.C18</t>
         </is>
       </c>
       <c r="B223" s="3" t="inlineStr">
@@ -15267,7 +15267,7 @@
       </c>
       <c r="C223" s="3" t="inlineStr">
         <is>
-          <t>Le texte que la conformité invoque</t>
+          <t>L'amendement et la dérogation dans l'ordre commercial</t>
         </is>
       </c>
       <c r="D223" s="3" t="inlineStr">
@@ -15292,35 +15292,35 @@
       </c>
       <c r="H223" s="3" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="I223" s="3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J223" s="3" t="n">
         <v>3</v>
       </c>
       <c r="K223" s="3" t="inlineStr">
         <is>
-          <t>bareme, additionnalite, limites_planetaires, seuil_d_activation, externalisation</t>
+          <t>bareme, seuil_d_activation, additionnalite, fenetre_de_reforme</t>
         </is>
       </c>
       <c r="L223" s="3" t="inlineStr">
         <is>
-          <t>L1.C27, L7.C17, L11.C24, L20.C01, L20.C18, L20.C20, L20.C22</t>
+          <t>L1.C27, L7.C17, L7.C20, L11.C24, L20.C01, L20.C06, L20.C09, L20.C13, L20.C19, L20.C20</t>
         </is>
       </c>
       <c r="M223" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-20-droit-international-monetaire-et-commercial/c19-le-texte-que-la-conformite-invoque.md</t>
+          <t>corpus/livre-20-droit-international-monetaire-et-commercial/c18-l-amendement-et-la-derogation-dans-l-ordre-commercial.md</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" s="2" t="inlineStr">
         <is>
-          <t>L20.C20</t>
+          <t>L20.C19</t>
         </is>
       </c>
       <c r="B224" s="3" t="inlineStr">
@@ -15330,7 +15330,7 @@
       </c>
       <c r="C224" s="3" t="inlineStr">
         <is>
-          <t>L'ajustement aux frontières comme précédent</t>
+          <t>Le texte que la conformité invoque</t>
         </is>
       </c>
       <c r="D224" s="3" t="inlineStr">
@@ -15355,7 +15355,7 @@
       </c>
       <c r="H224" s="3" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="I224" s="3" t="n">
@@ -15366,24 +15366,24 @@
       </c>
       <c r="K224" s="3" t="inlineStr">
         <is>
-          <t>bareme, seuil_d_activation, externalisation, additionnalite, contrepartie_comptable</t>
+          <t>bareme, additionnalite, limites_planetaires, seuil_d_activation, externalisation</t>
         </is>
       </c>
       <c r="L224" s="3" t="inlineStr">
         <is>
-          <t>L1.C27, L7.C17, L11.C21, L11.C24, L11.C25, L20.C01, L20.C18, L20.C19, L20.C22</t>
+          <t>L1.C27, L7.C17, L11.C24, L20.C01, L20.C18, L20.C20, L20.C22</t>
         </is>
       </c>
       <c r="M224" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-20-droit-international-monetaire-et-commercial/c20-l-ajustement-aux-frontieres-comme-precedent.md</t>
+          <t>corpus/livre-20-droit-international-monetaire-et-commercial/c19-le-texte-que-la-conformite-invoque.md</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" s="2" t="inlineStr">
         <is>
-          <t>L20.C21</t>
+          <t>L20.C20</t>
         </is>
       </c>
       <c r="B225" s="3" t="inlineStr">
@@ -15393,7 +15393,7 @@
       </c>
       <c r="C225" s="3" t="inlineStr">
         <is>
-          <t>La transparence et sa limite juridictionnelle</t>
+          <t>L'ajustement aux frontières comme précédent</t>
         </is>
       </c>
       <c r="D225" s="3" t="inlineStr">
@@ -15422,31 +15422,31 @@
         </is>
       </c>
       <c r="I225" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J225" s="3" t="n">
         <v>3</v>
       </c>
       <c r="K225" s="3" t="inlineStr">
         <is>
-          <t>robustesse, contrepartie_comptable, bareme, monnaie_comme_registre</t>
+          <t>bareme, seuil_d_activation, externalisation, additionnalite, contrepartie_comptable</t>
         </is>
       </c>
       <c r="L225" s="3" t="inlineStr">
         <is>
-          <t>L7.C18, L11.C21, L11.C24, L11.C25, L20.C01, L20.C11, L20.C14, L20.C20, L20.C22</t>
+          <t>L1.C27, L7.C17, L11.C21, L11.C24, L11.C25, L20.C01, L20.C18, L20.C19, L20.C22</t>
         </is>
       </c>
       <c r="M225" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-20-droit-international-monetaire-et-commercial/c21-la-transparence-et-sa-limite-juridictionnelle.md</t>
+          <t>corpus/livre-20-droit-international-monetaire-et-commercial/c20-l-ajustement-aux-frontieres-comme-precedent.md</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" s="2" t="inlineStr">
         <is>
-          <t>L20.C22</t>
+          <t>L20.C21</t>
         </is>
       </c>
       <c r="B226" s="3" t="inlineStr">
@@ -15456,7 +15456,7 @@
       </c>
       <c r="C226" s="3" t="inlineStr">
         <is>
-          <t>Ce que le droit devrait devenir</t>
+          <t>La transparence et sa limite juridictionnelle</t>
         </is>
       </c>
       <c r="D226" s="3" t="inlineStr">
@@ -15492,85 +15492,148 @@
       </c>
       <c r="K226" s="3" t="inlineStr">
         <is>
-          <t>fenetre_de_reforme, communs, limites_planetaires, regle_contre_discretion, bareme, referentiel_de_change</t>
+          <t>robustesse, contrepartie_comptable, bareme, monnaie_comme_registre</t>
         </is>
       </c>
       <c r="L226" s="3" t="inlineStr">
         <is>
-          <t>L1.C18, L7.C12, L7.C13, L11.C15, L11.C25, L20.C01, L20.C03, L20.C06, L20.C07, L20.C08, L20.C12, L20.C13, L20.C16, L20.C17, L20.C19, L20.C20, L20.C21, L20.C23</t>
+          <t>L7.C18, L11.C21, L11.C24, L11.C25, L20.C01, L20.C11, L20.C14, L20.C20, L20.C22</t>
         </is>
       </c>
       <c r="M226" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-20-droit-international-monetaire-et-commercial/c22-ce-que-le-droit-devrait-devenir.md</t>
+          <t>corpus/livre-20-droit-international-monetaire-et-commercial/c21-la-transparence-et-sa-limite-juridictionnelle.md</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" s="2" t="inlineStr">
         <is>
+          <t>L20.C22</t>
+        </is>
+      </c>
+      <c r="B227" s="3" t="inlineStr">
+        <is>
+          <t>L20</t>
+        </is>
+      </c>
+      <c r="C227" s="3" t="inlineStr">
+        <is>
+          <t>Ce que le droit devrait devenir</t>
+        </is>
+      </c>
+      <c r="D227" s="3" t="inlineStr">
+        <is>
+          <t>brouillon</t>
+        </is>
+      </c>
+      <c r="E227" s="3" t="inlineStr">
+        <is>
+          <t>preparatoire</t>
+        </is>
+      </c>
+      <c r="F227" s="3" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="G227" s="3" t="inlineStr">
+        <is>
+          <t>conception</t>
+        </is>
+      </c>
+      <c r="H227" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="I227" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="J227" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="K227" s="3" t="inlineStr">
+        <is>
+          <t>fenetre_de_reforme, communs, limites_planetaires, regle_contre_discretion, bareme, referentiel_de_change</t>
+        </is>
+      </c>
+      <c r="L227" s="3" t="inlineStr">
+        <is>
+          <t>L1.C18, L7.C12, L7.C13, L11.C15, L11.C25, L20.C01, L20.C03, L20.C06, L20.C07, L20.C08, L20.C12, L20.C13, L20.C16, L20.C17, L20.C19, L20.C20, L20.C21, L20.C23</t>
+        </is>
+      </c>
+      <c r="M227" s="3" t="inlineStr">
+        <is>
+          <t>corpus/livre-20-droit-international-monetaire-et-commercial/c22-ce-que-le-droit-devrait-devenir.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" s="2" t="inlineStr">
+        <is>
           <t>L20.C23</t>
         </is>
       </c>
-      <c r="B227" s="3" t="inlineStr">
+      <c r="B228" s="3" t="inlineStr">
         <is>
           <t>L20</t>
         </is>
       </c>
-      <c r="C227" s="3" t="inlineStr">
+      <c r="C228" s="3" t="inlineStr">
         <is>
           <t>La portée du livre</t>
         </is>
       </c>
-      <c r="D227" s="3" t="inlineStr">
-        <is>
-          <t>brouillon</t>
-        </is>
-      </c>
-      <c r="E227" s="3" t="inlineStr">
-        <is>
-          <t>preparatoire</t>
-        </is>
-      </c>
-      <c r="F227" s="3" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="G227" s="3" t="inlineStr">
+      <c r="D228" s="3" t="inlineStr">
+        <is>
+          <t>brouillon</t>
+        </is>
+      </c>
+      <c r="E228" s="3" t="inlineStr">
+        <is>
+          <t>preparatoire</t>
+        </is>
+      </c>
+      <c r="F228" s="3" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="G228" s="3" t="inlineStr">
         <is>
           <t>conception</t>
         </is>
       </c>
-      <c r="H227" s="3" t="inlineStr">
+      <c r="H228" s="3" t="inlineStr">
         <is>
           <t>2026-09-06</t>
         </is>
       </c>
-      <c r="I227" s="3" t="n">
+      <c r="I228" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="J227" s="3" t="n">
+      <c r="J228" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="K227" s="3" t="inlineStr">
+      <c r="K228" s="3" t="inlineStr">
         <is>
           <t>fenetre_de_reforme, communs, limites_planetaires, creation_monetaire, robustesse</t>
         </is>
       </c>
-      <c r="L227" s="3" t="inlineStr">
+      <c r="L228" s="3" t="inlineStr">
         <is>
           <t>L1.C18, L1.C27, L7.C05, L7.C10, L7.C12, L7.C13, L11.C15, L11.C24, L11.C25, L20.C01, L20.C02, L20.C03, L20.C06, L20.C07, L20.C08, L20.C11, L20.C12, L20.C13, L20.C16, L20.C17, L20.C19, L20.C20, L20.C21, L20.C22</t>
         </is>
       </c>
-      <c r="M227" s="3" t="inlineStr">
+      <c r="M228" s="3" t="inlineStr">
         <is>
           <t>corpus/livre-20-droit-international-monetaire-et-commercial/c23-la-portee-du-livre.md</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:M227"/>
+  <autoFilter ref="A1:M228"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -15649,7 +15712,7 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>226</v>
+        <v>227</v>
       </c>
     </row>
     <row r="7">
@@ -15659,7 +15722,7 @@
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>217</v>
+        <v>218</v>
       </c>
     </row>
     <row r="8">
@@ -15679,7 +15742,7 @@
         </is>
       </c>
       <c r="B9" s="3" t="n">
-        <v>1140</v>
+        <v>1143</v>
       </c>
     </row>
     <row r="10">
@@ -15689,7 +15752,7 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>948</v>
+        <v>951</v>
       </c>
     </row>
     <row r="11">
@@ -15771,7 +15834,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C255"/>
+  <dimension ref="A1:C256"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -18700,7 +18763,7 @@
       </c>
       <c r="C173" s="6" t="inlineStr">
         <is>
-          <t>en-cours — 6 chapitre(s)</t>
+          <t>en-cours — 7 chapitre(s)</t>
         </is>
       </c>
     </row>
@@ -18807,48 +18870,48 @@
       </c>
     </row>
     <row r="180">
-      <c r="A180" s="6" t="inlineStr">
+      <c r="A180" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    L10.C07</t>
+        </is>
+      </c>
+      <c r="B180" s="3" t="inlineStr">
+        <is>
+          <t>Ce qu'une banque centrale a le droit d'acheter, et le corpus généralisait depuis le cadre le plus permissif</t>
+        </is>
+      </c>
+      <c r="C180" s="3" t="inlineStr">
+        <is>
+          <t>brouillon</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" s="6" t="inlineStr">
         <is>
           <t>L11</t>
         </is>
       </c>
-      <c r="B180" s="6" t="inlineStr">
+      <c r="B181" s="6" t="inlineStr">
         <is>
           <t>Ingénierie des barèmes : reflux, qualification, périmètre et pondérations</t>
         </is>
       </c>
-      <c r="C180" s="6" t="inlineStr">
+      <c r="C181" s="6" t="inlineStr">
         <is>
           <t>defrichage — 29 chapitre(s)</t>
-        </is>
-      </c>
-    </row>
-    <row r="181">
-      <c r="A181" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    L11.C01</t>
-        </is>
-      </c>
-      <c r="B181" s="3" t="inlineStr">
-        <is>
-          <t>Reflux ou destruction — la bifurcation</t>
-        </is>
-      </c>
-      <c r="C181" s="3" t="inlineStr">
-        <is>
-          <t>brouillon</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L11.C02</t>
+          <t xml:space="preserve">    L11.C01</t>
         </is>
       </c>
       <c r="B182" s="3" t="inlineStr">
         <is>
-          <t>Le trajet complet de la valeur</t>
+          <t>Reflux ou destruction — la bifurcation</t>
         </is>
       </c>
       <c r="C182" s="3" t="inlineStr">
@@ -18860,12 +18923,12 @@
     <row r="183">
       <c r="A183" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L11.C03</t>
+          <t xml:space="preserve">    L11.C02</t>
         </is>
       </c>
       <c r="B183" s="3" t="inlineStr">
         <is>
-          <t>Le compte des objectifs et des instruments</t>
+          <t>Le trajet complet de la valeur</t>
         </is>
       </c>
       <c r="C183" s="3" t="inlineStr">
@@ -18877,12 +18940,12 @@
     <row r="184">
       <c r="A184" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L11.C04</t>
+          <t xml:space="preserve">    L11.C03</t>
         </is>
       </c>
       <c r="B184" s="3" t="inlineStr">
         <is>
-          <t>Les instruments du reflux sous parité fixe</t>
+          <t>Le compte des objectifs et des instruments</t>
         </is>
       </c>
       <c r="C184" s="3" t="inlineStr">
@@ -18894,12 +18957,12 @@
     <row r="185">
       <c r="A185" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L11.C05</t>
+          <t xml:space="preserve">    L11.C04</t>
         </is>
       </c>
       <c r="B185" s="3" t="inlineStr">
         <is>
-          <t>L'assiette du reflux transactionnel</t>
+          <t>Les instruments du reflux sous parité fixe</t>
         </is>
       </c>
       <c r="C185" s="3" t="inlineStr">
@@ -18911,12 +18974,12 @@
     <row r="186">
       <c r="A186" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L11.C06</t>
+          <t xml:space="preserve">    L11.C05</t>
         </is>
       </c>
       <c r="B186" s="3" t="inlineStr">
         <is>
-          <t>Le barème par défaut</t>
+          <t>L'assiette du reflux transactionnel</t>
         </is>
       </c>
       <c r="C186" s="3" t="inlineStr">
@@ -18928,12 +18991,12 @@
     <row r="187">
       <c r="A187" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L11.C07</t>
+          <t xml:space="preserve">    L11.C06</t>
         </is>
       </c>
       <c r="B187" s="3" t="inlineStr">
         <is>
-          <t>Le demurrage et son nœud de prélèvement</t>
+          <t>Le barème par défaut</t>
         </is>
       </c>
       <c r="C187" s="3" t="inlineStr">
@@ -18945,12 +19008,12 @@
     <row r="188">
       <c r="A188" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L11.C08</t>
+          <t xml:space="preserve">    L11.C07</t>
         </is>
       </c>
       <c r="B188" s="3" t="inlineStr">
         <is>
-          <t>Les dérogations</t>
+          <t>Le demurrage et son nœud de prélèvement</t>
         </is>
       </c>
       <c r="C188" s="3" t="inlineStr">
@@ -18962,12 +19025,12 @@
     <row r="189">
       <c r="A189" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L11.C09</t>
+          <t xml:space="preserve">    L11.C08</t>
         </is>
       </c>
       <c r="B189" s="3" t="inlineStr">
         <is>
-          <t>L'incidence — qui paie le reflux</t>
+          <t>Les dérogations</t>
         </is>
       </c>
       <c r="C189" s="3" t="inlineStr">
@@ -18979,12 +19042,12 @@
     <row r="190">
       <c r="A190" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L11.C10</t>
+          <t xml:space="preserve">    L11.C09</t>
         </is>
       </c>
       <c r="B190" s="3" t="inlineStr">
         <is>
-          <t>La trajectoire de mise en place</t>
+          <t>L'incidence — qui paie le reflux</t>
         </is>
       </c>
       <c r="C190" s="3" t="inlineStr">
@@ -18996,12 +19059,12 @@
     <row r="191">
       <c r="A191" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L11.C11</t>
+          <t xml:space="preserve">    L11.C10</t>
         </is>
       </c>
       <c r="B191" s="3" t="inlineStr">
         <is>
-          <t>Qui arrête le barème</t>
+          <t>La trajectoire de mise en place</t>
         </is>
       </c>
       <c r="C191" s="3" t="inlineStr">
@@ -19013,12 +19076,12 @@
     <row r="192">
       <c r="A192" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L11.C12</t>
+          <t xml:space="preserve">    L11.C11</t>
         </is>
       </c>
       <c r="B192" s="3" t="inlineStr">
         <is>
-          <t>La directive</t>
+          <t>Qui arrête le barème</t>
         </is>
       </c>
       <c r="C192" s="3" t="inlineStr">
@@ -19030,12 +19093,12 @@
     <row r="193">
       <c r="A193" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L11.C13</t>
+          <t xml:space="preserve">    L11.C12</t>
         </is>
       </c>
       <c r="B193" s="3" t="inlineStr">
         <is>
-          <t>Le barème de qualification</t>
+          <t>La directive</t>
         </is>
       </c>
       <c r="C193" s="3" t="inlineStr">
@@ -19047,12 +19110,12 @@
     <row r="194">
       <c r="A194" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L11.C14</t>
+          <t xml:space="preserve">    L11.C13</t>
         </is>
       </c>
       <c r="B194" s="3" t="inlineStr">
         <is>
-          <t>Le tableau de bord, ou les données de la directive</t>
+          <t>Le barème de qualification</t>
         </is>
       </c>
       <c r="C194" s="3" t="inlineStr">
@@ -19064,12 +19127,12 @@
     <row r="195">
       <c r="A195" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L11.C15</t>
+          <t xml:space="preserve">    L11.C14</t>
         </is>
       </c>
       <c r="B195" s="3" t="inlineStr">
         <is>
-          <t>Les parités du référentiel de change</t>
+          <t>Le tableau de bord, ou les données de la directive</t>
         </is>
       </c>
       <c r="C195" s="3" t="inlineStr">
@@ -19081,12 +19144,12 @@
     <row r="196">
       <c r="A196" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L11.C16</t>
+          <t xml:space="preserve">    L11.C15</t>
         </is>
       </c>
       <c r="B196" s="3" t="inlineStr">
         <is>
-          <t>La valorisation des communs</t>
+          <t>Les parités du référentiel de change</t>
         </is>
       </c>
       <c r="C196" s="3" t="inlineStr">
@@ -19098,12 +19161,12 @@
     <row r="197">
       <c r="A197" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L11.C17</t>
+          <t xml:space="preserve">    L11.C16</t>
         </is>
       </c>
       <c r="B197" s="3" t="inlineStr">
         <is>
-          <t>La cohérence des cinq barèmes</t>
+          <t>La valorisation des communs</t>
         </is>
       </c>
       <c r="C197" s="3" t="inlineStr">
@@ -19115,12 +19178,12 @@
     <row r="198">
       <c r="A198" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L11.C18</t>
+          <t xml:space="preserve">    L11.C17</t>
         </is>
       </c>
       <c r="B198" s="3" t="inlineStr">
         <is>
-          <t>Le seuil d'exemption</t>
+          <t>La cohérence des cinq barèmes</t>
         </is>
       </c>
       <c r="C198" s="3" t="inlineStr">
@@ -19132,12 +19195,12 @@
     <row r="199">
       <c r="A199" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L11.C19</t>
+          <t xml:space="preserve">    L11.C18</t>
         </is>
       </c>
       <c r="B199" s="3" t="inlineStr">
         <is>
-          <t>Le recours</t>
+          <t>Le seuil d'exemption</t>
         </is>
       </c>
       <c r="C199" s="3" t="inlineStr">
@@ -19149,12 +19212,12 @@
     <row r="200">
       <c r="A200" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L11.C20</t>
+          <t xml:space="preserve">    L11.C19</t>
         </is>
       </c>
       <c r="B200" s="3" t="inlineStr">
         <is>
-          <t>L'amendement de la directive</t>
+          <t>Le recours</t>
         </is>
       </c>
       <c r="C200" s="3" t="inlineStr">
@@ -19166,12 +19229,12 @@
     <row r="201">
       <c r="A201" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L11.C21</t>
+          <t xml:space="preserve">    L11.C20</t>
         </is>
       </c>
       <c r="B201" s="3" t="inlineStr">
         <is>
-          <t>La perception</t>
+          <t>L'amendement de la directive</t>
         </is>
       </c>
       <c r="C201" s="3" t="inlineStr">
@@ -19183,12 +19246,12 @@
     <row r="202">
       <c r="A202" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L11.C22</t>
+          <t xml:space="preserve">    L11.C21</t>
         </is>
       </c>
       <c r="B202" s="3" t="inlineStr">
         <is>
-          <t>Les délais</t>
+          <t>La perception</t>
         </is>
       </c>
       <c r="C202" s="3" t="inlineStr">
@@ -19200,12 +19263,12 @@
     <row r="203">
       <c r="A203" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L11.C23</t>
+          <t xml:space="preserve">    L11.C22</t>
         </is>
       </c>
       <c r="B203" s="3" t="inlineStr">
         <is>
-          <t>La contracyclicité</t>
+          <t>Les délais</t>
         </is>
       </c>
       <c r="C203" s="3" t="inlineStr">
@@ -19217,12 +19280,12 @@
     <row r="204">
       <c r="A204" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L11.C24</t>
+          <t xml:space="preserve">    L11.C23</t>
         </is>
       </c>
       <c r="B204" s="3" t="inlineStr">
         <is>
-          <t>Le barème aux frontières</t>
+          <t>La contracyclicité</t>
         </is>
       </c>
       <c r="C204" s="3" t="inlineStr">
@@ -19234,12 +19297,12 @@
     <row r="205">
       <c r="A205" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L11.C25</t>
+          <t xml:space="preserve">    L11.C24</t>
         </is>
       </c>
       <c r="B205" s="3" t="inlineStr">
         <is>
-          <t>Le contrôle</t>
+          <t>Le barème aux frontières</t>
         </is>
       </c>
       <c r="C205" s="3" t="inlineStr">
@@ -19251,12 +19314,12 @@
     <row r="206">
       <c r="A206" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L11.C26</t>
+          <t xml:space="preserve">    L11.C25</t>
         </is>
       </c>
       <c r="B206" s="3" t="inlineStr">
         <is>
-          <t>La portée du Livre 11</t>
+          <t>Le contrôle</t>
         </is>
       </c>
       <c r="C206" s="3" t="inlineStr">
@@ -19268,12 +19331,12 @@
     <row r="207">
       <c r="A207" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L11.C27</t>
+          <t xml:space="preserve">    L11.C26</t>
         </is>
       </c>
       <c r="B207" s="3" t="inlineStr">
         <is>
-          <t>L'assiette de la fonte est celle de la TVA</t>
+          <t>La portée du Livre 11</t>
         </is>
       </c>
       <c r="C207" s="3" t="inlineStr">
@@ -19285,12 +19348,12 @@
     <row r="208">
       <c r="A208" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L11.C28</t>
+          <t xml:space="preserve">    L11.C27</t>
         </is>
       </c>
       <c r="B208" s="3" t="inlineStr">
         <is>
-          <t>La fonte sur les acquisitions d'actifs, éprouvée</t>
+          <t>L'assiette de la fonte est celle de la TVA</t>
         </is>
       </c>
       <c r="C208" s="3" t="inlineStr">
@@ -19302,219 +19365,219 @@
     <row r="209">
       <c r="A209" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">    L11.C28</t>
+        </is>
+      </c>
+      <c r="B209" s="3" t="inlineStr">
+        <is>
+          <t>La fonte sur les acquisitions d'actifs, éprouvée</t>
+        </is>
+      </c>
+      <c r="C209" s="3" t="inlineStr">
+        <is>
+          <t>brouillon</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">    L11.C29</t>
         </is>
       </c>
-      <c r="B209" s="3" t="inlineStr">
+      <c r="B210" s="3" t="inlineStr">
         <is>
           <t>La structure des sanctions</t>
         </is>
       </c>
-      <c r="C209" s="3" t="inlineStr">
-        <is>
-          <t>brouillon</t>
-        </is>
-      </c>
-    </row>
-    <row r="210">
-      <c r="A210" s="6" t="inlineStr">
+      <c r="C210" s="3" t="inlineStr">
+        <is>
+          <t>brouillon</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" s="6" t="inlineStr">
         <is>
           <t>L12</t>
         </is>
       </c>
-      <c r="B210" s="6" t="inlineStr">
+      <c r="B211" s="6" t="inlineStr">
         <is>
           <t>Comment réaliser les ODD avec NEMO IMS ?</t>
         </is>
       </c>
-      <c r="C210" s="6" t="inlineStr">
+      <c r="C211" s="6" t="inlineStr">
         <is>
           <t>candidat — 0 chapitre(s)</t>
         </is>
       </c>
     </row>
-    <row r="211">
-      <c r="A211" s="7" t="inlineStr"/>
-      <c r="B211" s="7" t="inlineStr">
+    <row r="212">
+      <c r="A212" s="7" t="inlineStr"/>
+      <c r="B212" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">    (aucun chapitre écrit)</t>
         </is>
       </c>
-      <c r="C211" s="7" t="inlineStr"/>
-    </row>
-    <row r="212">
-      <c r="A212" s="6" t="inlineStr">
+      <c r="C212" s="7" t="inlineStr"/>
+    </row>
+    <row r="213">
+      <c r="A213" s="6" t="inlineStr">
         <is>
           <t>L13</t>
         </is>
       </c>
-      <c r="B212" s="6" t="inlineStr">
+      <c r="B213" s="6" t="inlineStr">
         <is>
           <t>Méthodes, données, scénarios et simulateur NEMO IMS</t>
         </is>
       </c>
-      <c r="C212" s="6" t="inlineStr">
+      <c r="C213" s="6" t="inlineStr">
         <is>
           <t>candidat — 0 chapitre(s)</t>
         </is>
       </c>
     </row>
-    <row r="213">
-      <c r="A213" s="7" t="inlineStr"/>
-      <c r="B213" s="7" t="inlineStr">
+    <row r="214">
+      <c r="A214" s="7" t="inlineStr"/>
+      <c r="B214" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">    (aucun chapitre écrit)</t>
         </is>
       </c>
-      <c r="C213" s="7" t="inlineStr"/>
-    </row>
-    <row r="214">
-      <c r="A214" s="6" t="inlineStr">
+      <c r="C214" s="7" t="inlineStr"/>
+    </row>
+    <row r="215">
+      <c r="A215" s="6" t="inlineStr">
         <is>
           <t>L14</t>
         </is>
       </c>
-      <c r="B214" s="6" t="inlineStr">
+      <c r="B215" s="6" t="inlineStr">
         <is>
           <t>Gouverner la preuve : méthodes, vérification et traçabilité</t>
         </is>
       </c>
-      <c r="C214" s="6" t="inlineStr">
+      <c r="C215" s="6" t="inlineStr">
         <is>
           <t>candidat — 0 chapitre(s)</t>
         </is>
       </c>
     </row>
-    <row r="215">
-      <c r="A215" s="7" t="inlineStr"/>
-      <c r="B215" s="7" t="inlineStr">
+    <row r="216">
+      <c r="A216" s="7" t="inlineStr"/>
+      <c r="B216" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">    (aucun chapitre écrit)</t>
         </is>
       </c>
-      <c r="C215" s="7" t="inlineStr"/>
-    </row>
-    <row r="216">
-      <c r="A216" s="6" t="inlineStr">
+      <c r="C216" s="7" t="inlineStr"/>
+    </row>
+    <row r="217">
+      <c r="A217" s="6" t="inlineStr">
         <is>
           <t>L15</t>
         </is>
       </c>
-      <c r="B216" s="6" t="inlineStr">
+      <c r="B217" s="6" t="inlineStr">
         <is>
           <t>Fraudes, corruptions et architectures de la triche</t>
         </is>
       </c>
-      <c r="C216" s="6" t="inlineStr">
+      <c r="C217" s="6" t="inlineStr">
         <is>
           <t>exploratoire — 0 chapitre(s)</t>
         </is>
       </c>
     </row>
-    <row r="217">
-      <c r="A217" s="7" t="inlineStr"/>
-      <c r="B217" s="7" t="inlineStr">
+    <row r="218">
+      <c r="A218" s="7" t="inlineStr"/>
+      <c r="B218" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">    (aucun chapitre écrit)</t>
         </is>
       </c>
-      <c r="C217" s="7" t="inlineStr"/>
-    </row>
-    <row r="218">
-      <c r="A218" s="6" t="inlineStr">
+      <c r="C218" s="7" t="inlineStr"/>
+    </row>
+    <row r="219">
+      <c r="A219" s="6" t="inlineStr">
         <is>
           <t>L16</t>
         </is>
       </c>
-      <c r="B218" s="6" t="inlineStr">
+      <c r="B219" s="6" t="inlineStr">
         <is>
           <t>Typologie comparée des systèmes et alternatives monétaires</t>
         </is>
       </c>
-      <c r="C218" s="6" t="inlineStr">
+      <c r="C219" s="6" t="inlineStr">
         <is>
           <t>candidat — 0 chapitre(s)</t>
         </is>
       </c>
     </row>
-    <row r="219">
-      <c r="A219" s="7" t="inlineStr"/>
-      <c r="B219" s="7" t="inlineStr">
+    <row r="220">
+      <c r="A220" s="7" t="inlineStr"/>
+      <c r="B220" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">    (aucun chapitre écrit)</t>
         </is>
       </c>
-      <c r="C219" s="7" t="inlineStr"/>
-    </row>
-    <row r="220">
-      <c r="A220" s="6" t="inlineStr">
+      <c r="C220" s="7" t="inlineStr"/>
+    </row>
+    <row r="221">
+      <c r="A221" s="6" t="inlineStr">
         <is>
           <t>L17</t>
         </is>
       </c>
-      <c r="B220" s="6" t="inlineStr">
+      <c r="B221" s="6" t="inlineStr">
         <is>
           <t>Après la croissance : décroissance, post-croissance et prospérité sans croissance</t>
         </is>
       </c>
-      <c r="C220" s="6" t="inlineStr">
+      <c r="C221" s="6" t="inlineStr">
         <is>
           <t>candidat — 0 chapitre(s)</t>
         </is>
       </c>
     </row>
-    <row r="221">
-      <c r="A221" s="7" t="inlineStr"/>
-      <c r="B221" s="7" t="inlineStr">
+    <row r="222">
+      <c r="A222" s="7" t="inlineStr"/>
+      <c r="B222" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">    (aucun chapitre écrit)</t>
         </is>
       </c>
-      <c r="C221" s="7" t="inlineStr"/>
-    </row>
-    <row r="222">
-      <c r="A222" s="6" t="inlineStr">
+      <c r="C222" s="7" t="inlineStr"/>
+    </row>
+    <row r="223">
+      <c r="A223" s="6" t="inlineStr">
         <is>
           <t>L18</t>
         </is>
       </c>
-      <c r="B222" s="6" t="inlineStr">
+      <c r="B223" s="6" t="inlineStr">
         <is>
           <t>Comptabilités écologiques, sociales et biophysiques</t>
         </is>
       </c>
-      <c r="C222" s="6" t="inlineStr">
+      <c r="C223" s="6" t="inlineStr">
         <is>
           <t>en-cours — 9 chapitre(s)</t>
-        </is>
-      </c>
-    </row>
-    <row r="223">
-      <c r="A223" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    L18.C01</t>
-        </is>
-      </c>
-      <c r="B223" s="3" t="inlineStr">
-        <is>
-          <t>Ce que ce livre doit établir, et le repli n'est pas l'annexe</t>
-        </is>
-      </c>
-      <c r="C223" s="3" t="inlineStr">
-        <is>
-          <t>brouillon</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L18.C02</t>
+          <t xml:space="preserve">    L18.C01</t>
         </is>
       </c>
       <c r="B224" s="3" t="inlineStr">
         <is>
-          <t>La métrologie existe, et ce qu'elle enregistre est l'ordre en place</t>
+          <t>Ce que ce livre doit établir, et le repli n'est pas l'annexe</t>
         </is>
       </c>
       <c r="C224" s="3" t="inlineStr">
@@ -19526,12 +19589,12 @@
     <row r="225">
       <c r="A225" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L18.C03</t>
+          <t xml:space="preserve">    L18.C02</t>
         </is>
       </c>
       <c r="B225" s="3" t="inlineStr">
         <is>
-          <t>L'échelle de repli, et qui l'a arrêtée</t>
+          <t>La métrologie existe, et ce qu'elle enregistre est l'ordre en place</t>
         </is>
       </c>
       <c r="C225" s="3" t="inlineStr">
@@ -19543,12 +19606,12 @@
     <row r="226">
       <c r="A226" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L18.C04</t>
+          <t xml:space="preserve">    L18.C03</t>
         </is>
       </c>
       <c r="B226" s="3" t="inlineStr">
         <is>
-          <t>Les grandeurs physiques, et l'endroit où elles frappent le dispositif</t>
+          <t>L'échelle de repli, et qui l'a arrêtée</t>
         </is>
       </c>
       <c r="C226" s="3" t="inlineStr">
@@ -19560,12 +19623,12 @@
     <row r="227">
       <c r="A227" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L18.C05</t>
+          <t xml:space="preserve">    L18.C04</t>
         </is>
       </c>
       <c r="B227" s="3" t="inlineStr">
         <is>
-          <t>Ce que la norme exclut, et ce n'est pas le commun</t>
+          <t>Les grandeurs physiques, et l'endroit où elles frappent le dispositif</t>
         </is>
       </c>
       <c r="C227" s="3" t="inlineStr">
@@ -19577,12 +19640,12 @@
     <row r="228">
       <c r="A228" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L18.C06</t>
+          <t xml:space="preserve">    L18.C05</t>
         </is>
       </c>
       <c r="B228" s="3" t="inlineStr">
         <is>
-          <t>Portée de la tranche, et une neuvième condition proposée</t>
+          <t>Ce que la norme exclut, et ce n'est pas le commun</t>
         </is>
       </c>
       <c r="C228" s="3" t="inlineStr">
@@ -19594,12 +19657,12 @@
     <row r="229">
       <c r="A229" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L18.C07</t>
+          <t xml:space="preserve">    L18.C06</t>
         </is>
       </c>
       <c r="B229" s="3" t="inlineStr">
         <is>
-          <t>CARE/TDL répare deux objections, et en crée une plus grave</t>
+          <t>Portée de la tranche, et une neuvième condition proposée</t>
         </is>
       </c>
       <c r="C229" s="3" t="inlineStr">
@@ -19611,12 +19674,12 @@
     <row r="230">
       <c r="A230" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L18.C08</t>
+          <t xml:space="preserve">    L18.C07</t>
         </is>
       </c>
       <c r="B230" s="3" t="inlineStr">
         <is>
-          <t>Le modèle au périmètre du dispositif, et F9 révisée</t>
+          <t>CARE/TDL répare deux objections, et en crée une plus grave</t>
         </is>
       </c>
       <c r="C230" s="3" t="inlineStr">
@@ -19628,63 +19691,63 @@
     <row r="231">
       <c r="A231" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">    L18.C08</t>
+        </is>
+      </c>
+      <c r="B231" s="3" t="inlineStr">
+        <is>
+          <t>Le modèle au périmètre du dispositif, et F9 révisée</t>
+        </is>
+      </c>
+      <c r="C231" s="3" t="inlineStr">
+        <is>
+          <t>brouillon</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">    L18.C09</t>
         </is>
       </c>
-      <c r="B231" s="3" t="inlineStr">
+      <c r="B232" s="3" t="inlineStr">
         <is>
           <t>L'ordre de grandeur, et le concurrent qu'il désigne</t>
         </is>
       </c>
-      <c r="C231" s="3" t="inlineStr">
-        <is>
-          <t>brouillon</t>
-        </is>
-      </c>
-    </row>
-    <row r="232">
-      <c r="A232" s="6" t="inlineStr">
+      <c r="C232" s="3" t="inlineStr">
+        <is>
+          <t>brouillon</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" s="6" t="inlineStr">
         <is>
           <t>L20</t>
         </is>
       </c>
-      <c r="B232" s="6" t="inlineStr">
+      <c r="B233" s="6" t="inlineStr">
         <is>
           <t>Droit international public, droit monétaire et commercial de la réforme</t>
         </is>
       </c>
-      <c r="C232" s="6" t="inlineStr">
+      <c r="C233" s="6" t="inlineStr">
         <is>
           <t>en-cours — 23 chapitre(s)</t>
-        </is>
-      </c>
-    </row>
-    <row r="233">
-      <c r="A233" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    L20.C01</t>
-        </is>
-      </c>
-      <c r="B233" s="3" t="inlineStr">
-        <is>
-          <t>Ce que ce livre doit établir</t>
-        </is>
-      </c>
-      <c r="C233" s="3" t="inlineStr">
-        <is>
-          <t>brouillon</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L20.C02</t>
+          <t xml:space="preserve">    L20.C01</t>
         </is>
       </c>
       <c r="B234" s="3" t="inlineStr">
         <is>
-          <t>L'interdiction du financement monétaire</t>
+          <t>Ce que ce livre doit établir</t>
         </is>
       </c>
       <c r="C234" s="3" t="inlineStr">
@@ -19696,12 +19759,12 @@
     <row r="235">
       <c r="A235" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L20.C03</t>
+          <t xml:space="preserve">    L20.C02</t>
         </is>
       </c>
       <c r="B235" s="3" t="inlineStr">
         <is>
-          <t>L'objectif principal et ce qu'il exclut</t>
+          <t>L'interdiction du financement monétaire</t>
         </is>
       </c>
       <c r="C235" s="3" t="inlineStr">
@@ -19713,12 +19776,12 @@
     <row r="236">
       <c r="A236" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L20.C04</t>
+          <t xml:space="preserve">    L20.C03</t>
         </is>
       </c>
       <c r="B236" s="3" t="inlineStr">
         <is>
-          <t>L'indépendance, et à l'égard de qui</t>
+          <t>L'objectif principal et ce qu'il exclut</t>
         </is>
       </c>
       <c r="C236" s="3" t="inlineStr">
@@ -19730,12 +19793,12 @@
     <row r="237">
       <c r="A237" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L20.C05</t>
+          <t xml:space="preserve">    L20.C04</t>
         </is>
       </c>
       <c r="B237" s="3" t="inlineStr">
         <is>
-          <t>Le monopole d'émission et le cours légal</t>
+          <t>L'indépendance, et à l'égard de qui</t>
         </is>
       </c>
       <c r="C237" s="3" t="inlineStr">
@@ -19747,12 +19810,12 @@
     <row r="238">
       <c r="A238" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L20.C06</t>
+          <t xml:space="preserve">    L20.C05</t>
         </is>
       </c>
       <c r="B238" s="3" t="inlineStr">
         <is>
-          <t>Les voies de révision et leur coût</t>
+          <t>Le monopole d'émission et le cours légal</t>
         </is>
       </c>
       <c r="C238" s="3" t="inlineStr">
@@ -19764,12 +19827,12 @@
     <row r="239">
       <c r="A239" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L20.C07</t>
+          <t xml:space="preserve">    L20.C06</t>
         </is>
       </c>
       <c r="B239" s="3" t="inlineStr">
         <is>
-          <t>L'accord monétaire international</t>
+          <t>Les voies de révision et leur coût</t>
         </is>
       </c>
       <c r="C239" s="3" t="inlineStr">
@@ -19781,12 +19844,12 @@
     <row r="240">
       <c r="A240" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L20.C08</t>
+          <t xml:space="preserve">    L20.C07</t>
         </is>
       </c>
       <c r="B240" s="3" t="inlineStr">
         <is>
-          <t>La parité inscrite dans le traité</t>
+          <t>L'accord monétaire international</t>
         </is>
       </c>
       <c r="C240" s="3" t="inlineStr">
@@ -19798,12 +19861,12 @@
     <row r="241">
       <c r="A241" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L20.C09</t>
+          <t xml:space="preserve">    L20.C08</t>
         </is>
       </c>
       <c r="B241" s="3" t="inlineStr">
         <is>
-          <t>L'amendement des statuts du Fonds</t>
+          <t>La parité inscrite dans le traité</t>
         </is>
       </c>
       <c r="C241" s="3" t="inlineStr">
@@ -19815,12 +19878,12 @@
     <row r="242">
       <c r="A242" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L20.C10</t>
+          <t xml:space="preserve">    L20.C09</t>
         </is>
       </c>
       <c r="B242" s="3" t="inlineStr">
         <is>
-          <t>Le vote pondéré et les voix de base</t>
+          <t>L'amendement des statuts du Fonds</t>
         </is>
       </c>
       <c r="C242" s="3" t="inlineStr">
@@ -19832,12 +19895,12 @@
     <row r="243">
       <c r="A243" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L20.C11</t>
+          <t xml:space="preserve">    L20.C10</t>
         </is>
       </c>
       <c r="B243" s="3" t="inlineStr">
         <is>
-          <t>La personnalité juridique et les immunités</t>
+          <t>Le vote pondéré et les voix de base</t>
         </is>
       </c>
       <c r="C243" s="3" t="inlineStr">
@@ -19849,12 +19912,12 @@
     <row r="244">
       <c r="A244" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L20.C12</t>
+          <t xml:space="preserve">    L20.C11</t>
         </is>
       </c>
       <c r="B244" s="3" t="inlineStr">
         <is>
-          <t>Les pouvoirs non délégables</t>
+          <t>La personnalité juridique et les immunités</t>
         </is>
       </c>
       <c r="C244" s="3" t="inlineStr">
@@ -19866,12 +19929,12 @@
     <row r="245">
       <c r="A245" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L20.C13</t>
+          <t xml:space="preserve">    L20.C12</t>
         </is>
       </c>
       <c r="B245" s="3" t="inlineStr">
         <is>
-          <t>L'entrée en vigueur, l'adhésion et le retrait</t>
+          <t>Les pouvoirs non délégables</t>
         </is>
       </c>
       <c r="C245" s="3" t="inlineStr">
@@ -19883,12 +19946,12 @@
     <row r="246">
       <c r="A246" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L20.C14</t>
+          <t xml:space="preserve">    L20.C13</t>
         </is>
       </c>
       <c r="B246" s="3" t="inlineStr">
         <is>
-          <t>Qui interprète le traité</t>
+          <t>L'entrée en vigueur, l'adhésion et le retrait</t>
         </is>
       </c>
       <c r="C246" s="3" t="inlineStr">
@@ -19900,12 +19963,12 @@
     <row r="247">
       <c r="A247" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L20.C15</t>
+          <t xml:space="preserve">    L20.C14</t>
         </is>
       </c>
       <c r="B247" s="3" t="inlineStr">
         <is>
-          <t>Le devoir international des agents</t>
+          <t>Qui interprète le traité</t>
         </is>
       </c>
       <c r="C247" s="3" t="inlineStr">
@@ -19917,12 +19980,12 @@
     <row r="248">
       <c r="A248" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L20.C16</t>
+          <t xml:space="preserve">    L20.C15</t>
         </is>
       </c>
       <c r="B248" s="3" t="inlineStr">
         <is>
-          <t>Le patrimoine commun de l'humanité</t>
+          <t>Le devoir international des agents</t>
         </is>
       </c>
       <c r="C248" s="3" t="inlineStr">
@@ -19934,12 +19997,12 @@
     <row r="249">
       <c r="A249" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L20.C17</t>
+          <t xml:space="preserve">    L20.C16</t>
         </is>
       </c>
       <c r="B249" s="3" t="inlineStr">
         <is>
-          <t>La sanctuarisation, et elle existe</t>
+          <t>Le patrimoine commun de l'humanité</t>
         </is>
       </c>
       <c r="C249" s="3" t="inlineStr">
@@ -19951,12 +20014,12 @@
     <row r="250">
       <c r="A250" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L20.C18</t>
+          <t xml:space="preserve">    L20.C17</t>
         </is>
       </c>
       <c r="B250" s="3" t="inlineStr">
         <is>
-          <t>L'amendement et la dérogation dans l'ordre commercial</t>
+          <t>La sanctuarisation, et elle existe</t>
         </is>
       </c>
       <c r="C250" s="3" t="inlineStr">
@@ -19968,12 +20031,12 @@
     <row r="251">
       <c r="A251" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L20.C19</t>
+          <t xml:space="preserve">    L20.C18</t>
         </is>
       </c>
       <c r="B251" s="3" t="inlineStr">
         <is>
-          <t>Le texte que la conformité invoque</t>
+          <t>L'amendement et la dérogation dans l'ordre commercial</t>
         </is>
       </c>
       <c r="C251" s="3" t="inlineStr">
@@ -19985,12 +20048,12 @@
     <row r="252">
       <c r="A252" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L20.C20</t>
+          <t xml:space="preserve">    L20.C19</t>
         </is>
       </c>
       <c r="B252" s="3" t="inlineStr">
         <is>
-          <t>L'ajustement aux frontières comme précédent</t>
+          <t>Le texte que la conformité invoque</t>
         </is>
       </c>
       <c r="C252" s="3" t="inlineStr">
@@ -20002,12 +20065,12 @@
     <row r="253">
       <c r="A253" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L20.C21</t>
+          <t xml:space="preserve">    L20.C20</t>
         </is>
       </c>
       <c r="B253" s="3" t="inlineStr">
         <is>
-          <t>La transparence et sa limite juridictionnelle</t>
+          <t>L'ajustement aux frontières comme précédent</t>
         </is>
       </c>
       <c r="C253" s="3" t="inlineStr">
@@ -20019,12 +20082,12 @@
     <row r="254">
       <c r="A254" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L20.C22</t>
+          <t xml:space="preserve">    L20.C21</t>
         </is>
       </c>
       <c r="B254" s="3" t="inlineStr">
         <is>
-          <t>Ce que le droit devrait devenir</t>
+          <t>La transparence et sa limite juridictionnelle</t>
         </is>
       </c>
       <c r="C254" s="3" t="inlineStr">
@@ -20036,15 +20099,32 @@
     <row r="255">
       <c r="A255" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">    L20.C22</t>
+        </is>
+      </c>
+      <c r="B255" s="3" t="inlineStr">
+        <is>
+          <t>Ce que le droit devrait devenir</t>
+        </is>
+      </c>
+      <c r="C255" s="3" t="inlineStr">
+        <is>
+          <t>brouillon</t>
+        </is>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">    L20.C23</t>
         </is>
       </c>
-      <c r="B255" s="3" t="inlineStr">
+      <c r="B256" s="3" t="inlineStr">
         <is>
           <t>La portée du livre</t>
         </is>
       </c>
-      <c r="C255" s="3" t="inlineStr">
+      <c r="C256" s="3" t="inlineStr">
         <is>
           <t>brouillon</t>
         </is>

--- a/plan-des-livres.xlsx
+++ b/plan-des-livres.xlsx
@@ -462,7 +462,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I21"/>
+  <dimension ref="A1:I27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -1303,43 +1303,289 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="4" t="inlineStr">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>L19</t>
+        </is>
+      </c>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>Comptabilité monétaire de l'émission sans dette</t>
+        </is>
+      </c>
+      <c r="C21" s="3" t="inlineStr">
+        <is>
+          <t>cahier-technique</t>
+        </is>
+      </c>
+      <c r="D21" s="3" t="inlineStr">
+        <is>
+          <t>reserve</t>
+        </is>
+      </c>
+      <c r="E21" s="3" t="inlineStr">
+        <is>
+          <t>non contraignant</t>
+        </is>
+      </c>
+      <c r="F21" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G21" s="3" t="inlineStr"/>
+      <c r="H21" s="3" t="inlineStr">
+        <is>
+          <t>Établir les écritures complètes d'une émission sans dette — chez l'émetteur, chez la banque centrale nationale, chez le bénéficiaire — et dire ce que l'unité est à l'actif comme au passif de chacun</t>
+        </is>
+      </c>
+      <c r="I21" s="3" t="inlineStr">
+        <is>
+          <t>écart de registre corrigé le 2026-09-07 — le matricule est réservé PAR LE PLAN DIRECTEUR et manquait à cette projection ; convention § 3, le plan tranche | arbitrage — A30 et A35 laissent ouvert ce que l'unité est AU PASSIF, et deux livres y ont buté : L10.C06 et L18.C06 | objection — L11.C02 : l'écriture du Symposium laisse les fonds propres négatifs du montant émis, et l'analogie qui la justifiait était fausse</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="inlineStr">
         <is>
           <t>L20</t>
         </is>
       </c>
-      <c r="B21" s="5" t="inlineStr">
+      <c r="B22" s="5" t="inlineStr">
         <is>
           <t>Droit international public, droit monétaire et commercial de la réforme</t>
         </is>
       </c>
-      <c r="C21" s="5" t="inlineStr">
+      <c r="C22" s="5" t="inlineStr">
         <is>
           <t>cahier-disciplinaire</t>
         </is>
       </c>
-      <c r="D21" s="5" t="inlineStr">
+      <c r="D22" s="5" t="inlineStr">
         <is>
           <t>en-cours</t>
         </is>
       </c>
-      <c r="E21" s="5" t="n">
+      <c r="E22" s="5" t="n">
         <v>23</v>
       </c>
-      <c r="F21" s="5" t="n">
+      <c r="F22" s="5" t="n">
         <v>23</v>
       </c>
-      <c r="G21" s="5" t="n">
+      <c r="G22" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="H21" s="5" t="inlineStr">
+      <c r="H22" s="5" t="inlineStr">
         <is>
           <t>Établir sous quel régime juridique NEMO IMS peut exister, ce que le droit positif lui interdit aujourd'hui, et par quelles voies ce droit devrait évoluer pour le rendre possible — la question n'étant pas seulement la conformité du dispositif au droit, mais l'évolution du droit avec lui</t>
         </is>
       </c>
-      <c r="I21" s="5" t="inlineStr">
+      <c r="I22" s="5" t="inlineStr">
         <is>
           <t>falsifieur — F4, seul falsifieur du corpus sans livre depuis l'établissement de la table de routage | objection — L1.C27 § 4 : le livre affirme que l'équivalence stricte « garantit sa conformité aux règles du commerce international », et l'affirmation n'est pas instruite | verrou — articles 123 et 130 du traité sur le fonctionnement de l'Union européenne, que L1.C18 § 6 déclare à trancher AVANT tout exposé du mécanisme d'émission | manque — L7.C01 et L7.C03 : le corpus ne tient AUCUNE source de droit international public, et c'est une lacune de nature différente de celles du Livre 11, qui étaient économiques</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>L21</t>
+        </is>
+      </c>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>La plomberie financière mondiale</t>
+        </is>
+      </c>
+      <c r="C23" s="3" t="inlineStr">
+        <is>
+          <t>cahier-disciplinaire</t>
+        </is>
+      </c>
+      <c r="D23" s="3" t="inlineStr">
+        <is>
+          <t>candidat</t>
+        </is>
+      </c>
+      <c r="E23" s="3" t="inlineStr">
+        <is>
+          <t>non contraignant</t>
+        </is>
+      </c>
+      <c r="F23" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G23" s="3" t="inlineStr"/>
+      <c r="H23" s="3" t="inlineStr">
+        <is>
+          <t>Comprendre comment les paiements, titres, garanties et devises circulent réellement — par quels bilans et quelles infrastructures une transaction mondiale devient-elle définitive</t>
+        </is>
+      </c>
+      <c r="I23" s="3" t="inlineStr">
+        <is>
+          <t>discipline — infrastructures de marché : messagerie, compensation, règlement, dépositaires, contreparties centrales | manque — L5.C02 a instruit SEPT des vingt-quatre principes du PFMI et le corpus n'a ouvert aucune infrastructure existante : ni coût, ni délai, ni volume d'équilibre | objection — L5.C09 : l'infrastructure fournit le rail de la séquence d'entrée, et le corpus ne sait pas où l'unité s'y logerait</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>L22</t>
+        </is>
+      </c>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>Le pouvoir de la finance non bancaire</t>
+        </is>
+      </c>
+      <c r="C24" s="3" t="inlineStr">
+        <is>
+          <t>cahier-disciplinaire</t>
+        </is>
+      </c>
+      <c r="D24" s="3" t="inlineStr">
+        <is>
+          <t>candidat</t>
+        </is>
+      </c>
+      <c r="E24" s="3" t="inlineStr">
+        <is>
+          <t>non contraignant</t>
+        </is>
+      </c>
+      <c r="F24" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G24" s="3" t="inlineStr"/>
+      <c r="H24" s="3" t="inlineStr">
+        <is>
+          <t>Étudier ceux qui allouent le capital hors du crédit bancaire classique — qui décide de l'allocation du capital lorsqu'il ne s'agit plus principalement des banques</t>
+        </is>
+      </c>
+      <c r="I24" s="3" t="inlineStr">
+        <is>
+          <t>discipline — gestion d'actifs, fonds de pension, assureurs, fonds souverains, fonds monétaires, fonds spéculatifs, capital-investissement, crédit privé | manque — le corpus raisonne sur les banques et les États, et n'a jamais instruit l'acteur qui détient environ la moitié des actifs financiers mondiaux | objection — L5.C09 : la protection de l'entrée expire quand la couche déplace des flux, et le corpus ne sait pas qui réagirait ni comment</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>L23</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>Fiscalité mondiale, finance offshore et opacité</t>
+        </is>
+      </c>
+      <c r="C25" s="3" t="inlineStr">
+        <is>
+          <t>cahier-disciplinaire</t>
+        </is>
+      </c>
+      <c r="D25" s="3" t="inlineStr">
+        <is>
+          <t>candidat</t>
+        </is>
+      </c>
+      <c r="E25" s="3" t="inlineStr">
+        <is>
+          <t>non contraignant</t>
+        </is>
+      </c>
+      <c r="F25" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G25" s="3" t="inlineStr"/>
+      <c r="H25" s="3" t="inlineStr">
+        <is>
+          <t>Examiner qui peut lever le reflux et comment les capitaux peuvent l'éviter — au nom de quelle compétence, avec quels moyens de contrôle, et contre quels mécanismes de contournement</t>
+        </is>
+      </c>
+      <c r="I25" s="3" t="inlineStr">
+        <is>
+          <t>arbitrage — A35 : la fonte est levée sur les agents, et le corpus n'a jamais dit QUI LA LÈVE NI DE QUEL TITRE | manque — l'ANCRAGE FISCAL, constaté et reporté par arbitrage le 2026-09-04, dont ce livre est la résolution : le registre avait retenu le livre propre comme recommandation | objection — L10.C06 pose un arbre de qualification à six branches et huit critères, et le corpus n'en tient aucun</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>L24</t>
+        </is>
+      </c>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>Les conditions matérielles de la vie</t>
+        </is>
+      </c>
+      <c r="C26" s="3" t="inlineStr">
+        <is>
+          <t>cahier-disciplinaire</t>
+        </is>
+      </c>
+      <c r="D26" s="3" t="inlineStr">
+        <is>
+          <t>candidat</t>
+        </is>
+      </c>
+      <c r="E26" s="3" t="inlineStr">
+        <is>
+          <t>non contraignant</t>
+        </is>
+      </c>
+      <c r="F26" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G26" s="3" t="inlineStr"/>
+      <c r="H26" s="3" t="inlineStr">
+        <is>
+          <t>Donner au corpus son socle biophysique complet — établir CE QUI DOIT ÊTRE MAINTENU et QUELS SEUILS NE PEUVENT PAS ÊTRE COMPENSÉS FINANCIÈREMENT</t>
+        </is>
+      </c>
+      <c r="I26" s="3" t="inlineStr">
+        <is>
+          <t>discipline — climat, biodiversité, eau, sols, cycles de l'azote et du phosphore, énergie, minerais, alimentation, dépendances matérielles | manque — L18 explique COMMENT MESURER ; aucun livre ne dit CE QU'IL FAUT MAINTENIR, et L5.C08 raisonne sur des catégories vides | objection — L18.C04 : la transition exige plus de trois milliards de tonnes de minéraux, et le corpus ne tient aucune nomenclature d'activités</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>L25</t>
+        </is>
+      </c>
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>Répartition, besoins essentiels et justice sociale</t>
+        </is>
+      </c>
+      <c r="C27" s="3" t="inlineStr">
+        <is>
+          <t>cahier-disciplinaire</t>
+        </is>
+      </c>
+      <c r="D27" s="3" t="inlineStr">
+        <is>
+          <t>candidat</t>
+        </is>
+      </c>
+      <c r="E27" s="3" t="inlineStr">
+        <is>
+          <t>non contraignant</t>
+        </is>
+      </c>
+      <c r="F27" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G27" s="3" t="inlineStr"/>
+      <c r="H27" s="3" t="inlineStr">
+        <is>
+          <t>Tester qui paie réellement le dispositif et qui reçoit ses bénéfices — ménages, revenus, patrimoine, accès aux besoins essentiels, services publics, inégalités territoriales, travail de soin, acceptabilité politique</t>
+        </is>
+      </c>
+      <c r="I27" s="3" t="inlineStr">
+        <is>
+          <t>objection — L11.C09 a découvert la question de l'incidence sans pouvoir la traiter, et A35 la rend décisive : la fonte est modulée par la décision de chacun | arbitrage — A34 : un barème qui dit vrai EXCLUT CEUX QUI NE PEUVENT PAS PAYER, et l'exclusion est maximale là où le signal doit être le plus fort | manque — L5.C09 a enregistré comme un MANQUEMENT que la contrainte de rédaction exigeait des coûts humains et qu'aucun chapitre n'en produit</t>
         </is>
       </c>
     </row>
@@ -15644,7 +15890,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B17"/>
+  <dimension ref="A1:B18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="52" customWidth="1" min="1" max="1"/>
@@ -15682,7 +15928,7 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>20</v>
+        <v>26</v>
       </c>
     </row>
     <row r="4">
@@ -15702,7 +15948,7 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
     </row>
     <row r="6">
@@ -15767,7 +16013,7 @@
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>L0, L9, L12, L13, L14, L15, L16, L17</t>
+          <t>L0, L9, L12, L13, L14, L15, L16, L17, L19, L21, L22, L23, L24, L25</t>
         </is>
       </c>
     </row>
@@ -15778,46 +16024,58 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>L19 : matricule NON DÉCLARÉ, réservé par la règle 3 du registre</t>
+          <t>Matricules réservés, sans chapitre écrit</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>prochain numéro libre</t>
+          <t>déclarés au registre</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>Rappel de la règle du matricule (convention § 3)</t>
+          <t>Prochain matricule disponible pour un livre nouveau</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>jamais réattribué, jamais renuméroté</t>
+          <t>26</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>Autorité en cas d'écart registre / plan directeur</t>
+          <t>Rappel de la règle du matricule (convention § 3)</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>le plan directeur tranche</t>
+          <t>jamais réattribué, jamais renuméroté</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
+          <t>Autorité en cas d'écart registre / plan directeur</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>le plan directeur tranche</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
           <t>Source de ce classeur</t>
         </is>
       </c>
-      <c r="B17" s="3" t="inlineStr">
+      <c r="B18" s="3" t="inlineStr">
         <is>
           <t>corpus/livres.yaml + en-têtes YAML des chapitres</t>
         </is>
@@ -15834,7 +16092,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C256"/>
+  <dimension ref="A1:C268"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -19725,63 +19983,55 @@
     <row r="233">
       <c r="A233" s="6" t="inlineStr">
         <is>
+          <t>L19</t>
+        </is>
+      </c>
+      <c r="B233" s="6" t="inlineStr">
+        <is>
+          <t>Comptabilité monétaire de l'émission sans dette</t>
+        </is>
+      </c>
+      <c r="C233" s="6" t="inlineStr">
+        <is>
+          <t>reserve — 0 chapitre(s)</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" s="7" t="inlineStr"/>
+      <c r="B234" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    (aucun chapitre écrit)</t>
+        </is>
+      </c>
+      <c r="C234" s="7" t="inlineStr"/>
+    </row>
+    <row r="235">
+      <c r="A235" s="6" t="inlineStr">
+        <is>
           <t>L20</t>
         </is>
       </c>
-      <c r="B233" s="6" t="inlineStr">
+      <c r="B235" s="6" t="inlineStr">
         <is>
           <t>Droit international public, droit monétaire et commercial de la réforme</t>
         </is>
       </c>
-      <c r="C233" s="6" t="inlineStr">
+      <c r="C235" s="6" t="inlineStr">
         <is>
           <t>en-cours — 23 chapitre(s)</t>
-        </is>
-      </c>
-    </row>
-    <row r="234">
-      <c r="A234" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    L20.C01</t>
-        </is>
-      </c>
-      <c r="B234" s="3" t="inlineStr">
-        <is>
-          <t>Ce que ce livre doit établir</t>
-        </is>
-      </c>
-      <c r="C234" s="3" t="inlineStr">
-        <is>
-          <t>brouillon</t>
-        </is>
-      </c>
-    </row>
-    <row r="235">
-      <c r="A235" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    L20.C02</t>
-        </is>
-      </c>
-      <c r="B235" s="3" t="inlineStr">
-        <is>
-          <t>L'interdiction du financement monétaire</t>
-        </is>
-      </c>
-      <c r="C235" s="3" t="inlineStr">
-        <is>
-          <t>brouillon</t>
         </is>
       </c>
     </row>
     <row r="236">
       <c r="A236" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L20.C03</t>
+          <t xml:space="preserve">    L20.C01</t>
         </is>
       </c>
       <c r="B236" s="3" t="inlineStr">
         <is>
-          <t>L'objectif principal et ce qu'il exclut</t>
+          <t>Ce que ce livre doit établir</t>
         </is>
       </c>
       <c r="C236" s="3" t="inlineStr">
@@ -19793,12 +20043,12 @@
     <row r="237">
       <c r="A237" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L20.C04</t>
+          <t xml:space="preserve">    L20.C02</t>
         </is>
       </c>
       <c r="B237" s="3" t="inlineStr">
         <is>
-          <t>L'indépendance, et à l'égard de qui</t>
+          <t>L'interdiction du financement monétaire</t>
         </is>
       </c>
       <c r="C237" s="3" t="inlineStr">
@@ -19810,12 +20060,12 @@
     <row r="238">
       <c r="A238" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L20.C05</t>
+          <t xml:space="preserve">    L20.C03</t>
         </is>
       </c>
       <c r="B238" s="3" t="inlineStr">
         <is>
-          <t>Le monopole d'émission et le cours légal</t>
+          <t>L'objectif principal et ce qu'il exclut</t>
         </is>
       </c>
       <c r="C238" s="3" t="inlineStr">
@@ -19827,12 +20077,12 @@
     <row r="239">
       <c r="A239" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L20.C06</t>
+          <t xml:space="preserve">    L20.C04</t>
         </is>
       </c>
       <c r="B239" s="3" t="inlineStr">
         <is>
-          <t>Les voies de révision et leur coût</t>
+          <t>L'indépendance, et à l'égard de qui</t>
         </is>
       </c>
       <c r="C239" s="3" t="inlineStr">
@@ -19844,12 +20094,12 @@
     <row r="240">
       <c r="A240" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L20.C07</t>
+          <t xml:space="preserve">    L20.C05</t>
         </is>
       </c>
       <c r="B240" s="3" t="inlineStr">
         <is>
-          <t>L'accord monétaire international</t>
+          <t>Le monopole d'émission et le cours légal</t>
         </is>
       </c>
       <c r="C240" s="3" t="inlineStr">
@@ -19861,12 +20111,12 @@
     <row r="241">
       <c r="A241" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L20.C08</t>
+          <t xml:space="preserve">    L20.C06</t>
         </is>
       </c>
       <c r="B241" s="3" t="inlineStr">
         <is>
-          <t>La parité inscrite dans le traité</t>
+          <t>Les voies de révision et leur coût</t>
         </is>
       </c>
       <c r="C241" s="3" t="inlineStr">
@@ -19878,12 +20128,12 @@
     <row r="242">
       <c r="A242" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L20.C09</t>
+          <t xml:space="preserve">    L20.C07</t>
         </is>
       </c>
       <c r="B242" s="3" t="inlineStr">
         <is>
-          <t>L'amendement des statuts du Fonds</t>
+          <t>L'accord monétaire international</t>
         </is>
       </c>
       <c r="C242" s="3" t="inlineStr">
@@ -19895,12 +20145,12 @@
     <row r="243">
       <c r="A243" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L20.C10</t>
+          <t xml:space="preserve">    L20.C08</t>
         </is>
       </c>
       <c r="B243" s="3" t="inlineStr">
         <is>
-          <t>Le vote pondéré et les voix de base</t>
+          <t>La parité inscrite dans le traité</t>
         </is>
       </c>
       <c r="C243" s="3" t="inlineStr">
@@ -19912,12 +20162,12 @@
     <row r="244">
       <c r="A244" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L20.C11</t>
+          <t xml:space="preserve">    L20.C09</t>
         </is>
       </c>
       <c r="B244" s="3" t="inlineStr">
         <is>
-          <t>La personnalité juridique et les immunités</t>
+          <t>L'amendement des statuts du Fonds</t>
         </is>
       </c>
       <c r="C244" s="3" t="inlineStr">
@@ -19929,12 +20179,12 @@
     <row r="245">
       <c r="A245" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L20.C12</t>
+          <t xml:space="preserve">    L20.C10</t>
         </is>
       </c>
       <c r="B245" s="3" t="inlineStr">
         <is>
-          <t>Les pouvoirs non délégables</t>
+          <t>Le vote pondéré et les voix de base</t>
         </is>
       </c>
       <c r="C245" s="3" t="inlineStr">
@@ -19946,12 +20196,12 @@
     <row r="246">
       <c r="A246" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L20.C13</t>
+          <t xml:space="preserve">    L20.C11</t>
         </is>
       </c>
       <c r="B246" s="3" t="inlineStr">
         <is>
-          <t>L'entrée en vigueur, l'adhésion et le retrait</t>
+          <t>La personnalité juridique et les immunités</t>
         </is>
       </c>
       <c r="C246" s="3" t="inlineStr">
@@ -19963,12 +20213,12 @@
     <row r="247">
       <c r="A247" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L20.C14</t>
+          <t xml:space="preserve">    L20.C12</t>
         </is>
       </c>
       <c r="B247" s="3" t="inlineStr">
         <is>
-          <t>Qui interprète le traité</t>
+          <t>Les pouvoirs non délégables</t>
         </is>
       </c>
       <c r="C247" s="3" t="inlineStr">
@@ -19980,12 +20230,12 @@
     <row r="248">
       <c r="A248" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L20.C15</t>
+          <t xml:space="preserve">    L20.C13</t>
         </is>
       </c>
       <c r="B248" s="3" t="inlineStr">
         <is>
-          <t>Le devoir international des agents</t>
+          <t>L'entrée en vigueur, l'adhésion et le retrait</t>
         </is>
       </c>
       <c r="C248" s="3" t="inlineStr">
@@ -19997,12 +20247,12 @@
     <row r="249">
       <c r="A249" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L20.C16</t>
+          <t xml:space="preserve">    L20.C14</t>
         </is>
       </c>
       <c r="B249" s="3" t="inlineStr">
         <is>
-          <t>Le patrimoine commun de l'humanité</t>
+          <t>Qui interprète le traité</t>
         </is>
       </c>
       <c r="C249" s="3" t="inlineStr">
@@ -20014,12 +20264,12 @@
     <row r="250">
       <c r="A250" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L20.C17</t>
+          <t xml:space="preserve">    L20.C15</t>
         </is>
       </c>
       <c r="B250" s="3" t="inlineStr">
         <is>
-          <t>La sanctuarisation, et elle existe</t>
+          <t>Le devoir international des agents</t>
         </is>
       </c>
       <c r="C250" s="3" t="inlineStr">
@@ -20031,12 +20281,12 @@
     <row r="251">
       <c r="A251" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L20.C18</t>
+          <t xml:space="preserve">    L20.C16</t>
         </is>
       </c>
       <c r="B251" s="3" t="inlineStr">
         <is>
-          <t>L'amendement et la dérogation dans l'ordre commercial</t>
+          <t>Le patrimoine commun de l'humanité</t>
         </is>
       </c>
       <c r="C251" s="3" t="inlineStr">
@@ -20048,12 +20298,12 @@
     <row r="252">
       <c r="A252" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L20.C19</t>
+          <t xml:space="preserve">    L20.C17</t>
         </is>
       </c>
       <c r="B252" s="3" t="inlineStr">
         <is>
-          <t>Le texte que la conformité invoque</t>
+          <t>La sanctuarisation, et elle existe</t>
         </is>
       </c>
       <c r="C252" s="3" t="inlineStr">
@@ -20065,12 +20315,12 @@
     <row r="253">
       <c r="A253" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L20.C20</t>
+          <t xml:space="preserve">    L20.C18</t>
         </is>
       </c>
       <c r="B253" s="3" t="inlineStr">
         <is>
-          <t>L'ajustement aux frontières comme précédent</t>
+          <t>L'amendement et la dérogation dans l'ordre commercial</t>
         </is>
       </c>
       <c r="C253" s="3" t="inlineStr">
@@ -20082,12 +20332,12 @@
     <row r="254">
       <c r="A254" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L20.C21</t>
+          <t xml:space="preserve">    L20.C19</t>
         </is>
       </c>
       <c r="B254" s="3" t="inlineStr">
         <is>
-          <t>La transparence et sa limite juridictionnelle</t>
+          <t>Le texte que la conformité invoque</t>
         </is>
       </c>
       <c r="C254" s="3" t="inlineStr">
@@ -20099,12 +20349,12 @@
     <row r="255">
       <c r="A255" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L20.C22</t>
+          <t xml:space="preserve">    L20.C20</t>
         </is>
       </c>
       <c r="B255" s="3" t="inlineStr">
         <is>
-          <t>Ce que le droit devrait devenir</t>
+          <t>L'ajustement aux frontières comme précédent</t>
         </is>
       </c>
       <c r="C255" s="3" t="inlineStr">
@@ -20116,19 +20366,183 @@
     <row r="256">
       <c r="A256" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">    L20.C21</t>
+        </is>
+      </c>
+      <c r="B256" s="3" t="inlineStr">
+        <is>
+          <t>La transparence et sa limite juridictionnelle</t>
+        </is>
+      </c>
+      <c r="C256" s="3" t="inlineStr">
+        <is>
+          <t>brouillon</t>
+        </is>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    L20.C22</t>
+        </is>
+      </c>
+      <c r="B257" s="3" t="inlineStr">
+        <is>
+          <t>Ce que le droit devrait devenir</t>
+        </is>
+      </c>
+      <c r="C257" s="3" t="inlineStr">
+        <is>
+          <t>brouillon</t>
+        </is>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">    L20.C23</t>
         </is>
       </c>
-      <c r="B256" s="3" t="inlineStr">
+      <c r="B258" s="3" t="inlineStr">
         <is>
           <t>La portée du livre</t>
         </is>
       </c>
-      <c r="C256" s="3" t="inlineStr">
-        <is>
-          <t>brouillon</t>
-        </is>
-      </c>
+      <c r="C258" s="3" t="inlineStr">
+        <is>
+          <t>brouillon</t>
+        </is>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" s="6" t="inlineStr">
+        <is>
+          <t>L21</t>
+        </is>
+      </c>
+      <c r="B259" s="6" t="inlineStr">
+        <is>
+          <t>La plomberie financière mondiale</t>
+        </is>
+      </c>
+      <c r="C259" s="6" t="inlineStr">
+        <is>
+          <t>candidat — 0 chapitre(s)</t>
+        </is>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" s="7" t="inlineStr"/>
+      <c r="B260" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    (aucun chapitre écrit)</t>
+        </is>
+      </c>
+      <c r="C260" s="7" t="inlineStr"/>
+    </row>
+    <row r="261">
+      <c r="A261" s="6" t="inlineStr">
+        <is>
+          <t>L22</t>
+        </is>
+      </c>
+      <c r="B261" s="6" t="inlineStr">
+        <is>
+          <t>Le pouvoir de la finance non bancaire</t>
+        </is>
+      </c>
+      <c r="C261" s="6" t="inlineStr">
+        <is>
+          <t>candidat — 0 chapitre(s)</t>
+        </is>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" s="7" t="inlineStr"/>
+      <c r="B262" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    (aucun chapitre écrit)</t>
+        </is>
+      </c>
+      <c r="C262" s="7" t="inlineStr"/>
+    </row>
+    <row r="263">
+      <c r="A263" s="6" t="inlineStr">
+        <is>
+          <t>L23</t>
+        </is>
+      </c>
+      <c r="B263" s="6" t="inlineStr">
+        <is>
+          <t>Fiscalité mondiale, finance offshore et opacité</t>
+        </is>
+      </c>
+      <c r="C263" s="6" t="inlineStr">
+        <is>
+          <t>candidat — 0 chapitre(s)</t>
+        </is>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" s="7" t="inlineStr"/>
+      <c r="B264" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    (aucun chapitre écrit)</t>
+        </is>
+      </c>
+      <c r="C264" s="7" t="inlineStr"/>
+    </row>
+    <row r="265">
+      <c r="A265" s="6" t="inlineStr">
+        <is>
+          <t>L24</t>
+        </is>
+      </c>
+      <c r="B265" s="6" t="inlineStr">
+        <is>
+          <t>Les conditions matérielles de la vie</t>
+        </is>
+      </c>
+      <c r="C265" s="6" t="inlineStr">
+        <is>
+          <t>candidat — 0 chapitre(s)</t>
+        </is>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" s="7" t="inlineStr"/>
+      <c r="B266" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    (aucun chapitre écrit)</t>
+        </is>
+      </c>
+      <c r="C266" s="7" t="inlineStr"/>
+    </row>
+    <row r="267">
+      <c r="A267" s="6" t="inlineStr">
+        <is>
+          <t>L25</t>
+        </is>
+      </c>
+      <c r="B267" s="6" t="inlineStr">
+        <is>
+          <t>Répartition, besoins essentiels et justice sociale</t>
+        </is>
+      </c>
+      <c r="C267" s="6" t="inlineStr">
+        <is>
+          <t>candidat — 0 chapitre(s)</t>
+        </is>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" s="7" t="inlineStr"/>
+      <c r="B268" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    (aucun chapitre écrit)</t>
+        </is>
+      </c>
+      <c r="C268" s="7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/plan-des-livres.xlsx
+++ b/plan-des-livres.xlsx
@@ -13,7 +13,7 @@
     <sheet name="Plan par livre" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Chapitres'!$A$1:$N$242</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Chapitres'!$A$1:$N$243</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I27"/>
+  <dimension ref="A1:I28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -1586,6 +1586,47 @@
         </is>
       </c>
     </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>L26</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>Thermodynamique, énergie et processus économique</t>
+        </is>
+      </c>
+      <c r="C28" s="3" t="inlineStr">
+        <is>
+          <t>cahier-disciplinaire</t>
+        </is>
+      </c>
+      <c r="D28" s="3" t="inlineStr">
+        <is>
+          <t>candidat</t>
+        </is>
+      </c>
+      <c r="E28" s="3" t="inlineStr">
+        <is>
+          <t>non contraignant</t>
+        </is>
+      </c>
+      <c r="F28" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G28" s="3" t="inlineStr"/>
+      <c r="H28" s="3" t="inlineStr">
+        <is>
+          <t>Établir ce que les lois de la thermodynamique imposent à un processus économique, et ce qu'elles interdisent à toute conception monétaire qui prétend régénérer — la question n'étant pas ce que le dispositif coûte, mais ce que l'énergie et la matière rendent possible</t>
+        </is>
+      </c>
+      <c r="I28" s="3" t="inlineStr">
+        <is>
+          <t>manque — `entropie` figure au vocabulaire depuis la première occurrence L1.C03 et AUCUN LIVRE NE LE PORTE ; le concept est employé dans six chapitres du Livre 1 et un du Livre 2, sans instruction | discipline — économie biophysique : Georgescu-Roegen, analyse énergétique, retour énergétique sur investissement, exergie, dissipation | objection — L18.C04 : aucune preuve de découplage absolu généralisé n'est observée, et le corpus ne sait pas si l'obstacle est économique ou THERMODYNAMIQUE | objection — `effet_rebond` et `jevons_monetaire` sont au vocabulaire ; le corpus les invoque sans tenir l'argument physique qui les fonde</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1597,7 +1638,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N242"/>
+  <dimension ref="A1:N243"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -16948,8 +16989,68 @@
         </is>
       </c>
     </row>
+    <row r="243">
+      <c r="A243" s="2" t="inlineStr">
+        <is>
+          <t>L26.C01</t>
+        </is>
+      </c>
+      <c r="B243" s="3" t="inlineStr">
+        <is>
+          <t>L26</t>
+        </is>
+      </c>
+      <c r="C243" s="3" t="inlineStr">
+        <is>
+          <t>Ce que ce livre doit établir</t>
+        </is>
+      </c>
+      <c r="D243" s="3" t="inlineStr">
+        <is>
+          <t>brouillon</t>
+        </is>
+      </c>
+      <c r="E243" s="3" t="inlineStr">
+        <is>
+          <t>preparatoire</t>
+        </is>
+      </c>
+      <c r="F243" s="3" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="G243" s="3" t="inlineStr">
+        <is>
+          <t>descriptif</t>
+        </is>
+      </c>
+      <c r="H243" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="I243" s="3" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="J243" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="K243" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="L243" s="3" t="inlineStr"/>
+      <c r="M243" s="3" t="inlineStr"/>
+      <c r="N243" s="3" t="inlineStr">
+        <is>
+          <t>corpus/livre-26-thermodynamique-et-processus-economique/c01-ce-que-ce-livre-doit-etablir.md</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:N242"/>
+  <autoFilter ref="A1:N243"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -16998,7 +17099,7 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="4">
@@ -17018,7 +17119,7 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="6">
@@ -17028,7 +17129,7 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>241</v>
+        <v>242</v>
       </c>
     </row>
     <row r="7">
@@ -17038,7 +17139,7 @@
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="8">
@@ -17058,7 +17159,7 @@
         </is>
       </c>
       <c r="B9" s="3" t="n">
-        <v>232</v>
+        <v>233</v>
       </c>
     </row>
     <row r="10">
@@ -17078,7 +17179,7 @@
         </is>
       </c>
       <c r="B11" s="3" t="n">
-        <v>1171</v>
+        <v>1173</v>
       </c>
     </row>
     <row r="12">
@@ -17088,7 +17189,7 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>965</v>
+        <v>966</v>
       </c>
     </row>
     <row r="13">
@@ -17103,7 +17204,7 @@
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>L0, L9, L12, L13, L14, L15, L16, L17, L19, L21, L22, L23, L24, L25</t>
+          <t>L0, L9, L12, L13, L14, L15, L16, L17, L19, L21, L22, L23, L24, L25, L26</t>
         </is>
       </c>
     </row>
@@ -17119,7 +17220,7 @@
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>27</t>
         </is>
       </c>
     </row>
@@ -17182,7 +17283,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C268"/>
+  <dimension ref="A1:C270"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -21746,6 +21847,40 @@
         </is>
       </c>
     </row>
+    <row r="269">
+      <c r="A269" s="6" t="inlineStr">
+        <is>
+          <t>L26</t>
+        </is>
+      </c>
+      <c r="B269" s="6" t="inlineStr">
+        <is>
+          <t>Thermodynamique, énergie et processus économique</t>
+        </is>
+      </c>
+      <c r="C269" s="6" t="inlineStr">
+        <is>
+          <t>candidat — AMORCE SEULE</t>
+        </is>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    L26.C01</t>
+        </is>
+      </c>
+      <c r="B270" s="3" t="inlineStr">
+        <is>
+          <t>[AMORCE] Ce que ce livre doit établir</t>
+        </is>
+      </c>
+      <c r="C270" s="3" t="inlineStr">
+        <is>
+          <t>brouillon</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/plan-des-livres.xlsx
+++ b/plan-des-livres.xlsx
@@ -1623,7 +1623,7 @@
       </c>
       <c r="I28" s="3" t="inlineStr">
         <is>
-          <t>manque — `entropie` figure au vocabulaire depuis la première occurrence L1.C03 et AUCUN LIVRE NE LE PORTE ; le concept est employé dans six chapitres du Livre 1 et un du Livre 2, sans instruction | discipline — économie biophysique : Georgescu-Roegen, analyse énergétique, retour énergétique sur investissement, exergie, dissipation | objection — L18.C04 : aucune preuve de découplage absolu généralisé n'est observée, et le corpus ne sait pas si l'obstacle est économique ou THERMODYNAMIQUE | objection — `effet_rebond` et `jevons_monetaire` sont au vocabulaire ; le corpus les invoque sans tenir l'argument physique qui les fonde</t>
+          <t>manque — `entropie` figure au vocabulaire depuis la première occurrence L1.C03 et AUCUN LIVRE NE LE PORTE ; le concept est employé dans six chapitres du Livre 1 et un du Livre 2, sans instruction | discipline — économie biophysique : Georgescu-Roegen, analyse énergétique, retour énergétique sur investissement, exergie, dissipation | objection — L18.C04 : aucune preuve de découplage absolu généralisé n'est observée, et le corpus ne sait pas si l'obstacle est économique ou THERMODYNAMIQUE | objection — `effet_rebond` et `jevons_monetaire` sont au vocabulaire ; le corpus les invoque sans tenir l'argument physique qui les fonde | falsifieur — F11, LA CONTRAINTE PHYSIQUE, posé le 2026-09-07 sur arbitrage de l'auteur : ce livre est le seul qui puisse l'établir ou le réfuter</t>
         </is>
       </c>
     </row>

--- a/plan-des-livres.xlsx
+++ b/plan-des-livres.xlsx
@@ -1464,41 +1464,41 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="2" t="inlineStr">
+      <c r="A25" s="4" t="inlineStr">
         <is>
           <t>L23</t>
         </is>
       </c>
-      <c r="B25" s="3" t="inlineStr">
+      <c r="B25" s="5" t="inlineStr">
         <is>
           <t>Fiscalité mondiale, finance offshore et opacité</t>
         </is>
       </c>
-      <c r="C25" s="3" t="inlineStr">
+      <c r="C25" s="5" t="inlineStr">
         <is>
           <t>cahier-disciplinaire</t>
         </is>
       </c>
-      <c r="D25" s="3" t="inlineStr">
-        <is>
-          <t>candidat</t>
-        </is>
-      </c>
-      <c r="E25" s="3" t="inlineStr">
+      <c r="D25" s="5" t="inlineStr">
+        <is>
+          <t>en-cours</t>
+        </is>
+      </c>
+      <c r="E25" s="5" t="inlineStr">
         <is>
           <t>non contraignant</t>
         </is>
       </c>
-      <c r="F25" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G25" s="3" t="inlineStr"/>
-      <c r="H25" s="3" t="inlineStr">
+      <c r="F25" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G25" s="5" t="inlineStr"/>
+      <c r="H25" s="5" t="inlineStr">
         <is>
           <t>Examiner qui peut lever le reflux et comment les capitaux peuvent l'éviter — au nom de quelle compétence, avec quels moyens de contrôle, et contre quels mécanismes de contournement</t>
         </is>
       </c>
-      <c r="I25" s="3" t="inlineStr">
+      <c r="I25" s="5" t="inlineStr">
         <is>
           <t>arbitrage — A35 : la fonte est levée sur les agents, et le corpus n'a jamais dit QUI LA LÈVE NI DE QUEL TITRE | manque — l'ANCRAGE FISCAL, constaté et reporté par arbitrage le 2026-09-04, dont ce livre est la résolution : le registre avait retenu le livre propre comme recommandation | objection — L10.C06 pose un arbre de qualification à six branches et huit critères, et le corpus n'en tient aucun</t>
         </is>
@@ -16842,7 +16842,7 @@
       </c>
       <c r="G240" s="3" t="inlineStr">
         <is>
-          <t>descriptif</t>
+          <t>conception</t>
         </is>
       </c>
       <c r="H240" s="3" t="inlineStr">
@@ -16850,19 +16850,23 @@
           <t>2026-09-07</t>
         </is>
       </c>
-      <c r="I240" s="3" t="inlineStr">
-        <is>
-          <t>oui</t>
-        </is>
-      </c>
+      <c r="I240" s="3" t="inlineStr"/>
       <c r="J240" s="3" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K240" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="L240" s="3" t="inlineStr"/>
-      <c r="M240" s="3" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="L240" s="3" t="inlineStr">
+        <is>
+          <t>bareme, reflux_transactionnel, externalisation, essentiel_insolvable, polycentricite, regle_contre_discretion</t>
+        </is>
+      </c>
+      <c r="M240" s="3" t="inlineStr">
+        <is>
+          <t>L1.C15, L5.C07, L10.C06, L11.C05, L11.C09, L11.C21, L11.C24, L18.C09, L20.C02, L20.C20</t>
+        </is>
+      </c>
       <c r="N240" s="3" t="inlineStr">
         <is>
           <t>corpus/livre-23-fiscalite-mondiale-et-opacite/c01-ce-que-ce-livre-doit-etablir.md</t>
@@ -17109,7 +17113,7 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="5">
@@ -17119,7 +17123,7 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="6">
@@ -17139,7 +17143,7 @@
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="8">
@@ -17149,7 +17153,7 @@
         </is>
       </c>
       <c r="B8" s="3" t="n">
-        <v>227</v>
+        <v>228</v>
       </c>
     </row>
     <row r="9">
@@ -17179,7 +17183,7 @@
         </is>
       </c>
       <c r="B11" s="3" t="n">
-        <v>1173</v>
+        <v>1174</v>
       </c>
     </row>
     <row r="12">
@@ -17189,7 +17193,7 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>966</v>
+        <v>969</v>
       </c>
     </row>
     <row r="13">
@@ -17204,7 +17208,7 @@
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>L0, L9, L12, L13, L14, L15, L16, L17, L19, L21, L22, L23, L24, L25, L26</t>
+          <t>L0, L9, L12, L13, L14, L15, L16, L17, L19, L21, L22, L24, L25, L26</t>
         </is>
       </c>
     </row>
@@ -21758,7 +21762,7 @@
       </c>
       <c r="C263" s="6" t="inlineStr">
         <is>
-          <t>candidat — AMORCE SEULE</t>
+          <t>en-cours — 1 chapitre(s)</t>
         </is>
       </c>
     </row>
@@ -21770,7 +21774,7 @@
       </c>
       <c r="B264" s="3" t="inlineStr">
         <is>
-          <t>[AMORCE] Ce que ce livre doit établir</t>
+          <t>Ce que ce livre doit établir</t>
         </is>
       </c>
       <c r="C264" s="3" t="inlineStr">

--- a/plan-des-livres.xlsx
+++ b/plan-des-livres.xlsx
@@ -13,7 +13,7 @@
     <sheet name="Plan par livre" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Chapitres'!$A$1:$N$243</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Chapitres'!$A$1:$N$244</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -1490,7 +1490,7 @@
         </is>
       </c>
       <c r="F25" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G25" s="5" t="inlineStr"/>
       <c r="H25" s="5" t="inlineStr">
@@ -1638,7 +1638,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N243"/>
+  <dimension ref="A1:N244"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -13683,7 +13683,7 @@
       </c>
       <c r="H190" s="3" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="I190" s="3" t="inlineStr"/>
@@ -16876,17 +16876,17 @@
     <row r="241">
       <c r="A241" s="2" t="inlineStr">
         <is>
-          <t>L24.C01</t>
+          <t>L23.C02</t>
         </is>
       </c>
       <c r="B241" s="3" t="inlineStr">
         <is>
-          <t>L24</t>
+          <t>L23</t>
         </is>
       </c>
       <c r="C241" s="3" t="inlineStr">
         <is>
-          <t>Ce que ce livre doit établir</t>
+          <t>La compétence que la convention ne crée pas, et le vote qu'elle a gagné</t>
         </is>
       </c>
       <c r="D241" s="3" t="inlineStr">
@@ -16906,7 +16906,7 @@
       </c>
       <c r="G241" s="3" t="inlineStr">
         <is>
-          <t>descriptif</t>
+          <t>hybride</t>
         </is>
       </c>
       <c r="H241" s="3" t="inlineStr">
@@ -16914,34 +16914,38 @@
           <t>2026-09-07</t>
         </is>
       </c>
-      <c r="I241" s="3" t="inlineStr">
-        <is>
-          <t>oui</t>
-        </is>
-      </c>
+      <c r="I241" s="3" t="inlineStr"/>
       <c r="J241" s="3" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K241" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="L241" s="3" t="inlineStr"/>
-      <c r="M241" s="3" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="L241" s="3" t="inlineStr">
+        <is>
+          <t>polycentricite, bareme, reflux_transactionnel, seuil_d_activation, regle_contre_discretion, externalisation</t>
+        </is>
+      </c>
+      <c r="M241" s="3" t="inlineStr">
+        <is>
+          <t>L1.C25, L5.C04, L10.C06, L11.C21, L20.C02, L20.C20, L23.C01</t>
+        </is>
+      </c>
       <c r="N241" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-24-conditions-materielles-de-la-vie/c01-ce-que-ce-livre-doit-etablir.md</t>
+          <t>corpus/livre-23-fiscalite-mondiale-et-opacite/c02-la-competence-que-la-convention-ne-cree-pas.md</t>
         </is>
       </c>
     </row>
     <row r="242">
       <c r="A242" s="2" t="inlineStr">
         <is>
-          <t>L25.C01</t>
+          <t>L24.C01</t>
         </is>
       </c>
       <c r="B242" s="3" t="inlineStr">
         <is>
-          <t>L25</t>
+          <t>L24</t>
         </is>
       </c>
       <c r="C242" s="3" t="inlineStr">
@@ -16989,19 +16993,19 @@
       <c r="M242" s="3" t="inlineStr"/>
       <c r="N242" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-25-repartition-et-justice-sociale/c01-ce-que-ce-livre-doit-etablir.md</t>
+          <t>corpus/livre-24-conditions-materielles-de-la-vie/c01-ce-que-ce-livre-doit-etablir.md</t>
         </is>
       </c>
     </row>
     <row r="243">
       <c r="A243" s="2" t="inlineStr">
         <is>
-          <t>L26.C01</t>
+          <t>L25.C01</t>
         </is>
       </c>
       <c r="B243" s="3" t="inlineStr">
         <is>
-          <t>L26</t>
+          <t>L25</t>
         </is>
       </c>
       <c r="C243" s="3" t="inlineStr">
@@ -17049,12 +17053,72 @@
       <c r="M243" s="3" t="inlineStr"/>
       <c r="N243" s="3" t="inlineStr">
         <is>
+          <t>corpus/livre-25-repartition-et-justice-sociale/c01-ce-que-ce-livre-doit-etablir.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" s="2" t="inlineStr">
+        <is>
+          <t>L26.C01</t>
+        </is>
+      </c>
+      <c r="B244" s="3" t="inlineStr">
+        <is>
+          <t>L26</t>
+        </is>
+      </c>
+      <c r="C244" s="3" t="inlineStr">
+        <is>
+          <t>Ce que ce livre doit établir</t>
+        </is>
+      </c>
+      <c r="D244" s="3" t="inlineStr">
+        <is>
+          <t>brouillon</t>
+        </is>
+      </c>
+      <c r="E244" s="3" t="inlineStr">
+        <is>
+          <t>preparatoire</t>
+        </is>
+      </c>
+      <c r="F244" s="3" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="G244" s="3" t="inlineStr">
+        <is>
+          <t>descriptif</t>
+        </is>
+      </c>
+      <c r="H244" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="I244" s="3" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="J244" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="K244" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="L244" s="3" t="inlineStr"/>
+      <c r="M244" s="3" t="inlineStr"/>
+      <c r="N244" s="3" t="inlineStr">
+        <is>
           <t>corpus/livre-26-thermodynamique-et-processus-economique/c01-ce-que-ce-livre-doit-etablir.md</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:N243"/>
+  <autoFilter ref="A1:N244"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -17133,7 +17197,7 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>242</v>
+        <v>243</v>
       </c>
     </row>
     <row r="7">
@@ -17153,7 +17217,7 @@
         </is>
       </c>
       <c r="B8" s="3" t="n">
-        <v>228</v>
+        <v>229</v>
       </c>
     </row>
     <row r="9">
@@ -17163,7 +17227,7 @@
         </is>
       </c>
       <c r="B9" s="3" t="n">
-        <v>233</v>
+        <v>234</v>
       </c>
     </row>
     <row r="10">
@@ -17183,7 +17247,7 @@
         </is>
       </c>
       <c r="B11" s="3" t="n">
-        <v>1174</v>
+        <v>1177</v>
       </c>
     </row>
     <row r="12">
@@ -17193,7 +17257,7 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>969</v>
+        <v>973</v>
       </c>
     </row>
     <row r="13">
@@ -17287,7 +17351,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C270"/>
+  <dimension ref="A1:C271"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -21762,7 +21826,7 @@
       </c>
       <c r="C263" s="6" t="inlineStr">
         <is>
-          <t>en-cours — 1 chapitre(s)</t>
+          <t>en-cours — 2 chapitre(s)</t>
         </is>
       </c>
     </row>
@@ -21784,102 +21848,119 @@
       </c>
     </row>
     <row r="265">
-      <c r="A265" s="6" t="inlineStr">
+      <c r="A265" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    L23.C02</t>
+        </is>
+      </c>
+      <c r="B265" s="3" t="inlineStr">
+        <is>
+          <t>La compétence que la convention ne crée pas, et le vote qu'elle a gagné</t>
+        </is>
+      </c>
+      <c r="C265" s="3" t="inlineStr">
+        <is>
+          <t>brouillon</t>
+        </is>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" s="6" t="inlineStr">
         <is>
           <t>L24</t>
         </is>
       </c>
-      <c r="B265" s="6" t="inlineStr">
+      <c r="B266" s="6" t="inlineStr">
         <is>
           <t>Les conditions matérielles de la vie</t>
         </is>
       </c>
-      <c r="C265" s="6" t="inlineStr">
+      <c r="C266" s="6" t="inlineStr">
         <is>
           <t>candidat — AMORCE SEULE</t>
         </is>
       </c>
     </row>
-    <row r="266">
-      <c r="A266" s="3" t="inlineStr">
+    <row r="267">
+      <c r="A267" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">    L24.C01</t>
         </is>
       </c>
-      <c r="B266" s="3" t="inlineStr">
+      <c r="B267" s="3" t="inlineStr">
         <is>
           <t>[AMORCE] Ce que ce livre doit établir</t>
         </is>
       </c>
-      <c r="C266" s="3" t="inlineStr">
-        <is>
-          <t>brouillon</t>
-        </is>
-      </c>
-    </row>
-    <row r="267">
-      <c r="A267" s="6" t="inlineStr">
+      <c r="C267" s="3" t="inlineStr">
+        <is>
+          <t>brouillon</t>
+        </is>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" s="6" t="inlineStr">
         <is>
           <t>L25</t>
         </is>
       </c>
-      <c r="B267" s="6" t="inlineStr">
+      <c r="B268" s="6" t="inlineStr">
         <is>
           <t>Répartition, besoins essentiels et justice sociale</t>
         </is>
       </c>
-      <c r="C267" s="6" t="inlineStr">
+      <c r="C268" s="6" t="inlineStr">
         <is>
           <t>candidat — AMORCE SEULE</t>
         </is>
       </c>
     </row>
-    <row r="268">
-      <c r="A268" s="3" t="inlineStr">
+    <row r="269">
+      <c r="A269" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">    L25.C01</t>
         </is>
       </c>
-      <c r="B268" s="3" t="inlineStr">
+      <c r="B269" s="3" t="inlineStr">
         <is>
           <t>[AMORCE] Ce que ce livre doit établir</t>
         </is>
       </c>
-      <c r="C268" s="3" t="inlineStr">
-        <is>
-          <t>brouillon</t>
-        </is>
-      </c>
-    </row>
-    <row r="269">
-      <c r="A269" s="6" t="inlineStr">
+      <c r="C269" s="3" t="inlineStr">
+        <is>
+          <t>brouillon</t>
+        </is>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" s="6" t="inlineStr">
         <is>
           <t>L26</t>
         </is>
       </c>
-      <c r="B269" s="6" t="inlineStr">
+      <c r="B270" s="6" t="inlineStr">
         <is>
           <t>Thermodynamique, énergie et processus économique</t>
         </is>
       </c>
-      <c r="C269" s="6" t="inlineStr">
+      <c r="C270" s="6" t="inlineStr">
         <is>
           <t>candidat — AMORCE SEULE</t>
         </is>
       </c>
     </row>
-    <row r="270">
-      <c r="A270" s="3" t="inlineStr">
+    <row r="271">
+      <c r="A271" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">    L26.C01</t>
         </is>
       </c>
-      <c r="B270" s="3" t="inlineStr">
+      <c r="B271" s="3" t="inlineStr">
         <is>
           <t>[AMORCE] Ce que ce livre doit établir</t>
         </is>
       </c>
-      <c r="C270" s="3" t="inlineStr">
+      <c r="C271" s="3" t="inlineStr">
         <is>
           <t>brouillon</t>
         </is>

--- a/plan-des-livres.xlsx
+++ b/plan-des-livres.xlsx
@@ -13,7 +13,7 @@
     <sheet name="Plan par livre" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Chapitres'!$A$1:$N$244</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Chapitres'!$A$1:$N$245</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -1490,7 +1490,7 @@
         </is>
       </c>
       <c r="F25" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G25" s="5" t="inlineStr"/>
       <c r="H25" s="5" t="inlineStr">
@@ -1638,7 +1638,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N244"/>
+  <dimension ref="A1:N245"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -16940,17 +16940,17 @@
     <row r="242">
       <c r="A242" s="2" t="inlineStr">
         <is>
-          <t>L24.C01</t>
+          <t>L23.C03</t>
         </is>
       </c>
       <c r="B242" s="3" t="inlineStr">
         <is>
-          <t>L24</t>
+          <t>L23</t>
         </is>
       </c>
       <c r="C242" s="3" t="inlineStr">
         <is>
-          <t>Ce que ce livre doit établir</t>
+          <t>F8 appliqué à une négociation en cours, et le résultat n'est pas le désarmement</t>
         </is>
       </c>
       <c r="D242" s="3" t="inlineStr">
@@ -16970,7 +16970,7 @@
       </c>
       <c r="G242" s="3" t="inlineStr">
         <is>
-          <t>descriptif</t>
+          <t>hybride</t>
         </is>
       </c>
       <c r="H242" s="3" t="inlineStr">
@@ -16978,34 +16978,38 @@
           <t>2026-09-07</t>
         </is>
       </c>
-      <c r="I242" s="3" t="inlineStr">
-        <is>
-          <t>oui</t>
-        </is>
-      </c>
+      <c r="I242" s="3" t="inlineStr"/>
       <c r="J242" s="3" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K242" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="L242" s="3" t="inlineStr"/>
-      <c r="M242" s="3" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="L242" s="3" t="inlineStr">
+        <is>
+          <t>regle_contre_discretion, polycentricite, seuil_d_activation, bareme, externalisation</t>
+        </is>
+      </c>
+      <c r="M242" s="3" t="inlineStr">
+        <is>
+          <t>L5.C04, L6.C09, L11.C21, L20.C02, L20.C13, L23.C01, L23.C02</t>
+        </is>
+      </c>
       <c r="N242" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-24-conditions-materielles-de-la-vie/c01-ce-que-ce-livre-doit-etablir.md</t>
+          <t>corpus/livre-23-fiscalite-mondiale-et-opacite/c03-f8-applique-a-une-negociation-en-cours.md</t>
         </is>
       </c>
     </row>
     <row r="243">
       <c r="A243" s="2" t="inlineStr">
         <is>
-          <t>L25.C01</t>
+          <t>L24.C01</t>
         </is>
       </c>
       <c r="B243" s="3" t="inlineStr">
         <is>
-          <t>L25</t>
+          <t>L24</t>
         </is>
       </c>
       <c r="C243" s="3" t="inlineStr">
@@ -17053,19 +17057,19 @@
       <c r="M243" s="3" t="inlineStr"/>
       <c r="N243" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-25-repartition-et-justice-sociale/c01-ce-que-ce-livre-doit-etablir.md</t>
+          <t>corpus/livre-24-conditions-materielles-de-la-vie/c01-ce-que-ce-livre-doit-etablir.md</t>
         </is>
       </c>
     </row>
     <row r="244">
       <c r="A244" s="2" t="inlineStr">
         <is>
-          <t>L26.C01</t>
+          <t>L25.C01</t>
         </is>
       </c>
       <c r="B244" s="3" t="inlineStr">
         <is>
-          <t>L26</t>
+          <t>L25</t>
         </is>
       </c>
       <c r="C244" s="3" t="inlineStr">
@@ -17113,12 +17117,72 @@
       <c r="M244" s="3" t="inlineStr"/>
       <c r="N244" s="3" t="inlineStr">
         <is>
+          <t>corpus/livre-25-repartition-et-justice-sociale/c01-ce-que-ce-livre-doit-etablir.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" s="2" t="inlineStr">
+        <is>
+          <t>L26.C01</t>
+        </is>
+      </c>
+      <c r="B245" s="3" t="inlineStr">
+        <is>
+          <t>L26</t>
+        </is>
+      </c>
+      <c r="C245" s="3" t="inlineStr">
+        <is>
+          <t>Ce que ce livre doit établir</t>
+        </is>
+      </c>
+      <c r="D245" s="3" t="inlineStr">
+        <is>
+          <t>brouillon</t>
+        </is>
+      </c>
+      <c r="E245" s="3" t="inlineStr">
+        <is>
+          <t>preparatoire</t>
+        </is>
+      </c>
+      <c r="F245" s="3" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="G245" s="3" t="inlineStr">
+        <is>
+          <t>descriptif</t>
+        </is>
+      </c>
+      <c r="H245" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="I245" s="3" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="J245" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="K245" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="L245" s="3" t="inlineStr"/>
+      <c r="M245" s="3" t="inlineStr"/>
+      <c r="N245" s="3" t="inlineStr">
+        <is>
           <t>corpus/livre-26-thermodynamique-et-processus-economique/c01-ce-que-ce-livre-doit-etablir.md</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:N244"/>
+  <autoFilter ref="A1:N245"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -17197,7 +17261,7 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>243</v>
+        <v>244</v>
       </c>
     </row>
     <row r="7">
@@ -17217,7 +17281,7 @@
         </is>
       </c>
       <c r="B8" s="3" t="n">
-        <v>229</v>
+        <v>230</v>
       </c>
     </row>
     <row r="9">
@@ -17227,7 +17291,7 @@
         </is>
       </c>
       <c r="B9" s="3" t="n">
-        <v>234</v>
+        <v>235</v>
       </c>
     </row>
     <row r="10">
@@ -17247,7 +17311,7 @@
         </is>
       </c>
       <c r="B11" s="3" t="n">
-        <v>1177</v>
+        <v>1180</v>
       </c>
     </row>
     <row r="12">
@@ -17257,7 +17321,7 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>973</v>
+        <v>977</v>
       </c>
     </row>
     <row r="13">
@@ -17351,7 +17415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C271"/>
+  <dimension ref="A1:C272"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -21826,7 +21890,7 @@
       </c>
       <c r="C263" s="6" t="inlineStr">
         <is>
-          <t>en-cours — 2 chapitre(s)</t>
+          <t>en-cours — 3 chapitre(s)</t>
         </is>
       </c>
     </row>
@@ -21865,102 +21929,119 @@
       </c>
     </row>
     <row r="266">
-      <c r="A266" s="6" t="inlineStr">
+      <c r="A266" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    L23.C03</t>
+        </is>
+      </c>
+      <c r="B266" s="3" t="inlineStr">
+        <is>
+          <t>F8 appliqué à une négociation en cours, et le résultat n'est pas le désarmement</t>
+        </is>
+      </c>
+      <c r="C266" s="3" t="inlineStr">
+        <is>
+          <t>brouillon</t>
+        </is>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" s="6" t="inlineStr">
         <is>
           <t>L24</t>
         </is>
       </c>
-      <c r="B266" s="6" t="inlineStr">
+      <c r="B267" s="6" t="inlineStr">
         <is>
           <t>Les conditions matérielles de la vie</t>
         </is>
       </c>
-      <c r="C266" s="6" t="inlineStr">
+      <c r="C267" s="6" t="inlineStr">
         <is>
           <t>candidat — AMORCE SEULE</t>
         </is>
       </c>
     </row>
-    <row r="267">
-      <c r="A267" s="3" t="inlineStr">
+    <row r="268">
+      <c r="A268" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">    L24.C01</t>
         </is>
       </c>
-      <c r="B267" s="3" t="inlineStr">
+      <c r="B268" s="3" t="inlineStr">
         <is>
           <t>[AMORCE] Ce que ce livre doit établir</t>
         </is>
       </c>
-      <c r="C267" s="3" t="inlineStr">
-        <is>
-          <t>brouillon</t>
-        </is>
-      </c>
-    </row>
-    <row r="268">
-      <c r="A268" s="6" t="inlineStr">
+      <c r="C268" s="3" t="inlineStr">
+        <is>
+          <t>brouillon</t>
+        </is>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" s="6" t="inlineStr">
         <is>
           <t>L25</t>
         </is>
       </c>
-      <c r="B268" s="6" t="inlineStr">
+      <c r="B269" s="6" t="inlineStr">
         <is>
           <t>Répartition, besoins essentiels et justice sociale</t>
         </is>
       </c>
-      <c r="C268" s="6" t="inlineStr">
+      <c r="C269" s="6" t="inlineStr">
         <is>
           <t>candidat — AMORCE SEULE</t>
         </is>
       </c>
     </row>
-    <row r="269">
-      <c r="A269" s="3" t="inlineStr">
+    <row r="270">
+      <c r="A270" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">    L25.C01</t>
         </is>
       </c>
-      <c r="B269" s="3" t="inlineStr">
+      <c r="B270" s="3" t="inlineStr">
         <is>
           <t>[AMORCE] Ce que ce livre doit établir</t>
         </is>
       </c>
-      <c r="C269" s="3" t="inlineStr">
-        <is>
-          <t>brouillon</t>
-        </is>
-      </c>
-    </row>
-    <row r="270">
-      <c r="A270" s="6" t="inlineStr">
+      <c r="C270" s="3" t="inlineStr">
+        <is>
+          <t>brouillon</t>
+        </is>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" s="6" t="inlineStr">
         <is>
           <t>L26</t>
         </is>
       </c>
-      <c r="B270" s="6" t="inlineStr">
+      <c r="B271" s="6" t="inlineStr">
         <is>
           <t>Thermodynamique, énergie et processus économique</t>
         </is>
       </c>
-      <c r="C270" s="6" t="inlineStr">
+      <c r="C271" s="6" t="inlineStr">
         <is>
           <t>candidat — AMORCE SEULE</t>
         </is>
       </c>
     </row>
-    <row r="271">
-      <c r="A271" s="3" t="inlineStr">
+    <row r="272">
+      <c r="A272" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">    L26.C01</t>
         </is>
       </c>
-      <c r="B271" s="3" t="inlineStr">
+      <c r="B272" s="3" t="inlineStr">
         <is>
           <t>[AMORCE] Ce que ce livre doit établir</t>
         </is>
       </c>
-      <c r="C271" s="3" t="inlineStr">
+      <c r="C272" s="3" t="inlineStr">
         <is>
           <t>brouillon</t>
         </is>

--- a/plan-des-livres.xlsx
+++ b/plan-des-livres.xlsx
@@ -13,7 +13,7 @@
     <sheet name="Plan par livre" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Chapitres'!$A$1:$N$245</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Chapitres'!$A$1:$N$246</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -1490,7 +1490,7 @@
         </is>
       </c>
       <c r="F25" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G25" s="5" t="inlineStr"/>
       <c r="H25" s="5" t="inlineStr">
@@ -1638,7 +1638,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N245"/>
+  <dimension ref="A1:N246"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -16471,7 +16471,7 @@
       </c>
       <c r="H234" s="3" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="I234" s="3" t="inlineStr"/>
@@ -17004,17 +17004,17 @@
     <row r="243">
       <c r="A243" s="2" t="inlineStr">
         <is>
-          <t>L24.C01</t>
+          <t>L23.C04</t>
         </is>
       </c>
       <c r="B243" s="3" t="inlineStr">
         <is>
-          <t>L24</t>
+          <t>L23</t>
         </is>
       </c>
       <c r="C243" s="3" t="inlineStr">
         <is>
-          <t>Ce que ce livre doit établir</t>
+          <t>La transparence que le corpus supposait a été invalidée</t>
         </is>
       </c>
       <c r="D243" s="3" t="inlineStr">
@@ -17034,7 +17034,7 @@
       </c>
       <c r="G243" s="3" t="inlineStr">
         <is>
-          <t>descriptif</t>
+          <t>hybride</t>
         </is>
       </c>
       <c r="H243" s="3" t="inlineStr">
@@ -17042,34 +17042,38 @@
           <t>2026-09-07</t>
         </is>
       </c>
-      <c r="I243" s="3" t="inlineStr">
-        <is>
-          <t>oui</t>
-        </is>
-      </c>
+      <c r="I243" s="3" t="inlineStr"/>
       <c r="J243" s="3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K243" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="L243" s="3" t="inlineStr"/>
-      <c r="M243" s="3" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="L243" s="3" t="inlineStr">
+        <is>
+          <t>regle_contre_discretion, externalisation, bareme, polycentricite, architecture_invisible</t>
+        </is>
+      </c>
+      <c r="M243" s="3" t="inlineStr">
+        <is>
+          <t>L6.C09, L11.C13, L11.C25, L20.C20, L23.C01, L23.C02, L23.C03</t>
+        </is>
+      </c>
       <c r="N243" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-24-conditions-materielles-de-la-vie/c01-ce-que-ce-livre-doit-etablir.md</t>
+          <t>corpus/livre-23-fiscalite-mondiale-et-opacite/c04-la-transparence-que-le-corpus-supposait-a-ete-invalidee.md</t>
         </is>
       </c>
     </row>
     <row r="244">
       <c r="A244" s="2" t="inlineStr">
         <is>
-          <t>L25.C01</t>
+          <t>L24.C01</t>
         </is>
       </c>
       <c r="B244" s="3" t="inlineStr">
         <is>
-          <t>L25</t>
+          <t>L24</t>
         </is>
       </c>
       <c r="C244" s="3" t="inlineStr">
@@ -17117,19 +17121,19 @@
       <c r="M244" s="3" t="inlineStr"/>
       <c r="N244" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-25-repartition-et-justice-sociale/c01-ce-que-ce-livre-doit-etablir.md</t>
+          <t>corpus/livre-24-conditions-materielles-de-la-vie/c01-ce-que-ce-livre-doit-etablir.md</t>
         </is>
       </c>
     </row>
     <row r="245">
       <c r="A245" s="2" t="inlineStr">
         <is>
-          <t>L26.C01</t>
+          <t>L25.C01</t>
         </is>
       </c>
       <c r="B245" s="3" t="inlineStr">
         <is>
-          <t>L26</t>
+          <t>L25</t>
         </is>
       </c>
       <c r="C245" s="3" t="inlineStr">
@@ -17177,12 +17181,72 @@
       <c r="M245" s="3" t="inlineStr"/>
       <c r="N245" s="3" t="inlineStr">
         <is>
+          <t>corpus/livre-25-repartition-et-justice-sociale/c01-ce-que-ce-livre-doit-etablir.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" s="2" t="inlineStr">
+        <is>
+          <t>L26.C01</t>
+        </is>
+      </c>
+      <c r="B246" s="3" t="inlineStr">
+        <is>
+          <t>L26</t>
+        </is>
+      </c>
+      <c r="C246" s="3" t="inlineStr">
+        <is>
+          <t>Ce que ce livre doit établir</t>
+        </is>
+      </c>
+      <c r="D246" s="3" t="inlineStr">
+        <is>
+          <t>brouillon</t>
+        </is>
+      </c>
+      <c r="E246" s="3" t="inlineStr">
+        <is>
+          <t>preparatoire</t>
+        </is>
+      </c>
+      <c r="F246" s="3" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="G246" s="3" t="inlineStr">
+        <is>
+          <t>descriptif</t>
+        </is>
+      </c>
+      <c r="H246" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="I246" s="3" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="J246" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="K246" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="L246" s="3" t="inlineStr"/>
+      <c r="M246" s="3" t="inlineStr"/>
+      <c r="N246" s="3" t="inlineStr">
+        <is>
           <t>corpus/livre-26-thermodynamique-et-processus-economique/c01-ce-que-ce-livre-doit-etablir.md</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:N245"/>
+  <autoFilter ref="A1:N246"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -17261,7 +17325,7 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>244</v>
+        <v>245</v>
       </c>
     </row>
     <row r="7">
@@ -17281,7 +17345,7 @@
         </is>
       </c>
       <c r="B8" s="3" t="n">
-        <v>230</v>
+        <v>231</v>
       </c>
     </row>
     <row r="9">
@@ -17291,7 +17355,7 @@
         </is>
       </c>
       <c r="B9" s="3" t="n">
-        <v>235</v>
+        <v>236</v>
       </c>
     </row>
     <row r="10">
@@ -17311,7 +17375,7 @@
         </is>
       </c>
       <c r="B11" s="3" t="n">
-        <v>1180</v>
+        <v>1183</v>
       </c>
     </row>
     <row r="12">
@@ -17321,7 +17385,7 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>977</v>
+        <v>980</v>
       </c>
     </row>
     <row r="13">
@@ -17415,7 +17479,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C272"/>
+  <dimension ref="A1:C273"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -21890,7 +21954,7 @@
       </c>
       <c r="C263" s="6" t="inlineStr">
         <is>
-          <t>en-cours — 3 chapitre(s)</t>
+          <t>en-cours — 4 chapitre(s)</t>
         </is>
       </c>
     </row>
@@ -21946,102 +22010,119 @@
       </c>
     </row>
     <row r="267">
-      <c r="A267" s="6" t="inlineStr">
+      <c r="A267" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    L23.C04</t>
+        </is>
+      </c>
+      <c r="B267" s="3" t="inlineStr">
+        <is>
+          <t>La transparence que le corpus supposait a été invalidée</t>
+        </is>
+      </c>
+      <c r="C267" s="3" t="inlineStr">
+        <is>
+          <t>brouillon</t>
+        </is>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" s="6" t="inlineStr">
         <is>
           <t>L24</t>
         </is>
       </c>
-      <c r="B267" s="6" t="inlineStr">
+      <c r="B268" s="6" t="inlineStr">
         <is>
           <t>Les conditions matérielles de la vie</t>
         </is>
       </c>
-      <c r="C267" s="6" t="inlineStr">
+      <c r="C268" s="6" t="inlineStr">
         <is>
           <t>candidat — AMORCE SEULE</t>
         </is>
       </c>
     </row>
-    <row r="268">
-      <c r="A268" s="3" t="inlineStr">
+    <row r="269">
+      <c r="A269" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">    L24.C01</t>
         </is>
       </c>
-      <c r="B268" s="3" t="inlineStr">
+      <c r="B269" s="3" t="inlineStr">
         <is>
           <t>[AMORCE] Ce que ce livre doit établir</t>
         </is>
       </c>
-      <c r="C268" s="3" t="inlineStr">
-        <is>
-          <t>brouillon</t>
-        </is>
-      </c>
-    </row>
-    <row r="269">
-      <c r="A269" s="6" t="inlineStr">
+      <c r="C269" s="3" t="inlineStr">
+        <is>
+          <t>brouillon</t>
+        </is>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" s="6" t="inlineStr">
         <is>
           <t>L25</t>
         </is>
       </c>
-      <c r="B269" s="6" t="inlineStr">
+      <c r="B270" s="6" t="inlineStr">
         <is>
           <t>Répartition, besoins essentiels et justice sociale</t>
         </is>
       </c>
-      <c r="C269" s="6" t="inlineStr">
+      <c r="C270" s="6" t="inlineStr">
         <is>
           <t>candidat — AMORCE SEULE</t>
         </is>
       </c>
     </row>
-    <row r="270">
-      <c r="A270" s="3" t="inlineStr">
+    <row r="271">
+      <c r="A271" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">    L25.C01</t>
         </is>
       </c>
-      <c r="B270" s="3" t="inlineStr">
+      <c r="B271" s="3" t="inlineStr">
         <is>
           <t>[AMORCE] Ce que ce livre doit établir</t>
         </is>
       </c>
-      <c r="C270" s="3" t="inlineStr">
-        <is>
-          <t>brouillon</t>
-        </is>
-      </c>
-    </row>
-    <row r="271">
-      <c r="A271" s="6" t="inlineStr">
+      <c r="C271" s="3" t="inlineStr">
+        <is>
+          <t>brouillon</t>
+        </is>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" s="6" t="inlineStr">
         <is>
           <t>L26</t>
         </is>
       </c>
-      <c r="B271" s="6" t="inlineStr">
+      <c r="B272" s="6" t="inlineStr">
         <is>
           <t>Thermodynamique, énergie et processus économique</t>
         </is>
       </c>
-      <c r="C271" s="6" t="inlineStr">
+      <c r="C272" s="6" t="inlineStr">
         <is>
           <t>candidat — AMORCE SEULE</t>
         </is>
       </c>
     </row>
-    <row r="272">
-      <c r="A272" s="3" t="inlineStr">
+    <row r="273">
+      <c r="A273" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">    L26.C01</t>
         </is>
       </c>
-      <c r="B272" s="3" t="inlineStr">
+      <c r="B273" s="3" t="inlineStr">
         <is>
           <t>[AMORCE] Ce que ce livre doit établir</t>
         </is>
       </c>
-      <c r="C272" s="3" t="inlineStr">
+      <c r="C273" s="3" t="inlineStr">
         <is>
           <t>brouillon</t>
         </is>

--- a/plan-des-livres.xlsx
+++ b/plan-des-livres.xlsx
@@ -13,7 +13,7 @@
     <sheet name="Plan par livre" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Chapitres'!$A$1:$N$246</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Chapitres'!$A$1:$N$247</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -1490,7 +1490,7 @@
         </is>
       </c>
       <c r="F25" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G25" s="5" t="inlineStr"/>
       <c r="H25" s="5" t="inlineStr">
@@ -1638,7 +1638,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N246"/>
+  <dimension ref="A1:N247"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -17068,17 +17068,17 @@
     <row r="244">
       <c r="A244" s="2" t="inlineStr">
         <is>
-          <t>L24.C01</t>
+          <t>L23.C05</t>
         </is>
       </c>
       <c r="B244" s="3" t="inlineStr">
         <is>
-          <t>L24</t>
+          <t>L23</t>
         </is>
       </c>
       <c r="C244" s="3" t="inlineStr">
         <is>
-          <t>Ce que ce livre doit établir</t>
+          <t>Intéresser le percepteur, et ce que le taux révèle</t>
         </is>
       </c>
       <c r="D244" s="3" t="inlineStr">
@@ -17098,7 +17098,7 @@
       </c>
       <c r="G244" s="3" t="inlineStr">
         <is>
-          <t>descriptif</t>
+          <t>hybride</t>
         </is>
       </c>
       <c r="H244" s="3" t="inlineStr">
@@ -17106,34 +17106,38 @@
           <t>2026-09-07</t>
         </is>
       </c>
-      <c r="I244" s="3" t="inlineStr">
-        <is>
-          <t>oui</t>
-        </is>
-      </c>
+      <c r="I244" s="3" t="inlineStr"/>
       <c r="J244" s="3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K244" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="L244" s="3" t="inlineStr"/>
-      <c r="M244" s="3" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="L244" s="3" t="inlineStr">
+        <is>
+          <t>bareme, reflux_transactionnel, regle_contre_discretion, polycentricite, seuil_d_activation</t>
+        </is>
+      </c>
+      <c r="M244" s="3" t="inlineStr">
+        <is>
+          <t>L11.C21, L11.C24, L18.C09, L20.C20, L23.C01, L23.C02, L23.C03</t>
+        </is>
+      </c>
       <c r="N244" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-24-conditions-materielles-de-la-vie/c01-ce-que-ce-livre-doit-etablir.md</t>
+          <t>corpus/livre-23-fiscalite-mondiale-et-opacite/c05-interesser-le-percepteur-et-ce-que-le-taux-revele.md</t>
         </is>
       </c>
     </row>
     <row r="245">
       <c r="A245" s="2" t="inlineStr">
         <is>
-          <t>L25.C01</t>
+          <t>L24.C01</t>
         </is>
       </c>
       <c r="B245" s="3" t="inlineStr">
         <is>
-          <t>L25</t>
+          <t>L24</t>
         </is>
       </c>
       <c r="C245" s="3" t="inlineStr">
@@ -17181,19 +17185,19 @@
       <c r="M245" s="3" t="inlineStr"/>
       <c r="N245" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-25-repartition-et-justice-sociale/c01-ce-que-ce-livre-doit-etablir.md</t>
+          <t>corpus/livre-24-conditions-materielles-de-la-vie/c01-ce-que-ce-livre-doit-etablir.md</t>
         </is>
       </c>
     </row>
     <row r="246">
       <c r="A246" s="2" t="inlineStr">
         <is>
-          <t>L26.C01</t>
+          <t>L25.C01</t>
         </is>
       </c>
       <c r="B246" s="3" t="inlineStr">
         <is>
-          <t>L26</t>
+          <t>L25</t>
         </is>
       </c>
       <c r="C246" s="3" t="inlineStr">
@@ -17241,12 +17245,72 @@
       <c r="M246" s="3" t="inlineStr"/>
       <c r="N246" s="3" t="inlineStr">
         <is>
+          <t>corpus/livre-25-repartition-et-justice-sociale/c01-ce-que-ce-livre-doit-etablir.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" s="2" t="inlineStr">
+        <is>
+          <t>L26.C01</t>
+        </is>
+      </c>
+      <c r="B247" s="3" t="inlineStr">
+        <is>
+          <t>L26</t>
+        </is>
+      </c>
+      <c r="C247" s="3" t="inlineStr">
+        <is>
+          <t>Ce que ce livre doit établir</t>
+        </is>
+      </c>
+      <c r="D247" s="3" t="inlineStr">
+        <is>
+          <t>brouillon</t>
+        </is>
+      </c>
+      <c r="E247" s="3" t="inlineStr">
+        <is>
+          <t>preparatoire</t>
+        </is>
+      </c>
+      <c r="F247" s="3" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="G247" s="3" t="inlineStr">
+        <is>
+          <t>descriptif</t>
+        </is>
+      </c>
+      <c r="H247" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="I247" s="3" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="J247" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="K247" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="L247" s="3" t="inlineStr"/>
+      <c r="M247" s="3" t="inlineStr"/>
+      <c r="N247" s="3" t="inlineStr">
+        <is>
           <t>corpus/livre-26-thermodynamique-et-processus-economique/c01-ce-que-ce-livre-doit-etablir.md</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:N246"/>
+  <autoFilter ref="A1:N247"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -17325,7 +17389,7 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>245</v>
+        <v>246</v>
       </c>
     </row>
     <row r="7">
@@ -17345,7 +17409,7 @@
         </is>
       </c>
       <c r="B8" s="3" t="n">
-        <v>231</v>
+        <v>232</v>
       </c>
     </row>
     <row r="9">
@@ -17355,7 +17419,7 @@
         </is>
       </c>
       <c r="B9" s="3" t="n">
-        <v>236</v>
+        <v>237</v>
       </c>
     </row>
     <row r="10">
@@ -17375,7 +17439,7 @@
         </is>
       </c>
       <c r="B11" s="3" t="n">
-        <v>1183</v>
+        <v>1186</v>
       </c>
     </row>
     <row r="12">
@@ -17385,7 +17449,7 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>980</v>
+        <v>983</v>
       </c>
     </row>
     <row r="13">
@@ -17479,7 +17543,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C273"/>
+  <dimension ref="A1:C274"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -21954,7 +22018,7 @@
       </c>
       <c r="C263" s="6" t="inlineStr">
         <is>
-          <t>en-cours — 4 chapitre(s)</t>
+          <t>en-cours — 5 chapitre(s)</t>
         </is>
       </c>
     </row>
@@ -22027,102 +22091,119 @@
       </c>
     </row>
     <row r="268">
-      <c r="A268" s="6" t="inlineStr">
+      <c r="A268" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    L23.C05</t>
+        </is>
+      </c>
+      <c r="B268" s="3" t="inlineStr">
+        <is>
+          <t>Intéresser le percepteur, et ce que le taux révèle</t>
+        </is>
+      </c>
+      <c r="C268" s="3" t="inlineStr">
+        <is>
+          <t>brouillon</t>
+        </is>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" s="6" t="inlineStr">
         <is>
           <t>L24</t>
         </is>
       </c>
-      <c r="B268" s="6" t="inlineStr">
+      <c r="B269" s="6" t="inlineStr">
         <is>
           <t>Les conditions matérielles de la vie</t>
         </is>
       </c>
-      <c r="C268" s="6" t="inlineStr">
+      <c r="C269" s="6" t="inlineStr">
         <is>
           <t>candidat — AMORCE SEULE</t>
         </is>
       </c>
     </row>
-    <row r="269">
-      <c r="A269" s="3" t="inlineStr">
+    <row r="270">
+      <c r="A270" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">    L24.C01</t>
         </is>
       </c>
-      <c r="B269" s="3" t="inlineStr">
+      <c r="B270" s="3" t="inlineStr">
         <is>
           <t>[AMORCE] Ce que ce livre doit établir</t>
         </is>
       </c>
-      <c r="C269" s="3" t="inlineStr">
-        <is>
-          <t>brouillon</t>
-        </is>
-      </c>
-    </row>
-    <row r="270">
-      <c r="A270" s="6" t="inlineStr">
+      <c r="C270" s="3" t="inlineStr">
+        <is>
+          <t>brouillon</t>
+        </is>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" s="6" t="inlineStr">
         <is>
           <t>L25</t>
         </is>
       </c>
-      <c r="B270" s="6" t="inlineStr">
+      <c r="B271" s="6" t="inlineStr">
         <is>
           <t>Répartition, besoins essentiels et justice sociale</t>
         </is>
       </c>
-      <c r="C270" s="6" t="inlineStr">
+      <c r="C271" s="6" t="inlineStr">
         <is>
           <t>candidat — AMORCE SEULE</t>
         </is>
       </c>
     </row>
-    <row r="271">
-      <c r="A271" s="3" t="inlineStr">
+    <row r="272">
+      <c r="A272" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">    L25.C01</t>
         </is>
       </c>
-      <c r="B271" s="3" t="inlineStr">
+      <c r="B272" s="3" t="inlineStr">
         <is>
           <t>[AMORCE] Ce que ce livre doit établir</t>
         </is>
       </c>
-      <c r="C271" s="3" t="inlineStr">
-        <is>
-          <t>brouillon</t>
-        </is>
-      </c>
-    </row>
-    <row r="272">
-      <c r="A272" s="6" t="inlineStr">
+      <c r="C272" s="3" t="inlineStr">
+        <is>
+          <t>brouillon</t>
+        </is>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" s="6" t="inlineStr">
         <is>
           <t>L26</t>
         </is>
       </c>
-      <c r="B272" s="6" t="inlineStr">
+      <c r="B273" s="6" t="inlineStr">
         <is>
           <t>Thermodynamique, énergie et processus économique</t>
         </is>
       </c>
-      <c r="C272" s="6" t="inlineStr">
+      <c r="C273" s="6" t="inlineStr">
         <is>
           <t>candidat — AMORCE SEULE</t>
         </is>
       </c>
     </row>
-    <row r="273">
-      <c r="A273" s="3" t="inlineStr">
+    <row r="274">
+      <c r="A274" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">    L26.C01</t>
         </is>
       </c>
-      <c r="B273" s="3" t="inlineStr">
+      <c r="B274" s="3" t="inlineStr">
         <is>
           <t>[AMORCE] Ce que ce livre doit établir</t>
         </is>
       </c>
-      <c r="C273" s="3" t="inlineStr">
+      <c r="C274" s="3" t="inlineStr">
         <is>
           <t>brouillon</t>
         </is>

--- a/plan-des-livres.xlsx
+++ b/plan-des-livres.xlsx
@@ -13,7 +13,7 @@
     <sheet name="Plan par livre" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Chapitres'!$A$1:$N$247</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Chapitres'!$A$1:$N$248</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -1490,7 +1490,7 @@
         </is>
       </c>
       <c r="F25" s="5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G25" s="5" t="inlineStr"/>
       <c r="H25" s="5" t="inlineStr">
@@ -1638,7 +1638,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N247"/>
+  <dimension ref="A1:N248"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -12659,7 +12659,7 @@
       </c>
       <c r="H174" s="3" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="I174" s="3" t="inlineStr"/>
@@ -12787,7 +12787,7 @@
       </c>
       <c r="H176" s="3" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="I176" s="3" t="inlineStr"/>
@@ -17132,17 +17132,17 @@
     <row r="245">
       <c r="A245" s="2" t="inlineStr">
         <is>
-          <t>L24.C01</t>
+          <t>L23.C06</t>
         </is>
       </c>
       <c r="B245" s="3" t="inlineStr">
         <is>
-          <t>L24</t>
+          <t>L23</t>
         </is>
       </c>
       <c r="C245" s="3" t="inlineStr">
         <is>
-          <t>Ce que ce livre doit établir</t>
+          <t>L'arbre appliqué à la fonte, et il ne reste que deux branches</t>
         </is>
       </c>
       <c r="D245" s="3" t="inlineStr">
@@ -17162,7 +17162,7 @@
       </c>
       <c r="G245" s="3" t="inlineStr">
         <is>
-          <t>descriptif</t>
+          <t>conception</t>
         </is>
       </c>
       <c r="H245" s="3" t="inlineStr">
@@ -17170,34 +17170,38 @@
           <t>2026-09-07</t>
         </is>
       </c>
-      <c r="I245" s="3" t="inlineStr">
-        <is>
-          <t>oui</t>
-        </is>
-      </c>
+      <c r="I245" s="3" t="inlineStr"/>
       <c r="J245" s="3" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K245" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="L245" s="3" t="inlineStr"/>
-      <c r="M245" s="3" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="L245" s="3" t="inlineStr">
+        <is>
+          <t>bareme, reflux_transactionnel, monnaie_fondante, demurrage, regle_contre_discretion, essentiel_insolvable</t>
+        </is>
+      </c>
+      <c r="M245" s="3" t="inlineStr">
+        <is>
+          <t>L10.C06, L11.C05, L11.C09, L11.C21, L11.C24, L18.C09, L20.C02, L23.C01, L23.C02, L23.C03, L23.C04, L23.C05</t>
+        </is>
+      </c>
       <c r="N245" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-24-conditions-materielles-de-la-vie/c01-ce-que-ce-livre-doit-etablir.md</t>
+          <t>corpus/livre-23-fiscalite-mondiale-et-opacite/c06-l-arbre-applique-a-la-fonte.md</t>
         </is>
       </c>
     </row>
     <row r="246">
       <c r="A246" s="2" t="inlineStr">
         <is>
-          <t>L25.C01</t>
+          <t>L24.C01</t>
         </is>
       </c>
       <c r="B246" s="3" t="inlineStr">
         <is>
-          <t>L25</t>
+          <t>L24</t>
         </is>
       </c>
       <c r="C246" s="3" t="inlineStr">
@@ -17245,19 +17249,19 @@
       <c r="M246" s="3" t="inlineStr"/>
       <c r="N246" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-25-repartition-et-justice-sociale/c01-ce-que-ce-livre-doit-etablir.md</t>
+          <t>corpus/livre-24-conditions-materielles-de-la-vie/c01-ce-que-ce-livre-doit-etablir.md</t>
         </is>
       </c>
     </row>
     <row r="247">
       <c r="A247" s="2" t="inlineStr">
         <is>
-          <t>L26.C01</t>
+          <t>L25.C01</t>
         </is>
       </c>
       <c r="B247" s="3" t="inlineStr">
         <is>
-          <t>L26</t>
+          <t>L25</t>
         </is>
       </c>
       <c r="C247" s="3" t="inlineStr">
@@ -17305,12 +17309,72 @@
       <c r="M247" s="3" t="inlineStr"/>
       <c r="N247" s="3" t="inlineStr">
         <is>
+          <t>corpus/livre-25-repartition-et-justice-sociale/c01-ce-que-ce-livre-doit-etablir.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" s="2" t="inlineStr">
+        <is>
+          <t>L26.C01</t>
+        </is>
+      </c>
+      <c r="B248" s="3" t="inlineStr">
+        <is>
+          <t>L26</t>
+        </is>
+      </c>
+      <c r="C248" s="3" t="inlineStr">
+        <is>
+          <t>Ce que ce livre doit établir</t>
+        </is>
+      </c>
+      <c r="D248" s="3" t="inlineStr">
+        <is>
+          <t>brouillon</t>
+        </is>
+      </c>
+      <c r="E248" s="3" t="inlineStr">
+        <is>
+          <t>preparatoire</t>
+        </is>
+      </c>
+      <c r="F248" s="3" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="G248" s="3" t="inlineStr">
+        <is>
+          <t>descriptif</t>
+        </is>
+      </c>
+      <c r="H248" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="I248" s="3" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="J248" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="K248" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="L248" s="3" t="inlineStr"/>
+      <c r="M248" s="3" t="inlineStr"/>
+      <c r="N248" s="3" t="inlineStr">
+        <is>
           <t>corpus/livre-26-thermodynamique-et-processus-economique/c01-ce-que-ce-livre-doit-etablir.md</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:N247"/>
+  <autoFilter ref="A1:N248"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -17389,7 +17453,7 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>246</v>
+        <v>247</v>
       </c>
     </row>
     <row r="7">
@@ -17409,7 +17473,7 @@
         </is>
       </c>
       <c r="B8" s="3" t="n">
-        <v>232</v>
+        <v>233</v>
       </c>
     </row>
     <row r="9">
@@ -17419,7 +17483,7 @@
         </is>
       </c>
       <c r="B9" s="3" t="n">
-        <v>237</v>
+        <v>238</v>
       </c>
     </row>
     <row r="10">
@@ -17439,7 +17503,7 @@
         </is>
       </c>
       <c r="B11" s="3" t="n">
-        <v>1186</v>
+        <v>1189</v>
       </c>
     </row>
     <row r="12">
@@ -17449,7 +17513,7 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>983</v>
+        <v>987</v>
       </c>
     </row>
     <row r="13">
@@ -17543,7 +17607,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C274"/>
+  <dimension ref="A1:C275"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -22018,7 +22082,7 @@
       </c>
       <c r="C263" s="6" t="inlineStr">
         <is>
-          <t>en-cours — 5 chapitre(s)</t>
+          <t>en-cours — 6 chapitre(s)</t>
         </is>
       </c>
     </row>
@@ -22108,102 +22172,119 @@
       </c>
     </row>
     <row r="269">
-      <c r="A269" s="6" t="inlineStr">
+      <c r="A269" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    L23.C06</t>
+        </is>
+      </c>
+      <c r="B269" s="3" t="inlineStr">
+        <is>
+          <t>L'arbre appliqué à la fonte, et il ne reste que deux branches</t>
+        </is>
+      </c>
+      <c r="C269" s="3" t="inlineStr">
+        <is>
+          <t>brouillon</t>
+        </is>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" s="6" t="inlineStr">
         <is>
           <t>L24</t>
         </is>
       </c>
-      <c r="B269" s="6" t="inlineStr">
+      <c r="B270" s="6" t="inlineStr">
         <is>
           <t>Les conditions matérielles de la vie</t>
         </is>
       </c>
-      <c r="C269" s="6" t="inlineStr">
+      <c r="C270" s="6" t="inlineStr">
         <is>
           <t>candidat — AMORCE SEULE</t>
         </is>
       </c>
     </row>
-    <row r="270">
-      <c r="A270" s="3" t="inlineStr">
+    <row r="271">
+      <c r="A271" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">    L24.C01</t>
         </is>
       </c>
-      <c r="B270" s="3" t="inlineStr">
+      <c r="B271" s="3" t="inlineStr">
         <is>
           <t>[AMORCE] Ce que ce livre doit établir</t>
         </is>
       </c>
-      <c r="C270" s="3" t="inlineStr">
-        <is>
-          <t>brouillon</t>
-        </is>
-      </c>
-    </row>
-    <row r="271">
-      <c r="A271" s="6" t="inlineStr">
+      <c r="C271" s="3" t="inlineStr">
+        <is>
+          <t>brouillon</t>
+        </is>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" s="6" t="inlineStr">
         <is>
           <t>L25</t>
         </is>
       </c>
-      <c r="B271" s="6" t="inlineStr">
+      <c r="B272" s="6" t="inlineStr">
         <is>
           <t>Répartition, besoins essentiels et justice sociale</t>
         </is>
       </c>
-      <c r="C271" s="6" t="inlineStr">
+      <c r="C272" s="6" t="inlineStr">
         <is>
           <t>candidat — AMORCE SEULE</t>
         </is>
       </c>
     </row>
-    <row r="272">
-      <c r="A272" s="3" t="inlineStr">
+    <row r="273">
+      <c r="A273" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">    L25.C01</t>
         </is>
       </c>
-      <c r="B272" s="3" t="inlineStr">
+      <c r="B273" s="3" t="inlineStr">
         <is>
           <t>[AMORCE] Ce que ce livre doit établir</t>
         </is>
       </c>
-      <c r="C272" s="3" t="inlineStr">
-        <is>
-          <t>brouillon</t>
-        </is>
-      </c>
-    </row>
-    <row r="273">
-      <c r="A273" s="6" t="inlineStr">
+      <c r="C273" s="3" t="inlineStr">
+        <is>
+          <t>brouillon</t>
+        </is>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" s="6" t="inlineStr">
         <is>
           <t>L26</t>
         </is>
       </c>
-      <c r="B273" s="6" t="inlineStr">
+      <c r="B274" s="6" t="inlineStr">
         <is>
           <t>Thermodynamique, énergie et processus économique</t>
         </is>
       </c>
-      <c r="C273" s="6" t="inlineStr">
+      <c r="C274" s="6" t="inlineStr">
         <is>
           <t>candidat — AMORCE SEULE</t>
         </is>
       </c>
     </row>
-    <row r="274">
-      <c r="A274" s="3" t="inlineStr">
+    <row r="275">
+      <c r="A275" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">    L26.C01</t>
         </is>
       </c>
-      <c r="B274" s="3" t="inlineStr">
+      <c r="B275" s="3" t="inlineStr">
         <is>
           <t>[AMORCE] Ce que ce livre doit établir</t>
         </is>
       </c>
-      <c r="C274" s="3" t="inlineStr">
+      <c r="C275" s="3" t="inlineStr">
         <is>
           <t>brouillon</t>
         </is>

--- a/plan-des-livres.xlsx
+++ b/plan-des-livres.xlsx
@@ -13,7 +13,7 @@
     <sheet name="Plan par livre" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Chapitres'!$A$1:$N$248</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Chapitres'!$A$1:$N$249</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -1490,7 +1490,7 @@
         </is>
       </c>
       <c r="F25" s="5" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G25" s="5" t="inlineStr"/>
       <c r="H25" s="5" t="inlineStr">
@@ -1638,7 +1638,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N248"/>
+  <dimension ref="A1:N249"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -17196,17 +17196,17 @@
     <row r="246">
       <c r="A246" s="2" t="inlineStr">
         <is>
-          <t>L24.C01</t>
+          <t>L23.C07</t>
         </is>
       </c>
       <c r="B246" s="3" t="inlineStr">
         <is>
-          <t>L24</t>
+          <t>L23</t>
         </is>
       </c>
       <c r="C246" s="3" t="inlineStr">
         <is>
-          <t>Ce que ce livre doit établir</t>
+          <t>Portée de la tranche, et la moitié qui n'est pas commencée</t>
         </is>
       </c>
       <c r="D246" s="3" t="inlineStr">
@@ -17226,7 +17226,7 @@
       </c>
       <c r="G246" s="3" t="inlineStr">
         <is>
-          <t>descriptif</t>
+          <t>conception</t>
         </is>
       </c>
       <c r="H246" s="3" t="inlineStr">
@@ -17234,34 +17234,38 @@
           <t>2026-09-07</t>
         </is>
       </c>
-      <c r="I246" s="3" t="inlineStr">
-        <is>
-          <t>oui</t>
-        </is>
-      </c>
+      <c r="I246" s="3" t="inlineStr"/>
       <c r="J246" s="3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K246" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="L246" s="3" t="inlineStr"/>
-      <c r="M246" s="3" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="L246" s="3" t="inlineStr">
+        <is>
+          <t>bareme, reflux_transactionnel, externalisation, regle_contre_discretion, polycentricite, essentiel_insolvable</t>
+        </is>
+      </c>
+      <c r="M246" s="3" t="inlineStr">
+        <is>
+          <t>L10.C06, L11.C05, L11.C21, L11.C25, L18.C09, L20.C20, L23.C01, L23.C02, L23.C03, L23.C04, L23.C05, L23.C06</t>
+        </is>
+      </c>
       <c r="N246" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-24-conditions-materielles-de-la-vie/c01-ce-que-ce-livre-doit-etablir.md</t>
+          <t>corpus/livre-23-fiscalite-mondiale-et-opacite/c07-portee-de-la-tranche.md</t>
         </is>
       </c>
     </row>
     <row r="247">
       <c r="A247" s="2" t="inlineStr">
         <is>
-          <t>L25.C01</t>
+          <t>L24.C01</t>
         </is>
       </c>
       <c r="B247" s="3" t="inlineStr">
         <is>
-          <t>L25</t>
+          <t>L24</t>
         </is>
       </c>
       <c r="C247" s="3" t="inlineStr">
@@ -17309,19 +17313,19 @@
       <c r="M247" s="3" t="inlineStr"/>
       <c r="N247" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-25-repartition-et-justice-sociale/c01-ce-que-ce-livre-doit-etablir.md</t>
+          <t>corpus/livre-24-conditions-materielles-de-la-vie/c01-ce-que-ce-livre-doit-etablir.md</t>
         </is>
       </c>
     </row>
     <row r="248">
       <c r="A248" s="2" t="inlineStr">
         <is>
-          <t>L26.C01</t>
+          <t>L25.C01</t>
         </is>
       </c>
       <c r="B248" s="3" t="inlineStr">
         <is>
-          <t>L26</t>
+          <t>L25</t>
         </is>
       </c>
       <c r="C248" s="3" t="inlineStr">
@@ -17369,12 +17373,72 @@
       <c r="M248" s="3" t="inlineStr"/>
       <c r="N248" s="3" t="inlineStr">
         <is>
+          <t>corpus/livre-25-repartition-et-justice-sociale/c01-ce-que-ce-livre-doit-etablir.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" s="2" t="inlineStr">
+        <is>
+          <t>L26.C01</t>
+        </is>
+      </c>
+      <c r="B249" s="3" t="inlineStr">
+        <is>
+          <t>L26</t>
+        </is>
+      </c>
+      <c r="C249" s="3" t="inlineStr">
+        <is>
+          <t>Ce que ce livre doit établir</t>
+        </is>
+      </c>
+      <c r="D249" s="3" t="inlineStr">
+        <is>
+          <t>brouillon</t>
+        </is>
+      </c>
+      <c r="E249" s="3" t="inlineStr">
+        <is>
+          <t>preparatoire</t>
+        </is>
+      </c>
+      <c r="F249" s="3" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="G249" s="3" t="inlineStr">
+        <is>
+          <t>descriptif</t>
+        </is>
+      </c>
+      <c r="H249" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="I249" s="3" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="J249" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="K249" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="L249" s="3" t="inlineStr"/>
+      <c r="M249" s="3" t="inlineStr"/>
+      <c r="N249" s="3" t="inlineStr">
+        <is>
           <t>corpus/livre-26-thermodynamique-et-processus-economique/c01-ce-que-ce-livre-doit-etablir.md</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:N248"/>
+  <autoFilter ref="A1:N249"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -17453,7 +17517,7 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>247</v>
+        <v>248</v>
       </c>
     </row>
     <row r="7">
@@ -17473,7 +17537,7 @@
         </is>
       </c>
       <c r="B8" s="3" t="n">
-        <v>233</v>
+        <v>234</v>
       </c>
     </row>
     <row r="9">
@@ -17483,7 +17547,7 @@
         </is>
       </c>
       <c r="B9" s="3" t="n">
-        <v>238</v>
+        <v>239</v>
       </c>
     </row>
     <row r="10">
@@ -17503,7 +17567,7 @@
         </is>
       </c>
       <c r="B11" s="3" t="n">
-        <v>1189</v>
+        <v>1192</v>
       </c>
     </row>
     <row r="12">
@@ -17513,7 +17577,7 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>987</v>
+        <v>990</v>
       </c>
     </row>
     <row r="13">
@@ -17607,7 +17671,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C275"/>
+  <dimension ref="A1:C276"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -22082,7 +22146,7 @@
       </c>
       <c r="C263" s="6" t="inlineStr">
         <is>
-          <t>en-cours — 6 chapitre(s)</t>
+          <t>en-cours — 7 chapitre(s)</t>
         </is>
       </c>
     </row>
@@ -22189,102 +22253,119 @@
       </c>
     </row>
     <row r="270">
-      <c r="A270" s="6" t="inlineStr">
+      <c r="A270" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    L23.C07</t>
+        </is>
+      </c>
+      <c r="B270" s="3" t="inlineStr">
+        <is>
+          <t>Portée de la tranche, et la moitié qui n'est pas commencée</t>
+        </is>
+      </c>
+      <c r="C270" s="3" t="inlineStr">
+        <is>
+          <t>brouillon</t>
+        </is>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" s="6" t="inlineStr">
         <is>
           <t>L24</t>
         </is>
       </c>
-      <c r="B270" s="6" t="inlineStr">
+      <c r="B271" s="6" t="inlineStr">
         <is>
           <t>Les conditions matérielles de la vie</t>
         </is>
       </c>
-      <c r="C270" s="6" t="inlineStr">
+      <c r="C271" s="6" t="inlineStr">
         <is>
           <t>candidat — AMORCE SEULE</t>
         </is>
       </c>
     </row>
-    <row r="271">
-      <c r="A271" s="3" t="inlineStr">
+    <row r="272">
+      <c r="A272" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">    L24.C01</t>
         </is>
       </c>
-      <c r="B271" s="3" t="inlineStr">
+      <c r="B272" s="3" t="inlineStr">
         <is>
           <t>[AMORCE] Ce que ce livre doit établir</t>
         </is>
       </c>
-      <c r="C271" s="3" t="inlineStr">
-        <is>
-          <t>brouillon</t>
-        </is>
-      </c>
-    </row>
-    <row r="272">
-      <c r="A272" s="6" t="inlineStr">
+      <c r="C272" s="3" t="inlineStr">
+        <is>
+          <t>brouillon</t>
+        </is>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" s="6" t="inlineStr">
         <is>
           <t>L25</t>
         </is>
       </c>
-      <c r="B272" s="6" t="inlineStr">
+      <c r="B273" s="6" t="inlineStr">
         <is>
           <t>Répartition, besoins essentiels et justice sociale</t>
         </is>
       </c>
-      <c r="C272" s="6" t="inlineStr">
+      <c r="C273" s="6" t="inlineStr">
         <is>
           <t>candidat — AMORCE SEULE</t>
         </is>
       </c>
     </row>
-    <row r="273">
-      <c r="A273" s="3" t="inlineStr">
+    <row r="274">
+      <c r="A274" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">    L25.C01</t>
         </is>
       </c>
-      <c r="B273" s="3" t="inlineStr">
+      <c r="B274" s="3" t="inlineStr">
         <is>
           <t>[AMORCE] Ce que ce livre doit établir</t>
         </is>
       </c>
-      <c r="C273" s="3" t="inlineStr">
-        <is>
-          <t>brouillon</t>
-        </is>
-      </c>
-    </row>
-    <row r="274">
-      <c r="A274" s="6" t="inlineStr">
+      <c r="C274" s="3" t="inlineStr">
+        <is>
+          <t>brouillon</t>
+        </is>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" s="6" t="inlineStr">
         <is>
           <t>L26</t>
         </is>
       </c>
-      <c r="B274" s="6" t="inlineStr">
+      <c r="B275" s="6" t="inlineStr">
         <is>
           <t>Thermodynamique, énergie et processus économique</t>
         </is>
       </c>
-      <c r="C274" s="6" t="inlineStr">
+      <c r="C275" s="6" t="inlineStr">
         <is>
           <t>candidat — AMORCE SEULE</t>
         </is>
       </c>
     </row>
-    <row r="275">
-      <c r="A275" s="3" t="inlineStr">
+    <row r="276">
+      <c r="A276" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">    L26.C01</t>
         </is>
       </c>
-      <c r="B275" s="3" t="inlineStr">
+      <c r="B276" s="3" t="inlineStr">
         <is>
           <t>[AMORCE] Ce que ce livre doit établir</t>
         </is>
       </c>
-      <c r="C275" s="3" t="inlineStr">
+      <c r="C276" s="3" t="inlineStr">
         <is>
           <t>brouillon</t>
         </is>

--- a/plan-des-livres.xlsx
+++ b/plan-des-livres.xlsx
@@ -1382,41 +1382,41 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="2" t="inlineStr">
+      <c r="A23" s="4" t="inlineStr">
         <is>
           <t>L21</t>
         </is>
       </c>
-      <c r="B23" s="3" t="inlineStr">
+      <c r="B23" s="5" t="inlineStr">
         <is>
           <t>La plomberie financière mondiale</t>
         </is>
       </c>
-      <c r="C23" s="3" t="inlineStr">
+      <c r="C23" s="5" t="inlineStr">
         <is>
           <t>cahier-disciplinaire</t>
         </is>
       </c>
-      <c r="D23" s="3" t="inlineStr">
-        <is>
-          <t>candidat</t>
-        </is>
-      </c>
-      <c r="E23" s="3" t="inlineStr">
+      <c r="D23" s="5" t="inlineStr">
+        <is>
+          <t>en-cours</t>
+        </is>
+      </c>
+      <c r="E23" s="5" t="inlineStr">
         <is>
           <t>non contraignant</t>
         </is>
       </c>
-      <c r="F23" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G23" s="3" t="inlineStr"/>
-      <c r="H23" s="3" t="inlineStr">
+      <c r="F23" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G23" s="5" t="inlineStr"/>
+      <c r="H23" s="5" t="inlineStr">
         <is>
           <t>Comprendre comment les paiements, titres, garanties et devises circulent réellement — par quels bilans et quelles infrastructures une transaction mondiale devient-elle définitive</t>
         </is>
       </c>
-      <c r="I23" s="3" t="inlineStr">
+      <c r="I23" s="5" t="inlineStr">
         <is>
           <t>discipline — infrastructures de marché : messagerie, compensation, règlement, dépositaires, contreparties centrales | manque — L5.C02 a instruit SEPT des vingt-quatre principes du PFMI et le corpus n'a ouvert aucune infrastructure existante : ni coût, ni délai, ni volume d'équilibre | objection — L5.C09 : l'infrastructure fournit le rail de la séquence d'entrée, et le corpus ne sait pas où l'unité s'y logerait</t>
         </is>
@@ -12467,7 +12467,7 @@
       </c>
       <c r="H171" s="3" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="I171" s="3" t="inlineStr"/>
@@ -16702,7 +16702,7 @@
       </c>
       <c r="C238" s="3" t="inlineStr">
         <is>
-          <t>Ce que ce livre doit établir</t>
+          <t>Ce que ce livre doit établir, et le principe qui exige des fonds propres</t>
         </is>
       </c>
       <c r="D238" s="3" t="inlineStr">
@@ -16722,7 +16722,7 @@
       </c>
       <c r="G238" s="3" t="inlineStr">
         <is>
-          <t>descriptif</t>
+          <t>hybride</t>
         </is>
       </c>
       <c r="H238" s="3" t="inlineStr">
@@ -16730,19 +16730,23 @@
           <t>2026-09-07</t>
         </is>
       </c>
-      <c r="I238" s="3" t="inlineStr">
-        <is>
-          <t>oui</t>
-        </is>
-      </c>
+      <c r="I238" s="3" t="inlineStr"/>
       <c r="J238" s="3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K238" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="L238" s="3" t="inlineStr"/>
-      <c r="M238" s="3" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="L238" s="3" t="inlineStr">
+        <is>
+          <t>contrepartie_comptable, creation_monetaire, hierarchie_monetaire, monnaie_comme_registre, seuil_d_activation</t>
+        </is>
+      </c>
+      <c r="M238" s="3" t="inlineStr">
+        <is>
+          <t>L1.C20, L5.C02, L5.C09, L10.C01, L10.C02, L11.C02, L18.C01, L21.C01</t>
+        </is>
+      </c>
       <c r="N238" s="3" t="inlineStr">
         <is>
           <t>corpus/livre-21-plomberie-financiere-mondiale/c01-ce-que-ce-livre-doit-etablir.md</t>
@@ -17497,7 +17501,7 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="5">
@@ -17507,7 +17511,7 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="6">
@@ -17527,7 +17531,7 @@
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="8">
@@ -17537,7 +17541,7 @@
         </is>
       </c>
       <c r="B8" s="3" t="n">
-        <v>234</v>
+        <v>235</v>
       </c>
     </row>
     <row r="9">
@@ -17567,7 +17571,7 @@
         </is>
       </c>
       <c r="B11" s="3" t="n">
-        <v>1192</v>
+        <v>1193</v>
       </c>
     </row>
     <row r="12">
@@ -17577,7 +17581,7 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>990</v>
+        <v>992</v>
       </c>
     </row>
     <row r="13">
@@ -17592,7 +17596,7 @@
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>L0, L9, L12, L13, L14, L15, L16, L17, L19, L21, L22, L24, L25, L26</t>
+          <t>L0, L9, L12, L13, L14, L15, L16, L17, L19, L22, L24, L25, L26</t>
         </is>
       </c>
     </row>
@@ -22078,7 +22082,7 @@
       </c>
       <c r="C259" s="6" t="inlineStr">
         <is>
-          <t>candidat — AMORCE SEULE</t>
+          <t>en-cours — 1 chapitre(s)</t>
         </is>
       </c>
     </row>
@@ -22090,7 +22094,7 @@
       </c>
       <c r="B260" s="3" t="inlineStr">
         <is>
-          <t>[AMORCE] Ce que ce livre doit établir</t>
+          <t>Ce que ce livre doit établir, et le principe qui exige des fonds propres</t>
         </is>
       </c>
       <c r="C260" s="3" t="inlineStr">

--- a/plan-des-livres.xlsx
+++ b/plan-des-livres.xlsx
@@ -13,7 +13,7 @@
     <sheet name="Plan par livre" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Chapitres'!$A$1:$N$249</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Chapitres'!$A$1:$N$259</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -1408,7 +1408,7 @@
         </is>
       </c>
       <c r="F23" s="5" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="G23" s="5" t="inlineStr"/>
       <c r="H23" s="5" t="inlineStr">
@@ -1423,41 +1423,41 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="2" t="inlineStr">
+      <c r="A24" s="4" t="inlineStr">
         <is>
           <t>L22</t>
         </is>
       </c>
-      <c r="B24" s="3" t="inlineStr">
+      <c r="B24" s="5" t="inlineStr">
         <is>
           <t>Le pouvoir de la finance non bancaire</t>
         </is>
       </c>
-      <c r="C24" s="3" t="inlineStr">
+      <c r="C24" s="5" t="inlineStr">
         <is>
           <t>cahier-disciplinaire</t>
         </is>
       </c>
-      <c r="D24" s="3" t="inlineStr">
-        <is>
-          <t>candidat</t>
-        </is>
-      </c>
-      <c r="E24" s="3" t="inlineStr">
+      <c r="D24" s="5" t="inlineStr">
+        <is>
+          <t>en-cours</t>
+        </is>
+      </c>
+      <c r="E24" s="5" t="inlineStr">
         <is>
           <t>non contraignant</t>
         </is>
       </c>
-      <c r="F24" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G24" s="3" t="inlineStr"/>
-      <c r="H24" s="3" t="inlineStr">
+      <c r="F24" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="G24" s="5" t="inlineStr"/>
+      <c r="H24" s="5" t="inlineStr">
         <is>
           <t>Étudier ceux qui allouent le capital hors du crédit bancaire classique — qui décide de l'allocation du capital lorsqu'il ne s'agit plus principalement des banques</t>
         </is>
       </c>
-      <c r="I24" s="3" t="inlineStr">
+      <c r="I24" s="5" t="inlineStr">
         <is>
           <t>discipline — gestion d'actifs, fonds de pension, assureurs, fonds souverains, fonds monétaires, fonds spéculatifs, capital-investissement, crédit privé | manque — le corpus raisonne sur les banques et les États, et n'a jamais instruit l'acteur qui détient environ la moitié des actifs financiers mondiaux | objection — L5.C09 : la protection de l'entrée expire quand la couche déplace des flux, et le corpus ne sait pas qui réagirait ni comment</t>
         </is>
@@ -1638,7 +1638,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N249"/>
+  <dimension ref="A1:N259"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -12403,7 +12403,7 @@
       </c>
       <c r="H170" s="3" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="I170" s="3" t="inlineStr"/>
@@ -12851,7 +12851,7 @@
       </c>
       <c r="H177" s="3" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="I177" s="3" t="inlineStr"/>
@@ -13043,7 +13043,7 @@
       </c>
       <c r="H180" s="3" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="I180" s="3" t="inlineStr"/>
@@ -13491,7 +13491,7 @@
       </c>
       <c r="H187" s="3" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="I187" s="3" t="inlineStr"/>
@@ -13811,7 +13811,7 @@
       </c>
       <c r="H192" s="3" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="I192" s="3" t="inlineStr"/>
@@ -15255,7 +15255,7 @@
       </c>
       <c r="H215" s="3" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="I215" s="3" t="inlineStr"/>
@@ -16756,17 +16756,17 @@
     <row r="239">
       <c r="A239" s="2" t="inlineStr">
         <is>
-          <t>L22.C01</t>
+          <t>L21.C02</t>
         </is>
       </c>
       <c r="B239" s="3" t="inlineStr">
         <is>
-          <t>L22</t>
+          <t>L21</t>
         </is>
       </c>
       <c r="C239" s="3" t="inlineStr">
         <is>
-          <t>Ce que ce livre doit établir</t>
+          <t>Comment l'unité circulerait vraiment, et ce que chaque étape exige</t>
         </is>
       </c>
       <c r="D239" s="3" t="inlineStr">
@@ -16786,7 +16786,7 @@
       </c>
       <c r="G239" s="3" t="inlineStr">
         <is>
-          <t>descriptif</t>
+          <t>hybride</t>
         </is>
       </c>
       <c r="H239" s="3" t="inlineStr">
@@ -16794,39 +16794,43 @@
           <t>2026-09-07</t>
         </is>
       </c>
-      <c r="I239" s="3" t="inlineStr">
-        <is>
-          <t>oui</t>
-        </is>
-      </c>
+      <c r="I239" s="3" t="inlineStr"/>
       <c r="J239" s="3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K239" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="L239" s="3" t="inlineStr"/>
-      <c r="M239" s="3" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="L239" s="3" t="inlineStr">
+        <is>
+          <t>monnaie_comme_registre, hierarchie_monetaire, contrepartie_comptable, devise_cle, seuil_d_activation</t>
+        </is>
+      </c>
+      <c r="M239" s="3" t="inlineStr">
+        <is>
+          <t>L1.C24, L3.C05, L3.C09, L5.C02, L5.C09, L10.C01, L11.C02, L21.C01</t>
+        </is>
+      </c>
       <c r="N239" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-22-finance-non-bancaire/c01-ce-que-ce-livre-doit-etablir.md</t>
+          <t>corpus/livre-21-plomberie-financiere-mondiale/c02-comment-l-unite-circulerait-vraiment.md</t>
         </is>
       </c>
     </row>
     <row r="240">
       <c r="A240" s="2" t="inlineStr">
         <is>
-          <t>L23.C01</t>
+          <t>L21.C03</t>
         </is>
       </c>
       <c r="B240" s="3" t="inlineStr">
         <is>
-          <t>L23</t>
+          <t>L21</t>
         </is>
       </c>
       <c r="C240" s="3" t="inlineStr">
         <is>
-          <t>Ce que ce livre doit établir</t>
+          <t>Une opération de bout en bout, bilan par bilan</t>
         </is>
       </c>
       <c r="D240" s="3" t="inlineStr">
@@ -16856,41 +16860,41 @@
       </c>
       <c r="I240" s="3" t="inlineStr"/>
       <c r="J240" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="K240" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="K240" s="3" t="n">
-        <v>3</v>
-      </c>
       <c r="L240" s="3" t="inlineStr">
         <is>
-          <t>bareme, reflux_transactionnel, externalisation, essentiel_insolvable, polycentricite, regle_contre_discretion</t>
+          <t>contrepartie_comptable, creation_monetaire, reflux_collectif, demurrage, monnaie_comme_registre, hierarchie_monetaire</t>
         </is>
       </c>
       <c r="M240" s="3" t="inlineStr">
         <is>
-          <t>L1.C15, L5.C07, L10.C06, L11.C05, L11.C09, L11.C21, L11.C24, L18.C09, L20.C02, L20.C20</t>
+          <t>L1.C07, L1.C29, L10.C06, L10.C07, L11.C01, L11.C02, L11.C11, L11.C13, L11.C23, L21.C01, L21.C02</t>
         </is>
       </c>
       <c r="N240" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-23-fiscalite-mondiale-et-opacite/c01-ce-que-ce-livre-doit-etablir.md</t>
+          <t>corpus/livre-21-plomberie-financiere-mondiale/c03-une-operation-de-bout-en-bout.md</t>
         </is>
       </c>
     </row>
     <row r="241">
       <c r="A241" s="2" t="inlineStr">
         <is>
-          <t>L23.C02</t>
+          <t>L21.C04</t>
         </is>
       </c>
       <c r="B241" s="3" t="inlineStr">
         <is>
-          <t>L23</t>
+          <t>L21</t>
         </is>
       </c>
       <c r="C241" s="3" t="inlineStr">
         <is>
-          <t>La compétence que la convention ne crée pas, et le vote qu'elle a gagné</t>
+          <t>Ce que l'émission coûte aux banques qui l'hébergent</t>
         </is>
       </c>
       <c r="D241" s="3" t="inlineStr">
@@ -16910,7 +16914,7 @@
       </c>
       <c r="G241" s="3" t="inlineStr">
         <is>
-          <t>hybride</t>
+          <t>descriptif</t>
         </is>
       </c>
       <c r="H241" s="3" t="inlineStr">
@@ -16920,41 +16924,41 @@
       </c>
       <c r="I241" s="3" t="inlineStr"/>
       <c r="J241" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="K241" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="K241" s="3" t="n">
-        <v>3</v>
-      </c>
       <c r="L241" s="3" t="inlineStr">
         <is>
-          <t>polycentricite, bareme, reflux_transactionnel, seuil_d_activation, regle_contre_discretion, externalisation</t>
+          <t>contrepartie_comptable, creation_monetaire, hierarchie_monetaire, reflux_collectif, demurrage</t>
         </is>
       </c>
       <c r="M241" s="3" t="inlineStr">
         <is>
-          <t>L1.C25, L5.C04, L10.C06, L11.C21, L20.C02, L20.C20, L23.C01</t>
+          <t>L1.C07, L10.C01, L11.C02, L11.C07, L11.C09, L11.C11, L11.C23, L21.C02, L21.C03</t>
         </is>
       </c>
       <c r="N241" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-23-fiscalite-mondiale-et-opacite/c02-la-competence-que-la-convention-ne-cree-pas.md</t>
+          <t>corpus/livre-21-plomberie-financiere-mondiale/c04-ce-que-l-emission-coute-aux-banques-qui-l-hebergent.md</t>
         </is>
       </c>
     </row>
     <row r="242">
       <c r="A242" s="2" t="inlineStr">
         <is>
-          <t>L23.C03</t>
+          <t>L21.C05</t>
         </is>
       </c>
       <c r="B242" s="3" t="inlineStr">
         <is>
-          <t>L23</t>
+          <t>L21</t>
         </is>
       </c>
       <c r="C242" s="3" t="inlineStr">
         <is>
-          <t>F8 appliqué à une négociation en cours, et le résultat n'est pas le désarmement</t>
+          <t>La première infrastructure ouverte, et ce qu'elle renverse</t>
         </is>
       </c>
       <c r="D242" s="3" t="inlineStr">
@@ -16984,41 +16988,41 @@
       </c>
       <c r="I242" s="3" t="inlineStr"/>
       <c r="J242" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="K242" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="K242" s="3" t="n">
-        <v>3</v>
-      </c>
       <c r="L242" s="3" t="inlineStr">
         <is>
-          <t>regle_contre_discretion, polycentricite, seuil_d_activation, bareme, externalisation</t>
+          <t>seuil_d_activation, hierarchie_monetaire, monnaie_comme_registre, devise_cle, demurrage, contrepartie_comptable</t>
         </is>
       </c>
       <c r="M242" s="3" t="inlineStr">
         <is>
-          <t>L5.C04, L6.C09, L11.C21, L20.C02, L20.C13, L23.C01, L23.C02</t>
+          <t>L3.C09, L5.C02, L5.C09, L11.C01, L11.C02, L11.C07, L21.C01, L21.C02, L21.C03, L21.C04</t>
         </is>
       </c>
       <c r="N242" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-23-fiscalite-mondiale-et-opacite/c03-f8-applique-a-une-negociation-en-cours.md</t>
+          <t>corpus/livre-21-plomberie-financiere-mondiale/c05-la-premiere-infrastructure-ouverte-et-ce-qu-elle-renverse.md</t>
         </is>
       </c>
     </row>
     <row r="243">
       <c r="A243" s="2" t="inlineStr">
         <is>
-          <t>L23.C04</t>
+          <t>L21.C06</t>
         </is>
       </c>
       <c r="B243" s="3" t="inlineStr">
         <is>
-          <t>L23</t>
+          <t>L21</t>
         </is>
       </c>
       <c r="C243" s="3" t="inlineStr">
         <is>
-          <t>La transparence que le corpus supposait a été invalidée</t>
+          <t>La jambe qui reste, et ce qu'il faut pour la protéger</t>
         </is>
       </c>
       <c r="D243" s="3" t="inlineStr">
@@ -17051,38 +17055,38 @@
         <v>3</v>
       </c>
       <c r="K243" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L243" s="3" t="inlineStr">
         <is>
-          <t>regle_contre_discretion, externalisation, bareme, polycentricite, architecture_invisible</t>
+          <t>contrepartie_comptable, hierarchie_monetaire, monnaie_comme_registre, seuil_d_activation</t>
         </is>
       </c>
       <c r="M243" s="3" t="inlineStr">
         <is>
-          <t>L6.C09, L11.C13, L11.C25, L20.C20, L23.C01, L23.C02, L23.C03</t>
+          <t>L5.C02, L11.C02, L11.C11, L20.C02, L21.C02, L21.C03, L21.C05</t>
         </is>
       </c>
       <c r="N243" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-23-fiscalite-mondiale-et-opacite/c04-la-transparence-que-le-corpus-supposait-a-ete-invalidee.md</t>
+          <t>corpus/livre-21-plomberie-financiere-mondiale/c06-la-jambe-qui-reste-et-ce-qu-il-faut-pour-la-proteger.md</t>
         </is>
       </c>
     </row>
     <row r="244">
       <c r="A244" s="2" t="inlineStr">
         <is>
-          <t>L23.C05</t>
+          <t>L21.C07</t>
         </is>
       </c>
       <c r="B244" s="3" t="inlineStr">
         <is>
-          <t>L23</t>
+          <t>L21</t>
         </is>
       </c>
       <c r="C244" s="3" t="inlineStr">
         <is>
-          <t>Intéresser le percepteur, et ce que le taux révèle</t>
+          <t>Portée de la tranche</t>
         </is>
       </c>
       <c r="D244" s="3" t="inlineStr">
@@ -17102,7 +17106,7 @@
       </c>
       <c r="G244" s="3" t="inlineStr">
         <is>
-          <t>hybride</t>
+          <t>descriptif</t>
         </is>
       </c>
       <c r="H244" s="3" t="inlineStr">
@@ -17112,41 +17116,41 @@
       </c>
       <c r="I244" s="3" t="inlineStr"/>
       <c r="J244" s="3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K244" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L244" s="3" t="inlineStr">
         <is>
-          <t>bareme, reflux_transactionnel, regle_contre_discretion, polycentricite, seuil_d_activation</t>
+          <t>seuil_d_activation, contrepartie_comptable, hierarchie_monetaire, monnaie_comme_registre</t>
         </is>
       </c>
       <c r="M244" s="3" t="inlineStr">
         <is>
-          <t>L11.C21, L11.C24, L18.C09, L20.C20, L23.C01, L23.C02, L23.C03</t>
+          <t>L5.C02, L10.C06, L11.C01, L11.C02, L20.C01, L21.C01, L21.C02, L21.C03, L21.C04, L21.C05, L21.C06</t>
         </is>
       </c>
       <c r="N244" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-23-fiscalite-mondiale-et-opacite/c05-interesser-le-percepteur-et-ce-que-le-taux-revele.md</t>
+          <t>corpus/livre-21-plomberie-financiere-mondiale/c07-portee-de-la-tranche.md</t>
         </is>
       </c>
     </row>
     <row r="245">
       <c r="A245" s="2" t="inlineStr">
         <is>
-          <t>L23.C06</t>
+          <t>L22.C01</t>
         </is>
       </c>
       <c r="B245" s="3" t="inlineStr">
         <is>
-          <t>L23</t>
+          <t>L22</t>
         </is>
       </c>
       <c r="C245" s="3" t="inlineStr">
         <is>
-          <t>L'arbre appliqué à la fonte, et il ne reste que deux branches</t>
+          <t>Ce que ce livre doit établir</t>
         </is>
       </c>
       <c r="D245" s="3" t="inlineStr">
@@ -17166,7 +17170,7 @@
       </c>
       <c r="G245" s="3" t="inlineStr">
         <is>
-          <t>conception</t>
+          <t>descriptif</t>
         </is>
       </c>
       <c r="H245" s="3" t="inlineStr">
@@ -17179,38 +17183,38 @@
         <v>4</v>
       </c>
       <c r="K245" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L245" s="3" t="inlineStr">
         <is>
-          <t>bareme, reflux_transactionnel, monnaie_fondante, demurrage, regle_contre_discretion, essentiel_insolvable</t>
+          <t>architecture_invisible, systeme_monetaire_et_financier, reflux_collectif, reflux_transactionnel, hierarchie_monetaire, monnaie_comme_registre</t>
         </is>
       </c>
       <c r="M245" s="3" t="inlineStr">
         <is>
-          <t>L10.C06, L11.C05, L11.C09, L11.C21, L11.C24, L18.C09, L20.C02, L23.C01, L23.C02, L23.C03, L23.C04, L23.C05</t>
+          <t>L1.C09, L1.C19, L5.C09, L11.C02, L11.C05, L11.C09, L11.C27, L21.C03, L21.C04</t>
         </is>
       </c>
       <c r="N245" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-23-fiscalite-mondiale-et-opacite/c06-l-arbre-applique-a-la-fonte.md</t>
+          <t>corpus/livre-22-finance-non-bancaire/c01-ce-que-ce-livre-doit-etablir.md</t>
         </is>
       </c>
     </row>
     <row r="246">
       <c r="A246" s="2" t="inlineStr">
         <is>
-          <t>L23.C07</t>
+          <t>L22.C02</t>
         </is>
       </c>
       <c r="B246" s="3" t="inlineStr">
         <is>
-          <t>L23</t>
+          <t>L22</t>
         </is>
       </c>
       <c r="C246" s="3" t="inlineStr">
         <is>
-          <t>Portée de la tranche, et la moitié qui n'est pas commencée</t>
+          <t>Où va la monnaie émise, et pourquoi le reflux ne l'y suit pas</t>
         </is>
       </c>
       <c r="D246" s="3" t="inlineStr">
@@ -17240,41 +17244,41 @@
       </c>
       <c r="I246" s="3" t="inlineStr"/>
       <c r="J246" s="3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K246" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L246" s="3" t="inlineStr">
         <is>
-          <t>bareme, reflux_transactionnel, externalisation, regle_contre_discretion, polycentricite, essentiel_insolvable</t>
+          <t>reflux_transactionnel, reflux_collectif, demurrage, monnaie_endogene, architecture_invisible, hierarchie_monetaire</t>
         </is>
       </c>
       <c r="M246" s="3" t="inlineStr">
         <is>
-          <t>L10.C06, L11.C05, L11.C21, L11.C25, L18.C09, L20.C20, L23.C01, L23.C02, L23.C03, L23.C04, L23.C05, L23.C06</t>
+          <t>L1.C19, L5.C09, L11.C02, L11.C05, L11.C09, L11.C27, L21.C03, L22.C01, L23.C04</t>
         </is>
       </c>
       <c r="N246" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-23-fiscalite-mondiale-et-opacite/c07-portee-de-la-tranche.md</t>
+          <t>corpus/livre-22-finance-non-bancaire/c02-ou-va-la-monnaie-emise.md</t>
         </is>
       </c>
     </row>
     <row r="247">
       <c r="A247" s="2" t="inlineStr">
         <is>
-          <t>L24.C01</t>
+          <t>L22.C03</t>
         </is>
       </c>
       <c r="B247" s="3" t="inlineStr">
         <is>
-          <t>L24</t>
+          <t>L22</t>
         </is>
       </c>
       <c r="C247" s="3" t="inlineStr">
         <is>
-          <t>Ce que ce livre doit établir</t>
+          <t>Le barème existe déjà, et il a trois pièces que le corpus n'a pas</t>
         </is>
       </c>
       <c r="D247" s="3" t="inlineStr">
@@ -17294,7 +17298,7 @@
       </c>
       <c r="G247" s="3" t="inlineStr">
         <is>
-          <t>descriptif</t>
+          <t>hybride</t>
         </is>
       </c>
       <c r="H247" s="3" t="inlineStr">
@@ -17302,39 +17306,43 @@
           <t>2026-09-07</t>
         </is>
       </c>
-      <c r="I247" s="3" t="inlineStr">
-        <is>
-          <t>oui</t>
-        </is>
-      </c>
+      <c r="I247" s="3" t="inlineStr"/>
       <c r="J247" s="3" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K247" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="L247" s="3" t="inlineStr"/>
-      <c r="M247" s="3" t="inlineStr"/>
+        <v>4</v>
+      </c>
+      <c r="L247" s="3" t="inlineStr">
+        <is>
+          <t>qualification_regenerative, bareme, additionnalite, indicateur_de_progres, communs, plafond_ecologique</t>
+        </is>
+      </c>
+      <c r="M247" s="3" t="inlineStr">
+        <is>
+          <t>L11.C13, L11.C11, L11.C25, L12.C01, L18.C06, L22.C01, L25.C01</t>
+        </is>
+      </c>
       <c r="N247" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-24-conditions-materielles-de-la-vie/c01-ce-que-ce-livre-doit-etablir.md</t>
+          <t>corpus/livre-22-finance-non-bancaire/c03-le-bareme-existe-deja.md</t>
         </is>
       </c>
     </row>
     <row r="248">
       <c r="A248" s="2" t="inlineStr">
         <is>
-          <t>L25.C01</t>
+          <t>L22.C04</t>
         </is>
       </c>
       <c r="B248" s="3" t="inlineStr">
         <is>
-          <t>L25</t>
+          <t>L22</t>
         </is>
       </c>
       <c r="C248" s="3" t="inlineStr">
         <is>
-          <t>Ce que ce livre doit établir</t>
+          <t>Les critères réels ne mesurent pas, ils certifient</t>
         </is>
       </c>
       <c r="D248" s="3" t="inlineStr">
@@ -17354,7 +17362,7 @@
       </c>
       <c r="G248" s="3" t="inlineStr">
         <is>
-          <t>descriptif</t>
+          <t>hybride</t>
         </is>
       </c>
       <c r="H248" s="3" t="inlineStr">
@@ -17362,87 +17370,723 @@
           <t>2026-09-07</t>
         </is>
       </c>
-      <c r="I248" s="3" t="inlineStr">
-        <is>
-          <t>oui</t>
-        </is>
-      </c>
+      <c r="I248" s="3" t="inlineStr"/>
       <c r="J248" s="3" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K248" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="L248" s="3" t="inlineStr"/>
-      <c r="M248" s="3" t="inlineStr"/>
+        <v>4</v>
+      </c>
+      <c r="L248" s="3" t="inlineStr">
+        <is>
+          <t>qualification_regenerative, bareme, additionnalite, communs, valorisation_des_communs, indicateur_de_progres</t>
+        </is>
+      </c>
+      <c r="M248" s="3" t="inlineStr">
+        <is>
+          <t>L6.C06, L11.C13, L11.C16, L11.C25, L13.C01, L14.C01, L18.C06, L22.C03</t>
+        </is>
+      </c>
       <c r="N248" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-25-repartition-et-justice-sociale/c01-ce-que-ce-livre-doit-etablir.md</t>
+          <t>corpus/livre-22-finance-non-bancaire/c04-les-criteres-reels-ne-mesurent-pas.md</t>
         </is>
       </c>
     </row>
     <row r="249">
       <c r="A249" s="2" t="inlineStr">
         <is>
+          <t>L22.C05</t>
+        </is>
+      </c>
+      <c r="B249" s="3" t="inlineStr">
+        <is>
+          <t>L22</t>
+        </is>
+      </c>
+      <c r="C249" s="3" t="inlineStr">
+        <is>
+          <t>L'épargne retraite, et le dilemme du troisième instrument</t>
+        </is>
+      </c>
+      <c r="D249" s="3" t="inlineStr">
+        <is>
+          <t>brouillon</t>
+        </is>
+      </c>
+      <c r="E249" s="3" t="inlineStr">
+        <is>
+          <t>preparatoire</t>
+        </is>
+      </c>
+      <c r="F249" s="3" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="G249" s="3" t="inlineStr">
+        <is>
+          <t>hybride</t>
+        </is>
+      </c>
+      <c r="H249" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="I249" s="3" t="inlineStr"/>
+      <c r="J249" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="K249" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="L249" s="3" t="inlineStr">
+        <is>
+          <t>reflux_collectif, demurrage, essentiel_insolvable, plancher_social, solvabilite_anticipee, architecture_invisible</t>
+        </is>
+      </c>
+      <c r="M249" s="3" t="inlineStr">
+        <is>
+          <t>L1.C15, L11.C07, L11.C09, L11.C18, L22.C01, L22.C02, L25.C01</t>
+        </is>
+      </c>
+      <c r="N249" s="3" t="inlineStr">
+        <is>
+          <t>corpus/livre-22-finance-non-bancaire/c05-l-epargne-retraite-et-le-dilemme-du-troisieme-instrument.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" s="2" t="inlineStr">
+        <is>
+          <t>L23.C01</t>
+        </is>
+      </c>
+      <c r="B250" s="3" t="inlineStr">
+        <is>
+          <t>L23</t>
+        </is>
+      </c>
+      <c r="C250" s="3" t="inlineStr">
+        <is>
+          <t>Ce que ce livre doit établir</t>
+        </is>
+      </c>
+      <c r="D250" s="3" t="inlineStr">
+        <is>
+          <t>brouillon</t>
+        </is>
+      </c>
+      <c r="E250" s="3" t="inlineStr">
+        <is>
+          <t>preparatoire</t>
+        </is>
+      </c>
+      <c r="F250" s="3" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="G250" s="3" t="inlineStr">
+        <is>
+          <t>conception</t>
+        </is>
+      </c>
+      <c r="H250" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="I250" s="3" t="inlineStr"/>
+      <c r="J250" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="K250" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="L250" s="3" t="inlineStr">
+        <is>
+          <t>bareme, reflux_transactionnel, externalisation, essentiel_insolvable, polycentricite, regle_contre_discretion</t>
+        </is>
+      </c>
+      <c r="M250" s="3" t="inlineStr">
+        <is>
+          <t>L1.C15, L5.C07, L10.C06, L11.C05, L11.C09, L11.C21, L11.C24, L18.C09, L20.C02, L20.C20</t>
+        </is>
+      </c>
+      <c r="N250" s="3" t="inlineStr">
+        <is>
+          <t>corpus/livre-23-fiscalite-mondiale-et-opacite/c01-ce-que-ce-livre-doit-etablir.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" s="2" t="inlineStr">
+        <is>
+          <t>L23.C02</t>
+        </is>
+      </c>
+      <c r="B251" s="3" t="inlineStr">
+        <is>
+          <t>L23</t>
+        </is>
+      </c>
+      <c r="C251" s="3" t="inlineStr">
+        <is>
+          <t>La compétence que la convention ne crée pas, et le vote qu'elle a gagné</t>
+        </is>
+      </c>
+      <c r="D251" s="3" t="inlineStr">
+        <is>
+          <t>brouillon</t>
+        </is>
+      </c>
+      <c r="E251" s="3" t="inlineStr">
+        <is>
+          <t>preparatoire</t>
+        </is>
+      </c>
+      <c r="F251" s="3" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="G251" s="3" t="inlineStr">
+        <is>
+          <t>hybride</t>
+        </is>
+      </c>
+      <c r="H251" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="I251" s="3" t="inlineStr"/>
+      <c r="J251" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="K251" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="L251" s="3" t="inlineStr">
+        <is>
+          <t>polycentricite, bareme, reflux_transactionnel, seuil_d_activation, regle_contre_discretion, externalisation</t>
+        </is>
+      </c>
+      <c r="M251" s="3" t="inlineStr">
+        <is>
+          <t>L1.C25, L5.C04, L10.C06, L11.C21, L20.C02, L20.C20, L23.C01</t>
+        </is>
+      </c>
+      <c r="N251" s="3" t="inlineStr">
+        <is>
+          <t>corpus/livre-23-fiscalite-mondiale-et-opacite/c02-la-competence-que-la-convention-ne-cree-pas.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" s="2" t="inlineStr">
+        <is>
+          <t>L23.C03</t>
+        </is>
+      </c>
+      <c r="B252" s="3" t="inlineStr">
+        <is>
+          <t>L23</t>
+        </is>
+      </c>
+      <c r="C252" s="3" t="inlineStr">
+        <is>
+          <t>F8 appliqué à une négociation en cours, et le résultat n'est pas le désarmement</t>
+        </is>
+      </c>
+      <c r="D252" s="3" t="inlineStr">
+        <is>
+          <t>brouillon</t>
+        </is>
+      </c>
+      <c r="E252" s="3" t="inlineStr">
+        <is>
+          <t>preparatoire</t>
+        </is>
+      </c>
+      <c r="F252" s="3" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="G252" s="3" t="inlineStr">
+        <is>
+          <t>hybride</t>
+        </is>
+      </c>
+      <c r="H252" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="I252" s="3" t="inlineStr"/>
+      <c r="J252" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="K252" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="L252" s="3" t="inlineStr">
+        <is>
+          <t>regle_contre_discretion, polycentricite, seuil_d_activation, bareme, externalisation</t>
+        </is>
+      </c>
+      <c r="M252" s="3" t="inlineStr">
+        <is>
+          <t>L5.C04, L6.C09, L11.C21, L20.C02, L20.C13, L23.C01, L23.C02</t>
+        </is>
+      </c>
+      <c r="N252" s="3" t="inlineStr">
+        <is>
+          <t>corpus/livre-23-fiscalite-mondiale-et-opacite/c03-f8-applique-a-une-negociation-en-cours.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" s="2" t="inlineStr">
+        <is>
+          <t>L23.C04</t>
+        </is>
+      </c>
+      <c r="B253" s="3" t="inlineStr">
+        <is>
+          <t>L23</t>
+        </is>
+      </c>
+      <c r="C253" s="3" t="inlineStr">
+        <is>
+          <t>La transparence que le corpus supposait a été invalidée</t>
+        </is>
+      </c>
+      <c r="D253" s="3" t="inlineStr">
+        <is>
+          <t>brouillon</t>
+        </is>
+      </c>
+      <c r="E253" s="3" t="inlineStr">
+        <is>
+          <t>preparatoire</t>
+        </is>
+      </c>
+      <c r="F253" s="3" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="G253" s="3" t="inlineStr">
+        <is>
+          <t>hybride</t>
+        </is>
+      </c>
+      <c r="H253" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="I253" s="3" t="inlineStr"/>
+      <c r="J253" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="K253" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="L253" s="3" t="inlineStr">
+        <is>
+          <t>regle_contre_discretion, externalisation, bareme, polycentricite, architecture_invisible</t>
+        </is>
+      </c>
+      <c r="M253" s="3" t="inlineStr">
+        <is>
+          <t>L6.C09, L11.C13, L11.C25, L20.C20, L23.C01, L23.C02, L23.C03</t>
+        </is>
+      </c>
+      <c r="N253" s="3" t="inlineStr">
+        <is>
+          <t>corpus/livre-23-fiscalite-mondiale-et-opacite/c04-la-transparence-que-le-corpus-supposait-a-ete-invalidee.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" s="2" t="inlineStr">
+        <is>
+          <t>L23.C05</t>
+        </is>
+      </c>
+      <c r="B254" s="3" t="inlineStr">
+        <is>
+          <t>L23</t>
+        </is>
+      </c>
+      <c r="C254" s="3" t="inlineStr">
+        <is>
+          <t>Intéresser le percepteur, et ce que le taux révèle</t>
+        </is>
+      </c>
+      <c r="D254" s="3" t="inlineStr">
+        <is>
+          <t>brouillon</t>
+        </is>
+      </c>
+      <c r="E254" s="3" t="inlineStr">
+        <is>
+          <t>preparatoire</t>
+        </is>
+      </c>
+      <c r="F254" s="3" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="G254" s="3" t="inlineStr">
+        <is>
+          <t>hybride</t>
+        </is>
+      </c>
+      <c r="H254" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="I254" s="3" t="inlineStr"/>
+      <c r="J254" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="K254" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="L254" s="3" t="inlineStr">
+        <is>
+          <t>bareme, reflux_transactionnel, regle_contre_discretion, polycentricite, seuil_d_activation</t>
+        </is>
+      </c>
+      <c r="M254" s="3" t="inlineStr">
+        <is>
+          <t>L11.C21, L11.C24, L18.C09, L20.C20, L23.C01, L23.C02, L23.C03</t>
+        </is>
+      </c>
+      <c r="N254" s="3" t="inlineStr">
+        <is>
+          <t>corpus/livre-23-fiscalite-mondiale-et-opacite/c05-interesser-le-percepteur-et-ce-que-le-taux-revele.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" s="2" t="inlineStr">
+        <is>
+          <t>L23.C06</t>
+        </is>
+      </c>
+      <c r="B255" s="3" t="inlineStr">
+        <is>
+          <t>L23</t>
+        </is>
+      </c>
+      <c r="C255" s="3" t="inlineStr">
+        <is>
+          <t>L'arbre appliqué à la fonte, et il ne reste que deux branches</t>
+        </is>
+      </c>
+      <c r="D255" s="3" t="inlineStr">
+        <is>
+          <t>brouillon</t>
+        </is>
+      </c>
+      <c r="E255" s="3" t="inlineStr">
+        <is>
+          <t>preparatoire</t>
+        </is>
+      </c>
+      <c r="F255" s="3" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="G255" s="3" t="inlineStr">
+        <is>
+          <t>conception</t>
+        </is>
+      </c>
+      <c r="H255" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="I255" s="3" t="inlineStr"/>
+      <c r="J255" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="K255" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="L255" s="3" t="inlineStr">
+        <is>
+          <t>bareme, reflux_transactionnel, monnaie_fondante, demurrage, regle_contre_discretion, essentiel_insolvable</t>
+        </is>
+      </c>
+      <c r="M255" s="3" t="inlineStr">
+        <is>
+          <t>L10.C06, L11.C05, L11.C09, L11.C21, L11.C24, L18.C09, L20.C02, L23.C01, L23.C02, L23.C03, L23.C04, L23.C05</t>
+        </is>
+      </c>
+      <c r="N255" s="3" t="inlineStr">
+        <is>
+          <t>corpus/livre-23-fiscalite-mondiale-et-opacite/c06-l-arbre-applique-a-la-fonte.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" s="2" t="inlineStr">
+        <is>
+          <t>L23.C07</t>
+        </is>
+      </c>
+      <c r="B256" s="3" t="inlineStr">
+        <is>
+          <t>L23</t>
+        </is>
+      </c>
+      <c r="C256" s="3" t="inlineStr">
+        <is>
+          <t>Portée de la tranche, et la moitié qui n'est pas commencée</t>
+        </is>
+      </c>
+      <c r="D256" s="3" t="inlineStr">
+        <is>
+          <t>brouillon</t>
+        </is>
+      </c>
+      <c r="E256" s="3" t="inlineStr">
+        <is>
+          <t>preparatoire</t>
+        </is>
+      </c>
+      <c r="F256" s="3" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="G256" s="3" t="inlineStr">
+        <is>
+          <t>conception</t>
+        </is>
+      </c>
+      <c r="H256" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="I256" s="3" t="inlineStr"/>
+      <c r="J256" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="K256" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="L256" s="3" t="inlineStr">
+        <is>
+          <t>bareme, reflux_transactionnel, externalisation, regle_contre_discretion, polycentricite, essentiel_insolvable</t>
+        </is>
+      </c>
+      <c r="M256" s="3" t="inlineStr">
+        <is>
+          <t>L10.C06, L11.C05, L11.C21, L11.C25, L18.C09, L20.C20, L23.C01, L23.C02, L23.C03, L23.C04, L23.C05, L23.C06</t>
+        </is>
+      </c>
+      <c r="N256" s="3" t="inlineStr">
+        <is>
+          <t>corpus/livre-23-fiscalite-mondiale-et-opacite/c07-portee-de-la-tranche.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" s="2" t="inlineStr">
+        <is>
+          <t>L24.C01</t>
+        </is>
+      </c>
+      <c r="B257" s="3" t="inlineStr">
+        <is>
+          <t>L24</t>
+        </is>
+      </c>
+      <c r="C257" s="3" t="inlineStr">
+        <is>
+          <t>Ce que ce livre doit établir</t>
+        </is>
+      </c>
+      <c r="D257" s="3" t="inlineStr">
+        <is>
+          <t>brouillon</t>
+        </is>
+      </c>
+      <c r="E257" s="3" t="inlineStr">
+        <is>
+          <t>preparatoire</t>
+        </is>
+      </c>
+      <c r="F257" s="3" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="G257" s="3" t="inlineStr">
+        <is>
+          <t>descriptif</t>
+        </is>
+      </c>
+      <c r="H257" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="I257" s="3" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="J257" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="K257" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="L257" s="3" t="inlineStr"/>
+      <c r="M257" s="3" t="inlineStr"/>
+      <c r="N257" s="3" t="inlineStr">
+        <is>
+          <t>corpus/livre-24-conditions-materielles-de-la-vie/c01-ce-que-ce-livre-doit-etablir.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" s="2" t="inlineStr">
+        <is>
+          <t>L25.C01</t>
+        </is>
+      </c>
+      <c r="B258" s="3" t="inlineStr">
+        <is>
+          <t>L25</t>
+        </is>
+      </c>
+      <c r="C258" s="3" t="inlineStr">
+        <is>
+          <t>Ce que ce livre doit établir</t>
+        </is>
+      </c>
+      <c r="D258" s="3" t="inlineStr">
+        <is>
+          <t>brouillon</t>
+        </is>
+      </c>
+      <c r="E258" s="3" t="inlineStr">
+        <is>
+          <t>preparatoire</t>
+        </is>
+      </c>
+      <c r="F258" s="3" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="G258" s="3" t="inlineStr">
+        <is>
+          <t>descriptif</t>
+        </is>
+      </c>
+      <c r="H258" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="I258" s="3" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="J258" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="K258" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="L258" s="3" t="inlineStr"/>
+      <c r="M258" s="3" t="inlineStr"/>
+      <c r="N258" s="3" t="inlineStr">
+        <is>
+          <t>corpus/livre-25-repartition-et-justice-sociale/c01-ce-que-ce-livre-doit-etablir.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" s="2" t="inlineStr">
+        <is>
           <t>L26.C01</t>
         </is>
       </c>
-      <c r="B249" s="3" t="inlineStr">
+      <c r="B259" s="3" t="inlineStr">
         <is>
           <t>L26</t>
         </is>
       </c>
-      <c r="C249" s="3" t="inlineStr">
+      <c r="C259" s="3" t="inlineStr">
         <is>
           <t>Ce que ce livre doit établir</t>
         </is>
       </c>
-      <c r="D249" s="3" t="inlineStr">
-        <is>
-          <t>brouillon</t>
-        </is>
-      </c>
-      <c r="E249" s="3" t="inlineStr">
-        <is>
-          <t>preparatoire</t>
-        </is>
-      </c>
-      <c r="F249" s="3" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="G249" s="3" t="inlineStr">
+      <c r="D259" s="3" t="inlineStr">
+        <is>
+          <t>brouillon</t>
+        </is>
+      </c>
+      <c r="E259" s="3" t="inlineStr">
+        <is>
+          <t>preparatoire</t>
+        </is>
+      </c>
+      <c r="F259" s="3" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="G259" s="3" t="inlineStr">
         <is>
           <t>descriptif</t>
         </is>
       </c>
-      <c r="H249" s="3" t="inlineStr">
+      <c r="H259" s="3" t="inlineStr">
         <is>
           <t>2026-09-07</t>
         </is>
       </c>
-      <c r="I249" s="3" t="inlineStr">
+      <c r="I259" s="3" t="inlineStr">
         <is>
           <t>oui</t>
         </is>
       </c>
-      <c r="J249" s="3" t="n">
+      <c r="J259" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="K249" s="3" t="n">
+      <c r="K259" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="L249" s="3" t="inlineStr"/>
-      <c r="M249" s="3" t="inlineStr"/>
-      <c r="N249" s="3" t="inlineStr">
+      <c r="L259" s="3" t="inlineStr"/>
+      <c r="M259" s="3" t="inlineStr"/>
+      <c r="N259" s="3" t="inlineStr">
         <is>
           <t>corpus/livre-26-thermodynamique-et-processus-economique/c01-ce-que-ce-livre-doit-etablir.md</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:N249"/>
+  <autoFilter ref="A1:N259"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -17501,7 +18145,7 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="5">
@@ -17511,7 +18155,7 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="6">
@@ -17521,7 +18165,7 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>248</v>
+        <v>258</v>
       </c>
     </row>
     <row r="7">
@@ -17531,7 +18175,7 @@
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="8">
@@ -17541,7 +18185,7 @@
         </is>
       </c>
       <c r="B8" s="3" t="n">
-        <v>235</v>
+        <v>246</v>
       </c>
     </row>
     <row r="9">
@@ -17551,7 +18195,7 @@
         </is>
       </c>
       <c r="B9" s="3" t="n">
-        <v>239</v>
+        <v>249</v>
       </c>
     </row>
     <row r="10">
@@ -17571,7 +18215,7 @@
         </is>
       </c>
       <c r="B11" s="3" t="n">
-        <v>1193</v>
+        <v>1234</v>
       </c>
     </row>
     <row r="12">
@@ -17581,7 +18225,7 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>992</v>
+        <v>1027</v>
       </c>
     </row>
     <row r="13">
@@ -17596,7 +18240,7 @@
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>L0, L9, L12, L13, L14, L15, L16, L17, L19, L22, L24, L25, L26</t>
+          <t>L0, L9, L12, L13, L14, L15, L16, L17, L19, L24, L25, L26</t>
         </is>
       </c>
     </row>
@@ -17675,7 +18319,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C276"/>
+  <dimension ref="A1:C286"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -22082,7 +22726,7 @@
       </c>
       <c r="C259" s="6" t="inlineStr">
         <is>
-          <t>en-cours — 1 chapitre(s)</t>
+          <t>en-cours — 7 chapitre(s)</t>
         </is>
       </c>
     </row>
@@ -22104,31 +22748,31 @@
       </c>
     </row>
     <row r="261">
-      <c r="A261" s="6" t="inlineStr">
-        <is>
-          <t>L22</t>
-        </is>
-      </c>
-      <c r="B261" s="6" t="inlineStr">
-        <is>
-          <t>Le pouvoir de la finance non bancaire</t>
-        </is>
-      </c>
-      <c r="C261" s="6" t="inlineStr">
-        <is>
-          <t>candidat — AMORCE SEULE</t>
+      <c r="A261" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    L21.C02</t>
+        </is>
+      </c>
+      <c r="B261" s="3" t="inlineStr">
+        <is>
+          <t>Comment l'unité circulerait vraiment, et ce que chaque étape exige</t>
+        </is>
+      </c>
+      <c r="C261" s="3" t="inlineStr">
+        <is>
+          <t>brouillon</t>
         </is>
       </c>
     </row>
     <row r="262">
       <c r="A262" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L22.C01</t>
+          <t xml:space="preserve">    L21.C03</t>
         </is>
       </c>
       <c r="B262" s="3" t="inlineStr">
         <is>
-          <t>[AMORCE] Ce que ce livre doit établir</t>
+          <t>Une opération de bout en bout, bilan par bilan</t>
         </is>
       </c>
       <c r="C262" s="3" t="inlineStr">
@@ -22138,31 +22782,31 @@
       </c>
     </row>
     <row r="263">
-      <c r="A263" s="6" t="inlineStr">
-        <is>
-          <t>L23</t>
-        </is>
-      </c>
-      <c r="B263" s="6" t="inlineStr">
-        <is>
-          <t>Fiscalité mondiale, finance offshore et opacité</t>
-        </is>
-      </c>
-      <c r="C263" s="6" t="inlineStr">
-        <is>
-          <t>en-cours — 7 chapitre(s)</t>
+      <c r="A263" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    L21.C04</t>
+        </is>
+      </c>
+      <c r="B263" s="3" t="inlineStr">
+        <is>
+          <t>Ce que l'émission coûte aux banques qui l'hébergent</t>
+        </is>
+      </c>
+      <c r="C263" s="3" t="inlineStr">
+        <is>
+          <t>brouillon</t>
         </is>
       </c>
     </row>
     <row r="264">
       <c r="A264" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L23.C01</t>
+          <t xml:space="preserve">    L21.C05</t>
         </is>
       </c>
       <c r="B264" s="3" t="inlineStr">
         <is>
-          <t>Ce que ce livre doit établir</t>
+          <t>La première infrastructure ouverte, et ce qu'elle renverse</t>
         </is>
       </c>
       <c r="C264" s="3" t="inlineStr">
@@ -22174,12 +22818,12 @@
     <row r="265">
       <c r="A265" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L23.C02</t>
+          <t xml:space="preserve">    L21.C06</t>
         </is>
       </c>
       <c r="B265" s="3" t="inlineStr">
         <is>
-          <t>La compétence que la convention ne crée pas, et le vote qu'elle a gagné</t>
+          <t>La jambe qui reste, et ce qu'il faut pour la protéger</t>
         </is>
       </c>
       <c r="C265" s="3" t="inlineStr">
@@ -22191,12 +22835,12 @@
     <row r="266">
       <c r="A266" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L23.C03</t>
+          <t xml:space="preserve">    L21.C07</t>
         </is>
       </c>
       <c r="B266" s="3" t="inlineStr">
         <is>
-          <t>F8 appliqué à une négociation en cours, et le résultat n'est pas le désarmement</t>
+          <t>Portée de la tranche</t>
         </is>
       </c>
       <c r="C266" s="3" t="inlineStr">
@@ -22206,31 +22850,31 @@
       </c>
     </row>
     <row r="267">
-      <c r="A267" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    L23.C04</t>
-        </is>
-      </c>
-      <c r="B267" s="3" t="inlineStr">
-        <is>
-          <t>La transparence que le corpus supposait a été invalidée</t>
-        </is>
-      </c>
-      <c r="C267" s="3" t="inlineStr">
-        <is>
-          <t>brouillon</t>
+      <c r="A267" s="6" t="inlineStr">
+        <is>
+          <t>L22</t>
+        </is>
+      </c>
+      <c r="B267" s="6" t="inlineStr">
+        <is>
+          <t>Le pouvoir de la finance non bancaire</t>
+        </is>
+      </c>
+      <c r="C267" s="6" t="inlineStr">
+        <is>
+          <t>en-cours — 5 chapitre(s)</t>
         </is>
       </c>
     </row>
     <row r="268">
       <c r="A268" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L23.C05</t>
+          <t xml:space="preserve">    L22.C01</t>
         </is>
       </c>
       <c r="B268" s="3" t="inlineStr">
         <is>
-          <t>Intéresser le percepteur, et ce que le taux révèle</t>
+          <t>Ce que ce livre doit établir</t>
         </is>
       </c>
       <c r="C268" s="3" t="inlineStr">
@@ -22242,12 +22886,12 @@
     <row r="269">
       <c r="A269" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L23.C06</t>
+          <t xml:space="preserve">    L22.C02</t>
         </is>
       </c>
       <c r="B269" s="3" t="inlineStr">
         <is>
-          <t>L'arbre appliqué à la fonte, et il ne reste que deux branches</t>
+          <t>Où va la monnaie émise, et pourquoi le reflux ne l'y suit pas</t>
         </is>
       </c>
       <c r="C269" s="3" t="inlineStr">
@@ -22259,12 +22903,12 @@
     <row r="270">
       <c r="A270" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L23.C07</t>
+          <t xml:space="preserve">    L22.C03</t>
         </is>
       </c>
       <c r="B270" s="3" t="inlineStr">
         <is>
-          <t>Portée de la tranche, et la moitié qui n'est pas commencée</t>
+          <t>Le barème existe déjà, et il a trois pièces que le corpus n'a pas</t>
         </is>
       </c>
       <c r="C270" s="3" t="inlineStr">
@@ -22274,31 +22918,31 @@
       </c>
     </row>
     <row r="271">
-      <c r="A271" s="6" t="inlineStr">
-        <is>
-          <t>L24</t>
-        </is>
-      </c>
-      <c r="B271" s="6" t="inlineStr">
-        <is>
-          <t>Les conditions matérielles de la vie</t>
-        </is>
-      </c>
-      <c r="C271" s="6" t="inlineStr">
-        <is>
-          <t>candidat — AMORCE SEULE</t>
+      <c r="A271" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    L22.C04</t>
+        </is>
+      </c>
+      <c r="B271" s="3" t="inlineStr">
+        <is>
+          <t>Les critères réels ne mesurent pas, ils certifient</t>
+        </is>
+      </c>
+      <c r="C271" s="3" t="inlineStr">
+        <is>
+          <t>brouillon</t>
         </is>
       </c>
     </row>
     <row r="272">
       <c r="A272" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L24.C01</t>
+          <t xml:space="preserve">    L22.C05</t>
         </is>
       </c>
       <c r="B272" s="3" t="inlineStr">
         <is>
-          <t>[AMORCE] Ce que ce livre doit établir</t>
+          <t>L'épargne retraite, et le dilemme du troisième instrument</t>
         </is>
       </c>
       <c r="C272" s="3" t="inlineStr">
@@ -22310,29 +22954,29 @@
     <row r="273">
       <c r="A273" s="6" t="inlineStr">
         <is>
-          <t>L25</t>
+          <t>L23</t>
         </is>
       </c>
       <c r="B273" s="6" t="inlineStr">
         <is>
-          <t>Répartition, besoins essentiels et justice sociale</t>
+          <t>Fiscalité mondiale, finance offshore et opacité</t>
         </is>
       </c>
       <c r="C273" s="6" t="inlineStr">
         <is>
-          <t>candidat — AMORCE SEULE</t>
+          <t>en-cours — 7 chapitre(s)</t>
         </is>
       </c>
     </row>
     <row r="274">
       <c r="A274" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L25.C01</t>
+          <t xml:space="preserve">    L23.C01</t>
         </is>
       </c>
       <c r="B274" s="3" t="inlineStr">
         <is>
-          <t>[AMORCE] Ce que ce livre doit établir</t>
+          <t>Ce que ce livre doit établir</t>
         </is>
       </c>
       <c r="C274" s="3" t="inlineStr">
@@ -22342,34 +22986,204 @@
       </c>
     </row>
     <row r="275">
-      <c r="A275" s="6" t="inlineStr">
-        <is>
-          <t>L26</t>
-        </is>
-      </c>
-      <c r="B275" s="6" t="inlineStr">
-        <is>
-          <t>Thermodynamique, énergie et processus économique</t>
-        </is>
-      </c>
-      <c r="C275" s="6" t="inlineStr">
-        <is>
-          <t>candidat — AMORCE SEULE</t>
+      <c r="A275" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    L23.C02</t>
+        </is>
+      </c>
+      <c r="B275" s="3" t="inlineStr">
+        <is>
+          <t>La compétence que la convention ne crée pas, et le vote qu'elle a gagné</t>
+        </is>
+      </c>
+      <c r="C275" s="3" t="inlineStr">
+        <is>
+          <t>brouillon</t>
         </is>
       </c>
     </row>
     <row r="276">
       <c r="A276" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">    L23.C03</t>
+        </is>
+      </c>
+      <c r="B276" s="3" t="inlineStr">
+        <is>
+          <t>F8 appliqué à une négociation en cours, et le résultat n'est pas le désarmement</t>
+        </is>
+      </c>
+      <c r="C276" s="3" t="inlineStr">
+        <is>
+          <t>brouillon</t>
+        </is>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    L23.C04</t>
+        </is>
+      </c>
+      <c r="B277" s="3" t="inlineStr">
+        <is>
+          <t>La transparence que le corpus supposait a été invalidée</t>
+        </is>
+      </c>
+      <c r="C277" s="3" t="inlineStr">
+        <is>
+          <t>brouillon</t>
+        </is>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    L23.C05</t>
+        </is>
+      </c>
+      <c r="B278" s="3" t="inlineStr">
+        <is>
+          <t>Intéresser le percepteur, et ce que le taux révèle</t>
+        </is>
+      </c>
+      <c r="C278" s="3" t="inlineStr">
+        <is>
+          <t>brouillon</t>
+        </is>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    L23.C06</t>
+        </is>
+      </c>
+      <c r="B279" s="3" t="inlineStr">
+        <is>
+          <t>L'arbre appliqué à la fonte, et il ne reste que deux branches</t>
+        </is>
+      </c>
+      <c r="C279" s="3" t="inlineStr">
+        <is>
+          <t>brouillon</t>
+        </is>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    L23.C07</t>
+        </is>
+      </c>
+      <c r="B280" s="3" t="inlineStr">
+        <is>
+          <t>Portée de la tranche, et la moitié qui n'est pas commencée</t>
+        </is>
+      </c>
+      <c r="C280" s="3" t="inlineStr">
+        <is>
+          <t>brouillon</t>
+        </is>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" s="6" t="inlineStr">
+        <is>
+          <t>L24</t>
+        </is>
+      </c>
+      <c r="B281" s="6" t="inlineStr">
+        <is>
+          <t>Les conditions matérielles de la vie</t>
+        </is>
+      </c>
+      <c r="C281" s="6" t="inlineStr">
+        <is>
+          <t>candidat — AMORCE SEULE</t>
+        </is>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    L24.C01</t>
+        </is>
+      </c>
+      <c r="B282" s="3" t="inlineStr">
+        <is>
+          <t>[AMORCE] Ce que ce livre doit établir</t>
+        </is>
+      </c>
+      <c r="C282" s="3" t="inlineStr">
+        <is>
+          <t>brouillon</t>
+        </is>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" s="6" t="inlineStr">
+        <is>
+          <t>L25</t>
+        </is>
+      </c>
+      <c r="B283" s="6" t="inlineStr">
+        <is>
+          <t>Répartition, besoins essentiels et justice sociale</t>
+        </is>
+      </c>
+      <c r="C283" s="6" t="inlineStr">
+        <is>
+          <t>candidat — AMORCE SEULE</t>
+        </is>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    L25.C01</t>
+        </is>
+      </c>
+      <c r="B284" s="3" t="inlineStr">
+        <is>
+          <t>[AMORCE] Ce que ce livre doit établir</t>
+        </is>
+      </c>
+      <c r="C284" s="3" t="inlineStr">
+        <is>
+          <t>brouillon</t>
+        </is>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" s="6" t="inlineStr">
+        <is>
+          <t>L26</t>
+        </is>
+      </c>
+      <c r="B285" s="6" t="inlineStr">
+        <is>
+          <t>Thermodynamique, énergie et processus économique</t>
+        </is>
+      </c>
+      <c r="C285" s="6" t="inlineStr">
+        <is>
+          <t>candidat — AMORCE SEULE</t>
+        </is>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">    L26.C01</t>
         </is>
       </c>
-      <c r="B276" s="3" t="inlineStr">
+      <c r="B286" s="3" t="inlineStr">
         <is>
           <t>[AMORCE] Ce que ce livre doit établir</t>
         </is>
       </c>
-      <c r="C276" s="3" t="inlineStr">
+      <c r="C286" s="3" t="inlineStr">
         <is>
           <t>brouillon</t>
         </is>

--- a/plan-des-livres.xlsx
+++ b/plan-des-livres.xlsx
@@ -13,7 +13,7 @@
     <sheet name="Plan par livre" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Chapitres'!$A$1:$N$259</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Chapitres'!$A$1:$N$264</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -1449,7 +1449,7 @@
         </is>
       </c>
       <c r="F24" s="5" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G24" s="5" t="inlineStr"/>
       <c r="H24" s="5" t="inlineStr">
@@ -1505,82 +1505,82 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="2" t="inlineStr">
+      <c r="A26" s="4" t="inlineStr">
         <is>
           <t>L24</t>
         </is>
       </c>
-      <c r="B26" s="3" t="inlineStr">
+      <c r="B26" s="5" t="inlineStr">
         <is>
           <t>Les conditions matérielles de la vie</t>
         </is>
       </c>
-      <c r="C26" s="3" t="inlineStr">
+      <c r="C26" s="5" t="inlineStr">
         <is>
           <t>cahier-disciplinaire</t>
         </is>
       </c>
-      <c r="D26" s="3" t="inlineStr">
-        <is>
-          <t>candidat</t>
-        </is>
-      </c>
-      <c r="E26" s="3" t="inlineStr">
+      <c r="D26" s="5" t="inlineStr">
+        <is>
+          <t>en-cours</t>
+        </is>
+      </c>
+      <c r="E26" s="5" t="inlineStr">
         <is>
           <t>non contraignant</t>
         </is>
       </c>
-      <c r="F26" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G26" s="3" t="inlineStr"/>
-      <c r="H26" s="3" t="inlineStr">
+      <c r="F26" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="G26" s="5" t="inlineStr"/>
+      <c r="H26" s="5" t="inlineStr">
         <is>
           <t>Donner au corpus son socle biophysique complet — établir CE QUI DOIT ÊTRE MAINTENU et QUELS SEUILS NE PEUVENT PAS ÊTRE COMPENSÉS FINANCIÈREMENT</t>
         </is>
       </c>
-      <c r="I26" s="3" t="inlineStr">
+      <c r="I26" s="5" t="inlineStr">
         <is>
           <t>discipline — climat, biodiversité, eau, sols, cycles de l'azote et du phosphore, énergie, minerais, alimentation, dépendances matérielles | manque — L18 explique COMMENT MESURER ; aucun livre ne dit CE QU'IL FAUT MAINTENIR, et L5.C08 raisonne sur des catégories vides | objection — L18.C04 : la transition exige plus de trois milliards de tonnes de minéraux, et le corpus ne tient aucune nomenclature d'activités</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="2" t="inlineStr">
+      <c r="A27" s="4" t="inlineStr">
         <is>
           <t>L25</t>
         </is>
       </c>
-      <c r="B27" s="3" t="inlineStr">
+      <c r="B27" s="5" t="inlineStr">
         <is>
           <t>Répartition, besoins essentiels et justice sociale</t>
         </is>
       </c>
-      <c r="C27" s="3" t="inlineStr">
+      <c r="C27" s="5" t="inlineStr">
         <is>
           <t>cahier-disciplinaire</t>
         </is>
       </c>
-      <c r="D27" s="3" t="inlineStr">
-        <is>
-          <t>candidat</t>
-        </is>
-      </c>
-      <c r="E27" s="3" t="inlineStr">
+      <c r="D27" s="5" t="inlineStr">
+        <is>
+          <t>en-cours</t>
+        </is>
+      </c>
+      <c r="E27" s="5" t="inlineStr">
         <is>
           <t>non contraignant</t>
         </is>
       </c>
-      <c r="F27" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G27" s="3" t="inlineStr"/>
-      <c r="H27" s="3" t="inlineStr">
+      <c r="F27" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="G27" s="5" t="inlineStr"/>
+      <c r="H27" s="5" t="inlineStr">
         <is>
           <t>Tester qui paie réellement le dispositif et qui reçoit ses bénéfices — ménages, revenus, patrimoine, accès aux besoins essentiels, services publics, inégalités territoriales, travail de soin, acceptabilité politique</t>
         </is>
       </c>
-      <c r="I27" s="3" t="inlineStr">
+      <c r="I27" s="5" t="inlineStr">
         <is>
           <t>objection — L11.C09 a découvert la question de l'incidence sans pouvoir la traiter, et A35 la rend décisive : la fonte est modulée par la décision de chacun | arbitrage — A34 : un barème qui dit vrai EXCLUT CEUX QUI NE PEUVENT PAS PAYER, et l'exclusion est maximale là où le signal doit être le plus fort | manque — L5.C09 a enregistré comme un MANQUEMENT que la contrainte de rédaction exigeait des coûts humains et qu'aucun chapitre n'en produit</t>
         </is>
@@ -1638,7 +1638,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N259"/>
+  <dimension ref="A1:N264"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -17460,17 +17460,17 @@
     <row r="250">
       <c r="A250" s="2" t="inlineStr">
         <is>
-          <t>L23.C01</t>
+          <t>L22.C06</t>
         </is>
       </c>
       <c r="B250" s="3" t="inlineStr">
         <is>
-          <t>L23</t>
+          <t>L22</t>
         </is>
       </c>
       <c r="C250" s="3" t="inlineStr">
         <is>
-          <t>Ce que ce livre doit établir</t>
+          <t>Qui décide, quand personne ne décide</t>
         </is>
       </c>
       <c r="D250" s="3" t="inlineStr">
@@ -17490,7 +17490,7 @@
       </c>
       <c r="G250" s="3" t="inlineStr">
         <is>
-          <t>conception</t>
+          <t>hybride</t>
         </is>
       </c>
       <c r="H250" s="3" t="inlineStr">
@@ -17503,38 +17503,38 @@
         <v>4</v>
       </c>
       <c r="K250" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L250" s="3" t="inlineStr">
         <is>
-          <t>bareme, reflux_transactionnel, externalisation, essentiel_insolvable, polycentricite, regle_contre_discretion</t>
+          <t>architecture_invisible, indicateur_de_progres, qualification_regenerative, essentiel_insolvable, fenetre_de_reforme, regle_contre_discretion</t>
         </is>
       </c>
       <c r="M250" s="3" t="inlineStr">
         <is>
-          <t>L1.C15, L5.C07, L10.C06, L11.C05, L11.C09, L11.C21, L11.C24, L18.C09, L20.C02, L20.C20</t>
+          <t>L1.C15, L5.C09, L11.C13, L14.C01, L22.C01, L22.C02, L22.C03, L22.C05</t>
         </is>
       </c>
       <c r="N250" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-23-fiscalite-mondiale-et-opacite/c01-ce-que-ce-livre-doit-etablir.md</t>
+          <t>corpus/livre-22-finance-non-bancaire/c06-qui-decide-quand-personne-ne-decide.md</t>
         </is>
       </c>
     </row>
     <row r="251">
       <c r="A251" s="2" t="inlineStr">
         <is>
-          <t>L23.C02</t>
+          <t>L22.C07</t>
         </is>
       </c>
       <c r="B251" s="3" t="inlineStr">
         <is>
-          <t>L23</t>
+          <t>L22</t>
         </is>
       </c>
       <c r="C251" s="3" t="inlineStr">
         <is>
-          <t>La compétence que la convention ne crée pas, et le vote qu'elle a gagné</t>
+          <t>Portée de la tranche</t>
         </is>
       </c>
       <c r="D251" s="3" t="inlineStr">
@@ -17554,7 +17554,7 @@
       </c>
       <c r="G251" s="3" t="inlineStr">
         <is>
-          <t>hybride</t>
+          <t>descriptif</t>
         </is>
       </c>
       <c r="H251" s="3" t="inlineStr">
@@ -17564,31 +17564,31 @@
       </c>
       <c r="I251" s="3" t="inlineStr"/>
       <c r="J251" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="K251" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="K251" s="3" t="n">
-        <v>3</v>
-      </c>
       <c r="L251" s="3" t="inlineStr">
         <is>
-          <t>polycentricite, bareme, reflux_transactionnel, seuil_d_activation, regle_contre_discretion, externalisation</t>
+          <t>architecture_invisible, reflux_transactionnel, qualification_regenerative, bareme, essentiel_insolvable</t>
         </is>
       </c>
       <c r="M251" s="3" t="inlineStr">
         <is>
-          <t>L1.C25, L5.C04, L10.C06, L11.C21, L20.C02, L20.C20, L23.C01</t>
+          <t>L1.C15, L5.C09, L11.C02, L11.C13, L11.C18, L22.C01, L22.C02, L22.C03, L22.C04, L22.C05, L22.C06</t>
         </is>
       </c>
       <c r="N251" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-23-fiscalite-mondiale-et-opacite/c02-la-competence-que-la-convention-ne-cree-pas.md</t>
+          <t>corpus/livre-22-finance-non-bancaire/c07-portee-de-la-tranche.md</t>
         </is>
       </c>
     </row>
     <row r="252">
       <c r="A252" s="2" t="inlineStr">
         <is>
-          <t>L23.C03</t>
+          <t>L23.C01</t>
         </is>
       </c>
       <c r="B252" s="3" t="inlineStr">
@@ -17598,7 +17598,7 @@
       </c>
       <c r="C252" s="3" t="inlineStr">
         <is>
-          <t>F8 appliqué à une négociation en cours, et le résultat n'est pas le désarmement</t>
+          <t>Ce que ce livre doit établir</t>
         </is>
       </c>
       <c r="D252" s="3" t="inlineStr">
@@ -17618,7 +17618,7 @@
       </c>
       <c r="G252" s="3" t="inlineStr">
         <is>
-          <t>hybride</t>
+          <t>conception</t>
         </is>
       </c>
       <c r="H252" s="3" t="inlineStr">
@@ -17635,24 +17635,24 @@
       </c>
       <c r="L252" s="3" t="inlineStr">
         <is>
-          <t>regle_contre_discretion, polycentricite, seuil_d_activation, bareme, externalisation</t>
+          <t>bareme, reflux_transactionnel, externalisation, essentiel_insolvable, polycentricite, regle_contre_discretion</t>
         </is>
       </c>
       <c r="M252" s="3" t="inlineStr">
         <is>
-          <t>L5.C04, L6.C09, L11.C21, L20.C02, L20.C13, L23.C01, L23.C02</t>
+          <t>L1.C15, L5.C07, L10.C06, L11.C05, L11.C09, L11.C21, L11.C24, L18.C09, L20.C02, L20.C20</t>
         </is>
       </c>
       <c r="N252" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-23-fiscalite-mondiale-et-opacite/c03-f8-applique-a-une-negociation-en-cours.md</t>
+          <t>corpus/livre-23-fiscalite-mondiale-et-opacite/c01-ce-que-ce-livre-doit-etablir.md</t>
         </is>
       </c>
     </row>
     <row r="253">
       <c r="A253" s="2" t="inlineStr">
         <is>
-          <t>L23.C04</t>
+          <t>L23.C02</t>
         </is>
       </c>
       <c r="B253" s="3" t="inlineStr">
@@ -17662,7 +17662,7 @@
       </c>
       <c r="C253" s="3" t="inlineStr">
         <is>
-          <t>La transparence que le corpus supposait a été invalidée</t>
+          <t>La compétence que la convention ne crée pas, et le vote qu'elle a gagné</t>
         </is>
       </c>
       <c r="D253" s="3" t="inlineStr">
@@ -17692,31 +17692,31 @@
       </c>
       <c r="I253" s="3" t="inlineStr"/>
       <c r="J253" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K253" s="3" t="n">
         <v>3</v>
       </c>
       <c r="L253" s="3" t="inlineStr">
         <is>
-          <t>regle_contre_discretion, externalisation, bareme, polycentricite, architecture_invisible</t>
+          <t>polycentricite, bareme, reflux_transactionnel, seuil_d_activation, regle_contre_discretion, externalisation</t>
         </is>
       </c>
       <c r="M253" s="3" t="inlineStr">
         <is>
-          <t>L6.C09, L11.C13, L11.C25, L20.C20, L23.C01, L23.C02, L23.C03</t>
+          <t>L1.C25, L5.C04, L10.C06, L11.C21, L20.C02, L20.C20, L23.C01</t>
         </is>
       </c>
       <c r="N253" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-23-fiscalite-mondiale-et-opacite/c04-la-transparence-que-le-corpus-supposait-a-ete-invalidee.md</t>
+          <t>corpus/livre-23-fiscalite-mondiale-et-opacite/c02-la-competence-que-la-convention-ne-cree-pas.md</t>
         </is>
       </c>
     </row>
     <row r="254">
       <c r="A254" s="2" t="inlineStr">
         <is>
-          <t>L23.C05</t>
+          <t>L23.C03</t>
         </is>
       </c>
       <c r="B254" s="3" t="inlineStr">
@@ -17726,7 +17726,7 @@
       </c>
       <c r="C254" s="3" t="inlineStr">
         <is>
-          <t>Intéresser le percepteur, et ce que le taux révèle</t>
+          <t>F8 appliqué à une négociation en cours, et le résultat n'est pas le désarmement</t>
         </is>
       </c>
       <c r="D254" s="3" t="inlineStr">
@@ -17756,31 +17756,31 @@
       </c>
       <c r="I254" s="3" t="inlineStr"/>
       <c r="J254" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K254" s="3" t="n">
         <v>3</v>
       </c>
       <c r="L254" s="3" t="inlineStr">
         <is>
-          <t>bareme, reflux_transactionnel, regle_contre_discretion, polycentricite, seuil_d_activation</t>
+          <t>regle_contre_discretion, polycentricite, seuil_d_activation, bareme, externalisation</t>
         </is>
       </c>
       <c r="M254" s="3" t="inlineStr">
         <is>
-          <t>L11.C21, L11.C24, L18.C09, L20.C20, L23.C01, L23.C02, L23.C03</t>
+          <t>L5.C04, L6.C09, L11.C21, L20.C02, L20.C13, L23.C01, L23.C02</t>
         </is>
       </c>
       <c r="N254" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-23-fiscalite-mondiale-et-opacite/c05-interesser-le-percepteur-et-ce-que-le-taux-revele.md</t>
+          <t>corpus/livre-23-fiscalite-mondiale-et-opacite/c03-f8-applique-a-une-negociation-en-cours.md</t>
         </is>
       </c>
     </row>
     <row r="255">
       <c r="A255" s="2" t="inlineStr">
         <is>
-          <t>L23.C06</t>
+          <t>L23.C04</t>
         </is>
       </c>
       <c r="B255" s="3" t="inlineStr">
@@ -17790,7 +17790,7 @@
       </c>
       <c r="C255" s="3" t="inlineStr">
         <is>
-          <t>L'arbre appliqué à la fonte, et il ne reste que deux branches</t>
+          <t>La transparence que le corpus supposait a été invalidée</t>
         </is>
       </c>
       <c r="D255" s="3" t="inlineStr">
@@ -17810,7 +17810,7 @@
       </c>
       <c r="G255" s="3" t="inlineStr">
         <is>
-          <t>conception</t>
+          <t>hybride</t>
         </is>
       </c>
       <c r="H255" s="3" t="inlineStr">
@@ -17820,31 +17820,31 @@
       </c>
       <c r="I255" s="3" t="inlineStr"/>
       <c r="J255" s="3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K255" s="3" t="n">
         <v>3</v>
       </c>
       <c r="L255" s="3" t="inlineStr">
         <is>
-          <t>bareme, reflux_transactionnel, monnaie_fondante, demurrage, regle_contre_discretion, essentiel_insolvable</t>
+          <t>regle_contre_discretion, externalisation, bareme, polycentricite, architecture_invisible</t>
         </is>
       </c>
       <c r="M255" s="3" t="inlineStr">
         <is>
-          <t>L10.C06, L11.C05, L11.C09, L11.C21, L11.C24, L18.C09, L20.C02, L23.C01, L23.C02, L23.C03, L23.C04, L23.C05</t>
+          <t>L6.C09, L11.C13, L11.C25, L20.C20, L23.C01, L23.C02, L23.C03</t>
         </is>
       </c>
       <c r="N255" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-23-fiscalite-mondiale-et-opacite/c06-l-arbre-applique-a-la-fonte.md</t>
+          <t>corpus/livre-23-fiscalite-mondiale-et-opacite/c04-la-transparence-que-le-corpus-supposait-a-ete-invalidee.md</t>
         </is>
       </c>
     </row>
     <row r="256">
       <c r="A256" s="2" t="inlineStr">
         <is>
-          <t>L23.C07</t>
+          <t>L23.C05</t>
         </is>
       </c>
       <c r="B256" s="3" t="inlineStr">
@@ -17854,7 +17854,7 @@
       </c>
       <c r="C256" s="3" t="inlineStr">
         <is>
-          <t>Portée de la tranche, et la moitié qui n'est pas commencée</t>
+          <t>Intéresser le percepteur, et ce que le taux révèle</t>
         </is>
       </c>
       <c r="D256" s="3" t="inlineStr">
@@ -17874,7 +17874,7 @@
       </c>
       <c r="G256" s="3" t="inlineStr">
         <is>
-          <t>conception</t>
+          <t>hybride</t>
         </is>
       </c>
       <c r="H256" s="3" t="inlineStr">
@@ -17891,34 +17891,34 @@
       </c>
       <c r="L256" s="3" t="inlineStr">
         <is>
-          <t>bareme, reflux_transactionnel, externalisation, regle_contre_discretion, polycentricite, essentiel_insolvable</t>
+          <t>bareme, reflux_transactionnel, regle_contre_discretion, polycentricite, seuil_d_activation</t>
         </is>
       </c>
       <c r="M256" s="3" t="inlineStr">
         <is>
-          <t>L10.C06, L11.C05, L11.C21, L11.C25, L18.C09, L20.C20, L23.C01, L23.C02, L23.C03, L23.C04, L23.C05, L23.C06</t>
+          <t>L11.C21, L11.C24, L18.C09, L20.C20, L23.C01, L23.C02, L23.C03</t>
         </is>
       </c>
       <c r="N256" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-23-fiscalite-mondiale-et-opacite/c07-portee-de-la-tranche.md</t>
+          <t>corpus/livre-23-fiscalite-mondiale-et-opacite/c05-interesser-le-percepteur-et-ce-que-le-taux-revele.md</t>
         </is>
       </c>
     </row>
     <row r="257">
       <c r="A257" s="2" t="inlineStr">
         <is>
-          <t>L24.C01</t>
+          <t>L23.C06</t>
         </is>
       </c>
       <c r="B257" s="3" t="inlineStr">
         <is>
-          <t>L24</t>
+          <t>L23</t>
         </is>
       </c>
       <c r="C257" s="3" t="inlineStr">
         <is>
-          <t>Ce que ce livre doit établir</t>
+          <t>L'arbre appliqué à la fonte, et il ne reste que deux branches</t>
         </is>
       </c>
       <c r="D257" s="3" t="inlineStr">
@@ -17938,7 +17938,7 @@
       </c>
       <c r="G257" s="3" t="inlineStr">
         <is>
-          <t>descriptif</t>
+          <t>conception</t>
         </is>
       </c>
       <c r="H257" s="3" t="inlineStr">
@@ -17946,39 +17946,43 @@
           <t>2026-09-07</t>
         </is>
       </c>
-      <c r="I257" s="3" t="inlineStr">
-        <is>
-          <t>oui</t>
-        </is>
-      </c>
+      <c r="I257" s="3" t="inlineStr"/>
       <c r="J257" s="3" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K257" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="L257" s="3" t="inlineStr"/>
-      <c r="M257" s="3" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="L257" s="3" t="inlineStr">
+        <is>
+          <t>bareme, reflux_transactionnel, monnaie_fondante, demurrage, regle_contre_discretion, essentiel_insolvable</t>
+        </is>
+      </c>
+      <c r="M257" s="3" t="inlineStr">
+        <is>
+          <t>L10.C06, L11.C05, L11.C09, L11.C21, L11.C24, L18.C09, L20.C02, L23.C01, L23.C02, L23.C03, L23.C04, L23.C05</t>
+        </is>
+      </c>
       <c r="N257" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-24-conditions-materielles-de-la-vie/c01-ce-que-ce-livre-doit-etablir.md</t>
+          <t>corpus/livre-23-fiscalite-mondiale-et-opacite/c06-l-arbre-applique-a-la-fonte.md</t>
         </is>
       </c>
     </row>
     <row r="258">
       <c r="A258" s="2" t="inlineStr">
         <is>
-          <t>L25.C01</t>
+          <t>L23.C07</t>
         </is>
       </c>
       <c r="B258" s="3" t="inlineStr">
         <is>
-          <t>L25</t>
+          <t>L23</t>
         </is>
       </c>
       <c r="C258" s="3" t="inlineStr">
         <is>
-          <t>Ce que ce livre doit établir</t>
+          <t>Portée de la tranche, et la moitié qui n'est pas commencée</t>
         </is>
       </c>
       <c r="D258" s="3" t="inlineStr">
@@ -17998,7 +18002,7 @@
       </c>
       <c r="G258" s="3" t="inlineStr">
         <is>
-          <t>descriptif</t>
+          <t>conception</t>
         </is>
       </c>
       <c r="H258" s="3" t="inlineStr">
@@ -18006,87 +18010,411 @@
           <t>2026-09-07</t>
         </is>
       </c>
-      <c r="I258" s="3" t="inlineStr">
-        <is>
-          <t>oui</t>
-        </is>
-      </c>
+      <c r="I258" s="3" t="inlineStr"/>
       <c r="J258" s="3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K258" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="L258" s="3" t="inlineStr"/>
-      <c r="M258" s="3" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="L258" s="3" t="inlineStr">
+        <is>
+          <t>bareme, reflux_transactionnel, externalisation, regle_contre_discretion, polycentricite, essentiel_insolvable</t>
+        </is>
+      </c>
+      <c r="M258" s="3" t="inlineStr">
+        <is>
+          <t>L10.C06, L11.C05, L11.C21, L11.C25, L18.C09, L20.C20, L23.C01, L23.C02, L23.C03, L23.C04, L23.C05, L23.C06</t>
+        </is>
+      </c>
       <c r="N258" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-25-repartition-et-justice-sociale/c01-ce-que-ce-livre-doit-etablir.md</t>
+          <t>corpus/livre-23-fiscalite-mondiale-et-opacite/c07-portee-de-la-tranche.md</t>
         </is>
       </c>
     </row>
     <row r="259">
       <c r="A259" s="2" t="inlineStr">
         <is>
+          <t>L24.C01</t>
+        </is>
+      </c>
+      <c r="B259" s="3" t="inlineStr">
+        <is>
+          <t>L24</t>
+        </is>
+      </c>
+      <c r="C259" s="3" t="inlineStr">
+        <is>
+          <t>Ce que ce livre doit établir</t>
+        </is>
+      </c>
+      <c r="D259" s="3" t="inlineStr">
+        <is>
+          <t>brouillon</t>
+        </is>
+      </c>
+      <c r="E259" s="3" t="inlineStr">
+        <is>
+          <t>preparatoire</t>
+        </is>
+      </c>
+      <c r="F259" s="3" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="G259" s="3" t="inlineStr">
+        <is>
+          <t>descriptif</t>
+        </is>
+      </c>
+      <c r="H259" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="I259" s="3" t="inlineStr"/>
+      <c r="J259" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="K259" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="L259" s="3" t="inlineStr">
+        <is>
+          <t>limites_planetaires, plafond_ecologique, entropie, decouplage, degeneratif, qualification_regenerative, essentiel_insolvable</t>
+        </is>
+      </c>
+      <c r="M259" s="3" t="inlineStr">
+        <is>
+          <t>L1.C15, L5.C08, L11.C13, L18.C01, L18.C04, L22.C04, L26.C01</t>
+        </is>
+      </c>
+      <c r="N259" s="3" t="inlineStr">
+        <is>
+          <t>corpus/livre-24-conditions-materielles-de-la-vie/c01-ce-que-ce-livre-doit-etablir.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" s="2" t="inlineStr">
+        <is>
+          <t>L24.C02</t>
+        </is>
+      </c>
+      <c r="B260" s="3" t="inlineStr">
+        <is>
+          <t>L24</t>
+        </is>
+      </c>
+      <c r="C260" s="3" t="inlineStr">
+        <is>
+          <t>Le seuil juste est plus strict que le seuil sûr</t>
+        </is>
+      </c>
+      <c r="D260" s="3" t="inlineStr">
+        <is>
+          <t>brouillon</t>
+        </is>
+      </c>
+      <c r="E260" s="3" t="inlineStr">
+        <is>
+          <t>preparatoire</t>
+        </is>
+      </c>
+      <c r="F260" s="3" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="G260" s="3" t="inlineStr">
+        <is>
+          <t>hybride</t>
+        </is>
+      </c>
+      <c r="H260" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="I260" s="3" t="inlineStr"/>
+      <c r="J260" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="K260" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="L260" s="3" t="inlineStr">
+        <is>
+          <t>limites_planetaires, plafond_ecologique, plancher_social, dette_ecologique, essentiel_insolvable, qualification_regenerative</t>
+        </is>
+      </c>
+      <c r="M260" s="3" t="inlineStr">
+        <is>
+          <t>L1.C15, L11.C13, L12.C01, L18.C01, L24.C01, L25.C01</t>
+        </is>
+      </c>
+      <c r="N260" s="3" t="inlineStr">
+        <is>
+          <t>corpus/livre-24-conditions-materielles-de-la-vie/c02-le-seuil-juste-est-plus-strict-que-le-seuil-sur.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" s="2" t="inlineStr">
+        <is>
+          <t>L24.C03</t>
+        </is>
+      </c>
+      <c r="B261" s="3" t="inlineStr">
+        <is>
+          <t>L24</t>
+        </is>
+      </c>
+      <c r="C261" s="3" t="inlineStr">
+        <is>
+          <t>La matière, et le levier commun que les neuf dimensions n'avaient pas</t>
+        </is>
+      </c>
+      <c r="D261" s="3" t="inlineStr">
+        <is>
+          <t>brouillon</t>
+        </is>
+      </c>
+      <c r="E261" s="3" t="inlineStr">
+        <is>
+          <t>preparatoire</t>
+        </is>
+      </c>
+      <c r="F261" s="3" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="G261" s="3" t="inlineStr">
+        <is>
+          <t>hybride</t>
+        </is>
+      </c>
+      <c r="H261" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="I261" s="3" t="inlineStr"/>
+      <c r="J261" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="K261" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="L261" s="3" t="inlineStr">
+        <is>
+          <t>limites_planetaires, decouplage, effet_rebond, sobriete, entropie, plafond_ecologique, externalisation, degeneratif</t>
+        </is>
+      </c>
+      <c r="M261" s="3" t="inlineStr">
+        <is>
+          <t>L1.C15, L11.C13, L17.C01, L18.C04, L24.C01, L24.C02, L26.C01</t>
+        </is>
+      </c>
+      <c r="N261" s="3" t="inlineStr">
+        <is>
+          <t>corpus/livre-24-conditions-materielles-de-la-vie/c03-la-matiere-et-le-levier-commun.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" s="2" t="inlineStr">
+        <is>
+          <t>L25.C01</t>
+        </is>
+      </c>
+      <c r="B262" s="3" t="inlineStr">
+        <is>
+          <t>L25</t>
+        </is>
+      </c>
+      <c r="C262" s="3" t="inlineStr">
+        <is>
+          <t>Ce que ce livre doit établir</t>
+        </is>
+      </c>
+      <c r="D262" s="3" t="inlineStr">
+        <is>
+          <t>brouillon</t>
+        </is>
+      </c>
+      <c r="E262" s="3" t="inlineStr">
+        <is>
+          <t>preparatoire</t>
+        </is>
+      </c>
+      <c r="F262" s="3" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="G262" s="3" t="inlineStr">
+        <is>
+          <t>descriptif</t>
+        </is>
+      </c>
+      <c r="H262" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="I262" s="3" t="inlineStr"/>
+      <c r="J262" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="K262" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="L262" s="3" t="inlineStr">
+        <is>
+          <t>plancher_social, plafond_ecologique, essentiel_insolvable, dette_ecologique, communs, solvabilite_anticipee</t>
+        </is>
+      </c>
+      <c r="M262" s="3" t="inlineStr">
+        <is>
+          <t>L1.C15, L11.C09, L11.C18, L12.C01, L24.C01, L24.C02, L24.C03</t>
+        </is>
+      </c>
+      <c r="N262" s="3" t="inlineStr">
+        <is>
+          <t>corpus/livre-25-repartition-et-justice-sociale/c01-ce-que-ce-livre-doit-etablir.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" s="2" t="inlineStr">
+        <is>
+          <t>L25.C02</t>
+        </is>
+      </c>
+      <c r="B263" s="3" t="inlineStr">
+        <is>
+          <t>L25</t>
+        </is>
+      </c>
+      <c r="C263" s="3" t="inlineStr">
+        <is>
+          <t>Le noyau dur, et la charge de la preuve renversée</t>
+        </is>
+      </c>
+      <c r="D263" s="3" t="inlineStr">
+        <is>
+          <t>brouillon</t>
+        </is>
+      </c>
+      <c r="E263" s="3" t="inlineStr">
+        <is>
+          <t>preparatoire</t>
+        </is>
+      </c>
+      <c r="F263" s="3" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="G263" s="3" t="inlineStr">
+        <is>
+          <t>hybride</t>
+        </is>
+      </c>
+      <c r="H263" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="I263" s="3" t="inlineStr"/>
+      <c r="J263" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="K263" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="L263" s="3" t="inlineStr">
+        <is>
+          <t>plancher_social, essentiel_insolvable, plafond_ecologique, solvabilite_anticipee, regle_contre_discretion</t>
+        </is>
+      </c>
+      <c r="M263" s="3" t="inlineStr">
+        <is>
+          <t>L1.C15, L11.C09, L11.C18, L22.C02, L22.C04, L24.C02, L25.C01</t>
+        </is>
+      </c>
+      <c r="N263" s="3" t="inlineStr">
+        <is>
+          <t>corpus/livre-25-repartition-et-justice-sociale/c02-le-noyau-dur-et-la-charge-de-la-preuve.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" s="2" t="inlineStr">
+        <is>
           <t>L26.C01</t>
         </is>
       </c>
-      <c r="B259" s="3" t="inlineStr">
+      <c r="B264" s="3" t="inlineStr">
         <is>
           <t>L26</t>
         </is>
       </c>
-      <c r="C259" s="3" t="inlineStr">
+      <c r="C264" s="3" t="inlineStr">
         <is>
           <t>Ce que ce livre doit établir</t>
         </is>
       </c>
-      <c r="D259" s="3" t="inlineStr">
-        <is>
-          <t>brouillon</t>
-        </is>
-      </c>
-      <c r="E259" s="3" t="inlineStr">
-        <is>
-          <t>preparatoire</t>
-        </is>
-      </c>
-      <c r="F259" s="3" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="G259" s="3" t="inlineStr">
+      <c r="D264" s="3" t="inlineStr">
+        <is>
+          <t>brouillon</t>
+        </is>
+      </c>
+      <c r="E264" s="3" t="inlineStr">
+        <is>
+          <t>preparatoire</t>
+        </is>
+      </c>
+      <c r="F264" s="3" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="G264" s="3" t="inlineStr">
         <is>
           <t>descriptif</t>
         </is>
       </c>
-      <c r="H259" s="3" t="inlineStr">
+      <c r="H264" s="3" t="inlineStr">
         <is>
           <t>2026-09-07</t>
         </is>
       </c>
-      <c r="I259" s="3" t="inlineStr">
+      <c r="I264" s="3" t="inlineStr">
         <is>
           <t>oui</t>
         </is>
       </c>
-      <c r="J259" s="3" t="n">
+      <c r="J264" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="K259" s="3" t="n">
+      <c r="K264" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="L259" s="3" t="inlineStr"/>
-      <c r="M259" s="3" t="inlineStr"/>
-      <c r="N259" s="3" t="inlineStr">
+      <c r="L264" s="3" t="inlineStr"/>
+      <c r="M264" s="3" t="inlineStr"/>
+      <c r="N264" s="3" t="inlineStr">
         <is>
           <t>corpus/livre-26-thermodynamique-et-processus-economique/c01-ce-que-ce-livre-doit-etablir.md</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:N259"/>
+  <autoFilter ref="A1:N264"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -18145,7 +18473,7 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
     </row>
     <row r="5">
@@ -18155,7 +18483,7 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="6">
@@ -18165,7 +18493,7 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>258</v>
+        <v>263</v>
       </c>
     </row>
     <row r="7">
@@ -18175,7 +18503,7 @@
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="8">
@@ -18185,7 +18513,7 @@
         </is>
       </c>
       <c r="B8" s="3" t="n">
-        <v>246</v>
+        <v>253</v>
       </c>
     </row>
     <row r="9">
@@ -18195,7 +18523,7 @@
         </is>
       </c>
       <c r="B9" s="3" t="n">
-        <v>249</v>
+        <v>254</v>
       </c>
     </row>
     <row r="10">
@@ -18215,7 +18543,7 @@
         </is>
       </c>
       <c r="B11" s="3" t="n">
-        <v>1234</v>
+        <v>1258</v>
       </c>
     </row>
     <row r="12">
@@ -18225,7 +18553,7 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>1027</v>
+        <v>1050</v>
       </c>
     </row>
     <row r="13">
@@ -18240,7 +18568,7 @@
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>L0, L9, L12, L13, L14, L15, L16, L17, L19, L24, L25, L26</t>
+          <t>L0, L9, L12, L13, L14, L15, L16, L17, L19, L26</t>
         </is>
       </c>
     </row>
@@ -18319,7 +18647,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C286"/>
+  <dimension ref="A1:C291"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -22862,7 +23190,7 @@
       </c>
       <c r="C267" s="6" t="inlineStr">
         <is>
-          <t>en-cours — 5 chapitre(s)</t>
+          <t>en-cours — 7 chapitre(s)</t>
         </is>
       </c>
     </row>
@@ -22952,31 +23280,31 @@
       </c>
     </row>
     <row r="273">
-      <c r="A273" s="6" t="inlineStr">
-        <is>
-          <t>L23</t>
-        </is>
-      </c>
-      <c r="B273" s="6" t="inlineStr">
-        <is>
-          <t>Fiscalité mondiale, finance offshore et opacité</t>
-        </is>
-      </c>
-      <c r="C273" s="6" t="inlineStr">
-        <is>
-          <t>en-cours — 7 chapitre(s)</t>
+      <c r="A273" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    L22.C06</t>
+        </is>
+      </c>
+      <c r="B273" s="3" t="inlineStr">
+        <is>
+          <t>Qui décide, quand personne ne décide</t>
+        </is>
+      </c>
+      <c r="C273" s="3" t="inlineStr">
+        <is>
+          <t>brouillon</t>
         </is>
       </c>
     </row>
     <row r="274">
       <c r="A274" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L23.C01</t>
+          <t xml:space="preserve">    L22.C07</t>
         </is>
       </c>
       <c r="B274" s="3" t="inlineStr">
         <is>
-          <t>Ce que ce livre doit établir</t>
+          <t>Portée de la tranche</t>
         </is>
       </c>
       <c r="C274" s="3" t="inlineStr">
@@ -22986,31 +23314,31 @@
       </c>
     </row>
     <row r="275">
-      <c r="A275" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    L23.C02</t>
-        </is>
-      </c>
-      <c r="B275" s="3" t="inlineStr">
-        <is>
-          <t>La compétence que la convention ne crée pas, et le vote qu'elle a gagné</t>
-        </is>
-      </c>
-      <c r="C275" s="3" t="inlineStr">
-        <is>
-          <t>brouillon</t>
+      <c r="A275" s="6" t="inlineStr">
+        <is>
+          <t>L23</t>
+        </is>
+      </c>
+      <c r="B275" s="6" t="inlineStr">
+        <is>
+          <t>Fiscalité mondiale, finance offshore et opacité</t>
+        </is>
+      </c>
+      <c r="C275" s="6" t="inlineStr">
+        <is>
+          <t>en-cours — 7 chapitre(s)</t>
         </is>
       </c>
     </row>
     <row r="276">
       <c r="A276" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L23.C03</t>
+          <t xml:space="preserve">    L23.C01</t>
         </is>
       </c>
       <c r="B276" s="3" t="inlineStr">
         <is>
-          <t>F8 appliqué à une négociation en cours, et le résultat n'est pas le désarmement</t>
+          <t>Ce que ce livre doit établir</t>
         </is>
       </c>
       <c r="C276" s="3" t="inlineStr">
@@ -23022,12 +23350,12 @@
     <row r="277">
       <c r="A277" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L23.C04</t>
+          <t xml:space="preserve">    L23.C02</t>
         </is>
       </c>
       <c r="B277" s="3" t="inlineStr">
         <is>
-          <t>La transparence que le corpus supposait a été invalidée</t>
+          <t>La compétence que la convention ne crée pas, et le vote qu'elle a gagné</t>
         </is>
       </c>
       <c r="C277" s="3" t="inlineStr">
@@ -23039,12 +23367,12 @@
     <row r="278">
       <c r="A278" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L23.C05</t>
+          <t xml:space="preserve">    L23.C03</t>
         </is>
       </c>
       <c r="B278" s="3" t="inlineStr">
         <is>
-          <t>Intéresser le percepteur, et ce que le taux révèle</t>
+          <t>F8 appliqué à une négociation en cours, et le résultat n'est pas le désarmement</t>
         </is>
       </c>
       <c r="C278" s="3" t="inlineStr">
@@ -23056,12 +23384,12 @@
     <row r="279">
       <c r="A279" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L23.C06</t>
+          <t xml:space="preserve">    L23.C04</t>
         </is>
       </c>
       <c r="B279" s="3" t="inlineStr">
         <is>
-          <t>L'arbre appliqué à la fonte, et il ne reste que deux branches</t>
+          <t>La transparence que le corpus supposait a été invalidée</t>
         </is>
       </c>
       <c r="C279" s="3" t="inlineStr">
@@ -23073,12 +23401,12 @@
     <row r="280">
       <c r="A280" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L23.C07</t>
+          <t xml:space="preserve">    L23.C05</t>
         </is>
       </c>
       <c r="B280" s="3" t="inlineStr">
         <is>
-          <t>Portée de la tranche, et la moitié qui n'est pas commencée</t>
+          <t>Intéresser le percepteur, et ce que le taux révèle</t>
         </is>
       </c>
       <c r="C280" s="3" t="inlineStr">
@@ -23088,31 +23416,31 @@
       </c>
     </row>
     <row r="281">
-      <c r="A281" s="6" t="inlineStr">
-        <is>
-          <t>L24</t>
-        </is>
-      </c>
-      <c r="B281" s="6" t="inlineStr">
-        <is>
-          <t>Les conditions matérielles de la vie</t>
-        </is>
-      </c>
-      <c r="C281" s="6" t="inlineStr">
-        <is>
-          <t>candidat — AMORCE SEULE</t>
+      <c r="A281" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    L23.C06</t>
+        </is>
+      </c>
+      <c r="B281" s="3" t="inlineStr">
+        <is>
+          <t>L'arbre appliqué à la fonte, et il ne reste que deux branches</t>
+        </is>
+      </c>
+      <c r="C281" s="3" t="inlineStr">
+        <is>
+          <t>brouillon</t>
         </is>
       </c>
     </row>
     <row r="282">
       <c r="A282" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L24.C01</t>
+          <t xml:space="preserve">    L23.C07</t>
         </is>
       </c>
       <c r="B282" s="3" t="inlineStr">
         <is>
-          <t>[AMORCE] Ce que ce livre doit établir</t>
+          <t>Portée de la tranche, et la moitié qui n'est pas commencée</t>
         </is>
       </c>
       <c r="C282" s="3" t="inlineStr">
@@ -23124,29 +23452,29 @@
     <row r="283">
       <c r="A283" s="6" t="inlineStr">
         <is>
-          <t>L25</t>
+          <t>L24</t>
         </is>
       </c>
       <c r="B283" s="6" t="inlineStr">
         <is>
-          <t>Répartition, besoins essentiels et justice sociale</t>
+          <t>Les conditions matérielles de la vie</t>
         </is>
       </c>
       <c r="C283" s="6" t="inlineStr">
         <is>
-          <t>candidat — AMORCE SEULE</t>
+          <t>en-cours — 3 chapitre(s)</t>
         </is>
       </c>
     </row>
     <row r="284">
       <c r="A284" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L25.C01</t>
+          <t xml:space="preserve">    L24.C01</t>
         </is>
       </c>
       <c r="B284" s="3" t="inlineStr">
         <is>
-          <t>[AMORCE] Ce que ce livre doit établir</t>
+          <t>Ce que ce livre doit établir</t>
         </is>
       </c>
       <c r="C284" s="3" t="inlineStr">
@@ -23156,34 +23484,119 @@
       </c>
     </row>
     <row r="285">
-      <c r="A285" s="6" t="inlineStr">
-        <is>
-          <t>L26</t>
-        </is>
-      </c>
-      <c r="B285" s="6" t="inlineStr">
-        <is>
-          <t>Thermodynamique, énergie et processus économique</t>
-        </is>
-      </c>
-      <c r="C285" s="6" t="inlineStr">
-        <is>
-          <t>candidat — AMORCE SEULE</t>
+      <c r="A285" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    L24.C02</t>
+        </is>
+      </c>
+      <c r="B285" s="3" t="inlineStr">
+        <is>
+          <t>Le seuil juste est plus strict que le seuil sûr</t>
+        </is>
+      </c>
+      <c r="C285" s="3" t="inlineStr">
+        <is>
+          <t>brouillon</t>
         </is>
       </c>
     </row>
     <row r="286">
       <c r="A286" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">    L24.C03</t>
+        </is>
+      </c>
+      <c r="B286" s="3" t="inlineStr">
+        <is>
+          <t>La matière, et le levier commun que les neuf dimensions n'avaient pas</t>
+        </is>
+      </c>
+      <c r="C286" s="3" t="inlineStr">
+        <is>
+          <t>brouillon</t>
+        </is>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" s="6" t="inlineStr">
+        <is>
+          <t>L25</t>
+        </is>
+      </c>
+      <c r="B287" s="6" t="inlineStr">
+        <is>
+          <t>Répartition, besoins essentiels et justice sociale</t>
+        </is>
+      </c>
+      <c r="C287" s="6" t="inlineStr">
+        <is>
+          <t>en-cours — 2 chapitre(s)</t>
+        </is>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    L25.C01</t>
+        </is>
+      </c>
+      <c r="B288" s="3" t="inlineStr">
+        <is>
+          <t>Ce que ce livre doit établir</t>
+        </is>
+      </c>
+      <c r="C288" s="3" t="inlineStr">
+        <is>
+          <t>brouillon</t>
+        </is>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    L25.C02</t>
+        </is>
+      </c>
+      <c r="B289" s="3" t="inlineStr">
+        <is>
+          <t>Le noyau dur, et la charge de la preuve renversée</t>
+        </is>
+      </c>
+      <c r="C289" s="3" t="inlineStr">
+        <is>
+          <t>brouillon</t>
+        </is>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" s="6" t="inlineStr">
+        <is>
+          <t>L26</t>
+        </is>
+      </c>
+      <c r="B290" s="6" t="inlineStr">
+        <is>
+          <t>Thermodynamique, énergie et processus économique</t>
+        </is>
+      </c>
+      <c r="C290" s="6" t="inlineStr">
+        <is>
+          <t>candidat — AMORCE SEULE</t>
+        </is>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">    L26.C01</t>
         </is>
       </c>
-      <c r="B286" s="3" t="inlineStr">
+      <c r="B291" s="3" t="inlineStr">
         <is>
           <t>[AMORCE] Ce que ce livre doit établir</t>
         </is>
       </c>
-      <c r="C286" s="3" t="inlineStr">
+      <c r="C291" s="3" t="inlineStr">
         <is>
           <t>brouillon</t>
         </is>

--- a/plan-des-livres.xlsx
+++ b/plan-des-livres.xlsx
@@ -13,7 +13,7 @@
     <sheet name="Plan par livre" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Chapitres'!$A$1:$N$264</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Chapitres'!$A$1:$N$270</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -1531,7 +1531,7 @@
         </is>
       </c>
       <c r="F26" s="5" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G26" s="5" t="inlineStr"/>
       <c r="H26" s="5" t="inlineStr">
@@ -1572,7 +1572,7 @@
         </is>
       </c>
       <c r="F27" s="5" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="G27" s="5" t="inlineStr"/>
       <c r="H27" s="5" t="inlineStr">
@@ -1638,7 +1638,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N264"/>
+  <dimension ref="A1:N270"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -18228,17 +18228,17 @@
     <row r="262">
       <c r="A262" s="2" t="inlineStr">
         <is>
-          <t>L25.C01</t>
+          <t>L24.C04</t>
         </is>
       </c>
       <c r="B262" s="3" t="inlineStr">
         <is>
-          <t>L25</t>
+          <t>L24</t>
         </is>
       </c>
       <c r="C262" s="3" t="inlineStr">
         <is>
-          <t>Ce que ce livre doit établir</t>
+          <t>Un budget mondial n'est pas partageable</t>
         </is>
       </c>
       <c r="D262" s="3" t="inlineStr">
@@ -18258,7 +18258,7 @@
       </c>
       <c r="G262" s="3" t="inlineStr">
         <is>
-          <t>descriptif</t>
+          <t>hybride</t>
         </is>
       </c>
       <c r="H262" s="3" t="inlineStr">
@@ -18275,34 +18275,34 @@
       </c>
       <c r="L262" s="3" t="inlineStr">
         <is>
-          <t>plancher_social, plafond_ecologique, essentiel_insolvable, dette_ecologique, communs, solvabilite_anticipee</t>
+          <t>limites_planetaires, plafond_ecologique, communs, qualification_regenerative, externalisation, polycentricite</t>
         </is>
       </c>
       <c r="M262" s="3" t="inlineStr">
         <is>
-          <t>L1.C15, L11.C09, L11.C18, L12.C01, L24.C01, L24.C02, L24.C03</t>
+          <t>L11.C13, L11.C24, L22.C04, L24.C01, L24.C02, L24.C03, L25.C05</t>
         </is>
       </c>
       <c r="N262" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-25-repartition-et-justice-sociale/c01-ce-que-ce-livre-doit-etablir.md</t>
+          <t>corpus/livre-24-conditions-materielles-de-la-vie/c04-un-budget-mondial-n-est-pas-partageable.md</t>
         </is>
       </c>
     </row>
     <row r="263">
       <c r="A263" s="2" t="inlineStr">
         <is>
-          <t>L25.C02</t>
+          <t>L24.C05</t>
         </is>
       </c>
       <c r="B263" s="3" t="inlineStr">
         <is>
-          <t>L25</t>
+          <t>L24</t>
         </is>
       </c>
       <c r="C263" s="3" t="inlineStr">
         <is>
-          <t>Le noyau dur, et la charge de la preuve renversée</t>
+          <t>Portée de la tranche</t>
         </is>
       </c>
       <c r="D263" s="3" t="inlineStr">
@@ -18322,7 +18322,7 @@
       </c>
       <c r="G263" s="3" t="inlineStr">
         <is>
-          <t>hybride</t>
+          <t>descriptif</t>
         </is>
       </c>
       <c r="H263" s="3" t="inlineStr">
@@ -18332,89 +18332,473 @@
       </c>
       <c r="I263" s="3" t="inlineStr"/>
       <c r="J263" s="3" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K263" s="3" t="n">
         <v>4</v>
       </c>
       <c r="L263" s="3" t="inlineStr">
         <is>
-          <t>plancher_social, essentiel_insolvable, plafond_ecologique, solvabilite_anticipee, regle_contre_discretion</t>
+          <t>limites_planetaires, plafond_ecologique, plancher_social, decouplage, qualification_regenerative, entropie</t>
         </is>
       </c>
       <c r="M263" s="3" t="inlineStr">
         <is>
-          <t>L1.C15, L11.C09, L11.C18, L22.C02, L22.C04, L24.C02, L25.C01</t>
+          <t>L11.C13, L11.C24, L18.C01, L22.C04, L24.C01, L24.C02, L24.C03, L24.C04, L25.C05, L26.C01</t>
         </is>
       </c>
       <c r="N263" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-25-repartition-et-justice-sociale/c02-le-noyau-dur-et-la-charge-de-la-preuve.md</t>
+          <t>corpus/livre-24-conditions-materielles-de-la-vie/c05-portee-de-la-tranche.md</t>
         </is>
       </c>
     </row>
     <row r="264">
       <c r="A264" s="2" t="inlineStr">
         <is>
+          <t>L25.C01</t>
+        </is>
+      </c>
+      <c r="B264" s="3" t="inlineStr">
+        <is>
+          <t>L25</t>
+        </is>
+      </c>
+      <c r="C264" s="3" t="inlineStr">
+        <is>
+          <t>Ce que ce livre doit établir</t>
+        </is>
+      </c>
+      <c r="D264" s="3" t="inlineStr">
+        <is>
+          <t>brouillon</t>
+        </is>
+      </c>
+      <c r="E264" s="3" t="inlineStr">
+        <is>
+          <t>preparatoire</t>
+        </is>
+      </c>
+      <c r="F264" s="3" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="G264" s="3" t="inlineStr">
+        <is>
+          <t>descriptif</t>
+        </is>
+      </c>
+      <c r="H264" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="I264" s="3" t="inlineStr"/>
+      <c r="J264" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="K264" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="L264" s="3" t="inlineStr">
+        <is>
+          <t>plancher_social, plafond_ecologique, essentiel_insolvable, dette_ecologique, communs, solvabilite_anticipee</t>
+        </is>
+      </c>
+      <c r="M264" s="3" t="inlineStr">
+        <is>
+          <t>L1.C15, L11.C09, L11.C18, L12.C01, L24.C01, L24.C02, L24.C03</t>
+        </is>
+      </c>
+      <c r="N264" s="3" t="inlineStr">
+        <is>
+          <t>corpus/livre-25-repartition-et-justice-sociale/c01-ce-que-ce-livre-doit-etablir.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" s="2" t="inlineStr">
+        <is>
+          <t>L25.C02</t>
+        </is>
+      </c>
+      <c r="B265" s="3" t="inlineStr">
+        <is>
+          <t>L25</t>
+        </is>
+      </c>
+      <c r="C265" s="3" t="inlineStr">
+        <is>
+          <t>Le noyau dur, et la charge de la preuve renversée</t>
+        </is>
+      </c>
+      <c r="D265" s="3" t="inlineStr">
+        <is>
+          <t>brouillon</t>
+        </is>
+      </c>
+      <c r="E265" s="3" t="inlineStr">
+        <is>
+          <t>preparatoire</t>
+        </is>
+      </c>
+      <c r="F265" s="3" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="G265" s="3" t="inlineStr">
+        <is>
+          <t>hybride</t>
+        </is>
+      </c>
+      <c r="H265" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="I265" s="3" t="inlineStr"/>
+      <c r="J265" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="K265" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="L265" s="3" t="inlineStr">
+        <is>
+          <t>plancher_social, essentiel_insolvable, plafond_ecologique, solvabilite_anticipee, regle_contre_discretion</t>
+        </is>
+      </c>
+      <c r="M265" s="3" t="inlineStr">
+        <is>
+          <t>L1.C15, L11.C09, L11.C18, L22.C02, L22.C04, L24.C02, L25.C01</t>
+        </is>
+      </c>
+      <c r="N265" s="3" t="inlineStr">
+        <is>
+          <t>corpus/livre-25-repartition-et-justice-sociale/c02-le-noyau-dur-et-la-charge-de-la-preuve.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" s="2" t="inlineStr">
+        <is>
+          <t>L25.C03</t>
+        </is>
+      </c>
+      <c r="B266" s="3" t="inlineStr">
+        <is>
+          <t>L25</t>
+        </is>
+      </c>
+      <c r="C266" s="3" t="inlineStr">
+        <is>
+          <t>Ce que le droit oblige à donner, et ce qu'il refuse de réparer</t>
+        </is>
+      </c>
+      <c r="D266" s="3" t="inlineStr">
+        <is>
+          <t>brouillon</t>
+        </is>
+      </c>
+      <c r="E266" s="3" t="inlineStr">
+        <is>
+          <t>preparatoire</t>
+        </is>
+      </c>
+      <c r="F266" s="3" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="G266" s="3" t="inlineStr">
+        <is>
+          <t>hybride</t>
+        </is>
+      </c>
+      <c r="H266" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="I266" s="3" t="inlineStr"/>
+      <c r="J266" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="K266" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="L266" s="3" t="inlineStr">
+        <is>
+          <t>dette_ecologique, plancher_social, creation_monetaire, reflux_collectif, essentiel_insolvable, solvabilite_anticipee</t>
+        </is>
+      </c>
+      <c r="M266" s="3" t="inlineStr">
+        <is>
+          <t>L1.C20, L11.C01, L20.C01, L24.C02, L25.C01, L25.C02</t>
+        </is>
+      </c>
+      <c r="N266" s="3" t="inlineStr">
+        <is>
+          <t>corpus/livre-25-repartition-et-justice-sociale/c03-ce-que-le-droit-oblige-a-donner.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" s="2" t="inlineStr">
+        <is>
+          <t>L25.C04</t>
+        </is>
+      </c>
+      <c r="B267" s="3" t="inlineStr">
+        <is>
+          <t>L25</t>
+        </is>
+      </c>
+      <c r="C267" s="3" t="inlineStr">
+        <is>
+          <t>A34 en droit positif, et le critère que le corpus n'avait pas</t>
+        </is>
+      </c>
+      <c r="D267" s="3" t="inlineStr">
+        <is>
+          <t>brouillon</t>
+        </is>
+      </c>
+      <c r="E267" s="3" t="inlineStr">
+        <is>
+          <t>preparatoire</t>
+        </is>
+      </c>
+      <c r="F267" s="3" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="G267" s="3" t="inlineStr">
+        <is>
+          <t>hybride</t>
+        </is>
+      </c>
+      <c r="H267" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="I267" s="3" t="inlineStr"/>
+      <c r="J267" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="K267" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="L267" s="3" t="inlineStr">
+        <is>
+          <t>plancher_social, bareme, essentiel_insolvable, sobriete, affectation_des_instruments, reflux_transactionnel</t>
+        </is>
+      </c>
+      <c r="M267" s="3" t="inlineStr">
+        <is>
+          <t>L1.C15, L11.C09, L11.C18, L11.C21, L22.C02, L24.C03, L25.C01, L25.C02</t>
+        </is>
+      </c>
+      <c r="N267" s="3" t="inlineStr">
+        <is>
+          <t>corpus/livre-25-repartition-et-justice-sociale/c04-a34-en-droit-positif.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" s="2" t="inlineStr">
+        <is>
+          <t>L25.C05</t>
+        </is>
+      </c>
+      <c r="B268" s="3" t="inlineStr">
+        <is>
+          <t>L25</t>
+        </is>
+      </c>
+      <c r="C268" s="3" t="inlineStr">
+        <is>
+          <t>Le droit différencie sans calculer</t>
+        </is>
+      </c>
+      <c r="D268" s="3" t="inlineStr">
+        <is>
+          <t>brouillon</t>
+        </is>
+      </c>
+      <c r="E268" s="3" t="inlineStr">
+        <is>
+          <t>preparatoire</t>
+        </is>
+      </c>
+      <c r="F268" s="3" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="G268" s="3" t="inlineStr">
+        <is>
+          <t>hybride</t>
+        </is>
+      </c>
+      <c r="H268" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="I268" s="3" t="inlineStr"/>
+      <c r="J268" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="K268" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="L268" s="3" t="inlineStr">
+        <is>
+          <t>dette_ecologique, plancher_social, plafond_ecologique, bareme, indicateur_de_progres, polycentricite</t>
+        </is>
+      </c>
+      <c r="M268" s="3" t="inlineStr">
+        <is>
+          <t>L11.C13, L22.C04, L22.C06, L24.C01, L24.C02, L25.C01, L25.C02, L25.C03, L25.C04</t>
+        </is>
+      </c>
+      <c r="N268" s="3" t="inlineStr">
+        <is>
+          <t>corpus/livre-25-repartition-et-justice-sociale/c05-le-droit-differencie-sans-calculer.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" s="2" t="inlineStr">
+        <is>
+          <t>L25.C06</t>
+        </is>
+      </c>
+      <c r="B269" s="3" t="inlineStr">
+        <is>
+          <t>L25</t>
+        </is>
+      </c>
+      <c r="C269" s="3" t="inlineStr">
+        <is>
+          <t>Portée de la tranche</t>
+        </is>
+      </c>
+      <c r="D269" s="3" t="inlineStr">
+        <is>
+          <t>brouillon</t>
+        </is>
+      </c>
+      <c r="E269" s="3" t="inlineStr">
+        <is>
+          <t>preparatoire</t>
+        </is>
+      </c>
+      <c r="F269" s="3" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="G269" s="3" t="inlineStr">
+        <is>
+          <t>descriptif</t>
+        </is>
+      </c>
+      <c r="H269" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="I269" s="3" t="inlineStr"/>
+      <c r="J269" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="K269" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="L269" s="3" t="inlineStr">
+        <is>
+          <t>plancher_social, plafond_ecologique, dette_ecologique, essentiel_insolvable, bareme</t>
+        </is>
+      </c>
+      <c r="M269" s="3" t="inlineStr">
+        <is>
+          <t>L5.C09, L11.C09, L11.C18, L24.C02, L25.C01, L25.C02, L25.C03, L25.C04, L25.C05</t>
+        </is>
+      </c>
+      <c r="N269" s="3" t="inlineStr">
+        <is>
+          <t>corpus/livre-25-repartition-et-justice-sociale/c06-portee-de-la-tranche.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" s="2" t="inlineStr">
+        <is>
           <t>L26.C01</t>
         </is>
       </c>
-      <c r="B264" s="3" t="inlineStr">
+      <c r="B270" s="3" t="inlineStr">
         <is>
           <t>L26</t>
         </is>
       </c>
-      <c r="C264" s="3" t="inlineStr">
+      <c r="C270" s="3" t="inlineStr">
         <is>
           <t>Ce que ce livre doit établir</t>
         </is>
       </c>
-      <c r="D264" s="3" t="inlineStr">
-        <is>
-          <t>brouillon</t>
-        </is>
-      </c>
-      <c r="E264" s="3" t="inlineStr">
-        <is>
-          <t>preparatoire</t>
-        </is>
-      </c>
-      <c r="F264" s="3" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="G264" s="3" t="inlineStr">
+      <c r="D270" s="3" t="inlineStr">
+        <is>
+          <t>brouillon</t>
+        </is>
+      </c>
+      <c r="E270" s="3" t="inlineStr">
+        <is>
+          <t>preparatoire</t>
+        </is>
+      </c>
+      <c r="F270" s="3" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="G270" s="3" t="inlineStr">
         <is>
           <t>descriptif</t>
         </is>
       </c>
-      <c r="H264" s="3" t="inlineStr">
+      <c r="H270" s="3" t="inlineStr">
         <is>
           <t>2026-09-07</t>
         </is>
       </c>
-      <c r="I264" s="3" t="inlineStr">
+      <c r="I270" s="3" t="inlineStr">
         <is>
           <t>oui</t>
         </is>
       </c>
-      <c r="J264" s="3" t="n">
+      <c r="J270" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="K264" s="3" t="n">
+      <c r="K270" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="L264" s="3" t="inlineStr"/>
-      <c r="M264" s="3" t="inlineStr"/>
-      <c r="N264" s="3" t="inlineStr">
+      <c r="L270" s="3" t="inlineStr"/>
+      <c r="M270" s="3" t="inlineStr"/>
+      <c r="N270" s="3" t="inlineStr">
         <is>
           <t>corpus/livre-26-thermodynamique-et-processus-economique/c01-ce-que-ce-livre-doit-etablir.md</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:N264"/>
+  <autoFilter ref="A1:N270"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -18493,7 +18877,7 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>263</v>
+        <v>269</v>
       </c>
     </row>
     <row r="7">
@@ -18513,7 +18897,7 @@
         </is>
       </c>
       <c r="B8" s="3" t="n">
-        <v>253</v>
+        <v>259</v>
       </c>
     </row>
     <row r="9">
@@ -18523,7 +18907,7 @@
         </is>
       </c>
       <c r="B9" s="3" t="n">
-        <v>254</v>
+        <v>260</v>
       </c>
     </row>
     <row r="10">
@@ -18543,7 +18927,7 @@
         </is>
       </c>
       <c r="B11" s="3" t="n">
-        <v>1258</v>
+        <v>1282</v>
       </c>
     </row>
     <row r="12">
@@ -18553,7 +18937,7 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>1050</v>
+        <v>1066</v>
       </c>
     </row>
     <row r="13">
@@ -18647,7 +19031,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C291"/>
+  <dimension ref="A1:C297"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -23462,7 +23846,7 @@
       </c>
       <c r="C283" s="6" t="inlineStr">
         <is>
-          <t>en-cours — 3 chapitre(s)</t>
+          <t>en-cours — 5 chapitre(s)</t>
         </is>
       </c>
     </row>
@@ -23518,85 +23902,187 @@
       </c>
     </row>
     <row r="287">
-      <c r="A287" s="6" t="inlineStr">
-        <is>
-          <t>L25</t>
-        </is>
-      </c>
-      <c r="B287" s="6" t="inlineStr">
-        <is>
-          <t>Répartition, besoins essentiels et justice sociale</t>
-        </is>
-      </c>
-      <c r="C287" s="6" t="inlineStr">
-        <is>
-          <t>en-cours — 2 chapitre(s)</t>
+      <c r="A287" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    L24.C04</t>
+        </is>
+      </c>
+      <c r="B287" s="3" t="inlineStr">
+        <is>
+          <t>Un budget mondial n'est pas partageable</t>
+        </is>
+      </c>
+      <c r="C287" s="3" t="inlineStr">
+        <is>
+          <t>brouillon</t>
         </is>
       </c>
     </row>
     <row r="288">
       <c r="A288" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">    L24.C05</t>
+        </is>
+      </c>
+      <c r="B288" s="3" t="inlineStr">
+        <is>
+          <t>Portée de la tranche</t>
+        </is>
+      </c>
+      <c r="C288" s="3" t="inlineStr">
+        <is>
+          <t>brouillon</t>
+        </is>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" s="6" t="inlineStr">
+        <is>
+          <t>L25</t>
+        </is>
+      </c>
+      <c r="B289" s="6" t="inlineStr">
+        <is>
+          <t>Répartition, besoins essentiels et justice sociale</t>
+        </is>
+      </c>
+      <c r="C289" s="6" t="inlineStr">
+        <is>
+          <t>en-cours — 6 chapitre(s)</t>
+        </is>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">    L25.C01</t>
         </is>
       </c>
-      <c r="B288" s="3" t="inlineStr">
+      <c r="B290" s="3" t="inlineStr">
         <is>
           <t>Ce que ce livre doit établir</t>
         </is>
       </c>
-      <c r="C288" s="3" t="inlineStr">
-        <is>
-          <t>brouillon</t>
-        </is>
-      </c>
-    </row>
-    <row r="289">
-      <c r="A289" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    L25.C02</t>
-        </is>
-      </c>
-      <c r="B289" s="3" t="inlineStr">
-        <is>
-          <t>Le noyau dur, et la charge de la preuve renversée</t>
-        </is>
-      </c>
-      <c r="C289" s="3" t="inlineStr">
-        <is>
-          <t>brouillon</t>
-        </is>
-      </c>
-    </row>
-    <row r="290">
-      <c r="A290" s="6" t="inlineStr">
-        <is>
-          <t>L26</t>
-        </is>
-      </c>
-      <c r="B290" s="6" t="inlineStr">
-        <is>
-          <t>Thermodynamique, énergie et processus économique</t>
-        </is>
-      </c>
-      <c r="C290" s="6" t="inlineStr">
-        <is>
-          <t>candidat — AMORCE SEULE</t>
+      <c r="C290" s="3" t="inlineStr">
+        <is>
+          <t>brouillon</t>
         </is>
       </c>
     </row>
     <row r="291">
       <c r="A291" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">    L25.C02</t>
+        </is>
+      </c>
+      <c r="B291" s="3" t="inlineStr">
+        <is>
+          <t>Le noyau dur, et la charge de la preuve renversée</t>
+        </is>
+      </c>
+      <c r="C291" s="3" t="inlineStr">
+        <is>
+          <t>brouillon</t>
+        </is>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    L25.C03</t>
+        </is>
+      </c>
+      <c r="B292" s="3" t="inlineStr">
+        <is>
+          <t>Ce que le droit oblige à donner, et ce qu'il refuse de réparer</t>
+        </is>
+      </c>
+      <c r="C292" s="3" t="inlineStr">
+        <is>
+          <t>brouillon</t>
+        </is>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    L25.C04</t>
+        </is>
+      </c>
+      <c r="B293" s="3" t="inlineStr">
+        <is>
+          <t>A34 en droit positif, et le critère que le corpus n'avait pas</t>
+        </is>
+      </c>
+      <c r="C293" s="3" t="inlineStr">
+        <is>
+          <t>brouillon</t>
+        </is>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    L25.C05</t>
+        </is>
+      </c>
+      <c r="B294" s="3" t="inlineStr">
+        <is>
+          <t>Le droit différencie sans calculer</t>
+        </is>
+      </c>
+      <c r="C294" s="3" t="inlineStr">
+        <is>
+          <t>brouillon</t>
+        </is>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    L25.C06</t>
+        </is>
+      </c>
+      <c r="B295" s="3" t="inlineStr">
+        <is>
+          <t>Portée de la tranche</t>
+        </is>
+      </c>
+      <c r="C295" s="3" t="inlineStr">
+        <is>
+          <t>brouillon</t>
+        </is>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" s="6" t="inlineStr">
+        <is>
+          <t>L26</t>
+        </is>
+      </c>
+      <c r="B296" s="6" t="inlineStr">
+        <is>
+          <t>Thermodynamique, énergie et processus économique</t>
+        </is>
+      </c>
+      <c r="C296" s="6" t="inlineStr">
+        <is>
+          <t>candidat — AMORCE SEULE</t>
+        </is>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">    L26.C01</t>
         </is>
       </c>
-      <c r="B291" s="3" t="inlineStr">
+      <c r="B297" s="3" t="inlineStr">
         <is>
           <t>[AMORCE] Ce que ce livre doit établir</t>
         </is>
       </c>
-      <c r="C291" s="3" t="inlineStr">
+      <c r="C297" s="3" t="inlineStr">
         <is>
           <t>brouillon</t>
         </is>

--- a/plan-des-livres.xlsx
+++ b/plan-des-livres.xlsx
@@ -13,7 +13,7 @@
     <sheet name="Plan par livre" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Chapitres'!$A$1:$N$270</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Chapitres'!$A$1:$N$275</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -1587,41 +1587,41 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="2" t="inlineStr">
+      <c r="A28" s="4" t="inlineStr">
         <is>
           <t>L26</t>
         </is>
       </c>
-      <c r="B28" s="3" t="inlineStr">
+      <c r="B28" s="5" t="inlineStr">
         <is>
           <t>Thermodynamique, énergie et processus économique</t>
         </is>
       </c>
-      <c r="C28" s="3" t="inlineStr">
+      <c r="C28" s="5" t="inlineStr">
         <is>
           <t>cahier-disciplinaire</t>
         </is>
       </c>
-      <c r="D28" s="3" t="inlineStr">
-        <is>
-          <t>candidat</t>
-        </is>
-      </c>
-      <c r="E28" s="3" t="inlineStr">
+      <c r="D28" s="5" t="inlineStr">
+        <is>
+          <t>en-cours</t>
+        </is>
+      </c>
+      <c r="E28" s="5" t="inlineStr">
         <is>
           <t>non contraignant</t>
         </is>
       </c>
-      <c r="F28" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G28" s="3" t="inlineStr"/>
-      <c r="H28" s="3" t="inlineStr">
+      <c r="F28" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="G28" s="5" t="inlineStr"/>
+      <c r="H28" s="5" t="inlineStr">
         <is>
           <t>Établir ce que les lois de la thermodynamique imposent à un processus économique, et ce qu'elles interdisent à toute conception monétaire qui prétend régénérer — la question n'étant pas ce que le dispositif coûte, mais ce que l'énergie et la matière rendent possible</t>
         </is>
       </c>
-      <c r="I28" s="3" t="inlineStr">
+      <c r="I28" s="5" t="inlineStr">
         <is>
           <t>manque — `entropie` figure au vocabulaire depuis la première occurrence L1.C03 et AUCUN LIVRE NE LE PORTE ; le concept est employé dans six chapitres du Livre 1 et un du Livre 2, sans instruction | discipline — économie biophysique : Georgescu-Roegen, analyse énergétique, retour énergétique sur investissement, exergie, dissipation | objection — L18.C04 : aucune preuve de découplage absolu généralisé n'est observée, et le corpus ne sait pas si l'obstacle est économique ou THERMODYNAMIQUE | objection — `effet_rebond` et `jevons_monetaire` sont au vocabulaire ; le corpus les invoque sans tenir l'argument physique qui les fonde | falsifieur — F11, LA CONTRAINTE PHYSIQUE, posé le 2026-09-07 sur arbitrage de l'auteur : ce livre est le seul qui puisse l'établir ou le réfuter</t>
         </is>
@@ -1638,7 +1638,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N270"/>
+  <dimension ref="A1:N275"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -1947,7 +1947,7 @@
       </c>
       <c r="H5" s="3" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="I5" s="3" t="inlineStr"/>
@@ -1962,7 +1962,11 @@
           <t>decouplage, effet_rebond, entropie, sobriete</t>
         </is>
       </c>
-      <c r="M5" s="3" t="inlineStr"/>
+      <c r="M5" s="3" t="inlineStr">
+        <is>
+          <t>L26.C01</t>
+        </is>
+      </c>
       <c r="N5" s="3" t="inlineStr">
         <is>
           <t>corpus/livre-01-monnaie-finance-limites-planetaires/c03-croissance-infinie-planete-finie.md</t>
@@ -2831,7 +2835,7 @@
       </c>
       <c r="H19" s="3" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="I19" s="3" t="inlineStr"/>
@@ -2848,7 +2852,7 @@
       </c>
       <c r="M19" s="3" t="inlineStr">
         <is>
-          <t>L1.C03, L1.C04, L1.C07, L1.C08, L1.C10, L1.C15, L1.C16</t>
+          <t>L1.C03, L1.C04, L1.C07, L1.C08, L1.C10, L1.C15, L1.C16, L26.C01, L26.C04</t>
         </is>
       </c>
       <c r="N19" s="3" t="inlineStr">
@@ -12979,7 +12983,7 @@
       </c>
       <c r="H179" s="3" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="I179" s="3" t="inlineStr"/>
@@ -12987,7 +12991,7 @@
         <v>9</v>
       </c>
       <c r="K179" s="3" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="L179" s="3" t="inlineStr">
         <is>
@@ -12996,7 +13000,7 @@
       </c>
       <c r="M179" s="3" t="inlineStr">
         <is>
-          <t>L1.C21, L1.C23, L1.C27, L11.C03, L11.C05, L11.C06, L11.C09</t>
+          <t>L1.C21, L1.C23, L1.C27, L11.C03, L11.C05, L11.C06, L11.C09, L26.C03</t>
         </is>
       </c>
       <c r="N179" s="3" t="inlineStr">
@@ -13171,7 +13175,7 @@
       </c>
       <c r="H182" s="3" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="I182" s="3" t="inlineStr"/>
@@ -13179,7 +13183,7 @@
         <v>6</v>
       </c>
       <c r="K182" s="3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L182" s="3" t="inlineStr">
         <is>
@@ -13188,7 +13192,7 @@
       </c>
       <c r="M182" s="3" t="inlineStr">
         <is>
-          <t>L1.C18, L1.C20, L1.C22, L1.C27, L11.C03, L11.C05, L11.C06, L11.C08, L11.C09, L11.C10, L11.C11, L11.C12</t>
+          <t>L1.C18, L1.C20, L1.C22, L1.C27, L11.C03, L11.C05, L11.C06, L11.C08, L11.C09, L11.C10, L11.C11, L11.C12, L26.C05</t>
         </is>
       </c>
       <c r="N182" s="3" t="inlineStr">
@@ -13875,7 +13879,7 @@
       </c>
       <c r="H193" s="3" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="I193" s="3" t="inlineStr"/>
@@ -13883,7 +13887,7 @@
         <v>3</v>
       </c>
       <c r="K193" s="3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L193" s="3" t="inlineStr">
         <is>
@@ -13892,7 +13896,7 @@
       </c>
       <c r="M193" s="3" t="inlineStr">
         <is>
-          <t>L1.C26, L1.C27, L11.C04, L11.C05, L11.C06, L11.C09, L11.C13, L11.C16, L11.C17, L11.C19, L11.C21</t>
+          <t>L1.C26, L1.C27, L11.C04, L11.C05, L11.C06, L11.C09, L11.C13, L11.C16, L11.C17, L11.C19, L11.C21, L26.C03</t>
         </is>
       </c>
       <c r="N193" s="3" t="inlineStr">
@@ -15131,7 +15135,7 @@
       </c>
       <c r="H213" s="3" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="I213" s="3" t="inlineStr"/>
@@ -15139,7 +15143,7 @@
         <v>3</v>
       </c>
       <c r="K213" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L213" s="3" t="inlineStr">
         <is>
@@ -15148,7 +15152,7 @@
       </c>
       <c r="M213" s="3" t="inlineStr">
         <is>
-          <t>L1.C15, L1.C18, L5.C07, L10.C04, L10.C06, L11.C03, L11.C13, L18.C01, L18.C04, L18.C06</t>
+          <t>L1.C15, L1.C18, L5.C07, L10.C04, L10.C06, L11.C03, L11.C13, L18.C01, L18.C04, L18.C06, L26.C05</t>
         </is>
       </c>
       <c r="N213" s="3" t="inlineStr">
@@ -17239,7 +17243,7 @@
       </c>
       <c r="H246" s="3" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="I246" s="3" t="inlineStr"/>
@@ -17247,7 +17251,7 @@
         <v>2</v>
       </c>
       <c r="K246" s="3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L246" s="3" t="inlineStr">
         <is>
@@ -17256,7 +17260,7 @@
       </c>
       <c r="M246" s="3" t="inlineStr">
         <is>
-          <t>L1.C19, L5.C09, L11.C02, L11.C05, L11.C09, L11.C27, L21.C03, L22.C01, L23.C04</t>
+          <t>L1.C19, L5.C09, L11.C02, L11.C05, L11.C09, L11.C27, L21.C03, L22.C01, L23.C04, L26.C04</t>
         </is>
       </c>
       <c r="N246" s="3" t="inlineStr">
@@ -18327,7 +18331,7 @@
       </c>
       <c r="H263" s="3" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="I263" s="3" t="inlineStr"/>
@@ -18344,7 +18348,7 @@
       </c>
       <c r="M263" s="3" t="inlineStr">
         <is>
-          <t>L11.C13, L11.C24, L18.C01, L22.C04, L24.C01, L24.C02, L24.C03, L24.C04, L25.C05, L26.C01</t>
+          <t>L11.C13, L11.C24, L18.C01, L22.C04, L24.C01, L24.C02, L24.C03, L24.C04, L25.C05, L26.C01, L26.C02</t>
         </is>
       </c>
       <c r="N263" s="3" t="inlineStr">
@@ -18770,35 +18774,359 @@
       </c>
       <c r="G270" s="3" t="inlineStr">
         <is>
+          <t>hybride</t>
+        </is>
+      </c>
+      <c r="H270" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="I270" s="3" t="inlineStr"/>
+      <c r="J270" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="K270" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="L270" s="3" t="inlineStr">
+        <is>
+          <t>entropie, decouplage, effet_rebond, limites_planetaires, sobriete, degeneratif, qualification_regenerative</t>
+        </is>
+      </c>
+      <c r="M270" s="3" t="inlineStr">
+        <is>
+          <t>L1.C03, L1.C15, L1.C17, L8.C13, L8.C34, L11.C13, L18.C04, L24.C03, L24.C05</t>
+        </is>
+      </c>
+      <c r="N270" s="3" t="inlineStr">
+        <is>
+          <t>corpus/livre-26-thermodynamique-et-processus-economique/c01-ce-que-ce-livre-doit-etablir.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" s="2" t="inlineStr">
+        <is>
+          <t>L26.C02</t>
+        </is>
+      </c>
+      <c r="B271" s="3" t="inlineStr">
+        <is>
+          <t>L26</t>
+        </is>
+      </c>
+      <c r="C271" s="3" t="inlineStr">
+        <is>
+          <t>Le stock n'existe pas sous la forme demandée</t>
+        </is>
+      </c>
+      <c r="D271" s="3" t="inlineStr">
+        <is>
+          <t>brouillon</t>
+        </is>
+      </c>
+      <c r="E271" s="3" t="inlineStr">
+        <is>
+          <t>preparatoire</t>
+        </is>
+      </c>
+      <c r="F271" s="3" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="G271" s="3" t="inlineStr">
+        <is>
+          <t>hybride</t>
+        </is>
+      </c>
+      <c r="H271" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="I271" s="3" t="inlineStr"/>
+      <c r="J271" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="K271" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="L271" s="3" t="inlineStr">
+        <is>
+          <t>entropie, bareme, limites_planetaires, decouplage, sobriete, fausse_richesse</t>
+        </is>
+      </c>
+      <c r="M271" s="3" t="inlineStr">
+        <is>
+          <t>L1.C15, L11.C13, L11.C24, L18.C04, L22.C04, L24.C03, L24.C05, L26.C01</t>
+        </is>
+      </c>
+      <c r="N271" s="3" t="inlineStr">
+        <is>
+          <t>corpus/livre-26-thermodynamique-et-processus-economique/c02-le-stock-n-existe-pas-sous-la-forme-demandee.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" s="2" t="inlineStr">
+        <is>
+          <t>L26.C03</t>
+        </is>
+      </c>
+      <c r="B272" s="3" t="inlineStr">
+        <is>
+          <t>L26</t>
+        </is>
+      </c>
+      <c r="C272" s="3" t="inlineStr">
+        <is>
+          <t>La frontière décide du chiffre</t>
+        </is>
+      </c>
+      <c r="D272" s="3" t="inlineStr">
+        <is>
+          <t>brouillon</t>
+        </is>
+      </c>
+      <c r="E272" s="3" t="inlineStr">
+        <is>
+          <t>preparatoire</t>
+        </is>
+      </c>
+      <c r="F272" s="3" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="G272" s="3" t="inlineStr">
+        <is>
+          <t>hybride</t>
+        </is>
+      </c>
+      <c r="H272" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="I272" s="3" t="inlineStr"/>
+      <c r="J272" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="K272" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="L272" s="3" t="inlineStr">
+        <is>
+          <t>entropie, decouplage, sobriete, limites_planetaires, robustesse, bareme</t>
+        </is>
+      </c>
+      <c r="M272" s="3" t="inlineStr">
+        <is>
+          <t>L11.C10, L11.C13, L11.C24, L18.C04, L18.C09, L24.C03, L24.C04, L26.C01, L26.C02</t>
+        </is>
+      </c>
+      <c r="N272" s="3" t="inlineStr">
+        <is>
+          <t>corpus/livre-26-thermodynamique-et-processus-economique/c03-la-frontiere-decide-du-chiffre.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" s="2" t="inlineStr">
+        <is>
+          <t>L26.C04</t>
+        </is>
+      </c>
+      <c r="B273" s="3" t="inlineStr">
+        <is>
+          <t>L26</t>
+        </is>
+      </c>
+      <c r="C273" s="3" t="inlineStr">
+        <is>
+          <t>L'effet rebond, et ce que le dispositif en hérite sans être une politique d'efficacité</t>
+        </is>
+      </c>
+      <c r="D273" s="3" t="inlineStr">
+        <is>
+          <t>brouillon</t>
+        </is>
+      </c>
+      <c r="E273" s="3" t="inlineStr">
+        <is>
+          <t>preparatoire</t>
+        </is>
+      </c>
+      <c r="F273" s="3" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="G273" s="3" t="inlineStr">
+        <is>
+          <t>hybride</t>
+        </is>
+      </c>
+      <c r="H273" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="I273" s="3" t="inlineStr"/>
+      <c r="J273" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="K273" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="L273" s="3" t="inlineStr">
+        <is>
+          <t>effet_rebond, jevons_monetaire, decouplage, sobriete, entropie, reflux_transactionnel</t>
+        </is>
+      </c>
+      <c r="M273" s="3" t="inlineStr">
+        <is>
+          <t>L1.C03, L1.C12, L1.C17, L11.C10, L13.C01, L18.C04, L22.C02, L24.C03, L26.C01, L26.C03</t>
+        </is>
+      </c>
+      <c r="N273" s="3" t="inlineStr">
+        <is>
+          <t>corpus/livre-26-thermodynamique-et-processus-economique/c04-l-effet-rebond-et-ce-que-le-dispositif-en-herite.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" s="2" t="inlineStr">
+        <is>
+          <t>L26.C05</t>
+        </is>
+      </c>
+      <c r="B274" s="3" t="inlineStr">
+        <is>
+          <t>L26</t>
+        </is>
+      </c>
+      <c r="C274" s="3" t="inlineStr">
+        <is>
+          <t>L'addition n'est pas la substitution</t>
+        </is>
+      </c>
+      <c r="D274" s="3" t="inlineStr">
+        <is>
+          <t>brouillon</t>
+        </is>
+      </c>
+      <c r="E274" s="3" t="inlineStr">
+        <is>
+          <t>preparatoire</t>
+        </is>
+      </c>
+      <c r="F274" s="3" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="G274" s="3" t="inlineStr">
+        <is>
+          <t>hybride</t>
+        </is>
+      </c>
+      <c r="H274" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="I274" s="3" t="inlineStr"/>
+      <c r="J274" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="K274" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="L274" s="3" t="inlineStr">
+        <is>
+          <t>decouplage, effet_rebond, sobriete, degeneratif, affectation_des_instruments</t>
+        </is>
+      </c>
+      <c r="M274" s="3" t="inlineStr">
+        <is>
+          <t>L1.C12, L11.C10, L11.C13, L18.C04, L18.C09, L22.C02, L24.C03, L26.C01, L26.C03, L26.C04</t>
+        </is>
+      </c>
+      <c r="N274" s="3" t="inlineStr">
+        <is>
+          <t>corpus/livre-26-thermodynamique-et-processus-economique/c05-l-addition-n-est-pas-la-substitution.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" s="2" t="inlineStr">
+        <is>
+          <t>L26.C06</t>
+        </is>
+      </c>
+      <c r="B275" s="3" t="inlineStr">
+        <is>
+          <t>L26</t>
+        </is>
+      </c>
+      <c r="C275" s="3" t="inlineStr">
+        <is>
+          <t>Portée de la tranche</t>
+        </is>
+      </c>
+      <c r="D275" s="3" t="inlineStr">
+        <is>
+          <t>brouillon</t>
+        </is>
+      </c>
+      <c r="E275" s="3" t="inlineStr">
+        <is>
+          <t>preparatoire</t>
+        </is>
+      </c>
+      <c r="F275" s="3" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="G275" s="3" t="inlineStr">
+        <is>
           <t>descriptif</t>
         </is>
       </c>
-      <c r="H270" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="I270" s="3" t="inlineStr">
-        <is>
-          <t>oui</t>
-        </is>
-      </c>
-      <c r="J270" s="3" t="n">
+      <c r="H275" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="I275" s="3" t="inlineStr"/>
+      <c r="J275" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="K270" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="L270" s="3" t="inlineStr"/>
-      <c r="M270" s="3" t="inlineStr"/>
-      <c r="N270" s="3" t="inlineStr">
-        <is>
-          <t>corpus/livre-26-thermodynamique-et-processus-economique/c01-ce-que-ce-livre-doit-etablir.md</t>
+      <c r="K275" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="L275" s="3" t="inlineStr">
+        <is>
+          <t>entropie, decouplage, effet_rebond, limites_planetaires, sobriete, affectation_des_instruments</t>
+        </is>
+      </c>
+      <c r="M275" s="3" t="inlineStr">
+        <is>
+          <t>L1.C03, L1.C17, L8.C34, L11.C10, L11.C13, L11.C24, L18.C04, L18.C09, L22.C02, L24.C05, L26.C01, L26.C02, L26.C03, L26.C04, L26.C05</t>
+        </is>
+      </c>
+      <c r="N275" s="3" t="inlineStr">
+        <is>
+          <t>corpus/livre-26-thermodynamique-et-processus-economique/c06-portee-de-la-tranche.md</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:N270"/>
+  <autoFilter ref="A1:N275"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -18836,7 +19164,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
     </row>
@@ -18857,7 +19185,7 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="5">
@@ -18867,7 +19195,7 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="6">
@@ -18877,7 +19205,7 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>269</v>
+        <v>274</v>
       </c>
     </row>
     <row r="7">
@@ -18887,7 +19215,7 @@
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="8">
@@ -18897,7 +19225,7 @@
         </is>
       </c>
       <c r="B8" s="3" t="n">
-        <v>259</v>
+        <v>265</v>
       </c>
     </row>
     <row r="9">
@@ -18907,7 +19235,7 @@
         </is>
       </c>
       <c r="B9" s="3" t="n">
-        <v>260</v>
+        <v>265</v>
       </c>
     </row>
     <row r="10">
@@ -18927,7 +19255,7 @@
         </is>
       </c>
       <c r="B11" s="3" t="n">
-        <v>1282</v>
+        <v>1309</v>
       </c>
     </row>
     <row r="12">
@@ -18937,7 +19265,7 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>1066</v>
+        <v>1073</v>
       </c>
     </row>
     <row r="13">
@@ -18952,7 +19280,7 @@
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>L0, L9, L12, L13, L14, L15, L16, L17, L19, L26</t>
+          <t>L0, L9, L12, L13, L14, L15, L16, L17, L19</t>
         </is>
       </c>
     </row>
@@ -19031,7 +19359,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C297"/>
+  <dimension ref="A1:C302"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -24067,7 +24395,7 @@
       </c>
       <c r="C296" s="6" t="inlineStr">
         <is>
-          <t>candidat — AMORCE SEULE</t>
+          <t>en-cours — 6 chapitre(s)</t>
         </is>
       </c>
     </row>
@@ -24079,10 +24407,95 @@
       </c>
       <c r="B297" s="3" t="inlineStr">
         <is>
-          <t>[AMORCE] Ce que ce livre doit établir</t>
+          <t>Ce que ce livre doit établir</t>
         </is>
       </c>
       <c r="C297" s="3" t="inlineStr">
+        <is>
+          <t>brouillon</t>
+        </is>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    L26.C02</t>
+        </is>
+      </c>
+      <c r="B298" s="3" t="inlineStr">
+        <is>
+          <t>Le stock n'existe pas sous la forme demandée</t>
+        </is>
+      </c>
+      <c r="C298" s="3" t="inlineStr">
+        <is>
+          <t>brouillon</t>
+        </is>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    L26.C03</t>
+        </is>
+      </c>
+      <c r="B299" s="3" t="inlineStr">
+        <is>
+          <t>La frontière décide du chiffre</t>
+        </is>
+      </c>
+      <c r="C299" s="3" t="inlineStr">
+        <is>
+          <t>brouillon</t>
+        </is>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    L26.C04</t>
+        </is>
+      </c>
+      <c r="B300" s="3" t="inlineStr">
+        <is>
+          <t>L'effet rebond, et ce que le dispositif en hérite sans être une politique d'efficacité</t>
+        </is>
+      </c>
+      <c r="C300" s="3" t="inlineStr">
+        <is>
+          <t>brouillon</t>
+        </is>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    L26.C05</t>
+        </is>
+      </c>
+      <c r="B301" s="3" t="inlineStr">
+        <is>
+          <t>L'addition n'est pas la substitution</t>
+        </is>
+      </c>
+      <c r="C301" s="3" t="inlineStr">
+        <is>
+          <t>brouillon</t>
+        </is>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    L26.C06</t>
+        </is>
+      </c>
+      <c r="B302" s="3" t="inlineStr">
+        <is>
+          <t>Portée de la tranche</t>
+        </is>
+      </c>
+      <c r="C302" s="3" t="inlineStr">
         <is>
           <t>brouillon</t>
         </is>

--- a/plan-des-livres.xlsx
+++ b/plan-des-livres.xlsx
@@ -13,7 +13,7 @@
     <sheet name="Plan par livre" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Chapitres'!$A$1:$N$275</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Chapitres'!$A$1:$N$281</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -1300,41 +1300,41 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="2" t="inlineStr">
+      <c r="A21" s="4" t="inlineStr">
         <is>
           <t>L19</t>
         </is>
       </c>
-      <c r="B21" s="3" t="inlineStr">
+      <c r="B21" s="5" t="inlineStr">
         <is>
           <t>Comptabilité monétaire de l'émission sans dette</t>
         </is>
       </c>
-      <c r="C21" s="3" t="inlineStr">
+      <c r="C21" s="5" t="inlineStr">
         <is>
           <t>cahier-technique</t>
         </is>
       </c>
-      <c r="D21" s="3" t="inlineStr">
-        <is>
-          <t>reserve</t>
-        </is>
-      </c>
-      <c r="E21" s="3" t="inlineStr">
+      <c r="D21" s="5" t="inlineStr">
+        <is>
+          <t>en-cours</t>
+        </is>
+      </c>
+      <c r="E21" s="5" t="inlineStr">
         <is>
           <t>non contraignant</t>
         </is>
       </c>
-      <c r="F21" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G21" s="3" t="inlineStr"/>
-      <c r="H21" s="3" t="inlineStr">
+      <c r="F21" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="G21" s="5" t="inlineStr"/>
+      <c r="H21" s="5" t="inlineStr">
         <is>
           <t>Établir les écritures complètes d'une émission sans dette — chez l'émetteur, chez la banque centrale nationale, chez le bénéficiaire — et dire ce que l'unité est à l'actif comme au passif de chacun</t>
         </is>
       </c>
-      <c r="I21" s="3" t="inlineStr">
+      <c r="I21" s="5" t="inlineStr">
         <is>
           <t>écart de registre corrigé le 2026-09-07 — le matricule est réservé PAR LE PLAN DIRECTEUR et manquait à cette projection ; convention § 3, le plan tranche | arbitrage — A30 et A35 laissent ouvert ce que l'unité est AU PASSIF, et deux livres y ont buté : L10.C06 et L18.C06 | objection — L11.C02 : l'écriture du Symposium laisse les fonds propres négatifs du montant émis, et l'analogie qui la justifiait était fausse</t>
         </is>
@@ -1638,7 +1638,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N275"/>
+  <dimension ref="A1:N281"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -12279,7 +12279,7 @@
       </c>
       <c r="H168" s="3" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="I168" s="3" t="inlineStr"/>
@@ -12287,7 +12287,7 @@
         <v>3</v>
       </c>
       <c r="K168" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L168" s="3" t="inlineStr">
         <is>
@@ -12296,7 +12296,7 @@
       </c>
       <c r="M168" s="3" t="inlineStr">
         <is>
-          <t>L1.C15, L1.C20, L1.C29, L10.C01, L10.C02, L10.C04, L10.C05, L11.C05, L11.C07, L11.C09, L18.C01, L18.C05, L20.C02</t>
+          <t>L1.C15, L1.C20, L1.C29, L10.C01, L10.C02, L10.C04, L10.C05, L11.C05, L11.C07, L11.C09, L18.C01, L18.C05, L20.C02, L19.C03</t>
         </is>
       </c>
       <c r="N168" s="3" t="inlineStr">
@@ -12343,7 +12343,7 @@
       </c>
       <c r="H169" s="3" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="I169" s="3" t="inlineStr"/>
@@ -12351,7 +12351,7 @@
         <v>3</v>
       </c>
       <c r="K169" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L169" s="3" t="inlineStr">
         <is>
@@ -12360,7 +12360,7 @@
       </c>
       <c r="M169" s="3" t="inlineStr">
         <is>
-          <t>L1.C20, L1.C22, L1.C29, L10.C01, L10.C02, L10.C04, L10.C05, L10.C06, L11.C13, L20.C02</t>
+          <t>L1.C20, L1.C22, L1.C29, L10.C01, L10.C02, L10.C04, L10.C05, L10.C06, L11.C13, L20.C02, L19.C04</t>
         </is>
       </c>
       <c r="N169" s="3" t="inlineStr">
@@ -12407,7 +12407,7 @@
       </c>
       <c r="H170" s="3" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="I170" s="3" t="inlineStr"/>
@@ -12415,7 +12415,7 @@
         <v>6</v>
       </c>
       <c r="K170" s="3" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L170" s="3" t="inlineStr">
         <is>
@@ -12424,7 +12424,7 @@
       </c>
       <c r="M170" s="3" t="inlineStr">
         <is>
-          <t>L1.C17, L1.C19, L1.C20, L1.C21, L1.C27, L1.C29</t>
+          <t>L1.C17, L1.C19, L1.C20, L1.C21, L1.C27, L1.C29, L19.C03</t>
         </is>
       </c>
       <c r="N170" s="3" t="inlineStr">
@@ -12471,7 +12471,7 @@
       </c>
       <c r="H171" s="3" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="I171" s="3" t="inlineStr"/>
@@ -12479,7 +12479,7 @@
         <v>5</v>
       </c>
       <c r="K171" s="3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L171" s="3" t="inlineStr">
         <is>
@@ -12488,7 +12488,7 @@
       </c>
       <c r="M171" s="3" t="inlineStr">
         <is>
-          <t>L1.C18, L1.C20, L1.C21, L1.C29, L11.C01</t>
+          <t>L1.C18, L1.C20, L1.C21, L1.C29, L11.C01, L19.C02</t>
         </is>
       </c>
       <c r="N171" s="3" t="inlineStr">
@@ -12791,7 +12791,7 @@
       </c>
       <c r="H176" s="3" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="I176" s="3" t="inlineStr"/>
@@ -12799,7 +12799,7 @@
         <v>5</v>
       </c>
       <c r="K176" s="3" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="L176" s="3" t="inlineStr">
         <is>
@@ -12808,7 +12808,7 @@
       </c>
       <c r="M176" s="3" t="inlineStr">
         <is>
-          <t>L1.C21, L1.C26, L11.C02, L11.C03, L11.C04, L11.C05, L11.C06</t>
+          <t>L1.C21, L1.C26, L11.C02, L11.C03, L11.C04, L11.C05, L11.C06, L19.C03, L19.C05</t>
         </is>
       </c>
       <c r="N176" s="3" t="inlineStr">
@@ -12919,7 +12919,7 @@
       </c>
       <c r="H178" s="3" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="I178" s="3" t="inlineStr"/>
@@ -12927,7 +12927,7 @@
         <v>5</v>
       </c>
       <c r="K178" s="3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L178" s="3" t="inlineStr">
         <is>
@@ -12936,7 +12936,7 @@
       </c>
       <c r="M178" s="3" t="inlineStr">
         <is>
-          <t>L1.C21, L1.C22, L11.C03, L11.C05, L11.C06, L11.C07, L11.C08</t>
+          <t>L1.C21, L1.C22, L11.C03, L11.C05, L11.C06, L11.C07, L11.C08, L19.C05</t>
         </is>
       </c>
       <c r="N178" s="3" t="inlineStr">
@@ -14383,7 +14383,7 @@
       </c>
       <c r="H201" s="3" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="I201" s="3" t="inlineStr">
@@ -14395,10 +14395,14 @@
         <v>1</v>
       </c>
       <c r="K201" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L201" s="3" t="inlineStr"/>
-      <c r="M201" s="3" t="inlineStr"/>
+      <c r="M201" s="3" t="inlineStr">
+        <is>
+          <t>L19.C06</t>
+        </is>
+      </c>
       <c r="N201" s="3" t="inlineStr">
         <is>
           <t>corpus/livre-14-gouverner-la-preuve/c01-ce-que-ce-livre-doit-etablir.md</t>
@@ -15194,27 +15198,31 @@
       </c>
       <c r="G214" s="3" t="inlineStr">
         <is>
-          <t>descriptif</t>
+          <t>hybride</t>
         </is>
       </c>
       <c r="H214" s="3" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="I214" s="3" t="inlineStr">
-        <is>
-          <t>oui</t>
-        </is>
-      </c>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="I214" s="3" t="inlineStr"/>
       <c r="J214" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K214" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="L214" s="3" t="inlineStr"/>
-      <c r="M214" s="3" t="inlineStr"/>
+        <v>4</v>
+      </c>
+      <c r="L214" s="3" t="inlineStr">
+        <is>
+          <t>contrepartie_comptable, creation_monetaire, monnaie_comme_registre, hierarchie_monetaire, reflux_collectif</t>
+        </is>
+      </c>
+      <c r="M214" s="3" t="inlineStr">
+        <is>
+          <t>L1.C07, L10.C01, L10.C06, L11.C01, L11.C02, L18.C06, L21.C01, L21.C03</t>
+        </is>
+      </c>
       <c r="N214" s="3" t="inlineStr">
         <is>
           <t>corpus/livre-19-comptabilite-monetaire-de-l-emission-sans-dette/c01-ce-que-ce-livre-doit-etablir.md</t>
@@ -15224,17 +15232,17 @@
     <row r="215">
       <c r="A215" s="2" t="inlineStr">
         <is>
-          <t>L20.C01</t>
+          <t>L19.C02</t>
         </is>
       </c>
       <c r="B215" s="3" t="inlineStr">
         <is>
-          <t>L20</t>
+          <t>L19</t>
         </is>
       </c>
       <c r="C215" s="3" t="inlineStr">
         <is>
-          <t>Ce que ce livre doit établir</t>
+          <t>Le seul précédent, et le passif lui a été reconnu en 2008</t>
         </is>
       </c>
       <c r="D215" s="3" t="inlineStr">
@@ -15254,51 +15262,51 @@
       </c>
       <c r="G215" s="3" t="inlineStr">
         <is>
-          <t>conception</t>
+          <t>hybride</t>
         </is>
       </c>
       <c r="H215" s="3" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="I215" s="3" t="inlineStr"/>
       <c r="J215" s="3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K215" s="3" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="L215" s="3" t="inlineStr">
         <is>
-          <t>fenetre_de_reforme, referentiel_de_change, communs, limites_planetaires, creation_monetaire</t>
+          <t>contrepartie_comptable, reflux_collectif, hierarchie_monetaire, creation_monetaire, devise_cle</t>
         </is>
       </c>
       <c r="M215" s="3" t="inlineStr">
         <is>
-          <t>L1.C18, L1.C25, L1.C27, L7.C01, L7.C03, L7.C13, L7.C17, L7.C21, L11.C24</t>
+          <t>L3.C09, L10.C06, L11.C01, L11.C02, L19.C01, L20.C09, L21.C01, L21.C03, L21.C05, L19.C06</t>
         </is>
       </c>
       <c r="N215" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-20-droit-international-monetaire-et-commercial/c01-ce-que-ce-livre-doit-etablir.md</t>
+          <t>corpus/livre-19-comptabilite-monetaire-de-l-emission-sans-dette/c02-le-seul-precedent-et-le-passif-reconnu-en-2008.md</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" s="2" t="inlineStr">
         <is>
-          <t>L20.C02</t>
+          <t>L19.C03</t>
         </is>
       </c>
       <c r="B216" s="3" t="inlineStr">
         <is>
-          <t>L20</t>
+          <t>L19</t>
         </is>
       </c>
       <c r="C216" s="3" t="inlineStr">
         <is>
-          <t>L'interdiction du financement monétaire</t>
+          <t>Le reflux est un intérêt négatif, ou une répudiation — et c'est le moment qui décide</t>
         </is>
       </c>
       <c r="D216" s="3" t="inlineStr">
@@ -15318,51 +15326,51 @@
       </c>
       <c r="G216" s="3" t="inlineStr">
         <is>
-          <t>conception</t>
+          <t>hybride</t>
         </is>
       </c>
       <c r="H216" s="3" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="I216" s="3" t="inlineStr"/>
       <c r="J216" s="3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K216" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L216" s="3" t="inlineStr">
         <is>
-          <t>creation_monetaire, contrepartie_comptable, reflux_collectif, fenetre_de_reforme</t>
+          <t>monnaie_fondante, demurrage, reflux_monetaire, reflux_transactionnel, regle_contre_discretion, contrepartie_comptable</t>
         </is>
       </c>
       <c r="M216" s="3" t="inlineStr">
         <is>
-          <t>L1.C05, L1.C18, L1.C20, L1.C22, L7.C11, L7.C13, L11.C10, L20.C01</t>
+          <t>L10.C06, L11.C01, L11.C02, L11.C05, L11.C07, L11.C27, L19.C01, L19.C02, L21.C01</t>
         </is>
       </c>
       <c r="N216" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-20-droit-international-monetaire-et-commercial/c02-l-interdiction-du-financement-monetaire.md</t>
+          <t>corpus/livre-19-comptabilite-monetaire-de-l-emission-sans-dette/c03-le-reflux-interet-negatif-ou-repudiation.md</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" s="2" t="inlineStr">
         <is>
-          <t>L20.C03</t>
+          <t>L19.C04</t>
         </is>
       </c>
       <c r="B217" s="3" t="inlineStr">
         <is>
-          <t>L20</t>
+          <t>L19</t>
         </is>
       </c>
       <c r="C217" s="3" t="inlineStr">
         <is>
-          <t>L'objectif principal et ce qu'il exclut</t>
+          <t>L'actif transitoire n'existe pas, et le problème change de bilan</t>
         </is>
       </c>
       <c r="D217" s="3" t="inlineStr">
@@ -15382,51 +15390,51 @@
       </c>
       <c r="G217" s="3" t="inlineStr">
         <is>
-          <t>conception</t>
+          <t>hybride</t>
         </is>
       </c>
       <c r="H217" s="3" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="I217" s="3" t="inlineStr"/>
       <c r="J217" s="3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K217" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L217" s="3" t="inlineStr">
         <is>
-          <t>regle_contre_discretion, limites_planetaires, creation_monetaire, plafond_ecologique</t>
+          <t>contrepartie_comptable, hierarchie_monetaire, creation_monetaire, monnaie_comme_registre, solvabilite_anticipee</t>
         </is>
       </c>
       <c r="M217" s="3" t="inlineStr">
         <is>
-          <t>L1.C01, L1.C18, L1.C20, L7.C03, L8.C12, L8.C34, L11.C16, L20.C01, L20.C02</t>
+          <t>L1.C07, L10.C06, L10.C07, L11.C01, L11.C02, L19.C01, L19.C02, L19.C03, L21.C03</t>
         </is>
       </c>
       <c r="N217" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-20-droit-international-monetaire-et-commercial/c03-l-objectif-principal-et-ce-qu-il-exclut.md</t>
+          <t>corpus/livre-19-comptabilite-monetaire-de-l-emission-sans-dette/c04-l-actif-transitoire-et-le-deplacement-du-probleme.md</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" s="2" t="inlineStr">
         <is>
-          <t>L20.C04</t>
+          <t>L19.C05</t>
         </is>
       </c>
       <c r="B218" s="3" t="inlineStr">
         <is>
-          <t>L20</t>
+          <t>L19</t>
         </is>
       </c>
       <c r="C218" s="3" t="inlineStr">
         <is>
-          <t>L'indépendance, et à l'égard de qui</t>
+          <t>Un débiteur collectif n'existe pas — sauf comme somme de débiteurs identifiés</t>
         </is>
       </c>
       <c r="D218" s="3" t="inlineStr">
@@ -15446,51 +15454,51 @@
       </c>
       <c r="G218" s="3" t="inlineStr">
         <is>
-          <t>conception</t>
+          <t>hybride</t>
         </is>
       </c>
       <c r="H218" s="3" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="I218" s="3" t="inlineStr"/>
       <c r="J218" s="3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K218" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L218" s="3" t="inlineStr">
         <is>
-          <t>regle_contre_discretion, creation_monetaire, fenetre_de_reforme</t>
+          <t>reflux_collectif, contrepartie_comptable, demurrage, monnaie_fondante, hierarchie_monetaire</t>
         </is>
       </c>
       <c r="M218" s="3" t="inlineStr">
         <is>
-          <t>L1.C18, L7.C04, L7.C07, L7.C10, L8.C31, L11.C17, L20.C01, L20.C03, L20.C11</t>
+          <t>L10.C06, L11.C05, L11.C07, L11.C09, L19.C01, L19.C02, L19.C03, L21.C01, L25.C05</t>
         </is>
       </c>
       <c r="N218" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-20-droit-international-monetaire-et-commercial/c04-l-independance-et-a-l-egard-de-qui.md</t>
+          <t>corpus/livre-19-comptabilite-monetaire-de-l-emission-sans-dette/c05-le-creancier-collectif-et-ce-qui-le-rend-representable.md</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" s="2" t="inlineStr">
         <is>
-          <t>L20.C05</t>
+          <t>L19.C06</t>
         </is>
       </c>
       <c r="B219" s="3" t="inlineStr">
         <is>
-          <t>L20</t>
+          <t>L19</t>
         </is>
       </c>
       <c r="C219" s="3" t="inlineStr">
         <is>
-          <t>Le monopole d'émission et le cours légal</t>
+          <t>Les fonds propres négatifs, et l'institution qui n'apparaît dans les comptes de personne</t>
         </is>
       </c>
       <c r="D219" s="3" t="inlineStr">
@@ -15510,51 +15518,51 @@
       </c>
       <c r="G219" s="3" t="inlineStr">
         <is>
-          <t>conception</t>
+          <t>hybride</t>
         </is>
       </c>
       <c r="H219" s="3" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="I219" s="3" t="inlineStr"/>
       <c r="J219" s="3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K219" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L219" s="3" t="inlineStr">
         <is>
-          <t>monnaie_comme_registre, creation_monetaire, referentiel_de_change, hierarchie_monetaire</t>
+          <t>contrepartie_comptable, solvabilite_anticipee, architecture_invisible, hierarchie_monetaire, robustesse</t>
         </is>
       </c>
       <c r="M219" s="3" t="inlineStr">
         <is>
-          <t>L1.C05, L1.C07, L1.C26, L7.C15, L11.C15, L20.C01, L20.C02, L20.C03</t>
+          <t>L1.C07, L7.C06, L14.C01, L19.C01, L19.C02, L19.C03, L19.C04, L21.C01, L21.C04</t>
         </is>
       </c>
       <c r="N219" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-20-droit-international-monetaire-et-commercial/c05-le-monopole-d-emission-et-le-cours-legal.md</t>
+          <t>corpus/livre-19-comptabilite-monetaire-de-l-emission-sans-dette/c06-les-fonds-propres-negatifs-et-l-institution-qui-n-apparait-nulle-part.md</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" s="2" t="inlineStr">
         <is>
-          <t>L20.C06</t>
+          <t>L19.C07</t>
         </is>
       </c>
       <c r="B220" s="3" t="inlineStr">
         <is>
-          <t>L20</t>
+          <t>L19</t>
         </is>
       </c>
       <c r="C220" s="3" t="inlineStr">
         <is>
-          <t>Les voies de révision et leur coût</t>
+          <t>Portée de la tranche</t>
         </is>
       </c>
       <c r="D220" s="3" t="inlineStr">
@@ -15574,41 +15582,41 @@
       </c>
       <c r="G220" s="3" t="inlineStr">
         <is>
-          <t>conception</t>
+          <t>descriptif</t>
         </is>
       </c>
       <c r="H220" s="3" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="I220" s="3" t="inlineStr"/>
       <c r="J220" s="3" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K220" s="3" t="n">
         <v>4</v>
       </c>
       <c r="L220" s="3" t="inlineStr">
         <is>
-          <t>fenetre_de_reforme, regle_contre_discretion, creation_monetaire</t>
+          <t>contrepartie_comptable, reflux_collectif, monnaie_fondante, hierarchie_monetaire, architecture_invisible, creation_monetaire</t>
         </is>
       </c>
       <c r="M220" s="3" t="inlineStr">
         <is>
-          <t>L1.C18, L7.C12, L7.C20, L7.C21, L11.C15, L20.C01, L20.C02, L20.C03, L20.C07, L20.C09, L20.C18</t>
+          <t>L10.C06, L11.C01, L11.C02, L11.C07, L19.C01, L19.C02, L19.C03, L19.C04, L19.C05, L19.C06, L21.C01, L21.C03</t>
         </is>
       </c>
       <c r="N220" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-20-droit-international-monetaire-et-commercial/c06-les-voies-de-revision-et-leur-cout.md</t>
+          <t>corpus/livre-19-comptabilite-monetaire-de-l-emission-sans-dette/c07-portee-de-la-tranche.md</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" s="2" t="inlineStr">
         <is>
-          <t>L20.C07</t>
+          <t>L20.C01</t>
         </is>
       </c>
       <c r="B221" s="3" t="inlineStr">
@@ -15618,7 +15626,7 @@
       </c>
       <c r="C221" s="3" t="inlineStr">
         <is>
-          <t>L'accord monétaire international</t>
+          <t>Ce que ce livre doit établir</t>
         </is>
       </c>
       <c r="D221" s="3" t="inlineStr">
@@ -15643,7 +15651,7 @@
       </c>
       <c r="H221" s="3" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="I221" s="3" t="inlineStr"/>
@@ -15655,24 +15663,24 @@
       </c>
       <c r="L221" s="3" t="inlineStr">
         <is>
-          <t>referentiel_de_change, fenetre_de_reforme, etalon_de_change_or, hierarchie_monetaire</t>
+          <t>fenetre_de_reforme, referentiel_de_change, communs, limites_planetaires, creation_monetaire</t>
         </is>
       </c>
       <c r="M221" s="3" t="inlineStr">
         <is>
-          <t>L1.C18, L1.C26, L7.C02, L7.C05, L7.C12, L7.C13, L11.C15, L20.C01, L20.C03, L20.C06, L20.C10</t>
+          <t>L1.C18, L1.C25, L1.C27, L7.C01, L7.C03, L7.C13, L7.C17, L7.C21, L11.C24</t>
         </is>
       </c>
       <c r="N221" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-20-droit-international-monetaire-et-commercial/c07-l-accord-monetaire-international.md</t>
+          <t>corpus/livre-20-droit-international-monetaire-et-commercial/c01-ce-que-ce-livre-doit-etablir.md</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" s="2" t="inlineStr">
         <is>
-          <t>L20.C08</t>
+          <t>L20.C02</t>
         </is>
       </c>
       <c r="B222" s="3" t="inlineStr">
@@ -15682,7 +15690,7 @@
       </c>
       <c r="C222" s="3" t="inlineStr">
         <is>
-          <t>La parité inscrite dans le traité</t>
+          <t>L'interdiction du financement monétaire</t>
         </is>
       </c>
       <c r="D222" s="3" t="inlineStr">
@@ -15712,31 +15720,31 @@
       </c>
       <c r="I222" s="3" t="inlineStr"/>
       <c r="J222" s="3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K222" s="3" t="n">
         <v>3</v>
       </c>
       <c r="L222" s="3" t="inlineStr">
         <is>
-          <t>referentiel_de_change, etalon_de_change_or, hierarchie_monetaire, bareme, devise_cle</t>
+          <t>creation_monetaire, contrepartie_comptable, reflux_collectif, fenetre_de_reforme</t>
         </is>
       </c>
       <c r="M222" s="3" t="inlineStr">
         <is>
-          <t>L1.C25, L1.C26, L1.C28, L7.C02, L7.C20, L11.C15, L11.C17, L20.C01, L20.C09, L20.C13</t>
+          <t>L1.C05, L1.C18, L1.C20, L1.C22, L7.C11, L7.C13, L11.C10, L20.C01</t>
         </is>
       </c>
       <c r="N222" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-20-droit-international-monetaire-et-commercial/c08-la-parite-inscrite-dans-le-traite.md</t>
+          <t>corpus/livre-20-droit-international-monetaire-et-commercial/c02-l-interdiction-du-financement-monetaire.md</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" s="2" t="inlineStr">
         <is>
-          <t>L20.C09</t>
+          <t>L20.C03</t>
         </is>
       </c>
       <c r="B223" s="3" t="inlineStr">
@@ -15746,7 +15754,7 @@
       </c>
       <c r="C223" s="3" t="inlineStr">
         <is>
-          <t>L'amendement des statuts du Fonds</t>
+          <t>L'objectif principal et ce qu'il exclut</t>
         </is>
       </c>
       <c r="D223" s="3" t="inlineStr">
@@ -15771,7 +15779,7 @@
       </c>
       <c r="H223" s="3" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="I223" s="3" t="inlineStr"/>
@@ -15783,24 +15791,24 @@
       </c>
       <c r="L223" s="3" t="inlineStr">
         <is>
-          <t>fenetre_de_reforme, referentiel_de_change, bareme, regle_contre_discretion</t>
+          <t>regle_contre_discretion, limites_planetaires, creation_monetaire, plafond_ecologique</t>
         </is>
       </c>
       <c r="M223" s="3" t="inlineStr">
         <is>
-          <t>L7.C06, L7.C09, L7.C16, L7.C20, L11.C15, L11.C20, L20.C01, L20.C06, L20.C08, L20.C10, L20.C13</t>
+          <t>L1.C01, L1.C18, L1.C20, L7.C03, L8.C12, L8.C34, L11.C16, L20.C01, L20.C02</t>
         </is>
       </c>
       <c r="N223" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-20-droit-international-monetaire-et-commercial/c09-l-amendement-des-statuts-du-fonds.md</t>
+          <t>corpus/livre-20-droit-international-monetaire-et-commercial/c03-l-objectif-principal-et-ce-qu-il-exclut.md</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" s="2" t="inlineStr">
         <is>
-          <t>L20.C10</t>
+          <t>L20.C04</t>
         </is>
       </c>
       <c r="B224" s="3" t="inlineStr">
@@ -15810,7 +15818,7 @@
       </c>
       <c r="C224" s="3" t="inlineStr">
         <is>
-          <t>Le vote pondéré et les voix de base</t>
+          <t>L'indépendance, et à l'égard de qui</t>
         </is>
       </c>
       <c r="D224" s="3" t="inlineStr">
@@ -15847,24 +15855,24 @@
       </c>
       <c r="L224" s="3" t="inlineStr">
         <is>
-          <t>bareme, devise_cle, hierarchie_monetaire, referentiel_de_change</t>
+          <t>regle_contre_discretion, creation_monetaire, fenetre_de_reforme</t>
         </is>
       </c>
       <c r="M224" s="3" t="inlineStr">
         <is>
-          <t>L1.C25, L7.C02, L7.C05, L7.C06, L7.C09, L7.C10, L11.C16, L20.C01, L20.C07, L20.C09, L20.C12</t>
+          <t>L1.C18, L7.C04, L7.C07, L7.C10, L8.C31, L11.C17, L20.C01, L20.C03, L20.C11</t>
         </is>
       </c>
       <c r="N224" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-20-droit-international-monetaire-et-commercial/c10-le-vote-pondere-et-les-voix-de-base.md</t>
+          <t>corpus/livre-20-droit-international-monetaire-et-commercial/c04-l-independance-et-a-l-egard-de-qui.md</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" s="2" t="inlineStr">
         <is>
-          <t>L20.C11</t>
+          <t>L20.C05</t>
         </is>
       </c>
       <c r="B225" s="3" t="inlineStr">
@@ -15874,7 +15882,7 @@
       </c>
       <c r="C225" s="3" t="inlineStr">
         <is>
-          <t>La personnalité juridique et les immunités</t>
+          <t>Le monopole d'émission et le cours légal</t>
         </is>
       </c>
       <c r="D225" s="3" t="inlineStr">
@@ -15904,31 +15912,31 @@
       </c>
       <c r="I225" s="3" t="inlineStr"/>
       <c r="J225" s="3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K225" s="3" t="n">
         <v>3</v>
       </c>
       <c r="L225" s="3" t="inlineStr">
         <is>
-          <t>communs, creation_monetaire, fenetre_de_reforme, robustesse</t>
+          <t>monnaie_comme_registre, creation_monetaire, referentiel_de_change, hierarchie_monetaire</t>
         </is>
       </c>
       <c r="M225" s="3" t="inlineStr">
         <is>
-          <t>L7.C01, L7.C03, L7.C07, L7.C10, L7.C13, L11.C25, L20.C01, L20.C04, L20.C12, L20.C14</t>
+          <t>L1.C05, L1.C07, L1.C26, L7.C15, L11.C15, L20.C01, L20.C02, L20.C03</t>
         </is>
       </c>
       <c r="N225" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-20-droit-international-monetaire-et-commercial/c11-la-personnalite-juridique-et-les-immunites.md</t>
+          <t>corpus/livre-20-droit-international-monetaire-et-commercial/c05-le-monopole-d-emission-et-le-cours-legal.md</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" s="2" t="inlineStr">
         <is>
-          <t>L20.C12</t>
+          <t>L20.C06</t>
         </is>
       </c>
       <c r="B226" s="3" t="inlineStr">
@@ -15938,7 +15946,7 @@
       </c>
       <c r="C226" s="3" t="inlineStr">
         <is>
-          <t>Les pouvoirs non délégables</t>
+          <t>Les voies de révision et leur coût</t>
         </is>
       </c>
       <c r="D226" s="3" t="inlineStr">
@@ -15963,36 +15971,36 @@
       </c>
       <c r="H226" s="3" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="I226" s="3" t="inlineStr"/>
       <c r="J226" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K226" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L226" s="3" t="inlineStr">
         <is>
-          <t>bareme, valorisation_des_communs, polycentricite, robustesse</t>
+          <t>fenetre_de_reforme, regle_contre_discretion, creation_monetaire</t>
         </is>
       </c>
       <c r="M226" s="3" t="inlineStr">
         <is>
-          <t>L7.C05, L7.C06, L7.C07, L7.C11, L7.C14, L11.C16, L11.C20, L20.C01, L20.C09, L20.C10, L20.C14</t>
+          <t>L1.C18, L7.C12, L7.C20, L7.C21, L11.C15, L20.C01, L20.C02, L20.C03, L20.C07, L20.C09, L20.C18</t>
         </is>
       </c>
       <c r="N226" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-20-droit-international-monetaire-et-commercial/c12-les-pouvoirs-non-delegables.md</t>
+          <t>corpus/livre-20-droit-international-monetaire-et-commercial/c06-les-voies-de-revision-et-leur-cout.md</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" s="2" t="inlineStr">
         <is>
-          <t>L20.C13</t>
+          <t>L20.C07</t>
         </is>
       </c>
       <c r="B227" s="3" t="inlineStr">
@@ -16002,7 +16010,7 @@
       </c>
       <c r="C227" s="3" t="inlineStr">
         <is>
-          <t>L'entrée en vigueur, l'adhésion et le retrait</t>
+          <t>L'accord monétaire international</t>
         </is>
       </c>
       <c r="D227" s="3" t="inlineStr">
@@ -16027,36 +16035,36 @@
       </c>
       <c r="H227" s="3" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="I227" s="3" t="inlineStr"/>
       <c r="J227" s="3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K227" s="3" t="n">
         <v>3</v>
       </c>
       <c r="L227" s="3" t="inlineStr">
         <is>
-          <t>seuil_d_activation, reflux_collectif, fenetre_de_reforme, additionnalite</t>
+          <t>referentiel_de_change, fenetre_de_reforme, etalon_de_change_or, hierarchie_monetaire</t>
         </is>
       </c>
       <c r="M227" s="3" t="inlineStr">
         <is>
-          <t>L7.C11, L7.C12, L7.C16, L7.C17, L7.C19, L11.C18, L20.C01, L20.C06, L20.C09, L20.C12</t>
+          <t>L1.C18, L1.C26, L7.C02, L7.C05, L7.C12, L7.C13, L11.C15, L20.C01, L20.C03, L20.C06, L20.C10</t>
         </is>
       </c>
       <c r="N227" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-20-droit-international-monetaire-et-commercial/c13-l-entree-en-vigueur-l-adhesion-et-le-retrait.md</t>
+          <t>corpus/livre-20-droit-international-monetaire-et-commercial/c07-l-accord-monetaire-international.md</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" s="2" t="inlineStr">
         <is>
-          <t>L20.C14</t>
+          <t>L20.C08</t>
         </is>
       </c>
       <c r="B228" s="3" t="inlineStr">
@@ -16066,7 +16074,7 @@
       </c>
       <c r="C228" s="3" t="inlineStr">
         <is>
-          <t>Qui interprète le traité</t>
+          <t>La parité inscrite dans le traité</t>
         </is>
       </c>
       <c r="D228" s="3" t="inlineStr">
@@ -16096,31 +16104,31 @@
       </c>
       <c r="I228" s="3" t="inlineStr"/>
       <c r="J228" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K228" s="3" t="n">
         <v>3</v>
       </c>
       <c r="L228" s="3" t="inlineStr">
         <is>
-          <t>robustesse, regle_contre_discretion, communs</t>
+          <t>referentiel_de_change, etalon_de_change_or, hierarchie_monetaire, bareme, devise_cle</t>
         </is>
       </c>
       <c r="M228" s="3" t="inlineStr">
         <is>
-          <t>L7.C07, L7.C13, L7.C14, L7.C19, L11.C19, L11.C25, L20.C01, L20.C03, L20.C11, L20.C12, L20.C21</t>
+          <t>L1.C25, L1.C26, L1.C28, L7.C02, L7.C20, L11.C15, L11.C17, L20.C01, L20.C09, L20.C13</t>
         </is>
       </c>
       <c r="N228" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-20-droit-international-monetaire-et-commercial/c14-qui-interprete-le-traite.md</t>
+          <t>corpus/livre-20-droit-international-monetaire-et-commercial/c08-la-parite-inscrite-dans-le-traite.md</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" s="2" t="inlineStr">
         <is>
-          <t>L20.C15</t>
+          <t>L20.C09</t>
         </is>
       </c>
       <c r="B229" s="3" t="inlineStr">
@@ -16130,7 +16138,7 @@
       </c>
       <c r="C229" s="3" t="inlineStr">
         <is>
-          <t>Le devoir international des agents</t>
+          <t>L'amendement des statuts du Fonds</t>
         </is>
       </c>
       <c r="D229" s="3" t="inlineStr">
@@ -16160,31 +16168,31 @@
       </c>
       <c r="I229" s="3" t="inlineStr"/>
       <c r="J229" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K229" s="3" t="n">
         <v>3</v>
       </c>
       <c r="L229" s="3" t="inlineStr">
         <is>
-          <t>robustesse, regle_contre_discretion, indicateur_de_progres</t>
+          <t>fenetre_de_reforme, referentiel_de_change, bareme, regle_contre_discretion</t>
         </is>
       </c>
       <c r="M229" s="3" t="inlineStr">
         <is>
-          <t>L7.C04, L7.C07, L7.C10, L11.C21, L11.C25, L20.C01, L20.C04, L20.C11, L20.C14</t>
+          <t>L7.C06, L7.C09, L7.C16, L7.C20, L11.C15, L11.C20, L20.C01, L20.C06, L20.C08, L20.C10, L20.C13</t>
         </is>
       </c>
       <c r="N229" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-20-droit-international-monetaire-et-commercial/c15-le-devoir-international-des-agents.md</t>
+          <t>corpus/livre-20-droit-international-monetaire-et-commercial/c09-l-amendement-des-statuts-du-fonds.md</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" s="2" t="inlineStr">
         <is>
-          <t>L20.C16</t>
+          <t>L20.C10</t>
         </is>
       </c>
       <c r="B230" s="3" t="inlineStr">
@@ -16194,7 +16202,7 @@
       </c>
       <c r="C230" s="3" t="inlineStr">
         <is>
-          <t>Le patrimoine commun de l'humanité</t>
+          <t>Le vote pondéré et les voix de base</t>
         </is>
       </c>
       <c r="D230" s="3" t="inlineStr">
@@ -16219,7 +16227,7 @@
       </c>
       <c r="H230" s="3" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="I230" s="3" t="inlineStr"/>
@@ -16231,24 +16239,24 @@
       </c>
       <c r="L230" s="3" t="inlineStr">
         <is>
-          <t>communs, valorisation_des_communs, limites_planetaires, additionnalite, plafond_ecologique</t>
+          <t>bareme, devise_cle, hierarchie_monetaire, referentiel_de_change</t>
         </is>
       </c>
       <c r="M230" s="3" t="inlineStr">
         <is>
-          <t>L1.C17, L1.C22, L7.C05, L7.C13, L11.C16, L20.C01, L20.C11, L20.C17, L20.C22</t>
+          <t>L1.C25, L7.C02, L7.C05, L7.C06, L7.C09, L7.C10, L11.C16, L20.C01, L20.C07, L20.C09, L20.C12</t>
         </is>
       </c>
       <c r="N230" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-20-droit-international-monetaire-et-commercial/c16-le-patrimoine-commun-de-l-humanite.md</t>
+          <t>corpus/livre-20-droit-international-monetaire-et-commercial/c10-le-vote-pondere-et-les-voix-de-base.md</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" s="2" t="inlineStr">
         <is>
-          <t>L20.C17</t>
+          <t>L20.C11</t>
         </is>
       </c>
       <c r="B231" s="3" t="inlineStr">
@@ -16258,7 +16266,7 @@
       </c>
       <c r="C231" s="3" t="inlineStr">
         <is>
-          <t>La sanctuarisation, et elle existe</t>
+          <t>La personnalité juridique et les immunités</t>
         </is>
       </c>
       <c r="D231" s="3" t="inlineStr">
@@ -16283,7 +16291,7 @@
       </c>
       <c r="H231" s="3" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="I231" s="3" t="inlineStr"/>
@@ -16291,28 +16299,28 @@
         <v>4</v>
       </c>
       <c r="K231" s="3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L231" s="3" t="inlineStr">
         <is>
-          <t>communs, limites_planetaires, fenetre_de_reforme, robustesse, plafond_ecologique</t>
+          <t>communs, creation_monetaire, fenetre_de_reforme, robustesse</t>
         </is>
       </c>
       <c r="M231" s="3" t="inlineStr">
         <is>
-          <t>L1.C17, L1.C18, L7.C13, L7.C19, L7.C20, L11.C20, L20.C01, L20.C06, L20.C09, L20.C16, L20.C22</t>
+          <t>L7.C01, L7.C03, L7.C07, L7.C10, L7.C13, L11.C25, L20.C01, L20.C04, L20.C12, L20.C14</t>
         </is>
       </c>
       <c r="N231" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-20-droit-international-monetaire-et-commercial/c17-la-sanctuarisation-et-elle-existe.md</t>
+          <t>corpus/livre-20-droit-international-monetaire-et-commercial/c11-la-personnalite-juridique-et-les-immunites.md</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="A232" s="2" t="inlineStr">
         <is>
-          <t>L20.C18</t>
+          <t>L20.C12</t>
         </is>
       </c>
       <c r="B232" s="3" t="inlineStr">
@@ -16322,7 +16330,7 @@
       </c>
       <c r="C232" s="3" t="inlineStr">
         <is>
-          <t>L'amendement et la dérogation dans l'ordre commercial</t>
+          <t>Les pouvoirs non délégables</t>
         </is>
       </c>
       <c r="D232" s="3" t="inlineStr">
@@ -16347,7 +16355,7 @@
       </c>
       <c r="H232" s="3" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="I232" s="3" t="inlineStr"/>
@@ -16359,24 +16367,24 @@
       </c>
       <c r="L232" s="3" t="inlineStr">
         <is>
-          <t>bareme, seuil_d_activation, additionnalite, fenetre_de_reforme</t>
+          <t>bareme, valorisation_des_communs, polycentricite, robustesse</t>
         </is>
       </c>
       <c r="M232" s="3" t="inlineStr">
         <is>
-          <t>L1.C27, L7.C17, L7.C20, L11.C24, L20.C01, L20.C06, L20.C09, L20.C13, L20.C19, L20.C20</t>
+          <t>L7.C05, L7.C06, L7.C07, L7.C11, L7.C14, L11.C16, L11.C20, L20.C01, L20.C09, L20.C10, L20.C14</t>
         </is>
       </c>
       <c r="N232" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-20-droit-international-monetaire-et-commercial/c18-l-amendement-et-la-derogation-dans-l-ordre-commercial.md</t>
+          <t>corpus/livre-20-droit-international-monetaire-et-commercial/c12-les-pouvoirs-non-delegables.md</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" s="2" t="inlineStr">
         <is>
-          <t>L20.C19</t>
+          <t>L20.C13</t>
         </is>
       </c>
       <c r="B233" s="3" t="inlineStr">
@@ -16386,7 +16394,7 @@
       </c>
       <c r="C233" s="3" t="inlineStr">
         <is>
-          <t>Le texte que la conformité invoque</t>
+          <t>L'entrée en vigueur, l'adhésion et le retrait</t>
         </is>
       </c>
       <c r="D233" s="3" t="inlineStr">
@@ -16423,24 +16431,24 @@
       </c>
       <c r="L233" s="3" t="inlineStr">
         <is>
-          <t>bareme, additionnalite, limites_planetaires, seuil_d_activation, externalisation</t>
+          <t>seuil_d_activation, reflux_collectif, fenetre_de_reforme, additionnalite</t>
         </is>
       </c>
       <c r="M233" s="3" t="inlineStr">
         <is>
-          <t>L1.C27, L7.C17, L11.C24, L20.C01, L20.C18, L20.C20, L20.C22</t>
+          <t>L7.C11, L7.C12, L7.C16, L7.C17, L7.C19, L11.C18, L20.C01, L20.C06, L20.C09, L20.C12</t>
         </is>
       </c>
       <c r="N233" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-20-droit-international-monetaire-et-commercial/c19-le-texte-que-la-conformite-invoque.md</t>
+          <t>corpus/livre-20-droit-international-monetaire-et-commercial/c13-l-entree-en-vigueur-l-adhesion-et-le-retrait.md</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" s="2" t="inlineStr">
         <is>
-          <t>L20.C20</t>
+          <t>L20.C14</t>
         </is>
       </c>
       <c r="B234" s="3" t="inlineStr">
@@ -16450,7 +16458,7 @@
       </c>
       <c r="C234" s="3" t="inlineStr">
         <is>
-          <t>L'ajustement aux frontières comme précédent</t>
+          <t>Qui interprète le traité</t>
         </is>
       </c>
       <c r="D234" s="3" t="inlineStr">
@@ -16480,31 +16488,31 @@
       </c>
       <c r="I234" s="3" t="inlineStr"/>
       <c r="J234" s="3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K234" s="3" t="n">
         <v>3</v>
       </c>
       <c r="L234" s="3" t="inlineStr">
         <is>
-          <t>bareme, seuil_d_activation, externalisation, additionnalite, contrepartie_comptable</t>
+          <t>robustesse, regle_contre_discretion, communs</t>
         </is>
       </c>
       <c r="M234" s="3" t="inlineStr">
         <is>
-          <t>L1.C27, L7.C17, L11.C21, L11.C24, L11.C25, L20.C01, L20.C18, L20.C19, L20.C22</t>
+          <t>L7.C07, L7.C13, L7.C14, L7.C19, L11.C19, L11.C25, L20.C01, L20.C03, L20.C11, L20.C12, L20.C21</t>
         </is>
       </c>
       <c r="N234" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-20-droit-international-monetaire-et-commercial/c20-l-ajustement-aux-frontieres-comme-precedent.md</t>
+          <t>corpus/livre-20-droit-international-monetaire-et-commercial/c14-qui-interprete-le-traite.md</t>
         </is>
       </c>
     </row>
     <row r="235">
       <c r="A235" s="2" t="inlineStr">
         <is>
-          <t>L20.C21</t>
+          <t>L20.C15</t>
         </is>
       </c>
       <c r="B235" s="3" t="inlineStr">
@@ -16514,7 +16522,7 @@
       </c>
       <c r="C235" s="3" t="inlineStr">
         <is>
-          <t>La transparence et sa limite juridictionnelle</t>
+          <t>Le devoir international des agents</t>
         </is>
       </c>
       <c r="D235" s="3" t="inlineStr">
@@ -16544,31 +16552,31 @@
       </c>
       <c r="I235" s="3" t="inlineStr"/>
       <c r="J235" s="3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K235" s="3" t="n">
         <v>3</v>
       </c>
       <c r="L235" s="3" t="inlineStr">
         <is>
-          <t>robustesse, contrepartie_comptable, bareme, monnaie_comme_registre</t>
+          <t>robustesse, regle_contre_discretion, indicateur_de_progres</t>
         </is>
       </c>
       <c r="M235" s="3" t="inlineStr">
         <is>
-          <t>L7.C18, L11.C21, L11.C24, L11.C25, L20.C01, L20.C11, L20.C14, L20.C20, L20.C22</t>
+          <t>L7.C04, L7.C07, L7.C10, L11.C21, L11.C25, L20.C01, L20.C04, L20.C11, L20.C14</t>
         </is>
       </c>
       <c r="N235" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-20-droit-international-monetaire-et-commercial/c21-la-transparence-et-sa-limite-juridictionnelle.md</t>
+          <t>corpus/livre-20-droit-international-monetaire-et-commercial/c15-le-devoir-international-des-agents.md</t>
         </is>
       </c>
     </row>
     <row r="236">
       <c r="A236" s="2" t="inlineStr">
         <is>
-          <t>L20.C22</t>
+          <t>L20.C16</t>
         </is>
       </c>
       <c r="B236" s="3" t="inlineStr">
@@ -16578,7 +16586,7 @@
       </c>
       <c r="C236" s="3" t="inlineStr">
         <is>
-          <t>Ce que le droit devrait devenir</t>
+          <t>Le patrimoine commun de l'humanité</t>
         </is>
       </c>
       <c r="D236" s="3" t="inlineStr">
@@ -16603,7 +16611,7 @@
       </c>
       <c r="H236" s="3" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="I236" s="3" t="inlineStr"/>
@@ -16615,24 +16623,24 @@
       </c>
       <c r="L236" s="3" t="inlineStr">
         <is>
-          <t>fenetre_de_reforme, communs, limites_planetaires, regle_contre_discretion, bareme, referentiel_de_change</t>
+          <t>communs, valorisation_des_communs, limites_planetaires, additionnalite, plafond_ecologique</t>
         </is>
       </c>
       <c r="M236" s="3" t="inlineStr">
         <is>
-          <t>L1.C18, L7.C12, L7.C13, L11.C15, L11.C25, L20.C01, L20.C03, L20.C06, L20.C07, L20.C08, L20.C12, L20.C13, L20.C16, L20.C17, L20.C19, L20.C20, L20.C21, L20.C23</t>
+          <t>L1.C17, L1.C22, L7.C05, L7.C13, L11.C16, L20.C01, L20.C11, L20.C17, L20.C22</t>
         </is>
       </c>
       <c r="N236" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-20-droit-international-monetaire-et-commercial/c22-ce-que-le-droit-devrait-devenir.md</t>
+          <t>corpus/livre-20-droit-international-monetaire-et-commercial/c16-le-patrimoine-commun-de-l-humanite.md</t>
         </is>
       </c>
     </row>
     <row r="237">
       <c r="A237" s="2" t="inlineStr">
         <is>
-          <t>L20.C23</t>
+          <t>L20.C17</t>
         </is>
       </c>
       <c r="B237" s="3" t="inlineStr">
@@ -16642,7 +16650,7 @@
       </c>
       <c r="C237" s="3" t="inlineStr">
         <is>
-          <t>La portée du livre</t>
+          <t>La sanctuarisation, et elle existe</t>
         </is>
       </c>
       <c r="D237" s="3" t="inlineStr">
@@ -16667,46 +16675,46 @@
       </c>
       <c r="H237" s="3" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="I237" s="3" t="inlineStr"/>
       <c r="J237" s="3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K237" s="3" t="n">
         <v>4</v>
       </c>
       <c r="L237" s="3" t="inlineStr">
         <is>
-          <t>fenetre_de_reforme, communs, limites_planetaires, creation_monetaire, robustesse</t>
+          <t>communs, limites_planetaires, fenetre_de_reforme, robustesse, plafond_ecologique</t>
         </is>
       </c>
       <c r="M237" s="3" t="inlineStr">
         <is>
-          <t>L1.C18, L1.C27, L7.C05, L7.C10, L7.C12, L7.C13, L11.C15, L11.C24, L11.C25, L20.C01, L20.C02, L20.C03, L20.C06, L20.C07, L20.C08, L20.C11, L20.C12, L20.C13, L20.C16, L20.C17, L20.C19, L20.C20, L20.C21, L20.C22</t>
+          <t>L1.C17, L1.C18, L7.C13, L7.C19, L7.C20, L11.C20, L20.C01, L20.C06, L20.C09, L20.C16, L20.C22</t>
         </is>
       </c>
       <c r="N237" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-20-droit-international-monetaire-et-commercial/c23-la-portee-du-livre.md</t>
+          <t>corpus/livre-20-droit-international-monetaire-et-commercial/c17-la-sanctuarisation-et-elle-existe.md</t>
         </is>
       </c>
     </row>
     <row r="238">
       <c r="A238" s="2" t="inlineStr">
         <is>
-          <t>L21.C01</t>
+          <t>L20.C18</t>
         </is>
       </c>
       <c r="B238" s="3" t="inlineStr">
         <is>
-          <t>L21</t>
+          <t>L20</t>
         </is>
       </c>
       <c r="C238" s="3" t="inlineStr">
         <is>
-          <t>Ce que ce livre doit établir, et le principe qui exige des fonds propres</t>
+          <t>L'amendement et la dérogation dans l'ordre commercial</t>
         </is>
       </c>
       <c r="D238" s="3" t="inlineStr">
@@ -16726,12 +16734,12 @@
       </c>
       <c r="G238" s="3" t="inlineStr">
         <is>
-          <t>hybride</t>
+          <t>conception</t>
         </is>
       </c>
       <c r="H238" s="3" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="I238" s="3" t="inlineStr"/>
@@ -16743,34 +16751,34 @@
       </c>
       <c r="L238" s="3" t="inlineStr">
         <is>
-          <t>contrepartie_comptable, creation_monetaire, hierarchie_monetaire, monnaie_comme_registre, seuil_d_activation</t>
+          <t>bareme, seuil_d_activation, additionnalite, fenetre_de_reforme</t>
         </is>
       </c>
       <c r="M238" s="3" t="inlineStr">
         <is>
-          <t>L1.C20, L5.C02, L5.C09, L10.C01, L10.C02, L11.C02, L18.C01, L21.C01</t>
+          <t>L1.C27, L7.C17, L7.C20, L11.C24, L20.C01, L20.C06, L20.C09, L20.C13, L20.C19, L20.C20</t>
         </is>
       </c>
       <c r="N238" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-21-plomberie-financiere-mondiale/c01-ce-que-ce-livre-doit-etablir.md</t>
+          <t>corpus/livre-20-droit-international-monetaire-et-commercial/c18-l-amendement-et-la-derogation-dans-l-ordre-commercial.md</t>
         </is>
       </c>
     </row>
     <row r="239">
       <c r="A239" s="2" t="inlineStr">
         <is>
-          <t>L21.C02</t>
+          <t>L20.C19</t>
         </is>
       </c>
       <c r="B239" s="3" t="inlineStr">
         <is>
-          <t>L21</t>
+          <t>L20</t>
         </is>
       </c>
       <c r="C239" s="3" t="inlineStr">
         <is>
-          <t>Comment l'unité circulerait vraiment, et ce que chaque étape exige</t>
+          <t>Le texte que la conformité invoque</t>
         </is>
       </c>
       <c r="D239" s="3" t="inlineStr">
@@ -16790,7 +16798,7 @@
       </c>
       <c r="G239" s="3" t="inlineStr">
         <is>
-          <t>hybride</t>
+          <t>conception</t>
         </is>
       </c>
       <c r="H239" s="3" t="inlineStr">
@@ -16800,41 +16808,41 @@
       </c>
       <c r="I239" s="3" t="inlineStr"/>
       <c r="J239" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K239" s="3" t="n">
         <v>3</v>
       </c>
       <c r="L239" s="3" t="inlineStr">
         <is>
-          <t>monnaie_comme_registre, hierarchie_monetaire, contrepartie_comptable, devise_cle, seuil_d_activation</t>
+          <t>bareme, additionnalite, limites_planetaires, seuil_d_activation, externalisation</t>
         </is>
       </c>
       <c r="M239" s="3" t="inlineStr">
         <is>
-          <t>L1.C24, L3.C05, L3.C09, L5.C02, L5.C09, L10.C01, L11.C02, L21.C01</t>
+          <t>L1.C27, L7.C17, L11.C24, L20.C01, L20.C18, L20.C20, L20.C22</t>
         </is>
       </c>
       <c r="N239" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-21-plomberie-financiere-mondiale/c02-comment-l-unite-circulerait-vraiment.md</t>
+          <t>corpus/livre-20-droit-international-monetaire-et-commercial/c19-le-texte-que-la-conformite-invoque.md</t>
         </is>
       </c>
     </row>
     <row r="240">
       <c r="A240" s="2" t="inlineStr">
         <is>
-          <t>L21.C03</t>
+          <t>L20.C20</t>
         </is>
       </c>
       <c r="B240" s="3" t="inlineStr">
         <is>
-          <t>L21</t>
+          <t>L20</t>
         </is>
       </c>
       <c r="C240" s="3" t="inlineStr">
         <is>
-          <t>Une opération de bout en bout, bilan par bilan</t>
+          <t>L'ajustement aux frontières comme précédent</t>
         </is>
       </c>
       <c r="D240" s="3" t="inlineStr">
@@ -16864,41 +16872,41 @@
       </c>
       <c r="I240" s="3" t="inlineStr"/>
       <c r="J240" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="K240" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="K240" s="3" t="n">
-        <v>4</v>
-      </c>
       <c r="L240" s="3" t="inlineStr">
         <is>
-          <t>contrepartie_comptable, creation_monetaire, reflux_collectif, demurrage, monnaie_comme_registre, hierarchie_monetaire</t>
+          <t>bareme, seuil_d_activation, externalisation, additionnalite, contrepartie_comptable</t>
         </is>
       </c>
       <c r="M240" s="3" t="inlineStr">
         <is>
-          <t>L1.C07, L1.C29, L10.C06, L10.C07, L11.C01, L11.C02, L11.C11, L11.C13, L11.C23, L21.C01, L21.C02</t>
+          <t>L1.C27, L7.C17, L11.C21, L11.C24, L11.C25, L20.C01, L20.C18, L20.C19, L20.C22</t>
         </is>
       </c>
       <c r="N240" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-21-plomberie-financiere-mondiale/c03-une-operation-de-bout-en-bout.md</t>
+          <t>corpus/livre-20-droit-international-monetaire-et-commercial/c20-l-ajustement-aux-frontieres-comme-precedent.md</t>
         </is>
       </c>
     </row>
     <row r="241">
       <c r="A241" s="2" t="inlineStr">
         <is>
-          <t>L21.C04</t>
+          <t>L20.C21</t>
         </is>
       </c>
       <c r="B241" s="3" t="inlineStr">
         <is>
-          <t>L21</t>
+          <t>L20</t>
         </is>
       </c>
       <c r="C241" s="3" t="inlineStr">
         <is>
-          <t>Ce que l'émission coûte aux banques qui l'hébergent</t>
+          <t>La transparence et sa limite juridictionnelle</t>
         </is>
       </c>
       <c r="D241" s="3" t="inlineStr">
@@ -16918,51 +16926,51 @@
       </c>
       <c r="G241" s="3" t="inlineStr">
         <is>
-          <t>descriptif</t>
+          <t>conception</t>
         </is>
       </c>
       <c r="H241" s="3" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="I241" s="3" t="inlineStr"/>
       <c r="J241" s="3" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="K241" s="3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L241" s="3" t="inlineStr">
         <is>
-          <t>contrepartie_comptable, creation_monetaire, hierarchie_monetaire, reflux_collectif, demurrage</t>
+          <t>robustesse, contrepartie_comptable, bareme, monnaie_comme_registre</t>
         </is>
       </c>
       <c r="M241" s="3" t="inlineStr">
         <is>
-          <t>L1.C07, L10.C01, L11.C02, L11.C07, L11.C09, L11.C11, L11.C23, L21.C02, L21.C03</t>
+          <t>L7.C18, L11.C21, L11.C24, L11.C25, L20.C01, L20.C11, L20.C14, L20.C20, L20.C22</t>
         </is>
       </c>
       <c r="N241" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-21-plomberie-financiere-mondiale/c04-ce-que-l-emission-coute-aux-banques-qui-l-hebergent.md</t>
+          <t>corpus/livre-20-droit-international-monetaire-et-commercial/c21-la-transparence-et-sa-limite-juridictionnelle.md</t>
         </is>
       </c>
     </row>
     <row r="242">
       <c r="A242" s="2" t="inlineStr">
         <is>
-          <t>L21.C05</t>
+          <t>L20.C22</t>
         </is>
       </c>
       <c r="B242" s="3" t="inlineStr">
         <is>
-          <t>L21</t>
+          <t>L20</t>
         </is>
       </c>
       <c r="C242" s="3" t="inlineStr">
         <is>
-          <t>La première infrastructure ouverte, et ce qu'elle renverse</t>
+          <t>Ce que le droit devrait devenir</t>
         </is>
       </c>
       <c r="D242" s="3" t="inlineStr">
@@ -16982,12 +16990,12 @@
       </c>
       <c r="G242" s="3" t="inlineStr">
         <is>
-          <t>hybride</t>
+          <t>conception</t>
         </is>
       </c>
       <c r="H242" s="3" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="I242" s="3" t="inlineStr"/>
@@ -16995,38 +17003,38 @@
         <v>3</v>
       </c>
       <c r="K242" s="3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L242" s="3" t="inlineStr">
         <is>
-          <t>seuil_d_activation, hierarchie_monetaire, monnaie_comme_registre, devise_cle, demurrage, contrepartie_comptable</t>
+          <t>fenetre_de_reforme, communs, limites_planetaires, regle_contre_discretion, bareme, referentiel_de_change</t>
         </is>
       </c>
       <c r="M242" s="3" t="inlineStr">
         <is>
-          <t>L3.C09, L5.C02, L5.C09, L11.C01, L11.C02, L11.C07, L21.C01, L21.C02, L21.C03, L21.C04</t>
+          <t>L1.C18, L7.C12, L7.C13, L11.C15, L11.C25, L20.C01, L20.C03, L20.C06, L20.C07, L20.C08, L20.C12, L20.C13, L20.C16, L20.C17, L20.C19, L20.C20, L20.C21, L20.C23</t>
         </is>
       </c>
       <c r="N242" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-21-plomberie-financiere-mondiale/c05-la-premiere-infrastructure-ouverte-et-ce-qu-elle-renverse.md</t>
+          <t>corpus/livre-20-droit-international-monetaire-et-commercial/c22-ce-que-le-droit-devrait-devenir.md</t>
         </is>
       </c>
     </row>
     <row r="243">
       <c r="A243" s="2" t="inlineStr">
         <is>
-          <t>L21.C06</t>
+          <t>L20.C23</t>
         </is>
       </c>
       <c r="B243" s="3" t="inlineStr">
         <is>
-          <t>L21</t>
+          <t>L20</t>
         </is>
       </c>
       <c r="C243" s="3" t="inlineStr">
         <is>
-          <t>La jambe qui reste, et ce qu'il faut pour la protéger</t>
+          <t>La portée du livre</t>
         </is>
       </c>
       <c r="D243" s="3" t="inlineStr">
@@ -17046,41 +17054,41 @@
       </c>
       <c r="G243" s="3" t="inlineStr">
         <is>
-          <t>hybride</t>
+          <t>conception</t>
         </is>
       </c>
       <c r="H243" s="3" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="I243" s="3" t="inlineStr"/>
       <c r="J243" s="3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K243" s="3" t="n">
         <v>4</v>
       </c>
       <c r="L243" s="3" t="inlineStr">
         <is>
-          <t>contrepartie_comptable, hierarchie_monetaire, monnaie_comme_registre, seuil_d_activation</t>
+          <t>fenetre_de_reforme, communs, limites_planetaires, creation_monetaire, robustesse</t>
         </is>
       </c>
       <c r="M243" s="3" t="inlineStr">
         <is>
-          <t>L5.C02, L11.C02, L11.C11, L20.C02, L21.C02, L21.C03, L21.C05</t>
+          <t>L1.C18, L1.C27, L7.C05, L7.C10, L7.C12, L7.C13, L11.C15, L11.C24, L11.C25, L20.C01, L20.C02, L20.C03, L20.C06, L20.C07, L20.C08, L20.C11, L20.C12, L20.C13, L20.C16, L20.C17, L20.C19, L20.C20, L20.C21, L20.C22</t>
         </is>
       </c>
       <c r="N243" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-21-plomberie-financiere-mondiale/c06-la-jambe-qui-reste-et-ce-qu-il-faut-pour-la-proteger.md</t>
+          <t>corpus/livre-20-droit-international-monetaire-et-commercial/c23-la-portee-du-livre.md</t>
         </is>
       </c>
     </row>
     <row r="244">
       <c r="A244" s="2" t="inlineStr">
         <is>
-          <t>L21.C07</t>
+          <t>L21.C01</t>
         </is>
       </c>
       <c r="B244" s="3" t="inlineStr">
@@ -17090,7 +17098,7 @@
       </c>
       <c r="C244" s="3" t="inlineStr">
         <is>
-          <t>Portée de la tranche</t>
+          <t>Ce que ce livre doit établir, et le principe qui exige des fonds propres</t>
         </is>
       </c>
       <c r="D244" s="3" t="inlineStr">
@@ -17110,51 +17118,51 @@
       </c>
       <c r="G244" s="3" t="inlineStr">
         <is>
-          <t>descriptif</t>
+          <t>hybride</t>
         </is>
       </c>
       <c r="H244" s="3" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="I244" s="3" t="inlineStr"/>
       <c r="J244" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K244" s="3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L244" s="3" t="inlineStr">
         <is>
-          <t>seuil_d_activation, contrepartie_comptable, hierarchie_monetaire, monnaie_comme_registre</t>
+          <t>contrepartie_comptable, creation_monetaire, hierarchie_monetaire, monnaie_comme_registre, seuil_d_activation</t>
         </is>
       </c>
       <c r="M244" s="3" t="inlineStr">
         <is>
-          <t>L5.C02, L10.C06, L11.C01, L11.C02, L20.C01, L21.C01, L21.C02, L21.C03, L21.C04, L21.C05, L21.C06</t>
+          <t>L1.C20, L5.C02, L5.C09, L10.C01, L10.C02, L11.C02, L18.C01, L21.C01, L19.C02, L19.C06</t>
         </is>
       </c>
       <c r="N244" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-21-plomberie-financiere-mondiale/c07-portee-de-la-tranche.md</t>
+          <t>corpus/livre-21-plomberie-financiere-mondiale/c01-ce-que-ce-livre-doit-etablir.md</t>
         </is>
       </c>
     </row>
     <row r="245">
       <c r="A245" s="2" t="inlineStr">
         <is>
-          <t>L22.C01</t>
+          <t>L21.C02</t>
         </is>
       </c>
       <c r="B245" s="3" t="inlineStr">
         <is>
-          <t>L22</t>
+          <t>L21</t>
         </is>
       </c>
       <c r="C245" s="3" t="inlineStr">
         <is>
-          <t>Ce que ce livre doit établir</t>
+          <t>Comment l'unité circulerait vraiment, et ce que chaque étape exige</t>
         </is>
       </c>
       <c r="D245" s="3" t="inlineStr">
@@ -17174,7 +17182,7 @@
       </c>
       <c r="G245" s="3" t="inlineStr">
         <is>
-          <t>descriptif</t>
+          <t>hybride</t>
         </is>
       </c>
       <c r="H245" s="3" t="inlineStr">
@@ -17184,41 +17192,41 @@
       </c>
       <c r="I245" s="3" t="inlineStr"/>
       <c r="J245" s="3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K245" s="3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L245" s="3" t="inlineStr">
         <is>
-          <t>architecture_invisible, systeme_monetaire_et_financier, reflux_collectif, reflux_transactionnel, hierarchie_monetaire, monnaie_comme_registre</t>
+          <t>monnaie_comme_registre, hierarchie_monetaire, contrepartie_comptable, devise_cle, seuil_d_activation</t>
         </is>
       </c>
       <c r="M245" s="3" t="inlineStr">
         <is>
-          <t>L1.C09, L1.C19, L5.C09, L11.C02, L11.C05, L11.C09, L11.C27, L21.C03, L21.C04</t>
+          <t>L1.C24, L3.C05, L3.C09, L5.C02, L5.C09, L10.C01, L11.C02, L21.C01</t>
         </is>
       </c>
       <c r="N245" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-22-finance-non-bancaire/c01-ce-que-ce-livre-doit-etablir.md</t>
+          <t>corpus/livre-21-plomberie-financiere-mondiale/c02-comment-l-unite-circulerait-vraiment.md</t>
         </is>
       </c>
     </row>
     <row r="246">
       <c r="A246" s="2" t="inlineStr">
         <is>
-          <t>L22.C02</t>
+          <t>L21.C03</t>
         </is>
       </c>
       <c r="B246" s="3" t="inlineStr">
         <is>
-          <t>L22</t>
+          <t>L21</t>
         </is>
       </c>
       <c r="C246" s="3" t="inlineStr">
         <is>
-          <t>Où va la monnaie émise, et pourquoi le reflux ne l'y suit pas</t>
+          <t>Une opération de bout en bout, bilan par bilan</t>
         </is>
       </c>
       <c r="D246" s="3" t="inlineStr">
@@ -17248,41 +17256,41 @@
       </c>
       <c r="I246" s="3" t="inlineStr"/>
       <c r="J246" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K246" s="3" t="n">
         <v>5</v>
       </c>
       <c r="L246" s="3" t="inlineStr">
         <is>
-          <t>reflux_transactionnel, reflux_collectif, demurrage, monnaie_endogene, architecture_invisible, hierarchie_monetaire</t>
+          <t>contrepartie_comptable, creation_monetaire, reflux_collectif, demurrage, monnaie_comme_registre, hierarchie_monetaire</t>
         </is>
       </c>
       <c r="M246" s="3" t="inlineStr">
         <is>
-          <t>L1.C19, L5.C09, L11.C02, L11.C05, L11.C09, L11.C27, L21.C03, L22.C01, L23.C04, L26.C04</t>
+          <t>L1.C07, L1.C29, L10.C06, L10.C07, L11.C01, L11.C02, L11.C11, L11.C13, L11.C23, L21.C01, L21.C02, L19.C04</t>
         </is>
       </c>
       <c r="N246" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-22-finance-non-bancaire/c02-ou-va-la-monnaie-emise.md</t>
+          <t>corpus/livre-21-plomberie-financiere-mondiale/c03-une-operation-de-bout-en-bout.md</t>
         </is>
       </c>
     </row>
     <row r="247">
       <c r="A247" s="2" t="inlineStr">
         <is>
-          <t>L22.C03</t>
+          <t>L21.C04</t>
         </is>
       </c>
       <c r="B247" s="3" t="inlineStr">
         <is>
-          <t>L22</t>
+          <t>L21</t>
         </is>
       </c>
       <c r="C247" s="3" t="inlineStr">
         <is>
-          <t>Le barème existe déjà, et il a trois pièces que le corpus n'a pas</t>
+          <t>Ce que l'émission coûte aux banques qui l'hébergent</t>
         </is>
       </c>
       <c r="D247" s="3" t="inlineStr">
@@ -17302,7 +17310,7 @@
       </c>
       <c r="G247" s="3" t="inlineStr">
         <is>
-          <t>hybride</t>
+          <t>descriptif</t>
         </is>
       </c>
       <c r="H247" s="3" t="inlineStr">
@@ -17312,41 +17320,41 @@
       </c>
       <c r="I247" s="3" t="inlineStr"/>
       <c r="J247" s="3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K247" s="3" t="n">
         <v>4</v>
       </c>
       <c r="L247" s="3" t="inlineStr">
         <is>
-          <t>qualification_regenerative, bareme, additionnalite, indicateur_de_progres, communs, plafond_ecologique</t>
+          <t>contrepartie_comptable, creation_monetaire, hierarchie_monetaire, reflux_collectif, demurrage</t>
         </is>
       </c>
       <c r="M247" s="3" t="inlineStr">
         <is>
-          <t>L11.C13, L11.C11, L11.C25, L12.C01, L18.C06, L22.C01, L25.C01</t>
+          <t>L1.C07, L10.C01, L11.C02, L11.C07, L11.C09, L11.C11, L11.C23, L21.C02, L21.C03</t>
         </is>
       </c>
       <c r="N247" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-22-finance-non-bancaire/c03-le-bareme-existe-deja.md</t>
+          <t>corpus/livre-21-plomberie-financiere-mondiale/c04-ce-que-l-emission-coute-aux-banques-qui-l-hebergent.md</t>
         </is>
       </c>
     </row>
     <row r="248">
       <c r="A248" s="2" t="inlineStr">
         <is>
-          <t>L22.C04</t>
+          <t>L21.C05</t>
         </is>
       </c>
       <c r="B248" s="3" t="inlineStr">
         <is>
-          <t>L22</t>
+          <t>L21</t>
         </is>
       </c>
       <c r="C248" s="3" t="inlineStr">
         <is>
-          <t>Les critères réels ne mesurent pas, ils certifient</t>
+          <t>La première infrastructure ouverte, et ce qu'elle renverse</t>
         </is>
       </c>
       <c r="D248" s="3" t="inlineStr">
@@ -17376,41 +17384,41 @@
       </c>
       <c r="I248" s="3" t="inlineStr"/>
       <c r="J248" s="3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K248" s="3" t="n">
         <v>4</v>
       </c>
       <c r="L248" s="3" t="inlineStr">
         <is>
-          <t>qualification_regenerative, bareme, additionnalite, communs, valorisation_des_communs, indicateur_de_progres</t>
+          <t>seuil_d_activation, hierarchie_monetaire, monnaie_comme_registre, devise_cle, demurrage, contrepartie_comptable</t>
         </is>
       </c>
       <c r="M248" s="3" t="inlineStr">
         <is>
-          <t>L6.C06, L11.C13, L11.C16, L11.C25, L13.C01, L14.C01, L18.C06, L22.C03</t>
+          <t>L3.C09, L5.C02, L5.C09, L11.C01, L11.C02, L11.C07, L21.C01, L21.C02, L21.C03, L21.C04</t>
         </is>
       </c>
       <c r="N248" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-22-finance-non-bancaire/c04-les-criteres-reels-ne-mesurent-pas.md</t>
+          <t>corpus/livre-21-plomberie-financiere-mondiale/c05-la-premiere-infrastructure-ouverte-et-ce-qu-elle-renverse.md</t>
         </is>
       </c>
     </row>
     <row r="249">
       <c r="A249" s="2" t="inlineStr">
         <is>
-          <t>L22.C05</t>
+          <t>L21.C06</t>
         </is>
       </c>
       <c r="B249" s="3" t="inlineStr">
         <is>
-          <t>L22</t>
+          <t>L21</t>
         </is>
       </c>
       <c r="C249" s="3" t="inlineStr">
         <is>
-          <t>L'épargne retraite, et le dilemme du troisième instrument</t>
+          <t>La jambe qui reste, et ce qu'il faut pour la protéger</t>
         </is>
       </c>
       <c r="D249" s="3" t="inlineStr">
@@ -17447,34 +17455,34 @@
       </c>
       <c r="L249" s="3" t="inlineStr">
         <is>
-          <t>reflux_collectif, demurrage, essentiel_insolvable, plancher_social, solvabilite_anticipee, architecture_invisible</t>
+          <t>contrepartie_comptable, hierarchie_monetaire, monnaie_comme_registre, seuil_d_activation</t>
         </is>
       </c>
       <c r="M249" s="3" t="inlineStr">
         <is>
-          <t>L1.C15, L11.C07, L11.C09, L11.C18, L22.C01, L22.C02, L25.C01</t>
+          <t>L5.C02, L11.C02, L11.C11, L20.C02, L21.C02, L21.C03, L21.C05</t>
         </is>
       </c>
       <c r="N249" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-22-finance-non-bancaire/c05-l-epargne-retraite-et-le-dilemme-du-troisieme-instrument.md</t>
+          <t>corpus/livre-21-plomberie-financiere-mondiale/c06-la-jambe-qui-reste-et-ce-qu-il-faut-pour-la-proteger.md</t>
         </is>
       </c>
     </row>
     <row r="250">
       <c r="A250" s="2" t="inlineStr">
         <is>
-          <t>L22.C06</t>
+          <t>L21.C07</t>
         </is>
       </c>
       <c r="B250" s="3" t="inlineStr">
         <is>
-          <t>L22</t>
+          <t>L21</t>
         </is>
       </c>
       <c r="C250" s="3" t="inlineStr">
         <is>
-          <t>Qui décide, quand personne ne décide</t>
+          <t>Portée de la tranche</t>
         </is>
       </c>
       <c r="D250" s="3" t="inlineStr">
@@ -17494,7 +17502,7 @@
       </c>
       <c r="G250" s="3" t="inlineStr">
         <is>
-          <t>hybride</t>
+          <t>descriptif</t>
         </is>
       </c>
       <c r="H250" s="3" t="inlineStr">
@@ -17504,31 +17512,31 @@
       </c>
       <c r="I250" s="3" t="inlineStr"/>
       <c r="J250" s="3" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K250" s="3" t="n">
         <v>4</v>
       </c>
       <c r="L250" s="3" t="inlineStr">
         <is>
-          <t>architecture_invisible, indicateur_de_progres, qualification_regenerative, essentiel_insolvable, fenetre_de_reforme, regle_contre_discretion</t>
+          <t>seuil_d_activation, contrepartie_comptable, hierarchie_monetaire, monnaie_comme_registre</t>
         </is>
       </c>
       <c r="M250" s="3" t="inlineStr">
         <is>
-          <t>L1.C15, L5.C09, L11.C13, L14.C01, L22.C01, L22.C02, L22.C03, L22.C05</t>
+          <t>L5.C02, L10.C06, L11.C01, L11.C02, L20.C01, L21.C01, L21.C02, L21.C03, L21.C04, L21.C05, L21.C06</t>
         </is>
       </c>
       <c r="N250" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-22-finance-non-bancaire/c06-qui-decide-quand-personne-ne-decide.md</t>
+          <t>corpus/livre-21-plomberie-financiere-mondiale/c07-portee-de-la-tranche.md</t>
         </is>
       </c>
     </row>
     <row r="251">
       <c r="A251" s="2" t="inlineStr">
         <is>
-          <t>L22.C07</t>
+          <t>L22.C01</t>
         </is>
       </c>
       <c r="B251" s="3" t="inlineStr">
@@ -17538,7 +17546,7 @@
       </c>
       <c r="C251" s="3" t="inlineStr">
         <is>
-          <t>Portée de la tranche</t>
+          <t>Ce que ce livre doit établir</t>
         </is>
       </c>
       <c r="D251" s="3" t="inlineStr">
@@ -17568,41 +17576,41 @@
       </c>
       <c r="I251" s="3" t="inlineStr"/>
       <c r="J251" s="3" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K251" s="3" t="n">
         <v>4</v>
       </c>
       <c r="L251" s="3" t="inlineStr">
         <is>
-          <t>architecture_invisible, reflux_transactionnel, qualification_regenerative, bareme, essentiel_insolvable</t>
+          <t>architecture_invisible, systeme_monetaire_et_financier, reflux_collectif, reflux_transactionnel, hierarchie_monetaire, monnaie_comme_registre</t>
         </is>
       </c>
       <c r="M251" s="3" t="inlineStr">
         <is>
-          <t>L1.C15, L5.C09, L11.C02, L11.C13, L11.C18, L22.C01, L22.C02, L22.C03, L22.C04, L22.C05, L22.C06</t>
+          <t>L1.C09, L1.C19, L5.C09, L11.C02, L11.C05, L11.C09, L11.C27, L21.C03, L21.C04</t>
         </is>
       </c>
       <c r="N251" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-22-finance-non-bancaire/c07-portee-de-la-tranche.md</t>
+          <t>corpus/livre-22-finance-non-bancaire/c01-ce-que-ce-livre-doit-etablir.md</t>
         </is>
       </c>
     </row>
     <row r="252">
       <c r="A252" s="2" t="inlineStr">
         <is>
-          <t>L23.C01</t>
+          <t>L22.C02</t>
         </is>
       </c>
       <c r="B252" s="3" t="inlineStr">
         <is>
-          <t>L23</t>
+          <t>L22</t>
         </is>
       </c>
       <c r="C252" s="3" t="inlineStr">
         <is>
-          <t>Ce que ce livre doit établir</t>
+          <t>Où va la monnaie émise, et pourquoi le reflux ne l'y suit pas</t>
         </is>
       </c>
       <c r="D252" s="3" t="inlineStr">
@@ -17627,46 +17635,46 @@
       </c>
       <c r="H252" s="3" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="I252" s="3" t="inlineStr"/>
       <c r="J252" s="3" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K252" s="3" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="L252" s="3" t="inlineStr">
         <is>
-          <t>bareme, reflux_transactionnel, externalisation, essentiel_insolvable, polycentricite, regle_contre_discretion</t>
+          <t>reflux_transactionnel, reflux_collectif, demurrage, monnaie_endogene, architecture_invisible, hierarchie_monetaire</t>
         </is>
       </c>
       <c r="M252" s="3" t="inlineStr">
         <is>
-          <t>L1.C15, L5.C07, L10.C06, L11.C05, L11.C09, L11.C21, L11.C24, L18.C09, L20.C02, L20.C20</t>
+          <t>L1.C19, L5.C09, L11.C02, L11.C05, L11.C09, L11.C27, L21.C03, L22.C01, L23.C04, L26.C04</t>
         </is>
       </c>
       <c r="N252" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-23-fiscalite-mondiale-et-opacite/c01-ce-que-ce-livre-doit-etablir.md</t>
+          <t>corpus/livre-22-finance-non-bancaire/c02-ou-va-la-monnaie-emise.md</t>
         </is>
       </c>
     </row>
     <row r="253">
       <c r="A253" s="2" t="inlineStr">
         <is>
-          <t>L23.C02</t>
+          <t>L22.C03</t>
         </is>
       </c>
       <c r="B253" s="3" t="inlineStr">
         <is>
-          <t>L23</t>
+          <t>L22</t>
         </is>
       </c>
       <c r="C253" s="3" t="inlineStr">
         <is>
-          <t>La compétence que la convention ne crée pas, et le vote qu'elle a gagné</t>
+          <t>Le barème existe déjà, et il a trois pièces que le corpus n'a pas</t>
         </is>
       </c>
       <c r="D253" s="3" t="inlineStr">
@@ -17699,38 +17707,38 @@
         <v>4</v>
       </c>
       <c r="K253" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L253" s="3" t="inlineStr">
         <is>
-          <t>polycentricite, bareme, reflux_transactionnel, seuil_d_activation, regle_contre_discretion, externalisation</t>
+          <t>qualification_regenerative, bareme, additionnalite, indicateur_de_progres, communs, plafond_ecologique</t>
         </is>
       </c>
       <c r="M253" s="3" t="inlineStr">
         <is>
-          <t>L1.C25, L5.C04, L10.C06, L11.C21, L20.C02, L20.C20, L23.C01</t>
+          <t>L11.C13, L11.C11, L11.C25, L12.C01, L18.C06, L22.C01, L25.C01</t>
         </is>
       </c>
       <c r="N253" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-23-fiscalite-mondiale-et-opacite/c02-la-competence-que-la-convention-ne-cree-pas.md</t>
+          <t>corpus/livre-22-finance-non-bancaire/c03-le-bareme-existe-deja.md</t>
         </is>
       </c>
     </row>
     <row r="254">
       <c r="A254" s="2" t="inlineStr">
         <is>
-          <t>L23.C03</t>
+          <t>L22.C04</t>
         </is>
       </c>
       <c r="B254" s="3" t="inlineStr">
         <is>
-          <t>L23</t>
+          <t>L22</t>
         </is>
       </c>
       <c r="C254" s="3" t="inlineStr">
         <is>
-          <t>F8 appliqué à une négociation en cours, et le résultat n'est pas le désarmement</t>
+          <t>Les critères réels ne mesurent pas, ils certifient</t>
         </is>
       </c>
       <c r="D254" s="3" t="inlineStr">
@@ -17763,38 +17771,38 @@
         <v>4</v>
       </c>
       <c r="K254" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L254" s="3" t="inlineStr">
         <is>
-          <t>regle_contre_discretion, polycentricite, seuil_d_activation, bareme, externalisation</t>
+          <t>qualification_regenerative, bareme, additionnalite, communs, valorisation_des_communs, indicateur_de_progres</t>
         </is>
       </c>
       <c r="M254" s="3" t="inlineStr">
         <is>
-          <t>L5.C04, L6.C09, L11.C21, L20.C02, L20.C13, L23.C01, L23.C02</t>
+          <t>L6.C06, L11.C13, L11.C16, L11.C25, L13.C01, L14.C01, L18.C06, L22.C03</t>
         </is>
       </c>
       <c r="N254" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-23-fiscalite-mondiale-et-opacite/c03-f8-applique-a-une-negociation-en-cours.md</t>
+          <t>corpus/livre-22-finance-non-bancaire/c04-les-criteres-reels-ne-mesurent-pas.md</t>
         </is>
       </c>
     </row>
     <row r="255">
       <c r="A255" s="2" t="inlineStr">
         <is>
-          <t>L23.C04</t>
+          <t>L22.C05</t>
         </is>
       </c>
       <c r="B255" s="3" t="inlineStr">
         <is>
-          <t>L23</t>
+          <t>L22</t>
         </is>
       </c>
       <c r="C255" s="3" t="inlineStr">
         <is>
-          <t>La transparence que le corpus supposait a été invalidée</t>
+          <t>L'épargne retraite, et le dilemme du troisième instrument</t>
         </is>
       </c>
       <c r="D255" s="3" t="inlineStr">
@@ -17827,38 +17835,38 @@
         <v>3</v>
       </c>
       <c r="K255" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L255" s="3" t="inlineStr">
         <is>
-          <t>regle_contre_discretion, externalisation, bareme, polycentricite, architecture_invisible</t>
+          <t>reflux_collectif, demurrage, essentiel_insolvable, plancher_social, solvabilite_anticipee, architecture_invisible</t>
         </is>
       </c>
       <c r="M255" s="3" t="inlineStr">
         <is>
-          <t>L6.C09, L11.C13, L11.C25, L20.C20, L23.C01, L23.C02, L23.C03</t>
+          <t>L1.C15, L11.C07, L11.C09, L11.C18, L22.C01, L22.C02, L25.C01</t>
         </is>
       </c>
       <c r="N255" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-23-fiscalite-mondiale-et-opacite/c04-la-transparence-que-le-corpus-supposait-a-ete-invalidee.md</t>
+          <t>corpus/livre-22-finance-non-bancaire/c05-l-epargne-retraite-et-le-dilemme-du-troisieme-instrument.md</t>
         </is>
       </c>
     </row>
     <row r="256">
       <c r="A256" s="2" t="inlineStr">
         <is>
-          <t>L23.C05</t>
+          <t>L22.C06</t>
         </is>
       </c>
       <c r="B256" s="3" t="inlineStr">
         <is>
-          <t>L23</t>
+          <t>L22</t>
         </is>
       </c>
       <c r="C256" s="3" t="inlineStr">
         <is>
-          <t>Intéresser le percepteur, et ce que le taux révèle</t>
+          <t>Qui décide, quand personne ne décide</t>
         </is>
       </c>
       <c r="D256" s="3" t="inlineStr">
@@ -17888,41 +17896,41 @@
       </c>
       <c r="I256" s="3" t="inlineStr"/>
       <c r="J256" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K256" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L256" s="3" t="inlineStr">
         <is>
-          <t>bareme, reflux_transactionnel, regle_contre_discretion, polycentricite, seuil_d_activation</t>
+          <t>architecture_invisible, indicateur_de_progres, qualification_regenerative, essentiel_insolvable, fenetre_de_reforme, regle_contre_discretion</t>
         </is>
       </c>
       <c r="M256" s="3" t="inlineStr">
         <is>
-          <t>L11.C21, L11.C24, L18.C09, L20.C20, L23.C01, L23.C02, L23.C03</t>
+          <t>L1.C15, L5.C09, L11.C13, L14.C01, L22.C01, L22.C02, L22.C03, L22.C05</t>
         </is>
       </c>
       <c r="N256" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-23-fiscalite-mondiale-et-opacite/c05-interesser-le-percepteur-et-ce-que-le-taux-revele.md</t>
+          <t>corpus/livre-22-finance-non-bancaire/c06-qui-decide-quand-personne-ne-decide.md</t>
         </is>
       </c>
     </row>
     <row r="257">
       <c r="A257" s="2" t="inlineStr">
         <is>
-          <t>L23.C06</t>
+          <t>L22.C07</t>
         </is>
       </c>
       <c r="B257" s="3" t="inlineStr">
         <is>
-          <t>L23</t>
+          <t>L22</t>
         </is>
       </c>
       <c r="C257" s="3" t="inlineStr">
         <is>
-          <t>L'arbre appliqué à la fonte, et il ne reste que deux branches</t>
+          <t>Portée de la tranche</t>
         </is>
       </c>
       <c r="D257" s="3" t="inlineStr">
@@ -17942,7 +17950,7 @@
       </c>
       <c r="G257" s="3" t="inlineStr">
         <is>
-          <t>conception</t>
+          <t>descriptif</t>
         </is>
       </c>
       <c r="H257" s="3" t="inlineStr">
@@ -17952,31 +17960,31 @@
       </c>
       <c r="I257" s="3" t="inlineStr"/>
       <c r="J257" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="K257" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="K257" s="3" t="n">
-        <v>3</v>
-      </c>
       <c r="L257" s="3" t="inlineStr">
         <is>
-          <t>bareme, reflux_transactionnel, monnaie_fondante, demurrage, regle_contre_discretion, essentiel_insolvable</t>
+          <t>architecture_invisible, reflux_transactionnel, qualification_regenerative, bareme, essentiel_insolvable</t>
         </is>
       </c>
       <c r="M257" s="3" t="inlineStr">
         <is>
-          <t>L10.C06, L11.C05, L11.C09, L11.C21, L11.C24, L18.C09, L20.C02, L23.C01, L23.C02, L23.C03, L23.C04, L23.C05</t>
+          <t>L1.C15, L5.C09, L11.C02, L11.C13, L11.C18, L22.C01, L22.C02, L22.C03, L22.C04, L22.C05, L22.C06</t>
         </is>
       </c>
       <c r="N257" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-23-fiscalite-mondiale-et-opacite/c06-l-arbre-applique-a-la-fonte.md</t>
+          <t>corpus/livre-22-finance-non-bancaire/c07-portee-de-la-tranche.md</t>
         </is>
       </c>
     </row>
     <row r="258">
       <c r="A258" s="2" t="inlineStr">
         <is>
-          <t>L23.C07</t>
+          <t>L23.C01</t>
         </is>
       </c>
       <c r="B258" s="3" t="inlineStr">
@@ -17986,7 +17994,7 @@
       </c>
       <c r="C258" s="3" t="inlineStr">
         <is>
-          <t>Portée de la tranche, et la moitié qui n'est pas commencée</t>
+          <t>Ce que ce livre doit établir</t>
         </is>
       </c>
       <c r="D258" s="3" t="inlineStr">
@@ -18016,41 +18024,41 @@
       </c>
       <c r="I258" s="3" t="inlineStr"/>
       <c r="J258" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K258" s="3" t="n">
         <v>3</v>
       </c>
       <c r="L258" s="3" t="inlineStr">
         <is>
-          <t>bareme, reflux_transactionnel, externalisation, regle_contre_discretion, polycentricite, essentiel_insolvable</t>
+          <t>bareme, reflux_transactionnel, externalisation, essentiel_insolvable, polycentricite, regle_contre_discretion</t>
         </is>
       </c>
       <c r="M258" s="3" t="inlineStr">
         <is>
-          <t>L10.C06, L11.C05, L11.C21, L11.C25, L18.C09, L20.C20, L23.C01, L23.C02, L23.C03, L23.C04, L23.C05, L23.C06</t>
+          <t>L1.C15, L5.C07, L10.C06, L11.C05, L11.C09, L11.C21, L11.C24, L18.C09, L20.C02, L20.C20</t>
         </is>
       </c>
       <c r="N258" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-23-fiscalite-mondiale-et-opacite/c07-portee-de-la-tranche.md</t>
+          <t>corpus/livre-23-fiscalite-mondiale-et-opacite/c01-ce-que-ce-livre-doit-etablir.md</t>
         </is>
       </c>
     </row>
     <row r="259">
       <c r="A259" s="2" t="inlineStr">
         <is>
-          <t>L24.C01</t>
+          <t>L23.C02</t>
         </is>
       </c>
       <c r="B259" s="3" t="inlineStr">
         <is>
-          <t>L24</t>
+          <t>L23</t>
         </is>
       </c>
       <c r="C259" s="3" t="inlineStr">
         <is>
-          <t>Ce que ce livre doit établir</t>
+          <t>La compétence que la convention ne crée pas, et le vote qu'elle a gagné</t>
         </is>
       </c>
       <c r="D259" s="3" t="inlineStr">
@@ -18070,7 +18078,7 @@
       </c>
       <c r="G259" s="3" t="inlineStr">
         <is>
-          <t>descriptif</t>
+          <t>hybride</t>
         </is>
       </c>
       <c r="H259" s="3" t="inlineStr">
@@ -18083,38 +18091,38 @@
         <v>4</v>
       </c>
       <c r="K259" s="3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L259" s="3" t="inlineStr">
         <is>
-          <t>limites_planetaires, plafond_ecologique, entropie, decouplage, degeneratif, qualification_regenerative, essentiel_insolvable</t>
+          <t>polycentricite, bareme, reflux_transactionnel, seuil_d_activation, regle_contre_discretion, externalisation</t>
         </is>
       </c>
       <c r="M259" s="3" t="inlineStr">
         <is>
-          <t>L1.C15, L5.C08, L11.C13, L18.C01, L18.C04, L22.C04, L26.C01</t>
+          <t>L1.C25, L5.C04, L10.C06, L11.C21, L20.C02, L20.C20, L23.C01</t>
         </is>
       </c>
       <c r="N259" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-24-conditions-materielles-de-la-vie/c01-ce-que-ce-livre-doit-etablir.md</t>
+          <t>corpus/livre-23-fiscalite-mondiale-et-opacite/c02-la-competence-que-la-convention-ne-cree-pas.md</t>
         </is>
       </c>
     </row>
     <row r="260">
       <c r="A260" s="2" t="inlineStr">
         <is>
-          <t>L24.C02</t>
+          <t>L23.C03</t>
         </is>
       </c>
       <c r="B260" s="3" t="inlineStr">
         <is>
-          <t>L24</t>
+          <t>L23</t>
         </is>
       </c>
       <c r="C260" s="3" t="inlineStr">
         <is>
-          <t>Le seuil juste est plus strict que le seuil sûr</t>
+          <t>F8 appliqué à une négociation en cours, et le résultat n'est pas le désarmement</t>
         </is>
       </c>
       <c r="D260" s="3" t="inlineStr">
@@ -18147,38 +18155,38 @@
         <v>4</v>
       </c>
       <c r="K260" s="3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L260" s="3" t="inlineStr">
         <is>
-          <t>limites_planetaires, plafond_ecologique, plancher_social, dette_ecologique, essentiel_insolvable, qualification_regenerative</t>
+          <t>regle_contre_discretion, polycentricite, seuil_d_activation, bareme, externalisation</t>
         </is>
       </c>
       <c r="M260" s="3" t="inlineStr">
         <is>
-          <t>L1.C15, L11.C13, L12.C01, L18.C01, L24.C01, L25.C01</t>
+          <t>L5.C04, L6.C09, L11.C21, L20.C02, L20.C13, L23.C01, L23.C02</t>
         </is>
       </c>
       <c r="N260" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-24-conditions-materielles-de-la-vie/c02-le-seuil-juste-est-plus-strict-que-le-seuil-sur.md</t>
+          <t>corpus/livre-23-fiscalite-mondiale-et-opacite/c03-f8-applique-a-une-negociation-en-cours.md</t>
         </is>
       </c>
     </row>
     <row r="261">
       <c r="A261" s="2" t="inlineStr">
         <is>
-          <t>L24.C03</t>
+          <t>L23.C04</t>
         </is>
       </c>
       <c r="B261" s="3" t="inlineStr">
         <is>
-          <t>L24</t>
+          <t>L23</t>
         </is>
       </c>
       <c r="C261" s="3" t="inlineStr">
         <is>
-          <t>La matière, et le levier commun que les neuf dimensions n'avaient pas</t>
+          <t>La transparence que le corpus supposait a été invalidée</t>
         </is>
       </c>
       <c r="D261" s="3" t="inlineStr">
@@ -18208,41 +18216,41 @@
       </c>
       <c r="I261" s="3" t="inlineStr"/>
       <c r="J261" s="3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K261" s="3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L261" s="3" t="inlineStr">
         <is>
-          <t>limites_planetaires, decouplage, effet_rebond, sobriete, entropie, plafond_ecologique, externalisation, degeneratif</t>
+          <t>regle_contre_discretion, externalisation, bareme, polycentricite, architecture_invisible</t>
         </is>
       </c>
       <c r="M261" s="3" t="inlineStr">
         <is>
-          <t>L1.C15, L11.C13, L17.C01, L18.C04, L24.C01, L24.C02, L26.C01</t>
+          <t>L6.C09, L11.C13, L11.C25, L20.C20, L23.C01, L23.C02, L23.C03</t>
         </is>
       </c>
       <c r="N261" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-24-conditions-materielles-de-la-vie/c03-la-matiere-et-le-levier-commun.md</t>
+          <t>corpus/livre-23-fiscalite-mondiale-et-opacite/c04-la-transparence-que-le-corpus-supposait-a-ete-invalidee.md</t>
         </is>
       </c>
     </row>
     <row r="262">
       <c r="A262" s="2" t="inlineStr">
         <is>
-          <t>L24.C04</t>
+          <t>L23.C05</t>
         </is>
       </c>
       <c r="B262" s="3" t="inlineStr">
         <is>
-          <t>L24</t>
+          <t>L23</t>
         </is>
       </c>
       <c r="C262" s="3" t="inlineStr">
         <is>
-          <t>Un budget mondial n'est pas partageable</t>
+          <t>Intéresser le percepteur, et ce que le taux révèle</t>
         </is>
       </c>
       <c r="D262" s="3" t="inlineStr">
@@ -18272,41 +18280,41 @@
       </c>
       <c r="I262" s="3" t="inlineStr"/>
       <c r="J262" s="3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K262" s="3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L262" s="3" t="inlineStr">
         <is>
-          <t>limites_planetaires, plafond_ecologique, communs, qualification_regenerative, externalisation, polycentricite</t>
+          <t>bareme, reflux_transactionnel, regle_contre_discretion, polycentricite, seuil_d_activation</t>
         </is>
       </c>
       <c r="M262" s="3" t="inlineStr">
         <is>
-          <t>L11.C13, L11.C24, L22.C04, L24.C01, L24.C02, L24.C03, L25.C05</t>
+          <t>L11.C21, L11.C24, L18.C09, L20.C20, L23.C01, L23.C02, L23.C03</t>
         </is>
       </c>
       <c r="N262" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-24-conditions-materielles-de-la-vie/c04-un-budget-mondial-n-est-pas-partageable.md</t>
+          <t>corpus/livre-23-fiscalite-mondiale-et-opacite/c05-interesser-le-percepteur-et-ce-que-le-taux-revele.md</t>
         </is>
       </c>
     </row>
     <row r="263">
       <c r="A263" s="2" t="inlineStr">
         <is>
-          <t>L24.C05</t>
+          <t>L23.C06</t>
         </is>
       </c>
       <c r="B263" s="3" t="inlineStr">
         <is>
-          <t>L24</t>
+          <t>L23</t>
         </is>
       </c>
       <c r="C263" s="3" t="inlineStr">
         <is>
-          <t>Portée de la tranche</t>
+          <t>L'arbre appliqué à la fonte, et il ne reste que deux branches</t>
         </is>
       </c>
       <c r="D263" s="3" t="inlineStr">
@@ -18326,51 +18334,51 @@
       </c>
       <c r="G263" s="3" t="inlineStr">
         <is>
-          <t>descriptif</t>
+          <t>conception</t>
         </is>
       </c>
       <c r="H263" s="3" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="I263" s="3" t="inlineStr"/>
       <c r="J263" s="3" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K263" s="3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L263" s="3" t="inlineStr">
         <is>
-          <t>limites_planetaires, plafond_ecologique, plancher_social, decouplage, qualification_regenerative, entropie</t>
+          <t>bareme, reflux_transactionnel, monnaie_fondante, demurrage, regle_contre_discretion, essentiel_insolvable</t>
         </is>
       </c>
       <c r="M263" s="3" t="inlineStr">
         <is>
-          <t>L11.C13, L11.C24, L18.C01, L22.C04, L24.C01, L24.C02, L24.C03, L24.C04, L25.C05, L26.C01, L26.C02</t>
+          <t>L10.C06, L11.C05, L11.C09, L11.C21, L11.C24, L18.C09, L20.C02, L23.C01, L23.C02, L23.C03, L23.C04, L23.C05</t>
         </is>
       </c>
       <c r="N263" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-24-conditions-materielles-de-la-vie/c05-portee-de-la-tranche.md</t>
+          <t>corpus/livre-23-fiscalite-mondiale-et-opacite/c06-l-arbre-applique-a-la-fonte.md</t>
         </is>
       </c>
     </row>
     <row r="264">
       <c r="A264" s="2" t="inlineStr">
         <is>
-          <t>L25.C01</t>
+          <t>L23.C07</t>
         </is>
       </c>
       <c r="B264" s="3" t="inlineStr">
         <is>
-          <t>L25</t>
+          <t>L23</t>
         </is>
       </c>
       <c r="C264" s="3" t="inlineStr">
         <is>
-          <t>Ce que ce livre doit établir</t>
+          <t>Portée de la tranche, et la moitié qui n'est pas commencée</t>
         </is>
       </c>
       <c r="D264" s="3" t="inlineStr">
@@ -18390,7 +18398,7 @@
       </c>
       <c r="G264" s="3" t="inlineStr">
         <is>
-          <t>descriptif</t>
+          <t>conception</t>
         </is>
       </c>
       <c r="H264" s="3" t="inlineStr">
@@ -18400,41 +18408,41 @@
       </c>
       <c r="I264" s="3" t="inlineStr"/>
       <c r="J264" s="3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K264" s="3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L264" s="3" t="inlineStr">
         <is>
-          <t>plancher_social, plafond_ecologique, essentiel_insolvable, dette_ecologique, communs, solvabilite_anticipee</t>
+          <t>bareme, reflux_transactionnel, externalisation, regle_contre_discretion, polycentricite, essentiel_insolvable</t>
         </is>
       </c>
       <c r="M264" s="3" t="inlineStr">
         <is>
-          <t>L1.C15, L11.C09, L11.C18, L12.C01, L24.C01, L24.C02, L24.C03</t>
+          <t>L10.C06, L11.C05, L11.C21, L11.C25, L18.C09, L20.C20, L23.C01, L23.C02, L23.C03, L23.C04, L23.C05, L23.C06</t>
         </is>
       </c>
       <c r="N264" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-25-repartition-et-justice-sociale/c01-ce-que-ce-livre-doit-etablir.md</t>
+          <t>corpus/livre-23-fiscalite-mondiale-et-opacite/c07-portee-de-la-tranche.md</t>
         </is>
       </c>
     </row>
     <row r="265">
       <c r="A265" s="2" t="inlineStr">
         <is>
-          <t>L25.C02</t>
+          <t>L24.C01</t>
         </is>
       </c>
       <c r="B265" s="3" t="inlineStr">
         <is>
-          <t>L25</t>
+          <t>L24</t>
         </is>
       </c>
       <c r="C265" s="3" t="inlineStr">
         <is>
-          <t>Le noyau dur, et la charge de la preuve renversée</t>
+          <t>Ce que ce livre doit établir</t>
         </is>
       </c>
       <c r="D265" s="3" t="inlineStr">
@@ -18454,7 +18462,7 @@
       </c>
       <c r="G265" s="3" t="inlineStr">
         <is>
-          <t>hybride</t>
+          <t>descriptif</t>
         </is>
       </c>
       <c r="H265" s="3" t="inlineStr">
@@ -18471,34 +18479,34 @@
       </c>
       <c r="L265" s="3" t="inlineStr">
         <is>
-          <t>plancher_social, essentiel_insolvable, plafond_ecologique, solvabilite_anticipee, regle_contre_discretion</t>
+          <t>limites_planetaires, plafond_ecologique, entropie, decouplage, degeneratif, qualification_regenerative, essentiel_insolvable</t>
         </is>
       </c>
       <c r="M265" s="3" t="inlineStr">
         <is>
-          <t>L1.C15, L11.C09, L11.C18, L22.C02, L22.C04, L24.C02, L25.C01</t>
+          <t>L1.C15, L5.C08, L11.C13, L18.C01, L18.C04, L22.C04, L26.C01</t>
         </is>
       </c>
       <c r="N265" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-25-repartition-et-justice-sociale/c02-le-noyau-dur-et-la-charge-de-la-preuve.md</t>
+          <t>corpus/livre-24-conditions-materielles-de-la-vie/c01-ce-que-ce-livre-doit-etablir.md</t>
         </is>
       </c>
     </row>
     <row r="266">
       <c r="A266" s="2" t="inlineStr">
         <is>
-          <t>L25.C03</t>
+          <t>L24.C02</t>
         </is>
       </c>
       <c r="B266" s="3" t="inlineStr">
         <is>
-          <t>L25</t>
+          <t>L24</t>
         </is>
       </c>
       <c r="C266" s="3" t="inlineStr">
         <is>
-          <t>Ce que le droit oblige à donner, et ce qu'il refuse de réparer</t>
+          <t>Le seuil juste est plus strict que le seuil sûr</t>
         </is>
       </c>
       <c r="D266" s="3" t="inlineStr">
@@ -18528,41 +18536,41 @@
       </c>
       <c r="I266" s="3" t="inlineStr"/>
       <c r="J266" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K266" s="3" t="n">
         <v>4</v>
       </c>
       <c r="L266" s="3" t="inlineStr">
         <is>
-          <t>dette_ecologique, plancher_social, creation_monetaire, reflux_collectif, essentiel_insolvable, solvabilite_anticipee</t>
+          <t>limites_planetaires, plafond_ecologique, plancher_social, dette_ecologique, essentiel_insolvable, qualification_regenerative</t>
         </is>
       </c>
       <c r="M266" s="3" t="inlineStr">
         <is>
-          <t>L1.C20, L11.C01, L20.C01, L24.C02, L25.C01, L25.C02</t>
+          <t>L1.C15, L11.C13, L12.C01, L18.C01, L24.C01, L25.C01</t>
         </is>
       </c>
       <c r="N266" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-25-repartition-et-justice-sociale/c03-ce-que-le-droit-oblige-a-donner.md</t>
+          <t>corpus/livre-24-conditions-materielles-de-la-vie/c02-le-seuil-juste-est-plus-strict-que-le-seuil-sur.md</t>
         </is>
       </c>
     </row>
     <row r="267">
       <c r="A267" s="2" t="inlineStr">
         <is>
-          <t>L25.C04</t>
+          <t>L24.C03</t>
         </is>
       </c>
       <c r="B267" s="3" t="inlineStr">
         <is>
-          <t>L25</t>
+          <t>L24</t>
         </is>
       </c>
       <c r="C267" s="3" t="inlineStr">
         <is>
-          <t>A34 en droit positif, et le critère que le corpus n'avait pas</t>
+          <t>La matière, et le levier commun que les neuf dimensions n'avaient pas</t>
         </is>
       </c>
       <c r="D267" s="3" t="inlineStr">
@@ -18599,34 +18607,34 @@
       </c>
       <c r="L267" s="3" t="inlineStr">
         <is>
-          <t>plancher_social, bareme, essentiel_insolvable, sobriete, affectation_des_instruments, reflux_transactionnel</t>
+          <t>limites_planetaires, decouplage, effet_rebond, sobriete, entropie, plafond_ecologique, externalisation, degeneratif</t>
         </is>
       </c>
       <c r="M267" s="3" t="inlineStr">
         <is>
-          <t>L1.C15, L11.C09, L11.C18, L11.C21, L22.C02, L24.C03, L25.C01, L25.C02</t>
+          <t>L1.C15, L11.C13, L17.C01, L18.C04, L24.C01, L24.C02, L26.C01</t>
         </is>
       </c>
       <c r="N267" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-25-repartition-et-justice-sociale/c04-a34-en-droit-positif.md</t>
+          <t>corpus/livre-24-conditions-materielles-de-la-vie/c03-la-matiere-et-le-levier-commun.md</t>
         </is>
       </c>
     </row>
     <row r="268">
       <c r="A268" s="2" t="inlineStr">
         <is>
-          <t>L25.C05</t>
+          <t>L24.C04</t>
         </is>
       </c>
       <c r="B268" s="3" t="inlineStr">
         <is>
-          <t>L25</t>
+          <t>L24</t>
         </is>
       </c>
       <c r="C268" s="3" t="inlineStr">
         <is>
-          <t>Le droit différencie sans calculer</t>
+          <t>Un budget mondial n'est pas partageable</t>
         </is>
       </c>
       <c r="D268" s="3" t="inlineStr">
@@ -18656,36 +18664,36 @@
       </c>
       <c r="I268" s="3" t="inlineStr"/>
       <c r="J268" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K268" s="3" t="n">
         <v>4</v>
       </c>
       <c r="L268" s="3" t="inlineStr">
         <is>
-          <t>dette_ecologique, plancher_social, plafond_ecologique, bareme, indicateur_de_progres, polycentricite</t>
+          <t>limites_planetaires, plafond_ecologique, communs, qualification_regenerative, externalisation, polycentricite</t>
         </is>
       </c>
       <c r="M268" s="3" t="inlineStr">
         <is>
-          <t>L11.C13, L22.C04, L22.C06, L24.C01, L24.C02, L25.C01, L25.C02, L25.C03, L25.C04</t>
+          <t>L11.C13, L11.C24, L22.C04, L24.C01, L24.C02, L24.C03, L25.C05</t>
         </is>
       </c>
       <c r="N268" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-25-repartition-et-justice-sociale/c05-le-droit-differencie-sans-calculer.md</t>
+          <t>corpus/livre-24-conditions-materielles-de-la-vie/c04-un-budget-mondial-n-est-pas-partageable.md</t>
         </is>
       </c>
     </row>
     <row r="269">
       <c r="A269" s="2" t="inlineStr">
         <is>
-          <t>L25.C06</t>
+          <t>L24.C05</t>
         </is>
       </c>
       <c r="B269" s="3" t="inlineStr">
         <is>
-          <t>L25</t>
+          <t>L24</t>
         </is>
       </c>
       <c r="C269" s="3" t="inlineStr">
@@ -18715,7 +18723,7 @@
       </c>
       <c r="H269" s="3" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="I269" s="3" t="inlineStr"/>
@@ -18727,29 +18735,29 @@
       </c>
       <c r="L269" s="3" t="inlineStr">
         <is>
-          <t>plancher_social, plafond_ecologique, dette_ecologique, essentiel_insolvable, bareme</t>
+          <t>limites_planetaires, plafond_ecologique, plancher_social, decouplage, qualification_regenerative, entropie</t>
         </is>
       </c>
       <c r="M269" s="3" t="inlineStr">
         <is>
-          <t>L5.C09, L11.C09, L11.C18, L24.C02, L25.C01, L25.C02, L25.C03, L25.C04, L25.C05</t>
+          <t>L11.C13, L11.C24, L18.C01, L22.C04, L24.C01, L24.C02, L24.C03, L24.C04, L25.C05, L26.C01, L26.C02</t>
         </is>
       </c>
       <c r="N269" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-25-repartition-et-justice-sociale/c06-portee-de-la-tranche.md</t>
+          <t>corpus/livre-24-conditions-materielles-de-la-vie/c05-portee-de-la-tranche.md</t>
         </is>
       </c>
     </row>
     <row r="270">
       <c r="A270" s="2" t="inlineStr">
         <is>
-          <t>L26.C01</t>
+          <t>L25.C01</t>
         </is>
       </c>
       <c r="B270" s="3" t="inlineStr">
         <is>
-          <t>L26</t>
+          <t>L25</t>
         </is>
       </c>
       <c r="C270" s="3" t="inlineStr">
@@ -18774,51 +18782,51 @@
       </c>
       <c r="G270" s="3" t="inlineStr">
         <is>
-          <t>hybride</t>
+          <t>descriptif</t>
         </is>
       </c>
       <c r="H270" s="3" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="I270" s="3" t="inlineStr"/>
       <c r="J270" s="3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K270" s="3" t="n">
         <v>4</v>
       </c>
       <c r="L270" s="3" t="inlineStr">
         <is>
-          <t>entropie, decouplage, effet_rebond, limites_planetaires, sobriete, degeneratif, qualification_regenerative</t>
+          <t>plancher_social, plafond_ecologique, essentiel_insolvable, dette_ecologique, communs, solvabilite_anticipee</t>
         </is>
       </c>
       <c r="M270" s="3" t="inlineStr">
         <is>
-          <t>L1.C03, L1.C15, L1.C17, L8.C13, L8.C34, L11.C13, L18.C04, L24.C03, L24.C05</t>
+          <t>L1.C15, L11.C09, L11.C18, L12.C01, L24.C01, L24.C02, L24.C03</t>
         </is>
       </c>
       <c r="N270" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-26-thermodynamique-et-processus-economique/c01-ce-que-ce-livre-doit-etablir.md</t>
+          <t>corpus/livre-25-repartition-et-justice-sociale/c01-ce-que-ce-livre-doit-etablir.md</t>
         </is>
       </c>
     </row>
     <row r="271">
       <c r="A271" s="2" t="inlineStr">
         <is>
-          <t>L26.C02</t>
+          <t>L25.C02</t>
         </is>
       </c>
       <c r="B271" s="3" t="inlineStr">
         <is>
-          <t>L26</t>
+          <t>L25</t>
         </is>
       </c>
       <c r="C271" s="3" t="inlineStr">
         <is>
-          <t>Le stock n'existe pas sous la forme demandée</t>
+          <t>Le noyau dur, et la charge de la preuve renversée</t>
         </is>
       </c>
       <c r="D271" s="3" t="inlineStr">
@@ -18843,46 +18851,46 @@
       </c>
       <c r="H271" s="3" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="I271" s="3" t="inlineStr"/>
       <c r="J271" s="3" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K271" s="3" t="n">
         <v>4</v>
       </c>
       <c r="L271" s="3" t="inlineStr">
         <is>
-          <t>entropie, bareme, limites_planetaires, decouplage, sobriete, fausse_richesse</t>
+          <t>plancher_social, essentiel_insolvable, plafond_ecologique, solvabilite_anticipee, regle_contre_discretion</t>
         </is>
       </c>
       <c r="M271" s="3" t="inlineStr">
         <is>
-          <t>L1.C15, L11.C13, L11.C24, L18.C04, L22.C04, L24.C03, L24.C05, L26.C01</t>
+          <t>L1.C15, L11.C09, L11.C18, L22.C02, L22.C04, L24.C02, L25.C01</t>
         </is>
       </c>
       <c r="N271" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-26-thermodynamique-et-processus-economique/c02-le-stock-n-existe-pas-sous-la-forme-demandee.md</t>
+          <t>corpus/livre-25-repartition-et-justice-sociale/c02-le-noyau-dur-et-la-charge-de-la-preuve.md</t>
         </is>
       </c>
     </row>
     <row r="272">
       <c r="A272" s="2" t="inlineStr">
         <is>
-          <t>L26.C03</t>
+          <t>L25.C03</t>
         </is>
       </c>
       <c r="B272" s="3" t="inlineStr">
         <is>
-          <t>L26</t>
+          <t>L25</t>
         </is>
       </c>
       <c r="C272" s="3" t="inlineStr">
         <is>
-          <t>La frontière décide du chiffre</t>
+          <t>Ce que le droit oblige à donner, et ce qu'il refuse de réparer</t>
         </is>
       </c>
       <c r="D272" s="3" t="inlineStr">
@@ -18907,46 +18915,46 @@
       </c>
       <c r="H272" s="3" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="I272" s="3" t="inlineStr"/>
       <c r="J272" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K272" s="3" t="n">
         <v>4</v>
       </c>
       <c r="L272" s="3" t="inlineStr">
         <is>
-          <t>entropie, decouplage, sobriete, limites_planetaires, robustesse, bareme</t>
+          <t>dette_ecologique, plancher_social, creation_monetaire, reflux_collectif, essentiel_insolvable, solvabilite_anticipee</t>
         </is>
       </c>
       <c r="M272" s="3" t="inlineStr">
         <is>
-          <t>L11.C10, L11.C13, L11.C24, L18.C04, L18.C09, L24.C03, L24.C04, L26.C01, L26.C02</t>
+          <t>L1.C20, L11.C01, L20.C01, L24.C02, L25.C01, L25.C02</t>
         </is>
       </c>
       <c r="N272" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-26-thermodynamique-et-processus-economique/c03-la-frontiere-decide-du-chiffre.md</t>
+          <t>corpus/livre-25-repartition-et-justice-sociale/c03-ce-que-le-droit-oblige-a-donner.md</t>
         </is>
       </c>
     </row>
     <row r="273">
       <c r="A273" s="2" t="inlineStr">
         <is>
-          <t>L26.C04</t>
+          <t>L25.C04</t>
         </is>
       </c>
       <c r="B273" s="3" t="inlineStr">
         <is>
-          <t>L26</t>
+          <t>L25</t>
         </is>
       </c>
       <c r="C273" s="3" t="inlineStr">
         <is>
-          <t>L'effet rebond, et ce que le dispositif en hérite sans être une politique d'efficacité</t>
+          <t>A34 en droit positif, et le critère que le corpus n'avait pas</t>
         </is>
       </c>
       <c r="D273" s="3" t="inlineStr">
@@ -18971,46 +18979,46 @@
       </c>
       <c r="H273" s="3" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="I273" s="3" t="inlineStr"/>
       <c r="J273" s="3" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K273" s="3" t="n">
         <v>4</v>
       </c>
       <c r="L273" s="3" t="inlineStr">
         <is>
-          <t>effet_rebond, jevons_monetaire, decouplage, sobriete, entropie, reflux_transactionnel</t>
+          <t>plancher_social, bareme, essentiel_insolvable, sobriete, affectation_des_instruments, reflux_transactionnel</t>
         </is>
       </c>
       <c r="M273" s="3" t="inlineStr">
         <is>
-          <t>L1.C03, L1.C12, L1.C17, L11.C10, L13.C01, L18.C04, L22.C02, L24.C03, L26.C01, L26.C03</t>
+          <t>L1.C15, L11.C09, L11.C18, L11.C21, L22.C02, L24.C03, L25.C01, L25.C02</t>
         </is>
       </c>
       <c r="N273" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-26-thermodynamique-et-processus-economique/c04-l-effet-rebond-et-ce-que-le-dispositif-en-herite.md</t>
+          <t>corpus/livre-25-repartition-et-justice-sociale/c04-a34-en-droit-positif.md</t>
         </is>
       </c>
     </row>
     <row r="274">
       <c r="A274" s="2" t="inlineStr">
         <is>
-          <t>L26.C05</t>
+          <t>L25.C05</t>
         </is>
       </c>
       <c r="B274" s="3" t="inlineStr">
         <is>
-          <t>L26</t>
+          <t>L25</t>
         </is>
       </c>
       <c r="C274" s="3" t="inlineStr">
         <is>
-          <t>L'addition n'est pas la substitution</t>
+          <t>Le droit différencie sans calculer</t>
         </is>
       </c>
       <c r="D274" s="3" t="inlineStr">
@@ -19035,41 +19043,41 @@
       </c>
       <c r="H274" s="3" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="I274" s="3" t="inlineStr"/>
       <c r="J274" s="3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K274" s="3" t="n">
         <v>4</v>
       </c>
       <c r="L274" s="3" t="inlineStr">
         <is>
-          <t>decouplage, effet_rebond, sobriete, degeneratif, affectation_des_instruments</t>
+          <t>dette_ecologique, plancher_social, plafond_ecologique, bareme, indicateur_de_progres, polycentricite</t>
         </is>
       </c>
       <c r="M274" s="3" t="inlineStr">
         <is>
-          <t>L1.C12, L11.C10, L11.C13, L18.C04, L18.C09, L22.C02, L24.C03, L26.C01, L26.C03, L26.C04</t>
+          <t>L11.C13, L22.C04, L22.C06, L24.C01, L24.C02, L25.C01, L25.C02, L25.C03, L25.C04</t>
         </is>
       </c>
       <c r="N274" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-26-thermodynamique-et-processus-economique/c05-l-addition-n-est-pas-la-substitution.md</t>
+          <t>corpus/livre-25-repartition-et-justice-sociale/c05-le-droit-differencie-sans-calculer.md</t>
         </is>
       </c>
     </row>
     <row r="275">
       <c r="A275" s="2" t="inlineStr">
         <is>
-          <t>L26.C06</t>
+          <t>L25.C06</t>
         </is>
       </c>
       <c r="B275" s="3" t="inlineStr">
         <is>
-          <t>L26</t>
+          <t>L25</t>
         </is>
       </c>
       <c r="C275" s="3" t="inlineStr">
@@ -19099,7 +19107,7 @@
       </c>
       <c r="H275" s="3" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="I275" s="3" t="inlineStr"/>
@@ -19111,22 +19119,406 @@
       </c>
       <c r="L275" s="3" t="inlineStr">
         <is>
+          <t>plancher_social, plafond_ecologique, dette_ecologique, essentiel_insolvable, bareme</t>
+        </is>
+      </c>
+      <c r="M275" s="3" t="inlineStr">
+        <is>
+          <t>L5.C09, L11.C09, L11.C18, L24.C02, L25.C01, L25.C02, L25.C03, L25.C04, L25.C05</t>
+        </is>
+      </c>
+      <c r="N275" s="3" t="inlineStr">
+        <is>
+          <t>corpus/livre-25-repartition-et-justice-sociale/c06-portee-de-la-tranche.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" s="2" t="inlineStr">
+        <is>
+          <t>L26.C01</t>
+        </is>
+      </c>
+      <c r="B276" s="3" t="inlineStr">
+        <is>
+          <t>L26</t>
+        </is>
+      </c>
+      <c r="C276" s="3" t="inlineStr">
+        <is>
+          <t>Ce que ce livre doit établir</t>
+        </is>
+      </c>
+      <c r="D276" s="3" t="inlineStr">
+        <is>
+          <t>brouillon</t>
+        </is>
+      </c>
+      <c r="E276" s="3" t="inlineStr">
+        <is>
+          <t>preparatoire</t>
+        </is>
+      </c>
+      <c r="F276" s="3" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="G276" s="3" t="inlineStr">
+        <is>
+          <t>hybride</t>
+        </is>
+      </c>
+      <c r="H276" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="I276" s="3" t="inlineStr"/>
+      <c r="J276" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="K276" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="L276" s="3" t="inlineStr">
+        <is>
+          <t>entropie, decouplage, effet_rebond, limites_planetaires, sobriete, degeneratif, qualification_regenerative</t>
+        </is>
+      </c>
+      <c r="M276" s="3" t="inlineStr">
+        <is>
+          <t>L1.C03, L1.C15, L1.C17, L8.C13, L8.C34, L11.C13, L18.C04, L24.C03, L24.C05</t>
+        </is>
+      </c>
+      <c r="N276" s="3" t="inlineStr">
+        <is>
+          <t>corpus/livre-26-thermodynamique-et-processus-economique/c01-ce-que-ce-livre-doit-etablir.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" s="2" t="inlineStr">
+        <is>
+          <t>L26.C02</t>
+        </is>
+      </c>
+      <c r="B277" s="3" t="inlineStr">
+        <is>
+          <t>L26</t>
+        </is>
+      </c>
+      <c r="C277" s="3" t="inlineStr">
+        <is>
+          <t>Le stock n'existe pas sous la forme demandée</t>
+        </is>
+      </c>
+      <c r="D277" s="3" t="inlineStr">
+        <is>
+          <t>brouillon</t>
+        </is>
+      </c>
+      <c r="E277" s="3" t="inlineStr">
+        <is>
+          <t>preparatoire</t>
+        </is>
+      </c>
+      <c r="F277" s="3" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="G277" s="3" t="inlineStr">
+        <is>
+          <t>hybride</t>
+        </is>
+      </c>
+      <c r="H277" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="I277" s="3" t="inlineStr"/>
+      <c r="J277" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="K277" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="L277" s="3" t="inlineStr">
+        <is>
+          <t>entropie, bareme, limites_planetaires, decouplage, sobriete, fausse_richesse</t>
+        </is>
+      </c>
+      <c r="M277" s="3" t="inlineStr">
+        <is>
+          <t>L1.C15, L11.C13, L11.C24, L18.C04, L22.C04, L24.C03, L24.C05, L26.C01</t>
+        </is>
+      </c>
+      <c r="N277" s="3" t="inlineStr">
+        <is>
+          <t>corpus/livre-26-thermodynamique-et-processus-economique/c02-le-stock-n-existe-pas-sous-la-forme-demandee.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" s="2" t="inlineStr">
+        <is>
+          <t>L26.C03</t>
+        </is>
+      </c>
+      <c r="B278" s="3" t="inlineStr">
+        <is>
+          <t>L26</t>
+        </is>
+      </c>
+      <c r="C278" s="3" t="inlineStr">
+        <is>
+          <t>La frontière décide du chiffre</t>
+        </is>
+      </c>
+      <c r="D278" s="3" t="inlineStr">
+        <is>
+          <t>brouillon</t>
+        </is>
+      </c>
+      <c r="E278" s="3" t="inlineStr">
+        <is>
+          <t>preparatoire</t>
+        </is>
+      </c>
+      <c r="F278" s="3" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="G278" s="3" t="inlineStr">
+        <is>
+          <t>hybride</t>
+        </is>
+      </c>
+      <c r="H278" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="I278" s="3" t="inlineStr"/>
+      <c r="J278" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="K278" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="L278" s="3" t="inlineStr">
+        <is>
+          <t>entropie, decouplage, sobriete, limites_planetaires, robustesse, bareme</t>
+        </is>
+      </c>
+      <c r="M278" s="3" t="inlineStr">
+        <is>
+          <t>L11.C10, L11.C13, L11.C24, L18.C04, L18.C09, L24.C03, L24.C04, L26.C01, L26.C02</t>
+        </is>
+      </c>
+      <c r="N278" s="3" t="inlineStr">
+        <is>
+          <t>corpus/livre-26-thermodynamique-et-processus-economique/c03-la-frontiere-decide-du-chiffre.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" s="2" t="inlineStr">
+        <is>
+          <t>L26.C04</t>
+        </is>
+      </c>
+      <c r="B279" s="3" t="inlineStr">
+        <is>
+          <t>L26</t>
+        </is>
+      </c>
+      <c r="C279" s="3" t="inlineStr">
+        <is>
+          <t>L'effet rebond, et ce que le dispositif en hérite sans être une politique d'efficacité</t>
+        </is>
+      </c>
+      <c r="D279" s="3" t="inlineStr">
+        <is>
+          <t>brouillon</t>
+        </is>
+      </c>
+      <c r="E279" s="3" t="inlineStr">
+        <is>
+          <t>preparatoire</t>
+        </is>
+      </c>
+      <c r="F279" s="3" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="G279" s="3" t="inlineStr">
+        <is>
+          <t>hybride</t>
+        </is>
+      </c>
+      <c r="H279" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="I279" s="3" t="inlineStr"/>
+      <c r="J279" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="K279" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="L279" s="3" t="inlineStr">
+        <is>
+          <t>effet_rebond, jevons_monetaire, decouplage, sobriete, entropie, reflux_transactionnel</t>
+        </is>
+      </c>
+      <c r="M279" s="3" t="inlineStr">
+        <is>
+          <t>L1.C03, L1.C12, L1.C17, L11.C10, L13.C01, L18.C04, L22.C02, L24.C03, L26.C01, L26.C03</t>
+        </is>
+      </c>
+      <c r="N279" s="3" t="inlineStr">
+        <is>
+          <t>corpus/livre-26-thermodynamique-et-processus-economique/c04-l-effet-rebond-et-ce-que-le-dispositif-en-herite.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" s="2" t="inlineStr">
+        <is>
+          <t>L26.C05</t>
+        </is>
+      </c>
+      <c r="B280" s="3" t="inlineStr">
+        <is>
+          <t>L26</t>
+        </is>
+      </c>
+      <c r="C280" s="3" t="inlineStr">
+        <is>
+          <t>L'addition n'est pas la substitution</t>
+        </is>
+      </c>
+      <c r="D280" s="3" t="inlineStr">
+        <is>
+          <t>brouillon</t>
+        </is>
+      </c>
+      <c r="E280" s="3" t="inlineStr">
+        <is>
+          <t>preparatoire</t>
+        </is>
+      </c>
+      <c r="F280" s="3" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="G280" s="3" t="inlineStr">
+        <is>
+          <t>hybride</t>
+        </is>
+      </c>
+      <c r="H280" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="I280" s="3" t="inlineStr"/>
+      <c r="J280" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="K280" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="L280" s="3" t="inlineStr">
+        <is>
+          <t>decouplage, effet_rebond, sobriete, degeneratif, affectation_des_instruments</t>
+        </is>
+      </c>
+      <c r="M280" s="3" t="inlineStr">
+        <is>
+          <t>L1.C12, L11.C10, L11.C13, L18.C04, L18.C09, L22.C02, L24.C03, L26.C01, L26.C03, L26.C04</t>
+        </is>
+      </c>
+      <c r="N280" s="3" t="inlineStr">
+        <is>
+          <t>corpus/livre-26-thermodynamique-et-processus-economique/c05-l-addition-n-est-pas-la-substitution.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" s="2" t="inlineStr">
+        <is>
+          <t>L26.C06</t>
+        </is>
+      </c>
+      <c r="B281" s="3" t="inlineStr">
+        <is>
+          <t>L26</t>
+        </is>
+      </c>
+      <c r="C281" s="3" t="inlineStr">
+        <is>
+          <t>Portée de la tranche</t>
+        </is>
+      </c>
+      <c r="D281" s="3" t="inlineStr">
+        <is>
+          <t>brouillon</t>
+        </is>
+      </c>
+      <c r="E281" s="3" t="inlineStr">
+        <is>
+          <t>preparatoire</t>
+        </is>
+      </c>
+      <c r="F281" s="3" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="G281" s="3" t="inlineStr">
+        <is>
+          <t>descriptif</t>
+        </is>
+      </c>
+      <c r="H281" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="I281" s="3" t="inlineStr"/>
+      <c r="J281" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="K281" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="L281" s="3" t="inlineStr">
+        <is>
           <t>entropie, decouplage, effet_rebond, limites_planetaires, sobriete, affectation_des_instruments</t>
         </is>
       </c>
-      <c r="M275" s="3" t="inlineStr">
+      <c r="M281" s="3" t="inlineStr">
         <is>
           <t>L1.C03, L1.C17, L8.C34, L11.C10, L11.C13, L11.C24, L18.C04, L18.C09, L22.C02, L24.C05, L26.C01, L26.C02, L26.C03, L26.C04, L26.C05</t>
         </is>
       </c>
-      <c r="N275" s="3" t="inlineStr">
+      <c r="N281" s="3" t="inlineStr">
         <is>
           <t>corpus/livre-26-thermodynamique-et-processus-economique/c06-portee-de-la-tranche.md</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:N275"/>
+  <autoFilter ref="A1:N281"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -19185,7 +19577,7 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="5">
@@ -19195,7 +19587,7 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="6">
@@ -19205,7 +19597,7 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>274</v>
+        <v>280</v>
       </c>
     </row>
     <row r="7">
@@ -19215,7 +19607,7 @@
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="8">
@@ -19225,7 +19617,7 @@
         </is>
       </c>
       <c r="B8" s="3" t="n">
-        <v>265</v>
+        <v>272</v>
       </c>
     </row>
     <row r="9">
@@ -19235,7 +19627,7 @@
         </is>
       </c>
       <c r="B9" s="3" t="n">
-        <v>265</v>
+        <v>271</v>
       </c>
     </row>
     <row r="10">
@@ -19255,7 +19647,7 @@
         </is>
       </c>
       <c r="B11" s="3" t="n">
-        <v>1309</v>
+        <v>1347</v>
       </c>
     </row>
     <row r="12">
@@ -19265,7 +19657,7 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>1073</v>
+        <v>1083</v>
       </c>
     </row>
     <row r="13">
@@ -19280,7 +19672,7 @@
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>L0, L9, L12, L13, L14, L15, L16, L17, L19</t>
+          <t>L0, L9, L12, L13, L14, L15, L16, L17</t>
         </is>
       </c>
     </row>
@@ -19359,7 +19751,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C302"/>
+  <dimension ref="A1:C308"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -23324,7 +23716,7 @@
       </c>
       <c r="C233" s="6" t="inlineStr">
         <is>
-          <t>reserve — AMORCE SEULE</t>
+          <t>en-cours — 7 chapitre(s)</t>
         </is>
       </c>
     </row>
@@ -23336,7 +23728,7 @@
       </c>
       <c r="B234" s="3" t="inlineStr">
         <is>
-          <t>[AMORCE] Ce que ce livre doit établir</t>
+          <t>Ce que ce livre doit établir</t>
         </is>
       </c>
       <c r="C234" s="3" t="inlineStr">
@@ -23346,31 +23738,31 @@
       </c>
     </row>
     <row r="235">
-      <c r="A235" s="6" t="inlineStr">
-        <is>
-          <t>L20</t>
-        </is>
-      </c>
-      <c r="B235" s="6" t="inlineStr">
-        <is>
-          <t>Droit international public, droit monétaire et commercial de la réforme</t>
-        </is>
-      </c>
-      <c r="C235" s="6" t="inlineStr">
-        <is>
-          <t>en-cours — 23 chapitre(s)</t>
+      <c r="A235" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    L19.C02</t>
+        </is>
+      </c>
+      <c r="B235" s="3" t="inlineStr">
+        <is>
+          <t>Le seul précédent, et le passif lui a été reconnu en 2008</t>
+        </is>
+      </c>
+      <c r="C235" s="3" t="inlineStr">
+        <is>
+          <t>brouillon</t>
         </is>
       </c>
     </row>
     <row r="236">
       <c r="A236" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L20.C01</t>
+          <t xml:space="preserve">    L19.C03</t>
         </is>
       </c>
       <c r="B236" s="3" t="inlineStr">
         <is>
-          <t>Ce que ce livre doit établir</t>
+          <t>Le reflux est un intérêt négatif, ou une répudiation — et c'est le moment qui décide</t>
         </is>
       </c>
       <c r="C236" s="3" t="inlineStr">
@@ -23382,12 +23774,12 @@
     <row r="237">
       <c r="A237" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L20.C02</t>
+          <t xml:space="preserve">    L19.C04</t>
         </is>
       </c>
       <c r="B237" s="3" t="inlineStr">
         <is>
-          <t>L'interdiction du financement monétaire</t>
+          <t>L'actif transitoire n'existe pas, et le problème change de bilan</t>
         </is>
       </c>
       <c r="C237" s="3" t="inlineStr">
@@ -23399,12 +23791,12 @@
     <row r="238">
       <c r="A238" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L20.C03</t>
+          <t xml:space="preserve">    L19.C05</t>
         </is>
       </c>
       <c r="B238" s="3" t="inlineStr">
         <is>
-          <t>L'objectif principal et ce qu'il exclut</t>
+          <t>Un débiteur collectif n'existe pas — sauf comme somme de débiteurs identifiés</t>
         </is>
       </c>
       <c r="C238" s="3" t="inlineStr">
@@ -23416,12 +23808,12 @@
     <row r="239">
       <c r="A239" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L20.C04</t>
+          <t xml:space="preserve">    L19.C06</t>
         </is>
       </c>
       <c r="B239" s="3" t="inlineStr">
         <is>
-          <t>L'indépendance, et à l'égard de qui</t>
+          <t>Les fonds propres négatifs, et l'institution qui n'apparaît dans les comptes de personne</t>
         </is>
       </c>
       <c r="C239" s="3" t="inlineStr">
@@ -23433,12 +23825,12 @@
     <row r="240">
       <c r="A240" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L20.C05</t>
+          <t xml:space="preserve">    L19.C07</t>
         </is>
       </c>
       <c r="B240" s="3" t="inlineStr">
         <is>
-          <t>Le monopole d'émission et le cours légal</t>
+          <t>Portée de la tranche</t>
         </is>
       </c>
       <c r="C240" s="3" t="inlineStr">
@@ -23448,31 +23840,31 @@
       </c>
     </row>
     <row r="241">
-      <c r="A241" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    L20.C06</t>
-        </is>
-      </c>
-      <c r="B241" s="3" t="inlineStr">
-        <is>
-          <t>Les voies de révision et leur coût</t>
-        </is>
-      </c>
-      <c r="C241" s="3" t="inlineStr">
-        <is>
-          <t>brouillon</t>
+      <c r="A241" s="6" t="inlineStr">
+        <is>
+          <t>L20</t>
+        </is>
+      </c>
+      <c r="B241" s="6" t="inlineStr">
+        <is>
+          <t>Droit international public, droit monétaire et commercial de la réforme</t>
+        </is>
+      </c>
+      <c r="C241" s="6" t="inlineStr">
+        <is>
+          <t>en-cours — 23 chapitre(s)</t>
         </is>
       </c>
     </row>
     <row r="242">
       <c r="A242" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L20.C07</t>
+          <t xml:space="preserve">    L20.C01</t>
         </is>
       </c>
       <c r="B242" s="3" t="inlineStr">
         <is>
-          <t>L'accord monétaire international</t>
+          <t>Ce que ce livre doit établir</t>
         </is>
       </c>
       <c r="C242" s="3" t="inlineStr">
@@ -23484,12 +23876,12 @@
     <row r="243">
       <c r="A243" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L20.C08</t>
+          <t xml:space="preserve">    L20.C02</t>
         </is>
       </c>
       <c r="B243" s="3" t="inlineStr">
         <is>
-          <t>La parité inscrite dans le traité</t>
+          <t>L'interdiction du financement monétaire</t>
         </is>
       </c>
       <c r="C243" s="3" t="inlineStr">
@@ -23501,12 +23893,12 @@
     <row r="244">
       <c r="A244" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L20.C09</t>
+          <t xml:space="preserve">    L20.C03</t>
         </is>
       </c>
       <c r="B244" s="3" t="inlineStr">
         <is>
-          <t>L'amendement des statuts du Fonds</t>
+          <t>L'objectif principal et ce qu'il exclut</t>
         </is>
       </c>
       <c r="C244" s="3" t="inlineStr">
@@ -23518,12 +23910,12 @@
     <row r="245">
       <c r="A245" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L20.C10</t>
+          <t xml:space="preserve">    L20.C04</t>
         </is>
       </c>
       <c r="B245" s="3" t="inlineStr">
         <is>
-          <t>Le vote pondéré et les voix de base</t>
+          <t>L'indépendance, et à l'égard de qui</t>
         </is>
       </c>
       <c r="C245" s="3" t="inlineStr">
@@ -23535,12 +23927,12 @@
     <row r="246">
       <c r="A246" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L20.C11</t>
+          <t xml:space="preserve">    L20.C05</t>
         </is>
       </c>
       <c r="B246" s="3" t="inlineStr">
         <is>
-          <t>La personnalité juridique et les immunités</t>
+          <t>Le monopole d'émission et le cours légal</t>
         </is>
       </c>
       <c r="C246" s="3" t="inlineStr">
@@ -23552,12 +23944,12 @@
     <row r="247">
       <c r="A247" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L20.C12</t>
+          <t xml:space="preserve">    L20.C06</t>
         </is>
       </c>
       <c r="B247" s="3" t="inlineStr">
         <is>
-          <t>Les pouvoirs non délégables</t>
+          <t>Les voies de révision et leur coût</t>
         </is>
       </c>
       <c r="C247" s="3" t="inlineStr">
@@ -23569,12 +23961,12 @@
     <row r="248">
       <c r="A248" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L20.C13</t>
+          <t xml:space="preserve">    L20.C07</t>
         </is>
       </c>
       <c r="B248" s="3" t="inlineStr">
         <is>
-          <t>L'entrée en vigueur, l'adhésion et le retrait</t>
+          <t>L'accord monétaire international</t>
         </is>
       </c>
       <c r="C248" s="3" t="inlineStr">
@@ -23586,12 +23978,12 @@
     <row r="249">
       <c r="A249" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L20.C14</t>
+          <t xml:space="preserve">    L20.C08</t>
         </is>
       </c>
       <c r="B249" s="3" t="inlineStr">
         <is>
-          <t>Qui interprète le traité</t>
+          <t>La parité inscrite dans le traité</t>
         </is>
       </c>
       <c r="C249" s="3" t="inlineStr">
@@ -23603,12 +23995,12 @@
     <row r="250">
       <c r="A250" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L20.C15</t>
+          <t xml:space="preserve">    L20.C09</t>
         </is>
       </c>
       <c r="B250" s="3" t="inlineStr">
         <is>
-          <t>Le devoir international des agents</t>
+          <t>L'amendement des statuts du Fonds</t>
         </is>
       </c>
       <c r="C250" s="3" t="inlineStr">
@@ -23620,12 +24012,12 @@
     <row r="251">
       <c r="A251" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L20.C16</t>
+          <t xml:space="preserve">    L20.C10</t>
         </is>
       </c>
       <c r="B251" s="3" t="inlineStr">
         <is>
-          <t>Le patrimoine commun de l'humanité</t>
+          <t>Le vote pondéré et les voix de base</t>
         </is>
       </c>
       <c r="C251" s="3" t="inlineStr">
@@ -23637,12 +24029,12 @@
     <row r="252">
       <c r="A252" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L20.C17</t>
+          <t xml:space="preserve">    L20.C11</t>
         </is>
       </c>
       <c r="B252" s="3" t="inlineStr">
         <is>
-          <t>La sanctuarisation, et elle existe</t>
+          <t>La personnalité juridique et les immunités</t>
         </is>
       </c>
       <c r="C252" s="3" t="inlineStr">
@@ -23654,12 +24046,12 @@
     <row r="253">
       <c r="A253" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L20.C18</t>
+          <t xml:space="preserve">    L20.C12</t>
         </is>
       </c>
       <c r="B253" s="3" t="inlineStr">
         <is>
-          <t>L'amendement et la dérogation dans l'ordre commercial</t>
+          <t>Les pouvoirs non délégables</t>
         </is>
       </c>
       <c r="C253" s="3" t="inlineStr">
@@ -23671,12 +24063,12 @@
     <row r="254">
       <c r="A254" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L20.C19</t>
+          <t xml:space="preserve">    L20.C13</t>
         </is>
       </c>
       <c r="B254" s="3" t="inlineStr">
         <is>
-          <t>Le texte que la conformité invoque</t>
+          <t>L'entrée en vigueur, l'adhésion et le retrait</t>
         </is>
       </c>
       <c r="C254" s="3" t="inlineStr">
@@ -23688,12 +24080,12 @@
     <row r="255">
       <c r="A255" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L20.C20</t>
+          <t xml:space="preserve">    L20.C14</t>
         </is>
       </c>
       <c r="B255" s="3" t="inlineStr">
         <is>
-          <t>L'ajustement aux frontières comme précédent</t>
+          <t>Qui interprète le traité</t>
         </is>
       </c>
       <c r="C255" s="3" t="inlineStr">
@@ -23705,12 +24097,12 @@
     <row r="256">
       <c r="A256" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L20.C21</t>
+          <t xml:space="preserve">    L20.C15</t>
         </is>
       </c>
       <c r="B256" s="3" t="inlineStr">
         <is>
-          <t>La transparence et sa limite juridictionnelle</t>
+          <t>Le devoir international des agents</t>
         </is>
       </c>
       <c r="C256" s="3" t="inlineStr">
@@ -23722,12 +24114,12 @@
     <row r="257">
       <c r="A257" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L20.C22</t>
+          <t xml:space="preserve">    L20.C16</t>
         </is>
       </c>
       <c r="B257" s="3" t="inlineStr">
         <is>
-          <t>Ce que le droit devrait devenir</t>
+          <t>Le patrimoine commun de l'humanité</t>
         </is>
       </c>
       <c r="C257" s="3" t="inlineStr">
@@ -23739,12 +24131,12 @@
     <row r="258">
       <c r="A258" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L20.C23</t>
+          <t xml:space="preserve">    L20.C17</t>
         </is>
       </c>
       <c r="B258" s="3" t="inlineStr">
         <is>
-          <t>La portée du livre</t>
+          <t>La sanctuarisation, et elle existe</t>
         </is>
       </c>
       <c r="C258" s="3" t="inlineStr">
@@ -23754,31 +24146,31 @@
       </c>
     </row>
     <row r="259">
-      <c r="A259" s="6" t="inlineStr">
-        <is>
-          <t>L21</t>
-        </is>
-      </c>
-      <c r="B259" s="6" t="inlineStr">
-        <is>
-          <t>La plomberie financière mondiale</t>
-        </is>
-      </c>
-      <c r="C259" s="6" t="inlineStr">
-        <is>
-          <t>en-cours — 7 chapitre(s)</t>
+      <c r="A259" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    L20.C18</t>
+        </is>
+      </c>
+      <c r="B259" s="3" t="inlineStr">
+        <is>
+          <t>L'amendement et la dérogation dans l'ordre commercial</t>
+        </is>
+      </c>
+      <c r="C259" s="3" t="inlineStr">
+        <is>
+          <t>brouillon</t>
         </is>
       </c>
     </row>
     <row r="260">
       <c r="A260" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L21.C01</t>
+          <t xml:space="preserve">    L20.C19</t>
         </is>
       </c>
       <c r="B260" s="3" t="inlineStr">
         <is>
-          <t>Ce que ce livre doit établir, et le principe qui exige des fonds propres</t>
+          <t>Le texte que la conformité invoque</t>
         </is>
       </c>
       <c r="C260" s="3" t="inlineStr">
@@ -23790,12 +24182,12 @@
     <row r="261">
       <c r="A261" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L21.C02</t>
+          <t xml:space="preserve">    L20.C20</t>
         </is>
       </c>
       <c r="B261" s="3" t="inlineStr">
         <is>
-          <t>Comment l'unité circulerait vraiment, et ce que chaque étape exige</t>
+          <t>L'ajustement aux frontières comme précédent</t>
         </is>
       </c>
       <c r="C261" s="3" t="inlineStr">
@@ -23807,12 +24199,12 @@
     <row r="262">
       <c r="A262" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L21.C03</t>
+          <t xml:space="preserve">    L20.C21</t>
         </is>
       </c>
       <c r="B262" s="3" t="inlineStr">
         <is>
-          <t>Une opération de bout en bout, bilan par bilan</t>
+          <t>La transparence et sa limite juridictionnelle</t>
         </is>
       </c>
       <c r="C262" s="3" t="inlineStr">
@@ -23824,12 +24216,12 @@
     <row r="263">
       <c r="A263" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L21.C04</t>
+          <t xml:space="preserve">    L20.C22</t>
         </is>
       </c>
       <c r="B263" s="3" t="inlineStr">
         <is>
-          <t>Ce que l'émission coûte aux banques qui l'hébergent</t>
+          <t>Ce que le droit devrait devenir</t>
         </is>
       </c>
       <c r="C263" s="3" t="inlineStr">
@@ -23841,12 +24233,12 @@
     <row r="264">
       <c r="A264" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L21.C05</t>
+          <t xml:space="preserve">    L20.C23</t>
         </is>
       </c>
       <c r="B264" s="3" t="inlineStr">
         <is>
-          <t>La première infrastructure ouverte, et ce qu'elle renverse</t>
+          <t>La portée du livre</t>
         </is>
       </c>
       <c r="C264" s="3" t="inlineStr">
@@ -23856,31 +24248,31 @@
       </c>
     </row>
     <row r="265">
-      <c r="A265" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    L21.C06</t>
-        </is>
-      </c>
-      <c r="B265" s="3" t="inlineStr">
-        <is>
-          <t>La jambe qui reste, et ce qu'il faut pour la protéger</t>
-        </is>
-      </c>
-      <c r="C265" s="3" t="inlineStr">
-        <is>
-          <t>brouillon</t>
+      <c r="A265" s="6" t="inlineStr">
+        <is>
+          <t>L21</t>
+        </is>
+      </c>
+      <c r="B265" s="6" t="inlineStr">
+        <is>
+          <t>La plomberie financière mondiale</t>
+        </is>
+      </c>
+      <c r="C265" s="6" t="inlineStr">
+        <is>
+          <t>en-cours — 7 chapitre(s)</t>
         </is>
       </c>
     </row>
     <row r="266">
       <c r="A266" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L21.C07</t>
+          <t xml:space="preserve">    L21.C01</t>
         </is>
       </c>
       <c r="B266" s="3" t="inlineStr">
         <is>
-          <t>Portée de la tranche</t>
+          <t>Ce que ce livre doit établir, et le principe qui exige des fonds propres</t>
         </is>
       </c>
       <c r="C266" s="3" t="inlineStr">
@@ -23890,31 +24282,31 @@
       </c>
     </row>
     <row r="267">
-      <c r="A267" s="6" t="inlineStr">
-        <is>
-          <t>L22</t>
-        </is>
-      </c>
-      <c r="B267" s="6" t="inlineStr">
-        <is>
-          <t>Le pouvoir de la finance non bancaire</t>
-        </is>
-      </c>
-      <c r="C267" s="6" t="inlineStr">
-        <is>
-          <t>en-cours — 7 chapitre(s)</t>
+      <c r="A267" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    L21.C02</t>
+        </is>
+      </c>
+      <c r="B267" s="3" t="inlineStr">
+        <is>
+          <t>Comment l'unité circulerait vraiment, et ce que chaque étape exige</t>
+        </is>
+      </c>
+      <c r="C267" s="3" t="inlineStr">
+        <is>
+          <t>brouillon</t>
         </is>
       </c>
     </row>
     <row r="268">
       <c r="A268" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L22.C01</t>
+          <t xml:space="preserve">    L21.C03</t>
         </is>
       </c>
       <c r="B268" s="3" t="inlineStr">
         <is>
-          <t>Ce que ce livre doit établir</t>
+          <t>Une opération de bout en bout, bilan par bilan</t>
         </is>
       </c>
       <c r="C268" s="3" t="inlineStr">
@@ -23926,12 +24318,12 @@
     <row r="269">
       <c r="A269" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L22.C02</t>
+          <t xml:space="preserve">    L21.C04</t>
         </is>
       </c>
       <c r="B269" s="3" t="inlineStr">
         <is>
-          <t>Où va la monnaie émise, et pourquoi le reflux ne l'y suit pas</t>
+          <t>Ce que l'émission coûte aux banques qui l'hébergent</t>
         </is>
       </c>
       <c r="C269" s="3" t="inlineStr">
@@ -23943,12 +24335,12 @@
     <row r="270">
       <c r="A270" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L22.C03</t>
+          <t xml:space="preserve">    L21.C05</t>
         </is>
       </c>
       <c r="B270" s="3" t="inlineStr">
         <is>
-          <t>Le barème existe déjà, et il a trois pièces que le corpus n'a pas</t>
+          <t>La première infrastructure ouverte, et ce qu'elle renverse</t>
         </is>
       </c>
       <c r="C270" s="3" t="inlineStr">
@@ -23960,12 +24352,12 @@
     <row r="271">
       <c r="A271" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L22.C04</t>
+          <t xml:space="preserve">    L21.C06</t>
         </is>
       </c>
       <c r="B271" s="3" t="inlineStr">
         <is>
-          <t>Les critères réels ne mesurent pas, ils certifient</t>
+          <t>La jambe qui reste, et ce qu'il faut pour la protéger</t>
         </is>
       </c>
       <c r="C271" s="3" t="inlineStr">
@@ -23977,12 +24369,12 @@
     <row r="272">
       <c r="A272" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L22.C05</t>
+          <t xml:space="preserve">    L21.C07</t>
         </is>
       </c>
       <c r="B272" s="3" t="inlineStr">
         <is>
-          <t>L'épargne retraite, et le dilemme du troisième instrument</t>
+          <t>Portée de la tranche</t>
         </is>
       </c>
       <c r="C272" s="3" t="inlineStr">
@@ -23992,31 +24384,31 @@
       </c>
     </row>
     <row r="273">
-      <c r="A273" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    L22.C06</t>
-        </is>
-      </c>
-      <c r="B273" s="3" t="inlineStr">
-        <is>
-          <t>Qui décide, quand personne ne décide</t>
-        </is>
-      </c>
-      <c r="C273" s="3" t="inlineStr">
-        <is>
-          <t>brouillon</t>
+      <c r="A273" s="6" t="inlineStr">
+        <is>
+          <t>L22</t>
+        </is>
+      </c>
+      <c r="B273" s="6" t="inlineStr">
+        <is>
+          <t>Le pouvoir de la finance non bancaire</t>
+        </is>
+      </c>
+      <c r="C273" s="6" t="inlineStr">
+        <is>
+          <t>en-cours — 7 chapitre(s)</t>
         </is>
       </c>
     </row>
     <row r="274">
       <c r="A274" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L22.C07</t>
+          <t xml:space="preserve">    L22.C01</t>
         </is>
       </c>
       <c r="B274" s="3" t="inlineStr">
         <is>
-          <t>Portée de la tranche</t>
+          <t>Ce que ce livre doit établir</t>
         </is>
       </c>
       <c r="C274" s="3" t="inlineStr">
@@ -24026,31 +24418,31 @@
       </c>
     </row>
     <row r="275">
-      <c r="A275" s="6" t="inlineStr">
-        <is>
-          <t>L23</t>
-        </is>
-      </c>
-      <c r="B275" s="6" t="inlineStr">
-        <is>
-          <t>Fiscalité mondiale, finance offshore et opacité</t>
-        </is>
-      </c>
-      <c r="C275" s="6" t="inlineStr">
-        <is>
-          <t>en-cours — 7 chapitre(s)</t>
+      <c r="A275" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    L22.C02</t>
+        </is>
+      </c>
+      <c r="B275" s="3" t="inlineStr">
+        <is>
+          <t>Où va la monnaie émise, et pourquoi le reflux ne l'y suit pas</t>
+        </is>
+      </c>
+      <c r="C275" s="3" t="inlineStr">
+        <is>
+          <t>brouillon</t>
         </is>
       </c>
     </row>
     <row r="276">
       <c r="A276" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L23.C01</t>
+          <t xml:space="preserve">    L22.C03</t>
         </is>
       </c>
       <c r="B276" s="3" t="inlineStr">
         <is>
-          <t>Ce que ce livre doit établir</t>
+          <t>Le barème existe déjà, et il a trois pièces que le corpus n'a pas</t>
         </is>
       </c>
       <c r="C276" s="3" t="inlineStr">
@@ -24062,12 +24454,12 @@
     <row r="277">
       <c r="A277" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L23.C02</t>
+          <t xml:space="preserve">    L22.C04</t>
         </is>
       </c>
       <c r="B277" s="3" t="inlineStr">
         <is>
-          <t>La compétence que la convention ne crée pas, et le vote qu'elle a gagné</t>
+          <t>Les critères réels ne mesurent pas, ils certifient</t>
         </is>
       </c>
       <c r="C277" s="3" t="inlineStr">
@@ -24079,12 +24471,12 @@
     <row r="278">
       <c r="A278" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L23.C03</t>
+          <t xml:space="preserve">    L22.C05</t>
         </is>
       </c>
       <c r="B278" s="3" t="inlineStr">
         <is>
-          <t>F8 appliqué à une négociation en cours, et le résultat n'est pas le désarmement</t>
+          <t>L'épargne retraite, et le dilemme du troisième instrument</t>
         </is>
       </c>
       <c r="C278" s="3" t="inlineStr">
@@ -24096,12 +24488,12 @@
     <row r="279">
       <c r="A279" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L23.C04</t>
+          <t xml:space="preserve">    L22.C06</t>
         </is>
       </c>
       <c r="B279" s="3" t="inlineStr">
         <is>
-          <t>La transparence que le corpus supposait a été invalidée</t>
+          <t>Qui décide, quand personne ne décide</t>
         </is>
       </c>
       <c r="C279" s="3" t="inlineStr">
@@ -24113,12 +24505,12 @@
     <row r="280">
       <c r="A280" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L23.C05</t>
+          <t xml:space="preserve">    L22.C07</t>
         </is>
       </c>
       <c r="B280" s="3" t="inlineStr">
         <is>
-          <t>Intéresser le percepteur, et ce que le taux révèle</t>
+          <t>Portée de la tranche</t>
         </is>
       </c>
       <c r="C280" s="3" t="inlineStr">
@@ -24128,31 +24520,31 @@
       </c>
     </row>
     <row r="281">
-      <c r="A281" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    L23.C06</t>
-        </is>
-      </c>
-      <c r="B281" s="3" t="inlineStr">
-        <is>
-          <t>L'arbre appliqué à la fonte, et il ne reste que deux branches</t>
-        </is>
-      </c>
-      <c r="C281" s="3" t="inlineStr">
-        <is>
-          <t>brouillon</t>
+      <c r="A281" s="6" t="inlineStr">
+        <is>
+          <t>L23</t>
+        </is>
+      </c>
+      <c r="B281" s="6" t="inlineStr">
+        <is>
+          <t>Fiscalité mondiale, finance offshore et opacité</t>
+        </is>
+      </c>
+      <c r="C281" s="6" t="inlineStr">
+        <is>
+          <t>en-cours — 7 chapitre(s)</t>
         </is>
       </c>
     </row>
     <row r="282">
       <c r="A282" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L23.C07</t>
+          <t xml:space="preserve">    L23.C01</t>
         </is>
       </c>
       <c r="B282" s="3" t="inlineStr">
         <is>
-          <t>Portée de la tranche, et la moitié qui n'est pas commencée</t>
+          <t>Ce que ce livre doit établir</t>
         </is>
       </c>
       <c r="C282" s="3" t="inlineStr">
@@ -24162,31 +24554,31 @@
       </c>
     </row>
     <row r="283">
-      <c r="A283" s="6" t="inlineStr">
-        <is>
-          <t>L24</t>
-        </is>
-      </c>
-      <c r="B283" s="6" t="inlineStr">
-        <is>
-          <t>Les conditions matérielles de la vie</t>
-        </is>
-      </c>
-      <c r="C283" s="6" t="inlineStr">
-        <is>
-          <t>en-cours — 5 chapitre(s)</t>
+      <c r="A283" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    L23.C02</t>
+        </is>
+      </c>
+      <c r="B283" s="3" t="inlineStr">
+        <is>
+          <t>La compétence que la convention ne crée pas, et le vote qu'elle a gagné</t>
+        </is>
+      </c>
+      <c r="C283" s="3" t="inlineStr">
+        <is>
+          <t>brouillon</t>
         </is>
       </c>
     </row>
     <row r="284">
       <c r="A284" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L24.C01</t>
+          <t xml:space="preserve">    L23.C03</t>
         </is>
       </c>
       <c r="B284" s="3" t="inlineStr">
         <is>
-          <t>Ce que ce livre doit établir</t>
+          <t>F8 appliqué à une négociation en cours, et le résultat n'est pas le désarmement</t>
         </is>
       </c>
       <c r="C284" s="3" t="inlineStr">
@@ -24198,12 +24590,12 @@
     <row r="285">
       <c r="A285" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L24.C02</t>
+          <t xml:space="preserve">    L23.C04</t>
         </is>
       </c>
       <c r="B285" s="3" t="inlineStr">
         <is>
-          <t>Le seuil juste est plus strict que le seuil sûr</t>
+          <t>La transparence que le corpus supposait a été invalidée</t>
         </is>
       </c>
       <c r="C285" s="3" t="inlineStr">
@@ -24215,12 +24607,12 @@
     <row r="286">
       <c r="A286" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L24.C03</t>
+          <t xml:space="preserve">    L23.C05</t>
         </is>
       </c>
       <c r="B286" s="3" t="inlineStr">
         <is>
-          <t>La matière, et le levier commun que les neuf dimensions n'avaient pas</t>
+          <t>Intéresser le percepteur, et ce que le taux révèle</t>
         </is>
       </c>
       <c r="C286" s="3" t="inlineStr">
@@ -24232,12 +24624,12 @@
     <row r="287">
       <c r="A287" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L24.C04</t>
+          <t xml:space="preserve">    L23.C06</t>
         </is>
       </c>
       <c r="B287" s="3" t="inlineStr">
         <is>
-          <t>Un budget mondial n'est pas partageable</t>
+          <t>L'arbre appliqué à la fonte, et il ne reste que deux branches</t>
         </is>
       </c>
       <c r="C287" s="3" t="inlineStr">
@@ -24249,12 +24641,12 @@
     <row r="288">
       <c r="A288" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L24.C05</t>
+          <t xml:space="preserve">    L23.C07</t>
         </is>
       </c>
       <c r="B288" s="3" t="inlineStr">
         <is>
-          <t>Portée de la tranche</t>
+          <t>Portée de la tranche, et la moitié qui n'est pas commencée</t>
         </is>
       </c>
       <c r="C288" s="3" t="inlineStr">
@@ -24266,24 +24658,24 @@
     <row r="289">
       <c r="A289" s="6" t="inlineStr">
         <is>
-          <t>L25</t>
+          <t>L24</t>
         </is>
       </c>
       <c r="B289" s="6" t="inlineStr">
         <is>
-          <t>Répartition, besoins essentiels et justice sociale</t>
+          <t>Les conditions matérielles de la vie</t>
         </is>
       </c>
       <c r="C289" s="6" t="inlineStr">
         <is>
-          <t>en-cours — 6 chapitre(s)</t>
+          <t>en-cours — 5 chapitre(s)</t>
         </is>
       </c>
     </row>
     <row r="290">
       <c r="A290" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L25.C01</t>
+          <t xml:space="preserve">    L24.C01</t>
         </is>
       </c>
       <c r="B290" s="3" t="inlineStr">
@@ -24300,12 +24692,12 @@
     <row r="291">
       <c r="A291" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L25.C02</t>
+          <t xml:space="preserve">    L24.C02</t>
         </is>
       </c>
       <c r="B291" s="3" t="inlineStr">
         <is>
-          <t>Le noyau dur, et la charge de la preuve renversée</t>
+          <t>Le seuil juste est plus strict que le seuil sûr</t>
         </is>
       </c>
       <c r="C291" s="3" t="inlineStr">
@@ -24317,12 +24709,12 @@
     <row r="292">
       <c r="A292" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L25.C03</t>
+          <t xml:space="preserve">    L24.C03</t>
         </is>
       </c>
       <c r="B292" s="3" t="inlineStr">
         <is>
-          <t>Ce que le droit oblige à donner, et ce qu'il refuse de réparer</t>
+          <t>La matière, et le levier commun que les neuf dimensions n'avaient pas</t>
         </is>
       </c>
       <c r="C292" s="3" t="inlineStr">
@@ -24334,12 +24726,12 @@
     <row r="293">
       <c r="A293" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L25.C04</t>
+          <t xml:space="preserve">    L24.C04</t>
         </is>
       </c>
       <c r="B293" s="3" t="inlineStr">
         <is>
-          <t>A34 en droit positif, et le critère que le corpus n'avait pas</t>
+          <t>Un budget mondial n'est pas partageable</t>
         </is>
       </c>
       <c r="C293" s="3" t="inlineStr">
@@ -24351,12 +24743,12 @@
     <row r="294">
       <c r="A294" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L25.C05</t>
+          <t xml:space="preserve">    L24.C05</t>
         </is>
       </c>
       <c r="B294" s="3" t="inlineStr">
         <is>
-          <t>Le droit différencie sans calculer</t>
+          <t>Portée de la tranche</t>
         </is>
       </c>
       <c r="C294" s="3" t="inlineStr">
@@ -24366,48 +24758,48 @@
       </c>
     </row>
     <row r="295">
-      <c r="A295" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    L25.C06</t>
-        </is>
-      </c>
-      <c r="B295" s="3" t="inlineStr">
-        <is>
-          <t>Portée de la tranche</t>
-        </is>
-      </c>
-      <c r="C295" s="3" t="inlineStr">
-        <is>
-          <t>brouillon</t>
+      <c r="A295" s="6" t="inlineStr">
+        <is>
+          <t>L25</t>
+        </is>
+      </c>
+      <c r="B295" s="6" t="inlineStr">
+        <is>
+          <t>Répartition, besoins essentiels et justice sociale</t>
+        </is>
+      </c>
+      <c r="C295" s="6" t="inlineStr">
+        <is>
+          <t>en-cours — 6 chapitre(s)</t>
         </is>
       </c>
     </row>
     <row r="296">
-      <c r="A296" s="6" t="inlineStr">
-        <is>
-          <t>L26</t>
-        </is>
-      </c>
-      <c r="B296" s="6" t="inlineStr">
-        <is>
-          <t>Thermodynamique, énergie et processus économique</t>
-        </is>
-      </c>
-      <c r="C296" s="6" t="inlineStr">
-        <is>
-          <t>en-cours — 6 chapitre(s)</t>
+      <c r="A296" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    L25.C01</t>
+        </is>
+      </c>
+      <c r="B296" s="3" t="inlineStr">
+        <is>
+          <t>Ce que ce livre doit établir</t>
+        </is>
+      </c>
+      <c r="C296" s="3" t="inlineStr">
+        <is>
+          <t>brouillon</t>
         </is>
       </c>
     </row>
     <row r="297">
       <c r="A297" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L26.C01</t>
+          <t xml:space="preserve">    L25.C02</t>
         </is>
       </c>
       <c r="B297" s="3" t="inlineStr">
         <is>
-          <t>Ce que ce livre doit établir</t>
+          <t>Le noyau dur, et la charge de la preuve renversée</t>
         </is>
       </c>
       <c r="C297" s="3" t="inlineStr">
@@ -24419,12 +24811,12 @@
     <row r="298">
       <c r="A298" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L26.C02</t>
+          <t xml:space="preserve">    L25.C03</t>
         </is>
       </c>
       <c r="B298" s="3" t="inlineStr">
         <is>
-          <t>Le stock n'existe pas sous la forme demandée</t>
+          <t>Ce que le droit oblige à donner, et ce qu'il refuse de réparer</t>
         </is>
       </c>
       <c r="C298" s="3" t="inlineStr">
@@ -24436,12 +24828,12 @@
     <row r="299">
       <c r="A299" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L26.C03</t>
+          <t xml:space="preserve">    L25.C04</t>
         </is>
       </c>
       <c r="B299" s="3" t="inlineStr">
         <is>
-          <t>La frontière décide du chiffre</t>
+          <t>A34 en droit positif, et le critère que le corpus n'avait pas</t>
         </is>
       </c>
       <c r="C299" s="3" t="inlineStr">
@@ -24453,12 +24845,12 @@
     <row r="300">
       <c r="A300" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L26.C04</t>
+          <t xml:space="preserve">    L25.C05</t>
         </is>
       </c>
       <c r="B300" s="3" t="inlineStr">
         <is>
-          <t>L'effet rebond, et ce que le dispositif en hérite sans être une politique d'efficacité</t>
+          <t>Le droit différencie sans calculer</t>
         </is>
       </c>
       <c r="C300" s="3" t="inlineStr">
@@ -24470,32 +24862,134 @@
     <row r="301">
       <c r="A301" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">    L25.C06</t>
+        </is>
+      </c>
+      <c r="B301" s="3" t="inlineStr">
+        <is>
+          <t>Portée de la tranche</t>
+        </is>
+      </c>
+      <c r="C301" s="3" t="inlineStr">
+        <is>
+          <t>brouillon</t>
+        </is>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" s="6" t="inlineStr">
+        <is>
+          <t>L26</t>
+        </is>
+      </c>
+      <c r="B302" s="6" t="inlineStr">
+        <is>
+          <t>Thermodynamique, énergie et processus économique</t>
+        </is>
+      </c>
+      <c r="C302" s="6" t="inlineStr">
+        <is>
+          <t>en-cours — 6 chapitre(s)</t>
+        </is>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    L26.C01</t>
+        </is>
+      </c>
+      <c r="B303" s="3" t="inlineStr">
+        <is>
+          <t>Ce que ce livre doit établir</t>
+        </is>
+      </c>
+      <c r="C303" s="3" t="inlineStr">
+        <is>
+          <t>brouillon</t>
+        </is>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    L26.C02</t>
+        </is>
+      </c>
+      <c r="B304" s="3" t="inlineStr">
+        <is>
+          <t>Le stock n'existe pas sous la forme demandée</t>
+        </is>
+      </c>
+      <c r="C304" s="3" t="inlineStr">
+        <is>
+          <t>brouillon</t>
+        </is>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    L26.C03</t>
+        </is>
+      </c>
+      <c r="B305" s="3" t="inlineStr">
+        <is>
+          <t>La frontière décide du chiffre</t>
+        </is>
+      </c>
+      <c r="C305" s="3" t="inlineStr">
+        <is>
+          <t>brouillon</t>
+        </is>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    L26.C04</t>
+        </is>
+      </c>
+      <c r="B306" s="3" t="inlineStr">
+        <is>
+          <t>L'effet rebond, et ce que le dispositif en hérite sans être une politique d'efficacité</t>
+        </is>
+      </c>
+      <c r="C306" s="3" t="inlineStr">
+        <is>
+          <t>brouillon</t>
+        </is>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">    L26.C05</t>
         </is>
       </c>
-      <c r="B301" s="3" t="inlineStr">
+      <c r="B307" s="3" t="inlineStr">
         <is>
           <t>L'addition n'est pas la substitution</t>
         </is>
       </c>
-      <c r="C301" s="3" t="inlineStr">
-        <is>
-          <t>brouillon</t>
-        </is>
-      </c>
-    </row>
-    <row r="302">
-      <c r="A302" s="3" t="inlineStr">
+      <c r="C307" s="3" t="inlineStr">
+        <is>
+          <t>brouillon</t>
+        </is>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">    L26.C06</t>
         </is>
       </c>
-      <c r="B302" s="3" t="inlineStr">
+      <c r="B308" s="3" t="inlineStr">
         <is>
           <t>Portée de la tranche</t>
         </is>
       </c>
-      <c r="C302" s="3" t="inlineStr">
+      <c r="C308" s="3" t="inlineStr">
         <is>
           <t>brouillon</t>
         </is>

--- a/plan-des-livres.xlsx
+++ b/plan-des-livres.xlsx
@@ -13,7 +13,7 @@
     <sheet name="Plan par livre" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Chapitres'!$A$1:$N$281</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Chapitres'!$A$1:$N$286</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -1218,41 +1218,41 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="2" t="inlineStr">
+      <c r="A19" s="4" t="inlineStr">
         <is>
           <t>L17</t>
         </is>
       </c>
-      <c r="B19" s="3" t="inlineStr">
+      <c r="B19" s="5" t="inlineStr">
         <is>
           <t>Après la croissance : décroissance, post-croissance et prospérité sans croissance</t>
         </is>
       </c>
-      <c r="C19" s="3" t="inlineStr">
+      <c r="C19" s="5" t="inlineStr">
         <is>
           <t>cahier-comparatif</t>
         </is>
       </c>
-      <c r="D19" s="3" t="inlineStr">
-        <is>
-          <t>candidat</t>
-        </is>
-      </c>
-      <c r="E19" s="3" t="inlineStr">
+      <c r="D19" s="5" t="inlineStr">
+        <is>
+          <t>en-cours</t>
+        </is>
+      </c>
+      <c r="E19" s="5" t="inlineStr">
         <is>
           <t>non contraignant</t>
         </is>
       </c>
-      <c r="F19" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G19" s="3" t="inlineStr"/>
-      <c r="H19" s="3" t="inlineStr">
+      <c r="F19" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="G19" s="5" t="inlineStr"/>
+      <c r="H19" s="5" t="inlineStr">
         <is>
           <t>Comparer les théories et expériences de l'après-croissance, du Bonheur national brut à la décroissance, puis tester leur concrétisation institutionnelle</t>
         </is>
       </c>
-      <c r="I19" s="3" t="inlineStr">
+      <c r="I19" s="5" t="inlineStr">
         <is>
           <t>discipline — théories de l'après-croissance et indicateurs au-delà du PIB | objection — P9 : sortir de l'exigence de croissance de l'encours sans contraction</t>
         </is>
@@ -1638,7 +1638,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N281"/>
+  <dimension ref="A1:N286"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -13111,7 +13111,7 @@
       </c>
       <c r="H181" s="3" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="I181" s="3" t="inlineStr"/>
@@ -13119,7 +13119,7 @@
         <v>5</v>
       </c>
       <c r="K181" s="3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L181" s="3" t="inlineStr">
         <is>
@@ -13128,7 +13128,7 @@
       </c>
       <c r="M181" s="3" t="inlineStr">
         <is>
-          <t>L1.C21, L11.C03, L11.C05, L11.C06, L11.C09, L11.C10, L11.C11</t>
+          <t>L1.C21, L11.C03, L11.C05, L11.C06, L11.C09, L11.C10, L11.C11, L17.C04</t>
         </is>
       </c>
       <c r="N181" s="3" t="inlineStr">
@@ -13887,7 +13887,7 @@
         <v>3</v>
       </c>
       <c r="K193" s="3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L193" s="3" t="inlineStr">
         <is>
@@ -13896,7 +13896,7 @@
       </c>
       <c r="M193" s="3" t="inlineStr">
         <is>
-          <t>L1.C26, L1.C27, L11.C04, L11.C05, L11.C06, L11.C09, L11.C13, L11.C16, L11.C17, L11.C19, L11.C21, L26.C03</t>
+          <t>L1.C26, L1.C27, L11.C04, L11.C05, L11.C06, L11.C09, L11.C13, L11.C16, L11.C17, L11.C19, L11.C21, L26.C03, L17.C05</t>
         </is>
       </c>
       <c r="N193" s="3" t="inlineStr">
@@ -14562,27 +14562,31 @@
       </c>
       <c r="G204" s="3" t="inlineStr">
         <is>
-          <t>descriptif</t>
+          <t>hybride</t>
         </is>
       </c>
       <c r="H204" s="3" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="I204" s="3" t="inlineStr">
-        <is>
-          <t>oui</t>
-        </is>
-      </c>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="I204" s="3" t="inlineStr"/>
       <c r="J204" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K204" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="L204" s="3" t="inlineStr"/>
-      <c r="M204" s="3" t="inlineStr"/>
+        <v>5</v>
+      </c>
+      <c r="L204" s="3" t="inlineStr">
+        <is>
+          <t>decouplage, sobriete, effet_rebond, limites_planetaires, indicateur_de_progres, degeneratif</t>
+        </is>
+      </c>
+      <c r="M204" s="3" t="inlineStr">
+        <is>
+          <t>L1.C08, L1.C12, L11.C24, L18.C04, L24.C03, L26.C03, L26.C04, L26.C05, L26.C06, L17.C03</t>
+        </is>
+      </c>
       <c r="N204" s="3" t="inlineStr">
         <is>
           <t>corpus/livre-17-apres-la-croissance/c01-ce-que-ce-livre-doit-etablir.md</t>
@@ -14592,17 +14596,17 @@
     <row r="205">
       <c r="A205" s="2" t="inlineStr">
         <is>
-          <t>L18.C01</t>
+          <t>L17.C02</t>
         </is>
       </c>
       <c r="B205" s="3" t="inlineStr">
         <is>
-          <t>L18</t>
+          <t>L17</t>
         </is>
       </c>
       <c r="C205" s="3" t="inlineStr">
         <is>
-          <t>Ce que ce livre doit établir, et le repli n'est pas l'annexe</t>
+          <t>Les sept raisons, testées une par une contre le dispositif</t>
         </is>
       </c>
       <c r="D205" s="3" t="inlineStr">
@@ -14627,46 +14631,46 @@
       </c>
       <c r="H205" s="3" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="I205" s="3" t="inlineStr"/>
       <c r="J205" s="3" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K205" s="3" t="n">
         <v>4</v>
       </c>
       <c r="L205" s="3" t="inlineStr">
         <is>
-          <t>contrepartie_comptable, valorisation_des_communs, communs, essentiel_insolvable, qualification_regenerative, architecture_invisible</t>
+          <t>decouplage, effet_rebond, sobriete, qualification_regenerative, externalisation, degeneratif</t>
         </is>
       </c>
       <c r="M205" s="3" t="inlineStr">
         <is>
-          <t>L1.C09, L1.C29, L5.C02, L5.C09, L5.C10, L6.C08, L6.C09, L6.C13, L11.C13, L11.C16, L20.C02</t>
+          <t>L11.C13, L11.C24, L17.C01, L18.C04, L24.C01, L24.C04, L26.C01, L26.C02, L26.C04, L26.C05</t>
         </is>
       </c>
       <c r="N205" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-18-comptabilites-ecologiques-et-biophysiques/c01-ce-que-ce-livre-doit-etablir.md</t>
+          <t>corpus/livre-17-apres-la-croissance/c02-les-sept-raisons-testees-contre-le-dispositif.md</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" s="2" t="inlineStr">
         <is>
-          <t>L18.C02</t>
+          <t>L17.C03</t>
         </is>
       </c>
       <c r="B206" s="3" t="inlineStr">
         <is>
-          <t>L18</t>
+          <t>L17</t>
         </is>
       </c>
       <c r="C206" s="3" t="inlineStr">
         <is>
-          <t>La métrologie existe, et ce qu'elle enregistre est l'ordre en place</t>
+          <t>La sobriété et l'émission : le dispositif échange du mou contre du dur</t>
         </is>
       </c>
       <c r="D206" s="3" t="inlineStr">
@@ -14691,46 +14695,46 @@
       </c>
       <c r="H206" s="3" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="I206" s="3" t="inlineStr"/>
       <c r="J206" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="K206" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="K206" s="3" t="n">
-        <v>3</v>
-      </c>
       <c r="L206" s="3" t="inlineStr">
         <is>
-          <t>valorisation_des_communs, contrepartie_comptable, bareme, essentiel_insolvable, indicateur_de_progres, fausse_richesse</t>
+          <t>sobriete, decouplage, robustesse, fenetre_de_reforme, effet_rebond</t>
         </is>
       </c>
       <c r="M206" s="3" t="inlineStr">
         <is>
-          <t>L1.C09, L1.C15, L1.C18, L6.C06, L11.C03, L11.C07, L11.C13, L11.C16, L18.C01</t>
+          <t>L1.C08, L1.C12, L11.C10, L17.C01, L17.C02, L18.C04, L24.C02, L26.C03, L26.C05</t>
         </is>
       </c>
       <c r="N206" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-18-comptabilites-ecologiques-et-biophysiques/c02-la-metrologie-existe-et-ce-qu-elle-enregistre.md</t>
+          <t>corpus/livre-17-apres-la-croissance/c03-la-sobriete-et-l-emission-un-echange-de-mou-contre-du-dur.md</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" s="2" t="inlineStr">
         <is>
-          <t>L18.C03</t>
+          <t>L17.C04</t>
         </is>
       </c>
       <c r="B207" s="3" t="inlineStr">
         <is>
-          <t>L18</t>
+          <t>L17</t>
         </is>
       </c>
       <c r="C207" s="3" t="inlineStr">
         <is>
-          <t>L'échelle de repli, et qui l'a arrêtée</t>
+          <t>La seule concrétisation institutionnelle ouverte, et sa seule sanction est de publier ses raisons</t>
         </is>
       </c>
       <c r="D207" s="3" t="inlineStr">
@@ -14755,46 +14759,46 @@
       </c>
       <c r="H207" s="3" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="I207" s="3" t="inlineStr"/>
       <c r="J207" s="3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K207" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L207" s="3" t="inlineStr">
         <is>
-          <t>contrepartie_comptable, architecture_invisible, valorisation_des_communs, essentiel_insolvable, regle_contre_discretion</t>
+          <t>indicateur_de_progres, sobriete, regle_contre_discretion, robustesse, polycentricite</t>
         </is>
       </c>
       <c r="M207" s="3" t="inlineStr">
         <is>
-          <t>L1.C09, L1.C15, L1.C29, L6.C09, L11.C29, L18.C01, L18.C02, L20.C02</t>
+          <t>L11.C12, L11.C13, L14.C01, L17.C01, L17.C02, L17.C03, L25.C05, L26.C05</t>
         </is>
       </c>
       <c r="N207" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-18-comptabilites-ecologiques-et-biophysiques/c03-l-echelle-de-repli-et-qui-l-a-arretee.md</t>
+          <t>corpus/livre-17-apres-la-croissance/c04-la-concretisation-institutionnelle-et-sa-seule-sanction.md</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" s="2" t="inlineStr">
         <is>
-          <t>L18.C04</t>
+          <t>L17.C05</t>
         </is>
       </c>
       <c r="B208" s="3" t="inlineStr">
         <is>
-          <t>L18</t>
+          <t>L17</t>
         </is>
       </c>
       <c r="C208" s="3" t="inlineStr">
         <is>
-          <t>Les grandeurs physiques, et l'endroit où elles frappent le dispositif</t>
+          <t>Le tableau de bord et le chiffre unique — ce que le corpus perd en refusant d'agréger</t>
         </is>
       </c>
       <c r="D208" s="3" t="inlineStr">
@@ -14819,46 +14823,46 @@
       </c>
       <c r="H208" s="3" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="I208" s="3" t="inlineStr"/>
       <c r="J208" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="K208" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="K208" s="3" t="n">
-        <v>3</v>
-      </c>
       <c r="L208" s="3" t="inlineStr">
         <is>
-          <t>decouplage, effet_rebond, externalisation, limites_planetaires, sobriete, fausse_richesse</t>
+          <t>indicateur_de_progres, bareme, limites_planetaires, sobriete, robustesse</t>
         </is>
       </c>
       <c r="M208" s="3" t="inlineStr">
         <is>
-          <t>L1.C02, L1.C03, L1.C04, L5.C08, L6.C08, L11.C10, L11.C24, L18.C01, L18.C02</t>
+          <t>L11.C13, L11.C24, L17.C01, L18.C01, L18.C04, L24.C01, L24.C05, L25.C05, L26.C02</t>
         </is>
       </c>
       <c r="N208" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-18-comptabilites-ecologiques-et-biophysiques/c04-les-grandeurs-physiques-et-ou-elles-frappent.md</t>
+          <t>corpus/livre-17-apres-la-croissance/c05-le-tableau-de-bord-et-le-chiffre-unique.md</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" s="2" t="inlineStr">
         <is>
-          <t>L18.C05</t>
+          <t>L17.C06</t>
         </is>
       </c>
       <c r="B209" s="3" t="inlineStr">
         <is>
-          <t>L18</t>
+          <t>L17</t>
         </is>
       </c>
       <c r="C209" s="3" t="inlineStr">
         <is>
-          <t>Ce que la norme exclut, et ce n'est pas le commun</t>
+          <t>Portée de la tranche</t>
         </is>
       </c>
       <c r="D209" s="3" t="inlineStr">
@@ -14878,41 +14882,41 @@
       </c>
       <c r="G209" s="3" t="inlineStr">
         <is>
-          <t>hybride</t>
+          <t>descriptif</t>
         </is>
       </c>
       <c r="H209" s="3" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="I209" s="3" t="inlineStr"/>
       <c r="J209" s="3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K209" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L209" s="3" t="inlineStr">
         <is>
-          <t>communs, contrepartie_comptable, valorisation_des_communs, architecture_invisible, monnaie_comme_registre, creation_monetaire</t>
+          <t>sobriete, decouplage, indicateur_de_progres, effet_rebond, limites_planetaires, robustesse</t>
         </is>
       </c>
       <c r="M209" s="3" t="inlineStr">
         <is>
-          <t>L1.C09, L1.C20, L1.C29, L6.C06, L6.C08, L11.C13, L11.C16, L18.C01, L18.C02, L18.C03, L20.C02</t>
+          <t>L11.C12, L11.C24, L17.C01, L17.C02, L17.C03, L17.C04, L17.C05, L18.C01, L24.C05, L26.C05</t>
         </is>
       </c>
       <c r="N209" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-18-comptabilites-ecologiques-et-biophysiques/c05-ce-que-la-norme-exclut-et-ce-n-est-pas-le-commun.md</t>
+          <t>corpus/livre-17-apres-la-croissance/c06-portee-de-la-tranche.md</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" s="2" t="inlineStr">
         <is>
-          <t>L18.C06</t>
+          <t>L18.C01</t>
         </is>
       </c>
       <c r="B210" s="3" t="inlineStr">
@@ -14922,7 +14926,7 @@
       </c>
       <c r="C210" s="3" t="inlineStr">
         <is>
-          <t>Portée de la tranche, et une neuvième condition proposée</t>
+          <t>Ce que ce livre doit établir, et le repli n'est pas l'annexe</t>
         </is>
       </c>
       <c r="D210" s="3" t="inlineStr">
@@ -14942,41 +14946,41 @@
       </c>
       <c r="G210" s="3" t="inlineStr">
         <is>
-          <t>conception</t>
+          <t>hybride</t>
         </is>
       </c>
       <c r="H210" s="3" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="I210" s="3" t="inlineStr"/>
       <c r="J210" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K210" s="3" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="L210" s="3" t="inlineStr">
         <is>
-          <t>contrepartie_comptable, communs, valorisation_des_communs, architecture_invisible, essentiel_insolvable</t>
+          <t>contrepartie_comptable, valorisation_des_communs, communs, essentiel_insolvable, qualification_regenerative, architecture_invisible</t>
         </is>
       </c>
       <c r="M210" s="3" t="inlineStr">
         <is>
-          <t>L1.C09, L1.C18, L1.C20, L1.C29, L5.C02, L5.C08, L6.C06, L6.C08, L11.C13, L11.C16, L18.C01, L18.C02, L18.C03, L18.C04, L18.C05, L20.C02</t>
+          <t>L1.C09, L1.C29, L5.C02, L5.C09, L5.C10, L6.C08, L6.C09, L6.C13, L11.C13, L11.C16, L20.C02, L17.C05</t>
         </is>
       </c>
       <c r="N210" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-18-comptabilites-ecologiques-et-biophysiques/c06-portee-de-la-tranche-et-une-neuvieme-condition.md</t>
+          <t>corpus/livre-18-comptabilites-ecologiques-et-biophysiques/c01-ce-que-ce-livre-doit-etablir.md</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" s="2" t="inlineStr">
         <is>
-          <t>L18.C07</t>
+          <t>L18.C02</t>
         </is>
       </c>
       <c r="B211" s="3" t="inlineStr">
@@ -14986,7 +14990,7 @@
       </c>
       <c r="C211" s="3" t="inlineStr">
         <is>
-          <t>CARE/TDL répare deux objections, et en crée une plus grave</t>
+          <t>La métrologie existe, et ce qu'elle enregistre est l'ordre en place</t>
         </is>
       </c>
       <c r="D211" s="3" t="inlineStr">
@@ -15023,24 +15027,24 @@
       </c>
       <c r="L211" s="3" t="inlineStr">
         <is>
-          <t>contrepartie_comptable, bareme, valorisation_des_communs, communs, architecture_invisible, fausse_richesse</t>
+          <t>valorisation_des_communs, contrepartie_comptable, bareme, essentiel_insolvable, indicateur_de_progres, fausse_richesse</t>
         </is>
       </c>
       <c r="M211" s="3" t="inlineStr">
         <is>
-          <t>L1.C09, L1.C18, L1.C20, L6.C06, L11.C03, L11.C13, L11.C16, L18.C01, L18.C02, L18.C05, L18.C06</t>
+          <t>L1.C09, L1.C15, L1.C18, L6.C06, L11.C03, L11.C07, L11.C13, L11.C16, L18.C01</t>
         </is>
       </c>
       <c r="N211" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-18-comptabilites-ecologiques-et-biophysiques/c07-care-tdl-repare-une-objection-et-en-cree-une-autre.md</t>
+          <t>corpus/livre-18-comptabilites-ecologiques-et-biophysiques/c02-la-metrologie-existe-et-ce-qu-elle-enregistre.md</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" s="2" t="inlineStr">
         <is>
-          <t>L18.C08</t>
+          <t>L18.C03</t>
         </is>
       </c>
       <c r="B212" s="3" t="inlineStr">
@@ -15050,7 +15054,7 @@
       </c>
       <c r="C212" s="3" t="inlineStr">
         <is>
-          <t>Le modèle au périmètre du dispositif, et F9 révisée</t>
+          <t>L'échelle de repli, et qui l'a arrêtée</t>
         </is>
       </c>
       <c r="D212" s="3" t="inlineStr">
@@ -15070,7 +15074,7 @@
       </c>
       <c r="G212" s="3" t="inlineStr">
         <is>
-          <t>conception</t>
+          <t>hybride</t>
         </is>
       </c>
       <c r="H212" s="3" t="inlineStr">
@@ -15080,31 +15084,31 @@
       </c>
       <c r="I212" s="3" t="inlineStr"/>
       <c r="J212" s="3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K212" s="3" t="n">
         <v>3</v>
       </c>
       <c r="L212" s="3" t="inlineStr">
         <is>
-          <t>contrepartie_comptable, communs, valorisation_des_communs, polycentricite, essentiel_insolvable, indicateur_de_progres</t>
+          <t>contrepartie_comptable, architecture_invisible, valorisation_des_communs, essentiel_insolvable, regle_contre_discretion</t>
         </is>
       </c>
       <c r="M212" s="3" t="inlineStr">
         <is>
-          <t>L1.C09, L1.C18, L6.C06, L7.C05, L11.C13, L11.C16, L11.C25, L18.C01, L18.C02, L18.C05, L18.C06, L18.C07</t>
+          <t>L1.C09, L1.C15, L1.C29, L6.C09, L11.C29, L18.C01, L18.C02, L20.C02</t>
         </is>
       </c>
       <c r="N212" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-18-comptabilites-ecologiques-et-biophysiques/c08-le-modele-au-perimetre-du-dispositif-et-f9-revisee.md</t>
+          <t>corpus/livre-18-comptabilites-ecologiques-et-biophysiques/c03-l-echelle-de-repli-et-qui-l-a-arretee.md</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" s="2" t="inlineStr">
         <is>
-          <t>L18.C09</t>
+          <t>L18.C04</t>
         </is>
       </c>
       <c r="B213" s="3" t="inlineStr">
@@ -15114,7 +15118,7 @@
       </c>
       <c r="C213" s="3" t="inlineStr">
         <is>
-          <t>L'ordre de grandeur, et le concurrent qu'il désigne</t>
+          <t>Les grandeurs physiques, et l'endroit où elles frappent le dispositif</t>
         </is>
       </c>
       <c r="D213" s="3" t="inlineStr">
@@ -15139,46 +15143,46 @@
       </c>
       <c r="H213" s="3" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="I213" s="3" t="inlineStr"/>
       <c r="J213" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="K213" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="K213" s="3" t="n">
-        <v>4</v>
-      </c>
       <c r="L213" s="3" t="inlineStr">
         <is>
-          <t>essentiel_insolvable, valorisation_des_communs, externalisation, additionnalite, fausse_richesse, degeneratif</t>
+          <t>decouplage, effet_rebond, externalisation, limites_planetaires, sobriete, fausse_richesse</t>
         </is>
       </c>
       <c r="M213" s="3" t="inlineStr">
         <is>
-          <t>L1.C15, L1.C18, L5.C07, L10.C04, L10.C06, L11.C03, L11.C13, L18.C01, L18.C04, L18.C06, L26.C05</t>
+          <t>L1.C02, L1.C03, L1.C04, L5.C08, L6.C08, L11.C10, L11.C24, L18.C01, L18.C02</t>
         </is>
       </c>
       <c r="N213" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-18-comptabilites-ecologiques-et-biophysiques/c09-l-ordre-de-grandeur-et-le-concurrent-qu-il-designe.md</t>
+          <t>corpus/livre-18-comptabilites-ecologiques-et-biophysiques/c04-les-grandeurs-physiques-et-ou-elles-frappent.md</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" s="2" t="inlineStr">
         <is>
-          <t>L19.C01</t>
+          <t>L18.C05</t>
         </is>
       </c>
       <c r="B214" s="3" t="inlineStr">
         <is>
-          <t>L19</t>
+          <t>L18</t>
         </is>
       </c>
       <c r="C214" s="3" t="inlineStr">
         <is>
-          <t>Ce que ce livre doit établir</t>
+          <t>Ce que la norme exclut, et ce n'est pas le commun</t>
         </is>
       </c>
       <c r="D214" s="3" t="inlineStr">
@@ -15203,46 +15207,46 @@
       </c>
       <c r="H214" s="3" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="I214" s="3" t="inlineStr"/>
       <c r="J214" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K214" s="3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L214" s="3" t="inlineStr">
         <is>
-          <t>contrepartie_comptable, creation_monetaire, monnaie_comme_registre, hierarchie_monetaire, reflux_collectif</t>
+          <t>communs, contrepartie_comptable, valorisation_des_communs, architecture_invisible, monnaie_comme_registre, creation_monetaire</t>
         </is>
       </c>
       <c r="M214" s="3" t="inlineStr">
         <is>
-          <t>L1.C07, L10.C01, L10.C06, L11.C01, L11.C02, L18.C06, L21.C01, L21.C03</t>
+          <t>L1.C09, L1.C20, L1.C29, L6.C06, L6.C08, L11.C13, L11.C16, L18.C01, L18.C02, L18.C03, L20.C02</t>
         </is>
       </c>
       <c r="N214" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-19-comptabilite-monetaire-de-l-emission-sans-dette/c01-ce-que-ce-livre-doit-etablir.md</t>
+          <t>corpus/livre-18-comptabilites-ecologiques-et-biophysiques/c05-ce-que-la-norme-exclut-et-ce-n-est-pas-le-commun.md</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" s="2" t="inlineStr">
         <is>
-          <t>L19.C02</t>
+          <t>L18.C06</t>
         </is>
       </c>
       <c r="B215" s="3" t="inlineStr">
         <is>
-          <t>L19</t>
+          <t>L18</t>
         </is>
       </c>
       <c r="C215" s="3" t="inlineStr">
         <is>
-          <t>Le seul précédent, et le passif lui a été reconnu en 2008</t>
+          <t>Portée de la tranche, et une neuvième condition proposée</t>
         </is>
       </c>
       <c r="D215" s="3" t="inlineStr">
@@ -15262,51 +15266,51 @@
       </c>
       <c r="G215" s="3" t="inlineStr">
         <is>
-          <t>hybride</t>
+          <t>conception</t>
         </is>
       </c>
       <c r="H215" s="3" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="I215" s="3" t="inlineStr"/>
       <c r="J215" s="3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K215" s="3" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="L215" s="3" t="inlineStr">
         <is>
-          <t>contrepartie_comptable, reflux_collectif, hierarchie_monetaire, creation_monetaire, devise_cle</t>
+          <t>contrepartie_comptable, communs, valorisation_des_communs, architecture_invisible, essentiel_insolvable</t>
         </is>
       </c>
       <c r="M215" s="3" t="inlineStr">
         <is>
-          <t>L3.C09, L10.C06, L11.C01, L11.C02, L19.C01, L20.C09, L21.C01, L21.C03, L21.C05, L19.C06</t>
+          <t>L1.C09, L1.C18, L1.C20, L1.C29, L5.C02, L5.C08, L6.C06, L6.C08, L11.C13, L11.C16, L18.C01, L18.C02, L18.C03, L18.C04, L18.C05, L20.C02</t>
         </is>
       </c>
       <c r="N215" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-19-comptabilite-monetaire-de-l-emission-sans-dette/c02-le-seul-precedent-et-le-passif-reconnu-en-2008.md</t>
+          <t>corpus/livre-18-comptabilites-ecologiques-et-biophysiques/c06-portee-de-la-tranche-et-une-neuvieme-condition.md</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" s="2" t="inlineStr">
         <is>
-          <t>L19.C03</t>
+          <t>L18.C07</t>
         </is>
       </c>
       <c r="B216" s="3" t="inlineStr">
         <is>
-          <t>L19</t>
+          <t>L18</t>
         </is>
       </c>
       <c r="C216" s="3" t="inlineStr">
         <is>
-          <t>Le reflux est un intérêt négatif, ou une répudiation — et c'est le moment qui décide</t>
+          <t>CARE/TDL répare deux objections, et en crée une plus grave</t>
         </is>
       </c>
       <c r="D216" s="3" t="inlineStr">
@@ -15331,46 +15335,46 @@
       </c>
       <c r="H216" s="3" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="I216" s="3" t="inlineStr"/>
       <c r="J216" s="3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K216" s="3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L216" s="3" t="inlineStr">
         <is>
-          <t>monnaie_fondante, demurrage, reflux_monetaire, reflux_transactionnel, regle_contre_discretion, contrepartie_comptable</t>
+          <t>contrepartie_comptable, bareme, valorisation_des_communs, communs, architecture_invisible, fausse_richesse</t>
         </is>
       </c>
       <c r="M216" s="3" t="inlineStr">
         <is>
-          <t>L10.C06, L11.C01, L11.C02, L11.C05, L11.C07, L11.C27, L19.C01, L19.C02, L21.C01</t>
+          <t>L1.C09, L1.C18, L1.C20, L6.C06, L11.C03, L11.C13, L11.C16, L18.C01, L18.C02, L18.C05, L18.C06</t>
         </is>
       </c>
       <c r="N216" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-19-comptabilite-monetaire-de-l-emission-sans-dette/c03-le-reflux-interet-negatif-ou-repudiation.md</t>
+          <t>corpus/livre-18-comptabilites-ecologiques-et-biophysiques/c07-care-tdl-repare-une-objection-et-en-cree-une-autre.md</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" s="2" t="inlineStr">
         <is>
-          <t>L19.C04</t>
+          <t>L18.C08</t>
         </is>
       </c>
       <c r="B217" s="3" t="inlineStr">
         <is>
-          <t>L19</t>
+          <t>L18</t>
         </is>
       </c>
       <c r="C217" s="3" t="inlineStr">
         <is>
-          <t>L'actif transitoire n'existe pas, et le problème change de bilan</t>
+          <t>Le modèle au périmètre du dispositif, et F9 révisée</t>
         </is>
       </c>
       <c r="D217" s="3" t="inlineStr">
@@ -15390,51 +15394,51 @@
       </c>
       <c r="G217" s="3" t="inlineStr">
         <is>
-          <t>hybride</t>
+          <t>conception</t>
         </is>
       </c>
       <c r="H217" s="3" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="I217" s="3" t="inlineStr"/>
       <c r="J217" s="3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K217" s="3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L217" s="3" t="inlineStr">
         <is>
-          <t>contrepartie_comptable, hierarchie_monetaire, creation_monetaire, monnaie_comme_registre, solvabilite_anticipee</t>
+          <t>contrepartie_comptable, communs, valorisation_des_communs, polycentricite, essentiel_insolvable, indicateur_de_progres</t>
         </is>
       </c>
       <c r="M217" s="3" t="inlineStr">
         <is>
-          <t>L1.C07, L10.C06, L10.C07, L11.C01, L11.C02, L19.C01, L19.C02, L19.C03, L21.C03</t>
+          <t>L1.C09, L1.C18, L6.C06, L7.C05, L11.C13, L11.C16, L11.C25, L18.C01, L18.C02, L18.C05, L18.C06, L18.C07</t>
         </is>
       </c>
       <c r="N217" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-19-comptabilite-monetaire-de-l-emission-sans-dette/c04-l-actif-transitoire-et-le-deplacement-du-probleme.md</t>
+          <t>corpus/livre-18-comptabilites-ecologiques-et-biophysiques/c08-le-modele-au-perimetre-du-dispositif-et-f9-revisee.md</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" s="2" t="inlineStr">
         <is>
-          <t>L19.C05</t>
+          <t>L18.C09</t>
         </is>
       </c>
       <c r="B218" s="3" t="inlineStr">
         <is>
-          <t>L19</t>
+          <t>L18</t>
         </is>
       </c>
       <c r="C218" s="3" t="inlineStr">
         <is>
-          <t>Un débiteur collectif n'existe pas — sauf comme somme de débiteurs identifiés</t>
+          <t>L'ordre de grandeur, et le concurrent qu'il désigne</t>
         </is>
       </c>
       <c r="D218" s="3" t="inlineStr">
@@ -15464,31 +15468,31 @@
       </c>
       <c r="I218" s="3" t="inlineStr"/>
       <c r="J218" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K218" s="3" t="n">
         <v>4</v>
       </c>
       <c r="L218" s="3" t="inlineStr">
         <is>
-          <t>reflux_collectif, contrepartie_comptable, demurrage, monnaie_fondante, hierarchie_monetaire</t>
+          <t>essentiel_insolvable, valorisation_des_communs, externalisation, additionnalite, fausse_richesse, degeneratif</t>
         </is>
       </c>
       <c r="M218" s="3" t="inlineStr">
         <is>
-          <t>L10.C06, L11.C05, L11.C07, L11.C09, L19.C01, L19.C02, L19.C03, L21.C01, L25.C05</t>
+          <t>L1.C15, L1.C18, L5.C07, L10.C04, L10.C06, L11.C03, L11.C13, L18.C01, L18.C04, L18.C06, L26.C05</t>
         </is>
       </c>
       <c r="N218" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-19-comptabilite-monetaire-de-l-emission-sans-dette/c05-le-creancier-collectif-et-ce-qui-le-rend-representable.md</t>
+          <t>corpus/livre-18-comptabilites-ecologiques-et-biophysiques/c09-l-ordre-de-grandeur-et-le-concurrent-qu-il-designe.md</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" s="2" t="inlineStr">
         <is>
-          <t>L19.C06</t>
+          <t>L19.C01</t>
         </is>
       </c>
       <c r="B219" s="3" t="inlineStr">
@@ -15498,7 +15502,7 @@
       </c>
       <c r="C219" s="3" t="inlineStr">
         <is>
-          <t>Les fonds propres négatifs, et l'institution qui n'apparaît dans les comptes de personne</t>
+          <t>Ce que ce livre doit établir</t>
         </is>
       </c>
       <c r="D219" s="3" t="inlineStr">
@@ -15528,31 +15532,31 @@
       </c>
       <c r="I219" s="3" t="inlineStr"/>
       <c r="J219" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K219" s="3" t="n">
         <v>4</v>
       </c>
       <c r="L219" s="3" t="inlineStr">
         <is>
-          <t>contrepartie_comptable, solvabilite_anticipee, architecture_invisible, hierarchie_monetaire, robustesse</t>
+          <t>contrepartie_comptable, creation_monetaire, monnaie_comme_registre, hierarchie_monetaire, reflux_collectif</t>
         </is>
       </c>
       <c r="M219" s="3" t="inlineStr">
         <is>
-          <t>L1.C07, L7.C06, L14.C01, L19.C01, L19.C02, L19.C03, L19.C04, L21.C01, L21.C04</t>
+          <t>L1.C07, L10.C01, L10.C06, L11.C01, L11.C02, L18.C06, L21.C01, L21.C03</t>
         </is>
       </c>
       <c r="N219" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-19-comptabilite-monetaire-de-l-emission-sans-dette/c06-les-fonds-propres-negatifs-et-l-institution-qui-n-apparait-nulle-part.md</t>
+          <t>corpus/livre-19-comptabilite-monetaire-de-l-emission-sans-dette/c01-ce-que-ce-livre-doit-etablir.md</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" s="2" t="inlineStr">
         <is>
-          <t>L19.C07</t>
+          <t>L19.C02</t>
         </is>
       </c>
       <c r="B220" s="3" t="inlineStr">
@@ -15562,7 +15566,7 @@
       </c>
       <c r="C220" s="3" t="inlineStr">
         <is>
-          <t>Portée de la tranche</t>
+          <t>Le seul précédent, et le passif lui a été reconnu en 2008</t>
         </is>
       </c>
       <c r="D220" s="3" t="inlineStr">
@@ -15582,7 +15586,7 @@
       </c>
       <c r="G220" s="3" t="inlineStr">
         <is>
-          <t>descriptif</t>
+          <t>hybride</t>
         </is>
       </c>
       <c r="H220" s="3" t="inlineStr">
@@ -15595,38 +15599,38 @@
         <v>1</v>
       </c>
       <c r="K220" s="3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L220" s="3" t="inlineStr">
         <is>
-          <t>contrepartie_comptable, reflux_collectif, monnaie_fondante, hierarchie_monetaire, architecture_invisible, creation_monetaire</t>
+          <t>contrepartie_comptable, reflux_collectif, hierarchie_monetaire, creation_monetaire, devise_cle</t>
         </is>
       </c>
       <c r="M220" s="3" t="inlineStr">
         <is>
-          <t>L10.C06, L11.C01, L11.C02, L11.C07, L19.C01, L19.C02, L19.C03, L19.C04, L19.C05, L19.C06, L21.C01, L21.C03</t>
+          <t>L3.C09, L10.C06, L11.C01, L11.C02, L19.C01, L20.C09, L21.C01, L21.C03, L21.C05, L19.C06</t>
         </is>
       </c>
       <c r="N220" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-19-comptabilite-monetaire-de-l-emission-sans-dette/c07-portee-de-la-tranche.md</t>
+          <t>corpus/livre-19-comptabilite-monetaire-de-l-emission-sans-dette/c02-le-seul-precedent-et-le-passif-reconnu-en-2008.md</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" s="2" t="inlineStr">
         <is>
-          <t>L20.C01</t>
+          <t>L19.C03</t>
         </is>
       </c>
       <c r="B221" s="3" t="inlineStr">
         <is>
-          <t>L20</t>
+          <t>L19</t>
         </is>
       </c>
       <c r="C221" s="3" t="inlineStr">
         <is>
-          <t>Ce que ce livre doit établir</t>
+          <t>Le reflux est un intérêt négatif, ou une répudiation — et c'est le moment qui décide</t>
         </is>
       </c>
       <c r="D221" s="3" t="inlineStr">
@@ -15646,51 +15650,51 @@
       </c>
       <c r="G221" s="3" t="inlineStr">
         <is>
-          <t>conception</t>
+          <t>hybride</t>
         </is>
       </c>
       <c r="H221" s="3" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="I221" s="3" t="inlineStr"/>
       <c r="J221" s="3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K221" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L221" s="3" t="inlineStr">
         <is>
-          <t>fenetre_de_reforme, referentiel_de_change, communs, limites_planetaires, creation_monetaire</t>
+          <t>monnaie_fondante, demurrage, reflux_monetaire, reflux_transactionnel, regle_contre_discretion, contrepartie_comptable</t>
         </is>
       </c>
       <c r="M221" s="3" t="inlineStr">
         <is>
-          <t>L1.C18, L1.C25, L1.C27, L7.C01, L7.C03, L7.C13, L7.C17, L7.C21, L11.C24</t>
+          <t>L10.C06, L11.C01, L11.C02, L11.C05, L11.C07, L11.C27, L19.C01, L19.C02, L21.C01</t>
         </is>
       </c>
       <c r="N221" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-20-droit-international-monetaire-et-commercial/c01-ce-que-ce-livre-doit-etablir.md</t>
+          <t>corpus/livre-19-comptabilite-monetaire-de-l-emission-sans-dette/c03-le-reflux-interet-negatif-ou-repudiation.md</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" s="2" t="inlineStr">
         <is>
-          <t>L20.C02</t>
+          <t>L19.C04</t>
         </is>
       </c>
       <c r="B222" s="3" t="inlineStr">
         <is>
-          <t>L20</t>
+          <t>L19</t>
         </is>
       </c>
       <c r="C222" s="3" t="inlineStr">
         <is>
-          <t>L'interdiction du financement monétaire</t>
+          <t>L'actif transitoire n'existe pas, et le problème change de bilan</t>
         </is>
       </c>
       <c r="D222" s="3" t="inlineStr">
@@ -15710,51 +15714,51 @@
       </c>
       <c r="G222" s="3" t="inlineStr">
         <is>
-          <t>conception</t>
+          <t>hybride</t>
         </is>
       </c>
       <c r="H222" s="3" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="I222" s="3" t="inlineStr"/>
       <c r="J222" s="3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K222" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L222" s="3" t="inlineStr">
         <is>
-          <t>creation_monetaire, contrepartie_comptable, reflux_collectif, fenetre_de_reforme</t>
+          <t>contrepartie_comptable, hierarchie_monetaire, creation_monetaire, monnaie_comme_registre, solvabilite_anticipee</t>
         </is>
       </c>
       <c r="M222" s="3" t="inlineStr">
         <is>
-          <t>L1.C05, L1.C18, L1.C20, L1.C22, L7.C11, L7.C13, L11.C10, L20.C01</t>
+          <t>L1.C07, L10.C06, L10.C07, L11.C01, L11.C02, L19.C01, L19.C02, L19.C03, L21.C03</t>
         </is>
       </c>
       <c r="N222" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-20-droit-international-monetaire-et-commercial/c02-l-interdiction-du-financement-monetaire.md</t>
+          <t>corpus/livre-19-comptabilite-monetaire-de-l-emission-sans-dette/c04-l-actif-transitoire-et-le-deplacement-du-probleme.md</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" s="2" t="inlineStr">
         <is>
-          <t>L20.C03</t>
+          <t>L19.C05</t>
         </is>
       </c>
       <c r="B223" s="3" t="inlineStr">
         <is>
-          <t>L20</t>
+          <t>L19</t>
         </is>
       </c>
       <c r="C223" s="3" t="inlineStr">
         <is>
-          <t>L'objectif principal et ce qu'il exclut</t>
+          <t>Un débiteur collectif n'existe pas — sauf comme somme de débiteurs identifiés</t>
         </is>
       </c>
       <c r="D223" s="3" t="inlineStr">
@@ -15774,51 +15778,51 @@
       </c>
       <c r="G223" s="3" t="inlineStr">
         <is>
-          <t>conception</t>
+          <t>hybride</t>
         </is>
       </c>
       <c r="H223" s="3" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="I223" s="3" t="inlineStr"/>
       <c r="J223" s="3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K223" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L223" s="3" t="inlineStr">
         <is>
-          <t>regle_contre_discretion, limites_planetaires, creation_monetaire, plafond_ecologique</t>
+          <t>reflux_collectif, contrepartie_comptable, demurrage, monnaie_fondante, hierarchie_monetaire</t>
         </is>
       </c>
       <c r="M223" s="3" t="inlineStr">
         <is>
-          <t>L1.C01, L1.C18, L1.C20, L7.C03, L8.C12, L8.C34, L11.C16, L20.C01, L20.C02</t>
+          <t>L10.C06, L11.C05, L11.C07, L11.C09, L19.C01, L19.C02, L19.C03, L21.C01, L25.C05</t>
         </is>
       </c>
       <c r="N223" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-20-droit-international-monetaire-et-commercial/c03-l-objectif-principal-et-ce-qu-il-exclut.md</t>
+          <t>corpus/livre-19-comptabilite-monetaire-de-l-emission-sans-dette/c05-le-creancier-collectif-et-ce-qui-le-rend-representable.md</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" s="2" t="inlineStr">
         <is>
-          <t>L20.C04</t>
+          <t>L19.C06</t>
         </is>
       </c>
       <c r="B224" s="3" t="inlineStr">
         <is>
-          <t>L20</t>
+          <t>L19</t>
         </is>
       </c>
       <c r="C224" s="3" t="inlineStr">
         <is>
-          <t>L'indépendance, et à l'égard de qui</t>
+          <t>Les fonds propres négatifs, et l'institution qui n'apparaît dans les comptes de personne</t>
         </is>
       </c>
       <c r="D224" s="3" t="inlineStr">
@@ -15838,51 +15842,51 @@
       </c>
       <c r="G224" s="3" t="inlineStr">
         <is>
-          <t>conception</t>
+          <t>hybride</t>
         </is>
       </c>
       <c r="H224" s="3" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="I224" s="3" t="inlineStr"/>
       <c r="J224" s="3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K224" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L224" s="3" t="inlineStr">
         <is>
-          <t>regle_contre_discretion, creation_monetaire, fenetre_de_reforme</t>
+          <t>contrepartie_comptable, solvabilite_anticipee, architecture_invisible, hierarchie_monetaire, robustesse</t>
         </is>
       </c>
       <c r="M224" s="3" t="inlineStr">
         <is>
-          <t>L1.C18, L7.C04, L7.C07, L7.C10, L8.C31, L11.C17, L20.C01, L20.C03, L20.C11</t>
+          <t>L1.C07, L7.C06, L14.C01, L19.C01, L19.C02, L19.C03, L19.C04, L21.C01, L21.C04</t>
         </is>
       </c>
       <c r="N224" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-20-droit-international-monetaire-et-commercial/c04-l-independance-et-a-l-egard-de-qui.md</t>
+          <t>corpus/livre-19-comptabilite-monetaire-de-l-emission-sans-dette/c06-les-fonds-propres-negatifs-et-l-institution-qui-n-apparait-nulle-part.md</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" s="2" t="inlineStr">
         <is>
-          <t>L20.C05</t>
+          <t>L19.C07</t>
         </is>
       </c>
       <c r="B225" s="3" t="inlineStr">
         <is>
-          <t>L20</t>
+          <t>L19</t>
         </is>
       </c>
       <c r="C225" s="3" t="inlineStr">
         <is>
-          <t>Le monopole d'émission et le cours légal</t>
+          <t>Portée de la tranche</t>
         </is>
       </c>
       <c r="D225" s="3" t="inlineStr">
@@ -15902,41 +15906,41 @@
       </c>
       <c r="G225" s="3" t="inlineStr">
         <is>
-          <t>conception</t>
+          <t>descriptif</t>
         </is>
       </c>
       <c r="H225" s="3" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="I225" s="3" t="inlineStr"/>
       <c r="J225" s="3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K225" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L225" s="3" t="inlineStr">
         <is>
-          <t>monnaie_comme_registre, creation_monetaire, referentiel_de_change, hierarchie_monetaire</t>
+          <t>contrepartie_comptable, reflux_collectif, monnaie_fondante, hierarchie_monetaire, architecture_invisible, creation_monetaire</t>
         </is>
       </c>
       <c r="M225" s="3" t="inlineStr">
         <is>
-          <t>L1.C05, L1.C07, L1.C26, L7.C15, L11.C15, L20.C01, L20.C02, L20.C03</t>
+          <t>L10.C06, L11.C01, L11.C02, L11.C07, L19.C01, L19.C02, L19.C03, L19.C04, L19.C05, L19.C06, L21.C01, L21.C03</t>
         </is>
       </c>
       <c r="N225" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-20-droit-international-monetaire-et-commercial/c05-le-monopole-d-emission-et-le-cours-legal.md</t>
+          <t>corpus/livre-19-comptabilite-monetaire-de-l-emission-sans-dette/c07-portee-de-la-tranche.md</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" s="2" t="inlineStr">
         <is>
-          <t>L20.C06</t>
+          <t>L20.C01</t>
         </is>
       </c>
       <c r="B226" s="3" t="inlineStr">
@@ -15946,7 +15950,7 @@
       </c>
       <c r="C226" s="3" t="inlineStr">
         <is>
-          <t>Les voies de révision et leur coût</t>
+          <t>Ce que ce livre doit établir</t>
         </is>
       </c>
       <c r="D226" s="3" t="inlineStr">
@@ -15971,36 +15975,36 @@
       </c>
       <c r="H226" s="3" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="I226" s="3" t="inlineStr"/>
       <c r="J226" s="3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K226" s="3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L226" s="3" t="inlineStr">
         <is>
-          <t>fenetre_de_reforme, regle_contre_discretion, creation_monetaire</t>
+          <t>fenetre_de_reforme, referentiel_de_change, communs, limites_planetaires, creation_monetaire</t>
         </is>
       </c>
       <c r="M226" s="3" t="inlineStr">
         <is>
-          <t>L1.C18, L7.C12, L7.C20, L7.C21, L11.C15, L20.C01, L20.C02, L20.C03, L20.C07, L20.C09, L20.C18</t>
+          <t>L1.C18, L1.C25, L1.C27, L7.C01, L7.C03, L7.C13, L7.C17, L7.C21, L11.C24</t>
         </is>
       </c>
       <c r="N226" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-20-droit-international-monetaire-et-commercial/c06-les-voies-de-revision-et-leur-cout.md</t>
+          <t>corpus/livre-20-droit-international-monetaire-et-commercial/c01-ce-que-ce-livre-doit-etablir.md</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" s="2" t="inlineStr">
         <is>
-          <t>L20.C07</t>
+          <t>L20.C02</t>
         </is>
       </c>
       <c r="B227" s="3" t="inlineStr">
@@ -16010,7 +16014,7 @@
       </c>
       <c r="C227" s="3" t="inlineStr">
         <is>
-          <t>L'accord monétaire international</t>
+          <t>L'interdiction du financement monétaire</t>
         </is>
       </c>
       <c r="D227" s="3" t="inlineStr">
@@ -16035,7 +16039,7 @@
       </c>
       <c r="H227" s="3" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="I227" s="3" t="inlineStr"/>
@@ -16047,24 +16051,24 @@
       </c>
       <c r="L227" s="3" t="inlineStr">
         <is>
-          <t>referentiel_de_change, fenetre_de_reforme, etalon_de_change_or, hierarchie_monetaire</t>
+          <t>creation_monetaire, contrepartie_comptable, reflux_collectif, fenetre_de_reforme</t>
         </is>
       </c>
       <c r="M227" s="3" t="inlineStr">
         <is>
-          <t>L1.C18, L1.C26, L7.C02, L7.C05, L7.C12, L7.C13, L11.C15, L20.C01, L20.C03, L20.C06, L20.C10</t>
+          <t>L1.C05, L1.C18, L1.C20, L1.C22, L7.C11, L7.C13, L11.C10, L20.C01</t>
         </is>
       </c>
       <c r="N227" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-20-droit-international-monetaire-et-commercial/c07-l-accord-monetaire-international.md</t>
+          <t>corpus/livre-20-droit-international-monetaire-et-commercial/c02-l-interdiction-du-financement-monetaire.md</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" s="2" t="inlineStr">
         <is>
-          <t>L20.C08</t>
+          <t>L20.C03</t>
         </is>
       </c>
       <c r="B228" s="3" t="inlineStr">
@@ -16074,7 +16078,7 @@
       </c>
       <c r="C228" s="3" t="inlineStr">
         <is>
-          <t>La parité inscrite dans le traité</t>
+          <t>L'objectif principal et ce qu'il exclut</t>
         </is>
       </c>
       <c r="D228" s="3" t="inlineStr">
@@ -16104,31 +16108,31 @@
       </c>
       <c r="I228" s="3" t="inlineStr"/>
       <c r="J228" s="3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K228" s="3" t="n">
         <v>3</v>
       </c>
       <c r="L228" s="3" t="inlineStr">
         <is>
-          <t>referentiel_de_change, etalon_de_change_or, hierarchie_monetaire, bareme, devise_cle</t>
+          <t>regle_contre_discretion, limites_planetaires, creation_monetaire, plafond_ecologique</t>
         </is>
       </c>
       <c r="M228" s="3" t="inlineStr">
         <is>
-          <t>L1.C25, L1.C26, L1.C28, L7.C02, L7.C20, L11.C15, L11.C17, L20.C01, L20.C09, L20.C13</t>
+          <t>L1.C01, L1.C18, L1.C20, L7.C03, L8.C12, L8.C34, L11.C16, L20.C01, L20.C02</t>
         </is>
       </c>
       <c r="N228" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-20-droit-international-monetaire-et-commercial/c08-la-parite-inscrite-dans-le-traite.md</t>
+          <t>corpus/livre-20-droit-international-monetaire-et-commercial/c03-l-objectif-principal-et-ce-qu-il-exclut.md</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" s="2" t="inlineStr">
         <is>
-          <t>L20.C09</t>
+          <t>L20.C04</t>
         </is>
       </c>
       <c r="B229" s="3" t="inlineStr">
@@ -16138,7 +16142,7 @@
       </c>
       <c r="C229" s="3" t="inlineStr">
         <is>
-          <t>L'amendement des statuts du Fonds</t>
+          <t>L'indépendance, et à l'égard de qui</t>
         </is>
       </c>
       <c r="D229" s="3" t="inlineStr">
@@ -16175,24 +16179,24 @@
       </c>
       <c r="L229" s="3" t="inlineStr">
         <is>
-          <t>fenetre_de_reforme, referentiel_de_change, bareme, regle_contre_discretion</t>
+          <t>regle_contre_discretion, creation_monetaire, fenetre_de_reforme</t>
         </is>
       </c>
       <c r="M229" s="3" t="inlineStr">
         <is>
-          <t>L7.C06, L7.C09, L7.C16, L7.C20, L11.C15, L11.C20, L20.C01, L20.C06, L20.C08, L20.C10, L20.C13</t>
+          <t>L1.C18, L7.C04, L7.C07, L7.C10, L8.C31, L11.C17, L20.C01, L20.C03, L20.C11</t>
         </is>
       </c>
       <c r="N229" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-20-droit-international-monetaire-et-commercial/c09-l-amendement-des-statuts-du-fonds.md</t>
+          <t>corpus/livre-20-droit-international-monetaire-et-commercial/c04-l-independance-et-a-l-egard-de-qui.md</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" s="2" t="inlineStr">
         <is>
-          <t>L20.C10</t>
+          <t>L20.C05</t>
         </is>
       </c>
       <c r="B230" s="3" t="inlineStr">
@@ -16202,7 +16206,7 @@
       </c>
       <c r="C230" s="3" t="inlineStr">
         <is>
-          <t>Le vote pondéré et les voix de base</t>
+          <t>Le monopole d'émission et le cours légal</t>
         </is>
       </c>
       <c r="D230" s="3" t="inlineStr">
@@ -16239,24 +16243,24 @@
       </c>
       <c r="L230" s="3" t="inlineStr">
         <is>
-          <t>bareme, devise_cle, hierarchie_monetaire, referentiel_de_change</t>
+          <t>monnaie_comme_registre, creation_monetaire, referentiel_de_change, hierarchie_monetaire</t>
         </is>
       </c>
       <c r="M230" s="3" t="inlineStr">
         <is>
-          <t>L1.C25, L7.C02, L7.C05, L7.C06, L7.C09, L7.C10, L11.C16, L20.C01, L20.C07, L20.C09, L20.C12</t>
+          <t>L1.C05, L1.C07, L1.C26, L7.C15, L11.C15, L20.C01, L20.C02, L20.C03</t>
         </is>
       </c>
       <c r="N230" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-20-droit-international-monetaire-et-commercial/c10-le-vote-pondere-et-les-voix-de-base.md</t>
+          <t>corpus/livre-20-droit-international-monetaire-et-commercial/c05-le-monopole-d-emission-et-le-cours-legal.md</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" s="2" t="inlineStr">
         <is>
-          <t>L20.C11</t>
+          <t>L20.C06</t>
         </is>
       </c>
       <c r="B231" s="3" t="inlineStr">
@@ -16266,7 +16270,7 @@
       </c>
       <c r="C231" s="3" t="inlineStr">
         <is>
-          <t>La personnalité juridique et les immunités</t>
+          <t>Les voies de révision et leur coût</t>
         </is>
       </c>
       <c r="D231" s="3" t="inlineStr">
@@ -16299,28 +16303,28 @@
         <v>4</v>
       </c>
       <c r="K231" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L231" s="3" t="inlineStr">
         <is>
-          <t>communs, creation_monetaire, fenetre_de_reforme, robustesse</t>
+          <t>fenetre_de_reforme, regle_contre_discretion, creation_monetaire</t>
         </is>
       </c>
       <c r="M231" s="3" t="inlineStr">
         <is>
-          <t>L7.C01, L7.C03, L7.C07, L7.C10, L7.C13, L11.C25, L20.C01, L20.C04, L20.C12, L20.C14</t>
+          <t>L1.C18, L7.C12, L7.C20, L7.C21, L11.C15, L20.C01, L20.C02, L20.C03, L20.C07, L20.C09, L20.C18</t>
         </is>
       </c>
       <c r="N231" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-20-droit-international-monetaire-et-commercial/c11-la-personnalite-juridique-et-les-immunites.md</t>
+          <t>corpus/livre-20-droit-international-monetaire-et-commercial/c06-les-voies-de-revision-et-leur-cout.md</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="A232" s="2" t="inlineStr">
         <is>
-          <t>L20.C12</t>
+          <t>L20.C07</t>
         </is>
       </c>
       <c r="B232" s="3" t="inlineStr">
@@ -16330,7 +16334,7 @@
       </c>
       <c r="C232" s="3" t="inlineStr">
         <is>
-          <t>Les pouvoirs non délégables</t>
+          <t>L'accord monétaire international</t>
         </is>
       </c>
       <c r="D232" s="3" t="inlineStr">
@@ -16355,7 +16359,7 @@
       </c>
       <c r="H232" s="3" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="I232" s="3" t="inlineStr"/>
@@ -16367,24 +16371,24 @@
       </c>
       <c r="L232" s="3" t="inlineStr">
         <is>
-          <t>bareme, valorisation_des_communs, polycentricite, robustesse</t>
+          <t>referentiel_de_change, fenetre_de_reforme, etalon_de_change_or, hierarchie_monetaire</t>
         </is>
       </c>
       <c r="M232" s="3" t="inlineStr">
         <is>
-          <t>L7.C05, L7.C06, L7.C07, L7.C11, L7.C14, L11.C16, L11.C20, L20.C01, L20.C09, L20.C10, L20.C14</t>
+          <t>L1.C18, L1.C26, L7.C02, L7.C05, L7.C12, L7.C13, L11.C15, L20.C01, L20.C03, L20.C06, L20.C10</t>
         </is>
       </c>
       <c r="N232" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-20-droit-international-monetaire-et-commercial/c12-les-pouvoirs-non-delegables.md</t>
+          <t>corpus/livre-20-droit-international-monetaire-et-commercial/c07-l-accord-monetaire-international.md</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" s="2" t="inlineStr">
         <is>
-          <t>L20.C13</t>
+          <t>L20.C08</t>
         </is>
       </c>
       <c r="B233" s="3" t="inlineStr">
@@ -16394,7 +16398,7 @@
       </c>
       <c r="C233" s="3" t="inlineStr">
         <is>
-          <t>L'entrée en vigueur, l'adhésion et le retrait</t>
+          <t>La parité inscrite dans le traité</t>
         </is>
       </c>
       <c r="D233" s="3" t="inlineStr">
@@ -16431,24 +16435,24 @@
       </c>
       <c r="L233" s="3" t="inlineStr">
         <is>
-          <t>seuil_d_activation, reflux_collectif, fenetre_de_reforme, additionnalite</t>
+          <t>referentiel_de_change, etalon_de_change_or, hierarchie_monetaire, bareme, devise_cle</t>
         </is>
       </c>
       <c r="M233" s="3" t="inlineStr">
         <is>
-          <t>L7.C11, L7.C12, L7.C16, L7.C17, L7.C19, L11.C18, L20.C01, L20.C06, L20.C09, L20.C12</t>
+          <t>L1.C25, L1.C26, L1.C28, L7.C02, L7.C20, L11.C15, L11.C17, L20.C01, L20.C09, L20.C13</t>
         </is>
       </c>
       <c r="N233" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-20-droit-international-monetaire-et-commercial/c13-l-entree-en-vigueur-l-adhesion-et-le-retrait.md</t>
+          <t>corpus/livre-20-droit-international-monetaire-et-commercial/c08-la-parite-inscrite-dans-le-traite.md</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" s="2" t="inlineStr">
         <is>
-          <t>L20.C14</t>
+          <t>L20.C09</t>
         </is>
       </c>
       <c r="B234" s="3" t="inlineStr">
@@ -16458,7 +16462,7 @@
       </c>
       <c r="C234" s="3" t="inlineStr">
         <is>
-          <t>Qui interprète le traité</t>
+          <t>L'amendement des statuts du Fonds</t>
         </is>
       </c>
       <c r="D234" s="3" t="inlineStr">
@@ -16483,7 +16487,7 @@
       </c>
       <c r="H234" s="3" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="I234" s="3" t="inlineStr"/>
@@ -16495,24 +16499,24 @@
       </c>
       <c r="L234" s="3" t="inlineStr">
         <is>
-          <t>robustesse, regle_contre_discretion, communs</t>
+          <t>fenetre_de_reforme, referentiel_de_change, bareme, regle_contre_discretion</t>
         </is>
       </c>
       <c r="M234" s="3" t="inlineStr">
         <is>
-          <t>L7.C07, L7.C13, L7.C14, L7.C19, L11.C19, L11.C25, L20.C01, L20.C03, L20.C11, L20.C12, L20.C21</t>
+          <t>L7.C06, L7.C09, L7.C16, L7.C20, L11.C15, L11.C20, L20.C01, L20.C06, L20.C08, L20.C10, L20.C13</t>
         </is>
       </c>
       <c r="N234" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-20-droit-international-monetaire-et-commercial/c14-qui-interprete-le-traite.md</t>
+          <t>corpus/livre-20-droit-international-monetaire-et-commercial/c09-l-amendement-des-statuts-du-fonds.md</t>
         </is>
       </c>
     </row>
     <row r="235">
       <c r="A235" s="2" t="inlineStr">
         <is>
-          <t>L20.C15</t>
+          <t>L20.C10</t>
         </is>
       </c>
       <c r="B235" s="3" t="inlineStr">
@@ -16522,7 +16526,7 @@
       </c>
       <c r="C235" s="3" t="inlineStr">
         <is>
-          <t>Le devoir international des agents</t>
+          <t>Le vote pondéré et les voix de base</t>
         </is>
       </c>
       <c r="D235" s="3" t="inlineStr">
@@ -16552,31 +16556,31 @@
       </c>
       <c r="I235" s="3" t="inlineStr"/>
       <c r="J235" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K235" s="3" t="n">
         <v>3</v>
       </c>
       <c r="L235" s="3" t="inlineStr">
         <is>
-          <t>robustesse, regle_contre_discretion, indicateur_de_progres</t>
+          <t>bareme, devise_cle, hierarchie_monetaire, referentiel_de_change</t>
         </is>
       </c>
       <c r="M235" s="3" t="inlineStr">
         <is>
-          <t>L7.C04, L7.C07, L7.C10, L11.C21, L11.C25, L20.C01, L20.C04, L20.C11, L20.C14</t>
+          <t>L1.C25, L7.C02, L7.C05, L7.C06, L7.C09, L7.C10, L11.C16, L20.C01, L20.C07, L20.C09, L20.C12</t>
         </is>
       </c>
       <c r="N235" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-20-droit-international-monetaire-et-commercial/c15-le-devoir-international-des-agents.md</t>
+          <t>corpus/livre-20-droit-international-monetaire-et-commercial/c10-le-vote-pondere-et-les-voix-de-base.md</t>
         </is>
       </c>
     </row>
     <row r="236">
       <c r="A236" s="2" t="inlineStr">
         <is>
-          <t>L20.C16</t>
+          <t>L20.C11</t>
         </is>
       </c>
       <c r="B236" s="3" t="inlineStr">
@@ -16586,7 +16590,7 @@
       </c>
       <c r="C236" s="3" t="inlineStr">
         <is>
-          <t>Le patrimoine commun de l'humanité</t>
+          <t>La personnalité juridique et les immunités</t>
         </is>
       </c>
       <c r="D236" s="3" t="inlineStr">
@@ -16611,36 +16615,36 @@
       </c>
       <c r="H236" s="3" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="I236" s="3" t="inlineStr"/>
       <c r="J236" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K236" s="3" t="n">
         <v>3</v>
       </c>
       <c r="L236" s="3" t="inlineStr">
         <is>
-          <t>communs, valorisation_des_communs, limites_planetaires, additionnalite, plafond_ecologique</t>
+          <t>communs, creation_monetaire, fenetre_de_reforme, robustesse</t>
         </is>
       </c>
       <c r="M236" s="3" t="inlineStr">
         <is>
-          <t>L1.C17, L1.C22, L7.C05, L7.C13, L11.C16, L20.C01, L20.C11, L20.C17, L20.C22</t>
+          <t>L7.C01, L7.C03, L7.C07, L7.C10, L7.C13, L11.C25, L20.C01, L20.C04, L20.C12, L20.C14</t>
         </is>
       </c>
       <c r="N236" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-20-droit-international-monetaire-et-commercial/c16-le-patrimoine-commun-de-l-humanite.md</t>
+          <t>corpus/livre-20-droit-international-monetaire-et-commercial/c11-la-personnalite-juridique-et-les-immunites.md</t>
         </is>
       </c>
     </row>
     <row r="237">
       <c r="A237" s="2" t="inlineStr">
         <is>
-          <t>L20.C17</t>
+          <t>L20.C12</t>
         </is>
       </c>
       <c r="B237" s="3" t="inlineStr">
@@ -16650,7 +16654,7 @@
       </c>
       <c r="C237" s="3" t="inlineStr">
         <is>
-          <t>La sanctuarisation, et elle existe</t>
+          <t>Les pouvoirs non délégables</t>
         </is>
       </c>
       <c r="D237" s="3" t="inlineStr">
@@ -16680,31 +16684,31 @@
       </c>
       <c r="I237" s="3" t="inlineStr"/>
       <c r="J237" s="3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K237" s="3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L237" s="3" t="inlineStr">
         <is>
-          <t>communs, limites_planetaires, fenetre_de_reforme, robustesse, plafond_ecologique</t>
+          <t>bareme, valorisation_des_communs, polycentricite, robustesse</t>
         </is>
       </c>
       <c r="M237" s="3" t="inlineStr">
         <is>
-          <t>L1.C17, L1.C18, L7.C13, L7.C19, L7.C20, L11.C20, L20.C01, L20.C06, L20.C09, L20.C16, L20.C22</t>
+          <t>L7.C05, L7.C06, L7.C07, L7.C11, L7.C14, L11.C16, L11.C20, L20.C01, L20.C09, L20.C10, L20.C14</t>
         </is>
       </c>
       <c r="N237" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-20-droit-international-monetaire-et-commercial/c17-la-sanctuarisation-et-elle-existe.md</t>
+          <t>corpus/livre-20-droit-international-monetaire-et-commercial/c12-les-pouvoirs-non-delegables.md</t>
         </is>
       </c>
     </row>
     <row r="238">
       <c r="A238" s="2" t="inlineStr">
         <is>
-          <t>L20.C18</t>
+          <t>L20.C13</t>
         </is>
       </c>
       <c r="B238" s="3" t="inlineStr">
@@ -16714,7 +16718,7 @@
       </c>
       <c r="C238" s="3" t="inlineStr">
         <is>
-          <t>L'amendement et la dérogation dans l'ordre commercial</t>
+          <t>L'entrée en vigueur, l'adhésion et le retrait</t>
         </is>
       </c>
       <c r="D238" s="3" t="inlineStr">
@@ -16739,36 +16743,36 @@
       </c>
       <c r="H238" s="3" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="I238" s="3" t="inlineStr"/>
       <c r="J238" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K238" s="3" t="n">
         <v>3</v>
       </c>
       <c r="L238" s="3" t="inlineStr">
         <is>
-          <t>bareme, seuil_d_activation, additionnalite, fenetre_de_reforme</t>
+          <t>seuil_d_activation, reflux_collectif, fenetre_de_reforme, additionnalite</t>
         </is>
       </c>
       <c r="M238" s="3" t="inlineStr">
         <is>
-          <t>L1.C27, L7.C17, L7.C20, L11.C24, L20.C01, L20.C06, L20.C09, L20.C13, L20.C19, L20.C20</t>
+          <t>L7.C11, L7.C12, L7.C16, L7.C17, L7.C19, L11.C18, L20.C01, L20.C06, L20.C09, L20.C12</t>
         </is>
       </c>
       <c r="N238" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-20-droit-international-monetaire-et-commercial/c18-l-amendement-et-la-derogation-dans-l-ordre-commercial.md</t>
+          <t>corpus/livre-20-droit-international-monetaire-et-commercial/c13-l-entree-en-vigueur-l-adhesion-et-le-retrait.md</t>
         </is>
       </c>
     </row>
     <row r="239">
       <c r="A239" s="2" t="inlineStr">
         <is>
-          <t>L20.C19</t>
+          <t>L20.C14</t>
         </is>
       </c>
       <c r="B239" s="3" t="inlineStr">
@@ -16778,7 +16782,7 @@
       </c>
       <c r="C239" s="3" t="inlineStr">
         <is>
-          <t>Le texte que la conformité invoque</t>
+          <t>Qui interprète le traité</t>
         </is>
       </c>
       <c r="D239" s="3" t="inlineStr">
@@ -16808,31 +16812,31 @@
       </c>
       <c r="I239" s="3" t="inlineStr"/>
       <c r="J239" s="3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K239" s="3" t="n">
         <v>3</v>
       </c>
       <c r="L239" s="3" t="inlineStr">
         <is>
-          <t>bareme, additionnalite, limites_planetaires, seuil_d_activation, externalisation</t>
+          <t>robustesse, regle_contre_discretion, communs</t>
         </is>
       </c>
       <c r="M239" s="3" t="inlineStr">
         <is>
-          <t>L1.C27, L7.C17, L11.C24, L20.C01, L20.C18, L20.C20, L20.C22</t>
+          <t>L7.C07, L7.C13, L7.C14, L7.C19, L11.C19, L11.C25, L20.C01, L20.C03, L20.C11, L20.C12, L20.C21</t>
         </is>
       </c>
       <c r="N239" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-20-droit-international-monetaire-et-commercial/c19-le-texte-que-la-conformite-invoque.md</t>
+          <t>corpus/livre-20-droit-international-monetaire-et-commercial/c14-qui-interprete-le-traite.md</t>
         </is>
       </c>
     </row>
     <row r="240">
       <c r="A240" s="2" t="inlineStr">
         <is>
-          <t>L20.C20</t>
+          <t>L20.C15</t>
         </is>
       </c>
       <c r="B240" s="3" t="inlineStr">
@@ -16842,7 +16846,7 @@
       </c>
       <c r="C240" s="3" t="inlineStr">
         <is>
-          <t>L'ajustement aux frontières comme précédent</t>
+          <t>Le devoir international des agents</t>
         </is>
       </c>
       <c r="D240" s="3" t="inlineStr">
@@ -16867,36 +16871,36 @@
       </c>
       <c r="H240" s="3" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="I240" s="3" t="inlineStr"/>
       <c r="J240" s="3" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K240" s="3" t="n">
         <v>3</v>
       </c>
       <c r="L240" s="3" t="inlineStr">
         <is>
-          <t>bareme, seuil_d_activation, externalisation, additionnalite, contrepartie_comptable</t>
+          <t>robustesse, regle_contre_discretion, indicateur_de_progres</t>
         </is>
       </c>
       <c r="M240" s="3" t="inlineStr">
         <is>
-          <t>L1.C27, L7.C17, L11.C21, L11.C24, L11.C25, L20.C01, L20.C18, L20.C19, L20.C22</t>
+          <t>L7.C04, L7.C07, L7.C10, L11.C21, L11.C25, L20.C01, L20.C04, L20.C11, L20.C14</t>
         </is>
       </c>
       <c r="N240" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-20-droit-international-monetaire-et-commercial/c20-l-ajustement-aux-frontieres-comme-precedent.md</t>
+          <t>corpus/livre-20-droit-international-monetaire-et-commercial/c15-le-devoir-international-des-agents.md</t>
         </is>
       </c>
     </row>
     <row r="241">
       <c r="A241" s="2" t="inlineStr">
         <is>
-          <t>L20.C21</t>
+          <t>L20.C16</t>
         </is>
       </c>
       <c r="B241" s="3" t="inlineStr">
@@ -16906,7 +16910,7 @@
       </c>
       <c r="C241" s="3" t="inlineStr">
         <is>
-          <t>La transparence et sa limite juridictionnelle</t>
+          <t>Le patrimoine commun de l'humanité</t>
         </is>
       </c>
       <c r="D241" s="3" t="inlineStr">
@@ -16931,7 +16935,7 @@
       </c>
       <c r="H241" s="3" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="I241" s="3" t="inlineStr"/>
@@ -16943,24 +16947,24 @@
       </c>
       <c r="L241" s="3" t="inlineStr">
         <is>
-          <t>robustesse, contrepartie_comptable, bareme, monnaie_comme_registre</t>
+          <t>communs, valorisation_des_communs, limites_planetaires, additionnalite, plafond_ecologique</t>
         </is>
       </c>
       <c r="M241" s="3" t="inlineStr">
         <is>
-          <t>L7.C18, L11.C21, L11.C24, L11.C25, L20.C01, L20.C11, L20.C14, L20.C20, L20.C22</t>
+          <t>L1.C17, L1.C22, L7.C05, L7.C13, L11.C16, L20.C01, L20.C11, L20.C17, L20.C22</t>
         </is>
       </c>
       <c r="N241" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-20-droit-international-monetaire-et-commercial/c21-la-transparence-et-sa-limite-juridictionnelle.md</t>
+          <t>corpus/livre-20-droit-international-monetaire-et-commercial/c16-le-patrimoine-commun-de-l-humanite.md</t>
         </is>
       </c>
     </row>
     <row r="242">
       <c r="A242" s="2" t="inlineStr">
         <is>
-          <t>L20.C22</t>
+          <t>L20.C17</t>
         </is>
       </c>
       <c r="B242" s="3" t="inlineStr">
@@ -16970,7 +16974,7 @@
       </c>
       <c r="C242" s="3" t="inlineStr">
         <is>
-          <t>Ce que le droit devrait devenir</t>
+          <t>La sanctuarisation, et elle existe</t>
         </is>
       </c>
       <c r="D242" s="3" t="inlineStr">
@@ -16995,36 +16999,36 @@
       </c>
       <c r="H242" s="3" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="I242" s="3" t="inlineStr"/>
       <c r="J242" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K242" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L242" s="3" t="inlineStr">
         <is>
-          <t>fenetre_de_reforme, communs, limites_planetaires, regle_contre_discretion, bareme, referentiel_de_change</t>
+          <t>communs, limites_planetaires, fenetre_de_reforme, robustesse, plafond_ecologique</t>
         </is>
       </c>
       <c r="M242" s="3" t="inlineStr">
         <is>
-          <t>L1.C18, L7.C12, L7.C13, L11.C15, L11.C25, L20.C01, L20.C03, L20.C06, L20.C07, L20.C08, L20.C12, L20.C13, L20.C16, L20.C17, L20.C19, L20.C20, L20.C21, L20.C23</t>
+          <t>L1.C17, L1.C18, L7.C13, L7.C19, L7.C20, L11.C20, L20.C01, L20.C06, L20.C09, L20.C16, L20.C22</t>
         </is>
       </c>
       <c r="N242" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-20-droit-international-monetaire-et-commercial/c22-ce-que-le-droit-devrait-devenir.md</t>
+          <t>corpus/livre-20-droit-international-monetaire-et-commercial/c17-la-sanctuarisation-et-elle-existe.md</t>
         </is>
       </c>
     </row>
     <row r="243">
       <c r="A243" s="2" t="inlineStr">
         <is>
-          <t>L20.C23</t>
+          <t>L20.C18</t>
         </is>
       </c>
       <c r="B243" s="3" t="inlineStr">
@@ -17034,7 +17038,7 @@
       </c>
       <c r="C243" s="3" t="inlineStr">
         <is>
-          <t>La portée du livre</t>
+          <t>L'amendement et la dérogation dans l'ordre commercial</t>
         </is>
       </c>
       <c r="D243" s="3" t="inlineStr">
@@ -17064,41 +17068,41 @@
       </c>
       <c r="I243" s="3" t="inlineStr"/>
       <c r="J243" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K243" s="3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L243" s="3" t="inlineStr">
         <is>
-          <t>fenetre_de_reforme, communs, limites_planetaires, creation_monetaire, robustesse</t>
+          <t>bareme, seuil_d_activation, additionnalite, fenetre_de_reforme</t>
         </is>
       </c>
       <c r="M243" s="3" t="inlineStr">
         <is>
-          <t>L1.C18, L1.C27, L7.C05, L7.C10, L7.C12, L7.C13, L11.C15, L11.C24, L11.C25, L20.C01, L20.C02, L20.C03, L20.C06, L20.C07, L20.C08, L20.C11, L20.C12, L20.C13, L20.C16, L20.C17, L20.C19, L20.C20, L20.C21, L20.C22</t>
+          <t>L1.C27, L7.C17, L7.C20, L11.C24, L20.C01, L20.C06, L20.C09, L20.C13, L20.C19, L20.C20</t>
         </is>
       </c>
       <c r="N243" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-20-droit-international-monetaire-et-commercial/c23-la-portee-du-livre.md</t>
+          <t>corpus/livre-20-droit-international-monetaire-et-commercial/c18-l-amendement-et-la-derogation-dans-l-ordre-commercial.md</t>
         </is>
       </c>
     </row>
     <row r="244">
       <c r="A244" s="2" t="inlineStr">
         <is>
-          <t>L21.C01</t>
+          <t>L20.C19</t>
         </is>
       </c>
       <c r="B244" s="3" t="inlineStr">
         <is>
-          <t>L21</t>
+          <t>L20</t>
         </is>
       </c>
       <c r="C244" s="3" t="inlineStr">
         <is>
-          <t>Ce que ce livre doit établir, et le principe qui exige des fonds propres</t>
+          <t>Le texte que la conformité invoque</t>
         </is>
       </c>
       <c r="D244" s="3" t="inlineStr">
@@ -17118,51 +17122,51 @@
       </c>
       <c r="G244" s="3" t="inlineStr">
         <is>
-          <t>hybride</t>
+          <t>conception</t>
         </is>
       </c>
       <c r="H244" s="3" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="I244" s="3" t="inlineStr"/>
       <c r="J244" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="K244" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="K244" s="3" t="n">
-        <v>5</v>
-      </c>
       <c r="L244" s="3" t="inlineStr">
         <is>
-          <t>contrepartie_comptable, creation_monetaire, hierarchie_monetaire, monnaie_comme_registre, seuil_d_activation</t>
+          <t>bareme, additionnalite, limites_planetaires, seuil_d_activation, externalisation</t>
         </is>
       </c>
       <c r="M244" s="3" t="inlineStr">
         <is>
-          <t>L1.C20, L5.C02, L5.C09, L10.C01, L10.C02, L11.C02, L18.C01, L21.C01, L19.C02, L19.C06</t>
+          <t>L1.C27, L7.C17, L11.C24, L20.C01, L20.C18, L20.C20, L20.C22</t>
         </is>
       </c>
       <c r="N244" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-21-plomberie-financiere-mondiale/c01-ce-que-ce-livre-doit-etablir.md</t>
+          <t>corpus/livre-20-droit-international-monetaire-et-commercial/c19-le-texte-que-la-conformite-invoque.md</t>
         </is>
       </c>
     </row>
     <row r="245">
       <c r="A245" s="2" t="inlineStr">
         <is>
-          <t>L21.C02</t>
+          <t>L20.C20</t>
         </is>
       </c>
       <c r="B245" s="3" t="inlineStr">
         <is>
-          <t>L21</t>
+          <t>L20</t>
         </is>
       </c>
       <c r="C245" s="3" t="inlineStr">
         <is>
-          <t>Comment l'unité circulerait vraiment, et ce que chaque étape exige</t>
+          <t>L'ajustement aux frontières comme précédent</t>
         </is>
       </c>
       <c r="D245" s="3" t="inlineStr">
@@ -17182,7 +17186,7 @@
       </c>
       <c r="G245" s="3" t="inlineStr">
         <is>
-          <t>hybride</t>
+          <t>conception</t>
         </is>
       </c>
       <c r="H245" s="3" t="inlineStr">
@@ -17192,41 +17196,41 @@
       </c>
       <c r="I245" s="3" t="inlineStr"/>
       <c r="J245" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K245" s="3" t="n">
         <v>3</v>
       </c>
       <c r="L245" s="3" t="inlineStr">
         <is>
-          <t>monnaie_comme_registre, hierarchie_monetaire, contrepartie_comptable, devise_cle, seuil_d_activation</t>
+          <t>bareme, seuil_d_activation, externalisation, additionnalite, contrepartie_comptable</t>
         </is>
       </c>
       <c r="M245" s="3" t="inlineStr">
         <is>
-          <t>L1.C24, L3.C05, L3.C09, L5.C02, L5.C09, L10.C01, L11.C02, L21.C01</t>
+          <t>L1.C27, L7.C17, L11.C21, L11.C24, L11.C25, L20.C01, L20.C18, L20.C19, L20.C22</t>
         </is>
       </c>
       <c r="N245" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-21-plomberie-financiere-mondiale/c02-comment-l-unite-circulerait-vraiment.md</t>
+          <t>corpus/livre-20-droit-international-monetaire-et-commercial/c20-l-ajustement-aux-frontieres-comme-precedent.md</t>
         </is>
       </c>
     </row>
     <row r="246">
       <c r="A246" s="2" t="inlineStr">
         <is>
-          <t>L21.C03</t>
+          <t>L20.C21</t>
         </is>
       </c>
       <c r="B246" s="3" t="inlineStr">
         <is>
-          <t>L21</t>
+          <t>L20</t>
         </is>
       </c>
       <c r="C246" s="3" t="inlineStr">
         <is>
-          <t>Une opération de bout en bout, bilan par bilan</t>
+          <t>La transparence et sa limite juridictionnelle</t>
         </is>
       </c>
       <c r="D246" s="3" t="inlineStr">
@@ -17251,7 +17255,7 @@
       </c>
       <c r="H246" s="3" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="I246" s="3" t="inlineStr"/>
@@ -17259,38 +17263,38 @@
         <v>3</v>
       </c>
       <c r="K246" s="3" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="L246" s="3" t="inlineStr">
         <is>
-          <t>contrepartie_comptable, creation_monetaire, reflux_collectif, demurrage, monnaie_comme_registre, hierarchie_monetaire</t>
+          <t>robustesse, contrepartie_comptable, bareme, monnaie_comme_registre</t>
         </is>
       </c>
       <c r="M246" s="3" t="inlineStr">
         <is>
-          <t>L1.C07, L1.C29, L10.C06, L10.C07, L11.C01, L11.C02, L11.C11, L11.C13, L11.C23, L21.C01, L21.C02, L19.C04</t>
+          <t>L7.C18, L11.C21, L11.C24, L11.C25, L20.C01, L20.C11, L20.C14, L20.C20, L20.C22</t>
         </is>
       </c>
       <c r="N246" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-21-plomberie-financiere-mondiale/c03-une-operation-de-bout-en-bout.md</t>
+          <t>corpus/livre-20-droit-international-monetaire-et-commercial/c21-la-transparence-et-sa-limite-juridictionnelle.md</t>
         </is>
       </c>
     </row>
     <row r="247">
       <c r="A247" s="2" t="inlineStr">
         <is>
-          <t>L21.C04</t>
+          <t>L20.C22</t>
         </is>
       </c>
       <c r="B247" s="3" t="inlineStr">
         <is>
-          <t>L21</t>
+          <t>L20</t>
         </is>
       </c>
       <c r="C247" s="3" t="inlineStr">
         <is>
-          <t>Ce que l'émission coûte aux banques qui l'hébergent</t>
+          <t>Ce que le droit devrait devenir</t>
         </is>
       </c>
       <c r="D247" s="3" t="inlineStr">
@@ -17310,51 +17314,51 @@
       </c>
       <c r="G247" s="3" t="inlineStr">
         <is>
-          <t>descriptif</t>
+          <t>conception</t>
         </is>
       </c>
       <c r="H247" s="3" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="I247" s="3" t="inlineStr"/>
       <c r="J247" s="3" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="K247" s="3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L247" s="3" t="inlineStr">
         <is>
-          <t>contrepartie_comptable, creation_monetaire, hierarchie_monetaire, reflux_collectif, demurrage</t>
+          <t>fenetre_de_reforme, communs, limites_planetaires, regle_contre_discretion, bareme, referentiel_de_change</t>
         </is>
       </c>
       <c r="M247" s="3" t="inlineStr">
         <is>
-          <t>L1.C07, L10.C01, L11.C02, L11.C07, L11.C09, L11.C11, L11.C23, L21.C02, L21.C03</t>
+          <t>L1.C18, L7.C12, L7.C13, L11.C15, L11.C25, L20.C01, L20.C03, L20.C06, L20.C07, L20.C08, L20.C12, L20.C13, L20.C16, L20.C17, L20.C19, L20.C20, L20.C21, L20.C23</t>
         </is>
       </c>
       <c r="N247" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-21-plomberie-financiere-mondiale/c04-ce-que-l-emission-coute-aux-banques-qui-l-hebergent.md</t>
+          <t>corpus/livre-20-droit-international-monetaire-et-commercial/c22-ce-que-le-droit-devrait-devenir.md</t>
         </is>
       </c>
     </row>
     <row r="248">
       <c r="A248" s="2" t="inlineStr">
         <is>
-          <t>L21.C05</t>
+          <t>L20.C23</t>
         </is>
       </c>
       <c r="B248" s="3" t="inlineStr">
         <is>
-          <t>L21</t>
+          <t>L20</t>
         </is>
       </c>
       <c r="C248" s="3" t="inlineStr">
         <is>
-          <t>La première infrastructure ouverte, et ce qu'elle renverse</t>
+          <t>La portée du livre</t>
         </is>
       </c>
       <c r="D248" s="3" t="inlineStr">
@@ -17374,41 +17378,41 @@
       </c>
       <c r="G248" s="3" t="inlineStr">
         <is>
-          <t>hybride</t>
+          <t>conception</t>
         </is>
       </c>
       <c r="H248" s="3" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="I248" s="3" t="inlineStr"/>
       <c r="J248" s="3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K248" s="3" t="n">
         <v>4</v>
       </c>
       <c r="L248" s="3" t="inlineStr">
         <is>
-          <t>seuil_d_activation, hierarchie_monetaire, monnaie_comme_registre, devise_cle, demurrage, contrepartie_comptable</t>
+          <t>fenetre_de_reforme, communs, limites_planetaires, creation_monetaire, robustesse</t>
         </is>
       </c>
       <c r="M248" s="3" t="inlineStr">
         <is>
-          <t>L3.C09, L5.C02, L5.C09, L11.C01, L11.C02, L11.C07, L21.C01, L21.C02, L21.C03, L21.C04</t>
+          <t>L1.C18, L1.C27, L7.C05, L7.C10, L7.C12, L7.C13, L11.C15, L11.C24, L11.C25, L20.C01, L20.C02, L20.C03, L20.C06, L20.C07, L20.C08, L20.C11, L20.C12, L20.C13, L20.C16, L20.C17, L20.C19, L20.C20, L20.C21, L20.C22</t>
         </is>
       </c>
       <c r="N248" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-21-plomberie-financiere-mondiale/c05-la-premiere-infrastructure-ouverte-et-ce-qu-elle-renverse.md</t>
+          <t>corpus/livre-20-droit-international-monetaire-et-commercial/c23-la-portee-du-livre.md</t>
         </is>
       </c>
     </row>
     <row r="249">
       <c r="A249" s="2" t="inlineStr">
         <is>
-          <t>L21.C06</t>
+          <t>L21.C01</t>
         </is>
       </c>
       <c r="B249" s="3" t="inlineStr">
@@ -17418,7 +17422,7 @@
       </c>
       <c r="C249" s="3" t="inlineStr">
         <is>
-          <t>La jambe qui reste, et ce qu'il faut pour la protéger</t>
+          <t>Ce que ce livre doit établir, et le principe qui exige des fonds propres</t>
         </is>
       </c>
       <c r="D249" s="3" t="inlineStr">
@@ -17443,7 +17447,7 @@
       </c>
       <c r="H249" s="3" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="I249" s="3" t="inlineStr"/>
@@ -17451,28 +17455,28 @@
         <v>3</v>
       </c>
       <c r="K249" s="3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L249" s="3" t="inlineStr">
         <is>
-          <t>contrepartie_comptable, hierarchie_monetaire, monnaie_comme_registre, seuil_d_activation</t>
+          <t>contrepartie_comptable, creation_monetaire, hierarchie_monetaire, monnaie_comme_registre, seuil_d_activation</t>
         </is>
       </c>
       <c r="M249" s="3" t="inlineStr">
         <is>
-          <t>L5.C02, L11.C02, L11.C11, L20.C02, L21.C02, L21.C03, L21.C05</t>
+          <t>L1.C20, L5.C02, L5.C09, L10.C01, L10.C02, L11.C02, L18.C01, L21.C01, L19.C02, L19.C06</t>
         </is>
       </c>
       <c r="N249" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-21-plomberie-financiere-mondiale/c06-la-jambe-qui-reste-et-ce-qu-il-faut-pour-la-proteger.md</t>
+          <t>corpus/livre-21-plomberie-financiere-mondiale/c01-ce-que-ce-livre-doit-etablir.md</t>
         </is>
       </c>
     </row>
     <row r="250">
       <c r="A250" s="2" t="inlineStr">
         <is>
-          <t>L21.C07</t>
+          <t>L21.C02</t>
         </is>
       </c>
       <c r="B250" s="3" t="inlineStr">
@@ -17482,7 +17486,7 @@
       </c>
       <c r="C250" s="3" t="inlineStr">
         <is>
-          <t>Portée de la tranche</t>
+          <t>Comment l'unité circulerait vraiment, et ce que chaque étape exige</t>
         </is>
       </c>
       <c r="D250" s="3" t="inlineStr">
@@ -17502,7 +17506,7 @@
       </c>
       <c r="G250" s="3" t="inlineStr">
         <is>
-          <t>descriptif</t>
+          <t>hybride</t>
         </is>
       </c>
       <c r="H250" s="3" t="inlineStr">
@@ -17512,41 +17516,41 @@
       </c>
       <c r="I250" s="3" t="inlineStr"/>
       <c r="J250" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K250" s="3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L250" s="3" t="inlineStr">
         <is>
-          <t>seuil_d_activation, contrepartie_comptable, hierarchie_monetaire, monnaie_comme_registre</t>
+          <t>monnaie_comme_registre, hierarchie_monetaire, contrepartie_comptable, devise_cle, seuil_d_activation</t>
         </is>
       </c>
       <c r="M250" s="3" t="inlineStr">
         <is>
-          <t>L5.C02, L10.C06, L11.C01, L11.C02, L20.C01, L21.C01, L21.C02, L21.C03, L21.C04, L21.C05, L21.C06</t>
+          <t>L1.C24, L3.C05, L3.C09, L5.C02, L5.C09, L10.C01, L11.C02, L21.C01</t>
         </is>
       </c>
       <c r="N250" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-21-plomberie-financiere-mondiale/c07-portee-de-la-tranche.md</t>
+          <t>corpus/livre-21-plomberie-financiere-mondiale/c02-comment-l-unite-circulerait-vraiment.md</t>
         </is>
       </c>
     </row>
     <row r="251">
       <c r="A251" s="2" t="inlineStr">
         <is>
-          <t>L22.C01</t>
+          <t>L21.C03</t>
         </is>
       </c>
       <c r="B251" s="3" t="inlineStr">
         <is>
-          <t>L22</t>
+          <t>L21</t>
         </is>
       </c>
       <c r="C251" s="3" t="inlineStr">
         <is>
-          <t>Ce que ce livre doit établir</t>
+          <t>Une opération de bout en bout, bilan par bilan</t>
         </is>
       </c>
       <c r="D251" s="3" t="inlineStr">
@@ -17566,51 +17570,51 @@
       </c>
       <c r="G251" s="3" t="inlineStr">
         <is>
-          <t>descriptif</t>
+          <t>conception</t>
         </is>
       </c>
       <c r="H251" s="3" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="I251" s="3" t="inlineStr"/>
       <c r="J251" s="3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K251" s="3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L251" s="3" t="inlineStr">
         <is>
-          <t>architecture_invisible, systeme_monetaire_et_financier, reflux_collectif, reflux_transactionnel, hierarchie_monetaire, monnaie_comme_registre</t>
+          <t>contrepartie_comptable, creation_monetaire, reflux_collectif, demurrage, monnaie_comme_registre, hierarchie_monetaire</t>
         </is>
       </c>
       <c r="M251" s="3" t="inlineStr">
         <is>
-          <t>L1.C09, L1.C19, L5.C09, L11.C02, L11.C05, L11.C09, L11.C27, L21.C03, L21.C04</t>
+          <t>L1.C07, L1.C29, L10.C06, L10.C07, L11.C01, L11.C02, L11.C11, L11.C13, L11.C23, L21.C01, L21.C02, L19.C04</t>
         </is>
       </c>
       <c r="N251" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-22-finance-non-bancaire/c01-ce-que-ce-livre-doit-etablir.md</t>
+          <t>corpus/livre-21-plomberie-financiere-mondiale/c03-une-operation-de-bout-en-bout.md</t>
         </is>
       </c>
     </row>
     <row r="252">
       <c r="A252" s="2" t="inlineStr">
         <is>
-          <t>L22.C02</t>
+          <t>L21.C04</t>
         </is>
       </c>
       <c r="B252" s="3" t="inlineStr">
         <is>
-          <t>L22</t>
+          <t>L21</t>
         </is>
       </c>
       <c r="C252" s="3" t="inlineStr">
         <is>
-          <t>Où va la monnaie émise, et pourquoi le reflux ne l'y suit pas</t>
+          <t>Ce que l'émission coûte aux banques qui l'hébergent</t>
         </is>
       </c>
       <c r="D252" s="3" t="inlineStr">
@@ -17630,51 +17634,51 @@
       </c>
       <c r="G252" s="3" t="inlineStr">
         <is>
-          <t>conception</t>
+          <t>descriptif</t>
         </is>
       </c>
       <c r="H252" s="3" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="I252" s="3" t="inlineStr"/>
       <c r="J252" s="3" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="K252" s="3" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L252" s="3" t="inlineStr">
         <is>
-          <t>reflux_transactionnel, reflux_collectif, demurrage, monnaie_endogene, architecture_invisible, hierarchie_monetaire</t>
+          <t>contrepartie_comptable, creation_monetaire, hierarchie_monetaire, reflux_collectif, demurrage</t>
         </is>
       </c>
       <c r="M252" s="3" t="inlineStr">
         <is>
-          <t>L1.C19, L5.C09, L11.C02, L11.C05, L11.C09, L11.C27, L21.C03, L22.C01, L23.C04, L26.C04</t>
+          <t>L1.C07, L10.C01, L11.C02, L11.C07, L11.C09, L11.C11, L11.C23, L21.C02, L21.C03</t>
         </is>
       </c>
       <c r="N252" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-22-finance-non-bancaire/c02-ou-va-la-monnaie-emise.md</t>
+          <t>corpus/livre-21-plomberie-financiere-mondiale/c04-ce-que-l-emission-coute-aux-banques-qui-l-hebergent.md</t>
         </is>
       </c>
     </row>
     <row r="253">
       <c r="A253" s="2" t="inlineStr">
         <is>
-          <t>L22.C03</t>
+          <t>L21.C05</t>
         </is>
       </c>
       <c r="B253" s="3" t="inlineStr">
         <is>
-          <t>L22</t>
+          <t>L21</t>
         </is>
       </c>
       <c r="C253" s="3" t="inlineStr">
         <is>
-          <t>Le barème existe déjà, et il a trois pièces que le corpus n'a pas</t>
+          <t>La première infrastructure ouverte, et ce qu'elle renverse</t>
         </is>
       </c>
       <c r="D253" s="3" t="inlineStr">
@@ -17704,41 +17708,41 @@
       </c>
       <c r="I253" s="3" t="inlineStr"/>
       <c r="J253" s="3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K253" s="3" t="n">
         <v>4</v>
       </c>
       <c r="L253" s="3" t="inlineStr">
         <is>
-          <t>qualification_regenerative, bareme, additionnalite, indicateur_de_progres, communs, plafond_ecologique</t>
+          <t>seuil_d_activation, hierarchie_monetaire, monnaie_comme_registre, devise_cle, demurrage, contrepartie_comptable</t>
         </is>
       </c>
       <c r="M253" s="3" t="inlineStr">
         <is>
-          <t>L11.C13, L11.C11, L11.C25, L12.C01, L18.C06, L22.C01, L25.C01</t>
+          <t>L3.C09, L5.C02, L5.C09, L11.C01, L11.C02, L11.C07, L21.C01, L21.C02, L21.C03, L21.C04</t>
         </is>
       </c>
       <c r="N253" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-22-finance-non-bancaire/c03-le-bareme-existe-deja.md</t>
+          <t>corpus/livre-21-plomberie-financiere-mondiale/c05-la-premiere-infrastructure-ouverte-et-ce-qu-elle-renverse.md</t>
         </is>
       </c>
     </row>
     <row r="254">
       <c r="A254" s="2" t="inlineStr">
         <is>
-          <t>L22.C04</t>
+          <t>L21.C06</t>
         </is>
       </c>
       <c r="B254" s="3" t="inlineStr">
         <is>
-          <t>L22</t>
+          <t>L21</t>
         </is>
       </c>
       <c r="C254" s="3" t="inlineStr">
         <is>
-          <t>Les critères réels ne mesurent pas, ils certifient</t>
+          <t>La jambe qui reste, et ce qu'il faut pour la protéger</t>
         </is>
       </c>
       <c r="D254" s="3" t="inlineStr">
@@ -17768,41 +17772,41 @@
       </c>
       <c r="I254" s="3" t="inlineStr"/>
       <c r="J254" s="3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K254" s="3" t="n">
         <v>4</v>
       </c>
       <c r="L254" s="3" t="inlineStr">
         <is>
-          <t>qualification_regenerative, bareme, additionnalite, communs, valorisation_des_communs, indicateur_de_progres</t>
+          <t>contrepartie_comptable, hierarchie_monetaire, monnaie_comme_registre, seuil_d_activation</t>
         </is>
       </c>
       <c r="M254" s="3" t="inlineStr">
         <is>
-          <t>L6.C06, L11.C13, L11.C16, L11.C25, L13.C01, L14.C01, L18.C06, L22.C03</t>
+          <t>L5.C02, L11.C02, L11.C11, L20.C02, L21.C02, L21.C03, L21.C05</t>
         </is>
       </c>
       <c r="N254" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-22-finance-non-bancaire/c04-les-criteres-reels-ne-mesurent-pas.md</t>
+          <t>corpus/livre-21-plomberie-financiere-mondiale/c06-la-jambe-qui-reste-et-ce-qu-il-faut-pour-la-proteger.md</t>
         </is>
       </c>
     </row>
     <row r="255">
       <c r="A255" s="2" t="inlineStr">
         <is>
-          <t>L22.C05</t>
+          <t>L21.C07</t>
         </is>
       </c>
       <c r="B255" s="3" t="inlineStr">
         <is>
-          <t>L22</t>
+          <t>L21</t>
         </is>
       </c>
       <c r="C255" s="3" t="inlineStr">
         <is>
-          <t>L'épargne retraite, et le dilemme du troisième instrument</t>
+          <t>Portée de la tranche</t>
         </is>
       </c>
       <c r="D255" s="3" t="inlineStr">
@@ -17822,7 +17826,7 @@
       </c>
       <c r="G255" s="3" t="inlineStr">
         <is>
-          <t>hybride</t>
+          <t>descriptif</t>
         </is>
       </c>
       <c r="H255" s="3" t="inlineStr">
@@ -17832,31 +17836,31 @@
       </c>
       <c r="I255" s="3" t="inlineStr"/>
       <c r="J255" s="3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K255" s="3" t="n">
         <v>4</v>
       </c>
       <c r="L255" s="3" t="inlineStr">
         <is>
-          <t>reflux_collectif, demurrage, essentiel_insolvable, plancher_social, solvabilite_anticipee, architecture_invisible</t>
+          <t>seuil_d_activation, contrepartie_comptable, hierarchie_monetaire, monnaie_comme_registre</t>
         </is>
       </c>
       <c r="M255" s="3" t="inlineStr">
         <is>
-          <t>L1.C15, L11.C07, L11.C09, L11.C18, L22.C01, L22.C02, L25.C01</t>
+          <t>L5.C02, L10.C06, L11.C01, L11.C02, L20.C01, L21.C01, L21.C02, L21.C03, L21.C04, L21.C05, L21.C06</t>
         </is>
       </c>
       <c r="N255" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-22-finance-non-bancaire/c05-l-epargne-retraite-et-le-dilemme-du-troisieme-instrument.md</t>
+          <t>corpus/livre-21-plomberie-financiere-mondiale/c07-portee-de-la-tranche.md</t>
         </is>
       </c>
     </row>
     <row r="256">
       <c r="A256" s="2" t="inlineStr">
         <is>
-          <t>L22.C06</t>
+          <t>L22.C01</t>
         </is>
       </c>
       <c r="B256" s="3" t="inlineStr">
@@ -17866,7 +17870,7 @@
       </c>
       <c r="C256" s="3" t="inlineStr">
         <is>
-          <t>Qui décide, quand personne ne décide</t>
+          <t>Ce que ce livre doit établir</t>
         </is>
       </c>
       <c r="D256" s="3" t="inlineStr">
@@ -17886,7 +17890,7 @@
       </c>
       <c r="G256" s="3" t="inlineStr">
         <is>
-          <t>hybride</t>
+          <t>descriptif</t>
         </is>
       </c>
       <c r="H256" s="3" t="inlineStr">
@@ -17903,24 +17907,24 @@
       </c>
       <c r="L256" s="3" t="inlineStr">
         <is>
-          <t>architecture_invisible, indicateur_de_progres, qualification_regenerative, essentiel_insolvable, fenetre_de_reforme, regle_contre_discretion</t>
+          <t>architecture_invisible, systeme_monetaire_et_financier, reflux_collectif, reflux_transactionnel, hierarchie_monetaire, monnaie_comme_registre</t>
         </is>
       </c>
       <c r="M256" s="3" t="inlineStr">
         <is>
-          <t>L1.C15, L5.C09, L11.C13, L14.C01, L22.C01, L22.C02, L22.C03, L22.C05</t>
+          <t>L1.C09, L1.C19, L5.C09, L11.C02, L11.C05, L11.C09, L11.C27, L21.C03, L21.C04</t>
         </is>
       </c>
       <c r="N256" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-22-finance-non-bancaire/c06-qui-decide-quand-personne-ne-decide.md</t>
+          <t>corpus/livre-22-finance-non-bancaire/c01-ce-que-ce-livre-doit-etablir.md</t>
         </is>
       </c>
     </row>
     <row r="257">
       <c r="A257" s="2" t="inlineStr">
         <is>
-          <t>L22.C07</t>
+          <t>L22.C02</t>
         </is>
       </c>
       <c r="B257" s="3" t="inlineStr">
@@ -17930,7 +17934,7 @@
       </c>
       <c r="C257" s="3" t="inlineStr">
         <is>
-          <t>Portée de la tranche</t>
+          <t>Où va la monnaie émise, et pourquoi le reflux ne l'y suit pas</t>
         </is>
       </c>
       <c r="D257" s="3" t="inlineStr">
@@ -17950,51 +17954,51 @@
       </c>
       <c r="G257" s="3" t="inlineStr">
         <is>
-          <t>descriptif</t>
+          <t>conception</t>
         </is>
       </c>
       <c r="H257" s="3" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="I257" s="3" t="inlineStr"/>
       <c r="J257" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K257" s="3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L257" s="3" t="inlineStr">
         <is>
-          <t>architecture_invisible, reflux_transactionnel, qualification_regenerative, bareme, essentiel_insolvable</t>
+          <t>reflux_transactionnel, reflux_collectif, demurrage, monnaie_endogene, architecture_invisible, hierarchie_monetaire</t>
         </is>
       </c>
       <c r="M257" s="3" t="inlineStr">
         <is>
-          <t>L1.C15, L5.C09, L11.C02, L11.C13, L11.C18, L22.C01, L22.C02, L22.C03, L22.C04, L22.C05, L22.C06</t>
+          <t>L1.C19, L5.C09, L11.C02, L11.C05, L11.C09, L11.C27, L21.C03, L22.C01, L23.C04, L26.C04</t>
         </is>
       </c>
       <c r="N257" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-22-finance-non-bancaire/c07-portee-de-la-tranche.md</t>
+          <t>corpus/livre-22-finance-non-bancaire/c02-ou-va-la-monnaie-emise.md</t>
         </is>
       </c>
     </row>
     <row r="258">
       <c r="A258" s="2" t="inlineStr">
         <is>
-          <t>L23.C01</t>
+          <t>L22.C03</t>
         </is>
       </c>
       <c r="B258" s="3" t="inlineStr">
         <is>
-          <t>L23</t>
+          <t>L22</t>
         </is>
       </c>
       <c r="C258" s="3" t="inlineStr">
         <is>
-          <t>Ce que ce livre doit établir</t>
+          <t>Le barème existe déjà, et il a trois pièces que le corpus n'a pas</t>
         </is>
       </c>
       <c r="D258" s="3" t="inlineStr">
@@ -18014,7 +18018,7 @@
       </c>
       <c r="G258" s="3" t="inlineStr">
         <is>
-          <t>conception</t>
+          <t>hybride</t>
         </is>
       </c>
       <c r="H258" s="3" t="inlineStr">
@@ -18027,38 +18031,38 @@
         <v>4</v>
       </c>
       <c r="K258" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L258" s="3" t="inlineStr">
         <is>
-          <t>bareme, reflux_transactionnel, externalisation, essentiel_insolvable, polycentricite, regle_contre_discretion</t>
+          <t>qualification_regenerative, bareme, additionnalite, indicateur_de_progres, communs, plafond_ecologique</t>
         </is>
       </c>
       <c r="M258" s="3" t="inlineStr">
         <is>
-          <t>L1.C15, L5.C07, L10.C06, L11.C05, L11.C09, L11.C21, L11.C24, L18.C09, L20.C02, L20.C20</t>
+          <t>L11.C13, L11.C11, L11.C25, L12.C01, L18.C06, L22.C01, L25.C01</t>
         </is>
       </c>
       <c r="N258" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-23-fiscalite-mondiale-et-opacite/c01-ce-que-ce-livre-doit-etablir.md</t>
+          <t>corpus/livre-22-finance-non-bancaire/c03-le-bareme-existe-deja.md</t>
         </is>
       </c>
     </row>
     <row r="259">
       <c r="A259" s="2" t="inlineStr">
         <is>
-          <t>L23.C02</t>
+          <t>L22.C04</t>
         </is>
       </c>
       <c r="B259" s="3" t="inlineStr">
         <is>
-          <t>L23</t>
+          <t>L22</t>
         </is>
       </c>
       <c r="C259" s="3" t="inlineStr">
         <is>
-          <t>La compétence que la convention ne crée pas, et le vote qu'elle a gagné</t>
+          <t>Les critères réels ne mesurent pas, ils certifient</t>
         </is>
       </c>
       <c r="D259" s="3" t="inlineStr">
@@ -18091,38 +18095,38 @@
         <v>4</v>
       </c>
       <c r="K259" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L259" s="3" t="inlineStr">
         <is>
-          <t>polycentricite, bareme, reflux_transactionnel, seuil_d_activation, regle_contre_discretion, externalisation</t>
+          <t>qualification_regenerative, bareme, additionnalite, communs, valorisation_des_communs, indicateur_de_progres</t>
         </is>
       </c>
       <c r="M259" s="3" t="inlineStr">
         <is>
-          <t>L1.C25, L5.C04, L10.C06, L11.C21, L20.C02, L20.C20, L23.C01</t>
+          <t>L6.C06, L11.C13, L11.C16, L11.C25, L13.C01, L14.C01, L18.C06, L22.C03</t>
         </is>
       </c>
       <c r="N259" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-23-fiscalite-mondiale-et-opacite/c02-la-competence-que-la-convention-ne-cree-pas.md</t>
+          <t>corpus/livre-22-finance-non-bancaire/c04-les-criteres-reels-ne-mesurent-pas.md</t>
         </is>
       </c>
     </row>
     <row r="260">
       <c r="A260" s="2" t="inlineStr">
         <is>
-          <t>L23.C03</t>
+          <t>L22.C05</t>
         </is>
       </c>
       <c r="B260" s="3" t="inlineStr">
         <is>
-          <t>L23</t>
+          <t>L22</t>
         </is>
       </c>
       <c r="C260" s="3" t="inlineStr">
         <is>
-          <t>F8 appliqué à une négociation en cours, et le résultat n'est pas le désarmement</t>
+          <t>L'épargne retraite, et le dilemme du troisième instrument</t>
         </is>
       </c>
       <c r="D260" s="3" t="inlineStr">
@@ -18152,41 +18156,41 @@
       </c>
       <c r="I260" s="3" t="inlineStr"/>
       <c r="J260" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="K260" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="K260" s="3" t="n">
-        <v>3</v>
-      </c>
       <c r="L260" s="3" t="inlineStr">
         <is>
-          <t>regle_contre_discretion, polycentricite, seuil_d_activation, bareme, externalisation</t>
+          <t>reflux_collectif, demurrage, essentiel_insolvable, plancher_social, solvabilite_anticipee, architecture_invisible</t>
         </is>
       </c>
       <c r="M260" s="3" t="inlineStr">
         <is>
-          <t>L5.C04, L6.C09, L11.C21, L20.C02, L20.C13, L23.C01, L23.C02</t>
+          <t>L1.C15, L11.C07, L11.C09, L11.C18, L22.C01, L22.C02, L25.C01</t>
         </is>
       </c>
       <c r="N260" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-23-fiscalite-mondiale-et-opacite/c03-f8-applique-a-une-negociation-en-cours.md</t>
+          <t>corpus/livre-22-finance-non-bancaire/c05-l-epargne-retraite-et-le-dilemme-du-troisieme-instrument.md</t>
         </is>
       </c>
     </row>
     <row r="261">
       <c r="A261" s="2" t="inlineStr">
         <is>
-          <t>L23.C04</t>
+          <t>L22.C06</t>
         </is>
       </c>
       <c r="B261" s="3" t="inlineStr">
         <is>
-          <t>L23</t>
+          <t>L22</t>
         </is>
       </c>
       <c r="C261" s="3" t="inlineStr">
         <is>
-          <t>La transparence que le corpus supposait a été invalidée</t>
+          <t>Qui décide, quand personne ne décide</t>
         </is>
       </c>
       <c r="D261" s="3" t="inlineStr">
@@ -18216,41 +18220,41 @@
       </c>
       <c r="I261" s="3" t="inlineStr"/>
       <c r="J261" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K261" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L261" s="3" t="inlineStr">
         <is>
-          <t>regle_contre_discretion, externalisation, bareme, polycentricite, architecture_invisible</t>
+          <t>architecture_invisible, indicateur_de_progres, qualification_regenerative, essentiel_insolvable, fenetre_de_reforme, regle_contre_discretion</t>
         </is>
       </c>
       <c r="M261" s="3" t="inlineStr">
         <is>
-          <t>L6.C09, L11.C13, L11.C25, L20.C20, L23.C01, L23.C02, L23.C03</t>
+          <t>L1.C15, L5.C09, L11.C13, L14.C01, L22.C01, L22.C02, L22.C03, L22.C05</t>
         </is>
       </c>
       <c r="N261" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-23-fiscalite-mondiale-et-opacite/c04-la-transparence-que-le-corpus-supposait-a-ete-invalidee.md</t>
+          <t>corpus/livre-22-finance-non-bancaire/c06-qui-decide-quand-personne-ne-decide.md</t>
         </is>
       </c>
     </row>
     <row r="262">
       <c r="A262" s="2" t="inlineStr">
         <is>
-          <t>L23.C05</t>
+          <t>L22.C07</t>
         </is>
       </c>
       <c r="B262" s="3" t="inlineStr">
         <is>
-          <t>L23</t>
+          <t>L22</t>
         </is>
       </c>
       <c r="C262" s="3" t="inlineStr">
         <is>
-          <t>Intéresser le percepteur, et ce que le taux révèle</t>
+          <t>Portée de la tranche</t>
         </is>
       </c>
       <c r="D262" s="3" t="inlineStr">
@@ -18270,7 +18274,7 @@
       </c>
       <c r="G262" s="3" t="inlineStr">
         <is>
-          <t>hybride</t>
+          <t>descriptif</t>
         </is>
       </c>
       <c r="H262" s="3" t="inlineStr">
@@ -18280,31 +18284,31 @@
       </c>
       <c r="I262" s="3" t="inlineStr"/>
       <c r="J262" s="3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K262" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L262" s="3" t="inlineStr">
         <is>
-          <t>bareme, reflux_transactionnel, regle_contre_discretion, polycentricite, seuil_d_activation</t>
+          <t>architecture_invisible, reflux_transactionnel, qualification_regenerative, bareme, essentiel_insolvable</t>
         </is>
       </c>
       <c r="M262" s="3" t="inlineStr">
         <is>
-          <t>L11.C21, L11.C24, L18.C09, L20.C20, L23.C01, L23.C02, L23.C03</t>
+          <t>L1.C15, L5.C09, L11.C02, L11.C13, L11.C18, L22.C01, L22.C02, L22.C03, L22.C04, L22.C05, L22.C06</t>
         </is>
       </c>
       <c r="N262" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-23-fiscalite-mondiale-et-opacite/c05-interesser-le-percepteur-et-ce-que-le-taux-revele.md</t>
+          <t>corpus/livre-22-finance-non-bancaire/c07-portee-de-la-tranche.md</t>
         </is>
       </c>
     </row>
     <row r="263">
       <c r="A263" s="2" t="inlineStr">
         <is>
-          <t>L23.C06</t>
+          <t>L23.C01</t>
         </is>
       </c>
       <c r="B263" s="3" t="inlineStr">
@@ -18314,7 +18318,7 @@
       </c>
       <c r="C263" s="3" t="inlineStr">
         <is>
-          <t>L'arbre appliqué à la fonte, et il ne reste que deux branches</t>
+          <t>Ce que ce livre doit établir</t>
         </is>
       </c>
       <c r="D263" s="3" t="inlineStr">
@@ -18351,24 +18355,24 @@
       </c>
       <c r="L263" s="3" t="inlineStr">
         <is>
-          <t>bareme, reflux_transactionnel, monnaie_fondante, demurrage, regle_contre_discretion, essentiel_insolvable</t>
+          <t>bareme, reflux_transactionnel, externalisation, essentiel_insolvable, polycentricite, regle_contre_discretion</t>
         </is>
       </c>
       <c r="M263" s="3" t="inlineStr">
         <is>
-          <t>L10.C06, L11.C05, L11.C09, L11.C21, L11.C24, L18.C09, L20.C02, L23.C01, L23.C02, L23.C03, L23.C04, L23.C05</t>
+          <t>L1.C15, L5.C07, L10.C06, L11.C05, L11.C09, L11.C21, L11.C24, L18.C09, L20.C02, L20.C20</t>
         </is>
       </c>
       <c r="N263" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-23-fiscalite-mondiale-et-opacite/c06-l-arbre-applique-a-la-fonte.md</t>
+          <t>corpus/livre-23-fiscalite-mondiale-et-opacite/c01-ce-que-ce-livre-doit-etablir.md</t>
         </is>
       </c>
     </row>
     <row r="264">
       <c r="A264" s="2" t="inlineStr">
         <is>
-          <t>L23.C07</t>
+          <t>L23.C02</t>
         </is>
       </c>
       <c r="B264" s="3" t="inlineStr">
@@ -18378,7 +18382,7 @@
       </c>
       <c r="C264" s="3" t="inlineStr">
         <is>
-          <t>Portée de la tranche, et la moitié qui n'est pas commencée</t>
+          <t>La compétence que la convention ne crée pas, et le vote qu'elle a gagné</t>
         </is>
       </c>
       <c r="D264" s="3" t="inlineStr">
@@ -18398,7 +18402,7 @@
       </c>
       <c r="G264" s="3" t="inlineStr">
         <is>
-          <t>conception</t>
+          <t>hybride</t>
         </is>
       </c>
       <c r="H264" s="3" t="inlineStr">
@@ -18408,41 +18412,41 @@
       </c>
       <c r="I264" s="3" t="inlineStr"/>
       <c r="J264" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K264" s="3" t="n">
         <v>3</v>
       </c>
       <c r="L264" s="3" t="inlineStr">
         <is>
-          <t>bareme, reflux_transactionnel, externalisation, regle_contre_discretion, polycentricite, essentiel_insolvable</t>
+          <t>polycentricite, bareme, reflux_transactionnel, seuil_d_activation, regle_contre_discretion, externalisation</t>
         </is>
       </c>
       <c r="M264" s="3" t="inlineStr">
         <is>
-          <t>L10.C06, L11.C05, L11.C21, L11.C25, L18.C09, L20.C20, L23.C01, L23.C02, L23.C03, L23.C04, L23.C05, L23.C06</t>
+          <t>L1.C25, L5.C04, L10.C06, L11.C21, L20.C02, L20.C20, L23.C01</t>
         </is>
       </c>
       <c r="N264" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-23-fiscalite-mondiale-et-opacite/c07-portee-de-la-tranche.md</t>
+          <t>corpus/livre-23-fiscalite-mondiale-et-opacite/c02-la-competence-que-la-convention-ne-cree-pas.md</t>
         </is>
       </c>
     </row>
     <row r="265">
       <c r="A265" s="2" t="inlineStr">
         <is>
-          <t>L24.C01</t>
+          <t>L23.C03</t>
         </is>
       </c>
       <c r="B265" s="3" t="inlineStr">
         <is>
-          <t>L24</t>
+          <t>L23</t>
         </is>
       </c>
       <c r="C265" s="3" t="inlineStr">
         <is>
-          <t>Ce que ce livre doit établir</t>
+          <t>F8 appliqué à une négociation en cours, et le résultat n'est pas le désarmement</t>
         </is>
       </c>
       <c r="D265" s="3" t="inlineStr">
@@ -18462,7 +18466,7 @@
       </c>
       <c r="G265" s="3" t="inlineStr">
         <is>
-          <t>descriptif</t>
+          <t>hybride</t>
         </is>
       </c>
       <c r="H265" s="3" t="inlineStr">
@@ -18475,38 +18479,38 @@
         <v>4</v>
       </c>
       <c r="K265" s="3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L265" s="3" t="inlineStr">
         <is>
-          <t>limites_planetaires, plafond_ecologique, entropie, decouplage, degeneratif, qualification_regenerative, essentiel_insolvable</t>
+          <t>regle_contre_discretion, polycentricite, seuil_d_activation, bareme, externalisation</t>
         </is>
       </c>
       <c r="M265" s="3" t="inlineStr">
         <is>
-          <t>L1.C15, L5.C08, L11.C13, L18.C01, L18.C04, L22.C04, L26.C01</t>
+          <t>L5.C04, L6.C09, L11.C21, L20.C02, L20.C13, L23.C01, L23.C02</t>
         </is>
       </c>
       <c r="N265" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-24-conditions-materielles-de-la-vie/c01-ce-que-ce-livre-doit-etablir.md</t>
+          <t>corpus/livre-23-fiscalite-mondiale-et-opacite/c03-f8-applique-a-une-negociation-en-cours.md</t>
         </is>
       </c>
     </row>
     <row r="266">
       <c r="A266" s="2" t="inlineStr">
         <is>
-          <t>L24.C02</t>
+          <t>L23.C04</t>
         </is>
       </c>
       <c r="B266" s="3" t="inlineStr">
         <is>
-          <t>L24</t>
+          <t>L23</t>
         </is>
       </c>
       <c r="C266" s="3" t="inlineStr">
         <is>
-          <t>Le seuil juste est plus strict que le seuil sûr</t>
+          <t>La transparence que le corpus supposait a été invalidée</t>
         </is>
       </c>
       <c r="D266" s="3" t="inlineStr">
@@ -18536,41 +18540,41 @@
       </c>
       <c r="I266" s="3" t="inlineStr"/>
       <c r="J266" s="3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K266" s="3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L266" s="3" t="inlineStr">
         <is>
-          <t>limites_planetaires, plafond_ecologique, plancher_social, dette_ecologique, essentiel_insolvable, qualification_regenerative</t>
+          <t>regle_contre_discretion, externalisation, bareme, polycentricite, architecture_invisible</t>
         </is>
       </c>
       <c r="M266" s="3" t="inlineStr">
         <is>
-          <t>L1.C15, L11.C13, L12.C01, L18.C01, L24.C01, L25.C01</t>
+          <t>L6.C09, L11.C13, L11.C25, L20.C20, L23.C01, L23.C02, L23.C03</t>
         </is>
       </c>
       <c r="N266" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-24-conditions-materielles-de-la-vie/c02-le-seuil-juste-est-plus-strict-que-le-seuil-sur.md</t>
+          <t>corpus/livre-23-fiscalite-mondiale-et-opacite/c04-la-transparence-que-le-corpus-supposait-a-ete-invalidee.md</t>
         </is>
       </c>
     </row>
     <row r="267">
       <c r="A267" s="2" t="inlineStr">
         <is>
-          <t>L24.C03</t>
+          <t>L23.C05</t>
         </is>
       </c>
       <c r="B267" s="3" t="inlineStr">
         <is>
-          <t>L24</t>
+          <t>L23</t>
         </is>
       </c>
       <c r="C267" s="3" t="inlineStr">
         <is>
-          <t>La matière, et le levier commun que les neuf dimensions n'avaient pas</t>
+          <t>Intéresser le percepteur, et ce que le taux révèle</t>
         </is>
       </c>
       <c r="D267" s="3" t="inlineStr">
@@ -18600,41 +18604,41 @@
       </c>
       <c r="I267" s="3" t="inlineStr"/>
       <c r="J267" s="3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K267" s="3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L267" s="3" t="inlineStr">
         <is>
-          <t>limites_planetaires, decouplage, effet_rebond, sobriete, entropie, plafond_ecologique, externalisation, degeneratif</t>
+          <t>bareme, reflux_transactionnel, regle_contre_discretion, polycentricite, seuil_d_activation</t>
         </is>
       </c>
       <c r="M267" s="3" t="inlineStr">
         <is>
-          <t>L1.C15, L11.C13, L17.C01, L18.C04, L24.C01, L24.C02, L26.C01</t>
+          <t>L11.C21, L11.C24, L18.C09, L20.C20, L23.C01, L23.C02, L23.C03</t>
         </is>
       </c>
       <c r="N267" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-24-conditions-materielles-de-la-vie/c03-la-matiere-et-le-levier-commun.md</t>
+          <t>corpus/livre-23-fiscalite-mondiale-et-opacite/c05-interesser-le-percepteur-et-ce-que-le-taux-revele.md</t>
         </is>
       </c>
     </row>
     <row r="268">
       <c r="A268" s="2" t="inlineStr">
         <is>
-          <t>L24.C04</t>
+          <t>L23.C06</t>
         </is>
       </c>
       <c r="B268" s="3" t="inlineStr">
         <is>
-          <t>L24</t>
+          <t>L23</t>
         </is>
       </c>
       <c r="C268" s="3" t="inlineStr">
         <is>
-          <t>Un budget mondial n'est pas partageable</t>
+          <t>L'arbre appliqué à la fonte, et il ne reste que deux branches</t>
         </is>
       </c>
       <c r="D268" s="3" t="inlineStr">
@@ -18654,7 +18658,7 @@
       </c>
       <c r="G268" s="3" t="inlineStr">
         <is>
-          <t>hybride</t>
+          <t>conception</t>
         </is>
       </c>
       <c r="H268" s="3" t="inlineStr">
@@ -18667,38 +18671,38 @@
         <v>4</v>
       </c>
       <c r="K268" s="3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L268" s="3" t="inlineStr">
         <is>
-          <t>limites_planetaires, plafond_ecologique, communs, qualification_regenerative, externalisation, polycentricite</t>
+          <t>bareme, reflux_transactionnel, monnaie_fondante, demurrage, regle_contre_discretion, essentiel_insolvable</t>
         </is>
       </c>
       <c r="M268" s="3" t="inlineStr">
         <is>
-          <t>L11.C13, L11.C24, L22.C04, L24.C01, L24.C02, L24.C03, L25.C05</t>
+          <t>L10.C06, L11.C05, L11.C09, L11.C21, L11.C24, L18.C09, L20.C02, L23.C01, L23.C02, L23.C03, L23.C04, L23.C05</t>
         </is>
       </c>
       <c r="N268" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-24-conditions-materielles-de-la-vie/c04-un-budget-mondial-n-est-pas-partageable.md</t>
+          <t>corpus/livre-23-fiscalite-mondiale-et-opacite/c06-l-arbre-applique-a-la-fonte.md</t>
         </is>
       </c>
     </row>
     <row r="269">
       <c r="A269" s="2" t="inlineStr">
         <is>
-          <t>L24.C05</t>
+          <t>L23.C07</t>
         </is>
       </c>
       <c r="B269" s="3" t="inlineStr">
         <is>
-          <t>L24</t>
+          <t>L23</t>
         </is>
       </c>
       <c r="C269" s="3" t="inlineStr">
         <is>
-          <t>Portée de la tranche</t>
+          <t>Portée de la tranche, et la moitié qui n'est pas commencée</t>
         </is>
       </c>
       <c r="D269" s="3" t="inlineStr">
@@ -18718,46 +18722,46 @@
       </c>
       <c r="G269" s="3" t="inlineStr">
         <is>
-          <t>descriptif</t>
+          <t>conception</t>
         </is>
       </c>
       <c r="H269" s="3" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="I269" s="3" t="inlineStr"/>
       <c r="J269" s="3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K269" s="3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L269" s="3" t="inlineStr">
         <is>
-          <t>limites_planetaires, plafond_ecologique, plancher_social, decouplage, qualification_regenerative, entropie</t>
+          <t>bareme, reflux_transactionnel, externalisation, regle_contre_discretion, polycentricite, essentiel_insolvable</t>
         </is>
       </c>
       <c r="M269" s="3" t="inlineStr">
         <is>
-          <t>L11.C13, L11.C24, L18.C01, L22.C04, L24.C01, L24.C02, L24.C03, L24.C04, L25.C05, L26.C01, L26.C02</t>
+          <t>L10.C06, L11.C05, L11.C21, L11.C25, L18.C09, L20.C20, L23.C01, L23.C02, L23.C03, L23.C04, L23.C05, L23.C06</t>
         </is>
       </c>
       <c r="N269" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-24-conditions-materielles-de-la-vie/c05-portee-de-la-tranche.md</t>
+          <t>corpus/livre-23-fiscalite-mondiale-et-opacite/c07-portee-de-la-tranche.md</t>
         </is>
       </c>
     </row>
     <row r="270">
       <c r="A270" s="2" t="inlineStr">
         <is>
-          <t>L25.C01</t>
+          <t>L24.C01</t>
         </is>
       </c>
       <c r="B270" s="3" t="inlineStr">
         <is>
-          <t>L25</t>
+          <t>L24</t>
         </is>
       </c>
       <c r="C270" s="3" t="inlineStr">
@@ -18799,34 +18803,34 @@
       </c>
       <c r="L270" s="3" t="inlineStr">
         <is>
-          <t>plancher_social, plafond_ecologique, essentiel_insolvable, dette_ecologique, communs, solvabilite_anticipee</t>
+          <t>limites_planetaires, plafond_ecologique, entropie, decouplage, degeneratif, qualification_regenerative, essentiel_insolvable</t>
         </is>
       </c>
       <c r="M270" s="3" t="inlineStr">
         <is>
-          <t>L1.C15, L11.C09, L11.C18, L12.C01, L24.C01, L24.C02, L24.C03</t>
+          <t>L1.C15, L5.C08, L11.C13, L18.C01, L18.C04, L22.C04, L26.C01</t>
         </is>
       </c>
       <c r="N270" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-25-repartition-et-justice-sociale/c01-ce-que-ce-livre-doit-etablir.md</t>
+          <t>corpus/livre-24-conditions-materielles-de-la-vie/c01-ce-que-ce-livre-doit-etablir.md</t>
         </is>
       </c>
     </row>
     <row r="271">
       <c r="A271" s="2" t="inlineStr">
         <is>
-          <t>L25.C02</t>
+          <t>L24.C02</t>
         </is>
       </c>
       <c r="B271" s="3" t="inlineStr">
         <is>
-          <t>L25</t>
+          <t>L24</t>
         </is>
       </c>
       <c r="C271" s="3" t="inlineStr">
         <is>
-          <t>Le noyau dur, et la charge de la preuve renversée</t>
+          <t>Le seuil juste est plus strict que le seuil sûr</t>
         </is>
       </c>
       <c r="D271" s="3" t="inlineStr">
@@ -18863,34 +18867,34 @@
       </c>
       <c r="L271" s="3" t="inlineStr">
         <is>
-          <t>plancher_social, essentiel_insolvable, plafond_ecologique, solvabilite_anticipee, regle_contre_discretion</t>
+          <t>limites_planetaires, plafond_ecologique, plancher_social, dette_ecologique, essentiel_insolvable, qualification_regenerative</t>
         </is>
       </c>
       <c r="M271" s="3" t="inlineStr">
         <is>
-          <t>L1.C15, L11.C09, L11.C18, L22.C02, L22.C04, L24.C02, L25.C01</t>
+          <t>L1.C15, L11.C13, L12.C01, L18.C01, L24.C01, L25.C01</t>
         </is>
       </c>
       <c r="N271" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-25-repartition-et-justice-sociale/c02-le-noyau-dur-et-la-charge-de-la-preuve.md</t>
+          <t>corpus/livre-24-conditions-materielles-de-la-vie/c02-le-seuil-juste-est-plus-strict-que-le-seuil-sur.md</t>
         </is>
       </c>
     </row>
     <row r="272">
       <c r="A272" s="2" t="inlineStr">
         <is>
-          <t>L25.C03</t>
+          <t>L24.C03</t>
         </is>
       </c>
       <c r="B272" s="3" t="inlineStr">
         <is>
-          <t>L25</t>
+          <t>L24</t>
         </is>
       </c>
       <c r="C272" s="3" t="inlineStr">
         <is>
-          <t>Ce que le droit oblige à donner, et ce qu'il refuse de réparer</t>
+          <t>La matière, et le levier commun que les neuf dimensions n'avaient pas</t>
         </is>
       </c>
       <c r="D272" s="3" t="inlineStr">
@@ -18920,41 +18924,41 @@
       </c>
       <c r="I272" s="3" t="inlineStr"/>
       <c r="J272" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K272" s="3" t="n">
         <v>4</v>
       </c>
       <c r="L272" s="3" t="inlineStr">
         <is>
-          <t>dette_ecologique, plancher_social, creation_monetaire, reflux_collectif, essentiel_insolvable, solvabilite_anticipee</t>
+          <t>limites_planetaires, decouplage, effet_rebond, sobriete, entropie, plafond_ecologique, externalisation, degeneratif</t>
         </is>
       </c>
       <c r="M272" s="3" t="inlineStr">
         <is>
-          <t>L1.C20, L11.C01, L20.C01, L24.C02, L25.C01, L25.C02</t>
+          <t>L1.C15, L11.C13, L17.C01, L18.C04, L24.C01, L24.C02, L26.C01</t>
         </is>
       </c>
       <c r="N272" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-25-repartition-et-justice-sociale/c03-ce-que-le-droit-oblige-a-donner.md</t>
+          <t>corpus/livre-24-conditions-materielles-de-la-vie/c03-la-matiere-et-le-levier-commun.md</t>
         </is>
       </c>
     </row>
     <row r="273">
       <c r="A273" s="2" t="inlineStr">
         <is>
-          <t>L25.C04</t>
+          <t>L24.C04</t>
         </is>
       </c>
       <c r="B273" s="3" t="inlineStr">
         <is>
-          <t>L25</t>
+          <t>L24</t>
         </is>
       </c>
       <c r="C273" s="3" t="inlineStr">
         <is>
-          <t>A34 en droit positif, et le critère que le corpus n'avait pas</t>
+          <t>Un budget mondial n'est pas partageable</t>
         </is>
       </c>
       <c r="D273" s="3" t="inlineStr">
@@ -18991,34 +18995,34 @@
       </c>
       <c r="L273" s="3" t="inlineStr">
         <is>
-          <t>plancher_social, bareme, essentiel_insolvable, sobriete, affectation_des_instruments, reflux_transactionnel</t>
+          <t>limites_planetaires, plafond_ecologique, communs, qualification_regenerative, externalisation, polycentricite</t>
         </is>
       </c>
       <c r="M273" s="3" t="inlineStr">
         <is>
-          <t>L1.C15, L11.C09, L11.C18, L11.C21, L22.C02, L24.C03, L25.C01, L25.C02</t>
+          <t>L11.C13, L11.C24, L22.C04, L24.C01, L24.C02, L24.C03, L25.C05</t>
         </is>
       </c>
       <c r="N273" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-25-repartition-et-justice-sociale/c04-a34-en-droit-positif.md</t>
+          <t>corpus/livre-24-conditions-materielles-de-la-vie/c04-un-budget-mondial-n-est-pas-partageable.md</t>
         </is>
       </c>
     </row>
     <row r="274">
       <c r="A274" s="2" t="inlineStr">
         <is>
-          <t>L25.C05</t>
+          <t>L24.C05</t>
         </is>
       </c>
       <c r="B274" s="3" t="inlineStr">
         <is>
-          <t>L25</t>
+          <t>L24</t>
         </is>
       </c>
       <c r="C274" s="3" t="inlineStr">
         <is>
-          <t>Le droit différencie sans calculer</t>
+          <t>Portée de la tranche</t>
         </is>
       </c>
       <c r="D274" s="3" t="inlineStr">
@@ -19038,41 +19042,41 @@
       </c>
       <c r="G274" s="3" t="inlineStr">
         <is>
-          <t>hybride</t>
+          <t>descriptif</t>
         </is>
       </c>
       <c r="H274" s="3" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="I274" s="3" t="inlineStr"/>
       <c r="J274" s="3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K274" s="3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L274" s="3" t="inlineStr">
         <is>
-          <t>dette_ecologique, plancher_social, plafond_ecologique, bareme, indicateur_de_progres, polycentricite</t>
+          <t>limites_planetaires, plafond_ecologique, plancher_social, decouplage, qualification_regenerative, entropie</t>
         </is>
       </c>
       <c r="M274" s="3" t="inlineStr">
         <is>
-          <t>L11.C13, L22.C04, L22.C06, L24.C01, L24.C02, L25.C01, L25.C02, L25.C03, L25.C04</t>
+          <t>L11.C13, L11.C24, L18.C01, L22.C04, L24.C01, L24.C02, L24.C03, L24.C04, L25.C05, L26.C01, L26.C02, L17.C05</t>
         </is>
       </c>
       <c r="N274" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-25-repartition-et-justice-sociale/c05-le-droit-differencie-sans-calculer.md</t>
+          <t>corpus/livre-24-conditions-materielles-de-la-vie/c05-portee-de-la-tranche.md</t>
         </is>
       </c>
     </row>
     <row r="275">
       <c r="A275" s="2" t="inlineStr">
         <is>
-          <t>L25.C06</t>
+          <t>L25.C01</t>
         </is>
       </c>
       <c r="B275" s="3" t="inlineStr">
@@ -19082,7 +19086,7 @@
       </c>
       <c r="C275" s="3" t="inlineStr">
         <is>
-          <t>Portée de la tranche</t>
+          <t>Ce que ce livre doit établir</t>
         </is>
       </c>
       <c r="D275" s="3" t="inlineStr">
@@ -19112,41 +19116,41 @@
       </c>
       <c r="I275" s="3" t="inlineStr"/>
       <c r="J275" s="3" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K275" s="3" t="n">
         <v>4</v>
       </c>
       <c r="L275" s="3" t="inlineStr">
         <is>
-          <t>plancher_social, plafond_ecologique, dette_ecologique, essentiel_insolvable, bareme</t>
+          <t>plancher_social, plafond_ecologique, essentiel_insolvable, dette_ecologique, communs, solvabilite_anticipee</t>
         </is>
       </c>
       <c r="M275" s="3" t="inlineStr">
         <is>
-          <t>L5.C09, L11.C09, L11.C18, L24.C02, L25.C01, L25.C02, L25.C03, L25.C04, L25.C05</t>
+          <t>L1.C15, L11.C09, L11.C18, L12.C01, L24.C01, L24.C02, L24.C03</t>
         </is>
       </c>
       <c r="N275" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-25-repartition-et-justice-sociale/c06-portee-de-la-tranche.md</t>
+          <t>corpus/livre-25-repartition-et-justice-sociale/c01-ce-que-ce-livre-doit-etablir.md</t>
         </is>
       </c>
     </row>
     <row r="276">
       <c r="A276" s="2" t="inlineStr">
         <is>
-          <t>L26.C01</t>
+          <t>L25.C02</t>
         </is>
       </c>
       <c r="B276" s="3" t="inlineStr">
         <is>
-          <t>L26</t>
+          <t>L25</t>
         </is>
       </c>
       <c r="C276" s="3" t="inlineStr">
         <is>
-          <t>Ce que ce livre doit établir</t>
+          <t>Le noyau dur, et la charge de la preuve renversée</t>
         </is>
       </c>
       <c r="D276" s="3" t="inlineStr">
@@ -19171,46 +19175,46 @@
       </c>
       <c r="H276" s="3" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="I276" s="3" t="inlineStr"/>
       <c r="J276" s="3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K276" s="3" t="n">
         <v>4</v>
       </c>
       <c r="L276" s="3" t="inlineStr">
         <is>
-          <t>entropie, decouplage, effet_rebond, limites_planetaires, sobriete, degeneratif, qualification_regenerative</t>
+          <t>plancher_social, essentiel_insolvable, plafond_ecologique, solvabilite_anticipee, regle_contre_discretion</t>
         </is>
       </c>
       <c r="M276" s="3" t="inlineStr">
         <is>
-          <t>L1.C03, L1.C15, L1.C17, L8.C13, L8.C34, L11.C13, L18.C04, L24.C03, L24.C05</t>
+          <t>L1.C15, L11.C09, L11.C18, L22.C02, L22.C04, L24.C02, L25.C01</t>
         </is>
       </c>
       <c r="N276" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-26-thermodynamique-et-processus-economique/c01-ce-que-ce-livre-doit-etablir.md</t>
+          <t>corpus/livre-25-repartition-et-justice-sociale/c02-le-noyau-dur-et-la-charge-de-la-preuve.md</t>
         </is>
       </c>
     </row>
     <row r="277">
       <c r="A277" s="2" t="inlineStr">
         <is>
-          <t>L26.C02</t>
+          <t>L25.C03</t>
         </is>
       </c>
       <c r="B277" s="3" t="inlineStr">
         <is>
-          <t>L26</t>
+          <t>L25</t>
         </is>
       </c>
       <c r="C277" s="3" t="inlineStr">
         <is>
-          <t>Le stock n'existe pas sous la forme demandée</t>
+          <t>Ce que le droit oblige à donner, et ce qu'il refuse de réparer</t>
         </is>
       </c>
       <c r="D277" s="3" t="inlineStr">
@@ -19235,46 +19239,46 @@
       </c>
       <c r="H277" s="3" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="I277" s="3" t="inlineStr"/>
       <c r="J277" s="3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K277" s="3" t="n">
         <v>4</v>
       </c>
       <c r="L277" s="3" t="inlineStr">
         <is>
-          <t>entropie, bareme, limites_planetaires, decouplage, sobriete, fausse_richesse</t>
+          <t>dette_ecologique, plancher_social, creation_monetaire, reflux_collectif, essentiel_insolvable, solvabilite_anticipee</t>
         </is>
       </c>
       <c r="M277" s="3" t="inlineStr">
         <is>
-          <t>L1.C15, L11.C13, L11.C24, L18.C04, L22.C04, L24.C03, L24.C05, L26.C01</t>
+          <t>L1.C20, L11.C01, L20.C01, L24.C02, L25.C01, L25.C02</t>
         </is>
       </c>
       <c r="N277" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-26-thermodynamique-et-processus-economique/c02-le-stock-n-existe-pas-sous-la-forme-demandee.md</t>
+          <t>corpus/livre-25-repartition-et-justice-sociale/c03-ce-que-le-droit-oblige-a-donner.md</t>
         </is>
       </c>
     </row>
     <row r="278">
       <c r="A278" s="2" t="inlineStr">
         <is>
-          <t>L26.C03</t>
+          <t>L25.C04</t>
         </is>
       </c>
       <c r="B278" s="3" t="inlineStr">
         <is>
-          <t>L26</t>
+          <t>L25</t>
         </is>
       </c>
       <c r="C278" s="3" t="inlineStr">
         <is>
-          <t>La frontière décide du chiffre</t>
+          <t>A34 en droit positif, et le critère que le corpus n'avait pas</t>
         </is>
       </c>
       <c r="D278" s="3" t="inlineStr">
@@ -19299,46 +19303,46 @@
       </c>
       <c r="H278" s="3" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="I278" s="3" t="inlineStr"/>
       <c r="J278" s="3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K278" s="3" t="n">
         <v>4</v>
       </c>
       <c r="L278" s="3" t="inlineStr">
         <is>
-          <t>entropie, decouplage, sobriete, limites_planetaires, robustesse, bareme</t>
+          <t>plancher_social, bareme, essentiel_insolvable, sobriete, affectation_des_instruments, reflux_transactionnel</t>
         </is>
       </c>
       <c r="M278" s="3" t="inlineStr">
         <is>
-          <t>L11.C10, L11.C13, L11.C24, L18.C04, L18.C09, L24.C03, L24.C04, L26.C01, L26.C02</t>
+          <t>L1.C15, L11.C09, L11.C18, L11.C21, L22.C02, L24.C03, L25.C01, L25.C02</t>
         </is>
       </c>
       <c r="N278" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-26-thermodynamique-et-processus-economique/c03-la-frontiere-decide-du-chiffre.md</t>
+          <t>corpus/livre-25-repartition-et-justice-sociale/c04-a34-en-droit-positif.md</t>
         </is>
       </c>
     </row>
     <row r="279">
       <c r="A279" s="2" t="inlineStr">
         <is>
-          <t>L26.C04</t>
+          <t>L25.C05</t>
         </is>
       </c>
       <c r="B279" s="3" t="inlineStr">
         <is>
-          <t>L26</t>
+          <t>L25</t>
         </is>
       </c>
       <c r="C279" s="3" t="inlineStr">
         <is>
-          <t>L'effet rebond, et ce que le dispositif en hérite sans être une politique d'efficacité</t>
+          <t>Le droit différencie sans calculer</t>
         </is>
       </c>
       <c r="D279" s="3" t="inlineStr">
@@ -19363,46 +19367,46 @@
       </c>
       <c r="H279" s="3" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="I279" s="3" t="inlineStr"/>
       <c r="J279" s="3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K279" s="3" t="n">
         <v>4</v>
       </c>
       <c r="L279" s="3" t="inlineStr">
         <is>
-          <t>effet_rebond, jevons_monetaire, decouplage, sobriete, entropie, reflux_transactionnel</t>
+          <t>dette_ecologique, plancher_social, plafond_ecologique, bareme, indicateur_de_progres, polycentricite</t>
         </is>
       </c>
       <c r="M279" s="3" t="inlineStr">
         <is>
-          <t>L1.C03, L1.C12, L1.C17, L11.C10, L13.C01, L18.C04, L22.C02, L24.C03, L26.C01, L26.C03</t>
+          <t>L11.C13, L22.C04, L22.C06, L24.C01, L24.C02, L25.C01, L25.C02, L25.C03, L25.C04</t>
         </is>
       </c>
       <c r="N279" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-26-thermodynamique-et-processus-economique/c04-l-effet-rebond-et-ce-que-le-dispositif-en-herite.md</t>
+          <t>corpus/livre-25-repartition-et-justice-sociale/c05-le-droit-differencie-sans-calculer.md</t>
         </is>
       </c>
     </row>
     <row r="280">
       <c r="A280" s="2" t="inlineStr">
         <is>
-          <t>L26.C05</t>
+          <t>L25.C06</t>
         </is>
       </c>
       <c r="B280" s="3" t="inlineStr">
         <is>
-          <t>L26</t>
+          <t>L25</t>
         </is>
       </c>
       <c r="C280" s="3" t="inlineStr">
         <is>
-          <t>L'addition n'est pas la substitution</t>
+          <t>Portée de la tranche</t>
         </is>
       </c>
       <c r="D280" s="3" t="inlineStr">
@@ -19422,12 +19426,12 @@
       </c>
       <c r="G280" s="3" t="inlineStr">
         <is>
-          <t>hybride</t>
+          <t>descriptif</t>
         </is>
       </c>
       <c r="H280" s="3" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="I280" s="3" t="inlineStr"/>
@@ -19439,24 +19443,24 @@
       </c>
       <c r="L280" s="3" t="inlineStr">
         <is>
-          <t>decouplage, effet_rebond, sobriete, degeneratif, affectation_des_instruments</t>
+          <t>plancher_social, plafond_ecologique, dette_ecologique, essentiel_insolvable, bareme</t>
         </is>
       </c>
       <c r="M280" s="3" t="inlineStr">
         <is>
-          <t>L1.C12, L11.C10, L11.C13, L18.C04, L18.C09, L22.C02, L24.C03, L26.C01, L26.C03, L26.C04</t>
+          <t>L5.C09, L11.C09, L11.C18, L24.C02, L25.C01, L25.C02, L25.C03, L25.C04, L25.C05</t>
         </is>
       </c>
       <c r="N280" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-26-thermodynamique-et-processus-economique/c05-l-addition-n-est-pas-la-substitution.md</t>
+          <t>corpus/livre-25-repartition-et-justice-sociale/c06-portee-de-la-tranche.md</t>
         </is>
       </c>
     </row>
     <row r="281">
       <c r="A281" s="2" t="inlineStr">
         <is>
-          <t>L26.C06</t>
+          <t>L26.C01</t>
         </is>
       </c>
       <c r="B281" s="3" t="inlineStr">
@@ -19466,7 +19470,7 @@
       </c>
       <c r="C281" s="3" t="inlineStr">
         <is>
-          <t>Portée de la tranche</t>
+          <t>Ce que ce livre doit établir</t>
         </is>
       </c>
       <c r="D281" s="3" t="inlineStr">
@@ -19486,7 +19490,7 @@
       </c>
       <c r="G281" s="3" t="inlineStr">
         <is>
-          <t>descriptif</t>
+          <t>hybride</t>
         </is>
       </c>
       <c r="H281" s="3" t="inlineStr">
@@ -19496,29 +19500,349 @@
       </c>
       <c r="I281" s="3" t="inlineStr"/>
       <c r="J281" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="K281" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="L281" s="3" t="inlineStr">
+        <is>
+          <t>entropie, decouplage, effet_rebond, limites_planetaires, sobriete, degeneratif, qualification_regenerative</t>
+        </is>
+      </c>
+      <c r="M281" s="3" t="inlineStr">
+        <is>
+          <t>L1.C03, L1.C15, L1.C17, L8.C13, L8.C34, L11.C13, L18.C04, L24.C03, L24.C05, L17.C02</t>
+        </is>
+      </c>
+      <c r="N281" s="3" t="inlineStr">
+        <is>
+          <t>corpus/livre-26-thermodynamique-et-processus-economique/c01-ce-que-ce-livre-doit-etablir.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" s="2" t="inlineStr">
+        <is>
+          <t>L26.C02</t>
+        </is>
+      </c>
+      <c r="B282" s="3" t="inlineStr">
+        <is>
+          <t>L26</t>
+        </is>
+      </c>
+      <c r="C282" s="3" t="inlineStr">
+        <is>
+          <t>Le stock n'existe pas sous la forme demandée</t>
+        </is>
+      </c>
+      <c r="D282" s="3" t="inlineStr">
+        <is>
+          <t>brouillon</t>
+        </is>
+      </c>
+      <c r="E282" s="3" t="inlineStr">
+        <is>
+          <t>preparatoire</t>
+        </is>
+      </c>
+      <c r="F282" s="3" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="G282" s="3" t="inlineStr">
+        <is>
+          <t>hybride</t>
+        </is>
+      </c>
+      <c r="H282" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="I282" s="3" t="inlineStr"/>
+      <c r="J282" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="K281" s="3" t="n">
+      <c r="K282" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="L282" s="3" t="inlineStr">
+        <is>
+          <t>entropie, bareme, limites_planetaires, decouplage, sobriete, fausse_richesse</t>
+        </is>
+      </c>
+      <c r="M282" s="3" t="inlineStr">
+        <is>
+          <t>L1.C15, L11.C13, L11.C24, L18.C04, L22.C04, L24.C03, L24.C05, L26.C01, L17.C02</t>
+        </is>
+      </c>
+      <c r="N282" s="3" t="inlineStr">
+        <is>
+          <t>corpus/livre-26-thermodynamique-et-processus-economique/c02-le-stock-n-existe-pas-sous-la-forme-demandee.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" s="2" t="inlineStr">
+        <is>
+          <t>L26.C03</t>
+        </is>
+      </c>
+      <c r="B283" s="3" t="inlineStr">
+        <is>
+          <t>L26</t>
+        </is>
+      </c>
+      <c r="C283" s="3" t="inlineStr">
+        <is>
+          <t>La frontière décide du chiffre</t>
+        </is>
+      </c>
+      <c r="D283" s="3" t="inlineStr">
+        <is>
+          <t>brouillon</t>
+        </is>
+      </c>
+      <c r="E283" s="3" t="inlineStr">
+        <is>
+          <t>preparatoire</t>
+        </is>
+      </c>
+      <c r="F283" s="3" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="G283" s="3" t="inlineStr">
+        <is>
+          <t>hybride</t>
+        </is>
+      </c>
+      <c r="H283" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="I283" s="3" t="inlineStr"/>
+      <c r="J283" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="K283" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="L281" s="3" t="inlineStr">
+      <c r="L283" s="3" t="inlineStr">
+        <is>
+          <t>entropie, decouplage, sobriete, limites_planetaires, robustesse, bareme</t>
+        </is>
+      </c>
+      <c r="M283" s="3" t="inlineStr">
+        <is>
+          <t>L11.C10, L11.C13, L11.C24, L18.C04, L18.C09, L24.C03, L24.C04, L26.C01, L26.C02</t>
+        </is>
+      </c>
+      <c r="N283" s="3" t="inlineStr">
+        <is>
+          <t>corpus/livre-26-thermodynamique-et-processus-economique/c03-la-frontiere-decide-du-chiffre.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" s="2" t="inlineStr">
+        <is>
+          <t>L26.C04</t>
+        </is>
+      </c>
+      <c r="B284" s="3" t="inlineStr">
+        <is>
+          <t>L26</t>
+        </is>
+      </c>
+      <c r="C284" s="3" t="inlineStr">
+        <is>
+          <t>L'effet rebond, et ce que le dispositif en hérite sans être une politique d'efficacité</t>
+        </is>
+      </c>
+      <c r="D284" s="3" t="inlineStr">
+        <is>
+          <t>brouillon</t>
+        </is>
+      </c>
+      <c r="E284" s="3" t="inlineStr">
+        <is>
+          <t>preparatoire</t>
+        </is>
+      </c>
+      <c r="F284" s="3" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="G284" s="3" t="inlineStr">
+        <is>
+          <t>hybride</t>
+        </is>
+      </c>
+      <c r="H284" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="I284" s="3" t="inlineStr"/>
+      <c r="J284" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="K284" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="L284" s="3" t="inlineStr">
+        <is>
+          <t>effet_rebond, jevons_monetaire, decouplage, sobriete, entropie, reflux_transactionnel</t>
+        </is>
+      </c>
+      <c r="M284" s="3" t="inlineStr">
+        <is>
+          <t>L1.C03, L1.C12, L1.C17, L11.C10, L13.C01, L18.C04, L22.C02, L24.C03, L26.C01, L26.C03</t>
+        </is>
+      </c>
+      <c r="N284" s="3" t="inlineStr">
+        <is>
+          <t>corpus/livre-26-thermodynamique-et-processus-economique/c04-l-effet-rebond-et-ce-que-le-dispositif-en-herite.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" s="2" t="inlineStr">
+        <is>
+          <t>L26.C05</t>
+        </is>
+      </c>
+      <c r="B285" s="3" t="inlineStr">
+        <is>
+          <t>L26</t>
+        </is>
+      </c>
+      <c r="C285" s="3" t="inlineStr">
+        <is>
+          <t>L'addition n'est pas la substitution</t>
+        </is>
+      </c>
+      <c r="D285" s="3" t="inlineStr">
+        <is>
+          <t>brouillon</t>
+        </is>
+      </c>
+      <c r="E285" s="3" t="inlineStr">
+        <is>
+          <t>preparatoire</t>
+        </is>
+      </c>
+      <c r="F285" s="3" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="G285" s="3" t="inlineStr">
+        <is>
+          <t>hybride</t>
+        </is>
+      </c>
+      <c r="H285" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="I285" s="3" t="inlineStr"/>
+      <c r="J285" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="K285" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="L285" s="3" t="inlineStr">
+        <is>
+          <t>decouplage, effet_rebond, sobriete, degeneratif, affectation_des_instruments</t>
+        </is>
+      </c>
+      <c r="M285" s="3" t="inlineStr">
+        <is>
+          <t>L1.C12, L11.C10, L11.C13, L18.C04, L18.C09, L22.C02, L24.C03, L26.C01, L26.C03, L26.C04</t>
+        </is>
+      </c>
+      <c r="N285" s="3" t="inlineStr">
+        <is>
+          <t>corpus/livre-26-thermodynamique-et-processus-economique/c05-l-addition-n-est-pas-la-substitution.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" s="2" t="inlineStr">
+        <is>
+          <t>L26.C06</t>
+        </is>
+      </c>
+      <c r="B286" s="3" t="inlineStr">
+        <is>
+          <t>L26</t>
+        </is>
+      </c>
+      <c r="C286" s="3" t="inlineStr">
+        <is>
+          <t>Portée de la tranche</t>
+        </is>
+      </c>
+      <c r="D286" s="3" t="inlineStr">
+        <is>
+          <t>brouillon</t>
+        </is>
+      </c>
+      <c r="E286" s="3" t="inlineStr">
+        <is>
+          <t>preparatoire</t>
+        </is>
+      </c>
+      <c r="F286" s="3" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="G286" s="3" t="inlineStr">
+        <is>
+          <t>descriptif</t>
+        </is>
+      </c>
+      <c r="H286" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="I286" s="3" t="inlineStr"/>
+      <c r="J286" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="K286" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="L286" s="3" t="inlineStr">
         <is>
           <t>entropie, decouplage, effet_rebond, limites_planetaires, sobriete, affectation_des_instruments</t>
         </is>
       </c>
-      <c r="M281" s="3" t="inlineStr">
+      <c r="M286" s="3" t="inlineStr">
         <is>
           <t>L1.C03, L1.C17, L8.C34, L11.C10, L11.C13, L11.C24, L18.C04, L18.C09, L22.C02, L24.C05, L26.C01, L26.C02, L26.C03, L26.C04, L26.C05</t>
         </is>
       </c>
-      <c r="N281" s="3" t="inlineStr">
+      <c r="N286" s="3" t="inlineStr">
         <is>
           <t>corpus/livre-26-thermodynamique-et-processus-economique/c06-portee-de-la-tranche.md</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:N281"/>
+  <autoFilter ref="A1:N286"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -19577,7 +19901,7 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="5">
@@ -19587,7 +19911,7 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="6">
@@ -19597,7 +19921,7 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>280</v>
+        <v>285</v>
       </c>
     </row>
     <row r="7">
@@ -19607,7 +19931,7 @@
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="8">
@@ -19617,7 +19941,7 @@
         </is>
       </c>
       <c r="B8" s="3" t="n">
-        <v>272</v>
+        <v>278</v>
       </c>
     </row>
     <row r="9">
@@ -19627,7 +19951,7 @@
         </is>
       </c>
       <c r="B9" s="3" t="n">
-        <v>271</v>
+        <v>276</v>
       </c>
     </row>
     <row r="10">
@@ -19647,7 +19971,7 @@
         </is>
       </c>
       <c r="B11" s="3" t="n">
-        <v>1347</v>
+        <v>1376</v>
       </c>
     </row>
     <row r="12">
@@ -19657,7 +19981,7 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>1083</v>
+        <v>1089</v>
       </c>
     </row>
     <row r="13">
@@ -19672,7 +19996,7 @@
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>L0, L9, L12, L13, L14, L15, L16, L17</t>
+          <t>L0, L9, L12, L13, L14, L15, L16</t>
         </is>
       </c>
     </row>
@@ -19751,7 +20075,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C308"/>
+  <dimension ref="A1:C313"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -23512,7 +23836,7 @@
       </c>
       <c r="C221" s="6" t="inlineStr">
         <is>
-          <t>candidat — AMORCE SEULE</t>
+          <t>en-cours — 6 chapitre(s)</t>
         </is>
       </c>
     </row>
@@ -23524,7 +23848,7 @@
       </c>
       <c r="B222" s="3" t="inlineStr">
         <is>
-          <t>[AMORCE] Ce que ce livre doit établir</t>
+          <t>Ce que ce livre doit établir</t>
         </is>
       </c>
       <c r="C222" s="3" t="inlineStr">
@@ -23534,31 +23858,31 @@
       </c>
     </row>
     <row r="223">
-      <c r="A223" s="6" t="inlineStr">
-        <is>
-          <t>L18</t>
-        </is>
-      </c>
-      <c r="B223" s="6" t="inlineStr">
-        <is>
-          <t>Comptabilités écologiques, sociales et biophysiques</t>
-        </is>
-      </c>
-      <c r="C223" s="6" t="inlineStr">
-        <is>
-          <t>en-cours — 9 chapitre(s)</t>
+      <c r="A223" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    L17.C02</t>
+        </is>
+      </c>
+      <c r="B223" s="3" t="inlineStr">
+        <is>
+          <t>Les sept raisons, testées une par une contre le dispositif</t>
+        </is>
+      </c>
+      <c r="C223" s="3" t="inlineStr">
+        <is>
+          <t>brouillon</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L18.C01</t>
+          <t xml:space="preserve">    L17.C03</t>
         </is>
       </c>
       <c r="B224" s="3" t="inlineStr">
         <is>
-          <t>Ce que ce livre doit établir, et le repli n'est pas l'annexe</t>
+          <t>La sobriété et l'émission : le dispositif échange du mou contre du dur</t>
         </is>
       </c>
       <c r="C224" s="3" t="inlineStr">
@@ -23570,12 +23894,12 @@
     <row r="225">
       <c r="A225" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L18.C02</t>
+          <t xml:space="preserve">    L17.C04</t>
         </is>
       </c>
       <c r="B225" s="3" t="inlineStr">
         <is>
-          <t>La métrologie existe, et ce qu'elle enregistre est l'ordre en place</t>
+          <t>La seule concrétisation institutionnelle ouverte, et sa seule sanction est de publier ses raisons</t>
         </is>
       </c>
       <c r="C225" s="3" t="inlineStr">
@@ -23587,12 +23911,12 @@
     <row r="226">
       <c r="A226" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L18.C03</t>
+          <t xml:space="preserve">    L17.C05</t>
         </is>
       </c>
       <c r="B226" s="3" t="inlineStr">
         <is>
-          <t>L'échelle de repli, et qui l'a arrêtée</t>
+          <t>Le tableau de bord et le chiffre unique — ce que le corpus perd en refusant d'agréger</t>
         </is>
       </c>
       <c r="C226" s="3" t="inlineStr">
@@ -23604,12 +23928,12 @@
     <row r="227">
       <c r="A227" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L18.C04</t>
+          <t xml:space="preserve">    L17.C06</t>
         </is>
       </c>
       <c r="B227" s="3" t="inlineStr">
         <is>
-          <t>Les grandeurs physiques, et l'endroit où elles frappent le dispositif</t>
+          <t>Portée de la tranche</t>
         </is>
       </c>
       <c r="C227" s="3" t="inlineStr">
@@ -23619,31 +23943,31 @@
       </c>
     </row>
     <row r="228">
-      <c r="A228" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    L18.C05</t>
-        </is>
-      </c>
-      <c r="B228" s="3" t="inlineStr">
-        <is>
-          <t>Ce que la norme exclut, et ce n'est pas le commun</t>
-        </is>
-      </c>
-      <c r="C228" s="3" t="inlineStr">
-        <is>
-          <t>brouillon</t>
+      <c r="A228" s="6" t="inlineStr">
+        <is>
+          <t>L18</t>
+        </is>
+      </c>
+      <c r="B228" s="6" t="inlineStr">
+        <is>
+          <t>Comptabilités écologiques, sociales et biophysiques</t>
+        </is>
+      </c>
+      <c r="C228" s="6" t="inlineStr">
+        <is>
+          <t>en-cours — 9 chapitre(s)</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L18.C06</t>
+          <t xml:space="preserve">    L18.C01</t>
         </is>
       </c>
       <c r="B229" s="3" t="inlineStr">
         <is>
-          <t>Portée de la tranche, et une neuvième condition proposée</t>
+          <t>Ce que ce livre doit établir, et le repli n'est pas l'annexe</t>
         </is>
       </c>
       <c r="C229" s="3" t="inlineStr">
@@ -23655,12 +23979,12 @@
     <row r="230">
       <c r="A230" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L18.C07</t>
+          <t xml:space="preserve">    L18.C02</t>
         </is>
       </c>
       <c r="B230" s="3" t="inlineStr">
         <is>
-          <t>CARE/TDL répare deux objections, et en crée une plus grave</t>
+          <t>La métrologie existe, et ce qu'elle enregistre est l'ordre en place</t>
         </is>
       </c>
       <c r="C230" s="3" t="inlineStr">
@@ -23672,12 +23996,12 @@
     <row r="231">
       <c r="A231" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L18.C08</t>
+          <t xml:space="preserve">    L18.C03</t>
         </is>
       </c>
       <c r="B231" s="3" t="inlineStr">
         <is>
-          <t>Le modèle au périmètre du dispositif, et F9 révisée</t>
+          <t>L'échelle de repli, et qui l'a arrêtée</t>
         </is>
       </c>
       <c r="C231" s="3" t="inlineStr">
@@ -23689,12 +24013,12 @@
     <row r="232">
       <c r="A232" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L18.C09</t>
+          <t xml:space="preserve">    L18.C04</t>
         </is>
       </c>
       <c r="B232" s="3" t="inlineStr">
         <is>
-          <t>L'ordre de grandeur, et le concurrent qu'il désigne</t>
+          <t>Les grandeurs physiques, et l'endroit où elles frappent le dispositif</t>
         </is>
       </c>
       <c r="C232" s="3" t="inlineStr">
@@ -23704,31 +24028,31 @@
       </c>
     </row>
     <row r="233">
-      <c r="A233" s="6" t="inlineStr">
-        <is>
-          <t>L19</t>
-        </is>
-      </c>
-      <c r="B233" s="6" t="inlineStr">
-        <is>
-          <t>Comptabilité monétaire de l'émission sans dette</t>
-        </is>
-      </c>
-      <c r="C233" s="6" t="inlineStr">
-        <is>
-          <t>en-cours — 7 chapitre(s)</t>
+      <c r="A233" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    L18.C05</t>
+        </is>
+      </c>
+      <c r="B233" s="3" t="inlineStr">
+        <is>
+          <t>Ce que la norme exclut, et ce n'est pas le commun</t>
+        </is>
+      </c>
+      <c r="C233" s="3" t="inlineStr">
+        <is>
+          <t>brouillon</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L19.C01</t>
+          <t xml:space="preserve">    L18.C06</t>
         </is>
       </c>
       <c r="B234" s="3" t="inlineStr">
         <is>
-          <t>Ce que ce livre doit établir</t>
+          <t>Portée de la tranche, et une neuvième condition proposée</t>
         </is>
       </c>
       <c r="C234" s="3" t="inlineStr">
@@ -23740,12 +24064,12 @@
     <row r="235">
       <c r="A235" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L19.C02</t>
+          <t xml:space="preserve">    L18.C07</t>
         </is>
       </c>
       <c r="B235" s="3" t="inlineStr">
         <is>
-          <t>Le seul précédent, et le passif lui a été reconnu en 2008</t>
+          <t>CARE/TDL répare deux objections, et en crée une plus grave</t>
         </is>
       </c>
       <c r="C235" s="3" t="inlineStr">
@@ -23757,12 +24081,12 @@
     <row r="236">
       <c r="A236" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L19.C03</t>
+          <t xml:space="preserve">    L18.C08</t>
         </is>
       </c>
       <c r="B236" s="3" t="inlineStr">
         <is>
-          <t>Le reflux est un intérêt négatif, ou une répudiation — et c'est le moment qui décide</t>
+          <t>Le modèle au périmètre du dispositif, et F9 révisée</t>
         </is>
       </c>
       <c r="C236" s="3" t="inlineStr">
@@ -23774,12 +24098,12 @@
     <row r="237">
       <c r="A237" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L19.C04</t>
+          <t xml:space="preserve">    L18.C09</t>
         </is>
       </c>
       <c r="B237" s="3" t="inlineStr">
         <is>
-          <t>L'actif transitoire n'existe pas, et le problème change de bilan</t>
+          <t>L'ordre de grandeur, et le concurrent qu'il désigne</t>
         </is>
       </c>
       <c r="C237" s="3" t="inlineStr">
@@ -23789,31 +24113,31 @@
       </c>
     </row>
     <row r="238">
-      <c r="A238" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    L19.C05</t>
-        </is>
-      </c>
-      <c r="B238" s="3" t="inlineStr">
-        <is>
-          <t>Un débiteur collectif n'existe pas — sauf comme somme de débiteurs identifiés</t>
-        </is>
-      </c>
-      <c r="C238" s="3" t="inlineStr">
-        <is>
-          <t>brouillon</t>
+      <c r="A238" s="6" t="inlineStr">
+        <is>
+          <t>L19</t>
+        </is>
+      </c>
+      <c r="B238" s="6" t="inlineStr">
+        <is>
+          <t>Comptabilité monétaire de l'émission sans dette</t>
+        </is>
+      </c>
+      <c r="C238" s="6" t="inlineStr">
+        <is>
+          <t>en-cours — 7 chapitre(s)</t>
         </is>
       </c>
     </row>
     <row r="239">
       <c r="A239" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L19.C06</t>
+          <t xml:space="preserve">    L19.C01</t>
         </is>
       </c>
       <c r="B239" s="3" t="inlineStr">
         <is>
-          <t>Les fonds propres négatifs, et l'institution qui n'apparaît dans les comptes de personne</t>
+          <t>Ce que ce livre doit établir</t>
         </is>
       </c>
       <c r="C239" s="3" t="inlineStr">
@@ -23825,12 +24149,12 @@
     <row r="240">
       <c r="A240" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L19.C07</t>
+          <t xml:space="preserve">    L19.C02</t>
         </is>
       </c>
       <c r="B240" s="3" t="inlineStr">
         <is>
-          <t>Portée de la tranche</t>
+          <t>Le seul précédent, et le passif lui a été reconnu en 2008</t>
         </is>
       </c>
       <c r="C240" s="3" t="inlineStr">
@@ -23840,31 +24164,31 @@
       </c>
     </row>
     <row r="241">
-      <c r="A241" s="6" t="inlineStr">
-        <is>
-          <t>L20</t>
-        </is>
-      </c>
-      <c r="B241" s="6" t="inlineStr">
-        <is>
-          <t>Droit international public, droit monétaire et commercial de la réforme</t>
-        </is>
-      </c>
-      <c r="C241" s="6" t="inlineStr">
-        <is>
-          <t>en-cours — 23 chapitre(s)</t>
+      <c r="A241" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    L19.C03</t>
+        </is>
+      </c>
+      <c r="B241" s="3" t="inlineStr">
+        <is>
+          <t>Le reflux est un intérêt négatif, ou une répudiation — et c'est le moment qui décide</t>
+        </is>
+      </c>
+      <c r="C241" s="3" t="inlineStr">
+        <is>
+          <t>brouillon</t>
         </is>
       </c>
     </row>
     <row r="242">
       <c r="A242" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L20.C01</t>
+          <t xml:space="preserve">    L19.C04</t>
         </is>
       </c>
       <c r="B242" s="3" t="inlineStr">
         <is>
-          <t>Ce que ce livre doit établir</t>
+          <t>L'actif transitoire n'existe pas, et le problème change de bilan</t>
         </is>
       </c>
       <c r="C242" s="3" t="inlineStr">
@@ -23876,12 +24200,12 @@
     <row r="243">
       <c r="A243" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L20.C02</t>
+          <t xml:space="preserve">    L19.C05</t>
         </is>
       </c>
       <c r="B243" s="3" t="inlineStr">
         <is>
-          <t>L'interdiction du financement monétaire</t>
+          <t>Un débiteur collectif n'existe pas — sauf comme somme de débiteurs identifiés</t>
         </is>
       </c>
       <c r="C243" s="3" t="inlineStr">
@@ -23893,12 +24217,12 @@
     <row r="244">
       <c r="A244" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L20.C03</t>
+          <t xml:space="preserve">    L19.C06</t>
         </is>
       </c>
       <c r="B244" s="3" t="inlineStr">
         <is>
-          <t>L'objectif principal et ce qu'il exclut</t>
+          <t>Les fonds propres négatifs, et l'institution qui n'apparaît dans les comptes de personne</t>
         </is>
       </c>
       <c r="C244" s="3" t="inlineStr">
@@ -23910,12 +24234,12 @@
     <row r="245">
       <c r="A245" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L20.C04</t>
+          <t xml:space="preserve">    L19.C07</t>
         </is>
       </c>
       <c r="B245" s="3" t="inlineStr">
         <is>
-          <t>L'indépendance, et à l'égard de qui</t>
+          <t>Portée de la tranche</t>
         </is>
       </c>
       <c r="C245" s="3" t="inlineStr">
@@ -23925,31 +24249,31 @@
       </c>
     </row>
     <row r="246">
-      <c r="A246" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    L20.C05</t>
-        </is>
-      </c>
-      <c r="B246" s="3" t="inlineStr">
-        <is>
-          <t>Le monopole d'émission et le cours légal</t>
-        </is>
-      </c>
-      <c r="C246" s="3" t="inlineStr">
-        <is>
-          <t>brouillon</t>
+      <c r="A246" s="6" t="inlineStr">
+        <is>
+          <t>L20</t>
+        </is>
+      </c>
+      <c r="B246" s="6" t="inlineStr">
+        <is>
+          <t>Droit international public, droit monétaire et commercial de la réforme</t>
+        </is>
+      </c>
+      <c r="C246" s="6" t="inlineStr">
+        <is>
+          <t>en-cours — 23 chapitre(s)</t>
         </is>
       </c>
     </row>
     <row r="247">
       <c r="A247" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L20.C06</t>
+          <t xml:space="preserve">    L20.C01</t>
         </is>
       </c>
       <c r="B247" s="3" t="inlineStr">
         <is>
-          <t>Les voies de révision et leur coût</t>
+          <t>Ce que ce livre doit établir</t>
         </is>
       </c>
       <c r="C247" s="3" t="inlineStr">
@@ -23961,12 +24285,12 @@
     <row r="248">
       <c r="A248" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L20.C07</t>
+          <t xml:space="preserve">    L20.C02</t>
         </is>
       </c>
       <c r="B248" s="3" t="inlineStr">
         <is>
-          <t>L'accord monétaire international</t>
+          <t>L'interdiction du financement monétaire</t>
         </is>
       </c>
       <c r="C248" s="3" t="inlineStr">
@@ -23978,12 +24302,12 @@
     <row r="249">
       <c r="A249" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L20.C08</t>
+          <t xml:space="preserve">    L20.C03</t>
         </is>
       </c>
       <c r="B249" s="3" t="inlineStr">
         <is>
-          <t>La parité inscrite dans le traité</t>
+          <t>L'objectif principal et ce qu'il exclut</t>
         </is>
       </c>
       <c r="C249" s="3" t="inlineStr">
@@ -23995,12 +24319,12 @@
     <row r="250">
       <c r="A250" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L20.C09</t>
+          <t xml:space="preserve">    L20.C04</t>
         </is>
       </c>
       <c r="B250" s="3" t="inlineStr">
         <is>
-          <t>L'amendement des statuts du Fonds</t>
+          <t>L'indépendance, et à l'égard de qui</t>
         </is>
       </c>
       <c r="C250" s="3" t="inlineStr">
@@ -24012,12 +24336,12 @@
     <row r="251">
       <c r="A251" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L20.C10</t>
+          <t xml:space="preserve">    L20.C05</t>
         </is>
       </c>
       <c r="B251" s="3" t="inlineStr">
         <is>
-          <t>Le vote pondéré et les voix de base</t>
+          <t>Le monopole d'émission et le cours légal</t>
         </is>
       </c>
       <c r="C251" s="3" t="inlineStr">
@@ -24029,12 +24353,12 @@
     <row r="252">
       <c r="A252" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L20.C11</t>
+          <t xml:space="preserve">    L20.C06</t>
         </is>
       </c>
       <c r="B252" s="3" t="inlineStr">
         <is>
-          <t>La personnalité juridique et les immunités</t>
+          <t>Les voies de révision et leur coût</t>
         </is>
       </c>
       <c r="C252" s="3" t="inlineStr">
@@ -24046,12 +24370,12 @@
     <row r="253">
       <c r="A253" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L20.C12</t>
+          <t xml:space="preserve">    L20.C07</t>
         </is>
       </c>
       <c r="B253" s="3" t="inlineStr">
         <is>
-          <t>Les pouvoirs non délégables</t>
+          <t>L'accord monétaire international</t>
         </is>
       </c>
       <c r="C253" s="3" t="inlineStr">
@@ -24063,12 +24387,12 @@
     <row r="254">
       <c r="A254" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L20.C13</t>
+          <t xml:space="preserve">    L20.C08</t>
         </is>
       </c>
       <c r="B254" s="3" t="inlineStr">
         <is>
-          <t>L'entrée en vigueur, l'adhésion et le retrait</t>
+          <t>La parité inscrite dans le traité</t>
         </is>
       </c>
       <c r="C254" s="3" t="inlineStr">
@@ -24080,12 +24404,12 @@
     <row r="255">
       <c r="A255" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L20.C14</t>
+          <t xml:space="preserve">    L20.C09</t>
         </is>
       </c>
       <c r="B255" s="3" t="inlineStr">
         <is>
-          <t>Qui interprète le traité</t>
+          <t>L'amendement des statuts du Fonds</t>
         </is>
       </c>
       <c r="C255" s="3" t="inlineStr">
@@ -24097,12 +24421,12 @@
     <row r="256">
       <c r="A256" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L20.C15</t>
+          <t xml:space="preserve">    L20.C10</t>
         </is>
       </c>
       <c r="B256" s="3" t="inlineStr">
         <is>
-          <t>Le devoir international des agents</t>
+          <t>Le vote pondéré et les voix de base</t>
         </is>
       </c>
       <c r="C256" s="3" t="inlineStr">
@@ -24114,12 +24438,12 @@
     <row r="257">
       <c r="A257" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L20.C16</t>
+          <t xml:space="preserve">    L20.C11</t>
         </is>
       </c>
       <c r="B257" s="3" t="inlineStr">
         <is>
-          <t>Le patrimoine commun de l'humanité</t>
+          <t>La personnalité juridique et les immunités</t>
         </is>
       </c>
       <c r="C257" s="3" t="inlineStr">
@@ -24131,12 +24455,12 @@
     <row r="258">
       <c r="A258" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L20.C17</t>
+          <t xml:space="preserve">    L20.C12</t>
         </is>
       </c>
       <c r="B258" s="3" t="inlineStr">
         <is>
-          <t>La sanctuarisation, et elle existe</t>
+          <t>Les pouvoirs non délégables</t>
         </is>
       </c>
       <c r="C258" s="3" t="inlineStr">
@@ -24148,12 +24472,12 @@
     <row r="259">
       <c r="A259" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L20.C18</t>
+          <t xml:space="preserve">    L20.C13</t>
         </is>
       </c>
       <c r="B259" s="3" t="inlineStr">
         <is>
-          <t>L'amendement et la dérogation dans l'ordre commercial</t>
+          <t>L'entrée en vigueur, l'adhésion et le retrait</t>
         </is>
       </c>
       <c r="C259" s="3" t="inlineStr">
@@ -24165,12 +24489,12 @@
     <row r="260">
       <c r="A260" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L20.C19</t>
+          <t xml:space="preserve">    L20.C14</t>
         </is>
       </c>
       <c r="B260" s="3" t="inlineStr">
         <is>
-          <t>Le texte que la conformité invoque</t>
+          <t>Qui interprète le traité</t>
         </is>
       </c>
       <c r="C260" s="3" t="inlineStr">
@@ -24182,12 +24506,12 @@
     <row r="261">
       <c r="A261" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L20.C20</t>
+          <t xml:space="preserve">    L20.C15</t>
         </is>
       </c>
       <c r="B261" s="3" t="inlineStr">
         <is>
-          <t>L'ajustement aux frontières comme précédent</t>
+          <t>Le devoir international des agents</t>
         </is>
       </c>
       <c r="C261" s="3" t="inlineStr">
@@ -24199,12 +24523,12 @@
     <row r="262">
       <c r="A262" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L20.C21</t>
+          <t xml:space="preserve">    L20.C16</t>
         </is>
       </c>
       <c r="B262" s="3" t="inlineStr">
         <is>
-          <t>La transparence et sa limite juridictionnelle</t>
+          <t>Le patrimoine commun de l'humanité</t>
         </is>
       </c>
       <c r="C262" s="3" t="inlineStr">
@@ -24216,12 +24540,12 @@
     <row r="263">
       <c r="A263" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L20.C22</t>
+          <t xml:space="preserve">    L20.C17</t>
         </is>
       </c>
       <c r="B263" s="3" t="inlineStr">
         <is>
-          <t>Ce que le droit devrait devenir</t>
+          <t>La sanctuarisation, et elle existe</t>
         </is>
       </c>
       <c r="C263" s="3" t="inlineStr">
@@ -24233,12 +24557,12 @@
     <row r="264">
       <c r="A264" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L20.C23</t>
+          <t xml:space="preserve">    L20.C18</t>
         </is>
       </c>
       <c r="B264" s="3" t="inlineStr">
         <is>
-          <t>La portée du livre</t>
+          <t>L'amendement et la dérogation dans l'ordre commercial</t>
         </is>
       </c>
       <c r="C264" s="3" t="inlineStr">
@@ -24248,31 +24572,31 @@
       </c>
     </row>
     <row r="265">
-      <c r="A265" s="6" t="inlineStr">
-        <is>
-          <t>L21</t>
-        </is>
-      </c>
-      <c r="B265" s="6" t="inlineStr">
-        <is>
-          <t>La plomberie financière mondiale</t>
-        </is>
-      </c>
-      <c r="C265" s="6" t="inlineStr">
-        <is>
-          <t>en-cours — 7 chapitre(s)</t>
+      <c r="A265" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    L20.C19</t>
+        </is>
+      </c>
+      <c r="B265" s="3" t="inlineStr">
+        <is>
+          <t>Le texte que la conformité invoque</t>
+        </is>
+      </c>
+      <c r="C265" s="3" t="inlineStr">
+        <is>
+          <t>brouillon</t>
         </is>
       </c>
     </row>
     <row r="266">
       <c r="A266" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L21.C01</t>
+          <t xml:space="preserve">    L20.C20</t>
         </is>
       </c>
       <c r="B266" s="3" t="inlineStr">
         <is>
-          <t>Ce que ce livre doit établir, et le principe qui exige des fonds propres</t>
+          <t>L'ajustement aux frontières comme précédent</t>
         </is>
       </c>
       <c r="C266" s="3" t="inlineStr">
@@ -24284,12 +24608,12 @@
     <row r="267">
       <c r="A267" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L21.C02</t>
+          <t xml:space="preserve">    L20.C21</t>
         </is>
       </c>
       <c r="B267" s="3" t="inlineStr">
         <is>
-          <t>Comment l'unité circulerait vraiment, et ce que chaque étape exige</t>
+          <t>La transparence et sa limite juridictionnelle</t>
         </is>
       </c>
       <c r="C267" s="3" t="inlineStr">
@@ -24301,12 +24625,12 @@
     <row r="268">
       <c r="A268" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L21.C03</t>
+          <t xml:space="preserve">    L20.C22</t>
         </is>
       </c>
       <c r="B268" s="3" t="inlineStr">
         <is>
-          <t>Une opération de bout en bout, bilan par bilan</t>
+          <t>Ce que le droit devrait devenir</t>
         </is>
       </c>
       <c r="C268" s="3" t="inlineStr">
@@ -24318,12 +24642,12 @@
     <row r="269">
       <c r="A269" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L21.C04</t>
+          <t xml:space="preserve">    L20.C23</t>
         </is>
       </c>
       <c r="B269" s="3" t="inlineStr">
         <is>
-          <t>Ce que l'émission coûte aux banques qui l'hébergent</t>
+          <t>La portée du livre</t>
         </is>
       </c>
       <c r="C269" s="3" t="inlineStr">
@@ -24333,31 +24657,31 @@
       </c>
     </row>
     <row r="270">
-      <c r="A270" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    L21.C05</t>
-        </is>
-      </c>
-      <c r="B270" s="3" t="inlineStr">
-        <is>
-          <t>La première infrastructure ouverte, et ce qu'elle renverse</t>
-        </is>
-      </c>
-      <c r="C270" s="3" t="inlineStr">
-        <is>
-          <t>brouillon</t>
+      <c r="A270" s="6" t="inlineStr">
+        <is>
+          <t>L21</t>
+        </is>
+      </c>
+      <c r="B270" s="6" t="inlineStr">
+        <is>
+          <t>La plomberie financière mondiale</t>
+        </is>
+      </c>
+      <c r="C270" s="6" t="inlineStr">
+        <is>
+          <t>en-cours — 7 chapitre(s)</t>
         </is>
       </c>
     </row>
     <row r="271">
       <c r="A271" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L21.C06</t>
+          <t xml:space="preserve">    L21.C01</t>
         </is>
       </c>
       <c r="B271" s="3" t="inlineStr">
         <is>
-          <t>La jambe qui reste, et ce qu'il faut pour la protéger</t>
+          <t>Ce que ce livre doit établir, et le principe qui exige des fonds propres</t>
         </is>
       </c>
       <c r="C271" s="3" t="inlineStr">
@@ -24369,12 +24693,12 @@
     <row r="272">
       <c r="A272" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L21.C07</t>
+          <t xml:space="preserve">    L21.C02</t>
         </is>
       </c>
       <c r="B272" s="3" t="inlineStr">
         <is>
-          <t>Portée de la tranche</t>
+          <t>Comment l'unité circulerait vraiment, et ce que chaque étape exige</t>
         </is>
       </c>
       <c r="C272" s="3" t="inlineStr">
@@ -24384,31 +24708,31 @@
       </c>
     </row>
     <row r="273">
-      <c r="A273" s="6" t="inlineStr">
-        <is>
-          <t>L22</t>
-        </is>
-      </c>
-      <c r="B273" s="6" t="inlineStr">
-        <is>
-          <t>Le pouvoir de la finance non bancaire</t>
-        </is>
-      </c>
-      <c r="C273" s="6" t="inlineStr">
-        <is>
-          <t>en-cours — 7 chapitre(s)</t>
+      <c r="A273" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    L21.C03</t>
+        </is>
+      </c>
+      <c r="B273" s="3" t="inlineStr">
+        <is>
+          <t>Une opération de bout en bout, bilan par bilan</t>
+        </is>
+      </c>
+      <c r="C273" s="3" t="inlineStr">
+        <is>
+          <t>brouillon</t>
         </is>
       </c>
     </row>
     <row r="274">
       <c r="A274" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L22.C01</t>
+          <t xml:space="preserve">    L21.C04</t>
         </is>
       </c>
       <c r="B274" s="3" t="inlineStr">
         <is>
-          <t>Ce que ce livre doit établir</t>
+          <t>Ce que l'émission coûte aux banques qui l'hébergent</t>
         </is>
       </c>
       <c r="C274" s="3" t="inlineStr">
@@ -24420,12 +24744,12 @@
     <row r="275">
       <c r="A275" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L22.C02</t>
+          <t xml:space="preserve">    L21.C05</t>
         </is>
       </c>
       <c r="B275" s="3" t="inlineStr">
         <is>
-          <t>Où va la monnaie émise, et pourquoi le reflux ne l'y suit pas</t>
+          <t>La première infrastructure ouverte, et ce qu'elle renverse</t>
         </is>
       </c>
       <c r="C275" s="3" t="inlineStr">
@@ -24437,12 +24761,12 @@
     <row r="276">
       <c r="A276" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L22.C03</t>
+          <t xml:space="preserve">    L21.C06</t>
         </is>
       </c>
       <c r="B276" s="3" t="inlineStr">
         <is>
-          <t>Le barème existe déjà, et il a trois pièces que le corpus n'a pas</t>
+          <t>La jambe qui reste, et ce qu'il faut pour la protéger</t>
         </is>
       </c>
       <c r="C276" s="3" t="inlineStr">
@@ -24454,12 +24778,12 @@
     <row r="277">
       <c r="A277" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L22.C04</t>
+          <t xml:space="preserve">    L21.C07</t>
         </is>
       </c>
       <c r="B277" s="3" t="inlineStr">
         <is>
-          <t>Les critères réels ne mesurent pas, ils certifient</t>
+          <t>Portée de la tranche</t>
         </is>
       </c>
       <c r="C277" s="3" t="inlineStr">
@@ -24469,31 +24793,31 @@
       </c>
     </row>
     <row r="278">
-      <c r="A278" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    L22.C05</t>
-        </is>
-      </c>
-      <c r="B278" s="3" t="inlineStr">
-        <is>
-          <t>L'épargne retraite, et le dilemme du troisième instrument</t>
-        </is>
-      </c>
-      <c r="C278" s="3" t="inlineStr">
-        <is>
-          <t>brouillon</t>
+      <c r="A278" s="6" t="inlineStr">
+        <is>
+          <t>L22</t>
+        </is>
+      </c>
+      <c r="B278" s="6" t="inlineStr">
+        <is>
+          <t>Le pouvoir de la finance non bancaire</t>
+        </is>
+      </c>
+      <c r="C278" s="6" t="inlineStr">
+        <is>
+          <t>en-cours — 7 chapitre(s)</t>
         </is>
       </c>
     </row>
     <row r="279">
       <c r="A279" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L22.C06</t>
+          <t xml:space="preserve">    L22.C01</t>
         </is>
       </c>
       <c r="B279" s="3" t="inlineStr">
         <is>
-          <t>Qui décide, quand personne ne décide</t>
+          <t>Ce que ce livre doit établir</t>
         </is>
       </c>
       <c r="C279" s="3" t="inlineStr">
@@ -24505,12 +24829,12 @@
     <row r="280">
       <c r="A280" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L22.C07</t>
+          <t xml:space="preserve">    L22.C02</t>
         </is>
       </c>
       <c r="B280" s="3" t="inlineStr">
         <is>
-          <t>Portée de la tranche</t>
+          <t>Où va la monnaie émise, et pourquoi le reflux ne l'y suit pas</t>
         </is>
       </c>
       <c r="C280" s="3" t="inlineStr">
@@ -24520,31 +24844,31 @@
       </c>
     </row>
     <row r="281">
-      <c r="A281" s="6" t="inlineStr">
-        <is>
-          <t>L23</t>
-        </is>
-      </c>
-      <c r="B281" s="6" t="inlineStr">
-        <is>
-          <t>Fiscalité mondiale, finance offshore et opacité</t>
-        </is>
-      </c>
-      <c r="C281" s="6" t="inlineStr">
-        <is>
-          <t>en-cours — 7 chapitre(s)</t>
+      <c r="A281" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    L22.C03</t>
+        </is>
+      </c>
+      <c r="B281" s="3" t="inlineStr">
+        <is>
+          <t>Le barème existe déjà, et il a trois pièces que le corpus n'a pas</t>
+        </is>
+      </c>
+      <c r="C281" s="3" t="inlineStr">
+        <is>
+          <t>brouillon</t>
         </is>
       </c>
     </row>
     <row r="282">
       <c r="A282" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L23.C01</t>
+          <t xml:space="preserve">    L22.C04</t>
         </is>
       </c>
       <c r="B282" s="3" t="inlineStr">
         <is>
-          <t>Ce que ce livre doit établir</t>
+          <t>Les critères réels ne mesurent pas, ils certifient</t>
         </is>
       </c>
       <c r="C282" s="3" t="inlineStr">
@@ -24556,12 +24880,12 @@
     <row r="283">
       <c r="A283" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L23.C02</t>
+          <t xml:space="preserve">    L22.C05</t>
         </is>
       </c>
       <c r="B283" s="3" t="inlineStr">
         <is>
-          <t>La compétence que la convention ne crée pas, et le vote qu'elle a gagné</t>
+          <t>L'épargne retraite, et le dilemme du troisième instrument</t>
         </is>
       </c>
       <c r="C283" s="3" t="inlineStr">
@@ -24573,12 +24897,12 @@
     <row r="284">
       <c r="A284" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L23.C03</t>
+          <t xml:space="preserve">    L22.C06</t>
         </is>
       </c>
       <c r="B284" s="3" t="inlineStr">
         <is>
-          <t>F8 appliqué à une négociation en cours, et le résultat n'est pas le désarmement</t>
+          <t>Qui décide, quand personne ne décide</t>
         </is>
       </c>
       <c r="C284" s="3" t="inlineStr">
@@ -24590,12 +24914,12 @@
     <row r="285">
       <c r="A285" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L23.C04</t>
+          <t xml:space="preserve">    L22.C07</t>
         </is>
       </c>
       <c r="B285" s="3" t="inlineStr">
         <is>
-          <t>La transparence que le corpus supposait a été invalidée</t>
+          <t>Portée de la tranche</t>
         </is>
       </c>
       <c r="C285" s="3" t="inlineStr">
@@ -24605,31 +24929,31 @@
       </c>
     </row>
     <row r="286">
-      <c r="A286" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    L23.C05</t>
-        </is>
-      </c>
-      <c r="B286" s="3" t="inlineStr">
-        <is>
-          <t>Intéresser le percepteur, et ce que le taux révèle</t>
-        </is>
-      </c>
-      <c r="C286" s="3" t="inlineStr">
-        <is>
-          <t>brouillon</t>
+      <c r="A286" s="6" t="inlineStr">
+        <is>
+          <t>L23</t>
+        </is>
+      </c>
+      <c r="B286" s="6" t="inlineStr">
+        <is>
+          <t>Fiscalité mondiale, finance offshore et opacité</t>
+        </is>
+      </c>
+      <c r="C286" s="6" t="inlineStr">
+        <is>
+          <t>en-cours — 7 chapitre(s)</t>
         </is>
       </c>
     </row>
     <row r="287">
       <c r="A287" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L23.C06</t>
+          <t xml:space="preserve">    L23.C01</t>
         </is>
       </c>
       <c r="B287" s="3" t="inlineStr">
         <is>
-          <t>L'arbre appliqué à la fonte, et il ne reste que deux branches</t>
+          <t>Ce que ce livre doit établir</t>
         </is>
       </c>
       <c r="C287" s="3" t="inlineStr">
@@ -24641,12 +24965,12 @@
     <row r="288">
       <c r="A288" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L23.C07</t>
+          <t xml:space="preserve">    L23.C02</t>
         </is>
       </c>
       <c r="B288" s="3" t="inlineStr">
         <is>
-          <t>Portée de la tranche, et la moitié qui n'est pas commencée</t>
+          <t>La compétence que la convention ne crée pas, et le vote qu'elle a gagné</t>
         </is>
       </c>
       <c r="C288" s="3" t="inlineStr">
@@ -24656,31 +24980,31 @@
       </c>
     </row>
     <row r="289">
-      <c r="A289" s="6" t="inlineStr">
-        <is>
-          <t>L24</t>
-        </is>
-      </c>
-      <c r="B289" s="6" t="inlineStr">
-        <is>
-          <t>Les conditions matérielles de la vie</t>
-        </is>
-      </c>
-      <c r="C289" s="6" t="inlineStr">
-        <is>
-          <t>en-cours — 5 chapitre(s)</t>
+      <c r="A289" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    L23.C03</t>
+        </is>
+      </c>
+      <c r="B289" s="3" t="inlineStr">
+        <is>
+          <t>F8 appliqué à une négociation en cours, et le résultat n'est pas le désarmement</t>
+        </is>
+      </c>
+      <c r="C289" s="3" t="inlineStr">
+        <is>
+          <t>brouillon</t>
         </is>
       </c>
     </row>
     <row r="290">
       <c r="A290" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L24.C01</t>
+          <t xml:space="preserve">    L23.C04</t>
         </is>
       </c>
       <c r="B290" s="3" t="inlineStr">
         <is>
-          <t>Ce que ce livre doit établir</t>
+          <t>La transparence que le corpus supposait a été invalidée</t>
         </is>
       </c>
       <c r="C290" s="3" t="inlineStr">
@@ -24692,12 +25016,12 @@
     <row r="291">
       <c r="A291" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L24.C02</t>
+          <t xml:space="preserve">    L23.C05</t>
         </is>
       </c>
       <c r="B291" s="3" t="inlineStr">
         <is>
-          <t>Le seuil juste est plus strict que le seuil sûr</t>
+          <t>Intéresser le percepteur, et ce que le taux révèle</t>
         </is>
       </c>
       <c r="C291" s="3" t="inlineStr">
@@ -24709,12 +25033,12 @@
     <row r="292">
       <c r="A292" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L24.C03</t>
+          <t xml:space="preserve">    L23.C06</t>
         </is>
       </c>
       <c r="B292" s="3" t="inlineStr">
         <is>
-          <t>La matière, et le levier commun que les neuf dimensions n'avaient pas</t>
+          <t>L'arbre appliqué à la fonte, et il ne reste que deux branches</t>
         </is>
       </c>
       <c r="C292" s="3" t="inlineStr">
@@ -24726,12 +25050,12 @@
     <row r="293">
       <c r="A293" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L24.C04</t>
+          <t xml:space="preserve">    L23.C07</t>
         </is>
       </c>
       <c r="B293" s="3" t="inlineStr">
         <is>
-          <t>Un budget mondial n'est pas partageable</t>
+          <t>Portée de la tranche, et la moitié qui n'est pas commencée</t>
         </is>
       </c>
       <c r="C293" s="3" t="inlineStr">
@@ -24741,48 +25065,48 @@
       </c>
     </row>
     <row r="294">
-      <c r="A294" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    L24.C05</t>
-        </is>
-      </c>
-      <c r="B294" s="3" t="inlineStr">
-        <is>
-          <t>Portée de la tranche</t>
-        </is>
-      </c>
-      <c r="C294" s="3" t="inlineStr">
-        <is>
-          <t>brouillon</t>
+      <c r="A294" s="6" t="inlineStr">
+        <is>
+          <t>L24</t>
+        </is>
+      </c>
+      <c r="B294" s="6" t="inlineStr">
+        <is>
+          <t>Les conditions matérielles de la vie</t>
+        </is>
+      </c>
+      <c r="C294" s="6" t="inlineStr">
+        <is>
+          <t>en-cours — 5 chapitre(s)</t>
         </is>
       </c>
     </row>
     <row r="295">
-      <c r="A295" s="6" t="inlineStr">
-        <is>
-          <t>L25</t>
-        </is>
-      </c>
-      <c r="B295" s="6" t="inlineStr">
-        <is>
-          <t>Répartition, besoins essentiels et justice sociale</t>
-        </is>
-      </c>
-      <c r="C295" s="6" t="inlineStr">
-        <is>
-          <t>en-cours — 6 chapitre(s)</t>
+      <c r="A295" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    L24.C01</t>
+        </is>
+      </c>
+      <c r="B295" s="3" t="inlineStr">
+        <is>
+          <t>Ce que ce livre doit établir</t>
+        </is>
+      </c>
+      <c r="C295" s="3" t="inlineStr">
+        <is>
+          <t>brouillon</t>
         </is>
       </c>
     </row>
     <row r="296">
       <c r="A296" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L25.C01</t>
+          <t xml:space="preserve">    L24.C02</t>
         </is>
       </c>
       <c r="B296" s="3" t="inlineStr">
         <is>
-          <t>Ce que ce livre doit établir</t>
+          <t>Le seuil juste est plus strict que le seuil sûr</t>
         </is>
       </c>
       <c r="C296" s="3" t="inlineStr">
@@ -24794,12 +25118,12 @@
     <row r="297">
       <c r="A297" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L25.C02</t>
+          <t xml:space="preserve">    L24.C03</t>
         </is>
       </c>
       <c r="B297" s="3" t="inlineStr">
         <is>
-          <t>Le noyau dur, et la charge de la preuve renversée</t>
+          <t>La matière, et le levier commun que les neuf dimensions n'avaient pas</t>
         </is>
       </c>
       <c r="C297" s="3" t="inlineStr">
@@ -24811,12 +25135,12 @@
     <row r="298">
       <c r="A298" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L25.C03</t>
+          <t xml:space="preserve">    L24.C04</t>
         </is>
       </c>
       <c r="B298" s="3" t="inlineStr">
         <is>
-          <t>Ce que le droit oblige à donner, et ce qu'il refuse de réparer</t>
+          <t>Un budget mondial n'est pas partageable</t>
         </is>
       </c>
       <c r="C298" s="3" t="inlineStr">
@@ -24828,12 +25152,12 @@
     <row r="299">
       <c r="A299" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L25.C04</t>
+          <t xml:space="preserve">    L24.C05</t>
         </is>
       </c>
       <c r="B299" s="3" t="inlineStr">
         <is>
-          <t>A34 en droit positif, et le critère que le corpus n'avait pas</t>
+          <t>Portée de la tranche</t>
         </is>
       </c>
       <c r="C299" s="3" t="inlineStr">
@@ -24843,31 +25167,31 @@
       </c>
     </row>
     <row r="300">
-      <c r="A300" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    L25.C05</t>
-        </is>
-      </c>
-      <c r="B300" s="3" t="inlineStr">
-        <is>
-          <t>Le droit différencie sans calculer</t>
-        </is>
-      </c>
-      <c r="C300" s="3" t="inlineStr">
-        <is>
-          <t>brouillon</t>
+      <c r="A300" s="6" t="inlineStr">
+        <is>
+          <t>L25</t>
+        </is>
+      </c>
+      <c r="B300" s="6" t="inlineStr">
+        <is>
+          <t>Répartition, besoins essentiels et justice sociale</t>
+        </is>
+      </c>
+      <c r="C300" s="6" t="inlineStr">
+        <is>
+          <t>en-cours — 6 chapitre(s)</t>
         </is>
       </c>
     </row>
     <row r="301">
       <c r="A301" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L25.C06</t>
+          <t xml:space="preserve">    L25.C01</t>
         </is>
       </c>
       <c r="B301" s="3" t="inlineStr">
         <is>
-          <t>Portée de la tranche</t>
+          <t>Ce que ce livre doit établir</t>
         </is>
       </c>
       <c r="C301" s="3" t="inlineStr">
@@ -24877,31 +25201,31 @@
       </c>
     </row>
     <row r="302">
-      <c r="A302" s="6" t="inlineStr">
-        <is>
-          <t>L26</t>
-        </is>
-      </c>
-      <c r="B302" s="6" t="inlineStr">
-        <is>
-          <t>Thermodynamique, énergie et processus économique</t>
-        </is>
-      </c>
-      <c r="C302" s="6" t="inlineStr">
-        <is>
-          <t>en-cours — 6 chapitre(s)</t>
+      <c r="A302" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    L25.C02</t>
+        </is>
+      </c>
+      <c r="B302" s="3" t="inlineStr">
+        <is>
+          <t>Le noyau dur, et la charge de la preuve renversée</t>
+        </is>
+      </c>
+      <c r="C302" s="3" t="inlineStr">
+        <is>
+          <t>brouillon</t>
         </is>
       </c>
     </row>
     <row r="303">
       <c r="A303" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L26.C01</t>
+          <t xml:space="preserve">    L25.C03</t>
         </is>
       </c>
       <c r="B303" s="3" t="inlineStr">
         <is>
-          <t>Ce que ce livre doit établir</t>
+          <t>Ce que le droit oblige à donner, et ce qu'il refuse de réparer</t>
         </is>
       </c>
       <c r="C303" s="3" t="inlineStr">
@@ -24913,12 +25237,12 @@
     <row r="304">
       <c r="A304" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L26.C02</t>
+          <t xml:space="preserve">    L25.C04</t>
         </is>
       </c>
       <c r="B304" s="3" t="inlineStr">
         <is>
-          <t>Le stock n'existe pas sous la forme demandée</t>
+          <t>A34 en droit positif, et le critère que le corpus n'avait pas</t>
         </is>
       </c>
       <c r="C304" s="3" t="inlineStr">
@@ -24930,12 +25254,12 @@
     <row r="305">
       <c r="A305" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L26.C03</t>
+          <t xml:space="preserve">    L25.C05</t>
         </is>
       </c>
       <c r="B305" s="3" t="inlineStr">
         <is>
-          <t>La frontière décide du chiffre</t>
+          <t>Le droit différencie sans calculer</t>
         </is>
       </c>
       <c r="C305" s="3" t="inlineStr">
@@ -24947,12 +25271,12 @@
     <row r="306">
       <c r="A306" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L26.C04</t>
+          <t xml:space="preserve">    L25.C06</t>
         </is>
       </c>
       <c r="B306" s="3" t="inlineStr">
         <is>
-          <t>L'effet rebond, et ce que le dispositif en hérite sans être une politique d'efficacité</t>
+          <t>Portée de la tranche</t>
         </is>
       </c>
       <c r="C306" s="3" t="inlineStr">
@@ -24962,34 +25286,119 @@
       </c>
     </row>
     <row r="307">
-      <c r="A307" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    L26.C05</t>
-        </is>
-      </c>
-      <c r="B307" s="3" t="inlineStr">
-        <is>
-          <t>L'addition n'est pas la substitution</t>
-        </is>
-      </c>
-      <c r="C307" s="3" t="inlineStr">
-        <is>
-          <t>brouillon</t>
+      <c r="A307" s="6" t="inlineStr">
+        <is>
+          <t>L26</t>
+        </is>
+      </c>
+      <c r="B307" s="6" t="inlineStr">
+        <is>
+          <t>Thermodynamique, énergie et processus économique</t>
+        </is>
+      </c>
+      <c r="C307" s="6" t="inlineStr">
+        <is>
+          <t>en-cours — 6 chapitre(s)</t>
         </is>
       </c>
     </row>
     <row r="308">
       <c r="A308" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">    L26.C01</t>
+        </is>
+      </c>
+      <c r="B308" s="3" t="inlineStr">
+        <is>
+          <t>Ce que ce livre doit établir</t>
+        </is>
+      </c>
+      <c r="C308" s="3" t="inlineStr">
+        <is>
+          <t>brouillon</t>
+        </is>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    L26.C02</t>
+        </is>
+      </c>
+      <c r="B309" s="3" t="inlineStr">
+        <is>
+          <t>Le stock n'existe pas sous la forme demandée</t>
+        </is>
+      </c>
+      <c r="C309" s="3" t="inlineStr">
+        <is>
+          <t>brouillon</t>
+        </is>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    L26.C03</t>
+        </is>
+      </c>
+      <c r="B310" s="3" t="inlineStr">
+        <is>
+          <t>La frontière décide du chiffre</t>
+        </is>
+      </c>
+      <c r="C310" s="3" t="inlineStr">
+        <is>
+          <t>brouillon</t>
+        </is>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    L26.C04</t>
+        </is>
+      </c>
+      <c r="B311" s="3" t="inlineStr">
+        <is>
+          <t>L'effet rebond, et ce que le dispositif en hérite sans être une politique d'efficacité</t>
+        </is>
+      </c>
+      <c r="C311" s="3" t="inlineStr">
+        <is>
+          <t>brouillon</t>
+        </is>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    L26.C05</t>
+        </is>
+      </c>
+      <c r="B312" s="3" t="inlineStr">
+        <is>
+          <t>L'addition n'est pas la substitution</t>
+        </is>
+      </c>
+      <c r="C312" s="3" t="inlineStr">
+        <is>
+          <t>brouillon</t>
+        </is>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">    L26.C06</t>
         </is>
       </c>
-      <c r="B308" s="3" t="inlineStr">
+      <c r="B313" s="3" t="inlineStr">
         <is>
           <t>Portée de la tranche</t>
         </is>
       </c>
-      <c r="C308" s="3" t="inlineStr">
+      <c r="C313" s="3" t="inlineStr">
         <is>
           <t>brouillon</t>
         </is>

--- a/plan-des-livres.xlsx
+++ b/plan-des-livres.xlsx
@@ -13,7 +13,7 @@
     <sheet name="Plan par livre" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Chapitres'!$A$1:$N$286</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Chapitres'!$A$1:$N$290</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -1177,41 +1177,41 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="2" t="inlineStr">
+      <c r="A18" s="4" t="inlineStr">
         <is>
           <t>L16</t>
         </is>
       </c>
-      <c r="B18" s="3" t="inlineStr">
+      <c r="B18" s="5" t="inlineStr">
         <is>
           <t>Typologie comparée des systèmes et alternatives monétaires</t>
         </is>
       </c>
-      <c r="C18" s="3" t="inlineStr">
+      <c r="C18" s="5" t="inlineStr">
         <is>
           <t>cahier-comparatif</t>
         </is>
       </c>
-      <c r="D18" s="3" t="inlineStr">
-        <is>
-          <t>candidat</t>
-        </is>
-      </c>
-      <c r="E18" s="3" t="inlineStr">
+      <c r="D18" s="5" t="inlineStr">
+        <is>
+          <t>en-cours</t>
+        </is>
+      </c>
+      <c r="E18" s="5" t="inlineStr">
         <is>
           <t>non contraignant</t>
         </is>
       </c>
-      <c r="F18" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G18" s="3" t="inlineStr"/>
-      <c r="H18" s="3" t="inlineStr">
+      <c r="F18" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="G18" s="5" t="inlineStr"/>
+      <c r="H18" s="5" t="inlineStr">
         <is>
           <t>Comparer les architectures monétaires selon une grille explicite et situer NEMO IMS parmi les solutions existantes ou proposées</t>
         </is>
       </c>
-      <c r="I18" s="3" t="inlineStr">
+      <c r="I18" s="5" t="inlineStr">
         <is>
           <t>discipline — monnaies souveraines, crédit bancaire, monnaies-marchandises, monnaies locales et libres, cryptoactifs, stablecoins, MNBC, unités de compensation, projets supranationaux</t>
         </is>
@@ -1638,7 +1638,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N286"/>
+  <dimension ref="A1:N290"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -2259,7 +2259,7 @@
       </c>
       <c r="H10" s="3" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="I10" s="3" t="inlineStr"/>
@@ -2267,7 +2267,7 @@
         <v>11</v>
       </c>
       <c r="K10" s="3" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="L10" s="3" t="inlineStr">
         <is>
@@ -2276,7 +2276,7 @@
       </c>
       <c r="M10" s="3" t="inlineStr">
         <is>
-          <t>L1.C01, L1.C03, L1.C05, L1.C07</t>
+          <t>L1.C01, L1.C03, L1.C05, L1.C07, L16.C01, L16.C03</t>
         </is>
       </c>
       <c r="N10" s="3" t="inlineStr">
@@ -2387,7 +2387,7 @@
       </c>
       <c r="H12" s="3" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="I12" s="3" t="inlineStr"/>
@@ -2395,7 +2395,7 @@
         <v>22</v>
       </c>
       <c r="K12" s="3" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="L12" s="3" t="inlineStr">
         <is>
@@ -2404,7 +2404,7 @@
       </c>
       <c r="M12" s="3" t="inlineStr">
         <is>
-          <t>L1.C05, L1.C08, L1.C09</t>
+          <t>L1.C05, L1.C08, L1.C09, L16.C01, L16.C02</t>
         </is>
       </c>
       <c r="N12" s="3" t="inlineStr">
@@ -12415,7 +12415,7 @@
         <v>6</v>
       </c>
       <c r="K170" s="3" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="L170" s="3" t="inlineStr">
         <is>
@@ -12424,7 +12424,7 @@
       </c>
       <c r="M170" s="3" t="inlineStr">
         <is>
-          <t>L1.C17, L1.C19, L1.C20, L1.C21, L1.C27, L1.C29, L19.C03</t>
+          <t>L1.C17, L1.C19, L1.C20, L1.C21, L1.C27, L1.C29, L19.C03, L16.C01</t>
         </is>
       </c>
       <c r="N170" s="3" t="inlineStr">
@@ -12799,7 +12799,7 @@
         <v>5</v>
       </c>
       <c r="K176" s="3" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="L176" s="3" t="inlineStr">
         <is>
@@ -12808,7 +12808,7 @@
       </c>
       <c r="M176" s="3" t="inlineStr">
         <is>
-          <t>L1.C21, L1.C26, L11.C02, L11.C03, L11.C04, L11.C05, L11.C06, L19.C03, L19.C05</t>
+          <t>L1.C21, L1.C26, L11.C02, L11.C03, L11.C04, L11.C05, L11.C06, L19.C03, L19.C05, L16.C01, L16.C03</t>
         </is>
       </c>
       <c r="N176" s="3" t="inlineStr">
@@ -13887,7 +13887,7 @@
         <v>3</v>
       </c>
       <c r="K193" s="3" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L193" s="3" t="inlineStr">
         <is>
@@ -13896,7 +13896,7 @@
       </c>
       <c r="M193" s="3" t="inlineStr">
         <is>
-          <t>L1.C26, L1.C27, L11.C04, L11.C05, L11.C06, L11.C09, L11.C13, L11.C16, L11.C17, L11.C19, L11.C21, L26.C03, L17.C05</t>
+          <t>L1.C26, L1.C27, L11.C04, L11.C05, L11.C06, L11.C09, L11.C13, L11.C16, L11.C17, L11.C19, L11.C21, L26.C03, L17.C05, L16.C02</t>
         </is>
       </c>
       <c r="N193" s="3" t="inlineStr">
@@ -14502,27 +14502,31 @@
       </c>
       <c r="G203" s="3" t="inlineStr">
         <is>
-          <t>descriptif</t>
+          <t>hybride</t>
         </is>
       </c>
       <c r="H203" s="3" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="I203" s="3" t="inlineStr">
-        <is>
-          <t>oui</t>
-        </is>
-      </c>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="I203" s="3" t="inlineStr"/>
       <c r="J203" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K203" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="L203" s="3" t="inlineStr"/>
-      <c r="M203" s="3" t="inlineStr"/>
+        <v>4</v>
+      </c>
+      <c r="L203" s="3" t="inlineStr">
+        <is>
+          <t>monnaie_fondante, demurrage, creation_monetaire, reflux_monetaire, regle_contre_discretion, contrepartie_comptable</t>
+        </is>
+      </c>
+      <c r="M203" s="3" t="inlineStr">
+        <is>
+          <t>L1.C08, L1.C10, L11.C01, L11.C07, L11.C12, L19.C01, L19.C03, L17.C05</t>
+        </is>
+      </c>
       <c r="N203" s="3" t="inlineStr">
         <is>
           <t>corpus/livre-16-typologie-des-alternatives-monetaires/c01-ce-que-ce-livre-doit-etablir.md</t>
@@ -14532,17 +14536,17 @@
     <row r="204">
       <c r="A204" s="2" t="inlineStr">
         <is>
-          <t>L17.C01</t>
+          <t>L16.C02</t>
         </is>
       </c>
       <c r="B204" s="3" t="inlineStr">
         <is>
-          <t>L17</t>
+          <t>L16</t>
         </is>
       </c>
       <c r="C204" s="3" t="inlineStr">
         <is>
-          <t>Ce que ce livre doit établir</t>
+          <t>La réponse à l'objection de fuite existe, et son prix est la propriété foncière</t>
         </is>
       </c>
       <c r="D204" s="3" t="inlineStr">
@@ -14572,41 +14576,41 @@
       </c>
       <c r="I204" s="3" t="inlineStr"/>
       <c r="J204" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K204" s="3" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L204" s="3" t="inlineStr">
         <is>
-          <t>decouplage, sobriete, effet_rebond, limites_planetaires, indicateur_de_progres, degeneratif</t>
+          <t>monnaie_fondante, demurrage, communs, valorisation_des_communs, hierarchie_monetaire</t>
         </is>
       </c>
       <c r="M204" s="3" t="inlineStr">
         <is>
-          <t>L1.C08, L1.C12, L11.C24, L18.C04, L24.C03, L26.C03, L26.C04, L26.C05, L26.C06, L17.C03</t>
+          <t>L1.C10, L11.C07, L11.C24, L16.C01, L19.C03, L25.C05</t>
         </is>
       </c>
       <c r="N204" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-17-apres-la-croissance/c01-ce-que-ce-livre-doit-etablir.md</t>
+          <t>corpus/livre-16-typologie-des-alternatives-monetaires/c02-la-reponse-a-la-fuite-et-son-prix.md</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" s="2" t="inlineStr">
         <is>
-          <t>L17.C02</t>
+          <t>L16.C03</t>
         </is>
       </c>
       <c r="B205" s="3" t="inlineStr">
         <is>
-          <t>L17</t>
+          <t>L16</t>
         </is>
       </c>
       <c r="C205" s="3" t="inlineStr">
         <is>
-          <t>Les sept raisons, testées une par une contre le dispositif</t>
+          <t>Ce que l'expérience a réellement produit, et la sortie était tarifée</t>
         </is>
       </c>
       <c r="D205" s="3" t="inlineStr">
@@ -14643,34 +14647,34 @@
       </c>
       <c r="L205" s="3" t="inlineStr">
         <is>
-          <t>decouplage, effet_rebond, sobriete, qualification_regenerative, externalisation, degeneratif</t>
+          <t>monnaie_fondante, demurrage, reflux_transactionnel, seuil_d_activation, additionnalite</t>
         </is>
       </c>
       <c r="M205" s="3" t="inlineStr">
         <is>
-          <t>L11.C13, L11.C24, L17.C01, L18.C04, L24.C01, L24.C04, L26.C01, L26.C02, L26.C04, L26.C05</t>
+          <t>L1.C08, L11.C01, L11.C07, L11.C24, L16.C01, L16.C02, L19.C03</t>
         </is>
       </c>
       <c r="N205" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-17-apres-la-croissance/c02-les-sept-raisons-testees-contre-le-dispositif.md</t>
+          <t>corpus/livre-16-typologie-des-alternatives-monetaires/c03-ce-que-l-experience-a-produit-et-la-sortie-tarifee.md</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" s="2" t="inlineStr">
         <is>
-          <t>L17.C03</t>
+          <t>L16.C04</t>
         </is>
       </c>
       <c r="B206" s="3" t="inlineStr">
         <is>
-          <t>L17</t>
+          <t>L16</t>
         </is>
       </c>
       <c r="C206" s="3" t="inlineStr">
         <is>
-          <t>La sobriété et l'émission : le dispositif échange du mou contre du dur</t>
+          <t>Une banque centrale conçoit l'instrument pour qu'il ne serve pas de réserve de valeur — et écrit qu'il lui faut des actifs en face</t>
         </is>
       </c>
       <c r="D206" s="3" t="inlineStr">
@@ -14707,34 +14711,34 @@
       </c>
       <c r="L206" s="3" t="inlineStr">
         <is>
-          <t>sobriete, decouplage, robustesse, fenetre_de_reforme, effet_rebond</t>
+          <t>monnaie_fondante, demurrage, hierarchie_monetaire, creation_monetaire, contrepartie_comptable, seuil_d_activation</t>
         </is>
       </c>
       <c r="M206" s="3" t="inlineStr">
         <is>
-          <t>L1.C08, L1.C12, L11.C10, L17.C01, L17.C02, L18.C04, L24.C02, L26.C03, L26.C05</t>
+          <t>L10.C01, L11.C07, L16.C01, L16.C02, L16.C03, L19.C01, L19.C05, L21.C03</t>
         </is>
       </c>
       <c r="N206" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-17-apres-la-croissance/c03-la-sobriete-et-l-emission-un-echange-de-mou-contre-du-dur.md</t>
+          <t>corpus/livre-16-typologie-des-alternatives-monetaires/c04-la-fonte-officielle-et-les-actifs-en-face.md</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" s="2" t="inlineStr">
         <is>
-          <t>L17.C04</t>
+          <t>L16.C05</t>
         </is>
       </c>
       <c r="B207" s="3" t="inlineStr">
         <is>
-          <t>L17</t>
+          <t>L16</t>
         </is>
       </c>
       <c r="C207" s="3" t="inlineStr">
         <is>
-          <t>La seule concrétisation institutionnelle ouverte, et sa seule sanction est de publier ses raisons</t>
+          <t>Portée de la tranche</t>
         </is>
       </c>
       <c r="D207" s="3" t="inlineStr">
@@ -14754,7 +14758,7 @@
       </c>
       <c r="G207" s="3" t="inlineStr">
         <is>
-          <t>hybride</t>
+          <t>descriptif</t>
         </is>
       </c>
       <c r="H207" s="3" t="inlineStr">
@@ -14771,24 +14775,24 @@
       </c>
       <c r="L207" s="3" t="inlineStr">
         <is>
-          <t>indicateur_de_progres, sobriete, regle_contre_discretion, robustesse, polycentricite</t>
+          <t>monnaie_fondante, demurrage, hierarchie_monetaire, contrepartie_comptable, creation_monetaire, regle_contre_discretion</t>
         </is>
       </c>
       <c r="M207" s="3" t="inlineStr">
         <is>
-          <t>L11.C12, L11.C13, L14.C01, L17.C01, L17.C02, L17.C03, L25.C05, L26.C05</t>
+          <t>L1.C08, L1.C10, L11.C01, L11.C07, L11.C24, L16.C01, L16.C02, L16.C03, L16.C04, L19.C01, L19.C03, L21.C03</t>
         </is>
       </c>
       <c r="N207" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-17-apres-la-croissance/c04-la-concretisation-institutionnelle-et-sa-seule-sanction.md</t>
+          <t>corpus/livre-16-typologie-des-alternatives-monetaires/c05-portee-de-la-tranche.md</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" s="2" t="inlineStr">
         <is>
-          <t>L17.C05</t>
+          <t>L17.C01</t>
         </is>
       </c>
       <c r="B208" s="3" t="inlineStr">
@@ -14798,7 +14802,7 @@
       </c>
       <c r="C208" s="3" t="inlineStr">
         <is>
-          <t>Le tableau de bord et le chiffre unique — ce que le corpus perd en refusant d'agréger</t>
+          <t>Ce que ce livre doit établir</t>
         </is>
       </c>
       <c r="D208" s="3" t="inlineStr">
@@ -14828,31 +14832,31 @@
       </c>
       <c r="I208" s="3" t="inlineStr"/>
       <c r="J208" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K208" s="3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L208" s="3" t="inlineStr">
         <is>
-          <t>indicateur_de_progres, bareme, limites_planetaires, sobriete, robustesse</t>
+          <t>decouplage, sobriete, effet_rebond, limites_planetaires, indicateur_de_progres, degeneratif</t>
         </is>
       </c>
       <c r="M208" s="3" t="inlineStr">
         <is>
-          <t>L11.C13, L11.C24, L17.C01, L18.C01, L18.C04, L24.C01, L24.C05, L25.C05, L26.C02</t>
+          <t>L1.C08, L1.C12, L11.C24, L18.C04, L24.C03, L26.C03, L26.C04, L26.C05, L26.C06, L17.C03</t>
         </is>
       </c>
       <c r="N208" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-17-apres-la-croissance/c05-le-tableau-de-bord-et-le-chiffre-unique.md</t>
+          <t>corpus/livre-17-apres-la-croissance/c01-ce-que-ce-livre-doit-etablir.md</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" s="2" t="inlineStr">
         <is>
-          <t>L17.C06</t>
+          <t>L17.C02</t>
         </is>
       </c>
       <c r="B209" s="3" t="inlineStr">
@@ -14862,7 +14866,7 @@
       </c>
       <c r="C209" s="3" t="inlineStr">
         <is>
-          <t>Portée de la tranche</t>
+          <t>Les sept raisons, testées une par une contre le dispositif</t>
         </is>
       </c>
       <c r="D209" s="3" t="inlineStr">
@@ -14882,7 +14886,7 @@
       </c>
       <c r="G209" s="3" t="inlineStr">
         <is>
-          <t>descriptif</t>
+          <t>hybride</t>
         </is>
       </c>
       <c r="H209" s="3" t="inlineStr">
@@ -14899,34 +14903,34 @@
       </c>
       <c r="L209" s="3" t="inlineStr">
         <is>
-          <t>sobriete, decouplage, indicateur_de_progres, effet_rebond, limites_planetaires, robustesse</t>
+          <t>decouplage, effet_rebond, sobriete, qualification_regenerative, externalisation, degeneratif</t>
         </is>
       </c>
       <c r="M209" s="3" t="inlineStr">
         <is>
-          <t>L11.C12, L11.C24, L17.C01, L17.C02, L17.C03, L17.C04, L17.C05, L18.C01, L24.C05, L26.C05</t>
+          <t>L11.C13, L11.C24, L17.C01, L18.C04, L24.C01, L24.C04, L26.C01, L26.C02, L26.C04, L26.C05</t>
         </is>
       </c>
       <c r="N209" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-17-apres-la-croissance/c06-portee-de-la-tranche.md</t>
+          <t>corpus/livre-17-apres-la-croissance/c02-les-sept-raisons-testees-contre-le-dispositif.md</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" s="2" t="inlineStr">
         <is>
-          <t>L18.C01</t>
+          <t>L17.C03</t>
         </is>
       </c>
       <c r="B210" s="3" t="inlineStr">
         <is>
-          <t>L18</t>
+          <t>L17</t>
         </is>
       </c>
       <c r="C210" s="3" t="inlineStr">
         <is>
-          <t>Ce que ce livre doit établir, et le repli n'est pas l'annexe</t>
+          <t>La sobriété et l'émission : le dispositif échange du mou contre du dur</t>
         </is>
       </c>
       <c r="D210" s="3" t="inlineStr">
@@ -14956,41 +14960,41 @@
       </c>
       <c r="I210" s="3" t="inlineStr"/>
       <c r="J210" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="K210" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="K210" s="3" t="n">
-        <v>5</v>
-      </c>
       <c r="L210" s="3" t="inlineStr">
         <is>
-          <t>contrepartie_comptable, valorisation_des_communs, communs, essentiel_insolvable, qualification_regenerative, architecture_invisible</t>
+          <t>sobriete, decouplage, robustesse, fenetre_de_reforme, effet_rebond</t>
         </is>
       </c>
       <c r="M210" s="3" t="inlineStr">
         <is>
-          <t>L1.C09, L1.C29, L5.C02, L5.C09, L5.C10, L6.C08, L6.C09, L6.C13, L11.C13, L11.C16, L20.C02, L17.C05</t>
+          <t>L1.C08, L1.C12, L11.C10, L17.C01, L17.C02, L18.C04, L24.C02, L26.C03, L26.C05</t>
         </is>
       </c>
       <c r="N210" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-18-comptabilites-ecologiques-et-biophysiques/c01-ce-que-ce-livre-doit-etablir.md</t>
+          <t>corpus/livre-17-apres-la-croissance/c03-la-sobriete-et-l-emission-un-echange-de-mou-contre-du-dur.md</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" s="2" t="inlineStr">
         <is>
-          <t>L18.C02</t>
+          <t>L17.C04</t>
         </is>
       </c>
       <c r="B211" s="3" t="inlineStr">
         <is>
-          <t>L18</t>
+          <t>L17</t>
         </is>
       </c>
       <c r="C211" s="3" t="inlineStr">
         <is>
-          <t>La métrologie existe, et ce qu'elle enregistre est l'ordre en place</t>
+          <t>La seule concrétisation institutionnelle ouverte, et sa seule sanction est de publier ses raisons</t>
         </is>
       </c>
       <c r="D211" s="3" t="inlineStr">
@@ -15015,46 +15019,46 @@
       </c>
       <c r="H211" s="3" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="I211" s="3" t="inlineStr"/>
       <c r="J211" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="K211" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="K211" s="3" t="n">
-        <v>3</v>
-      </c>
       <c r="L211" s="3" t="inlineStr">
         <is>
-          <t>valorisation_des_communs, contrepartie_comptable, bareme, essentiel_insolvable, indicateur_de_progres, fausse_richesse</t>
+          <t>indicateur_de_progres, sobriete, regle_contre_discretion, robustesse, polycentricite</t>
         </is>
       </c>
       <c r="M211" s="3" t="inlineStr">
         <is>
-          <t>L1.C09, L1.C15, L1.C18, L6.C06, L11.C03, L11.C07, L11.C13, L11.C16, L18.C01</t>
+          <t>L11.C12, L11.C13, L14.C01, L17.C01, L17.C02, L17.C03, L25.C05, L26.C05</t>
         </is>
       </c>
       <c r="N211" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-18-comptabilites-ecologiques-et-biophysiques/c02-la-metrologie-existe-et-ce-qu-elle-enregistre.md</t>
+          <t>corpus/livre-17-apres-la-croissance/c04-la-concretisation-institutionnelle-et-sa-seule-sanction.md</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" s="2" t="inlineStr">
         <is>
-          <t>L18.C03</t>
+          <t>L17.C05</t>
         </is>
       </c>
       <c r="B212" s="3" t="inlineStr">
         <is>
-          <t>L18</t>
+          <t>L17</t>
         </is>
       </c>
       <c r="C212" s="3" t="inlineStr">
         <is>
-          <t>L'échelle de repli, et qui l'a arrêtée</t>
+          <t>Le tableau de bord et le chiffre unique — ce que le corpus perd en refusant d'agréger</t>
         </is>
       </c>
       <c r="D212" s="3" t="inlineStr">
@@ -15079,46 +15083,46 @@
       </c>
       <c r="H212" s="3" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="I212" s="3" t="inlineStr"/>
       <c r="J212" s="3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K212" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L212" s="3" t="inlineStr">
         <is>
-          <t>contrepartie_comptable, architecture_invisible, valorisation_des_communs, essentiel_insolvable, regle_contre_discretion</t>
+          <t>indicateur_de_progres, bareme, limites_planetaires, sobriete, robustesse</t>
         </is>
       </c>
       <c r="M212" s="3" t="inlineStr">
         <is>
-          <t>L1.C09, L1.C15, L1.C29, L6.C09, L11.C29, L18.C01, L18.C02, L20.C02</t>
+          <t>L11.C13, L11.C24, L17.C01, L18.C01, L18.C04, L24.C01, L24.C05, L25.C05, L26.C02</t>
         </is>
       </c>
       <c r="N212" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-18-comptabilites-ecologiques-et-biophysiques/c03-l-echelle-de-repli-et-qui-l-a-arretee.md</t>
+          <t>corpus/livre-17-apres-la-croissance/c05-le-tableau-de-bord-et-le-chiffre-unique.md</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" s="2" t="inlineStr">
         <is>
-          <t>L18.C04</t>
+          <t>L17.C06</t>
         </is>
       </c>
       <c r="B213" s="3" t="inlineStr">
         <is>
-          <t>L18</t>
+          <t>L17</t>
         </is>
       </c>
       <c r="C213" s="3" t="inlineStr">
         <is>
-          <t>Les grandeurs physiques, et l'endroit où elles frappent le dispositif</t>
+          <t>Portée de la tranche</t>
         </is>
       </c>
       <c r="D213" s="3" t="inlineStr">
@@ -15138,41 +15142,41 @@
       </c>
       <c r="G213" s="3" t="inlineStr">
         <is>
-          <t>hybride</t>
+          <t>descriptif</t>
         </is>
       </c>
       <c r="H213" s="3" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="I213" s="3" t="inlineStr"/>
       <c r="J213" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="K213" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="K213" s="3" t="n">
-        <v>3</v>
-      </c>
       <c r="L213" s="3" t="inlineStr">
         <is>
-          <t>decouplage, effet_rebond, externalisation, limites_planetaires, sobriete, fausse_richesse</t>
+          <t>sobriete, decouplage, indicateur_de_progres, effet_rebond, limites_planetaires, robustesse</t>
         </is>
       </c>
       <c r="M213" s="3" t="inlineStr">
         <is>
-          <t>L1.C02, L1.C03, L1.C04, L5.C08, L6.C08, L11.C10, L11.C24, L18.C01, L18.C02</t>
+          <t>L11.C12, L11.C24, L17.C01, L17.C02, L17.C03, L17.C04, L17.C05, L18.C01, L24.C05, L26.C05</t>
         </is>
       </c>
       <c r="N213" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-18-comptabilites-ecologiques-et-biophysiques/c04-les-grandeurs-physiques-et-ou-elles-frappent.md</t>
+          <t>corpus/livre-17-apres-la-croissance/c06-portee-de-la-tranche.md</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" s="2" t="inlineStr">
         <is>
-          <t>L18.C05</t>
+          <t>L18.C01</t>
         </is>
       </c>
       <c r="B214" s="3" t="inlineStr">
@@ -15182,7 +15186,7 @@
       </c>
       <c r="C214" s="3" t="inlineStr">
         <is>
-          <t>Ce que la norme exclut, et ce n'est pas le commun</t>
+          <t>Ce que ce livre doit établir, et le repli n'est pas l'annexe</t>
         </is>
       </c>
       <c r="D214" s="3" t="inlineStr">
@@ -15207,36 +15211,36 @@
       </c>
       <c r="H214" s="3" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="I214" s="3" t="inlineStr"/>
       <c r="J214" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K214" s="3" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="L214" s="3" t="inlineStr">
         <is>
-          <t>communs, contrepartie_comptable, valorisation_des_communs, architecture_invisible, monnaie_comme_registre, creation_monetaire</t>
+          <t>contrepartie_comptable, valorisation_des_communs, communs, essentiel_insolvable, qualification_regenerative, architecture_invisible</t>
         </is>
       </c>
       <c r="M214" s="3" t="inlineStr">
         <is>
-          <t>L1.C09, L1.C20, L1.C29, L6.C06, L6.C08, L11.C13, L11.C16, L18.C01, L18.C02, L18.C03, L20.C02</t>
+          <t>L1.C09, L1.C29, L5.C02, L5.C09, L5.C10, L6.C08, L6.C09, L6.C13, L11.C13, L11.C16, L20.C02, L17.C05</t>
         </is>
       </c>
       <c r="N214" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-18-comptabilites-ecologiques-et-biophysiques/c05-ce-que-la-norme-exclut-et-ce-n-est-pas-le-commun.md</t>
+          <t>corpus/livre-18-comptabilites-ecologiques-et-biophysiques/c01-ce-que-ce-livre-doit-etablir.md</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" s="2" t="inlineStr">
         <is>
-          <t>L18.C06</t>
+          <t>L18.C02</t>
         </is>
       </c>
       <c r="B215" s="3" t="inlineStr">
@@ -15246,7 +15250,7 @@
       </c>
       <c r="C215" s="3" t="inlineStr">
         <is>
-          <t>Portée de la tranche, et une neuvième condition proposée</t>
+          <t>La métrologie existe, et ce qu'elle enregistre est l'ordre en place</t>
         </is>
       </c>
       <c r="D215" s="3" t="inlineStr">
@@ -15266,7 +15270,7 @@
       </c>
       <c r="G215" s="3" t="inlineStr">
         <is>
-          <t>conception</t>
+          <t>hybride</t>
         </is>
       </c>
       <c r="H215" s="3" t="inlineStr">
@@ -15276,31 +15280,31 @@
       </c>
       <c r="I215" s="3" t="inlineStr"/>
       <c r="J215" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K215" s="3" t="n">
         <v>3</v>
       </c>
       <c r="L215" s="3" t="inlineStr">
         <is>
-          <t>contrepartie_comptable, communs, valorisation_des_communs, architecture_invisible, essentiel_insolvable</t>
+          <t>valorisation_des_communs, contrepartie_comptable, bareme, essentiel_insolvable, indicateur_de_progres, fausse_richesse</t>
         </is>
       </c>
       <c r="M215" s="3" t="inlineStr">
         <is>
-          <t>L1.C09, L1.C18, L1.C20, L1.C29, L5.C02, L5.C08, L6.C06, L6.C08, L11.C13, L11.C16, L18.C01, L18.C02, L18.C03, L18.C04, L18.C05, L20.C02</t>
+          <t>L1.C09, L1.C15, L1.C18, L6.C06, L11.C03, L11.C07, L11.C13, L11.C16, L18.C01</t>
         </is>
       </c>
       <c r="N215" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-18-comptabilites-ecologiques-et-biophysiques/c06-portee-de-la-tranche-et-une-neuvieme-condition.md</t>
+          <t>corpus/livre-18-comptabilites-ecologiques-et-biophysiques/c02-la-metrologie-existe-et-ce-qu-elle-enregistre.md</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" s="2" t="inlineStr">
         <is>
-          <t>L18.C07</t>
+          <t>L18.C03</t>
         </is>
       </c>
       <c r="B216" s="3" t="inlineStr">
@@ -15310,7 +15314,7 @@
       </c>
       <c r="C216" s="3" t="inlineStr">
         <is>
-          <t>CARE/TDL répare deux objections, et en crée une plus grave</t>
+          <t>L'échelle de repli, et qui l'a arrêtée</t>
         </is>
       </c>
       <c r="D216" s="3" t="inlineStr">
@@ -15340,31 +15344,31 @@
       </c>
       <c r="I216" s="3" t="inlineStr"/>
       <c r="J216" s="3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K216" s="3" t="n">
         <v>3</v>
       </c>
       <c r="L216" s="3" t="inlineStr">
         <is>
-          <t>contrepartie_comptable, bareme, valorisation_des_communs, communs, architecture_invisible, fausse_richesse</t>
+          <t>contrepartie_comptable, architecture_invisible, valorisation_des_communs, essentiel_insolvable, regle_contre_discretion</t>
         </is>
       </c>
       <c r="M216" s="3" t="inlineStr">
         <is>
-          <t>L1.C09, L1.C18, L1.C20, L6.C06, L11.C03, L11.C13, L11.C16, L18.C01, L18.C02, L18.C05, L18.C06</t>
+          <t>L1.C09, L1.C15, L1.C29, L6.C09, L11.C29, L18.C01, L18.C02, L20.C02</t>
         </is>
       </c>
       <c r="N216" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-18-comptabilites-ecologiques-et-biophysiques/c07-care-tdl-repare-une-objection-et-en-cree-une-autre.md</t>
+          <t>corpus/livre-18-comptabilites-ecologiques-et-biophysiques/c03-l-echelle-de-repli-et-qui-l-a-arretee.md</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" s="2" t="inlineStr">
         <is>
-          <t>L18.C08</t>
+          <t>L18.C04</t>
         </is>
       </c>
       <c r="B217" s="3" t="inlineStr">
@@ -15374,7 +15378,7 @@
       </c>
       <c r="C217" s="3" t="inlineStr">
         <is>
-          <t>Le modèle au périmètre du dispositif, et F9 révisée</t>
+          <t>Les grandeurs physiques, et l'endroit où elles frappent le dispositif</t>
         </is>
       </c>
       <c r="D217" s="3" t="inlineStr">
@@ -15394,7 +15398,7 @@
       </c>
       <c r="G217" s="3" t="inlineStr">
         <is>
-          <t>conception</t>
+          <t>hybride</t>
         </is>
       </c>
       <c r="H217" s="3" t="inlineStr">
@@ -15411,24 +15415,24 @@
       </c>
       <c r="L217" s="3" t="inlineStr">
         <is>
-          <t>contrepartie_comptable, communs, valorisation_des_communs, polycentricite, essentiel_insolvable, indicateur_de_progres</t>
+          <t>decouplage, effet_rebond, externalisation, limites_planetaires, sobriete, fausse_richesse</t>
         </is>
       </c>
       <c r="M217" s="3" t="inlineStr">
         <is>
-          <t>L1.C09, L1.C18, L6.C06, L7.C05, L11.C13, L11.C16, L11.C25, L18.C01, L18.C02, L18.C05, L18.C06, L18.C07</t>
+          <t>L1.C02, L1.C03, L1.C04, L5.C08, L6.C08, L11.C10, L11.C24, L18.C01, L18.C02</t>
         </is>
       </c>
       <c r="N217" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-18-comptabilites-ecologiques-et-biophysiques/c08-le-modele-au-perimetre-du-dispositif-et-f9-revisee.md</t>
+          <t>corpus/livre-18-comptabilites-ecologiques-et-biophysiques/c04-les-grandeurs-physiques-et-ou-elles-frappent.md</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" s="2" t="inlineStr">
         <is>
-          <t>L18.C09</t>
+          <t>L18.C05</t>
         </is>
       </c>
       <c r="B218" s="3" t="inlineStr">
@@ -15438,7 +15442,7 @@
       </c>
       <c r="C218" s="3" t="inlineStr">
         <is>
-          <t>L'ordre de grandeur, et le concurrent qu'il désigne</t>
+          <t>Ce que la norme exclut, et ce n'est pas le commun</t>
         </is>
       </c>
       <c r="D218" s="3" t="inlineStr">
@@ -15463,7 +15467,7 @@
       </c>
       <c r="H218" s="3" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="I218" s="3" t="inlineStr"/>
@@ -15471,38 +15475,38 @@
         <v>3</v>
       </c>
       <c r="K218" s="3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L218" s="3" t="inlineStr">
         <is>
-          <t>essentiel_insolvable, valorisation_des_communs, externalisation, additionnalite, fausse_richesse, degeneratif</t>
+          <t>communs, contrepartie_comptable, valorisation_des_communs, architecture_invisible, monnaie_comme_registre, creation_monetaire</t>
         </is>
       </c>
       <c r="M218" s="3" t="inlineStr">
         <is>
-          <t>L1.C15, L1.C18, L5.C07, L10.C04, L10.C06, L11.C03, L11.C13, L18.C01, L18.C04, L18.C06, L26.C05</t>
+          <t>L1.C09, L1.C20, L1.C29, L6.C06, L6.C08, L11.C13, L11.C16, L18.C01, L18.C02, L18.C03, L20.C02</t>
         </is>
       </c>
       <c r="N218" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-18-comptabilites-ecologiques-et-biophysiques/c09-l-ordre-de-grandeur-et-le-concurrent-qu-il-designe.md</t>
+          <t>corpus/livre-18-comptabilites-ecologiques-et-biophysiques/c05-ce-que-la-norme-exclut-et-ce-n-est-pas-le-commun.md</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" s="2" t="inlineStr">
         <is>
-          <t>L19.C01</t>
+          <t>L18.C06</t>
         </is>
       </c>
       <c r="B219" s="3" t="inlineStr">
         <is>
-          <t>L19</t>
+          <t>L18</t>
         </is>
       </c>
       <c r="C219" s="3" t="inlineStr">
         <is>
-          <t>Ce que ce livre doit établir</t>
+          <t>Portée de la tranche, et une neuvième condition proposée</t>
         </is>
       </c>
       <c r="D219" s="3" t="inlineStr">
@@ -15522,51 +15526,51 @@
       </c>
       <c r="G219" s="3" t="inlineStr">
         <is>
-          <t>hybride</t>
+          <t>conception</t>
         </is>
       </c>
       <c r="H219" s="3" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="I219" s="3" t="inlineStr"/>
       <c r="J219" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K219" s="3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L219" s="3" t="inlineStr">
         <is>
-          <t>contrepartie_comptable, creation_monetaire, monnaie_comme_registre, hierarchie_monetaire, reflux_collectif</t>
+          <t>contrepartie_comptable, communs, valorisation_des_communs, architecture_invisible, essentiel_insolvable</t>
         </is>
       </c>
       <c r="M219" s="3" t="inlineStr">
         <is>
-          <t>L1.C07, L10.C01, L10.C06, L11.C01, L11.C02, L18.C06, L21.C01, L21.C03</t>
+          <t>L1.C09, L1.C18, L1.C20, L1.C29, L5.C02, L5.C08, L6.C06, L6.C08, L11.C13, L11.C16, L18.C01, L18.C02, L18.C03, L18.C04, L18.C05, L20.C02</t>
         </is>
       </c>
       <c r="N219" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-19-comptabilite-monetaire-de-l-emission-sans-dette/c01-ce-que-ce-livre-doit-etablir.md</t>
+          <t>corpus/livre-18-comptabilites-ecologiques-et-biophysiques/c06-portee-de-la-tranche-et-une-neuvieme-condition.md</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" s="2" t="inlineStr">
         <is>
-          <t>L19.C02</t>
+          <t>L18.C07</t>
         </is>
       </c>
       <c r="B220" s="3" t="inlineStr">
         <is>
-          <t>L19</t>
+          <t>L18</t>
         </is>
       </c>
       <c r="C220" s="3" t="inlineStr">
         <is>
-          <t>Le seul précédent, et le passif lui a été reconnu en 2008</t>
+          <t>CARE/TDL répare deux objections, et en crée une plus grave</t>
         </is>
       </c>
       <c r="D220" s="3" t="inlineStr">
@@ -15591,46 +15595,46 @@
       </c>
       <c r="H220" s="3" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="I220" s="3" t="inlineStr"/>
       <c r="J220" s="3" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K220" s="3" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="L220" s="3" t="inlineStr">
         <is>
-          <t>contrepartie_comptable, reflux_collectif, hierarchie_monetaire, creation_monetaire, devise_cle</t>
+          <t>contrepartie_comptable, bareme, valorisation_des_communs, communs, architecture_invisible, fausse_richesse</t>
         </is>
       </c>
       <c r="M220" s="3" t="inlineStr">
         <is>
-          <t>L3.C09, L10.C06, L11.C01, L11.C02, L19.C01, L20.C09, L21.C01, L21.C03, L21.C05, L19.C06</t>
+          <t>L1.C09, L1.C18, L1.C20, L6.C06, L11.C03, L11.C13, L11.C16, L18.C01, L18.C02, L18.C05, L18.C06</t>
         </is>
       </c>
       <c r="N220" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-19-comptabilite-monetaire-de-l-emission-sans-dette/c02-le-seul-precedent-et-le-passif-reconnu-en-2008.md</t>
+          <t>corpus/livre-18-comptabilites-ecologiques-et-biophysiques/c07-care-tdl-repare-une-objection-et-en-cree-une-autre.md</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" s="2" t="inlineStr">
         <is>
-          <t>L19.C03</t>
+          <t>L18.C08</t>
         </is>
       </c>
       <c r="B221" s="3" t="inlineStr">
         <is>
-          <t>L19</t>
+          <t>L18</t>
         </is>
       </c>
       <c r="C221" s="3" t="inlineStr">
         <is>
-          <t>Le reflux est un intérêt négatif, ou une répudiation — et c'est le moment qui décide</t>
+          <t>Le modèle au périmètre du dispositif, et F9 révisée</t>
         </is>
       </c>
       <c r="D221" s="3" t="inlineStr">
@@ -15650,51 +15654,51 @@
       </c>
       <c r="G221" s="3" t="inlineStr">
         <is>
-          <t>hybride</t>
+          <t>conception</t>
         </is>
       </c>
       <c r="H221" s="3" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="I221" s="3" t="inlineStr"/>
       <c r="J221" s="3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K221" s="3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L221" s="3" t="inlineStr">
         <is>
-          <t>monnaie_fondante, demurrage, reflux_monetaire, reflux_transactionnel, regle_contre_discretion, contrepartie_comptable</t>
+          <t>contrepartie_comptable, communs, valorisation_des_communs, polycentricite, essentiel_insolvable, indicateur_de_progres</t>
         </is>
       </c>
       <c r="M221" s="3" t="inlineStr">
         <is>
-          <t>L10.C06, L11.C01, L11.C02, L11.C05, L11.C07, L11.C27, L19.C01, L19.C02, L21.C01</t>
+          <t>L1.C09, L1.C18, L6.C06, L7.C05, L11.C13, L11.C16, L11.C25, L18.C01, L18.C02, L18.C05, L18.C06, L18.C07</t>
         </is>
       </c>
       <c r="N221" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-19-comptabilite-monetaire-de-l-emission-sans-dette/c03-le-reflux-interet-negatif-ou-repudiation.md</t>
+          <t>corpus/livre-18-comptabilites-ecologiques-et-biophysiques/c08-le-modele-au-perimetre-du-dispositif-et-f9-revisee.md</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" s="2" t="inlineStr">
         <is>
-          <t>L19.C04</t>
+          <t>L18.C09</t>
         </is>
       </c>
       <c r="B222" s="3" t="inlineStr">
         <is>
-          <t>L19</t>
+          <t>L18</t>
         </is>
       </c>
       <c r="C222" s="3" t="inlineStr">
         <is>
-          <t>L'actif transitoire n'existe pas, et le problème change de bilan</t>
+          <t>L'ordre de grandeur, et le concurrent qu'il désigne</t>
         </is>
       </c>
       <c r="D222" s="3" t="inlineStr">
@@ -15724,31 +15728,31 @@
       </c>
       <c r="I222" s="3" t="inlineStr"/>
       <c r="J222" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K222" s="3" t="n">
         <v>4</v>
       </c>
       <c r="L222" s="3" t="inlineStr">
         <is>
-          <t>contrepartie_comptable, hierarchie_monetaire, creation_monetaire, monnaie_comme_registre, solvabilite_anticipee</t>
+          <t>essentiel_insolvable, valorisation_des_communs, externalisation, additionnalite, fausse_richesse, degeneratif</t>
         </is>
       </c>
       <c r="M222" s="3" t="inlineStr">
         <is>
-          <t>L1.C07, L10.C06, L10.C07, L11.C01, L11.C02, L19.C01, L19.C02, L19.C03, L21.C03</t>
+          <t>L1.C15, L1.C18, L5.C07, L10.C04, L10.C06, L11.C03, L11.C13, L18.C01, L18.C04, L18.C06, L26.C05</t>
         </is>
       </c>
       <c r="N222" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-19-comptabilite-monetaire-de-l-emission-sans-dette/c04-l-actif-transitoire-et-le-deplacement-du-probleme.md</t>
+          <t>corpus/livre-18-comptabilites-ecologiques-et-biophysiques/c09-l-ordre-de-grandeur-et-le-concurrent-qu-il-designe.md</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" s="2" t="inlineStr">
         <is>
-          <t>L19.C05</t>
+          <t>L19.C01</t>
         </is>
       </c>
       <c r="B223" s="3" t="inlineStr">
@@ -15758,7 +15762,7 @@
       </c>
       <c r="C223" s="3" t="inlineStr">
         <is>
-          <t>Un débiteur collectif n'existe pas — sauf comme somme de débiteurs identifiés</t>
+          <t>Ce que ce livre doit établir</t>
         </is>
       </c>
       <c r="D223" s="3" t="inlineStr">
@@ -15791,28 +15795,28 @@
         <v>2</v>
       </c>
       <c r="K223" s="3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L223" s="3" t="inlineStr">
         <is>
-          <t>reflux_collectif, contrepartie_comptable, demurrage, monnaie_fondante, hierarchie_monetaire</t>
+          <t>contrepartie_comptable, creation_monetaire, monnaie_comme_registre, hierarchie_monetaire, reflux_collectif</t>
         </is>
       </c>
       <c r="M223" s="3" t="inlineStr">
         <is>
-          <t>L10.C06, L11.C05, L11.C07, L11.C09, L19.C01, L19.C02, L19.C03, L21.C01, L25.C05</t>
+          <t>L1.C07, L10.C01, L10.C06, L11.C01, L11.C02, L18.C06, L21.C01, L21.C03, L16.C04</t>
         </is>
       </c>
       <c r="N223" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-19-comptabilite-monetaire-de-l-emission-sans-dette/c05-le-creancier-collectif-et-ce-qui-le-rend-representable.md</t>
+          <t>corpus/livre-19-comptabilite-monetaire-de-l-emission-sans-dette/c01-ce-que-ce-livre-doit-etablir.md</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" s="2" t="inlineStr">
         <is>
-          <t>L19.C06</t>
+          <t>L19.C02</t>
         </is>
       </c>
       <c r="B224" s="3" t="inlineStr">
@@ -15822,7 +15826,7 @@
       </c>
       <c r="C224" s="3" t="inlineStr">
         <is>
-          <t>Les fonds propres négatifs, et l'institution qui n'apparaît dans les comptes de personne</t>
+          <t>Le seul précédent, et le passif lui a été reconnu en 2008</t>
         </is>
       </c>
       <c r="D224" s="3" t="inlineStr">
@@ -15855,28 +15859,28 @@
         <v>1</v>
       </c>
       <c r="K224" s="3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L224" s="3" t="inlineStr">
         <is>
-          <t>contrepartie_comptable, solvabilite_anticipee, architecture_invisible, hierarchie_monetaire, robustesse</t>
+          <t>contrepartie_comptable, reflux_collectif, hierarchie_monetaire, creation_monetaire, devise_cle</t>
         </is>
       </c>
       <c r="M224" s="3" t="inlineStr">
         <is>
-          <t>L1.C07, L7.C06, L14.C01, L19.C01, L19.C02, L19.C03, L19.C04, L21.C01, L21.C04</t>
+          <t>L3.C09, L10.C06, L11.C01, L11.C02, L19.C01, L20.C09, L21.C01, L21.C03, L21.C05, L19.C06</t>
         </is>
       </c>
       <c r="N224" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-19-comptabilite-monetaire-de-l-emission-sans-dette/c06-les-fonds-propres-negatifs-et-l-institution-qui-n-apparait-nulle-part.md</t>
+          <t>corpus/livre-19-comptabilite-monetaire-de-l-emission-sans-dette/c02-le-seul-precedent-et-le-passif-reconnu-en-2008.md</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" s="2" t="inlineStr">
         <is>
-          <t>L19.C07</t>
+          <t>L19.C03</t>
         </is>
       </c>
       <c r="B225" s="3" t="inlineStr">
@@ -15886,7 +15890,7 @@
       </c>
       <c r="C225" s="3" t="inlineStr">
         <is>
-          <t>Portée de la tranche</t>
+          <t>Le reflux est un intérêt négatif, ou une répudiation — et c'est le moment qui décide</t>
         </is>
       </c>
       <c r="D225" s="3" t="inlineStr">
@@ -15906,7 +15910,7 @@
       </c>
       <c r="G225" s="3" t="inlineStr">
         <is>
-          <t>descriptif</t>
+          <t>hybride</t>
         </is>
       </c>
       <c r="H225" s="3" t="inlineStr">
@@ -15916,41 +15920,41 @@
       </c>
       <c r="I225" s="3" t="inlineStr"/>
       <c r="J225" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K225" s="3" t="n">
         <v>4</v>
       </c>
       <c r="L225" s="3" t="inlineStr">
         <is>
-          <t>contrepartie_comptable, reflux_collectif, monnaie_fondante, hierarchie_monetaire, architecture_invisible, creation_monetaire</t>
+          <t>monnaie_fondante, demurrage, reflux_monetaire, reflux_transactionnel, regle_contre_discretion, contrepartie_comptable</t>
         </is>
       </c>
       <c r="M225" s="3" t="inlineStr">
         <is>
-          <t>L10.C06, L11.C01, L11.C02, L11.C07, L19.C01, L19.C02, L19.C03, L19.C04, L19.C05, L19.C06, L21.C01, L21.C03</t>
+          <t>L10.C06, L11.C01, L11.C02, L11.C05, L11.C07, L11.C27, L19.C01, L19.C02, L21.C01</t>
         </is>
       </c>
       <c r="N225" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-19-comptabilite-monetaire-de-l-emission-sans-dette/c07-portee-de-la-tranche.md</t>
+          <t>corpus/livre-19-comptabilite-monetaire-de-l-emission-sans-dette/c03-le-reflux-interet-negatif-ou-repudiation.md</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" s="2" t="inlineStr">
         <is>
-          <t>L20.C01</t>
+          <t>L19.C04</t>
         </is>
       </c>
       <c r="B226" s="3" t="inlineStr">
         <is>
-          <t>L20</t>
+          <t>L19</t>
         </is>
       </c>
       <c r="C226" s="3" t="inlineStr">
         <is>
-          <t>Ce que ce livre doit établir</t>
+          <t>L'actif transitoire n'existe pas, et le problème change de bilan</t>
         </is>
       </c>
       <c r="D226" s="3" t="inlineStr">
@@ -15970,51 +15974,51 @@
       </c>
       <c r="G226" s="3" t="inlineStr">
         <is>
-          <t>conception</t>
+          <t>hybride</t>
         </is>
       </c>
       <c r="H226" s="3" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="I226" s="3" t="inlineStr"/>
       <c r="J226" s="3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K226" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L226" s="3" t="inlineStr">
         <is>
-          <t>fenetre_de_reforme, referentiel_de_change, communs, limites_planetaires, creation_monetaire</t>
+          <t>contrepartie_comptable, hierarchie_monetaire, creation_monetaire, monnaie_comme_registre, solvabilite_anticipee</t>
         </is>
       </c>
       <c r="M226" s="3" t="inlineStr">
         <is>
-          <t>L1.C18, L1.C25, L1.C27, L7.C01, L7.C03, L7.C13, L7.C17, L7.C21, L11.C24</t>
+          <t>L1.C07, L10.C06, L10.C07, L11.C01, L11.C02, L19.C01, L19.C02, L19.C03, L21.C03</t>
         </is>
       </c>
       <c r="N226" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-20-droit-international-monetaire-et-commercial/c01-ce-que-ce-livre-doit-etablir.md</t>
+          <t>corpus/livre-19-comptabilite-monetaire-de-l-emission-sans-dette/c04-l-actif-transitoire-et-le-deplacement-du-probleme.md</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" s="2" t="inlineStr">
         <is>
-          <t>L20.C02</t>
+          <t>L19.C05</t>
         </is>
       </c>
       <c r="B227" s="3" t="inlineStr">
         <is>
-          <t>L20</t>
+          <t>L19</t>
         </is>
       </c>
       <c r="C227" s="3" t="inlineStr">
         <is>
-          <t>L'interdiction du financement monétaire</t>
+          <t>Un débiteur collectif n'existe pas — sauf comme somme de débiteurs identifiés</t>
         </is>
       </c>
       <c r="D227" s="3" t="inlineStr">
@@ -16034,51 +16038,51 @@
       </c>
       <c r="G227" s="3" t="inlineStr">
         <is>
-          <t>conception</t>
+          <t>hybride</t>
         </is>
       </c>
       <c r="H227" s="3" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="I227" s="3" t="inlineStr"/>
       <c r="J227" s="3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K227" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L227" s="3" t="inlineStr">
         <is>
-          <t>creation_monetaire, contrepartie_comptable, reflux_collectif, fenetre_de_reforme</t>
+          <t>reflux_collectif, contrepartie_comptable, demurrage, monnaie_fondante, hierarchie_monetaire</t>
         </is>
       </c>
       <c r="M227" s="3" t="inlineStr">
         <is>
-          <t>L1.C05, L1.C18, L1.C20, L1.C22, L7.C11, L7.C13, L11.C10, L20.C01</t>
+          <t>L10.C06, L11.C05, L11.C07, L11.C09, L19.C01, L19.C02, L19.C03, L21.C01, L25.C05</t>
         </is>
       </c>
       <c r="N227" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-20-droit-international-monetaire-et-commercial/c02-l-interdiction-du-financement-monetaire.md</t>
+          <t>corpus/livre-19-comptabilite-monetaire-de-l-emission-sans-dette/c05-le-creancier-collectif-et-ce-qui-le-rend-representable.md</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" s="2" t="inlineStr">
         <is>
-          <t>L20.C03</t>
+          <t>L19.C06</t>
         </is>
       </c>
       <c r="B228" s="3" t="inlineStr">
         <is>
-          <t>L20</t>
+          <t>L19</t>
         </is>
       </c>
       <c r="C228" s="3" t="inlineStr">
         <is>
-          <t>L'objectif principal et ce qu'il exclut</t>
+          <t>Les fonds propres négatifs, et l'institution qui n'apparaît dans les comptes de personne</t>
         </is>
       </c>
       <c r="D228" s="3" t="inlineStr">
@@ -16098,51 +16102,51 @@
       </c>
       <c r="G228" s="3" t="inlineStr">
         <is>
-          <t>conception</t>
+          <t>hybride</t>
         </is>
       </c>
       <c r="H228" s="3" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="I228" s="3" t="inlineStr"/>
       <c r="J228" s="3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K228" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L228" s="3" t="inlineStr">
         <is>
-          <t>regle_contre_discretion, limites_planetaires, creation_monetaire, plafond_ecologique</t>
+          <t>contrepartie_comptable, solvabilite_anticipee, architecture_invisible, hierarchie_monetaire, robustesse</t>
         </is>
       </c>
       <c r="M228" s="3" t="inlineStr">
         <is>
-          <t>L1.C01, L1.C18, L1.C20, L7.C03, L8.C12, L8.C34, L11.C16, L20.C01, L20.C02</t>
+          <t>L1.C07, L7.C06, L14.C01, L19.C01, L19.C02, L19.C03, L19.C04, L21.C01, L21.C04</t>
         </is>
       </c>
       <c r="N228" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-20-droit-international-monetaire-et-commercial/c03-l-objectif-principal-et-ce-qu-il-exclut.md</t>
+          <t>corpus/livre-19-comptabilite-monetaire-de-l-emission-sans-dette/c06-les-fonds-propres-negatifs-et-l-institution-qui-n-apparait-nulle-part.md</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" s="2" t="inlineStr">
         <is>
-          <t>L20.C04</t>
+          <t>L19.C07</t>
         </is>
       </c>
       <c r="B229" s="3" t="inlineStr">
         <is>
-          <t>L20</t>
+          <t>L19</t>
         </is>
       </c>
       <c r="C229" s="3" t="inlineStr">
         <is>
-          <t>L'indépendance, et à l'égard de qui</t>
+          <t>Portée de la tranche</t>
         </is>
       </c>
       <c r="D229" s="3" t="inlineStr">
@@ -16162,41 +16166,41 @@
       </c>
       <c r="G229" s="3" t="inlineStr">
         <is>
-          <t>conception</t>
+          <t>descriptif</t>
         </is>
       </c>
       <c r="H229" s="3" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="I229" s="3" t="inlineStr"/>
       <c r="J229" s="3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K229" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L229" s="3" t="inlineStr">
         <is>
-          <t>regle_contre_discretion, creation_monetaire, fenetre_de_reforme</t>
+          <t>contrepartie_comptable, reflux_collectif, monnaie_fondante, hierarchie_monetaire, architecture_invisible, creation_monetaire</t>
         </is>
       </c>
       <c r="M229" s="3" t="inlineStr">
         <is>
-          <t>L1.C18, L7.C04, L7.C07, L7.C10, L8.C31, L11.C17, L20.C01, L20.C03, L20.C11</t>
+          <t>L10.C06, L11.C01, L11.C02, L11.C07, L19.C01, L19.C02, L19.C03, L19.C04, L19.C05, L19.C06, L21.C01, L21.C03</t>
         </is>
       </c>
       <c r="N229" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-20-droit-international-monetaire-et-commercial/c04-l-independance-et-a-l-egard-de-qui.md</t>
+          <t>corpus/livre-19-comptabilite-monetaire-de-l-emission-sans-dette/c07-portee-de-la-tranche.md</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" s="2" t="inlineStr">
         <is>
-          <t>L20.C05</t>
+          <t>L20.C01</t>
         </is>
       </c>
       <c r="B230" s="3" t="inlineStr">
@@ -16206,7 +16210,7 @@
       </c>
       <c r="C230" s="3" t="inlineStr">
         <is>
-          <t>Le monopole d'émission et le cours légal</t>
+          <t>Ce que ce livre doit établir</t>
         </is>
       </c>
       <c r="D230" s="3" t="inlineStr">
@@ -16231,7 +16235,7 @@
       </c>
       <c r="H230" s="3" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="I230" s="3" t="inlineStr"/>
@@ -16243,24 +16247,24 @@
       </c>
       <c r="L230" s="3" t="inlineStr">
         <is>
-          <t>monnaie_comme_registre, creation_monetaire, referentiel_de_change, hierarchie_monetaire</t>
+          <t>fenetre_de_reforme, referentiel_de_change, communs, limites_planetaires, creation_monetaire</t>
         </is>
       </c>
       <c r="M230" s="3" t="inlineStr">
         <is>
-          <t>L1.C05, L1.C07, L1.C26, L7.C15, L11.C15, L20.C01, L20.C02, L20.C03</t>
+          <t>L1.C18, L1.C25, L1.C27, L7.C01, L7.C03, L7.C13, L7.C17, L7.C21, L11.C24</t>
         </is>
       </c>
       <c r="N230" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-20-droit-international-monetaire-et-commercial/c05-le-monopole-d-emission-et-le-cours-legal.md</t>
+          <t>corpus/livre-20-droit-international-monetaire-et-commercial/c01-ce-que-ce-livre-doit-etablir.md</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" s="2" t="inlineStr">
         <is>
-          <t>L20.C06</t>
+          <t>L20.C02</t>
         </is>
       </c>
       <c r="B231" s="3" t="inlineStr">
@@ -16270,7 +16274,7 @@
       </c>
       <c r="C231" s="3" t="inlineStr">
         <is>
-          <t>Les voies de révision et leur coût</t>
+          <t>L'interdiction du financement monétaire</t>
         </is>
       </c>
       <c r="D231" s="3" t="inlineStr">
@@ -16295,36 +16299,36 @@
       </c>
       <c r="H231" s="3" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="I231" s="3" t="inlineStr"/>
       <c r="J231" s="3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K231" s="3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L231" s="3" t="inlineStr">
         <is>
-          <t>fenetre_de_reforme, regle_contre_discretion, creation_monetaire</t>
+          <t>creation_monetaire, contrepartie_comptable, reflux_collectif, fenetre_de_reforme</t>
         </is>
       </c>
       <c r="M231" s="3" t="inlineStr">
         <is>
-          <t>L1.C18, L7.C12, L7.C20, L7.C21, L11.C15, L20.C01, L20.C02, L20.C03, L20.C07, L20.C09, L20.C18</t>
+          <t>L1.C05, L1.C18, L1.C20, L1.C22, L7.C11, L7.C13, L11.C10, L20.C01</t>
         </is>
       </c>
       <c r="N231" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-20-droit-international-monetaire-et-commercial/c06-les-voies-de-revision-et-leur-cout.md</t>
+          <t>corpus/livre-20-droit-international-monetaire-et-commercial/c02-l-interdiction-du-financement-monetaire.md</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="A232" s="2" t="inlineStr">
         <is>
-          <t>L20.C07</t>
+          <t>L20.C03</t>
         </is>
       </c>
       <c r="B232" s="3" t="inlineStr">
@@ -16334,7 +16338,7 @@
       </c>
       <c r="C232" s="3" t="inlineStr">
         <is>
-          <t>L'accord monétaire international</t>
+          <t>L'objectif principal et ce qu'il exclut</t>
         </is>
       </c>
       <c r="D232" s="3" t="inlineStr">
@@ -16359,7 +16363,7 @@
       </c>
       <c r="H232" s="3" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="I232" s="3" t="inlineStr"/>
@@ -16371,24 +16375,24 @@
       </c>
       <c r="L232" s="3" t="inlineStr">
         <is>
-          <t>referentiel_de_change, fenetre_de_reforme, etalon_de_change_or, hierarchie_monetaire</t>
+          <t>regle_contre_discretion, limites_planetaires, creation_monetaire, plafond_ecologique</t>
         </is>
       </c>
       <c r="M232" s="3" t="inlineStr">
         <is>
-          <t>L1.C18, L1.C26, L7.C02, L7.C05, L7.C12, L7.C13, L11.C15, L20.C01, L20.C03, L20.C06, L20.C10</t>
+          <t>L1.C01, L1.C18, L1.C20, L7.C03, L8.C12, L8.C34, L11.C16, L20.C01, L20.C02</t>
         </is>
       </c>
       <c r="N232" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-20-droit-international-monetaire-et-commercial/c07-l-accord-monetaire-international.md</t>
+          <t>corpus/livre-20-droit-international-monetaire-et-commercial/c03-l-objectif-principal-et-ce-qu-il-exclut.md</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" s="2" t="inlineStr">
         <is>
-          <t>L20.C08</t>
+          <t>L20.C04</t>
         </is>
       </c>
       <c r="B233" s="3" t="inlineStr">
@@ -16398,7 +16402,7 @@
       </c>
       <c r="C233" s="3" t="inlineStr">
         <is>
-          <t>La parité inscrite dans le traité</t>
+          <t>L'indépendance, et à l'égard de qui</t>
         </is>
       </c>
       <c r="D233" s="3" t="inlineStr">
@@ -16423,36 +16427,36 @@
       </c>
       <c r="H233" s="3" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="I233" s="3" t="inlineStr"/>
       <c r="J233" s="3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K233" s="3" t="n">
         <v>3</v>
       </c>
       <c r="L233" s="3" t="inlineStr">
         <is>
-          <t>referentiel_de_change, etalon_de_change_or, hierarchie_monetaire, bareme, devise_cle</t>
+          <t>regle_contre_discretion, creation_monetaire, fenetre_de_reforme</t>
         </is>
       </c>
       <c r="M233" s="3" t="inlineStr">
         <is>
-          <t>L1.C25, L1.C26, L1.C28, L7.C02, L7.C20, L11.C15, L11.C17, L20.C01, L20.C09, L20.C13</t>
+          <t>L1.C18, L7.C04, L7.C07, L7.C10, L8.C31, L11.C17, L20.C01, L20.C03, L20.C11</t>
         </is>
       </c>
       <c r="N233" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-20-droit-international-monetaire-et-commercial/c08-la-parite-inscrite-dans-le-traite.md</t>
+          <t>corpus/livre-20-droit-international-monetaire-et-commercial/c04-l-independance-et-a-l-egard-de-qui.md</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" s="2" t="inlineStr">
         <is>
-          <t>L20.C09</t>
+          <t>L20.C05</t>
         </is>
       </c>
       <c r="B234" s="3" t="inlineStr">
@@ -16462,7 +16466,7 @@
       </c>
       <c r="C234" s="3" t="inlineStr">
         <is>
-          <t>L'amendement des statuts du Fonds</t>
+          <t>Le monopole d'émission et le cours légal</t>
         </is>
       </c>
       <c r="D234" s="3" t="inlineStr">
@@ -16499,24 +16503,24 @@
       </c>
       <c r="L234" s="3" t="inlineStr">
         <is>
-          <t>fenetre_de_reforme, referentiel_de_change, bareme, regle_contre_discretion</t>
+          <t>monnaie_comme_registre, creation_monetaire, referentiel_de_change, hierarchie_monetaire</t>
         </is>
       </c>
       <c r="M234" s="3" t="inlineStr">
         <is>
-          <t>L7.C06, L7.C09, L7.C16, L7.C20, L11.C15, L11.C20, L20.C01, L20.C06, L20.C08, L20.C10, L20.C13</t>
+          <t>L1.C05, L1.C07, L1.C26, L7.C15, L11.C15, L20.C01, L20.C02, L20.C03</t>
         </is>
       </c>
       <c r="N234" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-20-droit-international-monetaire-et-commercial/c09-l-amendement-des-statuts-du-fonds.md</t>
+          <t>corpus/livre-20-droit-international-monetaire-et-commercial/c05-le-monopole-d-emission-et-le-cours-legal.md</t>
         </is>
       </c>
     </row>
     <row r="235">
       <c r="A235" s="2" t="inlineStr">
         <is>
-          <t>L20.C10</t>
+          <t>L20.C06</t>
         </is>
       </c>
       <c r="B235" s="3" t="inlineStr">
@@ -16526,7 +16530,7 @@
       </c>
       <c r="C235" s="3" t="inlineStr">
         <is>
-          <t>Le vote pondéré et les voix de base</t>
+          <t>Les voies de révision et leur coût</t>
         </is>
       </c>
       <c r="D235" s="3" t="inlineStr">
@@ -16556,31 +16560,31 @@
       </c>
       <c r="I235" s="3" t="inlineStr"/>
       <c r="J235" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K235" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L235" s="3" t="inlineStr">
         <is>
-          <t>bareme, devise_cle, hierarchie_monetaire, referentiel_de_change</t>
+          <t>fenetre_de_reforme, regle_contre_discretion, creation_monetaire</t>
         </is>
       </c>
       <c r="M235" s="3" t="inlineStr">
         <is>
-          <t>L1.C25, L7.C02, L7.C05, L7.C06, L7.C09, L7.C10, L11.C16, L20.C01, L20.C07, L20.C09, L20.C12</t>
+          <t>L1.C18, L7.C12, L7.C20, L7.C21, L11.C15, L20.C01, L20.C02, L20.C03, L20.C07, L20.C09, L20.C18</t>
         </is>
       </c>
       <c r="N235" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-20-droit-international-monetaire-et-commercial/c10-le-vote-pondere-et-les-voix-de-base.md</t>
+          <t>corpus/livre-20-droit-international-monetaire-et-commercial/c06-les-voies-de-revision-et-leur-cout.md</t>
         </is>
       </c>
     </row>
     <row r="236">
       <c r="A236" s="2" t="inlineStr">
         <is>
-          <t>L20.C11</t>
+          <t>L20.C07</t>
         </is>
       </c>
       <c r="B236" s="3" t="inlineStr">
@@ -16590,7 +16594,7 @@
       </c>
       <c r="C236" s="3" t="inlineStr">
         <is>
-          <t>La personnalité juridique et les immunités</t>
+          <t>L'accord monétaire international</t>
         </is>
       </c>
       <c r="D236" s="3" t="inlineStr">
@@ -16620,31 +16624,31 @@
       </c>
       <c r="I236" s="3" t="inlineStr"/>
       <c r="J236" s="3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K236" s="3" t="n">
         <v>3</v>
       </c>
       <c r="L236" s="3" t="inlineStr">
         <is>
-          <t>communs, creation_monetaire, fenetre_de_reforme, robustesse</t>
+          <t>referentiel_de_change, fenetre_de_reforme, etalon_de_change_or, hierarchie_monetaire</t>
         </is>
       </c>
       <c r="M236" s="3" t="inlineStr">
         <is>
-          <t>L7.C01, L7.C03, L7.C07, L7.C10, L7.C13, L11.C25, L20.C01, L20.C04, L20.C12, L20.C14</t>
+          <t>L1.C18, L1.C26, L7.C02, L7.C05, L7.C12, L7.C13, L11.C15, L20.C01, L20.C03, L20.C06, L20.C10</t>
         </is>
       </c>
       <c r="N236" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-20-droit-international-monetaire-et-commercial/c11-la-personnalite-juridique-et-les-immunites.md</t>
+          <t>corpus/livre-20-droit-international-monetaire-et-commercial/c07-l-accord-monetaire-international.md</t>
         </is>
       </c>
     </row>
     <row r="237">
       <c r="A237" s="2" t="inlineStr">
         <is>
-          <t>L20.C12</t>
+          <t>L20.C08</t>
         </is>
       </c>
       <c r="B237" s="3" t="inlineStr">
@@ -16654,7 +16658,7 @@
       </c>
       <c r="C237" s="3" t="inlineStr">
         <is>
-          <t>Les pouvoirs non délégables</t>
+          <t>La parité inscrite dans le traité</t>
         </is>
       </c>
       <c r="D237" s="3" t="inlineStr">
@@ -16684,31 +16688,31 @@
       </c>
       <c r="I237" s="3" t="inlineStr"/>
       <c r="J237" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K237" s="3" t="n">
         <v>3</v>
       </c>
       <c r="L237" s="3" t="inlineStr">
         <is>
-          <t>bareme, valorisation_des_communs, polycentricite, robustesse</t>
+          <t>referentiel_de_change, etalon_de_change_or, hierarchie_monetaire, bareme, devise_cle</t>
         </is>
       </c>
       <c r="M237" s="3" t="inlineStr">
         <is>
-          <t>L7.C05, L7.C06, L7.C07, L7.C11, L7.C14, L11.C16, L11.C20, L20.C01, L20.C09, L20.C10, L20.C14</t>
+          <t>L1.C25, L1.C26, L1.C28, L7.C02, L7.C20, L11.C15, L11.C17, L20.C01, L20.C09, L20.C13</t>
         </is>
       </c>
       <c r="N237" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-20-droit-international-monetaire-et-commercial/c12-les-pouvoirs-non-delegables.md</t>
+          <t>corpus/livre-20-droit-international-monetaire-et-commercial/c08-la-parite-inscrite-dans-le-traite.md</t>
         </is>
       </c>
     </row>
     <row r="238">
       <c r="A238" s="2" t="inlineStr">
         <is>
-          <t>L20.C13</t>
+          <t>L20.C09</t>
         </is>
       </c>
       <c r="B238" s="3" t="inlineStr">
@@ -16718,7 +16722,7 @@
       </c>
       <c r="C238" s="3" t="inlineStr">
         <is>
-          <t>L'entrée en vigueur, l'adhésion et le retrait</t>
+          <t>L'amendement des statuts du Fonds</t>
         </is>
       </c>
       <c r="D238" s="3" t="inlineStr">
@@ -16743,36 +16747,36 @@
       </c>
       <c r="H238" s="3" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="I238" s="3" t="inlineStr"/>
       <c r="J238" s="3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K238" s="3" t="n">
         <v>3</v>
       </c>
       <c r="L238" s="3" t="inlineStr">
         <is>
-          <t>seuil_d_activation, reflux_collectif, fenetre_de_reforme, additionnalite</t>
+          <t>fenetre_de_reforme, referentiel_de_change, bareme, regle_contre_discretion</t>
         </is>
       </c>
       <c r="M238" s="3" t="inlineStr">
         <is>
-          <t>L7.C11, L7.C12, L7.C16, L7.C17, L7.C19, L11.C18, L20.C01, L20.C06, L20.C09, L20.C12</t>
+          <t>L7.C06, L7.C09, L7.C16, L7.C20, L11.C15, L11.C20, L20.C01, L20.C06, L20.C08, L20.C10, L20.C13</t>
         </is>
       </c>
       <c r="N238" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-20-droit-international-monetaire-et-commercial/c13-l-entree-en-vigueur-l-adhesion-et-le-retrait.md</t>
+          <t>corpus/livre-20-droit-international-monetaire-et-commercial/c09-l-amendement-des-statuts-du-fonds.md</t>
         </is>
       </c>
     </row>
     <row r="239">
       <c r="A239" s="2" t="inlineStr">
         <is>
-          <t>L20.C14</t>
+          <t>L20.C10</t>
         </is>
       </c>
       <c r="B239" s="3" t="inlineStr">
@@ -16782,7 +16786,7 @@
       </c>
       <c r="C239" s="3" t="inlineStr">
         <is>
-          <t>Qui interprète le traité</t>
+          <t>Le vote pondéré et les voix de base</t>
         </is>
       </c>
       <c r="D239" s="3" t="inlineStr">
@@ -16807,7 +16811,7 @@
       </c>
       <c r="H239" s="3" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="I239" s="3" t="inlineStr"/>
@@ -16819,24 +16823,24 @@
       </c>
       <c r="L239" s="3" t="inlineStr">
         <is>
-          <t>robustesse, regle_contre_discretion, communs</t>
+          <t>bareme, devise_cle, hierarchie_monetaire, referentiel_de_change</t>
         </is>
       </c>
       <c r="M239" s="3" t="inlineStr">
         <is>
-          <t>L7.C07, L7.C13, L7.C14, L7.C19, L11.C19, L11.C25, L20.C01, L20.C03, L20.C11, L20.C12, L20.C21</t>
+          <t>L1.C25, L7.C02, L7.C05, L7.C06, L7.C09, L7.C10, L11.C16, L20.C01, L20.C07, L20.C09, L20.C12</t>
         </is>
       </c>
       <c r="N239" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-20-droit-international-monetaire-et-commercial/c14-qui-interprete-le-traite.md</t>
+          <t>corpus/livre-20-droit-international-monetaire-et-commercial/c10-le-vote-pondere-et-les-voix-de-base.md</t>
         </is>
       </c>
     </row>
     <row r="240">
       <c r="A240" s="2" t="inlineStr">
         <is>
-          <t>L20.C15</t>
+          <t>L20.C11</t>
         </is>
       </c>
       <c r="B240" s="3" t="inlineStr">
@@ -16846,7 +16850,7 @@
       </c>
       <c r="C240" s="3" t="inlineStr">
         <is>
-          <t>Le devoir international des agents</t>
+          <t>La personnalité juridique et les immunités</t>
         </is>
       </c>
       <c r="D240" s="3" t="inlineStr">
@@ -16876,31 +16880,31 @@
       </c>
       <c r="I240" s="3" t="inlineStr"/>
       <c r="J240" s="3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K240" s="3" t="n">
         <v>3</v>
       </c>
       <c r="L240" s="3" t="inlineStr">
         <is>
-          <t>robustesse, regle_contre_discretion, indicateur_de_progres</t>
+          <t>communs, creation_monetaire, fenetre_de_reforme, robustesse</t>
         </is>
       </c>
       <c r="M240" s="3" t="inlineStr">
         <is>
-          <t>L7.C04, L7.C07, L7.C10, L11.C21, L11.C25, L20.C01, L20.C04, L20.C11, L20.C14</t>
+          <t>L7.C01, L7.C03, L7.C07, L7.C10, L7.C13, L11.C25, L20.C01, L20.C04, L20.C12, L20.C14</t>
         </is>
       </c>
       <c r="N240" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-20-droit-international-monetaire-et-commercial/c15-le-devoir-international-des-agents.md</t>
+          <t>corpus/livre-20-droit-international-monetaire-et-commercial/c11-la-personnalite-juridique-et-les-immunites.md</t>
         </is>
       </c>
     </row>
     <row r="241">
       <c r="A241" s="2" t="inlineStr">
         <is>
-          <t>L20.C16</t>
+          <t>L20.C12</t>
         </is>
       </c>
       <c r="B241" s="3" t="inlineStr">
@@ -16910,7 +16914,7 @@
       </c>
       <c r="C241" s="3" t="inlineStr">
         <is>
-          <t>Le patrimoine commun de l'humanité</t>
+          <t>Les pouvoirs non délégables</t>
         </is>
       </c>
       <c r="D241" s="3" t="inlineStr">
@@ -16947,24 +16951,24 @@
       </c>
       <c r="L241" s="3" t="inlineStr">
         <is>
-          <t>communs, valorisation_des_communs, limites_planetaires, additionnalite, plafond_ecologique</t>
+          <t>bareme, valorisation_des_communs, polycentricite, robustesse</t>
         </is>
       </c>
       <c r="M241" s="3" t="inlineStr">
         <is>
-          <t>L1.C17, L1.C22, L7.C05, L7.C13, L11.C16, L20.C01, L20.C11, L20.C17, L20.C22</t>
+          <t>L7.C05, L7.C06, L7.C07, L7.C11, L7.C14, L11.C16, L11.C20, L20.C01, L20.C09, L20.C10, L20.C14</t>
         </is>
       </c>
       <c r="N241" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-20-droit-international-monetaire-et-commercial/c16-le-patrimoine-commun-de-l-humanite.md</t>
+          <t>corpus/livre-20-droit-international-monetaire-et-commercial/c12-les-pouvoirs-non-delegables.md</t>
         </is>
       </c>
     </row>
     <row r="242">
       <c r="A242" s="2" t="inlineStr">
         <is>
-          <t>L20.C17</t>
+          <t>L20.C13</t>
         </is>
       </c>
       <c r="B242" s="3" t="inlineStr">
@@ -16974,7 +16978,7 @@
       </c>
       <c r="C242" s="3" t="inlineStr">
         <is>
-          <t>La sanctuarisation, et elle existe</t>
+          <t>L'entrée en vigueur, l'adhésion et le retrait</t>
         </is>
       </c>
       <c r="D242" s="3" t="inlineStr">
@@ -17007,28 +17011,28 @@
         <v>4</v>
       </c>
       <c r="K242" s="3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L242" s="3" t="inlineStr">
         <is>
-          <t>communs, limites_planetaires, fenetre_de_reforme, robustesse, plafond_ecologique</t>
+          <t>seuil_d_activation, reflux_collectif, fenetre_de_reforme, additionnalite</t>
         </is>
       </c>
       <c r="M242" s="3" t="inlineStr">
         <is>
-          <t>L1.C17, L1.C18, L7.C13, L7.C19, L7.C20, L11.C20, L20.C01, L20.C06, L20.C09, L20.C16, L20.C22</t>
+          <t>L7.C11, L7.C12, L7.C16, L7.C17, L7.C19, L11.C18, L20.C01, L20.C06, L20.C09, L20.C12</t>
         </is>
       </c>
       <c r="N242" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-20-droit-international-monetaire-et-commercial/c17-la-sanctuarisation-et-elle-existe.md</t>
+          <t>corpus/livre-20-droit-international-monetaire-et-commercial/c13-l-entree-en-vigueur-l-adhesion-et-le-retrait.md</t>
         </is>
       </c>
     </row>
     <row r="243">
       <c r="A243" s="2" t="inlineStr">
         <is>
-          <t>L20.C18</t>
+          <t>L20.C14</t>
         </is>
       </c>
       <c r="B243" s="3" t="inlineStr">
@@ -17038,7 +17042,7 @@
       </c>
       <c r="C243" s="3" t="inlineStr">
         <is>
-          <t>L'amendement et la dérogation dans l'ordre commercial</t>
+          <t>Qui interprète le traité</t>
         </is>
       </c>
       <c r="D243" s="3" t="inlineStr">
@@ -17063,7 +17067,7 @@
       </c>
       <c r="H243" s="3" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="I243" s="3" t="inlineStr"/>
@@ -17075,24 +17079,24 @@
       </c>
       <c r="L243" s="3" t="inlineStr">
         <is>
-          <t>bareme, seuil_d_activation, additionnalite, fenetre_de_reforme</t>
+          <t>robustesse, regle_contre_discretion, communs</t>
         </is>
       </c>
       <c r="M243" s="3" t="inlineStr">
         <is>
-          <t>L1.C27, L7.C17, L7.C20, L11.C24, L20.C01, L20.C06, L20.C09, L20.C13, L20.C19, L20.C20</t>
+          <t>L7.C07, L7.C13, L7.C14, L7.C19, L11.C19, L11.C25, L20.C01, L20.C03, L20.C11, L20.C12, L20.C21</t>
         </is>
       </c>
       <c r="N243" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-20-droit-international-monetaire-et-commercial/c18-l-amendement-et-la-derogation-dans-l-ordre-commercial.md</t>
+          <t>corpus/livre-20-droit-international-monetaire-et-commercial/c14-qui-interprete-le-traite.md</t>
         </is>
       </c>
     </row>
     <row r="244">
       <c r="A244" s="2" t="inlineStr">
         <is>
-          <t>L20.C19</t>
+          <t>L20.C15</t>
         </is>
       </c>
       <c r="B244" s="3" t="inlineStr">
@@ -17102,7 +17106,7 @@
       </c>
       <c r="C244" s="3" t="inlineStr">
         <is>
-          <t>Le texte que la conformité invoque</t>
+          <t>Le devoir international des agents</t>
         </is>
       </c>
       <c r="D244" s="3" t="inlineStr">
@@ -17127,36 +17131,36 @@
       </c>
       <c r="H244" s="3" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="I244" s="3" t="inlineStr"/>
       <c r="J244" s="3" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K244" s="3" t="n">
         <v>3</v>
       </c>
       <c r="L244" s="3" t="inlineStr">
         <is>
-          <t>bareme, additionnalite, limites_planetaires, seuil_d_activation, externalisation</t>
+          <t>robustesse, regle_contre_discretion, indicateur_de_progres</t>
         </is>
       </c>
       <c r="M244" s="3" t="inlineStr">
         <is>
-          <t>L1.C27, L7.C17, L11.C24, L20.C01, L20.C18, L20.C20, L20.C22</t>
+          <t>L7.C04, L7.C07, L7.C10, L11.C21, L11.C25, L20.C01, L20.C04, L20.C11, L20.C14</t>
         </is>
       </c>
       <c r="N244" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-20-droit-international-monetaire-et-commercial/c19-le-texte-que-la-conformite-invoque.md</t>
+          <t>corpus/livre-20-droit-international-monetaire-et-commercial/c15-le-devoir-international-des-agents.md</t>
         </is>
       </c>
     </row>
     <row r="245">
       <c r="A245" s="2" t="inlineStr">
         <is>
-          <t>L20.C20</t>
+          <t>L20.C16</t>
         </is>
       </c>
       <c r="B245" s="3" t="inlineStr">
@@ -17166,7 +17170,7 @@
       </c>
       <c r="C245" s="3" t="inlineStr">
         <is>
-          <t>L'ajustement aux frontières comme précédent</t>
+          <t>Le patrimoine commun de l'humanité</t>
         </is>
       </c>
       <c r="D245" s="3" t="inlineStr">
@@ -17196,31 +17200,31 @@
       </c>
       <c r="I245" s="3" t="inlineStr"/>
       <c r="J245" s="3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K245" s="3" t="n">
         <v>3</v>
       </c>
       <c r="L245" s="3" t="inlineStr">
         <is>
-          <t>bareme, seuil_d_activation, externalisation, additionnalite, contrepartie_comptable</t>
+          <t>communs, valorisation_des_communs, limites_planetaires, additionnalite, plafond_ecologique</t>
         </is>
       </c>
       <c r="M245" s="3" t="inlineStr">
         <is>
-          <t>L1.C27, L7.C17, L11.C21, L11.C24, L11.C25, L20.C01, L20.C18, L20.C19, L20.C22</t>
+          <t>L1.C17, L1.C22, L7.C05, L7.C13, L11.C16, L20.C01, L20.C11, L20.C17, L20.C22</t>
         </is>
       </c>
       <c r="N245" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-20-droit-international-monetaire-et-commercial/c20-l-ajustement-aux-frontieres-comme-precedent.md</t>
+          <t>corpus/livre-20-droit-international-monetaire-et-commercial/c16-le-patrimoine-commun-de-l-humanite.md</t>
         </is>
       </c>
     </row>
     <row r="246">
       <c r="A246" s="2" t="inlineStr">
         <is>
-          <t>L20.C21</t>
+          <t>L20.C17</t>
         </is>
       </c>
       <c r="B246" s="3" t="inlineStr">
@@ -17230,7 +17234,7 @@
       </c>
       <c r="C246" s="3" t="inlineStr">
         <is>
-          <t>La transparence et sa limite juridictionnelle</t>
+          <t>La sanctuarisation, et elle existe</t>
         </is>
       </c>
       <c r="D246" s="3" t="inlineStr">
@@ -17255,36 +17259,36 @@
       </c>
       <c r="H246" s="3" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="I246" s="3" t="inlineStr"/>
       <c r="J246" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K246" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L246" s="3" t="inlineStr">
         <is>
-          <t>robustesse, contrepartie_comptable, bareme, monnaie_comme_registre</t>
+          <t>communs, limites_planetaires, fenetre_de_reforme, robustesse, plafond_ecologique</t>
         </is>
       </c>
       <c r="M246" s="3" t="inlineStr">
         <is>
-          <t>L7.C18, L11.C21, L11.C24, L11.C25, L20.C01, L20.C11, L20.C14, L20.C20, L20.C22</t>
+          <t>L1.C17, L1.C18, L7.C13, L7.C19, L7.C20, L11.C20, L20.C01, L20.C06, L20.C09, L20.C16, L20.C22</t>
         </is>
       </c>
       <c r="N246" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-20-droit-international-monetaire-et-commercial/c21-la-transparence-et-sa-limite-juridictionnelle.md</t>
+          <t>corpus/livre-20-droit-international-monetaire-et-commercial/c17-la-sanctuarisation-et-elle-existe.md</t>
         </is>
       </c>
     </row>
     <row r="247">
       <c r="A247" s="2" t="inlineStr">
         <is>
-          <t>L20.C22</t>
+          <t>L20.C18</t>
         </is>
       </c>
       <c r="B247" s="3" t="inlineStr">
@@ -17294,7 +17298,7 @@
       </c>
       <c r="C247" s="3" t="inlineStr">
         <is>
-          <t>Ce que le droit devrait devenir</t>
+          <t>L'amendement et la dérogation dans l'ordre commercial</t>
         </is>
       </c>
       <c r="D247" s="3" t="inlineStr">
@@ -17331,24 +17335,24 @@
       </c>
       <c r="L247" s="3" t="inlineStr">
         <is>
-          <t>fenetre_de_reforme, communs, limites_planetaires, regle_contre_discretion, bareme, referentiel_de_change</t>
+          <t>bareme, seuil_d_activation, additionnalite, fenetre_de_reforme</t>
         </is>
       </c>
       <c r="M247" s="3" t="inlineStr">
         <is>
-          <t>L1.C18, L7.C12, L7.C13, L11.C15, L11.C25, L20.C01, L20.C03, L20.C06, L20.C07, L20.C08, L20.C12, L20.C13, L20.C16, L20.C17, L20.C19, L20.C20, L20.C21, L20.C23</t>
+          <t>L1.C27, L7.C17, L7.C20, L11.C24, L20.C01, L20.C06, L20.C09, L20.C13, L20.C19, L20.C20</t>
         </is>
       </c>
       <c r="N247" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-20-droit-international-monetaire-et-commercial/c22-ce-que-le-droit-devrait-devenir.md</t>
+          <t>corpus/livre-20-droit-international-monetaire-et-commercial/c18-l-amendement-et-la-derogation-dans-l-ordre-commercial.md</t>
         </is>
       </c>
     </row>
     <row r="248">
       <c r="A248" s="2" t="inlineStr">
         <is>
-          <t>L20.C23</t>
+          <t>L20.C19</t>
         </is>
       </c>
       <c r="B248" s="3" t="inlineStr">
@@ -17358,7 +17362,7 @@
       </c>
       <c r="C248" s="3" t="inlineStr">
         <is>
-          <t>La portée du livre</t>
+          <t>Le texte que la conformité invoque</t>
         </is>
       </c>
       <c r="D248" s="3" t="inlineStr">
@@ -17383,46 +17387,46 @@
       </c>
       <c r="H248" s="3" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="I248" s="3" t="inlineStr"/>
       <c r="J248" s="3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K248" s="3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L248" s="3" t="inlineStr">
         <is>
-          <t>fenetre_de_reforme, communs, limites_planetaires, creation_monetaire, robustesse</t>
+          <t>bareme, additionnalite, limites_planetaires, seuil_d_activation, externalisation</t>
         </is>
       </c>
       <c r="M248" s="3" t="inlineStr">
         <is>
-          <t>L1.C18, L1.C27, L7.C05, L7.C10, L7.C12, L7.C13, L11.C15, L11.C24, L11.C25, L20.C01, L20.C02, L20.C03, L20.C06, L20.C07, L20.C08, L20.C11, L20.C12, L20.C13, L20.C16, L20.C17, L20.C19, L20.C20, L20.C21, L20.C22</t>
+          <t>L1.C27, L7.C17, L11.C24, L20.C01, L20.C18, L20.C20, L20.C22</t>
         </is>
       </c>
       <c r="N248" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-20-droit-international-monetaire-et-commercial/c23-la-portee-du-livre.md</t>
+          <t>corpus/livre-20-droit-international-monetaire-et-commercial/c19-le-texte-que-la-conformite-invoque.md</t>
         </is>
       </c>
     </row>
     <row r="249">
       <c r="A249" s="2" t="inlineStr">
         <is>
-          <t>L21.C01</t>
+          <t>L20.C20</t>
         </is>
       </c>
       <c r="B249" s="3" t="inlineStr">
         <is>
-          <t>L21</t>
+          <t>L20</t>
         </is>
       </c>
       <c r="C249" s="3" t="inlineStr">
         <is>
-          <t>Ce que ce livre doit établir, et le principe qui exige des fonds propres</t>
+          <t>L'ajustement aux frontières comme précédent</t>
         </is>
       </c>
       <c r="D249" s="3" t="inlineStr">
@@ -17442,51 +17446,51 @@
       </c>
       <c r="G249" s="3" t="inlineStr">
         <is>
-          <t>hybride</t>
+          <t>conception</t>
         </is>
       </c>
       <c r="H249" s="3" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="I249" s="3" t="inlineStr"/>
       <c r="J249" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="K249" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="K249" s="3" t="n">
-        <v>5</v>
-      </c>
       <c r="L249" s="3" t="inlineStr">
         <is>
-          <t>contrepartie_comptable, creation_monetaire, hierarchie_monetaire, monnaie_comme_registre, seuil_d_activation</t>
+          <t>bareme, seuil_d_activation, externalisation, additionnalite, contrepartie_comptable</t>
         </is>
       </c>
       <c r="M249" s="3" t="inlineStr">
         <is>
-          <t>L1.C20, L5.C02, L5.C09, L10.C01, L10.C02, L11.C02, L18.C01, L21.C01, L19.C02, L19.C06</t>
+          <t>L1.C27, L7.C17, L11.C21, L11.C24, L11.C25, L20.C01, L20.C18, L20.C19, L20.C22</t>
         </is>
       </c>
       <c r="N249" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-21-plomberie-financiere-mondiale/c01-ce-que-ce-livre-doit-etablir.md</t>
+          <t>corpus/livre-20-droit-international-monetaire-et-commercial/c20-l-ajustement-aux-frontieres-comme-precedent.md</t>
         </is>
       </c>
     </row>
     <row r="250">
       <c r="A250" s="2" t="inlineStr">
         <is>
-          <t>L21.C02</t>
+          <t>L20.C21</t>
         </is>
       </c>
       <c r="B250" s="3" t="inlineStr">
         <is>
-          <t>L21</t>
+          <t>L20</t>
         </is>
       </c>
       <c r="C250" s="3" t="inlineStr">
         <is>
-          <t>Comment l'unité circulerait vraiment, et ce que chaque étape exige</t>
+          <t>La transparence et sa limite juridictionnelle</t>
         </is>
       </c>
       <c r="D250" s="3" t="inlineStr">
@@ -17506,12 +17510,12 @@
       </c>
       <c r="G250" s="3" t="inlineStr">
         <is>
-          <t>hybride</t>
+          <t>conception</t>
         </is>
       </c>
       <c r="H250" s="3" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="I250" s="3" t="inlineStr"/>
@@ -17523,34 +17527,34 @@
       </c>
       <c r="L250" s="3" t="inlineStr">
         <is>
-          <t>monnaie_comme_registre, hierarchie_monetaire, contrepartie_comptable, devise_cle, seuil_d_activation</t>
+          <t>robustesse, contrepartie_comptable, bareme, monnaie_comme_registre</t>
         </is>
       </c>
       <c r="M250" s="3" t="inlineStr">
         <is>
-          <t>L1.C24, L3.C05, L3.C09, L5.C02, L5.C09, L10.C01, L11.C02, L21.C01</t>
+          <t>L7.C18, L11.C21, L11.C24, L11.C25, L20.C01, L20.C11, L20.C14, L20.C20, L20.C22</t>
         </is>
       </c>
       <c r="N250" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-21-plomberie-financiere-mondiale/c02-comment-l-unite-circulerait-vraiment.md</t>
+          <t>corpus/livre-20-droit-international-monetaire-et-commercial/c21-la-transparence-et-sa-limite-juridictionnelle.md</t>
         </is>
       </c>
     </row>
     <row r="251">
       <c r="A251" s="2" t="inlineStr">
         <is>
-          <t>L21.C03</t>
+          <t>L20.C22</t>
         </is>
       </c>
       <c r="B251" s="3" t="inlineStr">
         <is>
-          <t>L21</t>
+          <t>L20</t>
         </is>
       </c>
       <c r="C251" s="3" t="inlineStr">
         <is>
-          <t>Une opération de bout en bout, bilan par bilan</t>
+          <t>Ce que le droit devrait devenir</t>
         </is>
       </c>
       <c r="D251" s="3" t="inlineStr">
@@ -17575,7 +17579,7 @@
       </c>
       <c r="H251" s="3" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="I251" s="3" t="inlineStr"/>
@@ -17583,38 +17587,38 @@
         <v>3</v>
       </c>
       <c r="K251" s="3" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="L251" s="3" t="inlineStr">
         <is>
-          <t>contrepartie_comptable, creation_monetaire, reflux_collectif, demurrage, monnaie_comme_registre, hierarchie_monetaire</t>
+          <t>fenetre_de_reforme, communs, limites_planetaires, regle_contre_discretion, bareme, referentiel_de_change</t>
         </is>
       </c>
       <c r="M251" s="3" t="inlineStr">
         <is>
-          <t>L1.C07, L1.C29, L10.C06, L10.C07, L11.C01, L11.C02, L11.C11, L11.C13, L11.C23, L21.C01, L21.C02, L19.C04</t>
+          <t>L1.C18, L7.C12, L7.C13, L11.C15, L11.C25, L20.C01, L20.C03, L20.C06, L20.C07, L20.C08, L20.C12, L20.C13, L20.C16, L20.C17, L20.C19, L20.C20, L20.C21, L20.C23</t>
         </is>
       </c>
       <c r="N251" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-21-plomberie-financiere-mondiale/c03-une-operation-de-bout-en-bout.md</t>
+          <t>corpus/livre-20-droit-international-monetaire-et-commercial/c22-ce-que-le-droit-devrait-devenir.md</t>
         </is>
       </c>
     </row>
     <row r="252">
       <c r="A252" s="2" t="inlineStr">
         <is>
-          <t>L21.C04</t>
+          <t>L20.C23</t>
         </is>
       </c>
       <c r="B252" s="3" t="inlineStr">
         <is>
-          <t>L21</t>
+          <t>L20</t>
         </is>
       </c>
       <c r="C252" s="3" t="inlineStr">
         <is>
-          <t>Ce que l'émission coûte aux banques qui l'hébergent</t>
+          <t>La portée du livre</t>
         </is>
       </c>
       <c r="D252" s="3" t="inlineStr">
@@ -17634,41 +17638,41 @@
       </c>
       <c r="G252" s="3" t="inlineStr">
         <is>
-          <t>descriptif</t>
+          <t>conception</t>
         </is>
       </c>
       <c r="H252" s="3" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="I252" s="3" t="inlineStr"/>
       <c r="J252" s="3" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="K252" s="3" t="n">
         <v>4</v>
       </c>
       <c r="L252" s="3" t="inlineStr">
         <is>
-          <t>contrepartie_comptable, creation_monetaire, hierarchie_monetaire, reflux_collectif, demurrage</t>
+          <t>fenetre_de_reforme, communs, limites_planetaires, creation_monetaire, robustesse</t>
         </is>
       </c>
       <c r="M252" s="3" t="inlineStr">
         <is>
-          <t>L1.C07, L10.C01, L11.C02, L11.C07, L11.C09, L11.C11, L11.C23, L21.C02, L21.C03</t>
+          <t>L1.C18, L1.C27, L7.C05, L7.C10, L7.C12, L7.C13, L11.C15, L11.C24, L11.C25, L20.C01, L20.C02, L20.C03, L20.C06, L20.C07, L20.C08, L20.C11, L20.C12, L20.C13, L20.C16, L20.C17, L20.C19, L20.C20, L20.C21, L20.C22</t>
         </is>
       </c>
       <c r="N252" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-21-plomberie-financiere-mondiale/c04-ce-que-l-emission-coute-aux-banques-qui-l-hebergent.md</t>
+          <t>corpus/livre-20-droit-international-monetaire-et-commercial/c23-la-portee-du-livre.md</t>
         </is>
       </c>
     </row>
     <row r="253">
       <c r="A253" s="2" t="inlineStr">
         <is>
-          <t>L21.C05</t>
+          <t>L21.C01</t>
         </is>
       </c>
       <c r="B253" s="3" t="inlineStr">
@@ -17678,7 +17682,7 @@
       </c>
       <c r="C253" s="3" t="inlineStr">
         <is>
-          <t>La première infrastructure ouverte, et ce qu'elle renverse</t>
+          <t>Ce que ce livre doit établir, et le principe qui exige des fonds propres</t>
         </is>
       </c>
       <c r="D253" s="3" t="inlineStr">
@@ -17703,7 +17707,7 @@
       </c>
       <c r="H253" s="3" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="I253" s="3" t="inlineStr"/>
@@ -17711,28 +17715,28 @@
         <v>3</v>
       </c>
       <c r="K253" s="3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L253" s="3" t="inlineStr">
         <is>
-          <t>seuil_d_activation, hierarchie_monetaire, monnaie_comme_registre, devise_cle, demurrage, contrepartie_comptable</t>
+          <t>contrepartie_comptable, creation_monetaire, hierarchie_monetaire, monnaie_comme_registre, seuil_d_activation</t>
         </is>
       </c>
       <c r="M253" s="3" t="inlineStr">
         <is>
-          <t>L3.C09, L5.C02, L5.C09, L11.C01, L11.C02, L11.C07, L21.C01, L21.C02, L21.C03, L21.C04</t>
+          <t>L1.C20, L5.C02, L5.C09, L10.C01, L10.C02, L11.C02, L18.C01, L21.C01, L19.C02, L19.C06</t>
         </is>
       </c>
       <c r="N253" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-21-plomberie-financiere-mondiale/c05-la-premiere-infrastructure-ouverte-et-ce-qu-elle-renverse.md</t>
+          <t>corpus/livre-21-plomberie-financiere-mondiale/c01-ce-que-ce-livre-doit-etablir.md</t>
         </is>
       </c>
     </row>
     <row r="254">
       <c r="A254" s="2" t="inlineStr">
         <is>
-          <t>L21.C06</t>
+          <t>L21.C02</t>
         </is>
       </c>
       <c r="B254" s="3" t="inlineStr">
@@ -17742,7 +17746,7 @@
       </c>
       <c r="C254" s="3" t="inlineStr">
         <is>
-          <t>La jambe qui reste, et ce qu'il faut pour la protéger</t>
+          <t>Comment l'unité circulerait vraiment, et ce que chaque étape exige</t>
         </is>
       </c>
       <c r="D254" s="3" t="inlineStr">
@@ -17775,28 +17779,28 @@
         <v>3</v>
       </c>
       <c r="K254" s="3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L254" s="3" t="inlineStr">
         <is>
-          <t>contrepartie_comptable, hierarchie_monetaire, monnaie_comme_registre, seuil_d_activation</t>
+          <t>monnaie_comme_registre, hierarchie_monetaire, contrepartie_comptable, devise_cle, seuil_d_activation</t>
         </is>
       </c>
       <c r="M254" s="3" t="inlineStr">
         <is>
-          <t>L5.C02, L11.C02, L11.C11, L20.C02, L21.C02, L21.C03, L21.C05</t>
+          <t>L1.C24, L3.C05, L3.C09, L5.C02, L5.C09, L10.C01, L11.C02, L21.C01</t>
         </is>
       </c>
       <c r="N254" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-21-plomberie-financiere-mondiale/c06-la-jambe-qui-reste-et-ce-qu-il-faut-pour-la-proteger.md</t>
+          <t>corpus/livre-21-plomberie-financiere-mondiale/c02-comment-l-unite-circulerait-vraiment.md</t>
         </is>
       </c>
     </row>
     <row r="255">
       <c r="A255" s="2" t="inlineStr">
         <is>
-          <t>L21.C07</t>
+          <t>L21.C03</t>
         </is>
       </c>
       <c r="B255" s="3" t="inlineStr">
@@ -17806,7 +17810,7 @@
       </c>
       <c r="C255" s="3" t="inlineStr">
         <is>
-          <t>Portée de la tranche</t>
+          <t>Une opération de bout en bout, bilan par bilan</t>
         </is>
       </c>
       <c r="D255" s="3" t="inlineStr">
@@ -17826,51 +17830,51 @@
       </c>
       <c r="G255" s="3" t="inlineStr">
         <is>
-          <t>descriptif</t>
+          <t>conception</t>
         </is>
       </c>
       <c r="H255" s="3" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="I255" s="3" t="inlineStr"/>
       <c r="J255" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K255" s="3" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="L255" s="3" t="inlineStr">
         <is>
-          <t>seuil_d_activation, contrepartie_comptable, hierarchie_monetaire, monnaie_comme_registre</t>
+          <t>contrepartie_comptable, creation_monetaire, reflux_collectif, demurrage, monnaie_comme_registre, hierarchie_monetaire</t>
         </is>
       </c>
       <c r="M255" s="3" t="inlineStr">
         <is>
-          <t>L5.C02, L10.C06, L11.C01, L11.C02, L20.C01, L21.C01, L21.C02, L21.C03, L21.C04, L21.C05, L21.C06</t>
+          <t>L1.C07, L1.C29, L10.C06, L10.C07, L11.C01, L11.C02, L11.C11, L11.C13, L11.C23, L21.C01, L21.C02, L19.C04, L16.C04</t>
         </is>
       </c>
       <c r="N255" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-21-plomberie-financiere-mondiale/c07-portee-de-la-tranche.md</t>
+          <t>corpus/livre-21-plomberie-financiere-mondiale/c03-une-operation-de-bout-en-bout.md</t>
         </is>
       </c>
     </row>
     <row r="256">
       <c r="A256" s="2" t="inlineStr">
         <is>
-          <t>L22.C01</t>
+          <t>L21.C04</t>
         </is>
       </c>
       <c r="B256" s="3" t="inlineStr">
         <is>
-          <t>L22</t>
+          <t>L21</t>
         </is>
       </c>
       <c r="C256" s="3" t="inlineStr">
         <is>
-          <t>Ce que ce livre doit établir</t>
+          <t>Ce que l'émission coûte aux banques qui l'hébergent</t>
         </is>
       </c>
       <c r="D256" s="3" t="inlineStr">
@@ -17900,41 +17904,41 @@
       </c>
       <c r="I256" s="3" t="inlineStr"/>
       <c r="J256" s="3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K256" s="3" t="n">
         <v>4</v>
       </c>
       <c r="L256" s="3" t="inlineStr">
         <is>
-          <t>architecture_invisible, systeme_monetaire_et_financier, reflux_collectif, reflux_transactionnel, hierarchie_monetaire, monnaie_comme_registre</t>
+          <t>contrepartie_comptable, creation_monetaire, hierarchie_monetaire, reflux_collectif, demurrage</t>
         </is>
       </c>
       <c r="M256" s="3" t="inlineStr">
         <is>
-          <t>L1.C09, L1.C19, L5.C09, L11.C02, L11.C05, L11.C09, L11.C27, L21.C03, L21.C04</t>
+          <t>L1.C07, L10.C01, L11.C02, L11.C07, L11.C09, L11.C11, L11.C23, L21.C02, L21.C03</t>
         </is>
       </c>
       <c r="N256" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-22-finance-non-bancaire/c01-ce-que-ce-livre-doit-etablir.md</t>
+          <t>corpus/livre-21-plomberie-financiere-mondiale/c04-ce-que-l-emission-coute-aux-banques-qui-l-hebergent.md</t>
         </is>
       </c>
     </row>
     <row r="257">
       <c r="A257" s="2" t="inlineStr">
         <is>
-          <t>L22.C02</t>
+          <t>L21.C05</t>
         </is>
       </c>
       <c r="B257" s="3" t="inlineStr">
         <is>
-          <t>L22</t>
+          <t>L21</t>
         </is>
       </c>
       <c r="C257" s="3" t="inlineStr">
         <is>
-          <t>Où va la monnaie émise, et pourquoi le reflux ne l'y suit pas</t>
+          <t>La première infrastructure ouverte, et ce qu'elle renverse</t>
         </is>
       </c>
       <c r="D257" s="3" t="inlineStr">
@@ -17954,51 +17958,51 @@
       </c>
       <c r="G257" s="3" t="inlineStr">
         <is>
-          <t>conception</t>
+          <t>hybride</t>
         </is>
       </c>
       <c r="H257" s="3" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="I257" s="3" t="inlineStr"/>
       <c r="J257" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K257" s="3" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L257" s="3" t="inlineStr">
         <is>
-          <t>reflux_transactionnel, reflux_collectif, demurrage, monnaie_endogene, architecture_invisible, hierarchie_monetaire</t>
+          <t>seuil_d_activation, hierarchie_monetaire, monnaie_comme_registre, devise_cle, demurrage, contrepartie_comptable</t>
         </is>
       </c>
       <c r="M257" s="3" t="inlineStr">
         <is>
-          <t>L1.C19, L5.C09, L11.C02, L11.C05, L11.C09, L11.C27, L21.C03, L22.C01, L23.C04, L26.C04</t>
+          <t>L3.C09, L5.C02, L5.C09, L11.C01, L11.C02, L11.C07, L21.C01, L21.C02, L21.C03, L21.C04</t>
         </is>
       </c>
       <c r="N257" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-22-finance-non-bancaire/c02-ou-va-la-monnaie-emise.md</t>
+          <t>corpus/livre-21-plomberie-financiere-mondiale/c05-la-premiere-infrastructure-ouverte-et-ce-qu-elle-renverse.md</t>
         </is>
       </c>
     </row>
     <row r="258">
       <c r="A258" s="2" t="inlineStr">
         <is>
-          <t>L22.C03</t>
+          <t>L21.C06</t>
         </is>
       </c>
       <c r="B258" s="3" t="inlineStr">
         <is>
-          <t>L22</t>
+          <t>L21</t>
         </is>
       </c>
       <c r="C258" s="3" t="inlineStr">
         <is>
-          <t>Le barème existe déjà, et il a trois pièces que le corpus n'a pas</t>
+          <t>La jambe qui reste, et ce qu'il faut pour la protéger</t>
         </is>
       </c>
       <c r="D258" s="3" t="inlineStr">
@@ -18028,41 +18032,41 @@
       </c>
       <c r="I258" s="3" t="inlineStr"/>
       <c r="J258" s="3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K258" s="3" t="n">
         <v>4</v>
       </c>
       <c r="L258" s="3" t="inlineStr">
         <is>
-          <t>qualification_regenerative, bareme, additionnalite, indicateur_de_progres, communs, plafond_ecologique</t>
+          <t>contrepartie_comptable, hierarchie_monetaire, monnaie_comme_registre, seuil_d_activation</t>
         </is>
       </c>
       <c r="M258" s="3" t="inlineStr">
         <is>
-          <t>L11.C13, L11.C11, L11.C25, L12.C01, L18.C06, L22.C01, L25.C01</t>
+          <t>L5.C02, L11.C02, L11.C11, L20.C02, L21.C02, L21.C03, L21.C05</t>
         </is>
       </c>
       <c r="N258" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-22-finance-non-bancaire/c03-le-bareme-existe-deja.md</t>
+          <t>corpus/livre-21-plomberie-financiere-mondiale/c06-la-jambe-qui-reste-et-ce-qu-il-faut-pour-la-proteger.md</t>
         </is>
       </c>
     </row>
     <row r="259">
       <c r="A259" s="2" t="inlineStr">
         <is>
-          <t>L22.C04</t>
+          <t>L21.C07</t>
         </is>
       </c>
       <c r="B259" s="3" t="inlineStr">
         <is>
-          <t>L22</t>
+          <t>L21</t>
         </is>
       </c>
       <c r="C259" s="3" t="inlineStr">
         <is>
-          <t>Les critères réels ne mesurent pas, ils certifient</t>
+          <t>Portée de la tranche</t>
         </is>
       </c>
       <c r="D259" s="3" t="inlineStr">
@@ -18082,7 +18086,7 @@
       </c>
       <c r="G259" s="3" t="inlineStr">
         <is>
-          <t>hybride</t>
+          <t>descriptif</t>
         </is>
       </c>
       <c r="H259" s="3" t="inlineStr">
@@ -18092,31 +18096,31 @@
       </c>
       <c r="I259" s="3" t="inlineStr"/>
       <c r="J259" s="3" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K259" s="3" t="n">
         <v>4</v>
       </c>
       <c r="L259" s="3" t="inlineStr">
         <is>
-          <t>qualification_regenerative, bareme, additionnalite, communs, valorisation_des_communs, indicateur_de_progres</t>
+          <t>seuil_d_activation, contrepartie_comptable, hierarchie_monetaire, monnaie_comme_registre</t>
         </is>
       </c>
       <c r="M259" s="3" t="inlineStr">
         <is>
-          <t>L6.C06, L11.C13, L11.C16, L11.C25, L13.C01, L14.C01, L18.C06, L22.C03</t>
+          <t>L5.C02, L10.C06, L11.C01, L11.C02, L20.C01, L21.C01, L21.C02, L21.C03, L21.C04, L21.C05, L21.C06</t>
         </is>
       </c>
       <c r="N259" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-22-finance-non-bancaire/c04-les-criteres-reels-ne-mesurent-pas.md</t>
+          <t>corpus/livre-21-plomberie-financiere-mondiale/c07-portee-de-la-tranche.md</t>
         </is>
       </c>
     </row>
     <row r="260">
       <c r="A260" s="2" t="inlineStr">
         <is>
-          <t>L22.C05</t>
+          <t>L22.C01</t>
         </is>
       </c>
       <c r="B260" s="3" t="inlineStr">
@@ -18126,7 +18130,7 @@
       </c>
       <c r="C260" s="3" t="inlineStr">
         <is>
-          <t>L'épargne retraite, et le dilemme du troisième instrument</t>
+          <t>Ce que ce livre doit établir</t>
         </is>
       </c>
       <c r="D260" s="3" t="inlineStr">
@@ -18146,7 +18150,7 @@
       </c>
       <c r="G260" s="3" t="inlineStr">
         <is>
-          <t>hybride</t>
+          <t>descriptif</t>
         </is>
       </c>
       <c r="H260" s="3" t="inlineStr">
@@ -18156,31 +18160,31 @@
       </c>
       <c r="I260" s="3" t="inlineStr"/>
       <c r="J260" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K260" s="3" t="n">
         <v>4</v>
       </c>
       <c r="L260" s="3" t="inlineStr">
         <is>
-          <t>reflux_collectif, demurrage, essentiel_insolvable, plancher_social, solvabilite_anticipee, architecture_invisible</t>
+          <t>architecture_invisible, systeme_monetaire_et_financier, reflux_collectif, reflux_transactionnel, hierarchie_monetaire, monnaie_comme_registre</t>
         </is>
       </c>
       <c r="M260" s="3" t="inlineStr">
         <is>
-          <t>L1.C15, L11.C07, L11.C09, L11.C18, L22.C01, L22.C02, L25.C01</t>
+          <t>L1.C09, L1.C19, L5.C09, L11.C02, L11.C05, L11.C09, L11.C27, L21.C03, L21.C04</t>
         </is>
       </c>
       <c r="N260" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-22-finance-non-bancaire/c05-l-epargne-retraite-et-le-dilemme-du-troisieme-instrument.md</t>
+          <t>corpus/livre-22-finance-non-bancaire/c01-ce-que-ce-livre-doit-etablir.md</t>
         </is>
       </c>
     </row>
     <row r="261">
       <c r="A261" s="2" t="inlineStr">
         <is>
-          <t>L22.C06</t>
+          <t>L22.C02</t>
         </is>
       </c>
       <c r="B261" s="3" t="inlineStr">
@@ -18190,7 +18194,7 @@
       </c>
       <c r="C261" s="3" t="inlineStr">
         <is>
-          <t>Qui décide, quand personne ne décide</t>
+          <t>Où va la monnaie émise, et pourquoi le reflux ne l'y suit pas</t>
         </is>
       </c>
       <c r="D261" s="3" t="inlineStr">
@@ -18210,41 +18214,41 @@
       </c>
       <c r="G261" s="3" t="inlineStr">
         <is>
-          <t>hybride</t>
+          <t>conception</t>
         </is>
       </c>
       <c r="H261" s="3" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="I261" s="3" t="inlineStr"/>
       <c r="J261" s="3" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K261" s="3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L261" s="3" t="inlineStr">
         <is>
-          <t>architecture_invisible, indicateur_de_progres, qualification_regenerative, essentiel_insolvable, fenetre_de_reforme, regle_contre_discretion</t>
+          <t>reflux_transactionnel, reflux_collectif, demurrage, monnaie_endogene, architecture_invisible, hierarchie_monetaire</t>
         </is>
       </c>
       <c r="M261" s="3" t="inlineStr">
         <is>
-          <t>L1.C15, L5.C09, L11.C13, L14.C01, L22.C01, L22.C02, L22.C03, L22.C05</t>
+          <t>L1.C19, L5.C09, L11.C02, L11.C05, L11.C09, L11.C27, L21.C03, L22.C01, L23.C04, L26.C04</t>
         </is>
       </c>
       <c r="N261" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-22-finance-non-bancaire/c06-qui-decide-quand-personne-ne-decide.md</t>
+          <t>corpus/livre-22-finance-non-bancaire/c02-ou-va-la-monnaie-emise.md</t>
         </is>
       </c>
     </row>
     <row r="262">
       <c r="A262" s="2" t="inlineStr">
         <is>
-          <t>L22.C07</t>
+          <t>L22.C03</t>
         </is>
       </c>
       <c r="B262" s="3" t="inlineStr">
@@ -18254,7 +18258,7 @@
       </c>
       <c r="C262" s="3" t="inlineStr">
         <is>
-          <t>Portée de la tranche</t>
+          <t>Le barème existe déjà, et il a trois pièces que le corpus n'a pas</t>
         </is>
       </c>
       <c r="D262" s="3" t="inlineStr">
@@ -18274,7 +18278,7 @@
       </c>
       <c r="G262" s="3" t="inlineStr">
         <is>
-          <t>descriptif</t>
+          <t>hybride</t>
         </is>
       </c>
       <c r="H262" s="3" t="inlineStr">
@@ -18284,41 +18288,41 @@
       </c>
       <c r="I262" s="3" t="inlineStr"/>
       <c r="J262" s="3" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K262" s="3" t="n">
         <v>4</v>
       </c>
       <c r="L262" s="3" t="inlineStr">
         <is>
-          <t>architecture_invisible, reflux_transactionnel, qualification_regenerative, bareme, essentiel_insolvable</t>
+          <t>qualification_regenerative, bareme, additionnalite, indicateur_de_progres, communs, plafond_ecologique</t>
         </is>
       </c>
       <c r="M262" s="3" t="inlineStr">
         <is>
-          <t>L1.C15, L5.C09, L11.C02, L11.C13, L11.C18, L22.C01, L22.C02, L22.C03, L22.C04, L22.C05, L22.C06</t>
+          <t>L11.C13, L11.C11, L11.C25, L12.C01, L18.C06, L22.C01, L25.C01</t>
         </is>
       </c>
       <c r="N262" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-22-finance-non-bancaire/c07-portee-de-la-tranche.md</t>
+          <t>corpus/livre-22-finance-non-bancaire/c03-le-bareme-existe-deja.md</t>
         </is>
       </c>
     </row>
     <row r="263">
       <c r="A263" s="2" t="inlineStr">
         <is>
-          <t>L23.C01</t>
+          <t>L22.C04</t>
         </is>
       </c>
       <c r="B263" s="3" t="inlineStr">
         <is>
-          <t>L23</t>
+          <t>L22</t>
         </is>
       </c>
       <c r="C263" s="3" t="inlineStr">
         <is>
-          <t>Ce que ce livre doit établir</t>
+          <t>Les critères réels ne mesurent pas, ils certifient</t>
         </is>
       </c>
       <c r="D263" s="3" t="inlineStr">
@@ -18338,7 +18342,7 @@
       </c>
       <c r="G263" s="3" t="inlineStr">
         <is>
-          <t>conception</t>
+          <t>hybride</t>
         </is>
       </c>
       <c r="H263" s="3" t="inlineStr">
@@ -18351,38 +18355,38 @@
         <v>4</v>
       </c>
       <c r="K263" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L263" s="3" t="inlineStr">
         <is>
-          <t>bareme, reflux_transactionnel, externalisation, essentiel_insolvable, polycentricite, regle_contre_discretion</t>
+          <t>qualification_regenerative, bareme, additionnalite, communs, valorisation_des_communs, indicateur_de_progres</t>
         </is>
       </c>
       <c r="M263" s="3" t="inlineStr">
         <is>
-          <t>L1.C15, L5.C07, L10.C06, L11.C05, L11.C09, L11.C21, L11.C24, L18.C09, L20.C02, L20.C20</t>
+          <t>L6.C06, L11.C13, L11.C16, L11.C25, L13.C01, L14.C01, L18.C06, L22.C03</t>
         </is>
       </c>
       <c r="N263" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-23-fiscalite-mondiale-et-opacite/c01-ce-que-ce-livre-doit-etablir.md</t>
+          <t>corpus/livre-22-finance-non-bancaire/c04-les-criteres-reels-ne-mesurent-pas.md</t>
         </is>
       </c>
     </row>
     <row r="264">
       <c r="A264" s="2" t="inlineStr">
         <is>
-          <t>L23.C02</t>
+          <t>L22.C05</t>
         </is>
       </c>
       <c r="B264" s="3" t="inlineStr">
         <is>
-          <t>L23</t>
+          <t>L22</t>
         </is>
       </c>
       <c r="C264" s="3" t="inlineStr">
         <is>
-          <t>La compétence que la convention ne crée pas, et le vote qu'elle a gagné</t>
+          <t>L'épargne retraite, et le dilemme du troisième instrument</t>
         </is>
       </c>
       <c r="D264" s="3" t="inlineStr">
@@ -18412,41 +18416,41 @@
       </c>
       <c r="I264" s="3" t="inlineStr"/>
       <c r="J264" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="K264" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="K264" s="3" t="n">
-        <v>3</v>
-      </c>
       <c r="L264" s="3" t="inlineStr">
         <is>
-          <t>polycentricite, bareme, reflux_transactionnel, seuil_d_activation, regle_contre_discretion, externalisation</t>
+          <t>reflux_collectif, demurrage, essentiel_insolvable, plancher_social, solvabilite_anticipee, architecture_invisible</t>
         </is>
       </c>
       <c r="M264" s="3" t="inlineStr">
         <is>
-          <t>L1.C25, L5.C04, L10.C06, L11.C21, L20.C02, L20.C20, L23.C01</t>
+          <t>L1.C15, L11.C07, L11.C09, L11.C18, L22.C01, L22.C02, L25.C01</t>
         </is>
       </c>
       <c r="N264" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-23-fiscalite-mondiale-et-opacite/c02-la-competence-que-la-convention-ne-cree-pas.md</t>
+          <t>corpus/livre-22-finance-non-bancaire/c05-l-epargne-retraite-et-le-dilemme-du-troisieme-instrument.md</t>
         </is>
       </c>
     </row>
     <row r="265">
       <c r="A265" s="2" t="inlineStr">
         <is>
-          <t>L23.C03</t>
+          <t>L22.C06</t>
         </is>
       </c>
       <c r="B265" s="3" t="inlineStr">
         <is>
-          <t>L23</t>
+          <t>L22</t>
         </is>
       </c>
       <c r="C265" s="3" t="inlineStr">
         <is>
-          <t>F8 appliqué à une négociation en cours, et le résultat n'est pas le désarmement</t>
+          <t>Qui décide, quand personne ne décide</t>
         </is>
       </c>
       <c r="D265" s="3" t="inlineStr">
@@ -18479,38 +18483,38 @@
         <v>4</v>
       </c>
       <c r="K265" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L265" s="3" t="inlineStr">
         <is>
-          <t>regle_contre_discretion, polycentricite, seuil_d_activation, bareme, externalisation</t>
+          <t>architecture_invisible, indicateur_de_progres, qualification_regenerative, essentiel_insolvable, fenetre_de_reforme, regle_contre_discretion</t>
         </is>
       </c>
       <c r="M265" s="3" t="inlineStr">
         <is>
-          <t>L5.C04, L6.C09, L11.C21, L20.C02, L20.C13, L23.C01, L23.C02</t>
+          <t>L1.C15, L5.C09, L11.C13, L14.C01, L22.C01, L22.C02, L22.C03, L22.C05</t>
         </is>
       </c>
       <c r="N265" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-23-fiscalite-mondiale-et-opacite/c03-f8-applique-a-une-negociation-en-cours.md</t>
+          <t>corpus/livre-22-finance-non-bancaire/c06-qui-decide-quand-personne-ne-decide.md</t>
         </is>
       </c>
     </row>
     <row r="266">
       <c r="A266" s="2" t="inlineStr">
         <is>
-          <t>L23.C04</t>
+          <t>L22.C07</t>
         </is>
       </c>
       <c r="B266" s="3" t="inlineStr">
         <is>
-          <t>L23</t>
+          <t>L22</t>
         </is>
       </c>
       <c r="C266" s="3" t="inlineStr">
         <is>
-          <t>La transparence que le corpus supposait a été invalidée</t>
+          <t>Portée de la tranche</t>
         </is>
       </c>
       <c r="D266" s="3" t="inlineStr">
@@ -18530,7 +18534,7 @@
       </c>
       <c r="G266" s="3" t="inlineStr">
         <is>
-          <t>hybride</t>
+          <t>descriptif</t>
         </is>
       </c>
       <c r="H266" s="3" t="inlineStr">
@@ -18540,31 +18544,31 @@
       </c>
       <c r="I266" s="3" t="inlineStr"/>
       <c r="J266" s="3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K266" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L266" s="3" t="inlineStr">
         <is>
-          <t>regle_contre_discretion, externalisation, bareme, polycentricite, architecture_invisible</t>
+          <t>architecture_invisible, reflux_transactionnel, qualification_regenerative, bareme, essentiel_insolvable</t>
         </is>
       </c>
       <c r="M266" s="3" t="inlineStr">
         <is>
-          <t>L6.C09, L11.C13, L11.C25, L20.C20, L23.C01, L23.C02, L23.C03</t>
+          <t>L1.C15, L5.C09, L11.C02, L11.C13, L11.C18, L22.C01, L22.C02, L22.C03, L22.C04, L22.C05, L22.C06</t>
         </is>
       </c>
       <c r="N266" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-23-fiscalite-mondiale-et-opacite/c04-la-transparence-que-le-corpus-supposait-a-ete-invalidee.md</t>
+          <t>corpus/livre-22-finance-non-bancaire/c07-portee-de-la-tranche.md</t>
         </is>
       </c>
     </row>
     <row r="267">
       <c r="A267" s="2" t="inlineStr">
         <is>
-          <t>L23.C05</t>
+          <t>L23.C01</t>
         </is>
       </c>
       <c r="B267" s="3" t="inlineStr">
@@ -18574,7 +18578,7 @@
       </c>
       <c r="C267" s="3" t="inlineStr">
         <is>
-          <t>Intéresser le percepteur, et ce que le taux révèle</t>
+          <t>Ce que ce livre doit établir</t>
         </is>
       </c>
       <c r="D267" s="3" t="inlineStr">
@@ -18594,7 +18598,7 @@
       </c>
       <c r="G267" s="3" t="inlineStr">
         <is>
-          <t>hybride</t>
+          <t>conception</t>
         </is>
       </c>
       <c r="H267" s="3" t="inlineStr">
@@ -18604,31 +18608,31 @@
       </c>
       <c r="I267" s="3" t="inlineStr"/>
       <c r="J267" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K267" s="3" t="n">
         <v>3</v>
       </c>
       <c r="L267" s="3" t="inlineStr">
         <is>
-          <t>bareme, reflux_transactionnel, regle_contre_discretion, polycentricite, seuil_d_activation</t>
+          <t>bareme, reflux_transactionnel, externalisation, essentiel_insolvable, polycentricite, regle_contre_discretion</t>
         </is>
       </c>
       <c r="M267" s="3" t="inlineStr">
         <is>
-          <t>L11.C21, L11.C24, L18.C09, L20.C20, L23.C01, L23.C02, L23.C03</t>
+          <t>L1.C15, L5.C07, L10.C06, L11.C05, L11.C09, L11.C21, L11.C24, L18.C09, L20.C02, L20.C20</t>
         </is>
       </c>
       <c r="N267" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-23-fiscalite-mondiale-et-opacite/c05-interesser-le-percepteur-et-ce-que-le-taux-revele.md</t>
+          <t>corpus/livre-23-fiscalite-mondiale-et-opacite/c01-ce-que-ce-livre-doit-etablir.md</t>
         </is>
       </c>
     </row>
     <row r="268">
       <c r="A268" s="2" t="inlineStr">
         <is>
-          <t>L23.C06</t>
+          <t>L23.C02</t>
         </is>
       </c>
       <c r="B268" s="3" t="inlineStr">
@@ -18638,7 +18642,7 @@
       </c>
       <c r="C268" s="3" t="inlineStr">
         <is>
-          <t>L'arbre appliqué à la fonte, et il ne reste que deux branches</t>
+          <t>La compétence que la convention ne crée pas, et le vote qu'elle a gagné</t>
         </is>
       </c>
       <c r="D268" s="3" t="inlineStr">
@@ -18658,7 +18662,7 @@
       </c>
       <c r="G268" s="3" t="inlineStr">
         <is>
-          <t>conception</t>
+          <t>hybride</t>
         </is>
       </c>
       <c r="H268" s="3" t="inlineStr">
@@ -18675,24 +18679,24 @@
       </c>
       <c r="L268" s="3" t="inlineStr">
         <is>
-          <t>bareme, reflux_transactionnel, monnaie_fondante, demurrage, regle_contre_discretion, essentiel_insolvable</t>
+          <t>polycentricite, bareme, reflux_transactionnel, seuil_d_activation, regle_contre_discretion, externalisation</t>
         </is>
       </c>
       <c r="M268" s="3" t="inlineStr">
         <is>
-          <t>L10.C06, L11.C05, L11.C09, L11.C21, L11.C24, L18.C09, L20.C02, L23.C01, L23.C02, L23.C03, L23.C04, L23.C05</t>
+          <t>L1.C25, L5.C04, L10.C06, L11.C21, L20.C02, L20.C20, L23.C01</t>
         </is>
       </c>
       <c r="N268" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-23-fiscalite-mondiale-et-opacite/c06-l-arbre-applique-a-la-fonte.md</t>
+          <t>corpus/livre-23-fiscalite-mondiale-et-opacite/c02-la-competence-que-la-convention-ne-cree-pas.md</t>
         </is>
       </c>
     </row>
     <row r="269">
       <c r="A269" s="2" t="inlineStr">
         <is>
-          <t>L23.C07</t>
+          <t>L23.C03</t>
         </is>
       </c>
       <c r="B269" s="3" t="inlineStr">
@@ -18702,7 +18706,7 @@
       </c>
       <c r="C269" s="3" t="inlineStr">
         <is>
-          <t>Portée de la tranche, et la moitié qui n'est pas commencée</t>
+          <t>F8 appliqué à une négociation en cours, et le résultat n'est pas le désarmement</t>
         </is>
       </c>
       <c r="D269" s="3" t="inlineStr">
@@ -18722,7 +18726,7 @@
       </c>
       <c r="G269" s="3" t="inlineStr">
         <is>
-          <t>conception</t>
+          <t>hybride</t>
         </is>
       </c>
       <c r="H269" s="3" t="inlineStr">
@@ -18732,41 +18736,41 @@
       </c>
       <c r="I269" s="3" t="inlineStr"/>
       <c r="J269" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K269" s="3" t="n">
         <v>3</v>
       </c>
       <c r="L269" s="3" t="inlineStr">
         <is>
-          <t>bareme, reflux_transactionnel, externalisation, regle_contre_discretion, polycentricite, essentiel_insolvable</t>
+          <t>regle_contre_discretion, polycentricite, seuil_d_activation, bareme, externalisation</t>
         </is>
       </c>
       <c r="M269" s="3" t="inlineStr">
         <is>
-          <t>L10.C06, L11.C05, L11.C21, L11.C25, L18.C09, L20.C20, L23.C01, L23.C02, L23.C03, L23.C04, L23.C05, L23.C06</t>
+          <t>L5.C04, L6.C09, L11.C21, L20.C02, L20.C13, L23.C01, L23.C02</t>
         </is>
       </c>
       <c r="N269" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-23-fiscalite-mondiale-et-opacite/c07-portee-de-la-tranche.md</t>
+          <t>corpus/livre-23-fiscalite-mondiale-et-opacite/c03-f8-applique-a-une-negociation-en-cours.md</t>
         </is>
       </c>
     </row>
     <row r="270">
       <c r="A270" s="2" t="inlineStr">
         <is>
-          <t>L24.C01</t>
+          <t>L23.C04</t>
         </is>
       </c>
       <c r="B270" s="3" t="inlineStr">
         <is>
-          <t>L24</t>
+          <t>L23</t>
         </is>
       </c>
       <c r="C270" s="3" t="inlineStr">
         <is>
-          <t>Ce que ce livre doit établir</t>
+          <t>La transparence que le corpus supposait a été invalidée</t>
         </is>
       </c>
       <c r="D270" s="3" t="inlineStr">
@@ -18786,7 +18790,7 @@
       </c>
       <c r="G270" s="3" t="inlineStr">
         <is>
-          <t>descriptif</t>
+          <t>hybride</t>
         </is>
       </c>
       <c r="H270" s="3" t="inlineStr">
@@ -18796,41 +18800,41 @@
       </c>
       <c r="I270" s="3" t="inlineStr"/>
       <c r="J270" s="3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K270" s="3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L270" s="3" t="inlineStr">
         <is>
-          <t>limites_planetaires, plafond_ecologique, entropie, decouplage, degeneratif, qualification_regenerative, essentiel_insolvable</t>
+          <t>regle_contre_discretion, externalisation, bareme, polycentricite, architecture_invisible</t>
         </is>
       </c>
       <c r="M270" s="3" t="inlineStr">
         <is>
-          <t>L1.C15, L5.C08, L11.C13, L18.C01, L18.C04, L22.C04, L26.C01</t>
+          <t>L6.C09, L11.C13, L11.C25, L20.C20, L23.C01, L23.C02, L23.C03</t>
         </is>
       </c>
       <c r="N270" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-24-conditions-materielles-de-la-vie/c01-ce-que-ce-livre-doit-etablir.md</t>
+          <t>corpus/livre-23-fiscalite-mondiale-et-opacite/c04-la-transparence-que-le-corpus-supposait-a-ete-invalidee.md</t>
         </is>
       </c>
     </row>
     <row r="271">
       <c r="A271" s="2" t="inlineStr">
         <is>
-          <t>L24.C02</t>
+          <t>L23.C05</t>
         </is>
       </c>
       <c r="B271" s="3" t="inlineStr">
         <is>
-          <t>L24</t>
+          <t>L23</t>
         </is>
       </c>
       <c r="C271" s="3" t="inlineStr">
         <is>
-          <t>Le seuil juste est plus strict que le seuil sûr</t>
+          <t>Intéresser le percepteur, et ce que le taux révèle</t>
         </is>
       </c>
       <c r="D271" s="3" t="inlineStr">
@@ -18860,41 +18864,41 @@
       </c>
       <c r="I271" s="3" t="inlineStr"/>
       <c r="J271" s="3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K271" s="3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L271" s="3" t="inlineStr">
         <is>
-          <t>limites_planetaires, plafond_ecologique, plancher_social, dette_ecologique, essentiel_insolvable, qualification_regenerative</t>
+          <t>bareme, reflux_transactionnel, regle_contre_discretion, polycentricite, seuil_d_activation</t>
         </is>
       </c>
       <c r="M271" s="3" t="inlineStr">
         <is>
-          <t>L1.C15, L11.C13, L12.C01, L18.C01, L24.C01, L25.C01</t>
+          <t>L11.C21, L11.C24, L18.C09, L20.C20, L23.C01, L23.C02, L23.C03</t>
         </is>
       </c>
       <c r="N271" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-24-conditions-materielles-de-la-vie/c02-le-seuil-juste-est-plus-strict-que-le-seuil-sur.md</t>
+          <t>corpus/livre-23-fiscalite-mondiale-et-opacite/c05-interesser-le-percepteur-et-ce-que-le-taux-revele.md</t>
         </is>
       </c>
     </row>
     <row r="272">
       <c r="A272" s="2" t="inlineStr">
         <is>
-          <t>L24.C03</t>
+          <t>L23.C06</t>
         </is>
       </c>
       <c r="B272" s="3" t="inlineStr">
         <is>
-          <t>L24</t>
+          <t>L23</t>
         </is>
       </c>
       <c r="C272" s="3" t="inlineStr">
         <is>
-          <t>La matière, et le levier commun que les neuf dimensions n'avaient pas</t>
+          <t>L'arbre appliqué à la fonte, et il ne reste que deux branches</t>
         </is>
       </c>
       <c r="D272" s="3" t="inlineStr">
@@ -18914,7 +18918,7 @@
       </c>
       <c r="G272" s="3" t="inlineStr">
         <is>
-          <t>hybride</t>
+          <t>conception</t>
         </is>
       </c>
       <c r="H272" s="3" t="inlineStr">
@@ -18927,38 +18931,38 @@
         <v>4</v>
       </c>
       <c r="K272" s="3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L272" s="3" t="inlineStr">
         <is>
-          <t>limites_planetaires, decouplage, effet_rebond, sobriete, entropie, plafond_ecologique, externalisation, degeneratif</t>
+          <t>bareme, reflux_transactionnel, monnaie_fondante, demurrage, regle_contre_discretion, essentiel_insolvable</t>
         </is>
       </c>
       <c r="M272" s="3" t="inlineStr">
         <is>
-          <t>L1.C15, L11.C13, L17.C01, L18.C04, L24.C01, L24.C02, L26.C01</t>
+          <t>L10.C06, L11.C05, L11.C09, L11.C21, L11.C24, L18.C09, L20.C02, L23.C01, L23.C02, L23.C03, L23.C04, L23.C05</t>
         </is>
       </c>
       <c r="N272" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-24-conditions-materielles-de-la-vie/c03-la-matiere-et-le-levier-commun.md</t>
+          <t>corpus/livre-23-fiscalite-mondiale-et-opacite/c06-l-arbre-applique-a-la-fonte.md</t>
         </is>
       </c>
     </row>
     <row r="273">
       <c r="A273" s="2" t="inlineStr">
         <is>
-          <t>L24.C04</t>
+          <t>L23.C07</t>
         </is>
       </c>
       <c r="B273" s="3" t="inlineStr">
         <is>
-          <t>L24</t>
+          <t>L23</t>
         </is>
       </c>
       <c r="C273" s="3" t="inlineStr">
         <is>
-          <t>Un budget mondial n'est pas partageable</t>
+          <t>Portée de la tranche, et la moitié qui n'est pas commencée</t>
         </is>
       </c>
       <c r="D273" s="3" t="inlineStr">
@@ -18978,7 +18982,7 @@
       </c>
       <c r="G273" s="3" t="inlineStr">
         <is>
-          <t>hybride</t>
+          <t>conception</t>
         </is>
       </c>
       <c r="H273" s="3" t="inlineStr">
@@ -18988,31 +18992,31 @@
       </c>
       <c r="I273" s="3" t="inlineStr"/>
       <c r="J273" s="3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K273" s="3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L273" s="3" t="inlineStr">
         <is>
-          <t>limites_planetaires, plafond_ecologique, communs, qualification_regenerative, externalisation, polycentricite</t>
+          <t>bareme, reflux_transactionnel, externalisation, regle_contre_discretion, polycentricite, essentiel_insolvable</t>
         </is>
       </c>
       <c r="M273" s="3" t="inlineStr">
         <is>
-          <t>L11.C13, L11.C24, L22.C04, L24.C01, L24.C02, L24.C03, L25.C05</t>
+          <t>L10.C06, L11.C05, L11.C21, L11.C25, L18.C09, L20.C20, L23.C01, L23.C02, L23.C03, L23.C04, L23.C05, L23.C06</t>
         </is>
       </c>
       <c r="N273" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-24-conditions-materielles-de-la-vie/c04-un-budget-mondial-n-est-pas-partageable.md</t>
+          <t>corpus/livre-23-fiscalite-mondiale-et-opacite/c07-portee-de-la-tranche.md</t>
         </is>
       </c>
     </row>
     <row r="274">
       <c r="A274" s="2" t="inlineStr">
         <is>
-          <t>L24.C05</t>
+          <t>L24.C01</t>
         </is>
       </c>
       <c r="B274" s="3" t="inlineStr">
@@ -19022,7 +19026,7 @@
       </c>
       <c r="C274" s="3" t="inlineStr">
         <is>
-          <t>Portée de la tranche</t>
+          <t>Ce que ce livre doit établir</t>
         </is>
       </c>
       <c r="D274" s="3" t="inlineStr">
@@ -19047,46 +19051,46 @@
       </c>
       <c r="H274" s="3" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="I274" s="3" t="inlineStr"/>
       <c r="J274" s="3" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K274" s="3" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L274" s="3" t="inlineStr">
         <is>
-          <t>limites_planetaires, plafond_ecologique, plancher_social, decouplage, qualification_regenerative, entropie</t>
+          <t>limites_planetaires, plafond_ecologique, entropie, decouplage, degeneratif, qualification_regenerative, essentiel_insolvable</t>
         </is>
       </c>
       <c r="M274" s="3" t="inlineStr">
         <is>
-          <t>L11.C13, L11.C24, L18.C01, L22.C04, L24.C01, L24.C02, L24.C03, L24.C04, L25.C05, L26.C01, L26.C02, L17.C05</t>
+          <t>L1.C15, L5.C08, L11.C13, L18.C01, L18.C04, L22.C04, L26.C01</t>
         </is>
       </c>
       <c r="N274" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-24-conditions-materielles-de-la-vie/c05-portee-de-la-tranche.md</t>
+          <t>corpus/livre-24-conditions-materielles-de-la-vie/c01-ce-que-ce-livre-doit-etablir.md</t>
         </is>
       </c>
     </row>
     <row r="275">
       <c r="A275" s="2" t="inlineStr">
         <is>
-          <t>L25.C01</t>
+          <t>L24.C02</t>
         </is>
       </c>
       <c r="B275" s="3" t="inlineStr">
         <is>
-          <t>L25</t>
+          <t>L24</t>
         </is>
       </c>
       <c r="C275" s="3" t="inlineStr">
         <is>
-          <t>Ce que ce livre doit établir</t>
+          <t>Le seuil juste est plus strict que le seuil sûr</t>
         </is>
       </c>
       <c r="D275" s="3" t="inlineStr">
@@ -19106,7 +19110,7 @@
       </c>
       <c r="G275" s="3" t="inlineStr">
         <is>
-          <t>descriptif</t>
+          <t>hybride</t>
         </is>
       </c>
       <c r="H275" s="3" t="inlineStr">
@@ -19123,34 +19127,34 @@
       </c>
       <c r="L275" s="3" t="inlineStr">
         <is>
-          <t>plancher_social, plafond_ecologique, essentiel_insolvable, dette_ecologique, communs, solvabilite_anticipee</t>
+          <t>limites_planetaires, plafond_ecologique, plancher_social, dette_ecologique, essentiel_insolvable, qualification_regenerative</t>
         </is>
       </c>
       <c r="M275" s="3" t="inlineStr">
         <is>
-          <t>L1.C15, L11.C09, L11.C18, L12.C01, L24.C01, L24.C02, L24.C03</t>
+          <t>L1.C15, L11.C13, L12.C01, L18.C01, L24.C01, L25.C01</t>
         </is>
       </c>
       <c r="N275" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-25-repartition-et-justice-sociale/c01-ce-que-ce-livre-doit-etablir.md</t>
+          <t>corpus/livre-24-conditions-materielles-de-la-vie/c02-le-seuil-juste-est-plus-strict-que-le-seuil-sur.md</t>
         </is>
       </c>
     </row>
     <row r="276">
       <c r="A276" s="2" t="inlineStr">
         <is>
-          <t>L25.C02</t>
+          <t>L24.C03</t>
         </is>
       </c>
       <c r="B276" s="3" t="inlineStr">
         <is>
-          <t>L25</t>
+          <t>L24</t>
         </is>
       </c>
       <c r="C276" s="3" t="inlineStr">
         <is>
-          <t>Le noyau dur, et la charge de la preuve renversée</t>
+          <t>La matière, et le levier commun que les neuf dimensions n'avaient pas</t>
         </is>
       </c>
       <c r="D276" s="3" t="inlineStr">
@@ -19187,34 +19191,34 @@
       </c>
       <c r="L276" s="3" t="inlineStr">
         <is>
-          <t>plancher_social, essentiel_insolvable, plafond_ecologique, solvabilite_anticipee, regle_contre_discretion</t>
+          <t>limites_planetaires, decouplage, effet_rebond, sobriete, entropie, plafond_ecologique, externalisation, degeneratif</t>
         </is>
       </c>
       <c r="M276" s="3" t="inlineStr">
         <is>
-          <t>L1.C15, L11.C09, L11.C18, L22.C02, L22.C04, L24.C02, L25.C01</t>
+          <t>L1.C15, L11.C13, L17.C01, L18.C04, L24.C01, L24.C02, L26.C01</t>
         </is>
       </c>
       <c r="N276" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-25-repartition-et-justice-sociale/c02-le-noyau-dur-et-la-charge-de-la-preuve.md</t>
+          <t>corpus/livre-24-conditions-materielles-de-la-vie/c03-la-matiere-et-le-levier-commun.md</t>
         </is>
       </c>
     </row>
     <row r="277">
       <c r="A277" s="2" t="inlineStr">
         <is>
-          <t>L25.C03</t>
+          <t>L24.C04</t>
         </is>
       </c>
       <c r="B277" s="3" t="inlineStr">
         <is>
-          <t>L25</t>
+          <t>L24</t>
         </is>
       </c>
       <c r="C277" s="3" t="inlineStr">
         <is>
-          <t>Ce que le droit oblige à donner, et ce qu'il refuse de réparer</t>
+          <t>Un budget mondial n'est pas partageable</t>
         </is>
       </c>
       <c r="D277" s="3" t="inlineStr">
@@ -19244,41 +19248,41 @@
       </c>
       <c r="I277" s="3" t="inlineStr"/>
       <c r="J277" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K277" s="3" t="n">
         <v>4</v>
       </c>
       <c r="L277" s="3" t="inlineStr">
         <is>
-          <t>dette_ecologique, plancher_social, creation_monetaire, reflux_collectif, essentiel_insolvable, solvabilite_anticipee</t>
+          <t>limites_planetaires, plafond_ecologique, communs, qualification_regenerative, externalisation, polycentricite</t>
         </is>
       </c>
       <c r="M277" s="3" t="inlineStr">
         <is>
-          <t>L1.C20, L11.C01, L20.C01, L24.C02, L25.C01, L25.C02</t>
+          <t>L11.C13, L11.C24, L22.C04, L24.C01, L24.C02, L24.C03, L25.C05</t>
         </is>
       </c>
       <c r="N277" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-25-repartition-et-justice-sociale/c03-ce-que-le-droit-oblige-a-donner.md</t>
+          <t>corpus/livre-24-conditions-materielles-de-la-vie/c04-un-budget-mondial-n-est-pas-partageable.md</t>
         </is>
       </c>
     </row>
     <row r="278">
       <c r="A278" s="2" t="inlineStr">
         <is>
-          <t>L25.C04</t>
+          <t>L24.C05</t>
         </is>
       </c>
       <c r="B278" s="3" t="inlineStr">
         <is>
-          <t>L25</t>
+          <t>L24</t>
         </is>
       </c>
       <c r="C278" s="3" t="inlineStr">
         <is>
-          <t>A34 en droit positif, et le critère que le corpus n'avait pas</t>
+          <t>Portée de la tranche</t>
         </is>
       </c>
       <c r="D278" s="3" t="inlineStr">
@@ -19298,41 +19302,41 @@
       </c>
       <c r="G278" s="3" t="inlineStr">
         <is>
-          <t>hybride</t>
+          <t>descriptif</t>
         </is>
       </c>
       <c r="H278" s="3" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="I278" s="3" t="inlineStr"/>
       <c r="J278" s="3" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K278" s="3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L278" s="3" t="inlineStr">
         <is>
-          <t>plancher_social, bareme, essentiel_insolvable, sobriete, affectation_des_instruments, reflux_transactionnel</t>
+          <t>limites_planetaires, plafond_ecologique, plancher_social, decouplage, qualification_regenerative, entropie</t>
         </is>
       </c>
       <c r="M278" s="3" t="inlineStr">
         <is>
-          <t>L1.C15, L11.C09, L11.C18, L11.C21, L22.C02, L24.C03, L25.C01, L25.C02</t>
+          <t>L11.C13, L11.C24, L18.C01, L22.C04, L24.C01, L24.C02, L24.C03, L24.C04, L25.C05, L26.C01, L26.C02, L17.C05</t>
         </is>
       </c>
       <c r="N278" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-25-repartition-et-justice-sociale/c04-a34-en-droit-positif.md</t>
+          <t>corpus/livre-24-conditions-materielles-de-la-vie/c05-portee-de-la-tranche.md</t>
         </is>
       </c>
     </row>
     <row r="279">
       <c r="A279" s="2" t="inlineStr">
         <is>
-          <t>L25.C05</t>
+          <t>L25.C01</t>
         </is>
       </c>
       <c r="B279" s="3" t="inlineStr">
@@ -19342,7 +19346,7 @@
       </c>
       <c r="C279" s="3" t="inlineStr">
         <is>
-          <t>Le droit différencie sans calculer</t>
+          <t>Ce que ce livre doit établir</t>
         </is>
       </c>
       <c r="D279" s="3" t="inlineStr">
@@ -19362,7 +19366,7 @@
       </c>
       <c r="G279" s="3" t="inlineStr">
         <is>
-          <t>hybride</t>
+          <t>descriptif</t>
         </is>
       </c>
       <c r="H279" s="3" t="inlineStr">
@@ -19372,31 +19376,31 @@
       </c>
       <c r="I279" s="3" t="inlineStr"/>
       <c r="J279" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K279" s="3" t="n">
         <v>4</v>
       </c>
       <c r="L279" s="3" t="inlineStr">
         <is>
-          <t>dette_ecologique, plancher_social, plafond_ecologique, bareme, indicateur_de_progres, polycentricite</t>
+          <t>plancher_social, plafond_ecologique, essentiel_insolvable, dette_ecologique, communs, solvabilite_anticipee</t>
         </is>
       </c>
       <c r="M279" s="3" t="inlineStr">
         <is>
-          <t>L11.C13, L22.C04, L22.C06, L24.C01, L24.C02, L25.C01, L25.C02, L25.C03, L25.C04</t>
+          <t>L1.C15, L11.C09, L11.C18, L12.C01, L24.C01, L24.C02, L24.C03</t>
         </is>
       </c>
       <c r="N279" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-25-repartition-et-justice-sociale/c05-le-droit-differencie-sans-calculer.md</t>
+          <t>corpus/livre-25-repartition-et-justice-sociale/c01-ce-que-ce-livre-doit-etablir.md</t>
         </is>
       </c>
     </row>
     <row r="280">
       <c r="A280" s="2" t="inlineStr">
         <is>
-          <t>L25.C06</t>
+          <t>L25.C02</t>
         </is>
       </c>
       <c r="B280" s="3" t="inlineStr">
@@ -19406,7 +19410,7 @@
       </c>
       <c r="C280" s="3" t="inlineStr">
         <is>
-          <t>Portée de la tranche</t>
+          <t>Le noyau dur, et la charge de la preuve renversée</t>
         </is>
       </c>
       <c r="D280" s="3" t="inlineStr">
@@ -19426,7 +19430,7 @@
       </c>
       <c r="G280" s="3" t="inlineStr">
         <is>
-          <t>descriptif</t>
+          <t>hybride</t>
         </is>
       </c>
       <c r="H280" s="3" t="inlineStr">
@@ -19436,41 +19440,41 @@
       </c>
       <c r="I280" s="3" t="inlineStr"/>
       <c r="J280" s="3" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K280" s="3" t="n">
         <v>4</v>
       </c>
       <c r="L280" s="3" t="inlineStr">
         <is>
-          <t>plancher_social, plafond_ecologique, dette_ecologique, essentiel_insolvable, bareme</t>
+          <t>plancher_social, essentiel_insolvable, plafond_ecologique, solvabilite_anticipee, regle_contre_discretion</t>
         </is>
       </c>
       <c r="M280" s="3" t="inlineStr">
         <is>
-          <t>L5.C09, L11.C09, L11.C18, L24.C02, L25.C01, L25.C02, L25.C03, L25.C04, L25.C05</t>
+          <t>L1.C15, L11.C09, L11.C18, L22.C02, L22.C04, L24.C02, L25.C01</t>
         </is>
       </c>
       <c r="N280" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-25-repartition-et-justice-sociale/c06-portee-de-la-tranche.md</t>
+          <t>corpus/livre-25-repartition-et-justice-sociale/c02-le-noyau-dur-et-la-charge-de-la-preuve.md</t>
         </is>
       </c>
     </row>
     <row r="281">
       <c r="A281" s="2" t="inlineStr">
         <is>
-          <t>L26.C01</t>
+          <t>L25.C03</t>
         </is>
       </c>
       <c r="B281" s="3" t="inlineStr">
         <is>
-          <t>L26</t>
+          <t>L25</t>
         </is>
       </c>
       <c r="C281" s="3" t="inlineStr">
         <is>
-          <t>Ce que ce livre doit établir</t>
+          <t>Ce que le droit oblige à donner, et ce qu'il refuse de réparer</t>
         </is>
       </c>
       <c r="D281" s="3" t="inlineStr">
@@ -19495,46 +19499,46 @@
       </c>
       <c r="H281" s="3" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="I281" s="3" t="inlineStr"/>
       <c r="J281" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K281" s="3" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L281" s="3" t="inlineStr">
         <is>
-          <t>entropie, decouplage, effet_rebond, limites_planetaires, sobriete, degeneratif, qualification_regenerative</t>
+          <t>dette_ecologique, plancher_social, creation_monetaire, reflux_collectif, essentiel_insolvable, solvabilite_anticipee</t>
         </is>
       </c>
       <c r="M281" s="3" t="inlineStr">
         <is>
-          <t>L1.C03, L1.C15, L1.C17, L8.C13, L8.C34, L11.C13, L18.C04, L24.C03, L24.C05, L17.C02</t>
+          <t>L1.C20, L11.C01, L20.C01, L24.C02, L25.C01, L25.C02</t>
         </is>
       </c>
       <c r="N281" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-26-thermodynamique-et-processus-economique/c01-ce-que-ce-livre-doit-etablir.md</t>
+          <t>corpus/livre-25-repartition-et-justice-sociale/c03-ce-que-le-droit-oblige-a-donner.md</t>
         </is>
       </c>
     </row>
     <row r="282">
       <c r="A282" s="2" t="inlineStr">
         <is>
-          <t>L26.C02</t>
+          <t>L25.C04</t>
         </is>
       </c>
       <c r="B282" s="3" t="inlineStr">
         <is>
-          <t>L26</t>
+          <t>L25</t>
         </is>
       </c>
       <c r="C282" s="3" t="inlineStr">
         <is>
-          <t>Le stock n'existe pas sous la forme demandée</t>
+          <t>A34 en droit positif, et le critère que le corpus n'avait pas</t>
         </is>
       </c>
       <c r="D282" s="3" t="inlineStr">
@@ -19559,46 +19563,46 @@
       </c>
       <c r="H282" s="3" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="I282" s="3" t="inlineStr"/>
       <c r="J282" s="3" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K282" s="3" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L282" s="3" t="inlineStr">
         <is>
-          <t>entropie, bareme, limites_planetaires, decouplage, sobriete, fausse_richesse</t>
+          <t>plancher_social, bareme, essentiel_insolvable, sobriete, affectation_des_instruments, reflux_transactionnel</t>
         </is>
       </c>
       <c r="M282" s="3" t="inlineStr">
         <is>
-          <t>L1.C15, L11.C13, L11.C24, L18.C04, L22.C04, L24.C03, L24.C05, L26.C01, L17.C02</t>
+          <t>L1.C15, L11.C09, L11.C18, L11.C21, L22.C02, L24.C03, L25.C01, L25.C02</t>
         </is>
       </c>
       <c r="N282" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-26-thermodynamique-et-processus-economique/c02-le-stock-n-existe-pas-sous-la-forme-demandee.md</t>
+          <t>corpus/livre-25-repartition-et-justice-sociale/c04-a34-en-droit-positif.md</t>
         </is>
       </c>
     </row>
     <row r="283">
       <c r="A283" s="2" t="inlineStr">
         <is>
-          <t>L26.C03</t>
+          <t>L25.C05</t>
         </is>
       </c>
       <c r="B283" s="3" t="inlineStr">
         <is>
-          <t>L26</t>
+          <t>L25</t>
         </is>
       </c>
       <c r="C283" s="3" t="inlineStr">
         <is>
-          <t>La frontière décide du chiffre</t>
+          <t>Le droit différencie sans calculer</t>
         </is>
       </c>
       <c r="D283" s="3" t="inlineStr">
@@ -19623,46 +19627,46 @@
       </c>
       <c r="H283" s="3" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="I283" s="3" t="inlineStr"/>
       <c r="J283" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K283" s="3" t="n">
         <v>4</v>
       </c>
       <c r="L283" s="3" t="inlineStr">
         <is>
-          <t>entropie, decouplage, sobriete, limites_planetaires, robustesse, bareme</t>
+          <t>dette_ecologique, plancher_social, plafond_ecologique, bareme, indicateur_de_progres, polycentricite</t>
         </is>
       </c>
       <c r="M283" s="3" t="inlineStr">
         <is>
-          <t>L11.C10, L11.C13, L11.C24, L18.C04, L18.C09, L24.C03, L24.C04, L26.C01, L26.C02</t>
+          <t>L11.C13, L22.C04, L22.C06, L24.C01, L24.C02, L25.C01, L25.C02, L25.C03, L25.C04</t>
         </is>
       </c>
       <c r="N283" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-26-thermodynamique-et-processus-economique/c03-la-frontiere-decide-du-chiffre.md</t>
+          <t>corpus/livre-25-repartition-et-justice-sociale/c05-le-droit-differencie-sans-calculer.md</t>
         </is>
       </c>
     </row>
     <row r="284">
       <c r="A284" s="2" t="inlineStr">
         <is>
-          <t>L26.C04</t>
+          <t>L25.C06</t>
         </is>
       </c>
       <c r="B284" s="3" t="inlineStr">
         <is>
-          <t>L26</t>
+          <t>L25</t>
         </is>
       </c>
       <c r="C284" s="3" t="inlineStr">
         <is>
-          <t>L'effet rebond, et ce que le dispositif en hérite sans être une politique d'efficacité</t>
+          <t>Portée de la tranche</t>
         </is>
       </c>
       <c r="D284" s="3" t="inlineStr">
@@ -19682,12 +19686,12 @@
       </c>
       <c r="G284" s="3" t="inlineStr">
         <is>
-          <t>hybride</t>
+          <t>descriptif</t>
         </is>
       </c>
       <c r="H284" s="3" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="I284" s="3" t="inlineStr"/>
@@ -19699,24 +19703,24 @@
       </c>
       <c r="L284" s="3" t="inlineStr">
         <is>
-          <t>effet_rebond, jevons_monetaire, decouplage, sobriete, entropie, reflux_transactionnel</t>
+          <t>plancher_social, plafond_ecologique, dette_ecologique, essentiel_insolvable, bareme</t>
         </is>
       </c>
       <c r="M284" s="3" t="inlineStr">
         <is>
-          <t>L1.C03, L1.C12, L1.C17, L11.C10, L13.C01, L18.C04, L22.C02, L24.C03, L26.C01, L26.C03</t>
+          <t>L5.C09, L11.C09, L11.C18, L24.C02, L25.C01, L25.C02, L25.C03, L25.C04, L25.C05</t>
         </is>
       </c>
       <c r="N284" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-26-thermodynamique-et-processus-economique/c04-l-effet-rebond-et-ce-que-le-dispositif-en-herite.md</t>
+          <t>corpus/livre-25-repartition-et-justice-sociale/c06-portee-de-la-tranche.md</t>
         </is>
       </c>
     </row>
     <row r="285">
       <c r="A285" s="2" t="inlineStr">
         <is>
-          <t>L26.C05</t>
+          <t>L26.C01</t>
         </is>
       </c>
       <c r="B285" s="3" t="inlineStr">
@@ -19726,7 +19730,7 @@
       </c>
       <c r="C285" s="3" t="inlineStr">
         <is>
-          <t>L'addition n'est pas la substitution</t>
+          <t>Ce que ce livre doit établir</t>
         </is>
       </c>
       <c r="D285" s="3" t="inlineStr">
@@ -19756,31 +19760,31 @@
       </c>
       <c r="I285" s="3" t="inlineStr"/>
       <c r="J285" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K285" s="3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L285" s="3" t="inlineStr">
         <is>
-          <t>decouplage, effet_rebond, sobriete, degeneratif, affectation_des_instruments</t>
+          <t>entropie, decouplage, effet_rebond, limites_planetaires, sobriete, degeneratif, qualification_regenerative</t>
         </is>
       </c>
       <c r="M285" s="3" t="inlineStr">
         <is>
-          <t>L1.C12, L11.C10, L11.C13, L18.C04, L18.C09, L22.C02, L24.C03, L26.C01, L26.C03, L26.C04</t>
+          <t>L1.C03, L1.C15, L1.C17, L8.C13, L8.C34, L11.C13, L18.C04, L24.C03, L24.C05, L17.C02</t>
         </is>
       </c>
       <c r="N285" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-26-thermodynamique-et-processus-economique/c05-l-addition-n-est-pas-la-substitution.md</t>
+          <t>corpus/livre-26-thermodynamique-et-processus-economique/c01-ce-que-ce-livre-doit-etablir.md</t>
         </is>
       </c>
     </row>
     <row r="286">
       <c r="A286" s="2" t="inlineStr">
         <is>
-          <t>L26.C06</t>
+          <t>L26.C02</t>
         </is>
       </c>
       <c r="B286" s="3" t="inlineStr">
@@ -19790,7 +19794,7 @@
       </c>
       <c r="C286" s="3" t="inlineStr">
         <is>
-          <t>Portée de la tranche</t>
+          <t>Le stock n'existe pas sous la forme demandée</t>
         </is>
       </c>
       <c r="D286" s="3" t="inlineStr">
@@ -19810,7 +19814,7 @@
       </c>
       <c r="G286" s="3" t="inlineStr">
         <is>
-          <t>descriptif</t>
+          <t>hybride</t>
         </is>
       </c>
       <c r="H286" s="3" t="inlineStr">
@@ -19823,26 +19827,282 @@
         <v>1</v>
       </c>
       <c r="K286" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="L286" s="3" t="inlineStr">
+        <is>
+          <t>entropie, bareme, limites_planetaires, decouplage, sobriete, fausse_richesse</t>
+        </is>
+      </c>
+      <c r="M286" s="3" t="inlineStr">
+        <is>
+          <t>L1.C15, L11.C13, L11.C24, L18.C04, L22.C04, L24.C03, L24.C05, L26.C01, L17.C02</t>
+        </is>
+      </c>
+      <c r="N286" s="3" t="inlineStr">
+        <is>
+          <t>corpus/livre-26-thermodynamique-et-processus-economique/c02-le-stock-n-existe-pas-sous-la-forme-demandee.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" s="2" t="inlineStr">
+        <is>
+          <t>L26.C03</t>
+        </is>
+      </c>
+      <c r="B287" s="3" t="inlineStr">
+        <is>
+          <t>L26</t>
+        </is>
+      </c>
+      <c r="C287" s="3" t="inlineStr">
+        <is>
+          <t>La frontière décide du chiffre</t>
+        </is>
+      </c>
+      <c r="D287" s="3" t="inlineStr">
+        <is>
+          <t>brouillon</t>
+        </is>
+      </c>
+      <c r="E287" s="3" t="inlineStr">
+        <is>
+          <t>preparatoire</t>
+        </is>
+      </c>
+      <c r="F287" s="3" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="G287" s="3" t="inlineStr">
+        <is>
+          <t>hybride</t>
+        </is>
+      </c>
+      <c r="H287" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="I287" s="3" t="inlineStr"/>
+      <c r="J287" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="K287" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="L286" s="3" t="inlineStr">
+      <c r="L287" s="3" t="inlineStr">
+        <is>
+          <t>entropie, decouplage, sobriete, limites_planetaires, robustesse, bareme</t>
+        </is>
+      </c>
+      <c r="M287" s="3" t="inlineStr">
+        <is>
+          <t>L11.C10, L11.C13, L11.C24, L18.C04, L18.C09, L24.C03, L24.C04, L26.C01, L26.C02</t>
+        </is>
+      </c>
+      <c r="N287" s="3" t="inlineStr">
+        <is>
+          <t>corpus/livre-26-thermodynamique-et-processus-economique/c03-la-frontiere-decide-du-chiffre.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" s="2" t="inlineStr">
+        <is>
+          <t>L26.C04</t>
+        </is>
+      </c>
+      <c r="B288" s="3" t="inlineStr">
+        <is>
+          <t>L26</t>
+        </is>
+      </c>
+      <c r="C288" s="3" t="inlineStr">
+        <is>
+          <t>L'effet rebond, et ce que le dispositif en hérite sans être une politique d'efficacité</t>
+        </is>
+      </c>
+      <c r="D288" s="3" t="inlineStr">
+        <is>
+          <t>brouillon</t>
+        </is>
+      </c>
+      <c r="E288" s="3" t="inlineStr">
+        <is>
+          <t>preparatoire</t>
+        </is>
+      </c>
+      <c r="F288" s="3" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="G288" s="3" t="inlineStr">
+        <is>
+          <t>hybride</t>
+        </is>
+      </c>
+      <c r="H288" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="I288" s="3" t="inlineStr"/>
+      <c r="J288" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="K288" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="L288" s="3" t="inlineStr">
+        <is>
+          <t>effet_rebond, jevons_monetaire, decouplage, sobriete, entropie, reflux_transactionnel</t>
+        </is>
+      </c>
+      <c r="M288" s="3" t="inlineStr">
+        <is>
+          <t>L1.C03, L1.C12, L1.C17, L11.C10, L13.C01, L18.C04, L22.C02, L24.C03, L26.C01, L26.C03</t>
+        </is>
+      </c>
+      <c r="N288" s="3" t="inlineStr">
+        <is>
+          <t>corpus/livre-26-thermodynamique-et-processus-economique/c04-l-effet-rebond-et-ce-que-le-dispositif-en-herite.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" s="2" t="inlineStr">
+        <is>
+          <t>L26.C05</t>
+        </is>
+      </c>
+      <c r="B289" s="3" t="inlineStr">
+        <is>
+          <t>L26</t>
+        </is>
+      </c>
+      <c r="C289" s="3" t="inlineStr">
+        <is>
+          <t>L'addition n'est pas la substitution</t>
+        </is>
+      </c>
+      <c r="D289" s="3" t="inlineStr">
+        <is>
+          <t>brouillon</t>
+        </is>
+      </c>
+      <c r="E289" s="3" t="inlineStr">
+        <is>
+          <t>preparatoire</t>
+        </is>
+      </c>
+      <c r="F289" s="3" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="G289" s="3" t="inlineStr">
+        <is>
+          <t>hybride</t>
+        </is>
+      </c>
+      <c r="H289" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="I289" s="3" t="inlineStr"/>
+      <c r="J289" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="K289" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="L289" s="3" t="inlineStr">
+        <is>
+          <t>decouplage, effet_rebond, sobriete, degeneratif, affectation_des_instruments</t>
+        </is>
+      </c>
+      <c r="M289" s="3" t="inlineStr">
+        <is>
+          <t>L1.C12, L11.C10, L11.C13, L18.C04, L18.C09, L22.C02, L24.C03, L26.C01, L26.C03, L26.C04</t>
+        </is>
+      </c>
+      <c r="N289" s="3" t="inlineStr">
+        <is>
+          <t>corpus/livre-26-thermodynamique-et-processus-economique/c05-l-addition-n-est-pas-la-substitution.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" s="2" t="inlineStr">
+        <is>
+          <t>L26.C06</t>
+        </is>
+      </c>
+      <c r="B290" s="3" t="inlineStr">
+        <is>
+          <t>L26</t>
+        </is>
+      </c>
+      <c r="C290" s="3" t="inlineStr">
+        <is>
+          <t>Portée de la tranche</t>
+        </is>
+      </c>
+      <c r="D290" s="3" t="inlineStr">
+        <is>
+          <t>brouillon</t>
+        </is>
+      </c>
+      <c r="E290" s="3" t="inlineStr">
+        <is>
+          <t>preparatoire</t>
+        </is>
+      </c>
+      <c r="F290" s="3" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="G290" s="3" t="inlineStr">
+        <is>
+          <t>descriptif</t>
+        </is>
+      </c>
+      <c r="H290" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="I290" s="3" t="inlineStr"/>
+      <c r="J290" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="K290" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="L290" s="3" t="inlineStr">
         <is>
           <t>entropie, decouplage, effet_rebond, limites_planetaires, sobriete, affectation_des_instruments</t>
         </is>
       </c>
-      <c r="M286" s="3" t="inlineStr">
+      <c r="M290" s="3" t="inlineStr">
         <is>
           <t>L1.C03, L1.C17, L8.C34, L11.C10, L11.C13, L11.C24, L18.C04, L18.C09, L22.C02, L24.C05, L26.C01, L26.C02, L26.C03, L26.C04, L26.C05</t>
         </is>
       </c>
-      <c r="N286" s="3" t="inlineStr">
+      <c r="N290" s="3" t="inlineStr">
         <is>
           <t>corpus/livre-26-thermodynamique-et-processus-economique/c06-portee-de-la-tranche.md</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:N286"/>
+  <autoFilter ref="A1:N290"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -19901,7 +20161,7 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="5">
@@ -19911,7 +20171,7 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="6">
@@ -19921,7 +20181,7 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>285</v>
+        <v>289</v>
       </c>
     </row>
     <row r="7">
@@ -19931,7 +20191,7 @@
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="8">
@@ -19941,7 +20201,7 @@
         </is>
       </c>
       <c r="B8" s="3" t="n">
-        <v>278</v>
+        <v>283</v>
       </c>
     </row>
     <row r="9">
@@ -19951,7 +20211,7 @@
         </is>
       </c>
       <c r="B9" s="3" t="n">
-        <v>276</v>
+        <v>280</v>
       </c>
     </row>
     <row r="10">
@@ -19971,7 +20231,7 @@
         </is>
       </c>
       <c r="B11" s="3" t="n">
-        <v>1376</v>
+        <v>1404</v>
       </c>
     </row>
     <row r="12">
@@ -19981,7 +20241,7 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>1089</v>
+        <v>1094</v>
       </c>
     </row>
     <row r="13">
@@ -19996,7 +20256,7 @@
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>L0, L9, L12, L13, L14, L15, L16</t>
+          <t>L0, L9, L12, L13, L14, L15</t>
         </is>
       </c>
     </row>
@@ -20075,7 +20335,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C313"/>
+  <dimension ref="A1:C317"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -23802,7 +24062,7 @@
       </c>
       <c r="C219" s="6" t="inlineStr">
         <is>
-          <t>candidat — AMORCE SEULE</t>
+          <t>en-cours — 5 chapitre(s)</t>
         </is>
       </c>
     </row>
@@ -23814,7 +24074,7 @@
       </c>
       <c r="B220" s="3" t="inlineStr">
         <is>
-          <t>[AMORCE] Ce que ce livre doit établir</t>
+          <t>Ce que ce livre doit établir</t>
         </is>
       </c>
       <c r="C220" s="3" t="inlineStr">
@@ -23824,31 +24084,31 @@
       </c>
     </row>
     <row r="221">
-      <c r="A221" s="6" t="inlineStr">
-        <is>
-          <t>L17</t>
-        </is>
-      </c>
-      <c r="B221" s="6" t="inlineStr">
-        <is>
-          <t>Après la croissance : décroissance, post-croissance et prospérité sans croissance</t>
-        </is>
-      </c>
-      <c r="C221" s="6" t="inlineStr">
-        <is>
-          <t>en-cours — 6 chapitre(s)</t>
+      <c r="A221" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    L16.C02</t>
+        </is>
+      </c>
+      <c r="B221" s="3" t="inlineStr">
+        <is>
+          <t>La réponse à l'objection de fuite existe, et son prix est la propriété foncière</t>
+        </is>
+      </c>
+      <c r="C221" s="3" t="inlineStr">
+        <is>
+          <t>brouillon</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L17.C01</t>
+          <t xml:space="preserve">    L16.C03</t>
         </is>
       </c>
       <c r="B222" s="3" t="inlineStr">
         <is>
-          <t>Ce que ce livre doit établir</t>
+          <t>Ce que l'expérience a réellement produit, et la sortie était tarifée</t>
         </is>
       </c>
       <c r="C222" s="3" t="inlineStr">
@@ -23860,12 +24120,12 @@
     <row r="223">
       <c r="A223" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L17.C02</t>
+          <t xml:space="preserve">    L16.C04</t>
         </is>
       </c>
       <c r="B223" s="3" t="inlineStr">
         <is>
-          <t>Les sept raisons, testées une par une contre le dispositif</t>
+          <t>Une banque centrale conçoit l'instrument pour qu'il ne serve pas de réserve de valeur — et écrit qu'il lui faut des actifs en face</t>
         </is>
       </c>
       <c r="C223" s="3" t="inlineStr">
@@ -23877,12 +24137,12 @@
     <row r="224">
       <c r="A224" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L17.C03</t>
+          <t xml:space="preserve">    L16.C05</t>
         </is>
       </c>
       <c r="B224" s="3" t="inlineStr">
         <is>
-          <t>La sobriété et l'émission : le dispositif échange du mou contre du dur</t>
+          <t>Portée de la tranche</t>
         </is>
       </c>
       <c r="C224" s="3" t="inlineStr">
@@ -23892,31 +24152,31 @@
       </c>
     </row>
     <row r="225">
-      <c r="A225" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    L17.C04</t>
-        </is>
-      </c>
-      <c r="B225" s="3" t="inlineStr">
-        <is>
-          <t>La seule concrétisation institutionnelle ouverte, et sa seule sanction est de publier ses raisons</t>
-        </is>
-      </c>
-      <c r="C225" s="3" t="inlineStr">
-        <is>
-          <t>brouillon</t>
+      <c r="A225" s="6" t="inlineStr">
+        <is>
+          <t>L17</t>
+        </is>
+      </c>
+      <c r="B225" s="6" t="inlineStr">
+        <is>
+          <t>Après la croissance : décroissance, post-croissance et prospérité sans croissance</t>
+        </is>
+      </c>
+      <c r="C225" s="6" t="inlineStr">
+        <is>
+          <t>en-cours — 6 chapitre(s)</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L17.C05</t>
+          <t xml:space="preserve">    L17.C01</t>
         </is>
       </c>
       <c r="B226" s="3" t="inlineStr">
         <is>
-          <t>Le tableau de bord et le chiffre unique — ce que le corpus perd en refusant d'agréger</t>
+          <t>Ce que ce livre doit établir</t>
         </is>
       </c>
       <c r="C226" s="3" t="inlineStr">
@@ -23928,12 +24188,12 @@
     <row r="227">
       <c r="A227" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L17.C06</t>
+          <t xml:space="preserve">    L17.C02</t>
         </is>
       </c>
       <c r="B227" s="3" t="inlineStr">
         <is>
-          <t>Portée de la tranche</t>
+          <t>Les sept raisons, testées une par une contre le dispositif</t>
         </is>
       </c>
       <c r="C227" s="3" t="inlineStr">
@@ -23943,31 +24203,31 @@
       </c>
     </row>
     <row r="228">
-      <c r="A228" s="6" t="inlineStr">
-        <is>
-          <t>L18</t>
-        </is>
-      </c>
-      <c r="B228" s="6" t="inlineStr">
-        <is>
-          <t>Comptabilités écologiques, sociales et biophysiques</t>
-        </is>
-      </c>
-      <c r="C228" s="6" t="inlineStr">
-        <is>
-          <t>en-cours — 9 chapitre(s)</t>
+      <c r="A228" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    L17.C03</t>
+        </is>
+      </c>
+      <c r="B228" s="3" t="inlineStr">
+        <is>
+          <t>La sobriété et l'émission : le dispositif échange du mou contre du dur</t>
+        </is>
+      </c>
+      <c r="C228" s="3" t="inlineStr">
+        <is>
+          <t>brouillon</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L18.C01</t>
+          <t xml:space="preserve">    L17.C04</t>
         </is>
       </c>
       <c r="B229" s="3" t="inlineStr">
         <is>
-          <t>Ce que ce livre doit établir, et le repli n'est pas l'annexe</t>
+          <t>La seule concrétisation institutionnelle ouverte, et sa seule sanction est de publier ses raisons</t>
         </is>
       </c>
       <c r="C229" s="3" t="inlineStr">
@@ -23979,12 +24239,12 @@
     <row r="230">
       <c r="A230" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L18.C02</t>
+          <t xml:space="preserve">    L17.C05</t>
         </is>
       </c>
       <c r="B230" s="3" t="inlineStr">
         <is>
-          <t>La métrologie existe, et ce qu'elle enregistre est l'ordre en place</t>
+          <t>Le tableau de bord et le chiffre unique — ce que le corpus perd en refusant d'agréger</t>
         </is>
       </c>
       <c r="C230" s="3" t="inlineStr">
@@ -23996,12 +24256,12 @@
     <row r="231">
       <c r="A231" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L18.C03</t>
+          <t xml:space="preserve">    L17.C06</t>
         </is>
       </c>
       <c r="B231" s="3" t="inlineStr">
         <is>
-          <t>L'échelle de repli, et qui l'a arrêtée</t>
+          <t>Portée de la tranche</t>
         </is>
       </c>
       <c r="C231" s="3" t="inlineStr">
@@ -24011,31 +24271,31 @@
       </c>
     </row>
     <row r="232">
-      <c r="A232" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    L18.C04</t>
-        </is>
-      </c>
-      <c r="B232" s="3" t="inlineStr">
-        <is>
-          <t>Les grandeurs physiques, et l'endroit où elles frappent le dispositif</t>
-        </is>
-      </c>
-      <c r="C232" s="3" t="inlineStr">
-        <is>
-          <t>brouillon</t>
+      <c r="A232" s="6" t="inlineStr">
+        <is>
+          <t>L18</t>
+        </is>
+      </c>
+      <c r="B232" s="6" t="inlineStr">
+        <is>
+          <t>Comptabilités écologiques, sociales et biophysiques</t>
+        </is>
+      </c>
+      <c r="C232" s="6" t="inlineStr">
+        <is>
+          <t>en-cours — 9 chapitre(s)</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L18.C05</t>
+          <t xml:space="preserve">    L18.C01</t>
         </is>
       </c>
       <c r="B233" s="3" t="inlineStr">
         <is>
-          <t>Ce que la norme exclut, et ce n'est pas le commun</t>
+          <t>Ce que ce livre doit établir, et le repli n'est pas l'annexe</t>
         </is>
       </c>
       <c r="C233" s="3" t="inlineStr">
@@ -24047,12 +24307,12 @@
     <row r="234">
       <c r="A234" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L18.C06</t>
+          <t xml:space="preserve">    L18.C02</t>
         </is>
       </c>
       <c r="B234" s="3" t="inlineStr">
         <is>
-          <t>Portée de la tranche, et une neuvième condition proposée</t>
+          <t>La métrologie existe, et ce qu'elle enregistre est l'ordre en place</t>
         </is>
       </c>
       <c r="C234" s="3" t="inlineStr">
@@ -24064,12 +24324,12 @@
     <row r="235">
       <c r="A235" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L18.C07</t>
+          <t xml:space="preserve">    L18.C03</t>
         </is>
       </c>
       <c r="B235" s="3" t="inlineStr">
         <is>
-          <t>CARE/TDL répare deux objections, et en crée une plus grave</t>
+          <t>L'échelle de repli, et qui l'a arrêtée</t>
         </is>
       </c>
       <c r="C235" s="3" t="inlineStr">
@@ -24081,12 +24341,12 @@
     <row r="236">
       <c r="A236" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L18.C08</t>
+          <t xml:space="preserve">    L18.C04</t>
         </is>
       </c>
       <c r="B236" s="3" t="inlineStr">
         <is>
-          <t>Le modèle au périmètre du dispositif, et F9 révisée</t>
+          <t>Les grandeurs physiques, et l'endroit où elles frappent le dispositif</t>
         </is>
       </c>
       <c r="C236" s="3" t="inlineStr">
@@ -24098,12 +24358,12 @@
     <row r="237">
       <c r="A237" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L18.C09</t>
+          <t xml:space="preserve">    L18.C05</t>
         </is>
       </c>
       <c r="B237" s="3" t="inlineStr">
         <is>
-          <t>L'ordre de grandeur, et le concurrent qu'il désigne</t>
+          <t>Ce que la norme exclut, et ce n'est pas le commun</t>
         </is>
       </c>
       <c r="C237" s="3" t="inlineStr">
@@ -24113,31 +24373,31 @@
       </c>
     </row>
     <row r="238">
-      <c r="A238" s="6" t="inlineStr">
-        <is>
-          <t>L19</t>
-        </is>
-      </c>
-      <c r="B238" s="6" t="inlineStr">
-        <is>
-          <t>Comptabilité monétaire de l'émission sans dette</t>
-        </is>
-      </c>
-      <c r="C238" s="6" t="inlineStr">
-        <is>
-          <t>en-cours — 7 chapitre(s)</t>
+      <c r="A238" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    L18.C06</t>
+        </is>
+      </c>
+      <c r="B238" s="3" t="inlineStr">
+        <is>
+          <t>Portée de la tranche, et une neuvième condition proposée</t>
+        </is>
+      </c>
+      <c r="C238" s="3" t="inlineStr">
+        <is>
+          <t>brouillon</t>
         </is>
       </c>
     </row>
     <row r="239">
       <c r="A239" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L19.C01</t>
+          <t xml:space="preserve">    L18.C07</t>
         </is>
       </c>
       <c r="B239" s="3" t="inlineStr">
         <is>
-          <t>Ce que ce livre doit établir</t>
+          <t>CARE/TDL répare deux objections, et en crée une plus grave</t>
         </is>
       </c>
       <c r="C239" s="3" t="inlineStr">
@@ -24149,12 +24409,12 @@
     <row r="240">
       <c r="A240" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L19.C02</t>
+          <t xml:space="preserve">    L18.C08</t>
         </is>
       </c>
       <c r="B240" s="3" t="inlineStr">
         <is>
-          <t>Le seul précédent, et le passif lui a été reconnu en 2008</t>
+          <t>Le modèle au périmètre du dispositif, et F9 révisée</t>
         </is>
       </c>
       <c r="C240" s="3" t="inlineStr">
@@ -24166,12 +24426,12 @@
     <row r="241">
       <c r="A241" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L19.C03</t>
+          <t xml:space="preserve">    L18.C09</t>
         </is>
       </c>
       <c r="B241" s="3" t="inlineStr">
         <is>
-          <t>Le reflux est un intérêt négatif, ou une répudiation — et c'est le moment qui décide</t>
+          <t>L'ordre de grandeur, et le concurrent qu'il désigne</t>
         </is>
       </c>
       <c r="C241" s="3" t="inlineStr">
@@ -24181,31 +24441,31 @@
       </c>
     </row>
     <row r="242">
-      <c r="A242" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    L19.C04</t>
-        </is>
-      </c>
-      <c r="B242" s="3" t="inlineStr">
-        <is>
-          <t>L'actif transitoire n'existe pas, et le problème change de bilan</t>
-        </is>
-      </c>
-      <c r="C242" s="3" t="inlineStr">
-        <is>
-          <t>brouillon</t>
+      <c r="A242" s="6" t="inlineStr">
+        <is>
+          <t>L19</t>
+        </is>
+      </c>
+      <c r="B242" s="6" t="inlineStr">
+        <is>
+          <t>Comptabilité monétaire de l'émission sans dette</t>
+        </is>
+      </c>
+      <c r="C242" s="6" t="inlineStr">
+        <is>
+          <t>en-cours — 7 chapitre(s)</t>
         </is>
       </c>
     </row>
     <row r="243">
       <c r="A243" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L19.C05</t>
+          <t xml:space="preserve">    L19.C01</t>
         </is>
       </c>
       <c r="B243" s="3" t="inlineStr">
         <is>
-          <t>Un débiteur collectif n'existe pas — sauf comme somme de débiteurs identifiés</t>
+          <t>Ce que ce livre doit établir</t>
         </is>
       </c>
       <c r="C243" s="3" t="inlineStr">
@@ -24217,12 +24477,12 @@
     <row r="244">
       <c r="A244" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L19.C06</t>
+          <t xml:space="preserve">    L19.C02</t>
         </is>
       </c>
       <c r="B244" s="3" t="inlineStr">
         <is>
-          <t>Les fonds propres négatifs, et l'institution qui n'apparaît dans les comptes de personne</t>
+          <t>Le seul précédent, et le passif lui a été reconnu en 2008</t>
         </is>
       </c>
       <c r="C244" s="3" t="inlineStr">
@@ -24234,12 +24494,12 @@
     <row r="245">
       <c r="A245" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L19.C07</t>
+          <t xml:space="preserve">    L19.C03</t>
         </is>
       </c>
       <c r="B245" s="3" t="inlineStr">
         <is>
-          <t>Portée de la tranche</t>
+          <t>Le reflux est un intérêt négatif, ou une répudiation — et c'est le moment qui décide</t>
         </is>
       </c>
       <c r="C245" s="3" t="inlineStr">
@@ -24249,31 +24509,31 @@
       </c>
     </row>
     <row r="246">
-      <c r="A246" s="6" t="inlineStr">
-        <is>
-          <t>L20</t>
-        </is>
-      </c>
-      <c r="B246" s="6" t="inlineStr">
-        <is>
-          <t>Droit international public, droit monétaire et commercial de la réforme</t>
-        </is>
-      </c>
-      <c r="C246" s="6" t="inlineStr">
-        <is>
-          <t>en-cours — 23 chapitre(s)</t>
+      <c r="A246" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    L19.C04</t>
+        </is>
+      </c>
+      <c r="B246" s="3" t="inlineStr">
+        <is>
+          <t>L'actif transitoire n'existe pas, et le problème change de bilan</t>
+        </is>
+      </c>
+      <c r="C246" s="3" t="inlineStr">
+        <is>
+          <t>brouillon</t>
         </is>
       </c>
     </row>
     <row r="247">
       <c r="A247" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L20.C01</t>
+          <t xml:space="preserve">    L19.C05</t>
         </is>
       </c>
       <c r="B247" s="3" t="inlineStr">
         <is>
-          <t>Ce que ce livre doit établir</t>
+          <t>Un débiteur collectif n'existe pas — sauf comme somme de débiteurs identifiés</t>
         </is>
       </c>
       <c r="C247" s="3" t="inlineStr">
@@ -24285,12 +24545,12 @@
     <row r="248">
       <c r="A248" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L20.C02</t>
+          <t xml:space="preserve">    L19.C06</t>
         </is>
       </c>
       <c r="B248" s="3" t="inlineStr">
         <is>
-          <t>L'interdiction du financement monétaire</t>
+          <t>Les fonds propres négatifs, et l'institution qui n'apparaît dans les comptes de personne</t>
         </is>
       </c>
       <c r="C248" s="3" t="inlineStr">
@@ -24302,12 +24562,12 @@
     <row r="249">
       <c r="A249" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L20.C03</t>
+          <t xml:space="preserve">    L19.C07</t>
         </is>
       </c>
       <c r="B249" s="3" t="inlineStr">
         <is>
-          <t>L'objectif principal et ce qu'il exclut</t>
+          <t>Portée de la tranche</t>
         </is>
       </c>
       <c r="C249" s="3" t="inlineStr">
@@ -24317,31 +24577,31 @@
       </c>
     </row>
     <row r="250">
-      <c r="A250" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    L20.C04</t>
-        </is>
-      </c>
-      <c r="B250" s="3" t="inlineStr">
-        <is>
-          <t>L'indépendance, et à l'égard de qui</t>
-        </is>
-      </c>
-      <c r="C250" s="3" t="inlineStr">
-        <is>
-          <t>brouillon</t>
+      <c r="A250" s="6" t="inlineStr">
+        <is>
+          <t>L20</t>
+        </is>
+      </c>
+      <c r="B250" s="6" t="inlineStr">
+        <is>
+          <t>Droit international public, droit monétaire et commercial de la réforme</t>
+        </is>
+      </c>
+      <c r="C250" s="6" t="inlineStr">
+        <is>
+          <t>en-cours — 23 chapitre(s)</t>
         </is>
       </c>
     </row>
     <row r="251">
       <c r="A251" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L20.C05</t>
+          <t xml:space="preserve">    L20.C01</t>
         </is>
       </c>
       <c r="B251" s="3" t="inlineStr">
         <is>
-          <t>Le monopole d'émission et le cours légal</t>
+          <t>Ce que ce livre doit établir</t>
         </is>
       </c>
       <c r="C251" s="3" t="inlineStr">
@@ -24353,12 +24613,12 @@
     <row r="252">
       <c r="A252" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L20.C06</t>
+          <t xml:space="preserve">    L20.C02</t>
         </is>
       </c>
       <c r="B252" s="3" t="inlineStr">
         <is>
-          <t>Les voies de révision et leur coût</t>
+          <t>L'interdiction du financement monétaire</t>
         </is>
       </c>
       <c r="C252" s="3" t="inlineStr">
@@ -24370,12 +24630,12 @@
     <row r="253">
       <c r="A253" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L20.C07</t>
+          <t xml:space="preserve">    L20.C03</t>
         </is>
       </c>
       <c r="B253" s="3" t="inlineStr">
         <is>
-          <t>L'accord monétaire international</t>
+          <t>L'objectif principal et ce qu'il exclut</t>
         </is>
       </c>
       <c r="C253" s="3" t="inlineStr">
@@ -24387,12 +24647,12 @@
     <row r="254">
       <c r="A254" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L20.C08</t>
+          <t xml:space="preserve">    L20.C04</t>
         </is>
       </c>
       <c r="B254" s="3" t="inlineStr">
         <is>
-          <t>La parité inscrite dans le traité</t>
+          <t>L'indépendance, et à l'égard de qui</t>
         </is>
       </c>
       <c r="C254" s="3" t="inlineStr">
@@ -24404,12 +24664,12 @@
     <row r="255">
       <c r="A255" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L20.C09</t>
+          <t xml:space="preserve">    L20.C05</t>
         </is>
       </c>
       <c r="B255" s="3" t="inlineStr">
         <is>
-          <t>L'amendement des statuts du Fonds</t>
+          <t>Le monopole d'émission et le cours légal</t>
         </is>
       </c>
       <c r="C255" s="3" t="inlineStr">
@@ -24421,12 +24681,12 @@
     <row r="256">
       <c r="A256" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L20.C10</t>
+          <t xml:space="preserve">    L20.C06</t>
         </is>
       </c>
       <c r="B256" s="3" t="inlineStr">
         <is>
-          <t>Le vote pondéré et les voix de base</t>
+          <t>Les voies de révision et leur coût</t>
         </is>
       </c>
       <c r="C256" s="3" t="inlineStr">
@@ -24438,12 +24698,12 @@
     <row r="257">
       <c r="A257" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L20.C11</t>
+          <t xml:space="preserve">    L20.C07</t>
         </is>
       </c>
       <c r="B257" s="3" t="inlineStr">
         <is>
-          <t>La personnalité juridique et les immunités</t>
+          <t>L'accord monétaire international</t>
         </is>
       </c>
       <c r="C257" s="3" t="inlineStr">
@@ -24455,12 +24715,12 @@
     <row r="258">
       <c r="A258" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L20.C12</t>
+          <t xml:space="preserve">    L20.C08</t>
         </is>
       </c>
       <c r="B258" s="3" t="inlineStr">
         <is>
-          <t>Les pouvoirs non délégables</t>
+          <t>La parité inscrite dans le traité</t>
         </is>
       </c>
       <c r="C258" s="3" t="inlineStr">
@@ -24472,12 +24732,12 @@
     <row r="259">
       <c r="A259" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L20.C13</t>
+          <t xml:space="preserve">    L20.C09</t>
         </is>
       </c>
       <c r="B259" s="3" t="inlineStr">
         <is>
-          <t>L'entrée en vigueur, l'adhésion et le retrait</t>
+          <t>L'amendement des statuts du Fonds</t>
         </is>
       </c>
       <c r="C259" s="3" t="inlineStr">
@@ -24489,12 +24749,12 @@
     <row r="260">
       <c r="A260" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L20.C14</t>
+          <t xml:space="preserve">    L20.C10</t>
         </is>
       </c>
       <c r="B260" s="3" t="inlineStr">
         <is>
-          <t>Qui interprète le traité</t>
+          <t>Le vote pondéré et les voix de base</t>
         </is>
       </c>
       <c r="C260" s="3" t="inlineStr">
@@ -24506,12 +24766,12 @@
     <row r="261">
       <c r="A261" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L20.C15</t>
+          <t xml:space="preserve">    L20.C11</t>
         </is>
       </c>
       <c r="B261" s="3" t="inlineStr">
         <is>
-          <t>Le devoir international des agents</t>
+          <t>La personnalité juridique et les immunités</t>
         </is>
       </c>
       <c r="C261" s="3" t="inlineStr">
@@ -24523,12 +24783,12 @@
     <row r="262">
       <c r="A262" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L20.C16</t>
+          <t xml:space="preserve">    L20.C12</t>
         </is>
       </c>
       <c r="B262" s="3" t="inlineStr">
         <is>
-          <t>Le patrimoine commun de l'humanité</t>
+          <t>Les pouvoirs non délégables</t>
         </is>
       </c>
       <c r="C262" s="3" t="inlineStr">
@@ -24540,12 +24800,12 @@
     <row r="263">
       <c r="A263" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L20.C17</t>
+          <t xml:space="preserve">    L20.C13</t>
         </is>
       </c>
       <c r="B263" s="3" t="inlineStr">
         <is>
-          <t>La sanctuarisation, et elle existe</t>
+          <t>L'entrée en vigueur, l'adhésion et le retrait</t>
         </is>
       </c>
       <c r="C263" s="3" t="inlineStr">
@@ -24557,12 +24817,12 @@
     <row r="264">
       <c r="A264" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L20.C18</t>
+          <t xml:space="preserve">    L20.C14</t>
         </is>
       </c>
       <c r="B264" s="3" t="inlineStr">
         <is>
-          <t>L'amendement et la dérogation dans l'ordre commercial</t>
+          <t>Qui interprète le traité</t>
         </is>
       </c>
       <c r="C264" s="3" t="inlineStr">
@@ -24574,12 +24834,12 @@
     <row r="265">
       <c r="A265" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L20.C19</t>
+          <t xml:space="preserve">    L20.C15</t>
         </is>
       </c>
       <c r="B265" s="3" t="inlineStr">
         <is>
-          <t>Le texte que la conformité invoque</t>
+          <t>Le devoir international des agents</t>
         </is>
       </c>
       <c r="C265" s="3" t="inlineStr">
@@ -24591,12 +24851,12 @@
     <row r="266">
       <c r="A266" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L20.C20</t>
+          <t xml:space="preserve">    L20.C16</t>
         </is>
       </c>
       <c r="B266" s="3" t="inlineStr">
         <is>
-          <t>L'ajustement aux frontières comme précédent</t>
+          <t>Le patrimoine commun de l'humanité</t>
         </is>
       </c>
       <c r="C266" s="3" t="inlineStr">
@@ -24608,12 +24868,12 @@
     <row r="267">
       <c r="A267" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L20.C21</t>
+          <t xml:space="preserve">    L20.C17</t>
         </is>
       </c>
       <c r="B267" s="3" t="inlineStr">
         <is>
-          <t>La transparence et sa limite juridictionnelle</t>
+          <t>La sanctuarisation, et elle existe</t>
         </is>
       </c>
       <c r="C267" s="3" t="inlineStr">
@@ -24625,12 +24885,12 @@
     <row r="268">
       <c r="A268" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L20.C22</t>
+          <t xml:space="preserve">    L20.C18</t>
         </is>
       </c>
       <c r="B268" s="3" t="inlineStr">
         <is>
-          <t>Ce que le droit devrait devenir</t>
+          <t>L'amendement et la dérogation dans l'ordre commercial</t>
         </is>
       </c>
       <c r="C268" s="3" t="inlineStr">
@@ -24642,12 +24902,12 @@
     <row r="269">
       <c r="A269" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L20.C23</t>
+          <t xml:space="preserve">    L20.C19</t>
         </is>
       </c>
       <c r="B269" s="3" t="inlineStr">
         <is>
-          <t>La portée du livre</t>
+          <t>Le texte que la conformité invoque</t>
         </is>
       </c>
       <c r="C269" s="3" t="inlineStr">
@@ -24657,31 +24917,31 @@
       </c>
     </row>
     <row r="270">
-      <c r="A270" s="6" t="inlineStr">
-        <is>
-          <t>L21</t>
-        </is>
-      </c>
-      <c r="B270" s="6" t="inlineStr">
-        <is>
-          <t>La plomberie financière mondiale</t>
-        </is>
-      </c>
-      <c r="C270" s="6" t="inlineStr">
-        <is>
-          <t>en-cours — 7 chapitre(s)</t>
+      <c r="A270" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    L20.C20</t>
+        </is>
+      </c>
+      <c r="B270" s="3" t="inlineStr">
+        <is>
+          <t>L'ajustement aux frontières comme précédent</t>
+        </is>
+      </c>
+      <c r="C270" s="3" t="inlineStr">
+        <is>
+          <t>brouillon</t>
         </is>
       </c>
     </row>
     <row r="271">
       <c r="A271" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L21.C01</t>
+          <t xml:space="preserve">    L20.C21</t>
         </is>
       </c>
       <c r="B271" s="3" t="inlineStr">
         <is>
-          <t>Ce que ce livre doit établir, et le principe qui exige des fonds propres</t>
+          <t>La transparence et sa limite juridictionnelle</t>
         </is>
       </c>
       <c r="C271" s="3" t="inlineStr">
@@ -24693,12 +24953,12 @@
     <row r="272">
       <c r="A272" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L21.C02</t>
+          <t xml:space="preserve">    L20.C22</t>
         </is>
       </c>
       <c r="B272" s="3" t="inlineStr">
         <is>
-          <t>Comment l'unité circulerait vraiment, et ce que chaque étape exige</t>
+          <t>Ce que le droit devrait devenir</t>
         </is>
       </c>
       <c r="C272" s="3" t="inlineStr">
@@ -24710,12 +24970,12 @@
     <row r="273">
       <c r="A273" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L21.C03</t>
+          <t xml:space="preserve">    L20.C23</t>
         </is>
       </c>
       <c r="B273" s="3" t="inlineStr">
         <is>
-          <t>Une opération de bout en bout, bilan par bilan</t>
+          <t>La portée du livre</t>
         </is>
       </c>
       <c r="C273" s="3" t="inlineStr">
@@ -24725,31 +24985,31 @@
       </c>
     </row>
     <row r="274">
-      <c r="A274" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    L21.C04</t>
-        </is>
-      </c>
-      <c r="B274" s="3" t="inlineStr">
-        <is>
-          <t>Ce que l'émission coûte aux banques qui l'hébergent</t>
-        </is>
-      </c>
-      <c r="C274" s="3" t="inlineStr">
-        <is>
-          <t>brouillon</t>
+      <c r="A274" s="6" t="inlineStr">
+        <is>
+          <t>L21</t>
+        </is>
+      </c>
+      <c r="B274" s="6" t="inlineStr">
+        <is>
+          <t>La plomberie financière mondiale</t>
+        </is>
+      </c>
+      <c r="C274" s="6" t="inlineStr">
+        <is>
+          <t>en-cours — 7 chapitre(s)</t>
         </is>
       </c>
     </row>
     <row r="275">
       <c r="A275" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L21.C05</t>
+          <t xml:space="preserve">    L21.C01</t>
         </is>
       </c>
       <c r="B275" s="3" t="inlineStr">
         <is>
-          <t>La première infrastructure ouverte, et ce qu'elle renverse</t>
+          <t>Ce que ce livre doit établir, et le principe qui exige des fonds propres</t>
         </is>
       </c>
       <c r="C275" s="3" t="inlineStr">
@@ -24761,12 +25021,12 @@
     <row r="276">
       <c r="A276" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L21.C06</t>
+          <t xml:space="preserve">    L21.C02</t>
         </is>
       </c>
       <c r="B276" s="3" t="inlineStr">
         <is>
-          <t>La jambe qui reste, et ce qu'il faut pour la protéger</t>
+          <t>Comment l'unité circulerait vraiment, et ce que chaque étape exige</t>
         </is>
       </c>
       <c r="C276" s="3" t="inlineStr">
@@ -24778,12 +25038,12 @@
     <row r="277">
       <c r="A277" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L21.C07</t>
+          <t xml:space="preserve">    L21.C03</t>
         </is>
       </c>
       <c r="B277" s="3" t="inlineStr">
         <is>
-          <t>Portée de la tranche</t>
+          <t>Une opération de bout en bout, bilan par bilan</t>
         </is>
       </c>
       <c r="C277" s="3" t="inlineStr">
@@ -24793,31 +25053,31 @@
       </c>
     </row>
     <row r="278">
-      <c r="A278" s="6" t="inlineStr">
-        <is>
-          <t>L22</t>
-        </is>
-      </c>
-      <c r="B278" s="6" t="inlineStr">
-        <is>
-          <t>Le pouvoir de la finance non bancaire</t>
-        </is>
-      </c>
-      <c r="C278" s="6" t="inlineStr">
-        <is>
-          <t>en-cours — 7 chapitre(s)</t>
+      <c r="A278" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    L21.C04</t>
+        </is>
+      </c>
+      <c r="B278" s="3" t="inlineStr">
+        <is>
+          <t>Ce que l'émission coûte aux banques qui l'hébergent</t>
+        </is>
+      </c>
+      <c r="C278" s="3" t="inlineStr">
+        <is>
+          <t>brouillon</t>
         </is>
       </c>
     </row>
     <row r="279">
       <c r="A279" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L22.C01</t>
+          <t xml:space="preserve">    L21.C05</t>
         </is>
       </c>
       <c r="B279" s="3" t="inlineStr">
         <is>
-          <t>Ce que ce livre doit établir</t>
+          <t>La première infrastructure ouverte, et ce qu'elle renverse</t>
         </is>
       </c>
       <c r="C279" s="3" t="inlineStr">
@@ -24829,12 +25089,12 @@
     <row r="280">
       <c r="A280" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L22.C02</t>
+          <t xml:space="preserve">    L21.C06</t>
         </is>
       </c>
       <c r="B280" s="3" t="inlineStr">
         <is>
-          <t>Où va la monnaie émise, et pourquoi le reflux ne l'y suit pas</t>
+          <t>La jambe qui reste, et ce qu'il faut pour la protéger</t>
         </is>
       </c>
       <c r="C280" s="3" t="inlineStr">
@@ -24846,12 +25106,12 @@
     <row r="281">
       <c r="A281" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L22.C03</t>
+          <t xml:space="preserve">    L21.C07</t>
         </is>
       </c>
       <c r="B281" s="3" t="inlineStr">
         <is>
-          <t>Le barème existe déjà, et il a trois pièces que le corpus n'a pas</t>
+          <t>Portée de la tranche</t>
         </is>
       </c>
       <c r="C281" s="3" t="inlineStr">
@@ -24861,31 +25121,31 @@
       </c>
     </row>
     <row r="282">
-      <c r="A282" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    L22.C04</t>
-        </is>
-      </c>
-      <c r="B282" s="3" t="inlineStr">
-        <is>
-          <t>Les critères réels ne mesurent pas, ils certifient</t>
-        </is>
-      </c>
-      <c r="C282" s="3" t="inlineStr">
-        <is>
-          <t>brouillon</t>
+      <c r="A282" s="6" t="inlineStr">
+        <is>
+          <t>L22</t>
+        </is>
+      </c>
+      <c r="B282" s="6" t="inlineStr">
+        <is>
+          <t>Le pouvoir de la finance non bancaire</t>
+        </is>
+      </c>
+      <c r="C282" s="6" t="inlineStr">
+        <is>
+          <t>en-cours — 7 chapitre(s)</t>
         </is>
       </c>
     </row>
     <row r="283">
       <c r="A283" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L22.C05</t>
+          <t xml:space="preserve">    L22.C01</t>
         </is>
       </c>
       <c r="B283" s="3" t="inlineStr">
         <is>
-          <t>L'épargne retraite, et le dilemme du troisième instrument</t>
+          <t>Ce que ce livre doit établir</t>
         </is>
       </c>
       <c r="C283" s="3" t="inlineStr">
@@ -24897,12 +25157,12 @@
     <row r="284">
       <c r="A284" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L22.C06</t>
+          <t xml:space="preserve">    L22.C02</t>
         </is>
       </c>
       <c r="B284" s="3" t="inlineStr">
         <is>
-          <t>Qui décide, quand personne ne décide</t>
+          <t>Où va la monnaie émise, et pourquoi le reflux ne l'y suit pas</t>
         </is>
       </c>
       <c r="C284" s="3" t="inlineStr">
@@ -24914,12 +25174,12 @@
     <row r="285">
       <c r="A285" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L22.C07</t>
+          <t xml:space="preserve">    L22.C03</t>
         </is>
       </c>
       <c r="B285" s="3" t="inlineStr">
         <is>
-          <t>Portée de la tranche</t>
+          <t>Le barème existe déjà, et il a trois pièces que le corpus n'a pas</t>
         </is>
       </c>
       <c r="C285" s="3" t="inlineStr">
@@ -24929,31 +25189,31 @@
       </c>
     </row>
     <row r="286">
-      <c r="A286" s="6" t="inlineStr">
-        <is>
-          <t>L23</t>
-        </is>
-      </c>
-      <c r="B286" s="6" t="inlineStr">
-        <is>
-          <t>Fiscalité mondiale, finance offshore et opacité</t>
-        </is>
-      </c>
-      <c r="C286" s="6" t="inlineStr">
-        <is>
-          <t>en-cours — 7 chapitre(s)</t>
+      <c r="A286" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    L22.C04</t>
+        </is>
+      </c>
+      <c r="B286" s="3" t="inlineStr">
+        <is>
+          <t>Les critères réels ne mesurent pas, ils certifient</t>
+        </is>
+      </c>
+      <c r="C286" s="3" t="inlineStr">
+        <is>
+          <t>brouillon</t>
         </is>
       </c>
     </row>
     <row r="287">
       <c r="A287" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L23.C01</t>
+          <t xml:space="preserve">    L22.C05</t>
         </is>
       </c>
       <c r="B287" s="3" t="inlineStr">
         <is>
-          <t>Ce que ce livre doit établir</t>
+          <t>L'épargne retraite, et le dilemme du troisième instrument</t>
         </is>
       </c>
       <c r="C287" s="3" t="inlineStr">
@@ -24965,12 +25225,12 @@
     <row r="288">
       <c r="A288" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L23.C02</t>
+          <t xml:space="preserve">    L22.C06</t>
         </is>
       </c>
       <c r="B288" s="3" t="inlineStr">
         <is>
-          <t>La compétence que la convention ne crée pas, et le vote qu'elle a gagné</t>
+          <t>Qui décide, quand personne ne décide</t>
         </is>
       </c>
       <c r="C288" s="3" t="inlineStr">
@@ -24982,12 +25242,12 @@
     <row r="289">
       <c r="A289" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L23.C03</t>
+          <t xml:space="preserve">    L22.C07</t>
         </is>
       </c>
       <c r="B289" s="3" t="inlineStr">
         <is>
-          <t>F8 appliqué à une négociation en cours, et le résultat n'est pas le désarmement</t>
+          <t>Portée de la tranche</t>
         </is>
       </c>
       <c r="C289" s="3" t="inlineStr">
@@ -24997,31 +25257,31 @@
       </c>
     </row>
     <row r="290">
-      <c r="A290" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    L23.C04</t>
-        </is>
-      </c>
-      <c r="B290" s="3" t="inlineStr">
-        <is>
-          <t>La transparence que le corpus supposait a été invalidée</t>
-        </is>
-      </c>
-      <c r="C290" s="3" t="inlineStr">
-        <is>
-          <t>brouillon</t>
+      <c r="A290" s="6" t="inlineStr">
+        <is>
+          <t>L23</t>
+        </is>
+      </c>
+      <c r="B290" s="6" t="inlineStr">
+        <is>
+          <t>Fiscalité mondiale, finance offshore et opacité</t>
+        </is>
+      </c>
+      <c r="C290" s="6" t="inlineStr">
+        <is>
+          <t>en-cours — 7 chapitre(s)</t>
         </is>
       </c>
     </row>
     <row r="291">
       <c r="A291" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L23.C05</t>
+          <t xml:space="preserve">    L23.C01</t>
         </is>
       </c>
       <c r="B291" s="3" t="inlineStr">
         <is>
-          <t>Intéresser le percepteur, et ce que le taux révèle</t>
+          <t>Ce que ce livre doit établir</t>
         </is>
       </c>
       <c r="C291" s="3" t="inlineStr">
@@ -25033,12 +25293,12 @@
     <row r="292">
       <c r="A292" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L23.C06</t>
+          <t xml:space="preserve">    L23.C02</t>
         </is>
       </c>
       <c r="B292" s="3" t="inlineStr">
         <is>
-          <t>L'arbre appliqué à la fonte, et il ne reste que deux branches</t>
+          <t>La compétence que la convention ne crée pas, et le vote qu'elle a gagné</t>
         </is>
       </c>
       <c r="C292" s="3" t="inlineStr">
@@ -25050,12 +25310,12 @@
     <row r="293">
       <c r="A293" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L23.C07</t>
+          <t xml:space="preserve">    L23.C03</t>
         </is>
       </c>
       <c r="B293" s="3" t="inlineStr">
         <is>
-          <t>Portée de la tranche, et la moitié qui n'est pas commencée</t>
+          <t>F8 appliqué à une négociation en cours, et le résultat n'est pas le désarmement</t>
         </is>
       </c>
       <c r="C293" s="3" t="inlineStr">
@@ -25065,31 +25325,31 @@
       </c>
     </row>
     <row r="294">
-      <c r="A294" s="6" t="inlineStr">
-        <is>
-          <t>L24</t>
-        </is>
-      </c>
-      <c r="B294" s="6" t="inlineStr">
-        <is>
-          <t>Les conditions matérielles de la vie</t>
-        </is>
-      </c>
-      <c r="C294" s="6" t="inlineStr">
-        <is>
-          <t>en-cours — 5 chapitre(s)</t>
+      <c r="A294" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    L23.C04</t>
+        </is>
+      </c>
+      <c r="B294" s="3" t="inlineStr">
+        <is>
+          <t>La transparence que le corpus supposait a été invalidée</t>
+        </is>
+      </c>
+      <c r="C294" s="3" t="inlineStr">
+        <is>
+          <t>brouillon</t>
         </is>
       </c>
     </row>
     <row r="295">
       <c r="A295" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L24.C01</t>
+          <t xml:space="preserve">    L23.C05</t>
         </is>
       </c>
       <c r="B295" s="3" t="inlineStr">
         <is>
-          <t>Ce que ce livre doit établir</t>
+          <t>Intéresser le percepteur, et ce que le taux révèle</t>
         </is>
       </c>
       <c r="C295" s="3" t="inlineStr">
@@ -25101,12 +25361,12 @@
     <row r="296">
       <c r="A296" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L24.C02</t>
+          <t xml:space="preserve">    L23.C06</t>
         </is>
       </c>
       <c r="B296" s="3" t="inlineStr">
         <is>
-          <t>Le seuil juste est plus strict que le seuil sûr</t>
+          <t>L'arbre appliqué à la fonte, et il ne reste que deux branches</t>
         </is>
       </c>
       <c r="C296" s="3" t="inlineStr">
@@ -25118,12 +25378,12 @@
     <row r="297">
       <c r="A297" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L24.C03</t>
+          <t xml:space="preserve">    L23.C07</t>
         </is>
       </c>
       <c r="B297" s="3" t="inlineStr">
         <is>
-          <t>La matière, et le levier commun que les neuf dimensions n'avaient pas</t>
+          <t>Portée de la tranche, et la moitié qui n'est pas commencée</t>
         </is>
       </c>
       <c r="C297" s="3" t="inlineStr">
@@ -25133,31 +25393,31 @@
       </c>
     </row>
     <row r="298">
-      <c r="A298" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    L24.C04</t>
-        </is>
-      </c>
-      <c r="B298" s="3" t="inlineStr">
-        <is>
-          <t>Un budget mondial n'est pas partageable</t>
-        </is>
-      </c>
-      <c r="C298" s="3" t="inlineStr">
-        <is>
-          <t>brouillon</t>
+      <c r="A298" s="6" t="inlineStr">
+        <is>
+          <t>L24</t>
+        </is>
+      </c>
+      <c r="B298" s="6" t="inlineStr">
+        <is>
+          <t>Les conditions matérielles de la vie</t>
+        </is>
+      </c>
+      <c r="C298" s="6" t="inlineStr">
+        <is>
+          <t>en-cours — 5 chapitre(s)</t>
         </is>
       </c>
     </row>
     <row r="299">
       <c r="A299" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L24.C05</t>
+          <t xml:space="preserve">    L24.C01</t>
         </is>
       </c>
       <c r="B299" s="3" t="inlineStr">
         <is>
-          <t>Portée de la tranche</t>
+          <t>Ce que ce livre doit établir</t>
         </is>
       </c>
       <c r="C299" s="3" t="inlineStr">
@@ -25167,31 +25427,31 @@
       </c>
     </row>
     <row r="300">
-      <c r="A300" s="6" t="inlineStr">
-        <is>
-          <t>L25</t>
-        </is>
-      </c>
-      <c r="B300" s="6" t="inlineStr">
-        <is>
-          <t>Répartition, besoins essentiels et justice sociale</t>
-        </is>
-      </c>
-      <c r="C300" s="6" t="inlineStr">
-        <is>
-          <t>en-cours — 6 chapitre(s)</t>
+      <c r="A300" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    L24.C02</t>
+        </is>
+      </c>
+      <c r="B300" s="3" t="inlineStr">
+        <is>
+          <t>Le seuil juste est plus strict que le seuil sûr</t>
+        </is>
+      </c>
+      <c r="C300" s="3" t="inlineStr">
+        <is>
+          <t>brouillon</t>
         </is>
       </c>
     </row>
     <row r="301">
       <c r="A301" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L25.C01</t>
+          <t xml:space="preserve">    L24.C03</t>
         </is>
       </c>
       <c r="B301" s="3" t="inlineStr">
         <is>
-          <t>Ce que ce livre doit établir</t>
+          <t>La matière, et le levier commun que les neuf dimensions n'avaient pas</t>
         </is>
       </c>
       <c r="C301" s="3" t="inlineStr">
@@ -25203,12 +25463,12 @@
     <row r="302">
       <c r="A302" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L25.C02</t>
+          <t xml:space="preserve">    L24.C04</t>
         </is>
       </c>
       <c r="B302" s="3" t="inlineStr">
         <is>
-          <t>Le noyau dur, et la charge de la preuve renversée</t>
+          <t>Un budget mondial n'est pas partageable</t>
         </is>
       </c>
       <c r="C302" s="3" t="inlineStr">
@@ -25220,12 +25480,12 @@
     <row r="303">
       <c r="A303" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L25.C03</t>
+          <t xml:space="preserve">    L24.C05</t>
         </is>
       </c>
       <c r="B303" s="3" t="inlineStr">
         <is>
-          <t>Ce que le droit oblige à donner, et ce qu'il refuse de réparer</t>
+          <t>Portée de la tranche</t>
         </is>
       </c>
       <c r="C303" s="3" t="inlineStr">
@@ -25235,31 +25495,31 @@
       </c>
     </row>
     <row r="304">
-      <c r="A304" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    L25.C04</t>
-        </is>
-      </c>
-      <c r="B304" s="3" t="inlineStr">
-        <is>
-          <t>A34 en droit positif, et le critère que le corpus n'avait pas</t>
-        </is>
-      </c>
-      <c r="C304" s="3" t="inlineStr">
-        <is>
-          <t>brouillon</t>
+      <c r="A304" s="6" t="inlineStr">
+        <is>
+          <t>L25</t>
+        </is>
+      </c>
+      <c r="B304" s="6" t="inlineStr">
+        <is>
+          <t>Répartition, besoins essentiels et justice sociale</t>
+        </is>
+      </c>
+      <c r="C304" s="6" t="inlineStr">
+        <is>
+          <t>en-cours — 6 chapitre(s)</t>
         </is>
       </c>
     </row>
     <row r="305">
       <c r="A305" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L25.C05</t>
+          <t xml:space="preserve">    L25.C01</t>
         </is>
       </c>
       <c r="B305" s="3" t="inlineStr">
         <is>
-          <t>Le droit différencie sans calculer</t>
+          <t>Ce que ce livre doit établir</t>
         </is>
       </c>
       <c r="C305" s="3" t="inlineStr">
@@ -25271,12 +25531,12 @@
     <row r="306">
       <c r="A306" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L25.C06</t>
+          <t xml:space="preserve">    L25.C02</t>
         </is>
       </c>
       <c r="B306" s="3" t="inlineStr">
         <is>
-          <t>Portée de la tranche</t>
+          <t>Le noyau dur, et la charge de la preuve renversée</t>
         </is>
       </c>
       <c r="C306" s="3" t="inlineStr">
@@ -25286,31 +25546,31 @@
       </c>
     </row>
     <row r="307">
-      <c r="A307" s="6" t="inlineStr">
-        <is>
-          <t>L26</t>
-        </is>
-      </c>
-      <c r="B307" s="6" t="inlineStr">
-        <is>
-          <t>Thermodynamique, énergie et processus économique</t>
-        </is>
-      </c>
-      <c r="C307" s="6" t="inlineStr">
-        <is>
-          <t>en-cours — 6 chapitre(s)</t>
+      <c r="A307" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    L25.C03</t>
+        </is>
+      </c>
+      <c r="B307" s="3" t="inlineStr">
+        <is>
+          <t>Ce que le droit oblige à donner, et ce qu'il refuse de réparer</t>
+        </is>
+      </c>
+      <c r="C307" s="3" t="inlineStr">
+        <is>
+          <t>brouillon</t>
         </is>
       </c>
     </row>
     <row r="308">
       <c r="A308" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L26.C01</t>
+          <t xml:space="preserve">    L25.C04</t>
         </is>
       </c>
       <c r="B308" s="3" t="inlineStr">
         <is>
-          <t>Ce que ce livre doit établir</t>
+          <t>A34 en droit positif, et le critère que le corpus n'avait pas</t>
         </is>
       </c>
       <c r="C308" s="3" t="inlineStr">
@@ -25322,12 +25582,12 @@
     <row r="309">
       <c r="A309" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L26.C02</t>
+          <t xml:space="preserve">    L25.C05</t>
         </is>
       </c>
       <c r="B309" s="3" t="inlineStr">
         <is>
-          <t>Le stock n'existe pas sous la forme demandée</t>
+          <t>Le droit différencie sans calculer</t>
         </is>
       </c>
       <c r="C309" s="3" t="inlineStr">
@@ -25339,12 +25599,12 @@
     <row r="310">
       <c r="A310" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L26.C03</t>
+          <t xml:space="preserve">    L25.C06</t>
         </is>
       </c>
       <c r="B310" s="3" t="inlineStr">
         <is>
-          <t>La frontière décide du chiffre</t>
+          <t>Portée de la tranche</t>
         </is>
       </c>
       <c r="C310" s="3" t="inlineStr">
@@ -25354,31 +25614,31 @@
       </c>
     </row>
     <row r="311">
-      <c r="A311" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    L26.C04</t>
-        </is>
-      </c>
-      <c r="B311" s="3" t="inlineStr">
-        <is>
-          <t>L'effet rebond, et ce que le dispositif en hérite sans être une politique d'efficacité</t>
-        </is>
-      </c>
-      <c r="C311" s="3" t="inlineStr">
-        <is>
-          <t>brouillon</t>
+      <c r="A311" s="6" t="inlineStr">
+        <is>
+          <t>L26</t>
+        </is>
+      </c>
+      <c r="B311" s="6" t="inlineStr">
+        <is>
+          <t>Thermodynamique, énergie et processus économique</t>
+        </is>
+      </c>
+      <c r="C311" s="6" t="inlineStr">
+        <is>
+          <t>en-cours — 6 chapitre(s)</t>
         </is>
       </c>
     </row>
     <row r="312">
       <c r="A312" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L26.C05</t>
+          <t xml:space="preserve">    L26.C01</t>
         </is>
       </c>
       <c r="B312" s="3" t="inlineStr">
         <is>
-          <t>L'addition n'est pas la substitution</t>
+          <t>Ce que ce livre doit établir</t>
         </is>
       </c>
       <c r="C312" s="3" t="inlineStr">
@@ -25390,15 +25650,83 @@
     <row r="313">
       <c r="A313" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">    L26.C02</t>
+        </is>
+      </c>
+      <c r="B313" s="3" t="inlineStr">
+        <is>
+          <t>Le stock n'existe pas sous la forme demandée</t>
+        </is>
+      </c>
+      <c r="C313" s="3" t="inlineStr">
+        <is>
+          <t>brouillon</t>
+        </is>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    L26.C03</t>
+        </is>
+      </c>
+      <c r="B314" s="3" t="inlineStr">
+        <is>
+          <t>La frontière décide du chiffre</t>
+        </is>
+      </c>
+      <c r="C314" s="3" t="inlineStr">
+        <is>
+          <t>brouillon</t>
+        </is>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    L26.C04</t>
+        </is>
+      </c>
+      <c r="B315" s="3" t="inlineStr">
+        <is>
+          <t>L'effet rebond, et ce que le dispositif en hérite sans être une politique d'efficacité</t>
+        </is>
+      </c>
+      <c r="C315" s="3" t="inlineStr">
+        <is>
+          <t>brouillon</t>
+        </is>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    L26.C05</t>
+        </is>
+      </c>
+      <c r="B316" s="3" t="inlineStr">
+        <is>
+          <t>L'addition n'est pas la substitution</t>
+        </is>
+      </c>
+      <c r="C316" s="3" t="inlineStr">
+        <is>
+          <t>brouillon</t>
+        </is>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">    L26.C06</t>
         </is>
       </c>
-      <c r="B313" s="3" t="inlineStr">
+      <c r="B317" s="3" t="inlineStr">
         <is>
           <t>Portée de la tranche</t>
         </is>
       </c>
-      <c r="C313" s="3" t="inlineStr">
+      <c r="C317" s="3" t="inlineStr">
         <is>
           <t>brouillon</t>
         </is>

--- a/plan-des-livres.xlsx
+++ b/plan-des-livres.xlsx
@@ -13,7 +13,7 @@
     <sheet name="Plan par livre" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Chapitres'!$A$1:$N$290</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Chapitres'!$A$1:$N$294</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -1613,7 +1613,7 @@
         </is>
       </c>
       <c r="F28" s="5" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="G28" s="5" t="inlineStr"/>
       <c r="H28" s="5" t="inlineStr">
@@ -1638,7 +1638,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N290"/>
+  <dimension ref="A1:N294"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -2843,7 +2843,7 @@
         <v>14</v>
       </c>
       <c r="K19" s="3" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="L19" s="3" t="inlineStr">
         <is>
@@ -2852,7 +2852,7 @@
       </c>
       <c r="M19" s="3" t="inlineStr">
         <is>
-          <t>L1.C03, L1.C04, L1.C07, L1.C08, L1.C10, L1.C15, L1.C16, L26.C01, L26.C04</t>
+          <t>L1.C03, L1.C04, L1.C07, L1.C08, L1.C10, L1.C15, L1.C16, L26.C01, L26.C04, L26.C07</t>
         </is>
       </c>
       <c r="N19" s="3" t="inlineStr">
@@ -11387,7 +11387,7 @@
       </c>
       <c r="H154" s="3" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="I154" s="3" t="inlineStr"/>
@@ -11395,7 +11395,7 @@
         <v>1</v>
       </c>
       <c r="K154" s="3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L154" s="3" t="inlineStr">
         <is>
@@ -11404,7 +11404,7 @@
       </c>
       <c r="M154" s="3" t="inlineStr">
         <is>
-          <t>L1.C01, L1.C15, L8.C01, L8.C08, L8.C13, L8.C15, L8.C39, L11.C13</t>
+          <t>L1.C01, L1.C15, L8.C01, L8.C08, L8.C13, L8.C15, L8.C39, L11.C13, L26.C07</t>
         </is>
       </c>
       <c r="N154" s="3" t="inlineStr">
@@ -11579,7 +11579,7 @@
       </c>
       <c r="H157" s="3" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="I157" s="3" t="inlineStr"/>
@@ -11587,7 +11587,7 @@
         <v>1</v>
       </c>
       <c r="K157" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L157" s="3" t="inlineStr">
         <is>
@@ -11596,7 +11596,7 @@
       </c>
       <c r="M157" s="3" t="inlineStr">
         <is>
-          <t>L8.C01, L8.C22, L8.C26, L8.C32, L8.C36, L8.C38, L11.C02, L11.C03, L11.C17</t>
+          <t>L8.C01, L8.C22, L8.C26, L8.C32, L8.C36, L8.C38, L11.C02, L11.C03, L11.C17, L26.C08</t>
         </is>
       </c>
       <c r="N157" s="3" t="inlineStr">
@@ -13183,7 +13183,7 @@
         <v>6</v>
       </c>
       <c r="K182" s="3" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="L182" s="3" t="inlineStr">
         <is>
@@ -13192,7 +13192,7 @@
       </c>
       <c r="M182" s="3" t="inlineStr">
         <is>
-          <t>L1.C18, L1.C20, L1.C22, L1.C27, L11.C03, L11.C05, L11.C06, L11.C08, L11.C09, L11.C10, L11.C11, L11.C12, L26.C05</t>
+          <t>L1.C18, L1.C20, L1.C22, L1.C27, L11.C03, L11.C05, L11.C06, L11.C08, L11.C09, L11.C10, L11.C11, L11.C12, L26.C05, L26.C07, L26.C08, L26.C09, L26.C10</t>
         </is>
       </c>
       <c r="N182" s="3" t="inlineStr">
@@ -14771,7 +14771,7 @@
         <v>1</v>
       </c>
       <c r="K207" s="3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L207" s="3" t="inlineStr">
         <is>
@@ -14780,7 +14780,7 @@
       </c>
       <c r="M207" s="3" t="inlineStr">
         <is>
-          <t>L1.C08, L1.C10, L11.C01, L11.C07, L11.C24, L16.C01, L16.C02, L16.C03, L16.C04, L19.C01, L19.C03, L21.C03</t>
+          <t>L1.C08, L1.C10, L11.C01, L11.C07, L11.C24, L16.C01, L16.C02, L16.C03, L16.C04, L19.C01, L19.C03, L21.C03, L26.C07</t>
         </is>
       </c>
       <c r="N207" s="3" t="inlineStr">
@@ -14835,7 +14835,7 @@
         <v>2</v>
       </c>
       <c r="K208" s="3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L208" s="3" t="inlineStr">
         <is>
@@ -14844,7 +14844,7 @@
       </c>
       <c r="M208" s="3" t="inlineStr">
         <is>
-          <t>L1.C08, L1.C12, L11.C24, L18.C04, L24.C03, L26.C03, L26.C04, L26.C05, L26.C06, L17.C03</t>
+          <t>L1.C08, L1.C12, L11.C24, L18.C04, L24.C03, L26.C03, L26.C04, L26.C05, L26.C06, L17.C03, L26.C10</t>
         </is>
       </c>
       <c r="N208" s="3" t="inlineStr">
@@ -14899,7 +14899,7 @@
         <v>1</v>
       </c>
       <c r="K209" s="3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L209" s="3" t="inlineStr">
         <is>
@@ -14908,7 +14908,7 @@
       </c>
       <c r="M209" s="3" t="inlineStr">
         <is>
-          <t>L11.C13, L11.C24, L17.C01, L18.C04, L24.C01, L24.C04, L26.C01, L26.C02, L26.C04, L26.C05</t>
+          <t>L11.C13, L11.C24, L17.C01, L18.C04, L24.C01, L24.C04, L26.C01, L26.C02, L26.C04, L26.C05, L26.C07</t>
         </is>
       </c>
       <c r="N209" s="3" t="inlineStr">
@@ -19763,7 +19763,7 @@
         <v>2</v>
       </c>
       <c r="K285" s="3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L285" s="3" t="inlineStr">
         <is>
@@ -19772,7 +19772,7 @@
       </c>
       <c r="M285" s="3" t="inlineStr">
         <is>
-          <t>L1.C03, L1.C15, L1.C17, L8.C13, L8.C34, L11.C13, L18.C04, L24.C03, L24.C05, L17.C02</t>
+          <t>L1.C03, L1.C15, L1.C17, L8.C13, L8.C34, L11.C13, L18.C04, L24.C03, L24.C05, L17.C02, L26.C10</t>
         </is>
       </c>
       <c r="N285" s="3" t="inlineStr">
@@ -19891,7 +19891,7 @@
         <v>2</v>
       </c>
       <c r="K287" s="3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L287" s="3" t="inlineStr">
         <is>
@@ -19900,7 +19900,7 @@
       </c>
       <c r="M287" s="3" t="inlineStr">
         <is>
-          <t>L11.C10, L11.C13, L11.C24, L18.C04, L18.C09, L24.C03, L24.C04, L26.C01, L26.C02</t>
+          <t>L11.C10, L11.C13, L11.C24, L18.C04, L18.C09, L24.C03, L24.C04, L26.C01, L26.C02, L26.C08</t>
         </is>
       </c>
       <c r="N287" s="3" t="inlineStr">
@@ -19955,7 +19955,7 @@
         <v>1</v>
       </c>
       <c r="K288" s="3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L288" s="3" t="inlineStr">
         <is>
@@ -19964,7 +19964,7 @@
       </c>
       <c r="M288" s="3" t="inlineStr">
         <is>
-          <t>L1.C03, L1.C12, L1.C17, L11.C10, L13.C01, L18.C04, L22.C02, L24.C03, L26.C01, L26.C03</t>
+          <t>L1.C03, L1.C12, L1.C17, L11.C10, L13.C01, L18.C04, L22.C02, L24.C03, L26.C01, L26.C03, L26.C09</t>
         </is>
       </c>
       <c r="N288" s="3" t="inlineStr">
@@ -20083,26 +20083,282 @@
         <v>1</v>
       </c>
       <c r="K290" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="L290" s="3" t="inlineStr">
+        <is>
+          <t>entropie, decouplage, effet_rebond, limites_planetaires, sobriete, affectation_des_instruments</t>
+        </is>
+      </c>
+      <c r="M290" s="3" t="inlineStr">
+        <is>
+          <t>L1.C03, L1.C17, L8.C34, L11.C10, L11.C13, L11.C24, L18.C04, L18.C09, L22.C02, L24.C05, L26.C01, L26.C02, L26.C03, L26.C04, L26.C05, L26.C07</t>
+        </is>
+      </c>
+      <c r="N290" s="3" t="inlineStr">
+        <is>
+          <t>corpus/livre-26-thermodynamique-et-processus-economique/c06-portee-de-la-tranche.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" s="2" t="inlineStr">
+        <is>
+          <t>L26.C07</t>
+        </is>
+      </c>
+      <c r="B291" s="3" t="inlineStr">
+        <is>
+          <t>L26</t>
+        </is>
+      </c>
+      <c r="C291" s="3" t="inlineStr">
+        <is>
+          <t>Le fondateur ne propose aucun instrument monétaire</t>
+        </is>
+      </c>
+      <c r="D291" s="3" t="inlineStr">
+        <is>
+          <t>brouillon</t>
+        </is>
+      </c>
+      <c r="E291" s="3" t="inlineStr">
+        <is>
+          <t>preparatoire</t>
+        </is>
+      </c>
+      <c r="F291" s="3" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="G291" s="3" t="inlineStr">
+        <is>
+          <t>hybride</t>
+        </is>
+      </c>
+      <c r="H291" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="I291" s="3" t="inlineStr"/>
+      <c r="J291" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="K291" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="L291" s="3" t="inlineStr">
+        <is>
+          <t>entropie, sobriete, affectation_des_instruments, qualification_regenerative</t>
+        </is>
+      </c>
+      <c r="M291" s="3" t="inlineStr">
+        <is>
+          <t>L1.C03, L1.C17, L8.C34, L11.C13, L16.C01, L16.C05, L17.C02, L17.C03, L26.C01, L26.C03, L26.C06</t>
+        </is>
+      </c>
+      <c r="N291" s="3" t="inlineStr">
+        <is>
+          <t>corpus/livre-26-thermodynamique-et-processus-economique/c07-le-fondateur-ne-propose-aucun-instrument-monetaire.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" s="2" t="inlineStr">
+        <is>
+          <t>L26.C08</t>
+        </is>
+      </c>
+      <c r="B292" s="3" t="inlineStr">
+        <is>
+          <t>L26</t>
+        </is>
+      </c>
+      <c r="C292" s="3" t="inlineStr">
+        <is>
+          <t>Même un puits gratuit ne donne pas dix</t>
+        </is>
+      </c>
+      <c r="D292" s="3" t="inlineStr">
+        <is>
+          <t>brouillon</t>
+        </is>
+      </c>
+      <c r="E292" s="3" t="inlineStr">
+        <is>
+          <t>preparatoire</t>
+        </is>
+      </c>
+      <c r="F292" s="3" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="G292" s="3" t="inlineStr">
+        <is>
+          <t>hybride</t>
+        </is>
+      </c>
+      <c r="H292" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="I292" s="3" t="inlineStr"/>
+      <c r="J292" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="K292" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="L292" s="3" t="inlineStr">
+        <is>
+          <t>bareme, qualification_regenerative, decouplage</t>
+        </is>
+      </c>
+      <c r="M292" s="3" t="inlineStr">
+        <is>
+          <t>L1.C17, L8.C37, L11.C13, L17.C01, L24.C05, L26.C01, L26.C03, L26.C06, L26.C07</t>
+        </is>
+      </c>
+      <c r="N292" s="3" t="inlineStr">
+        <is>
+          <t>corpus/livre-26-thermodynamique-et-processus-economique/c08-meme-un-puits-gratuit-ne-donne-pas-dix.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" s="2" t="inlineStr">
+        <is>
+          <t>L26.C09</t>
+        </is>
+      </c>
+      <c r="B293" s="3" t="inlineStr">
+        <is>
+          <t>L26</t>
+        </is>
+      </c>
+      <c r="C293" s="3" t="inlineStr">
+        <is>
+          <t>La méthode décide du chiffre</t>
+        </is>
+      </c>
+      <c r="D293" s="3" t="inlineStr">
+        <is>
+          <t>brouillon</t>
+        </is>
+      </c>
+      <c r="E293" s="3" t="inlineStr">
+        <is>
+          <t>preparatoire</t>
+        </is>
+      </c>
+      <c r="F293" s="3" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="G293" s="3" t="inlineStr">
+        <is>
+          <t>hybride</t>
+        </is>
+      </c>
+      <c r="H293" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="I293" s="3" t="inlineStr"/>
+      <c r="J293" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="K293" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="L293" s="3" t="inlineStr">
+        <is>
+          <t>effet_rebond, jevons_monetaire, decouplage, bareme</t>
+        </is>
+      </c>
+      <c r="M293" s="3" t="inlineStr">
+        <is>
+          <t>L1.C03, L11.C13, L17.C02, L24.C03, L26.C03, L26.C04, L26.C06, L26.C08</t>
+        </is>
+      </c>
+      <c r="N293" s="3" t="inlineStr">
+        <is>
+          <t>corpus/livre-26-thermodynamique-et-processus-economique/c09-la-methode-decide-du-chiffre.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" s="2" t="inlineStr">
+        <is>
+          <t>L26.C10</t>
+        </is>
+      </c>
+      <c r="B294" s="3" t="inlineStr">
+        <is>
+          <t>L26</t>
+        </is>
+      </c>
+      <c r="C294" s="3" t="inlineStr">
+        <is>
+          <t>La financiarisation produit un découplage apparent</t>
+        </is>
+      </c>
+      <c r="D294" s="3" t="inlineStr">
+        <is>
+          <t>brouillon</t>
+        </is>
+      </c>
+      <c r="E294" s="3" t="inlineStr">
+        <is>
+          <t>preparatoire</t>
+        </is>
+      </c>
+      <c r="F294" s="3" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="G294" s="3" t="inlineStr">
+        <is>
+          <t>hybride</t>
+        </is>
+      </c>
+      <c r="H294" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="I294" s="3" t="inlineStr"/>
+      <c r="J294" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="K294" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="L290" s="3" t="inlineStr">
-        <is>
-          <t>entropie, decouplage, effet_rebond, limites_planetaires, sobriete, affectation_des_instruments</t>
-        </is>
-      </c>
-      <c r="M290" s="3" t="inlineStr">
-        <is>
-          <t>L1.C03, L1.C17, L8.C34, L11.C10, L11.C13, L11.C24, L18.C04, L18.C09, L22.C02, L24.C05, L26.C01, L26.C02, L26.C03, L26.C04, L26.C05</t>
-        </is>
-      </c>
-      <c r="N290" s="3" t="inlineStr">
-        <is>
-          <t>corpus/livre-26-thermodynamique-et-processus-economique/c06-portee-de-la-tranche.md</t>
+      <c r="L294" s="3" t="inlineStr">
+        <is>
+          <t>decouplage, fausse_richesse, jevons_monetaire, indicateur_de_progres</t>
+        </is>
+      </c>
+      <c r="M294" s="3" t="inlineStr">
+        <is>
+          <t>L1.C03, L11.C13, L17.C01, L17.C05, L24.C03, L26.C01, L26.C03, L26.C06, L26.C08, L26.C09</t>
+        </is>
+      </c>
+      <c r="N294" s="3" t="inlineStr">
+        <is>
+          <t>corpus/livre-26-thermodynamique-et-processus-economique/c10-la-financiarisation-produit-un-decouplage-apparent.md</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:N290"/>
+  <autoFilter ref="A1:N294"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -20181,7 +20437,7 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>289</v>
+        <v>293</v>
       </c>
     </row>
     <row r="7">
@@ -20201,7 +20457,7 @@
         </is>
       </c>
       <c r="B8" s="3" t="n">
-        <v>283</v>
+        <v>287</v>
       </c>
     </row>
     <row r="9">
@@ -20211,7 +20467,7 @@
         </is>
       </c>
       <c r="B9" s="3" t="n">
-        <v>280</v>
+        <v>284</v>
       </c>
     </row>
     <row r="10">
@@ -20231,7 +20487,7 @@
         </is>
       </c>
       <c r="B11" s="3" t="n">
-        <v>1404</v>
+        <v>1431</v>
       </c>
     </row>
     <row r="12">
@@ -20241,7 +20497,7 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>1094</v>
+        <v>1102</v>
       </c>
     </row>
     <row r="13">
@@ -20335,7 +20591,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C317"/>
+  <dimension ref="A1:C321"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -25626,7 +25882,7 @@
       </c>
       <c r="C311" s="6" t="inlineStr">
         <is>
-          <t>en-cours — 6 chapitre(s)</t>
+          <t>en-cours — 10 chapitre(s)</t>
         </is>
       </c>
     </row>
@@ -25727,6 +25983,74 @@
         </is>
       </c>
       <c r="C317" s="3" t="inlineStr">
+        <is>
+          <t>brouillon</t>
+        </is>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    L26.C07</t>
+        </is>
+      </c>
+      <c r="B318" s="3" t="inlineStr">
+        <is>
+          <t>Le fondateur ne propose aucun instrument monétaire</t>
+        </is>
+      </c>
+      <c r="C318" s="3" t="inlineStr">
+        <is>
+          <t>brouillon</t>
+        </is>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    L26.C08</t>
+        </is>
+      </c>
+      <c r="B319" s="3" t="inlineStr">
+        <is>
+          <t>Même un puits gratuit ne donne pas dix</t>
+        </is>
+      </c>
+      <c r="C319" s="3" t="inlineStr">
+        <is>
+          <t>brouillon</t>
+        </is>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    L26.C09</t>
+        </is>
+      </c>
+      <c r="B320" s="3" t="inlineStr">
+        <is>
+          <t>La méthode décide du chiffre</t>
+        </is>
+      </c>
+      <c r="C320" s="3" t="inlineStr">
+        <is>
+          <t>brouillon</t>
+        </is>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    L26.C10</t>
+        </is>
+      </c>
+      <c r="B321" s="3" t="inlineStr">
+        <is>
+          <t>La financiarisation produit un découplage apparent</t>
+        </is>
+      </c>
+      <c r="C321" s="3" t="inlineStr">
         <is>
           <t>brouillon</t>
         </is>

--- a/plan-des-livres.xlsx
+++ b/plan-des-livres.xlsx
@@ -1054,41 +1054,41 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="2" t="inlineStr">
+      <c r="A15" s="4" t="inlineStr">
         <is>
           <t>L13</t>
         </is>
       </c>
-      <c r="B15" s="3" t="inlineStr">
+      <c r="B15" s="5" t="inlineStr">
         <is>
           <t>Méthodes, données, scénarios et simulateur NEMO IMS</t>
         </is>
       </c>
-      <c r="C15" s="3" t="inlineStr">
+      <c r="C15" s="5" t="inlineStr">
         <is>
           <t>cahier-technique</t>
         </is>
       </c>
-      <c r="D15" s="3" t="inlineStr">
-        <is>
-          <t>candidat</t>
-        </is>
-      </c>
-      <c r="E15" s="3" t="inlineStr">
+      <c r="D15" s="5" t="inlineStr">
+        <is>
+          <t>en-cours</t>
+        </is>
+      </c>
+      <c r="E15" s="5" t="inlineStr">
         <is>
           <t>non contraignant</t>
         </is>
       </c>
-      <c r="F15" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G15" s="3" t="inlineStr"/>
-      <c r="H15" s="3" t="inlineStr">
+      <c r="F15" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G15" s="5" t="inlineStr"/>
+      <c r="H15" s="5" t="inlineStr">
         <is>
           <t>Documenter les hypothèses, données, modèles, scénarios, tests de sensibilité et limites du simulateur</t>
         </is>
       </c>
-      <c r="I15" s="3" t="inlineStr">
+      <c r="I15" s="5" t="inlineStr">
         <is>
           <t>rouage — quantification et test du dispositif | objection — P4, P18 : un simulateur est ce qui permettrait d'éprouver la calibration</t>
         </is>
@@ -11587,7 +11587,7 @@
         <v>1</v>
       </c>
       <c r="K157" s="3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L157" s="3" t="inlineStr">
         <is>
@@ -11596,7 +11596,7 @@
       </c>
       <c r="M157" s="3" t="inlineStr">
         <is>
-          <t>L8.C01, L8.C22, L8.C26, L8.C32, L8.C36, L8.C38, L11.C02, L11.C03, L11.C17, L26.C08</t>
+          <t>L8.C01, L8.C22, L8.C26, L8.C32, L8.C36, L8.C38, L11.C02, L11.C03, L11.C17, L26.C08, L13.C01</t>
         </is>
       </c>
       <c r="N157" s="3" t="inlineStr">
@@ -14318,27 +14318,31 @@
       </c>
       <c r="G200" s="3" t="inlineStr">
         <is>
-          <t>descriptif</t>
+          <t>hybride</t>
         </is>
       </c>
       <c r="H200" s="3" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="I200" s="3" t="inlineStr">
-        <is>
-          <t>oui</t>
-        </is>
-      </c>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="I200" s="3" t="inlineStr"/>
       <c r="J200" s="3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K200" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="L200" s="3" t="inlineStr"/>
-      <c r="M200" s="3" t="inlineStr"/>
+        <v>4</v>
+      </c>
+      <c r="L200" s="3" t="inlineStr">
+        <is>
+          <t>creation_monetaire, bareme, additionnalite, effet_rebond</t>
+        </is>
+      </c>
+      <c r="M200" s="3" t="inlineStr">
+        <is>
+          <t>L1.C21, L8.C34, L8.C37, L8.C40, L11.C13, L17.C03, L19.C05, L22.C04, L26.C04, L26.C07, L26.C08, L26.C09, L26.C10</t>
+        </is>
+      </c>
       <c r="N200" s="3" t="inlineStr">
         <is>
           <t>corpus/livre-13-methodes-donnees-scenarios-et-simulateur/c01-ce-que-ce-livre-doit-etablir.md</t>
@@ -16051,7 +16055,7 @@
         <v>2</v>
       </c>
       <c r="K227" s="3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L227" s="3" t="inlineStr">
         <is>
@@ -16060,7 +16064,7 @@
       </c>
       <c r="M227" s="3" t="inlineStr">
         <is>
-          <t>L10.C06, L11.C05, L11.C07, L11.C09, L19.C01, L19.C02, L19.C03, L21.C01, L25.C05</t>
+          <t>L10.C06, L11.C05, L11.C07, L11.C09, L19.C01, L19.C02, L19.C03, L21.C01, L25.C05, L13.C01</t>
         </is>
       </c>
       <c r="N227" s="3" t="inlineStr">
@@ -18347,7 +18351,7 @@
       </c>
       <c r="H263" s="3" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="I263" s="3" t="inlineStr"/>
@@ -18355,7 +18359,7 @@
         <v>4</v>
       </c>
       <c r="K263" s="3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L263" s="3" t="inlineStr">
         <is>
@@ -19955,7 +19959,7 @@
         <v>1</v>
       </c>
       <c r="K288" s="3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L288" s="3" t="inlineStr">
         <is>
@@ -20417,7 +20421,7 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="5">
@@ -20427,7 +20431,7 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6">
@@ -20447,7 +20451,7 @@
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="8">
@@ -20457,7 +20461,7 @@
         </is>
       </c>
       <c r="B8" s="3" t="n">
-        <v>287</v>
+        <v>288</v>
       </c>
     </row>
     <row r="9">
@@ -20487,7 +20491,7 @@
         </is>
       </c>
       <c r="B11" s="3" t="n">
-        <v>1431</v>
+        <v>1437</v>
       </c>
     </row>
     <row r="12">
@@ -20497,7 +20501,7 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>1102</v>
+        <v>1104</v>
       </c>
     </row>
     <row r="13">
@@ -20512,7 +20516,7 @@
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>L0, L9, L12, L13, L14, L15</t>
+          <t>L0, L9, L12, L14, L15</t>
         </is>
       </c>
     </row>
@@ -24216,7 +24220,7 @@
       </c>
       <c r="C213" s="6" t="inlineStr">
         <is>
-          <t>candidat — AMORCE SEULE</t>
+          <t>en-cours — 1 chapitre(s)</t>
         </is>
       </c>
     </row>
@@ -24228,7 +24232,7 @@
       </c>
       <c r="B214" s="3" t="inlineStr">
         <is>
-          <t>[AMORCE] Ce que ce livre doit établir</t>
+          <t>Ce que ce livre doit établir</t>
         </is>
       </c>
       <c r="C214" s="3" t="inlineStr">

--- a/plan-des-livres.xlsx
+++ b/plan-des-livres.xlsx
@@ -13,7 +13,7 @@
     <sheet name="Plan par livre" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Chapitres'!$A$1:$N$294</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Chapitres'!$A$1:$N$295</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -1013,41 +1013,41 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="2" t="inlineStr">
+      <c r="A14" s="4" t="inlineStr">
         <is>
           <t>L12</t>
         </is>
       </c>
-      <c r="B14" s="3" t="inlineStr">
+      <c r="B14" s="5" t="inlineStr">
         <is>
           <t>Comment réaliser les ODD avec NEMO IMS ?</t>
         </is>
       </c>
-      <c r="C14" s="3" t="inlineStr">
+      <c r="C14" s="5" t="inlineStr">
         <is>
           <t>cahier-comparatif</t>
         </is>
       </c>
-      <c r="D14" s="3" t="inlineStr">
-        <is>
-          <t>candidat</t>
-        </is>
-      </c>
-      <c r="E14" s="3" t="inlineStr">
+      <c r="D14" s="5" t="inlineStr">
+        <is>
+          <t>en-cours</t>
+        </is>
+      </c>
+      <c r="E14" s="5" t="inlineStr">
         <is>
           <t>non contraignant</t>
         </is>
       </c>
-      <c r="F14" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G14" s="3" t="inlineStr"/>
-      <c r="H14" s="3" t="inlineStr">
+      <c r="F14" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G14" s="5" t="inlineStr"/>
+      <c r="H14" s="5" t="inlineStr">
         <is>
           <t>Évaluer ce que NEMO IMS peut faciliter pour chaque objectif de développement durable, ses limites et les politiques complémentaires nécessaires</t>
         </is>
       </c>
-      <c r="I14" s="3" t="inlineStr">
+      <c r="I14" s="5" t="inlineStr">
         <is>
           <t>discipline — politiques de développement</t>
         </is>
@@ -1285,7 +1285,7 @@
         </is>
       </c>
       <c r="F20" s="5" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G20" s="5" t="inlineStr"/>
       <c r="H20" s="5" t="inlineStr">
@@ -1638,7 +1638,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N294"/>
+  <dimension ref="A1:N295"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -2707,7 +2707,7 @@
       </c>
       <c r="H17" s="3" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="I17" s="3" t="inlineStr"/>
@@ -2715,7 +2715,7 @@
         <v>15</v>
       </c>
       <c r="K17" s="3" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="L17" s="3" t="inlineStr">
         <is>
@@ -2724,7 +2724,7 @@
       </c>
       <c r="M17" s="3" t="inlineStr">
         <is>
-          <t>L1.C01, L1.C03, L1.C06, L1.C09, L1.C10, L1.C11, L1.C13</t>
+          <t>L1.C01, L1.C03, L1.C06, L1.C09, L1.C10, L1.C11, L1.C13, L18.C10</t>
         </is>
       </c>
       <c r="N17" s="3" t="inlineStr">
@@ -13183,7 +13183,7 @@
         <v>6</v>
       </c>
       <c r="K182" s="3" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="L182" s="3" t="inlineStr">
         <is>
@@ -13192,7 +13192,7 @@
       </c>
       <c r="M182" s="3" t="inlineStr">
         <is>
-          <t>L1.C18, L1.C20, L1.C22, L1.C27, L11.C03, L11.C05, L11.C06, L11.C08, L11.C09, L11.C10, L11.C11, L11.C12, L26.C05, L26.C07, L26.C08, L26.C09, L26.C10</t>
+          <t>L1.C18, L1.C20, L1.C22, L1.C27, L11.C03, L11.C05, L11.C06, L11.C08, L11.C09, L11.C10, L11.C11, L11.C12, L26.C05, L26.C07, L26.C08, L26.C09, L26.C10, L18.C10</t>
         </is>
       </c>
       <c r="N182" s="3" t="inlineStr">
@@ -14258,27 +14258,31 @@
       </c>
       <c r="G199" s="3" t="inlineStr">
         <is>
-          <t>descriptif</t>
+          <t>hybride</t>
         </is>
       </c>
       <c r="H199" s="3" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="I199" s="3" t="inlineStr">
-        <is>
-          <t>oui</t>
-        </is>
-      </c>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="I199" s="3" t="inlineStr"/>
       <c r="J199" s="3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K199" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="L199" s="3" t="inlineStr"/>
-      <c r="M199" s="3" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="L199" s="3" t="inlineStr">
+        <is>
+          <t>indicateur_de_progres, plancher_social, additionnalite, bareme</t>
+        </is>
+      </c>
+      <c r="M199" s="3" t="inlineStr">
+        <is>
+          <t>L11.C13, L13.C01, L17.C01, L17.C03, L18.C10, L22.C04, L24.C01, L25.C01, L26.C10</t>
+        </is>
+      </c>
       <c r="N199" s="3" t="inlineStr">
         <is>
           <t>corpus/livre-12-objectifs-de-developpement-durable/c01-ce-que-ce-livre-doit-etablir.md</t>
@@ -14331,7 +14335,7 @@
         <v>3</v>
       </c>
       <c r="K200" s="3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L200" s="3" t="inlineStr">
         <is>
@@ -14340,7 +14344,7 @@
       </c>
       <c r="M200" s="3" t="inlineStr">
         <is>
-          <t>L1.C21, L8.C34, L8.C37, L8.C40, L11.C13, L17.C03, L19.C05, L22.C04, L26.C04, L26.C07, L26.C08, L26.C09, L26.C10</t>
+          <t>L1.C21, L8.C34, L8.C37, L8.C40, L11.C13, L17.C03, L19.C05, L22.C04, L26.C04, L26.C07, L26.C08, L26.C09, L26.C10, L12.C01</t>
         </is>
       </c>
       <c r="N200" s="3" t="inlineStr">
@@ -14967,7 +14971,7 @@
         <v>1</v>
       </c>
       <c r="K210" s="3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L210" s="3" t="inlineStr">
         <is>
@@ -14976,7 +14980,7 @@
       </c>
       <c r="M210" s="3" t="inlineStr">
         <is>
-          <t>L1.C08, L1.C12, L11.C10, L17.C01, L17.C02, L18.C04, L24.C02, L26.C03, L26.C05</t>
+          <t>L1.C08, L1.C12, L11.C10, L17.C01, L17.C02, L18.C04, L24.C02, L26.C03, L26.C05, L12.C01</t>
         </is>
       </c>
       <c r="N210" s="3" t="inlineStr">
@@ -15095,7 +15099,7 @@
         <v>1</v>
       </c>
       <c r="K212" s="3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L212" s="3" t="inlineStr">
         <is>
@@ -15104,7 +15108,7 @@
       </c>
       <c r="M212" s="3" t="inlineStr">
         <is>
-          <t>L11.C13, L11.C24, L17.C01, L18.C01, L18.C04, L24.C01, L24.C05, L25.C05, L26.C02</t>
+          <t>L11.C13, L11.C24, L17.C01, L18.C01, L18.C04, L24.C01, L24.C05, L25.C05, L26.C02, L18.C10</t>
         </is>
       </c>
       <c r="N212" s="3" t="inlineStr">
@@ -15756,17 +15760,17 @@
     <row r="223">
       <c r="A223" s="2" t="inlineStr">
         <is>
-          <t>L19.C01</t>
+          <t>L18.C10</t>
         </is>
       </c>
       <c r="B223" s="3" t="inlineStr">
         <is>
-          <t>L19</t>
+          <t>L18</t>
         </is>
       </c>
       <c r="C223" s="3" t="inlineStr">
         <is>
-          <t>Ce que ce livre doit établir</t>
+          <t>La dégradation est un coût, l'amélioration n'est pas un revenu</t>
         </is>
       </c>
       <c r="D223" s="3" t="inlineStr">
@@ -15796,31 +15800,31 @@
       </c>
       <c r="I223" s="3" t="inlineStr"/>
       <c r="J223" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K223" s="3" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="L223" s="3" t="inlineStr">
         <is>
-          <t>contrepartie_comptable, creation_monetaire, monnaie_comme_registre, hierarchie_monetaire, reflux_collectif</t>
+          <t>essentiel_insolvable, valorisation_des_communs, indicateur_de_progres, contrepartie_comptable</t>
         </is>
       </c>
       <c r="M223" s="3" t="inlineStr">
         <is>
-          <t>L1.C07, L10.C01, L10.C06, L11.C01, L11.C02, L18.C06, L21.C01, L21.C03, L16.C04</t>
+          <t>L1.C15, L11.C13, L13.C01, L17.C05, L18.C01, L18.C04, L18.C09, L22.C04, L24.C05, L26.C10</t>
         </is>
       </c>
       <c r="N223" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-19-comptabilite-monetaire-de-l-emission-sans-dette/c01-ce-que-ce-livre-doit-etablir.md</t>
+          <t>corpus/livre-18-comptabilites-ecologiques-et-biophysiques/c10-la-degradation-est-un-cout-l-amelioration-n-est-pas-un-revenu.md</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" s="2" t="inlineStr">
         <is>
-          <t>L19.C02</t>
+          <t>L19.C01</t>
         </is>
       </c>
       <c r="B224" s="3" t="inlineStr">
@@ -15830,7 +15834,7 @@
       </c>
       <c r="C224" s="3" t="inlineStr">
         <is>
-          <t>Le seul précédent, et le passif lui a été reconnu en 2008</t>
+          <t>Ce que ce livre doit établir</t>
         </is>
       </c>
       <c r="D224" s="3" t="inlineStr">
@@ -15860,31 +15864,31 @@
       </c>
       <c r="I224" s="3" t="inlineStr"/>
       <c r="J224" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K224" s="3" t="n">
         <v>5</v>
       </c>
       <c r="L224" s="3" t="inlineStr">
         <is>
-          <t>contrepartie_comptable, reflux_collectif, hierarchie_monetaire, creation_monetaire, devise_cle</t>
+          <t>contrepartie_comptable, creation_monetaire, monnaie_comme_registre, hierarchie_monetaire, reflux_collectif</t>
         </is>
       </c>
       <c r="M224" s="3" t="inlineStr">
         <is>
-          <t>L3.C09, L10.C06, L11.C01, L11.C02, L19.C01, L20.C09, L21.C01, L21.C03, L21.C05, L19.C06</t>
+          <t>L1.C07, L10.C01, L10.C06, L11.C01, L11.C02, L18.C06, L21.C01, L21.C03, L16.C04</t>
         </is>
       </c>
       <c r="N224" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-19-comptabilite-monetaire-de-l-emission-sans-dette/c02-le-seul-precedent-et-le-passif-reconnu-en-2008.md</t>
+          <t>corpus/livre-19-comptabilite-monetaire-de-l-emission-sans-dette/c01-ce-que-ce-livre-doit-etablir.md</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" s="2" t="inlineStr">
         <is>
-          <t>L19.C03</t>
+          <t>L19.C02</t>
         </is>
       </c>
       <c r="B225" s="3" t="inlineStr">
@@ -15894,7 +15898,7 @@
       </c>
       <c r="C225" s="3" t="inlineStr">
         <is>
-          <t>Le reflux est un intérêt négatif, ou une répudiation — et c'est le moment qui décide</t>
+          <t>Le seul précédent, et le passif lui a été reconnu en 2008</t>
         </is>
       </c>
       <c r="D225" s="3" t="inlineStr">
@@ -15924,31 +15928,31 @@
       </c>
       <c r="I225" s="3" t="inlineStr"/>
       <c r="J225" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K225" s="3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L225" s="3" t="inlineStr">
         <is>
-          <t>monnaie_fondante, demurrage, reflux_monetaire, reflux_transactionnel, regle_contre_discretion, contrepartie_comptable</t>
+          <t>contrepartie_comptable, reflux_collectif, hierarchie_monetaire, creation_monetaire, devise_cle</t>
         </is>
       </c>
       <c r="M225" s="3" t="inlineStr">
         <is>
-          <t>L10.C06, L11.C01, L11.C02, L11.C05, L11.C07, L11.C27, L19.C01, L19.C02, L21.C01</t>
+          <t>L3.C09, L10.C06, L11.C01, L11.C02, L19.C01, L20.C09, L21.C01, L21.C03, L21.C05, L19.C06</t>
         </is>
       </c>
       <c r="N225" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-19-comptabilite-monetaire-de-l-emission-sans-dette/c03-le-reflux-interet-negatif-ou-repudiation.md</t>
+          <t>corpus/livre-19-comptabilite-monetaire-de-l-emission-sans-dette/c02-le-seul-precedent-et-le-passif-reconnu-en-2008.md</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" s="2" t="inlineStr">
         <is>
-          <t>L19.C04</t>
+          <t>L19.C03</t>
         </is>
       </c>
       <c r="B226" s="3" t="inlineStr">
@@ -15958,7 +15962,7 @@
       </c>
       <c r="C226" s="3" t="inlineStr">
         <is>
-          <t>L'actif transitoire n'existe pas, et le problème change de bilan</t>
+          <t>Le reflux est un intérêt négatif, ou une répudiation — et c'est le moment qui décide</t>
         </is>
       </c>
       <c r="D226" s="3" t="inlineStr">
@@ -15995,24 +15999,24 @@
       </c>
       <c r="L226" s="3" t="inlineStr">
         <is>
-          <t>contrepartie_comptable, hierarchie_monetaire, creation_monetaire, monnaie_comme_registre, solvabilite_anticipee</t>
+          <t>monnaie_fondante, demurrage, reflux_monetaire, reflux_transactionnel, regle_contre_discretion, contrepartie_comptable</t>
         </is>
       </c>
       <c r="M226" s="3" t="inlineStr">
         <is>
-          <t>L1.C07, L10.C06, L10.C07, L11.C01, L11.C02, L19.C01, L19.C02, L19.C03, L21.C03</t>
+          <t>L10.C06, L11.C01, L11.C02, L11.C05, L11.C07, L11.C27, L19.C01, L19.C02, L21.C01</t>
         </is>
       </c>
       <c r="N226" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-19-comptabilite-monetaire-de-l-emission-sans-dette/c04-l-actif-transitoire-et-le-deplacement-du-probleme.md</t>
+          <t>corpus/livre-19-comptabilite-monetaire-de-l-emission-sans-dette/c03-le-reflux-interet-negatif-ou-repudiation.md</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" s="2" t="inlineStr">
         <is>
-          <t>L19.C05</t>
+          <t>L19.C04</t>
         </is>
       </c>
       <c r="B227" s="3" t="inlineStr">
@@ -16022,7 +16026,7 @@
       </c>
       <c r="C227" s="3" t="inlineStr">
         <is>
-          <t>Un débiteur collectif n'existe pas — sauf comme somme de débiteurs identifiés</t>
+          <t>L'actif transitoire n'existe pas, et le problème change de bilan</t>
         </is>
       </c>
       <c r="D227" s="3" t="inlineStr">
@@ -16055,28 +16059,28 @@
         <v>2</v>
       </c>
       <c r="K227" s="3" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L227" s="3" t="inlineStr">
         <is>
-          <t>reflux_collectif, contrepartie_comptable, demurrage, monnaie_fondante, hierarchie_monetaire</t>
+          <t>contrepartie_comptable, hierarchie_monetaire, creation_monetaire, monnaie_comme_registre, solvabilite_anticipee</t>
         </is>
       </c>
       <c r="M227" s="3" t="inlineStr">
         <is>
-          <t>L10.C06, L11.C05, L11.C07, L11.C09, L19.C01, L19.C02, L19.C03, L21.C01, L25.C05, L13.C01</t>
+          <t>L1.C07, L10.C06, L10.C07, L11.C01, L11.C02, L19.C01, L19.C02, L19.C03, L21.C03</t>
         </is>
       </c>
       <c r="N227" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-19-comptabilite-monetaire-de-l-emission-sans-dette/c05-le-creancier-collectif-et-ce-qui-le-rend-representable.md</t>
+          <t>corpus/livre-19-comptabilite-monetaire-de-l-emission-sans-dette/c04-l-actif-transitoire-et-le-deplacement-du-probleme.md</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" s="2" t="inlineStr">
         <is>
-          <t>L19.C06</t>
+          <t>L19.C05</t>
         </is>
       </c>
       <c r="B228" s="3" t="inlineStr">
@@ -16086,7 +16090,7 @@
       </c>
       <c r="C228" s="3" t="inlineStr">
         <is>
-          <t>Les fonds propres négatifs, et l'institution qui n'apparaît dans les comptes de personne</t>
+          <t>Un débiteur collectif n'existe pas — sauf comme somme de débiteurs identifiés</t>
         </is>
       </c>
       <c r="D228" s="3" t="inlineStr">
@@ -16116,31 +16120,31 @@
       </c>
       <c r="I228" s="3" t="inlineStr"/>
       <c r="J228" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K228" s="3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L228" s="3" t="inlineStr">
         <is>
-          <t>contrepartie_comptable, solvabilite_anticipee, architecture_invisible, hierarchie_monetaire, robustesse</t>
+          <t>reflux_collectif, contrepartie_comptable, demurrage, monnaie_fondante, hierarchie_monetaire</t>
         </is>
       </c>
       <c r="M228" s="3" t="inlineStr">
         <is>
-          <t>L1.C07, L7.C06, L14.C01, L19.C01, L19.C02, L19.C03, L19.C04, L21.C01, L21.C04</t>
+          <t>L10.C06, L11.C05, L11.C07, L11.C09, L19.C01, L19.C02, L19.C03, L21.C01, L25.C05, L13.C01</t>
         </is>
       </c>
       <c r="N228" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-19-comptabilite-monetaire-de-l-emission-sans-dette/c06-les-fonds-propres-negatifs-et-l-institution-qui-n-apparait-nulle-part.md</t>
+          <t>corpus/livre-19-comptabilite-monetaire-de-l-emission-sans-dette/c05-le-creancier-collectif-et-ce-qui-le-rend-representable.md</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" s="2" t="inlineStr">
         <is>
-          <t>L19.C07</t>
+          <t>L19.C06</t>
         </is>
       </c>
       <c r="B229" s="3" t="inlineStr">
@@ -16150,7 +16154,7 @@
       </c>
       <c r="C229" s="3" t="inlineStr">
         <is>
-          <t>Portée de la tranche</t>
+          <t>Les fonds propres négatifs, et l'institution qui n'apparaît dans les comptes de personne</t>
         </is>
       </c>
       <c r="D229" s="3" t="inlineStr">
@@ -16170,7 +16174,7 @@
       </c>
       <c r="G229" s="3" t="inlineStr">
         <is>
-          <t>descriptif</t>
+          <t>hybride</t>
         </is>
       </c>
       <c r="H229" s="3" t="inlineStr">
@@ -16187,34 +16191,34 @@
       </c>
       <c r="L229" s="3" t="inlineStr">
         <is>
-          <t>contrepartie_comptable, reflux_collectif, monnaie_fondante, hierarchie_monetaire, architecture_invisible, creation_monetaire</t>
+          <t>contrepartie_comptable, solvabilite_anticipee, architecture_invisible, hierarchie_monetaire, robustesse</t>
         </is>
       </c>
       <c r="M229" s="3" t="inlineStr">
         <is>
-          <t>L10.C06, L11.C01, L11.C02, L11.C07, L19.C01, L19.C02, L19.C03, L19.C04, L19.C05, L19.C06, L21.C01, L21.C03</t>
+          <t>L1.C07, L7.C06, L14.C01, L19.C01, L19.C02, L19.C03, L19.C04, L21.C01, L21.C04</t>
         </is>
       </c>
       <c r="N229" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-19-comptabilite-monetaire-de-l-emission-sans-dette/c07-portee-de-la-tranche.md</t>
+          <t>corpus/livre-19-comptabilite-monetaire-de-l-emission-sans-dette/c06-les-fonds-propres-negatifs-et-l-institution-qui-n-apparait-nulle-part.md</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" s="2" t="inlineStr">
         <is>
-          <t>L20.C01</t>
+          <t>L19.C07</t>
         </is>
       </c>
       <c r="B230" s="3" t="inlineStr">
         <is>
-          <t>L20</t>
+          <t>L19</t>
         </is>
       </c>
       <c r="C230" s="3" t="inlineStr">
         <is>
-          <t>Ce que ce livre doit établir</t>
+          <t>Portée de la tranche</t>
         </is>
       </c>
       <c r="D230" s="3" t="inlineStr">
@@ -16234,41 +16238,41 @@
       </c>
       <c r="G230" s="3" t="inlineStr">
         <is>
-          <t>conception</t>
+          <t>descriptif</t>
         </is>
       </c>
       <c r="H230" s="3" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="I230" s="3" t="inlineStr"/>
       <c r="J230" s="3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K230" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L230" s="3" t="inlineStr">
         <is>
-          <t>fenetre_de_reforme, referentiel_de_change, communs, limites_planetaires, creation_monetaire</t>
+          <t>contrepartie_comptable, reflux_collectif, monnaie_fondante, hierarchie_monetaire, architecture_invisible, creation_monetaire</t>
         </is>
       </c>
       <c r="M230" s="3" t="inlineStr">
         <is>
-          <t>L1.C18, L1.C25, L1.C27, L7.C01, L7.C03, L7.C13, L7.C17, L7.C21, L11.C24</t>
+          <t>L10.C06, L11.C01, L11.C02, L11.C07, L19.C01, L19.C02, L19.C03, L19.C04, L19.C05, L19.C06, L21.C01, L21.C03</t>
         </is>
       </c>
       <c r="N230" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-20-droit-international-monetaire-et-commercial/c01-ce-que-ce-livre-doit-etablir.md</t>
+          <t>corpus/livre-19-comptabilite-monetaire-de-l-emission-sans-dette/c07-portee-de-la-tranche.md</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" s="2" t="inlineStr">
         <is>
-          <t>L20.C02</t>
+          <t>L20.C01</t>
         </is>
       </c>
       <c r="B231" s="3" t="inlineStr">
@@ -16278,7 +16282,7 @@
       </c>
       <c r="C231" s="3" t="inlineStr">
         <is>
-          <t>L'interdiction du financement monétaire</t>
+          <t>Ce que ce livre doit établir</t>
         </is>
       </c>
       <c r="D231" s="3" t="inlineStr">
@@ -16315,24 +16319,24 @@
       </c>
       <c r="L231" s="3" t="inlineStr">
         <is>
-          <t>creation_monetaire, contrepartie_comptable, reflux_collectif, fenetre_de_reforme</t>
+          <t>fenetre_de_reforme, referentiel_de_change, communs, limites_planetaires, creation_monetaire</t>
         </is>
       </c>
       <c r="M231" s="3" t="inlineStr">
         <is>
-          <t>L1.C05, L1.C18, L1.C20, L1.C22, L7.C11, L7.C13, L11.C10, L20.C01</t>
+          <t>L1.C18, L1.C25, L1.C27, L7.C01, L7.C03, L7.C13, L7.C17, L7.C21, L11.C24</t>
         </is>
       </c>
       <c r="N231" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-20-droit-international-monetaire-et-commercial/c02-l-interdiction-du-financement-monetaire.md</t>
+          <t>corpus/livre-20-droit-international-monetaire-et-commercial/c01-ce-que-ce-livre-doit-etablir.md</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="A232" s="2" t="inlineStr">
         <is>
-          <t>L20.C03</t>
+          <t>L20.C02</t>
         </is>
       </c>
       <c r="B232" s="3" t="inlineStr">
@@ -16342,7 +16346,7 @@
       </c>
       <c r="C232" s="3" t="inlineStr">
         <is>
-          <t>L'objectif principal et ce qu'il exclut</t>
+          <t>L'interdiction du financement monétaire</t>
         </is>
       </c>
       <c r="D232" s="3" t="inlineStr">
@@ -16379,24 +16383,24 @@
       </c>
       <c r="L232" s="3" t="inlineStr">
         <is>
-          <t>regle_contre_discretion, limites_planetaires, creation_monetaire, plafond_ecologique</t>
+          <t>creation_monetaire, contrepartie_comptable, reflux_collectif, fenetre_de_reforme</t>
         </is>
       </c>
       <c r="M232" s="3" t="inlineStr">
         <is>
-          <t>L1.C01, L1.C18, L1.C20, L7.C03, L8.C12, L8.C34, L11.C16, L20.C01, L20.C02</t>
+          <t>L1.C05, L1.C18, L1.C20, L1.C22, L7.C11, L7.C13, L11.C10, L20.C01</t>
         </is>
       </c>
       <c r="N232" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-20-droit-international-monetaire-et-commercial/c03-l-objectif-principal-et-ce-qu-il-exclut.md</t>
+          <t>corpus/livre-20-droit-international-monetaire-et-commercial/c02-l-interdiction-du-financement-monetaire.md</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" s="2" t="inlineStr">
         <is>
-          <t>L20.C04</t>
+          <t>L20.C03</t>
         </is>
       </c>
       <c r="B233" s="3" t="inlineStr">
@@ -16406,7 +16410,7 @@
       </c>
       <c r="C233" s="3" t="inlineStr">
         <is>
-          <t>L'indépendance, et à l'égard de qui</t>
+          <t>L'objectif principal et ce qu'il exclut</t>
         </is>
       </c>
       <c r="D233" s="3" t="inlineStr">
@@ -16431,7 +16435,7 @@
       </c>
       <c r="H233" s="3" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="I233" s="3" t="inlineStr"/>
@@ -16443,24 +16447,24 @@
       </c>
       <c r="L233" s="3" t="inlineStr">
         <is>
-          <t>regle_contre_discretion, creation_monetaire, fenetre_de_reforme</t>
+          <t>regle_contre_discretion, limites_planetaires, creation_monetaire, plafond_ecologique</t>
         </is>
       </c>
       <c r="M233" s="3" t="inlineStr">
         <is>
-          <t>L1.C18, L7.C04, L7.C07, L7.C10, L8.C31, L11.C17, L20.C01, L20.C03, L20.C11</t>
+          <t>L1.C01, L1.C18, L1.C20, L7.C03, L8.C12, L8.C34, L11.C16, L20.C01, L20.C02</t>
         </is>
       </c>
       <c r="N233" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-20-droit-international-monetaire-et-commercial/c04-l-independance-et-a-l-egard-de-qui.md</t>
+          <t>corpus/livre-20-droit-international-monetaire-et-commercial/c03-l-objectif-principal-et-ce-qu-il-exclut.md</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" s="2" t="inlineStr">
         <is>
-          <t>L20.C05</t>
+          <t>L20.C04</t>
         </is>
       </c>
       <c r="B234" s="3" t="inlineStr">
@@ -16470,7 +16474,7 @@
       </c>
       <c r="C234" s="3" t="inlineStr">
         <is>
-          <t>Le monopole d'émission et le cours légal</t>
+          <t>L'indépendance, et à l'égard de qui</t>
         </is>
       </c>
       <c r="D234" s="3" t="inlineStr">
@@ -16507,24 +16511,24 @@
       </c>
       <c r="L234" s="3" t="inlineStr">
         <is>
-          <t>monnaie_comme_registre, creation_monetaire, referentiel_de_change, hierarchie_monetaire</t>
+          <t>regle_contre_discretion, creation_monetaire, fenetre_de_reforme</t>
         </is>
       </c>
       <c r="M234" s="3" t="inlineStr">
         <is>
-          <t>L1.C05, L1.C07, L1.C26, L7.C15, L11.C15, L20.C01, L20.C02, L20.C03</t>
+          <t>L1.C18, L7.C04, L7.C07, L7.C10, L8.C31, L11.C17, L20.C01, L20.C03, L20.C11</t>
         </is>
       </c>
       <c r="N234" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-20-droit-international-monetaire-et-commercial/c05-le-monopole-d-emission-et-le-cours-legal.md</t>
+          <t>corpus/livre-20-droit-international-monetaire-et-commercial/c04-l-independance-et-a-l-egard-de-qui.md</t>
         </is>
       </c>
     </row>
     <row r="235">
       <c r="A235" s="2" t="inlineStr">
         <is>
-          <t>L20.C06</t>
+          <t>L20.C05</t>
         </is>
       </c>
       <c r="B235" s="3" t="inlineStr">
@@ -16534,7 +16538,7 @@
       </c>
       <c r="C235" s="3" t="inlineStr">
         <is>
-          <t>Les voies de révision et leur coût</t>
+          <t>Le monopole d'émission et le cours légal</t>
         </is>
       </c>
       <c r="D235" s="3" t="inlineStr">
@@ -16564,31 +16568,31 @@
       </c>
       <c r="I235" s="3" t="inlineStr"/>
       <c r="J235" s="3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K235" s="3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L235" s="3" t="inlineStr">
         <is>
-          <t>fenetre_de_reforme, regle_contre_discretion, creation_monetaire</t>
+          <t>monnaie_comme_registre, creation_monetaire, referentiel_de_change, hierarchie_monetaire</t>
         </is>
       </c>
       <c r="M235" s="3" t="inlineStr">
         <is>
-          <t>L1.C18, L7.C12, L7.C20, L7.C21, L11.C15, L20.C01, L20.C02, L20.C03, L20.C07, L20.C09, L20.C18</t>
+          <t>L1.C05, L1.C07, L1.C26, L7.C15, L11.C15, L20.C01, L20.C02, L20.C03</t>
         </is>
       </c>
       <c r="N235" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-20-droit-international-monetaire-et-commercial/c06-les-voies-de-revision-et-leur-cout.md</t>
+          <t>corpus/livre-20-droit-international-monetaire-et-commercial/c05-le-monopole-d-emission-et-le-cours-legal.md</t>
         </is>
       </c>
     </row>
     <row r="236">
       <c r="A236" s="2" t="inlineStr">
         <is>
-          <t>L20.C07</t>
+          <t>L20.C06</t>
         </is>
       </c>
       <c r="B236" s="3" t="inlineStr">
@@ -16598,7 +16602,7 @@
       </c>
       <c r="C236" s="3" t="inlineStr">
         <is>
-          <t>L'accord monétaire international</t>
+          <t>Les voies de révision et leur coût</t>
         </is>
       </c>
       <c r="D236" s="3" t="inlineStr">
@@ -16628,31 +16632,31 @@
       </c>
       <c r="I236" s="3" t="inlineStr"/>
       <c r="J236" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K236" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L236" s="3" t="inlineStr">
         <is>
-          <t>referentiel_de_change, fenetre_de_reforme, etalon_de_change_or, hierarchie_monetaire</t>
+          <t>fenetre_de_reforme, regle_contre_discretion, creation_monetaire</t>
         </is>
       </c>
       <c r="M236" s="3" t="inlineStr">
         <is>
-          <t>L1.C18, L1.C26, L7.C02, L7.C05, L7.C12, L7.C13, L11.C15, L20.C01, L20.C03, L20.C06, L20.C10</t>
+          <t>L1.C18, L7.C12, L7.C20, L7.C21, L11.C15, L20.C01, L20.C02, L20.C03, L20.C07, L20.C09, L20.C18</t>
         </is>
       </c>
       <c r="N236" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-20-droit-international-monetaire-et-commercial/c07-l-accord-monetaire-international.md</t>
+          <t>corpus/livre-20-droit-international-monetaire-et-commercial/c06-les-voies-de-revision-et-leur-cout.md</t>
         </is>
       </c>
     </row>
     <row r="237">
       <c r="A237" s="2" t="inlineStr">
         <is>
-          <t>L20.C08</t>
+          <t>L20.C07</t>
         </is>
       </c>
       <c r="B237" s="3" t="inlineStr">
@@ -16662,7 +16666,7 @@
       </c>
       <c r="C237" s="3" t="inlineStr">
         <is>
-          <t>La parité inscrite dans le traité</t>
+          <t>L'accord monétaire international</t>
         </is>
       </c>
       <c r="D237" s="3" t="inlineStr">
@@ -16687,36 +16691,36 @@
       </c>
       <c r="H237" s="3" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="I237" s="3" t="inlineStr"/>
       <c r="J237" s="3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K237" s="3" t="n">
         <v>3</v>
       </c>
       <c r="L237" s="3" t="inlineStr">
         <is>
-          <t>referentiel_de_change, etalon_de_change_or, hierarchie_monetaire, bareme, devise_cle</t>
+          <t>referentiel_de_change, fenetre_de_reforme, etalon_de_change_or, hierarchie_monetaire</t>
         </is>
       </c>
       <c r="M237" s="3" t="inlineStr">
         <is>
-          <t>L1.C25, L1.C26, L1.C28, L7.C02, L7.C20, L11.C15, L11.C17, L20.C01, L20.C09, L20.C13</t>
+          <t>L1.C18, L1.C26, L7.C02, L7.C05, L7.C12, L7.C13, L11.C15, L20.C01, L20.C03, L20.C06, L20.C10</t>
         </is>
       </c>
       <c r="N237" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-20-droit-international-monetaire-et-commercial/c08-la-parite-inscrite-dans-le-traite.md</t>
+          <t>corpus/livre-20-droit-international-monetaire-et-commercial/c07-l-accord-monetaire-international.md</t>
         </is>
       </c>
     </row>
     <row r="238">
       <c r="A238" s="2" t="inlineStr">
         <is>
-          <t>L20.C09</t>
+          <t>L20.C08</t>
         </is>
       </c>
       <c r="B238" s="3" t="inlineStr">
@@ -16726,7 +16730,7 @@
       </c>
       <c r="C238" s="3" t="inlineStr">
         <is>
-          <t>L'amendement des statuts du Fonds</t>
+          <t>La parité inscrite dans le traité</t>
         </is>
       </c>
       <c r="D238" s="3" t="inlineStr">
@@ -16751,36 +16755,36 @@
       </c>
       <c r="H238" s="3" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="I238" s="3" t="inlineStr"/>
       <c r="J238" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K238" s="3" t="n">
         <v>3</v>
       </c>
       <c r="L238" s="3" t="inlineStr">
         <is>
-          <t>fenetre_de_reforme, referentiel_de_change, bareme, regle_contre_discretion</t>
+          <t>referentiel_de_change, etalon_de_change_or, hierarchie_monetaire, bareme, devise_cle</t>
         </is>
       </c>
       <c r="M238" s="3" t="inlineStr">
         <is>
-          <t>L7.C06, L7.C09, L7.C16, L7.C20, L11.C15, L11.C20, L20.C01, L20.C06, L20.C08, L20.C10, L20.C13</t>
+          <t>L1.C25, L1.C26, L1.C28, L7.C02, L7.C20, L11.C15, L11.C17, L20.C01, L20.C09, L20.C13</t>
         </is>
       </c>
       <c r="N238" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-20-droit-international-monetaire-et-commercial/c09-l-amendement-des-statuts-du-fonds.md</t>
+          <t>corpus/livre-20-droit-international-monetaire-et-commercial/c08-la-parite-inscrite-dans-le-traite.md</t>
         </is>
       </c>
     </row>
     <row r="239">
       <c r="A239" s="2" t="inlineStr">
         <is>
-          <t>L20.C10</t>
+          <t>L20.C09</t>
         </is>
       </c>
       <c r="B239" s="3" t="inlineStr">
@@ -16790,7 +16794,7 @@
       </c>
       <c r="C239" s="3" t="inlineStr">
         <is>
-          <t>Le vote pondéré et les voix de base</t>
+          <t>L'amendement des statuts du Fonds</t>
         </is>
       </c>
       <c r="D239" s="3" t="inlineStr">
@@ -16827,24 +16831,24 @@
       </c>
       <c r="L239" s="3" t="inlineStr">
         <is>
-          <t>bareme, devise_cle, hierarchie_monetaire, referentiel_de_change</t>
+          <t>fenetre_de_reforme, referentiel_de_change, bareme, regle_contre_discretion</t>
         </is>
       </c>
       <c r="M239" s="3" t="inlineStr">
         <is>
-          <t>L1.C25, L7.C02, L7.C05, L7.C06, L7.C09, L7.C10, L11.C16, L20.C01, L20.C07, L20.C09, L20.C12</t>
+          <t>L7.C06, L7.C09, L7.C16, L7.C20, L11.C15, L11.C20, L20.C01, L20.C06, L20.C08, L20.C10, L20.C13</t>
         </is>
       </c>
       <c r="N239" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-20-droit-international-monetaire-et-commercial/c10-le-vote-pondere-et-les-voix-de-base.md</t>
+          <t>corpus/livre-20-droit-international-monetaire-et-commercial/c09-l-amendement-des-statuts-du-fonds.md</t>
         </is>
       </c>
     </row>
     <row r="240">
       <c r="A240" s="2" t="inlineStr">
         <is>
-          <t>L20.C11</t>
+          <t>L20.C10</t>
         </is>
       </c>
       <c r="B240" s="3" t="inlineStr">
@@ -16854,7 +16858,7 @@
       </c>
       <c r="C240" s="3" t="inlineStr">
         <is>
-          <t>La personnalité juridique et les immunités</t>
+          <t>Le vote pondéré et les voix de base</t>
         </is>
       </c>
       <c r="D240" s="3" t="inlineStr">
@@ -16884,31 +16888,31 @@
       </c>
       <c r="I240" s="3" t="inlineStr"/>
       <c r="J240" s="3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K240" s="3" t="n">
         <v>3</v>
       </c>
       <c r="L240" s="3" t="inlineStr">
         <is>
-          <t>communs, creation_monetaire, fenetre_de_reforme, robustesse</t>
+          <t>bareme, devise_cle, hierarchie_monetaire, referentiel_de_change</t>
         </is>
       </c>
       <c r="M240" s="3" t="inlineStr">
         <is>
-          <t>L7.C01, L7.C03, L7.C07, L7.C10, L7.C13, L11.C25, L20.C01, L20.C04, L20.C12, L20.C14</t>
+          <t>L1.C25, L7.C02, L7.C05, L7.C06, L7.C09, L7.C10, L11.C16, L20.C01, L20.C07, L20.C09, L20.C12</t>
         </is>
       </c>
       <c r="N240" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-20-droit-international-monetaire-et-commercial/c11-la-personnalite-juridique-et-les-immunites.md</t>
+          <t>corpus/livre-20-droit-international-monetaire-et-commercial/c10-le-vote-pondere-et-les-voix-de-base.md</t>
         </is>
       </c>
     </row>
     <row r="241">
       <c r="A241" s="2" t="inlineStr">
         <is>
-          <t>L20.C12</t>
+          <t>L20.C11</t>
         </is>
       </c>
       <c r="B241" s="3" t="inlineStr">
@@ -16918,7 +16922,7 @@
       </c>
       <c r="C241" s="3" t="inlineStr">
         <is>
-          <t>Les pouvoirs non délégables</t>
+          <t>La personnalité juridique et les immunités</t>
         </is>
       </c>
       <c r="D241" s="3" t="inlineStr">
@@ -16943,36 +16947,36 @@
       </c>
       <c r="H241" s="3" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="I241" s="3" t="inlineStr"/>
       <c r="J241" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K241" s="3" t="n">
         <v>3</v>
       </c>
       <c r="L241" s="3" t="inlineStr">
         <is>
-          <t>bareme, valorisation_des_communs, polycentricite, robustesse</t>
+          <t>communs, creation_monetaire, fenetre_de_reforme, robustesse</t>
         </is>
       </c>
       <c r="M241" s="3" t="inlineStr">
         <is>
-          <t>L7.C05, L7.C06, L7.C07, L7.C11, L7.C14, L11.C16, L11.C20, L20.C01, L20.C09, L20.C10, L20.C14</t>
+          <t>L7.C01, L7.C03, L7.C07, L7.C10, L7.C13, L11.C25, L20.C01, L20.C04, L20.C12, L20.C14</t>
         </is>
       </c>
       <c r="N241" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-20-droit-international-monetaire-et-commercial/c12-les-pouvoirs-non-delegables.md</t>
+          <t>corpus/livre-20-droit-international-monetaire-et-commercial/c11-la-personnalite-juridique-et-les-immunites.md</t>
         </is>
       </c>
     </row>
     <row r="242">
       <c r="A242" s="2" t="inlineStr">
         <is>
-          <t>L20.C13</t>
+          <t>L20.C12</t>
         </is>
       </c>
       <c r="B242" s="3" t="inlineStr">
@@ -16982,7 +16986,7 @@
       </c>
       <c r="C242" s="3" t="inlineStr">
         <is>
-          <t>L'entrée en vigueur, l'adhésion et le retrait</t>
+          <t>Les pouvoirs non délégables</t>
         </is>
       </c>
       <c r="D242" s="3" t="inlineStr">
@@ -17012,31 +17016,31 @@
       </c>
       <c r="I242" s="3" t="inlineStr"/>
       <c r="J242" s="3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K242" s="3" t="n">
         <v>3</v>
       </c>
       <c r="L242" s="3" t="inlineStr">
         <is>
-          <t>seuil_d_activation, reflux_collectif, fenetre_de_reforme, additionnalite</t>
+          <t>bareme, valorisation_des_communs, polycentricite, robustesse</t>
         </is>
       </c>
       <c r="M242" s="3" t="inlineStr">
         <is>
-          <t>L7.C11, L7.C12, L7.C16, L7.C17, L7.C19, L11.C18, L20.C01, L20.C06, L20.C09, L20.C12</t>
+          <t>L7.C05, L7.C06, L7.C07, L7.C11, L7.C14, L11.C16, L11.C20, L20.C01, L20.C09, L20.C10, L20.C14</t>
         </is>
       </c>
       <c r="N242" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-20-droit-international-monetaire-et-commercial/c13-l-entree-en-vigueur-l-adhesion-et-le-retrait.md</t>
+          <t>corpus/livre-20-droit-international-monetaire-et-commercial/c12-les-pouvoirs-non-delegables.md</t>
         </is>
       </c>
     </row>
     <row r="243">
       <c r="A243" s="2" t="inlineStr">
         <is>
-          <t>L20.C14</t>
+          <t>L20.C13</t>
         </is>
       </c>
       <c r="B243" s="3" t="inlineStr">
@@ -17046,7 +17050,7 @@
       </c>
       <c r="C243" s="3" t="inlineStr">
         <is>
-          <t>Qui interprète le traité</t>
+          <t>L'entrée en vigueur, l'adhésion et le retrait</t>
         </is>
       </c>
       <c r="D243" s="3" t="inlineStr">
@@ -17076,31 +17080,31 @@
       </c>
       <c r="I243" s="3" t="inlineStr"/>
       <c r="J243" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K243" s="3" t="n">
         <v>3</v>
       </c>
       <c r="L243" s="3" t="inlineStr">
         <is>
-          <t>robustesse, regle_contre_discretion, communs</t>
+          <t>seuil_d_activation, reflux_collectif, fenetre_de_reforme, additionnalite</t>
         </is>
       </c>
       <c r="M243" s="3" t="inlineStr">
         <is>
-          <t>L7.C07, L7.C13, L7.C14, L7.C19, L11.C19, L11.C25, L20.C01, L20.C03, L20.C11, L20.C12, L20.C21</t>
+          <t>L7.C11, L7.C12, L7.C16, L7.C17, L7.C19, L11.C18, L20.C01, L20.C06, L20.C09, L20.C12</t>
         </is>
       </c>
       <c r="N243" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-20-droit-international-monetaire-et-commercial/c14-qui-interprete-le-traite.md</t>
+          <t>corpus/livre-20-droit-international-monetaire-et-commercial/c13-l-entree-en-vigueur-l-adhesion-et-le-retrait.md</t>
         </is>
       </c>
     </row>
     <row r="244">
       <c r="A244" s="2" t="inlineStr">
         <is>
-          <t>L20.C15</t>
+          <t>L20.C14</t>
         </is>
       </c>
       <c r="B244" s="3" t="inlineStr">
@@ -17110,7 +17114,7 @@
       </c>
       <c r="C244" s="3" t="inlineStr">
         <is>
-          <t>Le devoir international des agents</t>
+          <t>Qui interprète le traité</t>
         </is>
       </c>
       <c r="D244" s="3" t="inlineStr">
@@ -17135,36 +17139,36 @@
       </c>
       <c r="H244" s="3" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="I244" s="3" t="inlineStr"/>
       <c r="J244" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K244" s="3" t="n">
         <v>3</v>
       </c>
       <c r="L244" s="3" t="inlineStr">
         <is>
-          <t>robustesse, regle_contre_discretion, indicateur_de_progres</t>
+          <t>robustesse, regle_contre_discretion, communs</t>
         </is>
       </c>
       <c r="M244" s="3" t="inlineStr">
         <is>
-          <t>L7.C04, L7.C07, L7.C10, L11.C21, L11.C25, L20.C01, L20.C04, L20.C11, L20.C14</t>
+          <t>L7.C07, L7.C13, L7.C14, L7.C19, L11.C19, L11.C25, L20.C01, L20.C03, L20.C11, L20.C12, L20.C21</t>
         </is>
       </c>
       <c r="N244" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-20-droit-international-monetaire-et-commercial/c15-le-devoir-international-des-agents.md</t>
+          <t>corpus/livre-20-droit-international-monetaire-et-commercial/c14-qui-interprete-le-traite.md</t>
         </is>
       </c>
     </row>
     <row r="245">
       <c r="A245" s="2" t="inlineStr">
         <is>
-          <t>L20.C16</t>
+          <t>L20.C15</t>
         </is>
       </c>
       <c r="B245" s="3" t="inlineStr">
@@ -17174,7 +17178,7 @@
       </c>
       <c r="C245" s="3" t="inlineStr">
         <is>
-          <t>Le patrimoine commun de l'humanité</t>
+          <t>Le devoir international des agents</t>
         </is>
       </c>
       <c r="D245" s="3" t="inlineStr">
@@ -17199,36 +17203,36 @@
       </c>
       <c r="H245" s="3" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="I245" s="3" t="inlineStr"/>
       <c r="J245" s="3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K245" s="3" t="n">
         <v>3</v>
       </c>
       <c r="L245" s="3" t="inlineStr">
         <is>
-          <t>communs, valorisation_des_communs, limites_planetaires, additionnalite, plafond_ecologique</t>
+          <t>robustesse, regle_contre_discretion, indicateur_de_progres</t>
         </is>
       </c>
       <c r="M245" s="3" t="inlineStr">
         <is>
-          <t>L1.C17, L1.C22, L7.C05, L7.C13, L11.C16, L20.C01, L20.C11, L20.C17, L20.C22</t>
+          <t>L7.C04, L7.C07, L7.C10, L11.C21, L11.C25, L20.C01, L20.C04, L20.C11, L20.C14</t>
         </is>
       </c>
       <c r="N245" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-20-droit-international-monetaire-et-commercial/c16-le-patrimoine-commun-de-l-humanite.md</t>
+          <t>corpus/livre-20-droit-international-monetaire-et-commercial/c15-le-devoir-international-des-agents.md</t>
         </is>
       </c>
     </row>
     <row r="246">
       <c r="A246" s="2" t="inlineStr">
         <is>
-          <t>L20.C17</t>
+          <t>L20.C16</t>
         </is>
       </c>
       <c r="B246" s="3" t="inlineStr">
@@ -17238,7 +17242,7 @@
       </c>
       <c r="C246" s="3" t="inlineStr">
         <is>
-          <t>La sanctuarisation, et elle existe</t>
+          <t>Le patrimoine commun de l'humanité</t>
         </is>
       </c>
       <c r="D246" s="3" t="inlineStr">
@@ -17268,31 +17272,31 @@
       </c>
       <c r="I246" s="3" t="inlineStr"/>
       <c r="J246" s="3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K246" s="3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L246" s="3" t="inlineStr">
         <is>
-          <t>communs, limites_planetaires, fenetre_de_reforme, robustesse, plafond_ecologique</t>
+          <t>communs, valorisation_des_communs, limites_planetaires, additionnalite, plafond_ecologique</t>
         </is>
       </c>
       <c r="M246" s="3" t="inlineStr">
         <is>
-          <t>L1.C17, L1.C18, L7.C13, L7.C19, L7.C20, L11.C20, L20.C01, L20.C06, L20.C09, L20.C16, L20.C22</t>
+          <t>L1.C17, L1.C22, L7.C05, L7.C13, L11.C16, L20.C01, L20.C11, L20.C17, L20.C22</t>
         </is>
       </c>
       <c r="N246" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-20-droit-international-monetaire-et-commercial/c17-la-sanctuarisation-et-elle-existe.md</t>
+          <t>corpus/livre-20-droit-international-monetaire-et-commercial/c16-le-patrimoine-commun-de-l-humanite.md</t>
         </is>
       </c>
     </row>
     <row r="247">
       <c r="A247" s="2" t="inlineStr">
         <is>
-          <t>L20.C18</t>
+          <t>L20.C17</t>
         </is>
       </c>
       <c r="B247" s="3" t="inlineStr">
@@ -17302,7 +17306,7 @@
       </c>
       <c r="C247" s="3" t="inlineStr">
         <is>
-          <t>L'amendement et la dérogation dans l'ordre commercial</t>
+          <t>La sanctuarisation, et elle existe</t>
         </is>
       </c>
       <c r="D247" s="3" t="inlineStr">
@@ -17327,36 +17331,36 @@
       </c>
       <c r="H247" s="3" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="I247" s="3" t="inlineStr"/>
       <c r="J247" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K247" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L247" s="3" t="inlineStr">
         <is>
-          <t>bareme, seuil_d_activation, additionnalite, fenetre_de_reforme</t>
+          <t>communs, limites_planetaires, fenetre_de_reforme, robustesse, plafond_ecologique</t>
         </is>
       </c>
       <c r="M247" s="3" t="inlineStr">
         <is>
-          <t>L1.C27, L7.C17, L7.C20, L11.C24, L20.C01, L20.C06, L20.C09, L20.C13, L20.C19, L20.C20</t>
+          <t>L1.C17, L1.C18, L7.C13, L7.C19, L7.C20, L11.C20, L20.C01, L20.C06, L20.C09, L20.C16, L20.C22</t>
         </is>
       </c>
       <c r="N247" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-20-droit-international-monetaire-et-commercial/c18-l-amendement-et-la-derogation-dans-l-ordre-commercial.md</t>
+          <t>corpus/livre-20-droit-international-monetaire-et-commercial/c17-la-sanctuarisation-et-elle-existe.md</t>
         </is>
       </c>
     </row>
     <row r="248">
       <c r="A248" s="2" t="inlineStr">
         <is>
-          <t>L20.C19</t>
+          <t>L20.C18</t>
         </is>
       </c>
       <c r="B248" s="3" t="inlineStr">
@@ -17366,7 +17370,7 @@
       </c>
       <c r="C248" s="3" t="inlineStr">
         <is>
-          <t>Le texte que la conformité invoque</t>
+          <t>L'amendement et la dérogation dans l'ordre commercial</t>
         </is>
       </c>
       <c r="D248" s="3" t="inlineStr">
@@ -17391,36 +17395,36 @@
       </c>
       <c r="H248" s="3" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="I248" s="3" t="inlineStr"/>
       <c r="J248" s="3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K248" s="3" t="n">
         <v>3</v>
       </c>
       <c r="L248" s="3" t="inlineStr">
         <is>
-          <t>bareme, additionnalite, limites_planetaires, seuil_d_activation, externalisation</t>
+          <t>bareme, seuil_d_activation, additionnalite, fenetre_de_reforme</t>
         </is>
       </c>
       <c r="M248" s="3" t="inlineStr">
         <is>
-          <t>L1.C27, L7.C17, L11.C24, L20.C01, L20.C18, L20.C20, L20.C22</t>
+          <t>L1.C27, L7.C17, L7.C20, L11.C24, L20.C01, L20.C06, L20.C09, L20.C13, L20.C19, L20.C20</t>
         </is>
       </c>
       <c r="N248" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-20-droit-international-monetaire-et-commercial/c19-le-texte-que-la-conformite-invoque.md</t>
+          <t>corpus/livre-20-droit-international-monetaire-et-commercial/c18-l-amendement-et-la-derogation-dans-l-ordre-commercial.md</t>
         </is>
       </c>
     </row>
     <row r="249">
       <c r="A249" s="2" t="inlineStr">
         <is>
-          <t>L20.C20</t>
+          <t>L20.C19</t>
         </is>
       </c>
       <c r="B249" s="3" t="inlineStr">
@@ -17430,7 +17434,7 @@
       </c>
       <c r="C249" s="3" t="inlineStr">
         <is>
-          <t>L'ajustement aux frontières comme précédent</t>
+          <t>Le texte que la conformité invoque</t>
         </is>
       </c>
       <c r="D249" s="3" t="inlineStr">
@@ -17467,24 +17471,24 @@
       </c>
       <c r="L249" s="3" t="inlineStr">
         <is>
-          <t>bareme, seuil_d_activation, externalisation, additionnalite, contrepartie_comptable</t>
+          <t>bareme, additionnalite, limites_planetaires, seuil_d_activation, externalisation</t>
         </is>
       </c>
       <c r="M249" s="3" t="inlineStr">
         <is>
-          <t>L1.C27, L7.C17, L11.C21, L11.C24, L11.C25, L20.C01, L20.C18, L20.C19, L20.C22</t>
+          <t>L1.C27, L7.C17, L11.C24, L20.C01, L20.C18, L20.C20, L20.C22</t>
         </is>
       </c>
       <c r="N249" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-20-droit-international-monetaire-et-commercial/c20-l-ajustement-aux-frontieres-comme-precedent.md</t>
+          <t>corpus/livre-20-droit-international-monetaire-et-commercial/c19-le-texte-que-la-conformite-invoque.md</t>
         </is>
       </c>
     </row>
     <row r="250">
       <c r="A250" s="2" t="inlineStr">
         <is>
-          <t>L20.C21</t>
+          <t>L20.C20</t>
         </is>
       </c>
       <c r="B250" s="3" t="inlineStr">
@@ -17494,7 +17498,7 @@
       </c>
       <c r="C250" s="3" t="inlineStr">
         <is>
-          <t>La transparence et sa limite juridictionnelle</t>
+          <t>L'ajustement aux frontières comme précédent</t>
         </is>
       </c>
       <c r="D250" s="3" t="inlineStr">
@@ -17519,36 +17523,36 @@
       </c>
       <c r="H250" s="3" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="I250" s="3" t="inlineStr"/>
       <c r="J250" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K250" s="3" t="n">
         <v>3</v>
       </c>
       <c r="L250" s="3" t="inlineStr">
         <is>
-          <t>robustesse, contrepartie_comptable, bareme, monnaie_comme_registre</t>
+          <t>bareme, seuil_d_activation, externalisation, additionnalite, contrepartie_comptable</t>
         </is>
       </c>
       <c r="M250" s="3" t="inlineStr">
         <is>
-          <t>L7.C18, L11.C21, L11.C24, L11.C25, L20.C01, L20.C11, L20.C14, L20.C20, L20.C22</t>
+          <t>L1.C27, L7.C17, L11.C21, L11.C24, L11.C25, L20.C01, L20.C18, L20.C19, L20.C22</t>
         </is>
       </c>
       <c r="N250" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-20-droit-international-monetaire-et-commercial/c21-la-transparence-et-sa-limite-juridictionnelle.md</t>
+          <t>corpus/livre-20-droit-international-monetaire-et-commercial/c20-l-ajustement-aux-frontieres-comme-precedent.md</t>
         </is>
       </c>
     </row>
     <row r="251">
       <c r="A251" s="2" t="inlineStr">
         <is>
-          <t>L20.C22</t>
+          <t>L20.C21</t>
         </is>
       </c>
       <c r="B251" s="3" t="inlineStr">
@@ -17558,7 +17562,7 @@
       </c>
       <c r="C251" s="3" t="inlineStr">
         <is>
-          <t>Ce que le droit devrait devenir</t>
+          <t>La transparence et sa limite juridictionnelle</t>
         </is>
       </c>
       <c r="D251" s="3" t="inlineStr">
@@ -17595,24 +17599,24 @@
       </c>
       <c r="L251" s="3" t="inlineStr">
         <is>
-          <t>fenetre_de_reforme, communs, limites_planetaires, regle_contre_discretion, bareme, referentiel_de_change</t>
+          <t>robustesse, contrepartie_comptable, bareme, monnaie_comme_registre</t>
         </is>
       </c>
       <c r="M251" s="3" t="inlineStr">
         <is>
-          <t>L1.C18, L7.C12, L7.C13, L11.C15, L11.C25, L20.C01, L20.C03, L20.C06, L20.C07, L20.C08, L20.C12, L20.C13, L20.C16, L20.C17, L20.C19, L20.C20, L20.C21, L20.C23</t>
+          <t>L7.C18, L11.C21, L11.C24, L11.C25, L20.C01, L20.C11, L20.C14, L20.C20, L20.C22</t>
         </is>
       </c>
       <c r="N251" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-20-droit-international-monetaire-et-commercial/c22-ce-que-le-droit-devrait-devenir.md</t>
+          <t>corpus/livre-20-droit-international-monetaire-et-commercial/c21-la-transparence-et-sa-limite-juridictionnelle.md</t>
         </is>
       </c>
     </row>
     <row r="252">
       <c r="A252" s="2" t="inlineStr">
         <is>
-          <t>L20.C23</t>
+          <t>L20.C22</t>
         </is>
       </c>
       <c r="B252" s="3" t="inlineStr">
@@ -17622,7 +17626,7 @@
       </c>
       <c r="C252" s="3" t="inlineStr">
         <is>
-          <t>La portée du livre</t>
+          <t>Ce que le droit devrait devenir</t>
         </is>
       </c>
       <c r="D252" s="3" t="inlineStr">
@@ -17652,41 +17656,41 @@
       </c>
       <c r="I252" s="3" t="inlineStr"/>
       <c r="J252" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K252" s="3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L252" s="3" t="inlineStr">
         <is>
-          <t>fenetre_de_reforme, communs, limites_planetaires, creation_monetaire, robustesse</t>
+          <t>fenetre_de_reforme, communs, limites_planetaires, regle_contre_discretion, bareme, referentiel_de_change</t>
         </is>
       </c>
       <c r="M252" s="3" t="inlineStr">
         <is>
-          <t>L1.C18, L1.C27, L7.C05, L7.C10, L7.C12, L7.C13, L11.C15, L11.C24, L11.C25, L20.C01, L20.C02, L20.C03, L20.C06, L20.C07, L20.C08, L20.C11, L20.C12, L20.C13, L20.C16, L20.C17, L20.C19, L20.C20, L20.C21, L20.C22</t>
+          <t>L1.C18, L7.C12, L7.C13, L11.C15, L11.C25, L20.C01, L20.C03, L20.C06, L20.C07, L20.C08, L20.C12, L20.C13, L20.C16, L20.C17, L20.C19, L20.C20, L20.C21, L20.C23</t>
         </is>
       </c>
       <c r="N252" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-20-droit-international-monetaire-et-commercial/c23-la-portee-du-livre.md</t>
+          <t>corpus/livre-20-droit-international-monetaire-et-commercial/c22-ce-que-le-droit-devrait-devenir.md</t>
         </is>
       </c>
     </row>
     <row r="253">
       <c r="A253" s="2" t="inlineStr">
         <is>
-          <t>L21.C01</t>
+          <t>L20.C23</t>
         </is>
       </c>
       <c r="B253" s="3" t="inlineStr">
         <is>
-          <t>L21</t>
+          <t>L20</t>
         </is>
       </c>
       <c r="C253" s="3" t="inlineStr">
         <is>
-          <t>Ce que ce livre doit établir, et le principe qui exige des fonds propres</t>
+          <t>La portée du livre</t>
         </is>
       </c>
       <c r="D253" s="3" t="inlineStr">
@@ -17706,41 +17710,41 @@
       </c>
       <c r="G253" s="3" t="inlineStr">
         <is>
-          <t>hybride</t>
+          <t>conception</t>
         </is>
       </c>
       <c r="H253" s="3" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="I253" s="3" t="inlineStr"/>
       <c r="J253" s="3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K253" s="3" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L253" s="3" t="inlineStr">
         <is>
-          <t>contrepartie_comptable, creation_monetaire, hierarchie_monetaire, monnaie_comme_registre, seuil_d_activation</t>
+          <t>fenetre_de_reforme, communs, limites_planetaires, creation_monetaire, robustesse</t>
         </is>
       </c>
       <c r="M253" s="3" t="inlineStr">
         <is>
-          <t>L1.C20, L5.C02, L5.C09, L10.C01, L10.C02, L11.C02, L18.C01, L21.C01, L19.C02, L19.C06</t>
+          <t>L1.C18, L1.C27, L7.C05, L7.C10, L7.C12, L7.C13, L11.C15, L11.C24, L11.C25, L20.C01, L20.C02, L20.C03, L20.C06, L20.C07, L20.C08, L20.C11, L20.C12, L20.C13, L20.C16, L20.C17, L20.C19, L20.C20, L20.C21, L20.C22</t>
         </is>
       </c>
       <c r="N253" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-21-plomberie-financiere-mondiale/c01-ce-que-ce-livre-doit-etablir.md</t>
+          <t>corpus/livre-20-droit-international-monetaire-et-commercial/c23-la-portee-du-livre.md</t>
         </is>
       </c>
     </row>
     <row r="254">
       <c r="A254" s="2" t="inlineStr">
         <is>
-          <t>L21.C02</t>
+          <t>L21.C01</t>
         </is>
       </c>
       <c r="B254" s="3" t="inlineStr">
@@ -17750,7 +17754,7 @@
       </c>
       <c r="C254" s="3" t="inlineStr">
         <is>
-          <t>Comment l'unité circulerait vraiment, et ce que chaque étape exige</t>
+          <t>Ce que ce livre doit établir, et le principe qui exige des fonds propres</t>
         </is>
       </c>
       <c r="D254" s="3" t="inlineStr">
@@ -17775,7 +17779,7 @@
       </c>
       <c r="H254" s="3" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="I254" s="3" t="inlineStr"/>
@@ -17783,28 +17787,28 @@
         <v>3</v>
       </c>
       <c r="K254" s="3" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="L254" s="3" t="inlineStr">
         <is>
-          <t>monnaie_comme_registre, hierarchie_monetaire, contrepartie_comptable, devise_cle, seuil_d_activation</t>
+          <t>contrepartie_comptable, creation_monetaire, hierarchie_monetaire, monnaie_comme_registre, seuil_d_activation</t>
         </is>
       </c>
       <c r="M254" s="3" t="inlineStr">
         <is>
-          <t>L1.C24, L3.C05, L3.C09, L5.C02, L5.C09, L10.C01, L11.C02, L21.C01</t>
+          <t>L1.C20, L5.C02, L5.C09, L10.C01, L10.C02, L11.C02, L18.C01, L21.C01, L19.C02, L19.C06</t>
         </is>
       </c>
       <c r="N254" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-21-plomberie-financiere-mondiale/c02-comment-l-unite-circulerait-vraiment.md</t>
+          <t>corpus/livre-21-plomberie-financiere-mondiale/c01-ce-que-ce-livre-doit-etablir.md</t>
         </is>
       </c>
     </row>
     <row r="255">
       <c r="A255" s="2" t="inlineStr">
         <is>
-          <t>L21.C03</t>
+          <t>L21.C02</t>
         </is>
       </c>
       <c r="B255" s="3" t="inlineStr">
@@ -17814,7 +17818,7 @@
       </c>
       <c r="C255" s="3" t="inlineStr">
         <is>
-          <t>Une opération de bout en bout, bilan par bilan</t>
+          <t>Comment l'unité circulerait vraiment, et ce que chaque étape exige</t>
         </is>
       </c>
       <c r="D255" s="3" t="inlineStr">
@@ -17834,12 +17838,12 @@
       </c>
       <c r="G255" s="3" t="inlineStr">
         <is>
-          <t>conception</t>
+          <t>hybride</t>
         </is>
       </c>
       <c r="H255" s="3" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="I255" s="3" t="inlineStr"/>
@@ -17847,28 +17851,28 @@
         <v>3</v>
       </c>
       <c r="K255" s="3" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="L255" s="3" t="inlineStr">
         <is>
-          <t>contrepartie_comptable, creation_monetaire, reflux_collectif, demurrage, monnaie_comme_registre, hierarchie_monetaire</t>
+          <t>monnaie_comme_registre, hierarchie_monetaire, contrepartie_comptable, devise_cle, seuil_d_activation</t>
         </is>
       </c>
       <c r="M255" s="3" t="inlineStr">
         <is>
-          <t>L1.C07, L1.C29, L10.C06, L10.C07, L11.C01, L11.C02, L11.C11, L11.C13, L11.C23, L21.C01, L21.C02, L19.C04, L16.C04</t>
+          <t>L1.C24, L3.C05, L3.C09, L5.C02, L5.C09, L10.C01, L11.C02, L21.C01</t>
         </is>
       </c>
       <c r="N255" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-21-plomberie-financiere-mondiale/c03-une-operation-de-bout-en-bout.md</t>
+          <t>corpus/livre-21-plomberie-financiere-mondiale/c02-comment-l-unite-circulerait-vraiment.md</t>
         </is>
       </c>
     </row>
     <row r="256">
       <c r="A256" s="2" t="inlineStr">
         <is>
-          <t>L21.C04</t>
+          <t>L21.C03</t>
         </is>
       </c>
       <c r="B256" s="3" t="inlineStr">
@@ -17878,7 +17882,7 @@
       </c>
       <c r="C256" s="3" t="inlineStr">
         <is>
-          <t>Ce que l'émission coûte aux banques qui l'hébergent</t>
+          <t>Une opération de bout en bout, bilan par bilan</t>
         </is>
       </c>
       <c r="D256" s="3" t="inlineStr">
@@ -17898,41 +17902,41 @@
       </c>
       <c r="G256" s="3" t="inlineStr">
         <is>
-          <t>descriptif</t>
+          <t>conception</t>
         </is>
       </c>
       <c r="H256" s="3" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="I256" s="3" t="inlineStr"/>
       <c r="J256" s="3" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="K256" s="3" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="L256" s="3" t="inlineStr">
         <is>
-          <t>contrepartie_comptable, creation_monetaire, hierarchie_monetaire, reflux_collectif, demurrage</t>
+          <t>contrepartie_comptable, creation_monetaire, reflux_collectif, demurrage, monnaie_comme_registre, hierarchie_monetaire</t>
         </is>
       </c>
       <c r="M256" s="3" t="inlineStr">
         <is>
-          <t>L1.C07, L10.C01, L11.C02, L11.C07, L11.C09, L11.C11, L11.C23, L21.C02, L21.C03</t>
+          <t>L1.C07, L1.C29, L10.C06, L10.C07, L11.C01, L11.C02, L11.C11, L11.C13, L11.C23, L21.C01, L21.C02, L19.C04, L16.C04</t>
         </is>
       </c>
       <c r="N256" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-21-plomberie-financiere-mondiale/c04-ce-que-l-emission-coute-aux-banques-qui-l-hebergent.md</t>
+          <t>corpus/livre-21-plomberie-financiere-mondiale/c03-une-operation-de-bout-en-bout.md</t>
         </is>
       </c>
     </row>
     <row r="257">
       <c r="A257" s="2" t="inlineStr">
         <is>
-          <t>L21.C05</t>
+          <t>L21.C04</t>
         </is>
       </c>
       <c r="B257" s="3" t="inlineStr">
@@ -17942,7 +17946,7 @@
       </c>
       <c r="C257" s="3" t="inlineStr">
         <is>
-          <t>La première infrastructure ouverte, et ce qu'elle renverse</t>
+          <t>Ce que l'émission coûte aux banques qui l'hébergent</t>
         </is>
       </c>
       <c r="D257" s="3" t="inlineStr">
@@ -17962,7 +17966,7 @@
       </c>
       <c r="G257" s="3" t="inlineStr">
         <is>
-          <t>hybride</t>
+          <t>descriptif</t>
         </is>
       </c>
       <c r="H257" s="3" t="inlineStr">
@@ -17972,31 +17976,31 @@
       </c>
       <c r="I257" s="3" t="inlineStr"/>
       <c r="J257" s="3" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K257" s="3" t="n">
         <v>4</v>
       </c>
       <c r="L257" s="3" t="inlineStr">
         <is>
-          <t>seuil_d_activation, hierarchie_monetaire, monnaie_comme_registre, devise_cle, demurrage, contrepartie_comptable</t>
+          <t>contrepartie_comptable, creation_monetaire, hierarchie_monetaire, reflux_collectif, demurrage</t>
         </is>
       </c>
       <c r="M257" s="3" t="inlineStr">
         <is>
-          <t>L3.C09, L5.C02, L5.C09, L11.C01, L11.C02, L11.C07, L21.C01, L21.C02, L21.C03, L21.C04</t>
+          <t>L1.C07, L10.C01, L11.C02, L11.C07, L11.C09, L11.C11, L11.C23, L21.C02, L21.C03</t>
         </is>
       </c>
       <c r="N257" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-21-plomberie-financiere-mondiale/c05-la-premiere-infrastructure-ouverte-et-ce-qu-elle-renverse.md</t>
+          <t>corpus/livre-21-plomberie-financiere-mondiale/c04-ce-que-l-emission-coute-aux-banques-qui-l-hebergent.md</t>
         </is>
       </c>
     </row>
     <row r="258">
       <c r="A258" s="2" t="inlineStr">
         <is>
-          <t>L21.C06</t>
+          <t>L21.C05</t>
         </is>
       </c>
       <c r="B258" s="3" t="inlineStr">
@@ -18006,7 +18010,7 @@
       </c>
       <c r="C258" s="3" t="inlineStr">
         <is>
-          <t>La jambe qui reste, et ce qu'il faut pour la protéger</t>
+          <t>La première infrastructure ouverte, et ce qu'elle renverse</t>
         </is>
       </c>
       <c r="D258" s="3" t="inlineStr">
@@ -18043,24 +18047,24 @@
       </c>
       <c r="L258" s="3" t="inlineStr">
         <is>
-          <t>contrepartie_comptable, hierarchie_monetaire, monnaie_comme_registre, seuil_d_activation</t>
+          <t>seuil_d_activation, hierarchie_monetaire, monnaie_comme_registre, devise_cle, demurrage, contrepartie_comptable</t>
         </is>
       </c>
       <c r="M258" s="3" t="inlineStr">
         <is>
-          <t>L5.C02, L11.C02, L11.C11, L20.C02, L21.C02, L21.C03, L21.C05</t>
+          <t>L3.C09, L5.C02, L5.C09, L11.C01, L11.C02, L11.C07, L21.C01, L21.C02, L21.C03, L21.C04</t>
         </is>
       </c>
       <c r="N258" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-21-plomberie-financiere-mondiale/c06-la-jambe-qui-reste-et-ce-qu-il-faut-pour-la-proteger.md</t>
+          <t>corpus/livre-21-plomberie-financiere-mondiale/c05-la-premiere-infrastructure-ouverte-et-ce-qu-elle-renverse.md</t>
         </is>
       </c>
     </row>
     <row r="259">
       <c r="A259" s="2" t="inlineStr">
         <is>
-          <t>L21.C07</t>
+          <t>L21.C06</t>
         </is>
       </c>
       <c r="B259" s="3" t="inlineStr">
@@ -18070,7 +18074,7 @@
       </c>
       <c r="C259" s="3" t="inlineStr">
         <is>
-          <t>Portée de la tranche</t>
+          <t>La jambe qui reste, et ce qu'il faut pour la protéger</t>
         </is>
       </c>
       <c r="D259" s="3" t="inlineStr">
@@ -18090,7 +18094,7 @@
       </c>
       <c r="G259" s="3" t="inlineStr">
         <is>
-          <t>descriptif</t>
+          <t>hybride</t>
         </is>
       </c>
       <c r="H259" s="3" t="inlineStr">
@@ -18100,41 +18104,41 @@
       </c>
       <c r="I259" s="3" t="inlineStr"/>
       <c r="J259" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K259" s="3" t="n">
         <v>4</v>
       </c>
       <c r="L259" s="3" t="inlineStr">
         <is>
-          <t>seuil_d_activation, contrepartie_comptable, hierarchie_monetaire, monnaie_comme_registre</t>
+          <t>contrepartie_comptable, hierarchie_monetaire, monnaie_comme_registre, seuil_d_activation</t>
         </is>
       </c>
       <c r="M259" s="3" t="inlineStr">
         <is>
-          <t>L5.C02, L10.C06, L11.C01, L11.C02, L20.C01, L21.C01, L21.C02, L21.C03, L21.C04, L21.C05, L21.C06</t>
+          <t>L5.C02, L11.C02, L11.C11, L20.C02, L21.C02, L21.C03, L21.C05</t>
         </is>
       </c>
       <c r="N259" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-21-plomberie-financiere-mondiale/c07-portee-de-la-tranche.md</t>
+          <t>corpus/livre-21-plomberie-financiere-mondiale/c06-la-jambe-qui-reste-et-ce-qu-il-faut-pour-la-proteger.md</t>
         </is>
       </c>
     </row>
     <row r="260">
       <c r="A260" s="2" t="inlineStr">
         <is>
-          <t>L22.C01</t>
+          <t>L21.C07</t>
         </is>
       </c>
       <c r="B260" s="3" t="inlineStr">
         <is>
-          <t>L22</t>
+          <t>L21</t>
         </is>
       </c>
       <c r="C260" s="3" t="inlineStr">
         <is>
-          <t>Ce que ce livre doit établir</t>
+          <t>Portée de la tranche</t>
         </is>
       </c>
       <c r="D260" s="3" t="inlineStr">
@@ -18164,31 +18168,31 @@
       </c>
       <c r="I260" s="3" t="inlineStr"/>
       <c r="J260" s="3" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K260" s="3" t="n">
         <v>4</v>
       </c>
       <c r="L260" s="3" t="inlineStr">
         <is>
-          <t>architecture_invisible, systeme_monetaire_et_financier, reflux_collectif, reflux_transactionnel, hierarchie_monetaire, monnaie_comme_registre</t>
+          <t>seuil_d_activation, contrepartie_comptable, hierarchie_monetaire, monnaie_comme_registre</t>
         </is>
       </c>
       <c r="M260" s="3" t="inlineStr">
         <is>
-          <t>L1.C09, L1.C19, L5.C09, L11.C02, L11.C05, L11.C09, L11.C27, L21.C03, L21.C04</t>
+          <t>L5.C02, L10.C06, L11.C01, L11.C02, L20.C01, L21.C01, L21.C02, L21.C03, L21.C04, L21.C05, L21.C06</t>
         </is>
       </c>
       <c r="N260" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-22-finance-non-bancaire/c01-ce-que-ce-livre-doit-etablir.md</t>
+          <t>corpus/livre-21-plomberie-financiere-mondiale/c07-portee-de-la-tranche.md</t>
         </is>
       </c>
     </row>
     <row r="261">
       <c r="A261" s="2" t="inlineStr">
         <is>
-          <t>L22.C02</t>
+          <t>L22.C01</t>
         </is>
       </c>
       <c r="B261" s="3" t="inlineStr">
@@ -18198,7 +18202,7 @@
       </c>
       <c r="C261" s="3" t="inlineStr">
         <is>
-          <t>Où va la monnaie émise, et pourquoi le reflux ne l'y suit pas</t>
+          <t>Ce que ce livre doit établir</t>
         </is>
       </c>
       <c r="D261" s="3" t="inlineStr">
@@ -18218,41 +18222,41 @@
       </c>
       <c r="G261" s="3" t="inlineStr">
         <is>
-          <t>conception</t>
+          <t>descriptif</t>
         </is>
       </c>
       <c r="H261" s="3" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="I261" s="3" t="inlineStr"/>
       <c r="J261" s="3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K261" s="3" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L261" s="3" t="inlineStr">
         <is>
-          <t>reflux_transactionnel, reflux_collectif, demurrage, monnaie_endogene, architecture_invisible, hierarchie_monetaire</t>
+          <t>architecture_invisible, systeme_monetaire_et_financier, reflux_collectif, reflux_transactionnel, hierarchie_monetaire, monnaie_comme_registre</t>
         </is>
       </c>
       <c r="M261" s="3" t="inlineStr">
         <is>
-          <t>L1.C19, L5.C09, L11.C02, L11.C05, L11.C09, L11.C27, L21.C03, L22.C01, L23.C04, L26.C04</t>
+          <t>L1.C09, L1.C19, L5.C09, L11.C02, L11.C05, L11.C09, L11.C27, L21.C03, L21.C04</t>
         </is>
       </c>
       <c r="N261" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-22-finance-non-bancaire/c02-ou-va-la-monnaie-emise.md</t>
+          <t>corpus/livre-22-finance-non-bancaire/c01-ce-que-ce-livre-doit-etablir.md</t>
         </is>
       </c>
     </row>
     <row r="262">
       <c r="A262" s="2" t="inlineStr">
         <is>
-          <t>L22.C03</t>
+          <t>L22.C02</t>
         </is>
       </c>
       <c r="B262" s="3" t="inlineStr">
@@ -18262,7 +18266,7 @@
       </c>
       <c r="C262" s="3" t="inlineStr">
         <is>
-          <t>Le barème existe déjà, et il a trois pièces que le corpus n'a pas</t>
+          <t>Où va la monnaie émise, et pourquoi le reflux ne l'y suit pas</t>
         </is>
       </c>
       <c r="D262" s="3" t="inlineStr">
@@ -18282,41 +18286,41 @@
       </c>
       <c r="G262" s="3" t="inlineStr">
         <is>
-          <t>hybride</t>
+          <t>conception</t>
         </is>
       </c>
       <c r="H262" s="3" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="I262" s="3" t="inlineStr"/>
       <c r="J262" s="3" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K262" s="3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L262" s="3" t="inlineStr">
         <is>
-          <t>qualification_regenerative, bareme, additionnalite, indicateur_de_progres, communs, plafond_ecologique</t>
+          <t>reflux_transactionnel, reflux_collectif, demurrage, monnaie_endogene, architecture_invisible, hierarchie_monetaire</t>
         </is>
       </c>
       <c r="M262" s="3" t="inlineStr">
         <is>
-          <t>L11.C13, L11.C11, L11.C25, L12.C01, L18.C06, L22.C01, L25.C01</t>
+          <t>L1.C19, L5.C09, L11.C02, L11.C05, L11.C09, L11.C27, L21.C03, L22.C01, L23.C04, L26.C04</t>
         </is>
       </c>
       <c r="N262" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-22-finance-non-bancaire/c03-le-bareme-existe-deja.md</t>
+          <t>corpus/livre-22-finance-non-bancaire/c02-ou-va-la-monnaie-emise.md</t>
         </is>
       </c>
     </row>
     <row r="263">
       <c r="A263" s="2" t="inlineStr">
         <is>
-          <t>L22.C04</t>
+          <t>L22.C03</t>
         </is>
       </c>
       <c r="B263" s="3" t="inlineStr">
@@ -18326,7 +18330,7 @@
       </c>
       <c r="C263" s="3" t="inlineStr">
         <is>
-          <t>Les critères réels ne mesurent pas, ils certifient</t>
+          <t>Le barème existe déjà, et il a trois pièces que le corpus n'a pas</t>
         </is>
       </c>
       <c r="D263" s="3" t="inlineStr">
@@ -18351,7 +18355,7 @@
       </c>
       <c r="H263" s="3" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="I263" s="3" t="inlineStr"/>
@@ -18359,28 +18363,28 @@
         <v>4</v>
       </c>
       <c r="K263" s="3" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L263" s="3" t="inlineStr">
         <is>
-          <t>qualification_regenerative, bareme, additionnalite, communs, valorisation_des_communs, indicateur_de_progres</t>
+          <t>qualification_regenerative, bareme, additionnalite, indicateur_de_progres, communs, plafond_ecologique</t>
         </is>
       </c>
       <c r="M263" s="3" t="inlineStr">
         <is>
-          <t>L6.C06, L11.C13, L11.C16, L11.C25, L13.C01, L14.C01, L18.C06, L22.C03</t>
+          <t>L11.C13, L11.C11, L11.C25, L12.C01, L18.C06, L22.C01, L25.C01</t>
         </is>
       </c>
       <c r="N263" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-22-finance-non-bancaire/c04-les-criteres-reels-ne-mesurent-pas.md</t>
+          <t>corpus/livre-22-finance-non-bancaire/c03-le-bareme-existe-deja.md</t>
         </is>
       </c>
     </row>
     <row r="264">
       <c r="A264" s="2" t="inlineStr">
         <is>
-          <t>L22.C05</t>
+          <t>L22.C04</t>
         </is>
       </c>
       <c r="B264" s="3" t="inlineStr">
@@ -18390,7 +18394,7 @@
       </c>
       <c r="C264" s="3" t="inlineStr">
         <is>
-          <t>L'épargne retraite, et le dilemme du troisième instrument</t>
+          <t>Les critères réels ne mesurent pas, ils certifient</t>
         </is>
       </c>
       <c r="D264" s="3" t="inlineStr">
@@ -18415,36 +18419,36 @@
       </c>
       <c r="H264" s="3" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="I264" s="3" t="inlineStr"/>
       <c r="J264" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K264" s="3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L264" s="3" t="inlineStr">
         <is>
-          <t>reflux_collectif, demurrage, essentiel_insolvable, plancher_social, solvabilite_anticipee, architecture_invisible</t>
+          <t>qualification_regenerative, bareme, additionnalite, communs, valorisation_des_communs, indicateur_de_progres</t>
         </is>
       </c>
       <c r="M264" s="3" t="inlineStr">
         <is>
-          <t>L1.C15, L11.C07, L11.C09, L11.C18, L22.C01, L22.C02, L25.C01</t>
+          <t>L6.C06, L11.C13, L11.C16, L11.C25, L13.C01, L14.C01, L18.C06, L22.C03</t>
         </is>
       </c>
       <c r="N264" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-22-finance-non-bancaire/c05-l-epargne-retraite-et-le-dilemme-du-troisieme-instrument.md</t>
+          <t>corpus/livre-22-finance-non-bancaire/c04-les-criteres-reels-ne-mesurent-pas.md</t>
         </is>
       </c>
     </row>
     <row r="265">
       <c r="A265" s="2" t="inlineStr">
         <is>
-          <t>L22.C06</t>
+          <t>L22.C05</t>
         </is>
       </c>
       <c r="B265" s="3" t="inlineStr">
@@ -18454,7 +18458,7 @@
       </c>
       <c r="C265" s="3" t="inlineStr">
         <is>
-          <t>Qui décide, quand personne ne décide</t>
+          <t>L'épargne retraite, et le dilemme du troisième instrument</t>
         </is>
       </c>
       <c r="D265" s="3" t="inlineStr">
@@ -18484,31 +18488,31 @@
       </c>
       <c r="I265" s="3" t="inlineStr"/>
       <c r="J265" s="3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K265" s="3" t="n">
         <v>4</v>
       </c>
       <c r="L265" s="3" t="inlineStr">
         <is>
-          <t>architecture_invisible, indicateur_de_progres, qualification_regenerative, essentiel_insolvable, fenetre_de_reforme, regle_contre_discretion</t>
+          <t>reflux_collectif, demurrage, essentiel_insolvable, plancher_social, solvabilite_anticipee, architecture_invisible</t>
         </is>
       </c>
       <c r="M265" s="3" t="inlineStr">
         <is>
-          <t>L1.C15, L5.C09, L11.C13, L14.C01, L22.C01, L22.C02, L22.C03, L22.C05</t>
+          <t>L1.C15, L11.C07, L11.C09, L11.C18, L22.C01, L22.C02, L25.C01</t>
         </is>
       </c>
       <c r="N265" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-22-finance-non-bancaire/c06-qui-decide-quand-personne-ne-decide.md</t>
+          <t>corpus/livre-22-finance-non-bancaire/c05-l-epargne-retraite-et-le-dilemme-du-troisieme-instrument.md</t>
         </is>
       </c>
     </row>
     <row r="266">
       <c r="A266" s="2" t="inlineStr">
         <is>
-          <t>L22.C07</t>
+          <t>L22.C06</t>
         </is>
       </c>
       <c r="B266" s="3" t="inlineStr">
@@ -18518,7 +18522,7 @@
       </c>
       <c r="C266" s="3" t="inlineStr">
         <is>
-          <t>Portée de la tranche</t>
+          <t>Qui décide, quand personne ne décide</t>
         </is>
       </c>
       <c r="D266" s="3" t="inlineStr">
@@ -18538,7 +18542,7 @@
       </c>
       <c r="G266" s="3" t="inlineStr">
         <is>
-          <t>descriptif</t>
+          <t>hybride</t>
         </is>
       </c>
       <c r="H266" s="3" t="inlineStr">
@@ -18548,41 +18552,41 @@
       </c>
       <c r="I266" s="3" t="inlineStr"/>
       <c r="J266" s="3" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K266" s="3" t="n">
         <v>4</v>
       </c>
       <c r="L266" s="3" t="inlineStr">
         <is>
-          <t>architecture_invisible, reflux_transactionnel, qualification_regenerative, bareme, essentiel_insolvable</t>
+          <t>architecture_invisible, indicateur_de_progres, qualification_regenerative, essentiel_insolvable, fenetre_de_reforme, regle_contre_discretion</t>
         </is>
       </c>
       <c r="M266" s="3" t="inlineStr">
         <is>
-          <t>L1.C15, L5.C09, L11.C02, L11.C13, L11.C18, L22.C01, L22.C02, L22.C03, L22.C04, L22.C05, L22.C06</t>
+          <t>L1.C15, L5.C09, L11.C13, L14.C01, L22.C01, L22.C02, L22.C03, L22.C05</t>
         </is>
       </c>
       <c r="N266" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-22-finance-non-bancaire/c07-portee-de-la-tranche.md</t>
+          <t>corpus/livre-22-finance-non-bancaire/c06-qui-decide-quand-personne-ne-decide.md</t>
         </is>
       </c>
     </row>
     <row r="267">
       <c r="A267" s="2" t="inlineStr">
         <is>
-          <t>L23.C01</t>
+          <t>L22.C07</t>
         </is>
       </c>
       <c r="B267" s="3" t="inlineStr">
         <is>
-          <t>L23</t>
+          <t>L22</t>
         </is>
       </c>
       <c r="C267" s="3" t="inlineStr">
         <is>
-          <t>Ce que ce livre doit établir</t>
+          <t>Portée de la tranche</t>
         </is>
       </c>
       <c r="D267" s="3" t="inlineStr">
@@ -18602,7 +18606,7 @@
       </c>
       <c r="G267" s="3" t="inlineStr">
         <is>
-          <t>conception</t>
+          <t>descriptif</t>
         </is>
       </c>
       <c r="H267" s="3" t="inlineStr">
@@ -18612,31 +18616,31 @@
       </c>
       <c r="I267" s="3" t="inlineStr"/>
       <c r="J267" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="K267" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="K267" s="3" t="n">
-        <v>3</v>
-      </c>
       <c r="L267" s="3" t="inlineStr">
         <is>
-          <t>bareme, reflux_transactionnel, externalisation, essentiel_insolvable, polycentricite, regle_contre_discretion</t>
+          <t>architecture_invisible, reflux_transactionnel, qualification_regenerative, bareme, essentiel_insolvable</t>
         </is>
       </c>
       <c r="M267" s="3" t="inlineStr">
         <is>
-          <t>L1.C15, L5.C07, L10.C06, L11.C05, L11.C09, L11.C21, L11.C24, L18.C09, L20.C02, L20.C20</t>
+          <t>L1.C15, L5.C09, L11.C02, L11.C13, L11.C18, L22.C01, L22.C02, L22.C03, L22.C04, L22.C05, L22.C06</t>
         </is>
       </c>
       <c r="N267" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-23-fiscalite-mondiale-et-opacite/c01-ce-que-ce-livre-doit-etablir.md</t>
+          <t>corpus/livre-22-finance-non-bancaire/c07-portee-de-la-tranche.md</t>
         </is>
       </c>
     </row>
     <row r="268">
       <c r="A268" s="2" t="inlineStr">
         <is>
-          <t>L23.C02</t>
+          <t>L23.C01</t>
         </is>
       </c>
       <c r="B268" s="3" t="inlineStr">
@@ -18646,7 +18650,7 @@
       </c>
       <c r="C268" s="3" t="inlineStr">
         <is>
-          <t>La compétence que la convention ne crée pas, et le vote qu'elle a gagné</t>
+          <t>Ce que ce livre doit établir</t>
         </is>
       </c>
       <c r="D268" s="3" t="inlineStr">
@@ -18666,7 +18670,7 @@
       </c>
       <c r="G268" s="3" t="inlineStr">
         <is>
-          <t>hybride</t>
+          <t>conception</t>
         </is>
       </c>
       <c r="H268" s="3" t="inlineStr">
@@ -18683,24 +18687,24 @@
       </c>
       <c r="L268" s="3" t="inlineStr">
         <is>
-          <t>polycentricite, bareme, reflux_transactionnel, seuil_d_activation, regle_contre_discretion, externalisation</t>
+          <t>bareme, reflux_transactionnel, externalisation, essentiel_insolvable, polycentricite, regle_contre_discretion</t>
         </is>
       </c>
       <c r="M268" s="3" t="inlineStr">
         <is>
-          <t>L1.C25, L5.C04, L10.C06, L11.C21, L20.C02, L20.C20, L23.C01</t>
+          <t>L1.C15, L5.C07, L10.C06, L11.C05, L11.C09, L11.C21, L11.C24, L18.C09, L20.C02, L20.C20</t>
         </is>
       </c>
       <c r="N268" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-23-fiscalite-mondiale-et-opacite/c02-la-competence-que-la-convention-ne-cree-pas.md</t>
+          <t>corpus/livre-23-fiscalite-mondiale-et-opacite/c01-ce-que-ce-livre-doit-etablir.md</t>
         </is>
       </c>
     </row>
     <row r="269">
       <c r="A269" s="2" t="inlineStr">
         <is>
-          <t>L23.C03</t>
+          <t>L23.C02</t>
         </is>
       </c>
       <c r="B269" s="3" t="inlineStr">
@@ -18710,7 +18714,7 @@
       </c>
       <c r="C269" s="3" t="inlineStr">
         <is>
-          <t>F8 appliqué à une négociation en cours, et le résultat n'est pas le désarmement</t>
+          <t>La compétence que la convention ne crée pas, et le vote qu'elle a gagné</t>
         </is>
       </c>
       <c r="D269" s="3" t="inlineStr">
@@ -18747,24 +18751,24 @@
       </c>
       <c r="L269" s="3" t="inlineStr">
         <is>
-          <t>regle_contre_discretion, polycentricite, seuil_d_activation, bareme, externalisation</t>
+          <t>polycentricite, bareme, reflux_transactionnel, seuil_d_activation, regle_contre_discretion, externalisation</t>
         </is>
       </c>
       <c r="M269" s="3" t="inlineStr">
         <is>
-          <t>L5.C04, L6.C09, L11.C21, L20.C02, L20.C13, L23.C01, L23.C02</t>
+          <t>L1.C25, L5.C04, L10.C06, L11.C21, L20.C02, L20.C20, L23.C01</t>
         </is>
       </c>
       <c r="N269" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-23-fiscalite-mondiale-et-opacite/c03-f8-applique-a-une-negociation-en-cours.md</t>
+          <t>corpus/livre-23-fiscalite-mondiale-et-opacite/c02-la-competence-que-la-convention-ne-cree-pas.md</t>
         </is>
       </c>
     </row>
     <row r="270">
       <c r="A270" s="2" t="inlineStr">
         <is>
-          <t>L23.C04</t>
+          <t>L23.C03</t>
         </is>
       </c>
       <c r="B270" s="3" t="inlineStr">
@@ -18774,7 +18778,7 @@
       </c>
       <c r="C270" s="3" t="inlineStr">
         <is>
-          <t>La transparence que le corpus supposait a été invalidée</t>
+          <t>F8 appliqué à une négociation en cours, et le résultat n'est pas le désarmement</t>
         </is>
       </c>
       <c r="D270" s="3" t="inlineStr">
@@ -18804,31 +18808,31 @@
       </c>
       <c r="I270" s="3" t="inlineStr"/>
       <c r="J270" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K270" s="3" t="n">
         <v>3</v>
       </c>
       <c r="L270" s="3" t="inlineStr">
         <is>
-          <t>regle_contre_discretion, externalisation, bareme, polycentricite, architecture_invisible</t>
+          <t>regle_contre_discretion, polycentricite, seuil_d_activation, bareme, externalisation</t>
         </is>
       </c>
       <c r="M270" s="3" t="inlineStr">
         <is>
-          <t>L6.C09, L11.C13, L11.C25, L20.C20, L23.C01, L23.C02, L23.C03</t>
+          <t>L5.C04, L6.C09, L11.C21, L20.C02, L20.C13, L23.C01, L23.C02</t>
         </is>
       </c>
       <c r="N270" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-23-fiscalite-mondiale-et-opacite/c04-la-transparence-que-le-corpus-supposait-a-ete-invalidee.md</t>
+          <t>corpus/livre-23-fiscalite-mondiale-et-opacite/c03-f8-applique-a-une-negociation-en-cours.md</t>
         </is>
       </c>
     </row>
     <row r="271">
       <c r="A271" s="2" t="inlineStr">
         <is>
-          <t>L23.C05</t>
+          <t>L23.C04</t>
         </is>
       </c>
       <c r="B271" s="3" t="inlineStr">
@@ -18838,7 +18842,7 @@
       </c>
       <c r="C271" s="3" t="inlineStr">
         <is>
-          <t>Intéresser le percepteur, et ce que le taux révèle</t>
+          <t>La transparence que le corpus supposait a été invalidée</t>
         </is>
       </c>
       <c r="D271" s="3" t="inlineStr">
@@ -18875,24 +18879,24 @@
       </c>
       <c r="L271" s="3" t="inlineStr">
         <is>
-          <t>bareme, reflux_transactionnel, regle_contre_discretion, polycentricite, seuil_d_activation</t>
+          <t>regle_contre_discretion, externalisation, bareme, polycentricite, architecture_invisible</t>
         </is>
       </c>
       <c r="M271" s="3" t="inlineStr">
         <is>
-          <t>L11.C21, L11.C24, L18.C09, L20.C20, L23.C01, L23.C02, L23.C03</t>
+          <t>L6.C09, L11.C13, L11.C25, L20.C20, L23.C01, L23.C02, L23.C03</t>
         </is>
       </c>
       <c r="N271" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-23-fiscalite-mondiale-et-opacite/c05-interesser-le-percepteur-et-ce-que-le-taux-revele.md</t>
+          <t>corpus/livre-23-fiscalite-mondiale-et-opacite/c04-la-transparence-que-le-corpus-supposait-a-ete-invalidee.md</t>
         </is>
       </c>
     </row>
     <row r="272">
       <c r="A272" s="2" t="inlineStr">
         <is>
-          <t>L23.C06</t>
+          <t>L23.C05</t>
         </is>
       </c>
       <c r="B272" s="3" t="inlineStr">
@@ -18902,7 +18906,7 @@
       </c>
       <c r="C272" s="3" t="inlineStr">
         <is>
-          <t>L'arbre appliqué à la fonte, et il ne reste que deux branches</t>
+          <t>Intéresser le percepteur, et ce que le taux révèle</t>
         </is>
       </c>
       <c r="D272" s="3" t="inlineStr">
@@ -18922,7 +18926,7 @@
       </c>
       <c r="G272" s="3" t="inlineStr">
         <is>
-          <t>conception</t>
+          <t>hybride</t>
         </is>
       </c>
       <c r="H272" s="3" t="inlineStr">
@@ -18932,31 +18936,31 @@
       </c>
       <c r="I272" s="3" t="inlineStr"/>
       <c r="J272" s="3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K272" s="3" t="n">
         <v>3</v>
       </c>
       <c r="L272" s="3" t="inlineStr">
         <is>
-          <t>bareme, reflux_transactionnel, monnaie_fondante, demurrage, regle_contre_discretion, essentiel_insolvable</t>
+          <t>bareme, reflux_transactionnel, regle_contre_discretion, polycentricite, seuil_d_activation</t>
         </is>
       </c>
       <c r="M272" s="3" t="inlineStr">
         <is>
-          <t>L10.C06, L11.C05, L11.C09, L11.C21, L11.C24, L18.C09, L20.C02, L23.C01, L23.C02, L23.C03, L23.C04, L23.C05</t>
+          <t>L11.C21, L11.C24, L18.C09, L20.C20, L23.C01, L23.C02, L23.C03</t>
         </is>
       </c>
       <c r="N272" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-23-fiscalite-mondiale-et-opacite/c06-l-arbre-applique-a-la-fonte.md</t>
+          <t>corpus/livre-23-fiscalite-mondiale-et-opacite/c05-interesser-le-percepteur-et-ce-que-le-taux-revele.md</t>
         </is>
       </c>
     </row>
     <row r="273">
       <c r="A273" s="2" t="inlineStr">
         <is>
-          <t>L23.C07</t>
+          <t>L23.C06</t>
         </is>
       </c>
       <c r="B273" s="3" t="inlineStr">
@@ -18966,7 +18970,7 @@
       </c>
       <c r="C273" s="3" t="inlineStr">
         <is>
-          <t>Portée de la tranche, et la moitié qui n'est pas commencée</t>
+          <t>L'arbre appliqué à la fonte, et il ne reste que deux branches</t>
         </is>
       </c>
       <c r="D273" s="3" t="inlineStr">
@@ -18996,41 +19000,41 @@
       </c>
       <c r="I273" s="3" t="inlineStr"/>
       <c r="J273" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K273" s="3" t="n">
         <v>3</v>
       </c>
       <c r="L273" s="3" t="inlineStr">
         <is>
-          <t>bareme, reflux_transactionnel, externalisation, regle_contre_discretion, polycentricite, essentiel_insolvable</t>
+          <t>bareme, reflux_transactionnel, monnaie_fondante, demurrage, regle_contre_discretion, essentiel_insolvable</t>
         </is>
       </c>
       <c r="M273" s="3" t="inlineStr">
         <is>
-          <t>L10.C06, L11.C05, L11.C21, L11.C25, L18.C09, L20.C20, L23.C01, L23.C02, L23.C03, L23.C04, L23.C05, L23.C06</t>
+          <t>L10.C06, L11.C05, L11.C09, L11.C21, L11.C24, L18.C09, L20.C02, L23.C01, L23.C02, L23.C03, L23.C04, L23.C05</t>
         </is>
       </c>
       <c r="N273" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-23-fiscalite-mondiale-et-opacite/c07-portee-de-la-tranche.md</t>
+          <t>corpus/livre-23-fiscalite-mondiale-et-opacite/c06-l-arbre-applique-a-la-fonte.md</t>
         </is>
       </c>
     </row>
     <row r="274">
       <c r="A274" s="2" t="inlineStr">
         <is>
-          <t>L24.C01</t>
+          <t>L23.C07</t>
         </is>
       </c>
       <c r="B274" s="3" t="inlineStr">
         <is>
-          <t>L24</t>
+          <t>L23</t>
         </is>
       </c>
       <c r="C274" s="3" t="inlineStr">
         <is>
-          <t>Ce que ce livre doit établir</t>
+          <t>Portée de la tranche, et la moitié qui n'est pas commencée</t>
         </is>
       </c>
       <c r="D274" s="3" t="inlineStr">
@@ -19050,7 +19054,7 @@
       </c>
       <c r="G274" s="3" t="inlineStr">
         <is>
-          <t>descriptif</t>
+          <t>conception</t>
         </is>
       </c>
       <c r="H274" s="3" t="inlineStr">
@@ -19060,31 +19064,31 @@
       </c>
       <c r="I274" s="3" t="inlineStr"/>
       <c r="J274" s="3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K274" s="3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L274" s="3" t="inlineStr">
         <is>
-          <t>limites_planetaires, plafond_ecologique, entropie, decouplage, degeneratif, qualification_regenerative, essentiel_insolvable</t>
+          <t>bareme, reflux_transactionnel, externalisation, regle_contre_discretion, polycentricite, essentiel_insolvable</t>
         </is>
       </c>
       <c r="M274" s="3" t="inlineStr">
         <is>
-          <t>L1.C15, L5.C08, L11.C13, L18.C01, L18.C04, L22.C04, L26.C01</t>
+          <t>L10.C06, L11.C05, L11.C21, L11.C25, L18.C09, L20.C20, L23.C01, L23.C02, L23.C03, L23.C04, L23.C05, L23.C06</t>
         </is>
       </c>
       <c r="N274" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-24-conditions-materielles-de-la-vie/c01-ce-que-ce-livre-doit-etablir.md</t>
+          <t>corpus/livre-23-fiscalite-mondiale-et-opacite/c07-portee-de-la-tranche.md</t>
         </is>
       </c>
     </row>
     <row r="275">
       <c r="A275" s="2" t="inlineStr">
         <is>
-          <t>L24.C02</t>
+          <t>L24.C01</t>
         </is>
       </c>
       <c r="B275" s="3" t="inlineStr">
@@ -19094,7 +19098,7 @@
       </c>
       <c r="C275" s="3" t="inlineStr">
         <is>
-          <t>Le seuil juste est plus strict que le seuil sûr</t>
+          <t>Ce que ce livre doit établir</t>
         </is>
       </c>
       <c r="D275" s="3" t="inlineStr">
@@ -19114,7 +19118,7 @@
       </c>
       <c r="G275" s="3" t="inlineStr">
         <is>
-          <t>hybride</t>
+          <t>descriptif</t>
         </is>
       </c>
       <c r="H275" s="3" t="inlineStr">
@@ -19131,24 +19135,24 @@
       </c>
       <c r="L275" s="3" t="inlineStr">
         <is>
-          <t>limites_planetaires, plafond_ecologique, plancher_social, dette_ecologique, essentiel_insolvable, qualification_regenerative</t>
+          <t>limites_planetaires, plafond_ecologique, entropie, decouplage, degeneratif, qualification_regenerative, essentiel_insolvable</t>
         </is>
       </c>
       <c r="M275" s="3" t="inlineStr">
         <is>
-          <t>L1.C15, L11.C13, L12.C01, L18.C01, L24.C01, L25.C01</t>
+          <t>L1.C15, L5.C08, L11.C13, L18.C01, L18.C04, L22.C04, L26.C01</t>
         </is>
       </c>
       <c r="N275" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-24-conditions-materielles-de-la-vie/c02-le-seuil-juste-est-plus-strict-que-le-seuil-sur.md</t>
+          <t>corpus/livre-24-conditions-materielles-de-la-vie/c01-ce-que-ce-livre-doit-etablir.md</t>
         </is>
       </c>
     </row>
     <row r="276">
       <c r="A276" s="2" t="inlineStr">
         <is>
-          <t>L24.C03</t>
+          <t>L24.C02</t>
         </is>
       </c>
       <c r="B276" s="3" t="inlineStr">
@@ -19158,7 +19162,7 @@
       </c>
       <c r="C276" s="3" t="inlineStr">
         <is>
-          <t>La matière, et le levier commun que les neuf dimensions n'avaient pas</t>
+          <t>Le seuil juste est plus strict que le seuil sûr</t>
         </is>
       </c>
       <c r="D276" s="3" t="inlineStr">
@@ -19195,24 +19199,24 @@
       </c>
       <c r="L276" s="3" t="inlineStr">
         <is>
-          <t>limites_planetaires, decouplage, effet_rebond, sobriete, entropie, plafond_ecologique, externalisation, degeneratif</t>
+          <t>limites_planetaires, plafond_ecologique, plancher_social, dette_ecologique, essentiel_insolvable, qualification_regenerative</t>
         </is>
       </c>
       <c r="M276" s="3" t="inlineStr">
         <is>
-          <t>L1.C15, L11.C13, L17.C01, L18.C04, L24.C01, L24.C02, L26.C01</t>
+          <t>L1.C15, L11.C13, L12.C01, L18.C01, L24.C01, L25.C01</t>
         </is>
       </c>
       <c r="N276" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-24-conditions-materielles-de-la-vie/c03-la-matiere-et-le-levier-commun.md</t>
+          <t>corpus/livre-24-conditions-materielles-de-la-vie/c02-le-seuil-juste-est-plus-strict-que-le-seuil-sur.md</t>
         </is>
       </c>
     </row>
     <row r="277">
       <c r="A277" s="2" t="inlineStr">
         <is>
-          <t>L24.C04</t>
+          <t>L24.C03</t>
         </is>
       </c>
       <c r="B277" s="3" t="inlineStr">
@@ -19222,7 +19226,7 @@
       </c>
       <c r="C277" s="3" t="inlineStr">
         <is>
-          <t>Un budget mondial n'est pas partageable</t>
+          <t>La matière, et le levier commun que les neuf dimensions n'avaient pas</t>
         </is>
       </c>
       <c r="D277" s="3" t="inlineStr">
@@ -19259,24 +19263,24 @@
       </c>
       <c r="L277" s="3" t="inlineStr">
         <is>
-          <t>limites_planetaires, plafond_ecologique, communs, qualification_regenerative, externalisation, polycentricite</t>
+          <t>limites_planetaires, decouplage, effet_rebond, sobriete, entropie, plafond_ecologique, externalisation, degeneratif</t>
         </is>
       </c>
       <c r="M277" s="3" t="inlineStr">
         <is>
-          <t>L11.C13, L11.C24, L22.C04, L24.C01, L24.C02, L24.C03, L25.C05</t>
+          <t>L1.C15, L11.C13, L17.C01, L18.C04, L24.C01, L24.C02, L26.C01</t>
         </is>
       </c>
       <c r="N277" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-24-conditions-materielles-de-la-vie/c04-un-budget-mondial-n-est-pas-partageable.md</t>
+          <t>corpus/livre-24-conditions-materielles-de-la-vie/c03-la-matiere-et-le-levier-commun.md</t>
         </is>
       </c>
     </row>
     <row r="278">
       <c r="A278" s="2" t="inlineStr">
         <is>
-          <t>L24.C05</t>
+          <t>L24.C04</t>
         </is>
       </c>
       <c r="B278" s="3" t="inlineStr">
@@ -19286,7 +19290,7 @@
       </c>
       <c r="C278" s="3" t="inlineStr">
         <is>
-          <t>Portée de la tranche</t>
+          <t>Un budget mondial n'est pas partageable</t>
         </is>
       </c>
       <c r="D278" s="3" t="inlineStr">
@@ -19306,51 +19310,51 @@
       </c>
       <c r="G278" s="3" t="inlineStr">
         <is>
-          <t>descriptif</t>
+          <t>hybride</t>
         </is>
       </c>
       <c r="H278" s="3" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="I278" s="3" t="inlineStr"/>
       <c r="J278" s="3" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K278" s="3" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L278" s="3" t="inlineStr">
         <is>
-          <t>limites_planetaires, plafond_ecologique, plancher_social, decouplage, qualification_regenerative, entropie</t>
+          <t>limites_planetaires, plafond_ecologique, communs, qualification_regenerative, externalisation, polycentricite</t>
         </is>
       </c>
       <c r="M278" s="3" t="inlineStr">
         <is>
-          <t>L11.C13, L11.C24, L18.C01, L22.C04, L24.C01, L24.C02, L24.C03, L24.C04, L25.C05, L26.C01, L26.C02, L17.C05</t>
+          <t>L11.C13, L11.C24, L22.C04, L24.C01, L24.C02, L24.C03, L25.C05</t>
         </is>
       </c>
       <c r="N278" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-24-conditions-materielles-de-la-vie/c05-portee-de-la-tranche.md</t>
+          <t>corpus/livre-24-conditions-materielles-de-la-vie/c04-un-budget-mondial-n-est-pas-partageable.md</t>
         </is>
       </c>
     </row>
     <row r="279">
       <c r="A279" s="2" t="inlineStr">
         <is>
-          <t>L25.C01</t>
+          <t>L24.C05</t>
         </is>
       </c>
       <c r="B279" s="3" t="inlineStr">
         <is>
-          <t>L25</t>
+          <t>L24</t>
         </is>
       </c>
       <c r="C279" s="3" t="inlineStr">
         <is>
-          <t>Ce que ce livre doit établir</t>
+          <t>Portée de la tranche</t>
         </is>
       </c>
       <c r="D279" s="3" t="inlineStr">
@@ -19375,36 +19379,36 @@
       </c>
       <c r="H279" s="3" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="I279" s="3" t="inlineStr"/>
       <c r="J279" s="3" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K279" s="3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L279" s="3" t="inlineStr">
         <is>
-          <t>plancher_social, plafond_ecologique, essentiel_insolvable, dette_ecologique, communs, solvabilite_anticipee</t>
+          <t>limites_planetaires, plafond_ecologique, plancher_social, decouplage, qualification_regenerative, entropie</t>
         </is>
       </c>
       <c r="M279" s="3" t="inlineStr">
         <is>
-          <t>L1.C15, L11.C09, L11.C18, L12.C01, L24.C01, L24.C02, L24.C03</t>
+          <t>L11.C13, L11.C24, L18.C01, L22.C04, L24.C01, L24.C02, L24.C03, L24.C04, L25.C05, L26.C01, L26.C02, L17.C05</t>
         </is>
       </c>
       <c r="N279" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-25-repartition-et-justice-sociale/c01-ce-que-ce-livre-doit-etablir.md</t>
+          <t>corpus/livre-24-conditions-materielles-de-la-vie/c05-portee-de-la-tranche.md</t>
         </is>
       </c>
     </row>
     <row r="280">
       <c r="A280" s="2" t="inlineStr">
         <is>
-          <t>L25.C02</t>
+          <t>L25.C01</t>
         </is>
       </c>
       <c r="B280" s="3" t="inlineStr">
@@ -19414,7 +19418,7 @@
       </c>
       <c r="C280" s="3" t="inlineStr">
         <is>
-          <t>Le noyau dur, et la charge de la preuve renversée</t>
+          <t>Ce que ce livre doit établir</t>
         </is>
       </c>
       <c r="D280" s="3" t="inlineStr">
@@ -19434,7 +19438,7 @@
       </c>
       <c r="G280" s="3" t="inlineStr">
         <is>
-          <t>hybride</t>
+          <t>descriptif</t>
         </is>
       </c>
       <c r="H280" s="3" t="inlineStr">
@@ -19451,24 +19455,24 @@
       </c>
       <c r="L280" s="3" t="inlineStr">
         <is>
-          <t>plancher_social, essentiel_insolvable, plafond_ecologique, solvabilite_anticipee, regle_contre_discretion</t>
+          <t>plancher_social, plafond_ecologique, essentiel_insolvable, dette_ecologique, communs, solvabilite_anticipee</t>
         </is>
       </c>
       <c r="M280" s="3" t="inlineStr">
         <is>
-          <t>L1.C15, L11.C09, L11.C18, L22.C02, L22.C04, L24.C02, L25.C01</t>
+          <t>L1.C15, L11.C09, L11.C18, L12.C01, L24.C01, L24.C02, L24.C03</t>
         </is>
       </c>
       <c r="N280" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-25-repartition-et-justice-sociale/c02-le-noyau-dur-et-la-charge-de-la-preuve.md</t>
+          <t>corpus/livre-25-repartition-et-justice-sociale/c01-ce-que-ce-livre-doit-etablir.md</t>
         </is>
       </c>
     </row>
     <row r="281">
       <c r="A281" s="2" t="inlineStr">
         <is>
-          <t>L25.C03</t>
+          <t>L25.C02</t>
         </is>
       </c>
       <c r="B281" s="3" t="inlineStr">
@@ -19478,7 +19482,7 @@
       </c>
       <c r="C281" s="3" t="inlineStr">
         <is>
-          <t>Ce que le droit oblige à donner, et ce qu'il refuse de réparer</t>
+          <t>Le noyau dur, et la charge de la preuve renversée</t>
         </is>
       </c>
       <c r="D281" s="3" t="inlineStr">
@@ -19508,31 +19512,31 @@
       </c>
       <c r="I281" s="3" t="inlineStr"/>
       <c r="J281" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K281" s="3" t="n">
         <v>4</v>
       </c>
       <c r="L281" s="3" t="inlineStr">
         <is>
-          <t>dette_ecologique, plancher_social, creation_monetaire, reflux_collectif, essentiel_insolvable, solvabilite_anticipee</t>
+          <t>plancher_social, essentiel_insolvable, plafond_ecologique, solvabilite_anticipee, regle_contre_discretion</t>
         </is>
       </c>
       <c r="M281" s="3" t="inlineStr">
         <is>
-          <t>L1.C20, L11.C01, L20.C01, L24.C02, L25.C01, L25.C02</t>
+          <t>L1.C15, L11.C09, L11.C18, L22.C02, L22.C04, L24.C02, L25.C01</t>
         </is>
       </c>
       <c r="N281" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-25-repartition-et-justice-sociale/c03-ce-que-le-droit-oblige-a-donner.md</t>
+          <t>corpus/livre-25-repartition-et-justice-sociale/c02-le-noyau-dur-et-la-charge-de-la-preuve.md</t>
         </is>
       </c>
     </row>
     <row r="282">
       <c r="A282" s="2" t="inlineStr">
         <is>
-          <t>L25.C04</t>
+          <t>L25.C03</t>
         </is>
       </c>
       <c r="B282" s="3" t="inlineStr">
@@ -19542,7 +19546,7 @@
       </c>
       <c r="C282" s="3" t="inlineStr">
         <is>
-          <t>A34 en droit positif, et le critère que le corpus n'avait pas</t>
+          <t>Ce que le droit oblige à donner, et ce qu'il refuse de réparer</t>
         </is>
       </c>
       <c r="D282" s="3" t="inlineStr">
@@ -19572,31 +19576,31 @@
       </c>
       <c r="I282" s="3" t="inlineStr"/>
       <c r="J282" s="3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K282" s="3" t="n">
         <v>4</v>
       </c>
       <c r="L282" s="3" t="inlineStr">
         <is>
-          <t>plancher_social, bareme, essentiel_insolvable, sobriete, affectation_des_instruments, reflux_transactionnel</t>
+          <t>dette_ecologique, plancher_social, creation_monetaire, reflux_collectif, essentiel_insolvable, solvabilite_anticipee</t>
         </is>
       </c>
       <c r="M282" s="3" t="inlineStr">
         <is>
-          <t>L1.C15, L11.C09, L11.C18, L11.C21, L22.C02, L24.C03, L25.C01, L25.C02</t>
+          <t>L1.C20, L11.C01, L20.C01, L24.C02, L25.C01, L25.C02</t>
         </is>
       </c>
       <c r="N282" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-25-repartition-et-justice-sociale/c04-a34-en-droit-positif.md</t>
+          <t>corpus/livre-25-repartition-et-justice-sociale/c03-ce-que-le-droit-oblige-a-donner.md</t>
         </is>
       </c>
     </row>
     <row r="283">
       <c r="A283" s="2" t="inlineStr">
         <is>
-          <t>L25.C05</t>
+          <t>L25.C04</t>
         </is>
       </c>
       <c r="B283" s="3" t="inlineStr">
@@ -19606,7 +19610,7 @@
       </c>
       <c r="C283" s="3" t="inlineStr">
         <is>
-          <t>Le droit différencie sans calculer</t>
+          <t>A34 en droit positif, et le critère que le corpus n'avait pas</t>
         </is>
       </c>
       <c r="D283" s="3" t="inlineStr">
@@ -19636,31 +19640,31 @@
       </c>
       <c r="I283" s="3" t="inlineStr"/>
       <c r="J283" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K283" s="3" t="n">
         <v>4</v>
       </c>
       <c r="L283" s="3" t="inlineStr">
         <is>
-          <t>dette_ecologique, plancher_social, plafond_ecologique, bareme, indicateur_de_progres, polycentricite</t>
+          <t>plancher_social, bareme, essentiel_insolvable, sobriete, affectation_des_instruments, reflux_transactionnel</t>
         </is>
       </c>
       <c r="M283" s="3" t="inlineStr">
         <is>
-          <t>L11.C13, L22.C04, L22.C06, L24.C01, L24.C02, L25.C01, L25.C02, L25.C03, L25.C04</t>
+          <t>L1.C15, L11.C09, L11.C18, L11.C21, L22.C02, L24.C03, L25.C01, L25.C02</t>
         </is>
       </c>
       <c r="N283" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-25-repartition-et-justice-sociale/c05-le-droit-differencie-sans-calculer.md</t>
+          <t>corpus/livre-25-repartition-et-justice-sociale/c04-a34-en-droit-positif.md</t>
         </is>
       </c>
     </row>
     <row r="284">
       <c r="A284" s="2" t="inlineStr">
         <is>
-          <t>L25.C06</t>
+          <t>L25.C05</t>
         </is>
       </c>
       <c r="B284" s="3" t="inlineStr">
@@ -19670,7 +19674,7 @@
       </c>
       <c r="C284" s="3" t="inlineStr">
         <is>
-          <t>Portée de la tranche</t>
+          <t>Le droit différencie sans calculer</t>
         </is>
       </c>
       <c r="D284" s="3" t="inlineStr">
@@ -19690,7 +19694,7 @@
       </c>
       <c r="G284" s="3" t="inlineStr">
         <is>
-          <t>descriptif</t>
+          <t>hybride</t>
         </is>
       </c>
       <c r="H284" s="3" t="inlineStr">
@@ -19700,41 +19704,41 @@
       </c>
       <c r="I284" s="3" t="inlineStr"/>
       <c r="J284" s="3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K284" s="3" t="n">
         <v>4</v>
       </c>
       <c r="L284" s="3" t="inlineStr">
         <is>
-          <t>plancher_social, plafond_ecologique, dette_ecologique, essentiel_insolvable, bareme</t>
+          <t>dette_ecologique, plancher_social, plafond_ecologique, bareme, indicateur_de_progres, polycentricite</t>
         </is>
       </c>
       <c r="M284" s="3" t="inlineStr">
         <is>
-          <t>L5.C09, L11.C09, L11.C18, L24.C02, L25.C01, L25.C02, L25.C03, L25.C04, L25.C05</t>
+          <t>L11.C13, L22.C04, L22.C06, L24.C01, L24.C02, L25.C01, L25.C02, L25.C03, L25.C04</t>
         </is>
       </c>
       <c r="N284" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-25-repartition-et-justice-sociale/c06-portee-de-la-tranche.md</t>
+          <t>corpus/livre-25-repartition-et-justice-sociale/c05-le-droit-differencie-sans-calculer.md</t>
         </is>
       </c>
     </row>
     <row r="285">
       <c r="A285" s="2" t="inlineStr">
         <is>
-          <t>L26.C01</t>
+          <t>L25.C06</t>
         </is>
       </c>
       <c r="B285" s="3" t="inlineStr">
         <is>
-          <t>L26</t>
+          <t>L25</t>
         </is>
       </c>
       <c r="C285" s="3" t="inlineStr">
         <is>
-          <t>Ce que ce livre doit établir</t>
+          <t>Portée de la tranche</t>
         </is>
       </c>
       <c r="D285" s="3" t="inlineStr">
@@ -19754,41 +19758,41 @@
       </c>
       <c r="G285" s="3" t="inlineStr">
         <is>
-          <t>hybride</t>
+          <t>descriptif</t>
         </is>
       </c>
       <c r="H285" s="3" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="I285" s="3" t="inlineStr"/>
       <c r="J285" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K285" s="3" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="L285" s="3" t="inlineStr">
         <is>
-          <t>entropie, decouplage, effet_rebond, limites_planetaires, sobriete, degeneratif, qualification_regenerative</t>
+          <t>plancher_social, plafond_ecologique, dette_ecologique, essentiel_insolvable, bareme</t>
         </is>
       </c>
       <c r="M285" s="3" t="inlineStr">
         <is>
-          <t>L1.C03, L1.C15, L1.C17, L8.C13, L8.C34, L11.C13, L18.C04, L24.C03, L24.C05, L17.C02, L26.C10</t>
+          <t>L5.C09, L11.C09, L11.C18, L24.C02, L25.C01, L25.C02, L25.C03, L25.C04, L25.C05</t>
         </is>
       </c>
       <c r="N285" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-26-thermodynamique-et-processus-economique/c01-ce-que-ce-livre-doit-etablir.md</t>
+          <t>corpus/livre-25-repartition-et-justice-sociale/c06-portee-de-la-tranche.md</t>
         </is>
       </c>
     </row>
     <row r="286">
       <c r="A286" s="2" t="inlineStr">
         <is>
-          <t>L26.C02</t>
+          <t>L26.C01</t>
         </is>
       </c>
       <c r="B286" s="3" t="inlineStr">
@@ -19798,7 +19802,7 @@
       </c>
       <c r="C286" s="3" t="inlineStr">
         <is>
-          <t>Le stock n'existe pas sous la forme demandée</t>
+          <t>Ce que ce livre doit établir</t>
         </is>
       </c>
       <c r="D286" s="3" t="inlineStr">
@@ -19828,31 +19832,31 @@
       </c>
       <c r="I286" s="3" t="inlineStr"/>
       <c r="J286" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K286" s="3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L286" s="3" t="inlineStr">
         <is>
-          <t>entropie, bareme, limites_planetaires, decouplage, sobriete, fausse_richesse</t>
+          <t>entropie, decouplage, effet_rebond, limites_planetaires, sobriete, degeneratif, qualification_regenerative</t>
         </is>
       </c>
       <c r="M286" s="3" t="inlineStr">
         <is>
-          <t>L1.C15, L11.C13, L11.C24, L18.C04, L22.C04, L24.C03, L24.C05, L26.C01, L17.C02</t>
+          <t>L1.C03, L1.C15, L1.C17, L8.C13, L8.C34, L11.C13, L18.C04, L24.C03, L24.C05, L17.C02, L26.C10</t>
         </is>
       </c>
       <c r="N286" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-26-thermodynamique-et-processus-economique/c02-le-stock-n-existe-pas-sous-la-forme-demandee.md</t>
+          <t>corpus/livre-26-thermodynamique-et-processus-economique/c01-ce-que-ce-livre-doit-etablir.md</t>
         </is>
       </c>
     </row>
     <row r="287">
       <c r="A287" s="2" t="inlineStr">
         <is>
-          <t>L26.C03</t>
+          <t>L26.C02</t>
         </is>
       </c>
       <c r="B287" s="3" t="inlineStr">
@@ -19862,7 +19866,7 @@
       </c>
       <c r="C287" s="3" t="inlineStr">
         <is>
-          <t>La frontière décide du chiffre</t>
+          <t>Le stock n'existe pas sous la forme demandée</t>
         </is>
       </c>
       <c r="D287" s="3" t="inlineStr">
@@ -19892,31 +19896,31 @@
       </c>
       <c r="I287" s="3" t="inlineStr"/>
       <c r="J287" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K287" s="3" t="n">
         <v>5</v>
       </c>
       <c r="L287" s="3" t="inlineStr">
         <is>
-          <t>entropie, decouplage, sobriete, limites_planetaires, robustesse, bareme</t>
+          <t>entropie, bareme, limites_planetaires, decouplage, sobriete, fausse_richesse</t>
         </is>
       </c>
       <c r="M287" s="3" t="inlineStr">
         <is>
-          <t>L11.C10, L11.C13, L11.C24, L18.C04, L18.C09, L24.C03, L24.C04, L26.C01, L26.C02, L26.C08</t>
+          <t>L1.C15, L11.C13, L11.C24, L18.C04, L22.C04, L24.C03, L24.C05, L26.C01, L17.C02</t>
         </is>
       </c>
       <c r="N287" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-26-thermodynamique-et-processus-economique/c03-la-frontiere-decide-du-chiffre.md</t>
+          <t>corpus/livre-26-thermodynamique-et-processus-economique/c02-le-stock-n-existe-pas-sous-la-forme-demandee.md</t>
         </is>
       </c>
     </row>
     <row r="288">
       <c r="A288" s="2" t="inlineStr">
         <is>
-          <t>L26.C04</t>
+          <t>L26.C03</t>
         </is>
       </c>
       <c r="B288" s="3" t="inlineStr">
@@ -19926,7 +19930,7 @@
       </c>
       <c r="C288" s="3" t="inlineStr">
         <is>
-          <t>L'effet rebond, et ce que le dispositif en hérite sans être une politique d'efficacité</t>
+          <t>La frontière décide du chiffre</t>
         </is>
       </c>
       <c r="D288" s="3" t="inlineStr">
@@ -19956,31 +19960,31 @@
       </c>
       <c r="I288" s="3" t="inlineStr"/>
       <c r="J288" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K288" s="3" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L288" s="3" t="inlineStr">
         <is>
-          <t>effet_rebond, jevons_monetaire, decouplage, sobriete, entropie, reflux_transactionnel</t>
+          <t>entropie, decouplage, sobriete, limites_planetaires, robustesse, bareme</t>
         </is>
       </c>
       <c r="M288" s="3" t="inlineStr">
         <is>
-          <t>L1.C03, L1.C12, L1.C17, L11.C10, L13.C01, L18.C04, L22.C02, L24.C03, L26.C01, L26.C03, L26.C09</t>
+          <t>L11.C10, L11.C13, L11.C24, L18.C04, L18.C09, L24.C03, L24.C04, L26.C01, L26.C02, L26.C08</t>
         </is>
       </c>
       <c r="N288" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-26-thermodynamique-et-processus-economique/c04-l-effet-rebond-et-ce-que-le-dispositif-en-herite.md</t>
+          <t>corpus/livre-26-thermodynamique-et-processus-economique/c03-la-frontiere-decide-du-chiffre.md</t>
         </is>
       </c>
     </row>
     <row r="289">
       <c r="A289" s="2" t="inlineStr">
         <is>
-          <t>L26.C05</t>
+          <t>L26.C04</t>
         </is>
       </c>
       <c r="B289" s="3" t="inlineStr">
@@ -19990,7 +19994,7 @@
       </c>
       <c r="C289" s="3" t="inlineStr">
         <is>
-          <t>L'addition n'est pas la substitution</t>
+          <t>L'effet rebond, et ce que le dispositif en hérite sans être une politique d'efficacité</t>
         </is>
       </c>
       <c r="D289" s="3" t="inlineStr">
@@ -20023,28 +20027,28 @@
         <v>1</v>
       </c>
       <c r="K289" s="3" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="L289" s="3" t="inlineStr">
         <is>
-          <t>decouplage, effet_rebond, sobriete, degeneratif, affectation_des_instruments</t>
+          <t>effet_rebond, jevons_monetaire, decouplage, sobriete, entropie, reflux_transactionnel</t>
         </is>
       </c>
       <c r="M289" s="3" t="inlineStr">
         <is>
-          <t>L1.C12, L11.C10, L11.C13, L18.C04, L18.C09, L22.C02, L24.C03, L26.C01, L26.C03, L26.C04</t>
+          <t>L1.C03, L1.C12, L1.C17, L11.C10, L13.C01, L18.C04, L22.C02, L24.C03, L26.C01, L26.C03, L26.C09</t>
         </is>
       </c>
       <c r="N289" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-26-thermodynamique-et-processus-economique/c05-l-addition-n-est-pas-la-substitution.md</t>
+          <t>corpus/livre-26-thermodynamique-et-processus-economique/c04-l-effet-rebond-et-ce-que-le-dispositif-en-herite.md</t>
         </is>
       </c>
     </row>
     <row r="290">
       <c r="A290" s="2" t="inlineStr">
         <is>
-          <t>L26.C06</t>
+          <t>L26.C05</t>
         </is>
       </c>
       <c r="B290" s="3" t="inlineStr">
@@ -20054,7 +20058,7 @@
       </c>
       <c r="C290" s="3" t="inlineStr">
         <is>
-          <t>Portée de la tranche</t>
+          <t>L'addition n'est pas la substitution</t>
         </is>
       </c>
       <c r="D290" s="3" t="inlineStr">
@@ -20074,7 +20078,7 @@
       </c>
       <c r="G290" s="3" t="inlineStr">
         <is>
-          <t>descriptif</t>
+          <t>hybride</t>
         </is>
       </c>
       <c r="H290" s="3" t="inlineStr">
@@ -20087,28 +20091,28 @@
         <v>1</v>
       </c>
       <c r="K290" s="3" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L290" s="3" t="inlineStr">
         <is>
-          <t>entropie, decouplage, effet_rebond, limites_planetaires, sobriete, affectation_des_instruments</t>
+          <t>decouplage, effet_rebond, sobriete, degeneratif, affectation_des_instruments</t>
         </is>
       </c>
       <c r="M290" s="3" t="inlineStr">
         <is>
-          <t>L1.C03, L1.C17, L8.C34, L11.C10, L11.C13, L11.C24, L18.C04, L18.C09, L22.C02, L24.C05, L26.C01, L26.C02, L26.C03, L26.C04, L26.C05, L26.C07</t>
+          <t>L1.C12, L11.C10, L11.C13, L18.C04, L18.C09, L22.C02, L24.C03, L26.C01, L26.C03, L26.C04</t>
         </is>
       </c>
       <c r="N290" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-26-thermodynamique-et-processus-economique/c06-portee-de-la-tranche.md</t>
+          <t>corpus/livre-26-thermodynamique-et-processus-economique/c05-l-addition-n-est-pas-la-substitution.md</t>
         </is>
       </c>
     </row>
     <row r="291">
       <c r="A291" s="2" t="inlineStr">
         <is>
-          <t>L26.C07</t>
+          <t>L26.C06</t>
         </is>
       </c>
       <c r="B291" s="3" t="inlineStr">
@@ -20118,7 +20122,7 @@
       </c>
       <c r="C291" s="3" t="inlineStr">
         <is>
-          <t>Le fondateur ne propose aucun instrument monétaire</t>
+          <t>Portée de la tranche</t>
         </is>
       </c>
       <c r="D291" s="3" t="inlineStr">
@@ -20138,7 +20142,7 @@
       </c>
       <c r="G291" s="3" t="inlineStr">
         <is>
-          <t>hybride</t>
+          <t>descriptif</t>
         </is>
       </c>
       <c r="H291" s="3" t="inlineStr">
@@ -20148,31 +20152,31 @@
       </c>
       <c r="I291" s="3" t="inlineStr"/>
       <c r="J291" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K291" s="3" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="L291" s="3" t="inlineStr">
         <is>
-          <t>entropie, sobriete, affectation_des_instruments, qualification_regenerative</t>
+          <t>entropie, decouplage, effet_rebond, limites_planetaires, sobriete, affectation_des_instruments</t>
         </is>
       </c>
       <c r="M291" s="3" t="inlineStr">
         <is>
-          <t>L1.C03, L1.C17, L8.C34, L11.C13, L16.C01, L16.C05, L17.C02, L17.C03, L26.C01, L26.C03, L26.C06</t>
+          <t>L1.C03, L1.C17, L8.C34, L11.C10, L11.C13, L11.C24, L18.C04, L18.C09, L22.C02, L24.C05, L26.C01, L26.C02, L26.C03, L26.C04, L26.C05, L26.C07</t>
         </is>
       </c>
       <c r="N291" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-26-thermodynamique-et-processus-economique/c07-le-fondateur-ne-propose-aucun-instrument-monetaire.md</t>
+          <t>corpus/livre-26-thermodynamique-et-processus-economique/c06-portee-de-la-tranche.md</t>
         </is>
       </c>
     </row>
     <row r="292">
       <c r="A292" s="2" t="inlineStr">
         <is>
-          <t>L26.C08</t>
+          <t>L26.C07</t>
         </is>
       </c>
       <c r="B292" s="3" t="inlineStr">
@@ -20182,7 +20186,7 @@
       </c>
       <c r="C292" s="3" t="inlineStr">
         <is>
-          <t>Même un puits gratuit ne donne pas dix</t>
+          <t>Le fondateur ne propose aucun instrument monétaire</t>
         </is>
       </c>
       <c r="D292" s="3" t="inlineStr">
@@ -20219,24 +20223,24 @@
       </c>
       <c r="L292" s="3" t="inlineStr">
         <is>
-          <t>bareme, qualification_regenerative, decouplage</t>
+          <t>entropie, sobriete, affectation_des_instruments, qualification_regenerative</t>
         </is>
       </c>
       <c r="M292" s="3" t="inlineStr">
         <is>
-          <t>L1.C17, L8.C37, L11.C13, L17.C01, L24.C05, L26.C01, L26.C03, L26.C06, L26.C07</t>
+          <t>L1.C03, L1.C17, L8.C34, L11.C13, L16.C01, L16.C05, L17.C02, L17.C03, L26.C01, L26.C03, L26.C06</t>
         </is>
       </c>
       <c r="N292" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-26-thermodynamique-et-processus-economique/c08-meme-un-puits-gratuit-ne-donne-pas-dix.md</t>
+          <t>corpus/livre-26-thermodynamique-et-processus-economique/c07-le-fondateur-ne-propose-aucun-instrument-monetaire.md</t>
         </is>
       </c>
     </row>
     <row r="293">
       <c r="A293" s="2" t="inlineStr">
         <is>
-          <t>L26.C09</t>
+          <t>L26.C08</t>
         </is>
       </c>
       <c r="B293" s="3" t="inlineStr">
@@ -20246,7 +20250,7 @@
       </c>
       <c r="C293" s="3" t="inlineStr">
         <is>
-          <t>La méthode décide du chiffre</t>
+          <t>Même un puits gratuit ne donne pas dix</t>
         </is>
       </c>
       <c r="D293" s="3" t="inlineStr">
@@ -20283,24 +20287,24 @@
       </c>
       <c r="L293" s="3" t="inlineStr">
         <is>
-          <t>effet_rebond, jevons_monetaire, decouplage, bareme</t>
+          <t>bareme, qualification_regenerative, decouplage</t>
         </is>
       </c>
       <c r="M293" s="3" t="inlineStr">
         <is>
-          <t>L1.C03, L11.C13, L17.C02, L24.C03, L26.C03, L26.C04, L26.C06, L26.C08</t>
+          <t>L1.C17, L8.C37, L11.C13, L17.C01, L24.C05, L26.C01, L26.C03, L26.C06, L26.C07</t>
         </is>
       </c>
       <c r="N293" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-26-thermodynamique-et-processus-economique/c09-la-methode-decide-du-chiffre.md</t>
+          <t>corpus/livre-26-thermodynamique-et-processus-economique/c08-meme-un-puits-gratuit-ne-donne-pas-dix.md</t>
         </is>
       </c>
     </row>
     <row r="294">
       <c r="A294" s="2" t="inlineStr">
         <is>
-          <t>L26.C10</t>
+          <t>L26.C09</t>
         </is>
       </c>
       <c r="B294" s="3" t="inlineStr">
@@ -20310,7 +20314,7 @@
       </c>
       <c r="C294" s="3" t="inlineStr">
         <is>
-          <t>La financiarisation produit un découplage apparent</t>
+          <t>La méthode décide du chiffre</t>
         </is>
       </c>
       <c r="D294" s="3" t="inlineStr">
@@ -20343,26 +20347,90 @@
         <v>2</v>
       </c>
       <c r="K294" s="3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L294" s="3" t="inlineStr">
         <is>
+          <t>effet_rebond, jevons_monetaire, decouplage, bareme</t>
+        </is>
+      </c>
+      <c r="M294" s="3" t="inlineStr">
+        <is>
+          <t>L1.C03, L11.C13, L17.C02, L24.C03, L26.C03, L26.C04, L26.C06, L26.C08</t>
+        </is>
+      </c>
+      <c r="N294" s="3" t="inlineStr">
+        <is>
+          <t>corpus/livre-26-thermodynamique-et-processus-economique/c09-la-methode-decide-du-chiffre.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" s="2" t="inlineStr">
+        <is>
+          <t>L26.C10</t>
+        </is>
+      </c>
+      <c r="B295" s="3" t="inlineStr">
+        <is>
+          <t>L26</t>
+        </is>
+      </c>
+      <c r="C295" s="3" t="inlineStr">
+        <is>
+          <t>La financiarisation produit un découplage apparent</t>
+        </is>
+      </c>
+      <c r="D295" s="3" t="inlineStr">
+        <is>
+          <t>brouillon</t>
+        </is>
+      </c>
+      <c r="E295" s="3" t="inlineStr">
+        <is>
+          <t>preparatoire</t>
+        </is>
+      </c>
+      <c r="F295" s="3" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="G295" s="3" t="inlineStr">
+        <is>
+          <t>hybride</t>
+        </is>
+      </c>
+      <c r="H295" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="I295" s="3" t="inlineStr"/>
+      <c r="J295" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="K295" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="L295" s="3" t="inlineStr">
+        <is>
           <t>decouplage, fausse_richesse, jevons_monetaire, indicateur_de_progres</t>
         </is>
       </c>
-      <c r="M294" s="3" t="inlineStr">
-        <is>
-          <t>L1.C03, L11.C13, L17.C01, L17.C05, L24.C03, L26.C01, L26.C03, L26.C06, L26.C08, L26.C09</t>
-        </is>
-      </c>
-      <c r="N294" s="3" t="inlineStr">
+      <c r="M295" s="3" t="inlineStr">
+        <is>
+          <t>L1.C03, L11.C13, L17.C01, L17.C05, L24.C03, L26.C01, L26.C03, L26.C06, L26.C08, L26.C09, L18.C10</t>
+        </is>
+      </c>
+      <c r="N295" s="3" t="inlineStr">
         <is>
           <t>corpus/livre-26-thermodynamique-et-processus-economique/c10-la-financiarisation-produit-un-decouplage-apparent.md</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:N294"/>
+  <autoFilter ref="A1:N295"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -20421,7 +20489,7 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="5">
@@ -20431,7 +20499,7 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="6">
@@ -20441,7 +20509,7 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>293</v>
+        <v>294</v>
       </c>
     </row>
     <row r="7">
@@ -20451,7 +20519,7 @@
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="8">
@@ -20461,7 +20529,7 @@
         </is>
       </c>
       <c r="B8" s="3" t="n">
-        <v>288</v>
+        <v>290</v>
       </c>
     </row>
     <row r="9">
@@ -20471,7 +20539,7 @@
         </is>
       </c>
       <c r="B9" s="3" t="n">
-        <v>284</v>
+        <v>285</v>
       </c>
     </row>
     <row r="10">
@@ -20491,7 +20559,7 @@
         </is>
       </c>
       <c r="B11" s="3" t="n">
-        <v>1437</v>
+        <v>1448</v>
       </c>
     </row>
     <row r="12">
@@ -20501,7 +20569,7 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>1104</v>
+        <v>1107</v>
       </c>
     </row>
     <row r="13">
@@ -20516,7 +20584,7 @@
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>L0, L9, L12, L14, L15</t>
+          <t>L0, L9, L14, L15</t>
         </is>
       </c>
     </row>
@@ -20595,7 +20663,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C321"/>
+  <dimension ref="A1:C322"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -24186,7 +24254,7 @@
       </c>
       <c r="C211" s="6" t="inlineStr">
         <is>
-          <t>candidat — AMORCE SEULE</t>
+          <t>en-cours — 1 chapitre(s)</t>
         </is>
       </c>
     </row>
@@ -24198,7 +24266,7 @@
       </c>
       <c r="B212" s="3" t="inlineStr">
         <is>
-          <t>[AMORCE] Ce que ce livre doit établir</t>
+          <t>Ce que ce livre doit établir</t>
         </is>
       </c>
       <c r="C212" s="3" t="inlineStr">
@@ -24543,7 +24611,7 @@
       </c>
       <c r="C232" s="6" t="inlineStr">
         <is>
-          <t>en-cours — 9 chapitre(s)</t>
+          <t>en-cours — 10 chapitre(s)</t>
         </is>
       </c>
     </row>
@@ -24701,48 +24769,48 @@
       </c>
     </row>
     <row r="242">
-      <c r="A242" s="6" t="inlineStr">
+      <c r="A242" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    L18.C10</t>
+        </is>
+      </c>
+      <c r="B242" s="3" t="inlineStr">
+        <is>
+          <t>La dégradation est un coût, l'amélioration n'est pas un revenu</t>
+        </is>
+      </c>
+      <c r="C242" s="3" t="inlineStr">
+        <is>
+          <t>brouillon</t>
+        </is>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" s="6" t="inlineStr">
         <is>
           <t>L19</t>
         </is>
       </c>
-      <c r="B242" s="6" t="inlineStr">
+      <c r="B243" s="6" t="inlineStr">
         <is>
           <t>Comptabilité monétaire de l'émission sans dette</t>
         </is>
       </c>
-      <c r="C242" s="6" t="inlineStr">
+      <c r="C243" s="6" t="inlineStr">
         <is>
           <t>en-cours — 7 chapitre(s)</t>
-        </is>
-      </c>
-    </row>
-    <row r="243">
-      <c r="A243" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    L19.C01</t>
-        </is>
-      </c>
-      <c r="B243" s="3" t="inlineStr">
-        <is>
-          <t>Ce que ce livre doit établir</t>
-        </is>
-      </c>
-      <c r="C243" s="3" t="inlineStr">
-        <is>
-          <t>brouillon</t>
         </is>
       </c>
     </row>
     <row r="244">
       <c r="A244" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L19.C02</t>
+          <t xml:space="preserve">    L19.C01</t>
         </is>
       </c>
       <c r="B244" s="3" t="inlineStr">
         <is>
-          <t>Le seul précédent, et le passif lui a été reconnu en 2008</t>
+          <t>Ce que ce livre doit établir</t>
         </is>
       </c>
       <c r="C244" s="3" t="inlineStr">
@@ -24754,12 +24822,12 @@
     <row r="245">
       <c r="A245" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L19.C03</t>
+          <t xml:space="preserve">    L19.C02</t>
         </is>
       </c>
       <c r="B245" s="3" t="inlineStr">
         <is>
-          <t>Le reflux est un intérêt négatif, ou une répudiation — et c'est le moment qui décide</t>
+          <t>Le seul précédent, et le passif lui a été reconnu en 2008</t>
         </is>
       </c>
       <c r="C245" s="3" t="inlineStr">
@@ -24771,12 +24839,12 @@
     <row r="246">
       <c r="A246" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L19.C04</t>
+          <t xml:space="preserve">    L19.C03</t>
         </is>
       </c>
       <c r="B246" s="3" t="inlineStr">
         <is>
-          <t>L'actif transitoire n'existe pas, et le problème change de bilan</t>
+          <t>Le reflux est un intérêt négatif, ou une répudiation — et c'est le moment qui décide</t>
         </is>
       </c>
       <c r="C246" s="3" t="inlineStr">
@@ -24788,12 +24856,12 @@
     <row r="247">
       <c r="A247" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L19.C05</t>
+          <t xml:space="preserve">    L19.C04</t>
         </is>
       </c>
       <c r="B247" s="3" t="inlineStr">
         <is>
-          <t>Un débiteur collectif n'existe pas — sauf comme somme de débiteurs identifiés</t>
+          <t>L'actif transitoire n'existe pas, et le problème change de bilan</t>
         </is>
       </c>
       <c r="C247" s="3" t="inlineStr">
@@ -24805,12 +24873,12 @@
     <row r="248">
       <c r="A248" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L19.C06</t>
+          <t xml:space="preserve">    L19.C05</t>
         </is>
       </c>
       <c r="B248" s="3" t="inlineStr">
         <is>
-          <t>Les fonds propres négatifs, et l'institution qui n'apparaît dans les comptes de personne</t>
+          <t>Un débiteur collectif n'existe pas — sauf comme somme de débiteurs identifiés</t>
         </is>
       </c>
       <c r="C248" s="3" t="inlineStr">
@@ -24822,63 +24890,63 @@
     <row r="249">
       <c r="A249" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">    L19.C06</t>
+        </is>
+      </c>
+      <c r="B249" s="3" t="inlineStr">
+        <is>
+          <t>Les fonds propres négatifs, et l'institution qui n'apparaît dans les comptes de personne</t>
+        </is>
+      </c>
+      <c r="C249" s="3" t="inlineStr">
+        <is>
+          <t>brouillon</t>
+        </is>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">    L19.C07</t>
         </is>
       </c>
-      <c r="B249" s="3" t="inlineStr">
+      <c r="B250" s="3" t="inlineStr">
         <is>
           <t>Portée de la tranche</t>
         </is>
       </c>
-      <c r="C249" s="3" t="inlineStr">
-        <is>
-          <t>brouillon</t>
-        </is>
-      </c>
-    </row>
-    <row r="250">
-      <c r="A250" s="6" t="inlineStr">
+      <c r="C250" s="3" t="inlineStr">
+        <is>
+          <t>brouillon</t>
+        </is>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" s="6" t="inlineStr">
         <is>
           <t>L20</t>
         </is>
       </c>
-      <c r="B250" s="6" t="inlineStr">
+      <c r="B251" s="6" t="inlineStr">
         <is>
           <t>Droit international public, droit monétaire et commercial de la réforme</t>
         </is>
       </c>
-      <c r="C250" s="6" t="inlineStr">
+      <c r="C251" s="6" t="inlineStr">
         <is>
           <t>en-cours — 23 chapitre(s)</t>
-        </is>
-      </c>
-    </row>
-    <row r="251">
-      <c r="A251" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    L20.C01</t>
-        </is>
-      </c>
-      <c r="B251" s="3" t="inlineStr">
-        <is>
-          <t>Ce que ce livre doit établir</t>
-        </is>
-      </c>
-      <c r="C251" s="3" t="inlineStr">
-        <is>
-          <t>brouillon</t>
         </is>
       </c>
     </row>
     <row r="252">
       <c r="A252" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L20.C02</t>
+          <t xml:space="preserve">    L20.C01</t>
         </is>
       </c>
       <c r="B252" s="3" t="inlineStr">
         <is>
-          <t>L'interdiction du financement monétaire</t>
+          <t>Ce que ce livre doit établir</t>
         </is>
       </c>
       <c r="C252" s="3" t="inlineStr">
@@ -24890,12 +24958,12 @@
     <row r="253">
       <c r="A253" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L20.C03</t>
+          <t xml:space="preserve">    L20.C02</t>
         </is>
       </c>
       <c r="B253" s="3" t="inlineStr">
         <is>
-          <t>L'objectif principal et ce qu'il exclut</t>
+          <t>L'interdiction du financement monétaire</t>
         </is>
       </c>
       <c r="C253" s="3" t="inlineStr">
@@ -24907,12 +24975,12 @@
     <row r="254">
       <c r="A254" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L20.C04</t>
+          <t xml:space="preserve">    L20.C03</t>
         </is>
       </c>
       <c r="B254" s="3" t="inlineStr">
         <is>
-          <t>L'indépendance, et à l'égard de qui</t>
+          <t>L'objectif principal et ce qu'il exclut</t>
         </is>
       </c>
       <c r="C254" s="3" t="inlineStr">
@@ -24924,12 +24992,12 @@
     <row r="255">
       <c r="A255" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L20.C05</t>
+          <t xml:space="preserve">    L20.C04</t>
         </is>
       </c>
       <c r="B255" s="3" t="inlineStr">
         <is>
-          <t>Le monopole d'émission et le cours légal</t>
+          <t>L'indépendance, et à l'égard de qui</t>
         </is>
       </c>
       <c r="C255" s="3" t="inlineStr">
@@ -24941,12 +25009,12 @@
     <row r="256">
       <c r="A256" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L20.C06</t>
+          <t xml:space="preserve">    L20.C05</t>
         </is>
       </c>
       <c r="B256" s="3" t="inlineStr">
         <is>
-          <t>Les voies de révision et leur coût</t>
+          <t>Le monopole d'émission et le cours légal</t>
         </is>
       </c>
       <c r="C256" s="3" t="inlineStr">
@@ -24958,12 +25026,12 @@
     <row r="257">
       <c r="A257" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L20.C07</t>
+          <t xml:space="preserve">    L20.C06</t>
         </is>
       </c>
       <c r="B257" s="3" t="inlineStr">
         <is>
-          <t>L'accord monétaire international</t>
+          <t>Les voies de révision et leur coût</t>
         </is>
       </c>
       <c r="C257" s="3" t="inlineStr">
@@ -24975,12 +25043,12 @@
     <row r="258">
       <c r="A258" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L20.C08</t>
+          <t xml:space="preserve">    L20.C07</t>
         </is>
       </c>
       <c r="B258" s="3" t="inlineStr">
         <is>
-          <t>La parité inscrite dans le traité</t>
+          <t>L'accord monétaire international</t>
         </is>
       </c>
       <c r="C258" s="3" t="inlineStr">
@@ -24992,12 +25060,12 @@
     <row r="259">
       <c r="A259" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L20.C09</t>
+          <t xml:space="preserve">    L20.C08</t>
         </is>
       </c>
       <c r="B259" s="3" t="inlineStr">
         <is>
-          <t>L'amendement des statuts du Fonds</t>
+          <t>La parité inscrite dans le traité</t>
         </is>
       </c>
       <c r="C259" s="3" t="inlineStr">
@@ -25009,12 +25077,12 @@
     <row r="260">
       <c r="A260" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L20.C10</t>
+          <t xml:space="preserve">    L20.C09</t>
         </is>
       </c>
       <c r="B260" s="3" t="inlineStr">
         <is>
-          <t>Le vote pondéré et les voix de base</t>
+          <t>L'amendement des statuts du Fonds</t>
         </is>
       </c>
       <c r="C260" s="3" t="inlineStr">
@@ -25026,12 +25094,12 @@
     <row r="261">
       <c r="A261" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L20.C11</t>
+          <t xml:space="preserve">    L20.C10</t>
         </is>
       </c>
       <c r="B261" s="3" t="inlineStr">
         <is>
-          <t>La personnalité juridique et les immunités</t>
+          <t>Le vote pondéré et les voix de base</t>
         </is>
       </c>
       <c r="C261" s="3" t="inlineStr">
@@ -25043,12 +25111,12 @@
     <row r="262">
       <c r="A262" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L20.C12</t>
+          <t xml:space="preserve">    L20.C11</t>
         </is>
       </c>
       <c r="B262" s="3" t="inlineStr">
         <is>
-          <t>Les pouvoirs non délégables</t>
+          <t>La personnalité juridique et les immunités</t>
         </is>
       </c>
       <c r="C262" s="3" t="inlineStr">
@@ -25060,12 +25128,12 @@
     <row r="263">
       <c r="A263" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L20.C13</t>
+          <t xml:space="preserve">    L20.C12</t>
         </is>
       </c>
       <c r="B263" s="3" t="inlineStr">
         <is>
-          <t>L'entrée en vigueur, l'adhésion et le retrait</t>
+          <t>Les pouvoirs non délégables</t>
         </is>
       </c>
       <c r="C263" s="3" t="inlineStr">
@@ -25077,12 +25145,12 @@
     <row r="264">
       <c r="A264" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L20.C14</t>
+          <t xml:space="preserve">    L20.C13</t>
         </is>
       </c>
       <c r="B264" s="3" t="inlineStr">
         <is>
-          <t>Qui interprète le traité</t>
+          <t>L'entrée en vigueur, l'adhésion et le retrait</t>
         </is>
       </c>
       <c r="C264" s="3" t="inlineStr">
@@ -25094,12 +25162,12 @@
     <row r="265">
       <c r="A265" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L20.C15</t>
+          <t xml:space="preserve">    L20.C14</t>
         </is>
       </c>
       <c r="B265" s="3" t="inlineStr">
         <is>
-          <t>Le devoir international des agents</t>
+          <t>Qui interprète le traité</t>
         </is>
       </c>
       <c r="C265" s="3" t="inlineStr">
@@ -25111,12 +25179,12 @@
     <row r="266">
       <c r="A266" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L20.C16</t>
+          <t xml:space="preserve">    L20.C15</t>
         </is>
       </c>
       <c r="B266" s="3" t="inlineStr">
         <is>
-          <t>Le patrimoine commun de l'humanité</t>
+          <t>Le devoir international des agents</t>
         </is>
       </c>
       <c r="C266" s="3" t="inlineStr">
@@ -25128,12 +25196,12 @@
     <row r="267">
       <c r="A267" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L20.C17</t>
+          <t xml:space="preserve">    L20.C16</t>
         </is>
       </c>
       <c r="B267" s="3" t="inlineStr">
         <is>
-          <t>La sanctuarisation, et elle existe</t>
+          <t>Le patrimoine commun de l'humanité</t>
         </is>
       </c>
       <c r="C267" s="3" t="inlineStr">
@@ -25145,12 +25213,12 @@
     <row r="268">
       <c r="A268" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L20.C18</t>
+          <t xml:space="preserve">    L20.C17</t>
         </is>
       </c>
       <c r="B268" s="3" t="inlineStr">
         <is>
-          <t>L'amendement et la dérogation dans l'ordre commercial</t>
+          <t>La sanctuarisation, et elle existe</t>
         </is>
       </c>
       <c r="C268" s="3" t="inlineStr">
@@ -25162,12 +25230,12 @@
     <row r="269">
       <c r="A269" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L20.C19</t>
+          <t xml:space="preserve">    L20.C18</t>
         </is>
       </c>
       <c r="B269" s="3" t="inlineStr">
         <is>
-          <t>Le texte que la conformité invoque</t>
+          <t>L'amendement et la dérogation dans l'ordre commercial</t>
         </is>
       </c>
       <c r="C269" s="3" t="inlineStr">
@@ -25179,12 +25247,12 @@
     <row r="270">
       <c r="A270" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L20.C20</t>
+          <t xml:space="preserve">    L20.C19</t>
         </is>
       </c>
       <c r="B270" s="3" t="inlineStr">
         <is>
-          <t>L'ajustement aux frontières comme précédent</t>
+          <t>Le texte que la conformité invoque</t>
         </is>
       </c>
       <c r="C270" s="3" t="inlineStr">
@@ -25196,12 +25264,12 @@
     <row r="271">
       <c r="A271" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L20.C21</t>
+          <t xml:space="preserve">    L20.C20</t>
         </is>
       </c>
       <c r="B271" s="3" t="inlineStr">
         <is>
-          <t>La transparence et sa limite juridictionnelle</t>
+          <t>L'ajustement aux frontières comme précédent</t>
         </is>
       </c>
       <c r="C271" s="3" t="inlineStr">
@@ -25213,12 +25281,12 @@
     <row r="272">
       <c r="A272" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L20.C22</t>
+          <t xml:space="preserve">    L20.C21</t>
         </is>
       </c>
       <c r="B272" s="3" t="inlineStr">
         <is>
-          <t>Ce que le droit devrait devenir</t>
+          <t>La transparence et sa limite juridictionnelle</t>
         </is>
       </c>
       <c r="C272" s="3" t="inlineStr">
@@ -25230,63 +25298,63 @@
     <row r="273">
       <c r="A273" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">    L20.C22</t>
+        </is>
+      </c>
+      <c r="B273" s="3" t="inlineStr">
+        <is>
+          <t>Ce que le droit devrait devenir</t>
+        </is>
+      </c>
+      <c r="C273" s="3" t="inlineStr">
+        <is>
+          <t>brouillon</t>
+        </is>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">    L20.C23</t>
         </is>
       </c>
-      <c r="B273" s="3" t="inlineStr">
+      <c r="B274" s="3" t="inlineStr">
         <is>
           <t>La portée du livre</t>
         </is>
       </c>
-      <c r="C273" s="3" t="inlineStr">
-        <is>
-          <t>brouillon</t>
-        </is>
-      </c>
-    </row>
-    <row r="274">
-      <c r="A274" s="6" t="inlineStr">
+      <c r="C274" s="3" t="inlineStr">
+        <is>
+          <t>brouillon</t>
+        </is>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" s="6" t="inlineStr">
         <is>
           <t>L21</t>
         </is>
       </c>
-      <c r="B274" s="6" t="inlineStr">
+      <c r="B275" s="6" t="inlineStr">
         <is>
           <t>La plomberie financière mondiale</t>
         </is>
       </c>
-      <c r="C274" s="6" t="inlineStr">
+      <c r="C275" s="6" t="inlineStr">
         <is>
           <t>en-cours — 7 chapitre(s)</t>
-        </is>
-      </c>
-    </row>
-    <row r="275">
-      <c r="A275" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    L21.C01</t>
-        </is>
-      </c>
-      <c r="B275" s="3" t="inlineStr">
-        <is>
-          <t>Ce que ce livre doit établir, et le principe qui exige des fonds propres</t>
-        </is>
-      </c>
-      <c r="C275" s="3" t="inlineStr">
-        <is>
-          <t>brouillon</t>
         </is>
       </c>
     </row>
     <row r="276">
       <c r="A276" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L21.C02</t>
+          <t xml:space="preserve">    L21.C01</t>
         </is>
       </c>
       <c r="B276" s="3" t="inlineStr">
         <is>
-          <t>Comment l'unité circulerait vraiment, et ce que chaque étape exige</t>
+          <t>Ce que ce livre doit établir, et le principe qui exige des fonds propres</t>
         </is>
       </c>
       <c r="C276" s="3" t="inlineStr">
@@ -25298,12 +25366,12 @@
     <row r="277">
       <c r="A277" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L21.C03</t>
+          <t xml:space="preserve">    L21.C02</t>
         </is>
       </c>
       <c r="B277" s="3" t="inlineStr">
         <is>
-          <t>Une opération de bout en bout, bilan par bilan</t>
+          <t>Comment l'unité circulerait vraiment, et ce que chaque étape exige</t>
         </is>
       </c>
       <c r="C277" s="3" t="inlineStr">
@@ -25315,12 +25383,12 @@
     <row r="278">
       <c r="A278" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L21.C04</t>
+          <t xml:space="preserve">    L21.C03</t>
         </is>
       </c>
       <c r="B278" s="3" t="inlineStr">
         <is>
-          <t>Ce que l'émission coûte aux banques qui l'hébergent</t>
+          <t>Une opération de bout en bout, bilan par bilan</t>
         </is>
       </c>
       <c r="C278" s="3" t="inlineStr">
@@ -25332,12 +25400,12 @@
     <row r="279">
       <c r="A279" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L21.C05</t>
+          <t xml:space="preserve">    L21.C04</t>
         </is>
       </c>
       <c r="B279" s="3" t="inlineStr">
         <is>
-          <t>La première infrastructure ouverte, et ce qu'elle renverse</t>
+          <t>Ce que l'émission coûte aux banques qui l'hébergent</t>
         </is>
       </c>
       <c r="C279" s="3" t="inlineStr">
@@ -25349,12 +25417,12 @@
     <row r="280">
       <c r="A280" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L21.C06</t>
+          <t xml:space="preserve">    L21.C05</t>
         </is>
       </c>
       <c r="B280" s="3" t="inlineStr">
         <is>
-          <t>La jambe qui reste, et ce qu'il faut pour la protéger</t>
+          <t>La première infrastructure ouverte, et ce qu'elle renverse</t>
         </is>
       </c>
       <c r="C280" s="3" t="inlineStr">
@@ -25366,63 +25434,63 @@
     <row r="281">
       <c r="A281" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">    L21.C06</t>
+        </is>
+      </c>
+      <c r="B281" s="3" t="inlineStr">
+        <is>
+          <t>La jambe qui reste, et ce qu'il faut pour la protéger</t>
+        </is>
+      </c>
+      <c r="C281" s="3" t="inlineStr">
+        <is>
+          <t>brouillon</t>
+        </is>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">    L21.C07</t>
         </is>
       </c>
-      <c r="B281" s="3" t="inlineStr">
+      <c r="B282" s="3" t="inlineStr">
         <is>
           <t>Portée de la tranche</t>
         </is>
       </c>
-      <c r="C281" s="3" t="inlineStr">
-        <is>
-          <t>brouillon</t>
-        </is>
-      </c>
-    </row>
-    <row r="282">
-      <c r="A282" s="6" t="inlineStr">
+      <c r="C282" s="3" t="inlineStr">
+        <is>
+          <t>brouillon</t>
+        </is>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" s="6" t="inlineStr">
         <is>
           <t>L22</t>
         </is>
       </c>
-      <c r="B282" s="6" t="inlineStr">
+      <c r="B283" s="6" t="inlineStr">
         <is>
           <t>Le pouvoir de la finance non bancaire</t>
         </is>
       </c>
-      <c r="C282" s="6" t="inlineStr">
+      <c r="C283" s="6" t="inlineStr">
         <is>
           <t>en-cours — 7 chapitre(s)</t>
-        </is>
-      </c>
-    </row>
-    <row r="283">
-      <c r="A283" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    L22.C01</t>
-        </is>
-      </c>
-      <c r="B283" s="3" t="inlineStr">
-        <is>
-          <t>Ce que ce livre doit établir</t>
-        </is>
-      </c>
-      <c r="C283" s="3" t="inlineStr">
-        <is>
-          <t>brouillon</t>
         </is>
       </c>
     </row>
     <row r="284">
       <c r="A284" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L22.C02</t>
+          <t xml:space="preserve">    L22.C01</t>
         </is>
       </c>
       <c r="B284" s="3" t="inlineStr">
         <is>
-          <t>Où va la monnaie émise, et pourquoi le reflux ne l'y suit pas</t>
+          <t>Ce que ce livre doit établir</t>
         </is>
       </c>
       <c r="C284" s="3" t="inlineStr">
@@ -25434,12 +25502,12 @@
     <row r="285">
       <c r="A285" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L22.C03</t>
+          <t xml:space="preserve">    L22.C02</t>
         </is>
       </c>
       <c r="B285" s="3" t="inlineStr">
         <is>
-          <t>Le barème existe déjà, et il a trois pièces que le corpus n'a pas</t>
+          <t>Où va la monnaie émise, et pourquoi le reflux ne l'y suit pas</t>
         </is>
       </c>
       <c r="C285" s="3" t="inlineStr">
@@ -25451,12 +25519,12 @@
     <row r="286">
       <c r="A286" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L22.C04</t>
+          <t xml:space="preserve">    L22.C03</t>
         </is>
       </c>
       <c r="B286" s="3" t="inlineStr">
         <is>
-          <t>Les critères réels ne mesurent pas, ils certifient</t>
+          <t>Le barème existe déjà, et il a trois pièces que le corpus n'a pas</t>
         </is>
       </c>
       <c r="C286" s="3" t="inlineStr">
@@ -25468,12 +25536,12 @@
     <row r="287">
       <c r="A287" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L22.C05</t>
+          <t xml:space="preserve">    L22.C04</t>
         </is>
       </c>
       <c r="B287" s="3" t="inlineStr">
         <is>
-          <t>L'épargne retraite, et le dilemme du troisième instrument</t>
+          <t>Les critères réels ne mesurent pas, ils certifient</t>
         </is>
       </c>
       <c r="C287" s="3" t="inlineStr">
@@ -25485,12 +25553,12 @@
     <row r="288">
       <c r="A288" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L22.C06</t>
+          <t xml:space="preserve">    L22.C05</t>
         </is>
       </c>
       <c r="B288" s="3" t="inlineStr">
         <is>
-          <t>Qui décide, quand personne ne décide</t>
+          <t>L'épargne retraite, et le dilemme du troisième instrument</t>
         </is>
       </c>
       <c r="C288" s="3" t="inlineStr">
@@ -25502,63 +25570,63 @@
     <row r="289">
       <c r="A289" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">    L22.C06</t>
+        </is>
+      </c>
+      <c r="B289" s="3" t="inlineStr">
+        <is>
+          <t>Qui décide, quand personne ne décide</t>
+        </is>
+      </c>
+      <c r="C289" s="3" t="inlineStr">
+        <is>
+          <t>brouillon</t>
+        </is>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">    L22.C07</t>
         </is>
       </c>
-      <c r="B289" s="3" t="inlineStr">
+      <c r="B290" s="3" t="inlineStr">
         <is>
           <t>Portée de la tranche</t>
         </is>
       </c>
-      <c r="C289" s="3" t="inlineStr">
-        <is>
-          <t>brouillon</t>
-        </is>
-      </c>
-    </row>
-    <row r="290">
-      <c r="A290" s="6" t="inlineStr">
+      <c r="C290" s="3" t="inlineStr">
+        <is>
+          <t>brouillon</t>
+        </is>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" s="6" t="inlineStr">
         <is>
           <t>L23</t>
         </is>
       </c>
-      <c r="B290" s="6" t="inlineStr">
+      <c r="B291" s="6" t="inlineStr">
         <is>
           <t>Fiscalité mondiale, finance offshore et opacité</t>
         </is>
       </c>
-      <c r="C290" s="6" t="inlineStr">
+      <c r="C291" s="6" t="inlineStr">
         <is>
           <t>en-cours — 7 chapitre(s)</t>
-        </is>
-      </c>
-    </row>
-    <row r="291">
-      <c r="A291" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    L23.C01</t>
-        </is>
-      </c>
-      <c r="B291" s="3" t="inlineStr">
-        <is>
-          <t>Ce que ce livre doit établir</t>
-        </is>
-      </c>
-      <c r="C291" s="3" t="inlineStr">
-        <is>
-          <t>brouillon</t>
         </is>
       </c>
     </row>
     <row r="292">
       <c r="A292" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L23.C02</t>
+          <t xml:space="preserve">    L23.C01</t>
         </is>
       </c>
       <c r="B292" s="3" t="inlineStr">
         <is>
-          <t>La compétence que la convention ne crée pas, et le vote qu'elle a gagné</t>
+          <t>Ce que ce livre doit établir</t>
         </is>
       </c>
       <c r="C292" s="3" t="inlineStr">
@@ -25570,12 +25638,12 @@
     <row r="293">
       <c r="A293" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L23.C03</t>
+          <t xml:space="preserve">    L23.C02</t>
         </is>
       </c>
       <c r="B293" s="3" t="inlineStr">
         <is>
-          <t>F8 appliqué à une négociation en cours, et le résultat n'est pas le désarmement</t>
+          <t>La compétence que la convention ne crée pas, et le vote qu'elle a gagné</t>
         </is>
       </c>
       <c r="C293" s="3" t="inlineStr">
@@ -25587,12 +25655,12 @@
     <row r="294">
       <c r="A294" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L23.C04</t>
+          <t xml:space="preserve">    L23.C03</t>
         </is>
       </c>
       <c r="B294" s="3" t="inlineStr">
         <is>
-          <t>La transparence que le corpus supposait a été invalidée</t>
+          <t>F8 appliqué à une négociation en cours, et le résultat n'est pas le désarmement</t>
         </is>
       </c>
       <c r="C294" s="3" t="inlineStr">
@@ -25604,12 +25672,12 @@
     <row r="295">
       <c r="A295" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L23.C05</t>
+          <t xml:space="preserve">    L23.C04</t>
         </is>
       </c>
       <c r="B295" s="3" t="inlineStr">
         <is>
-          <t>Intéresser le percepteur, et ce que le taux révèle</t>
+          <t>La transparence que le corpus supposait a été invalidée</t>
         </is>
       </c>
       <c r="C295" s="3" t="inlineStr">
@@ -25621,12 +25689,12 @@
     <row r="296">
       <c r="A296" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L23.C06</t>
+          <t xml:space="preserve">    L23.C05</t>
         </is>
       </c>
       <c r="B296" s="3" t="inlineStr">
         <is>
-          <t>L'arbre appliqué à la fonte, et il ne reste que deux branches</t>
+          <t>Intéresser le percepteur, et ce que le taux révèle</t>
         </is>
       </c>
       <c r="C296" s="3" t="inlineStr">
@@ -25638,63 +25706,63 @@
     <row r="297">
       <c r="A297" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">    L23.C06</t>
+        </is>
+      </c>
+      <c r="B297" s="3" t="inlineStr">
+        <is>
+          <t>L'arbre appliqué à la fonte, et il ne reste que deux branches</t>
+        </is>
+      </c>
+      <c r="C297" s="3" t="inlineStr">
+        <is>
+          <t>brouillon</t>
+        </is>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">    L23.C07</t>
         </is>
       </c>
-      <c r="B297" s="3" t="inlineStr">
+      <c r="B298" s="3" t="inlineStr">
         <is>
           <t>Portée de la tranche, et la moitié qui n'est pas commencée</t>
         </is>
       </c>
-      <c r="C297" s="3" t="inlineStr">
-        <is>
-          <t>brouillon</t>
-        </is>
-      </c>
-    </row>
-    <row r="298">
-      <c r="A298" s="6" t="inlineStr">
+      <c r="C298" s="3" t="inlineStr">
+        <is>
+          <t>brouillon</t>
+        </is>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" s="6" t="inlineStr">
         <is>
           <t>L24</t>
         </is>
       </c>
-      <c r="B298" s="6" t="inlineStr">
+      <c r="B299" s="6" t="inlineStr">
         <is>
           <t>Les conditions matérielles de la vie</t>
         </is>
       </c>
-      <c r="C298" s="6" t="inlineStr">
+      <c r="C299" s="6" t="inlineStr">
         <is>
           <t>en-cours — 5 chapitre(s)</t>
-        </is>
-      </c>
-    </row>
-    <row r="299">
-      <c r="A299" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    L24.C01</t>
-        </is>
-      </c>
-      <c r="B299" s="3" t="inlineStr">
-        <is>
-          <t>Ce que ce livre doit établir</t>
-        </is>
-      </c>
-      <c r="C299" s="3" t="inlineStr">
-        <is>
-          <t>brouillon</t>
         </is>
       </c>
     </row>
     <row r="300">
       <c r="A300" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L24.C02</t>
+          <t xml:space="preserve">    L24.C01</t>
         </is>
       </c>
       <c r="B300" s="3" t="inlineStr">
         <is>
-          <t>Le seuil juste est plus strict que le seuil sûr</t>
+          <t>Ce que ce livre doit établir</t>
         </is>
       </c>
       <c r="C300" s="3" t="inlineStr">
@@ -25706,12 +25774,12 @@
     <row r="301">
       <c r="A301" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L24.C03</t>
+          <t xml:space="preserve">    L24.C02</t>
         </is>
       </c>
       <c r="B301" s="3" t="inlineStr">
         <is>
-          <t>La matière, et le levier commun que les neuf dimensions n'avaient pas</t>
+          <t>Le seuil juste est plus strict que le seuil sûr</t>
         </is>
       </c>
       <c r="C301" s="3" t="inlineStr">
@@ -25723,12 +25791,12 @@
     <row r="302">
       <c r="A302" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L24.C04</t>
+          <t xml:space="preserve">    L24.C03</t>
         </is>
       </c>
       <c r="B302" s="3" t="inlineStr">
         <is>
-          <t>Un budget mondial n'est pas partageable</t>
+          <t>La matière, et le levier commun que les neuf dimensions n'avaient pas</t>
         </is>
       </c>
       <c r="C302" s="3" t="inlineStr">
@@ -25740,63 +25808,63 @@
     <row r="303">
       <c r="A303" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">    L24.C04</t>
+        </is>
+      </c>
+      <c r="B303" s="3" t="inlineStr">
+        <is>
+          <t>Un budget mondial n'est pas partageable</t>
+        </is>
+      </c>
+      <c r="C303" s="3" t="inlineStr">
+        <is>
+          <t>brouillon</t>
+        </is>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">    L24.C05</t>
         </is>
       </c>
-      <c r="B303" s="3" t="inlineStr">
+      <c r="B304" s="3" t="inlineStr">
         <is>
           <t>Portée de la tranche</t>
         </is>
       </c>
-      <c r="C303" s="3" t="inlineStr">
-        <is>
-          <t>brouillon</t>
-        </is>
-      </c>
-    </row>
-    <row r="304">
-      <c r="A304" s="6" t="inlineStr">
+      <c r="C304" s="3" t="inlineStr">
+        <is>
+          <t>brouillon</t>
+        </is>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" s="6" t="inlineStr">
         <is>
           <t>L25</t>
         </is>
       </c>
-      <c r="B304" s="6" t="inlineStr">
+      <c r="B305" s="6" t="inlineStr">
         <is>
           <t>Répartition, besoins essentiels et justice sociale</t>
         </is>
       </c>
-      <c r="C304" s="6" t="inlineStr">
+      <c r="C305" s="6" t="inlineStr">
         <is>
           <t>en-cours — 6 chapitre(s)</t>
-        </is>
-      </c>
-    </row>
-    <row r="305">
-      <c r="A305" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    L25.C01</t>
-        </is>
-      </c>
-      <c r="B305" s="3" t="inlineStr">
-        <is>
-          <t>Ce que ce livre doit établir</t>
-        </is>
-      </c>
-      <c r="C305" s="3" t="inlineStr">
-        <is>
-          <t>brouillon</t>
         </is>
       </c>
     </row>
     <row r="306">
       <c r="A306" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L25.C02</t>
+          <t xml:space="preserve">    L25.C01</t>
         </is>
       </c>
       <c r="B306" s="3" t="inlineStr">
         <is>
-          <t>Le noyau dur, et la charge de la preuve renversée</t>
+          <t>Ce que ce livre doit établir</t>
         </is>
       </c>
       <c r="C306" s="3" t="inlineStr">
@@ -25808,12 +25876,12 @@
     <row r="307">
       <c r="A307" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L25.C03</t>
+          <t xml:space="preserve">    L25.C02</t>
         </is>
       </c>
       <c r="B307" s="3" t="inlineStr">
         <is>
-          <t>Ce que le droit oblige à donner, et ce qu'il refuse de réparer</t>
+          <t>Le noyau dur, et la charge de la preuve renversée</t>
         </is>
       </c>
       <c r="C307" s="3" t="inlineStr">
@@ -25825,12 +25893,12 @@
     <row r="308">
       <c r="A308" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L25.C04</t>
+          <t xml:space="preserve">    L25.C03</t>
         </is>
       </c>
       <c r="B308" s="3" t="inlineStr">
         <is>
-          <t>A34 en droit positif, et le critère que le corpus n'avait pas</t>
+          <t>Ce que le droit oblige à donner, et ce qu'il refuse de réparer</t>
         </is>
       </c>
       <c r="C308" s="3" t="inlineStr">
@@ -25842,12 +25910,12 @@
     <row r="309">
       <c r="A309" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L25.C05</t>
+          <t xml:space="preserve">    L25.C04</t>
         </is>
       </c>
       <c r="B309" s="3" t="inlineStr">
         <is>
-          <t>Le droit différencie sans calculer</t>
+          <t>A34 en droit positif, et le critère que le corpus n'avait pas</t>
         </is>
       </c>
       <c r="C309" s="3" t="inlineStr">
@@ -25859,63 +25927,63 @@
     <row r="310">
       <c r="A310" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">    L25.C05</t>
+        </is>
+      </c>
+      <c r="B310" s="3" t="inlineStr">
+        <is>
+          <t>Le droit différencie sans calculer</t>
+        </is>
+      </c>
+      <c r="C310" s="3" t="inlineStr">
+        <is>
+          <t>brouillon</t>
+        </is>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">    L25.C06</t>
         </is>
       </c>
-      <c r="B310" s="3" t="inlineStr">
+      <c r="B311" s="3" t="inlineStr">
         <is>
           <t>Portée de la tranche</t>
         </is>
       </c>
-      <c r="C310" s="3" t="inlineStr">
-        <is>
-          <t>brouillon</t>
-        </is>
-      </c>
-    </row>
-    <row r="311">
-      <c r="A311" s="6" t="inlineStr">
+      <c r="C311" s="3" t="inlineStr">
+        <is>
+          <t>brouillon</t>
+        </is>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" s="6" t="inlineStr">
         <is>
           <t>L26</t>
         </is>
       </c>
-      <c r="B311" s="6" t="inlineStr">
+      <c r="B312" s="6" t="inlineStr">
         <is>
           <t>Thermodynamique, énergie et processus économique</t>
         </is>
       </c>
-      <c r="C311" s="6" t="inlineStr">
+      <c r="C312" s="6" t="inlineStr">
         <is>
           <t>en-cours — 10 chapitre(s)</t>
-        </is>
-      </c>
-    </row>
-    <row r="312">
-      <c r="A312" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    L26.C01</t>
-        </is>
-      </c>
-      <c r="B312" s="3" t="inlineStr">
-        <is>
-          <t>Ce que ce livre doit établir</t>
-        </is>
-      </c>
-      <c r="C312" s="3" t="inlineStr">
-        <is>
-          <t>brouillon</t>
         </is>
       </c>
     </row>
     <row r="313">
       <c r="A313" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L26.C02</t>
+          <t xml:space="preserve">    L26.C01</t>
         </is>
       </c>
       <c r="B313" s="3" t="inlineStr">
         <is>
-          <t>Le stock n'existe pas sous la forme demandée</t>
+          <t>Ce que ce livre doit établir</t>
         </is>
       </c>
       <c r="C313" s="3" t="inlineStr">
@@ -25927,12 +25995,12 @@
     <row r="314">
       <c r="A314" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L26.C03</t>
+          <t xml:space="preserve">    L26.C02</t>
         </is>
       </c>
       <c r="B314" s="3" t="inlineStr">
         <is>
-          <t>La frontière décide du chiffre</t>
+          <t>Le stock n'existe pas sous la forme demandée</t>
         </is>
       </c>
       <c r="C314" s="3" t="inlineStr">
@@ -25944,12 +26012,12 @@
     <row r="315">
       <c r="A315" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L26.C04</t>
+          <t xml:space="preserve">    L26.C03</t>
         </is>
       </c>
       <c r="B315" s="3" t="inlineStr">
         <is>
-          <t>L'effet rebond, et ce que le dispositif en hérite sans être une politique d'efficacité</t>
+          <t>La frontière décide du chiffre</t>
         </is>
       </c>
       <c r="C315" s="3" t="inlineStr">
@@ -25961,12 +26029,12 @@
     <row r="316">
       <c r="A316" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L26.C05</t>
+          <t xml:space="preserve">    L26.C04</t>
         </is>
       </c>
       <c r="B316" s="3" t="inlineStr">
         <is>
-          <t>L'addition n'est pas la substitution</t>
+          <t>L'effet rebond, et ce que le dispositif en hérite sans être une politique d'efficacité</t>
         </is>
       </c>
       <c r="C316" s="3" t="inlineStr">
@@ -25978,12 +26046,12 @@
     <row r="317">
       <c r="A317" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L26.C06</t>
+          <t xml:space="preserve">    L26.C05</t>
         </is>
       </c>
       <c r="B317" s="3" t="inlineStr">
         <is>
-          <t>Portée de la tranche</t>
+          <t>L'addition n'est pas la substitution</t>
         </is>
       </c>
       <c r="C317" s="3" t="inlineStr">
@@ -25995,12 +26063,12 @@
     <row r="318">
       <c r="A318" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L26.C07</t>
+          <t xml:space="preserve">    L26.C06</t>
         </is>
       </c>
       <c r="B318" s="3" t="inlineStr">
         <is>
-          <t>Le fondateur ne propose aucun instrument monétaire</t>
+          <t>Portée de la tranche</t>
         </is>
       </c>
       <c r="C318" s="3" t="inlineStr">
@@ -26012,12 +26080,12 @@
     <row r="319">
       <c r="A319" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L26.C08</t>
+          <t xml:space="preserve">    L26.C07</t>
         </is>
       </c>
       <c r="B319" s="3" t="inlineStr">
         <is>
-          <t>Même un puits gratuit ne donne pas dix</t>
+          <t>Le fondateur ne propose aucun instrument monétaire</t>
         </is>
       </c>
       <c r="C319" s="3" t="inlineStr">
@@ -26029,12 +26097,12 @@
     <row r="320">
       <c r="A320" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L26.C09</t>
+          <t xml:space="preserve">    L26.C08</t>
         </is>
       </c>
       <c r="B320" s="3" t="inlineStr">
         <is>
-          <t>La méthode décide du chiffre</t>
+          <t>Même un puits gratuit ne donne pas dix</t>
         </is>
       </c>
       <c r="C320" s="3" t="inlineStr">
@@ -26046,15 +26114,32 @@
     <row r="321">
       <c r="A321" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">    L26.C09</t>
+        </is>
+      </c>
+      <c r="B321" s="3" t="inlineStr">
+        <is>
+          <t>La méthode décide du chiffre</t>
+        </is>
+      </c>
+      <c r="C321" s="3" t="inlineStr">
+        <is>
+          <t>brouillon</t>
+        </is>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">    L26.C10</t>
         </is>
       </c>
-      <c r="B321" s="3" t="inlineStr">
+      <c r="B322" s="3" t="inlineStr">
         <is>
           <t>La financiarisation produit un découplage apparent</t>
         </is>
       </c>
-      <c r="C321" s="3" t="inlineStr">
+      <c r="C322" s="3" t="inlineStr">
         <is>
           <t>brouillon</t>
         </is>

--- a/plan-des-livres.xlsx
+++ b/plan-des-livres.xlsx
@@ -1095,41 +1095,41 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="2" t="inlineStr">
+      <c r="A16" s="4" t="inlineStr">
         <is>
           <t>L14</t>
         </is>
       </c>
-      <c r="B16" s="3" t="inlineStr">
+      <c r="B16" s="5" t="inlineStr">
         <is>
           <t>Gouverner la preuve : méthodes, vérification et traçabilité</t>
         </is>
       </c>
-      <c r="C16" s="3" t="inlineStr">
+      <c r="C16" s="5" t="inlineStr">
         <is>
           <t>cahier-disciplinaire</t>
         </is>
       </c>
-      <c r="D16" s="3" t="inlineStr">
-        <is>
-          <t>candidat</t>
-        </is>
-      </c>
-      <c r="E16" s="3" t="inlineStr">
+      <c r="D16" s="5" t="inlineStr">
+        <is>
+          <t>en-cours</t>
+        </is>
+      </c>
+      <c r="E16" s="5" t="inlineStr">
         <is>
           <t>non contraignant</t>
         </is>
       </c>
-      <c r="F16" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G16" s="3" t="inlineStr"/>
-      <c r="H16" s="3" t="inlineStr">
+      <c r="F16" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G16" s="5" t="inlineStr"/>
+      <c r="H16" s="5" t="inlineStr">
         <is>
           <t>Rendre publique, reproductible et contestable la méthode de vérification, de provenance et de révision du corpus</t>
         </is>
       </c>
-      <c r="I16" s="3" t="inlineStr">
+      <c r="I16" s="5" t="inlineStr">
         <is>
           <t>discipline — épistémologie documentaire et méthode de vérification</t>
         </is>
@@ -14386,7 +14386,7 @@
       </c>
       <c r="G201" s="3" t="inlineStr">
         <is>
-          <t>descriptif</t>
+          <t>hybride</t>
         </is>
       </c>
       <c r="H201" s="3" t="inlineStr">
@@ -14394,21 +14394,21 @@
           <t>2026-09-08</t>
         </is>
       </c>
-      <c r="I201" s="3" t="inlineStr">
-        <is>
-          <t>oui</t>
-        </is>
-      </c>
+      <c r="I201" s="3" t="inlineStr"/>
       <c r="J201" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K201" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="L201" s="3" t="inlineStr"/>
+      <c r="L201" s="3" t="inlineStr">
+        <is>
+          <t>robustesse, indicateur_de_progres</t>
+        </is>
+      </c>
       <c r="M201" s="3" t="inlineStr">
         <is>
-          <t>L19.C06</t>
+          <t>L1.C15, L8.C34, L12.C01, L13.C01, L18.C10, L26.C07, L26.C09, L26.C10</t>
         </is>
       </c>
       <c r="N201" s="3" t="inlineStr">
@@ -20489,7 +20489,7 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="5">
@@ -20499,7 +20499,7 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6">
@@ -20519,7 +20519,7 @@
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="8">
@@ -20529,7 +20529,7 @@
         </is>
       </c>
       <c r="B8" s="3" t="n">
-        <v>290</v>
+        <v>291</v>
       </c>
     </row>
     <row r="9">
@@ -20569,7 +20569,7 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>1107</v>
+        <v>1108</v>
       </c>
     </row>
     <row r="13">
@@ -20584,7 +20584,7 @@
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>L0, L9, L14, L15</t>
+          <t>L0, L9, L15</t>
         </is>
       </c>
     </row>
@@ -24322,7 +24322,7 @@
       </c>
       <c r="C215" s="6" t="inlineStr">
         <is>
-          <t>candidat — AMORCE SEULE</t>
+          <t>en-cours — 1 chapitre(s)</t>
         </is>
       </c>
     </row>
@@ -24334,7 +24334,7 @@
       </c>
       <c r="B216" s="3" t="inlineStr">
         <is>
-          <t>[AMORCE] Ce que ce livre doit établir</t>
+          <t>Ce que ce livre doit établir</t>
         </is>
       </c>
       <c r="C216" s="3" t="inlineStr">

--- a/plan-des-livres.xlsx
+++ b/plan-des-livres.xlsx
@@ -13,7 +13,7 @@
     <sheet name="Plan par livre" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Chapitres'!$A$1:$N$295</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Chapitres'!$A$1:$N$296</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -1408,7 +1408,7 @@
         </is>
       </c>
       <c r="F23" s="5" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G23" s="5" t="inlineStr"/>
       <c r="H23" s="5" t="inlineStr">
@@ -1638,7 +1638,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N295"/>
+  <dimension ref="A1:N296"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -16251,7 +16251,7 @@
         <v>1</v>
       </c>
       <c r="K230" s="3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L230" s="3" t="inlineStr">
         <is>
@@ -16260,7 +16260,7 @@
       </c>
       <c r="M230" s="3" t="inlineStr">
         <is>
-          <t>L10.C06, L11.C01, L11.C02, L11.C07, L19.C01, L19.C02, L19.C03, L19.C04, L19.C05, L19.C06, L21.C01, L21.C03</t>
+          <t>L10.C06, L11.C01, L11.C02, L11.C07, L19.C01, L19.C02, L19.C03, L19.C04, L19.C05, L19.C06, L21.C01, L21.C03, L21.C08</t>
         </is>
       </c>
       <c r="N230" s="3" t="inlineStr">
@@ -18163,7 +18163,7 @@
       </c>
       <c r="H260" s="3" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="I260" s="3" t="inlineStr"/>
@@ -18171,7 +18171,7 @@
         <v>2</v>
       </c>
       <c r="K260" s="3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L260" s="3" t="inlineStr">
         <is>
@@ -18180,7 +18180,7 @@
       </c>
       <c r="M260" s="3" t="inlineStr">
         <is>
-          <t>L5.C02, L10.C06, L11.C01, L11.C02, L20.C01, L21.C01, L21.C02, L21.C03, L21.C04, L21.C05, L21.C06</t>
+          <t>L5.C02, L10.C06, L11.C01, L11.C02, L20.C01, L21.C01, L21.C02, L21.C03, L21.C04, L21.C05, L21.C06, L21.C08</t>
         </is>
       </c>
       <c r="N260" s="3" t="inlineStr">
@@ -18192,17 +18192,17 @@
     <row r="261">
       <c r="A261" s="2" t="inlineStr">
         <is>
-          <t>L22.C01</t>
+          <t>L21.C08</t>
         </is>
       </c>
       <c r="B261" s="3" t="inlineStr">
         <is>
-          <t>L22</t>
+          <t>L21</t>
         </is>
       </c>
       <c r="C261" s="3" t="inlineStr">
         <is>
-          <t>Ce que ce livre doit établir</t>
+          <t>La norme des infrastructures exige des fonds propres</t>
         </is>
       </c>
       <c r="D261" s="3" t="inlineStr">
@@ -18222,41 +18222,41 @@
       </c>
       <c r="G261" s="3" t="inlineStr">
         <is>
-          <t>descriptif</t>
+          <t>hybride</t>
         </is>
       </c>
       <c r="H261" s="3" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="I261" s="3" t="inlineStr"/>
       <c r="J261" s="3" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K261" s="3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L261" s="3" t="inlineStr">
         <is>
-          <t>architecture_invisible, systeme_monetaire_et_financier, reflux_collectif, reflux_transactionnel, hierarchie_monetaire, monnaie_comme_registre</t>
+          <t>contrepartie_comptable, robustesse, hierarchie_monetaire</t>
         </is>
       </c>
       <c r="M261" s="3" t="inlineStr">
         <is>
-          <t>L1.C09, L1.C19, L5.C09, L11.C02, L11.C05, L11.C09, L11.C27, L21.C03, L21.C04</t>
+          <t>L16.C04, L19.C01, L19.C03, L19.C06, L19.C07, L21.C03, L21.C05, L21.C07</t>
         </is>
       </c>
       <c r="N261" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-22-finance-non-bancaire/c01-ce-que-ce-livre-doit-etablir.md</t>
+          <t>corpus/livre-21-plomberie-financiere-mondiale/c08-la-norme-des-infrastructures-exige-des-fonds-propres.md</t>
         </is>
       </c>
     </row>
     <row r="262">
       <c r="A262" s="2" t="inlineStr">
         <is>
-          <t>L22.C02</t>
+          <t>L22.C01</t>
         </is>
       </c>
       <c r="B262" s="3" t="inlineStr">
@@ -18266,7 +18266,7 @@
       </c>
       <c r="C262" s="3" t="inlineStr">
         <is>
-          <t>Où va la monnaie émise, et pourquoi le reflux ne l'y suit pas</t>
+          <t>Ce que ce livre doit établir</t>
         </is>
       </c>
       <c r="D262" s="3" t="inlineStr">
@@ -18286,41 +18286,41 @@
       </c>
       <c r="G262" s="3" t="inlineStr">
         <is>
-          <t>conception</t>
+          <t>descriptif</t>
         </is>
       </c>
       <c r="H262" s="3" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="I262" s="3" t="inlineStr"/>
       <c r="J262" s="3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K262" s="3" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L262" s="3" t="inlineStr">
         <is>
-          <t>reflux_transactionnel, reflux_collectif, demurrage, monnaie_endogene, architecture_invisible, hierarchie_monetaire</t>
+          <t>architecture_invisible, systeme_monetaire_et_financier, reflux_collectif, reflux_transactionnel, hierarchie_monetaire, monnaie_comme_registre</t>
         </is>
       </c>
       <c r="M262" s="3" t="inlineStr">
         <is>
-          <t>L1.C19, L5.C09, L11.C02, L11.C05, L11.C09, L11.C27, L21.C03, L22.C01, L23.C04, L26.C04</t>
+          <t>L1.C09, L1.C19, L5.C09, L11.C02, L11.C05, L11.C09, L11.C27, L21.C03, L21.C04</t>
         </is>
       </c>
       <c r="N262" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-22-finance-non-bancaire/c02-ou-va-la-monnaie-emise.md</t>
+          <t>corpus/livre-22-finance-non-bancaire/c01-ce-que-ce-livre-doit-etablir.md</t>
         </is>
       </c>
     </row>
     <row r="263">
       <c r="A263" s="2" t="inlineStr">
         <is>
-          <t>L22.C03</t>
+          <t>L22.C02</t>
         </is>
       </c>
       <c r="B263" s="3" t="inlineStr">
@@ -18330,7 +18330,7 @@
       </c>
       <c r="C263" s="3" t="inlineStr">
         <is>
-          <t>Le barème existe déjà, et il a trois pièces que le corpus n'a pas</t>
+          <t>Où va la monnaie émise, et pourquoi le reflux ne l'y suit pas</t>
         </is>
       </c>
       <c r="D263" s="3" t="inlineStr">
@@ -18350,41 +18350,41 @@
       </c>
       <c r="G263" s="3" t="inlineStr">
         <is>
-          <t>hybride</t>
+          <t>conception</t>
         </is>
       </c>
       <c r="H263" s="3" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="I263" s="3" t="inlineStr"/>
       <c r="J263" s="3" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K263" s="3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L263" s="3" t="inlineStr">
         <is>
-          <t>qualification_regenerative, bareme, additionnalite, indicateur_de_progres, communs, plafond_ecologique</t>
+          <t>reflux_transactionnel, reflux_collectif, demurrage, monnaie_endogene, architecture_invisible, hierarchie_monetaire</t>
         </is>
       </c>
       <c r="M263" s="3" t="inlineStr">
         <is>
-          <t>L11.C13, L11.C11, L11.C25, L12.C01, L18.C06, L22.C01, L25.C01</t>
+          <t>L1.C19, L5.C09, L11.C02, L11.C05, L11.C09, L11.C27, L21.C03, L22.C01, L23.C04, L26.C04</t>
         </is>
       </c>
       <c r="N263" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-22-finance-non-bancaire/c03-le-bareme-existe-deja.md</t>
+          <t>corpus/livre-22-finance-non-bancaire/c02-ou-va-la-monnaie-emise.md</t>
         </is>
       </c>
     </row>
     <row r="264">
       <c r="A264" s="2" t="inlineStr">
         <is>
-          <t>L22.C04</t>
+          <t>L22.C03</t>
         </is>
       </c>
       <c r="B264" s="3" t="inlineStr">
@@ -18394,7 +18394,7 @@
       </c>
       <c r="C264" s="3" t="inlineStr">
         <is>
-          <t>Les critères réels ne mesurent pas, ils certifient</t>
+          <t>Le barème existe déjà, et il a trois pièces que le corpus n'a pas</t>
         </is>
       </c>
       <c r="D264" s="3" t="inlineStr">
@@ -18419,7 +18419,7 @@
       </c>
       <c r="H264" s="3" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="I264" s="3" t="inlineStr"/>
@@ -18427,28 +18427,28 @@
         <v>4</v>
       </c>
       <c r="K264" s="3" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L264" s="3" t="inlineStr">
         <is>
-          <t>qualification_regenerative, bareme, additionnalite, communs, valorisation_des_communs, indicateur_de_progres</t>
+          <t>qualification_regenerative, bareme, additionnalite, indicateur_de_progres, communs, plafond_ecologique</t>
         </is>
       </c>
       <c r="M264" s="3" t="inlineStr">
         <is>
-          <t>L6.C06, L11.C13, L11.C16, L11.C25, L13.C01, L14.C01, L18.C06, L22.C03</t>
+          <t>L11.C13, L11.C11, L11.C25, L12.C01, L18.C06, L22.C01, L25.C01</t>
         </is>
       </c>
       <c r="N264" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-22-finance-non-bancaire/c04-les-criteres-reels-ne-mesurent-pas.md</t>
+          <t>corpus/livre-22-finance-non-bancaire/c03-le-bareme-existe-deja.md</t>
         </is>
       </c>
     </row>
     <row r="265">
       <c r="A265" s="2" t="inlineStr">
         <is>
-          <t>L22.C05</t>
+          <t>L22.C04</t>
         </is>
       </c>
       <c r="B265" s="3" t="inlineStr">
@@ -18458,7 +18458,7 @@
       </c>
       <c r="C265" s="3" t="inlineStr">
         <is>
-          <t>L'épargne retraite, et le dilemme du troisième instrument</t>
+          <t>Les critères réels ne mesurent pas, ils certifient</t>
         </is>
       </c>
       <c r="D265" s="3" t="inlineStr">
@@ -18483,36 +18483,36 @@
       </c>
       <c r="H265" s="3" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="I265" s="3" t="inlineStr"/>
       <c r="J265" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K265" s="3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L265" s="3" t="inlineStr">
         <is>
-          <t>reflux_collectif, demurrage, essentiel_insolvable, plancher_social, solvabilite_anticipee, architecture_invisible</t>
+          <t>qualification_regenerative, bareme, additionnalite, communs, valorisation_des_communs, indicateur_de_progres</t>
         </is>
       </c>
       <c r="M265" s="3" t="inlineStr">
         <is>
-          <t>L1.C15, L11.C07, L11.C09, L11.C18, L22.C01, L22.C02, L25.C01</t>
+          <t>L6.C06, L11.C13, L11.C16, L11.C25, L13.C01, L14.C01, L18.C06, L22.C03</t>
         </is>
       </c>
       <c r="N265" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-22-finance-non-bancaire/c05-l-epargne-retraite-et-le-dilemme-du-troisieme-instrument.md</t>
+          <t>corpus/livre-22-finance-non-bancaire/c04-les-criteres-reels-ne-mesurent-pas.md</t>
         </is>
       </c>
     </row>
     <row r="266">
       <c r="A266" s="2" t="inlineStr">
         <is>
-          <t>L22.C06</t>
+          <t>L22.C05</t>
         </is>
       </c>
       <c r="B266" s="3" t="inlineStr">
@@ -18522,7 +18522,7 @@
       </c>
       <c r="C266" s="3" t="inlineStr">
         <is>
-          <t>Qui décide, quand personne ne décide</t>
+          <t>L'épargne retraite, et le dilemme du troisième instrument</t>
         </is>
       </c>
       <c r="D266" s="3" t="inlineStr">
@@ -18552,31 +18552,31 @@
       </c>
       <c r="I266" s="3" t="inlineStr"/>
       <c r="J266" s="3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K266" s="3" t="n">
         <v>4</v>
       </c>
       <c r="L266" s="3" t="inlineStr">
         <is>
-          <t>architecture_invisible, indicateur_de_progres, qualification_regenerative, essentiel_insolvable, fenetre_de_reforme, regle_contre_discretion</t>
+          <t>reflux_collectif, demurrage, essentiel_insolvable, plancher_social, solvabilite_anticipee, architecture_invisible</t>
         </is>
       </c>
       <c r="M266" s="3" t="inlineStr">
         <is>
-          <t>L1.C15, L5.C09, L11.C13, L14.C01, L22.C01, L22.C02, L22.C03, L22.C05</t>
+          <t>L1.C15, L11.C07, L11.C09, L11.C18, L22.C01, L22.C02, L25.C01</t>
         </is>
       </c>
       <c r="N266" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-22-finance-non-bancaire/c06-qui-decide-quand-personne-ne-decide.md</t>
+          <t>corpus/livre-22-finance-non-bancaire/c05-l-epargne-retraite-et-le-dilemme-du-troisieme-instrument.md</t>
         </is>
       </c>
     </row>
     <row r="267">
       <c r="A267" s="2" t="inlineStr">
         <is>
-          <t>L22.C07</t>
+          <t>L22.C06</t>
         </is>
       </c>
       <c r="B267" s="3" t="inlineStr">
@@ -18586,7 +18586,7 @@
       </c>
       <c r="C267" s="3" t="inlineStr">
         <is>
-          <t>Portée de la tranche</t>
+          <t>Qui décide, quand personne ne décide</t>
         </is>
       </c>
       <c r="D267" s="3" t="inlineStr">
@@ -18606,7 +18606,7 @@
       </c>
       <c r="G267" s="3" t="inlineStr">
         <is>
-          <t>descriptif</t>
+          <t>hybride</t>
         </is>
       </c>
       <c r="H267" s="3" t="inlineStr">
@@ -18616,41 +18616,41 @@
       </c>
       <c r="I267" s="3" t="inlineStr"/>
       <c r="J267" s="3" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K267" s="3" t="n">
         <v>4</v>
       </c>
       <c r="L267" s="3" t="inlineStr">
         <is>
-          <t>architecture_invisible, reflux_transactionnel, qualification_regenerative, bareme, essentiel_insolvable</t>
+          <t>architecture_invisible, indicateur_de_progres, qualification_regenerative, essentiel_insolvable, fenetre_de_reforme, regle_contre_discretion</t>
         </is>
       </c>
       <c r="M267" s="3" t="inlineStr">
         <is>
-          <t>L1.C15, L5.C09, L11.C02, L11.C13, L11.C18, L22.C01, L22.C02, L22.C03, L22.C04, L22.C05, L22.C06</t>
+          <t>L1.C15, L5.C09, L11.C13, L14.C01, L22.C01, L22.C02, L22.C03, L22.C05</t>
         </is>
       </c>
       <c r="N267" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-22-finance-non-bancaire/c07-portee-de-la-tranche.md</t>
+          <t>corpus/livre-22-finance-non-bancaire/c06-qui-decide-quand-personne-ne-decide.md</t>
         </is>
       </c>
     </row>
     <row r="268">
       <c r="A268" s="2" t="inlineStr">
         <is>
-          <t>L23.C01</t>
+          <t>L22.C07</t>
         </is>
       </c>
       <c r="B268" s="3" t="inlineStr">
         <is>
-          <t>L23</t>
+          <t>L22</t>
         </is>
       </c>
       <c r="C268" s="3" t="inlineStr">
         <is>
-          <t>Ce que ce livre doit établir</t>
+          <t>Portée de la tranche</t>
         </is>
       </c>
       <c r="D268" s="3" t="inlineStr">
@@ -18670,7 +18670,7 @@
       </c>
       <c r="G268" s="3" t="inlineStr">
         <is>
-          <t>conception</t>
+          <t>descriptif</t>
         </is>
       </c>
       <c r="H268" s="3" t="inlineStr">
@@ -18680,31 +18680,31 @@
       </c>
       <c r="I268" s="3" t="inlineStr"/>
       <c r="J268" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="K268" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="K268" s="3" t="n">
-        <v>3</v>
-      </c>
       <c r="L268" s="3" t="inlineStr">
         <is>
-          <t>bareme, reflux_transactionnel, externalisation, essentiel_insolvable, polycentricite, regle_contre_discretion</t>
+          <t>architecture_invisible, reflux_transactionnel, qualification_regenerative, bareme, essentiel_insolvable</t>
         </is>
       </c>
       <c r="M268" s="3" t="inlineStr">
         <is>
-          <t>L1.C15, L5.C07, L10.C06, L11.C05, L11.C09, L11.C21, L11.C24, L18.C09, L20.C02, L20.C20</t>
+          <t>L1.C15, L5.C09, L11.C02, L11.C13, L11.C18, L22.C01, L22.C02, L22.C03, L22.C04, L22.C05, L22.C06</t>
         </is>
       </c>
       <c r="N268" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-23-fiscalite-mondiale-et-opacite/c01-ce-que-ce-livre-doit-etablir.md</t>
+          <t>corpus/livre-22-finance-non-bancaire/c07-portee-de-la-tranche.md</t>
         </is>
       </c>
     </row>
     <row r="269">
       <c r="A269" s="2" t="inlineStr">
         <is>
-          <t>L23.C02</t>
+          <t>L23.C01</t>
         </is>
       </c>
       <c r="B269" s="3" t="inlineStr">
@@ -18714,7 +18714,7 @@
       </c>
       <c r="C269" s="3" t="inlineStr">
         <is>
-          <t>La compétence que la convention ne crée pas, et le vote qu'elle a gagné</t>
+          <t>Ce que ce livre doit établir</t>
         </is>
       </c>
       <c r="D269" s="3" t="inlineStr">
@@ -18734,7 +18734,7 @@
       </c>
       <c r="G269" s="3" t="inlineStr">
         <is>
-          <t>hybride</t>
+          <t>conception</t>
         </is>
       </c>
       <c r="H269" s="3" t="inlineStr">
@@ -18751,24 +18751,24 @@
       </c>
       <c r="L269" s="3" t="inlineStr">
         <is>
-          <t>polycentricite, bareme, reflux_transactionnel, seuil_d_activation, regle_contre_discretion, externalisation</t>
+          <t>bareme, reflux_transactionnel, externalisation, essentiel_insolvable, polycentricite, regle_contre_discretion</t>
         </is>
       </c>
       <c r="M269" s="3" t="inlineStr">
         <is>
-          <t>L1.C25, L5.C04, L10.C06, L11.C21, L20.C02, L20.C20, L23.C01</t>
+          <t>L1.C15, L5.C07, L10.C06, L11.C05, L11.C09, L11.C21, L11.C24, L18.C09, L20.C02, L20.C20</t>
         </is>
       </c>
       <c r="N269" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-23-fiscalite-mondiale-et-opacite/c02-la-competence-que-la-convention-ne-cree-pas.md</t>
+          <t>corpus/livre-23-fiscalite-mondiale-et-opacite/c01-ce-que-ce-livre-doit-etablir.md</t>
         </is>
       </c>
     </row>
     <row r="270">
       <c r="A270" s="2" t="inlineStr">
         <is>
-          <t>L23.C03</t>
+          <t>L23.C02</t>
         </is>
       </c>
       <c r="B270" s="3" t="inlineStr">
@@ -18778,7 +18778,7 @@
       </c>
       <c r="C270" s="3" t="inlineStr">
         <is>
-          <t>F8 appliqué à une négociation en cours, et le résultat n'est pas le désarmement</t>
+          <t>La compétence que la convention ne crée pas, et le vote qu'elle a gagné</t>
         </is>
       </c>
       <c r="D270" s="3" t="inlineStr">
@@ -18815,24 +18815,24 @@
       </c>
       <c r="L270" s="3" t="inlineStr">
         <is>
-          <t>regle_contre_discretion, polycentricite, seuil_d_activation, bareme, externalisation</t>
+          <t>polycentricite, bareme, reflux_transactionnel, seuil_d_activation, regle_contre_discretion, externalisation</t>
         </is>
       </c>
       <c r="M270" s="3" t="inlineStr">
         <is>
-          <t>L5.C04, L6.C09, L11.C21, L20.C02, L20.C13, L23.C01, L23.C02</t>
+          <t>L1.C25, L5.C04, L10.C06, L11.C21, L20.C02, L20.C20, L23.C01</t>
         </is>
       </c>
       <c r="N270" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-23-fiscalite-mondiale-et-opacite/c03-f8-applique-a-une-negociation-en-cours.md</t>
+          <t>corpus/livre-23-fiscalite-mondiale-et-opacite/c02-la-competence-que-la-convention-ne-cree-pas.md</t>
         </is>
       </c>
     </row>
     <row r="271">
       <c r="A271" s="2" t="inlineStr">
         <is>
-          <t>L23.C04</t>
+          <t>L23.C03</t>
         </is>
       </c>
       <c r="B271" s="3" t="inlineStr">
@@ -18842,7 +18842,7 @@
       </c>
       <c r="C271" s="3" t="inlineStr">
         <is>
-          <t>La transparence que le corpus supposait a été invalidée</t>
+          <t>F8 appliqué à une négociation en cours, et le résultat n'est pas le désarmement</t>
         </is>
       </c>
       <c r="D271" s="3" t="inlineStr">
@@ -18872,31 +18872,31 @@
       </c>
       <c r="I271" s="3" t="inlineStr"/>
       <c r="J271" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K271" s="3" t="n">
         <v>3</v>
       </c>
       <c r="L271" s="3" t="inlineStr">
         <is>
-          <t>regle_contre_discretion, externalisation, bareme, polycentricite, architecture_invisible</t>
+          <t>regle_contre_discretion, polycentricite, seuil_d_activation, bareme, externalisation</t>
         </is>
       </c>
       <c r="M271" s="3" t="inlineStr">
         <is>
-          <t>L6.C09, L11.C13, L11.C25, L20.C20, L23.C01, L23.C02, L23.C03</t>
+          <t>L5.C04, L6.C09, L11.C21, L20.C02, L20.C13, L23.C01, L23.C02</t>
         </is>
       </c>
       <c r="N271" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-23-fiscalite-mondiale-et-opacite/c04-la-transparence-que-le-corpus-supposait-a-ete-invalidee.md</t>
+          <t>corpus/livre-23-fiscalite-mondiale-et-opacite/c03-f8-applique-a-une-negociation-en-cours.md</t>
         </is>
       </c>
     </row>
     <row r="272">
       <c r="A272" s="2" t="inlineStr">
         <is>
-          <t>L23.C05</t>
+          <t>L23.C04</t>
         </is>
       </c>
       <c r="B272" s="3" t="inlineStr">
@@ -18906,7 +18906,7 @@
       </c>
       <c r="C272" s="3" t="inlineStr">
         <is>
-          <t>Intéresser le percepteur, et ce que le taux révèle</t>
+          <t>La transparence que le corpus supposait a été invalidée</t>
         </is>
       </c>
       <c r="D272" s="3" t="inlineStr">
@@ -18943,24 +18943,24 @@
       </c>
       <c r="L272" s="3" t="inlineStr">
         <is>
-          <t>bareme, reflux_transactionnel, regle_contre_discretion, polycentricite, seuil_d_activation</t>
+          <t>regle_contre_discretion, externalisation, bareme, polycentricite, architecture_invisible</t>
         </is>
       </c>
       <c r="M272" s="3" t="inlineStr">
         <is>
-          <t>L11.C21, L11.C24, L18.C09, L20.C20, L23.C01, L23.C02, L23.C03</t>
+          <t>L6.C09, L11.C13, L11.C25, L20.C20, L23.C01, L23.C02, L23.C03</t>
         </is>
       </c>
       <c r="N272" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-23-fiscalite-mondiale-et-opacite/c05-interesser-le-percepteur-et-ce-que-le-taux-revele.md</t>
+          <t>corpus/livre-23-fiscalite-mondiale-et-opacite/c04-la-transparence-que-le-corpus-supposait-a-ete-invalidee.md</t>
         </is>
       </c>
     </row>
     <row r="273">
       <c r="A273" s="2" t="inlineStr">
         <is>
-          <t>L23.C06</t>
+          <t>L23.C05</t>
         </is>
       </c>
       <c r="B273" s="3" t="inlineStr">
@@ -18970,7 +18970,7 @@
       </c>
       <c r="C273" s="3" t="inlineStr">
         <is>
-          <t>L'arbre appliqué à la fonte, et il ne reste que deux branches</t>
+          <t>Intéresser le percepteur, et ce que le taux révèle</t>
         </is>
       </c>
       <c r="D273" s="3" t="inlineStr">
@@ -18990,7 +18990,7 @@
       </c>
       <c r="G273" s="3" t="inlineStr">
         <is>
-          <t>conception</t>
+          <t>hybride</t>
         </is>
       </c>
       <c r="H273" s="3" t="inlineStr">
@@ -19000,31 +19000,31 @@
       </c>
       <c r="I273" s="3" t="inlineStr"/>
       <c r="J273" s="3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K273" s="3" t="n">
         <v>3</v>
       </c>
       <c r="L273" s="3" t="inlineStr">
         <is>
-          <t>bareme, reflux_transactionnel, monnaie_fondante, demurrage, regle_contre_discretion, essentiel_insolvable</t>
+          <t>bareme, reflux_transactionnel, regle_contre_discretion, polycentricite, seuil_d_activation</t>
         </is>
       </c>
       <c r="M273" s="3" t="inlineStr">
         <is>
-          <t>L10.C06, L11.C05, L11.C09, L11.C21, L11.C24, L18.C09, L20.C02, L23.C01, L23.C02, L23.C03, L23.C04, L23.C05</t>
+          <t>L11.C21, L11.C24, L18.C09, L20.C20, L23.C01, L23.C02, L23.C03</t>
         </is>
       </c>
       <c r="N273" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-23-fiscalite-mondiale-et-opacite/c06-l-arbre-applique-a-la-fonte.md</t>
+          <t>corpus/livre-23-fiscalite-mondiale-et-opacite/c05-interesser-le-percepteur-et-ce-que-le-taux-revele.md</t>
         </is>
       </c>
     </row>
     <row r="274">
       <c r="A274" s="2" t="inlineStr">
         <is>
-          <t>L23.C07</t>
+          <t>L23.C06</t>
         </is>
       </c>
       <c r="B274" s="3" t="inlineStr">
@@ -19034,7 +19034,7 @@
       </c>
       <c r="C274" s="3" t="inlineStr">
         <is>
-          <t>Portée de la tranche, et la moitié qui n'est pas commencée</t>
+          <t>L'arbre appliqué à la fonte, et il ne reste que deux branches</t>
         </is>
       </c>
       <c r="D274" s="3" t="inlineStr">
@@ -19064,41 +19064,41 @@
       </c>
       <c r="I274" s="3" t="inlineStr"/>
       <c r="J274" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K274" s="3" t="n">
         <v>3</v>
       </c>
       <c r="L274" s="3" t="inlineStr">
         <is>
-          <t>bareme, reflux_transactionnel, externalisation, regle_contre_discretion, polycentricite, essentiel_insolvable</t>
+          <t>bareme, reflux_transactionnel, monnaie_fondante, demurrage, regle_contre_discretion, essentiel_insolvable</t>
         </is>
       </c>
       <c r="M274" s="3" t="inlineStr">
         <is>
-          <t>L10.C06, L11.C05, L11.C21, L11.C25, L18.C09, L20.C20, L23.C01, L23.C02, L23.C03, L23.C04, L23.C05, L23.C06</t>
+          <t>L10.C06, L11.C05, L11.C09, L11.C21, L11.C24, L18.C09, L20.C02, L23.C01, L23.C02, L23.C03, L23.C04, L23.C05</t>
         </is>
       </c>
       <c r="N274" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-23-fiscalite-mondiale-et-opacite/c07-portee-de-la-tranche.md</t>
+          <t>corpus/livre-23-fiscalite-mondiale-et-opacite/c06-l-arbre-applique-a-la-fonte.md</t>
         </is>
       </c>
     </row>
     <row r="275">
       <c r="A275" s="2" t="inlineStr">
         <is>
-          <t>L24.C01</t>
+          <t>L23.C07</t>
         </is>
       </c>
       <c r="B275" s="3" t="inlineStr">
         <is>
-          <t>L24</t>
+          <t>L23</t>
         </is>
       </c>
       <c r="C275" s="3" t="inlineStr">
         <is>
-          <t>Ce que ce livre doit établir</t>
+          <t>Portée de la tranche, et la moitié qui n'est pas commencée</t>
         </is>
       </c>
       <c r="D275" s="3" t="inlineStr">
@@ -19118,7 +19118,7 @@
       </c>
       <c r="G275" s="3" t="inlineStr">
         <is>
-          <t>descriptif</t>
+          <t>conception</t>
         </is>
       </c>
       <c r="H275" s="3" t="inlineStr">
@@ -19128,31 +19128,31 @@
       </c>
       <c r="I275" s="3" t="inlineStr"/>
       <c r="J275" s="3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K275" s="3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L275" s="3" t="inlineStr">
         <is>
-          <t>limites_planetaires, plafond_ecologique, entropie, decouplage, degeneratif, qualification_regenerative, essentiel_insolvable</t>
+          <t>bareme, reflux_transactionnel, externalisation, regle_contre_discretion, polycentricite, essentiel_insolvable</t>
         </is>
       </c>
       <c r="M275" s="3" t="inlineStr">
         <is>
-          <t>L1.C15, L5.C08, L11.C13, L18.C01, L18.C04, L22.C04, L26.C01</t>
+          <t>L10.C06, L11.C05, L11.C21, L11.C25, L18.C09, L20.C20, L23.C01, L23.C02, L23.C03, L23.C04, L23.C05, L23.C06</t>
         </is>
       </c>
       <c r="N275" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-24-conditions-materielles-de-la-vie/c01-ce-que-ce-livre-doit-etablir.md</t>
+          <t>corpus/livre-23-fiscalite-mondiale-et-opacite/c07-portee-de-la-tranche.md</t>
         </is>
       </c>
     </row>
     <row r="276">
       <c r="A276" s="2" t="inlineStr">
         <is>
-          <t>L24.C02</t>
+          <t>L24.C01</t>
         </is>
       </c>
       <c r="B276" s="3" t="inlineStr">
@@ -19162,7 +19162,7 @@
       </c>
       <c r="C276" s="3" t="inlineStr">
         <is>
-          <t>Le seuil juste est plus strict que le seuil sûr</t>
+          <t>Ce que ce livre doit établir</t>
         </is>
       </c>
       <c r="D276" s="3" t="inlineStr">
@@ -19182,7 +19182,7 @@
       </c>
       <c r="G276" s="3" t="inlineStr">
         <is>
-          <t>hybride</t>
+          <t>descriptif</t>
         </is>
       </c>
       <c r="H276" s="3" t="inlineStr">
@@ -19199,24 +19199,24 @@
       </c>
       <c r="L276" s="3" t="inlineStr">
         <is>
-          <t>limites_planetaires, plafond_ecologique, plancher_social, dette_ecologique, essentiel_insolvable, qualification_regenerative</t>
+          <t>limites_planetaires, plafond_ecologique, entropie, decouplage, degeneratif, qualification_regenerative, essentiel_insolvable</t>
         </is>
       </c>
       <c r="M276" s="3" t="inlineStr">
         <is>
-          <t>L1.C15, L11.C13, L12.C01, L18.C01, L24.C01, L25.C01</t>
+          <t>L1.C15, L5.C08, L11.C13, L18.C01, L18.C04, L22.C04, L26.C01</t>
         </is>
       </c>
       <c r="N276" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-24-conditions-materielles-de-la-vie/c02-le-seuil-juste-est-plus-strict-que-le-seuil-sur.md</t>
+          <t>corpus/livre-24-conditions-materielles-de-la-vie/c01-ce-que-ce-livre-doit-etablir.md</t>
         </is>
       </c>
     </row>
     <row r="277">
       <c r="A277" s="2" t="inlineStr">
         <is>
-          <t>L24.C03</t>
+          <t>L24.C02</t>
         </is>
       </c>
       <c r="B277" s="3" t="inlineStr">
@@ -19226,7 +19226,7 @@
       </c>
       <c r="C277" s="3" t="inlineStr">
         <is>
-          <t>La matière, et le levier commun que les neuf dimensions n'avaient pas</t>
+          <t>Le seuil juste est plus strict que le seuil sûr</t>
         </is>
       </c>
       <c r="D277" s="3" t="inlineStr">
@@ -19263,24 +19263,24 @@
       </c>
       <c r="L277" s="3" t="inlineStr">
         <is>
-          <t>limites_planetaires, decouplage, effet_rebond, sobriete, entropie, plafond_ecologique, externalisation, degeneratif</t>
+          <t>limites_planetaires, plafond_ecologique, plancher_social, dette_ecologique, essentiel_insolvable, qualification_regenerative</t>
         </is>
       </c>
       <c r="M277" s="3" t="inlineStr">
         <is>
-          <t>L1.C15, L11.C13, L17.C01, L18.C04, L24.C01, L24.C02, L26.C01</t>
+          <t>L1.C15, L11.C13, L12.C01, L18.C01, L24.C01, L25.C01</t>
         </is>
       </c>
       <c r="N277" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-24-conditions-materielles-de-la-vie/c03-la-matiere-et-le-levier-commun.md</t>
+          <t>corpus/livre-24-conditions-materielles-de-la-vie/c02-le-seuil-juste-est-plus-strict-que-le-seuil-sur.md</t>
         </is>
       </c>
     </row>
     <row r="278">
       <c r="A278" s="2" t="inlineStr">
         <is>
-          <t>L24.C04</t>
+          <t>L24.C03</t>
         </is>
       </c>
       <c r="B278" s="3" t="inlineStr">
@@ -19290,7 +19290,7 @@
       </c>
       <c r="C278" s="3" t="inlineStr">
         <is>
-          <t>Un budget mondial n'est pas partageable</t>
+          <t>La matière, et le levier commun que les neuf dimensions n'avaient pas</t>
         </is>
       </c>
       <c r="D278" s="3" t="inlineStr">
@@ -19327,24 +19327,24 @@
       </c>
       <c r="L278" s="3" t="inlineStr">
         <is>
-          <t>limites_planetaires, plafond_ecologique, communs, qualification_regenerative, externalisation, polycentricite</t>
+          <t>limites_planetaires, decouplage, effet_rebond, sobriete, entropie, plafond_ecologique, externalisation, degeneratif</t>
         </is>
       </c>
       <c r="M278" s="3" t="inlineStr">
         <is>
-          <t>L11.C13, L11.C24, L22.C04, L24.C01, L24.C02, L24.C03, L25.C05</t>
+          <t>L1.C15, L11.C13, L17.C01, L18.C04, L24.C01, L24.C02, L26.C01</t>
         </is>
       </c>
       <c r="N278" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-24-conditions-materielles-de-la-vie/c04-un-budget-mondial-n-est-pas-partageable.md</t>
+          <t>corpus/livre-24-conditions-materielles-de-la-vie/c03-la-matiere-et-le-levier-commun.md</t>
         </is>
       </c>
     </row>
     <row r="279">
       <c r="A279" s="2" t="inlineStr">
         <is>
-          <t>L24.C05</t>
+          <t>L24.C04</t>
         </is>
       </c>
       <c r="B279" s="3" t="inlineStr">
@@ -19354,7 +19354,7 @@
       </c>
       <c r="C279" s="3" t="inlineStr">
         <is>
-          <t>Portée de la tranche</t>
+          <t>Un budget mondial n'est pas partageable</t>
         </is>
       </c>
       <c r="D279" s="3" t="inlineStr">
@@ -19374,51 +19374,51 @@
       </c>
       <c r="G279" s="3" t="inlineStr">
         <is>
-          <t>descriptif</t>
+          <t>hybride</t>
         </is>
       </c>
       <c r="H279" s="3" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="I279" s="3" t="inlineStr"/>
       <c r="J279" s="3" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K279" s="3" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L279" s="3" t="inlineStr">
         <is>
-          <t>limites_planetaires, plafond_ecologique, plancher_social, decouplage, qualification_regenerative, entropie</t>
+          <t>limites_planetaires, plafond_ecologique, communs, qualification_regenerative, externalisation, polycentricite</t>
         </is>
       </c>
       <c r="M279" s="3" t="inlineStr">
         <is>
-          <t>L11.C13, L11.C24, L18.C01, L22.C04, L24.C01, L24.C02, L24.C03, L24.C04, L25.C05, L26.C01, L26.C02, L17.C05</t>
+          <t>L11.C13, L11.C24, L22.C04, L24.C01, L24.C02, L24.C03, L25.C05</t>
         </is>
       </c>
       <c r="N279" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-24-conditions-materielles-de-la-vie/c05-portee-de-la-tranche.md</t>
+          <t>corpus/livre-24-conditions-materielles-de-la-vie/c04-un-budget-mondial-n-est-pas-partageable.md</t>
         </is>
       </c>
     </row>
     <row r="280">
       <c r="A280" s="2" t="inlineStr">
         <is>
-          <t>L25.C01</t>
+          <t>L24.C05</t>
         </is>
       </c>
       <c r="B280" s="3" t="inlineStr">
         <is>
-          <t>L25</t>
+          <t>L24</t>
         </is>
       </c>
       <c r="C280" s="3" t="inlineStr">
         <is>
-          <t>Ce que ce livre doit établir</t>
+          <t>Portée de la tranche</t>
         </is>
       </c>
       <c r="D280" s="3" t="inlineStr">
@@ -19443,36 +19443,36 @@
       </c>
       <c r="H280" s="3" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="I280" s="3" t="inlineStr"/>
       <c r="J280" s="3" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K280" s="3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L280" s="3" t="inlineStr">
         <is>
-          <t>plancher_social, plafond_ecologique, essentiel_insolvable, dette_ecologique, communs, solvabilite_anticipee</t>
+          <t>limites_planetaires, plafond_ecologique, plancher_social, decouplage, qualification_regenerative, entropie</t>
         </is>
       </c>
       <c r="M280" s="3" t="inlineStr">
         <is>
-          <t>L1.C15, L11.C09, L11.C18, L12.C01, L24.C01, L24.C02, L24.C03</t>
+          <t>L11.C13, L11.C24, L18.C01, L22.C04, L24.C01, L24.C02, L24.C03, L24.C04, L25.C05, L26.C01, L26.C02, L17.C05</t>
         </is>
       </c>
       <c r="N280" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-25-repartition-et-justice-sociale/c01-ce-que-ce-livre-doit-etablir.md</t>
+          <t>corpus/livre-24-conditions-materielles-de-la-vie/c05-portee-de-la-tranche.md</t>
         </is>
       </c>
     </row>
     <row r="281">
       <c r="A281" s="2" t="inlineStr">
         <is>
-          <t>L25.C02</t>
+          <t>L25.C01</t>
         </is>
       </c>
       <c r="B281" s="3" t="inlineStr">
@@ -19482,7 +19482,7 @@
       </c>
       <c r="C281" s="3" t="inlineStr">
         <is>
-          <t>Le noyau dur, et la charge de la preuve renversée</t>
+          <t>Ce que ce livre doit établir</t>
         </is>
       </c>
       <c r="D281" s="3" t="inlineStr">
@@ -19502,7 +19502,7 @@
       </c>
       <c r="G281" s="3" t="inlineStr">
         <is>
-          <t>hybride</t>
+          <t>descriptif</t>
         </is>
       </c>
       <c r="H281" s="3" t="inlineStr">
@@ -19519,24 +19519,24 @@
       </c>
       <c r="L281" s="3" t="inlineStr">
         <is>
-          <t>plancher_social, essentiel_insolvable, plafond_ecologique, solvabilite_anticipee, regle_contre_discretion</t>
+          <t>plancher_social, plafond_ecologique, essentiel_insolvable, dette_ecologique, communs, solvabilite_anticipee</t>
         </is>
       </c>
       <c r="M281" s="3" t="inlineStr">
         <is>
-          <t>L1.C15, L11.C09, L11.C18, L22.C02, L22.C04, L24.C02, L25.C01</t>
+          <t>L1.C15, L11.C09, L11.C18, L12.C01, L24.C01, L24.C02, L24.C03</t>
         </is>
       </c>
       <c r="N281" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-25-repartition-et-justice-sociale/c02-le-noyau-dur-et-la-charge-de-la-preuve.md</t>
+          <t>corpus/livre-25-repartition-et-justice-sociale/c01-ce-que-ce-livre-doit-etablir.md</t>
         </is>
       </c>
     </row>
     <row r="282">
       <c r="A282" s="2" t="inlineStr">
         <is>
-          <t>L25.C03</t>
+          <t>L25.C02</t>
         </is>
       </c>
       <c r="B282" s="3" t="inlineStr">
@@ -19546,7 +19546,7 @@
       </c>
       <c r="C282" s="3" t="inlineStr">
         <is>
-          <t>Ce que le droit oblige à donner, et ce qu'il refuse de réparer</t>
+          <t>Le noyau dur, et la charge de la preuve renversée</t>
         </is>
       </c>
       <c r="D282" s="3" t="inlineStr">
@@ -19576,31 +19576,31 @@
       </c>
       <c r="I282" s="3" t="inlineStr"/>
       <c r="J282" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K282" s="3" t="n">
         <v>4</v>
       </c>
       <c r="L282" s="3" t="inlineStr">
         <is>
-          <t>dette_ecologique, plancher_social, creation_monetaire, reflux_collectif, essentiel_insolvable, solvabilite_anticipee</t>
+          <t>plancher_social, essentiel_insolvable, plafond_ecologique, solvabilite_anticipee, regle_contre_discretion</t>
         </is>
       </c>
       <c r="M282" s="3" t="inlineStr">
         <is>
-          <t>L1.C20, L11.C01, L20.C01, L24.C02, L25.C01, L25.C02</t>
+          <t>L1.C15, L11.C09, L11.C18, L22.C02, L22.C04, L24.C02, L25.C01</t>
         </is>
       </c>
       <c r="N282" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-25-repartition-et-justice-sociale/c03-ce-que-le-droit-oblige-a-donner.md</t>
+          <t>corpus/livre-25-repartition-et-justice-sociale/c02-le-noyau-dur-et-la-charge-de-la-preuve.md</t>
         </is>
       </c>
     </row>
     <row r="283">
       <c r="A283" s="2" t="inlineStr">
         <is>
-          <t>L25.C04</t>
+          <t>L25.C03</t>
         </is>
       </c>
       <c r="B283" s="3" t="inlineStr">
@@ -19610,7 +19610,7 @@
       </c>
       <c r="C283" s="3" t="inlineStr">
         <is>
-          <t>A34 en droit positif, et le critère que le corpus n'avait pas</t>
+          <t>Ce que le droit oblige à donner, et ce qu'il refuse de réparer</t>
         </is>
       </c>
       <c r="D283" s="3" t="inlineStr">
@@ -19640,31 +19640,31 @@
       </c>
       <c r="I283" s="3" t="inlineStr"/>
       <c r="J283" s="3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K283" s="3" t="n">
         <v>4</v>
       </c>
       <c r="L283" s="3" t="inlineStr">
         <is>
-          <t>plancher_social, bareme, essentiel_insolvable, sobriete, affectation_des_instruments, reflux_transactionnel</t>
+          <t>dette_ecologique, plancher_social, creation_monetaire, reflux_collectif, essentiel_insolvable, solvabilite_anticipee</t>
         </is>
       </c>
       <c r="M283" s="3" t="inlineStr">
         <is>
-          <t>L1.C15, L11.C09, L11.C18, L11.C21, L22.C02, L24.C03, L25.C01, L25.C02</t>
+          <t>L1.C20, L11.C01, L20.C01, L24.C02, L25.C01, L25.C02</t>
         </is>
       </c>
       <c r="N283" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-25-repartition-et-justice-sociale/c04-a34-en-droit-positif.md</t>
+          <t>corpus/livre-25-repartition-et-justice-sociale/c03-ce-que-le-droit-oblige-a-donner.md</t>
         </is>
       </c>
     </row>
     <row r="284">
       <c r="A284" s="2" t="inlineStr">
         <is>
-          <t>L25.C05</t>
+          <t>L25.C04</t>
         </is>
       </c>
       <c r="B284" s="3" t="inlineStr">
@@ -19674,7 +19674,7 @@
       </c>
       <c r="C284" s="3" t="inlineStr">
         <is>
-          <t>Le droit différencie sans calculer</t>
+          <t>A34 en droit positif, et le critère que le corpus n'avait pas</t>
         </is>
       </c>
       <c r="D284" s="3" t="inlineStr">
@@ -19704,31 +19704,31 @@
       </c>
       <c r="I284" s="3" t="inlineStr"/>
       <c r="J284" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K284" s="3" t="n">
         <v>4</v>
       </c>
       <c r="L284" s="3" t="inlineStr">
         <is>
-          <t>dette_ecologique, plancher_social, plafond_ecologique, bareme, indicateur_de_progres, polycentricite</t>
+          <t>plancher_social, bareme, essentiel_insolvable, sobriete, affectation_des_instruments, reflux_transactionnel</t>
         </is>
       </c>
       <c r="M284" s="3" t="inlineStr">
         <is>
-          <t>L11.C13, L22.C04, L22.C06, L24.C01, L24.C02, L25.C01, L25.C02, L25.C03, L25.C04</t>
+          <t>L1.C15, L11.C09, L11.C18, L11.C21, L22.C02, L24.C03, L25.C01, L25.C02</t>
         </is>
       </c>
       <c r="N284" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-25-repartition-et-justice-sociale/c05-le-droit-differencie-sans-calculer.md</t>
+          <t>corpus/livre-25-repartition-et-justice-sociale/c04-a34-en-droit-positif.md</t>
         </is>
       </c>
     </row>
     <row r="285">
       <c r="A285" s="2" t="inlineStr">
         <is>
-          <t>L25.C06</t>
+          <t>L25.C05</t>
         </is>
       </c>
       <c r="B285" s="3" t="inlineStr">
@@ -19738,7 +19738,7 @@
       </c>
       <c r="C285" s="3" t="inlineStr">
         <is>
-          <t>Portée de la tranche</t>
+          <t>Le droit différencie sans calculer</t>
         </is>
       </c>
       <c r="D285" s="3" t="inlineStr">
@@ -19758,7 +19758,7 @@
       </c>
       <c r="G285" s="3" t="inlineStr">
         <is>
-          <t>descriptif</t>
+          <t>hybride</t>
         </is>
       </c>
       <c r="H285" s="3" t="inlineStr">
@@ -19768,41 +19768,41 @@
       </c>
       <c r="I285" s="3" t="inlineStr"/>
       <c r="J285" s="3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K285" s="3" t="n">
         <v>4</v>
       </c>
       <c r="L285" s="3" t="inlineStr">
         <is>
-          <t>plancher_social, plafond_ecologique, dette_ecologique, essentiel_insolvable, bareme</t>
+          <t>dette_ecologique, plancher_social, plafond_ecologique, bareme, indicateur_de_progres, polycentricite</t>
         </is>
       </c>
       <c r="M285" s="3" t="inlineStr">
         <is>
-          <t>L5.C09, L11.C09, L11.C18, L24.C02, L25.C01, L25.C02, L25.C03, L25.C04, L25.C05</t>
+          <t>L11.C13, L22.C04, L22.C06, L24.C01, L24.C02, L25.C01, L25.C02, L25.C03, L25.C04</t>
         </is>
       </c>
       <c r="N285" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-25-repartition-et-justice-sociale/c06-portee-de-la-tranche.md</t>
+          <t>corpus/livre-25-repartition-et-justice-sociale/c05-le-droit-differencie-sans-calculer.md</t>
         </is>
       </c>
     </row>
     <row r="286">
       <c r="A286" s="2" t="inlineStr">
         <is>
-          <t>L26.C01</t>
+          <t>L25.C06</t>
         </is>
       </c>
       <c r="B286" s="3" t="inlineStr">
         <is>
-          <t>L26</t>
+          <t>L25</t>
         </is>
       </c>
       <c r="C286" s="3" t="inlineStr">
         <is>
-          <t>Ce que ce livre doit établir</t>
+          <t>Portée de la tranche</t>
         </is>
       </c>
       <c r="D286" s="3" t="inlineStr">
@@ -19822,41 +19822,41 @@
       </c>
       <c r="G286" s="3" t="inlineStr">
         <is>
-          <t>hybride</t>
+          <t>descriptif</t>
         </is>
       </c>
       <c r="H286" s="3" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="I286" s="3" t="inlineStr"/>
       <c r="J286" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K286" s="3" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="L286" s="3" t="inlineStr">
         <is>
-          <t>entropie, decouplage, effet_rebond, limites_planetaires, sobriete, degeneratif, qualification_regenerative</t>
+          <t>plancher_social, plafond_ecologique, dette_ecologique, essentiel_insolvable, bareme</t>
         </is>
       </c>
       <c r="M286" s="3" t="inlineStr">
         <is>
-          <t>L1.C03, L1.C15, L1.C17, L8.C13, L8.C34, L11.C13, L18.C04, L24.C03, L24.C05, L17.C02, L26.C10</t>
+          <t>L5.C09, L11.C09, L11.C18, L24.C02, L25.C01, L25.C02, L25.C03, L25.C04, L25.C05</t>
         </is>
       </c>
       <c r="N286" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-26-thermodynamique-et-processus-economique/c01-ce-que-ce-livre-doit-etablir.md</t>
+          <t>corpus/livre-25-repartition-et-justice-sociale/c06-portee-de-la-tranche.md</t>
         </is>
       </c>
     </row>
     <row r="287">
       <c r="A287" s="2" t="inlineStr">
         <is>
-          <t>L26.C02</t>
+          <t>L26.C01</t>
         </is>
       </c>
       <c r="B287" s="3" t="inlineStr">
@@ -19866,7 +19866,7 @@
       </c>
       <c r="C287" s="3" t="inlineStr">
         <is>
-          <t>Le stock n'existe pas sous la forme demandée</t>
+          <t>Ce que ce livre doit établir</t>
         </is>
       </c>
       <c r="D287" s="3" t="inlineStr">
@@ -19896,31 +19896,31 @@
       </c>
       <c r="I287" s="3" t="inlineStr"/>
       <c r="J287" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K287" s="3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L287" s="3" t="inlineStr">
         <is>
-          <t>entropie, bareme, limites_planetaires, decouplage, sobriete, fausse_richesse</t>
+          <t>entropie, decouplage, effet_rebond, limites_planetaires, sobriete, degeneratif, qualification_regenerative</t>
         </is>
       </c>
       <c r="M287" s="3" t="inlineStr">
         <is>
-          <t>L1.C15, L11.C13, L11.C24, L18.C04, L22.C04, L24.C03, L24.C05, L26.C01, L17.C02</t>
+          <t>L1.C03, L1.C15, L1.C17, L8.C13, L8.C34, L11.C13, L18.C04, L24.C03, L24.C05, L17.C02, L26.C10</t>
         </is>
       </c>
       <c r="N287" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-26-thermodynamique-et-processus-economique/c02-le-stock-n-existe-pas-sous-la-forme-demandee.md</t>
+          <t>corpus/livre-26-thermodynamique-et-processus-economique/c01-ce-que-ce-livre-doit-etablir.md</t>
         </is>
       </c>
     </row>
     <row r="288">
       <c r="A288" s="2" t="inlineStr">
         <is>
-          <t>L26.C03</t>
+          <t>L26.C02</t>
         </is>
       </c>
       <c r="B288" s="3" t="inlineStr">
@@ -19930,7 +19930,7 @@
       </c>
       <c r="C288" s="3" t="inlineStr">
         <is>
-          <t>La frontière décide du chiffre</t>
+          <t>Le stock n'existe pas sous la forme demandée</t>
         </is>
       </c>
       <c r="D288" s="3" t="inlineStr">
@@ -19960,31 +19960,31 @@
       </c>
       <c r="I288" s="3" t="inlineStr"/>
       <c r="J288" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K288" s="3" t="n">
         <v>5</v>
       </c>
       <c r="L288" s="3" t="inlineStr">
         <is>
-          <t>entropie, decouplage, sobriete, limites_planetaires, robustesse, bareme</t>
+          <t>entropie, bareme, limites_planetaires, decouplage, sobriete, fausse_richesse</t>
         </is>
       </c>
       <c r="M288" s="3" t="inlineStr">
         <is>
-          <t>L11.C10, L11.C13, L11.C24, L18.C04, L18.C09, L24.C03, L24.C04, L26.C01, L26.C02, L26.C08</t>
+          <t>L1.C15, L11.C13, L11.C24, L18.C04, L22.C04, L24.C03, L24.C05, L26.C01, L17.C02</t>
         </is>
       </c>
       <c r="N288" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-26-thermodynamique-et-processus-economique/c03-la-frontiere-decide-du-chiffre.md</t>
+          <t>corpus/livre-26-thermodynamique-et-processus-economique/c02-le-stock-n-existe-pas-sous-la-forme-demandee.md</t>
         </is>
       </c>
     </row>
     <row r="289">
       <c r="A289" s="2" t="inlineStr">
         <is>
-          <t>L26.C04</t>
+          <t>L26.C03</t>
         </is>
       </c>
       <c r="B289" s="3" t="inlineStr">
@@ -19994,7 +19994,7 @@
       </c>
       <c r="C289" s="3" t="inlineStr">
         <is>
-          <t>L'effet rebond, et ce que le dispositif en hérite sans être une politique d'efficacité</t>
+          <t>La frontière décide du chiffre</t>
         </is>
       </c>
       <c r="D289" s="3" t="inlineStr">
@@ -20024,31 +20024,31 @@
       </c>
       <c r="I289" s="3" t="inlineStr"/>
       <c r="J289" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K289" s="3" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L289" s="3" t="inlineStr">
         <is>
-          <t>effet_rebond, jevons_monetaire, decouplage, sobriete, entropie, reflux_transactionnel</t>
+          <t>entropie, decouplage, sobriete, limites_planetaires, robustesse, bareme</t>
         </is>
       </c>
       <c r="M289" s="3" t="inlineStr">
         <is>
-          <t>L1.C03, L1.C12, L1.C17, L11.C10, L13.C01, L18.C04, L22.C02, L24.C03, L26.C01, L26.C03, L26.C09</t>
+          <t>L11.C10, L11.C13, L11.C24, L18.C04, L18.C09, L24.C03, L24.C04, L26.C01, L26.C02, L26.C08</t>
         </is>
       </c>
       <c r="N289" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-26-thermodynamique-et-processus-economique/c04-l-effet-rebond-et-ce-que-le-dispositif-en-herite.md</t>
+          <t>corpus/livre-26-thermodynamique-et-processus-economique/c03-la-frontiere-decide-du-chiffre.md</t>
         </is>
       </c>
     </row>
     <row r="290">
       <c r="A290" s="2" t="inlineStr">
         <is>
-          <t>L26.C05</t>
+          <t>L26.C04</t>
         </is>
       </c>
       <c r="B290" s="3" t="inlineStr">
@@ -20058,7 +20058,7 @@
       </c>
       <c r="C290" s="3" t="inlineStr">
         <is>
-          <t>L'addition n'est pas la substitution</t>
+          <t>L'effet rebond, et ce que le dispositif en hérite sans être une politique d'efficacité</t>
         </is>
       </c>
       <c r="D290" s="3" t="inlineStr">
@@ -20091,28 +20091,28 @@
         <v>1</v>
       </c>
       <c r="K290" s="3" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="L290" s="3" t="inlineStr">
         <is>
-          <t>decouplage, effet_rebond, sobriete, degeneratif, affectation_des_instruments</t>
+          <t>effet_rebond, jevons_monetaire, decouplage, sobriete, entropie, reflux_transactionnel</t>
         </is>
       </c>
       <c r="M290" s="3" t="inlineStr">
         <is>
-          <t>L1.C12, L11.C10, L11.C13, L18.C04, L18.C09, L22.C02, L24.C03, L26.C01, L26.C03, L26.C04</t>
+          <t>L1.C03, L1.C12, L1.C17, L11.C10, L13.C01, L18.C04, L22.C02, L24.C03, L26.C01, L26.C03, L26.C09</t>
         </is>
       </c>
       <c r="N290" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-26-thermodynamique-et-processus-economique/c05-l-addition-n-est-pas-la-substitution.md</t>
+          <t>corpus/livre-26-thermodynamique-et-processus-economique/c04-l-effet-rebond-et-ce-que-le-dispositif-en-herite.md</t>
         </is>
       </c>
     </row>
     <row r="291">
       <c r="A291" s="2" t="inlineStr">
         <is>
-          <t>L26.C06</t>
+          <t>L26.C05</t>
         </is>
       </c>
       <c r="B291" s="3" t="inlineStr">
@@ -20122,7 +20122,7 @@
       </c>
       <c r="C291" s="3" t="inlineStr">
         <is>
-          <t>Portée de la tranche</t>
+          <t>L'addition n'est pas la substitution</t>
         </is>
       </c>
       <c r="D291" s="3" t="inlineStr">
@@ -20142,7 +20142,7 @@
       </c>
       <c r="G291" s="3" t="inlineStr">
         <is>
-          <t>descriptif</t>
+          <t>hybride</t>
         </is>
       </c>
       <c r="H291" s="3" t="inlineStr">
@@ -20155,28 +20155,28 @@
         <v>1</v>
       </c>
       <c r="K291" s="3" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L291" s="3" t="inlineStr">
         <is>
-          <t>entropie, decouplage, effet_rebond, limites_planetaires, sobriete, affectation_des_instruments</t>
+          <t>decouplage, effet_rebond, sobriete, degeneratif, affectation_des_instruments</t>
         </is>
       </c>
       <c r="M291" s="3" t="inlineStr">
         <is>
-          <t>L1.C03, L1.C17, L8.C34, L11.C10, L11.C13, L11.C24, L18.C04, L18.C09, L22.C02, L24.C05, L26.C01, L26.C02, L26.C03, L26.C04, L26.C05, L26.C07</t>
+          <t>L1.C12, L11.C10, L11.C13, L18.C04, L18.C09, L22.C02, L24.C03, L26.C01, L26.C03, L26.C04</t>
         </is>
       </c>
       <c r="N291" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-26-thermodynamique-et-processus-economique/c06-portee-de-la-tranche.md</t>
+          <t>corpus/livre-26-thermodynamique-et-processus-economique/c05-l-addition-n-est-pas-la-substitution.md</t>
         </is>
       </c>
     </row>
     <row r="292">
       <c r="A292" s="2" t="inlineStr">
         <is>
-          <t>L26.C07</t>
+          <t>L26.C06</t>
         </is>
       </c>
       <c r="B292" s="3" t="inlineStr">
@@ -20186,7 +20186,7 @@
       </c>
       <c r="C292" s="3" t="inlineStr">
         <is>
-          <t>Le fondateur ne propose aucun instrument monétaire</t>
+          <t>Portée de la tranche</t>
         </is>
       </c>
       <c r="D292" s="3" t="inlineStr">
@@ -20206,7 +20206,7 @@
       </c>
       <c r="G292" s="3" t="inlineStr">
         <is>
-          <t>hybride</t>
+          <t>descriptif</t>
         </is>
       </c>
       <c r="H292" s="3" t="inlineStr">
@@ -20216,31 +20216,31 @@
       </c>
       <c r="I292" s="3" t="inlineStr"/>
       <c r="J292" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K292" s="3" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="L292" s="3" t="inlineStr">
         <is>
-          <t>entropie, sobriete, affectation_des_instruments, qualification_regenerative</t>
+          <t>entropie, decouplage, effet_rebond, limites_planetaires, sobriete, affectation_des_instruments</t>
         </is>
       </c>
       <c r="M292" s="3" t="inlineStr">
         <is>
-          <t>L1.C03, L1.C17, L8.C34, L11.C13, L16.C01, L16.C05, L17.C02, L17.C03, L26.C01, L26.C03, L26.C06</t>
+          <t>L1.C03, L1.C17, L8.C34, L11.C10, L11.C13, L11.C24, L18.C04, L18.C09, L22.C02, L24.C05, L26.C01, L26.C02, L26.C03, L26.C04, L26.C05, L26.C07</t>
         </is>
       </c>
       <c r="N292" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-26-thermodynamique-et-processus-economique/c07-le-fondateur-ne-propose-aucun-instrument-monetaire.md</t>
+          <t>corpus/livre-26-thermodynamique-et-processus-economique/c06-portee-de-la-tranche.md</t>
         </is>
       </c>
     </row>
     <row r="293">
       <c r="A293" s="2" t="inlineStr">
         <is>
-          <t>L26.C08</t>
+          <t>L26.C07</t>
         </is>
       </c>
       <c r="B293" s="3" t="inlineStr">
@@ -20250,7 +20250,7 @@
       </c>
       <c r="C293" s="3" t="inlineStr">
         <is>
-          <t>Même un puits gratuit ne donne pas dix</t>
+          <t>Le fondateur ne propose aucun instrument monétaire</t>
         </is>
       </c>
       <c r="D293" s="3" t="inlineStr">
@@ -20287,24 +20287,24 @@
       </c>
       <c r="L293" s="3" t="inlineStr">
         <is>
-          <t>bareme, qualification_regenerative, decouplage</t>
+          <t>entropie, sobriete, affectation_des_instruments, qualification_regenerative</t>
         </is>
       </c>
       <c r="M293" s="3" t="inlineStr">
         <is>
-          <t>L1.C17, L8.C37, L11.C13, L17.C01, L24.C05, L26.C01, L26.C03, L26.C06, L26.C07</t>
+          <t>L1.C03, L1.C17, L8.C34, L11.C13, L16.C01, L16.C05, L17.C02, L17.C03, L26.C01, L26.C03, L26.C06</t>
         </is>
       </c>
       <c r="N293" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-26-thermodynamique-et-processus-economique/c08-meme-un-puits-gratuit-ne-donne-pas-dix.md</t>
+          <t>corpus/livre-26-thermodynamique-et-processus-economique/c07-le-fondateur-ne-propose-aucun-instrument-monetaire.md</t>
         </is>
       </c>
     </row>
     <row r="294">
       <c r="A294" s="2" t="inlineStr">
         <is>
-          <t>L26.C09</t>
+          <t>L26.C08</t>
         </is>
       </c>
       <c r="B294" s="3" t="inlineStr">
@@ -20314,7 +20314,7 @@
       </c>
       <c r="C294" s="3" t="inlineStr">
         <is>
-          <t>La méthode décide du chiffre</t>
+          <t>Même un puits gratuit ne donne pas dix</t>
         </is>
       </c>
       <c r="D294" s="3" t="inlineStr">
@@ -20351,24 +20351,24 @@
       </c>
       <c r="L294" s="3" t="inlineStr">
         <is>
-          <t>effet_rebond, jevons_monetaire, decouplage, bareme</t>
+          <t>bareme, qualification_regenerative, decouplage</t>
         </is>
       </c>
       <c r="M294" s="3" t="inlineStr">
         <is>
-          <t>L1.C03, L11.C13, L17.C02, L24.C03, L26.C03, L26.C04, L26.C06, L26.C08</t>
+          <t>L1.C17, L8.C37, L11.C13, L17.C01, L24.C05, L26.C01, L26.C03, L26.C06, L26.C07</t>
         </is>
       </c>
       <c r="N294" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-26-thermodynamique-et-processus-economique/c09-la-methode-decide-du-chiffre.md</t>
+          <t>corpus/livre-26-thermodynamique-et-processus-economique/c08-meme-un-puits-gratuit-ne-donne-pas-dix.md</t>
         </is>
       </c>
     </row>
     <row r="295">
       <c r="A295" s="2" t="inlineStr">
         <is>
-          <t>L26.C10</t>
+          <t>L26.C09</t>
         </is>
       </c>
       <c r="B295" s="3" t="inlineStr">
@@ -20378,7 +20378,7 @@
       </c>
       <c r="C295" s="3" t="inlineStr">
         <is>
-          <t>La financiarisation produit un découplage apparent</t>
+          <t>La méthode décide du chiffre</t>
         </is>
       </c>
       <c r="D295" s="3" t="inlineStr">
@@ -20411,26 +20411,90 @@
         <v>2</v>
       </c>
       <c r="K295" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="L295" s="3" t="inlineStr">
+        <is>
+          <t>effet_rebond, jevons_monetaire, decouplage, bareme</t>
+        </is>
+      </c>
+      <c r="M295" s="3" t="inlineStr">
+        <is>
+          <t>L1.C03, L11.C13, L17.C02, L24.C03, L26.C03, L26.C04, L26.C06, L26.C08</t>
+        </is>
+      </c>
+      <c r="N295" s="3" t="inlineStr">
+        <is>
+          <t>corpus/livre-26-thermodynamique-et-processus-economique/c09-la-methode-decide-du-chiffre.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" s="2" t="inlineStr">
+        <is>
+          <t>L26.C10</t>
+        </is>
+      </c>
+      <c r="B296" s="3" t="inlineStr">
+        <is>
+          <t>L26</t>
+        </is>
+      </c>
+      <c r="C296" s="3" t="inlineStr">
+        <is>
+          <t>La financiarisation produit un découplage apparent</t>
+        </is>
+      </c>
+      <c r="D296" s="3" t="inlineStr">
+        <is>
+          <t>brouillon</t>
+        </is>
+      </c>
+      <c r="E296" s="3" t="inlineStr">
+        <is>
+          <t>preparatoire</t>
+        </is>
+      </c>
+      <c r="F296" s="3" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="G296" s="3" t="inlineStr">
+        <is>
+          <t>hybride</t>
+        </is>
+      </c>
+      <c r="H296" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="I296" s="3" t="inlineStr"/>
+      <c r="J296" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="K296" s="3" t="n">
         <v>5</v>
       </c>
-      <c r="L295" s="3" t="inlineStr">
+      <c r="L296" s="3" t="inlineStr">
         <is>
           <t>decouplage, fausse_richesse, jevons_monetaire, indicateur_de_progres</t>
         </is>
       </c>
-      <c r="M295" s="3" t="inlineStr">
+      <c r="M296" s="3" t="inlineStr">
         <is>
           <t>L1.C03, L11.C13, L17.C01, L17.C05, L24.C03, L26.C01, L26.C03, L26.C06, L26.C08, L26.C09, L18.C10</t>
         </is>
       </c>
-      <c r="N295" s="3" t="inlineStr">
+      <c r="N296" s="3" t="inlineStr">
         <is>
           <t>corpus/livre-26-thermodynamique-et-processus-economique/c10-la-financiarisation-produit-un-decouplage-apparent.md</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:N295"/>
+  <autoFilter ref="A1:N296"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -20509,7 +20573,7 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>294</v>
+        <v>295</v>
       </c>
     </row>
     <row r="7">
@@ -20529,7 +20593,7 @@
         </is>
       </c>
       <c r="B8" s="3" t="n">
-        <v>291</v>
+        <v>292</v>
       </c>
     </row>
     <row r="9">
@@ -20539,7 +20603,7 @@
         </is>
       </c>
       <c r="B9" s="3" t="n">
-        <v>285</v>
+        <v>286</v>
       </c>
     </row>
     <row r="10">
@@ -20559,7 +20623,7 @@
         </is>
       </c>
       <c r="B11" s="3" t="n">
-        <v>1448</v>
+        <v>1453</v>
       </c>
     </row>
     <row r="12">
@@ -20569,7 +20633,7 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>1108</v>
+        <v>1109</v>
       </c>
     </row>
     <row r="13">
@@ -20663,7 +20727,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C322"/>
+  <dimension ref="A1:C323"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -25342,7 +25406,7 @@
       </c>
       <c r="C275" s="6" t="inlineStr">
         <is>
-          <t>en-cours — 7 chapitre(s)</t>
+          <t>en-cours — 8 chapitre(s)</t>
         </is>
       </c>
     </row>
@@ -25466,48 +25530,48 @@
       </c>
     </row>
     <row r="283">
-      <c r="A283" s="6" t="inlineStr">
+      <c r="A283" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    L21.C08</t>
+        </is>
+      </c>
+      <c r="B283" s="3" t="inlineStr">
+        <is>
+          <t>La norme des infrastructures exige des fonds propres</t>
+        </is>
+      </c>
+      <c r="C283" s="3" t="inlineStr">
+        <is>
+          <t>brouillon</t>
+        </is>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" s="6" t="inlineStr">
         <is>
           <t>L22</t>
         </is>
       </c>
-      <c r="B283" s="6" t="inlineStr">
+      <c r="B284" s="6" t="inlineStr">
         <is>
           <t>Le pouvoir de la finance non bancaire</t>
         </is>
       </c>
-      <c r="C283" s="6" t="inlineStr">
+      <c r="C284" s="6" t="inlineStr">
         <is>
           <t>en-cours — 7 chapitre(s)</t>
-        </is>
-      </c>
-    </row>
-    <row r="284">
-      <c r="A284" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    L22.C01</t>
-        </is>
-      </c>
-      <c r="B284" s="3" t="inlineStr">
-        <is>
-          <t>Ce que ce livre doit établir</t>
-        </is>
-      </c>
-      <c r="C284" s="3" t="inlineStr">
-        <is>
-          <t>brouillon</t>
         </is>
       </c>
     </row>
     <row r="285">
       <c r="A285" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L22.C02</t>
+          <t xml:space="preserve">    L22.C01</t>
         </is>
       </c>
       <c r="B285" s="3" t="inlineStr">
         <is>
-          <t>Où va la monnaie émise, et pourquoi le reflux ne l'y suit pas</t>
+          <t>Ce que ce livre doit établir</t>
         </is>
       </c>
       <c r="C285" s="3" t="inlineStr">
@@ -25519,12 +25583,12 @@
     <row r="286">
       <c r="A286" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L22.C03</t>
+          <t xml:space="preserve">    L22.C02</t>
         </is>
       </c>
       <c r="B286" s="3" t="inlineStr">
         <is>
-          <t>Le barème existe déjà, et il a trois pièces que le corpus n'a pas</t>
+          <t>Où va la monnaie émise, et pourquoi le reflux ne l'y suit pas</t>
         </is>
       </c>
       <c r="C286" s="3" t="inlineStr">
@@ -25536,12 +25600,12 @@
     <row r="287">
       <c r="A287" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L22.C04</t>
+          <t xml:space="preserve">    L22.C03</t>
         </is>
       </c>
       <c r="B287" s="3" t="inlineStr">
         <is>
-          <t>Les critères réels ne mesurent pas, ils certifient</t>
+          <t>Le barème existe déjà, et il a trois pièces que le corpus n'a pas</t>
         </is>
       </c>
       <c r="C287" s="3" t="inlineStr">
@@ -25553,12 +25617,12 @@
     <row r="288">
       <c r="A288" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L22.C05</t>
+          <t xml:space="preserve">    L22.C04</t>
         </is>
       </c>
       <c r="B288" s="3" t="inlineStr">
         <is>
-          <t>L'épargne retraite, et le dilemme du troisième instrument</t>
+          <t>Les critères réels ne mesurent pas, ils certifient</t>
         </is>
       </c>
       <c r="C288" s="3" t="inlineStr">
@@ -25570,12 +25634,12 @@
     <row r="289">
       <c r="A289" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L22.C06</t>
+          <t xml:space="preserve">    L22.C05</t>
         </is>
       </c>
       <c r="B289" s="3" t="inlineStr">
         <is>
-          <t>Qui décide, quand personne ne décide</t>
+          <t>L'épargne retraite, et le dilemme du troisième instrument</t>
         </is>
       </c>
       <c r="C289" s="3" t="inlineStr">
@@ -25587,63 +25651,63 @@
     <row r="290">
       <c r="A290" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">    L22.C06</t>
+        </is>
+      </c>
+      <c r="B290" s="3" t="inlineStr">
+        <is>
+          <t>Qui décide, quand personne ne décide</t>
+        </is>
+      </c>
+      <c r="C290" s="3" t="inlineStr">
+        <is>
+          <t>brouillon</t>
+        </is>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">    L22.C07</t>
         </is>
       </c>
-      <c r="B290" s="3" t="inlineStr">
+      <c r="B291" s="3" t="inlineStr">
         <is>
           <t>Portée de la tranche</t>
         </is>
       </c>
-      <c r="C290" s="3" t="inlineStr">
-        <is>
-          <t>brouillon</t>
-        </is>
-      </c>
-    </row>
-    <row r="291">
-      <c r="A291" s="6" t="inlineStr">
+      <c r="C291" s="3" t="inlineStr">
+        <is>
+          <t>brouillon</t>
+        </is>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" s="6" t="inlineStr">
         <is>
           <t>L23</t>
         </is>
       </c>
-      <c r="B291" s="6" t="inlineStr">
+      <c r="B292" s="6" t="inlineStr">
         <is>
           <t>Fiscalité mondiale, finance offshore et opacité</t>
         </is>
       </c>
-      <c r="C291" s="6" t="inlineStr">
+      <c r="C292" s="6" t="inlineStr">
         <is>
           <t>en-cours — 7 chapitre(s)</t>
-        </is>
-      </c>
-    </row>
-    <row r="292">
-      <c r="A292" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    L23.C01</t>
-        </is>
-      </c>
-      <c r="B292" s="3" t="inlineStr">
-        <is>
-          <t>Ce que ce livre doit établir</t>
-        </is>
-      </c>
-      <c r="C292" s="3" t="inlineStr">
-        <is>
-          <t>brouillon</t>
         </is>
       </c>
     </row>
     <row r="293">
       <c r="A293" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L23.C02</t>
+          <t xml:space="preserve">    L23.C01</t>
         </is>
       </c>
       <c r="B293" s="3" t="inlineStr">
         <is>
-          <t>La compétence que la convention ne crée pas, et le vote qu'elle a gagné</t>
+          <t>Ce que ce livre doit établir</t>
         </is>
       </c>
       <c r="C293" s="3" t="inlineStr">
@@ -25655,12 +25719,12 @@
     <row r="294">
       <c r="A294" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L23.C03</t>
+          <t xml:space="preserve">    L23.C02</t>
         </is>
       </c>
       <c r="B294" s="3" t="inlineStr">
         <is>
-          <t>F8 appliqué à une négociation en cours, et le résultat n'est pas le désarmement</t>
+          <t>La compétence que la convention ne crée pas, et le vote qu'elle a gagné</t>
         </is>
       </c>
       <c r="C294" s="3" t="inlineStr">
@@ -25672,12 +25736,12 @@
     <row r="295">
       <c r="A295" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L23.C04</t>
+          <t xml:space="preserve">    L23.C03</t>
         </is>
       </c>
       <c r="B295" s="3" t="inlineStr">
         <is>
-          <t>La transparence que le corpus supposait a été invalidée</t>
+          <t>F8 appliqué à une négociation en cours, et le résultat n'est pas le désarmement</t>
         </is>
       </c>
       <c r="C295" s="3" t="inlineStr">
@@ -25689,12 +25753,12 @@
     <row r="296">
       <c r="A296" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L23.C05</t>
+          <t xml:space="preserve">    L23.C04</t>
         </is>
       </c>
       <c r="B296" s="3" t="inlineStr">
         <is>
-          <t>Intéresser le percepteur, et ce que le taux révèle</t>
+          <t>La transparence que le corpus supposait a été invalidée</t>
         </is>
       </c>
       <c r="C296" s="3" t="inlineStr">
@@ -25706,12 +25770,12 @@
     <row r="297">
       <c r="A297" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L23.C06</t>
+          <t xml:space="preserve">    L23.C05</t>
         </is>
       </c>
       <c r="B297" s="3" t="inlineStr">
         <is>
-          <t>L'arbre appliqué à la fonte, et il ne reste que deux branches</t>
+          <t>Intéresser le percepteur, et ce que le taux révèle</t>
         </is>
       </c>
       <c r="C297" s="3" t="inlineStr">
@@ -25723,63 +25787,63 @@
     <row r="298">
       <c r="A298" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">    L23.C06</t>
+        </is>
+      </c>
+      <c r="B298" s="3" t="inlineStr">
+        <is>
+          <t>L'arbre appliqué à la fonte, et il ne reste que deux branches</t>
+        </is>
+      </c>
+      <c r="C298" s="3" t="inlineStr">
+        <is>
+          <t>brouillon</t>
+        </is>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">    L23.C07</t>
         </is>
       </c>
-      <c r="B298" s="3" t="inlineStr">
+      <c r="B299" s="3" t="inlineStr">
         <is>
           <t>Portée de la tranche, et la moitié qui n'est pas commencée</t>
         </is>
       </c>
-      <c r="C298" s="3" t="inlineStr">
-        <is>
-          <t>brouillon</t>
-        </is>
-      </c>
-    </row>
-    <row r="299">
-      <c r="A299" s="6" t="inlineStr">
+      <c r="C299" s="3" t="inlineStr">
+        <is>
+          <t>brouillon</t>
+        </is>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" s="6" t="inlineStr">
         <is>
           <t>L24</t>
         </is>
       </c>
-      <c r="B299" s="6" t="inlineStr">
+      <c r="B300" s="6" t="inlineStr">
         <is>
           <t>Les conditions matérielles de la vie</t>
         </is>
       </c>
-      <c r="C299" s="6" t="inlineStr">
+      <c r="C300" s="6" t="inlineStr">
         <is>
           <t>en-cours — 5 chapitre(s)</t>
-        </is>
-      </c>
-    </row>
-    <row r="300">
-      <c r="A300" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    L24.C01</t>
-        </is>
-      </c>
-      <c r="B300" s="3" t="inlineStr">
-        <is>
-          <t>Ce que ce livre doit établir</t>
-        </is>
-      </c>
-      <c r="C300" s="3" t="inlineStr">
-        <is>
-          <t>brouillon</t>
         </is>
       </c>
     </row>
     <row r="301">
       <c r="A301" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L24.C02</t>
+          <t xml:space="preserve">    L24.C01</t>
         </is>
       </c>
       <c r="B301" s="3" t="inlineStr">
         <is>
-          <t>Le seuil juste est plus strict que le seuil sûr</t>
+          <t>Ce que ce livre doit établir</t>
         </is>
       </c>
       <c r="C301" s="3" t="inlineStr">
@@ -25791,12 +25855,12 @@
     <row r="302">
       <c r="A302" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L24.C03</t>
+          <t xml:space="preserve">    L24.C02</t>
         </is>
       </c>
       <c r="B302" s="3" t="inlineStr">
         <is>
-          <t>La matière, et le levier commun que les neuf dimensions n'avaient pas</t>
+          <t>Le seuil juste est plus strict que le seuil sûr</t>
         </is>
       </c>
       <c r="C302" s="3" t="inlineStr">
@@ -25808,12 +25872,12 @@
     <row r="303">
       <c r="A303" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L24.C04</t>
+          <t xml:space="preserve">    L24.C03</t>
         </is>
       </c>
       <c r="B303" s="3" t="inlineStr">
         <is>
-          <t>Un budget mondial n'est pas partageable</t>
+          <t>La matière, et le levier commun que les neuf dimensions n'avaient pas</t>
         </is>
       </c>
       <c r="C303" s="3" t="inlineStr">
@@ -25825,63 +25889,63 @@
     <row r="304">
       <c r="A304" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">    L24.C04</t>
+        </is>
+      </c>
+      <c r="B304" s="3" t="inlineStr">
+        <is>
+          <t>Un budget mondial n'est pas partageable</t>
+        </is>
+      </c>
+      <c r="C304" s="3" t="inlineStr">
+        <is>
+          <t>brouillon</t>
+        </is>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">    L24.C05</t>
         </is>
       </c>
-      <c r="B304" s="3" t="inlineStr">
+      <c r="B305" s="3" t="inlineStr">
         <is>
           <t>Portée de la tranche</t>
         </is>
       </c>
-      <c r="C304" s="3" t="inlineStr">
-        <is>
-          <t>brouillon</t>
-        </is>
-      </c>
-    </row>
-    <row r="305">
-      <c r="A305" s="6" t="inlineStr">
+      <c r="C305" s="3" t="inlineStr">
+        <is>
+          <t>brouillon</t>
+        </is>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" s="6" t="inlineStr">
         <is>
           <t>L25</t>
         </is>
       </c>
-      <c r="B305" s="6" t="inlineStr">
+      <c r="B306" s="6" t="inlineStr">
         <is>
           <t>Répartition, besoins essentiels et justice sociale</t>
         </is>
       </c>
-      <c r="C305" s="6" t="inlineStr">
+      <c r="C306" s="6" t="inlineStr">
         <is>
           <t>en-cours — 6 chapitre(s)</t>
-        </is>
-      </c>
-    </row>
-    <row r="306">
-      <c r="A306" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    L25.C01</t>
-        </is>
-      </c>
-      <c r="B306" s="3" t="inlineStr">
-        <is>
-          <t>Ce que ce livre doit établir</t>
-        </is>
-      </c>
-      <c r="C306" s="3" t="inlineStr">
-        <is>
-          <t>brouillon</t>
         </is>
       </c>
     </row>
     <row r="307">
       <c r="A307" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L25.C02</t>
+          <t xml:space="preserve">    L25.C01</t>
         </is>
       </c>
       <c r="B307" s="3" t="inlineStr">
         <is>
-          <t>Le noyau dur, et la charge de la preuve renversée</t>
+          <t>Ce que ce livre doit établir</t>
         </is>
       </c>
       <c r="C307" s="3" t="inlineStr">
@@ -25893,12 +25957,12 @@
     <row r="308">
       <c r="A308" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L25.C03</t>
+          <t xml:space="preserve">    L25.C02</t>
         </is>
       </c>
       <c r="B308" s="3" t="inlineStr">
         <is>
-          <t>Ce que le droit oblige à donner, et ce qu'il refuse de réparer</t>
+          <t>Le noyau dur, et la charge de la preuve renversée</t>
         </is>
       </c>
       <c r="C308" s="3" t="inlineStr">
@@ -25910,12 +25974,12 @@
     <row r="309">
       <c r="A309" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L25.C04</t>
+          <t xml:space="preserve">    L25.C03</t>
         </is>
       </c>
       <c r="B309" s="3" t="inlineStr">
         <is>
-          <t>A34 en droit positif, et le critère que le corpus n'avait pas</t>
+          <t>Ce que le droit oblige à donner, et ce qu'il refuse de réparer</t>
         </is>
       </c>
       <c r="C309" s="3" t="inlineStr">
@@ -25927,12 +25991,12 @@
     <row r="310">
       <c r="A310" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L25.C05</t>
+          <t xml:space="preserve">    L25.C04</t>
         </is>
       </c>
       <c r="B310" s="3" t="inlineStr">
         <is>
-          <t>Le droit différencie sans calculer</t>
+          <t>A34 en droit positif, et le critère que le corpus n'avait pas</t>
         </is>
       </c>
       <c r="C310" s="3" t="inlineStr">
@@ -25944,63 +26008,63 @@
     <row r="311">
       <c r="A311" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">    L25.C05</t>
+        </is>
+      </c>
+      <c r="B311" s="3" t="inlineStr">
+        <is>
+          <t>Le droit différencie sans calculer</t>
+        </is>
+      </c>
+      <c r="C311" s="3" t="inlineStr">
+        <is>
+          <t>brouillon</t>
+        </is>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">    L25.C06</t>
         </is>
       </c>
-      <c r="B311" s="3" t="inlineStr">
+      <c r="B312" s="3" t="inlineStr">
         <is>
           <t>Portée de la tranche</t>
         </is>
       </c>
-      <c r="C311" s="3" t="inlineStr">
-        <is>
-          <t>brouillon</t>
-        </is>
-      </c>
-    </row>
-    <row r="312">
-      <c r="A312" s="6" t="inlineStr">
+      <c r="C312" s="3" t="inlineStr">
+        <is>
+          <t>brouillon</t>
+        </is>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" s="6" t="inlineStr">
         <is>
           <t>L26</t>
         </is>
       </c>
-      <c r="B312" s="6" t="inlineStr">
+      <c r="B313" s="6" t="inlineStr">
         <is>
           <t>Thermodynamique, énergie et processus économique</t>
         </is>
       </c>
-      <c r="C312" s="6" t="inlineStr">
+      <c r="C313" s="6" t="inlineStr">
         <is>
           <t>en-cours — 10 chapitre(s)</t>
-        </is>
-      </c>
-    </row>
-    <row r="313">
-      <c r="A313" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    L26.C01</t>
-        </is>
-      </c>
-      <c r="B313" s="3" t="inlineStr">
-        <is>
-          <t>Ce que ce livre doit établir</t>
-        </is>
-      </c>
-      <c r="C313" s="3" t="inlineStr">
-        <is>
-          <t>brouillon</t>
         </is>
       </c>
     </row>
     <row r="314">
       <c r="A314" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L26.C02</t>
+          <t xml:space="preserve">    L26.C01</t>
         </is>
       </c>
       <c r="B314" s="3" t="inlineStr">
         <is>
-          <t>Le stock n'existe pas sous la forme demandée</t>
+          <t>Ce que ce livre doit établir</t>
         </is>
       </c>
       <c r="C314" s="3" t="inlineStr">
@@ -26012,12 +26076,12 @@
     <row r="315">
       <c r="A315" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L26.C03</t>
+          <t xml:space="preserve">    L26.C02</t>
         </is>
       </c>
       <c r="B315" s="3" t="inlineStr">
         <is>
-          <t>La frontière décide du chiffre</t>
+          <t>Le stock n'existe pas sous la forme demandée</t>
         </is>
       </c>
       <c r="C315" s="3" t="inlineStr">
@@ -26029,12 +26093,12 @@
     <row r="316">
       <c r="A316" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L26.C04</t>
+          <t xml:space="preserve">    L26.C03</t>
         </is>
       </c>
       <c r="B316" s="3" t="inlineStr">
         <is>
-          <t>L'effet rebond, et ce que le dispositif en hérite sans être une politique d'efficacité</t>
+          <t>La frontière décide du chiffre</t>
         </is>
       </c>
       <c r="C316" s="3" t="inlineStr">
@@ -26046,12 +26110,12 @@
     <row r="317">
       <c r="A317" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L26.C05</t>
+          <t xml:space="preserve">    L26.C04</t>
         </is>
       </c>
       <c r="B317" s="3" t="inlineStr">
         <is>
-          <t>L'addition n'est pas la substitution</t>
+          <t>L'effet rebond, et ce que le dispositif en hérite sans être une politique d'efficacité</t>
         </is>
       </c>
       <c r="C317" s="3" t="inlineStr">
@@ -26063,12 +26127,12 @@
     <row r="318">
       <c r="A318" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L26.C06</t>
+          <t xml:space="preserve">    L26.C05</t>
         </is>
       </c>
       <c r="B318" s="3" t="inlineStr">
         <is>
-          <t>Portée de la tranche</t>
+          <t>L'addition n'est pas la substitution</t>
         </is>
       </c>
       <c r="C318" s="3" t="inlineStr">
@@ -26080,12 +26144,12 @@
     <row r="319">
       <c r="A319" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L26.C07</t>
+          <t xml:space="preserve">    L26.C06</t>
         </is>
       </c>
       <c r="B319" s="3" t="inlineStr">
         <is>
-          <t>Le fondateur ne propose aucun instrument monétaire</t>
+          <t>Portée de la tranche</t>
         </is>
       </c>
       <c r="C319" s="3" t="inlineStr">
@@ -26097,12 +26161,12 @@
     <row r="320">
       <c r="A320" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L26.C08</t>
+          <t xml:space="preserve">    L26.C07</t>
         </is>
       </c>
       <c r="B320" s="3" t="inlineStr">
         <is>
-          <t>Même un puits gratuit ne donne pas dix</t>
+          <t>Le fondateur ne propose aucun instrument monétaire</t>
         </is>
       </c>
       <c r="C320" s="3" t="inlineStr">
@@ -26114,12 +26178,12 @@
     <row r="321">
       <c r="A321" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L26.C09</t>
+          <t xml:space="preserve">    L26.C08</t>
         </is>
       </c>
       <c r="B321" s="3" t="inlineStr">
         <is>
-          <t>La méthode décide du chiffre</t>
+          <t>Même un puits gratuit ne donne pas dix</t>
         </is>
       </c>
       <c r="C321" s="3" t="inlineStr">
@@ -26131,15 +26195,32 @@
     <row r="322">
       <c r="A322" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">    L26.C09</t>
+        </is>
+      </c>
+      <c r="B322" s="3" t="inlineStr">
+        <is>
+          <t>La méthode décide du chiffre</t>
+        </is>
+      </c>
+      <c r="C322" s="3" t="inlineStr">
+        <is>
+          <t>brouillon</t>
+        </is>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">    L26.C10</t>
         </is>
       </c>
-      <c r="B322" s="3" t="inlineStr">
+      <c r="B323" s="3" t="inlineStr">
         <is>
           <t>La financiarisation produit un découplage apparent</t>
         </is>
       </c>
-      <c r="C322" s="3" t="inlineStr">
+      <c r="C323" s="3" t="inlineStr">
         <is>
           <t>brouillon</t>
         </is>

--- a/plan-des-livres.xlsx
+++ b/plan-des-livres.xlsx
@@ -13,7 +13,7 @@
     <sheet name="Plan par livre" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Chapitres'!$A$1:$N$296</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Chapitres'!$A$1:$N$297</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -1285,7 +1285,7 @@
         </is>
       </c>
       <c r="F20" s="5" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G20" s="5" t="inlineStr"/>
       <c r="H20" s="5" t="inlineStr">
@@ -1638,7 +1638,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N296"/>
+  <dimension ref="A1:N297"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -13183,7 +13183,7 @@
         <v>6</v>
       </c>
       <c r="K182" s="3" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="L182" s="3" t="inlineStr">
         <is>
@@ -13192,7 +13192,7 @@
       </c>
       <c r="M182" s="3" t="inlineStr">
         <is>
-          <t>L1.C18, L1.C20, L1.C22, L1.C27, L11.C03, L11.C05, L11.C06, L11.C08, L11.C09, L11.C10, L11.C11, L11.C12, L26.C05, L26.C07, L26.C08, L26.C09, L26.C10, L18.C10</t>
+          <t>L1.C18, L1.C20, L1.C22, L1.C27, L11.C03, L11.C05, L11.C06, L11.C08, L11.C09, L11.C10, L11.C11, L11.C12, L26.C05, L26.C07, L26.C08, L26.C09, L26.C10, L18.C10, L18.C11</t>
         </is>
       </c>
       <c r="N182" s="3" t="inlineStr">
@@ -14271,7 +14271,7 @@
         <v>3</v>
       </c>
       <c r="K199" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L199" s="3" t="inlineStr">
         <is>
@@ -14843,7 +14843,7 @@
         <v>2</v>
       </c>
       <c r="K208" s="3" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L208" s="3" t="inlineStr">
         <is>
@@ -14852,7 +14852,7 @@
       </c>
       <c r="M208" s="3" t="inlineStr">
         <is>
-          <t>L1.C08, L1.C12, L11.C24, L18.C04, L24.C03, L26.C03, L26.C04, L26.C05, L26.C06, L17.C03, L26.C10</t>
+          <t>L1.C08, L1.C12, L11.C24, L18.C04, L24.C03, L26.C03, L26.C04, L26.C05, L26.C06, L17.C03, L26.C10, L12.C01</t>
         </is>
       </c>
       <c r="N208" s="3" t="inlineStr">
@@ -15099,7 +15099,7 @@
         <v>1</v>
       </c>
       <c r="K212" s="3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L212" s="3" t="inlineStr">
         <is>
@@ -15108,7 +15108,7 @@
       </c>
       <c r="M212" s="3" t="inlineStr">
         <is>
-          <t>L11.C13, L11.C24, L17.C01, L18.C01, L18.C04, L24.C01, L24.C05, L25.C05, L26.C02, L18.C10</t>
+          <t>L11.C13, L11.C24, L17.C01, L18.C01, L18.C04, L24.C01, L24.C05, L25.C05, L26.C02, L18.C10, L18.C11</t>
         </is>
       </c>
       <c r="N212" s="3" t="inlineStr">
@@ -15803,7 +15803,7 @@
         <v>1</v>
       </c>
       <c r="K223" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L223" s="3" t="inlineStr">
         <is>
@@ -15812,7 +15812,7 @@
       </c>
       <c r="M223" s="3" t="inlineStr">
         <is>
-          <t>L1.C15, L11.C13, L13.C01, L17.C05, L18.C01, L18.C04, L18.C09, L22.C04, L24.C05, L26.C10</t>
+          <t>L1.C15, L11.C13, L13.C01, L17.C05, L18.C01, L18.C04, L18.C09, L22.C04, L24.C05, L26.C10, L18.C11</t>
         </is>
       </c>
       <c r="N223" s="3" t="inlineStr">
@@ -15824,17 +15824,17 @@
     <row r="224">
       <c r="A224" s="2" t="inlineStr">
         <is>
-          <t>L19.C01</t>
+          <t>L18.C11</t>
         </is>
       </c>
       <c r="B224" s="3" t="inlineStr">
         <is>
-          <t>L19</t>
+          <t>L18</t>
         </is>
       </c>
       <c r="C224" s="3" t="inlineStr">
         <is>
-          <t>Ce que ce livre doit établir</t>
+          <t>L'adversaire déclare l'hypothèse qu'on lui reproche</t>
         </is>
       </c>
       <c r="D224" s="3" t="inlineStr">
@@ -15864,31 +15864,31 @@
       </c>
       <c r="I224" s="3" t="inlineStr"/>
       <c r="J224" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K224" s="3" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="L224" s="3" t="inlineStr">
         <is>
-          <t>contrepartie_comptable, creation_monetaire, monnaie_comme_registre, hierarchie_monetaire, reflux_collectif</t>
+          <t>valorisation_des_communs, indicateur_de_progres, fausse_richesse</t>
         </is>
       </c>
       <c r="M224" s="3" t="inlineStr">
         <is>
-          <t>L1.C07, L10.C01, L10.C06, L11.C01, L11.C02, L18.C06, L21.C01, L21.C03, L16.C04</t>
+          <t>L11.C13, L12.C01, L17.C05, L18.C01, L18.C10, L24.C05, L26.C10</t>
         </is>
       </c>
       <c r="N224" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-19-comptabilite-monetaire-de-l-emission-sans-dette/c01-ce-que-ce-livre-doit-etablir.md</t>
+          <t>corpus/livre-18-comptabilites-ecologiques-et-biophysiques/c11-l-adversaire-declare-l-hypothese-qu-on-lui-reproche.md</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" s="2" t="inlineStr">
         <is>
-          <t>L19.C02</t>
+          <t>L19.C01</t>
         </is>
       </c>
       <c r="B225" s="3" t="inlineStr">
@@ -15898,7 +15898,7 @@
       </c>
       <c r="C225" s="3" t="inlineStr">
         <is>
-          <t>Le seul précédent, et le passif lui a été reconnu en 2008</t>
+          <t>Ce que ce livre doit établir</t>
         </is>
       </c>
       <c r="D225" s="3" t="inlineStr">
@@ -15928,31 +15928,31 @@
       </c>
       <c r="I225" s="3" t="inlineStr"/>
       <c r="J225" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K225" s="3" t="n">
         <v>5</v>
       </c>
       <c r="L225" s="3" t="inlineStr">
         <is>
-          <t>contrepartie_comptable, reflux_collectif, hierarchie_monetaire, creation_monetaire, devise_cle</t>
+          <t>contrepartie_comptable, creation_monetaire, monnaie_comme_registre, hierarchie_monetaire, reflux_collectif</t>
         </is>
       </c>
       <c r="M225" s="3" t="inlineStr">
         <is>
-          <t>L3.C09, L10.C06, L11.C01, L11.C02, L19.C01, L20.C09, L21.C01, L21.C03, L21.C05, L19.C06</t>
+          <t>L1.C07, L10.C01, L10.C06, L11.C01, L11.C02, L18.C06, L21.C01, L21.C03, L16.C04</t>
         </is>
       </c>
       <c r="N225" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-19-comptabilite-monetaire-de-l-emission-sans-dette/c02-le-seul-precedent-et-le-passif-reconnu-en-2008.md</t>
+          <t>corpus/livre-19-comptabilite-monetaire-de-l-emission-sans-dette/c01-ce-que-ce-livre-doit-etablir.md</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" s="2" t="inlineStr">
         <is>
-          <t>L19.C03</t>
+          <t>L19.C02</t>
         </is>
       </c>
       <c r="B226" s="3" t="inlineStr">
@@ -15962,7 +15962,7 @@
       </c>
       <c r="C226" s="3" t="inlineStr">
         <is>
-          <t>Le reflux est un intérêt négatif, ou une répudiation — et c'est le moment qui décide</t>
+          <t>Le seul précédent, et le passif lui a été reconnu en 2008</t>
         </is>
       </c>
       <c r="D226" s="3" t="inlineStr">
@@ -15992,31 +15992,31 @@
       </c>
       <c r="I226" s="3" t="inlineStr"/>
       <c r="J226" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K226" s="3" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="L226" s="3" t="inlineStr">
         <is>
-          <t>monnaie_fondante, demurrage, reflux_monetaire, reflux_transactionnel, regle_contre_discretion, contrepartie_comptable</t>
+          <t>contrepartie_comptable, reflux_collectif, hierarchie_monetaire, creation_monetaire, devise_cle</t>
         </is>
       </c>
       <c r="M226" s="3" t="inlineStr">
         <is>
-          <t>L10.C06, L11.C01, L11.C02, L11.C05, L11.C07, L11.C27, L19.C01, L19.C02, L21.C01</t>
+          <t>L3.C09, L10.C06, L11.C01, L11.C02, L19.C01, L20.C09, L21.C01, L21.C03, L21.C05, L19.C06</t>
         </is>
       </c>
       <c r="N226" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-19-comptabilite-monetaire-de-l-emission-sans-dette/c03-le-reflux-interet-negatif-ou-repudiation.md</t>
+          <t>corpus/livre-19-comptabilite-monetaire-de-l-emission-sans-dette/c02-le-seul-precedent-et-le-passif-reconnu-en-2008.md</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" s="2" t="inlineStr">
         <is>
-          <t>L19.C04</t>
+          <t>L19.C03</t>
         </is>
       </c>
       <c r="B227" s="3" t="inlineStr">
@@ -16026,7 +16026,7 @@
       </c>
       <c r="C227" s="3" t="inlineStr">
         <is>
-          <t>L'actif transitoire n'existe pas, et le problème change de bilan</t>
+          <t>Le reflux est un intérêt négatif, ou une répudiation — et c'est le moment qui décide</t>
         </is>
       </c>
       <c r="D227" s="3" t="inlineStr">
@@ -16063,24 +16063,24 @@
       </c>
       <c r="L227" s="3" t="inlineStr">
         <is>
-          <t>contrepartie_comptable, hierarchie_monetaire, creation_monetaire, monnaie_comme_registre, solvabilite_anticipee</t>
+          <t>monnaie_fondante, demurrage, reflux_monetaire, reflux_transactionnel, regle_contre_discretion, contrepartie_comptable</t>
         </is>
       </c>
       <c r="M227" s="3" t="inlineStr">
         <is>
-          <t>L1.C07, L10.C06, L10.C07, L11.C01, L11.C02, L19.C01, L19.C02, L19.C03, L21.C03</t>
+          <t>L10.C06, L11.C01, L11.C02, L11.C05, L11.C07, L11.C27, L19.C01, L19.C02, L21.C01</t>
         </is>
       </c>
       <c r="N227" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-19-comptabilite-monetaire-de-l-emission-sans-dette/c04-l-actif-transitoire-et-le-deplacement-du-probleme.md</t>
+          <t>corpus/livre-19-comptabilite-monetaire-de-l-emission-sans-dette/c03-le-reflux-interet-negatif-ou-repudiation.md</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" s="2" t="inlineStr">
         <is>
-          <t>L19.C05</t>
+          <t>L19.C04</t>
         </is>
       </c>
       <c r="B228" s="3" t="inlineStr">
@@ -16090,7 +16090,7 @@
       </c>
       <c r="C228" s="3" t="inlineStr">
         <is>
-          <t>Un débiteur collectif n'existe pas — sauf comme somme de débiteurs identifiés</t>
+          <t>L'actif transitoire n'existe pas, et le problème change de bilan</t>
         </is>
       </c>
       <c r="D228" s="3" t="inlineStr">
@@ -16123,28 +16123,28 @@
         <v>2</v>
       </c>
       <c r="K228" s="3" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L228" s="3" t="inlineStr">
         <is>
-          <t>reflux_collectif, contrepartie_comptable, demurrage, monnaie_fondante, hierarchie_monetaire</t>
+          <t>contrepartie_comptable, hierarchie_monetaire, creation_monetaire, monnaie_comme_registre, solvabilite_anticipee</t>
         </is>
       </c>
       <c r="M228" s="3" t="inlineStr">
         <is>
-          <t>L10.C06, L11.C05, L11.C07, L11.C09, L19.C01, L19.C02, L19.C03, L21.C01, L25.C05, L13.C01</t>
+          <t>L1.C07, L10.C06, L10.C07, L11.C01, L11.C02, L19.C01, L19.C02, L19.C03, L21.C03</t>
         </is>
       </c>
       <c r="N228" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-19-comptabilite-monetaire-de-l-emission-sans-dette/c05-le-creancier-collectif-et-ce-qui-le-rend-representable.md</t>
+          <t>corpus/livre-19-comptabilite-monetaire-de-l-emission-sans-dette/c04-l-actif-transitoire-et-le-deplacement-du-probleme.md</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" s="2" t="inlineStr">
         <is>
-          <t>L19.C06</t>
+          <t>L19.C05</t>
         </is>
       </c>
       <c r="B229" s="3" t="inlineStr">
@@ -16154,7 +16154,7 @@
       </c>
       <c r="C229" s="3" t="inlineStr">
         <is>
-          <t>Les fonds propres négatifs, et l'institution qui n'apparaît dans les comptes de personne</t>
+          <t>Un débiteur collectif n'existe pas — sauf comme somme de débiteurs identifiés</t>
         </is>
       </c>
       <c r="D229" s="3" t="inlineStr">
@@ -16184,31 +16184,31 @@
       </c>
       <c r="I229" s="3" t="inlineStr"/>
       <c r="J229" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K229" s="3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L229" s="3" t="inlineStr">
         <is>
-          <t>contrepartie_comptable, solvabilite_anticipee, architecture_invisible, hierarchie_monetaire, robustesse</t>
+          <t>reflux_collectif, contrepartie_comptable, demurrage, monnaie_fondante, hierarchie_monetaire</t>
         </is>
       </c>
       <c r="M229" s="3" t="inlineStr">
         <is>
-          <t>L1.C07, L7.C06, L14.C01, L19.C01, L19.C02, L19.C03, L19.C04, L21.C01, L21.C04</t>
+          <t>L10.C06, L11.C05, L11.C07, L11.C09, L19.C01, L19.C02, L19.C03, L21.C01, L25.C05, L13.C01</t>
         </is>
       </c>
       <c r="N229" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-19-comptabilite-monetaire-de-l-emission-sans-dette/c06-les-fonds-propres-negatifs-et-l-institution-qui-n-apparait-nulle-part.md</t>
+          <t>corpus/livre-19-comptabilite-monetaire-de-l-emission-sans-dette/c05-le-creancier-collectif-et-ce-qui-le-rend-representable.md</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" s="2" t="inlineStr">
         <is>
-          <t>L19.C07</t>
+          <t>L19.C06</t>
         </is>
       </c>
       <c r="B230" s="3" t="inlineStr">
@@ -16218,7 +16218,7 @@
       </c>
       <c r="C230" s="3" t="inlineStr">
         <is>
-          <t>Portée de la tranche</t>
+          <t>Les fonds propres négatifs, et l'institution qui n'apparaît dans les comptes de personne</t>
         </is>
       </c>
       <c r="D230" s="3" t="inlineStr">
@@ -16238,7 +16238,7 @@
       </c>
       <c r="G230" s="3" t="inlineStr">
         <is>
-          <t>descriptif</t>
+          <t>hybride</t>
         </is>
       </c>
       <c r="H230" s="3" t="inlineStr">
@@ -16251,38 +16251,38 @@
         <v>1</v>
       </c>
       <c r="K230" s="3" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L230" s="3" t="inlineStr">
         <is>
-          <t>contrepartie_comptable, reflux_collectif, monnaie_fondante, hierarchie_monetaire, architecture_invisible, creation_monetaire</t>
+          <t>contrepartie_comptable, solvabilite_anticipee, architecture_invisible, hierarchie_monetaire, robustesse</t>
         </is>
       </c>
       <c r="M230" s="3" t="inlineStr">
         <is>
-          <t>L10.C06, L11.C01, L11.C02, L11.C07, L19.C01, L19.C02, L19.C03, L19.C04, L19.C05, L19.C06, L21.C01, L21.C03, L21.C08</t>
+          <t>L1.C07, L7.C06, L14.C01, L19.C01, L19.C02, L19.C03, L19.C04, L21.C01, L21.C04</t>
         </is>
       </c>
       <c r="N230" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-19-comptabilite-monetaire-de-l-emission-sans-dette/c07-portee-de-la-tranche.md</t>
+          <t>corpus/livre-19-comptabilite-monetaire-de-l-emission-sans-dette/c06-les-fonds-propres-negatifs-et-l-institution-qui-n-apparait-nulle-part.md</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" s="2" t="inlineStr">
         <is>
-          <t>L20.C01</t>
+          <t>L19.C07</t>
         </is>
       </c>
       <c r="B231" s="3" t="inlineStr">
         <is>
-          <t>L20</t>
+          <t>L19</t>
         </is>
       </c>
       <c r="C231" s="3" t="inlineStr">
         <is>
-          <t>Ce que ce livre doit établir</t>
+          <t>Portée de la tranche</t>
         </is>
       </c>
       <c r="D231" s="3" t="inlineStr">
@@ -16302,41 +16302,41 @@
       </c>
       <c r="G231" s="3" t="inlineStr">
         <is>
-          <t>conception</t>
+          <t>descriptif</t>
         </is>
       </c>
       <c r="H231" s="3" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="I231" s="3" t="inlineStr"/>
       <c r="J231" s="3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K231" s="3" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="L231" s="3" t="inlineStr">
         <is>
-          <t>fenetre_de_reforme, referentiel_de_change, communs, limites_planetaires, creation_monetaire</t>
+          <t>contrepartie_comptable, reflux_collectif, monnaie_fondante, hierarchie_monetaire, architecture_invisible, creation_monetaire</t>
         </is>
       </c>
       <c r="M231" s="3" t="inlineStr">
         <is>
-          <t>L1.C18, L1.C25, L1.C27, L7.C01, L7.C03, L7.C13, L7.C17, L7.C21, L11.C24</t>
+          <t>L10.C06, L11.C01, L11.C02, L11.C07, L19.C01, L19.C02, L19.C03, L19.C04, L19.C05, L19.C06, L21.C01, L21.C03, L21.C08</t>
         </is>
       </c>
       <c r="N231" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-20-droit-international-monetaire-et-commercial/c01-ce-que-ce-livre-doit-etablir.md</t>
+          <t>corpus/livre-19-comptabilite-monetaire-de-l-emission-sans-dette/c07-portee-de-la-tranche.md</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="A232" s="2" t="inlineStr">
         <is>
-          <t>L20.C02</t>
+          <t>L20.C01</t>
         </is>
       </c>
       <c r="B232" s="3" t="inlineStr">
@@ -16346,7 +16346,7 @@
       </c>
       <c r="C232" s="3" t="inlineStr">
         <is>
-          <t>L'interdiction du financement monétaire</t>
+          <t>Ce que ce livre doit établir</t>
         </is>
       </c>
       <c r="D232" s="3" t="inlineStr">
@@ -16383,24 +16383,24 @@
       </c>
       <c r="L232" s="3" t="inlineStr">
         <is>
-          <t>creation_monetaire, contrepartie_comptable, reflux_collectif, fenetre_de_reforme</t>
+          <t>fenetre_de_reforme, referentiel_de_change, communs, limites_planetaires, creation_monetaire</t>
         </is>
       </c>
       <c r="M232" s="3" t="inlineStr">
         <is>
-          <t>L1.C05, L1.C18, L1.C20, L1.C22, L7.C11, L7.C13, L11.C10, L20.C01</t>
+          <t>L1.C18, L1.C25, L1.C27, L7.C01, L7.C03, L7.C13, L7.C17, L7.C21, L11.C24</t>
         </is>
       </c>
       <c r="N232" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-20-droit-international-monetaire-et-commercial/c02-l-interdiction-du-financement-monetaire.md</t>
+          <t>corpus/livre-20-droit-international-monetaire-et-commercial/c01-ce-que-ce-livre-doit-etablir.md</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" s="2" t="inlineStr">
         <is>
-          <t>L20.C03</t>
+          <t>L20.C02</t>
         </is>
       </c>
       <c r="B233" s="3" t="inlineStr">
@@ -16410,7 +16410,7 @@
       </c>
       <c r="C233" s="3" t="inlineStr">
         <is>
-          <t>L'objectif principal et ce qu'il exclut</t>
+          <t>L'interdiction du financement monétaire</t>
         </is>
       </c>
       <c r="D233" s="3" t="inlineStr">
@@ -16447,24 +16447,24 @@
       </c>
       <c r="L233" s="3" t="inlineStr">
         <is>
-          <t>regle_contre_discretion, limites_planetaires, creation_monetaire, plafond_ecologique</t>
+          <t>creation_monetaire, contrepartie_comptable, reflux_collectif, fenetre_de_reforme</t>
         </is>
       </c>
       <c r="M233" s="3" t="inlineStr">
         <is>
-          <t>L1.C01, L1.C18, L1.C20, L7.C03, L8.C12, L8.C34, L11.C16, L20.C01, L20.C02</t>
+          <t>L1.C05, L1.C18, L1.C20, L1.C22, L7.C11, L7.C13, L11.C10, L20.C01</t>
         </is>
       </c>
       <c r="N233" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-20-droit-international-monetaire-et-commercial/c03-l-objectif-principal-et-ce-qu-il-exclut.md</t>
+          <t>corpus/livre-20-droit-international-monetaire-et-commercial/c02-l-interdiction-du-financement-monetaire.md</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" s="2" t="inlineStr">
         <is>
-          <t>L20.C04</t>
+          <t>L20.C03</t>
         </is>
       </c>
       <c r="B234" s="3" t="inlineStr">
@@ -16474,7 +16474,7 @@
       </c>
       <c r="C234" s="3" t="inlineStr">
         <is>
-          <t>L'indépendance, et à l'égard de qui</t>
+          <t>L'objectif principal et ce qu'il exclut</t>
         </is>
       </c>
       <c r="D234" s="3" t="inlineStr">
@@ -16499,7 +16499,7 @@
       </c>
       <c r="H234" s="3" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="I234" s="3" t="inlineStr"/>
@@ -16511,24 +16511,24 @@
       </c>
       <c r="L234" s="3" t="inlineStr">
         <is>
-          <t>regle_contre_discretion, creation_monetaire, fenetre_de_reforme</t>
+          <t>regle_contre_discretion, limites_planetaires, creation_monetaire, plafond_ecologique</t>
         </is>
       </c>
       <c r="M234" s="3" t="inlineStr">
         <is>
-          <t>L1.C18, L7.C04, L7.C07, L7.C10, L8.C31, L11.C17, L20.C01, L20.C03, L20.C11</t>
+          <t>L1.C01, L1.C18, L1.C20, L7.C03, L8.C12, L8.C34, L11.C16, L20.C01, L20.C02</t>
         </is>
       </c>
       <c r="N234" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-20-droit-international-monetaire-et-commercial/c04-l-independance-et-a-l-egard-de-qui.md</t>
+          <t>corpus/livre-20-droit-international-monetaire-et-commercial/c03-l-objectif-principal-et-ce-qu-il-exclut.md</t>
         </is>
       </c>
     </row>
     <row r="235">
       <c r="A235" s="2" t="inlineStr">
         <is>
-          <t>L20.C05</t>
+          <t>L20.C04</t>
         </is>
       </c>
       <c r="B235" s="3" t="inlineStr">
@@ -16538,7 +16538,7 @@
       </c>
       <c r="C235" s="3" t="inlineStr">
         <is>
-          <t>Le monopole d'émission et le cours légal</t>
+          <t>L'indépendance, et à l'égard de qui</t>
         </is>
       </c>
       <c r="D235" s="3" t="inlineStr">
@@ -16575,24 +16575,24 @@
       </c>
       <c r="L235" s="3" t="inlineStr">
         <is>
-          <t>monnaie_comme_registre, creation_monetaire, referentiel_de_change, hierarchie_monetaire</t>
+          <t>regle_contre_discretion, creation_monetaire, fenetre_de_reforme</t>
         </is>
       </c>
       <c r="M235" s="3" t="inlineStr">
         <is>
-          <t>L1.C05, L1.C07, L1.C26, L7.C15, L11.C15, L20.C01, L20.C02, L20.C03</t>
+          <t>L1.C18, L7.C04, L7.C07, L7.C10, L8.C31, L11.C17, L20.C01, L20.C03, L20.C11</t>
         </is>
       </c>
       <c r="N235" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-20-droit-international-monetaire-et-commercial/c05-le-monopole-d-emission-et-le-cours-legal.md</t>
+          <t>corpus/livre-20-droit-international-monetaire-et-commercial/c04-l-independance-et-a-l-egard-de-qui.md</t>
         </is>
       </c>
     </row>
     <row r="236">
       <c r="A236" s="2" t="inlineStr">
         <is>
-          <t>L20.C06</t>
+          <t>L20.C05</t>
         </is>
       </c>
       <c r="B236" s="3" t="inlineStr">
@@ -16602,7 +16602,7 @@
       </c>
       <c r="C236" s="3" t="inlineStr">
         <is>
-          <t>Les voies de révision et leur coût</t>
+          <t>Le monopole d'émission et le cours légal</t>
         </is>
       </c>
       <c r="D236" s="3" t="inlineStr">
@@ -16632,31 +16632,31 @@
       </c>
       <c r="I236" s="3" t="inlineStr"/>
       <c r="J236" s="3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K236" s="3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L236" s="3" t="inlineStr">
         <is>
-          <t>fenetre_de_reforme, regle_contre_discretion, creation_monetaire</t>
+          <t>monnaie_comme_registre, creation_monetaire, referentiel_de_change, hierarchie_monetaire</t>
         </is>
       </c>
       <c r="M236" s="3" t="inlineStr">
         <is>
-          <t>L1.C18, L7.C12, L7.C20, L7.C21, L11.C15, L20.C01, L20.C02, L20.C03, L20.C07, L20.C09, L20.C18</t>
+          <t>L1.C05, L1.C07, L1.C26, L7.C15, L11.C15, L20.C01, L20.C02, L20.C03</t>
         </is>
       </c>
       <c r="N236" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-20-droit-international-monetaire-et-commercial/c06-les-voies-de-revision-et-leur-cout.md</t>
+          <t>corpus/livre-20-droit-international-monetaire-et-commercial/c05-le-monopole-d-emission-et-le-cours-legal.md</t>
         </is>
       </c>
     </row>
     <row r="237">
       <c r="A237" s="2" t="inlineStr">
         <is>
-          <t>L20.C07</t>
+          <t>L20.C06</t>
         </is>
       </c>
       <c r="B237" s="3" t="inlineStr">
@@ -16666,7 +16666,7 @@
       </c>
       <c r="C237" s="3" t="inlineStr">
         <is>
-          <t>L'accord monétaire international</t>
+          <t>Les voies de révision et leur coût</t>
         </is>
       </c>
       <c r="D237" s="3" t="inlineStr">
@@ -16696,31 +16696,31 @@
       </c>
       <c r="I237" s="3" t="inlineStr"/>
       <c r="J237" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K237" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L237" s="3" t="inlineStr">
         <is>
-          <t>referentiel_de_change, fenetre_de_reforme, etalon_de_change_or, hierarchie_monetaire</t>
+          <t>fenetre_de_reforme, regle_contre_discretion, creation_monetaire</t>
         </is>
       </c>
       <c r="M237" s="3" t="inlineStr">
         <is>
-          <t>L1.C18, L1.C26, L7.C02, L7.C05, L7.C12, L7.C13, L11.C15, L20.C01, L20.C03, L20.C06, L20.C10</t>
+          <t>L1.C18, L7.C12, L7.C20, L7.C21, L11.C15, L20.C01, L20.C02, L20.C03, L20.C07, L20.C09, L20.C18</t>
         </is>
       </c>
       <c r="N237" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-20-droit-international-monetaire-et-commercial/c07-l-accord-monetaire-international.md</t>
+          <t>corpus/livre-20-droit-international-monetaire-et-commercial/c06-les-voies-de-revision-et-leur-cout.md</t>
         </is>
       </c>
     </row>
     <row r="238">
       <c r="A238" s="2" t="inlineStr">
         <is>
-          <t>L20.C08</t>
+          <t>L20.C07</t>
         </is>
       </c>
       <c r="B238" s="3" t="inlineStr">
@@ -16730,7 +16730,7 @@
       </c>
       <c r="C238" s="3" t="inlineStr">
         <is>
-          <t>La parité inscrite dans le traité</t>
+          <t>L'accord monétaire international</t>
         </is>
       </c>
       <c r="D238" s="3" t="inlineStr">
@@ -16755,36 +16755,36 @@
       </c>
       <c r="H238" s="3" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="I238" s="3" t="inlineStr"/>
       <c r="J238" s="3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K238" s="3" t="n">
         <v>3</v>
       </c>
       <c r="L238" s="3" t="inlineStr">
         <is>
-          <t>referentiel_de_change, etalon_de_change_or, hierarchie_monetaire, bareme, devise_cle</t>
+          <t>referentiel_de_change, fenetre_de_reforme, etalon_de_change_or, hierarchie_monetaire</t>
         </is>
       </c>
       <c r="M238" s="3" t="inlineStr">
         <is>
-          <t>L1.C25, L1.C26, L1.C28, L7.C02, L7.C20, L11.C15, L11.C17, L20.C01, L20.C09, L20.C13</t>
+          <t>L1.C18, L1.C26, L7.C02, L7.C05, L7.C12, L7.C13, L11.C15, L20.C01, L20.C03, L20.C06, L20.C10</t>
         </is>
       </c>
       <c r="N238" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-20-droit-international-monetaire-et-commercial/c08-la-parite-inscrite-dans-le-traite.md</t>
+          <t>corpus/livre-20-droit-international-monetaire-et-commercial/c07-l-accord-monetaire-international.md</t>
         </is>
       </c>
     </row>
     <row r="239">
       <c r="A239" s="2" t="inlineStr">
         <is>
-          <t>L20.C09</t>
+          <t>L20.C08</t>
         </is>
       </c>
       <c r="B239" s="3" t="inlineStr">
@@ -16794,7 +16794,7 @@
       </c>
       <c r="C239" s="3" t="inlineStr">
         <is>
-          <t>L'amendement des statuts du Fonds</t>
+          <t>La parité inscrite dans le traité</t>
         </is>
       </c>
       <c r="D239" s="3" t="inlineStr">
@@ -16819,36 +16819,36 @@
       </c>
       <c r="H239" s="3" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="I239" s="3" t="inlineStr"/>
       <c r="J239" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K239" s="3" t="n">
         <v>3</v>
       </c>
       <c r="L239" s="3" t="inlineStr">
         <is>
-          <t>fenetre_de_reforme, referentiel_de_change, bareme, regle_contre_discretion</t>
+          <t>referentiel_de_change, etalon_de_change_or, hierarchie_monetaire, bareme, devise_cle</t>
         </is>
       </c>
       <c r="M239" s="3" t="inlineStr">
         <is>
-          <t>L7.C06, L7.C09, L7.C16, L7.C20, L11.C15, L11.C20, L20.C01, L20.C06, L20.C08, L20.C10, L20.C13</t>
+          <t>L1.C25, L1.C26, L1.C28, L7.C02, L7.C20, L11.C15, L11.C17, L20.C01, L20.C09, L20.C13</t>
         </is>
       </c>
       <c r="N239" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-20-droit-international-monetaire-et-commercial/c09-l-amendement-des-statuts-du-fonds.md</t>
+          <t>corpus/livre-20-droit-international-monetaire-et-commercial/c08-la-parite-inscrite-dans-le-traite.md</t>
         </is>
       </c>
     </row>
     <row r="240">
       <c r="A240" s="2" t="inlineStr">
         <is>
-          <t>L20.C10</t>
+          <t>L20.C09</t>
         </is>
       </c>
       <c r="B240" s="3" t="inlineStr">
@@ -16858,7 +16858,7 @@
       </c>
       <c r="C240" s="3" t="inlineStr">
         <is>
-          <t>Le vote pondéré et les voix de base</t>
+          <t>L'amendement des statuts du Fonds</t>
         </is>
       </c>
       <c r="D240" s="3" t="inlineStr">
@@ -16895,24 +16895,24 @@
       </c>
       <c r="L240" s="3" t="inlineStr">
         <is>
-          <t>bareme, devise_cle, hierarchie_monetaire, referentiel_de_change</t>
+          <t>fenetre_de_reforme, referentiel_de_change, bareme, regle_contre_discretion</t>
         </is>
       </c>
       <c r="M240" s="3" t="inlineStr">
         <is>
-          <t>L1.C25, L7.C02, L7.C05, L7.C06, L7.C09, L7.C10, L11.C16, L20.C01, L20.C07, L20.C09, L20.C12</t>
+          <t>L7.C06, L7.C09, L7.C16, L7.C20, L11.C15, L11.C20, L20.C01, L20.C06, L20.C08, L20.C10, L20.C13</t>
         </is>
       </c>
       <c r="N240" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-20-droit-international-monetaire-et-commercial/c10-le-vote-pondere-et-les-voix-de-base.md</t>
+          <t>corpus/livre-20-droit-international-monetaire-et-commercial/c09-l-amendement-des-statuts-du-fonds.md</t>
         </is>
       </c>
     </row>
     <row r="241">
       <c r="A241" s="2" t="inlineStr">
         <is>
-          <t>L20.C11</t>
+          <t>L20.C10</t>
         </is>
       </c>
       <c r="B241" s="3" t="inlineStr">
@@ -16922,7 +16922,7 @@
       </c>
       <c r="C241" s="3" t="inlineStr">
         <is>
-          <t>La personnalité juridique et les immunités</t>
+          <t>Le vote pondéré et les voix de base</t>
         </is>
       </c>
       <c r="D241" s="3" t="inlineStr">
@@ -16952,31 +16952,31 @@
       </c>
       <c r="I241" s="3" t="inlineStr"/>
       <c r="J241" s="3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K241" s="3" t="n">
         <v>3</v>
       </c>
       <c r="L241" s="3" t="inlineStr">
         <is>
-          <t>communs, creation_monetaire, fenetre_de_reforme, robustesse</t>
+          <t>bareme, devise_cle, hierarchie_monetaire, referentiel_de_change</t>
         </is>
       </c>
       <c r="M241" s="3" t="inlineStr">
         <is>
-          <t>L7.C01, L7.C03, L7.C07, L7.C10, L7.C13, L11.C25, L20.C01, L20.C04, L20.C12, L20.C14</t>
+          <t>L1.C25, L7.C02, L7.C05, L7.C06, L7.C09, L7.C10, L11.C16, L20.C01, L20.C07, L20.C09, L20.C12</t>
         </is>
       </c>
       <c r="N241" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-20-droit-international-monetaire-et-commercial/c11-la-personnalite-juridique-et-les-immunites.md</t>
+          <t>corpus/livre-20-droit-international-monetaire-et-commercial/c10-le-vote-pondere-et-les-voix-de-base.md</t>
         </is>
       </c>
     </row>
     <row r="242">
       <c r="A242" s="2" t="inlineStr">
         <is>
-          <t>L20.C12</t>
+          <t>L20.C11</t>
         </is>
       </c>
       <c r="B242" s="3" t="inlineStr">
@@ -16986,7 +16986,7 @@
       </c>
       <c r="C242" s="3" t="inlineStr">
         <is>
-          <t>Les pouvoirs non délégables</t>
+          <t>La personnalité juridique et les immunités</t>
         </is>
       </c>
       <c r="D242" s="3" t="inlineStr">
@@ -17011,36 +17011,36 @@
       </c>
       <c r="H242" s="3" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="I242" s="3" t="inlineStr"/>
       <c r="J242" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K242" s="3" t="n">
         <v>3</v>
       </c>
       <c r="L242" s="3" t="inlineStr">
         <is>
-          <t>bareme, valorisation_des_communs, polycentricite, robustesse</t>
+          <t>communs, creation_monetaire, fenetre_de_reforme, robustesse</t>
         </is>
       </c>
       <c r="M242" s="3" t="inlineStr">
         <is>
-          <t>L7.C05, L7.C06, L7.C07, L7.C11, L7.C14, L11.C16, L11.C20, L20.C01, L20.C09, L20.C10, L20.C14</t>
+          <t>L7.C01, L7.C03, L7.C07, L7.C10, L7.C13, L11.C25, L20.C01, L20.C04, L20.C12, L20.C14</t>
         </is>
       </c>
       <c r="N242" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-20-droit-international-monetaire-et-commercial/c12-les-pouvoirs-non-delegables.md</t>
+          <t>corpus/livre-20-droit-international-monetaire-et-commercial/c11-la-personnalite-juridique-et-les-immunites.md</t>
         </is>
       </c>
     </row>
     <row r="243">
       <c r="A243" s="2" t="inlineStr">
         <is>
-          <t>L20.C13</t>
+          <t>L20.C12</t>
         </is>
       </c>
       <c r="B243" s="3" t="inlineStr">
@@ -17050,7 +17050,7 @@
       </c>
       <c r="C243" s="3" t="inlineStr">
         <is>
-          <t>L'entrée en vigueur, l'adhésion et le retrait</t>
+          <t>Les pouvoirs non délégables</t>
         </is>
       </c>
       <c r="D243" s="3" t="inlineStr">
@@ -17080,31 +17080,31 @@
       </c>
       <c r="I243" s="3" t="inlineStr"/>
       <c r="J243" s="3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K243" s="3" t="n">
         <v>3</v>
       </c>
       <c r="L243" s="3" t="inlineStr">
         <is>
-          <t>seuil_d_activation, reflux_collectif, fenetre_de_reforme, additionnalite</t>
+          <t>bareme, valorisation_des_communs, polycentricite, robustesse</t>
         </is>
       </c>
       <c r="M243" s="3" t="inlineStr">
         <is>
-          <t>L7.C11, L7.C12, L7.C16, L7.C17, L7.C19, L11.C18, L20.C01, L20.C06, L20.C09, L20.C12</t>
+          <t>L7.C05, L7.C06, L7.C07, L7.C11, L7.C14, L11.C16, L11.C20, L20.C01, L20.C09, L20.C10, L20.C14</t>
         </is>
       </c>
       <c r="N243" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-20-droit-international-monetaire-et-commercial/c13-l-entree-en-vigueur-l-adhesion-et-le-retrait.md</t>
+          <t>corpus/livre-20-droit-international-monetaire-et-commercial/c12-les-pouvoirs-non-delegables.md</t>
         </is>
       </c>
     </row>
     <row r="244">
       <c r="A244" s="2" t="inlineStr">
         <is>
-          <t>L20.C14</t>
+          <t>L20.C13</t>
         </is>
       </c>
       <c r="B244" s="3" t="inlineStr">
@@ -17114,7 +17114,7 @@
       </c>
       <c r="C244" s="3" t="inlineStr">
         <is>
-          <t>Qui interprète le traité</t>
+          <t>L'entrée en vigueur, l'adhésion et le retrait</t>
         </is>
       </c>
       <c r="D244" s="3" t="inlineStr">
@@ -17144,31 +17144,31 @@
       </c>
       <c r="I244" s="3" t="inlineStr"/>
       <c r="J244" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K244" s="3" t="n">
         <v>3</v>
       </c>
       <c r="L244" s="3" t="inlineStr">
         <is>
-          <t>robustesse, regle_contre_discretion, communs</t>
+          <t>seuil_d_activation, reflux_collectif, fenetre_de_reforme, additionnalite</t>
         </is>
       </c>
       <c r="M244" s="3" t="inlineStr">
         <is>
-          <t>L7.C07, L7.C13, L7.C14, L7.C19, L11.C19, L11.C25, L20.C01, L20.C03, L20.C11, L20.C12, L20.C21</t>
+          <t>L7.C11, L7.C12, L7.C16, L7.C17, L7.C19, L11.C18, L20.C01, L20.C06, L20.C09, L20.C12</t>
         </is>
       </c>
       <c r="N244" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-20-droit-international-monetaire-et-commercial/c14-qui-interprete-le-traite.md</t>
+          <t>corpus/livre-20-droit-international-monetaire-et-commercial/c13-l-entree-en-vigueur-l-adhesion-et-le-retrait.md</t>
         </is>
       </c>
     </row>
     <row r="245">
       <c r="A245" s="2" t="inlineStr">
         <is>
-          <t>L20.C15</t>
+          <t>L20.C14</t>
         </is>
       </c>
       <c r="B245" s="3" t="inlineStr">
@@ -17178,7 +17178,7 @@
       </c>
       <c r="C245" s="3" t="inlineStr">
         <is>
-          <t>Le devoir international des agents</t>
+          <t>Qui interprète le traité</t>
         </is>
       </c>
       <c r="D245" s="3" t="inlineStr">
@@ -17203,36 +17203,36 @@
       </c>
       <c r="H245" s="3" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="I245" s="3" t="inlineStr"/>
       <c r="J245" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K245" s="3" t="n">
         <v>3</v>
       </c>
       <c r="L245" s="3" t="inlineStr">
         <is>
-          <t>robustesse, regle_contre_discretion, indicateur_de_progres</t>
+          <t>robustesse, regle_contre_discretion, communs</t>
         </is>
       </c>
       <c r="M245" s="3" t="inlineStr">
         <is>
-          <t>L7.C04, L7.C07, L7.C10, L11.C21, L11.C25, L20.C01, L20.C04, L20.C11, L20.C14</t>
+          <t>L7.C07, L7.C13, L7.C14, L7.C19, L11.C19, L11.C25, L20.C01, L20.C03, L20.C11, L20.C12, L20.C21</t>
         </is>
       </c>
       <c r="N245" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-20-droit-international-monetaire-et-commercial/c15-le-devoir-international-des-agents.md</t>
+          <t>corpus/livre-20-droit-international-monetaire-et-commercial/c14-qui-interprete-le-traite.md</t>
         </is>
       </c>
     </row>
     <row r="246">
       <c r="A246" s="2" t="inlineStr">
         <is>
-          <t>L20.C16</t>
+          <t>L20.C15</t>
         </is>
       </c>
       <c r="B246" s="3" t="inlineStr">
@@ -17242,7 +17242,7 @@
       </c>
       <c r="C246" s="3" t="inlineStr">
         <is>
-          <t>Le patrimoine commun de l'humanité</t>
+          <t>Le devoir international des agents</t>
         </is>
       </c>
       <c r="D246" s="3" t="inlineStr">
@@ -17267,36 +17267,36 @@
       </c>
       <c r="H246" s="3" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="I246" s="3" t="inlineStr"/>
       <c r="J246" s="3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K246" s="3" t="n">
         <v>3</v>
       </c>
       <c r="L246" s="3" t="inlineStr">
         <is>
-          <t>communs, valorisation_des_communs, limites_planetaires, additionnalite, plafond_ecologique</t>
+          <t>robustesse, regle_contre_discretion, indicateur_de_progres</t>
         </is>
       </c>
       <c r="M246" s="3" t="inlineStr">
         <is>
-          <t>L1.C17, L1.C22, L7.C05, L7.C13, L11.C16, L20.C01, L20.C11, L20.C17, L20.C22</t>
+          <t>L7.C04, L7.C07, L7.C10, L11.C21, L11.C25, L20.C01, L20.C04, L20.C11, L20.C14</t>
         </is>
       </c>
       <c r="N246" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-20-droit-international-monetaire-et-commercial/c16-le-patrimoine-commun-de-l-humanite.md</t>
+          <t>corpus/livre-20-droit-international-monetaire-et-commercial/c15-le-devoir-international-des-agents.md</t>
         </is>
       </c>
     </row>
     <row r="247">
       <c r="A247" s="2" t="inlineStr">
         <is>
-          <t>L20.C17</t>
+          <t>L20.C16</t>
         </is>
       </c>
       <c r="B247" s="3" t="inlineStr">
@@ -17306,7 +17306,7 @@
       </c>
       <c r="C247" s="3" t="inlineStr">
         <is>
-          <t>La sanctuarisation, et elle existe</t>
+          <t>Le patrimoine commun de l'humanité</t>
         </is>
       </c>
       <c r="D247" s="3" t="inlineStr">
@@ -17336,31 +17336,31 @@
       </c>
       <c r="I247" s="3" t="inlineStr"/>
       <c r="J247" s="3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K247" s="3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L247" s="3" t="inlineStr">
         <is>
-          <t>communs, limites_planetaires, fenetre_de_reforme, robustesse, plafond_ecologique</t>
+          <t>communs, valorisation_des_communs, limites_planetaires, additionnalite, plafond_ecologique</t>
         </is>
       </c>
       <c r="M247" s="3" t="inlineStr">
         <is>
-          <t>L1.C17, L1.C18, L7.C13, L7.C19, L7.C20, L11.C20, L20.C01, L20.C06, L20.C09, L20.C16, L20.C22</t>
+          <t>L1.C17, L1.C22, L7.C05, L7.C13, L11.C16, L20.C01, L20.C11, L20.C17, L20.C22</t>
         </is>
       </c>
       <c r="N247" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-20-droit-international-monetaire-et-commercial/c17-la-sanctuarisation-et-elle-existe.md</t>
+          <t>corpus/livre-20-droit-international-monetaire-et-commercial/c16-le-patrimoine-commun-de-l-humanite.md</t>
         </is>
       </c>
     </row>
     <row r="248">
       <c r="A248" s="2" t="inlineStr">
         <is>
-          <t>L20.C18</t>
+          <t>L20.C17</t>
         </is>
       </c>
       <c r="B248" s="3" t="inlineStr">
@@ -17370,7 +17370,7 @@
       </c>
       <c r="C248" s="3" t="inlineStr">
         <is>
-          <t>L'amendement et la dérogation dans l'ordre commercial</t>
+          <t>La sanctuarisation, et elle existe</t>
         </is>
       </c>
       <c r="D248" s="3" t="inlineStr">
@@ -17395,36 +17395,36 @@
       </c>
       <c r="H248" s="3" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="I248" s="3" t="inlineStr"/>
       <c r="J248" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K248" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L248" s="3" t="inlineStr">
         <is>
-          <t>bareme, seuil_d_activation, additionnalite, fenetre_de_reforme</t>
+          <t>communs, limites_planetaires, fenetre_de_reforme, robustesse, plafond_ecologique</t>
         </is>
       </c>
       <c r="M248" s="3" t="inlineStr">
         <is>
-          <t>L1.C27, L7.C17, L7.C20, L11.C24, L20.C01, L20.C06, L20.C09, L20.C13, L20.C19, L20.C20</t>
+          <t>L1.C17, L1.C18, L7.C13, L7.C19, L7.C20, L11.C20, L20.C01, L20.C06, L20.C09, L20.C16, L20.C22</t>
         </is>
       </c>
       <c r="N248" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-20-droit-international-monetaire-et-commercial/c18-l-amendement-et-la-derogation-dans-l-ordre-commercial.md</t>
+          <t>corpus/livre-20-droit-international-monetaire-et-commercial/c17-la-sanctuarisation-et-elle-existe.md</t>
         </is>
       </c>
     </row>
     <row r="249">
       <c r="A249" s="2" t="inlineStr">
         <is>
-          <t>L20.C19</t>
+          <t>L20.C18</t>
         </is>
       </c>
       <c r="B249" s="3" t="inlineStr">
@@ -17434,7 +17434,7 @@
       </c>
       <c r="C249" s="3" t="inlineStr">
         <is>
-          <t>Le texte que la conformité invoque</t>
+          <t>L'amendement et la dérogation dans l'ordre commercial</t>
         </is>
       </c>
       <c r="D249" s="3" t="inlineStr">
@@ -17459,36 +17459,36 @@
       </c>
       <c r="H249" s="3" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="I249" s="3" t="inlineStr"/>
       <c r="J249" s="3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K249" s="3" t="n">
         <v>3</v>
       </c>
       <c r="L249" s="3" t="inlineStr">
         <is>
-          <t>bareme, additionnalite, limites_planetaires, seuil_d_activation, externalisation</t>
+          <t>bareme, seuil_d_activation, additionnalite, fenetre_de_reforme</t>
         </is>
       </c>
       <c r="M249" s="3" t="inlineStr">
         <is>
-          <t>L1.C27, L7.C17, L11.C24, L20.C01, L20.C18, L20.C20, L20.C22</t>
+          <t>L1.C27, L7.C17, L7.C20, L11.C24, L20.C01, L20.C06, L20.C09, L20.C13, L20.C19, L20.C20</t>
         </is>
       </c>
       <c r="N249" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-20-droit-international-monetaire-et-commercial/c19-le-texte-que-la-conformite-invoque.md</t>
+          <t>corpus/livre-20-droit-international-monetaire-et-commercial/c18-l-amendement-et-la-derogation-dans-l-ordre-commercial.md</t>
         </is>
       </c>
     </row>
     <row r="250">
       <c r="A250" s="2" t="inlineStr">
         <is>
-          <t>L20.C20</t>
+          <t>L20.C19</t>
         </is>
       </c>
       <c r="B250" s="3" t="inlineStr">
@@ -17498,7 +17498,7 @@
       </c>
       <c r="C250" s="3" t="inlineStr">
         <is>
-          <t>L'ajustement aux frontières comme précédent</t>
+          <t>Le texte que la conformité invoque</t>
         </is>
       </c>
       <c r="D250" s="3" t="inlineStr">
@@ -17535,24 +17535,24 @@
       </c>
       <c r="L250" s="3" t="inlineStr">
         <is>
-          <t>bareme, seuil_d_activation, externalisation, additionnalite, contrepartie_comptable</t>
+          <t>bareme, additionnalite, limites_planetaires, seuil_d_activation, externalisation</t>
         </is>
       </c>
       <c r="M250" s="3" t="inlineStr">
         <is>
-          <t>L1.C27, L7.C17, L11.C21, L11.C24, L11.C25, L20.C01, L20.C18, L20.C19, L20.C22</t>
+          <t>L1.C27, L7.C17, L11.C24, L20.C01, L20.C18, L20.C20, L20.C22</t>
         </is>
       </c>
       <c r="N250" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-20-droit-international-monetaire-et-commercial/c20-l-ajustement-aux-frontieres-comme-precedent.md</t>
+          <t>corpus/livre-20-droit-international-monetaire-et-commercial/c19-le-texte-que-la-conformite-invoque.md</t>
         </is>
       </c>
     </row>
     <row r="251">
       <c r="A251" s="2" t="inlineStr">
         <is>
-          <t>L20.C21</t>
+          <t>L20.C20</t>
         </is>
       </c>
       <c r="B251" s="3" t="inlineStr">
@@ -17562,7 +17562,7 @@
       </c>
       <c r="C251" s="3" t="inlineStr">
         <is>
-          <t>La transparence et sa limite juridictionnelle</t>
+          <t>L'ajustement aux frontières comme précédent</t>
         </is>
       </c>
       <c r="D251" s="3" t="inlineStr">
@@ -17587,36 +17587,36 @@
       </c>
       <c r="H251" s="3" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="I251" s="3" t="inlineStr"/>
       <c r="J251" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K251" s="3" t="n">
         <v>3</v>
       </c>
       <c r="L251" s="3" t="inlineStr">
         <is>
-          <t>robustesse, contrepartie_comptable, bareme, monnaie_comme_registre</t>
+          <t>bareme, seuil_d_activation, externalisation, additionnalite, contrepartie_comptable</t>
         </is>
       </c>
       <c r="M251" s="3" t="inlineStr">
         <is>
-          <t>L7.C18, L11.C21, L11.C24, L11.C25, L20.C01, L20.C11, L20.C14, L20.C20, L20.C22</t>
+          <t>L1.C27, L7.C17, L11.C21, L11.C24, L11.C25, L20.C01, L20.C18, L20.C19, L20.C22</t>
         </is>
       </c>
       <c r="N251" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-20-droit-international-monetaire-et-commercial/c21-la-transparence-et-sa-limite-juridictionnelle.md</t>
+          <t>corpus/livre-20-droit-international-monetaire-et-commercial/c20-l-ajustement-aux-frontieres-comme-precedent.md</t>
         </is>
       </c>
     </row>
     <row r="252">
       <c r="A252" s="2" t="inlineStr">
         <is>
-          <t>L20.C22</t>
+          <t>L20.C21</t>
         </is>
       </c>
       <c r="B252" s="3" t="inlineStr">
@@ -17626,7 +17626,7 @@
       </c>
       <c r="C252" s="3" t="inlineStr">
         <is>
-          <t>Ce que le droit devrait devenir</t>
+          <t>La transparence et sa limite juridictionnelle</t>
         </is>
       </c>
       <c r="D252" s="3" t="inlineStr">
@@ -17663,24 +17663,24 @@
       </c>
       <c r="L252" s="3" t="inlineStr">
         <is>
-          <t>fenetre_de_reforme, communs, limites_planetaires, regle_contre_discretion, bareme, referentiel_de_change</t>
+          <t>robustesse, contrepartie_comptable, bareme, monnaie_comme_registre</t>
         </is>
       </c>
       <c r="M252" s="3" t="inlineStr">
         <is>
-          <t>L1.C18, L7.C12, L7.C13, L11.C15, L11.C25, L20.C01, L20.C03, L20.C06, L20.C07, L20.C08, L20.C12, L20.C13, L20.C16, L20.C17, L20.C19, L20.C20, L20.C21, L20.C23</t>
+          <t>L7.C18, L11.C21, L11.C24, L11.C25, L20.C01, L20.C11, L20.C14, L20.C20, L20.C22</t>
         </is>
       </c>
       <c r="N252" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-20-droit-international-monetaire-et-commercial/c22-ce-que-le-droit-devrait-devenir.md</t>
+          <t>corpus/livre-20-droit-international-monetaire-et-commercial/c21-la-transparence-et-sa-limite-juridictionnelle.md</t>
         </is>
       </c>
     </row>
     <row r="253">
       <c r="A253" s="2" t="inlineStr">
         <is>
-          <t>L20.C23</t>
+          <t>L20.C22</t>
         </is>
       </c>
       <c r="B253" s="3" t="inlineStr">
@@ -17690,7 +17690,7 @@
       </c>
       <c r="C253" s="3" t="inlineStr">
         <is>
-          <t>La portée du livre</t>
+          <t>Ce que le droit devrait devenir</t>
         </is>
       </c>
       <c r="D253" s="3" t="inlineStr">
@@ -17720,41 +17720,41 @@
       </c>
       <c r="I253" s="3" t="inlineStr"/>
       <c r="J253" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K253" s="3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L253" s="3" t="inlineStr">
         <is>
-          <t>fenetre_de_reforme, communs, limites_planetaires, creation_monetaire, robustesse</t>
+          <t>fenetre_de_reforme, communs, limites_planetaires, regle_contre_discretion, bareme, referentiel_de_change</t>
         </is>
       </c>
       <c r="M253" s="3" t="inlineStr">
         <is>
-          <t>L1.C18, L1.C27, L7.C05, L7.C10, L7.C12, L7.C13, L11.C15, L11.C24, L11.C25, L20.C01, L20.C02, L20.C03, L20.C06, L20.C07, L20.C08, L20.C11, L20.C12, L20.C13, L20.C16, L20.C17, L20.C19, L20.C20, L20.C21, L20.C22</t>
+          <t>L1.C18, L7.C12, L7.C13, L11.C15, L11.C25, L20.C01, L20.C03, L20.C06, L20.C07, L20.C08, L20.C12, L20.C13, L20.C16, L20.C17, L20.C19, L20.C20, L20.C21, L20.C23</t>
         </is>
       </c>
       <c r="N253" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-20-droit-international-monetaire-et-commercial/c23-la-portee-du-livre.md</t>
+          <t>corpus/livre-20-droit-international-monetaire-et-commercial/c22-ce-que-le-droit-devrait-devenir.md</t>
         </is>
       </c>
     </row>
     <row r="254">
       <c r="A254" s="2" t="inlineStr">
         <is>
-          <t>L21.C01</t>
+          <t>L20.C23</t>
         </is>
       </c>
       <c r="B254" s="3" t="inlineStr">
         <is>
-          <t>L21</t>
+          <t>L20</t>
         </is>
       </c>
       <c r="C254" s="3" t="inlineStr">
         <is>
-          <t>Ce que ce livre doit établir, et le principe qui exige des fonds propres</t>
+          <t>La portée du livre</t>
         </is>
       </c>
       <c r="D254" s="3" t="inlineStr">
@@ -17774,41 +17774,41 @@
       </c>
       <c r="G254" s="3" t="inlineStr">
         <is>
-          <t>hybride</t>
+          <t>conception</t>
         </is>
       </c>
       <c r="H254" s="3" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="I254" s="3" t="inlineStr"/>
       <c r="J254" s="3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K254" s="3" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L254" s="3" t="inlineStr">
         <is>
-          <t>contrepartie_comptable, creation_monetaire, hierarchie_monetaire, monnaie_comme_registre, seuil_d_activation</t>
+          <t>fenetre_de_reforme, communs, limites_planetaires, creation_monetaire, robustesse</t>
         </is>
       </c>
       <c r="M254" s="3" t="inlineStr">
         <is>
-          <t>L1.C20, L5.C02, L5.C09, L10.C01, L10.C02, L11.C02, L18.C01, L21.C01, L19.C02, L19.C06</t>
+          <t>L1.C18, L1.C27, L7.C05, L7.C10, L7.C12, L7.C13, L11.C15, L11.C24, L11.C25, L20.C01, L20.C02, L20.C03, L20.C06, L20.C07, L20.C08, L20.C11, L20.C12, L20.C13, L20.C16, L20.C17, L20.C19, L20.C20, L20.C21, L20.C22</t>
         </is>
       </c>
       <c r="N254" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-21-plomberie-financiere-mondiale/c01-ce-que-ce-livre-doit-etablir.md</t>
+          <t>corpus/livre-20-droit-international-monetaire-et-commercial/c23-la-portee-du-livre.md</t>
         </is>
       </c>
     </row>
     <row r="255">
       <c r="A255" s="2" t="inlineStr">
         <is>
-          <t>L21.C02</t>
+          <t>L21.C01</t>
         </is>
       </c>
       <c r="B255" s="3" t="inlineStr">
@@ -17818,7 +17818,7 @@
       </c>
       <c r="C255" s="3" t="inlineStr">
         <is>
-          <t>Comment l'unité circulerait vraiment, et ce que chaque étape exige</t>
+          <t>Ce que ce livre doit établir, et le principe qui exige des fonds propres</t>
         </is>
       </c>
       <c r="D255" s="3" t="inlineStr">
@@ -17843,7 +17843,7 @@
       </c>
       <c r="H255" s="3" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="I255" s="3" t="inlineStr"/>
@@ -17851,28 +17851,28 @@
         <v>3</v>
       </c>
       <c r="K255" s="3" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="L255" s="3" t="inlineStr">
         <is>
-          <t>monnaie_comme_registre, hierarchie_monetaire, contrepartie_comptable, devise_cle, seuil_d_activation</t>
+          <t>contrepartie_comptable, creation_monetaire, hierarchie_monetaire, monnaie_comme_registre, seuil_d_activation</t>
         </is>
       </c>
       <c r="M255" s="3" t="inlineStr">
         <is>
-          <t>L1.C24, L3.C05, L3.C09, L5.C02, L5.C09, L10.C01, L11.C02, L21.C01</t>
+          <t>L1.C20, L5.C02, L5.C09, L10.C01, L10.C02, L11.C02, L18.C01, L21.C01, L19.C02, L19.C06</t>
         </is>
       </c>
       <c r="N255" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-21-plomberie-financiere-mondiale/c02-comment-l-unite-circulerait-vraiment.md</t>
+          <t>corpus/livre-21-plomberie-financiere-mondiale/c01-ce-que-ce-livre-doit-etablir.md</t>
         </is>
       </c>
     </row>
     <row r="256">
       <c r="A256" s="2" t="inlineStr">
         <is>
-          <t>L21.C03</t>
+          <t>L21.C02</t>
         </is>
       </c>
       <c r="B256" s="3" t="inlineStr">
@@ -17882,7 +17882,7 @@
       </c>
       <c r="C256" s="3" t="inlineStr">
         <is>
-          <t>Une opération de bout en bout, bilan par bilan</t>
+          <t>Comment l'unité circulerait vraiment, et ce que chaque étape exige</t>
         </is>
       </c>
       <c r="D256" s="3" t="inlineStr">
@@ -17902,12 +17902,12 @@
       </c>
       <c r="G256" s="3" t="inlineStr">
         <is>
-          <t>conception</t>
+          <t>hybride</t>
         </is>
       </c>
       <c r="H256" s="3" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="I256" s="3" t="inlineStr"/>
@@ -17915,28 +17915,28 @@
         <v>3</v>
       </c>
       <c r="K256" s="3" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="L256" s="3" t="inlineStr">
         <is>
-          <t>contrepartie_comptable, creation_monetaire, reflux_collectif, demurrage, monnaie_comme_registre, hierarchie_monetaire</t>
+          <t>monnaie_comme_registre, hierarchie_monetaire, contrepartie_comptable, devise_cle, seuil_d_activation</t>
         </is>
       </c>
       <c r="M256" s="3" t="inlineStr">
         <is>
-          <t>L1.C07, L1.C29, L10.C06, L10.C07, L11.C01, L11.C02, L11.C11, L11.C13, L11.C23, L21.C01, L21.C02, L19.C04, L16.C04</t>
+          <t>L1.C24, L3.C05, L3.C09, L5.C02, L5.C09, L10.C01, L11.C02, L21.C01</t>
         </is>
       </c>
       <c r="N256" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-21-plomberie-financiere-mondiale/c03-une-operation-de-bout-en-bout.md</t>
+          <t>corpus/livre-21-plomberie-financiere-mondiale/c02-comment-l-unite-circulerait-vraiment.md</t>
         </is>
       </c>
     </row>
     <row r="257">
       <c r="A257" s="2" t="inlineStr">
         <is>
-          <t>L21.C04</t>
+          <t>L21.C03</t>
         </is>
       </c>
       <c r="B257" s="3" t="inlineStr">
@@ -17946,7 +17946,7 @@
       </c>
       <c r="C257" s="3" t="inlineStr">
         <is>
-          <t>Ce que l'émission coûte aux banques qui l'hébergent</t>
+          <t>Une opération de bout en bout, bilan par bilan</t>
         </is>
       </c>
       <c r="D257" s="3" t="inlineStr">
@@ -17966,41 +17966,41 @@
       </c>
       <c r="G257" s="3" t="inlineStr">
         <is>
-          <t>descriptif</t>
+          <t>conception</t>
         </is>
       </c>
       <c r="H257" s="3" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="I257" s="3" t="inlineStr"/>
       <c r="J257" s="3" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="K257" s="3" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="L257" s="3" t="inlineStr">
         <is>
-          <t>contrepartie_comptable, creation_monetaire, hierarchie_monetaire, reflux_collectif, demurrage</t>
+          <t>contrepartie_comptable, creation_monetaire, reflux_collectif, demurrage, monnaie_comme_registre, hierarchie_monetaire</t>
         </is>
       </c>
       <c r="M257" s="3" t="inlineStr">
         <is>
-          <t>L1.C07, L10.C01, L11.C02, L11.C07, L11.C09, L11.C11, L11.C23, L21.C02, L21.C03</t>
+          <t>L1.C07, L1.C29, L10.C06, L10.C07, L11.C01, L11.C02, L11.C11, L11.C13, L11.C23, L21.C01, L21.C02, L19.C04, L16.C04</t>
         </is>
       </c>
       <c r="N257" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-21-plomberie-financiere-mondiale/c04-ce-que-l-emission-coute-aux-banques-qui-l-hebergent.md</t>
+          <t>corpus/livre-21-plomberie-financiere-mondiale/c03-une-operation-de-bout-en-bout.md</t>
         </is>
       </c>
     </row>
     <row r="258">
       <c r="A258" s="2" t="inlineStr">
         <is>
-          <t>L21.C05</t>
+          <t>L21.C04</t>
         </is>
       </c>
       <c r="B258" s="3" t="inlineStr">
@@ -18010,7 +18010,7 @@
       </c>
       <c r="C258" s="3" t="inlineStr">
         <is>
-          <t>La première infrastructure ouverte, et ce qu'elle renverse</t>
+          <t>Ce que l'émission coûte aux banques qui l'hébergent</t>
         </is>
       </c>
       <c r="D258" s="3" t="inlineStr">
@@ -18030,7 +18030,7 @@
       </c>
       <c r="G258" s="3" t="inlineStr">
         <is>
-          <t>hybride</t>
+          <t>descriptif</t>
         </is>
       </c>
       <c r="H258" s="3" t="inlineStr">
@@ -18040,31 +18040,31 @@
       </c>
       <c r="I258" s="3" t="inlineStr"/>
       <c r="J258" s="3" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K258" s="3" t="n">
         <v>4</v>
       </c>
       <c r="L258" s="3" t="inlineStr">
         <is>
-          <t>seuil_d_activation, hierarchie_monetaire, monnaie_comme_registre, devise_cle, demurrage, contrepartie_comptable</t>
+          <t>contrepartie_comptable, creation_monetaire, hierarchie_monetaire, reflux_collectif, demurrage</t>
         </is>
       </c>
       <c r="M258" s="3" t="inlineStr">
         <is>
-          <t>L3.C09, L5.C02, L5.C09, L11.C01, L11.C02, L11.C07, L21.C01, L21.C02, L21.C03, L21.C04</t>
+          <t>L1.C07, L10.C01, L11.C02, L11.C07, L11.C09, L11.C11, L11.C23, L21.C02, L21.C03</t>
         </is>
       </c>
       <c r="N258" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-21-plomberie-financiere-mondiale/c05-la-premiere-infrastructure-ouverte-et-ce-qu-elle-renverse.md</t>
+          <t>corpus/livre-21-plomberie-financiere-mondiale/c04-ce-que-l-emission-coute-aux-banques-qui-l-hebergent.md</t>
         </is>
       </c>
     </row>
     <row r="259">
       <c r="A259" s="2" t="inlineStr">
         <is>
-          <t>L21.C06</t>
+          <t>L21.C05</t>
         </is>
       </c>
       <c r="B259" s="3" t="inlineStr">
@@ -18074,7 +18074,7 @@
       </c>
       <c r="C259" s="3" t="inlineStr">
         <is>
-          <t>La jambe qui reste, et ce qu'il faut pour la protéger</t>
+          <t>La première infrastructure ouverte, et ce qu'elle renverse</t>
         </is>
       </c>
       <c r="D259" s="3" t="inlineStr">
@@ -18111,24 +18111,24 @@
       </c>
       <c r="L259" s="3" t="inlineStr">
         <is>
-          <t>contrepartie_comptable, hierarchie_monetaire, monnaie_comme_registre, seuil_d_activation</t>
+          <t>seuil_d_activation, hierarchie_monetaire, monnaie_comme_registre, devise_cle, demurrage, contrepartie_comptable</t>
         </is>
       </c>
       <c r="M259" s="3" t="inlineStr">
         <is>
-          <t>L5.C02, L11.C02, L11.C11, L20.C02, L21.C02, L21.C03, L21.C05</t>
+          <t>L3.C09, L5.C02, L5.C09, L11.C01, L11.C02, L11.C07, L21.C01, L21.C02, L21.C03, L21.C04</t>
         </is>
       </c>
       <c r="N259" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-21-plomberie-financiere-mondiale/c06-la-jambe-qui-reste-et-ce-qu-il-faut-pour-la-proteger.md</t>
+          <t>corpus/livre-21-plomberie-financiere-mondiale/c05-la-premiere-infrastructure-ouverte-et-ce-qu-elle-renverse.md</t>
         </is>
       </c>
     </row>
     <row r="260">
       <c r="A260" s="2" t="inlineStr">
         <is>
-          <t>L21.C07</t>
+          <t>L21.C06</t>
         </is>
       </c>
       <c r="B260" s="3" t="inlineStr">
@@ -18138,7 +18138,7 @@
       </c>
       <c r="C260" s="3" t="inlineStr">
         <is>
-          <t>Portée de la tranche</t>
+          <t>La jambe qui reste, et ce qu'il faut pour la protéger</t>
         </is>
       </c>
       <c r="D260" s="3" t="inlineStr">
@@ -18158,41 +18158,41 @@
       </c>
       <c r="G260" s="3" t="inlineStr">
         <is>
-          <t>descriptif</t>
+          <t>hybride</t>
         </is>
       </c>
       <c r="H260" s="3" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="I260" s="3" t="inlineStr"/>
       <c r="J260" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K260" s="3" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L260" s="3" t="inlineStr">
         <is>
-          <t>seuil_d_activation, contrepartie_comptable, hierarchie_monetaire, monnaie_comme_registre</t>
+          <t>contrepartie_comptable, hierarchie_monetaire, monnaie_comme_registre, seuil_d_activation</t>
         </is>
       </c>
       <c r="M260" s="3" t="inlineStr">
         <is>
-          <t>L5.C02, L10.C06, L11.C01, L11.C02, L20.C01, L21.C01, L21.C02, L21.C03, L21.C04, L21.C05, L21.C06, L21.C08</t>
+          <t>L5.C02, L11.C02, L11.C11, L20.C02, L21.C02, L21.C03, L21.C05</t>
         </is>
       </c>
       <c r="N260" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-21-plomberie-financiere-mondiale/c07-portee-de-la-tranche.md</t>
+          <t>corpus/livre-21-plomberie-financiere-mondiale/c06-la-jambe-qui-reste-et-ce-qu-il-faut-pour-la-proteger.md</t>
         </is>
       </c>
     </row>
     <row r="261">
       <c r="A261" s="2" t="inlineStr">
         <is>
-          <t>L21.C08</t>
+          <t>L21.C07</t>
         </is>
       </c>
       <c r="B261" s="3" t="inlineStr">
@@ -18202,7 +18202,7 @@
       </c>
       <c r="C261" s="3" t="inlineStr">
         <is>
-          <t>La norme des infrastructures exige des fonds propres</t>
+          <t>Portée de la tranche</t>
         </is>
       </c>
       <c r="D261" s="3" t="inlineStr">
@@ -18222,7 +18222,7 @@
       </c>
       <c r="G261" s="3" t="inlineStr">
         <is>
-          <t>hybride</t>
+          <t>descriptif</t>
         </is>
       </c>
       <c r="H261" s="3" t="inlineStr">
@@ -18232,41 +18232,41 @@
       </c>
       <c r="I261" s="3" t="inlineStr"/>
       <c r="J261" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K261" s="3" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="L261" s="3" t="inlineStr">
         <is>
-          <t>contrepartie_comptable, robustesse, hierarchie_monetaire</t>
+          <t>seuil_d_activation, contrepartie_comptable, hierarchie_monetaire, monnaie_comme_registre</t>
         </is>
       </c>
       <c r="M261" s="3" t="inlineStr">
         <is>
-          <t>L16.C04, L19.C01, L19.C03, L19.C06, L19.C07, L21.C03, L21.C05, L21.C07</t>
+          <t>L5.C02, L10.C06, L11.C01, L11.C02, L20.C01, L21.C01, L21.C02, L21.C03, L21.C04, L21.C05, L21.C06, L21.C08</t>
         </is>
       </c>
       <c r="N261" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-21-plomberie-financiere-mondiale/c08-la-norme-des-infrastructures-exige-des-fonds-propres.md</t>
+          <t>corpus/livre-21-plomberie-financiere-mondiale/c07-portee-de-la-tranche.md</t>
         </is>
       </c>
     </row>
     <row r="262">
       <c r="A262" s="2" t="inlineStr">
         <is>
-          <t>L22.C01</t>
+          <t>L21.C08</t>
         </is>
       </c>
       <c r="B262" s="3" t="inlineStr">
         <is>
-          <t>L22</t>
+          <t>L21</t>
         </is>
       </c>
       <c r="C262" s="3" t="inlineStr">
         <is>
-          <t>Ce que ce livre doit établir</t>
+          <t>La norme des infrastructures exige des fonds propres</t>
         </is>
       </c>
       <c r="D262" s="3" t="inlineStr">
@@ -18286,41 +18286,41 @@
       </c>
       <c r="G262" s="3" t="inlineStr">
         <is>
-          <t>descriptif</t>
+          <t>hybride</t>
         </is>
       </c>
       <c r="H262" s="3" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="I262" s="3" t="inlineStr"/>
       <c r="J262" s="3" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K262" s="3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L262" s="3" t="inlineStr">
         <is>
-          <t>architecture_invisible, systeme_monetaire_et_financier, reflux_collectif, reflux_transactionnel, hierarchie_monetaire, monnaie_comme_registre</t>
+          <t>contrepartie_comptable, robustesse, hierarchie_monetaire</t>
         </is>
       </c>
       <c r="M262" s="3" t="inlineStr">
         <is>
-          <t>L1.C09, L1.C19, L5.C09, L11.C02, L11.C05, L11.C09, L11.C27, L21.C03, L21.C04</t>
+          <t>L16.C04, L19.C01, L19.C03, L19.C06, L19.C07, L21.C03, L21.C05, L21.C07</t>
         </is>
       </c>
       <c r="N262" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-22-finance-non-bancaire/c01-ce-que-ce-livre-doit-etablir.md</t>
+          <t>corpus/livre-21-plomberie-financiere-mondiale/c08-la-norme-des-infrastructures-exige-des-fonds-propres.md</t>
         </is>
       </c>
     </row>
     <row r="263">
       <c r="A263" s="2" t="inlineStr">
         <is>
-          <t>L22.C02</t>
+          <t>L22.C01</t>
         </is>
       </c>
       <c r="B263" s="3" t="inlineStr">
@@ -18330,7 +18330,7 @@
       </c>
       <c r="C263" s="3" t="inlineStr">
         <is>
-          <t>Où va la monnaie émise, et pourquoi le reflux ne l'y suit pas</t>
+          <t>Ce que ce livre doit établir</t>
         </is>
       </c>
       <c r="D263" s="3" t="inlineStr">
@@ -18350,41 +18350,41 @@
       </c>
       <c r="G263" s="3" t="inlineStr">
         <is>
-          <t>conception</t>
+          <t>descriptif</t>
         </is>
       </c>
       <c r="H263" s="3" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="I263" s="3" t="inlineStr"/>
       <c r="J263" s="3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K263" s="3" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L263" s="3" t="inlineStr">
         <is>
-          <t>reflux_transactionnel, reflux_collectif, demurrage, monnaie_endogene, architecture_invisible, hierarchie_monetaire</t>
+          <t>architecture_invisible, systeme_monetaire_et_financier, reflux_collectif, reflux_transactionnel, hierarchie_monetaire, monnaie_comme_registre</t>
         </is>
       </c>
       <c r="M263" s="3" t="inlineStr">
         <is>
-          <t>L1.C19, L5.C09, L11.C02, L11.C05, L11.C09, L11.C27, L21.C03, L22.C01, L23.C04, L26.C04</t>
+          <t>L1.C09, L1.C19, L5.C09, L11.C02, L11.C05, L11.C09, L11.C27, L21.C03, L21.C04</t>
         </is>
       </c>
       <c r="N263" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-22-finance-non-bancaire/c02-ou-va-la-monnaie-emise.md</t>
+          <t>corpus/livre-22-finance-non-bancaire/c01-ce-que-ce-livre-doit-etablir.md</t>
         </is>
       </c>
     </row>
     <row r="264">
       <c r="A264" s="2" t="inlineStr">
         <is>
-          <t>L22.C03</t>
+          <t>L22.C02</t>
         </is>
       </c>
       <c r="B264" s="3" t="inlineStr">
@@ -18394,7 +18394,7 @@
       </c>
       <c r="C264" s="3" t="inlineStr">
         <is>
-          <t>Le barème existe déjà, et il a trois pièces que le corpus n'a pas</t>
+          <t>Où va la monnaie émise, et pourquoi le reflux ne l'y suit pas</t>
         </is>
       </c>
       <c r="D264" s="3" t="inlineStr">
@@ -18414,41 +18414,41 @@
       </c>
       <c r="G264" s="3" t="inlineStr">
         <is>
-          <t>hybride</t>
+          <t>conception</t>
         </is>
       </c>
       <c r="H264" s="3" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="I264" s="3" t="inlineStr"/>
       <c r="J264" s="3" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K264" s="3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L264" s="3" t="inlineStr">
         <is>
-          <t>qualification_regenerative, bareme, additionnalite, indicateur_de_progres, communs, plafond_ecologique</t>
+          <t>reflux_transactionnel, reflux_collectif, demurrage, monnaie_endogene, architecture_invisible, hierarchie_monetaire</t>
         </is>
       </c>
       <c r="M264" s="3" t="inlineStr">
         <is>
-          <t>L11.C13, L11.C11, L11.C25, L12.C01, L18.C06, L22.C01, L25.C01</t>
+          <t>L1.C19, L5.C09, L11.C02, L11.C05, L11.C09, L11.C27, L21.C03, L22.C01, L23.C04, L26.C04</t>
         </is>
       </c>
       <c r="N264" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-22-finance-non-bancaire/c03-le-bareme-existe-deja.md</t>
+          <t>corpus/livre-22-finance-non-bancaire/c02-ou-va-la-monnaie-emise.md</t>
         </is>
       </c>
     </row>
     <row r="265">
       <c r="A265" s="2" t="inlineStr">
         <is>
-          <t>L22.C04</t>
+          <t>L22.C03</t>
         </is>
       </c>
       <c r="B265" s="3" t="inlineStr">
@@ -18458,7 +18458,7 @@
       </c>
       <c r="C265" s="3" t="inlineStr">
         <is>
-          <t>Les critères réels ne mesurent pas, ils certifient</t>
+          <t>Le barème existe déjà, et il a trois pièces que le corpus n'a pas</t>
         </is>
       </c>
       <c r="D265" s="3" t="inlineStr">
@@ -18483,7 +18483,7 @@
       </c>
       <c r="H265" s="3" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="I265" s="3" t="inlineStr"/>
@@ -18491,28 +18491,28 @@
         <v>4</v>
       </c>
       <c r="K265" s="3" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L265" s="3" t="inlineStr">
         <is>
-          <t>qualification_regenerative, bareme, additionnalite, communs, valorisation_des_communs, indicateur_de_progres</t>
+          <t>qualification_regenerative, bareme, additionnalite, indicateur_de_progres, communs, plafond_ecologique</t>
         </is>
       </c>
       <c r="M265" s="3" t="inlineStr">
         <is>
-          <t>L6.C06, L11.C13, L11.C16, L11.C25, L13.C01, L14.C01, L18.C06, L22.C03</t>
+          <t>L11.C13, L11.C11, L11.C25, L12.C01, L18.C06, L22.C01, L25.C01</t>
         </is>
       </c>
       <c r="N265" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-22-finance-non-bancaire/c04-les-criteres-reels-ne-mesurent-pas.md</t>
+          <t>corpus/livre-22-finance-non-bancaire/c03-le-bareme-existe-deja.md</t>
         </is>
       </c>
     </row>
     <row r="266">
       <c r="A266" s="2" t="inlineStr">
         <is>
-          <t>L22.C05</t>
+          <t>L22.C04</t>
         </is>
       </c>
       <c r="B266" s="3" t="inlineStr">
@@ -18522,7 +18522,7 @@
       </c>
       <c r="C266" s="3" t="inlineStr">
         <is>
-          <t>L'épargne retraite, et le dilemme du troisième instrument</t>
+          <t>Les critères réels ne mesurent pas, ils certifient</t>
         </is>
       </c>
       <c r="D266" s="3" t="inlineStr">
@@ -18547,36 +18547,36 @@
       </c>
       <c r="H266" s="3" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="I266" s="3" t="inlineStr"/>
       <c r="J266" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K266" s="3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L266" s="3" t="inlineStr">
         <is>
-          <t>reflux_collectif, demurrage, essentiel_insolvable, plancher_social, solvabilite_anticipee, architecture_invisible</t>
+          <t>qualification_regenerative, bareme, additionnalite, communs, valorisation_des_communs, indicateur_de_progres</t>
         </is>
       </c>
       <c r="M266" s="3" t="inlineStr">
         <is>
-          <t>L1.C15, L11.C07, L11.C09, L11.C18, L22.C01, L22.C02, L25.C01</t>
+          <t>L6.C06, L11.C13, L11.C16, L11.C25, L13.C01, L14.C01, L18.C06, L22.C03</t>
         </is>
       </c>
       <c r="N266" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-22-finance-non-bancaire/c05-l-epargne-retraite-et-le-dilemme-du-troisieme-instrument.md</t>
+          <t>corpus/livre-22-finance-non-bancaire/c04-les-criteres-reels-ne-mesurent-pas.md</t>
         </is>
       </c>
     </row>
     <row r="267">
       <c r="A267" s="2" t="inlineStr">
         <is>
-          <t>L22.C06</t>
+          <t>L22.C05</t>
         </is>
       </c>
       <c r="B267" s="3" t="inlineStr">
@@ -18586,7 +18586,7 @@
       </c>
       <c r="C267" s="3" t="inlineStr">
         <is>
-          <t>Qui décide, quand personne ne décide</t>
+          <t>L'épargne retraite, et le dilemme du troisième instrument</t>
         </is>
       </c>
       <c r="D267" s="3" t="inlineStr">
@@ -18616,31 +18616,31 @@
       </c>
       <c r="I267" s="3" t="inlineStr"/>
       <c r="J267" s="3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K267" s="3" t="n">
         <v>4</v>
       </c>
       <c r="L267" s="3" t="inlineStr">
         <is>
-          <t>architecture_invisible, indicateur_de_progres, qualification_regenerative, essentiel_insolvable, fenetre_de_reforme, regle_contre_discretion</t>
+          <t>reflux_collectif, demurrage, essentiel_insolvable, plancher_social, solvabilite_anticipee, architecture_invisible</t>
         </is>
       </c>
       <c r="M267" s="3" t="inlineStr">
         <is>
-          <t>L1.C15, L5.C09, L11.C13, L14.C01, L22.C01, L22.C02, L22.C03, L22.C05</t>
+          <t>L1.C15, L11.C07, L11.C09, L11.C18, L22.C01, L22.C02, L25.C01</t>
         </is>
       </c>
       <c r="N267" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-22-finance-non-bancaire/c06-qui-decide-quand-personne-ne-decide.md</t>
+          <t>corpus/livre-22-finance-non-bancaire/c05-l-epargne-retraite-et-le-dilemme-du-troisieme-instrument.md</t>
         </is>
       </c>
     </row>
     <row r="268">
       <c r="A268" s="2" t="inlineStr">
         <is>
-          <t>L22.C07</t>
+          <t>L22.C06</t>
         </is>
       </c>
       <c r="B268" s="3" t="inlineStr">
@@ -18650,7 +18650,7 @@
       </c>
       <c r="C268" s="3" t="inlineStr">
         <is>
-          <t>Portée de la tranche</t>
+          <t>Qui décide, quand personne ne décide</t>
         </is>
       </c>
       <c r="D268" s="3" t="inlineStr">
@@ -18670,7 +18670,7 @@
       </c>
       <c r="G268" s="3" t="inlineStr">
         <is>
-          <t>descriptif</t>
+          <t>hybride</t>
         </is>
       </c>
       <c r="H268" s="3" t="inlineStr">
@@ -18680,41 +18680,41 @@
       </c>
       <c r="I268" s="3" t="inlineStr"/>
       <c r="J268" s="3" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K268" s="3" t="n">
         <v>4</v>
       </c>
       <c r="L268" s="3" t="inlineStr">
         <is>
-          <t>architecture_invisible, reflux_transactionnel, qualification_regenerative, bareme, essentiel_insolvable</t>
+          <t>architecture_invisible, indicateur_de_progres, qualification_regenerative, essentiel_insolvable, fenetre_de_reforme, regle_contre_discretion</t>
         </is>
       </c>
       <c r="M268" s="3" t="inlineStr">
         <is>
-          <t>L1.C15, L5.C09, L11.C02, L11.C13, L11.C18, L22.C01, L22.C02, L22.C03, L22.C04, L22.C05, L22.C06</t>
+          <t>L1.C15, L5.C09, L11.C13, L14.C01, L22.C01, L22.C02, L22.C03, L22.C05</t>
         </is>
       </c>
       <c r="N268" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-22-finance-non-bancaire/c07-portee-de-la-tranche.md</t>
+          <t>corpus/livre-22-finance-non-bancaire/c06-qui-decide-quand-personne-ne-decide.md</t>
         </is>
       </c>
     </row>
     <row r="269">
       <c r="A269" s="2" t="inlineStr">
         <is>
-          <t>L23.C01</t>
+          <t>L22.C07</t>
         </is>
       </c>
       <c r="B269" s="3" t="inlineStr">
         <is>
-          <t>L23</t>
+          <t>L22</t>
         </is>
       </c>
       <c r="C269" s="3" t="inlineStr">
         <is>
-          <t>Ce que ce livre doit établir</t>
+          <t>Portée de la tranche</t>
         </is>
       </c>
       <c r="D269" s="3" t="inlineStr">
@@ -18734,7 +18734,7 @@
       </c>
       <c r="G269" s="3" t="inlineStr">
         <is>
-          <t>conception</t>
+          <t>descriptif</t>
         </is>
       </c>
       <c r="H269" s="3" t="inlineStr">
@@ -18744,31 +18744,31 @@
       </c>
       <c r="I269" s="3" t="inlineStr"/>
       <c r="J269" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="K269" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="K269" s="3" t="n">
-        <v>3</v>
-      </c>
       <c r="L269" s="3" t="inlineStr">
         <is>
-          <t>bareme, reflux_transactionnel, externalisation, essentiel_insolvable, polycentricite, regle_contre_discretion</t>
+          <t>architecture_invisible, reflux_transactionnel, qualification_regenerative, bareme, essentiel_insolvable</t>
         </is>
       </c>
       <c r="M269" s="3" t="inlineStr">
         <is>
-          <t>L1.C15, L5.C07, L10.C06, L11.C05, L11.C09, L11.C21, L11.C24, L18.C09, L20.C02, L20.C20</t>
+          <t>L1.C15, L5.C09, L11.C02, L11.C13, L11.C18, L22.C01, L22.C02, L22.C03, L22.C04, L22.C05, L22.C06</t>
         </is>
       </c>
       <c r="N269" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-23-fiscalite-mondiale-et-opacite/c01-ce-que-ce-livre-doit-etablir.md</t>
+          <t>corpus/livre-22-finance-non-bancaire/c07-portee-de-la-tranche.md</t>
         </is>
       </c>
     </row>
     <row r="270">
       <c r="A270" s="2" t="inlineStr">
         <is>
-          <t>L23.C02</t>
+          <t>L23.C01</t>
         </is>
       </c>
       <c r="B270" s="3" t="inlineStr">
@@ -18778,7 +18778,7 @@
       </c>
       <c r="C270" s="3" t="inlineStr">
         <is>
-          <t>La compétence que la convention ne crée pas, et le vote qu'elle a gagné</t>
+          <t>Ce que ce livre doit établir</t>
         </is>
       </c>
       <c r="D270" s="3" t="inlineStr">
@@ -18798,7 +18798,7 @@
       </c>
       <c r="G270" s="3" t="inlineStr">
         <is>
-          <t>hybride</t>
+          <t>conception</t>
         </is>
       </c>
       <c r="H270" s="3" t="inlineStr">
@@ -18815,24 +18815,24 @@
       </c>
       <c r="L270" s="3" t="inlineStr">
         <is>
-          <t>polycentricite, bareme, reflux_transactionnel, seuil_d_activation, regle_contre_discretion, externalisation</t>
+          <t>bareme, reflux_transactionnel, externalisation, essentiel_insolvable, polycentricite, regle_contre_discretion</t>
         </is>
       </c>
       <c r="M270" s="3" t="inlineStr">
         <is>
-          <t>L1.C25, L5.C04, L10.C06, L11.C21, L20.C02, L20.C20, L23.C01</t>
+          <t>L1.C15, L5.C07, L10.C06, L11.C05, L11.C09, L11.C21, L11.C24, L18.C09, L20.C02, L20.C20</t>
         </is>
       </c>
       <c r="N270" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-23-fiscalite-mondiale-et-opacite/c02-la-competence-que-la-convention-ne-cree-pas.md</t>
+          <t>corpus/livre-23-fiscalite-mondiale-et-opacite/c01-ce-que-ce-livre-doit-etablir.md</t>
         </is>
       </c>
     </row>
     <row r="271">
       <c r="A271" s="2" t="inlineStr">
         <is>
-          <t>L23.C03</t>
+          <t>L23.C02</t>
         </is>
       </c>
       <c r="B271" s="3" t="inlineStr">
@@ -18842,7 +18842,7 @@
       </c>
       <c r="C271" s="3" t="inlineStr">
         <is>
-          <t>F8 appliqué à une négociation en cours, et le résultat n'est pas le désarmement</t>
+          <t>La compétence que la convention ne crée pas, et le vote qu'elle a gagné</t>
         </is>
       </c>
       <c r="D271" s="3" t="inlineStr">
@@ -18879,24 +18879,24 @@
       </c>
       <c r="L271" s="3" t="inlineStr">
         <is>
-          <t>regle_contre_discretion, polycentricite, seuil_d_activation, bareme, externalisation</t>
+          <t>polycentricite, bareme, reflux_transactionnel, seuil_d_activation, regle_contre_discretion, externalisation</t>
         </is>
       </c>
       <c r="M271" s="3" t="inlineStr">
         <is>
-          <t>L5.C04, L6.C09, L11.C21, L20.C02, L20.C13, L23.C01, L23.C02</t>
+          <t>L1.C25, L5.C04, L10.C06, L11.C21, L20.C02, L20.C20, L23.C01</t>
         </is>
       </c>
       <c r="N271" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-23-fiscalite-mondiale-et-opacite/c03-f8-applique-a-une-negociation-en-cours.md</t>
+          <t>corpus/livre-23-fiscalite-mondiale-et-opacite/c02-la-competence-que-la-convention-ne-cree-pas.md</t>
         </is>
       </c>
     </row>
     <row r="272">
       <c r="A272" s="2" t="inlineStr">
         <is>
-          <t>L23.C04</t>
+          <t>L23.C03</t>
         </is>
       </c>
       <c r="B272" s="3" t="inlineStr">
@@ -18906,7 +18906,7 @@
       </c>
       <c r="C272" s="3" t="inlineStr">
         <is>
-          <t>La transparence que le corpus supposait a été invalidée</t>
+          <t>F8 appliqué à une négociation en cours, et le résultat n'est pas le désarmement</t>
         </is>
       </c>
       <c r="D272" s="3" t="inlineStr">
@@ -18936,31 +18936,31 @@
       </c>
       <c r="I272" s="3" t="inlineStr"/>
       <c r="J272" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K272" s="3" t="n">
         <v>3</v>
       </c>
       <c r="L272" s="3" t="inlineStr">
         <is>
-          <t>regle_contre_discretion, externalisation, bareme, polycentricite, architecture_invisible</t>
+          <t>regle_contre_discretion, polycentricite, seuil_d_activation, bareme, externalisation</t>
         </is>
       </c>
       <c r="M272" s="3" t="inlineStr">
         <is>
-          <t>L6.C09, L11.C13, L11.C25, L20.C20, L23.C01, L23.C02, L23.C03</t>
+          <t>L5.C04, L6.C09, L11.C21, L20.C02, L20.C13, L23.C01, L23.C02</t>
         </is>
       </c>
       <c r="N272" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-23-fiscalite-mondiale-et-opacite/c04-la-transparence-que-le-corpus-supposait-a-ete-invalidee.md</t>
+          <t>corpus/livre-23-fiscalite-mondiale-et-opacite/c03-f8-applique-a-une-negociation-en-cours.md</t>
         </is>
       </c>
     </row>
     <row r="273">
       <c r="A273" s="2" t="inlineStr">
         <is>
-          <t>L23.C05</t>
+          <t>L23.C04</t>
         </is>
       </c>
       <c r="B273" s="3" t="inlineStr">
@@ -18970,7 +18970,7 @@
       </c>
       <c r="C273" s="3" t="inlineStr">
         <is>
-          <t>Intéresser le percepteur, et ce que le taux révèle</t>
+          <t>La transparence que le corpus supposait a été invalidée</t>
         </is>
       </c>
       <c r="D273" s="3" t="inlineStr">
@@ -19007,24 +19007,24 @@
       </c>
       <c r="L273" s="3" t="inlineStr">
         <is>
-          <t>bareme, reflux_transactionnel, regle_contre_discretion, polycentricite, seuil_d_activation</t>
+          <t>regle_contre_discretion, externalisation, bareme, polycentricite, architecture_invisible</t>
         </is>
       </c>
       <c r="M273" s="3" t="inlineStr">
         <is>
-          <t>L11.C21, L11.C24, L18.C09, L20.C20, L23.C01, L23.C02, L23.C03</t>
+          <t>L6.C09, L11.C13, L11.C25, L20.C20, L23.C01, L23.C02, L23.C03</t>
         </is>
       </c>
       <c r="N273" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-23-fiscalite-mondiale-et-opacite/c05-interesser-le-percepteur-et-ce-que-le-taux-revele.md</t>
+          <t>corpus/livre-23-fiscalite-mondiale-et-opacite/c04-la-transparence-que-le-corpus-supposait-a-ete-invalidee.md</t>
         </is>
       </c>
     </row>
     <row r="274">
       <c r="A274" s="2" t="inlineStr">
         <is>
-          <t>L23.C06</t>
+          <t>L23.C05</t>
         </is>
       </c>
       <c r="B274" s="3" t="inlineStr">
@@ -19034,7 +19034,7 @@
       </c>
       <c r="C274" s="3" t="inlineStr">
         <is>
-          <t>L'arbre appliqué à la fonte, et il ne reste que deux branches</t>
+          <t>Intéresser le percepteur, et ce que le taux révèle</t>
         </is>
       </c>
       <c r="D274" s="3" t="inlineStr">
@@ -19054,7 +19054,7 @@
       </c>
       <c r="G274" s="3" t="inlineStr">
         <is>
-          <t>conception</t>
+          <t>hybride</t>
         </is>
       </c>
       <c r="H274" s="3" t="inlineStr">
@@ -19064,31 +19064,31 @@
       </c>
       <c r="I274" s="3" t="inlineStr"/>
       <c r="J274" s="3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K274" s="3" t="n">
         <v>3</v>
       </c>
       <c r="L274" s="3" t="inlineStr">
         <is>
-          <t>bareme, reflux_transactionnel, monnaie_fondante, demurrage, regle_contre_discretion, essentiel_insolvable</t>
+          <t>bareme, reflux_transactionnel, regle_contre_discretion, polycentricite, seuil_d_activation</t>
         </is>
       </c>
       <c r="M274" s="3" t="inlineStr">
         <is>
-          <t>L10.C06, L11.C05, L11.C09, L11.C21, L11.C24, L18.C09, L20.C02, L23.C01, L23.C02, L23.C03, L23.C04, L23.C05</t>
+          <t>L11.C21, L11.C24, L18.C09, L20.C20, L23.C01, L23.C02, L23.C03</t>
         </is>
       </c>
       <c r="N274" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-23-fiscalite-mondiale-et-opacite/c06-l-arbre-applique-a-la-fonte.md</t>
+          <t>corpus/livre-23-fiscalite-mondiale-et-opacite/c05-interesser-le-percepteur-et-ce-que-le-taux-revele.md</t>
         </is>
       </c>
     </row>
     <row r="275">
       <c r="A275" s="2" t="inlineStr">
         <is>
-          <t>L23.C07</t>
+          <t>L23.C06</t>
         </is>
       </c>
       <c r="B275" s="3" t="inlineStr">
@@ -19098,7 +19098,7 @@
       </c>
       <c r="C275" s="3" t="inlineStr">
         <is>
-          <t>Portée de la tranche, et la moitié qui n'est pas commencée</t>
+          <t>L'arbre appliqué à la fonte, et il ne reste que deux branches</t>
         </is>
       </c>
       <c r="D275" s="3" t="inlineStr">
@@ -19128,41 +19128,41 @@
       </c>
       <c r="I275" s="3" t="inlineStr"/>
       <c r="J275" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K275" s="3" t="n">
         <v>3</v>
       </c>
       <c r="L275" s="3" t="inlineStr">
         <is>
-          <t>bareme, reflux_transactionnel, externalisation, regle_contre_discretion, polycentricite, essentiel_insolvable</t>
+          <t>bareme, reflux_transactionnel, monnaie_fondante, demurrage, regle_contre_discretion, essentiel_insolvable</t>
         </is>
       </c>
       <c r="M275" s="3" t="inlineStr">
         <is>
-          <t>L10.C06, L11.C05, L11.C21, L11.C25, L18.C09, L20.C20, L23.C01, L23.C02, L23.C03, L23.C04, L23.C05, L23.C06</t>
+          <t>L10.C06, L11.C05, L11.C09, L11.C21, L11.C24, L18.C09, L20.C02, L23.C01, L23.C02, L23.C03, L23.C04, L23.C05</t>
         </is>
       </c>
       <c r="N275" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-23-fiscalite-mondiale-et-opacite/c07-portee-de-la-tranche.md</t>
+          <t>corpus/livre-23-fiscalite-mondiale-et-opacite/c06-l-arbre-applique-a-la-fonte.md</t>
         </is>
       </c>
     </row>
     <row r="276">
       <c r="A276" s="2" t="inlineStr">
         <is>
-          <t>L24.C01</t>
+          <t>L23.C07</t>
         </is>
       </c>
       <c r="B276" s="3" t="inlineStr">
         <is>
-          <t>L24</t>
+          <t>L23</t>
         </is>
       </c>
       <c r="C276" s="3" t="inlineStr">
         <is>
-          <t>Ce que ce livre doit établir</t>
+          <t>Portée de la tranche, et la moitié qui n'est pas commencée</t>
         </is>
       </c>
       <c r="D276" s="3" t="inlineStr">
@@ -19182,7 +19182,7 @@
       </c>
       <c r="G276" s="3" t="inlineStr">
         <is>
-          <t>descriptif</t>
+          <t>conception</t>
         </is>
       </c>
       <c r="H276" s="3" t="inlineStr">
@@ -19192,31 +19192,31 @@
       </c>
       <c r="I276" s="3" t="inlineStr"/>
       <c r="J276" s="3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K276" s="3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L276" s="3" t="inlineStr">
         <is>
-          <t>limites_planetaires, plafond_ecologique, entropie, decouplage, degeneratif, qualification_regenerative, essentiel_insolvable</t>
+          <t>bareme, reflux_transactionnel, externalisation, regle_contre_discretion, polycentricite, essentiel_insolvable</t>
         </is>
       </c>
       <c r="M276" s="3" t="inlineStr">
         <is>
-          <t>L1.C15, L5.C08, L11.C13, L18.C01, L18.C04, L22.C04, L26.C01</t>
+          <t>L10.C06, L11.C05, L11.C21, L11.C25, L18.C09, L20.C20, L23.C01, L23.C02, L23.C03, L23.C04, L23.C05, L23.C06</t>
         </is>
       </c>
       <c r="N276" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-24-conditions-materielles-de-la-vie/c01-ce-que-ce-livre-doit-etablir.md</t>
+          <t>corpus/livre-23-fiscalite-mondiale-et-opacite/c07-portee-de-la-tranche.md</t>
         </is>
       </c>
     </row>
     <row r="277">
       <c r="A277" s="2" t="inlineStr">
         <is>
-          <t>L24.C02</t>
+          <t>L24.C01</t>
         </is>
       </c>
       <c r="B277" s="3" t="inlineStr">
@@ -19226,7 +19226,7 @@
       </c>
       <c r="C277" s="3" t="inlineStr">
         <is>
-          <t>Le seuil juste est plus strict que le seuil sûr</t>
+          <t>Ce que ce livre doit établir</t>
         </is>
       </c>
       <c r="D277" s="3" t="inlineStr">
@@ -19246,7 +19246,7 @@
       </c>
       <c r="G277" s="3" t="inlineStr">
         <is>
-          <t>hybride</t>
+          <t>descriptif</t>
         </is>
       </c>
       <c r="H277" s="3" t="inlineStr">
@@ -19263,24 +19263,24 @@
       </c>
       <c r="L277" s="3" t="inlineStr">
         <is>
-          <t>limites_planetaires, plafond_ecologique, plancher_social, dette_ecologique, essentiel_insolvable, qualification_regenerative</t>
+          <t>limites_planetaires, plafond_ecologique, entropie, decouplage, degeneratif, qualification_regenerative, essentiel_insolvable</t>
         </is>
       </c>
       <c r="M277" s="3" t="inlineStr">
         <is>
-          <t>L1.C15, L11.C13, L12.C01, L18.C01, L24.C01, L25.C01</t>
+          <t>L1.C15, L5.C08, L11.C13, L18.C01, L18.C04, L22.C04, L26.C01</t>
         </is>
       </c>
       <c r="N277" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-24-conditions-materielles-de-la-vie/c02-le-seuil-juste-est-plus-strict-que-le-seuil-sur.md</t>
+          <t>corpus/livre-24-conditions-materielles-de-la-vie/c01-ce-que-ce-livre-doit-etablir.md</t>
         </is>
       </c>
     </row>
     <row r="278">
       <c r="A278" s="2" t="inlineStr">
         <is>
-          <t>L24.C03</t>
+          <t>L24.C02</t>
         </is>
       </c>
       <c r="B278" s="3" t="inlineStr">
@@ -19290,7 +19290,7 @@
       </c>
       <c r="C278" s="3" t="inlineStr">
         <is>
-          <t>La matière, et le levier commun que les neuf dimensions n'avaient pas</t>
+          <t>Le seuil juste est plus strict que le seuil sûr</t>
         </is>
       </c>
       <c r="D278" s="3" t="inlineStr">
@@ -19327,24 +19327,24 @@
       </c>
       <c r="L278" s="3" t="inlineStr">
         <is>
-          <t>limites_planetaires, decouplage, effet_rebond, sobriete, entropie, plafond_ecologique, externalisation, degeneratif</t>
+          <t>limites_planetaires, plafond_ecologique, plancher_social, dette_ecologique, essentiel_insolvable, qualification_regenerative</t>
         </is>
       </c>
       <c r="M278" s="3" t="inlineStr">
         <is>
-          <t>L1.C15, L11.C13, L17.C01, L18.C04, L24.C01, L24.C02, L26.C01</t>
+          <t>L1.C15, L11.C13, L12.C01, L18.C01, L24.C01, L25.C01</t>
         </is>
       </c>
       <c r="N278" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-24-conditions-materielles-de-la-vie/c03-la-matiere-et-le-levier-commun.md</t>
+          <t>corpus/livre-24-conditions-materielles-de-la-vie/c02-le-seuil-juste-est-plus-strict-que-le-seuil-sur.md</t>
         </is>
       </c>
     </row>
     <row r="279">
       <c r="A279" s="2" t="inlineStr">
         <is>
-          <t>L24.C04</t>
+          <t>L24.C03</t>
         </is>
       </c>
       <c r="B279" s="3" t="inlineStr">
@@ -19354,7 +19354,7 @@
       </c>
       <c r="C279" s="3" t="inlineStr">
         <is>
-          <t>Un budget mondial n'est pas partageable</t>
+          <t>La matière, et le levier commun que les neuf dimensions n'avaient pas</t>
         </is>
       </c>
       <c r="D279" s="3" t="inlineStr">
@@ -19391,24 +19391,24 @@
       </c>
       <c r="L279" s="3" t="inlineStr">
         <is>
-          <t>limites_planetaires, plafond_ecologique, communs, qualification_regenerative, externalisation, polycentricite</t>
+          <t>limites_planetaires, decouplage, effet_rebond, sobriete, entropie, plafond_ecologique, externalisation, degeneratif</t>
         </is>
       </c>
       <c r="M279" s="3" t="inlineStr">
         <is>
-          <t>L11.C13, L11.C24, L22.C04, L24.C01, L24.C02, L24.C03, L25.C05</t>
+          <t>L1.C15, L11.C13, L17.C01, L18.C04, L24.C01, L24.C02, L26.C01</t>
         </is>
       </c>
       <c r="N279" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-24-conditions-materielles-de-la-vie/c04-un-budget-mondial-n-est-pas-partageable.md</t>
+          <t>corpus/livre-24-conditions-materielles-de-la-vie/c03-la-matiere-et-le-levier-commun.md</t>
         </is>
       </c>
     </row>
     <row r="280">
       <c r="A280" s="2" t="inlineStr">
         <is>
-          <t>L24.C05</t>
+          <t>L24.C04</t>
         </is>
       </c>
       <c r="B280" s="3" t="inlineStr">
@@ -19418,7 +19418,7 @@
       </c>
       <c r="C280" s="3" t="inlineStr">
         <is>
-          <t>Portée de la tranche</t>
+          <t>Un budget mondial n'est pas partageable</t>
         </is>
       </c>
       <c r="D280" s="3" t="inlineStr">
@@ -19438,51 +19438,51 @@
       </c>
       <c r="G280" s="3" t="inlineStr">
         <is>
-          <t>descriptif</t>
+          <t>hybride</t>
         </is>
       </c>
       <c r="H280" s="3" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="I280" s="3" t="inlineStr"/>
       <c r="J280" s="3" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K280" s="3" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L280" s="3" t="inlineStr">
         <is>
-          <t>limites_planetaires, plafond_ecologique, plancher_social, decouplage, qualification_regenerative, entropie</t>
+          <t>limites_planetaires, plafond_ecologique, communs, qualification_regenerative, externalisation, polycentricite</t>
         </is>
       </c>
       <c r="M280" s="3" t="inlineStr">
         <is>
-          <t>L11.C13, L11.C24, L18.C01, L22.C04, L24.C01, L24.C02, L24.C03, L24.C04, L25.C05, L26.C01, L26.C02, L17.C05</t>
+          <t>L11.C13, L11.C24, L22.C04, L24.C01, L24.C02, L24.C03, L25.C05</t>
         </is>
       </c>
       <c r="N280" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-24-conditions-materielles-de-la-vie/c05-portee-de-la-tranche.md</t>
+          <t>corpus/livre-24-conditions-materielles-de-la-vie/c04-un-budget-mondial-n-est-pas-partageable.md</t>
         </is>
       </c>
     </row>
     <row r="281">
       <c r="A281" s="2" t="inlineStr">
         <is>
-          <t>L25.C01</t>
+          <t>L24.C05</t>
         </is>
       </c>
       <c r="B281" s="3" t="inlineStr">
         <is>
-          <t>L25</t>
+          <t>L24</t>
         </is>
       </c>
       <c r="C281" s="3" t="inlineStr">
         <is>
-          <t>Ce que ce livre doit établir</t>
+          <t>Portée de la tranche</t>
         </is>
       </c>
       <c r="D281" s="3" t="inlineStr">
@@ -19507,36 +19507,36 @@
       </c>
       <c r="H281" s="3" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="I281" s="3" t="inlineStr"/>
       <c r="J281" s="3" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K281" s="3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L281" s="3" t="inlineStr">
         <is>
-          <t>plancher_social, plafond_ecologique, essentiel_insolvable, dette_ecologique, communs, solvabilite_anticipee</t>
+          <t>limites_planetaires, plafond_ecologique, plancher_social, decouplage, qualification_regenerative, entropie</t>
         </is>
       </c>
       <c r="M281" s="3" t="inlineStr">
         <is>
-          <t>L1.C15, L11.C09, L11.C18, L12.C01, L24.C01, L24.C02, L24.C03</t>
+          <t>L11.C13, L11.C24, L18.C01, L22.C04, L24.C01, L24.C02, L24.C03, L24.C04, L25.C05, L26.C01, L26.C02, L17.C05</t>
         </is>
       </c>
       <c r="N281" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-25-repartition-et-justice-sociale/c01-ce-que-ce-livre-doit-etablir.md</t>
+          <t>corpus/livre-24-conditions-materielles-de-la-vie/c05-portee-de-la-tranche.md</t>
         </is>
       </c>
     </row>
     <row r="282">
       <c r="A282" s="2" t="inlineStr">
         <is>
-          <t>L25.C02</t>
+          <t>L25.C01</t>
         </is>
       </c>
       <c r="B282" s="3" t="inlineStr">
@@ -19546,7 +19546,7 @@
       </c>
       <c r="C282" s="3" t="inlineStr">
         <is>
-          <t>Le noyau dur, et la charge de la preuve renversée</t>
+          <t>Ce que ce livre doit établir</t>
         </is>
       </c>
       <c r="D282" s="3" t="inlineStr">
@@ -19566,12 +19566,12 @@
       </c>
       <c r="G282" s="3" t="inlineStr">
         <is>
-          <t>hybride</t>
+          <t>descriptif</t>
         </is>
       </c>
       <c r="H282" s="3" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="I282" s="3" t="inlineStr"/>
@@ -19579,28 +19579,28 @@
         <v>4</v>
       </c>
       <c r="K282" s="3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L282" s="3" t="inlineStr">
         <is>
-          <t>plancher_social, essentiel_insolvable, plafond_ecologique, solvabilite_anticipee, regle_contre_discretion</t>
+          <t>plancher_social, plafond_ecologique, essentiel_insolvable, dette_ecologique, communs, solvabilite_anticipee</t>
         </is>
       </c>
       <c r="M282" s="3" t="inlineStr">
         <is>
-          <t>L1.C15, L11.C09, L11.C18, L22.C02, L22.C04, L24.C02, L25.C01</t>
+          <t>L1.C15, L11.C09, L11.C18, L12.C01, L24.C01, L24.C02, L24.C03</t>
         </is>
       </c>
       <c r="N282" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-25-repartition-et-justice-sociale/c02-le-noyau-dur-et-la-charge-de-la-preuve.md</t>
+          <t>corpus/livre-25-repartition-et-justice-sociale/c01-ce-que-ce-livre-doit-etablir.md</t>
         </is>
       </c>
     </row>
     <row r="283">
       <c r="A283" s="2" t="inlineStr">
         <is>
-          <t>L25.C03</t>
+          <t>L25.C02</t>
         </is>
       </c>
       <c r="B283" s="3" t="inlineStr">
@@ -19610,7 +19610,7 @@
       </c>
       <c r="C283" s="3" t="inlineStr">
         <is>
-          <t>Ce que le droit oblige à donner, et ce qu'il refuse de réparer</t>
+          <t>Le noyau dur, et la charge de la preuve renversée</t>
         </is>
       </c>
       <c r="D283" s="3" t="inlineStr">
@@ -19640,31 +19640,31 @@
       </c>
       <c r="I283" s="3" t="inlineStr"/>
       <c r="J283" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K283" s="3" t="n">
         <v>4</v>
       </c>
       <c r="L283" s="3" t="inlineStr">
         <is>
-          <t>dette_ecologique, plancher_social, creation_monetaire, reflux_collectif, essentiel_insolvable, solvabilite_anticipee</t>
+          <t>plancher_social, essentiel_insolvable, plafond_ecologique, solvabilite_anticipee, regle_contre_discretion</t>
         </is>
       </c>
       <c r="M283" s="3" t="inlineStr">
         <is>
-          <t>L1.C20, L11.C01, L20.C01, L24.C02, L25.C01, L25.C02</t>
+          <t>L1.C15, L11.C09, L11.C18, L22.C02, L22.C04, L24.C02, L25.C01</t>
         </is>
       </c>
       <c r="N283" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-25-repartition-et-justice-sociale/c03-ce-que-le-droit-oblige-a-donner.md</t>
+          <t>corpus/livre-25-repartition-et-justice-sociale/c02-le-noyau-dur-et-la-charge-de-la-preuve.md</t>
         </is>
       </c>
     </row>
     <row r="284">
       <c r="A284" s="2" t="inlineStr">
         <is>
-          <t>L25.C04</t>
+          <t>L25.C03</t>
         </is>
       </c>
       <c r="B284" s="3" t="inlineStr">
@@ -19674,7 +19674,7 @@
       </c>
       <c r="C284" s="3" t="inlineStr">
         <is>
-          <t>A34 en droit positif, et le critère que le corpus n'avait pas</t>
+          <t>Ce que le droit oblige à donner, et ce qu'il refuse de réparer</t>
         </is>
       </c>
       <c r="D284" s="3" t="inlineStr">
@@ -19704,31 +19704,31 @@
       </c>
       <c r="I284" s="3" t="inlineStr"/>
       <c r="J284" s="3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K284" s="3" t="n">
         <v>4</v>
       </c>
       <c r="L284" s="3" t="inlineStr">
         <is>
-          <t>plancher_social, bareme, essentiel_insolvable, sobriete, affectation_des_instruments, reflux_transactionnel</t>
+          <t>dette_ecologique, plancher_social, creation_monetaire, reflux_collectif, essentiel_insolvable, solvabilite_anticipee</t>
         </is>
       </c>
       <c r="M284" s="3" t="inlineStr">
         <is>
-          <t>L1.C15, L11.C09, L11.C18, L11.C21, L22.C02, L24.C03, L25.C01, L25.C02</t>
+          <t>L1.C20, L11.C01, L20.C01, L24.C02, L25.C01, L25.C02</t>
         </is>
       </c>
       <c r="N284" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-25-repartition-et-justice-sociale/c04-a34-en-droit-positif.md</t>
+          <t>corpus/livre-25-repartition-et-justice-sociale/c03-ce-que-le-droit-oblige-a-donner.md</t>
         </is>
       </c>
     </row>
     <row r="285">
       <c r="A285" s="2" t="inlineStr">
         <is>
-          <t>L25.C05</t>
+          <t>L25.C04</t>
         </is>
       </c>
       <c r="B285" s="3" t="inlineStr">
@@ -19738,7 +19738,7 @@
       </c>
       <c r="C285" s="3" t="inlineStr">
         <is>
-          <t>Le droit différencie sans calculer</t>
+          <t>A34 en droit positif, et le critère que le corpus n'avait pas</t>
         </is>
       </c>
       <c r="D285" s="3" t="inlineStr">
@@ -19768,31 +19768,31 @@
       </c>
       <c r="I285" s="3" t="inlineStr"/>
       <c r="J285" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K285" s="3" t="n">
         <v>4</v>
       </c>
       <c r="L285" s="3" t="inlineStr">
         <is>
-          <t>dette_ecologique, plancher_social, plafond_ecologique, bareme, indicateur_de_progres, polycentricite</t>
+          <t>plancher_social, bareme, essentiel_insolvable, sobriete, affectation_des_instruments, reflux_transactionnel</t>
         </is>
       </c>
       <c r="M285" s="3" t="inlineStr">
         <is>
-          <t>L11.C13, L22.C04, L22.C06, L24.C01, L24.C02, L25.C01, L25.C02, L25.C03, L25.C04</t>
+          <t>L1.C15, L11.C09, L11.C18, L11.C21, L22.C02, L24.C03, L25.C01, L25.C02</t>
         </is>
       </c>
       <c r="N285" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-25-repartition-et-justice-sociale/c05-le-droit-differencie-sans-calculer.md</t>
+          <t>corpus/livre-25-repartition-et-justice-sociale/c04-a34-en-droit-positif.md</t>
         </is>
       </c>
     </row>
     <row r="286">
       <c r="A286" s="2" t="inlineStr">
         <is>
-          <t>L25.C06</t>
+          <t>L25.C05</t>
         </is>
       </c>
       <c r="B286" s="3" t="inlineStr">
@@ -19802,7 +19802,7 @@
       </c>
       <c r="C286" s="3" t="inlineStr">
         <is>
-          <t>Portée de la tranche</t>
+          <t>Le droit différencie sans calculer</t>
         </is>
       </c>
       <c r="D286" s="3" t="inlineStr">
@@ -19822,7 +19822,7 @@
       </c>
       <c r="G286" s="3" t="inlineStr">
         <is>
-          <t>descriptif</t>
+          <t>hybride</t>
         </is>
       </c>
       <c r="H286" s="3" t="inlineStr">
@@ -19832,41 +19832,41 @@
       </c>
       <c r="I286" s="3" t="inlineStr"/>
       <c r="J286" s="3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K286" s="3" t="n">
         <v>4</v>
       </c>
       <c r="L286" s="3" t="inlineStr">
         <is>
-          <t>plancher_social, plafond_ecologique, dette_ecologique, essentiel_insolvable, bareme</t>
+          <t>dette_ecologique, plancher_social, plafond_ecologique, bareme, indicateur_de_progres, polycentricite</t>
         </is>
       </c>
       <c r="M286" s="3" t="inlineStr">
         <is>
-          <t>L5.C09, L11.C09, L11.C18, L24.C02, L25.C01, L25.C02, L25.C03, L25.C04, L25.C05</t>
+          <t>L11.C13, L22.C04, L22.C06, L24.C01, L24.C02, L25.C01, L25.C02, L25.C03, L25.C04</t>
         </is>
       </c>
       <c r="N286" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-25-repartition-et-justice-sociale/c06-portee-de-la-tranche.md</t>
+          <t>corpus/livre-25-repartition-et-justice-sociale/c05-le-droit-differencie-sans-calculer.md</t>
         </is>
       </c>
     </row>
     <row r="287">
       <c r="A287" s="2" t="inlineStr">
         <is>
-          <t>L26.C01</t>
+          <t>L25.C06</t>
         </is>
       </c>
       <c r="B287" s="3" t="inlineStr">
         <is>
-          <t>L26</t>
+          <t>L25</t>
         </is>
       </c>
       <c r="C287" s="3" t="inlineStr">
         <is>
-          <t>Ce que ce livre doit établir</t>
+          <t>Portée de la tranche</t>
         </is>
       </c>
       <c r="D287" s="3" t="inlineStr">
@@ -19886,41 +19886,41 @@
       </c>
       <c r="G287" s="3" t="inlineStr">
         <is>
-          <t>hybride</t>
+          <t>descriptif</t>
         </is>
       </c>
       <c r="H287" s="3" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="I287" s="3" t="inlineStr"/>
       <c r="J287" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K287" s="3" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="L287" s="3" t="inlineStr">
         <is>
-          <t>entropie, decouplage, effet_rebond, limites_planetaires, sobriete, degeneratif, qualification_regenerative</t>
+          <t>plancher_social, plafond_ecologique, dette_ecologique, essentiel_insolvable, bareme</t>
         </is>
       </c>
       <c r="M287" s="3" t="inlineStr">
         <is>
-          <t>L1.C03, L1.C15, L1.C17, L8.C13, L8.C34, L11.C13, L18.C04, L24.C03, L24.C05, L17.C02, L26.C10</t>
+          <t>L5.C09, L11.C09, L11.C18, L24.C02, L25.C01, L25.C02, L25.C03, L25.C04, L25.C05</t>
         </is>
       </c>
       <c r="N287" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-26-thermodynamique-et-processus-economique/c01-ce-que-ce-livre-doit-etablir.md</t>
+          <t>corpus/livre-25-repartition-et-justice-sociale/c06-portee-de-la-tranche.md</t>
         </is>
       </c>
     </row>
     <row r="288">
       <c r="A288" s="2" t="inlineStr">
         <is>
-          <t>L26.C02</t>
+          <t>L26.C01</t>
         </is>
       </c>
       <c r="B288" s="3" t="inlineStr">
@@ -19930,7 +19930,7 @@
       </c>
       <c r="C288" s="3" t="inlineStr">
         <is>
-          <t>Le stock n'existe pas sous la forme demandée</t>
+          <t>Ce que ce livre doit établir</t>
         </is>
       </c>
       <c r="D288" s="3" t="inlineStr">
@@ -19960,31 +19960,31 @@
       </c>
       <c r="I288" s="3" t="inlineStr"/>
       <c r="J288" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K288" s="3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L288" s="3" t="inlineStr">
         <is>
-          <t>entropie, bareme, limites_planetaires, decouplage, sobriete, fausse_richesse</t>
+          <t>entropie, decouplage, effet_rebond, limites_planetaires, sobriete, degeneratif, qualification_regenerative</t>
         </is>
       </c>
       <c r="M288" s="3" t="inlineStr">
         <is>
-          <t>L1.C15, L11.C13, L11.C24, L18.C04, L22.C04, L24.C03, L24.C05, L26.C01, L17.C02</t>
+          <t>L1.C03, L1.C15, L1.C17, L8.C13, L8.C34, L11.C13, L18.C04, L24.C03, L24.C05, L17.C02, L26.C10</t>
         </is>
       </c>
       <c r="N288" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-26-thermodynamique-et-processus-economique/c02-le-stock-n-existe-pas-sous-la-forme-demandee.md</t>
+          <t>corpus/livre-26-thermodynamique-et-processus-economique/c01-ce-que-ce-livre-doit-etablir.md</t>
         </is>
       </c>
     </row>
     <row r="289">
       <c r="A289" s="2" t="inlineStr">
         <is>
-          <t>L26.C03</t>
+          <t>L26.C02</t>
         </is>
       </c>
       <c r="B289" s="3" t="inlineStr">
@@ -19994,7 +19994,7 @@
       </c>
       <c r="C289" s="3" t="inlineStr">
         <is>
-          <t>La frontière décide du chiffre</t>
+          <t>Le stock n'existe pas sous la forme demandée</t>
         </is>
       </c>
       <c r="D289" s="3" t="inlineStr">
@@ -20024,31 +20024,31 @@
       </c>
       <c r="I289" s="3" t="inlineStr"/>
       <c r="J289" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K289" s="3" t="n">
         <v>5</v>
       </c>
       <c r="L289" s="3" t="inlineStr">
         <is>
-          <t>entropie, decouplage, sobriete, limites_planetaires, robustesse, bareme</t>
+          <t>entropie, bareme, limites_planetaires, decouplage, sobriete, fausse_richesse</t>
         </is>
       </c>
       <c r="M289" s="3" t="inlineStr">
         <is>
-          <t>L11.C10, L11.C13, L11.C24, L18.C04, L18.C09, L24.C03, L24.C04, L26.C01, L26.C02, L26.C08</t>
+          <t>L1.C15, L11.C13, L11.C24, L18.C04, L22.C04, L24.C03, L24.C05, L26.C01, L17.C02</t>
         </is>
       </c>
       <c r="N289" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-26-thermodynamique-et-processus-economique/c03-la-frontiere-decide-du-chiffre.md</t>
+          <t>corpus/livre-26-thermodynamique-et-processus-economique/c02-le-stock-n-existe-pas-sous-la-forme-demandee.md</t>
         </is>
       </c>
     </row>
     <row r="290">
       <c r="A290" s="2" t="inlineStr">
         <is>
-          <t>L26.C04</t>
+          <t>L26.C03</t>
         </is>
       </c>
       <c r="B290" s="3" t="inlineStr">
@@ -20058,7 +20058,7 @@
       </c>
       <c r="C290" s="3" t="inlineStr">
         <is>
-          <t>L'effet rebond, et ce que le dispositif en hérite sans être une politique d'efficacité</t>
+          <t>La frontière décide du chiffre</t>
         </is>
       </c>
       <c r="D290" s="3" t="inlineStr">
@@ -20088,31 +20088,31 @@
       </c>
       <c r="I290" s="3" t="inlineStr"/>
       <c r="J290" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K290" s="3" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L290" s="3" t="inlineStr">
         <is>
-          <t>effet_rebond, jevons_monetaire, decouplage, sobriete, entropie, reflux_transactionnel</t>
+          <t>entropie, decouplage, sobriete, limites_planetaires, robustesse, bareme</t>
         </is>
       </c>
       <c r="M290" s="3" t="inlineStr">
         <is>
-          <t>L1.C03, L1.C12, L1.C17, L11.C10, L13.C01, L18.C04, L22.C02, L24.C03, L26.C01, L26.C03, L26.C09</t>
+          <t>L11.C10, L11.C13, L11.C24, L18.C04, L18.C09, L24.C03, L24.C04, L26.C01, L26.C02, L26.C08</t>
         </is>
       </c>
       <c r="N290" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-26-thermodynamique-et-processus-economique/c04-l-effet-rebond-et-ce-que-le-dispositif-en-herite.md</t>
+          <t>corpus/livre-26-thermodynamique-et-processus-economique/c03-la-frontiere-decide-du-chiffre.md</t>
         </is>
       </c>
     </row>
     <row r="291">
       <c r="A291" s="2" t="inlineStr">
         <is>
-          <t>L26.C05</t>
+          <t>L26.C04</t>
         </is>
       </c>
       <c r="B291" s="3" t="inlineStr">
@@ -20122,7 +20122,7 @@
       </c>
       <c r="C291" s="3" t="inlineStr">
         <is>
-          <t>L'addition n'est pas la substitution</t>
+          <t>L'effet rebond, et ce que le dispositif en hérite sans être une politique d'efficacité</t>
         </is>
       </c>
       <c r="D291" s="3" t="inlineStr">
@@ -20155,28 +20155,28 @@
         <v>1</v>
       </c>
       <c r="K291" s="3" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="L291" s="3" t="inlineStr">
         <is>
-          <t>decouplage, effet_rebond, sobriete, degeneratif, affectation_des_instruments</t>
+          <t>effet_rebond, jevons_monetaire, decouplage, sobriete, entropie, reflux_transactionnel</t>
         </is>
       </c>
       <c r="M291" s="3" t="inlineStr">
         <is>
-          <t>L1.C12, L11.C10, L11.C13, L18.C04, L18.C09, L22.C02, L24.C03, L26.C01, L26.C03, L26.C04</t>
+          <t>L1.C03, L1.C12, L1.C17, L11.C10, L13.C01, L18.C04, L22.C02, L24.C03, L26.C01, L26.C03, L26.C09</t>
         </is>
       </c>
       <c r="N291" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-26-thermodynamique-et-processus-economique/c05-l-addition-n-est-pas-la-substitution.md</t>
+          <t>corpus/livre-26-thermodynamique-et-processus-economique/c04-l-effet-rebond-et-ce-que-le-dispositif-en-herite.md</t>
         </is>
       </c>
     </row>
     <row r="292">
       <c r="A292" s="2" t="inlineStr">
         <is>
-          <t>L26.C06</t>
+          <t>L26.C05</t>
         </is>
       </c>
       <c r="B292" s="3" t="inlineStr">
@@ -20186,7 +20186,7 @@
       </c>
       <c r="C292" s="3" t="inlineStr">
         <is>
-          <t>Portée de la tranche</t>
+          <t>L'addition n'est pas la substitution</t>
         </is>
       </c>
       <c r="D292" s="3" t="inlineStr">
@@ -20206,7 +20206,7 @@
       </c>
       <c r="G292" s="3" t="inlineStr">
         <is>
-          <t>descriptif</t>
+          <t>hybride</t>
         </is>
       </c>
       <c r="H292" s="3" t="inlineStr">
@@ -20219,28 +20219,28 @@
         <v>1</v>
       </c>
       <c r="K292" s="3" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L292" s="3" t="inlineStr">
         <is>
-          <t>entropie, decouplage, effet_rebond, limites_planetaires, sobriete, affectation_des_instruments</t>
+          <t>decouplage, effet_rebond, sobriete, degeneratif, affectation_des_instruments</t>
         </is>
       </c>
       <c r="M292" s="3" t="inlineStr">
         <is>
-          <t>L1.C03, L1.C17, L8.C34, L11.C10, L11.C13, L11.C24, L18.C04, L18.C09, L22.C02, L24.C05, L26.C01, L26.C02, L26.C03, L26.C04, L26.C05, L26.C07</t>
+          <t>L1.C12, L11.C10, L11.C13, L18.C04, L18.C09, L22.C02, L24.C03, L26.C01, L26.C03, L26.C04</t>
         </is>
       </c>
       <c r="N292" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-26-thermodynamique-et-processus-economique/c06-portee-de-la-tranche.md</t>
+          <t>corpus/livre-26-thermodynamique-et-processus-economique/c05-l-addition-n-est-pas-la-substitution.md</t>
         </is>
       </c>
     </row>
     <row r="293">
       <c r="A293" s="2" t="inlineStr">
         <is>
-          <t>L26.C07</t>
+          <t>L26.C06</t>
         </is>
       </c>
       <c r="B293" s="3" t="inlineStr">
@@ -20250,7 +20250,7 @@
       </c>
       <c r="C293" s="3" t="inlineStr">
         <is>
-          <t>Le fondateur ne propose aucun instrument monétaire</t>
+          <t>Portée de la tranche</t>
         </is>
       </c>
       <c r="D293" s="3" t="inlineStr">
@@ -20270,7 +20270,7 @@
       </c>
       <c r="G293" s="3" t="inlineStr">
         <is>
-          <t>hybride</t>
+          <t>descriptif</t>
         </is>
       </c>
       <c r="H293" s="3" t="inlineStr">
@@ -20280,31 +20280,31 @@
       </c>
       <c r="I293" s="3" t="inlineStr"/>
       <c r="J293" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K293" s="3" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="L293" s="3" t="inlineStr">
         <is>
-          <t>entropie, sobriete, affectation_des_instruments, qualification_regenerative</t>
+          <t>entropie, decouplage, effet_rebond, limites_planetaires, sobriete, affectation_des_instruments</t>
         </is>
       </c>
       <c r="M293" s="3" t="inlineStr">
         <is>
-          <t>L1.C03, L1.C17, L8.C34, L11.C13, L16.C01, L16.C05, L17.C02, L17.C03, L26.C01, L26.C03, L26.C06</t>
+          <t>L1.C03, L1.C17, L8.C34, L11.C10, L11.C13, L11.C24, L18.C04, L18.C09, L22.C02, L24.C05, L26.C01, L26.C02, L26.C03, L26.C04, L26.C05, L26.C07</t>
         </is>
       </c>
       <c r="N293" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-26-thermodynamique-et-processus-economique/c07-le-fondateur-ne-propose-aucun-instrument-monetaire.md</t>
+          <t>corpus/livre-26-thermodynamique-et-processus-economique/c06-portee-de-la-tranche.md</t>
         </is>
       </c>
     </row>
     <row r="294">
       <c r="A294" s="2" t="inlineStr">
         <is>
-          <t>L26.C08</t>
+          <t>L26.C07</t>
         </is>
       </c>
       <c r="B294" s="3" t="inlineStr">
@@ -20314,7 +20314,7 @@
       </c>
       <c r="C294" s="3" t="inlineStr">
         <is>
-          <t>Même un puits gratuit ne donne pas dix</t>
+          <t>Le fondateur ne propose aucun instrument monétaire</t>
         </is>
       </c>
       <c r="D294" s="3" t="inlineStr">
@@ -20351,24 +20351,24 @@
       </c>
       <c r="L294" s="3" t="inlineStr">
         <is>
-          <t>bareme, qualification_regenerative, decouplage</t>
+          <t>entropie, sobriete, affectation_des_instruments, qualification_regenerative</t>
         </is>
       </c>
       <c r="M294" s="3" t="inlineStr">
         <is>
-          <t>L1.C17, L8.C37, L11.C13, L17.C01, L24.C05, L26.C01, L26.C03, L26.C06, L26.C07</t>
+          <t>L1.C03, L1.C17, L8.C34, L11.C13, L16.C01, L16.C05, L17.C02, L17.C03, L26.C01, L26.C03, L26.C06</t>
         </is>
       </c>
       <c r="N294" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-26-thermodynamique-et-processus-economique/c08-meme-un-puits-gratuit-ne-donne-pas-dix.md</t>
+          <t>corpus/livre-26-thermodynamique-et-processus-economique/c07-le-fondateur-ne-propose-aucun-instrument-monetaire.md</t>
         </is>
       </c>
     </row>
     <row r="295">
       <c r="A295" s="2" t="inlineStr">
         <is>
-          <t>L26.C09</t>
+          <t>L26.C08</t>
         </is>
       </c>
       <c r="B295" s="3" t="inlineStr">
@@ -20378,7 +20378,7 @@
       </c>
       <c r="C295" s="3" t="inlineStr">
         <is>
-          <t>La méthode décide du chiffre</t>
+          <t>Même un puits gratuit ne donne pas dix</t>
         </is>
       </c>
       <c r="D295" s="3" t="inlineStr">
@@ -20415,24 +20415,24 @@
       </c>
       <c r="L295" s="3" t="inlineStr">
         <is>
-          <t>effet_rebond, jevons_monetaire, decouplage, bareme</t>
+          <t>bareme, qualification_regenerative, decouplage</t>
         </is>
       </c>
       <c r="M295" s="3" t="inlineStr">
         <is>
-          <t>L1.C03, L11.C13, L17.C02, L24.C03, L26.C03, L26.C04, L26.C06, L26.C08</t>
+          <t>L1.C17, L8.C37, L11.C13, L17.C01, L24.C05, L26.C01, L26.C03, L26.C06, L26.C07</t>
         </is>
       </c>
       <c r="N295" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-26-thermodynamique-et-processus-economique/c09-la-methode-decide-du-chiffre.md</t>
+          <t>corpus/livre-26-thermodynamique-et-processus-economique/c08-meme-un-puits-gratuit-ne-donne-pas-dix.md</t>
         </is>
       </c>
     </row>
     <row r="296">
       <c r="A296" s="2" t="inlineStr">
         <is>
-          <t>L26.C10</t>
+          <t>L26.C09</t>
         </is>
       </c>
       <c r="B296" s="3" t="inlineStr">
@@ -20442,7 +20442,7 @@
       </c>
       <c r="C296" s="3" t="inlineStr">
         <is>
-          <t>La financiarisation produit un découplage apparent</t>
+          <t>La méthode décide du chiffre</t>
         </is>
       </c>
       <c r="D296" s="3" t="inlineStr">
@@ -20475,26 +20475,90 @@
         <v>2</v>
       </c>
       <c r="K296" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="L296" s="3" t="inlineStr">
+        <is>
+          <t>effet_rebond, jevons_monetaire, decouplage, bareme</t>
+        </is>
+      </c>
+      <c r="M296" s="3" t="inlineStr">
+        <is>
+          <t>L1.C03, L11.C13, L17.C02, L24.C03, L26.C03, L26.C04, L26.C06, L26.C08</t>
+        </is>
+      </c>
+      <c r="N296" s="3" t="inlineStr">
+        <is>
+          <t>corpus/livre-26-thermodynamique-et-processus-economique/c09-la-methode-decide-du-chiffre.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" s="2" t="inlineStr">
+        <is>
+          <t>L26.C10</t>
+        </is>
+      </c>
+      <c r="B297" s="3" t="inlineStr">
+        <is>
+          <t>L26</t>
+        </is>
+      </c>
+      <c r="C297" s="3" t="inlineStr">
+        <is>
+          <t>La financiarisation produit un découplage apparent</t>
+        </is>
+      </c>
+      <c r="D297" s="3" t="inlineStr">
+        <is>
+          <t>brouillon</t>
+        </is>
+      </c>
+      <c r="E297" s="3" t="inlineStr">
+        <is>
+          <t>preparatoire</t>
+        </is>
+      </c>
+      <c r="F297" s="3" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="G297" s="3" t="inlineStr">
+        <is>
+          <t>hybride</t>
+        </is>
+      </c>
+      <c r="H297" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="I297" s="3" t="inlineStr"/>
+      <c r="J297" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="K297" s="3" t="n">
         <v>5</v>
       </c>
-      <c r="L296" s="3" t="inlineStr">
+      <c r="L297" s="3" t="inlineStr">
         <is>
           <t>decouplage, fausse_richesse, jevons_monetaire, indicateur_de_progres</t>
         </is>
       </c>
-      <c r="M296" s="3" t="inlineStr">
+      <c r="M297" s="3" t="inlineStr">
         <is>
           <t>L1.C03, L11.C13, L17.C01, L17.C05, L24.C03, L26.C01, L26.C03, L26.C06, L26.C08, L26.C09, L18.C10</t>
         </is>
       </c>
-      <c r="N296" s="3" t="inlineStr">
+      <c r="N297" s="3" t="inlineStr">
         <is>
           <t>corpus/livre-26-thermodynamique-et-processus-economique/c10-la-financiarisation-produit-un-decouplage-apparent.md</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:N296"/>
+  <autoFilter ref="A1:N297"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -20573,7 +20637,7 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>295</v>
+        <v>296</v>
       </c>
     </row>
     <row r="7">
@@ -20593,7 +20657,7 @@
         </is>
       </c>
       <c r="B8" s="3" t="n">
-        <v>292</v>
+        <v>293</v>
       </c>
     </row>
     <row r="9">
@@ -20603,7 +20667,7 @@
         </is>
       </c>
       <c r="B9" s="3" t="n">
-        <v>286</v>
+        <v>287</v>
       </c>
     </row>
     <row r="10">
@@ -20623,7 +20687,7 @@
         </is>
       </c>
       <c r="B11" s="3" t="n">
-        <v>1453</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="12">
@@ -20633,7 +20697,7 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>1109</v>
+        <v>1110</v>
       </c>
     </row>
     <row r="13">
@@ -20727,7 +20791,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C323"/>
+  <dimension ref="A1:C324"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -24675,7 +24739,7 @@
       </c>
       <c r="C232" s="6" t="inlineStr">
         <is>
-          <t>en-cours — 10 chapitre(s)</t>
+          <t>en-cours — 11 chapitre(s)</t>
         </is>
       </c>
     </row>
@@ -24850,48 +24914,48 @@
       </c>
     </row>
     <row r="243">
-      <c r="A243" s="6" t="inlineStr">
+      <c r="A243" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    L18.C11</t>
+        </is>
+      </c>
+      <c r="B243" s="3" t="inlineStr">
+        <is>
+          <t>L'adversaire déclare l'hypothèse qu'on lui reproche</t>
+        </is>
+      </c>
+      <c r="C243" s="3" t="inlineStr">
+        <is>
+          <t>brouillon</t>
+        </is>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" s="6" t="inlineStr">
         <is>
           <t>L19</t>
         </is>
       </c>
-      <c r="B243" s="6" t="inlineStr">
+      <c r="B244" s="6" t="inlineStr">
         <is>
           <t>Comptabilité monétaire de l'émission sans dette</t>
         </is>
       </c>
-      <c r="C243" s="6" t="inlineStr">
+      <c r="C244" s="6" t="inlineStr">
         <is>
           <t>en-cours — 7 chapitre(s)</t>
-        </is>
-      </c>
-    </row>
-    <row r="244">
-      <c r="A244" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    L19.C01</t>
-        </is>
-      </c>
-      <c r="B244" s="3" t="inlineStr">
-        <is>
-          <t>Ce que ce livre doit établir</t>
-        </is>
-      </c>
-      <c r="C244" s="3" t="inlineStr">
-        <is>
-          <t>brouillon</t>
         </is>
       </c>
     </row>
     <row r="245">
       <c r="A245" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L19.C02</t>
+          <t xml:space="preserve">    L19.C01</t>
         </is>
       </c>
       <c r="B245" s="3" t="inlineStr">
         <is>
-          <t>Le seul précédent, et le passif lui a été reconnu en 2008</t>
+          <t>Ce que ce livre doit établir</t>
         </is>
       </c>
       <c r="C245" s="3" t="inlineStr">
@@ -24903,12 +24967,12 @@
     <row r="246">
       <c r="A246" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L19.C03</t>
+          <t xml:space="preserve">    L19.C02</t>
         </is>
       </c>
       <c r="B246" s="3" t="inlineStr">
         <is>
-          <t>Le reflux est un intérêt négatif, ou une répudiation — et c'est le moment qui décide</t>
+          <t>Le seul précédent, et le passif lui a été reconnu en 2008</t>
         </is>
       </c>
       <c r="C246" s="3" t="inlineStr">
@@ -24920,12 +24984,12 @@
     <row r="247">
       <c r="A247" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L19.C04</t>
+          <t xml:space="preserve">    L19.C03</t>
         </is>
       </c>
       <c r="B247" s="3" t="inlineStr">
         <is>
-          <t>L'actif transitoire n'existe pas, et le problème change de bilan</t>
+          <t>Le reflux est un intérêt négatif, ou une répudiation — et c'est le moment qui décide</t>
         </is>
       </c>
       <c r="C247" s="3" t="inlineStr">
@@ -24937,12 +25001,12 @@
     <row r="248">
       <c r="A248" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L19.C05</t>
+          <t xml:space="preserve">    L19.C04</t>
         </is>
       </c>
       <c r="B248" s="3" t="inlineStr">
         <is>
-          <t>Un débiteur collectif n'existe pas — sauf comme somme de débiteurs identifiés</t>
+          <t>L'actif transitoire n'existe pas, et le problème change de bilan</t>
         </is>
       </c>
       <c r="C248" s="3" t="inlineStr">
@@ -24954,12 +25018,12 @@
     <row r="249">
       <c r="A249" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L19.C06</t>
+          <t xml:space="preserve">    L19.C05</t>
         </is>
       </c>
       <c r="B249" s="3" t="inlineStr">
         <is>
-          <t>Les fonds propres négatifs, et l'institution qui n'apparaît dans les comptes de personne</t>
+          <t>Un débiteur collectif n'existe pas — sauf comme somme de débiteurs identifiés</t>
         </is>
       </c>
       <c r="C249" s="3" t="inlineStr">
@@ -24971,63 +25035,63 @@
     <row r="250">
       <c r="A250" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">    L19.C06</t>
+        </is>
+      </c>
+      <c r="B250" s="3" t="inlineStr">
+        <is>
+          <t>Les fonds propres négatifs, et l'institution qui n'apparaît dans les comptes de personne</t>
+        </is>
+      </c>
+      <c r="C250" s="3" t="inlineStr">
+        <is>
+          <t>brouillon</t>
+        </is>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">    L19.C07</t>
         </is>
       </c>
-      <c r="B250" s="3" t="inlineStr">
+      <c r="B251" s="3" t="inlineStr">
         <is>
           <t>Portée de la tranche</t>
         </is>
       </c>
-      <c r="C250" s="3" t="inlineStr">
-        <is>
-          <t>brouillon</t>
-        </is>
-      </c>
-    </row>
-    <row r="251">
-      <c r="A251" s="6" t="inlineStr">
+      <c r="C251" s="3" t="inlineStr">
+        <is>
+          <t>brouillon</t>
+        </is>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" s="6" t="inlineStr">
         <is>
           <t>L20</t>
         </is>
       </c>
-      <c r="B251" s="6" t="inlineStr">
+      <c r="B252" s="6" t="inlineStr">
         <is>
           <t>Droit international public, droit monétaire et commercial de la réforme</t>
         </is>
       </c>
-      <c r="C251" s="6" t="inlineStr">
+      <c r="C252" s="6" t="inlineStr">
         <is>
           <t>en-cours — 23 chapitre(s)</t>
-        </is>
-      </c>
-    </row>
-    <row r="252">
-      <c r="A252" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    L20.C01</t>
-        </is>
-      </c>
-      <c r="B252" s="3" t="inlineStr">
-        <is>
-          <t>Ce que ce livre doit établir</t>
-        </is>
-      </c>
-      <c r="C252" s="3" t="inlineStr">
-        <is>
-          <t>brouillon</t>
         </is>
       </c>
     </row>
     <row r="253">
       <c r="A253" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L20.C02</t>
+          <t xml:space="preserve">    L20.C01</t>
         </is>
       </c>
       <c r="B253" s="3" t="inlineStr">
         <is>
-          <t>L'interdiction du financement monétaire</t>
+          <t>Ce que ce livre doit établir</t>
         </is>
       </c>
       <c r="C253" s="3" t="inlineStr">
@@ -25039,12 +25103,12 @@
     <row r="254">
       <c r="A254" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L20.C03</t>
+          <t xml:space="preserve">    L20.C02</t>
         </is>
       </c>
       <c r="B254" s="3" t="inlineStr">
         <is>
-          <t>L'objectif principal et ce qu'il exclut</t>
+          <t>L'interdiction du financement monétaire</t>
         </is>
       </c>
       <c r="C254" s="3" t="inlineStr">
@@ -25056,12 +25120,12 @@
     <row r="255">
       <c r="A255" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L20.C04</t>
+          <t xml:space="preserve">    L20.C03</t>
         </is>
       </c>
       <c r="B255" s="3" t="inlineStr">
         <is>
-          <t>L'indépendance, et à l'égard de qui</t>
+          <t>L'objectif principal et ce qu'il exclut</t>
         </is>
       </c>
       <c r="C255" s="3" t="inlineStr">
@@ -25073,12 +25137,12 @@
     <row r="256">
       <c r="A256" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L20.C05</t>
+          <t xml:space="preserve">    L20.C04</t>
         </is>
       </c>
       <c r="B256" s="3" t="inlineStr">
         <is>
-          <t>Le monopole d'émission et le cours légal</t>
+          <t>L'indépendance, et à l'égard de qui</t>
         </is>
       </c>
       <c r="C256" s="3" t="inlineStr">
@@ -25090,12 +25154,12 @@
     <row r="257">
       <c r="A257" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L20.C06</t>
+          <t xml:space="preserve">    L20.C05</t>
         </is>
       </c>
       <c r="B257" s="3" t="inlineStr">
         <is>
-          <t>Les voies de révision et leur coût</t>
+          <t>Le monopole d'émission et le cours légal</t>
         </is>
       </c>
       <c r="C257" s="3" t="inlineStr">
@@ -25107,12 +25171,12 @@
     <row r="258">
       <c r="A258" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L20.C07</t>
+          <t xml:space="preserve">    L20.C06</t>
         </is>
       </c>
       <c r="B258" s="3" t="inlineStr">
         <is>
-          <t>L'accord monétaire international</t>
+          <t>Les voies de révision et leur coût</t>
         </is>
       </c>
       <c r="C258" s="3" t="inlineStr">
@@ -25124,12 +25188,12 @@
     <row r="259">
       <c r="A259" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L20.C08</t>
+          <t xml:space="preserve">    L20.C07</t>
         </is>
       </c>
       <c r="B259" s="3" t="inlineStr">
         <is>
-          <t>La parité inscrite dans le traité</t>
+          <t>L'accord monétaire international</t>
         </is>
       </c>
       <c r="C259" s="3" t="inlineStr">
@@ -25141,12 +25205,12 @@
     <row r="260">
       <c r="A260" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L20.C09</t>
+          <t xml:space="preserve">    L20.C08</t>
         </is>
       </c>
       <c r="B260" s="3" t="inlineStr">
         <is>
-          <t>L'amendement des statuts du Fonds</t>
+          <t>La parité inscrite dans le traité</t>
         </is>
       </c>
       <c r="C260" s="3" t="inlineStr">
@@ -25158,12 +25222,12 @@
     <row r="261">
       <c r="A261" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L20.C10</t>
+          <t xml:space="preserve">    L20.C09</t>
         </is>
       </c>
       <c r="B261" s="3" t="inlineStr">
         <is>
-          <t>Le vote pondéré et les voix de base</t>
+          <t>L'amendement des statuts du Fonds</t>
         </is>
       </c>
       <c r="C261" s="3" t="inlineStr">
@@ -25175,12 +25239,12 @@
     <row r="262">
       <c r="A262" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L20.C11</t>
+          <t xml:space="preserve">    L20.C10</t>
         </is>
       </c>
       <c r="B262" s="3" t="inlineStr">
         <is>
-          <t>La personnalité juridique et les immunités</t>
+          <t>Le vote pondéré et les voix de base</t>
         </is>
       </c>
       <c r="C262" s="3" t="inlineStr">
@@ -25192,12 +25256,12 @@
     <row r="263">
       <c r="A263" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L20.C12</t>
+          <t xml:space="preserve">    L20.C11</t>
         </is>
       </c>
       <c r="B263" s="3" t="inlineStr">
         <is>
-          <t>Les pouvoirs non délégables</t>
+          <t>La personnalité juridique et les immunités</t>
         </is>
       </c>
       <c r="C263" s="3" t="inlineStr">
@@ -25209,12 +25273,12 @@
     <row r="264">
       <c r="A264" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L20.C13</t>
+          <t xml:space="preserve">    L20.C12</t>
         </is>
       </c>
       <c r="B264" s="3" t="inlineStr">
         <is>
-          <t>L'entrée en vigueur, l'adhésion et le retrait</t>
+          <t>Les pouvoirs non délégables</t>
         </is>
       </c>
       <c r="C264" s="3" t="inlineStr">
@@ -25226,12 +25290,12 @@
     <row r="265">
       <c r="A265" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L20.C14</t>
+          <t xml:space="preserve">    L20.C13</t>
         </is>
       </c>
       <c r="B265" s="3" t="inlineStr">
         <is>
-          <t>Qui interprète le traité</t>
+          <t>L'entrée en vigueur, l'adhésion et le retrait</t>
         </is>
       </c>
       <c r="C265" s="3" t="inlineStr">
@@ -25243,12 +25307,12 @@
     <row r="266">
       <c r="A266" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L20.C15</t>
+          <t xml:space="preserve">    L20.C14</t>
         </is>
       </c>
       <c r="B266" s="3" t="inlineStr">
         <is>
-          <t>Le devoir international des agents</t>
+          <t>Qui interprète le traité</t>
         </is>
       </c>
       <c r="C266" s="3" t="inlineStr">
@@ -25260,12 +25324,12 @@
     <row r="267">
       <c r="A267" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L20.C16</t>
+          <t xml:space="preserve">    L20.C15</t>
         </is>
       </c>
       <c r="B267" s="3" t="inlineStr">
         <is>
-          <t>Le patrimoine commun de l'humanité</t>
+          <t>Le devoir international des agents</t>
         </is>
       </c>
       <c r="C267" s="3" t="inlineStr">
@@ -25277,12 +25341,12 @@
     <row r="268">
       <c r="A268" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L20.C17</t>
+          <t xml:space="preserve">    L20.C16</t>
         </is>
       </c>
       <c r="B268" s="3" t="inlineStr">
         <is>
-          <t>La sanctuarisation, et elle existe</t>
+          <t>Le patrimoine commun de l'humanité</t>
         </is>
       </c>
       <c r="C268" s="3" t="inlineStr">
@@ -25294,12 +25358,12 @@
     <row r="269">
       <c r="A269" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L20.C18</t>
+          <t xml:space="preserve">    L20.C17</t>
         </is>
       </c>
       <c r="B269" s="3" t="inlineStr">
         <is>
-          <t>L'amendement et la dérogation dans l'ordre commercial</t>
+          <t>La sanctuarisation, et elle existe</t>
         </is>
       </c>
       <c r="C269" s="3" t="inlineStr">
@@ -25311,12 +25375,12 @@
     <row r="270">
       <c r="A270" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L20.C19</t>
+          <t xml:space="preserve">    L20.C18</t>
         </is>
       </c>
       <c r="B270" s="3" t="inlineStr">
         <is>
-          <t>Le texte que la conformité invoque</t>
+          <t>L'amendement et la dérogation dans l'ordre commercial</t>
         </is>
       </c>
       <c r="C270" s="3" t="inlineStr">
@@ -25328,12 +25392,12 @@
     <row r="271">
       <c r="A271" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L20.C20</t>
+          <t xml:space="preserve">    L20.C19</t>
         </is>
       </c>
       <c r="B271" s="3" t="inlineStr">
         <is>
-          <t>L'ajustement aux frontières comme précédent</t>
+          <t>Le texte que la conformité invoque</t>
         </is>
       </c>
       <c r="C271" s="3" t="inlineStr">
@@ -25345,12 +25409,12 @@
     <row r="272">
       <c r="A272" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L20.C21</t>
+          <t xml:space="preserve">    L20.C20</t>
         </is>
       </c>
       <c r="B272" s="3" t="inlineStr">
         <is>
-          <t>La transparence et sa limite juridictionnelle</t>
+          <t>L'ajustement aux frontières comme précédent</t>
         </is>
       </c>
       <c r="C272" s="3" t="inlineStr">
@@ -25362,12 +25426,12 @@
     <row r="273">
       <c r="A273" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L20.C22</t>
+          <t xml:space="preserve">    L20.C21</t>
         </is>
       </c>
       <c r="B273" s="3" t="inlineStr">
         <is>
-          <t>Ce que le droit devrait devenir</t>
+          <t>La transparence et sa limite juridictionnelle</t>
         </is>
       </c>
       <c r="C273" s="3" t="inlineStr">
@@ -25379,63 +25443,63 @@
     <row r="274">
       <c r="A274" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">    L20.C22</t>
+        </is>
+      </c>
+      <c r="B274" s="3" t="inlineStr">
+        <is>
+          <t>Ce que le droit devrait devenir</t>
+        </is>
+      </c>
+      <c r="C274" s="3" t="inlineStr">
+        <is>
+          <t>brouillon</t>
+        </is>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">    L20.C23</t>
         </is>
       </c>
-      <c r="B274" s="3" t="inlineStr">
+      <c r="B275" s="3" t="inlineStr">
         <is>
           <t>La portée du livre</t>
         </is>
       </c>
-      <c r="C274" s="3" t="inlineStr">
-        <is>
-          <t>brouillon</t>
-        </is>
-      </c>
-    </row>
-    <row r="275">
-      <c r="A275" s="6" t="inlineStr">
+      <c r="C275" s="3" t="inlineStr">
+        <is>
+          <t>brouillon</t>
+        </is>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" s="6" t="inlineStr">
         <is>
           <t>L21</t>
         </is>
       </c>
-      <c r="B275" s="6" t="inlineStr">
+      <c r="B276" s="6" t="inlineStr">
         <is>
           <t>La plomberie financière mondiale</t>
         </is>
       </c>
-      <c r="C275" s="6" t="inlineStr">
+      <c r="C276" s="6" t="inlineStr">
         <is>
           <t>en-cours — 8 chapitre(s)</t>
-        </is>
-      </c>
-    </row>
-    <row r="276">
-      <c r="A276" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    L21.C01</t>
-        </is>
-      </c>
-      <c r="B276" s="3" t="inlineStr">
-        <is>
-          <t>Ce que ce livre doit établir, et le principe qui exige des fonds propres</t>
-        </is>
-      </c>
-      <c r="C276" s="3" t="inlineStr">
-        <is>
-          <t>brouillon</t>
         </is>
       </c>
     </row>
     <row r="277">
       <c r="A277" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L21.C02</t>
+          <t xml:space="preserve">    L21.C01</t>
         </is>
       </c>
       <c r="B277" s="3" t="inlineStr">
         <is>
-          <t>Comment l'unité circulerait vraiment, et ce que chaque étape exige</t>
+          <t>Ce que ce livre doit établir, et le principe qui exige des fonds propres</t>
         </is>
       </c>
       <c r="C277" s="3" t="inlineStr">
@@ -25447,12 +25511,12 @@
     <row r="278">
       <c r="A278" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L21.C03</t>
+          <t xml:space="preserve">    L21.C02</t>
         </is>
       </c>
       <c r="B278" s="3" t="inlineStr">
         <is>
-          <t>Une opération de bout en bout, bilan par bilan</t>
+          <t>Comment l'unité circulerait vraiment, et ce que chaque étape exige</t>
         </is>
       </c>
       <c r="C278" s="3" t="inlineStr">
@@ -25464,12 +25528,12 @@
     <row r="279">
       <c r="A279" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L21.C04</t>
+          <t xml:space="preserve">    L21.C03</t>
         </is>
       </c>
       <c r="B279" s="3" t="inlineStr">
         <is>
-          <t>Ce que l'émission coûte aux banques qui l'hébergent</t>
+          <t>Une opération de bout en bout, bilan par bilan</t>
         </is>
       </c>
       <c r="C279" s="3" t="inlineStr">
@@ -25481,12 +25545,12 @@
     <row r="280">
       <c r="A280" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L21.C05</t>
+          <t xml:space="preserve">    L21.C04</t>
         </is>
       </c>
       <c r="B280" s="3" t="inlineStr">
         <is>
-          <t>La première infrastructure ouverte, et ce qu'elle renverse</t>
+          <t>Ce que l'émission coûte aux banques qui l'hébergent</t>
         </is>
       </c>
       <c r="C280" s="3" t="inlineStr">
@@ -25498,12 +25562,12 @@
     <row r="281">
       <c r="A281" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L21.C06</t>
+          <t xml:space="preserve">    L21.C05</t>
         </is>
       </c>
       <c r="B281" s="3" t="inlineStr">
         <is>
-          <t>La jambe qui reste, et ce qu'il faut pour la protéger</t>
+          <t>La première infrastructure ouverte, et ce qu'elle renverse</t>
         </is>
       </c>
       <c r="C281" s="3" t="inlineStr">
@@ -25515,12 +25579,12 @@
     <row r="282">
       <c r="A282" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L21.C07</t>
+          <t xml:space="preserve">    L21.C06</t>
         </is>
       </c>
       <c r="B282" s="3" t="inlineStr">
         <is>
-          <t>Portée de la tranche</t>
+          <t>La jambe qui reste, et ce qu'il faut pour la protéger</t>
         </is>
       </c>
       <c r="C282" s="3" t="inlineStr">
@@ -25532,63 +25596,63 @@
     <row r="283">
       <c r="A283" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">    L21.C07</t>
+        </is>
+      </c>
+      <c r="B283" s="3" t="inlineStr">
+        <is>
+          <t>Portée de la tranche</t>
+        </is>
+      </c>
+      <c r="C283" s="3" t="inlineStr">
+        <is>
+          <t>brouillon</t>
+        </is>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">    L21.C08</t>
         </is>
       </c>
-      <c r="B283" s="3" t="inlineStr">
+      <c r="B284" s="3" t="inlineStr">
         <is>
           <t>La norme des infrastructures exige des fonds propres</t>
         </is>
       </c>
-      <c r="C283" s="3" t="inlineStr">
-        <is>
-          <t>brouillon</t>
-        </is>
-      </c>
-    </row>
-    <row r="284">
-      <c r="A284" s="6" t="inlineStr">
+      <c r="C284" s="3" t="inlineStr">
+        <is>
+          <t>brouillon</t>
+        </is>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" s="6" t="inlineStr">
         <is>
           <t>L22</t>
         </is>
       </c>
-      <c r="B284" s="6" t="inlineStr">
+      <c r="B285" s="6" t="inlineStr">
         <is>
           <t>Le pouvoir de la finance non bancaire</t>
         </is>
       </c>
-      <c r="C284" s="6" t="inlineStr">
+      <c r="C285" s="6" t="inlineStr">
         <is>
           <t>en-cours — 7 chapitre(s)</t>
-        </is>
-      </c>
-    </row>
-    <row r="285">
-      <c r="A285" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    L22.C01</t>
-        </is>
-      </c>
-      <c r="B285" s="3" t="inlineStr">
-        <is>
-          <t>Ce que ce livre doit établir</t>
-        </is>
-      </c>
-      <c r="C285" s="3" t="inlineStr">
-        <is>
-          <t>brouillon</t>
         </is>
       </c>
     </row>
     <row r="286">
       <c r="A286" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L22.C02</t>
+          <t xml:space="preserve">    L22.C01</t>
         </is>
       </c>
       <c r="B286" s="3" t="inlineStr">
         <is>
-          <t>Où va la monnaie émise, et pourquoi le reflux ne l'y suit pas</t>
+          <t>Ce que ce livre doit établir</t>
         </is>
       </c>
       <c r="C286" s="3" t="inlineStr">
@@ -25600,12 +25664,12 @@
     <row r="287">
       <c r="A287" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L22.C03</t>
+          <t xml:space="preserve">    L22.C02</t>
         </is>
       </c>
       <c r="B287" s="3" t="inlineStr">
         <is>
-          <t>Le barème existe déjà, et il a trois pièces que le corpus n'a pas</t>
+          <t>Où va la monnaie émise, et pourquoi le reflux ne l'y suit pas</t>
         </is>
       </c>
       <c r="C287" s="3" t="inlineStr">
@@ -25617,12 +25681,12 @@
     <row r="288">
       <c r="A288" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L22.C04</t>
+          <t xml:space="preserve">    L22.C03</t>
         </is>
       </c>
       <c r="B288" s="3" t="inlineStr">
         <is>
-          <t>Les critères réels ne mesurent pas, ils certifient</t>
+          <t>Le barème existe déjà, et il a trois pièces que le corpus n'a pas</t>
         </is>
       </c>
       <c r="C288" s="3" t="inlineStr">
@@ -25634,12 +25698,12 @@
     <row r="289">
       <c r="A289" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L22.C05</t>
+          <t xml:space="preserve">    L22.C04</t>
         </is>
       </c>
       <c r="B289" s="3" t="inlineStr">
         <is>
-          <t>L'épargne retraite, et le dilemme du troisième instrument</t>
+          <t>Les critères réels ne mesurent pas, ils certifient</t>
         </is>
       </c>
       <c r="C289" s="3" t="inlineStr">
@@ -25651,12 +25715,12 @@
     <row r="290">
       <c r="A290" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L22.C06</t>
+          <t xml:space="preserve">    L22.C05</t>
         </is>
       </c>
       <c r="B290" s="3" t="inlineStr">
         <is>
-          <t>Qui décide, quand personne ne décide</t>
+          <t>L'épargne retraite, et le dilemme du troisième instrument</t>
         </is>
       </c>
       <c r="C290" s="3" t="inlineStr">
@@ -25668,63 +25732,63 @@
     <row r="291">
       <c r="A291" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">    L22.C06</t>
+        </is>
+      </c>
+      <c r="B291" s="3" t="inlineStr">
+        <is>
+          <t>Qui décide, quand personne ne décide</t>
+        </is>
+      </c>
+      <c r="C291" s="3" t="inlineStr">
+        <is>
+          <t>brouillon</t>
+        </is>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">    L22.C07</t>
         </is>
       </c>
-      <c r="B291" s="3" t="inlineStr">
+      <c r="B292" s="3" t="inlineStr">
         <is>
           <t>Portée de la tranche</t>
         </is>
       </c>
-      <c r="C291" s="3" t="inlineStr">
-        <is>
-          <t>brouillon</t>
-        </is>
-      </c>
-    </row>
-    <row r="292">
-      <c r="A292" s="6" t="inlineStr">
+      <c r="C292" s="3" t="inlineStr">
+        <is>
+          <t>brouillon</t>
+        </is>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" s="6" t="inlineStr">
         <is>
           <t>L23</t>
         </is>
       </c>
-      <c r="B292" s="6" t="inlineStr">
+      <c r="B293" s="6" t="inlineStr">
         <is>
           <t>Fiscalité mondiale, finance offshore et opacité</t>
         </is>
       </c>
-      <c r="C292" s="6" t="inlineStr">
+      <c r="C293" s="6" t="inlineStr">
         <is>
           <t>en-cours — 7 chapitre(s)</t>
-        </is>
-      </c>
-    </row>
-    <row r="293">
-      <c r="A293" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    L23.C01</t>
-        </is>
-      </c>
-      <c r="B293" s="3" t="inlineStr">
-        <is>
-          <t>Ce que ce livre doit établir</t>
-        </is>
-      </c>
-      <c r="C293" s="3" t="inlineStr">
-        <is>
-          <t>brouillon</t>
         </is>
       </c>
     </row>
     <row r="294">
       <c r="A294" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L23.C02</t>
+          <t xml:space="preserve">    L23.C01</t>
         </is>
       </c>
       <c r="B294" s="3" t="inlineStr">
         <is>
-          <t>La compétence que la convention ne crée pas, et le vote qu'elle a gagné</t>
+          <t>Ce que ce livre doit établir</t>
         </is>
       </c>
       <c r="C294" s="3" t="inlineStr">
@@ -25736,12 +25800,12 @@
     <row r="295">
       <c r="A295" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L23.C03</t>
+          <t xml:space="preserve">    L23.C02</t>
         </is>
       </c>
       <c r="B295" s="3" t="inlineStr">
         <is>
-          <t>F8 appliqué à une négociation en cours, et le résultat n'est pas le désarmement</t>
+          <t>La compétence que la convention ne crée pas, et le vote qu'elle a gagné</t>
         </is>
       </c>
       <c r="C295" s="3" t="inlineStr">
@@ -25753,12 +25817,12 @@
     <row r="296">
       <c r="A296" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L23.C04</t>
+          <t xml:space="preserve">    L23.C03</t>
         </is>
       </c>
       <c r="B296" s="3" t="inlineStr">
         <is>
-          <t>La transparence que le corpus supposait a été invalidée</t>
+          <t>F8 appliqué à une négociation en cours, et le résultat n'est pas le désarmement</t>
         </is>
       </c>
       <c r="C296" s="3" t="inlineStr">
@@ -25770,12 +25834,12 @@
     <row r="297">
       <c r="A297" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L23.C05</t>
+          <t xml:space="preserve">    L23.C04</t>
         </is>
       </c>
       <c r="B297" s="3" t="inlineStr">
         <is>
-          <t>Intéresser le percepteur, et ce que le taux révèle</t>
+          <t>La transparence que le corpus supposait a été invalidée</t>
         </is>
       </c>
       <c r="C297" s="3" t="inlineStr">
@@ -25787,12 +25851,12 @@
     <row r="298">
       <c r="A298" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L23.C06</t>
+          <t xml:space="preserve">    L23.C05</t>
         </is>
       </c>
       <c r="B298" s="3" t="inlineStr">
         <is>
-          <t>L'arbre appliqué à la fonte, et il ne reste que deux branches</t>
+          <t>Intéresser le percepteur, et ce que le taux révèle</t>
         </is>
       </c>
       <c r="C298" s="3" t="inlineStr">
@@ -25804,63 +25868,63 @@
     <row r="299">
       <c r="A299" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">    L23.C06</t>
+        </is>
+      </c>
+      <c r="B299" s="3" t="inlineStr">
+        <is>
+          <t>L'arbre appliqué à la fonte, et il ne reste que deux branches</t>
+        </is>
+      </c>
+      <c r="C299" s="3" t="inlineStr">
+        <is>
+          <t>brouillon</t>
+        </is>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">    L23.C07</t>
         </is>
       </c>
-      <c r="B299" s="3" t="inlineStr">
+      <c r="B300" s="3" t="inlineStr">
         <is>
           <t>Portée de la tranche, et la moitié qui n'est pas commencée</t>
         </is>
       </c>
-      <c r="C299" s="3" t="inlineStr">
-        <is>
-          <t>brouillon</t>
-        </is>
-      </c>
-    </row>
-    <row r="300">
-      <c r="A300" s="6" t="inlineStr">
+      <c r="C300" s="3" t="inlineStr">
+        <is>
+          <t>brouillon</t>
+        </is>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" s="6" t="inlineStr">
         <is>
           <t>L24</t>
         </is>
       </c>
-      <c r="B300" s="6" t="inlineStr">
+      <c r="B301" s="6" t="inlineStr">
         <is>
           <t>Les conditions matérielles de la vie</t>
         </is>
       </c>
-      <c r="C300" s="6" t="inlineStr">
+      <c r="C301" s="6" t="inlineStr">
         <is>
           <t>en-cours — 5 chapitre(s)</t>
-        </is>
-      </c>
-    </row>
-    <row r="301">
-      <c r="A301" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    L24.C01</t>
-        </is>
-      </c>
-      <c r="B301" s="3" t="inlineStr">
-        <is>
-          <t>Ce que ce livre doit établir</t>
-        </is>
-      </c>
-      <c r="C301" s="3" t="inlineStr">
-        <is>
-          <t>brouillon</t>
         </is>
       </c>
     </row>
     <row r="302">
       <c r="A302" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L24.C02</t>
+          <t xml:space="preserve">    L24.C01</t>
         </is>
       </c>
       <c r="B302" s="3" t="inlineStr">
         <is>
-          <t>Le seuil juste est plus strict que le seuil sûr</t>
+          <t>Ce que ce livre doit établir</t>
         </is>
       </c>
       <c r="C302" s="3" t="inlineStr">
@@ -25872,12 +25936,12 @@
     <row r="303">
       <c r="A303" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L24.C03</t>
+          <t xml:space="preserve">    L24.C02</t>
         </is>
       </c>
       <c r="B303" s="3" t="inlineStr">
         <is>
-          <t>La matière, et le levier commun que les neuf dimensions n'avaient pas</t>
+          <t>Le seuil juste est plus strict que le seuil sûr</t>
         </is>
       </c>
       <c r="C303" s="3" t="inlineStr">
@@ -25889,12 +25953,12 @@
     <row r="304">
       <c r="A304" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L24.C04</t>
+          <t xml:space="preserve">    L24.C03</t>
         </is>
       </c>
       <c r="B304" s="3" t="inlineStr">
         <is>
-          <t>Un budget mondial n'est pas partageable</t>
+          <t>La matière, et le levier commun que les neuf dimensions n'avaient pas</t>
         </is>
       </c>
       <c r="C304" s="3" t="inlineStr">
@@ -25906,63 +25970,63 @@
     <row r="305">
       <c r="A305" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">    L24.C04</t>
+        </is>
+      </c>
+      <c r="B305" s="3" t="inlineStr">
+        <is>
+          <t>Un budget mondial n'est pas partageable</t>
+        </is>
+      </c>
+      <c r="C305" s="3" t="inlineStr">
+        <is>
+          <t>brouillon</t>
+        </is>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">    L24.C05</t>
         </is>
       </c>
-      <c r="B305" s="3" t="inlineStr">
+      <c r="B306" s="3" t="inlineStr">
         <is>
           <t>Portée de la tranche</t>
         </is>
       </c>
-      <c r="C305" s="3" t="inlineStr">
-        <is>
-          <t>brouillon</t>
-        </is>
-      </c>
-    </row>
-    <row r="306">
-      <c r="A306" s="6" t="inlineStr">
+      <c r="C306" s="3" t="inlineStr">
+        <is>
+          <t>brouillon</t>
+        </is>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" s="6" t="inlineStr">
         <is>
           <t>L25</t>
         </is>
       </c>
-      <c r="B306" s="6" t="inlineStr">
+      <c r="B307" s="6" t="inlineStr">
         <is>
           <t>Répartition, besoins essentiels et justice sociale</t>
         </is>
       </c>
-      <c r="C306" s="6" t="inlineStr">
+      <c r="C307" s="6" t="inlineStr">
         <is>
           <t>en-cours — 6 chapitre(s)</t>
-        </is>
-      </c>
-    </row>
-    <row r="307">
-      <c r="A307" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    L25.C01</t>
-        </is>
-      </c>
-      <c r="B307" s="3" t="inlineStr">
-        <is>
-          <t>Ce que ce livre doit établir</t>
-        </is>
-      </c>
-      <c r="C307" s="3" t="inlineStr">
-        <is>
-          <t>brouillon</t>
         </is>
       </c>
     </row>
     <row r="308">
       <c r="A308" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L25.C02</t>
+          <t xml:space="preserve">    L25.C01</t>
         </is>
       </c>
       <c r="B308" s="3" t="inlineStr">
         <is>
-          <t>Le noyau dur, et la charge de la preuve renversée</t>
+          <t>Ce que ce livre doit établir</t>
         </is>
       </c>
       <c r="C308" s="3" t="inlineStr">
@@ -25974,12 +26038,12 @@
     <row r="309">
       <c r="A309" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L25.C03</t>
+          <t xml:space="preserve">    L25.C02</t>
         </is>
       </c>
       <c r="B309" s="3" t="inlineStr">
         <is>
-          <t>Ce que le droit oblige à donner, et ce qu'il refuse de réparer</t>
+          <t>Le noyau dur, et la charge de la preuve renversée</t>
         </is>
       </c>
       <c r="C309" s="3" t="inlineStr">
@@ -25991,12 +26055,12 @@
     <row r="310">
       <c r="A310" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L25.C04</t>
+          <t xml:space="preserve">    L25.C03</t>
         </is>
       </c>
       <c r="B310" s="3" t="inlineStr">
         <is>
-          <t>A34 en droit positif, et le critère que le corpus n'avait pas</t>
+          <t>Ce que le droit oblige à donner, et ce qu'il refuse de réparer</t>
         </is>
       </c>
       <c r="C310" s="3" t="inlineStr">
@@ -26008,12 +26072,12 @@
     <row r="311">
       <c r="A311" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L25.C05</t>
+          <t xml:space="preserve">    L25.C04</t>
         </is>
       </c>
       <c r="B311" s="3" t="inlineStr">
         <is>
-          <t>Le droit différencie sans calculer</t>
+          <t>A34 en droit positif, et le critère que le corpus n'avait pas</t>
         </is>
       </c>
       <c r="C311" s="3" t="inlineStr">
@@ -26025,63 +26089,63 @@
     <row r="312">
       <c r="A312" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">    L25.C05</t>
+        </is>
+      </c>
+      <c r="B312" s="3" t="inlineStr">
+        <is>
+          <t>Le droit différencie sans calculer</t>
+        </is>
+      </c>
+      <c r="C312" s="3" t="inlineStr">
+        <is>
+          <t>brouillon</t>
+        </is>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">    L25.C06</t>
         </is>
       </c>
-      <c r="B312" s="3" t="inlineStr">
+      <c r="B313" s="3" t="inlineStr">
         <is>
           <t>Portée de la tranche</t>
         </is>
       </c>
-      <c r="C312" s="3" t="inlineStr">
-        <is>
-          <t>brouillon</t>
-        </is>
-      </c>
-    </row>
-    <row r="313">
-      <c r="A313" s="6" t="inlineStr">
+      <c r="C313" s="3" t="inlineStr">
+        <is>
+          <t>brouillon</t>
+        </is>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" s="6" t="inlineStr">
         <is>
           <t>L26</t>
         </is>
       </c>
-      <c r="B313" s="6" t="inlineStr">
+      <c r="B314" s="6" t="inlineStr">
         <is>
           <t>Thermodynamique, énergie et processus économique</t>
         </is>
       </c>
-      <c r="C313" s="6" t="inlineStr">
+      <c r="C314" s="6" t="inlineStr">
         <is>
           <t>en-cours — 10 chapitre(s)</t>
-        </is>
-      </c>
-    </row>
-    <row r="314">
-      <c r="A314" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    L26.C01</t>
-        </is>
-      </c>
-      <c r="B314" s="3" t="inlineStr">
-        <is>
-          <t>Ce que ce livre doit établir</t>
-        </is>
-      </c>
-      <c r="C314" s="3" t="inlineStr">
-        <is>
-          <t>brouillon</t>
         </is>
       </c>
     </row>
     <row r="315">
       <c r="A315" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L26.C02</t>
+          <t xml:space="preserve">    L26.C01</t>
         </is>
       </c>
       <c r="B315" s="3" t="inlineStr">
         <is>
-          <t>Le stock n'existe pas sous la forme demandée</t>
+          <t>Ce que ce livre doit établir</t>
         </is>
       </c>
       <c r="C315" s="3" t="inlineStr">
@@ -26093,12 +26157,12 @@
     <row r="316">
       <c r="A316" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L26.C03</t>
+          <t xml:space="preserve">    L26.C02</t>
         </is>
       </c>
       <c r="B316" s="3" t="inlineStr">
         <is>
-          <t>La frontière décide du chiffre</t>
+          <t>Le stock n'existe pas sous la forme demandée</t>
         </is>
       </c>
       <c r="C316" s="3" t="inlineStr">
@@ -26110,12 +26174,12 @@
     <row r="317">
       <c r="A317" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L26.C04</t>
+          <t xml:space="preserve">    L26.C03</t>
         </is>
       </c>
       <c r="B317" s="3" t="inlineStr">
         <is>
-          <t>L'effet rebond, et ce que le dispositif en hérite sans être une politique d'efficacité</t>
+          <t>La frontière décide du chiffre</t>
         </is>
       </c>
       <c r="C317" s="3" t="inlineStr">
@@ -26127,12 +26191,12 @@
     <row r="318">
       <c r="A318" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L26.C05</t>
+          <t xml:space="preserve">    L26.C04</t>
         </is>
       </c>
       <c r="B318" s="3" t="inlineStr">
         <is>
-          <t>L'addition n'est pas la substitution</t>
+          <t>L'effet rebond, et ce que le dispositif en hérite sans être une politique d'efficacité</t>
         </is>
       </c>
       <c r="C318" s="3" t="inlineStr">
@@ -26144,12 +26208,12 @@
     <row r="319">
       <c r="A319" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L26.C06</t>
+          <t xml:space="preserve">    L26.C05</t>
         </is>
       </c>
       <c r="B319" s="3" t="inlineStr">
         <is>
-          <t>Portée de la tranche</t>
+          <t>L'addition n'est pas la substitution</t>
         </is>
       </c>
       <c r="C319" s="3" t="inlineStr">
@@ -26161,12 +26225,12 @@
     <row r="320">
       <c r="A320" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L26.C07</t>
+          <t xml:space="preserve">    L26.C06</t>
         </is>
       </c>
       <c r="B320" s="3" t="inlineStr">
         <is>
-          <t>Le fondateur ne propose aucun instrument monétaire</t>
+          <t>Portée de la tranche</t>
         </is>
       </c>
       <c r="C320" s="3" t="inlineStr">
@@ -26178,12 +26242,12 @@
     <row r="321">
       <c r="A321" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L26.C08</t>
+          <t xml:space="preserve">    L26.C07</t>
         </is>
       </c>
       <c r="B321" s="3" t="inlineStr">
         <is>
-          <t>Même un puits gratuit ne donne pas dix</t>
+          <t>Le fondateur ne propose aucun instrument monétaire</t>
         </is>
       </c>
       <c r="C321" s="3" t="inlineStr">
@@ -26195,12 +26259,12 @@
     <row r="322">
       <c r="A322" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    L26.C09</t>
+          <t xml:space="preserve">    L26.C08</t>
         </is>
       </c>
       <c r="B322" s="3" t="inlineStr">
         <is>
-          <t>La méthode décide du chiffre</t>
+          <t>Même un puits gratuit ne donne pas dix</t>
         </is>
       </c>
       <c r="C322" s="3" t="inlineStr">
@@ -26212,15 +26276,32 @@
     <row r="323">
       <c r="A323" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">    L26.C09</t>
+        </is>
+      </c>
+      <c r="B323" s="3" t="inlineStr">
+        <is>
+          <t>La méthode décide du chiffre</t>
+        </is>
+      </c>
+      <c r="C323" s="3" t="inlineStr">
+        <is>
+          <t>brouillon</t>
+        </is>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">    L26.C10</t>
         </is>
       </c>
-      <c r="B323" s="3" t="inlineStr">
+      <c r="B324" s="3" t="inlineStr">
         <is>
           <t>La financiarisation produit un découplage apparent</t>
         </is>
       </c>
-      <c r="C323" s="3" t="inlineStr">
+      <c r="C324" s="3" t="inlineStr">
         <is>
           <t>brouillon</t>
         </is>

--- a/plan-des-livres.xlsx
+++ b/plan-des-livres.xlsx
@@ -13,7 +13,7 @@
     <sheet name="Plan par livre" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Chapitres'!$A$1:$N$297</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Chapitres'!$A$1:$N$298</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -1326,7 +1326,7 @@
         </is>
       </c>
       <c r="F21" s="5" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G21" s="5" t="inlineStr"/>
       <c r="H21" s="5" t="inlineStr">
@@ -1638,7 +1638,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N297"/>
+  <dimension ref="A1:N298"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -15803,7 +15803,7 @@
         <v>1</v>
       </c>
       <c r="K223" s="3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L223" s="3" t="inlineStr">
         <is>
@@ -15812,7 +15812,7 @@
       </c>
       <c r="M223" s="3" t="inlineStr">
         <is>
-          <t>L1.C15, L11.C13, L13.C01, L17.C05, L18.C01, L18.C04, L18.C09, L22.C04, L24.C05, L26.C10, L18.C11</t>
+          <t>L1.C15, L11.C13, L13.C01, L17.C05, L18.C01, L18.C04, L18.C09, L22.C04, L24.C05, L26.C10, L18.C11, L19.C08</t>
         </is>
       </c>
       <c r="N223" s="3" t="inlineStr">
@@ -15931,7 +15931,7 @@
         <v>2</v>
       </c>
       <c r="K225" s="3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L225" s="3" t="inlineStr">
         <is>
@@ -15940,7 +15940,7 @@
       </c>
       <c r="M225" s="3" t="inlineStr">
         <is>
-          <t>L1.C07, L10.C01, L10.C06, L11.C01, L11.C02, L18.C06, L21.C01, L21.C03, L16.C04</t>
+          <t>L1.C07, L10.C01, L10.C06, L11.C01, L11.C02, L18.C06, L21.C01, L21.C03, L16.C04, L19.C08</t>
         </is>
       </c>
       <c r="N225" s="3" t="inlineStr">
@@ -16059,7 +16059,7 @@
         <v>2</v>
       </c>
       <c r="K227" s="3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L227" s="3" t="inlineStr">
         <is>
@@ -16068,7 +16068,7 @@
       </c>
       <c r="M227" s="3" t="inlineStr">
         <is>
-          <t>L10.C06, L11.C01, L11.C02, L11.C05, L11.C07, L11.C27, L19.C01, L19.C02, L21.C01</t>
+          <t>L10.C06, L11.C01, L11.C02, L11.C05, L11.C07, L11.C27, L19.C01, L19.C02, L21.C01, L19.C08</t>
         </is>
       </c>
       <c r="N227" s="3" t="inlineStr">
@@ -16336,17 +16336,17 @@
     <row r="232">
       <c r="A232" s="2" t="inlineStr">
         <is>
-          <t>L20.C01</t>
+          <t>L19.C08</t>
         </is>
       </c>
       <c r="B232" s="3" t="inlineStr">
         <is>
-          <t>L20</t>
+          <t>L19</t>
         </is>
       </c>
       <c r="C232" s="3" t="inlineStr">
         <is>
-          <t>Ce que ce livre doit établir</t>
+          <t>Payer sans passif, c'est troquer</t>
         </is>
       </c>
       <c r="D232" s="3" t="inlineStr">
@@ -16366,41 +16366,41 @@
       </c>
       <c r="G232" s="3" t="inlineStr">
         <is>
-          <t>conception</t>
+          <t>hybride</t>
         </is>
       </c>
       <c r="H232" s="3" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="I232" s="3" t="inlineStr"/>
       <c r="J232" s="3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K232" s="3" t="n">
         <v>3</v>
       </c>
       <c r="L232" s="3" t="inlineStr">
         <is>
-          <t>fenetre_de_reforme, referentiel_de_change, communs, limites_planetaires, creation_monetaire</t>
+          <t>creation_monetaire, contrepartie_comptable, monnaie_comme_registre</t>
         </is>
       </c>
       <c r="M232" s="3" t="inlineStr">
         <is>
-          <t>L1.C18, L1.C25, L1.C27, L7.C01, L7.C03, L7.C13, L7.C17, L7.C21, L11.C24</t>
+          <t>L11.C01, L16.C04, L18.C10, L19.C01, L19.C02, L19.C03, L19.C07, L21.C08, L26.C10</t>
         </is>
       </c>
       <c r="N232" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-20-droit-international-monetaire-et-commercial/c01-ce-que-ce-livre-doit-etablir.md</t>
+          <t>corpus/livre-19-comptabilite-monetaire-de-l-emission-sans-dette/c08-payer-sans-passif-c-est-troquer.md</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" s="2" t="inlineStr">
         <is>
-          <t>L20.C02</t>
+          <t>L20.C01</t>
         </is>
       </c>
       <c r="B233" s="3" t="inlineStr">
@@ -16410,7 +16410,7 @@
       </c>
       <c r="C233" s="3" t="inlineStr">
         <is>
-          <t>L'interdiction du financement monétaire</t>
+          <t>Ce que ce livre doit établir</t>
         </is>
       </c>
       <c r="D233" s="3" t="inlineStr">
@@ -16447,24 +16447,24 @@
       </c>
       <c r="L233" s="3" t="inlineStr">
         <is>
-          <t>creation_monetaire, contrepartie_comptable, reflux_collectif, fenetre_de_reforme</t>
+          <t>fenetre_de_reforme, referentiel_de_change, communs, limites_planetaires, creation_monetaire</t>
         </is>
       </c>
       <c r="M233" s="3" t="inlineStr">
         <is>
-          <t>L1.C05, L1.C18, L1.C20, L1.C22, L7.C11, L7.C13, L11.C10, L20.C01</t>
+          <t>L1.C18, L1.C25, L1.C27, L7.C01, L7.C03, L7.C13, L7.C17, L7.C21, L11.C24</t>
         </is>
       </c>
       <c r="N233" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-20-droit-international-monetaire-et-commercial/c02-l-interdiction-du-financement-monetaire.md</t>
+          <t>corpus/livre-20-droit-international-monetaire-et-commercial/c01-ce-que-ce-livre-doit-etablir.md</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" s="2" t="inlineStr">
         <is>
-          <t>L20.C03</t>
+          <t>L20.C02</t>
         </is>
       </c>
       <c r="B234" s="3" t="inlineStr">
@@ -16474,7 +16474,7 @@
       </c>
       <c r="C234" s="3" t="inlineStr">
         <is>
-          <t>L'objectif principal et ce qu'il exclut</t>
+          <t>L'interdiction du financement monétaire</t>
         </is>
       </c>
       <c r="D234" s="3" t="inlineStr">
@@ -16511,24 +16511,24 @@
       </c>
       <c r="L234" s="3" t="inlineStr">
         <is>
-          <t>regle_contre_discretion, limites_planetaires, creation_monetaire, plafond_ecologique</t>
+          <t>creation_monetaire, contrepartie_comptable, reflux_collectif, fenetre_de_reforme</t>
         </is>
       </c>
       <c r="M234" s="3" t="inlineStr">
         <is>
-          <t>L1.C01, L1.C18, L1.C20, L7.C03, L8.C12, L8.C34, L11.C16, L20.C01, L20.C02</t>
+          <t>L1.C05, L1.C18, L1.C20, L1.C22, L7.C11, L7.C13, L11.C10, L20.C01</t>
         </is>
       </c>
       <c r="N234" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-20-droit-international-monetaire-et-commercial/c03-l-objectif-principal-et-ce-qu-il-exclut.md</t>
+          <t>corpus/livre-20-droit-international-monetaire-et-commercial/c02-l-interdiction-du-financement-monetaire.md</t>
         </is>
       </c>
     </row>
     <row r="235">
       <c r="A235" s="2" t="inlineStr">
         <is>
-          <t>L20.C04</t>
+          <t>L20.C03</t>
         </is>
       </c>
       <c r="B235" s="3" t="inlineStr">
@@ -16538,7 +16538,7 @@
       </c>
       <c r="C235" s="3" t="inlineStr">
         <is>
-          <t>L'indépendance, et à l'égard de qui</t>
+          <t>L'objectif principal et ce qu'il exclut</t>
         </is>
       </c>
       <c r="D235" s="3" t="inlineStr">
@@ -16563,7 +16563,7 @@
       </c>
       <c r="H235" s="3" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="I235" s="3" t="inlineStr"/>
@@ -16575,24 +16575,24 @@
       </c>
       <c r="L235" s="3" t="inlineStr">
         <is>
-          <t>regle_contre_discretion, creation_monetaire, fenetre_de_reforme</t>
+          <t>regle_contre_discretion, limites_planetaires, creation_monetaire, plafond_ecologique</t>
         </is>
       </c>
       <c r="M235" s="3" t="inlineStr">
         <is>
-          <t>L1.C18, L7.C04, L7.C07, L7.C10, L8.C31, L11.C17, L20.C01, L20.C03, L20.C11</t>
+          <t>L1.C01, L1.C18, L1.C20, L7.C03, L8.C12, L8.C34, L11.C16, L20.C01, L20.C02</t>
         </is>
       </c>
       <c r="N235" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-20-droit-international-monetaire-et-commercial/c04-l-independance-et-a-l-egard-de-qui.md</t>
+          <t>corpus/livre-20-droit-international-monetaire-et-commercial/c03-l-objectif-principal-et-ce-qu-il-exclut.md</t>
         </is>
       </c>
     </row>
     <row r="236">
       <c r="A236" s="2" t="inlineStr">
         <is>
-          <t>L20.C05</t>
+          <t>L20.C04</t>
         </is>
       </c>
       <c r="B236" s="3" t="inlineStr">
@@ -16602,7 +16602,7 @@
       </c>
       <c r="C236" s="3" t="inlineStr">
         <is>
-          <t>Le monopole d'émission et le cours légal</t>
+          <t>L'indépendance, et à l'égard de qui</t>
         </is>
       </c>
       <c r="D236" s="3" t="inlineStr">
@@ -16639,24 +16639,24 @@
       </c>
       <c r="L236" s="3" t="inlineStr">
         <is>
-          <t>monnaie_comme_registre, creation_monetaire, referentiel_de_change, hierarchie_monetaire</t>
+          <t>regle_contre_discretion, creation_monetaire, fenetre_de_reforme</t>
         </is>
       </c>
       <c r="M236" s="3" t="inlineStr">
         <is>
-          <t>L1.C05, L1.C07, L1.C26, L7.C15, L11.C15, L20.C01, L20.C02, L20.C03</t>
+          <t>L1.C18, L7.C04, L7.C07, L7.C10, L8.C31, L11.C17, L20.C01, L20.C03, L20.C11</t>
         </is>
       </c>
       <c r="N236" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-20-droit-international-monetaire-et-commercial/c05-le-monopole-d-emission-et-le-cours-legal.md</t>
+          <t>corpus/livre-20-droit-international-monetaire-et-commercial/c04-l-independance-et-a-l-egard-de-qui.md</t>
         </is>
       </c>
     </row>
     <row r="237">
       <c r="A237" s="2" t="inlineStr">
         <is>
-          <t>L20.C06</t>
+          <t>L20.C05</t>
         </is>
       </c>
       <c r="B237" s="3" t="inlineStr">
@@ -16666,7 +16666,7 @@
       </c>
       <c r="C237" s="3" t="inlineStr">
         <is>
-          <t>Les voies de révision et leur coût</t>
+          <t>Le monopole d'émission et le cours légal</t>
         </is>
       </c>
       <c r="D237" s="3" t="inlineStr">
@@ -16696,31 +16696,31 @@
       </c>
       <c r="I237" s="3" t="inlineStr"/>
       <c r="J237" s="3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K237" s="3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L237" s="3" t="inlineStr">
         <is>
-          <t>fenetre_de_reforme, regle_contre_discretion, creation_monetaire</t>
+          <t>monnaie_comme_registre, creation_monetaire, referentiel_de_change, hierarchie_monetaire</t>
         </is>
       </c>
       <c r="M237" s="3" t="inlineStr">
         <is>
-          <t>L1.C18, L7.C12, L7.C20, L7.C21, L11.C15, L20.C01, L20.C02, L20.C03, L20.C07, L20.C09, L20.C18</t>
+          <t>L1.C05, L1.C07, L1.C26, L7.C15, L11.C15, L20.C01, L20.C02, L20.C03</t>
         </is>
       </c>
       <c r="N237" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-20-droit-international-monetaire-et-commercial/c06-les-voies-de-revision-et-leur-cout.md</t>
+          <t>corpus/livre-20-droit-international-monetaire-et-commercial/c05-le-monopole-d-emission-et-le-cours-legal.md</t>
         </is>
       </c>
     </row>
     <row r="238">
       <c r="A238" s="2" t="inlineStr">
         <is>
-          <t>L20.C07</t>
+          <t>L20.C06</t>
         </is>
       </c>
       <c r="B238" s="3" t="inlineStr">
@@ -16730,7 +16730,7 @@
       </c>
       <c r="C238" s="3" t="inlineStr">
         <is>
-          <t>L'accord monétaire international</t>
+          <t>Les voies de révision et leur coût</t>
         </is>
       </c>
       <c r="D238" s="3" t="inlineStr">
@@ -16760,31 +16760,31 @@
       </c>
       <c r="I238" s="3" t="inlineStr"/>
       <c r="J238" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K238" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L238" s="3" t="inlineStr">
         <is>
-          <t>referentiel_de_change, fenetre_de_reforme, etalon_de_change_or, hierarchie_monetaire</t>
+          <t>fenetre_de_reforme, regle_contre_discretion, creation_monetaire</t>
         </is>
       </c>
       <c r="M238" s="3" t="inlineStr">
         <is>
-          <t>L1.C18, L1.C26, L7.C02, L7.C05, L7.C12, L7.C13, L11.C15, L20.C01, L20.C03, L20.C06, L20.C10</t>
+          <t>L1.C18, L7.C12, L7.C20, L7.C21, L11.C15, L20.C01, L20.C02, L20.C03, L20.C07, L20.C09, L20.C18</t>
         </is>
       </c>
       <c r="N238" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-20-droit-international-monetaire-et-commercial/c07-l-accord-monetaire-international.md</t>
+          <t>corpus/livre-20-droit-international-monetaire-et-commercial/c06-les-voies-de-revision-et-leur-cout.md</t>
         </is>
       </c>
     </row>
     <row r="239">
       <c r="A239" s="2" t="inlineStr">
         <is>
-          <t>L20.C08</t>
+          <t>L20.C07</t>
         </is>
       </c>
       <c r="B239" s="3" t="inlineStr">
@@ -16794,7 +16794,7 @@
       </c>
       <c r="C239" s="3" t="inlineStr">
         <is>
-          <t>La parité inscrite dans le traité</t>
+          <t>L'accord monétaire international</t>
         </is>
       </c>
       <c r="D239" s="3" t="inlineStr">
@@ -16819,36 +16819,36 @@
       </c>
       <c r="H239" s="3" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="I239" s="3" t="inlineStr"/>
       <c r="J239" s="3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K239" s="3" t="n">
         <v>3</v>
       </c>
       <c r="L239" s="3" t="inlineStr">
         <is>
-          <t>referentiel_de_change, etalon_de_change_or, hierarchie_monetaire, bareme, devise_cle</t>
+          <t>referentiel_de_change, fenetre_de_reforme, etalon_de_change_or, hierarchie_monetaire</t>
         </is>
       </c>
       <c r="M239" s="3" t="inlineStr">
         <is>
-          <t>L1.C25, L1.C26, L1.C28, L7.C02, L7.C20, L11.C15, L11.C17, L20.C01, L20.C09, L20.C13</t>
+          <t>L1.C18, L1.C26, L7.C02, L7.C05, L7.C12, L7.C13, L11.C15, L20.C01, L20.C03, L20.C06, L20.C10</t>
         </is>
       </c>
       <c r="N239" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-20-droit-international-monetaire-et-commercial/c08-la-parite-inscrite-dans-le-traite.md</t>
+          <t>corpus/livre-20-droit-international-monetaire-et-commercial/c07-l-accord-monetaire-international.md</t>
         </is>
       </c>
     </row>
     <row r="240">
       <c r="A240" s="2" t="inlineStr">
         <is>
-          <t>L20.C09</t>
+          <t>L20.C08</t>
         </is>
       </c>
       <c r="B240" s="3" t="inlineStr">
@@ -16858,7 +16858,7 @@
       </c>
       <c r="C240" s="3" t="inlineStr">
         <is>
-          <t>L'amendement des statuts du Fonds</t>
+          <t>La parité inscrite dans le traité</t>
         </is>
       </c>
       <c r="D240" s="3" t="inlineStr">
@@ -16883,36 +16883,36 @@
       </c>
       <c r="H240" s="3" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="I240" s="3" t="inlineStr"/>
       <c r="J240" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K240" s="3" t="n">
         <v>3</v>
       </c>
       <c r="L240" s="3" t="inlineStr">
         <is>
-          <t>fenetre_de_reforme, referentiel_de_change, bareme, regle_contre_discretion</t>
+          <t>referentiel_de_change, etalon_de_change_or, hierarchie_monetaire, bareme, devise_cle</t>
         </is>
       </c>
       <c r="M240" s="3" t="inlineStr">
         <is>
-          <t>L7.C06, L7.C09, L7.C16, L7.C20, L11.C15, L11.C20, L20.C01, L20.C06, L20.C08, L20.C10, L20.C13</t>
+          <t>L1.C25, L1.C26, L1.C28, L7.C02, L7.C20, L11.C15, L11.C17, L20.C01, L20.C09, L20.C13</t>
         </is>
       </c>
       <c r="N240" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-20-droit-international-monetaire-et-commercial/c09-l-amendement-des-statuts-du-fonds.md</t>
+          <t>corpus/livre-20-droit-international-monetaire-et-commercial/c08-la-parite-inscrite-dans-le-traite.md</t>
         </is>
       </c>
     </row>
     <row r="241">
       <c r="A241" s="2" t="inlineStr">
         <is>
-          <t>L20.C10</t>
+          <t>L20.C09</t>
         </is>
       </c>
       <c r="B241" s="3" t="inlineStr">
@@ -16922,7 +16922,7 @@
       </c>
       <c r="C241" s="3" t="inlineStr">
         <is>
-          <t>Le vote pondéré et les voix de base</t>
+          <t>L'amendement des statuts du Fonds</t>
         </is>
       </c>
       <c r="D241" s="3" t="inlineStr">
@@ -16959,24 +16959,24 @@
       </c>
       <c r="L241" s="3" t="inlineStr">
         <is>
-          <t>bareme, devise_cle, hierarchie_monetaire, referentiel_de_change</t>
+          <t>fenetre_de_reforme, referentiel_de_change, bareme, regle_contre_discretion</t>
         </is>
       </c>
       <c r="M241" s="3" t="inlineStr">
         <is>
-          <t>L1.C25, L7.C02, L7.C05, L7.C06, L7.C09, L7.C10, L11.C16, L20.C01, L20.C07, L20.C09, L20.C12</t>
+          <t>L7.C06, L7.C09, L7.C16, L7.C20, L11.C15, L11.C20, L20.C01, L20.C06, L20.C08, L20.C10, L20.C13</t>
         </is>
       </c>
       <c r="N241" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-20-droit-international-monetaire-et-commercial/c10-le-vote-pondere-et-les-voix-de-base.md</t>
+          <t>corpus/livre-20-droit-international-monetaire-et-commercial/c09-l-amendement-des-statuts-du-fonds.md</t>
         </is>
       </c>
     </row>
     <row r="242">
       <c r="A242" s="2" t="inlineStr">
         <is>
-          <t>L20.C11</t>
+          <t>L20.C10</t>
         </is>
       </c>
       <c r="B242" s="3" t="inlineStr">
@@ -16986,7 +16986,7 @@
       </c>
       <c r="C242" s="3" t="inlineStr">
         <is>
-          <t>La personnalité juridique et les immunités</t>
+          <t>Le vote pondéré et les voix de base</t>
         </is>
       </c>
       <c r="D242" s="3" t="inlineStr">
@@ -17016,31 +17016,31 @@
       </c>
       <c r="I242" s="3" t="inlineStr"/>
       <c r="J242" s="3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K242" s="3" t="n">
         <v>3</v>
       </c>
       <c r="L242" s="3" t="inlineStr">
         <is>
-          <t>communs, creation_monetaire, fenetre_de_reforme, robustesse</t>
+          <t>bareme, devise_cle, hierarchie_monetaire, referentiel_de_change</t>
         </is>
       </c>
       <c r="M242" s="3" t="inlineStr">
         <is>
-          <t>L7.C01, L7.C03, L7.C07, L7.C10, L7.C13, L11.C25, L20.C01, L20.C04, L20.C12, L20.C14</t>
+          <t>L1.C25, L7.C02, L7.C05, L7.C06, L7.C09, L7.C10, L11.C16, L20.C01, L20.C07, L20.C09, L20.C12</t>
         </is>
       </c>
       <c r="N242" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-20-droit-international-monetaire-et-commercial/c11-la-personnalite-juridique-et-les-immunites.md</t>
+          <t>corpus/livre-20-droit-international-monetaire-et-commercial/c10-le-vote-pondere-et-les-voix-de-base.md</t>
         </is>
       </c>
     </row>
     <row r="243">
       <c r="A243" s="2" t="inlineStr">
         <is>
-          <t>L20.C12</t>
+          <t>L20.C11</t>
         </is>
       </c>
       <c r="B243" s="3" t="inlineStr">
@@ -17050,7 +17050,7 @@
       </c>
       <c r="C243" s="3" t="inlineStr">
         <is>
-          <t>Les pouvoirs non délégables</t>
+          <t>La personnalité juridique et les immunités</t>
         </is>
       </c>
       <c r="D243" s="3" t="inlineStr">
@@ -17075,36 +17075,36 @@
       </c>
       <c r="H243" s="3" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="I243" s="3" t="inlineStr"/>
       <c r="J243" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K243" s="3" t="n">
         <v>3</v>
       </c>
       <c r="L243" s="3" t="inlineStr">
         <is>
-          <t>bareme, valorisation_des_communs, polycentricite, robustesse</t>
+          <t>communs, creation_monetaire, fenetre_de_reforme, robustesse</t>
         </is>
       </c>
       <c r="M243" s="3" t="inlineStr">
         <is>
-          <t>L7.C05, L7.C06, L7.C07, L7.C11, L7.C14, L11.C16, L11.C20, L20.C01, L20.C09, L20.C10, L20.C14</t>
+          <t>L7.C01, L7.C03, L7.C07, L7.C10, L7.C13, L11.C25, L20.C01, L20.C04, L20.C12, L20.C14</t>
         </is>
       </c>
       <c r="N243" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-20-droit-international-monetaire-et-commercial/c12-les-pouvoirs-non-delegables.md</t>
+          <t>corpus/livre-20-droit-international-monetaire-et-commercial/c11-la-personnalite-juridique-et-les-immunites.md</t>
         </is>
       </c>
     </row>
     <row r="244">
       <c r="A244" s="2" t="inlineStr">
         <is>
-          <t>L20.C13</t>
+          <t>L20.C12</t>
         </is>
       </c>
       <c r="B244" s="3" t="inlineStr">
@@ -17114,7 +17114,7 @@
       </c>
       <c r="C244" s="3" t="inlineStr">
         <is>
-          <t>L'entrée en vigueur, l'adhésion et le retrait</t>
+          <t>Les pouvoirs non délégables</t>
         </is>
       </c>
       <c r="D244" s="3" t="inlineStr">
@@ -17144,31 +17144,31 @@
       </c>
       <c r="I244" s="3" t="inlineStr"/>
       <c r="J244" s="3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K244" s="3" t="n">
         <v>3</v>
       </c>
       <c r="L244" s="3" t="inlineStr">
         <is>
-          <t>seuil_d_activation, reflux_collectif, fenetre_de_reforme, additionnalite</t>
+          <t>bareme, valorisation_des_communs, polycentricite, robustesse</t>
         </is>
       </c>
       <c r="M244" s="3" t="inlineStr">
         <is>
-          <t>L7.C11, L7.C12, L7.C16, L7.C17, L7.C19, L11.C18, L20.C01, L20.C06, L20.C09, L20.C12</t>
+          <t>L7.C05, L7.C06, L7.C07, L7.C11, L7.C14, L11.C16, L11.C20, L20.C01, L20.C09, L20.C10, L20.C14</t>
         </is>
       </c>
       <c r="N244" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-20-droit-international-monetaire-et-commercial/c13-l-entree-en-vigueur-l-adhesion-et-le-retrait.md</t>
+          <t>corpus/livre-20-droit-international-monetaire-et-commercial/c12-les-pouvoirs-non-delegables.md</t>
         </is>
       </c>
     </row>
     <row r="245">
       <c r="A245" s="2" t="inlineStr">
         <is>
-          <t>L20.C14</t>
+          <t>L20.C13</t>
         </is>
       </c>
       <c r="B245" s="3" t="inlineStr">
@@ -17178,7 +17178,7 @@
       </c>
       <c r="C245" s="3" t="inlineStr">
         <is>
-          <t>Qui interprète le traité</t>
+          <t>L'entrée en vigueur, l'adhésion et le retrait</t>
         </is>
       </c>
       <c r="D245" s="3" t="inlineStr">
@@ -17208,31 +17208,31 @@
       </c>
       <c r="I245" s="3" t="inlineStr"/>
       <c r="J245" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K245" s="3" t="n">
         <v>3</v>
       </c>
       <c r="L245" s="3" t="inlineStr">
         <is>
-          <t>robustesse, regle_contre_discretion, communs</t>
+          <t>seuil_d_activation, reflux_collectif, fenetre_de_reforme, additionnalite</t>
         </is>
       </c>
       <c r="M245" s="3" t="inlineStr">
         <is>
-          <t>L7.C07, L7.C13, L7.C14, L7.C19, L11.C19, L11.C25, L20.C01, L20.C03, L20.C11, L20.C12, L20.C21</t>
+          <t>L7.C11, L7.C12, L7.C16, L7.C17, L7.C19, L11.C18, L20.C01, L20.C06, L20.C09, L20.C12</t>
         </is>
       </c>
       <c r="N245" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-20-droit-international-monetaire-et-commercial/c14-qui-interprete-le-traite.md</t>
+          <t>corpus/livre-20-droit-international-monetaire-et-commercial/c13-l-entree-en-vigueur-l-adhesion-et-le-retrait.md</t>
         </is>
       </c>
     </row>
     <row r="246">
       <c r="A246" s="2" t="inlineStr">
         <is>
-          <t>L20.C15</t>
+          <t>L20.C14</t>
         </is>
       </c>
       <c r="B246" s="3" t="inlineStr">
@@ -17242,7 +17242,7 @@
       </c>
       <c r="C246" s="3" t="inlineStr">
         <is>
-          <t>Le devoir international des agents</t>
+          <t>Qui interprète le traité</t>
         </is>
       </c>
       <c r="D246" s="3" t="inlineStr">
@@ -17267,36 +17267,36 @@
       </c>
       <c r="H246" s="3" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="I246" s="3" t="inlineStr"/>
       <c r="J246" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K246" s="3" t="n">
         <v>3</v>
       </c>
       <c r="L246" s="3" t="inlineStr">
         <is>
-          <t>robustesse, regle_contre_discretion, indicateur_de_progres</t>
+          <t>robustesse, regle_contre_discretion, communs</t>
         </is>
       </c>
       <c r="M246" s="3" t="inlineStr">
         <is>
-          <t>L7.C04, L7.C07, L7.C10, L11.C21, L11.C25, L20.C01, L20.C04, L20.C11, L20.C14</t>
+          <t>L7.C07, L7.C13, L7.C14, L7.C19, L11.C19, L11.C25, L20.C01, L20.C03, L20.C11, L20.C12, L20.C21</t>
         </is>
       </c>
       <c r="N246" s="3" t="inlineStr">
         <is>
-          <t>corpus/livre-20-droit-international-monetaire-et-commercial/c15-le-devoir-international-des-agents.md</t>
+          <t>corpus/livre-20-droit-international-monetaire-et-commercial/c14-qui-interprete-le-traite.md</t>
         </is>
       </c>
     </row>
     <row r="247">
       <c r="A247" s="2" t="inlineStr">
         <is>
-          <t>L20.C16</t>
+          <t>L20.C15</t>
         </is>
       </c>
       <c r="B247" s="3" t="inlineStr">
@@ -17306,7 +17306,7 @@
       </c>
       <c r="C247" s="3" t="inlineStr">
         <is>
-          <t>Le patrimoine commun de l'humanité</t>
+          <t>Le devoir international des agents</t>
         </is>
       </c>
       <c r="D247" s="3" t="inlineStr">
@@ -17331,36 +17331,36 @@
       </c>
       <c r="H247" s="3" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="I247" s="3" t="inlineStr"/>
       <c r="J247" s="3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K247" s="3" t="n">
         <v>3</v>
       </c>
       <c r="L247" s="3" t="inlineStr">
         <is>
-          <t>communs, valorisation_des_communs, limites_planetaires, 